--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$D$355]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$D$367]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="1147">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -3197,6 +3197,111 @@
   </si>
   <si>
     <t xml:space="preserve">Collector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.HighCard.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하이 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.Pair.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">페어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.TwoPair.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">투 페어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two Pair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.ThreeOfAKind.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트리플</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three of a Kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.Straight.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스트레이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.Flush.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플러시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.FullHouse.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">풀 하우스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.FourOfAKind.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four of a Kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.StraightFlush.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스트레이트 플러시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight Flush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.FiveOfAKind.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파이브 오브 어 카인드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five of a Kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.FlushHouse.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플러시 하우스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flush House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand.FlushFive.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플러시 파이브</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -3552,12 +3657,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D355"/>
+  <dimension ref="A1:D367"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
     <col min="2" max="2" width="49.21875" customWidth="1"/>
-    <col min="3" max="3" width="12.890625" customWidth="1"/>
+    <col min="3" max="3" width="16.40625" customWidth="1"/>
     <col min="4" max="4" width="25.78125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7474,8 +7579,140 @@
         <v>1059</v>
       </c>
     </row>
+    <row r="356">
+      <c r="B356" s="6" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D356" s="6" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" s="5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D357" s="5" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" s="6" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D358" s="6" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D359" s="5" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D361" s="5" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D362" s="6" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D363" s="5" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D364" s="6" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C365" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D365" s="5" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D366" s="6" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" s="5" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C367" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D367" s="5" t="s">
+        <v>1028</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:D355"/>
+  <autoFilter ref="B2:D367"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7494,10 +7731,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1060</v>
+        <v>1095</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1061</v>
+        <v>1096</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -7508,16 +7745,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1062</v>
+        <v>1097</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1063</v>
+        <v>1098</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1064</v>
+        <v>1099</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1065</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="3">
@@ -7525,16 +7762,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1066</v>
+        <v>1101</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1067</v>
+        <v>1102</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1068</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4">
@@ -7545,24 +7782,24 @@
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1069</v>
+        <v>1104</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1070</v>
+        <v>1105</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1071</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>1072</v>
+        <v>1107</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1073</v>
+        <v>1108</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -7570,13 +7807,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>1074</v>
+        <v>1109</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1075</v>
+        <v>1110</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -7584,13 +7821,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>1076</v>
+        <v>1111</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>1009</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1077</v>
+        <v>1112</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -7598,13 +7835,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>1078</v>
+        <v>1113</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1012</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1079</v>
+        <v>1114</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -7612,13 +7849,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>1080</v>
+        <v>1115</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>1015</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1081</v>
+        <v>1116</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -7626,13 +7863,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>1082</v>
+        <v>1117</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1018</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1083</v>
+        <v>1118</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -7640,13 +7877,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>1084</v>
+        <v>1119</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>1021</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1085</v>
+        <v>1120</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -7654,13 +7891,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>1086</v>
+        <v>1121</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1024</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1087</v>
+        <v>1122</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -7668,13 +7905,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>1088</v>
+        <v>1123</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>1027</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1089</v>
+        <v>1124</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -7682,13 +7919,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>1090</v>
+        <v>1125</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1091</v>
+        <v>1126</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -7696,13 +7933,13 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>1092</v>
+        <v>1127</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>1033</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1093</v>
+        <v>1128</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -7710,13 +7947,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>1094</v>
+        <v>1129</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1036</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1095</v>
+        <v>1130</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -7724,13 +7961,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>1096</v>
+        <v>1131</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>1039</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1097</v>
+        <v>1132</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -7738,13 +7975,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>1098</v>
+        <v>1133</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1042</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1099</v>
+        <v>1134</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -7752,13 +7989,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>1100</v>
+        <v>1135</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>1045</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -7766,13 +8003,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>1102</v>
+        <v>1137</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1048</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1103</v>
+        <v>1138</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -7780,13 +8017,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>1104</v>
+        <v>1139</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>1051</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1105</v>
+        <v>1140</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -7794,13 +8031,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>1106</v>
+        <v>1141</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1054</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1107</v>
+        <v>1142</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -7808,13 +8045,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>1108</v>
+        <v>1143</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>970</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1109</v>
+        <v>1144</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -7822,13 +8059,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>1058</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1111</v>
+        <v>1146</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$D$367]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$D$611]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="1853">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -3304,6 +3304,2127 @@
     <t xml:space="preserve">플러시 파이브</t>
   </si>
   <si>
+    <t xml:space="preserve">phrase.trigger.Passive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cond} {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnCardScored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cond} 득점할 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for each scoring {cond}{op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnCardHeld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패에 든 {cond} 마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for each {cond}held in hand, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnHandPlayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnHandDiscarded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cond} 버리면 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when discarding {cond}{op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnCardDiscarded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cond} 버릴 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for each discarded {cond}{op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnRoundStart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드가 시작할 때 {cond} {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at round start, {cond}{op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnRoundEnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드 종료 시 {cond} {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at end of round, {cond}{op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnBlindSelect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">블라인드를 고를 때 {cond} {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when a blind is selected, {cond}{op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnBossDefeated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스를 격파하면 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when a boss is defeated, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnShopEnter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점에 들어갈 때 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on entering the shop, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnShopExit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점을 나갈 때 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on leaving the shop, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnReroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점에서 리롤할 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for each shop reroll, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnPackSkipped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팩을 넘길 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for each skipped pack, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnPackOpened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팩을 열 때 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when a pack is opened, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnCardAdded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱에 카드가 더해질 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when a card joins the deck, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnCardDestroyed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cond} 파괴될 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when {cond}is destroyed, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnJokerSold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커를 팔 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when a joker is sold, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnConsumableUsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cond} 쓸 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when {cond}is used, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnSell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팔면 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sell this card to {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnUse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnScoreResolved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnRunStart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">런을 시작할 때 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at the start of the run, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trigger.OnLuckyTriggered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`행운` 카드가 발동할 때마다 {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when a Lucky card triggers, {op}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondAlways</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondHandContains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{hand} 포함 시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the hand contains a {hand}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondHandIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">족보가 {hand}면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the hand is a {hand}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCardSuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{suit} 카드가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{suit} card </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCardRankSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{ranks} 카드가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{ranks} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCardIsFace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림 카드가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">face card </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCardEnhancement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`{enhancement}` 카드가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{enhancement} card </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCardEnhanced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강화된 카드가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enhanced card </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCardSeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`{seal}` 인장이 붙은 카드가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card with a {seal} seal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCardEdition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`{edition}` 카드가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{edition} card </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCardCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낸 카드가 {n}장 {compare}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if played cards are {compare} {n}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondAllSuitsPresent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네 무늬가 모두 있으면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if all four suits score, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondSuitPair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{suit} 하나와 다른 무늬 하나가 득점하면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if a {suit} and another suit both score, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondAllHeldSuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패가 전부 {suits} 면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if all cards held are {suits}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondBlindKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{blind} 블라인드에서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on a {blind} blind, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보유 금액이 ${n} {compare}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if money is {compare} ${n}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondDiscardsLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남은 버리기가 {n} {compare}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if discards left are {compare} {n}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondHandsLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남은 핸드가 {n} {compare}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if hands left are {compare} {n}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondDiscardsUnused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버리기를 쓰지 않았으면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if no discards were used, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondHandRepeated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 라운드에 이미 낸 족보면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if this hand was already played this round, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondIsMostPlayedHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최다 사용 족보면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if this is your most played hand, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondNotMostPlayedHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최다 사용 족보가 아니면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if this is not your most played hand, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondFirstHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드의 첫 핸드면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on the first hand of the round, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondLastHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드의 마지막 핸드면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on the final hand of the round, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondFirstDiscard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드의 첫 버리기면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on the first discard of the round, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondEveryNHands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n}핸드마다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">every {n} hands, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCounterAtLeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{counter}가 {n} 이상이면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if {counter} reaches {n}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondCounterAtMost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{counter}가 {n} 이하가 되면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if {counter} drops to {n}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondChargeLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남은 횟수가 있으면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">while charges remain, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondTargetMatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지정된 {target}과 맞으면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if it matches the chosen {target}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondDeckEnhancedAtLeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱에 강화 카드가 {n}장 이상이면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the deck holds {n} or more enhanced cards, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondBossTriggered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스 능력을 발동시키면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the boss ability triggers, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondScoreRatioAtLeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">점수가 요구의 {num}/{den} 이상이면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the score is at least {num}/{den} of the target, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondNoFaceScored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림 카드가 득점하지 않은 핸드마다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for each hand with no scoring face card, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondFaceScored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림 카드가 득점하면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if a face card scores, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondDiscardedFaceAtLeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림 카드를 {n}장 이상 한 번에</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} or more face cards at once, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondHandContainsRankAndHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{hand} 안에 {ranks} 카드가 있으면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if a {hand} contains {ranks}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondFirstHandSingleCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드의 첫 핸드가 카드 한 장이면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the first hand is a single card, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondFirstHandSingleRank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드의 첫 핸드가 {ranks} 카드 한 장이면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the first hand is a single {ranks}, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondFirstDiscardSingleCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드의 첫 버리기가 카드 한 장이면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the first discard is a single card, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.cond.CondConsumableKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{consumable} 카드를</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{consumable} card </t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpAddChips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">칩 +{chips}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+{chips} chips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpAddMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배수 +{mult}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+{mult} mult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpMulMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배수 ×{mult}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X{mult} mult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpAddMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${money}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earn ${money}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpSetMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금액이 ${money}이 됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set money to ${money}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpPerUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{unit} 마다 {per}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{per} for each {unit}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpRandomRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{per} +{min}~{max}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{per} +{min} to +{max}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpRetrigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{times}회 재발동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retrigger {times} more times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpGrowSelf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{counter}가 {step}씩 늘어납니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gains {step} {counter}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpResetSelf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{counter}가 처음으로 돌아갑니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resets {counter}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpGrowOthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scope}의 {counter}가 {step}씩 늘어납니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scope} gain {step} {counter}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpLevelUpHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{hand_pick} 레벨 {levels}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level up {hand_pick} by {levels}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpCreateCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{create}를 {count}장 만듭니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create {count} {create}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpAddCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{create}를 {count}장 더합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add {count} {create}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpDestroyCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드 {count}장을 파괴합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destroy {count} cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpModifyCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scope}를 {modify}로 바꿉니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">change {scope} {modify}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpModifyJoker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scope}에 `{edition}`을 붙입니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add {edition} to {scope}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpDestroyJoker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{pick}를 파괴합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destroy {pick}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpCopyJoker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{pick}의 능력을 복사합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copy the ability of {pick}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpDebuff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{debuff}를 무력화합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">debuff {debuff}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpDisableBoss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스 효과를 끕니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disable the boss blind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpPreventLoss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패배를 막습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prevent death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpChangeRule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{rule}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpChangeRuleByCounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{rule} — 누적값만큼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{rule}, by the counter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpCardTrait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{trait}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpMulMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금액이 {value}배가 됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multiply money by {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpShopGift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 상점에 {create}를 놓습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the next shop offers {create}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpDuplicateNextTag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 태그를 복제합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duplicate the next tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpRerollBoss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스 블라인드를 다시 뽑습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reroll the boss blind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpForceDiscard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패에서 {count}장을 버립니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discard {count} cards from hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpDrawFaceDown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드를 뒤집힌 채로 뽑습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cards are drawn face down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpFlipJokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커를 뒤집고 섞습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flip and shuffle all jokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpDisableRandomJoker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핸드마다 조커 하나가 꺼집니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one random joker is disabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpGrant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{create}를 {count}개 가지고 시작합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start with {count} {create}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpNothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아무것도 하지 않습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">does nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.op.OpCustom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{handler}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.JokerCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커 하나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.EmptyJokerSlots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빈 조커 슬롯 하나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">empty joker slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.DeckRemaining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱에 남은 카드 한 장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card left in deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.DeckDeficit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱에서 모자란 카드 한 장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card below the deck size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.Money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보유 $1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.MoneyPer5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보유 $5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.DiscardsLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남은 버리기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remaining discard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.HandsLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남은 핸드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remaining hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.BlindsSkipped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스킵한 블라인드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skipped blind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.TarotUsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 런에 쓴 타로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tarot used this run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.UniquePlanetUsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 런에 쓴 고유 행성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique planet used this run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.DeckRankCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱의 {ranks} 한 장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{ranks} in the deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.DeckEnhancementCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱의 `{enhancement}` 카드 한 장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{enhancement} card in the deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.JokerRarityCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{rarity} 조커 하나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{rarity} joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.HandPlayCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 족보를 낸 횟수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time this hand was played</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.OtherJokerSellValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다른 조커의 판매가 $1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1 of other jokers sell value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.LowestHeldRankChips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패의 최저 랭크 칩값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chip of the lowest held rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.CardsPlayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낸 카드 한 장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">played card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.SelfCounterMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">누적한 $1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1 accumulated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.HandsPlayedThisRun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 런에 낸 핸드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand played this run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.unit.DiscardsUnusedThisRun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 런에 쓰지 않은 버리기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unused discard this run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.HandSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패 크기 {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand size {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.HandsPerRound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드당 핸드 {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value} hands each round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.DiscardsPerRound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드당 버리기 {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value} discards each round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.JokerSlots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커 슬롯 {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value} joker slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ConsumableSlots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품 슬롯 {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value} consumable slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.DebtLimit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빚을 {value}까지 집니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go up to ${value} in debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.FreeRerolls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점마다 무료 리롤 {value}회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value} free reroll each shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.RerollCostDelta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리롤 비용 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rerolls cost ${value} less</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.RerollStartsFree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 상점의 리롤이 $0에서 시작합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rerolls start at $0 in the next shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.InterestPer5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보유 $5마다 이자 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${value} extra interest per $5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.InterestCap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이자 상한 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interest cap ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ShopCardSlots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점 카드 칸 {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value} shop card slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ShopDiscount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점 {value}% 할인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop is {value}% off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ShopAllowsPlayingCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점에서 플레잉 카드를 살 수 있습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">playing cards appear in the shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ShopAllowsSpectral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점에 유령 카드가 나옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spectral cards appear in the shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ShopWeightTarot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점 타로 등장 {value}배</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tarot cards appear {value}X as often</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ShopWeightPlanet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점 행성 등장 {value}배</t>
+  </si>
+  <si>
+    <t xml:space="preserve">planet cards appear {value}X as often</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.FreePlanets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 행성 카드와 천체 팩이 무료입니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">planet cards and celestial packs are free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.AllCardsScore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낸 카드 전부가 득점합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">every played card scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.AllCardsAreFace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 카드를 그림 카드로 봅니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all cards count as face cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.FlushStraightCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플러시와 스트레이트를 {value}장으로 이룹니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flushes and straights need {value} cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.StraightGap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스트레이트에 {value}칸 빈틈을 허용합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">straights may skip {value} rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.SuitsMerged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하트와 다이아를, 스페이드와 클럽을 한 무늬로 봅니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hearts count as diamonds and spades as clubs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ProbabilityScale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 확률이 {value}배가 됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all listed odds are {value}X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.AllowDuplicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">같은 카드가 여러 번 나올 수 있습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cards may appear more than once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.BalanceChipsAndMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">칩과 배수를 평균으로 맞춥니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chips and mult are balanced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.BossRerollsPerAnte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안테마다 보스를 {value}회 다시 뽑습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reroll the boss {value} times per ante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.AnteDelta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안테 {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ante {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.EditionWeightScale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에디션 등장 {value}배</t>
+  </si>
+  <si>
+    <t xml:space="preserve">editions appear {value}X as often</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.PlanetGivesMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">행성 카드가 해당 족보에 배수 ×{value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">planet cards give X{value} mult to their hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.StartingMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${value}을 더 가지고 시작합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start with ${value} more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.NoInterest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이자를 받지 않습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earn no interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.MoneyPerHandLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남은 핸드마다 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${value} per remaining hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.MoneyPerDiscardLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남은 버리기마다 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${value} per remaining discard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.RandomizeDeck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱 52장의 랭크와 무늬가 무작위입니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all ranks and suits are randomized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.DoubleTagOnBossDefeat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스 격파마다 `Double Tag`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gain a Double Tag after each boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.BlindSizeScale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">블라인드 요구 점수 {value}배</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blind size {value}X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.SetDiscardsZero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버리기 0으로 시작합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start with 0 discards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.SpectralInArcanaPacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아르카나 팩에 유령 카드가 섞입니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spectral cards appear in arcana packs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.CelestialHasMostPlayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">천체 팩에 최다 사용 족보의 행성이 반드시 들어갑니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">celestial packs always contain your most played hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ShopCardsHaveModifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 플레잉 카드가 강화와 인장을 가집니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop playing cards may be enhanced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.NoRepeatHandTypes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">같은 족보를 두 번 낼 수 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no repeat hand types this round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.SingleHandTypeOnly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한 종류의 족보만 낼 수 있습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">only one hand type may be played</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.MustPlayFiveCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">반드시 5장을 내야 합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">must play 5 cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.AlwaysDrawThree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항상 3장만 뽑습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">always draw 3 cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.HalveBaseChipsAndMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 칩과 배수가 절반이 됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base chips and mult are halved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.DebuffUntilJokerSold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커 하나를 팔기 전까지 모든 카드가 무력화됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all cards are debuffed until a joker is sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ForceCardSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드 한 장이 항상 선택된 상태가 됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one card is always forced to be selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.RemoveFaceCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림 카드 없이 시작합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start with no face cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.SuitsOnly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{suits} 로만 시작합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start with only {suits}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.NextShopFree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 상점의 처음 카드와 팩이 무료입니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the next shop starts free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.suit.Spade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스페이드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.suit.Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.suit.Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.suit.Diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다이아</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.counter.Chips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">칩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.counter.MultAdd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.counter.MultMul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곱 배수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X mult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.counter.Money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.counter.SellValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판매가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sell value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.counter.Charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남은 횟수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">charges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.counter.Tick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지난 라운드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.compare.AtLeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이상이면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at least</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.compare.AtMost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이하면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at most</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.compare.Exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.pick.Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오른쪽 조커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the joker to the right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.pick.Leftmost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">맨 왼쪽 조커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the leftmost joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.pick.Random</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무작위 조커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a random joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.pick.AllOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나머지 조커 전부</t>
+  </si>
+  <si>
+    <t xml:space="preserve">every other joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.pick.SelfPick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 조커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.Tarot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">타로 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a tarot card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.Planet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">행성 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a planet card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.Spectral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유령 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a spectral card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.Joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.PlayingCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플레잉 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a playing card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.Tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">태그</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.LastUsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마지막으로 쓴 소모품</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the last used consumable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.CopyOfScored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그 카드의 사본</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a copy of that card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.CopyOfSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고른 카드의 사본</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a copy of the selected card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.create.Voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바우처</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.modify.Enhancement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enhancement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.modify.Seal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.modify.Edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에디션</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.modify.Suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무늬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.modify.RankStep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">랭크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.modify.BonusChips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영구 칩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">permanent chips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.modify.CopyRight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오른쪽 카드와 같게</t>
+  </si>
+  <si>
+    <t xml:space="preserve">into the card on the right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.modify.RankTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">같은 랭크로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to one rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.debuff.BySuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그 무늬의 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cards of that suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.debuff.FaceCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">face cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.debuff.PlayedThisAnte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 안테에 이미 낸 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cards played this ante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.debuff.AllCards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.target.Hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">족보</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.target.Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.target.Suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.target.Card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trait.AnySuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 무늬로 취급됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">counts as every suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trait.NoRankSuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">랭크와 무늬가 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has no rank or suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.trait.AlwaysScores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항상 득점합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">always scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.handpick.Played</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낸 족보의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the played hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.handpick.FirstDiscarded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">처음 버린 족보의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the first discarded hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.handpick.MostPlayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최다 사용 족보의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">your most played hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.handpick.Random</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무작위 족보의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a random hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.handpick.All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 족보의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">every hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rarity.Common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">커먼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rarity.Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">언커먼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rarity.Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rarity.Legendary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legendary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.AllJokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 조커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all jokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.AllOtherJokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나머지 조커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other jokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.AllConsumables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 소모품</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all consumables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.RandomJoker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.Selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고른 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the selected cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.RandomInHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패의 무작위 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">random cards in hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.AllInHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">패의 모든 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all cards in hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.ScoredCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">that card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.HeldCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.AllInDeck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱의 모든 카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all cards in the deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.SelfTarget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이것</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.scope.Run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.handler.pruning_shears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오른쪽 조커를 파괴하고 그 판매가의 2배를 배수로 얻습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destroy the joker to the right and gain double its sell value as mult</t>
+  </si>
+  <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
   </si>
   <si>
@@ -3398,9 +5519,6 @@
   </si>
   <si>
     <t xml:space="preserve">조커 슬롯을 전부 채웁니다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">legendary</t>
   </si>
   <si>
     <t xml:space="preserve">전설 조커를 얻습니다</t>
@@ -3657,13 +5775,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D367"/>
+  <dimension ref="A1:D611"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
     <col min="2" max="2" width="49.21875" customWidth="1"/>
-    <col min="3" max="3" width="16.40625" customWidth="1"/>
-    <col min="4" max="4" width="25.78125" customWidth="1"/>
+    <col min="3" max="3" width="41.015625" customWidth="1"/>
+    <col min="4" max="4" width="53.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7711,8 +9829,2680 @@
         <v>1028</v>
       </c>
     </row>
+    <row r="368">
+      <c r="B368" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C368" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D368" s="6" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C369" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D369" s="5" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D370" s="6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C371" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D371" s="5" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D372" s="6" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" s="5" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D373" s="5" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C374" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D374" s="6" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D375" s="5" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D376" s="6" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" s="5" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D377" s="5" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D378" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D379" s="5" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D380" s="6" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D381" s="5" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D382" s="6" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D383" s="5" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D385" s="5" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D386" s="6" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C387" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D387" s="5" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C389" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D389" s="5" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C390" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D390" s="6" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D391" s="5" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" s="6" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D393" s="5" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C394" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D394" s="6" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D395" s="5" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C396" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D396" s="6" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" s="5" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D397" s="5" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C398" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D398" s="6" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D399" s="5" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C400" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D400" s="6" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D401" s="5" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C402" s="6" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D402" s="6" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D403" s="5" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="6" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C404" s="6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D404" s="6" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" s="5" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D405" s="5" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" s="6" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C406" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D406" s="6" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" s="5" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D407" s="5" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" s="6" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C408" s="6" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D408" s="6" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D409" s="5" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C410" s="6" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D410" s="6" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" s="5" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D411" s="5" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" s="6" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C412" s="6" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D412" s="6" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D413" s="5" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C414" s="6" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D414" s="6" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" s="5" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D415" s="5" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" s="6" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C416" s="6" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D416" s="6" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D417" s="5" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C418" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D418" s="6" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" s="5" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D419" s="5" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" s="6" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C420" s="6" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D420" s="6" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D421" s="5" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" s="6" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C422" s="6" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D422" s="6" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" s="5" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D423" s="5" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" s="6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C424" s="6" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D424" s="6" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D425" s="5" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" s="6" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C426" s="6" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D426" s="6" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" s="5" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C427" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D427" s="5" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" s="6" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C428" s="6" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D428" s="6" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" s="5" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C429" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D429" s="5" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" s="6" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C430" s="6" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D430" s="6" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" s="5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C431" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D431" s="5" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" s="6" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D432" s="6" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C433" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D433" s="5" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" s="6" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C434" s="6" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D434" s="6" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" s="5" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C435" s="5" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D435" s="5" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" s="6" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C436" s="6" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D436" s="6" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" s="5" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C437" s="5" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D437" s="5" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C438" s="6" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D438" s="6" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" s="5" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D439" s="5" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" s="6" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C440" s="6" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D440" s="6" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" s="5" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C441" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D441" s="5" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C442" s="6" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D442" s="6" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D443" s="5" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" s="6" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C444" s="6" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D444" s="6" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" s="5" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C445" s="5" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D445" s="5" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" s="6" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C446" s="6" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D446" s="6" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" s="5" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D447" s="5" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" s="6" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C448" s="6" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D448" s="6" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D449" s="5" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C450" s="6" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D450" s="6" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" s="5" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D451" s="5" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C452" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D452" s="6" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C453" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D453" s="5" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C454" s="6" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D454" s="6" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" s="5" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C455" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D455" s="5" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" s="6" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C456" s="6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D456" s="6" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D457" s="5" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" s="6" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C458" s="6" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D458" s="6" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D459" s="5" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" s="6" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C460" s="6" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D460" s="6" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" s="5" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D461" s="5" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" s="6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C462" s="6" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D462" s="6" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" s="5" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C463" s="5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D463" s="5" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" s="6" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C464" s="6" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D464" s="6" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" s="5" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C465" s="5" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D465" s="5" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" s="6" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C466" s="6" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D466" s="6" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C467" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D467" s="5" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" s="6" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C468" s="6" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D468" s="6" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" s="5" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C469" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D469" s="5" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" s="6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C470" s="6" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D470" s="6" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" s="5" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C471" s="5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D471" s="5" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C472" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D472" s="6" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D473" s="5" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" s="6" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C474" s="6" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D474" s="6" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C475" s="5" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D475" s="5" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" s="6" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C476" s="6" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D476" s="6" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" s="5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C477" s="5" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D477" s="5" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C478" s="6" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D478" s="6" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" s="5" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C479" s="5" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D479" s="5" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" s="6" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C480" s="6" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D480" s="6" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" s="5" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C481" s="5" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D481" s="5" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" s="6" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C482" s="6" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D482" s="6" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" s="5" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D483" s="5" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" s="6" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C484" s="6" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D484" s="6" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" s="5" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C485" s="5" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D485" s="5" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" s="6" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C486" s="6" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D486" s="6" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" s="5" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C487" s="5" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D487" s="5" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" s="6" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C488" s="6" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D488" s="6" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" s="5" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C489" s="5" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D489" s="5" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" s="6" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C490" s="6" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D490" s="6" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" s="5" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C491" s="5" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D491" s="5" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C492" s="6" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D492" s="6" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" s="5" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C493" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D493" s="5" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" s="6" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C494" s="6" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D494" s="6" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" s="5" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C495" s="5" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D495" s="5" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" s="6" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C496" s="6" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D496" s="6" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" s="5" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C497" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D497" s="5" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" s="6" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C498" s="6" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D498" s="6" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" s="5" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D499" s="5" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" s="6" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C500" s="6" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D500" s="6" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" s="5" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D501" s="5" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" s="6" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C502" s="6" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D502" s="6" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C503" s="5" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D503" s="5" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" s="6" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C504" s="6" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D504" s="6" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" s="5" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D505" s="5" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" s="6" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C506" s="6" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D506" s="6" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" s="5" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C507" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D507" s="5" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" s="6" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C508" s="6" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D508" s="6" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" s="5" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C509" s="5" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D509" s="5" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" s="6" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C510" s="6" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D510" s="6" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" s="5" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C511" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D511" s="5" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" s="6" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C512" s="6" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D512" s="6" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" s="5" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C513" s="5" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D513" s="5" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" s="6" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C514" s="6" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D514" s="6" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C515" s="5" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D515" s="5" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" s="6" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C516" s="6" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D516" s="6" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" s="5" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D517" s="5" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="B518" s="6" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C518" s="6" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D518" s="6" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" s="5" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D519" s="5" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" s="6" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C520" s="6" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D520" s="6" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" s="5" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D521" s="5" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="B522" s="6" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C522" s="6" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D522" s="6" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="B523" s="5" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D523" s="5" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" s="6" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C524" s="6" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D524" s="6" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" s="5" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D525" s="5" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" s="6" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C526" s="6" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D526" s="6" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" s="5" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D527" s="5" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" s="6" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C528" s="6" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D528" s="6" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" s="5" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D529" s="5" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C530" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D530" s="6" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" s="5" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D531" s="5" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C532" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D532" s="6" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D533" s="5" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" s="6" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C534" s="6" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D534" s="6" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D535" s="5" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" s="6" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C536" s="6" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D536" s="6" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" s="5" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D537" s="5" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" s="6" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C538" s="6" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D538" s="6" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" s="5" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D539" s="5" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" s="6" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C540" s="6" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D540" s="6" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="B541" s="5" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D541" s="5" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" s="6" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C542" s="6" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D542" s="6" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" s="5" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="D543" s="5" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" s="6" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C544" s="6" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D544" s="6" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="B545" s="5" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D545" s="5" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" s="6" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C546" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="D546" s="6" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" s="5" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D547" s="5" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" s="6" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C548" s="6" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D548" s="6" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" s="5" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D549" s="5" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" s="6" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C550" s="6" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D550" s="6" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" s="5" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D551" s="5" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" s="6" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C552" s="6" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D552" s="6" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" s="5" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D553" s="5" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="B554" s="6" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C554" s="6" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D554" s="6" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="B555" s="5" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D555" s="5" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="B556" s="6" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C556" s="6" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D556" s="6" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="B557" s="5" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C557" s="5" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D557" s="5" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="B558" s="6" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C558" s="6" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D558" s="6" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="B559" s="5" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D559" s="5" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="B560" s="6" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C560" s="6" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D560" s="6" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" s="5" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D561" s="5" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="B562" s="6" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C562" s="6" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D562" s="6" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" s="5" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D563" s="5" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="B564" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C564" s="6" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D564" s="6" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="B565" s="5" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D565" s="5" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="B566" s="6" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C566" s="6" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D566" s="6" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="B567" s="5" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C567" s="5" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D567" s="5" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="B568" s="6" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C568" s="6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D568" s="6" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="B569" s="5" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D569" s="5" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="B570" s="6" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C570" s="6" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D570" s="6" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="B571" s="5" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D571" s="5" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="B572" s="6" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C572" s="6" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D572" s="6" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="B573" s="5" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D573" s="5" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="B574" s="6" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C574" s="6" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D574" s="6" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="B575" s="5" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D575" s="5" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="B576" s="6" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C576" s="6" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D576" s="6" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="B577" s="5" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D577" s="5" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="B578" s="6" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C578" s="6" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D578" s="6" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" s="5" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C579" s="5" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D579" s="5" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" s="6" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C580" s="6" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D580" s="6" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="B581" s="5" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C581" s="5" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D581" s="5" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" s="6" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C582" s="6" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D582" s="6" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="B583" s="5" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C583" s="5" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D583" s="5" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="B584" s="6" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C584" s="6" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D584" s="6" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="B585" s="5" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C585" s="5" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D585" s="5" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="B586" s="6" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C586" s="6" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D586" s="6" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="B587" s="5" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C587" s="5" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D587" s="5" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="B588" s="6" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C588" s="6" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D588" s="6" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="B589" s="5" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C589" s="5" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D589" s="5" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="B590" s="6" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C590" s="6" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D590" s="6" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="B591" s="5" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C591" s="5" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D591" s="5" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" s="6" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C592" s="6" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D592" s="6" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="B593" s="5" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C593" s="5" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D593" s="5" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" s="6" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C594" s="6" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D594" s="6" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="B595" s="5" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C595" s="5" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D595" s="5" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="B596" s="6" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C596" s="6" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D596" s="6" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" s="5" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C597" s="5" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D597" s="5" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" s="6" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C598" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D598" s="6" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" s="5" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C599" s="5" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D599" s="5" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="B600" s="6" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C600" s="6" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D600" s="6" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="B601" s="5" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C601" s="5" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D601" s="5" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" s="6" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C602" s="6" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D602" s="6" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" s="5" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C603" s="5" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D603" s="5" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" s="6" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C604" s="6" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D604" s="6" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="B605" s="5" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D605" s="5" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="B606" s="6" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C606" s="6" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D606" s="6" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" s="5" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C607" s="5" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D607" s="5" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" s="6" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C608" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D608" s="6" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" s="5" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C609" s="5" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D609" s="5" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" s="6" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" s="5" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C611" s="5" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D611" s="5" t="s">
+        <v>1801</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:D367"/>
+  <autoFilter ref="B2:D611"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7731,10 +12521,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1095</v>
+        <v>1802</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1096</v>
+        <v>1803</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -7745,16 +12535,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1097</v>
+        <v>1804</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1098</v>
+        <v>1805</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1099</v>
+        <v>1806</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1100</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="3">
@@ -7762,16 +12552,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1101</v>
+        <v>1808</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1102</v>
+        <v>1809</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1103</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="4">
@@ -7782,24 +12572,24 @@
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1104</v>
+        <v>1811</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1105</v>
+        <v>1812</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1106</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>1107</v>
+        <v>1814</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1108</v>
+        <v>1815</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -7807,13 +12597,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>1109</v>
+        <v>1816</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1110</v>
+        <v>1817</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -7821,13 +12611,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>1111</v>
+        <v>1818</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>1009</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1112</v>
+        <v>1819</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -7835,13 +12625,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>1113</v>
+        <v>1820</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1012</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1114</v>
+        <v>1821</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -7849,13 +12639,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>1115</v>
+        <v>1822</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>1015</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1116</v>
+        <v>1823</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -7863,13 +12653,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>1117</v>
+        <v>1824</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1018</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1118</v>
+        <v>1825</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -7877,13 +12667,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>1119</v>
+        <v>1826</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>1021</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1120</v>
+        <v>1827</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -7891,13 +12681,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>1121</v>
+        <v>1828</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1024</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1122</v>
+        <v>1829</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -7905,13 +12695,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>1123</v>
+        <v>1830</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>1027</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1124</v>
+        <v>1831</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -7919,13 +12709,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>1125</v>
+        <v>1832</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1126</v>
+        <v>1833</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -7933,13 +12723,13 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>1127</v>
+        <v>1768</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>1033</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1128</v>
+        <v>1834</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -7947,13 +12737,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>1129</v>
+        <v>1835</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1036</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1130</v>
+        <v>1836</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -7961,13 +12751,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>1131</v>
+        <v>1837</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>1039</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1132</v>
+        <v>1838</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -7975,13 +12765,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>1133</v>
+        <v>1839</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1042</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1134</v>
+        <v>1840</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -7989,13 +12779,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>1135</v>
+        <v>1841</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>1045</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1136</v>
+        <v>1842</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -8003,13 +12793,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>1137</v>
+        <v>1843</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1048</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1138</v>
+        <v>1844</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -8017,13 +12807,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>1139</v>
+        <v>1845</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>1051</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1140</v>
+        <v>1846</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -8031,13 +12821,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>1141</v>
+        <v>1847</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1054</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1142</v>
+        <v>1848</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -8045,13 +12835,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>1143</v>
+        <v>1849</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>970</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1144</v>
+        <v>1850</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -8059,13 +12849,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>1145</v>
+        <v>1851</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>1058</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1146</v>
+        <v>1852</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$D$611]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$D$662]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="1853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="2006">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -5423,6 +5423,465 @@
   </si>
   <si>
     <t xml:space="preserve">destroy the joker to the right and gain double its sell value as mult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.hand_size.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">손패의 크기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.hands_per_round.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드마다의 핸드 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hands per round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.discards_per_round.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드마다의 버리기 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discards per round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.joker_slots.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커 칸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.consumable_slots.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품 칸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumable slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.debt_limit.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빚을 낼 수 있는 한도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.free_rerolls.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공짜 리롤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free rerolls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.reroll_cost_delta.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리롤 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reroll cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.reroll_starts_free.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 첫 리롤이 공짜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First reroll free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.interest_per5.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보유 5마다 받는 이자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest per $5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.interest_cap.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이자의 상한</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.shop_card_slots.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 카드 칸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop card slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.shop_discount.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점 할인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.shop_allows_playing_cards.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점에 플레잉 카드가 나옴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playing cards in shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.shop_allows_spectral.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점에 유령 카드가 나옴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spectral cards in shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.shop_weight_tarot.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 타로 가중치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarot weight in shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.shop_weight_planet.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 행성 가중치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planet weight in shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.free_planets.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 행성이 공짜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free planets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.all_cards_score.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">족보에 들지 않은 카드도 득점</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All played cards score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.all_cards_are_face.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 카드를 그림 카드로 봄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All cards count as face</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.flush_straight_cards.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플러시와 스트레이트에 드는 장수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cards for flush and straight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.straight_gap.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스트레이트가 건너뛸 수 있는 폭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.suits_merged.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네 무늬를 하나로 봄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All suits count as one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.probability_scale.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">확률</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.allow_duplicates.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">같은 것을 둘 이상 가질 수 있음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicates allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.balance_chips_and_mult.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">칩과 배수를 평균으로 맞춤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chips and mult balanced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.boss_rerolls_per_ante.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안테마다의 보스 리롤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss rerolls per ante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.ante_delta.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안테</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.edition_weight_scale.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에디션이 붙을 확률</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edition chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.planet_gives_mult.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">행성이 배수도 올림</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planets raise mult too</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.starting_money.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작 금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.no_interest.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이자를 받지 않음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.money_per_hand_left.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남긴 핸드마다 받는 금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money per unused hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.money_per_discard_left.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남긴 버리기마다 받는 금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money per unused discard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.randomize_deck.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작 덱의 랭크와 무늬를 다시 뽑음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deck ranks and suits randomized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.double_tag_on_boss_defeat.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스를 깨면 태그를 둘 받음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two tags on boss defeat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.blind_size_scale.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">블라인드의 요구 점수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blind requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.set_discards_zero.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버리기 횟수가 0이 됨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discards set to zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.spectral_in_arcana_packs.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아르카나 팩에 유령 카드가 섞임</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spectral cards in arcana packs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.celestial_has_most_played.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">천체 팩에 가장 많이 낸 족보의 행성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most-played planet in celestial packs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.shop_cards_have_modifiers.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 카드에 강화와 인장이 붙음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop cards carry modifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.no_repeat_hand_types.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한 라운드에 같은 족보를 두 번 낼 수 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No repeated hand types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.single_hand_type_only.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한 라운드에 한 가지 족보만</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One hand type only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.must_play_five_cards.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핸드마다 다섯 장을 내야 함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must play five cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.always_draw_three.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">언제나 세 장씩 뽑음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always draw three</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.halve_base_chips_and_mult.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">족보의 기본 칩과 배수가 절반</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base chips and mult halved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.debuff_until_joker_sold.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커를 팔 때까지 카드가 무력화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debuffed until a joker is sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.force_card_selected.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드 한 장이 반드시 골라짐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One card always selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.remove_face_cards.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작 덱에서 그림 카드를 뺌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Face cards removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.suits_only.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작 덱을 그 무늬들로만 채움</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deck limited to those suits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.next_shop_free.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 상점의 처음 카드와 팩이 공짜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next shop starts free</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -5775,7 +6234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D611"/>
+  <dimension ref="A1:D662"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -12501,8 +12960,569 @@
         <v>1801</v>
       </c>
     </row>
+    <row r="612">
+      <c r="B612" s="6" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C612" s="6" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D612" s="6" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" s="5" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C613" s="5" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D613" s="5" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" s="6" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C614" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D614" s="6" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" s="5" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D615" s="5" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="B616" s="6" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C616" s="6" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D616" s="6" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" s="5" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C617" s="5" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D617" s="5" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" s="6" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C618" s="6" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D618" s="6" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" s="5" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C619" s="5" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D619" s="5" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" s="6" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C620" s="6" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D620" s="6" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" s="5" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C621" s="5" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D621" s="5" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" s="6" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C622" s="6" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D622" s="6" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C623" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D623" s="5" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" s="6" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C624" s="6" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D624" s="6" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" s="5" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C625" s="5" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D625" s="5" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" s="6" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C626" s="6" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D626" s="6" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" s="5" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C627" s="5" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D627" s="5" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" s="6" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C628" s="6" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D628" s="6" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C629" s="5" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D629" s="5" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" s="6" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C630" s="6" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D630" s="6" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" s="5" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C631" s="5" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D631" s="5" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="B632" s="6" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C632" s="6" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D632" s="6" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C633" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D633" s="5" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" s="6" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C634" s="6" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D634" s="6" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" s="5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C635" s="5" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D635" s="5" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" s="6" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C636" s="6" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D636" s="6" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" s="5" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C637" s="5" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D637" s="5" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" s="6" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C638" s="6" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D638" s="6" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" s="5" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C639" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D639" s="5" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" s="6" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C640" s="6" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D640" s="6" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" s="5" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C641" s="5" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D641" s="5" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" s="6" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C642" s="6" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D642" s="6" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" s="5" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C643" s="5" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D643" s="5" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" s="6" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C644" s="6" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D644" s="6" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="B645" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C645" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D645" s="5" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="B646" s="6" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C646" s="6" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D646" s="6" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="B647" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D647" s="5" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="B648" s="6" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C648" s="6" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D648" s="6" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="B649" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C649" s="5" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D649" s="5" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="B650" s="6" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C650" s="6" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D650" s="6" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="B651" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D651" s="5" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" s="6" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C652" s="6" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D652" s="6" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D653" s="5" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" s="6" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C654" s="6" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D654" s="6" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" s="5" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D655" s="5" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" s="6" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C656" s="6" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D656" s="6" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D657" s="5" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" s="6" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C658" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D658" s="6" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="B659" s="5" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C659" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D659" s="5" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="B660" s="6" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C660" s="6" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D660" s="6" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="B661" s="5" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C661" s="5" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D661" s="5" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="B662" s="6" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C662" s="6" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D662" s="6" t="s">
+        <v>1954</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:D611"/>
+  <autoFilter ref="B2:D662"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12521,10 +13541,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1802</v>
+        <v>1955</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1803</v>
+        <v>1956</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -12535,16 +13555,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1804</v>
+        <v>1957</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1805</v>
+        <v>1958</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1806</v>
+        <v>1959</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1807</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="3">
@@ -12552,16 +13572,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1808</v>
+        <v>1961</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1809</v>
+        <v>1962</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1810</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="4">
@@ -12572,24 +13592,24 @@
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1811</v>
+        <v>1964</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1812</v>
+        <v>1965</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1813</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>1814</v>
+        <v>1967</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1815</v>
+        <v>1968</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -12597,13 +13617,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>1816</v>
+        <v>1969</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1817</v>
+        <v>1970</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -12611,13 +13631,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>1818</v>
+        <v>1971</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>1009</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1819</v>
+        <v>1972</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -12625,13 +13645,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>1820</v>
+        <v>1973</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1012</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1821</v>
+        <v>1974</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -12639,13 +13659,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>1822</v>
+        <v>1975</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>1015</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1823</v>
+        <v>1976</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -12653,13 +13673,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>1824</v>
+        <v>1977</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1018</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1825</v>
+        <v>1978</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -12667,13 +13687,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>1826</v>
+        <v>1979</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>1021</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1827</v>
+        <v>1980</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -12681,13 +13701,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>1828</v>
+        <v>1981</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1024</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1829</v>
+        <v>1982</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -12695,13 +13715,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>1830</v>
+        <v>1983</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>1027</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1831</v>
+        <v>1984</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -12709,13 +13729,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>1832</v>
+        <v>1985</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1030</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1833</v>
+        <v>1986</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -12729,7 +13749,7 @@
         <v>1033</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1834</v>
+        <v>1987</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -12737,13 +13757,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>1835</v>
+        <v>1988</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1036</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1836</v>
+        <v>1989</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -12751,13 +13771,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>1837</v>
+        <v>1990</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>1039</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1838</v>
+        <v>1991</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -12765,13 +13785,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>1839</v>
+        <v>1992</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1042</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1840</v>
+        <v>1993</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -12779,13 +13799,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>1841</v>
+        <v>1994</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>1045</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1842</v>
+        <v>1995</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -12793,13 +13813,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>1843</v>
+        <v>1996</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1048</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1844</v>
+        <v>1997</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -12807,13 +13827,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>1845</v>
+        <v>1998</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>1051</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1846</v>
+        <v>1999</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -12821,13 +13841,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>1847</v>
+        <v>2000</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1054</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1848</v>
+        <v>2001</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -12835,13 +13855,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>1849</v>
+        <v>2002</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>970</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1850</v>
+        <v>2003</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -12849,13 +13869,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>1851</v>
+        <v>2004</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>1058</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1852</v>
+        <v>2005</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$D$662]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$662]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="2006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="2014">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -37,6 +37,18 @@
     <t xml:space="preserve">en</t>
   </si>
   <si>
+    <t xml:space="preserve">ja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zh_hans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zh_hant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de</t>
+  </si>
+  <si>
     <t xml:space="preserve">:type</t>
   </si>
   <si>
@@ -53,6 +65,18 @@
   </si>
   <si>
     <t xml:space="preserve">영어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일본어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">중국어 간체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">중국어 번체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">독일어</t>
   </si>
   <si>
     <t xml:space="preserve">joker.twig.name</t>
@@ -6234,13 +6258,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D662"/>
+  <dimension ref="A1:H662"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
     <col min="2" max="2" width="49.21875" customWidth="1"/>
     <col min="3" max="3" width="41.015625" customWidth="1"/>
     <col min="4" max="4" width="53.90625" customWidth="1"/>
+    <col min="5" max="5" width="9.375" customWidth="1"/>
+    <col min="6" max="7" width="10.546875" customWidth="1"/>
+    <col min="8" max="8" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6252,6 +6279,10 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -6266,7263 +6297,7299 @@
       <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="5" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="5" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="6" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="6" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="6" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="5" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="5" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="5" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="5" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="5" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="6" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="5" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="5" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="5" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="5" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="5" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="6" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="5" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="6" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="5" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="5" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="6" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="5" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="6" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="5" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="5" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="6" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="5" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="6" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="5" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="5" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="6" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="5" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="6" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="5" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="6" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="5" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="6" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="5" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="6" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" s="5" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="6" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="5" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="6" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" s="5" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="6" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="5" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" s="6" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="5" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="6" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="5" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="6" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="5" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="6" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="5" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" s="6" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="5" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="6" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" s="5" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" s="6" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="5" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" s="6" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="5" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="6" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="5" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="6" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="6" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="5" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="6" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="5" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="6" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="5" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="6" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="5" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="6" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="5" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="6" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="5" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="6" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="5" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="6" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="5" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="6" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="5" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="6" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="5" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="6" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="5" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="6" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="5" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="6" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" s="5" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" s="6" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" s="5" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" s="6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" s="5" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" s="6" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" s="5" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" s="6" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="189">
       <c r="B189" s="5" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" s="6" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" s="5" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="192">
       <c r="B192" s="6" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="193">
       <c r="B193" s="5" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" s="6" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="195">
       <c r="B195" s="5" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="196">
       <c r="B196" s="6" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" s="5" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" s="6" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" s="5" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" s="6" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" s="5" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" s="6" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" s="5" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
     </row>
     <row r="204">
       <c r="B204" s="6" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" s="5" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="6" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" s="5" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" s="6" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" s="5" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" s="6" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" s="5" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" s="6" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" s="5" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" s="6" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" s="5" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" s="6" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" s="5" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="6" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" s="5" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" s="6" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" s="5" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" s="6" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" s="5" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" s="6" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" s="5" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="6" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" s="5" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" s="6" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" s="5" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" s="6" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="6" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" s="5" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" s="6" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" s="5" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" s="6" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" s="5" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" s="6" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" s="5" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" s="6" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="5" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" s="6" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" s="5" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="6" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="5" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="6" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="5" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="248">
       <c r="B248" s="6" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" s="5" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" s="6" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" s="5" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" s="6" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" s="5" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" s="6" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" s="5" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" s="6" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" s="5" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="6" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="5" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="6" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="5" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="6" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="5" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="6" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" s="5" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="6" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" s="6" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="5" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="6" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" s="5" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" s="6" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" s="5" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
     </row>
     <row r="275">
       <c r="B275" s="5" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" s="6" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" s="5" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="6" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" s="5" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" s="6" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" s="5" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" s="6" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" s="5" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
     </row>
     <row r="284">
       <c r="B284" s="6" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" s="5" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" s="6" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
     </row>
     <row r="287">
       <c r="B287" s="5" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
     </row>
     <row r="288">
       <c r="B288" s="6" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" s="5" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" s="6" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" s="5" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" s="6" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" s="5" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" s="6" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" s="5" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" s="6" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" s="5" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" s="6" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="5" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
     </row>
     <row r="300">
       <c r="B300" s="6" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
     </row>
     <row r="301">
       <c r="B301" s="5" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
     </row>
     <row r="302">
       <c r="B302" s="6" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
     </row>
     <row r="303">
       <c r="B303" s="5" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
     </row>
     <row r="304">
       <c r="B304" s="6" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
     </row>
     <row r="305">
       <c r="B305" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
     </row>
     <row r="306">
       <c r="B306" s="6" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" s="5" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
     </row>
     <row r="308">
       <c r="B308" s="6" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
     </row>
     <row r="309">
       <c r="B309" s="5" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
     </row>
     <row r="310">
       <c r="B310" s="6" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" s="5" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" s="6" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="D312" s="6" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
     </row>
     <row r="313">
       <c r="B313" s="5" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
     </row>
     <row r="314">
       <c r="B314" s="6" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
     </row>
     <row r="315">
       <c r="B315" s="5" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" s="6" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="D316" s="6" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" s="5" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
     </row>
     <row r="318">
       <c r="B318" s="6" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="D318" s="6" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
     </row>
     <row r="319">
       <c r="B319" s="5" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
     </row>
     <row r="320">
       <c r="B320" s="6" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="D320" s="6" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
     </row>
     <row r="321">
       <c r="B321" s="5" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
     </row>
     <row r="322">
       <c r="B322" s="6" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="D322" s="6" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
     </row>
     <row r="323">
       <c r="B323" s="5" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="324">
       <c r="B324" s="6" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="D324" s="6" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
     </row>
     <row r="325">
       <c r="B325" s="5" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
     </row>
     <row r="326">
       <c r="B326" s="6" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="D326" s="6" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
     </row>
     <row r="327">
       <c r="B327" s="5" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="328">
       <c r="B328" s="6" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="D328" s="6" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
     </row>
     <row r="329">
       <c r="B329" s="5" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
     </row>
     <row r="330">
       <c r="B330" s="6" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="D330" s="6" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
     </row>
     <row r="331">
       <c r="B331" s="5" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
     </row>
     <row r="332">
       <c r="B332" s="6" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="D332" s="6" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="333">
       <c r="B333" s="5" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="334">
       <c r="B334" s="6" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="D334" s="6" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="335">
       <c r="B335" s="5" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="336">
       <c r="B336" s="6" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="D336" s="6" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="337">
       <c r="B337" s="5" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="338">
       <c r="B338" s="6" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="D338" s="6" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="339">
       <c r="B339" s="5" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="340">
       <c r="B340" s="6" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="D340" s="6" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="341">
       <c r="B341" s="5" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="342">
       <c r="B342" s="6" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="D342" s="6" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="343">
       <c r="B343" s="5" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="344">
       <c r="B344" s="6" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="D344" s="6" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="345">
       <c r="B345" s="5" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="D345" s="5" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="346">
       <c r="B346" s="6" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="D346" s="6" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="347">
       <c r="B347" s="5" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="348">
       <c r="B348" s="6" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="D348" s="6" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="349">
       <c r="B349" s="5" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="D349" s="5" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="350">
       <c r="B350" s="6" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="D350" s="6" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="351">
       <c r="B351" s="5" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="D351" s="5" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="352">
       <c r="B352" s="6" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="D352" s="6" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="353">
       <c r="B353" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="D353" s="5" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="354">
       <c r="B354" s="6" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="D354" s="6" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
     </row>
     <row r="355">
       <c r="B355" s="5" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="356">
       <c r="B356" s="6" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="D356" s="6" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="357">
       <c r="B357" s="5" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="D357" s="5" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="358">
       <c r="B358" s="6" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="D358" s="6" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="359">
       <c r="B359" s="5" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="D359" s="5" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="360">
       <c r="B360" s="6" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="D360" s="6" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="361">
       <c r="B361" s="5" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="D361" s="5" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="362">
       <c r="B362" s="6" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="D362" s="6" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="363">
       <c r="B363" s="5" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D363" s="5" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="364">
       <c r="B364" s="6" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="D364" s="6" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="365">
       <c r="B365" s="5" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="D365" s="5" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="366">
       <c r="B366" s="6" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="D366" s="6" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="367">
       <c r="B367" s="5" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="368">
       <c r="B368" s="6" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="D368" s="6" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="369">
       <c r="B369" s="5" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="370">
       <c r="B370" s="6" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="D370" s="6" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="371">
       <c r="B371" s="5" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="372">
       <c r="B372" s="6" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="D372" s="6" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="373">
       <c r="B373" s="5" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="D373" s="5" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="374">
       <c r="B374" s="6" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="D374" s="6" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="375">
       <c r="B375" s="5" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="D375" s="5" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="376">
       <c r="B376" s="6" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="D376" s="6" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="377">
       <c r="B377" s="5" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="D377" s="5" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="378">
       <c r="B378" s="6" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="D378" s="6" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="379">
       <c r="B379" s="5" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="D379" s="5" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="380">
       <c r="B380" s="6" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="D380" s="6" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="381">
       <c r="B381" s="5" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="382">
       <c r="B382" s="6" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="D382" s="6" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="383">
       <c r="B383" s="5" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="D383" s="5" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="384">
       <c r="B384" s="6" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="D384" s="6" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="385">
       <c r="B385" s="5" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="D385" s="5" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="386">
       <c r="B386" s="6" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="D386" s="6" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="387">
       <c r="B387" s="5" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="388">
       <c r="B388" s="6" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="D388" s="6" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="389">
       <c r="B389" s="5" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="D389" s="5" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="390">
       <c r="B390" s="6" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="D390" s="6" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="391">
       <c r="B391" s="5" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="D391" s="5" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="392">
       <c r="B392" s="6" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="393">
       <c r="B393" s="5" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="D393" s="5" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="394">
       <c r="B394" s="6" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="D394" s="6" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="395">
       <c r="B395" s="5" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="D395" s="5" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="396">
       <c r="B396" s="6" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="D396" s="6" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="397">
       <c r="B397" s="5" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="398">
       <c r="B398" s="6" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="D398" s="6" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="399">
       <c r="B399" s="5" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="D399" s="5" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="400">
       <c r="B400" s="6" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D400" s="6" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="401">
       <c r="B401" s="5" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="D401" s="5" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="402">
       <c r="B402" s="6" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="D402" s="6" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="403">
       <c r="B403" s="5" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="404">
       <c r="B404" s="6" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="D404" s="6" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="405">
       <c r="B405" s="5" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="406">
       <c r="B406" s="6" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="D406" s="6" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="407">
       <c r="B407" s="5" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="408">
       <c r="B408" s="6" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="D408" s="6" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="409">
       <c r="B409" s="5" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="410">
       <c r="B410" s="6" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="D410" s="6" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="411">
       <c r="B411" s="5" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="412">
       <c r="B412" s="6" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="D412" s="6" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="413">
       <c r="B413" s="5" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="414">
       <c r="B414" s="6" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="D414" s="6" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="415">
       <c r="B415" s="5" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="416">
       <c r="B416" s="6" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="D416" s="6" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="417">
       <c r="B417" s="5" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="418">
       <c r="B418" s="6" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="D418" s="6" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="419">
       <c r="B419" s="5" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="420">
       <c r="B420" s="6" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="D420" s="6" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="421">
       <c r="B421" s="5" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="422">
       <c r="B422" s="6" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="D422" s="6" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="423">
       <c r="B423" s="5" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="424">
       <c r="B424" s="6" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="D424" s="6" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="425">
       <c r="B425" s="5" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="426">
       <c r="B426" s="6" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="D426" s="6" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="427">
       <c r="B427" s="5" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="428">
       <c r="B428" s="6" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="D428" s="6" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="429">
       <c r="B429" s="5" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="430">
       <c r="B430" s="6" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="D430" s="6" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="431">
       <c r="B431" s="5" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="432">
       <c r="B432" s="6" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="D432" s="6" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="433">
       <c r="B433" s="5" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="D433" s="5" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="434">
       <c r="B434" s="6" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="D434" s="6" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="435">
       <c r="B435" s="5" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="D435" s="5" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="436">
       <c r="B436" s="6" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="D436" s="6" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="437">
       <c r="B437" s="5" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="D437" s="5" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="438">
       <c r="B438" s="6" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D438" s="6" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="439">
       <c r="B439" s="5" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="D439" s="5" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="440">
       <c r="B440" s="6" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="D440" s="6" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="441">
       <c r="B441" s="5" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="D441" s="5" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="442">
       <c r="B442" s="6" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="D442" s="6" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="443">
       <c r="B443" s="5" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="D443" s="5" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="444">
       <c r="B444" s="6" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="D444" s="6" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="445">
       <c r="B445" s="5" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="D445" s="5" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="446">
       <c r="B446" s="6" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="D446" s="6" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="447">
       <c r="B447" s="5" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="D447" s="5" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="448">
       <c r="B448" s="6" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="D448" s="6" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="449">
       <c r="B449" s="5" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="D449" s="5" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="450">
       <c r="B450" s="6" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="D450" s="6" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="451">
       <c r="B451" s="5" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="D451" s="5" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="452">
       <c r="B452" s="6" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="D452" s="6" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="453">
       <c r="B453" s="5" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="D453" s="5" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="454">
       <c r="B454" s="6" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="C454" s="6" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="D454" s="6" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="455">
       <c r="B455" s="5" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="D455" s="5" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="456">
       <c r="B456" s="6" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="C456" s="6" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="D456" s="6" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="457">
       <c r="B457" s="5" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
       <c r="D457" s="5" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="458">
       <c r="B458" s="6" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="C458" s="6" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="D458" s="6" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="459">
       <c r="B459" s="5" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="D459" s="5" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="460">
       <c r="B460" s="6" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="D460" s="6" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="461">
       <c r="B461" s="5" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="D461" s="5" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="462">
       <c r="B462" s="6" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="C462" s="6" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="D462" s="6" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="463">
       <c r="B463" s="5" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="D463" s="5" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="464">
       <c r="B464" s="6" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="C464" s="6" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="D464" s="6" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="465">
       <c r="B465" s="5" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="D465" s="5" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="466">
       <c r="B466" s="6" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>1379</v>
+        <v>1387</v>
       </c>
       <c r="D466" s="6" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="467">
       <c r="B467" s="5" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="D467" s="5" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="468">
       <c r="B468" s="6" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D468" s="6" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="469">
       <c r="B469" s="5" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="D469" s="5" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="470">
       <c r="B470" s="6" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
       <c r="C470" s="6" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="D470" s="6" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="471">
       <c r="B471" s="5" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="D471" s="5" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="472">
       <c r="B472" s="6" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="C472" s="6" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="D472" s="6" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="473">
       <c r="B473" s="5" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="D473" s="5" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="474">
       <c r="B474" s="6" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="D474" s="6" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="475">
       <c r="B475" s="5" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="D475" s="5" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="476">
       <c r="B476" s="6" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="D476" s="6" t="s">
-        <v>1409</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="477">
       <c r="B477" s="5" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="D477" s="5" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="478">
       <c r="B478" s="6" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="D478" s="6" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="479">
       <c r="B479" s="5" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
       <c r="D479" s="5" t="s">
-        <v>1418</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="480">
       <c r="B480" s="6" t="s">
-        <v>1419</v>
+        <v>1427</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="D480" s="6" t="s">
-        <v>1421</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="481">
       <c r="B481" s="5" t="s">
-        <v>1422</v>
+        <v>1430</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>1423</v>
+        <v>1431</v>
       </c>
       <c r="D481" s="5" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="482">
       <c r="B482" s="6" t="s">
-        <v>1425</v>
+        <v>1433</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>1426</v>
+        <v>1434</v>
       </c>
       <c r="D482" s="6" t="s">
-        <v>1427</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="483">
       <c r="B483" s="5" t="s">
-        <v>1428</v>
+        <v>1436</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="D483" s="5" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="484">
       <c r="B484" s="6" t="s">
-        <v>1431</v>
+        <v>1439</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="D484" s="6" t="s">
-        <v>1433</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="485">
       <c r="B485" s="5" t="s">
-        <v>1434</v>
+        <v>1442</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="D485" s="5" t="s">
-        <v>1436</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="486">
       <c r="B486" s="6" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="D486" s="6" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="487">
       <c r="B487" s="5" t="s">
-        <v>1440</v>
+        <v>1448</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>1441</v>
+        <v>1449</v>
       </c>
       <c r="D487" s="5" t="s">
-        <v>1442</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="488">
       <c r="B488" s="6" t="s">
-        <v>1443</v>
+        <v>1451</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>1444</v>
+        <v>1452</v>
       </c>
       <c r="D488" s="6" t="s">
-        <v>1445</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="489">
       <c r="B489" s="5" t="s">
-        <v>1446</v>
+        <v>1454</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="D489" s="5" t="s">
-        <v>1448</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="490">
       <c r="B490" s="6" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="D490" s="6" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="491">
       <c r="B491" s="5" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>1453</v>
+        <v>1461</v>
       </c>
       <c r="D491" s="5" t="s">
-        <v>1454</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="492">
       <c r="B492" s="6" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="D492" s="6" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="493">
       <c r="B493" s="5" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
       <c r="D493" s="5" t="s">
-        <v>1460</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="494">
       <c r="B494" s="6" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="D494" s="6" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="495">
       <c r="B495" s="5" t="s">
-        <v>1464</v>
+        <v>1472</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="D495" s="5" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="496">
       <c r="B496" s="6" t="s">
-        <v>1467</v>
+        <v>1475</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="D496" s="6" t="s">
-        <v>1469</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="497">
       <c r="B497" s="5" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="D497" s="5" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="498">
       <c r="B498" s="6" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="D498" s="6" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="499">
       <c r="B499" s="5" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
       <c r="D499" s="5" t="s">
-        <v>1478</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="500">
       <c r="B500" s="6" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="D500" s="6" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="501">
       <c r="B501" s="5" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
       <c r="D501" s="5" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="502">
       <c r="B502" s="6" t="s">
-        <v>1485</v>
+        <v>1493</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
       <c r="D502" s="6" t="s">
-        <v>1487</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="503">
       <c r="B503" s="5" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>1489</v>
+        <v>1497</v>
       </c>
       <c r="D503" s="5" t="s">
-        <v>1490</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="504">
       <c r="B504" s="6" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1492</v>
+        <v>1500</v>
       </c>
       <c r="D504" s="6" t="s">
-        <v>1493</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="505">
       <c r="B505" s="5" t="s">
-        <v>1494</v>
+        <v>1502</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>1495</v>
+        <v>1503</v>
       </c>
       <c r="D505" s="5" t="s">
-        <v>1496</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="506">
       <c r="B506" s="6" t="s">
-        <v>1497</v>
+        <v>1505</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>1498</v>
+        <v>1506</v>
       </c>
       <c r="D506" s="6" t="s">
-        <v>1499</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="507">
       <c r="B507" s="5" t="s">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>1501</v>
+        <v>1509</v>
       </c>
       <c r="D507" s="5" t="s">
-        <v>1502</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="508">
       <c r="B508" s="6" t="s">
-        <v>1503</v>
+        <v>1511</v>
       </c>
       <c r="C508" s="6" t="s">
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="D508" s="6" t="s">
-        <v>1505</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="509">
       <c r="B509" s="5" t="s">
-        <v>1506</v>
+        <v>1514</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>1507</v>
+        <v>1515</v>
       </c>
       <c r="D509" s="5" t="s">
-        <v>1508</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="510">
       <c r="B510" s="6" t="s">
-        <v>1509</v>
+        <v>1517</v>
       </c>
       <c r="C510" s="6" t="s">
-        <v>1510</v>
+        <v>1518</v>
       </c>
       <c r="D510" s="6" t="s">
-        <v>1511</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="511">
       <c r="B511" s="5" t="s">
-        <v>1512</v>
+        <v>1520</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>1513</v>
+        <v>1521</v>
       </c>
       <c r="D511" s="5" t="s">
-        <v>1514</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="512">
       <c r="B512" s="6" t="s">
-        <v>1515</v>
+        <v>1523</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>1516</v>
+        <v>1524</v>
       </c>
       <c r="D512" s="6" t="s">
-        <v>1517</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="513">
       <c r="B513" s="5" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>1519</v>
+        <v>1527</v>
       </c>
       <c r="D513" s="5" t="s">
-        <v>1520</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="514">
       <c r="B514" s="6" t="s">
-        <v>1521</v>
+        <v>1529</v>
       </c>
       <c r="C514" s="6" t="s">
-        <v>1522</v>
+        <v>1530</v>
       </c>
       <c r="D514" s="6" t="s">
-        <v>1523</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="515">
       <c r="B515" s="5" t="s">
-        <v>1524</v>
+        <v>1532</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="D515" s="5" t="s">
-        <v>1526</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="516">
       <c r="B516" s="6" t="s">
-        <v>1527</v>
+        <v>1535</v>
       </c>
       <c r="C516" s="6" t="s">
-        <v>1528</v>
+        <v>1536</v>
       </c>
       <c r="D516" s="6" t="s">
-        <v>1529</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="517">
       <c r="B517" s="5" t="s">
-        <v>1530</v>
+        <v>1538</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>1531</v>
+        <v>1539</v>
       </c>
       <c r="D517" s="5" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="518">
       <c r="B518" s="6" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="C518" s="6" t="s">
-        <v>1534</v>
+        <v>1542</v>
       </c>
       <c r="D518" s="6" t="s">
-        <v>1535</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="519">
       <c r="B519" s="5" t="s">
-        <v>1536</v>
+        <v>1544</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="D519" s="5" t="s">
-        <v>1538</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="520">
       <c r="B520" s="6" t="s">
-        <v>1539</v>
+        <v>1547</v>
       </c>
       <c r="C520" s="6" t="s">
-        <v>1540</v>
+        <v>1548</v>
       </c>
       <c r="D520" s="6" t="s">
-        <v>1541</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="521">
       <c r="B521" s="5" t="s">
-        <v>1542</v>
+        <v>1550</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>1543</v>
+        <v>1551</v>
       </c>
       <c r="D521" s="5" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="522">
       <c r="B522" s="6" t="s">
-        <v>1545</v>
+        <v>1553</v>
       </c>
       <c r="C522" s="6" t="s">
-        <v>1546</v>
+        <v>1554</v>
       </c>
       <c r="D522" s="6" t="s">
-        <v>1547</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="523">
       <c r="B523" s="5" t="s">
-        <v>1548</v>
+        <v>1556</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>1549</v>
+        <v>1557</v>
       </c>
       <c r="D523" s="5" t="s">
-        <v>1550</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="524">
       <c r="B524" s="6" t="s">
-        <v>1551</v>
+        <v>1559</v>
       </c>
       <c r="C524" s="6" t="s">
-        <v>1552</v>
+        <v>1560</v>
       </c>
       <c r="D524" s="6" t="s">
-        <v>1553</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="525">
       <c r="B525" s="5" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>1555</v>
+        <v>1563</v>
       </c>
       <c r="D525" s="5" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="526">
       <c r="B526" s="6" t="s">
-        <v>1557</v>
+        <v>1565</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>1558</v>
+        <v>1566</v>
       </c>
       <c r="D526" s="6" t="s">
-        <v>1559</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="527">
       <c r="B527" s="5" t="s">
-        <v>1560</v>
+        <v>1568</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>1561</v>
+        <v>1569</v>
       </c>
       <c r="D527" s="5" t="s">
-        <v>1562</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="528">
       <c r="B528" s="6" t="s">
-        <v>1563</v>
+        <v>1571</v>
       </c>
       <c r="C528" s="6" t="s">
-        <v>1564</v>
+        <v>1572</v>
       </c>
       <c r="D528" s="6" t="s">
-        <v>1565</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="529">
       <c r="B529" s="5" t="s">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
       <c r="D529" s="5" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="530">
       <c r="B530" s="6" t="s">
-        <v>1569</v>
+        <v>1577</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>1570</v>
+        <v>1578</v>
       </c>
       <c r="D530" s="6" t="s">
-        <v>1571</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="531">
       <c r="B531" s="5" t="s">
-        <v>1572</v>
+        <v>1580</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>1573</v>
+        <v>1581</v>
       </c>
       <c r="D531" s="5" t="s">
-        <v>1574</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="532">
       <c r="B532" s="6" t="s">
-        <v>1575</v>
+        <v>1583</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="D532" s="6" t="s">
-        <v>1577</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="533">
       <c r="B533" s="5" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>1579</v>
+        <v>1587</v>
       </c>
       <c r="D533" s="5" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="534">
       <c r="B534" s="6" t="s">
-        <v>1581</v>
+        <v>1589</v>
       </c>
       <c r="C534" s="6" t="s">
-        <v>1582</v>
+        <v>1590</v>
       </c>
       <c r="D534" s="6" t="s">
-        <v>1583</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="535">
       <c r="B535" s="5" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>1585</v>
+        <v>1593</v>
       </c>
       <c r="D535" s="5" t="s">
-        <v>1586</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="536">
       <c r="B536" s="6" t="s">
-        <v>1587</v>
+        <v>1595</v>
       </c>
       <c r="C536" s="6" t="s">
-        <v>1588</v>
+        <v>1596</v>
       </c>
       <c r="D536" s="6" t="s">
-        <v>1589</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="537">
       <c r="B537" s="5" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="D537" s="5" t="s">
-        <v>1592</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="538">
       <c r="B538" s="6" t="s">
-        <v>1593</v>
+        <v>1601</v>
       </c>
       <c r="C538" s="6" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="D538" s="6" t="s">
-        <v>1595</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="539">
       <c r="B539" s="5" t="s">
-        <v>1596</v>
+        <v>1604</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>1597</v>
+        <v>1605</v>
       </c>
       <c r="D539" s="5" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="540">
       <c r="B540" s="6" t="s">
-        <v>1599</v>
+        <v>1607</v>
       </c>
       <c r="C540" s="6" t="s">
-        <v>1600</v>
+        <v>1608</v>
       </c>
       <c r="D540" s="6" t="s">
-        <v>1601</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="541">
       <c r="B541" s="5" t="s">
-        <v>1602</v>
+        <v>1610</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>1603</v>
+        <v>1611</v>
       </c>
       <c r="D541" s="5" t="s">
-        <v>1604</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="542">
       <c r="B542" s="6" t="s">
-        <v>1605</v>
+        <v>1613</v>
       </c>
       <c r="C542" s="6" t="s">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="D542" s="6" t="s">
-        <v>1607</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="543">
       <c r="B543" s="5" t="s">
-        <v>1608</v>
+        <v>1616</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="D543" s="5" t="s">
-        <v>1609</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="544">
       <c r="B544" s="6" t="s">
-        <v>1610</v>
+        <v>1618</v>
       </c>
       <c r="C544" s="6" t="s">
-        <v>1611</v>
+        <v>1619</v>
       </c>
       <c r="D544" s="6" t="s">
-        <v>1612</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="545">
       <c r="B545" s="5" t="s">
-        <v>1613</v>
+        <v>1621</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>1614</v>
+        <v>1622</v>
       </c>
       <c r="D545" s="5" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="546">
       <c r="B546" s="6" t="s">
-        <v>1616</v>
+        <v>1624</v>
       </c>
       <c r="C546" s="6" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="D546" s="6" t="s">
-        <v>1617</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="547">
       <c r="B547" s="5" t="s">
-        <v>1618</v>
+        <v>1626</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>1619</v>
+        <v>1627</v>
       </c>
       <c r="D547" s="5" t="s">
-        <v>1620</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="548">
       <c r="B548" s="6" t="s">
-        <v>1621</v>
+        <v>1629</v>
       </c>
       <c r="C548" s="6" t="s">
-        <v>1622</v>
+        <v>1630</v>
       </c>
       <c r="D548" s="6" t="s">
-        <v>1623</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="549">
       <c r="B549" s="5" t="s">
-        <v>1624</v>
+        <v>1632</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>1625</v>
+        <v>1633</v>
       </c>
       <c r="D549" s="5" t="s">
-        <v>1626</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="550">
       <c r="B550" s="6" t="s">
-        <v>1627</v>
+        <v>1635</v>
       </c>
       <c r="C550" s="6" t="s">
-        <v>1628</v>
+        <v>1636</v>
       </c>
       <c r="D550" s="6" t="s">
-        <v>1629</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="551">
       <c r="B551" s="5" t="s">
-        <v>1630</v>
+        <v>1638</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="D551" s="5" t="s">
-        <v>1632</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="552">
       <c r="B552" s="6" t="s">
-        <v>1633</v>
+        <v>1641</v>
       </c>
       <c r="C552" s="6" t="s">
-        <v>1634</v>
+        <v>1642</v>
       </c>
       <c r="D552" s="6" t="s">
-        <v>1635</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="553">
       <c r="B553" s="5" t="s">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>1637</v>
+        <v>1645</v>
       </c>
       <c r="D553" s="5" t="s">
-        <v>1638</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="554">
       <c r="B554" s="6" t="s">
-        <v>1639</v>
+        <v>1647</v>
       </c>
       <c r="C554" s="6" t="s">
-        <v>1640</v>
+        <v>1648</v>
       </c>
       <c r="D554" s="6" t="s">
-        <v>1641</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="555">
       <c r="B555" s="5" t="s">
-        <v>1642</v>
+        <v>1650</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>1643</v>
+        <v>1651</v>
       </c>
       <c r="D555" s="5" t="s">
-        <v>1644</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="556">
       <c r="B556" s="6" t="s">
-        <v>1645</v>
+        <v>1653</v>
       </c>
       <c r="C556" s="6" t="s">
-        <v>1646</v>
+        <v>1654</v>
       </c>
       <c r="D556" s="6" t="s">
-        <v>1647</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="557">
       <c r="B557" s="5" t="s">
-        <v>1648</v>
+        <v>1656</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>1649</v>
+        <v>1657</v>
       </c>
       <c r="D557" s="5" t="s">
-        <v>1650</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="558">
       <c r="B558" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="C558" s="6" t="s">
-        <v>1652</v>
+        <v>1660</v>
       </c>
       <c r="D558" s="6" t="s">
-        <v>1653</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="559">
       <c r="B559" s="5" t="s">
-        <v>1654</v>
+        <v>1662</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>1655</v>
+        <v>1663</v>
       </c>
       <c r="D559" s="5" t="s">
-        <v>1656</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="560">
       <c r="B560" s="6" t="s">
-        <v>1657</v>
+        <v>1665</v>
       </c>
       <c r="C560" s="6" t="s">
-        <v>1658</v>
+        <v>1666</v>
       </c>
       <c r="D560" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="561">
       <c r="B561" s="5" t="s">
-        <v>1660</v>
+        <v>1668</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>1661</v>
+        <v>1669</v>
       </c>
       <c r="D561" s="5" t="s">
-        <v>1662</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="562">
       <c r="B562" s="6" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="C562" s="6" t="s">
-        <v>1664</v>
+        <v>1672</v>
       </c>
       <c r="D562" s="6" t="s">
-        <v>1665</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="563">
       <c r="B563" s="5" t="s">
-        <v>1666</v>
+        <v>1674</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>1667</v>
+        <v>1675</v>
       </c>
       <c r="D563" s="5" t="s">
-        <v>1668</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="564">
       <c r="B564" s="6" t="s">
-        <v>1669</v>
+        <v>1677</v>
       </c>
       <c r="C564" s="6" t="s">
-        <v>1670</v>
+        <v>1678</v>
       </c>
       <c r="D564" s="6" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="565">
       <c r="B565" s="5" t="s">
-        <v>1672</v>
+        <v>1680</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>1673</v>
+        <v>1681</v>
       </c>
       <c r="D565" s="5" t="s">
-        <v>1674</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="566">
       <c r="B566" s="6" t="s">
-        <v>1675</v>
+        <v>1683</v>
       </c>
       <c r="C566" s="6" t="s">
-        <v>1676</v>
+        <v>1684</v>
       </c>
       <c r="D566" s="6" t="s">
-        <v>1677</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="567">
       <c r="B567" s="5" t="s">
-        <v>1678</v>
+        <v>1686</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>1679</v>
+        <v>1687</v>
       </c>
       <c r="D567" s="5" t="s">
-        <v>1680</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="568">
       <c r="B568" s="6" t="s">
-        <v>1681</v>
+        <v>1689</v>
       </c>
       <c r="C568" s="6" t="s">
-        <v>1682</v>
+        <v>1690</v>
       </c>
       <c r="D568" s="6" t="s">
-        <v>1683</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="569">
       <c r="B569" s="5" t="s">
-        <v>1684</v>
+        <v>1692</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>1685</v>
+        <v>1693</v>
       </c>
       <c r="D569" s="5" t="s">
-        <v>1686</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="570">
       <c r="B570" s="6" t="s">
-        <v>1687</v>
+        <v>1695</v>
       </c>
       <c r="C570" s="6" t="s">
-        <v>1688</v>
+        <v>1696</v>
       </c>
       <c r="D570" s="6" t="s">
-        <v>1689</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="571">
       <c r="B571" s="5" t="s">
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>1691</v>
+        <v>1699</v>
       </c>
       <c r="D571" s="5" t="s">
-        <v>1692</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="572">
       <c r="B572" s="6" t="s">
-        <v>1693</v>
+        <v>1701</v>
       </c>
       <c r="C572" s="6" t="s">
-        <v>1694</v>
+        <v>1702</v>
       </c>
       <c r="D572" s="6" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="573">
       <c r="B573" s="5" t="s">
-        <v>1696</v>
+        <v>1704</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>1697</v>
+        <v>1705</v>
       </c>
       <c r="D573" s="5" t="s">
-        <v>1698</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="574">
       <c r="B574" s="6" t="s">
-        <v>1699</v>
+        <v>1707</v>
       </c>
       <c r="C574" s="6" t="s">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="D574" s="6" t="s">
-        <v>1701</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="575">
       <c r="B575" s="5" t="s">
-        <v>1702</v>
+        <v>1710</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="D575" s="5" t="s">
-        <v>1704</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="576">
       <c r="B576" s="6" t="s">
-        <v>1705</v>
+        <v>1713</v>
       </c>
       <c r="C576" s="6" t="s">
-        <v>1706</v>
+        <v>1714</v>
       </c>
       <c r="D576" s="6" t="s">
-        <v>1707</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="577">
       <c r="B577" s="5" t="s">
-        <v>1708</v>
+        <v>1716</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>1709</v>
+        <v>1717</v>
       </c>
       <c r="D577" s="5" t="s">
-        <v>1710</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="578">
       <c r="B578" s="6" t="s">
-        <v>1711</v>
+        <v>1719</v>
       </c>
       <c r="C578" s="6" t="s">
-        <v>1712</v>
+        <v>1720</v>
       </c>
       <c r="D578" s="6" t="s">
-        <v>1713</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="579">
       <c r="B579" s="5" t="s">
-        <v>1714</v>
+        <v>1722</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>1715</v>
+        <v>1723</v>
       </c>
       <c r="D579" s="5" t="s">
-        <v>1716</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="580">
       <c r="B580" s="6" t="s">
-        <v>1717</v>
+        <v>1725</v>
       </c>
       <c r="C580" s="6" t="s">
-        <v>1718</v>
+        <v>1726</v>
       </c>
       <c r="D580" s="6" t="s">
-        <v>1719</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="581">
       <c r="B581" s="5" t="s">
-        <v>1720</v>
+        <v>1728</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>1721</v>
+        <v>1729</v>
       </c>
       <c r="D581" s="5" t="s">
-        <v>1722</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="582">
       <c r="B582" s="6" t="s">
-        <v>1723</v>
+        <v>1731</v>
       </c>
       <c r="C582" s="6" t="s">
-        <v>1724</v>
+        <v>1732</v>
       </c>
       <c r="D582" s="6" t="s">
-        <v>1725</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="583">
       <c r="B583" s="5" t="s">
-        <v>1726</v>
+        <v>1734</v>
       </c>
       <c r="C583" s="5" t="s">
-        <v>1727</v>
+        <v>1735</v>
       </c>
       <c r="D583" s="5" t="s">
-        <v>1728</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="584">
       <c r="B584" s="6" t="s">
-        <v>1729</v>
+        <v>1737</v>
       </c>
       <c r="C584" s="6" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="D584" s="6" t="s">
-        <v>1704</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="585">
       <c r="B585" s="5" t="s">
-        <v>1730</v>
+        <v>1738</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="D585" s="5" t="s">
-        <v>1701</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="586">
       <c r="B586" s="6" t="s">
-        <v>1731</v>
+        <v>1739</v>
       </c>
       <c r="C586" s="6" t="s">
-        <v>1732</v>
+        <v>1740</v>
       </c>
       <c r="D586" s="6" t="s">
-        <v>1733</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="587">
       <c r="B587" s="5" t="s">
-        <v>1734</v>
+        <v>1742</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>1735</v>
+        <v>1743</v>
       </c>
       <c r="D587" s="5" t="s">
-        <v>1736</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="588">
       <c r="B588" s="6" t="s">
-        <v>1737</v>
+        <v>1745</v>
       </c>
       <c r="C588" s="6" t="s">
-        <v>1738</v>
+        <v>1746</v>
       </c>
       <c r="D588" s="6" t="s">
-        <v>1739</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="589">
       <c r="B589" s="5" t="s">
-        <v>1740</v>
+        <v>1748</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>1741</v>
+        <v>1749</v>
       </c>
       <c r="D589" s="5" t="s">
-        <v>1742</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="590">
       <c r="B590" s="6" t="s">
-        <v>1743</v>
+        <v>1751</v>
       </c>
       <c r="C590" s="6" t="s">
-        <v>1744</v>
+        <v>1752</v>
       </c>
       <c r="D590" s="6" t="s">
-        <v>1745</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="591">
       <c r="B591" s="5" t="s">
-        <v>1746</v>
+        <v>1754</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>1747</v>
+        <v>1755</v>
       </c>
       <c r="D591" s="5" t="s">
-        <v>1748</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="592">
       <c r="B592" s="6" t="s">
-        <v>1749</v>
+        <v>1757</v>
       </c>
       <c r="C592" s="6" t="s">
-        <v>1750</v>
+        <v>1758</v>
       </c>
       <c r="D592" s="6" t="s">
-        <v>1751</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="593">
       <c r="B593" s="5" t="s">
-        <v>1752</v>
+        <v>1760</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>1753</v>
+        <v>1761</v>
       </c>
       <c r="D593" s="5" t="s">
-        <v>1754</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="594">
       <c r="B594" s="6" t="s">
-        <v>1755</v>
+        <v>1763</v>
       </c>
       <c r="C594" s="6" t="s">
-        <v>1756</v>
+        <v>1764</v>
       </c>
       <c r="D594" s="6" t="s">
-        <v>1757</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="595">
       <c r="B595" s="5" t="s">
-        <v>1758</v>
+        <v>1766</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>1759</v>
+        <v>1767</v>
       </c>
       <c r="D595" s="5" t="s">
-        <v>1760</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="596">
       <c r="B596" s="6" t="s">
-        <v>1761</v>
+        <v>1769</v>
       </c>
       <c r="C596" s="6" t="s">
-        <v>1762</v>
+        <v>1770</v>
       </c>
       <c r="D596" s="6" t="s">
-        <v>1763</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="597">
       <c r="B597" s="5" t="s">
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="C597" s="5" t="s">
-        <v>1765</v>
+        <v>1773</v>
       </c>
       <c r="D597" s="5" t="s">
-        <v>1766</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="598">
       <c r="B598" s="6" t="s">
-        <v>1767</v>
+        <v>1775</v>
       </c>
       <c r="C598" s="6" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="D598" s="6" t="s">
-        <v>1768</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="599">
       <c r="B599" s="5" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>1770</v>
+        <v>1778</v>
       </c>
       <c r="D599" s="5" t="s">
-        <v>1771</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="600">
       <c r="B600" s="6" t="s">
-        <v>1772</v>
+        <v>1780</v>
       </c>
       <c r="C600" s="6" t="s">
-        <v>1773</v>
+        <v>1781</v>
       </c>
       <c r="D600" s="6" t="s">
-        <v>1774</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="601">
       <c r="B601" s="5" t="s">
-        <v>1775</v>
+        <v>1783</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>1776</v>
+        <v>1784</v>
       </c>
       <c r="D601" s="5" t="s">
-        <v>1777</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="602">
       <c r="B602" s="6" t="s">
-        <v>1778</v>
+        <v>1786</v>
       </c>
       <c r="C602" s="6" t="s">
-        <v>1649</v>
+        <v>1657</v>
       </c>
       <c r="D602" s="6" t="s">
-        <v>1650</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="603">
       <c r="B603" s="5" t="s">
-        <v>1779</v>
+        <v>1787</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>1780</v>
+        <v>1788</v>
       </c>
       <c r="D603" s="5" t="s">
-        <v>1781</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="604">
       <c r="B604" s="6" t="s">
-        <v>1782</v>
+        <v>1790</v>
       </c>
       <c r="C604" s="6" t="s">
-        <v>1783</v>
+        <v>1791</v>
       </c>
       <c r="D604" s="6" t="s">
-        <v>1784</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="605">
       <c r="B605" s="5" t="s">
-        <v>1785</v>
+        <v>1793</v>
       </c>
       <c r="C605" s="5" t="s">
-        <v>1786</v>
+        <v>1794</v>
       </c>
       <c r="D605" s="5" t="s">
-        <v>1787</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="606">
       <c r="B606" s="6" t="s">
-        <v>1788</v>
+        <v>1796</v>
       </c>
       <c r="C606" s="6" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="D606" s="6" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="607">
       <c r="B607" s="5" t="s">
-        <v>1791</v>
+        <v>1799</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="D607" s="5" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="608">
       <c r="B608" s="6" t="s">
-        <v>1792</v>
+        <v>1800</v>
       </c>
       <c r="C608" s="6" t="s">
-        <v>1793</v>
+        <v>1801</v>
       </c>
       <c r="D608" s="6" t="s">
-        <v>1794</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="609">
       <c r="B609" s="5" t="s">
-        <v>1795</v>
+        <v>1803</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>1796</v>
+        <v>1804</v>
       </c>
       <c r="D609" s="5" t="s">
-        <v>1797</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="610">
       <c r="B610" s="6" t="s">
-        <v>1798</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="611">
       <c r="B611" s="5" t="s">
-        <v>1799</v>
+        <v>1807</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>1800</v>
+        <v>1808</v>
       </c>
       <c r="D611" s="5" t="s">
-        <v>1801</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="612">
       <c r="B612" s="6" t="s">
-        <v>1802</v>
+        <v>1810</v>
       </c>
       <c r="C612" s="6" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D612" s="6" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="613">
       <c r="B613" s="5" t="s">
-        <v>1805</v>
+        <v>1813</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>1806</v>
+        <v>1814</v>
       </c>
       <c r="D613" s="5" t="s">
-        <v>1807</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="614">
       <c r="B614" s="6" t="s">
-        <v>1808</v>
+        <v>1816</v>
       </c>
       <c r="C614" s="6" t="s">
-        <v>1809</v>
+        <v>1817</v>
       </c>
       <c r="D614" s="6" t="s">
-        <v>1810</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="615">
       <c r="B615" s="5" t="s">
-        <v>1811</v>
+        <v>1819</v>
       </c>
       <c r="C615" s="5" t="s">
-        <v>1812</v>
+        <v>1820</v>
       </c>
       <c r="D615" s="5" t="s">
-        <v>1813</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="616">
       <c r="B616" s="6" t="s">
-        <v>1814</v>
+        <v>1822</v>
       </c>
       <c r="C616" s="6" t="s">
-        <v>1815</v>
+        <v>1823</v>
       </c>
       <c r="D616" s="6" t="s">
-        <v>1816</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="617">
       <c r="B617" s="5" t="s">
-        <v>1817</v>
+        <v>1825</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>1818</v>
+        <v>1826</v>
       </c>
       <c r="D617" s="5" t="s">
-        <v>1819</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="618">
       <c r="B618" s="6" t="s">
-        <v>1820</v>
+        <v>1828</v>
       </c>
       <c r="C618" s="6" t="s">
-        <v>1821</v>
+        <v>1829</v>
       </c>
       <c r="D618" s="6" t="s">
-        <v>1822</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="619">
       <c r="B619" s="5" t="s">
-        <v>1823</v>
+        <v>1831</v>
       </c>
       <c r="C619" s="5" t="s">
-        <v>1824</v>
+        <v>1832</v>
       </c>
       <c r="D619" s="5" t="s">
-        <v>1825</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="620">
       <c r="B620" s="6" t="s">
-        <v>1826</v>
+        <v>1834</v>
       </c>
       <c r="C620" s="6" t="s">
-        <v>1827</v>
+        <v>1835</v>
       </c>
       <c r="D620" s="6" t="s">
-        <v>1828</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="621">
       <c r="B621" s="5" t="s">
-        <v>1829</v>
+        <v>1837</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>1830</v>
+        <v>1838</v>
       </c>
       <c r="D621" s="5" t="s">
-        <v>1831</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="622">
       <c r="B622" s="6" t="s">
-        <v>1832</v>
+        <v>1840</v>
       </c>
       <c r="C622" s="6" t="s">
-        <v>1833</v>
+        <v>1841</v>
       </c>
       <c r="D622" s="6" t="s">
-        <v>1834</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="623">
       <c r="B623" s="5" t="s">
-        <v>1835</v>
+        <v>1843</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>1836</v>
+        <v>1844</v>
       </c>
       <c r="D623" s="5" t="s">
-        <v>1837</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="624">
       <c r="B624" s="6" t="s">
-        <v>1838</v>
+        <v>1846</v>
       </c>
       <c r="C624" s="6" t="s">
-        <v>1839</v>
+        <v>1847</v>
       </c>
       <c r="D624" s="6" t="s">
-        <v>1840</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="625">
       <c r="B625" s="5" t="s">
-        <v>1841</v>
+        <v>1849</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>1842</v>
+        <v>1850</v>
       </c>
       <c r="D625" s="5" t="s">
-        <v>1843</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="626">
       <c r="B626" s="6" t="s">
-        <v>1844</v>
+        <v>1852</v>
       </c>
       <c r="C626" s="6" t="s">
-        <v>1845</v>
+        <v>1853</v>
       </c>
       <c r="D626" s="6" t="s">
-        <v>1846</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="627">
       <c r="B627" s="5" t="s">
-        <v>1847</v>
+        <v>1855</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>1848</v>
+        <v>1856</v>
       </c>
       <c r="D627" s="5" t="s">
-        <v>1849</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="628">
       <c r="B628" s="6" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="C628" s="6" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="D628" s="6" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="629">
       <c r="B629" s="5" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>1854</v>
+        <v>1862</v>
       </c>
       <c r="D629" s="5" t="s">
-        <v>1855</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="630">
       <c r="B630" s="6" t="s">
-        <v>1856</v>
+        <v>1864</v>
       </c>
       <c r="C630" s="6" t="s">
-        <v>1857</v>
+        <v>1865</v>
       </c>
       <c r="D630" s="6" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="631">
       <c r="B631" s="5" t="s">
-        <v>1859</v>
+        <v>1867</v>
       </c>
       <c r="C631" s="5" t="s">
-        <v>1860</v>
+        <v>1868</v>
       </c>
       <c r="D631" s="5" t="s">
-        <v>1861</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="632">
       <c r="B632" s="6" t="s">
-        <v>1862</v>
+        <v>1870</v>
       </c>
       <c r="C632" s="6" t="s">
-        <v>1863</v>
+        <v>1871</v>
       </c>
       <c r="D632" s="6" t="s">
-        <v>1864</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="633">
       <c r="B633" s="5" t="s">
-        <v>1865</v>
+        <v>1873</v>
       </c>
       <c r="C633" s="5" t="s">
-        <v>1866</v>
+        <v>1874</v>
       </c>
       <c r="D633" s="5" t="s">
-        <v>1867</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="634">
       <c r="B634" s="6" t="s">
-        <v>1868</v>
+        <v>1876</v>
       </c>
       <c r="C634" s="6" t="s">
-        <v>1869</v>
+        <v>1877</v>
       </c>
       <c r="D634" s="6" t="s">
-        <v>1870</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="635">
       <c r="B635" s="5" t="s">
-        <v>1871</v>
+        <v>1879</v>
       </c>
       <c r="C635" s="5" t="s">
-        <v>1872</v>
+        <v>1880</v>
       </c>
       <c r="D635" s="5" t="s">
-        <v>1873</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="636">
       <c r="B636" s="6" t="s">
-        <v>1874</v>
+        <v>1882</v>
       </c>
       <c r="C636" s="6" t="s">
-        <v>1875</v>
+        <v>1883</v>
       </c>
       <c r="D636" s="6" t="s">
-        <v>1876</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="637">
       <c r="B637" s="5" t="s">
-        <v>1877</v>
+        <v>1885</v>
       </c>
       <c r="C637" s="5" t="s">
-        <v>1878</v>
+        <v>1886</v>
       </c>
       <c r="D637" s="5" t="s">
-        <v>1879</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="638">
       <c r="B638" s="6" t="s">
-        <v>1880</v>
+        <v>1888</v>
       </c>
       <c r="C638" s="6" t="s">
-        <v>1881</v>
+        <v>1889</v>
       </c>
       <c r="D638" s="6" t="s">
-        <v>1882</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="639">
       <c r="B639" s="5" t="s">
-        <v>1883</v>
+        <v>1891</v>
       </c>
       <c r="C639" s="5" t="s">
-        <v>1884</v>
+        <v>1892</v>
       </c>
       <c r="D639" s="5" t="s">
-        <v>1885</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="640">
       <c r="B640" s="6" t="s">
-        <v>1886</v>
+        <v>1894</v>
       </c>
       <c r="C640" s="6" t="s">
-        <v>1887</v>
+        <v>1895</v>
       </c>
       <c r="D640" s="6" t="s">
-        <v>1888</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="641">
       <c r="B641" s="5" t="s">
-        <v>1889</v>
+        <v>1897</v>
       </c>
       <c r="C641" s="5" t="s">
-        <v>1890</v>
+        <v>1898</v>
       </c>
       <c r="D641" s="5" t="s">
-        <v>1891</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="642">
       <c r="B642" s="6" t="s">
-        <v>1892</v>
+        <v>1900</v>
       </c>
       <c r="C642" s="6" t="s">
-        <v>1893</v>
+        <v>1901</v>
       </c>
       <c r="D642" s="6" t="s">
-        <v>1894</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="643">
       <c r="B643" s="5" t="s">
-        <v>1895</v>
+        <v>1903</v>
       </c>
       <c r="C643" s="5" t="s">
-        <v>1896</v>
+        <v>1904</v>
       </c>
       <c r="D643" s="5" t="s">
-        <v>1897</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="644">
       <c r="B644" s="6" t="s">
-        <v>1898</v>
+        <v>1906</v>
       </c>
       <c r="C644" s="6" t="s">
-        <v>1899</v>
+        <v>1907</v>
       </c>
       <c r="D644" s="6" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="645">
       <c r="B645" s="5" t="s">
-        <v>1901</v>
+        <v>1909</v>
       </c>
       <c r="C645" s="5" t="s">
-        <v>1902</v>
+        <v>1910</v>
       </c>
       <c r="D645" s="5" t="s">
-        <v>1903</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="646">
       <c r="B646" s="6" t="s">
-        <v>1904</v>
+        <v>1912</v>
       </c>
       <c r="C646" s="6" t="s">
-        <v>1905</v>
+        <v>1913</v>
       </c>
       <c r="D646" s="6" t="s">
-        <v>1906</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="647">
       <c r="B647" s="5" t="s">
-        <v>1907</v>
+        <v>1915</v>
       </c>
       <c r="C647" s="5" t="s">
-        <v>1908</v>
+        <v>1916</v>
       </c>
       <c r="D647" s="5" t="s">
-        <v>1909</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="648">
       <c r="B648" s="6" t="s">
-        <v>1910</v>
+        <v>1918</v>
       </c>
       <c r="C648" s="6" t="s">
-        <v>1911</v>
+        <v>1919</v>
       </c>
       <c r="D648" s="6" t="s">
-        <v>1912</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="649">
       <c r="B649" s="5" t="s">
-        <v>1913</v>
+        <v>1921</v>
       </c>
       <c r="C649" s="5" t="s">
-        <v>1914</v>
+        <v>1922</v>
       </c>
       <c r="D649" s="5" t="s">
-        <v>1915</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="650">
       <c r="B650" s="6" t="s">
-        <v>1916</v>
+        <v>1924</v>
       </c>
       <c r="C650" s="6" t="s">
-        <v>1917</v>
+        <v>1925</v>
       </c>
       <c r="D650" s="6" t="s">
-        <v>1918</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="651">
       <c r="B651" s="5" t="s">
-        <v>1919</v>
+        <v>1927</v>
       </c>
       <c r="C651" s="5" t="s">
-        <v>1920</v>
+        <v>1928</v>
       </c>
       <c r="D651" s="5" t="s">
-        <v>1921</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="652">
       <c r="B652" s="6" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="C652" s="6" t="s">
-        <v>1923</v>
+        <v>1931</v>
       </c>
       <c r="D652" s="6" t="s">
-        <v>1924</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="653">
       <c r="B653" s="5" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="C653" s="5" t="s">
-        <v>1926</v>
+        <v>1934</v>
       </c>
       <c r="D653" s="5" t="s">
-        <v>1927</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="654">
       <c r="B654" s="6" t="s">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="C654" s="6" t="s">
-        <v>1929</v>
+        <v>1937</v>
       </c>
       <c r="D654" s="6" t="s">
-        <v>1930</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="655">
       <c r="B655" s="5" t="s">
-        <v>1931</v>
+        <v>1939</v>
       </c>
       <c r="C655" s="5" t="s">
-        <v>1932</v>
+        <v>1940</v>
       </c>
       <c r="D655" s="5" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="656">
       <c r="B656" s="6" t="s">
-        <v>1934</v>
+        <v>1942</v>
       </c>
       <c r="C656" s="6" t="s">
-        <v>1935</v>
+        <v>1943</v>
       </c>
       <c r="D656" s="6" t="s">
-        <v>1936</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="657">
       <c r="B657" s="5" t="s">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="C657" s="5" t="s">
-        <v>1938</v>
+        <v>1946</v>
       </c>
       <c r="D657" s="5" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="658">
       <c r="B658" s="6" t="s">
-        <v>1940</v>
+        <v>1948</v>
       </c>
       <c r="C658" s="6" t="s">
-        <v>1941</v>
+        <v>1949</v>
       </c>
       <c r="D658" s="6" t="s">
-        <v>1942</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="659">
       <c r="B659" s="5" t="s">
-        <v>1943</v>
+        <v>1951</v>
       </c>
       <c r="C659" s="5" t="s">
-        <v>1944</v>
+        <v>1952</v>
       </c>
       <c r="D659" s="5" t="s">
-        <v>1945</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="660">
       <c r="B660" s="6" t="s">
-        <v>1946</v>
+        <v>1954</v>
       </c>
       <c r="C660" s="6" t="s">
-        <v>1947</v>
+        <v>1955</v>
       </c>
       <c r="D660" s="6" t="s">
-        <v>1948</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="661">
       <c r="B661" s="5" t="s">
-        <v>1949</v>
+        <v>1957</v>
       </c>
       <c r="C661" s="5" t="s">
-        <v>1950</v>
+        <v>1958</v>
       </c>
       <c r="D661" s="5" t="s">
-        <v>1951</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="662">
       <c r="B662" s="6" t="s">
-        <v>1952</v>
+        <v>1960</v>
       </c>
       <c r="C662" s="6" t="s">
-        <v>1953</v>
+        <v>1961</v>
       </c>
       <c r="D662" s="6" t="s">
-        <v>1954</v>
+        <v>1962</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:D662"/>
+  <autoFilter ref="B2:H662"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13541,10 +13608,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1955</v>
+        <v>1963</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1956</v>
+        <v>1964</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -13555,61 +13622,61 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1957</v>
+        <v>1965</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1958</v>
+        <v>1966</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1959</v>
+        <v>1967</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1960</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1961</v>
+        <v>1969</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1962</v>
+        <v>1970</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1963</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1964</v>
+        <v>1972</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1965</v>
+        <v>1973</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1966</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>1967</v>
+        <v>1975</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1968</v>
+        <v>1976</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -13617,13 +13684,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>1969</v>
+        <v>1977</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -13631,13 +13698,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>1971</v>
+        <v>1979</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -13645,13 +13712,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>1973</v>
+        <v>1981</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1974</v>
+        <v>1982</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -13659,13 +13726,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>1975</v>
+        <v>1983</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1976</v>
+        <v>1984</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -13673,13 +13740,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>1977</v>
+        <v>1985</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1978</v>
+        <v>1986</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -13687,13 +13754,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>1979</v>
+        <v>1987</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1980</v>
+        <v>1988</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -13701,13 +13768,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -13715,13 +13782,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>1983</v>
+        <v>1991</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1984</v>
+        <v>1992</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -13729,13 +13796,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1986</v>
+        <v>1994</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -13743,13 +13810,13 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>1768</v>
+        <v>1776</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1987</v>
+        <v>1995</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -13757,13 +13824,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>1988</v>
+        <v>1996</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -13771,13 +13838,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>1990</v>
+        <v>1998</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1991</v>
+        <v>1999</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -13785,13 +13852,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1993</v>
+        <v>2001</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -13799,13 +13866,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -13813,13 +13880,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>1996</v>
+        <v>2004</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -13827,13 +13894,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -13841,13 +13908,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -13855,13 +13922,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -13869,13 +13936,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -14857,43 +14857,43 @@
     <t xml:space="preserve">ui.title.tagline</t>
   </si>
   <si>
-    <t xml:space="preserve">조커를 모아 점수를 불리는 포커 로그라이크</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A poker roguelike about stacking Jokers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ジョーカーを重ねて得点を膨らませるポーカーローグライク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">收集小丑、放大分数的扑克 Roguelike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">收集小丑、放大分數的撲克 Roguelike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ein Poker-Roguelike, in dem Joker die Punkte türmen</t>
+    <t xml:space="preserve">숫자가 미쳐 날뛰는 포커 로그라이크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The poker roguelike where the numbers go feral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字が暴れ出すポーカーローグライク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字疯狂飙升的扑克 Roguelike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">數字瘋狂飆升的撲克 Roguelike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das Poker-Roguelike, in dem die Zahlen durchdrehen</t>
   </si>
   <si>
     <t xml:space="preserve">ui.title.note</t>
   </si>
   <si>
-    <t xml:space="preserve">안테 8까지. 조커 150종과 소모품 52종이 같은 패를 다른 점수로 만듭니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eight antes. 150 Jokers and 52 consumables turn the same hand into a different score.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アンティ8まで。ジョーカー150種と消耗品52種が、同じ手札を違う得点に変えます。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一路打到底注 8。150 种小丑与 52 种消耗品，让同一手牌得出不同的分数。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一路打到底注 8。150 種小丑與 52 種消耗品，讓同一手牌得出不同的分數。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acht Antes. 150 Joker und 52 Verbrauchsgegenstände machen aus derselben Hand eine andere Punktzahl.</t>
+    <t xml:space="preserve">조커 하나가 배수를 두 배로, 그다음 조커가 또 두 배로. 한 판이면 안 멈춥니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Joker doubles the mult. The next one doubles it again. One run is never one run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ジョーカー1枚が倍率を2倍に、次の1枚がまた2倍に。1ランでは終わりません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一个小丑让倍率翻倍，下一个再翻一倍。一局根本停不下来。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一個小丑讓倍率翻倍，下一個再翻一倍。一局根本停不下來。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein Joker verdoppelt den Mult. Der nächste verdoppelt ihn wieder. Ein Lauf bleibt nie einer.</t>
   </si>
   <si>
     <t xml:space="preserve">ui.guide.lead</t>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$851]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$853]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6020" uniqueCount="5401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="5414">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -16067,6 +16067,45 @@
   </si>
   <si>
     <t xml:space="preserve">+{n} 籌碼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.payout.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정산</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">精算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">結算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auszahlung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.payout.take</t>
+  </si>
+  <si>
+    <t xml:space="preserve">받는다  ${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Out  ${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受け取る  ${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">收下  ${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kassieren  ${n}</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -16419,7 +16458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H851"/>
+  <dimension ref="A1:H853"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -35964,8 +36003,54 @@
         <v>5319</v>
       </c>
     </row>
+    <row r="852">
+      <c r="B852" s="6" t="s">
+        <v>5350</v>
+      </c>
+      <c r="C852" s="6" t="s">
+        <v>5351</v>
+      </c>
+      <c r="D852" s="6" t="s">
+        <v>5352</v>
+      </c>
+      <c r="E852" s="6" t="s">
+        <v>5353</v>
+      </c>
+      <c r="F852" s="6" t="s">
+        <v>5354</v>
+      </c>
+      <c r="G852" s="6" t="s">
+        <v>5355</v>
+      </c>
+      <c r="H852" s="6" t="s">
+        <v>5356</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="B853" s="5" t="s">
+        <v>5357</v>
+      </c>
+      <c r="C853" s="5" t="s">
+        <v>5358</v>
+      </c>
+      <c r="D853" s="5" t="s">
+        <v>5359</v>
+      </c>
+      <c r="E853" s="5" t="s">
+        <v>5360</v>
+      </c>
+      <c r="F853" s="5" t="s">
+        <v>5361</v>
+      </c>
+      <c r="G853" s="5" t="s">
+        <v>5361</v>
+      </c>
+      <c r="H853" s="5" t="s">
+        <v>5362</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H851"/>
+  <autoFilter ref="B2:H853"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -35984,10 +36069,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5350</v>
+        <v>5363</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5351</v>
+        <v>5364</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -35998,16 +36083,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5352</v>
+        <v>5365</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5353</v>
+        <v>5366</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5354</v>
+        <v>5367</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5355</v>
+        <v>5368</v>
       </c>
     </row>
     <row r="3">
@@ -36015,16 +36100,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5356</v>
+        <v>5369</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5357</v>
+        <v>5370</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5358</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="4">
@@ -36035,24 +36120,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5359</v>
+        <v>5372</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5360</v>
+        <v>5373</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5361</v>
+        <v>5374</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5362</v>
+        <v>5375</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5363</v>
+        <v>5376</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36060,13 +36145,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5364</v>
+        <v>5377</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5365</v>
+        <v>5378</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36074,13 +36159,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5366</v>
+        <v>5379</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5367</v>
+        <v>5380</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36088,13 +36173,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5368</v>
+        <v>5381</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5369</v>
+        <v>5382</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36102,13 +36187,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5370</v>
+        <v>5383</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5371</v>
+        <v>5384</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36116,13 +36201,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5372</v>
+        <v>5385</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5373</v>
+        <v>5386</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36130,13 +36215,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5374</v>
+        <v>5387</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5375</v>
+        <v>5388</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36144,13 +36229,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5376</v>
+        <v>5389</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5377</v>
+        <v>5390</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36158,13 +36243,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5378</v>
+        <v>5391</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5379</v>
+        <v>5392</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36172,13 +36257,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5380</v>
+        <v>5393</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5381</v>
+        <v>5394</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36192,7 +36277,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5382</v>
+        <v>5395</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36200,13 +36285,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5383</v>
+        <v>5396</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5384</v>
+        <v>5397</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36214,13 +36299,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5385</v>
+        <v>5398</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5386</v>
+        <v>5399</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36228,13 +36313,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5387</v>
+        <v>5400</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5388</v>
+        <v>5401</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36242,13 +36327,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5389</v>
+        <v>5402</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5390</v>
+        <v>5403</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36256,13 +36341,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5391</v>
+        <v>5404</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5392</v>
+        <v>5405</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36270,13 +36355,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5393</v>
+        <v>5406</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5394</v>
+        <v>5407</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36284,13 +36369,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5395</v>
+        <v>5408</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5396</v>
+        <v>5409</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36298,13 +36383,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5397</v>
+        <v>5410</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5398</v>
+        <v>5411</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36312,13 +36397,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5399</v>
+        <v>5412</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5400</v>
+        <v>5413</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="5414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="5410">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -15877,19 +15877,7 @@
     <t xml:space="preserve">ui.stat.deck</t>
   </si>
   <si>
-    <t xml:space="preserve">덱  {left} / {all}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deck  {left} / {all}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デッキ  {left} / {all}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">牌组  {left} / {all}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">牌組  {left} / {all}</t>
+    <t xml:space="preserve">{left} / {all}</t>
   </si>
   <si>
     <t xml:space="preserve">ui.stat.ante</t>
@@ -35758,295 +35746,295 @@
         <v>5286</v>
       </c>
       <c r="D841" s="5" t="s">
-        <v>5287</v>
+        <v>5286</v>
       </c>
       <c r="E841" s="5" t="s">
-        <v>5288</v>
+        <v>5286</v>
       </c>
       <c r="F841" s="5" t="s">
-        <v>5289</v>
+        <v>5286</v>
       </c>
       <c r="G841" s="5" t="s">
-        <v>5290</v>
+        <v>5286</v>
       </c>
       <c r="H841" s="5" t="s">
-        <v>5287</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
+        <v>5287</v>
+      </c>
+      <c r="C842" s="6" t="s">
+        <v>5288</v>
+      </c>
+      <c r="D842" s="6" t="s">
+        <v>5289</v>
+      </c>
+      <c r="E842" s="6" t="s">
+        <v>5290</v>
+      </c>
+      <c r="F842" s="6" t="s">
         <v>5291</v>
       </c>
-      <c r="C842" s="6" t="s">
-        <v>5292</v>
-      </c>
-      <c r="D842" s="6" t="s">
-        <v>5293</v>
-      </c>
-      <c r="E842" s="6" t="s">
-        <v>5294</v>
-      </c>
-      <c r="F842" s="6" t="s">
-        <v>5295</v>
-      </c>
       <c r="G842" s="6" t="s">
-        <v>5295</v>
+        <v>5291</v>
       </c>
       <c r="H842" s="6" t="s">
-        <v>5293</v>
+        <v>5289</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
+        <v>5292</v>
+      </c>
+      <c r="C843" s="5" t="s">
+        <v>5293</v>
+      </c>
+      <c r="D843" s="5" t="s">
+        <v>5294</v>
+      </c>
+      <c r="E843" s="5" t="s">
+        <v>5295</v>
+      </c>
+      <c r="F843" s="5" t="s">
         <v>5296</v>
       </c>
-      <c r="C843" s="5" t="s">
+      <c r="G843" s="5" t="s">
         <v>5297</v>
       </c>
-      <c r="D843" s="5" t="s">
-        <v>5298</v>
-      </c>
-      <c r="E843" s="5" t="s">
-        <v>5299</v>
-      </c>
-      <c r="F843" s="5" t="s">
-        <v>5300</v>
-      </c>
-      <c r="G843" s="5" t="s">
-        <v>5301</v>
-      </c>
       <c r="H843" s="5" t="s">
-        <v>5298</v>
+        <v>5294</v>
       </c>
     </row>
     <row r="844">
       <c r="B844" s="6" t="s">
-        <v>5302</v>
+        <v>5298</v>
       </c>
       <c r="C844" s="6" t="s">
-        <v>5303</v>
+        <v>5299</v>
       </c>
       <c r="D844" s="6" t="s">
-        <v>5304</v>
+        <v>5300</v>
       </c>
       <c r="E844" s="6" t="s">
-        <v>5305</v>
+        <v>5301</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>5305</v>
+        <v>5301</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5305</v>
+        <v>5301</v>
       </c>
       <c r="H844" s="6" t="s">
-        <v>5304</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5306</v>
+        <v>5302</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>5307</v>
+        <v>5303</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5308</v>
+        <v>5304</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>5309</v>
+        <v>5305</v>
       </c>
       <c r="F845" s="5" t="s">
-        <v>5309</v>
+        <v>5305</v>
       </c>
       <c r="G845" s="5" t="s">
-        <v>5309</v>
+        <v>5305</v>
       </c>
       <c r="H845" s="5" t="s">
-        <v>5308</v>
+        <v>5304</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
+        <v>5306</v>
+      </c>
+      <c r="C846" s="6" t="s">
+        <v>5307</v>
+      </c>
+      <c r="D846" s="6" t="s">
+        <v>5308</v>
+      </c>
+      <c r="E846" s="6" t="s">
+        <v>5309</v>
+      </c>
+      <c r="F846" s="6" t="s">
         <v>5310</v>
       </c>
-      <c r="C846" s="6" t="s">
+      <c r="G846" s="6" t="s">
         <v>5311</v>
       </c>
-      <c r="D846" s="6" t="s">
+      <c r="H846" s="6" t="s">
         <v>5312</v>
-      </c>
-      <c r="E846" s="6" t="s">
-        <v>5313</v>
-      </c>
-      <c r="F846" s="6" t="s">
-        <v>5314</v>
-      </c>
-      <c r="G846" s="6" t="s">
-        <v>5315</v>
-      </c>
-      <c r="H846" s="6" t="s">
-        <v>5316</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
+        <v>5313</v>
+      </c>
+      <c r="C847" s="5" t="s">
+        <v>5314</v>
+      </c>
+      <c r="D847" s="5" t="s">
+        <v>5315</v>
+      </c>
+      <c r="E847" s="5" t="s">
+        <v>5316</v>
+      </c>
+      <c r="F847" s="5" t="s">
         <v>5317</v>
       </c>
-      <c r="C847" s="5" t="s">
+      <c r="G847" s="5" t="s">
         <v>5318</v>
       </c>
-      <c r="D847" s="5" t="s">
-        <v>5319</v>
-      </c>
-      <c r="E847" s="5" t="s">
-        <v>5320</v>
-      </c>
-      <c r="F847" s="5" t="s">
-        <v>5321</v>
-      </c>
-      <c r="G847" s="5" t="s">
-        <v>5322</v>
-      </c>
       <c r="H847" s="5" t="s">
-        <v>5319</v>
+        <v>5315</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
+        <v>5319</v>
+      </c>
+      <c r="C848" s="6" t="s">
+        <v>5320</v>
+      </c>
+      <c r="D848" s="6" t="s">
+        <v>5321</v>
+      </c>
+      <c r="E848" s="6" t="s">
+        <v>5322</v>
+      </c>
+      <c r="F848" s="6" t="s">
         <v>5323</v>
       </c>
-      <c r="C848" s="6" t="s">
+      <c r="G848" s="6" t="s">
         <v>5324</v>
       </c>
-      <c r="D848" s="6" t="s">
+      <c r="H848" s="6" t="s">
         <v>5325</v>
-      </c>
-      <c r="E848" s="6" t="s">
-        <v>5326</v>
-      </c>
-      <c r="F848" s="6" t="s">
-        <v>5327</v>
-      </c>
-      <c r="G848" s="6" t="s">
-        <v>5328</v>
-      </c>
-      <c r="H848" s="6" t="s">
-        <v>5329</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
+        <v>5326</v>
+      </c>
+      <c r="C849" s="5" t="s">
+        <v>5327</v>
+      </c>
+      <c r="D849" s="5" t="s">
+        <v>5328</v>
+      </c>
+      <c r="E849" s="5" t="s">
+        <v>5329</v>
+      </c>
+      <c r="F849" s="5" t="s">
         <v>5330</v>
       </c>
-      <c r="C849" s="5" t="s">
+      <c r="G849" s="5" t="s">
         <v>5331</v>
       </c>
-      <c r="D849" s="5" t="s">
+      <c r="H849" s="5" t="s">
         <v>5332</v>
-      </c>
-      <c r="E849" s="5" t="s">
-        <v>5333</v>
-      </c>
-      <c r="F849" s="5" t="s">
-        <v>5334</v>
-      </c>
-      <c r="G849" s="5" t="s">
-        <v>5335</v>
-      </c>
-      <c r="H849" s="5" t="s">
-        <v>5336</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
+        <v>5333</v>
+      </c>
+      <c r="C850" s="6" t="s">
+        <v>5334</v>
+      </c>
+      <c r="D850" s="6" t="s">
+        <v>5335</v>
+      </c>
+      <c r="E850" s="6" t="s">
+        <v>5336</v>
+      </c>
+      <c r="F850" s="6" t="s">
         <v>5337</v>
       </c>
-      <c r="C850" s="6" t="s">
+      <c r="G850" s="6" t="s">
         <v>5338</v>
       </c>
-      <c r="D850" s="6" t="s">
+      <c r="H850" s="6" t="s">
         <v>5339</v>
-      </c>
-      <c r="E850" s="6" t="s">
-        <v>5340</v>
-      </c>
-      <c r="F850" s="6" t="s">
-        <v>5341</v>
-      </c>
-      <c r="G850" s="6" t="s">
-        <v>5342</v>
-      </c>
-      <c r="H850" s="6" t="s">
-        <v>5343</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
+        <v>5340</v>
+      </c>
+      <c r="C851" s="5" t="s">
+        <v>5341</v>
+      </c>
+      <c r="D851" s="5" t="s">
+        <v>5342</v>
+      </c>
+      <c r="E851" s="5" t="s">
+        <v>5343</v>
+      </c>
+      <c r="F851" s="5" t="s">
         <v>5344</v>
       </c>
-      <c r="C851" s="5" t="s">
+      <c r="G851" s="5" t="s">
         <v>5345</v>
       </c>
-      <c r="D851" s="5" t="s">
-        <v>5346</v>
-      </c>
-      <c r="E851" s="5" t="s">
-        <v>5347</v>
-      </c>
-      <c r="F851" s="5" t="s">
-        <v>5348</v>
-      </c>
-      <c r="G851" s="5" t="s">
-        <v>5349</v>
-      </c>
       <c r="H851" s="5" t="s">
-        <v>5319</v>
+        <v>5315</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
+        <v>5346</v>
+      </c>
+      <c r="C852" s="6" t="s">
+        <v>5347</v>
+      </c>
+      <c r="D852" s="6" t="s">
+        <v>5348</v>
+      </c>
+      <c r="E852" s="6" t="s">
+        <v>5349</v>
+      </c>
+      <c r="F852" s="6" t="s">
         <v>5350</v>
       </c>
-      <c r="C852" s="6" t="s">
+      <c r="G852" s="6" t="s">
         <v>5351</v>
       </c>
-      <c r="D852" s="6" t="s">
+      <c r="H852" s="6" t="s">
         <v>5352</v>
-      </c>
-      <c r="E852" s="6" t="s">
-        <v>5353</v>
-      </c>
-      <c r="F852" s="6" t="s">
-        <v>5354</v>
-      </c>
-      <c r="G852" s="6" t="s">
-        <v>5355</v>
-      </c>
-      <c r="H852" s="6" t="s">
-        <v>5356</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
+        <v>5353</v>
+      </c>
+      <c r="C853" s="5" t="s">
+        <v>5354</v>
+      </c>
+      <c r="D853" s="5" t="s">
+        <v>5355</v>
+      </c>
+      <c r="E853" s="5" t="s">
+        <v>5356</v>
+      </c>
+      <c r="F853" s="5" t="s">
         <v>5357</v>
       </c>
-      <c r="C853" s="5" t="s">
+      <c r="G853" s="5" t="s">
+        <v>5357</v>
+      </c>
+      <c r="H853" s="5" t="s">
         <v>5358</v>
-      </c>
-      <c r="D853" s="5" t="s">
-        <v>5359</v>
-      </c>
-      <c r="E853" s="5" t="s">
-        <v>5360</v>
-      </c>
-      <c r="F853" s="5" t="s">
-        <v>5361</v>
-      </c>
-      <c r="G853" s="5" t="s">
-        <v>5361</v>
-      </c>
-      <c r="H853" s="5" t="s">
-        <v>5362</v>
       </c>
     </row>
   </sheetData>
@@ -36069,10 +36057,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5363</v>
+        <v>5359</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5364</v>
+        <v>5360</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36083,16 +36071,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5365</v>
+        <v>5361</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5366</v>
+        <v>5362</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5367</v>
+        <v>5363</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5368</v>
+        <v>5364</v>
       </c>
     </row>
     <row r="3">
@@ -36100,16 +36088,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5369</v>
+        <v>5365</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5370</v>
+        <v>5366</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5371</v>
+        <v>5367</v>
       </c>
     </row>
     <row r="4">
@@ -36120,24 +36108,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5372</v>
+        <v>5368</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5373</v>
+        <v>5369</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5374</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5375</v>
+        <v>5371</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5376</v>
+        <v>5372</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36145,13 +36133,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5377</v>
+        <v>5373</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5378</v>
+        <v>5374</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36159,13 +36147,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5379</v>
+        <v>5375</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5380</v>
+        <v>5376</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36173,13 +36161,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5381</v>
+        <v>5377</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5382</v>
+        <v>5378</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36187,13 +36175,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5383</v>
+        <v>5379</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5384</v>
+        <v>5380</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36201,13 +36189,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5385</v>
+        <v>5381</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5386</v>
+        <v>5382</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36215,13 +36203,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5387</v>
+        <v>5383</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5388</v>
+        <v>5384</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36229,13 +36217,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5389</v>
+        <v>5385</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5390</v>
+        <v>5386</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36243,13 +36231,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5391</v>
+        <v>5387</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5392</v>
+        <v>5388</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36257,13 +36245,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5393</v>
+        <v>5389</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5394</v>
+        <v>5390</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36277,7 +36265,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5395</v>
+        <v>5391</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36285,13 +36273,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5396</v>
+        <v>5392</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5397</v>
+        <v>5393</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36299,13 +36287,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5398</v>
+        <v>5394</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5399</v>
+        <v>5395</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36313,13 +36301,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5400</v>
+        <v>5396</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5401</v>
+        <v>5397</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36327,13 +36315,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5402</v>
+        <v>5398</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5403</v>
+        <v>5399</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36341,13 +36329,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5404</v>
+        <v>5400</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5405</v>
+        <v>5401</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36355,13 +36343,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5406</v>
+        <v>5402</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5407</v>
+        <v>5403</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36369,13 +36357,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5408</v>
+        <v>5404</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5409</v>
+        <v>5405</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36383,13 +36371,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5410</v>
+        <v>5406</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5411</v>
+        <v>5407</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36397,13 +36385,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5412</v>
+        <v>5408</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5413</v>
+        <v>5409</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$853]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$854]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="5410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6041" uniqueCount="5416">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -14747,6 +14747,24 @@
   </si>
   <si>
     <t xml:space="preserve">Der Gutschein dieser Ante ist schon gekauft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.shop.sold_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다 팔렸습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything is sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">すべて売れました</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全部售出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alles ist verkauft</t>
   </si>
   <si>
     <t xml:space="preserve">ui.edition.random</t>
@@ -16446,7 +16464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H853"/>
+  <dimension ref="A1:H854"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -34421,280 +34439,280 @@
         <v>4914</v>
       </c>
       <c r="G783" s="5" t="s">
+        <v>4914</v>
+      </c>
+      <c r="H783" s="5" t="s">
         <v>4915</v>
-      </c>
-      <c r="H783" s="5" t="s">
-        <v>4916</v>
       </c>
     </row>
     <row r="784">
       <c r="B784" s="6" t="s">
+        <v>4916</v>
+      </c>
+      <c r="C784" s="6" t="s">
         <v>4917</v>
       </c>
-      <c r="C784" s="6" t="s">
+      <c r="D784" s="6" t="s">
         <v>4918</v>
       </c>
-      <c r="D784" s="6" t="s">
+      <c r="E784" s="6" t="s">
         <v>4919</v>
       </c>
-      <c r="E784" s="6" t="s">
+      <c r="F784" s="6" t="s">
         <v>4920</v>
       </c>
-      <c r="F784" s="6" t="s">
+      <c r="G784" s="6" t="s">
         <v>4921</v>
       </c>
-      <c r="G784" s="6" t="s">
+      <c r="H784" s="6" t="s">
         <v>4922</v>
-      </c>
-      <c r="H784" s="6" t="s">
-        <v>4923</v>
       </c>
     </row>
     <row r="785">
       <c r="B785" s="5" t="s">
+        <v>4923</v>
+      </c>
+      <c r="C785" s="5" t="s">
         <v>4924</v>
       </c>
-      <c r="C785" s="5" t="s">
+      <c r="D785" s="5" t="s">
         <v>4925</v>
       </c>
-      <c r="D785" s="5" t="s">
+      <c r="E785" s="5" t="s">
         <v>4926</v>
       </c>
-      <c r="E785" s="5" t="s">
+      <c r="F785" s="5" t="s">
         <v>4927</v>
       </c>
-      <c r="F785" s="5" t="s">
+      <c r="G785" s="5" t="s">
         <v>4928</v>
       </c>
-      <c r="G785" s="5" t="s">
+      <c r="H785" s="5" t="s">
         <v>4929</v>
-      </c>
-      <c r="H785" s="5" t="s">
-        <v>4930</v>
       </c>
     </row>
     <row r="786">
       <c r="B786" s="6" t="s">
+        <v>4930</v>
+      </c>
+      <c r="C786" s="6" t="s">
         <v>4931</v>
       </c>
-      <c r="C786" s="6" t="s">
+      <c r="D786" s="6" t="s">
         <v>4932</v>
       </c>
-      <c r="D786" s="6" t="s">
+      <c r="E786" s="6" t="s">
         <v>4933</v>
       </c>
-      <c r="E786" s="6" t="s">
+      <c r="F786" s="6" t="s">
         <v>4934</v>
       </c>
-      <c r="F786" s="6" t="s">
+      <c r="G786" s="6" t="s">
         <v>4935</v>
       </c>
-      <c r="G786" s="6" t="s">
+      <c r="H786" s="6" t="s">
         <v>4936</v>
-      </c>
-      <c r="H786" s="6" t="s">
-        <v>4937</v>
       </c>
     </row>
     <row r="787">
       <c r="B787" s="5" t="s">
+        <v>4937</v>
+      </c>
+      <c r="C787" s="5" t="s">
         <v>4938</v>
       </c>
-      <c r="C787" s="5" t="s">
+      <c r="D787" s="5" t="s">
         <v>4939</v>
       </c>
-      <c r="D787" s="5" t="s">
+      <c r="E787" s="5" t="s">
         <v>4940</v>
       </c>
-      <c r="E787" s="5" t="s">
+      <c r="F787" s="5" t="s">
         <v>4941</v>
       </c>
-      <c r="F787" s="5" t="s">
+      <c r="G787" s="5" t="s">
         <v>4942</v>
       </c>
-      <c r="G787" s="5" t="s">
+      <c r="H787" s="5" t="s">
         <v>4943</v>
-      </c>
-      <c r="H787" s="5" t="s">
-        <v>4944</v>
       </c>
     </row>
     <row r="788">
       <c r="B788" s="6" t="s">
+        <v>4944</v>
+      </c>
+      <c r="C788" s="6" t="s">
         <v>4945</v>
       </c>
-      <c r="C788" s="6" t="s">
+      <c r="D788" s="6" t="s">
         <v>4946</v>
       </c>
-      <c r="D788" s="6" t="s">
+      <c r="E788" s="6" t="s">
         <v>4947</v>
       </c>
-      <c r="E788" s="6" t="s">
+      <c r="F788" s="6" t="s">
         <v>4948</v>
       </c>
-      <c r="F788" s="6" t="s">
+      <c r="G788" s="6" t="s">
         <v>4949</v>
       </c>
-      <c r="G788" s="6" t="s">
+      <c r="H788" s="6" t="s">
         <v>4950</v>
-      </c>
-      <c r="H788" s="6" t="s">
-        <v>4951</v>
       </c>
     </row>
     <row r="789">
       <c r="B789" s="5" t="s">
+        <v>4951</v>
+      </c>
+      <c r="C789" s="5" t="s">
         <v>4952</v>
       </c>
-      <c r="C789" s="5" t="s">
+      <c r="D789" s="5" t="s">
         <v>4953</v>
       </c>
-      <c r="D789" s="5" t="s">
+      <c r="E789" s="5" t="s">
         <v>4954</v>
       </c>
-      <c r="E789" s="5" t="s">
+      <c r="F789" s="5" t="s">
         <v>4955</v>
       </c>
-      <c r="F789" s="5" t="s">
+      <c r="G789" s="5" t="s">
         <v>4956</v>
       </c>
-      <c r="G789" s="5" t="s">
+      <c r="H789" s="5" t="s">
         <v>4957</v>
-      </c>
-      <c r="H789" s="5" t="s">
-        <v>4958</v>
       </c>
     </row>
     <row r="790">
       <c r="B790" s="6" t="s">
+        <v>4958</v>
+      </c>
+      <c r="C790" s="6" t="s">
         <v>4959</v>
       </c>
-      <c r="C790" s="6" t="s">
+      <c r="D790" s="6" t="s">
         <v>4960</v>
       </c>
-      <c r="D790" s="6" t="s">
+      <c r="E790" s="6" t="s">
         <v>4961</v>
       </c>
-      <c r="E790" s="6" t="s">
+      <c r="F790" s="6" t="s">
         <v>4962</v>
       </c>
-      <c r="F790" s="6" t="s">
+      <c r="G790" s="6" t="s">
         <v>4963</v>
       </c>
-      <c r="G790" s="6" t="s">
+      <c r="H790" s="6" t="s">
         <v>4964</v>
-      </c>
-      <c r="H790" s="6" t="s">
-        <v>4965</v>
       </c>
     </row>
     <row r="791">
       <c r="B791" s="5" t="s">
+        <v>4965</v>
+      </c>
+      <c r="C791" s="5" t="s">
         <v>4966</v>
-      </c>
-      <c r="C791" s="5" t="s">
-        <v>3021</v>
       </c>
       <c r="D791" s="5" t="s">
         <v>4967</v>
       </c>
       <c r="E791" s="5" t="s">
-        <v>3023</v>
+        <v>4968</v>
       </c>
       <c r="F791" s="5" t="s">
-        <v>4968</v>
+        <v>4969</v>
       </c>
       <c r="G791" s="5" t="s">
-        <v>4969</v>
+        <v>4970</v>
       </c>
       <c r="H791" s="5" t="s">
-        <v>4970</v>
+        <v>4971</v>
       </c>
     </row>
     <row r="792">
       <c r="B792" s="6" t="s">
-        <v>4971</v>
+        <v>4972</v>
       </c>
       <c r="C792" s="6" t="s">
-        <v>3014</v>
+        <v>3021</v>
       </c>
       <c r="D792" s="6" t="s">
-        <v>4972</v>
+        <v>4973</v>
       </c>
       <c r="E792" s="6" t="s">
-        <v>3016</v>
+        <v>3023</v>
       </c>
       <c r="F792" s="6" t="s">
-        <v>4973</v>
+        <v>4974</v>
       </c>
       <c r="G792" s="6" t="s">
-        <v>4974</v>
+        <v>4975</v>
       </c>
       <c r="H792" s="6" t="s">
-        <v>4975</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="793">
       <c r="B793" s="5" t="s">
-        <v>4976</v>
+        <v>4977</v>
       </c>
       <c r="C793" s="5" t="s">
-        <v>4977</v>
+        <v>3014</v>
       </c>
       <c r="D793" s="5" t="s">
         <v>4978</v>
       </c>
       <c r="E793" s="5" t="s">
+        <v>3016</v>
+      </c>
+      <c r="F793" s="5" t="s">
         <v>4979</v>
       </c>
-      <c r="F793" s="5" t="s">
+      <c r="G793" s="5" t="s">
         <v>4980</v>
       </c>
-      <c r="G793" s="5" t="s">
-        <v>4979</v>
-      </c>
       <c r="H793" s="5" t="s">
-        <v>4429</v>
+        <v>4981</v>
       </c>
     </row>
     <row r="794">
       <c r="B794" s="6" t="s">
-        <v>4981</v>
+        <v>4982</v>
       </c>
       <c r="C794" s="6" t="s">
-        <v>4982</v>
+        <v>4983</v>
       </c>
       <c r="D794" s="6" t="s">
-        <v>4983</v>
+        <v>4984</v>
       </c>
       <c r="E794" s="6" t="s">
-        <v>4984</v>
+        <v>4985</v>
       </c>
       <c r="F794" s="6" t="s">
+        <v>4986</v>
+      </c>
+      <c r="G794" s="6" t="s">
         <v>4985</v>
       </c>
-      <c r="G794" s="6" t="s">
-        <v>4986</v>
-      </c>
       <c r="H794" s="6" t="s">
-        <v>4987</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="795">
       <c r="B795" s="5" t="s">
+        <v>4987</v>
+      </c>
+      <c r="C795" s="5" t="s">
         <v>4988</v>
       </c>
-      <c r="C795" s="5" t="s">
+      <c r="D795" s="5" t="s">
         <v>4989</v>
       </c>
-      <c r="D795" s="5" t="s">
+      <c r="E795" s="5" t="s">
         <v>4990</v>
       </c>
-      <c r="E795" s="5" t="s">
+      <c r="F795" s="5" t="s">
         <v>4991</v>
-      </c>
-      <c r="F795" s="5" t="s">
-        <v>4992</v>
       </c>
       <c r="G795" s="5" t="s">
         <v>4992</v>
@@ -34720,211 +34738,211 @@
         <v>4998</v>
       </c>
       <c r="G796" s="6" t="s">
+        <v>4998</v>
+      </c>
+      <c r="H796" s="6" t="s">
         <v>4999</v>
-      </c>
-      <c r="H796" s="6" t="s">
-        <v>5000</v>
       </c>
     </row>
     <row r="797">
       <c r="B797" s="5" t="s">
+        <v>5000</v>
+      </c>
+      <c r="C797" s="5" t="s">
         <v>5001</v>
       </c>
-      <c r="C797" s="5" t="s">
+      <c r="D797" s="5" t="s">
         <v>5002</v>
       </c>
-      <c r="D797" s="5" t="s">
+      <c r="E797" s="5" t="s">
         <v>5003</v>
       </c>
-      <c r="E797" s="5" t="s">
+      <c r="F797" s="5" t="s">
         <v>5004</v>
       </c>
-      <c r="F797" s="5" t="s">
+      <c r="G797" s="5" t="s">
         <v>5005</v>
       </c>
-      <c r="G797" s="5" t="s">
+      <c r="H797" s="5" t="s">
         <v>5006</v>
-      </c>
-      <c r="H797" s="5" t="s">
-        <v>5007</v>
       </c>
     </row>
     <row r="798">
       <c r="B798" s="6" t="s">
+        <v>5007</v>
+      </c>
+      <c r="C798" s="6" t="s">
         <v>5008</v>
       </c>
-      <c r="C798" s="6" t="s">
+      <c r="D798" s="6" t="s">
         <v>5009</v>
       </c>
-      <c r="D798" s="6" t="s">
+      <c r="E798" s="6" t="s">
         <v>5010</v>
       </c>
-      <c r="E798" s="6" t="s">
+      <c r="F798" s="6" t="s">
         <v>5011</v>
       </c>
-      <c r="F798" s="6" t="s">
+      <c r="G798" s="6" t="s">
         <v>5012</v>
       </c>
-      <c r="G798" s="6" t="s">
+      <c r="H798" s="6" t="s">
         <v>5013</v>
-      </c>
-      <c r="H798" s="6" t="s">
-        <v>5014</v>
       </c>
     </row>
     <row r="799">
       <c r="B799" s="5" t="s">
+        <v>5014</v>
+      </c>
+      <c r="C799" s="5" t="s">
         <v>5015</v>
       </c>
-      <c r="C799" s="5" t="s">
+      <c r="D799" s="5" t="s">
         <v>5016</v>
       </c>
-      <c r="D799" s="5" t="s">
+      <c r="E799" s="5" t="s">
         <v>5017</v>
       </c>
-      <c r="E799" s="5" t="s">
+      <c r="F799" s="5" t="s">
         <v>5018</v>
       </c>
-      <c r="F799" s="5" t="s">
+      <c r="G799" s="5" t="s">
         <v>5019</v>
       </c>
-      <c r="G799" s="5" t="s">
+      <c r="H799" s="5" t="s">
         <v>5020</v>
-      </c>
-      <c r="H799" s="5" t="s">
-        <v>5021</v>
       </c>
     </row>
     <row r="800">
       <c r="B800" s="6" t="s">
+        <v>5021</v>
+      </c>
+      <c r="C800" s="6" t="s">
         <v>5022</v>
       </c>
-      <c r="C800" s="6" t="s">
+      <c r="D800" s="6" t="s">
         <v>5023</v>
       </c>
-      <c r="D800" s="6" t="s">
+      <c r="E800" s="6" t="s">
         <v>5024</v>
       </c>
-      <c r="E800" s="6" t="s">
+      <c r="F800" s="6" t="s">
         <v>5025</v>
       </c>
-      <c r="F800" s="6" t="s">
+      <c r="G800" s="6" t="s">
         <v>5026</v>
       </c>
-      <c r="G800" s="6" t="s">
+      <c r="H800" s="6" t="s">
         <v>5027</v>
-      </c>
-      <c r="H800" s="6" t="s">
-        <v>5028</v>
       </c>
     </row>
     <row r="801">
       <c r="B801" s="5" t="s">
+        <v>5028</v>
+      </c>
+      <c r="C801" s="5" t="s">
         <v>5029</v>
       </c>
-      <c r="C801" s="5" t="s">
+      <c r="D801" s="5" t="s">
         <v>5030</v>
       </c>
-      <c r="D801" s="5" t="s">
+      <c r="E801" s="5" t="s">
         <v>5031</v>
-      </c>
-      <c r="E801" s="5" t="s">
-        <v>5032</v>
       </c>
       <c r="F801" s="5" t="s">
         <v>5032</v>
       </c>
       <c r="G801" s="5" t="s">
-        <v>5032</v>
+        <v>5033</v>
       </c>
       <c r="H801" s="5" t="s">
-        <v>5033</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="802">
       <c r="B802" s="6" t="s">
-        <v>5034</v>
+        <v>5035</v>
       </c>
       <c r="C802" s="6" t="s">
-        <v>5035</v>
+        <v>5036</v>
       </c>
       <c r="D802" s="6" t="s">
-        <v>5036</v>
+        <v>5037</v>
       </c>
       <c r="E802" s="6" t="s">
-        <v>5037</v>
+        <v>5038</v>
       </c>
       <c r="F802" s="6" t="s">
         <v>5038</v>
       </c>
       <c r="G802" s="6" t="s">
+        <v>5038</v>
+      </c>
+      <c r="H802" s="6" t="s">
         <v>5039</v>
-      </c>
-      <c r="H802" s="6" t="s">
-        <v>5040</v>
       </c>
     </row>
     <row r="803">
       <c r="B803" s="5" t="s">
+        <v>5040</v>
+      </c>
+      <c r="C803" s="5" t="s">
         <v>5041</v>
       </c>
-      <c r="C803" s="5" t="s">
+      <c r="D803" s="5" t="s">
         <v>5042</v>
       </c>
-      <c r="D803" s="5" t="s">
+      <c r="E803" s="5" t="s">
         <v>5043</v>
       </c>
-      <c r="E803" s="5" t="s">
+      <c r="F803" s="5" t="s">
         <v>5044</v>
       </c>
-      <c r="F803" s="5" t="s">
+      <c r="G803" s="5" t="s">
         <v>5045</v>
       </c>
-      <c r="G803" s="5" t="s">
+      <c r="H803" s="5" t="s">
         <v>5046</v>
-      </c>
-      <c r="H803" s="5" t="s">
-        <v>5047</v>
       </c>
     </row>
     <row r="804">
       <c r="B804" s="6" t="s">
+        <v>5047</v>
+      </c>
+      <c r="C804" s="6" t="s">
         <v>5048</v>
       </c>
-      <c r="C804" s="6" t="s">
+      <c r="D804" s="6" t="s">
         <v>5049</v>
       </c>
-      <c r="D804" s="6" t="s">
+      <c r="E804" s="6" t="s">
         <v>5050</v>
       </c>
-      <c r="E804" s="6" t="s">
+      <c r="F804" s="6" t="s">
         <v>5051</v>
       </c>
-      <c r="F804" s="6" t="s">
+      <c r="G804" s="6" t="s">
         <v>5052</v>
       </c>
-      <c r="G804" s="6" t="s">
+      <c r="H804" s="6" t="s">
         <v>5053</v>
-      </c>
-      <c r="H804" s="6" t="s">
-        <v>5054</v>
       </c>
     </row>
     <row r="805">
       <c r="B805" s="5" t="s">
+        <v>5054</v>
+      </c>
+      <c r="C805" s="5" t="s">
         <v>5055</v>
       </c>
-      <c r="C805" s="5" t="s">
+      <c r="D805" s="5" t="s">
         <v>5056</v>
       </c>
-      <c r="D805" s="5" t="s">
+      <c r="E805" s="5" t="s">
         <v>5057</v>
       </c>
-      <c r="E805" s="5" t="s">
+      <c r="F805" s="5" t="s">
         <v>5058</v>
-      </c>
-      <c r="F805" s="5" t="s">
-        <v>5059</v>
       </c>
       <c r="G805" s="5" t="s">
         <v>5059</v>
@@ -34996,119 +35014,119 @@
         <v>5077</v>
       </c>
       <c r="G808" s="6" t="s">
+        <v>5077</v>
+      </c>
+      <c r="H808" s="6" t="s">
         <v>5078</v>
-      </c>
-      <c r="H808" s="6" t="s">
-        <v>5079</v>
       </c>
     </row>
     <row r="809">
       <c r="B809" s="5" t="s">
+        <v>5079</v>
+      </c>
+      <c r="C809" s="5" t="s">
         <v>5080</v>
       </c>
-      <c r="C809" s="5" t="s">
+      <c r="D809" s="5" t="s">
         <v>5081</v>
       </c>
-      <c r="D809" s="5" t="s">
+      <c r="E809" s="5" t="s">
         <v>5082</v>
       </c>
-      <c r="E809" s="5" t="s">
+      <c r="F809" s="5" t="s">
         <v>5083</v>
       </c>
-      <c r="F809" s="5" t="s">
+      <c r="G809" s="5" t="s">
         <v>5084</v>
       </c>
-      <c r="G809" s="5" t="s">
+      <c r="H809" s="5" t="s">
         <v>5085</v>
-      </c>
-      <c r="H809" s="5" t="s">
-        <v>5086</v>
       </c>
     </row>
     <row r="810">
       <c r="B810" s="6" t="s">
+        <v>5086</v>
+      </c>
+      <c r="C810" s="6" t="s">
         <v>5087</v>
       </c>
-      <c r="C810" s="6" t="s">
+      <c r="D810" s="6" t="s">
         <v>5088</v>
       </c>
-      <c r="D810" s="6" t="s">
+      <c r="E810" s="6" t="s">
         <v>5089</v>
       </c>
-      <c r="E810" s="6" t="s">
+      <c r="F810" s="6" t="s">
         <v>5090</v>
       </c>
-      <c r="F810" s="6" t="s">
+      <c r="G810" s="6" t="s">
         <v>5091</v>
       </c>
-      <c r="G810" s="6" t="s">
+      <c r="H810" s="6" t="s">
         <v>5092</v>
-      </c>
-      <c r="H810" s="6" t="s">
-        <v>5093</v>
       </c>
     </row>
     <row r="811">
       <c r="B811" s="5" t="s">
+        <v>5093</v>
+      </c>
+      <c r="C811" s="5" t="s">
         <v>5094</v>
       </c>
-      <c r="C811" s="5" t="s">
+      <c r="D811" s="5" t="s">
         <v>5095</v>
       </c>
-      <c r="D811" s="5" t="s">
+      <c r="E811" s="5" t="s">
         <v>5096</v>
       </c>
-      <c r="E811" s="5" t="s">
+      <c r="F811" s="5" t="s">
         <v>5097</v>
       </c>
-      <c r="F811" s="5" t="s">
+      <c r="G811" s="5" t="s">
         <v>5098</v>
       </c>
-      <c r="G811" s="5" t="s">
+      <c r="H811" s="5" t="s">
         <v>5099</v>
-      </c>
-      <c r="H811" s="5" t="s">
-        <v>5100</v>
       </c>
     </row>
     <row r="812">
       <c r="B812" s="6" t="s">
+        <v>5100</v>
+      </c>
+      <c r="C812" s="6" t="s">
         <v>5101</v>
       </c>
-      <c r="C812" s="6" t="s">
+      <c r="D812" s="6" t="s">
         <v>5102</v>
       </c>
-      <c r="D812" s="6" t="s">
+      <c r="E812" s="6" t="s">
         <v>5103</v>
       </c>
-      <c r="E812" s="6" t="s">
+      <c r="F812" s="6" t="s">
         <v>5104</v>
       </c>
-      <c r="F812" s="6" t="s">
+      <c r="G812" s="6" t="s">
         <v>5105</v>
       </c>
-      <c r="G812" s="6" t="s">
+      <c r="H812" s="6" t="s">
         <v>5106</v>
-      </c>
-      <c r="H812" s="6" t="s">
-        <v>5107</v>
       </c>
     </row>
     <row r="813">
       <c r="B813" s="5" t="s">
+        <v>5107</v>
+      </c>
+      <c r="C813" s="5" t="s">
         <v>5108</v>
       </c>
-      <c r="C813" s="5" t="s">
+      <c r="D813" s="5" t="s">
         <v>5109</v>
       </c>
-      <c r="D813" s="5" t="s">
+      <c r="E813" s="5" t="s">
         <v>5110</v>
       </c>
-      <c r="E813" s="5" t="s">
+      <c r="F813" s="5" t="s">
         <v>5111</v>
-      </c>
-      <c r="F813" s="5" t="s">
-        <v>5112</v>
       </c>
       <c r="G813" s="5" t="s">
         <v>5112</v>
@@ -35131,93 +35149,93 @@
         <v>5117</v>
       </c>
       <c r="F814" s="6" t="s">
-        <v>5117</v>
+        <v>5118</v>
       </c>
       <c r="G814" s="6" t="s">
-        <v>5117</v>
+        <v>5118</v>
       </c>
       <c r="H814" s="6" t="s">
-        <v>5116</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="815">
       <c r="B815" s="5" t="s">
-        <v>5118</v>
+        <v>5120</v>
       </c>
       <c r="C815" s="5" t="s">
-        <v>5119</v>
+        <v>5121</v>
       </c>
       <c r="D815" s="5" t="s">
-        <v>5120</v>
+        <v>5122</v>
       </c>
       <c r="E815" s="5" t="s">
-        <v>5121</v>
+        <v>5123</v>
       </c>
       <c r="F815" s="5" t="s">
-        <v>5122</v>
+        <v>5123</v>
       </c>
       <c r="G815" s="5" t="s">
         <v>5123</v>
       </c>
       <c r="H815" s="5" t="s">
-        <v>5124</v>
+        <v>5122</v>
       </c>
     </row>
     <row r="816">
       <c r="B816" s="6" t="s">
+        <v>5124</v>
+      </c>
+      <c r="C816" s="6" t="s">
         <v>5125</v>
       </c>
-      <c r="C816" s="6" t="s">
+      <c r="D816" s="6" t="s">
         <v>5126</v>
       </c>
-      <c r="D816" s="6" t="s">
+      <c r="E816" s="6" t="s">
         <v>5127</v>
       </c>
-      <c r="E816" s="6" t="s">
+      <c r="F816" s="6" t="s">
         <v>5128</v>
       </c>
-      <c r="F816" s="6" t="s">
+      <c r="G816" s="6" t="s">
         <v>5129</v>
       </c>
-      <c r="G816" s="6" t="s">
+      <c r="H816" s="6" t="s">
         <v>5130</v>
-      </c>
-      <c r="H816" s="6" t="s">
-        <v>5131</v>
       </c>
     </row>
     <row r="817">
       <c r="B817" s="5" t="s">
+        <v>5131</v>
+      </c>
+      <c r="C817" s="5" t="s">
         <v>5132</v>
       </c>
-      <c r="C817" s="5" t="s">
+      <c r="D817" s="5" t="s">
         <v>5133</v>
       </c>
-      <c r="D817" s="5" t="s">
+      <c r="E817" s="5" t="s">
         <v>5134</v>
       </c>
-      <c r="E817" s="5" t="s">
+      <c r="F817" s="5" t="s">
         <v>5135</v>
       </c>
-      <c r="F817" s="5" t="s">
+      <c r="G817" s="5" t="s">
         <v>5136</v>
       </c>
-      <c r="G817" s="5" t="s">
+      <c r="H817" s="5" t="s">
         <v>5137</v>
-      </c>
-      <c r="H817" s="5" t="s">
-        <v>5138</v>
       </c>
     </row>
     <row r="818">
       <c r="B818" s="6" t="s">
+        <v>5138</v>
+      </c>
+      <c r="C818" s="6" t="s">
         <v>5139</v>
       </c>
-      <c r="C818" s="6" t="s">
+      <c r="D818" s="6" t="s">
         <v>5140</v>
-      </c>
-      <c r="D818" s="6" t="s">
-        <v>5116</v>
       </c>
       <c r="E818" s="6" t="s">
         <v>5141</v>
@@ -35226,56 +35244,56 @@
         <v>5142</v>
       </c>
       <c r="G818" s="6" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="H818" s="6" t="s">
-        <v>5116</v>
+        <v>5144</v>
       </c>
     </row>
     <row r="819">
       <c r="B819" s="5" t="s">
-        <v>5143</v>
+        <v>5145</v>
       </c>
       <c r="C819" s="5" t="s">
-        <v>5144</v>
+        <v>5146</v>
       </c>
       <c r="D819" s="5" t="s">
-        <v>5145</v>
+        <v>5122</v>
       </c>
       <c r="E819" s="5" t="s">
-        <v>5146</v>
+        <v>5147</v>
       </c>
       <c r="F819" s="5" t="s">
-        <v>5147</v>
+        <v>5148</v>
       </c>
       <c r="G819" s="5" t="s">
         <v>5148</v>
       </c>
       <c r="H819" s="5" t="s">
-        <v>5149</v>
+        <v>5122</v>
       </c>
     </row>
     <row r="820">
       <c r="B820" s="6" t="s">
+        <v>5149</v>
+      </c>
+      <c r="C820" s="6" t="s">
         <v>5150</v>
       </c>
-      <c r="C820" s="6" t="s">
+      <c r="D820" s="6" t="s">
         <v>5151</v>
       </c>
-      <c r="D820" s="6" t="s">
+      <c r="E820" s="6" t="s">
         <v>5152</v>
       </c>
-      <c r="E820" s="6" t="s">
+      <c r="F820" s="6" t="s">
         <v>5153</v>
       </c>
-      <c r="F820" s="6" t="s">
+      <c r="G820" s="6" t="s">
         <v>5154</v>
       </c>
-      <c r="G820" s="6" t="s">
+      <c r="H820" s="6" t="s">
         <v>5155</v>
-      </c>
-      <c r="H820" s="6" t="s">
-        <v>5152</v>
       </c>
     </row>
     <row r="821">
@@ -35298,93 +35316,93 @@
         <v>5161</v>
       </c>
       <c r="H821" s="5" t="s">
-        <v>5162</v>
+        <v>5158</v>
       </c>
     </row>
     <row r="822">
       <c r="B822" s="6" t="s">
+        <v>5162</v>
+      </c>
+      <c r="C822" s="6" t="s">
         <v>5163</v>
       </c>
-      <c r="C822" s="6" t="s">
+      <c r="D822" s="6" t="s">
         <v>5164</v>
       </c>
-      <c r="D822" s="6" t="s">
+      <c r="E822" s="6" t="s">
         <v>5165</v>
       </c>
-      <c r="E822" s="6" t="s">
+      <c r="F822" s="6" t="s">
         <v>5166</v>
       </c>
-      <c r="F822" s="6" t="s">
+      <c r="G822" s="6" t="s">
         <v>5167</v>
       </c>
-      <c r="G822" s="6" t="s">
+      <c r="H822" s="6" t="s">
         <v>5168</v>
-      </c>
-      <c r="H822" s="6" t="s">
-        <v>5169</v>
       </c>
     </row>
     <row r="823">
       <c r="B823" s="5" t="s">
+        <v>5169</v>
+      </c>
+      <c r="C823" s="5" t="s">
         <v>5170</v>
       </c>
-      <c r="C823" s="5" t="s">
+      <c r="D823" s="5" t="s">
         <v>5171</v>
       </c>
-      <c r="D823" s="5" t="s">
+      <c r="E823" s="5" t="s">
         <v>5172</v>
       </c>
-      <c r="E823" s="5" t="s">
+      <c r="F823" s="5" t="s">
         <v>5173</v>
       </c>
-      <c r="F823" s="5" t="s">
+      <c r="G823" s="5" t="s">
         <v>5174</v>
       </c>
-      <c r="G823" s="5" t="s">
+      <c r="H823" s="5" t="s">
         <v>5175</v>
-      </c>
-      <c r="H823" s="5" t="s">
-        <v>5176</v>
       </c>
     </row>
     <row r="824">
       <c r="B824" s="6" t="s">
+        <v>5176</v>
+      </c>
+      <c r="C824" s="6" t="s">
         <v>5177</v>
       </c>
-      <c r="C824" s="6" t="s">
+      <c r="D824" s="6" t="s">
         <v>5178</v>
       </c>
-      <c r="D824" s="6" t="s">
+      <c r="E824" s="6" t="s">
         <v>5179</v>
       </c>
-      <c r="E824" s="6" t="s">
+      <c r="F824" s="6" t="s">
         <v>5180</v>
       </c>
-      <c r="F824" s="6" t="s">
+      <c r="G824" s="6" t="s">
         <v>5181</v>
       </c>
-      <c r="G824" s="6" t="s">
+      <c r="H824" s="6" t="s">
         <v>5182</v>
-      </c>
-      <c r="H824" s="6" t="s">
-        <v>5183</v>
       </c>
     </row>
     <row r="825">
       <c r="B825" s="5" t="s">
+        <v>5183</v>
+      </c>
+      <c r="C825" s="5" t="s">
         <v>5184</v>
       </c>
-      <c r="C825" s="5" t="s">
+      <c r="D825" s="5" t="s">
         <v>5185</v>
       </c>
-      <c r="D825" s="5" t="s">
+      <c r="E825" s="5" t="s">
         <v>5186</v>
       </c>
-      <c r="E825" s="5" t="s">
+      <c r="F825" s="5" t="s">
         <v>5187</v>
-      </c>
-      <c r="F825" s="5" t="s">
-        <v>5188</v>
       </c>
       <c r="G825" s="5" t="s">
         <v>5188</v>
@@ -35410,27 +35428,27 @@
         <v>5194</v>
       </c>
       <c r="G826" s="6" t="s">
+        <v>5194</v>
+      </c>
+      <c r="H826" s="6" t="s">
         <v>5195</v>
-      </c>
-      <c r="H826" s="6" t="s">
-        <v>5196</v>
       </c>
     </row>
     <row r="827">
       <c r="B827" s="5" t="s">
+        <v>5196</v>
+      </c>
+      <c r="C827" s="5" t="s">
         <v>5197</v>
       </c>
-      <c r="C827" s="5" t="s">
+      <c r="D827" s="5" t="s">
         <v>5198</v>
       </c>
-      <c r="D827" s="5" t="s">
+      <c r="E827" s="5" t="s">
         <v>5199</v>
       </c>
-      <c r="E827" s="5" t="s">
+      <c r="F827" s="5" t="s">
         <v>5200</v>
-      </c>
-      <c r="F827" s="5" t="s">
-        <v>5201</v>
       </c>
       <c r="G827" s="5" t="s">
         <v>5201</v>
@@ -35456,30 +35474,30 @@
         <v>5207</v>
       </c>
       <c r="G828" s="6" t="s">
+        <v>5207</v>
+      </c>
+      <c r="H828" s="6" t="s">
         <v>5208</v>
-      </c>
-      <c r="H828" s="6" t="s">
-        <v>5209</v>
       </c>
     </row>
     <row r="829">
       <c r="B829" s="5" t="s">
+        <v>5209</v>
+      </c>
+      <c r="C829" s="5" t="s">
         <v>5210</v>
       </c>
-      <c r="C829" s="5" t="s">
+      <c r="D829" s="5" t="s">
         <v>5211</v>
       </c>
-      <c r="D829" s="5" t="s">
+      <c r="E829" s="5" t="s">
         <v>5212</v>
       </c>
-      <c r="E829" s="5" t="s">
+      <c r="F829" s="5" t="s">
         <v>5213</v>
       </c>
-      <c r="F829" s="5" t="s">
+      <c r="G829" s="5" t="s">
         <v>5214</v>
-      </c>
-      <c r="G829" s="5" t="s">
-        <v>5213</v>
       </c>
       <c r="H829" s="5" t="s">
         <v>5215</v>
@@ -35502,56 +35520,56 @@
         <v>5220</v>
       </c>
       <c r="G830" s="6" t="s">
-        <v>5220</v>
+        <v>5219</v>
       </c>
       <c r="H830" s="6" t="s">
-        <v>5218</v>
+        <v>5221</v>
       </c>
     </row>
     <row r="831">
       <c r="B831" s="5" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="C831" s="5" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="D831" s="5" t="s">
-        <v>5223</v>
+        <v>5224</v>
       </c>
       <c r="E831" s="5" t="s">
-        <v>5224</v>
+        <v>5225</v>
       </c>
       <c r="F831" s="5" t="s">
-        <v>5225</v>
+        <v>5226</v>
       </c>
       <c r="G831" s="5" t="s">
         <v>5226</v>
       </c>
       <c r="H831" s="5" t="s">
-        <v>5227</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="832">
       <c r="B832" s="6" t="s">
+        <v>5227</v>
+      </c>
+      <c r="C832" s="6" t="s">
         <v>5228</v>
       </c>
-      <c r="C832" s="6" t="s">
+      <c r="D832" s="6" t="s">
         <v>5229</v>
       </c>
-      <c r="D832" s="6" t="s">
+      <c r="E832" s="6" t="s">
         <v>5230</v>
       </c>
-      <c r="E832" s="6" t="s">
+      <c r="F832" s="6" t="s">
         <v>5231</v>
       </c>
-      <c r="F832" s="6" t="s">
+      <c r="G832" s="6" t="s">
         <v>5232</v>
       </c>
-      <c r="G832" s="6" t="s">
+      <c r="H832" s="6" t="s">
         <v>5233</v>
-      </c>
-      <c r="H832" s="6" t="s">
-        <v>5230</v>
       </c>
     </row>
     <row r="833">
@@ -35574,24 +35592,24 @@
         <v>5239</v>
       </c>
       <c r="H833" s="5" t="s">
-        <v>5240</v>
+        <v>5236</v>
       </c>
     </row>
     <row r="834">
       <c r="B834" s="6" t="s">
+        <v>5240</v>
+      </c>
+      <c r="C834" s="6" t="s">
         <v>5241</v>
       </c>
-      <c r="C834" s="6" t="s">
+      <c r="D834" s="6" t="s">
         <v>5242</v>
       </c>
-      <c r="D834" s="6" t="s">
+      <c r="E834" s="6" t="s">
         <v>5243</v>
       </c>
-      <c r="E834" s="6" t="s">
+      <c r="F834" s="6" t="s">
         <v>5244</v>
-      </c>
-      <c r="F834" s="6" t="s">
-        <v>5245</v>
       </c>
       <c r="G834" s="6" t="s">
         <v>5245</v>
@@ -35640,27 +35658,27 @@
         <v>5257</v>
       </c>
       <c r="G836" s="6" t="s">
+        <v>5257</v>
+      </c>
+      <c r="H836" s="6" t="s">
         <v>5258</v>
-      </c>
-      <c r="H836" s="6" t="s">
-        <v>5259</v>
       </c>
     </row>
     <row r="837">
       <c r="B837" s="5" t="s">
+        <v>5259</v>
+      </c>
+      <c r="C837" s="5" t="s">
         <v>5260</v>
       </c>
-      <c r="C837" s="5" t="s">
+      <c r="D837" s="5" t="s">
         <v>5261</v>
       </c>
-      <c r="D837" s="5" t="s">
+      <c r="E837" s="5" t="s">
         <v>5262</v>
       </c>
-      <c r="E837" s="5" t="s">
+      <c r="F837" s="5" t="s">
         <v>5263</v>
-      </c>
-      <c r="F837" s="5" t="s">
-        <v>5264</v>
       </c>
       <c r="G837" s="5" t="s">
         <v>5264</v>
@@ -35686,27 +35704,27 @@
         <v>5270</v>
       </c>
       <c r="G838" s="6" t="s">
+        <v>5270</v>
+      </c>
+      <c r="H838" s="6" t="s">
         <v>5271</v>
-      </c>
-      <c r="H838" s="6" t="s">
-        <v>5272</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
+        <v>5272</v>
+      </c>
+      <c r="C839" s="5" t="s">
         <v>5273</v>
       </c>
-      <c r="C839" s="5" t="s">
+      <c r="D839" s="5" t="s">
         <v>5274</v>
       </c>
-      <c r="D839" s="5" t="s">
+      <c r="E839" s="5" t="s">
         <v>5275</v>
       </c>
-      <c r="E839" s="5" t="s">
+      <c r="F839" s="5" t="s">
         <v>5276</v>
-      </c>
-      <c r="F839" s="5" t="s">
-        <v>5277</v>
       </c>
       <c r="G839" s="5" t="s">
         <v>5277</v>
@@ -35746,65 +35764,65 @@
         <v>5286</v>
       </c>
       <c r="D841" s="5" t="s">
-        <v>5286</v>
+        <v>5287</v>
       </c>
       <c r="E841" s="5" t="s">
-        <v>5286</v>
+        <v>5288</v>
       </c>
       <c r="F841" s="5" t="s">
-        <v>5286</v>
+        <v>5289</v>
       </c>
       <c r="G841" s="5" t="s">
-        <v>5286</v>
+        <v>5289</v>
       </c>
       <c r="H841" s="5" t="s">
-        <v>5286</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
-        <v>5287</v>
+        <v>5291</v>
       </c>
       <c r="C842" s="6" t="s">
-        <v>5288</v>
+        <v>5292</v>
       </c>
       <c r="D842" s="6" t="s">
-        <v>5289</v>
+        <v>5292</v>
       </c>
       <c r="E842" s="6" t="s">
-        <v>5290</v>
+        <v>5292</v>
       </c>
       <c r="F842" s="6" t="s">
-        <v>5291</v>
+        <v>5292</v>
       </c>
       <c r="G842" s="6" t="s">
-        <v>5291</v>
+        <v>5292</v>
       </c>
       <c r="H842" s="6" t="s">
-        <v>5289</v>
+        <v>5292</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
-        <v>5292</v>
+        <v>5293</v>
       </c>
       <c r="C843" s="5" t="s">
-        <v>5293</v>
+        <v>5294</v>
       </c>
       <c r="D843" s="5" t="s">
-        <v>5294</v>
+        <v>5295</v>
       </c>
       <c r="E843" s="5" t="s">
-        <v>5295</v>
+        <v>5296</v>
       </c>
       <c r="F843" s="5" t="s">
-        <v>5296</v>
+        <v>5297</v>
       </c>
       <c r="G843" s="5" t="s">
         <v>5297</v>
       </c>
       <c r="H843" s="5" t="s">
-        <v>5294</v>
+        <v>5295</v>
       </c>
     </row>
     <row r="844">
@@ -35821,10 +35839,10 @@
         <v>5301</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>5301</v>
+        <v>5302</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5301</v>
+        <v>5303</v>
       </c>
       <c r="H844" s="6" t="s">
         <v>5300</v>
@@ -35832,71 +35850,71 @@
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5302</v>
+        <v>5304</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>5303</v>
+        <v>5305</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5304</v>
+        <v>5306</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>5305</v>
+        <v>5307</v>
       </c>
       <c r="F845" s="5" t="s">
-        <v>5305</v>
+        <v>5307</v>
       </c>
       <c r="G845" s="5" t="s">
-        <v>5305</v>
+        <v>5307</v>
       </c>
       <c r="H845" s="5" t="s">
-        <v>5304</v>
+        <v>5306</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
-        <v>5306</v>
+        <v>5308</v>
       </c>
       <c r="C846" s="6" t="s">
-        <v>5307</v>
+        <v>5309</v>
       </c>
       <c r="D846" s="6" t="s">
-        <v>5308</v>
+        <v>5310</v>
       </c>
       <c r="E846" s="6" t="s">
-        <v>5309</v>
+        <v>5311</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="G846" s="6" t="s">
         <v>5311</v>
       </c>
       <c r="H846" s="6" t="s">
-        <v>5312</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
+        <v>5312</v>
+      </c>
+      <c r="C847" s="5" t="s">
         <v>5313</v>
       </c>
-      <c r="C847" s="5" t="s">
+      <c r="D847" s="5" t="s">
         <v>5314</v>
       </c>
-      <c r="D847" s="5" t="s">
+      <c r="E847" s="5" t="s">
         <v>5315</v>
       </c>
-      <c r="E847" s="5" t="s">
+      <c r="F847" s="5" t="s">
         <v>5316</v>
       </c>
-      <c r="F847" s="5" t="s">
+      <c r="G847" s="5" t="s">
         <v>5317</v>
       </c>
-      <c r="G847" s="5" t="s">
+      <c r="H847" s="5" t="s">
         <v>5318</v>
-      </c>
-      <c r="H847" s="5" t="s">
-        <v>5315</v>
       </c>
     </row>
     <row r="848">
@@ -35919,76 +35937,76 @@
         <v>5324</v>
       </c>
       <c r="H848" s="6" t="s">
-        <v>5325</v>
+        <v>5321</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
+        <v>5325</v>
+      </c>
+      <c r="C849" s="5" t="s">
         <v>5326</v>
       </c>
-      <c r="C849" s="5" t="s">
+      <c r="D849" s="5" t="s">
         <v>5327</v>
       </c>
-      <c r="D849" s="5" t="s">
+      <c r="E849" s="5" t="s">
         <v>5328</v>
       </c>
-      <c r="E849" s="5" t="s">
+      <c r="F849" s="5" t="s">
         <v>5329</v>
       </c>
-      <c r="F849" s="5" t="s">
+      <c r="G849" s="5" t="s">
         <v>5330</v>
       </c>
-      <c r="G849" s="5" t="s">
+      <c r="H849" s="5" t="s">
         <v>5331</v>
-      </c>
-      <c r="H849" s="5" t="s">
-        <v>5332</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
+        <v>5332</v>
+      </c>
+      <c r="C850" s="6" t="s">
         <v>5333</v>
       </c>
-      <c r="C850" s="6" t="s">
+      <c r="D850" s="6" t="s">
         <v>5334</v>
       </c>
-      <c r="D850" s="6" t="s">
+      <c r="E850" s="6" t="s">
         <v>5335</v>
       </c>
-      <c r="E850" s="6" t="s">
+      <c r="F850" s="6" t="s">
         <v>5336</v>
       </c>
-      <c r="F850" s="6" t="s">
+      <c r="G850" s="6" t="s">
         <v>5337</v>
       </c>
-      <c r="G850" s="6" t="s">
+      <c r="H850" s="6" t="s">
         <v>5338</v>
-      </c>
-      <c r="H850" s="6" t="s">
-        <v>5339</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
+        <v>5339</v>
+      </c>
+      <c r="C851" s="5" t="s">
         <v>5340</v>
       </c>
-      <c r="C851" s="5" t="s">
+      <c r="D851" s="5" t="s">
         <v>5341</v>
       </c>
-      <c r="D851" s="5" t="s">
+      <c r="E851" s="5" t="s">
         <v>5342</v>
       </c>
-      <c r="E851" s="5" t="s">
+      <c r="F851" s="5" t="s">
         <v>5343</v>
       </c>
-      <c r="F851" s="5" t="s">
+      <c r="G851" s="5" t="s">
         <v>5344</v>
       </c>
-      <c r="G851" s="5" t="s">
+      <c r="H851" s="5" t="s">
         <v>5345</v>
-      </c>
-      <c r="H851" s="5" t="s">
-        <v>5315</v>
       </c>
     </row>
     <row r="852">
@@ -36011,24 +36029,24 @@
         <v>5351</v>
       </c>
       <c r="H852" s="6" t="s">
-        <v>5352</v>
+        <v>5321</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
+        <v>5352</v>
+      </c>
+      <c r="C853" s="5" t="s">
         <v>5353</v>
       </c>
-      <c r="C853" s="5" t="s">
+      <c r="D853" s="5" t="s">
         <v>5354</v>
       </c>
-      <c r="D853" s="5" t="s">
+      <c r="E853" s="5" t="s">
         <v>5355</v>
       </c>
-      <c r="E853" s="5" t="s">
+      <c r="F853" s="5" t="s">
         <v>5356</v>
-      </c>
-      <c r="F853" s="5" t="s">
-        <v>5357</v>
       </c>
       <c r="G853" s="5" t="s">
         <v>5357</v>
@@ -36037,8 +36055,31 @@
         <v>5358</v>
       </c>
     </row>
+    <row r="854">
+      <c r="B854" s="6" t="s">
+        <v>5359</v>
+      </c>
+      <c r="C854" s="6" t="s">
+        <v>5360</v>
+      </c>
+      <c r="D854" s="6" t="s">
+        <v>5361</v>
+      </c>
+      <c r="E854" s="6" t="s">
+        <v>5362</v>
+      </c>
+      <c r="F854" s="6" t="s">
+        <v>5363</v>
+      </c>
+      <c r="G854" s="6" t="s">
+        <v>5363</v>
+      </c>
+      <c r="H854" s="6" t="s">
+        <v>5364</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H853"/>
+  <autoFilter ref="B2:H854"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36057,10 +36098,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5359</v>
+        <v>5365</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5360</v>
+        <v>5366</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36071,16 +36112,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5361</v>
+        <v>5367</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5362</v>
+        <v>5368</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5363</v>
+        <v>5369</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5364</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="3">
@@ -36088,16 +36129,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5365</v>
+        <v>5371</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5366</v>
+        <v>5372</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5367</v>
+        <v>5373</v>
       </c>
     </row>
     <row r="4">
@@ -36108,24 +36149,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5368</v>
+        <v>5374</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5369</v>
+        <v>5375</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5370</v>
+        <v>5376</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5371</v>
+        <v>5377</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5372</v>
+        <v>5378</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36133,13 +36174,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5373</v>
+        <v>5379</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5374</v>
+        <v>5380</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36147,13 +36188,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5375</v>
+        <v>5381</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5376</v>
+        <v>5382</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36161,13 +36202,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5377</v>
+        <v>5383</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5378</v>
+        <v>5384</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36175,13 +36216,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5379</v>
+        <v>5385</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5380</v>
+        <v>5386</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36189,13 +36230,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5381</v>
+        <v>5387</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5382</v>
+        <v>5388</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36203,13 +36244,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5383</v>
+        <v>5389</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5384</v>
+        <v>5390</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36217,13 +36258,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5385</v>
+        <v>5391</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5386</v>
+        <v>5392</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36231,13 +36272,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5387</v>
+        <v>5393</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5388</v>
+        <v>5394</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36245,13 +36286,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5389</v>
+        <v>5395</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5390</v>
+        <v>5396</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36265,7 +36306,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5391</v>
+        <v>5397</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36273,13 +36314,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5392</v>
+        <v>5398</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5393</v>
+        <v>5399</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36287,13 +36328,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5394</v>
+        <v>5400</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5395</v>
+        <v>5401</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36301,13 +36342,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5396</v>
+        <v>5402</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5397</v>
+        <v>5403</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36315,13 +36356,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5398</v>
+        <v>5404</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5399</v>
+        <v>5405</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36329,13 +36370,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5400</v>
+        <v>5406</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5401</v>
+        <v>5407</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36343,13 +36384,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5402</v>
+        <v>5408</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5403</v>
+        <v>5409</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36357,13 +36398,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5404</v>
+        <v>5410</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5405</v>
+        <v>5411</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36371,13 +36412,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5406</v>
+        <v>5412</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5407</v>
+        <v>5413</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36385,13 +36426,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5408</v>
+        <v>5414</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5409</v>
+        <v>5415</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$854]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$858]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6041" uniqueCount="5416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6069" uniqueCount="5443">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -14912,6 +14912,87 @@
   </si>
   <si>
     <t xml:space="preserve">Ein Joker verdoppelt den Mult. Der nächste verdoppelt ihn wieder. Ein Lauf bleibt nie einer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.title.seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シード</t>
+  </si>
+  <si>
+    <t xml:space="preserve">种子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">種子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.title.seed_hint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">같은 시드를 넣으면 같은 판이 나옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same seed gives the same run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同じシードなら同じゲームになります</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相同的种子会生成相同的一局</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相同的種子會生成相同的一局</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derselbe Seed ergibt denselben Durchgang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.title.seed_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱 섞기 · 상점 · 팩 · 확률 발동이 모두 이 글에서 갈라집니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deck shuffle, shop, packs and procs all derive from it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デッキのシャッフル・ショップ・パック・確率発動がすべてこの文字列から決まります</t>
+  </si>
+  <si>
+    <t xml:space="preserve">洗牌、商店、卡包、概率触发全部由它决定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">洗牌、商店、卡包、機率觸發全部由它決定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mischen, Shop, Packs und Auslöser gehen alle daraus hervor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.random</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무작위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ランダム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">随机</t>
+  </si>
+  <si>
+    <t xml:space="preserve">隨機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zufall</t>
   </si>
   <si>
     <t xml:space="preserve">ui.guide.lead</t>
@@ -16464,7 +16545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H854"/>
+  <dimension ref="A1:H858"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -34626,168 +34707,168 @@
         <v>4970</v>
       </c>
       <c r="H791" s="5" t="s">
-        <v>4971</v>
+        <v>4967</v>
       </c>
     </row>
     <row r="792">
       <c r="B792" s="6" t="s">
+        <v>4971</v>
+      </c>
+      <c r="C792" s="6" t="s">
         <v>4972</v>
-      </c>
-      <c r="C792" s="6" t="s">
-        <v>3021</v>
       </c>
       <c r="D792" s="6" t="s">
         <v>4973</v>
       </c>
       <c r="E792" s="6" t="s">
-        <v>3023</v>
+        <v>4974</v>
       </c>
       <c r="F792" s="6" t="s">
-        <v>4974</v>
+        <v>4975</v>
       </c>
       <c r="G792" s="6" t="s">
-        <v>4975</v>
+        <v>4976</v>
       </c>
       <c r="H792" s="6" t="s">
-        <v>4976</v>
+        <v>4977</v>
       </c>
     </row>
     <row r="793">
       <c r="B793" s="5" t="s">
-        <v>4977</v>
+        <v>4978</v>
       </c>
       <c r="C793" s="5" t="s">
-        <v>3014</v>
+        <v>4979</v>
       </c>
       <c r="D793" s="5" t="s">
-        <v>4978</v>
+        <v>4980</v>
       </c>
       <c r="E793" s="5" t="s">
-        <v>3016</v>
+        <v>4981</v>
       </c>
       <c r="F793" s="5" t="s">
-        <v>4979</v>
+        <v>4982</v>
       </c>
       <c r="G793" s="5" t="s">
-        <v>4980</v>
+        <v>4983</v>
       </c>
       <c r="H793" s="5" t="s">
-        <v>4981</v>
+        <v>4984</v>
       </c>
     </row>
     <row r="794">
       <c r="B794" s="6" t="s">
-        <v>4982</v>
+        <v>4985</v>
       </c>
       <c r="C794" s="6" t="s">
-        <v>4983</v>
+        <v>4986</v>
       </c>
       <c r="D794" s="6" t="s">
-        <v>4984</v>
+        <v>4987</v>
       </c>
       <c r="E794" s="6" t="s">
-        <v>4985</v>
+        <v>4988</v>
       </c>
       <c r="F794" s="6" t="s">
-        <v>4986</v>
+        <v>4989</v>
       </c>
       <c r="G794" s="6" t="s">
-        <v>4985</v>
+        <v>4990</v>
       </c>
       <c r="H794" s="6" t="s">
-        <v>4429</v>
+        <v>4991</v>
       </c>
     </row>
     <row r="795">
       <c r="B795" s="5" t="s">
-        <v>4987</v>
+        <v>4992</v>
       </c>
       <c r="C795" s="5" t="s">
-        <v>4988</v>
+        <v>4993</v>
       </c>
       <c r="D795" s="5" t="s">
-        <v>4989</v>
+        <v>4994</v>
       </c>
       <c r="E795" s="5" t="s">
-        <v>4990</v>
+        <v>4995</v>
       </c>
       <c r="F795" s="5" t="s">
-        <v>4991</v>
+        <v>4996</v>
       </c>
       <c r="G795" s="5" t="s">
-        <v>4992</v>
+        <v>4997</v>
       </c>
       <c r="H795" s="5" t="s">
-        <v>4993</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="796">
       <c r="B796" s="6" t="s">
-        <v>4994</v>
+        <v>4999</v>
       </c>
       <c r="C796" s="6" t="s">
-        <v>4995</v>
+        <v>3021</v>
       </c>
       <c r="D796" s="6" t="s">
-        <v>4996</v>
+        <v>5000</v>
       </c>
       <c r="E796" s="6" t="s">
-        <v>4997</v>
+        <v>3023</v>
       </c>
       <c r="F796" s="6" t="s">
-        <v>4998</v>
+        <v>5001</v>
       </c>
       <c r="G796" s="6" t="s">
-        <v>4998</v>
+        <v>5002</v>
       </c>
       <c r="H796" s="6" t="s">
-        <v>4999</v>
+        <v>5003</v>
       </c>
     </row>
     <row r="797">
       <c r="B797" s="5" t="s">
-        <v>5000</v>
+        <v>5004</v>
       </c>
       <c r="C797" s="5" t="s">
-        <v>5001</v>
+        <v>3014</v>
       </c>
       <c r="D797" s="5" t="s">
-        <v>5002</v>
+        <v>5005</v>
       </c>
       <c r="E797" s="5" t="s">
-        <v>5003</v>
+        <v>3016</v>
       </c>
       <c r="F797" s="5" t="s">
-        <v>5004</v>
+        <v>5006</v>
       </c>
       <c r="G797" s="5" t="s">
-        <v>5005</v>
+        <v>5007</v>
       </c>
       <c r="H797" s="5" t="s">
-        <v>5006</v>
+        <v>5008</v>
       </c>
     </row>
     <row r="798">
       <c r="B798" s="6" t="s">
-        <v>5007</v>
+        <v>5009</v>
       </c>
       <c r="C798" s="6" t="s">
-        <v>5008</v>
+        <v>5010</v>
       </c>
       <c r="D798" s="6" t="s">
-        <v>5009</v>
+        <v>5011</v>
       </c>
       <c r="E798" s="6" t="s">
-        <v>5010</v>
+        <v>5012</v>
       </c>
       <c r="F798" s="6" t="s">
-        <v>5011</v>
+        <v>5013</v>
       </c>
       <c r="G798" s="6" t="s">
         <v>5012</v>
       </c>
       <c r="H798" s="6" t="s">
-        <v>5013</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="799">
@@ -34830,139 +34911,139 @@
         <v>5025</v>
       </c>
       <c r="G800" s="6" t="s">
+        <v>5025</v>
+      </c>
+      <c r="H800" s="6" t="s">
         <v>5026</v>
-      </c>
-      <c r="H800" s="6" t="s">
-        <v>5027</v>
       </c>
     </row>
     <row r="801">
       <c r="B801" s="5" t="s">
+        <v>5027</v>
+      </c>
+      <c r="C801" s="5" t="s">
         <v>5028</v>
       </c>
-      <c r="C801" s="5" t="s">
+      <c r="D801" s="5" t="s">
         <v>5029</v>
       </c>
-      <c r="D801" s="5" t="s">
+      <c r="E801" s="5" t="s">
         <v>5030</v>
       </c>
-      <c r="E801" s="5" t="s">
+      <c r="F801" s="5" t="s">
         <v>5031</v>
       </c>
-      <c r="F801" s="5" t="s">
+      <c r="G801" s="5" t="s">
         <v>5032</v>
       </c>
-      <c r="G801" s="5" t="s">
+      <c r="H801" s="5" t="s">
         <v>5033</v>
-      </c>
-      <c r="H801" s="5" t="s">
-        <v>5034</v>
       </c>
     </row>
     <row r="802">
       <c r="B802" s="6" t="s">
+        <v>5034</v>
+      </c>
+      <c r="C802" s="6" t="s">
         <v>5035</v>
       </c>
-      <c r="C802" s="6" t="s">
+      <c r="D802" s="6" t="s">
         <v>5036</v>
       </c>
-      <c r="D802" s="6" t="s">
+      <c r="E802" s="6" t="s">
         <v>5037</v>
-      </c>
-      <c r="E802" s="6" t="s">
-        <v>5038</v>
       </c>
       <c r="F802" s="6" t="s">
         <v>5038</v>
       </c>
       <c r="G802" s="6" t="s">
-        <v>5038</v>
+        <v>5039</v>
       </c>
       <c r="H802" s="6" t="s">
-        <v>5039</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="803">
       <c r="B803" s="5" t="s">
-        <v>5040</v>
+        <v>5041</v>
       </c>
       <c r="C803" s="5" t="s">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="D803" s="5" t="s">
-        <v>5042</v>
+        <v>5043</v>
       </c>
       <c r="E803" s="5" t="s">
-        <v>5043</v>
+        <v>5044</v>
       </c>
       <c r="F803" s="5" t="s">
-        <v>5044</v>
+        <v>5045</v>
       </c>
       <c r="G803" s="5" t="s">
-        <v>5045</v>
+        <v>5046</v>
       </c>
       <c r="H803" s="5" t="s">
-        <v>5046</v>
+        <v>5047</v>
       </c>
     </row>
     <row r="804">
       <c r="B804" s="6" t="s">
-        <v>5047</v>
+        <v>5048</v>
       </c>
       <c r="C804" s="6" t="s">
-        <v>5048</v>
+        <v>5049</v>
       </c>
       <c r="D804" s="6" t="s">
-        <v>5049</v>
+        <v>5050</v>
       </c>
       <c r="E804" s="6" t="s">
-        <v>5050</v>
+        <v>5051</v>
       </c>
       <c r="F804" s="6" t="s">
-        <v>5051</v>
+        <v>5052</v>
       </c>
       <c r="G804" s="6" t="s">
-        <v>5052</v>
+        <v>5053</v>
       </c>
       <c r="H804" s="6" t="s">
-        <v>5053</v>
+        <v>5054</v>
       </c>
     </row>
     <row r="805">
       <c r="B805" s="5" t="s">
-        <v>5054</v>
+        <v>5055</v>
       </c>
       <c r="C805" s="5" t="s">
-        <v>5055</v>
+        <v>5056</v>
       </c>
       <c r="D805" s="5" t="s">
-        <v>5056</v>
+        <v>5057</v>
       </c>
       <c r="E805" s="5" t="s">
-        <v>5057</v>
+        <v>5058</v>
       </c>
       <c r="F805" s="5" t="s">
-        <v>5058</v>
+        <v>5059</v>
       </c>
       <c r="G805" s="5" t="s">
-        <v>5059</v>
+        <v>5060</v>
       </c>
       <c r="H805" s="5" t="s">
-        <v>5060</v>
+        <v>5061</v>
       </c>
     </row>
     <row r="806">
       <c r="B806" s="6" t="s">
-        <v>5061</v>
+        <v>5062</v>
       </c>
       <c r="C806" s="6" t="s">
-        <v>5062</v>
+        <v>5063</v>
       </c>
       <c r="D806" s="6" t="s">
-        <v>5063</v>
+        <v>5064</v>
       </c>
       <c r="E806" s="6" t="s">
-        <v>5064</v>
+        <v>5065</v>
       </c>
       <c r="F806" s="6" t="s">
         <v>5065</v>
@@ -34991,96 +35072,96 @@
         <v>5071</v>
       </c>
       <c r="G807" s="5" t="s">
-        <v>5071</v>
+        <v>5072</v>
       </c>
       <c r="H807" s="5" t="s">
-        <v>5072</v>
+        <v>5073</v>
       </c>
     </row>
     <row r="808">
       <c r="B808" s="6" t="s">
-        <v>5073</v>
+        <v>5074</v>
       </c>
       <c r="C808" s="6" t="s">
-        <v>5074</v>
+        <v>5075</v>
       </c>
       <c r="D808" s="6" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="E808" s="6" t="s">
-        <v>5076</v>
+        <v>5077</v>
       </c>
       <c r="F808" s="6" t="s">
-        <v>5077</v>
+        <v>5078</v>
       </c>
       <c r="G808" s="6" t="s">
-        <v>5077</v>
+        <v>5079</v>
       </c>
       <c r="H808" s="6" t="s">
-        <v>5078</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="809">
       <c r="B809" s="5" t="s">
-        <v>5079</v>
+        <v>5081</v>
       </c>
       <c r="C809" s="5" t="s">
-        <v>5080</v>
+        <v>5082</v>
       </c>
       <c r="D809" s="5" t="s">
-        <v>5081</v>
+        <v>5083</v>
       </c>
       <c r="E809" s="5" t="s">
-        <v>5082</v>
+        <v>5084</v>
       </c>
       <c r="F809" s="5" t="s">
-        <v>5083</v>
+        <v>5085</v>
       </c>
       <c r="G809" s="5" t="s">
-        <v>5084</v>
+        <v>5086</v>
       </c>
       <c r="H809" s="5" t="s">
-        <v>5085</v>
+        <v>5087</v>
       </c>
     </row>
     <row r="810">
       <c r="B810" s="6" t="s">
-        <v>5086</v>
+        <v>5088</v>
       </c>
       <c r="C810" s="6" t="s">
-        <v>5087</v>
+        <v>5089</v>
       </c>
       <c r="D810" s="6" t="s">
-        <v>5088</v>
+        <v>5090</v>
       </c>
       <c r="E810" s="6" t="s">
-        <v>5089</v>
+        <v>5091</v>
       </c>
       <c r="F810" s="6" t="s">
-        <v>5090</v>
+        <v>5092</v>
       </c>
       <c r="G810" s="6" t="s">
-        <v>5091</v>
+        <v>5092</v>
       </c>
       <c r="H810" s="6" t="s">
-        <v>5092</v>
+        <v>5093</v>
       </c>
     </row>
     <row r="811">
       <c r="B811" s="5" t="s">
-        <v>5093</v>
+        <v>5094</v>
       </c>
       <c r="C811" s="5" t="s">
-        <v>5094</v>
+        <v>5095</v>
       </c>
       <c r="D811" s="5" t="s">
-        <v>5095</v>
+        <v>5096</v>
       </c>
       <c r="E811" s="5" t="s">
-        <v>5096</v>
+        <v>5097</v>
       </c>
       <c r="F811" s="5" t="s">
-        <v>5097</v>
+        <v>5098</v>
       </c>
       <c r="G811" s="5" t="s">
         <v>5098</v>
@@ -35106,50 +35187,50 @@
         <v>5104</v>
       </c>
       <c r="G812" s="6" t="s">
+        <v>5104</v>
+      </c>
+      <c r="H812" s="6" t="s">
         <v>5105</v>
-      </c>
-      <c r="H812" s="6" t="s">
-        <v>5106</v>
       </c>
     </row>
     <row r="813">
       <c r="B813" s="5" t="s">
+        <v>5106</v>
+      </c>
+      <c r="C813" s="5" t="s">
         <v>5107</v>
       </c>
-      <c r="C813" s="5" t="s">
+      <c r="D813" s="5" t="s">
         <v>5108</v>
       </c>
-      <c r="D813" s="5" t="s">
+      <c r="E813" s="5" t="s">
         <v>5109</v>
       </c>
-      <c r="E813" s="5" t="s">
+      <c r="F813" s="5" t="s">
         <v>5110</v>
       </c>
-      <c r="F813" s="5" t="s">
+      <c r="G813" s="5" t="s">
         <v>5111</v>
       </c>
-      <c r="G813" s="5" t="s">
+      <c r="H813" s="5" t="s">
         <v>5112</v>
-      </c>
-      <c r="H813" s="5" t="s">
-        <v>5113</v>
       </c>
     </row>
     <row r="814">
       <c r="B814" s="6" t="s">
+        <v>5113</v>
+      </c>
+      <c r="C814" s="6" t="s">
         <v>5114</v>
       </c>
-      <c r="C814" s="6" t="s">
+      <c r="D814" s="6" t="s">
         <v>5115</v>
       </c>
-      <c r="D814" s="6" t="s">
+      <c r="E814" s="6" t="s">
         <v>5116</v>
       </c>
-      <c r="E814" s="6" t="s">
+      <c r="F814" s="6" t="s">
         <v>5117</v>
-      </c>
-      <c r="F814" s="6" t="s">
-        <v>5118</v>
       </c>
       <c r="G814" s="6" t="s">
         <v>5118</v>
@@ -35172,197 +35253,197 @@
         <v>5123</v>
       </c>
       <c r="F815" s="5" t="s">
-        <v>5123</v>
+        <v>5124</v>
       </c>
       <c r="G815" s="5" t="s">
-        <v>5123</v>
+        <v>5125</v>
       </c>
       <c r="H815" s="5" t="s">
-        <v>5122</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="816">
       <c r="B816" s="6" t="s">
-        <v>5124</v>
+        <v>5127</v>
       </c>
       <c r="C816" s="6" t="s">
-        <v>5125</v>
+        <v>5128</v>
       </c>
       <c r="D816" s="6" t="s">
-        <v>5126</v>
+        <v>5129</v>
       </c>
       <c r="E816" s="6" t="s">
-        <v>5127</v>
+        <v>5130</v>
       </c>
       <c r="F816" s="6" t="s">
-        <v>5128</v>
+        <v>5131</v>
       </c>
       <c r="G816" s="6" t="s">
-        <v>5129</v>
+        <v>5132</v>
       </c>
       <c r="H816" s="6" t="s">
-        <v>5130</v>
+        <v>5133</v>
       </c>
     </row>
     <row r="817">
       <c r="B817" s="5" t="s">
-        <v>5131</v>
+        <v>5134</v>
       </c>
       <c r="C817" s="5" t="s">
-        <v>5132</v>
+        <v>5135</v>
       </c>
       <c r="D817" s="5" t="s">
-        <v>5133</v>
+        <v>5136</v>
       </c>
       <c r="E817" s="5" t="s">
-        <v>5134</v>
+        <v>5137</v>
       </c>
       <c r="F817" s="5" t="s">
-        <v>5135</v>
+        <v>5138</v>
       </c>
       <c r="G817" s="5" t="s">
-        <v>5136</v>
+        <v>5139</v>
       </c>
       <c r="H817" s="5" t="s">
-        <v>5137</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="818">
       <c r="B818" s="6" t="s">
-        <v>5138</v>
+        <v>5141</v>
       </c>
       <c r="C818" s="6" t="s">
-        <v>5139</v>
+        <v>5142</v>
       </c>
       <c r="D818" s="6" t="s">
-        <v>5140</v>
+        <v>5143</v>
       </c>
       <c r="E818" s="6" t="s">
-        <v>5141</v>
+        <v>5144</v>
       </c>
       <c r="F818" s="6" t="s">
-        <v>5142</v>
+        <v>5145</v>
       </c>
       <c r="G818" s="6" t="s">
-        <v>5143</v>
+        <v>5145</v>
       </c>
       <c r="H818" s="6" t="s">
-        <v>5144</v>
+        <v>5146</v>
       </c>
     </row>
     <row r="819">
       <c r="B819" s="5" t="s">
-        <v>5145</v>
+        <v>5147</v>
       </c>
       <c r="C819" s="5" t="s">
-        <v>5146</v>
+        <v>5148</v>
       </c>
       <c r="D819" s="5" t="s">
-        <v>5122</v>
+        <v>5149</v>
       </c>
       <c r="E819" s="5" t="s">
-        <v>5147</v>
+        <v>5150</v>
       </c>
       <c r="F819" s="5" t="s">
-        <v>5148</v>
+        <v>5150</v>
       </c>
       <c r="G819" s="5" t="s">
-        <v>5148</v>
+        <v>5150</v>
       </c>
       <c r="H819" s="5" t="s">
-        <v>5122</v>
+        <v>5149</v>
       </c>
     </row>
     <row r="820">
       <c r="B820" s="6" t="s">
-        <v>5149</v>
+        <v>5151</v>
       </c>
       <c r="C820" s="6" t="s">
-        <v>5150</v>
+        <v>5152</v>
       </c>
       <c r="D820" s="6" t="s">
-        <v>5151</v>
+        <v>5153</v>
       </c>
       <c r="E820" s="6" t="s">
-        <v>5152</v>
+        <v>5154</v>
       </c>
       <c r="F820" s="6" t="s">
-        <v>5153</v>
+        <v>5155</v>
       </c>
       <c r="G820" s="6" t="s">
-        <v>5154</v>
+        <v>5156</v>
       </c>
       <c r="H820" s="6" t="s">
-        <v>5155</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="821">
       <c r="B821" s="5" t="s">
-        <v>5156</v>
+        <v>5158</v>
       </c>
       <c r="C821" s="5" t="s">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="D821" s="5" t="s">
-        <v>5158</v>
+        <v>5160</v>
       </c>
       <c r="E821" s="5" t="s">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="F821" s="5" t="s">
-        <v>5160</v>
+        <v>5162</v>
       </c>
       <c r="G821" s="5" t="s">
-        <v>5161</v>
+        <v>5163</v>
       </c>
       <c r="H821" s="5" t="s">
-        <v>5158</v>
+        <v>5164</v>
       </c>
     </row>
     <row r="822">
       <c r="B822" s="6" t="s">
-        <v>5162</v>
+        <v>5165</v>
       </c>
       <c r="C822" s="6" t="s">
-        <v>5163</v>
+        <v>5166</v>
       </c>
       <c r="D822" s="6" t="s">
-        <v>5164</v>
+        <v>5167</v>
       </c>
       <c r="E822" s="6" t="s">
-        <v>5165</v>
+        <v>5168</v>
       </c>
       <c r="F822" s="6" t="s">
-        <v>5166</v>
+        <v>5169</v>
       </c>
       <c r="G822" s="6" t="s">
-        <v>5167</v>
+        <v>5170</v>
       </c>
       <c r="H822" s="6" t="s">
-        <v>5168</v>
+        <v>5171</v>
       </c>
     </row>
     <row r="823">
       <c r="B823" s="5" t="s">
-        <v>5169</v>
+        <v>5172</v>
       </c>
       <c r="C823" s="5" t="s">
-        <v>5170</v>
+        <v>5173</v>
       </c>
       <c r="D823" s="5" t="s">
-        <v>5171</v>
+        <v>5149</v>
       </c>
       <c r="E823" s="5" t="s">
-        <v>5172</v>
+        <v>5174</v>
       </c>
       <c r="F823" s="5" t="s">
-        <v>5173</v>
+        <v>5175</v>
       </c>
       <c r="G823" s="5" t="s">
-        <v>5174</v>
+        <v>5175</v>
       </c>
       <c r="H823" s="5" t="s">
-        <v>5175</v>
+        <v>5149</v>
       </c>
     </row>
     <row r="824">
@@ -35408,24 +35489,24 @@
         <v>5188</v>
       </c>
       <c r="H825" s="5" t="s">
-        <v>5189</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="826">
       <c r="B826" s="6" t="s">
+        <v>5189</v>
+      </c>
+      <c r="C826" s="6" t="s">
         <v>5190</v>
       </c>
-      <c r="C826" s="6" t="s">
+      <c r="D826" s="6" t="s">
         <v>5191</v>
       </c>
-      <c r="D826" s="6" t="s">
+      <c r="E826" s="6" t="s">
         <v>5192</v>
       </c>
-      <c r="E826" s="6" t="s">
+      <c r="F826" s="6" t="s">
         <v>5193</v>
-      </c>
-      <c r="F826" s="6" t="s">
-        <v>5194</v>
       </c>
       <c r="G826" s="6" t="s">
         <v>5194</v>
@@ -35474,516 +35555,516 @@
         <v>5207</v>
       </c>
       <c r="G828" s="6" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="H828" s="6" t="s">
-        <v>5208</v>
+        <v>5209</v>
       </c>
     </row>
     <row r="829">
       <c r="B829" s="5" t="s">
-        <v>5209</v>
+        <v>5210</v>
       </c>
       <c r="C829" s="5" t="s">
-        <v>5210</v>
+        <v>5211</v>
       </c>
       <c r="D829" s="5" t="s">
-        <v>5211</v>
+        <v>5212</v>
       </c>
       <c r="E829" s="5" t="s">
-        <v>5212</v>
+        <v>5213</v>
       </c>
       <c r="F829" s="5" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="G829" s="5" t="s">
-        <v>5214</v>
+        <v>5215</v>
       </c>
       <c r="H829" s="5" t="s">
-        <v>5215</v>
+        <v>5216</v>
       </c>
     </row>
     <row r="830">
       <c r="B830" s="6" t="s">
-        <v>5216</v>
+        <v>5217</v>
       </c>
       <c r="C830" s="6" t="s">
-        <v>5217</v>
+        <v>5218</v>
       </c>
       <c r="D830" s="6" t="s">
-        <v>5218</v>
+        <v>5219</v>
       </c>
       <c r="E830" s="6" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="F830" s="6" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="G830" s="6" t="s">
-        <v>5219</v>
+        <v>5221</v>
       </c>
       <c r="H830" s="6" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
     </row>
     <row r="831">
       <c r="B831" s="5" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C831" s="5" t="s">
-        <v>5223</v>
+        <v>5224</v>
       </c>
       <c r="D831" s="5" t="s">
-        <v>5224</v>
+        <v>5225</v>
       </c>
       <c r="E831" s="5" t="s">
-        <v>5225</v>
+        <v>5226</v>
       </c>
       <c r="F831" s="5" t="s">
-        <v>5226</v>
+        <v>5227</v>
       </c>
       <c r="G831" s="5" t="s">
-        <v>5226</v>
+        <v>5228</v>
       </c>
       <c r="H831" s="5" t="s">
-        <v>5224</v>
+        <v>5229</v>
       </c>
     </row>
     <row r="832">
       <c r="B832" s="6" t="s">
-        <v>5227</v>
+        <v>5230</v>
       </c>
       <c r="C832" s="6" t="s">
-        <v>5228</v>
+        <v>5231</v>
       </c>
       <c r="D832" s="6" t="s">
-        <v>5229</v>
+        <v>5232</v>
       </c>
       <c r="E832" s="6" t="s">
-        <v>5230</v>
+        <v>5233</v>
       </c>
       <c r="F832" s="6" t="s">
-        <v>5231</v>
+        <v>5234</v>
       </c>
       <c r="G832" s="6" t="s">
-        <v>5232</v>
+        <v>5234</v>
       </c>
       <c r="H832" s="6" t="s">
-        <v>5233</v>
+        <v>5235</v>
       </c>
     </row>
     <row r="833">
       <c r="B833" s="5" t="s">
-        <v>5234</v>
+        <v>5236</v>
       </c>
       <c r="C833" s="5" t="s">
-        <v>5235</v>
+        <v>5237</v>
       </c>
       <c r="D833" s="5" t="s">
-        <v>5236</v>
+        <v>5238</v>
       </c>
       <c r="E833" s="5" t="s">
-        <v>5237</v>
+        <v>5239</v>
       </c>
       <c r="F833" s="5" t="s">
-        <v>5238</v>
+        <v>5240</v>
       </c>
       <c r="G833" s="5" t="s">
-        <v>5239</v>
+        <v>5241</v>
       </c>
       <c r="H833" s="5" t="s">
-        <v>5236</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="834">
       <c r="B834" s="6" t="s">
-        <v>5240</v>
+        <v>5243</v>
       </c>
       <c r="C834" s="6" t="s">
-        <v>5241</v>
+        <v>5244</v>
       </c>
       <c r="D834" s="6" t="s">
-        <v>5242</v>
+        <v>5245</v>
       </c>
       <c r="E834" s="6" t="s">
-        <v>5243</v>
+        <v>5246</v>
       </c>
       <c r="F834" s="6" t="s">
-        <v>5244</v>
+        <v>5247</v>
       </c>
       <c r="G834" s="6" t="s">
-        <v>5245</v>
+        <v>5246</v>
       </c>
       <c r="H834" s="6" t="s">
-        <v>5246</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="835">
       <c r="B835" s="5" t="s">
-        <v>5247</v>
+        <v>5249</v>
       </c>
       <c r="C835" s="5" t="s">
-        <v>5248</v>
+        <v>5250</v>
       </c>
       <c r="D835" s="5" t="s">
-        <v>5249</v>
+        <v>5251</v>
       </c>
       <c r="E835" s="5" t="s">
-        <v>5250</v>
+        <v>5252</v>
       </c>
       <c r="F835" s="5" t="s">
+        <v>5253</v>
+      </c>
+      <c r="G835" s="5" t="s">
+        <v>5253</v>
+      </c>
+      <c r="H835" s="5" t="s">
         <v>5251</v>
-      </c>
-      <c r="G835" s="5" t="s">
-        <v>5251</v>
-      </c>
-      <c r="H835" s="5" t="s">
-        <v>5252</v>
       </c>
     </row>
     <row r="836">
       <c r="B836" s="6" t="s">
-        <v>5253</v>
+        <v>5254</v>
       </c>
       <c r="C836" s="6" t="s">
-        <v>5254</v>
+        <v>5255</v>
       </c>
       <c r="D836" s="6" t="s">
-        <v>5255</v>
+        <v>5256</v>
       </c>
       <c r="E836" s="6" t="s">
-        <v>5256</v>
+        <v>5257</v>
       </c>
       <c r="F836" s="6" t="s">
-        <v>5257</v>
+        <v>5258</v>
       </c>
       <c r="G836" s="6" t="s">
-        <v>5257</v>
+        <v>5259</v>
       </c>
       <c r="H836" s="6" t="s">
-        <v>5258</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="837">
       <c r="B837" s="5" t="s">
-        <v>5259</v>
+        <v>5261</v>
       </c>
       <c r="C837" s="5" t="s">
-        <v>5260</v>
+        <v>5262</v>
       </c>
       <c r="D837" s="5" t="s">
-        <v>5261</v>
+        <v>5263</v>
       </c>
       <c r="E837" s="5" t="s">
-        <v>5262</v>
+        <v>5264</v>
       </c>
       <c r="F837" s="5" t="s">
+        <v>5265</v>
+      </c>
+      <c r="G837" s="5" t="s">
+        <v>5266</v>
+      </c>
+      <c r="H837" s="5" t="s">
         <v>5263</v>
-      </c>
-      <c r="G837" s="5" t="s">
-        <v>5264</v>
-      </c>
-      <c r="H837" s="5" t="s">
-        <v>5265</v>
       </c>
     </row>
     <row r="838">
       <c r="B838" s="6" t="s">
-        <v>5266</v>
+        <v>5267</v>
       </c>
       <c r="C838" s="6" t="s">
-        <v>5267</v>
+        <v>5268</v>
       </c>
       <c r="D838" s="6" t="s">
-        <v>5268</v>
+        <v>5269</v>
       </c>
       <c r="E838" s="6" t="s">
-        <v>5269</v>
+        <v>5270</v>
       </c>
       <c r="F838" s="6" t="s">
-        <v>5270</v>
+        <v>5271</v>
       </c>
       <c r="G838" s="6" t="s">
-        <v>5270</v>
+        <v>5272</v>
       </c>
       <c r="H838" s="6" t="s">
-        <v>5271</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
-        <v>5272</v>
+        <v>5274</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>5273</v>
+        <v>5275</v>
       </c>
       <c r="D839" s="5" t="s">
-        <v>5274</v>
+        <v>5276</v>
       </c>
       <c r="E839" s="5" t="s">
-        <v>5275</v>
+        <v>5277</v>
       </c>
       <c r="F839" s="5" t="s">
-        <v>5276</v>
+        <v>5278</v>
       </c>
       <c r="G839" s="5" t="s">
-        <v>5277</v>
+        <v>5278</v>
       </c>
       <c r="H839" s="5" t="s">
-        <v>5278</v>
+        <v>5279</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
-        <v>5279</v>
+        <v>5280</v>
       </c>
       <c r="C840" s="6" t="s">
-        <v>5280</v>
+        <v>5281</v>
       </c>
       <c r="D840" s="6" t="s">
-        <v>5281</v>
+        <v>5282</v>
       </c>
       <c r="E840" s="6" t="s">
-        <v>5282</v>
+        <v>5283</v>
       </c>
       <c r="F840" s="6" t="s">
-        <v>5283</v>
+        <v>5284</v>
       </c>
       <c r="G840" s="6" t="s">
-        <v>5283</v>
+        <v>5284</v>
       </c>
       <c r="H840" s="6" t="s">
-        <v>5284</v>
+        <v>5285</v>
       </c>
     </row>
     <row r="841">
       <c r="B841" s="5" t="s">
-        <v>5285</v>
+        <v>5286</v>
       </c>
       <c r="C841" s="5" t="s">
-        <v>5286</v>
+        <v>5287</v>
       </c>
       <c r="D841" s="5" t="s">
-        <v>5287</v>
+        <v>5288</v>
       </c>
       <c r="E841" s="5" t="s">
-        <v>5288</v>
+        <v>5289</v>
       </c>
       <c r="F841" s="5" t="s">
-        <v>5289</v>
+        <v>5290</v>
       </c>
       <c r="G841" s="5" t="s">
-        <v>5289</v>
+        <v>5291</v>
       </c>
       <c r="H841" s="5" t="s">
-        <v>5290</v>
+        <v>5292</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
-        <v>5291</v>
+        <v>5293</v>
       </c>
       <c r="C842" s="6" t="s">
-        <v>5292</v>
+        <v>5294</v>
       </c>
       <c r="D842" s="6" t="s">
-        <v>5292</v>
+        <v>5295</v>
       </c>
       <c r="E842" s="6" t="s">
-        <v>5292</v>
+        <v>5296</v>
       </c>
       <c r="F842" s="6" t="s">
-        <v>5292</v>
+        <v>5297</v>
       </c>
       <c r="G842" s="6" t="s">
-        <v>5292</v>
+        <v>5297</v>
       </c>
       <c r="H842" s="6" t="s">
-        <v>5292</v>
+        <v>5298</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
-        <v>5293</v>
+        <v>5299</v>
       </c>
       <c r="C843" s="5" t="s">
-        <v>5294</v>
+        <v>5300</v>
       </c>
       <c r="D843" s="5" t="s">
-        <v>5295</v>
+        <v>5301</v>
       </c>
       <c r="E843" s="5" t="s">
-        <v>5296</v>
+        <v>5302</v>
       </c>
       <c r="F843" s="5" t="s">
-        <v>5297</v>
+        <v>5303</v>
       </c>
       <c r="G843" s="5" t="s">
-        <v>5297</v>
+        <v>5304</v>
       </c>
       <c r="H843" s="5" t="s">
-        <v>5295</v>
+        <v>5305</v>
       </c>
     </row>
     <row r="844">
       <c r="B844" s="6" t="s">
-        <v>5298</v>
+        <v>5306</v>
       </c>
       <c r="C844" s="6" t="s">
-        <v>5299</v>
+        <v>5307</v>
       </c>
       <c r="D844" s="6" t="s">
-        <v>5300</v>
+        <v>5308</v>
       </c>
       <c r="E844" s="6" t="s">
-        <v>5301</v>
+        <v>5309</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>5302</v>
+        <v>5310</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5303</v>
+        <v>5310</v>
       </c>
       <c r="H844" s="6" t="s">
-        <v>5300</v>
+        <v>5311</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5304</v>
+        <v>5312</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>5305</v>
+        <v>5313</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5306</v>
+        <v>5314</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>5307</v>
+        <v>5315</v>
       </c>
       <c r="F845" s="5" t="s">
-        <v>5307</v>
+        <v>5316</v>
       </c>
       <c r="G845" s="5" t="s">
-        <v>5307</v>
+        <v>5316</v>
       </c>
       <c r="H845" s="5" t="s">
-        <v>5306</v>
+        <v>5317</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
-        <v>5308</v>
+        <v>5318</v>
       </c>
       <c r="C846" s="6" t="s">
-        <v>5309</v>
+        <v>5319</v>
       </c>
       <c r="D846" s="6" t="s">
-        <v>5310</v>
+        <v>5319</v>
       </c>
       <c r="E846" s="6" t="s">
-        <v>5311</v>
+        <v>5319</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>5311</v>
+        <v>5319</v>
       </c>
       <c r="G846" s="6" t="s">
-        <v>5311</v>
+        <v>5319</v>
       </c>
       <c r="H846" s="6" t="s">
-        <v>5310</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
-        <v>5312</v>
+        <v>5320</v>
       </c>
       <c r="C847" s="5" t="s">
-        <v>5313</v>
+        <v>5321</v>
       </c>
       <c r="D847" s="5" t="s">
-        <v>5314</v>
+        <v>5322</v>
       </c>
       <c r="E847" s="5" t="s">
-        <v>5315</v>
+        <v>5323</v>
       </c>
       <c r="F847" s="5" t="s">
-        <v>5316</v>
+        <v>5324</v>
       </c>
       <c r="G847" s="5" t="s">
-        <v>5317</v>
+        <v>5324</v>
       </c>
       <c r="H847" s="5" t="s">
-        <v>5318</v>
+        <v>5322</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
-        <v>5319</v>
+        <v>5325</v>
       </c>
       <c r="C848" s="6" t="s">
-        <v>5320</v>
+        <v>5326</v>
       </c>
       <c r="D848" s="6" t="s">
-        <v>5321</v>
+        <v>5327</v>
       </c>
       <c r="E848" s="6" t="s">
-        <v>5322</v>
+        <v>5328</v>
       </c>
       <c r="F848" s="6" t="s">
-        <v>5323</v>
+        <v>5329</v>
       </c>
       <c r="G848" s="6" t="s">
-        <v>5324</v>
+        <v>5330</v>
       </c>
       <c r="H848" s="6" t="s">
-        <v>5321</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
-        <v>5325</v>
+        <v>5331</v>
       </c>
       <c r="C849" s="5" t="s">
-        <v>5326</v>
+        <v>5332</v>
       </c>
       <c r="D849" s="5" t="s">
-        <v>5327</v>
+        <v>5333</v>
       </c>
       <c r="E849" s="5" t="s">
-        <v>5328</v>
+        <v>5334</v>
       </c>
       <c r="F849" s="5" t="s">
-        <v>5329</v>
+        <v>5334</v>
       </c>
       <c r="G849" s="5" t="s">
-        <v>5330</v>
+        <v>5334</v>
       </c>
       <c r="H849" s="5" t="s">
-        <v>5331</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
-        <v>5332</v>
+        <v>5335</v>
       </c>
       <c r="C850" s="6" t="s">
-        <v>5333</v>
+        <v>5336</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>5334</v>
+        <v>5337</v>
       </c>
       <c r="E850" s="6" t="s">
-        <v>5335</v>
+        <v>5338</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>5336</v>
+        <v>5338</v>
       </c>
       <c r="G850" s="6" t="s">
+        <v>5338</v>
+      </c>
+      <c r="H850" s="6" t="s">
         <v>5337</v>
-      </c>
-      <c r="H850" s="6" t="s">
-        <v>5338</v>
       </c>
     </row>
     <row r="851">
@@ -36029,7 +36110,7 @@
         <v>5351</v>
       </c>
       <c r="H852" s="6" t="s">
-        <v>5321</v>
+        <v>5348</v>
       </c>
     </row>
     <row r="853">
@@ -36072,14 +36153,106 @@
         <v>5363</v>
       </c>
       <c r="G854" s="6" t="s">
-        <v>5363</v>
+        <v>5364</v>
       </c>
       <c r="H854" s="6" t="s">
-        <v>5364</v>
+        <v>5365</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="B855" s="5" t="s">
+        <v>5366</v>
+      </c>
+      <c r="C855" s="5" t="s">
+        <v>5367</v>
+      </c>
+      <c r="D855" s="5" t="s">
+        <v>5368</v>
+      </c>
+      <c r="E855" s="5" t="s">
+        <v>5369</v>
+      </c>
+      <c r="F855" s="5" t="s">
+        <v>5370</v>
+      </c>
+      <c r="G855" s="5" t="s">
+        <v>5371</v>
+      </c>
+      <c r="H855" s="5" t="s">
+        <v>5372</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="B856" s="6" t="s">
+        <v>5373</v>
+      </c>
+      <c r="C856" s="6" t="s">
+        <v>5374</v>
+      </c>
+      <c r="D856" s="6" t="s">
+        <v>5375</v>
+      </c>
+      <c r="E856" s="6" t="s">
+        <v>5376</v>
+      </c>
+      <c r="F856" s="6" t="s">
+        <v>5377</v>
+      </c>
+      <c r="G856" s="6" t="s">
+        <v>5378</v>
+      </c>
+      <c r="H856" s="6" t="s">
+        <v>5348</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="B857" s="5" t="s">
+        <v>5379</v>
+      </c>
+      <c r="C857" s="5" t="s">
+        <v>5380</v>
+      </c>
+      <c r="D857" s="5" t="s">
+        <v>5381</v>
+      </c>
+      <c r="E857" s="5" t="s">
+        <v>5382</v>
+      </c>
+      <c r="F857" s="5" t="s">
+        <v>5383</v>
+      </c>
+      <c r="G857" s="5" t="s">
+        <v>5384</v>
+      </c>
+      <c r="H857" s="5" t="s">
+        <v>5385</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="B858" s="6" t="s">
+        <v>5386</v>
+      </c>
+      <c r="C858" s="6" t="s">
+        <v>5387</v>
+      </c>
+      <c r="D858" s="6" t="s">
+        <v>5388</v>
+      </c>
+      <c r="E858" s="6" t="s">
+        <v>5389</v>
+      </c>
+      <c r="F858" s="6" t="s">
+        <v>5390</v>
+      </c>
+      <c r="G858" s="6" t="s">
+        <v>5390</v>
+      </c>
+      <c r="H858" s="6" t="s">
+        <v>5391</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H854"/>
+  <autoFilter ref="B2:H858"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36098,10 +36271,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5365</v>
+        <v>5392</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5366</v>
+        <v>5393</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36112,16 +36285,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5367</v>
+        <v>5394</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5368</v>
+        <v>5395</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5369</v>
+        <v>5396</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5370</v>
+        <v>5397</v>
       </c>
     </row>
     <row r="3">
@@ -36129,16 +36302,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5371</v>
+        <v>5398</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5372</v>
+        <v>5399</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5373</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="4">
@@ -36149,24 +36322,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5374</v>
+        <v>5401</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5375</v>
+        <v>5402</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5376</v>
+        <v>5403</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5377</v>
+        <v>5404</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5378</v>
+        <v>5405</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36174,13 +36347,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5379</v>
+        <v>5406</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5380</v>
+        <v>5407</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36188,13 +36361,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5381</v>
+        <v>5408</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5382</v>
+        <v>5409</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36202,13 +36375,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5383</v>
+        <v>5410</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5384</v>
+        <v>5411</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36216,13 +36389,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5385</v>
+        <v>5412</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5386</v>
+        <v>5413</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36230,13 +36403,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5387</v>
+        <v>5414</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5388</v>
+        <v>5415</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36244,13 +36417,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5389</v>
+        <v>5416</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5390</v>
+        <v>5417</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36258,13 +36431,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5391</v>
+        <v>5418</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5392</v>
+        <v>5419</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36272,13 +36445,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5393</v>
+        <v>5420</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5394</v>
+        <v>5421</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36286,13 +36459,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5395</v>
+        <v>5422</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5396</v>
+        <v>5423</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36306,7 +36479,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5397</v>
+        <v>5424</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36314,13 +36487,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5398</v>
+        <v>5425</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5399</v>
+        <v>5426</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36328,13 +36501,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5400</v>
+        <v>5427</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5401</v>
+        <v>5428</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36342,13 +36515,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5402</v>
+        <v>5429</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5403</v>
+        <v>5430</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36356,13 +36529,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5404</v>
+        <v>5431</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5405</v>
+        <v>5432</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36370,13 +36543,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5406</v>
+        <v>5433</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5407</v>
+        <v>5434</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36384,13 +36557,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5408</v>
+        <v>5435</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5409</v>
+        <v>5436</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36398,13 +36571,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5410</v>
+        <v>5437</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5411</v>
+        <v>5438</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36412,13 +36585,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5412</v>
+        <v>5439</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5413</v>
+        <v>5440</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36426,13 +36599,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5414</v>
+        <v>5441</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5415</v>
+        <v>5442</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$858]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$860]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6069" uniqueCount="5443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6083" uniqueCount="5457">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -13946,6 +13946,48 @@
   </si>
   <si>
     <t xml:space="preserve">Lautstärke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.option.music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배경음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">背景音乐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">背景音樂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.option.music_volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배경음 크기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGM 音量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">背景音乐音量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">背景音樂音量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musiklautstärke</t>
   </si>
   <si>
     <t xml:space="preserve">ui.option.shake</t>
@@ -16545,7 +16587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H858"/>
+  <dimension ref="A1:H860"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -33646,119 +33688,119 @@
         <v>4654</v>
       </c>
       <c r="G745" s="5" t="s">
-        <v>4654</v>
+        <v>4655</v>
       </c>
       <c r="H745" s="5" t="s">
-        <v>4655</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="746">
       <c r="B746" s="6" t="s">
-        <v>4656</v>
+        <v>4657</v>
       </c>
       <c r="C746" s="6" t="s">
-        <v>4657</v>
+        <v>4658</v>
       </c>
       <c r="D746" s="6" t="s">
-        <v>4658</v>
+        <v>4659</v>
       </c>
       <c r="E746" s="6" t="s">
-        <v>4659</v>
+        <v>4660</v>
       </c>
       <c r="F746" s="6" t="s">
-        <v>4660</v>
+        <v>4661</v>
       </c>
       <c r="G746" s="6" t="s">
-        <v>4660</v>
+        <v>4662</v>
       </c>
       <c r="H746" s="6" t="s">
-        <v>4661</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="747">
       <c r="B747" s="5" t="s">
-        <v>4662</v>
+        <v>4664</v>
       </c>
       <c r="C747" s="5" t="s">
-        <v>4663</v>
+        <v>4665</v>
       </c>
       <c r="D747" s="5" t="s">
-        <v>4664</v>
+        <v>4666</v>
       </c>
       <c r="E747" s="5" t="s">
-        <v>4665</v>
+        <v>4667</v>
       </c>
       <c r="F747" s="5" t="s">
-        <v>4666</v>
+        <v>4668</v>
       </c>
       <c r="G747" s="5" t="s">
-        <v>4667</v>
+        <v>4668</v>
       </c>
       <c r="H747" s="5" t="s">
-        <v>4668</v>
+        <v>4669</v>
       </c>
     </row>
     <row r="748">
       <c r="B748" s="6" t="s">
-        <v>4669</v>
+        <v>4670</v>
       </c>
       <c r="C748" s="6" t="s">
-        <v>4670</v>
+        <v>4671</v>
       </c>
       <c r="D748" s="6" t="s">
-        <v>4671</v>
+        <v>4672</v>
       </c>
       <c r="E748" s="6" t="s">
-        <v>4672</v>
+        <v>4673</v>
       </c>
       <c r="F748" s="6" t="s">
-        <v>4673</v>
+        <v>4674</v>
       </c>
       <c r="G748" s="6" t="s">
-        <v>4673</v>
+        <v>4674</v>
       </c>
       <c r="H748" s="6" t="s">
-        <v>4674</v>
+        <v>4675</v>
       </c>
     </row>
     <row r="749">
       <c r="B749" s="5" t="s">
-        <v>4675</v>
+        <v>4676</v>
       </c>
       <c r="C749" s="5" t="s">
-        <v>4676</v>
+        <v>4677</v>
       </c>
       <c r="D749" s="5" t="s">
-        <v>4677</v>
+        <v>4678</v>
       </c>
       <c r="E749" s="5" t="s">
-        <v>4678</v>
+        <v>4679</v>
       </c>
       <c r="F749" s="5" t="s">
-        <v>4679</v>
+        <v>4680</v>
       </c>
       <c r="G749" s="5" t="s">
-        <v>4680</v>
+        <v>4681</v>
       </c>
       <c r="H749" s="5" t="s">
-        <v>4681</v>
+        <v>4682</v>
       </c>
     </row>
     <row r="750">
       <c r="B750" s="6" t="s">
-        <v>4682</v>
+        <v>4683</v>
       </c>
       <c r="C750" s="6" t="s">
-        <v>4683</v>
+        <v>4684</v>
       </c>
       <c r="D750" s="6" t="s">
-        <v>4684</v>
+        <v>4685</v>
       </c>
       <c r="E750" s="6" t="s">
-        <v>4685</v>
+        <v>4686</v>
       </c>
       <c r="F750" s="6" t="s">
-        <v>4686</v>
+        <v>4687</v>
       </c>
       <c r="G750" s="6" t="s">
         <v>4687</v>
@@ -33968,50 +34010,50 @@
         <v>4749</v>
       </c>
       <c r="G759" s="5" t="s">
-        <v>4749</v>
+        <v>4750</v>
       </c>
       <c r="H759" s="5" t="s">
-        <v>4750</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="760">
       <c r="B760" s="6" t="s">
-        <v>4751</v>
+        <v>4752</v>
       </c>
       <c r="C760" s="6" t="s">
-        <v>4752</v>
+        <v>4753</v>
       </c>
       <c r="D760" s="6" t="s">
-        <v>4753</v>
+        <v>4754</v>
       </c>
       <c r="E760" s="6" t="s">
-        <v>4754</v>
+        <v>4755</v>
       </c>
       <c r="F760" s="6" t="s">
-        <v>4755</v>
+        <v>4756</v>
       </c>
       <c r="G760" s="6" t="s">
-        <v>4756</v>
+        <v>4757</v>
       </c>
       <c r="H760" s="6" t="s">
-        <v>4757</v>
+        <v>4758</v>
       </c>
     </row>
     <row r="761">
       <c r="B761" s="5" t="s">
-        <v>4758</v>
+        <v>4759</v>
       </c>
       <c r="C761" s="5" t="s">
-        <v>4759</v>
+        <v>4760</v>
       </c>
       <c r="D761" s="5" t="s">
-        <v>4760</v>
+        <v>4761</v>
       </c>
       <c r="E761" s="5" t="s">
-        <v>4761</v>
+        <v>4762</v>
       </c>
       <c r="F761" s="5" t="s">
-        <v>4762</v>
+        <v>4763</v>
       </c>
       <c r="G761" s="5" t="s">
         <v>4763</v>
@@ -34359,50 +34401,50 @@
         <v>4867</v>
       </c>
       <c r="G776" s="6" t="s">
-        <v>4867</v>
+        <v>4868</v>
       </c>
       <c r="H776" s="6" t="s">
-        <v>4868</v>
+        <v>4869</v>
       </c>
     </row>
     <row r="777">
       <c r="B777" s="5" t="s">
-        <v>4869</v>
+        <v>4870</v>
       </c>
       <c r="C777" s="5" t="s">
-        <v>4870</v>
+        <v>4871</v>
       </c>
       <c r="D777" s="5" t="s">
-        <v>4871</v>
+        <v>4872</v>
       </c>
       <c r="E777" s="5" t="s">
-        <v>4872</v>
+        <v>4873</v>
       </c>
       <c r="F777" s="5" t="s">
-        <v>4873</v>
+        <v>4874</v>
       </c>
       <c r="G777" s="5" t="s">
-        <v>4874</v>
+        <v>4875</v>
       </c>
       <c r="H777" s="5" t="s">
-        <v>4875</v>
+        <v>4876</v>
       </c>
     </row>
     <row r="778">
       <c r="B778" s="6" t="s">
-        <v>4876</v>
+        <v>4877</v>
       </c>
       <c r="C778" s="6" t="s">
-        <v>4877</v>
+        <v>4878</v>
       </c>
       <c r="D778" s="6" t="s">
-        <v>4878</v>
+        <v>4879</v>
       </c>
       <c r="E778" s="6" t="s">
-        <v>4879</v>
+        <v>4880</v>
       </c>
       <c r="F778" s="6" t="s">
-        <v>4880</v>
+        <v>4881</v>
       </c>
       <c r="G778" s="6" t="s">
         <v>4881</v>
@@ -34428,50 +34470,50 @@
         <v>4887</v>
       </c>
       <c r="G779" s="5" t="s">
-        <v>4887</v>
+        <v>4888</v>
       </c>
       <c r="H779" s="5" t="s">
-        <v>4888</v>
+        <v>4889</v>
       </c>
     </row>
     <row r="780">
       <c r="B780" s="6" t="s">
-        <v>4889</v>
+        <v>4890</v>
       </c>
       <c r="C780" s="6" t="s">
-        <v>4890</v>
+        <v>4891</v>
       </c>
       <c r="D780" s="6" t="s">
-        <v>4891</v>
+        <v>4892</v>
       </c>
       <c r="E780" s="6" t="s">
-        <v>4892</v>
+        <v>4893</v>
       </c>
       <c r="F780" s="6" t="s">
-        <v>4893</v>
+        <v>4894</v>
       </c>
       <c r="G780" s="6" t="s">
-        <v>4894</v>
+        <v>4895</v>
       </c>
       <c r="H780" s="6" t="s">
-        <v>4895</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="781">
       <c r="B781" s="5" t="s">
-        <v>4896</v>
+        <v>4897</v>
       </c>
       <c r="C781" s="5" t="s">
-        <v>4897</v>
+        <v>4898</v>
       </c>
       <c r="D781" s="5" t="s">
-        <v>4898</v>
+        <v>4899</v>
       </c>
       <c r="E781" s="5" t="s">
-        <v>4899</v>
+        <v>4900</v>
       </c>
       <c r="F781" s="5" t="s">
-        <v>4900</v>
+        <v>4901</v>
       </c>
       <c r="G781" s="5" t="s">
         <v>4901</v>
@@ -34520,50 +34562,50 @@
         <v>4914</v>
       </c>
       <c r="G783" s="5" t="s">
-        <v>4914</v>
+        <v>4915</v>
       </c>
       <c r="H783" s="5" t="s">
-        <v>4915</v>
+        <v>4916</v>
       </c>
     </row>
     <row r="784">
       <c r="B784" s="6" t="s">
-        <v>4916</v>
+        <v>4917</v>
       </c>
       <c r="C784" s="6" t="s">
-        <v>4917</v>
+        <v>4918</v>
       </c>
       <c r="D784" s="6" t="s">
-        <v>4918</v>
+        <v>4919</v>
       </c>
       <c r="E784" s="6" t="s">
-        <v>4919</v>
+        <v>4920</v>
       </c>
       <c r="F784" s="6" t="s">
-        <v>4920</v>
+        <v>4921</v>
       </c>
       <c r="G784" s="6" t="s">
-        <v>4921</v>
+        <v>4922</v>
       </c>
       <c r="H784" s="6" t="s">
-        <v>4922</v>
+        <v>4923</v>
       </c>
     </row>
     <row r="785">
       <c r="B785" s="5" t="s">
-        <v>4923</v>
+        <v>4924</v>
       </c>
       <c r="C785" s="5" t="s">
-        <v>4924</v>
+        <v>4925</v>
       </c>
       <c r="D785" s="5" t="s">
-        <v>4925</v>
+        <v>4926</v>
       </c>
       <c r="E785" s="5" t="s">
-        <v>4926</v>
+        <v>4927</v>
       </c>
       <c r="F785" s="5" t="s">
-        <v>4927</v>
+        <v>4928</v>
       </c>
       <c r="G785" s="5" t="s">
         <v>4928</v>
@@ -34707,53 +34749,53 @@
         <v>4970</v>
       </c>
       <c r="H791" s="5" t="s">
-        <v>4967</v>
+        <v>4971</v>
       </c>
     </row>
     <row r="792">
       <c r="B792" s="6" t="s">
-        <v>4971</v>
+        <v>4972</v>
       </c>
       <c r="C792" s="6" t="s">
-        <v>4972</v>
+        <v>4973</v>
       </c>
       <c r="D792" s="6" t="s">
-        <v>4973</v>
+        <v>4974</v>
       </c>
       <c r="E792" s="6" t="s">
-        <v>4974</v>
+        <v>4975</v>
       </c>
       <c r="F792" s="6" t="s">
-        <v>4975</v>
+        <v>4976</v>
       </c>
       <c r="G792" s="6" t="s">
-        <v>4976</v>
+        <v>4977</v>
       </c>
       <c r="H792" s="6" t="s">
-        <v>4977</v>
+        <v>4978</v>
       </c>
     </row>
     <row r="793">
       <c r="B793" s="5" t="s">
-        <v>4978</v>
+        <v>4979</v>
       </c>
       <c r="C793" s="5" t="s">
-        <v>4979</v>
+        <v>4980</v>
       </c>
       <c r="D793" s="5" t="s">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="E793" s="5" t="s">
+        <v>4982</v>
+      </c>
+      <c r="F793" s="5" t="s">
+        <v>4983</v>
+      </c>
+      <c r="G793" s="5" t="s">
+        <v>4984</v>
+      </c>
+      <c r="H793" s="5" t="s">
         <v>4981</v>
-      </c>
-      <c r="F793" s="5" t="s">
-        <v>4982</v>
-      </c>
-      <c r="G793" s="5" t="s">
-        <v>4983</v>
-      </c>
-      <c r="H793" s="5" t="s">
-        <v>4984</v>
       </c>
     </row>
     <row r="794">
@@ -34807,154 +34849,154 @@
         <v>4999</v>
       </c>
       <c r="C796" s="6" t="s">
-        <v>3021</v>
+        <v>5000</v>
       </c>
       <c r="D796" s="6" t="s">
-        <v>5000</v>
+        <v>5001</v>
       </c>
       <c r="E796" s="6" t="s">
-        <v>3023</v>
+        <v>5002</v>
       </c>
       <c r="F796" s="6" t="s">
-        <v>5001</v>
+        <v>5003</v>
       </c>
       <c r="G796" s="6" t="s">
-        <v>5002</v>
+        <v>5004</v>
       </c>
       <c r="H796" s="6" t="s">
-        <v>5003</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="797">
       <c r="B797" s="5" t="s">
-        <v>5004</v>
+        <v>5006</v>
       </c>
       <c r="C797" s="5" t="s">
-        <v>3014</v>
+        <v>5007</v>
       </c>
       <c r="D797" s="5" t="s">
-        <v>5005</v>
+        <v>5008</v>
       </c>
       <c r="E797" s="5" t="s">
-        <v>3016</v>
+        <v>5009</v>
       </c>
       <c r="F797" s="5" t="s">
-        <v>5006</v>
+        <v>5010</v>
       </c>
       <c r="G797" s="5" t="s">
-        <v>5007</v>
+        <v>5011</v>
       </c>
       <c r="H797" s="5" t="s">
-        <v>5008</v>
+        <v>5012</v>
       </c>
     </row>
     <row r="798">
       <c r="B798" s="6" t="s">
-        <v>5009</v>
+        <v>5013</v>
       </c>
       <c r="C798" s="6" t="s">
-        <v>5010</v>
+        <v>3021</v>
       </c>
       <c r="D798" s="6" t="s">
-        <v>5011</v>
+        <v>5014</v>
       </c>
       <c r="E798" s="6" t="s">
-        <v>5012</v>
+        <v>3023</v>
       </c>
       <c r="F798" s="6" t="s">
-        <v>5013</v>
+        <v>5015</v>
       </c>
       <c r="G798" s="6" t="s">
-        <v>5012</v>
+        <v>5016</v>
       </c>
       <c r="H798" s="6" t="s">
-        <v>4429</v>
+        <v>5017</v>
       </c>
     </row>
     <row r="799">
       <c r="B799" s="5" t="s">
-        <v>5014</v>
+        <v>5018</v>
       </c>
       <c r="C799" s="5" t="s">
-        <v>5015</v>
+        <v>3014</v>
       </c>
       <c r="D799" s="5" t="s">
-        <v>5016</v>
+        <v>5019</v>
       </c>
       <c r="E799" s="5" t="s">
-        <v>5017</v>
+        <v>3016</v>
       </c>
       <c r="F799" s="5" t="s">
-        <v>5018</v>
+        <v>5020</v>
       </c>
       <c r="G799" s="5" t="s">
-        <v>5019</v>
+        <v>5021</v>
       </c>
       <c r="H799" s="5" t="s">
-        <v>5020</v>
+        <v>5022</v>
       </c>
     </row>
     <row r="800">
       <c r="B800" s="6" t="s">
-        <v>5021</v>
+        <v>5023</v>
       </c>
       <c r="C800" s="6" t="s">
-        <v>5022</v>
+        <v>5024</v>
       </c>
       <c r="D800" s="6" t="s">
-        <v>5023</v>
+        <v>5025</v>
       </c>
       <c r="E800" s="6" t="s">
-        <v>5024</v>
+        <v>5026</v>
       </c>
       <c r="F800" s="6" t="s">
-        <v>5025</v>
+        <v>5027</v>
       </c>
       <c r="G800" s="6" t="s">
-        <v>5025</v>
+        <v>5026</v>
       </c>
       <c r="H800" s="6" t="s">
-        <v>5026</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="801">
       <c r="B801" s="5" t="s">
-        <v>5027</v>
+        <v>5028</v>
       </c>
       <c r="C801" s="5" t="s">
-        <v>5028</v>
+        <v>5029</v>
       </c>
       <c r="D801" s="5" t="s">
-        <v>5029</v>
+        <v>5030</v>
       </c>
       <c r="E801" s="5" t="s">
-        <v>5030</v>
+        <v>5031</v>
       </c>
       <c r="F801" s="5" t="s">
-        <v>5031</v>
+        <v>5032</v>
       </c>
       <c r="G801" s="5" t="s">
-        <v>5032</v>
+        <v>5033</v>
       </c>
       <c r="H801" s="5" t="s">
-        <v>5033</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="802">
       <c r="B802" s="6" t="s">
-        <v>5034</v>
+        <v>5035</v>
       </c>
       <c r="C802" s="6" t="s">
-        <v>5035</v>
+        <v>5036</v>
       </c>
       <c r="D802" s="6" t="s">
-        <v>5036</v>
+        <v>5037</v>
       </c>
       <c r="E802" s="6" t="s">
-        <v>5037</v>
+        <v>5038</v>
       </c>
       <c r="F802" s="6" t="s">
-        <v>5038</v>
+        <v>5039</v>
       </c>
       <c r="G802" s="6" t="s">
         <v>5039</v>
@@ -35046,53 +35088,53 @@
         <v>5065</v>
       </c>
       <c r="F806" s="6" t="s">
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="G806" s="6" t="s">
-        <v>5065</v>
+        <v>5067</v>
       </c>
       <c r="H806" s="6" t="s">
-        <v>5066</v>
+        <v>5068</v>
       </c>
     </row>
     <row r="807">
       <c r="B807" s="5" t="s">
-        <v>5067</v>
+        <v>5069</v>
       </c>
       <c r="C807" s="5" t="s">
-        <v>5068</v>
+        <v>5070</v>
       </c>
       <c r="D807" s="5" t="s">
-        <v>5069</v>
+        <v>5071</v>
       </c>
       <c r="E807" s="5" t="s">
-        <v>5070</v>
+        <v>5072</v>
       </c>
       <c r="F807" s="5" t="s">
-        <v>5071</v>
+        <v>5073</v>
       </c>
       <c r="G807" s="5" t="s">
-        <v>5072</v>
+        <v>5074</v>
       </c>
       <c r="H807" s="5" t="s">
-        <v>5073</v>
+        <v>5075</v>
       </c>
     </row>
     <row r="808">
       <c r="B808" s="6" t="s">
-        <v>5074</v>
+        <v>5076</v>
       </c>
       <c r="C808" s="6" t="s">
-        <v>5075</v>
+        <v>5077</v>
       </c>
       <c r="D808" s="6" t="s">
-        <v>5076</v>
+        <v>5078</v>
       </c>
       <c r="E808" s="6" t="s">
-        <v>5077</v>
+        <v>5079</v>
       </c>
       <c r="F808" s="6" t="s">
-        <v>5078</v>
+        <v>5079</v>
       </c>
       <c r="G808" s="6" t="s">
         <v>5079</v>
@@ -35141,96 +35183,96 @@
         <v>5092</v>
       </c>
       <c r="G810" s="6" t="s">
-        <v>5092</v>
+        <v>5093</v>
       </c>
       <c r="H810" s="6" t="s">
-        <v>5093</v>
+        <v>5094</v>
       </c>
     </row>
     <row r="811">
       <c r="B811" s="5" t="s">
-        <v>5094</v>
+        <v>5095</v>
       </c>
       <c r="C811" s="5" t="s">
-        <v>5095</v>
+        <v>5096</v>
       </c>
       <c r="D811" s="5" t="s">
-        <v>5096</v>
+        <v>5097</v>
       </c>
       <c r="E811" s="5" t="s">
-        <v>5097</v>
+        <v>5098</v>
       </c>
       <c r="F811" s="5" t="s">
-        <v>5098</v>
+        <v>5099</v>
       </c>
       <c r="G811" s="5" t="s">
-        <v>5098</v>
+        <v>5100</v>
       </c>
       <c r="H811" s="5" t="s">
-        <v>5099</v>
+        <v>5101</v>
       </c>
     </row>
     <row r="812">
       <c r="B812" s="6" t="s">
-        <v>5100</v>
+        <v>5102</v>
       </c>
       <c r="C812" s="6" t="s">
-        <v>5101</v>
+        <v>5103</v>
       </c>
       <c r="D812" s="6" t="s">
-        <v>5102</v>
+        <v>5104</v>
       </c>
       <c r="E812" s="6" t="s">
-        <v>5103</v>
+        <v>5105</v>
       </c>
       <c r="F812" s="6" t="s">
-        <v>5104</v>
+        <v>5106</v>
       </c>
       <c r="G812" s="6" t="s">
-        <v>5104</v>
+        <v>5106</v>
       </c>
       <c r="H812" s="6" t="s">
-        <v>5105</v>
+        <v>5107</v>
       </c>
     </row>
     <row r="813">
       <c r="B813" s="5" t="s">
-        <v>5106</v>
+        <v>5108</v>
       </c>
       <c r="C813" s="5" t="s">
-        <v>5107</v>
+        <v>5109</v>
       </c>
       <c r="D813" s="5" t="s">
-        <v>5108</v>
+        <v>5110</v>
       </c>
       <c r="E813" s="5" t="s">
-        <v>5109</v>
+        <v>5111</v>
       </c>
       <c r="F813" s="5" t="s">
-        <v>5110</v>
+        <v>5112</v>
       </c>
       <c r="G813" s="5" t="s">
-        <v>5111</v>
+        <v>5112</v>
       </c>
       <c r="H813" s="5" t="s">
-        <v>5112</v>
+        <v>5113</v>
       </c>
     </row>
     <row r="814">
       <c r="B814" s="6" t="s">
-        <v>5113</v>
+        <v>5114</v>
       </c>
       <c r="C814" s="6" t="s">
-        <v>5114</v>
+        <v>5115</v>
       </c>
       <c r="D814" s="6" t="s">
-        <v>5115</v>
+        <v>5116</v>
       </c>
       <c r="E814" s="6" t="s">
-        <v>5116</v>
+        <v>5117</v>
       </c>
       <c r="F814" s="6" t="s">
-        <v>5117</v>
+        <v>5118</v>
       </c>
       <c r="G814" s="6" t="s">
         <v>5118</v>
@@ -35325,79 +35367,79 @@
         <v>5145</v>
       </c>
       <c r="G818" s="6" t="s">
-        <v>5145</v>
+        <v>5146</v>
       </c>
       <c r="H818" s="6" t="s">
-        <v>5146</v>
+        <v>5147</v>
       </c>
     </row>
     <row r="819">
       <c r="B819" s="5" t="s">
-        <v>5147</v>
+        <v>5148</v>
       </c>
       <c r="C819" s="5" t="s">
-        <v>5148</v>
+        <v>5149</v>
       </c>
       <c r="D819" s="5" t="s">
-        <v>5149</v>
+        <v>5150</v>
       </c>
       <c r="E819" s="5" t="s">
-        <v>5150</v>
+        <v>5151</v>
       </c>
       <c r="F819" s="5" t="s">
-        <v>5150</v>
+        <v>5152</v>
       </c>
       <c r="G819" s="5" t="s">
-        <v>5150</v>
+        <v>5153</v>
       </c>
       <c r="H819" s="5" t="s">
-        <v>5149</v>
+        <v>5154</v>
       </c>
     </row>
     <row r="820">
       <c r="B820" s="6" t="s">
-        <v>5151</v>
+        <v>5155</v>
       </c>
       <c r="C820" s="6" t="s">
-        <v>5152</v>
+        <v>5156</v>
       </c>
       <c r="D820" s="6" t="s">
-        <v>5153</v>
+        <v>5157</v>
       </c>
       <c r="E820" s="6" t="s">
-        <v>5154</v>
+        <v>5158</v>
       </c>
       <c r="F820" s="6" t="s">
-        <v>5155</v>
+        <v>5159</v>
       </c>
       <c r="G820" s="6" t="s">
-        <v>5156</v>
+        <v>5159</v>
       </c>
       <c r="H820" s="6" t="s">
-        <v>5157</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="821">
       <c r="B821" s="5" t="s">
-        <v>5158</v>
+        <v>5161</v>
       </c>
       <c r="C821" s="5" t="s">
-        <v>5159</v>
+        <v>5162</v>
       </c>
       <c r="D821" s="5" t="s">
-        <v>5160</v>
+        <v>5163</v>
       </c>
       <c r="E821" s="5" t="s">
-        <v>5161</v>
+        <v>5164</v>
       </c>
       <c r="F821" s="5" t="s">
-        <v>5162</v>
+        <v>5164</v>
       </c>
       <c r="G821" s="5" t="s">
+        <v>5164</v>
+      </c>
+      <c r="H821" s="5" t="s">
         <v>5163</v>
-      </c>
-      <c r="H821" s="5" t="s">
-        <v>5164</v>
       </c>
     </row>
     <row r="822">
@@ -35431,111 +35473,111 @@
         <v>5173</v>
       </c>
       <c r="D823" s="5" t="s">
-        <v>5149</v>
+        <v>5174</v>
       </c>
       <c r="E823" s="5" t="s">
-        <v>5174</v>
+        <v>5175</v>
       </c>
       <c r="F823" s="5" t="s">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="G823" s="5" t="s">
-        <v>5175</v>
+        <v>5177</v>
       </c>
       <c r="H823" s="5" t="s">
-        <v>5149</v>
+        <v>5178</v>
       </c>
     </row>
     <row r="824">
       <c r="B824" s="6" t="s">
-        <v>5176</v>
+        <v>5179</v>
       </c>
       <c r="C824" s="6" t="s">
-        <v>5177</v>
+        <v>5180</v>
       </c>
       <c r="D824" s="6" t="s">
-        <v>5178</v>
+        <v>5181</v>
       </c>
       <c r="E824" s="6" t="s">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="F824" s="6" t="s">
-        <v>5180</v>
+        <v>5183</v>
       </c>
       <c r="G824" s="6" t="s">
-        <v>5181</v>
+        <v>5184</v>
       </c>
       <c r="H824" s="6" t="s">
-        <v>5182</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="825">
       <c r="B825" s="5" t="s">
-        <v>5183</v>
+        <v>5186</v>
       </c>
       <c r="C825" s="5" t="s">
-        <v>5184</v>
+        <v>5187</v>
       </c>
       <c r="D825" s="5" t="s">
-        <v>5185</v>
+        <v>5163</v>
       </c>
       <c r="E825" s="5" t="s">
-        <v>5186</v>
+        <v>5188</v>
       </c>
       <c r="F825" s="5" t="s">
-        <v>5187</v>
+        <v>5189</v>
       </c>
       <c r="G825" s="5" t="s">
-        <v>5188</v>
+        <v>5189</v>
       </c>
       <c r="H825" s="5" t="s">
-        <v>5185</v>
+        <v>5163</v>
       </c>
     </row>
     <row r="826">
       <c r="B826" s="6" t="s">
-        <v>5189</v>
+        <v>5190</v>
       </c>
       <c r="C826" s="6" t="s">
-        <v>5190</v>
+        <v>5191</v>
       </c>
       <c r="D826" s="6" t="s">
-        <v>5191</v>
+        <v>5192</v>
       </c>
       <c r="E826" s="6" t="s">
-        <v>5192</v>
+        <v>5193</v>
       </c>
       <c r="F826" s="6" t="s">
-        <v>5193</v>
+        <v>5194</v>
       </c>
       <c r="G826" s="6" t="s">
-        <v>5194</v>
+        <v>5195</v>
       </c>
       <c r="H826" s="6" t="s">
-        <v>5195</v>
+        <v>5196</v>
       </c>
     </row>
     <row r="827">
       <c r="B827" s="5" t="s">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="C827" s="5" t="s">
-        <v>5197</v>
+        <v>5198</v>
       </c>
       <c r="D827" s="5" t="s">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="E827" s="5" t="s">
+        <v>5200</v>
+      </c>
+      <c r="F827" s="5" t="s">
+        <v>5201</v>
+      </c>
+      <c r="G827" s="5" t="s">
+        <v>5202</v>
+      </c>
+      <c r="H827" s="5" t="s">
         <v>5199</v>
-      </c>
-      <c r="F827" s="5" t="s">
-        <v>5200</v>
-      </c>
-      <c r="G827" s="5" t="s">
-        <v>5201</v>
-      </c>
-      <c r="H827" s="5" t="s">
-        <v>5202</v>
       </c>
     </row>
     <row r="828">
@@ -35601,562 +35643,562 @@
         <v>5221</v>
       </c>
       <c r="G830" s="6" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="H830" s="6" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
     </row>
     <row r="831">
       <c r="B831" s="5" t="s">
-        <v>5223</v>
+        <v>5224</v>
       </c>
       <c r="C831" s="5" t="s">
-        <v>5224</v>
+        <v>5225</v>
       </c>
       <c r="D831" s="5" t="s">
-        <v>5225</v>
+        <v>5226</v>
       </c>
       <c r="E831" s="5" t="s">
-        <v>5226</v>
+        <v>5227</v>
       </c>
       <c r="F831" s="5" t="s">
-        <v>5227</v>
+        <v>5228</v>
       </c>
       <c r="G831" s="5" t="s">
-        <v>5228</v>
+        <v>5229</v>
       </c>
       <c r="H831" s="5" t="s">
-        <v>5229</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="832">
       <c r="B832" s="6" t="s">
-        <v>5230</v>
+        <v>5231</v>
       </c>
       <c r="C832" s="6" t="s">
-        <v>5231</v>
+        <v>5232</v>
       </c>
       <c r="D832" s="6" t="s">
-        <v>5232</v>
+        <v>5233</v>
       </c>
       <c r="E832" s="6" t="s">
-        <v>5233</v>
+        <v>5234</v>
       </c>
       <c r="F832" s="6" t="s">
-        <v>5234</v>
+        <v>5235</v>
       </c>
       <c r="G832" s="6" t="s">
-        <v>5234</v>
+        <v>5235</v>
       </c>
       <c r="H832" s="6" t="s">
-        <v>5235</v>
+        <v>5236</v>
       </c>
     </row>
     <row r="833">
       <c r="B833" s="5" t="s">
-        <v>5236</v>
+        <v>5237</v>
       </c>
       <c r="C833" s="5" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="D833" s="5" t="s">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="E833" s="5" t="s">
-        <v>5239</v>
+        <v>5240</v>
       </c>
       <c r="F833" s="5" t="s">
-        <v>5240</v>
+        <v>5241</v>
       </c>
       <c r="G833" s="5" t="s">
-        <v>5241</v>
+        <v>5242</v>
       </c>
       <c r="H833" s="5" t="s">
-        <v>5242</v>
+        <v>5243</v>
       </c>
     </row>
     <row r="834">
       <c r="B834" s="6" t="s">
-        <v>5243</v>
+        <v>5244</v>
       </c>
       <c r="C834" s="6" t="s">
-        <v>5244</v>
+        <v>5245</v>
       </c>
       <c r="D834" s="6" t="s">
-        <v>5245</v>
+        <v>5246</v>
       </c>
       <c r="E834" s="6" t="s">
-        <v>5246</v>
+        <v>5247</v>
       </c>
       <c r="F834" s="6" t="s">
-        <v>5247</v>
+        <v>5248</v>
       </c>
       <c r="G834" s="6" t="s">
-        <v>5246</v>
+        <v>5248</v>
       </c>
       <c r="H834" s="6" t="s">
-        <v>5248</v>
+        <v>5249</v>
       </c>
     </row>
     <row r="835">
       <c r="B835" s="5" t="s">
-        <v>5249</v>
+        <v>5250</v>
       </c>
       <c r="C835" s="5" t="s">
-        <v>5250</v>
+        <v>5251</v>
       </c>
       <c r="D835" s="5" t="s">
-        <v>5251</v>
+        <v>5252</v>
       </c>
       <c r="E835" s="5" t="s">
-        <v>5252</v>
+        <v>5253</v>
       </c>
       <c r="F835" s="5" t="s">
-        <v>5253</v>
+        <v>5254</v>
       </c>
       <c r="G835" s="5" t="s">
-        <v>5253</v>
+        <v>5255</v>
       </c>
       <c r="H835" s="5" t="s">
-        <v>5251</v>
+        <v>5256</v>
       </c>
     </row>
     <row r="836">
       <c r="B836" s="6" t="s">
-        <v>5254</v>
+        <v>5257</v>
       </c>
       <c r="C836" s="6" t="s">
-        <v>5255</v>
+        <v>5258</v>
       </c>
       <c r="D836" s="6" t="s">
-        <v>5256</v>
+        <v>5259</v>
       </c>
       <c r="E836" s="6" t="s">
-        <v>5257</v>
+        <v>5260</v>
       </c>
       <c r="F836" s="6" t="s">
-        <v>5258</v>
+        <v>5261</v>
       </c>
       <c r="G836" s="6" t="s">
-        <v>5259</v>
+        <v>5260</v>
       </c>
       <c r="H836" s="6" t="s">
-        <v>5260</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="837">
       <c r="B837" s="5" t="s">
-        <v>5261</v>
+        <v>5263</v>
       </c>
       <c r="C837" s="5" t="s">
-        <v>5262</v>
+        <v>5264</v>
       </c>
       <c r="D837" s="5" t="s">
-        <v>5263</v>
+        <v>5265</v>
       </c>
       <c r="E837" s="5" t="s">
-        <v>5264</v>
+        <v>5266</v>
       </c>
       <c r="F837" s="5" t="s">
+        <v>5267</v>
+      </c>
+      <c r="G837" s="5" t="s">
+        <v>5267</v>
+      </c>
+      <c r="H837" s="5" t="s">
         <v>5265</v>
-      </c>
-      <c r="G837" s="5" t="s">
-        <v>5266</v>
-      </c>
-      <c r="H837" s="5" t="s">
-        <v>5263</v>
       </c>
     </row>
     <row r="838">
       <c r="B838" s="6" t="s">
-        <v>5267</v>
+        <v>5268</v>
       </c>
       <c r="C838" s="6" t="s">
-        <v>5268</v>
+        <v>5269</v>
       </c>
       <c r="D838" s="6" t="s">
-        <v>5269</v>
+        <v>5270</v>
       </c>
       <c r="E838" s="6" t="s">
-        <v>5270</v>
+        <v>5271</v>
       </c>
       <c r="F838" s="6" t="s">
-        <v>5271</v>
+        <v>5272</v>
       </c>
       <c r="G838" s="6" t="s">
-        <v>5272</v>
+        <v>5273</v>
       </c>
       <c r="H838" s="6" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
-        <v>5274</v>
+        <v>5275</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>5275</v>
+        <v>5276</v>
       </c>
       <c r="D839" s="5" t="s">
-        <v>5276</v>
+        <v>5277</v>
       </c>
       <c r="E839" s="5" t="s">
+        <v>5278</v>
+      </c>
+      <c r="F839" s="5" t="s">
+        <v>5279</v>
+      </c>
+      <c r="G839" s="5" t="s">
+        <v>5280</v>
+      </c>
+      <c r="H839" s="5" t="s">
         <v>5277</v>
-      </c>
-      <c r="F839" s="5" t="s">
-        <v>5278</v>
-      </c>
-      <c r="G839" s="5" t="s">
-        <v>5278</v>
-      </c>
-      <c r="H839" s="5" t="s">
-        <v>5279</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
-        <v>5280</v>
+        <v>5281</v>
       </c>
       <c r="C840" s="6" t="s">
-        <v>5281</v>
+        <v>5282</v>
       </c>
       <c r="D840" s="6" t="s">
-        <v>5282</v>
+        <v>5283</v>
       </c>
       <c r="E840" s="6" t="s">
-        <v>5283</v>
+        <v>5284</v>
       </c>
       <c r="F840" s="6" t="s">
-        <v>5284</v>
+        <v>5285</v>
       </c>
       <c r="G840" s="6" t="s">
-        <v>5284</v>
+        <v>5286</v>
       </c>
       <c r="H840" s="6" t="s">
-        <v>5285</v>
+        <v>5287</v>
       </c>
     </row>
     <row r="841">
       <c r="B841" s="5" t="s">
-        <v>5286</v>
+        <v>5288</v>
       </c>
       <c r="C841" s="5" t="s">
-        <v>5287</v>
+        <v>5289</v>
       </c>
       <c r="D841" s="5" t="s">
-        <v>5288</v>
+        <v>5290</v>
       </c>
       <c r="E841" s="5" t="s">
-        <v>5289</v>
+        <v>5291</v>
       </c>
       <c r="F841" s="5" t="s">
-        <v>5290</v>
+        <v>5292</v>
       </c>
       <c r="G841" s="5" t="s">
-        <v>5291</v>
+        <v>5292</v>
       </c>
       <c r="H841" s="5" t="s">
-        <v>5292</v>
+        <v>5293</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
-        <v>5293</v>
+        <v>5294</v>
       </c>
       <c r="C842" s="6" t="s">
-        <v>5294</v>
+        <v>5295</v>
       </c>
       <c r="D842" s="6" t="s">
-        <v>5295</v>
+        <v>5296</v>
       </c>
       <c r="E842" s="6" t="s">
-        <v>5296</v>
+        <v>5297</v>
       </c>
       <c r="F842" s="6" t="s">
-        <v>5297</v>
+        <v>5298</v>
       </c>
       <c r="G842" s="6" t="s">
-        <v>5297</v>
+        <v>5298</v>
       </c>
       <c r="H842" s="6" t="s">
-        <v>5298</v>
+        <v>5299</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
-        <v>5299</v>
+        <v>5300</v>
       </c>
       <c r="C843" s="5" t="s">
-        <v>5300</v>
+        <v>5301</v>
       </c>
       <c r="D843" s="5" t="s">
-        <v>5301</v>
+        <v>5302</v>
       </c>
       <c r="E843" s="5" t="s">
-        <v>5302</v>
+        <v>5303</v>
       </c>
       <c r="F843" s="5" t="s">
-        <v>5303</v>
+        <v>5304</v>
       </c>
       <c r="G843" s="5" t="s">
-        <v>5304</v>
+        <v>5305</v>
       </c>
       <c r="H843" s="5" t="s">
-        <v>5305</v>
+        <v>5306</v>
       </c>
     </row>
     <row r="844">
       <c r="B844" s="6" t="s">
-        <v>5306</v>
+        <v>5307</v>
       </c>
       <c r="C844" s="6" t="s">
-        <v>5307</v>
+        <v>5308</v>
       </c>
       <c r="D844" s="6" t="s">
-        <v>5308</v>
+        <v>5309</v>
       </c>
       <c r="E844" s="6" t="s">
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="H844" s="6" t="s">
-        <v>5311</v>
+        <v>5312</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5312</v>
+        <v>5313</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>5313</v>
+        <v>5314</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5314</v>
+        <v>5315</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>5315</v>
+        <v>5316</v>
       </c>
       <c r="F845" s="5" t="s">
-        <v>5316</v>
+        <v>5317</v>
       </c>
       <c r="G845" s="5" t="s">
-        <v>5316</v>
+        <v>5318</v>
       </c>
       <c r="H845" s="5" t="s">
-        <v>5317</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
-        <v>5318</v>
+        <v>5320</v>
       </c>
       <c r="C846" s="6" t="s">
-        <v>5319</v>
+        <v>5321</v>
       </c>
       <c r="D846" s="6" t="s">
-        <v>5319</v>
+        <v>5322</v>
       </c>
       <c r="E846" s="6" t="s">
-        <v>5319</v>
+        <v>5323</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>5319</v>
+        <v>5324</v>
       </c>
       <c r="G846" s="6" t="s">
-        <v>5319</v>
+        <v>5324</v>
       </c>
       <c r="H846" s="6" t="s">
-        <v>5319</v>
+        <v>5325</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
-        <v>5320</v>
+        <v>5326</v>
       </c>
       <c r="C847" s="5" t="s">
-        <v>5321</v>
+        <v>5327</v>
       </c>
       <c r="D847" s="5" t="s">
-        <v>5322</v>
+        <v>5328</v>
       </c>
       <c r="E847" s="5" t="s">
-        <v>5323</v>
+        <v>5329</v>
       </c>
       <c r="F847" s="5" t="s">
-        <v>5324</v>
+        <v>5330</v>
       </c>
       <c r="G847" s="5" t="s">
-        <v>5324</v>
+        <v>5330</v>
       </c>
       <c r="H847" s="5" t="s">
-        <v>5322</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
-        <v>5325</v>
+        <v>5332</v>
       </c>
       <c r="C848" s="6" t="s">
-        <v>5326</v>
+        <v>5333</v>
       </c>
       <c r="D848" s="6" t="s">
-        <v>5327</v>
+        <v>5333</v>
       </c>
       <c r="E848" s="6" t="s">
-        <v>5328</v>
+        <v>5333</v>
       </c>
       <c r="F848" s="6" t="s">
-        <v>5329</v>
+        <v>5333</v>
       </c>
       <c r="G848" s="6" t="s">
-        <v>5330</v>
+        <v>5333</v>
       </c>
       <c r="H848" s="6" t="s">
-        <v>5327</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
-        <v>5331</v>
+        <v>5334</v>
       </c>
       <c r="C849" s="5" t="s">
-        <v>5332</v>
+        <v>5335</v>
       </c>
       <c r="D849" s="5" t="s">
-        <v>5333</v>
+        <v>5336</v>
       </c>
       <c r="E849" s="5" t="s">
-        <v>5334</v>
+        <v>5337</v>
       </c>
       <c r="F849" s="5" t="s">
-        <v>5334</v>
+        <v>5338</v>
       </c>
       <c r="G849" s="5" t="s">
-        <v>5334</v>
+        <v>5338</v>
       </c>
       <c r="H849" s="5" t="s">
-        <v>5333</v>
+        <v>5336</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
-        <v>5335</v>
+        <v>5339</v>
       </c>
       <c r="C850" s="6" t="s">
-        <v>5336</v>
+        <v>5340</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>5337</v>
+        <v>5341</v>
       </c>
       <c r="E850" s="6" t="s">
-        <v>5338</v>
+        <v>5342</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>5338</v>
+        <v>5343</v>
       </c>
       <c r="G850" s="6" t="s">
-        <v>5338</v>
+        <v>5344</v>
       </c>
       <c r="H850" s="6" t="s">
-        <v>5337</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
-        <v>5339</v>
+        <v>5345</v>
       </c>
       <c r="C851" s="5" t="s">
-        <v>5340</v>
+        <v>5346</v>
       </c>
       <c r="D851" s="5" t="s">
-        <v>5341</v>
+        <v>5347</v>
       </c>
       <c r="E851" s="5" t="s">
-        <v>5342</v>
+        <v>5348</v>
       </c>
       <c r="F851" s="5" t="s">
-        <v>5343</v>
+        <v>5348</v>
       </c>
       <c r="G851" s="5" t="s">
-        <v>5344</v>
+        <v>5348</v>
       </c>
       <c r="H851" s="5" t="s">
-        <v>5345</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
-        <v>5346</v>
+        <v>5349</v>
       </c>
       <c r="C852" s="6" t="s">
-        <v>5347</v>
+        <v>5350</v>
       </c>
       <c r="D852" s="6" t="s">
-        <v>5348</v>
+        <v>5351</v>
       </c>
       <c r="E852" s="6" t="s">
-        <v>5349</v>
+        <v>5352</v>
       </c>
       <c r="F852" s="6" t="s">
-        <v>5350</v>
+        <v>5352</v>
       </c>
       <c r="G852" s="6" t="s">
+        <v>5352</v>
+      </c>
+      <c r="H852" s="6" t="s">
         <v>5351</v>
-      </c>
-      <c r="H852" s="6" t="s">
-        <v>5348</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
-        <v>5352</v>
+        <v>5353</v>
       </c>
       <c r="C853" s="5" t="s">
-        <v>5353</v>
+        <v>5354</v>
       </c>
       <c r="D853" s="5" t="s">
-        <v>5354</v>
+        <v>5355</v>
       </c>
       <c r="E853" s="5" t="s">
-        <v>5355</v>
+        <v>5356</v>
       </c>
       <c r="F853" s="5" t="s">
-        <v>5356</v>
+        <v>5357</v>
       </c>
       <c r="G853" s="5" t="s">
-        <v>5357</v>
+        <v>5358</v>
       </c>
       <c r="H853" s="5" t="s">
-        <v>5358</v>
+        <v>5359</v>
       </c>
     </row>
     <row r="854">
       <c r="B854" s="6" t="s">
-        <v>5359</v>
+        <v>5360</v>
       </c>
       <c r="C854" s="6" t="s">
-        <v>5360</v>
+        <v>5361</v>
       </c>
       <c r="D854" s="6" t="s">
-        <v>5361</v>
+        <v>5362</v>
       </c>
       <c r="E854" s="6" t="s">
+        <v>5363</v>
+      </c>
+      <c r="F854" s="6" t="s">
+        <v>5364</v>
+      </c>
+      <c r="G854" s="6" t="s">
+        <v>5365</v>
+      </c>
+      <c r="H854" s="6" t="s">
         <v>5362</v>
-      </c>
-      <c r="F854" s="6" t="s">
-        <v>5363</v>
-      </c>
-      <c r="G854" s="6" t="s">
-        <v>5364</v>
-      </c>
-      <c r="H854" s="6" t="s">
-        <v>5365</v>
       </c>
     </row>
     <row r="855">
@@ -36202,57 +36244,103 @@
         <v>5378</v>
       </c>
       <c r="H856" s="6" t="s">
-        <v>5348</v>
+        <v>5379</v>
       </c>
     </row>
     <row r="857">
       <c r="B857" s="5" t="s">
-        <v>5379</v>
+        <v>5380</v>
       </c>
       <c r="C857" s="5" t="s">
-        <v>5380</v>
+        <v>5381</v>
       </c>
       <c r="D857" s="5" t="s">
-        <v>5381</v>
+        <v>5382</v>
       </c>
       <c r="E857" s="5" t="s">
-        <v>5382</v>
+        <v>5383</v>
       </c>
       <c r="F857" s="5" t="s">
-        <v>5383</v>
+        <v>5384</v>
       </c>
       <c r="G857" s="5" t="s">
-        <v>5384</v>
+        <v>5385</v>
       </c>
       <c r="H857" s="5" t="s">
-        <v>5385</v>
+        <v>5386</v>
       </c>
     </row>
     <row r="858">
       <c r="B858" s="6" t="s">
-        <v>5386</v>
+        <v>5387</v>
       </c>
       <c r="C858" s="6" t="s">
-        <v>5387</v>
+        <v>5388</v>
       </c>
       <c r="D858" s="6" t="s">
-        <v>5388</v>
+        <v>5389</v>
       </c>
       <c r="E858" s="6" t="s">
-        <v>5389</v>
+        <v>5390</v>
       </c>
       <c r="F858" s="6" t="s">
-        <v>5390</v>
+        <v>5391</v>
       </c>
       <c r="G858" s="6" t="s">
-        <v>5390</v>
+        <v>5392</v>
       </c>
       <c r="H858" s="6" t="s">
-        <v>5391</v>
+        <v>5362</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="B859" s="5" t="s">
+        <v>5393</v>
+      </c>
+      <c r="C859" s="5" t="s">
+        <v>5394</v>
+      </c>
+      <c r="D859" s="5" t="s">
+        <v>5395</v>
+      </c>
+      <c r="E859" s="5" t="s">
+        <v>5396</v>
+      </c>
+      <c r="F859" s="5" t="s">
+        <v>5397</v>
+      </c>
+      <c r="G859" s="5" t="s">
+        <v>5398</v>
+      </c>
+      <c r="H859" s="5" t="s">
+        <v>5399</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="B860" s="6" t="s">
+        <v>5400</v>
+      </c>
+      <c r="C860" s="6" t="s">
+        <v>5401</v>
+      </c>
+      <c r="D860" s="6" t="s">
+        <v>5402</v>
+      </c>
+      <c r="E860" s="6" t="s">
+        <v>5403</v>
+      </c>
+      <c r="F860" s="6" t="s">
+        <v>5404</v>
+      </c>
+      <c r="G860" s="6" t="s">
+        <v>5404</v>
+      </c>
+      <c r="H860" s="6" t="s">
+        <v>5405</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H858"/>
+  <autoFilter ref="B2:H860"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36271,10 +36359,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5392</v>
+        <v>5406</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5393</v>
+        <v>5407</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36285,16 +36373,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5394</v>
+        <v>5408</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5395</v>
+        <v>5409</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5396</v>
+        <v>5410</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5397</v>
+        <v>5411</v>
       </c>
     </row>
     <row r="3">
@@ -36302,16 +36390,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5398</v>
+        <v>5412</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5399</v>
+        <v>5413</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5400</v>
+        <v>5414</v>
       </c>
     </row>
     <row r="4">
@@ -36322,24 +36410,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5401</v>
+        <v>5415</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5402</v>
+        <v>5416</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5403</v>
+        <v>5417</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5404</v>
+        <v>5418</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5405</v>
+        <v>5419</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36347,13 +36435,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5406</v>
+        <v>5420</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5407</v>
+        <v>5421</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36361,13 +36449,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5408</v>
+        <v>5422</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5409</v>
+        <v>5423</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36375,13 +36463,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5410</v>
+        <v>5424</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5411</v>
+        <v>5425</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36389,13 +36477,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5412</v>
+        <v>5426</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5413</v>
+        <v>5427</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36403,13 +36491,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5414</v>
+        <v>5428</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5415</v>
+        <v>5429</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36417,13 +36505,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5416</v>
+        <v>5430</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5417</v>
+        <v>5431</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36431,13 +36519,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5418</v>
+        <v>5432</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5419</v>
+        <v>5433</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36445,13 +36533,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5420</v>
+        <v>5434</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5421</v>
+        <v>5435</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36459,13 +36547,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5422</v>
+        <v>5436</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5423</v>
+        <v>5437</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36479,7 +36567,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5424</v>
+        <v>5438</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36487,13 +36575,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5425</v>
+        <v>5439</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5426</v>
+        <v>5440</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36501,13 +36589,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5427</v>
+        <v>5441</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5428</v>
+        <v>5442</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36515,13 +36603,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5429</v>
+        <v>5443</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5430</v>
+        <v>5444</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36529,13 +36617,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5431</v>
+        <v>5445</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5432</v>
+        <v>5446</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36543,13 +36631,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5433</v>
+        <v>5447</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5434</v>
+        <v>5448</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36557,13 +36645,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5435</v>
+        <v>5449</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5436</v>
+        <v>5450</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36571,13 +36659,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5437</v>
+        <v>5451</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5438</v>
+        <v>5452</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36585,13 +36673,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5439</v>
+        <v>5453</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5440</v>
+        <v>5454</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36599,13 +36687,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5441</v>
+        <v>5455</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5442</v>
+        <v>5456</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$860]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$862]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6083" uniqueCount="5457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6097" uniqueCount="5471">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -13085,6 +13085,48 @@
   </si>
   <si>
     <t xml:space="preserve">剩餘牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニュー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">菜单</t>
+  </si>
+  <si>
+    <t xml:space="preserve">選單</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.deck.tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">눌러서 남은 카드를 봅니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap to see the cards left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">押すと残りのカードを見ます</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击查看剩余的牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">點擊查看剩餘的牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antippen für die restlichen Karten</t>
   </si>
   <si>
     <t xml:space="preserve">ui.button.reroll</t>
@@ -16587,7 +16629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H860"/>
+  <dimension ref="A1:H862"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -32216,99 +32258,99 @@
         <v>4360</v>
       </c>
       <c r="G681" s="5" t="s">
-        <v>4360</v>
+        <v>4361</v>
       </c>
       <c r="H681" s="5" t="s">
-        <v>4361</v>
+        <v>4362</v>
       </c>
     </row>
     <row r="682">
       <c r="B682" s="6" t="s">
-        <v>4362</v>
+        <v>4363</v>
       </c>
       <c r="C682" s="6" t="s">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="D682" s="6" t="s">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="E682" s="6" t="s">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F682" s="6" t="s">
-        <v>4366</v>
+        <v>4367</v>
       </c>
       <c r="G682" s="6" t="s">
-        <v>4366</v>
+        <v>4368</v>
       </c>
       <c r="H682" s="6" t="s">
-        <v>4367</v>
+        <v>4369</v>
       </c>
     </row>
     <row r="683">
       <c r="B683" s="5" t="s">
-        <v>4368</v>
+        <v>4370</v>
       </c>
       <c r="C683" s="5" t="s">
-        <v>4369</v>
+        <v>4371</v>
       </c>
       <c r="D683" s="5" t="s">
-        <v>4370</v>
+        <v>4372</v>
       </c>
       <c r="E683" s="5" t="s">
-        <v>2250</v>
+        <v>4373</v>
       </c>
       <c r="F683" s="5" t="s">
-        <v>2251</v>
+        <v>4374</v>
       </c>
       <c r="G683" s="5" t="s">
-        <v>2252</v>
+        <v>4374</v>
       </c>
       <c r="H683" s="5" t="s">
-        <v>4371</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="684">
       <c r="B684" s="6" t="s">
-        <v>4372</v>
+        <v>4376</v>
       </c>
       <c r="C684" s="6" t="s">
-        <v>4373</v>
+        <v>4377</v>
       </c>
       <c r="D684" s="6" t="s">
-        <v>4374</v>
+        <v>4378</v>
       </c>
       <c r="E684" s="6" t="s">
-        <v>4375</v>
+        <v>4379</v>
       </c>
       <c r="F684" s="6" t="s">
-        <v>4376</v>
+        <v>4380</v>
       </c>
       <c r="G684" s="6" t="s">
-        <v>4377</v>
+        <v>4380</v>
       </c>
       <c r="H684" s="6" t="s">
-        <v>4378</v>
+        <v>4381</v>
       </c>
     </row>
     <row r="685">
       <c r="B685" s="5" t="s">
-        <v>4379</v>
+        <v>4382</v>
       </c>
       <c r="C685" s="5" t="s">
-        <v>4380</v>
+        <v>4383</v>
       </c>
       <c r="D685" s="5" t="s">
-        <v>4381</v>
+        <v>4384</v>
       </c>
       <c r="E685" s="5" t="s">
-        <v>4382</v>
+        <v>2250</v>
       </c>
       <c r="F685" s="5" t="s">
-        <v>4383</v>
+        <v>2251</v>
       </c>
       <c r="G685" s="5" t="s">
-        <v>4384</v>
+        <v>2252</v>
       </c>
       <c r="H685" s="5" t="s">
         <v>4385</v>
@@ -32331,240 +32373,240 @@
         <v>4390</v>
       </c>
       <c r="G686" s="6" t="s">
-        <v>4390</v>
+        <v>4391</v>
       </c>
       <c r="H686" s="6" t="s">
-        <v>4391</v>
+        <v>4392</v>
       </c>
     </row>
     <row r="687">
       <c r="B687" s="5" t="s">
-        <v>4392</v>
+        <v>4393</v>
       </c>
       <c r="C687" s="5" t="s">
-        <v>3495</v>
+        <v>4394</v>
       </c>
       <c r="D687" s="5" t="s">
-        <v>3500</v>
+        <v>4395</v>
       </c>
       <c r="E687" s="5" t="s">
-        <v>3497</v>
+        <v>4396</v>
       </c>
       <c r="F687" s="5" t="s">
-        <v>3498</v>
+        <v>4397</v>
       </c>
       <c r="G687" s="5" t="s">
-        <v>3499</v>
+        <v>4398</v>
       </c>
       <c r="H687" s="5" t="s">
-        <v>3500</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="688">
       <c r="B688" s="6" t="s">
-        <v>4393</v>
+        <v>4400</v>
       </c>
       <c r="C688" s="6" t="s">
-        <v>2045</v>
+        <v>4401</v>
       </c>
       <c r="D688" s="6" t="s">
-        <v>2046</v>
+        <v>4402</v>
       </c>
       <c r="E688" s="6" t="s">
-        <v>2048</v>
+        <v>4403</v>
       </c>
       <c r="F688" s="6" t="s">
-        <v>2048</v>
+        <v>4404</v>
       </c>
       <c r="G688" s="6" t="s">
-        <v>2048</v>
+        <v>4404</v>
       </c>
       <c r="H688" s="6" t="s">
-        <v>2046</v>
+        <v>4405</v>
       </c>
     </row>
     <row r="689">
       <c r="B689" s="5" t="s">
-        <v>4394</v>
+        <v>4406</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>4395</v>
+        <v>3495</v>
       </c>
       <c r="D689" s="5" t="s">
-        <v>4396</v>
+        <v>3500</v>
       </c>
       <c r="E689" s="5" t="s">
-        <v>4397</v>
+        <v>3497</v>
       </c>
       <c r="F689" s="5" t="s">
-        <v>4398</v>
+        <v>3498</v>
       </c>
       <c r="G689" s="5" t="s">
-        <v>4399</v>
+        <v>3499</v>
       </c>
       <c r="H689" s="5" t="s">
-        <v>4396</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="690">
       <c r="B690" s="6" t="s">
-        <v>4400</v>
+        <v>4407</v>
       </c>
       <c r="C690" s="6" t="s">
-        <v>4401</v>
+        <v>2045</v>
       </c>
       <c r="D690" s="6" t="s">
-        <v>4402</v>
+        <v>2046</v>
       </c>
       <c r="E690" s="6" t="s">
-        <v>4403</v>
+        <v>2048</v>
       </c>
       <c r="F690" s="6" t="s">
-        <v>4403</v>
+        <v>2048</v>
       </c>
       <c r="G690" s="6" t="s">
-        <v>4403</v>
+        <v>2048</v>
       </c>
       <c r="H690" s="6" t="s">
-        <v>4402</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="691">
       <c r="B691" s="5" t="s">
-        <v>4404</v>
+        <v>4408</v>
       </c>
       <c r="C691" s="5" t="s">
-        <v>4405</v>
+        <v>4409</v>
       </c>
       <c r="D691" s="5" t="s">
-        <v>4341</v>
+        <v>4410</v>
       </c>
       <c r="E691" s="5" t="s">
-        <v>4406</v>
+        <v>4411</v>
       </c>
       <c r="F691" s="5" t="s">
-        <v>4310</v>
+        <v>4412</v>
       </c>
       <c r="G691" s="5" t="s">
-        <v>4310</v>
+        <v>4413</v>
       </c>
       <c r="H691" s="5" t="s">
-        <v>4407</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="692">
       <c r="B692" s="6" t="s">
-        <v>4408</v>
+        <v>4414</v>
       </c>
       <c r="C692" s="6" t="s">
-        <v>4409</v>
+        <v>4415</v>
       </c>
       <c r="D692" s="6" t="s">
-        <v>4410</v>
+        <v>4416</v>
       </c>
       <c r="E692" s="6" t="s">
-        <v>4411</v>
+        <v>4417</v>
       </c>
       <c r="F692" s="6" t="s">
-        <v>4316</v>
+        <v>4417</v>
       </c>
       <c r="G692" s="6" t="s">
-        <v>4317</v>
+        <v>4417</v>
       </c>
       <c r="H692" s="6" t="s">
-        <v>4412</v>
+        <v>4416</v>
       </c>
     </row>
     <row r="693">
       <c r="B693" s="5" t="s">
-        <v>4413</v>
+        <v>4418</v>
       </c>
       <c r="C693" s="5" t="s">
-        <v>3510</v>
+        <v>4419</v>
       </c>
       <c r="D693" s="5" t="s">
-        <v>4414</v>
+        <v>4341</v>
       </c>
       <c r="E693" s="5" t="s">
-        <v>3512</v>
+        <v>4420</v>
       </c>
       <c r="F693" s="5" t="s">
-        <v>3513</v>
+        <v>4310</v>
       </c>
       <c r="G693" s="5" t="s">
-        <v>3514</v>
+        <v>4310</v>
       </c>
       <c r="H693" s="5" t="s">
-        <v>3515</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="694">
       <c r="B694" s="6" t="s">
-        <v>4415</v>
+        <v>4422</v>
       </c>
       <c r="C694" s="6" t="s">
-        <v>4081</v>
+        <v>4423</v>
       </c>
       <c r="D694" s="6" t="s">
-        <v>4082</v>
+        <v>4424</v>
       </c>
       <c r="E694" s="6" t="s">
-        <v>4083</v>
+        <v>4425</v>
       </c>
       <c r="F694" s="6" t="s">
-        <v>4084</v>
+        <v>4316</v>
       </c>
       <c r="G694" s="6" t="s">
-        <v>4084</v>
+        <v>4317</v>
       </c>
       <c r="H694" s="6" t="s">
-        <v>4082</v>
+        <v>4426</v>
       </c>
     </row>
     <row r="695">
       <c r="B695" s="5" t="s">
-        <v>4416</v>
+        <v>4427</v>
       </c>
       <c r="C695" s="5" t="s">
-        <v>4417</v>
+        <v>3510</v>
       </c>
       <c r="D695" s="5" t="s">
-        <v>4418</v>
+        <v>4428</v>
       </c>
       <c r="E695" s="5" t="s">
-        <v>4419</v>
+        <v>3512</v>
       </c>
       <c r="F695" s="5" t="s">
-        <v>4420</v>
+        <v>3513</v>
       </c>
       <c r="G695" s="5" t="s">
-        <v>4421</v>
+        <v>3514</v>
       </c>
       <c r="H695" s="5" t="s">
-        <v>4422</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="696">
       <c r="B696" s="6" t="s">
-        <v>4423</v>
+        <v>4429</v>
       </c>
       <c r="C696" s="6" t="s">
-        <v>4424</v>
+        <v>4081</v>
       </c>
       <c r="D696" s="6" t="s">
-        <v>4425</v>
+        <v>4082</v>
       </c>
       <c r="E696" s="6" t="s">
-        <v>4426</v>
+        <v>4083</v>
       </c>
       <c r="F696" s="6" t="s">
-        <v>4427</v>
+        <v>4084</v>
       </c>
       <c r="G696" s="6" t="s">
-        <v>4428</v>
+        <v>4084</v>
       </c>
       <c r="H696" s="6" t="s">
-        <v>4429</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="697">
@@ -32581,56 +32623,56 @@
         <v>4433</v>
       </c>
       <c r="F697" s="5" t="s">
-        <v>2042</v>
+        <v>4434</v>
       </c>
       <c r="G697" s="5" t="s">
-        <v>2043</v>
+        <v>4435</v>
       </c>
       <c r="H697" s="5" t="s">
-        <v>4434</v>
+        <v>4436</v>
       </c>
     </row>
     <row r="698">
       <c r="B698" s="6" t="s">
-        <v>4435</v>
+        <v>4437</v>
       </c>
       <c r="C698" s="6" t="s">
-        <v>4436</v>
+        <v>4438</v>
       </c>
       <c r="D698" s="6" t="s">
-        <v>4437</v>
+        <v>4439</v>
       </c>
       <c r="E698" s="6" t="s">
-        <v>4438</v>
+        <v>4440</v>
       </c>
       <c r="F698" s="6" t="s">
-        <v>4439</v>
+        <v>4441</v>
       </c>
       <c r="G698" s="6" t="s">
-        <v>4440</v>
+        <v>4442</v>
       </c>
       <c r="H698" s="6" t="s">
-        <v>4441</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="699">
       <c r="B699" s="5" t="s">
-        <v>4442</v>
+        <v>4444</v>
       </c>
       <c r="C699" s="5" t="s">
-        <v>4443</v>
+        <v>4445</v>
       </c>
       <c r="D699" s="5" t="s">
-        <v>4444</v>
+        <v>4446</v>
       </c>
       <c r="E699" s="5" t="s">
-        <v>4445</v>
+        <v>4447</v>
       </c>
       <c r="F699" s="5" t="s">
-        <v>4446</v>
+        <v>2042</v>
       </c>
       <c r="G699" s="5" t="s">
-        <v>4447</v>
+        <v>2043</v>
       </c>
       <c r="H699" s="5" t="s">
         <v>4448</v>
@@ -32676,53 +32718,53 @@
         <v>4460</v>
       </c>
       <c r="G701" s="5" t="s">
-        <v>4459</v>
+        <v>4461</v>
       </c>
       <c r="H701" s="5" t="s">
-        <v>4461</v>
+        <v>4462</v>
       </c>
     </row>
     <row r="702">
       <c r="B702" s="6" t="s">
-        <v>4462</v>
+        <v>4463</v>
       </c>
       <c r="C702" s="6" t="s">
-        <v>4463</v>
+        <v>4464</v>
       </c>
       <c r="D702" s="6" t="s">
-        <v>4464</v>
+        <v>4465</v>
       </c>
       <c r="E702" s="6" t="s">
-        <v>4465</v>
+        <v>4466</v>
       </c>
       <c r="F702" s="6" t="s">
-        <v>4466</v>
+        <v>4467</v>
       </c>
       <c r="G702" s="6" t="s">
-        <v>4467</v>
+        <v>4468</v>
       </c>
       <c r="H702" s="6" t="s">
-        <v>4468</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="703">
       <c r="B703" s="5" t="s">
-        <v>4469</v>
+        <v>4470</v>
       </c>
       <c r="C703" s="5" t="s">
-        <v>4470</v>
+        <v>4471</v>
       </c>
       <c r="D703" s="5" t="s">
-        <v>4471</v>
+        <v>4472</v>
       </c>
       <c r="E703" s="5" t="s">
-        <v>4472</v>
+        <v>4473</v>
       </c>
       <c r="F703" s="5" t="s">
+        <v>4474</v>
+      </c>
+      <c r="G703" s="5" t="s">
         <v>4473</v>
-      </c>
-      <c r="G703" s="5" t="s">
-        <v>4474</v>
       </c>
       <c r="H703" s="5" t="s">
         <v>4475</v>
@@ -32765,772 +32807,772 @@
         <v>4486</v>
       </c>
       <c r="F705" s="5" t="s">
-        <v>4486</v>
+        <v>4487</v>
       </c>
       <c r="G705" s="5" t="s">
-        <v>4486</v>
+        <v>4488</v>
       </c>
       <c r="H705" s="5" t="s">
-        <v>4487</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="706">
       <c r="B706" s="6" t="s">
-        <v>4488</v>
+        <v>4490</v>
       </c>
       <c r="C706" s="6" t="s">
-        <v>4489</v>
+        <v>4491</v>
       </c>
       <c r="D706" s="6" t="s">
-        <v>4490</v>
+        <v>4492</v>
       </c>
       <c r="E706" s="6" t="s">
-        <v>4491</v>
+        <v>4493</v>
       </c>
       <c r="F706" s="6" t="s">
-        <v>4492</v>
+        <v>4494</v>
       </c>
       <c r="G706" s="6" t="s">
-        <v>4492</v>
+        <v>4495</v>
       </c>
       <c r="H706" s="6" t="s">
-        <v>4493</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="707">
       <c r="B707" s="5" t="s">
-        <v>4494</v>
+        <v>4497</v>
       </c>
       <c r="C707" s="5" t="s">
-        <v>4495</v>
+        <v>4498</v>
       </c>
       <c r="D707" s="5" t="s">
-        <v>4496</v>
+        <v>4499</v>
       </c>
       <c r="E707" s="5" t="s">
-        <v>4497</v>
+        <v>4500</v>
       </c>
       <c r="F707" s="5" t="s">
-        <v>4498</v>
+        <v>4500</v>
       </c>
       <c r="G707" s="5" t="s">
-        <v>4498</v>
+        <v>4500</v>
       </c>
       <c r="H707" s="5" t="s">
-        <v>4499</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="708">
       <c r="B708" s="6" t="s">
-        <v>4500</v>
+        <v>4502</v>
       </c>
       <c r="C708" s="6" t="s">
-        <v>4501</v>
+        <v>4503</v>
       </c>
       <c r="D708" s="6" t="s">
-        <v>4502</v>
+        <v>4504</v>
       </c>
       <c r="E708" s="6" t="s">
-        <v>4503</v>
+        <v>4505</v>
       </c>
       <c r="F708" s="6" t="s">
-        <v>4502</v>
+        <v>4506</v>
       </c>
       <c r="G708" s="6" t="s">
-        <v>4502</v>
+        <v>4506</v>
       </c>
       <c r="H708" s="6" t="s">
-        <v>4502</v>
+        <v>4507</v>
       </c>
     </row>
     <row r="709">
       <c r="B709" s="5" t="s">
-        <v>4504</v>
+        <v>4508</v>
       </c>
       <c r="C709" s="5" t="s">
-        <v>3610</v>
+        <v>4509</v>
       </c>
       <c r="D709" s="5" t="s">
-        <v>2981</v>
+        <v>4510</v>
       </c>
       <c r="E709" s="5" t="s">
-        <v>3612</v>
+        <v>4511</v>
       </c>
       <c r="F709" s="5" t="s">
-        <v>3613</v>
+        <v>4512</v>
       </c>
       <c r="G709" s="5" t="s">
-        <v>3613</v>
+        <v>4512</v>
       </c>
       <c r="H709" s="5" t="s">
-        <v>2981</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="710">
       <c r="B710" s="6" t="s">
-        <v>4505</v>
+        <v>4514</v>
       </c>
       <c r="C710" s="6" t="s">
-        <v>4506</v>
+        <v>4515</v>
       </c>
       <c r="D710" s="6" t="s">
-        <v>4507</v>
+        <v>4516</v>
       </c>
       <c r="E710" s="6" t="s">
-        <v>4508</v>
+        <v>4517</v>
       </c>
       <c r="F710" s="6" t="s">
-        <v>4508</v>
+        <v>4516</v>
       </c>
       <c r="G710" s="6" t="s">
-        <v>4508</v>
+        <v>4516</v>
       </c>
       <c r="H710" s="6" t="s">
-        <v>4509</v>
+        <v>4516</v>
       </c>
     </row>
     <row r="711">
       <c r="B711" s="5" t="s">
-        <v>4510</v>
+        <v>4518</v>
       </c>
       <c r="C711" s="5" t="s">
-        <v>3657</v>
+        <v>3610</v>
       </c>
       <c r="D711" s="5" t="s">
-        <v>4511</v>
+        <v>2981</v>
       </c>
       <c r="E711" s="5" t="s">
-        <v>3659</v>
+        <v>3612</v>
       </c>
       <c r="F711" s="5" t="s">
-        <v>3660</v>
+        <v>3613</v>
       </c>
       <c r="G711" s="5" t="s">
-        <v>3661</v>
+        <v>3613</v>
       </c>
       <c r="H711" s="5" t="s">
-        <v>4512</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="712">
       <c r="B712" s="6" t="s">
-        <v>4513</v>
+        <v>4519</v>
       </c>
       <c r="C712" s="6" t="s">
-        <v>3651</v>
+        <v>4520</v>
       </c>
       <c r="D712" s="6" t="s">
-        <v>4514</v>
+        <v>4521</v>
       </c>
       <c r="E712" s="6" t="s">
-        <v>3653</v>
+        <v>4522</v>
       </c>
       <c r="F712" s="6" t="s">
-        <v>3654</v>
+        <v>4522</v>
       </c>
       <c r="G712" s="6" t="s">
-        <v>3654</v>
+        <v>4522</v>
       </c>
       <c r="H712" s="6" t="s">
-        <v>4515</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="713">
       <c r="B713" s="5" t="s">
-        <v>4516</v>
+        <v>4524</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>4517</v>
+        <v>3657</v>
       </c>
       <c r="D713" s="5" t="s">
-        <v>4518</v>
+        <v>4525</v>
       </c>
       <c r="E713" s="5" t="s">
-        <v>4519</v>
+        <v>3659</v>
       </c>
       <c r="F713" s="5" t="s">
-        <v>4520</v>
+        <v>3660</v>
       </c>
       <c r="G713" s="5" t="s">
-        <v>4521</v>
+        <v>3661</v>
       </c>
       <c r="H713" s="5" t="s">
-        <v>4518</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="714">
       <c r="B714" s="6" t="s">
-        <v>4522</v>
+        <v>4527</v>
       </c>
       <c r="C714" s="6" t="s">
-        <v>4523</v>
+        <v>3651</v>
       </c>
       <c r="D714" s="6" t="s">
-        <v>4524</v>
+        <v>4528</v>
       </c>
       <c r="E714" s="6" t="s">
-        <v>4525</v>
+        <v>3653</v>
       </c>
       <c r="F714" s="6" t="s">
-        <v>4526</v>
+        <v>3654</v>
       </c>
       <c r="G714" s="6" t="s">
-        <v>4526</v>
+        <v>3654</v>
       </c>
       <c r="H714" s="6" t="s">
-        <v>4524</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="715">
       <c r="B715" s="5" t="s">
-        <v>4527</v>
+        <v>4530</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>4528</v>
+        <v>4531</v>
       </c>
       <c r="D715" s="5" t="s">
-        <v>4529</v>
+        <v>4532</v>
       </c>
       <c r="E715" s="5" t="s">
-        <v>4530</v>
+        <v>4533</v>
       </c>
       <c r="F715" s="5" t="s">
-        <v>4531</v>
+        <v>4534</v>
       </c>
       <c r="G715" s="5" t="s">
+        <v>4535</v>
+      </c>
+      <c r="H715" s="5" t="s">
         <v>4532</v>
-      </c>
-      <c r="H715" s="5" t="s">
-        <v>4533</v>
       </c>
     </row>
     <row r="716">
       <c r="B716" s="6" t="s">
-        <v>4534</v>
+        <v>4536</v>
       </c>
       <c r="C716" s="6" t="s">
-        <v>3749</v>
+        <v>4537</v>
       </c>
       <c r="D716" s="6" t="s">
-        <v>4535</v>
+        <v>4538</v>
       </c>
       <c r="E716" s="6" t="s">
-        <v>3751</v>
+        <v>4539</v>
       </c>
       <c r="F716" s="6" t="s">
-        <v>3752</v>
+        <v>4540</v>
       </c>
       <c r="G716" s="6" t="s">
-        <v>3752</v>
+        <v>4540</v>
       </c>
       <c r="H716" s="6" t="s">
-        <v>3753</v>
+        <v>4538</v>
       </c>
     </row>
     <row r="717">
       <c r="B717" s="5" t="s">
-        <v>4536</v>
+        <v>4541</v>
       </c>
       <c r="C717" s="5" t="s">
-        <v>4537</v>
+        <v>4542</v>
       </c>
       <c r="D717" s="5" t="s">
-        <v>4352</v>
+        <v>4543</v>
       </c>
       <c r="E717" s="5" t="s">
-        <v>4538</v>
+        <v>4544</v>
       </c>
       <c r="F717" s="5" t="s">
-        <v>4539</v>
+        <v>4545</v>
       </c>
       <c r="G717" s="5" t="s">
-        <v>4540</v>
+        <v>4546</v>
       </c>
       <c r="H717" s="5" t="s">
-        <v>4352</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="718">
       <c r="B718" s="6" t="s">
-        <v>4541</v>
+        <v>4548</v>
       </c>
       <c r="C718" s="6" t="s">
-        <v>4542</v>
+        <v>3749</v>
       </c>
       <c r="D718" s="6" t="s">
-        <v>4543</v>
+        <v>4549</v>
       </c>
       <c r="E718" s="6" t="s">
-        <v>4544</v>
+        <v>3751</v>
       </c>
       <c r="F718" s="6" t="s">
-        <v>4545</v>
+        <v>3752</v>
       </c>
       <c r="G718" s="6" t="s">
-        <v>4545</v>
+        <v>3752</v>
       </c>
       <c r="H718" s="6" t="s">
-        <v>4543</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="719">
       <c r="B719" s="5" t="s">
-        <v>4546</v>
+        <v>4550</v>
       </c>
       <c r="C719" s="5" t="s">
-        <v>4547</v>
+        <v>4551</v>
       </c>
       <c r="D719" s="5" t="s">
-        <v>4548</v>
+        <v>4352</v>
       </c>
       <c r="E719" s="5" t="s">
-        <v>4549</v>
+        <v>4552</v>
       </c>
       <c r="F719" s="5" t="s">
-        <v>4550</v>
+        <v>4553</v>
       </c>
       <c r="G719" s="5" t="s">
-        <v>4550</v>
+        <v>4554</v>
       </c>
       <c r="H719" s="5" t="s">
-        <v>4551</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="720">
       <c r="B720" s="6" t="s">
-        <v>4552</v>
+        <v>4555</v>
       </c>
       <c r="C720" s="6" t="s">
-        <v>3741</v>
+        <v>4556</v>
       </c>
       <c r="D720" s="6" t="s">
-        <v>4543</v>
+        <v>4557</v>
       </c>
       <c r="E720" s="6" t="s">
-        <v>3743</v>
+        <v>4558</v>
       </c>
       <c r="F720" s="6" t="s">
-        <v>3744</v>
+        <v>4559</v>
       </c>
       <c r="G720" s="6" t="s">
-        <v>3744</v>
+        <v>4559</v>
       </c>
       <c r="H720" s="6" t="s">
-        <v>3745</v>
+        <v>4557</v>
       </c>
     </row>
     <row r="721">
       <c r="B721" s="5" t="s">
-        <v>4553</v>
+        <v>4560</v>
       </c>
       <c r="C721" s="5" t="s">
-        <v>3623</v>
+        <v>4561</v>
       </c>
       <c r="D721" s="5" t="s">
-        <v>4554</v>
+        <v>4562</v>
       </c>
       <c r="E721" s="5" t="s">
-        <v>3625</v>
+        <v>4563</v>
       </c>
       <c r="F721" s="5" t="s">
-        <v>3626</v>
+        <v>4564</v>
       </c>
       <c r="G721" s="5" t="s">
-        <v>3627</v>
+        <v>4564</v>
       </c>
       <c r="H721" s="5" t="s">
-        <v>4555</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="722">
       <c r="B722" s="6" t="s">
-        <v>4556</v>
+        <v>4566</v>
       </c>
       <c r="C722" s="6" t="s">
+        <v>3741</v>
+      </c>
+      <c r="D722" s="6" t="s">
         <v>4557</v>
       </c>
-      <c r="D722" s="6" t="s">
-        <v>4558</v>
-      </c>
       <c r="E722" s="6" t="s">
-        <v>4559</v>
+        <v>3743</v>
       </c>
       <c r="F722" s="6" t="s">
-        <v>4560</v>
+        <v>3744</v>
       </c>
       <c r="G722" s="6" t="s">
-        <v>4560</v>
+        <v>3744</v>
       </c>
       <c r="H722" s="6" t="s">
-        <v>4561</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="723">
       <c r="B723" s="5" t="s">
-        <v>4562</v>
+        <v>4567</v>
       </c>
       <c r="C723" s="5" t="s">
-        <v>4563</v>
+        <v>3623</v>
       </c>
       <c r="D723" s="5" t="s">
-        <v>4564</v>
+        <v>4568</v>
       </c>
       <c r="E723" s="5" t="s">
-        <v>4565</v>
+        <v>3625</v>
       </c>
       <c r="F723" s="5" t="s">
-        <v>4565</v>
+        <v>3626</v>
       </c>
       <c r="G723" s="5" t="s">
-        <v>4565</v>
+        <v>3627</v>
       </c>
       <c r="H723" s="5" t="s">
-        <v>4566</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="724">
       <c r="B724" s="6" t="s">
-        <v>4567</v>
+        <v>4570</v>
       </c>
       <c r="C724" s="6" t="s">
-        <v>4568</v>
+        <v>4571</v>
       </c>
       <c r="D724" s="6" t="s">
-        <v>4569</v>
+        <v>4572</v>
       </c>
       <c r="E724" s="6" t="s">
-        <v>4570</v>
+        <v>4573</v>
       </c>
       <c r="F724" s="6" t="s">
-        <v>4571</v>
+        <v>4574</v>
       </c>
       <c r="G724" s="6" t="s">
-        <v>4571</v>
+        <v>4574</v>
       </c>
       <c r="H724" s="6" t="s">
-        <v>4572</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="725">
       <c r="B725" s="5" t="s">
-        <v>4573</v>
+        <v>4576</v>
       </c>
       <c r="C725" s="5" t="s">
-        <v>3808</v>
+        <v>4577</v>
       </c>
       <c r="D725" s="5" t="s">
-        <v>4574</v>
+        <v>4578</v>
       </c>
       <c r="E725" s="5" t="s">
-        <v>3810</v>
+        <v>4579</v>
       </c>
       <c r="F725" s="5" t="s">
-        <v>2116</v>
+        <v>4579</v>
       </c>
       <c r="G725" s="5" t="s">
-        <v>2116</v>
+        <v>4579</v>
       </c>
       <c r="H725" s="5" t="s">
-        <v>4575</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="726">
       <c r="B726" s="6" t="s">
-        <v>4576</v>
+        <v>4581</v>
       </c>
       <c r="C726" s="6" t="s">
-        <v>3813</v>
+        <v>4582</v>
       </c>
       <c r="D726" s="6" t="s">
-        <v>4577</v>
+        <v>4583</v>
       </c>
       <c r="E726" s="6" t="s">
-        <v>3815</v>
+        <v>4584</v>
       </c>
       <c r="F726" s="6" t="s">
-        <v>3816</v>
+        <v>4585</v>
       </c>
       <c r="G726" s="6" t="s">
-        <v>3817</v>
+        <v>4585</v>
       </c>
       <c r="H726" s="6" t="s">
-        <v>4578</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="727">
       <c r="B727" s="5" t="s">
-        <v>4579</v>
+        <v>4587</v>
       </c>
       <c r="C727" s="5" t="s">
-        <v>3820</v>
+        <v>3808</v>
       </c>
       <c r="D727" s="5" t="s">
-        <v>4580</v>
+        <v>4588</v>
       </c>
       <c r="E727" s="5" t="s">
-        <v>3822</v>
+        <v>3810</v>
       </c>
       <c r="F727" s="5" t="s">
-        <v>3823</v>
+        <v>2116</v>
       </c>
       <c r="G727" s="5" t="s">
-        <v>3823</v>
+        <v>2116</v>
       </c>
       <c r="H727" s="5" t="s">
-        <v>4581</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="728">
       <c r="B728" s="6" t="s">
-        <v>4582</v>
+        <v>4590</v>
       </c>
       <c r="C728" s="6" t="s">
-        <v>2210</v>
+        <v>3813</v>
       </c>
       <c r="D728" s="6" t="s">
-        <v>2211</v>
+        <v>4591</v>
       </c>
       <c r="E728" s="6" t="s">
-        <v>2212</v>
+        <v>3815</v>
       </c>
       <c r="F728" s="6" t="s">
-        <v>2213</v>
+        <v>3816</v>
       </c>
       <c r="G728" s="6" t="s">
-        <v>2214</v>
+        <v>3817</v>
       </c>
       <c r="H728" s="6" t="s">
-        <v>2215</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="729">
       <c r="B729" s="5" t="s">
-        <v>4583</v>
+        <v>4593</v>
       </c>
       <c r="C729" s="5" t="s">
-        <v>2076</v>
+        <v>3820</v>
       </c>
       <c r="D729" s="5" t="s">
-        <v>2077</v>
+        <v>4594</v>
       </c>
       <c r="E729" s="5" t="s">
-        <v>2078</v>
+        <v>3822</v>
       </c>
       <c r="F729" s="5" t="s">
-        <v>2079</v>
+        <v>3823</v>
       </c>
       <c r="G729" s="5" t="s">
-        <v>2080</v>
+        <v>3823</v>
       </c>
       <c r="H729" s="5" t="s">
-        <v>2077</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="730">
       <c r="B730" s="6" t="s">
-        <v>4584</v>
+        <v>4596</v>
       </c>
       <c r="C730" s="6" t="s">
-        <v>2062</v>
+        <v>2210</v>
       </c>
       <c r="D730" s="6" t="s">
-        <v>2063</v>
+        <v>2211</v>
       </c>
       <c r="E730" s="6" t="s">
-        <v>2064</v>
+        <v>2212</v>
       </c>
       <c r="F730" s="6" t="s">
-        <v>2065</v>
+        <v>2213</v>
       </c>
       <c r="G730" s="6" t="s">
-        <v>2066</v>
+        <v>2214</v>
       </c>
       <c r="H730" s="6" t="s">
-        <v>2067</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="731">
       <c r="B731" s="5" t="s">
-        <v>4585</v>
+        <v>4597</v>
       </c>
       <c r="C731" s="5" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="D731" s="5" t="s">
-        <v>2057</v>
+        <v>2077</v>
       </c>
       <c r="E731" s="5" t="s">
-        <v>2058</v>
+        <v>2078</v>
       </c>
       <c r="F731" s="5" t="s">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="G731" s="5" t="s">
-        <v>2059</v>
+        <v>2080</v>
       </c>
       <c r="H731" s="5" t="s">
-        <v>2060</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="732">
       <c r="B732" s="6" t="s">
-        <v>4586</v>
+        <v>4598</v>
       </c>
       <c r="C732" s="6" t="s">
-        <v>2069</v>
+        <v>2062</v>
       </c>
       <c r="D732" s="6" t="s">
-        <v>2070</v>
+        <v>2063</v>
       </c>
       <c r="E732" s="6" t="s">
-        <v>2071</v>
+        <v>2064</v>
       </c>
       <c r="F732" s="6" t="s">
-        <v>2072</v>
+        <v>2065</v>
       </c>
       <c r="G732" s="6" t="s">
-        <v>2073</v>
+        <v>2066</v>
       </c>
       <c r="H732" s="6" t="s">
-        <v>2074</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="733">
       <c r="B733" s="5" t="s">
-        <v>4587</v>
+        <v>4599</v>
       </c>
       <c r="C733" s="5" t="s">
-        <v>2050</v>
+        <v>2056</v>
       </c>
       <c r="D733" s="5" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
       <c r="E733" s="5" t="s">
-        <v>2052</v>
+        <v>2058</v>
       </c>
       <c r="F733" s="5" t="s">
-        <v>2053</v>
+        <v>2059</v>
       </c>
       <c r="G733" s="5" t="s">
-        <v>2054</v>
+        <v>2059</v>
       </c>
       <c r="H733" s="5" t="s">
-        <v>2051</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="734">
       <c r="B734" s="6" t="s">
-        <v>4588</v>
+        <v>4600</v>
       </c>
       <c r="C734" s="6" t="s">
-        <v>2082</v>
+        <v>2069</v>
       </c>
       <c r="D734" s="6" t="s">
-        <v>2083</v>
+        <v>2070</v>
       </c>
       <c r="E734" s="6" t="s">
-        <v>2084</v>
+        <v>2071</v>
       </c>
       <c r="F734" s="6" t="s">
-        <v>2085</v>
+        <v>2072</v>
       </c>
       <c r="G734" s="6" t="s">
-        <v>2086</v>
+        <v>2073</v>
       </c>
       <c r="H734" s="6" t="s">
-        <v>2087</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="735">
       <c r="B735" s="5" t="s">
-        <v>4589</v>
+        <v>4601</v>
       </c>
       <c r="C735" s="5" t="s">
-        <v>4590</v>
+        <v>2050</v>
       </c>
       <c r="D735" s="5" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="E735" s="5" t="s">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="F735" s="5" t="s">
-        <v>2048</v>
+        <v>2053</v>
       </c>
       <c r="G735" s="5" t="s">
-        <v>2048</v>
+        <v>2054</v>
       </c>
       <c r="H735" s="5" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="736">
       <c r="B736" s="6" t="s">
-        <v>4591</v>
+        <v>4602</v>
       </c>
       <c r="C736" s="6" t="s">
-        <v>4592</v>
+        <v>2082</v>
       </c>
       <c r="D736" s="6" t="s">
-        <v>4593</v>
+        <v>2083</v>
       </c>
       <c r="E736" s="6" t="s">
-        <v>4594</v>
+        <v>2084</v>
       </c>
       <c r="F736" s="6" t="s">
-        <v>4595</v>
+        <v>2085</v>
       </c>
       <c r="G736" s="6" t="s">
-        <v>4596</v>
+        <v>2086</v>
       </c>
       <c r="H736" s="6" t="s">
-        <v>4593</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="737">
       <c r="B737" s="5" t="s">
-        <v>4597</v>
+        <v>4603</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>4598</v>
+        <v>4604</v>
       </c>
       <c r="D737" s="5" t="s">
-        <v>4599</v>
+        <v>2046</v>
       </c>
       <c r="E737" s="5" t="s">
-        <v>4600</v>
+        <v>2047</v>
       </c>
       <c r="F737" s="5" t="s">
-        <v>4601</v>
+        <v>2048</v>
       </c>
       <c r="G737" s="5" t="s">
-        <v>4602</v>
+        <v>2048</v>
       </c>
       <c r="H737" s="5" t="s">
-        <v>4603</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="738">
       <c r="B738" s="6" t="s">
-        <v>4604</v>
+        <v>4605</v>
       </c>
       <c r="C738" s="6" t="s">
-        <v>4605</v>
+        <v>4606</v>
       </c>
       <c r="D738" s="6" t="s">
-        <v>4606</v>
+        <v>4607</v>
       </c>
       <c r="E738" s="6" t="s">
+        <v>4608</v>
+      </c>
+      <c r="F738" s="6" t="s">
+        <v>4609</v>
+      </c>
+      <c r="G738" s="6" t="s">
+        <v>4610</v>
+      </c>
+      <c r="H738" s="6" t="s">
         <v>4607</v>
-      </c>
-      <c r="F738" s="6" t="s">
-        <v>4608</v>
-      </c>
-      <c r="G738" s="6" t="s">
-        <v>4609</v>
-      </c>
-      <c r="H738" s="6" t="s">
-        <v>4610</v>
       </c>
     </row>
     <row r="739">
@@ -33573,50 +33615,50 @@
         <v>4622</v>
       </c>
       <c r="G740" s="6" t="s">
-        <v>4622</v>
+        <v>4623</v>
       </c>
       <c r="H740" s="6" t="s">
-        <v>4623</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="741">
       <c r="B741" s="5" t="s">
-        <v>4624</v>
+        <v>4625</v>
       </c>
       <c r="C741" s="5" t="s">
-        <v>4625</v>
+        <v>4626</v>
       </c>
       <c r="D741" s="5" t="s">
-        <v>4626</v>
+        <v>4627</v>
       </c>
       <c r="E741" s="5" t="s">
-        <v>4627</v>
+        <v>4628</v>
       </c>
       <c r="F741" s="5" t="s">
-        <v>4628</v>
+        <v>4629</v>
       </c>
       <c r="G741" s="5" t="s">
-        <v>4629</v>
+        <v>4630</v>
       </c>
       <c r="H741" s="5" t="s">
-        <v>4630</v>
+        <v>4631</v>
       </c>
     </row>
     <row r="742">
       <c r="B742" s="6" t="s">
-        <v>4631</v>
+        <v>4632</v>
       </c>
       <c r="C742" s="6" t="s">
-        <v>4632</v>
+        <v>4633</v>
       </c>
       <c r="D742" s="6" t="s">
-        <v>4633</v>
+        <v>4634</v>
       </c>
       <c r="E742" s="6" t="s">
-        <v>4634</v>
+        <v>4635</v>
       </c>
       <c r="F742" s="6" t="s">
-        <v>4635</v>
+        <v>4636</v>
       </c>
       <c r="G742" s="6" t="s">
         <v>4636</v>
@@ -33639,53 +33681,53 @@
         <v>4641</v>
       </c>
       <c r="F743" s="5" t="s">
-        <v>4641</v>
+        <v>4642</v>
       </c>
       <c r="G743" s="5" t="s">
-        <v>4641</v>
+        <v>4643</v>
       </c>
       <c r="H743" s="5" t="s">
-        <v>4642</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="744">
       <c r="B744" s="6" t="s">
-        <v>4643</v>
+        <v>4645</v>
       </c>
       <c r="C744" s="6" t="s">
-        <v>4644</v>
+        <v>4646</v>
       </c>
       <c r="D744" s="6" t="s">
-        <v>4645</v>
+        <v>4647</v>
       </c>
       <c r="E744" s="6" t="s">
-        <v>4646</v>
+        <v>4648</v>
       </c>
       <c r="F744" s="6" t="s">
-        <v>4647</v>
+        <v>4649</v>
       </c>
       <c r="G744" s="6" t="s">
-        <v>4648</v>
+        <v>4650</v>
       </c>
       <c r="H744" s="6" t="s">
-        <v>4649</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="745">
       <c r="B745" s="5" t="s">
-        <v>4650</v>
+        <v>4652</v>
       </c>
       <c r="C745" s="5" t="s">
-        <v>4651</v>
+        <v>4653</v>
       </c>
       <c r="D745" s="5" t="s">
-        <v>4652</v>
+        <v>4654</v>
       </c>
       <c r="E745" s="5" t="s">
-        <v>4653</v>
+        <v>4655</v>
       </c>
       <c r="F745" s="5" t="s">
-        <v>4654</v>
+        <v>4655</v>
       </c>
       <c r="G745" s="5" t="s">
         <v>4655</v>
@@ -33734,119 +33776,119 @@
         <v>4668</v>
       </c>
       <c r="G747" s="5" t="s">
-        <v>4668</v>
+        <v>4669</v>
       </c>
       <c r="H747" s="5" t="s">
-        <v>4669</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="748">
       <c r="B748" s="6" t="s">
-        <v>4670</v>
+        <v>4671</v>
       </c>
       <c r="C748" s="6" t="s">
-        <v>4671</v>
+        <v>4672</v>
       </c>
       <c r="D748" s="6" t="s">
-        <v>4672</v>
+        <v>4673</v>
       </c>
       <c r="E748" s="6" t="s">
-        <v>4673</v>
+        <v>4674</v>
       </c>
       <c r="F748" s="6" t="s">
-        <v>4674</v>
+        <v>4675</v>
       </c>
       <c r="G748" s="6" t="s">
-        <v>4674</v>
+        <v>4676</v>
       </c>
       <c r="H748" s="6" t="s">
-        <v>4675</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="749">
       <c r="B749" s="5" t="s">
-        <v>4676</v>
+        <v>4678</v>
       </c>
       <c r="C749" s="5" t="s">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="D749" s="5" t="s">
-        <v>4678</v>
+        <v>4680</v>
       </c>
       <c r="E749" s="5" t="s">
-        <v>4679</v>
+        <v>4681</v>
       </c>
       <c r="F749" s="5" t="s">
-        <v>4680</v>
+        <v>4682</v>
       </c>
       <c r="G749" s="5" t="s">
-        <v>4681</v>
+        <v>4682</v>
       </c>
       <c r="H749" s="5" t="s">
-        <v>4682</v>
+        <v>4683</v>
       </c>
     </row>
     <row r="750">
       <c r="B750" s="6" t="s">
-        <v>4683</v>
+        <v>4684</v>
       </c>
       <c r="C750" s="6" t="s">
-        <v>4684</v>
+        <v>4685</v>
       </c>
       <c r="D750" s="6" t="s">
-        <v>4685</v>
+        <v>4686</v>
       </c>
       <c r="E750" s="6" t="s">
-        <v>4686</v>
+        <v>4687</v>
       </c>
       <c r="F750" s="6" t="s">
-        <v>4687</v>
+        <v>4688</v>
       </c>
       <c r="G750" s="6" t="s">
-        <v>4687</v>
+        <v>4688</v>
       </c>
       <c r="H750" s="6" t="s">
-        <v>4688</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="751">
       <c r="B751" s="5" t="s">
-        <v>4689</v>
+        <v>4690</v>
       </c>
       <c r="C751" s="5" t="s">
-        <v>4690</v>
+        <v>4691</v>
       </c>
       <c r="D751" s="5" t="s">
-        <v>4691</v>
+        <v>4692</v>
       </c>
       <c r="E751" s="5" t="s">
-        <v>4692</v>
+        <v>4693</v>
       </c>
       <c r="F751" s="5" t="s">
-        <v>4693</v>
+        <v>4694</v>
       </c>
       <c r="G751" s="5" t="s">
-        <v>4694</v>
+        <v>4695</v>
       </c>
       <c r="H751" s="5" t="s">
-        <v>4695</v>
+        <v>4696</v>
       </c>
     </row>
     <row r="752">
       <c r="B752" s="6" t="s">
-        <v>4696</v>
+        <v>4697</v>
       </c>
       <c r="C752" s="6" t="s">
-        <v>4697</v>
+        <v>4698</v>
       </c>
       <c r="D752" s="6" t="s">
-        <v>4698</v>
+        <v>4699</v>
       </c>
       <c r="E752" s="6" t="s">
-        <v>4699</v>
+        <v>4700</v>
       </c>
       <c r="F752" s="6" t="s">
-        <v>4700</v>
+        <v>4701</v>
       </c>
       <c r="G752" s="6" t="s">
         <v>4701</v>
@@ -34056,50 +34098,50 @@
         <v>4763</v>
       </c>
       <c r="G761" s="5" t="s">
-        <v>4763</v>
+        <v>4764</v>
       </c>
       <c r="H761" s="5" t="s">
-        <v>4764</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="762">
       <c r="B762" s="6" t="s">
-        <v>4765</v>
+        <v>4766</v>
       </c>
       <c r="C762" s="6" t="s">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="D762" s="6" t="s">
-        <v>4767</v>
+        <v>4768</v>
       </c>
       <c r="E762" s="6" t="s">
-        <v>4768</v>
+        <v>4769</v>
       </c>
       <c r="F762" s="6" t="s">
-        <v>4769</v>
+        <v>4770</v>
       </c>
       <c r="G762" s="6" t="s">
-        <v>4770</v>
+        <v>4771</v>
       </c>
       <c r="H762" s="6" t="s">
-        <v>4771</v>
+        <v>4772</v>
       </c>
     </row>
     <row r="763">
       <c r="B763" s="5" t="s">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="C763" s="5" t="s">
-        <v>4773</v>
+        <v>4774</v>
       </c>
       <c r="D763" s="5" t="s">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="E763" s="5" t="s">
-        <v>4775</v>
+        <v>4776</v>
       </c>
       <c r="F763" s="5" t="s">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="G763" s="5" t="s">
         <v>4777</v>
@@ -34447,50 +34489,50 @@
         <v>4881</v>
       </c>
       <c r="G778" s="6" t="s">
-        <v>4881</v>
+        <v>4882</v>
       </c>
       <c r="H778" s="6" t="s">
-        <v>4882</v>
+        <v>4883</v>
       </c>
     </row>
     <row r="779">
       <c r="B779" s="5" t="s">
-        <v>4883</v>
+        <v>4884</v>
       </c>
       <c r="C779" s="5" t="s">
-        <v>4884</v>
+        <v>4885</v>
       </c>
       <c r="D779" s="5" t="s">
-        <v>4885</v>
+        <v>4886</v>
       </c>
       <c r="E779" s="5" t="s">
-        <v>4886</v>
+        <v>4887</v>
       </c>
       <c r="F779" s="5" t="s">
-        <v>4887</v>
+        <v>4888</v>
       </c>
       <c r="G779" s="5" t="s">
-        <v>4888</v>
+        <v>4889</v>
       </c>
       <c r="H779" s="5" t="s">
-        <v>4889</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="780">
       <c r="B780" s="6" t="s">
-        <v>4890</v>
+        <v>4891</v>
       </c>
       <c r="C780" s="6" t="s">
-        <v>4891</v>
+        <v>4892</v>
       </c>
       <c r="D780" s="6" t="s">
-        <v>4892</v>
+        <v>4893</v>
       </c>
       <c r="E780" s="6" t="s">
-        <v>4893</v>
+        <v>4894</v>
       </c>
       <c r="F780" s="6" t="s">
-        <v>4894</v>
+        <v>4895</v>
       </c>
       <c r="G780" s="6" t="s">
         <v>4895</v>
@@ -34516,50 +34558,50 @@
         <v>4901</v>
       </c>
       <c r="G781" s="5" t="s">
-        <v>4901</v>
+        <v>4902</v>
       </c>
       <c r="H781" s="5" t="s">
-        <v>4902</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="782">
       <c r="B782" s="6" t="s">
-        <v>4903</v>
+        <v>4904</v>
       </c>
       <c r="C782" s="6" t="s">
-        <v>4904</v>
+        <v>4905</v>
       </c>
       <c r="D782" s="6" t="s">
-        <v>4905</v>
+        <v>4906</v>
       </c>
       <c r="E782" s="6" t="s">
-        <v>4906</v>
+        <v>4907</v>
       </c>
       <c r="F782" s="6" t="s">
-        <v>4907</v>
+        <v>4908</v>
       </c>
       <c r="G782" s="6" t="s">
-        <v>4908</v>
+        <v>4909</v>
       </c>
       <c r="H782" s="6" t="s">
-        <v>4909</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="783">
       <c r="B783" s="5" t="s">
-        <v>4910</v>
+        <v>4911</v>
       </c>
       <c r="C783" s="5" t="s">
-        <v>4911</v>
+        <v>4912</v>
       </c>
       <c r="D783" s="5" t="s">
-        <v>4912</v>
+        <v>4913</v>
       </c>
       <c r="E783" s="5" t="s">
-        <v>4913</v>
+        <v>4914</v>
       </c>
       <c r="F783" s="5" t="s">
-        <v>4914</v>
+        <v>4915</v>
       </c>
       <c r="G783" s="5" t="s">
         <v>4915</v>
@@ -34608,50 +34650,50 @@
         <v>4928</v>
       </c>
       <c r="G785" s="5" t="s">
-        <v>4928</v>
+        <v>4929</v>
       </c>
       <c r="H785" s="5" t="s">
-        <v>4929</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="786">
       <c r="B786" s="6" t="s">
-        <v>4930</v>
+        <v>4931</v>
       </c>
       <c r="C786" s="6" t="s">
-        <v>4931</v>
+        <v>4932</v>
       </c>
       <c r="D786" s="6" t="s">
-        <v>4932</v>
+        <v>4933</v>
       </c>
       <c r="E786" s="6" t="s">
-        <v>4933</v>
+        <v>4934</v>
       </c>
       <c r="F786" s="6" t="s">
-        <v>4934</v>
+        <v>4935</v>
       </c>
       <c r="G786" s="6" t="s">
-        <v>4935</v>
+        <v>4936</v>
       </c>
       <c r="H786" s="6" t="s">
-        <v>4936</v>
+        <v>4937</v>
       </c>
     </row>
     <row r="787">
       <c r="B787" s="5" t="s">
-        <v>4937</v>
+        <v>4938</v>
       </c>
       <c r="C787" s="5" t="s">
-        <v>4938</v>
+        <v>4939</v>
       </c>
       <c r="D787" s="5" t="s">
-        <v>4939</v>
+        <v>4940</v>
       </c>
       <c r="E787" s="5" t="s">
-        <v>4940</v>
+        <v>4941</v>
       </c>
       <c r="F787" s="5" t="s">
-        <v>4941</v>
+        <v>4942</v>
       </c>
       <c r="G787" s="5" t="s">
         <v>4942</v>
@@ -34795,53 +34837,53 @@
         <v>4984</v>
       </c>
       <c r="H793" s="5" t="s">
-        <v>4981</v>
+        <v>4985</v>
       </c>
     </row>
     <row r="794">
       <c r="B794" s="6" t="s">
-        <v>4985</v>
+        <v>4986</v>
       </c>
       <c r="C794" s="6" t="s">
-        <v>4986</v>
+        <v>4987</v>
       </c>
       <c r="D794" s="6" t="s">
-        <v>4987</v>
+        <v>4988</v>
       </c>
       <c r="E794" s="6" t="s">
-        <v>4988</v>
+        <v>4989</v>
       </c>
       <c r="F794" s="6" t="s">
-        <v>4989</v>
+        <v>4990</v>
       </c>
       <c r="G794" s="6" t="s">
-        <v>4990</v>
+        <v>4991</v>
       </c>
       <c r="H794" s="6" t="s">
-        <v>4991</v>
+        <v>4992</v>
       </c>
     </row>
     <row r="795">
       <c r="B795" s="5" t="s">
-        <v>4992</v>
+        <v>4993</v>
       </c>
       <c r="C795" s="5" t="s">
-        <v>4993</v>
+        <v>4994</v>
       </c>
       <c r="D795" s="5" t="s">
-        <v>4994</v>
+        <v>4995</v>
       </c>
       <c r="E795" s="5" t="s">
+        <v>4996</v>
+      </c>
+      <c r="F795" s="5" t="s">
+        <v>4997</v>
+      </c>
+      <c r="G795" s="5" t="s">
+        <v>4998</v>
+      </c>
+      <c r="H795" s="5" t="s">
         <v>4995</v>
-      </c>
-      <c r="F795" s="5" t="s">
-        <v>4996</v>
-      </c>
-      <c r="G795" s="5" t="s">
-        <v>4997</v>
-      </c>
-      <c r="H795" s="5" t="s">
-        <v>4998</v>
       </c>
     </row>
     <row r="796">
@@ -34895,154 +34937,154 @@
         <v>5013</v>
       </c>
       <c r="C798" s="6" t="s">
-        <v>3021</v>
+        <v>5014</v>
       </c>
       <c r="D798" s="6" t="s">
-        <v>5014</v>
+        <v>5015</v>
       </c>
       <c r="E798" s="6" t="s">
-        <v>3023</v>
+        <v>5016</v>
       </c>
       <c r="F798" s="6" t="s">
-        <v>5015</v>
+        <v>5017</v>
       </c>
       <c r="G798" s="6" t="s">
-        <v>5016</v>
+        <v>5018</v>
       </c>
       <c r="H798" s="6" t="s">
-        <v>5017</v>
+        <v>5019</v>
       </c>
     </row>
     <row r="799">
       <c r="B799" s="5" t="s">
-        <v>5018</v>
+        <v>5020</v>
       </c>
       <c r="C799" s="5" t="s">
-        <v>3014</v>
+        <v>5021</v>
       </c>
       <c r="D799" s="5" t="s">
-        <v>5019</v>
+        <v>5022</v>
       </c>
       <c r="E799" s="5" t="s">
-        <v>3016</v>
+        <v>5023</v>
       </c>
       <c r="F799" s="5" t="s">
-        <v>5020</v>
+        <v>5024</v>
       </c>
       <c r="G799" s="5" t="s">
-        <v>5021</v>
+        <v>5025</v>
       </c>
       <c r="H799" s="5" t="s">
-        <v>5022</v>
+        <v>5026</v>
       </c>
     </row>
     <row r="800">
       <c r="B800" s="6" t="s">
-        <v>5023</v>
+        <v>5027</v>
       </c>
       <c r="C800" s="6" t="s">
-        <v>5024</v>
+        <v>3021</v>
       </c>
       <c r="D800" s="6" t="s">
-        <v>5025</v>
+        <v>5028</v>
       </c>
       <c r="E800" s="6" t="s">
-        <v>5026</v>
+        <v>3023</v>
       </c>
       <c r="F800" s="6" t="s">
-        <v>5027</v>
+        <v>5029</v>
       </c>
       <c r="G800" s="6" t="s">
-        <v>5026</v>
+        <v>5030</v>
       </c>
       <c r="H800" s="6" t="s">
-        <v>4429</v>
+        <v>5031</v>
       </c>
     </row>
     <row r="801">
       <c r="B801" s="5" t="s">
-        <v>5028</v>
+        <v>5032</v>
       </c>
       <c r="C801" s="5" t="s">
-        <v>5029</v>
+        <v>3014</v>
       </c>
       <c r="D801" s="5" t="s">
-        <v>5030</v>
+        <v>5033</v>
       </c>
       <c r="E801" s="5" t="s">
-        <v>5031</v>
+        <v>3016</v>
       </c>
       <c r="F801" s="5" t="s">
-        <v>5032</v>
+        <v>5034</v>
       </c>
       <c r="G801" s="5" t="s">
-        <v>5033</v>
+        <v>5035</v>
       </c>
       <c r="H801" s="5" t="s">
-        <v>5034</v>
+        <v>5036</v>
       </c>
     </row>
     <row r="802">
       <c r="B802" s="6" t="s">
-        <v>5035</v>
+        <v>5037</v>
       </c>
       <c r="C802" s="6" t="s">
-        <v>5036</v>
+        <v>5038</v>
       </c>
       <c r="D802" s="6" t="s">
-        <v>5037</v>
+        <v>5039</v>
       </c>
       <c r="E802" s="6" t="s">
-        <v>5038</v>
+        <v>5040</v>
       </c>
       <c r="F802" s="6" t="s">
-        <v>5039</v>
+        <v>5041</v>
       </c>
       <c r="G802" s="6" t="s">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="H802" s="6" t="s">
-        <v>5040</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="803">
       <c r="B803" s="5" t="s">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="C803" s="5" t="s">
-        <v>5042</v>
+        <v>5043</v>
       </c>
       <c r="D803" s="5" t="s">
-        <v>5043</v>
+        <v>5044</v>
       </c>
       <c r="E803" s="5" t="s">
-        <v>5044</v>
+        <v>5045</v>
       </c>
       <c r="F803" s="5" t="s">
-        <v>5045</v>
+        <v>5046</v>
       </c>
       <c r="G803" s="5" t="s">
-        <v>5046</v>
+        <v>5047</v>
       </c>
       <c r="H803" s="5" t="s">
-        <v>5047</v>
+        <v>5048</v>
       </c>
     </row>
     <row r="804">
       <c r="B804" s="6" t="s">
-        <v>5048</v>
+        <v>5049</v>
       </c>
       <c r="C804" s="6" t="s">
-        <v>5049</v>
+        <v>5050</v>
       </c>
       <c r="D804" s="6" t="s">
-        <v>5050</v>
+        <v>5051</v>
       </c>
       <c r="E804" s="6" t="s">
-        <v>5051</v>
+        <v>5052</v>
       </c>
       <c r="F804" s="6" t="s">
-        <v>5052</v>
+        <v>5053</v>
       </c>
       <c r="G804" s="6" t="s">
         <v>5053</v>
@@ -35134,53 +35176,53 @@
         <v>5079</v>
       </c>
       <c r="F808" s="6" t="s">
-        <v>5079</v>
+        <v>5080</v>
       </c>
       <c r="G808" s="6" t="s">
-        <v>5079</v>
+        <v>5081</v>
       </c>
       <c r="H808" s="6" t="s">
-        <v>5080</v>
+        <v>5082</v>
       </c>
     </row>
     <row r="809">
       <c r="B809" s="5" t="s">
-        <v>5081</v>
+        <v>5083</v>
       </c>
       <c r="C809" s="5" t="s">
-        <v>5082</v>
+        <v>5084</v>
       </c>
       <c r="D809" s="5" t="s">
-        <v>5083</v>
+        <v>5085</v>
       </c>
       <c r="E809" s="5" t="s">
-        <v>5084</v>
+        <v>5086</v>
       </c>
       <c r="F809" s="5" t="s">
-        <v>5085</v>
+        <v>5087</v>
       </c>
       <c r="G809" s="5" t="s">
-        <v>5086</v>
+        <v>5088</v>
       </c>
       <c r="H809" s="5" t="s">
-        <v>5087</v>
+        <v>5089</v>
       </c>
     </row>
     <row r="810">
       <c r="B810" s="6" t="s">
-        <v>5088</v>
+        <v>5090</v>
       </c>
       <c r="C810" s="6" t="s">
-        <v>5089</v>
+        <v>5091</v>
       </c>
       <c r="D810" s="6" t="s">
-        <v>5090</v>
+        <v>5092</v>
       </c>
       <c r="E810" s="6" t="s">
-        <v>5091</v>
+        <v>5093</v>
       </c>
       <c r="F810" s="6" t="s">
-        <v>5092</v>
+        <v>5093</v>
       </c>
       <c r="G810" s="6" t="s">
         <v>5093</v>
@@ -35229,96 +35271,96 @@
         <v>5106</v>
       </c>
       <c r="G812" s="6" t="s">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="H812" s="6" t="s">
-        <v>5107</v>
+        <v>5108</v>
       </c>
     </row>
     <row r="813">
       <c r="B813" s="5" t="s">
-        <v>5108</v>
+        <v>5109</v>
       </c>
       <c r="C813" s="5" t="s">
-        <v>5109</v>
+        <v>5110</v>
       </c>
       <c r="D813" s="5" t="s">
-        <v>5110</v>
+        <v>5111</v>
       </c>
       <c r="E813" s="5" t="s">
-        <v>5111</v>
+        <v>5112</v>
       </c>
       <c r="F813" s="5" t="s">
-        <v>5112</v>
+        <v>5113</v>
       </c>
       <c r="G813" s="5" t="s">
-        <v>5112</v>
+        <v>5114</v>
       </c>
       <c r="H813" s="5" t="s">
-        <v>5113</v>
+        <v>5115</v>
       </c>
     </row>
     <row r="814">
       <c r="B814" s="6" t="s">
-        <v>5114</v>
+        <v>5116</v>
       </c>
       <c r="C814" s="6" t="s">
-        <v>5115</v>
+        <v>5117</v>
       </c>
       <c r="D814" s="6" t="s">
-        <v>5116</v>
+        <v>5118</v>
       </c>
       <c r="E814" s="6" t="s">
-        <v>5117</v>
+        <v>5119</v>
       </c>
       <c r="F814" s="6" t="s">
-        <v>5118</v>
+        <v>5120</v>
       </c>
       <c r="G814" s="6" t="s">
-        <v>5118</v>
+        <v>5120</v>
       </c>
       <c r="H814" s="6" t="s">
-        <v>5119</v>
+        <v>5121</v>
       </c>
     </row>
     <row r="815">
       <c r="B815" s="5" t="s">
-        <v>5120</v>
+        <v>5122</v>
       </c>
       <c r="C815" s="5" t="s">
-        <v>5121</v>
+        <v>5123</v>
       </c>
       <c r="D815" s="5" t="s">
-        <v>5122</v>
+        <v>5124</v>
       </c>
       <c r="E815" s="5" t="s">
-        <v>5123</v>
+        <v>5125</v>
       </c>
       <c r="F815" s="5" t="s">
-        <v>5124</v>
+        <v>5126</v>
       </c>
       <c r="G815" s="5" t="s">
-        <v>5125</v>
+        <v>5126</v>
       </c>
       <c r="H815" s="5" t="s">
-        <v>5126</v>
+        <v>5127</v>
       </c>
     </row>
     <row r="816">
       <c r="B816" s="6" t="s">
-        <v>5127</v>
+        <v>5128</v>
       </c>
       <c r="C816" s="6" t="s">
-        <v>5128</v>
+        <v>5129</v>
       </c>
       <c r="D816" s="6" t="s">
-        <v>5129</v>
+        <v>5130</v>
       </c>
       <c r="E816" s="6" t="s">
-        <v>5130</v>
+        <v>5131</v>
       </c>
       <c r="F816" s="6" t="s">
-        <v>5131</v>
+        <v>5132</v>
       </c>
       <c r="G816" s="6" t="s">
         <v>5132</v>
@@ -35413,79 +35455,79 @@
         <v>5159</v>
       </c>
       <c r="G820" s="6" t="s">
-        <v>5159</v>
+        <v>5160</v>
       </c>
       <c r="H820" s="6" t="s">
-        <v>5160</v>
+        <v>5161</v>
       </c>
     </row>
     <row r="821">
       <c r="B821" s="5" t="s">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="C821" s="5" t="s">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="D821" s="5" t="s">
-        <v>5163</v>
+        <v>5164</v>
       </c>
       <c r="E821" s="5" t="s">
-        <v>5164</v>
+        <v>5165</v>
       </c>
       <c r="F821" s="5" t="s">
-        <v>5164</v>
+        <v>5166</v>
       </c>
       <c r="G821" s="5" t="s">
-        <v>5164</v>
+        <v>5167</v>
       </c>
       <c r="H821" s="5" t="s">
-        <v>5163</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="822">
       <c r="B822" s="6" t="s">
-        <v>5165</v>
+        <v>5169</v>
       </c>
       <c r="C822" s="6" t="s">
-        <v>5166</v>
+        <v>5170</v>
       </c>
       <c r="D822" s="6" t="s">
-        <v>5167</v>
+        <v>5171</v>
       </c>
       <c r="E822" s="6" t="s">
-        <v>5168</v>
+        <v>5172</v>
       </c>
       <c r="F822" s="6" t="s">
-        <v>5169</v>
+        <v>5173</v>
       </c>
       <c r="G822" s="6" t="s">
-        <v>5170</v>
+        <v>5173</v>
       </c>
       <c r="H822" s="6" t="s">
-        <v>5171</v>
+        <v>5174</v>
       </c>
     </row>
     <row r="823">
       <c r="B823" s="5" t="s">
-        <v>5172</v>
+        <v>5175</v>
       </c>
       <c r="C823" s="5" t="s">
-        <v>5173</v>
+        <v>5176</v>
       </c>
       <c r="D823" s="5" t="s">
-        <v>5174</v>
+        <v>5177</v>
       </c>
       <c r="E823" s="5" t="s">
-        <v>5175</v>
+        <v>5178</v>
       </c>
       <c r="F823" s="5" t="s">
-        <v>5176</v>
+        <v>5178</v>
       </c>
       <c r="G823" s="5" t="s">
+        <v>5178</v>
+      </c>
+      <c r="H823" s="5" t="s">
         <v>5177</v>
-      </c>
-      <c r="H823" s="5" t="s">
-        <v>5178</v>
       </c>
     </row>
     <row r="824">
@@ -35519,111 +35561,111 @@
         <v>5187</v>
       </c>
       <c r="D825" s="5" t="s">
-        <v>5163</v>
+        <v>5188</v>
       </c>
       <c r="E825" s="5" t="s">
-        <v>5188</v>
+        <v>5189</v>
       </c>
       <c r="F825" s="5" t="s">
-        <v>5189</v>
+        <v>5190</v>
       </c>
       <c r="G825" s="5" t="s">
-        <v>5189</v>
+        <v>5191</v>
       </c>
       <c r="H825" s="5" t="s">
-        <v>5163</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="826">
       <c r="B826" s="6" t="s">
-        <v>5190</v>
+        <v>5193</v>
       </c>
       <c r="C826" s="6" t="s">
-        <v>5191</v>
+        <v>5194</v>
       </c>
       <c r="D826" s="6" t="s">
-        <v>5192</v>
+        <v>5195</v>
       </c>
       <c r="E826" s="6" t="s">
-        <v>5193</v>
+        <v>5196</v>
       </c>
       <c r="F826" s="6" t="s">
-        <v>5194</v>
+        <v>5197</v>
       </c>
       <c r="G826" s="6" t="s">
-        <v>5195</v>
+        <v>5198</v>
       </c>
       <c r="H826" s="6" t="s">
-        <v>5196</v>
+        <v>5199</v>
       </c>
     </row>
     <row r="827">
       <c r="B827" s="5" t="s">
-        <v>5197</v>
+        <v>5200</v>
       </c>
       <c r="C827" s="5" t="s">
-        <v>5198</v>
+        <v>5201</v>
       </c>
       <c r="D827" s="5" t="s">
-        <v>5199</v>
+        <v>5177</v>
       </c>
       <c r="E827" s="5" t="s">
-        <v>5200</v>
+        <v>5202</v>
       </c>
       <c r="F827" s="5" t="s">
-        <v>5201</v>
+        <v>5203</v>
       </c>
       <c r="G827" s="5" t="s">
-        <v>5202</v>
+        <v>5203</v>
       </c>
       <c r="H827" s="5" t="s">
-        <v>5199</v>
+        <v>5177</v>
       </c>
     </row>
     <row r="828">
       <c r="B828" s="6" t="s">
-        <v>5203</v>
+        <v>5204</v>
       </c>
       <c r="C828" s="6" t="s">
-        <v>5204</v>
+        <v>5205</v>
       </c>
       <c r="D828" s="6" t="s">
-        <v>5205</v>
+        <v>5206</v>
       </c>
       <c r="E828" s="6" t="s">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="F828" s="6" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="G828" s="6" t="s">
-        <v>5208</v>
+        <v>5209</v>
       </c>
       <c r="H828" s="6" t="s">
-        <v>5209</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="829">
       <c r="B829" s="5" t="s">
-        <v>5210</v>
+        <v>5211</v>
       </c>
       <c r="C829" s="5" t="s">
-        <v>5211</v>
+        <v>5212</v>
       </c>
       <c r="D829" s="5" t="s">
-        <v>5212</v>
+        <v>5213</v>
       </c>
       <c r="E829" s="5" t="s">
+        <v>5214</v>
+      </c>
+      <c r="F829" s="5" t="s">
+        <v>5215</v>
+      </c>
+      <c r="G829" s="5" t="s">
+        <v>5216</v>
+      </c>
+      <c r="H829" s="5" t="s">
         <v>5213</v>
-      </c>
-      <c r="F829" s="5" t="s">
-        <v>5214</v>
-      </c>
-      <c r="G829" s="5" t="s">
-        <v>5215</v>
-      </c>
-      <c r="H829" s="5" t="s">
-        <v>5216</v>
       </c>
     </row>
     <row r="830">
@@ -35689,562 +35731,562 @@
         <v>5235</v>
       </c>
       <c r="G832" s="6" t="s">
-        <v>5235</v>
+        <v>5236</v>
       </c>
       <c r="H832" s="6" t="s">
-        <v>5236</v>
+        <v>5237</v>
       </c>
     </row>
     <row r="833">
       <c r="B833" s="5" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C833" s="5" t="s">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="D833" s="5" t="s">
-        <v>5239</v>
+        <v>5240</v>
       </c>
       <c r="E833" s="5" t="s">
-        <v>5240</v>
+        <v>5241</v>
       </c>
       <c r="F833" s="5" t="s">
-        <v>5241</v>
+        <v>5242</v>
       </c>
       <c r="G833" s="5" t="s">
-        <v>5242</v>
+        <v>5243</v>
       </c>
       <c r="H833" s="5" t="s">
-        <v>5243</v>
+        <v>5244</v>
       </c>
     </row>
     <row r="834">
       <c r="B834" s="6" t="s">
-        <v>5244</v>
+        <v>5245</v>
       </c>
       <c r="C834" s="6" t="s">
-        <v>5245</v>
+        <v>5246</v>
       </c>
       <c r="D834" s="6" t="s">
-        <v>5246</v>
+        <v>5247</v>
       </c>
       <c r="E834" s="6" t="s">
-        <v>5247</v>
+        <v>5248</v>
       </c>
       <c r="F834" s="6" t="s">
-        <v>5248</v>
+        <v>5249</v>
       </c>
       <c r="G834" s="6" t="s">
-        <v>5248</v>
+        <v>5249</v>
       </c>
       <c r="H834" s="6" t="s">
-        <v>5249</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="835">
       <c r="B835" s="5" t="s">
-        <v>5250</v>
+        <v>5251</v>
       </c>
       <c r="C835" s="5" t="s">
-        <v>5251</v>
+        <v>5252</v>
       </c>
       <c r="D835" s="5" t="s">
-        <v>5252</v>
+        <v>5253</v>
       </c>
       <c r="E835" s="5" t="s">
-        <v>5253</v>
+        <v>5254</v>
       </c>
       <c r="F835" s="5" t="s">
-        <v>5254</v>
+        <v>5255</v>
       </c>
       <c r="G835" s="5" t="s">
-        <v>5255</v>
+        <v>5256</v>
       </c>
       <c r="H835" s="5" t="s">
-        <v>5256</v>
+        <v>5257</v>
       </c>
     </row>
     <row r="836">
       <c r="B836" s="6" t="s">
-        <v>5257</v>
+        <v>5258</v>
       </c>
       <c r="C836" s="6" t="s">
-        <v>5258</v>
+        <v>5259</v>
       </c>
       <c r="D836" s="6" t="s">
-        <v>5259</v>
+        <v>5260</v>
       </c>
       <c r="E836" s="6" t="s">
-        <v>5260</v>
+        <v>5261</v>
       </c>
       <c r="F836" s="6" t="s">
-        <v>5261</v>
+        <v>5262</v>
       </c>
       <c r="G836" s="6" t="s">
-        <v>5260</v>
+        <v>5262</v>
       </c>
       <c r="H836" s="6" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
     </row>
     <row r="837">
       <c r="B837" s="5" t="s">
-        <v>5263</v>
+        <v>5264</v>
       </c>
       <c r="C837" s="5" t="s">
-        <v>5264</v>
+        <v>5265</v>
       </c>
       <c r="D837" s="5" t="s">
-        <v>5265</v>
+        <v>5266</v>
       </c>
       <c r="E837" s="5" t="s">
-        <v>5266</v>
+        <v>5267</v>
       </c>
       <c r="F837" s="5" t="s">
-        <v>5267</v>
+        <v>5268</v>
       </c>
       <c r="G837" s="5" t="s">
-        <v>5267</v>
+        <v>5269</v>
       </c>
       <c r="H837" s="5" t="s">
-        <v>5265</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="838">
       <c r="B838" s="6" t="s">
-        <v>5268</v>
+        <v>5271</v>
       </c>
       <c r="C838" s="6" t="s">
-        <v>5269</v>
+        <v>5272</v>
       </c>
       <c r="D838" s="6" t="s">
-        <v>5270</v>
+        <v>5273</v>
       </c>
       <c r="E838" s="6" t="s">
-        <v>5271</v>
+        <v>5274</v>
       </c>
       <c r="F838" s="6" t="s">
-        <v>5272</v>
+        <v>5275</v>
       </c>
       <c r="G838" s="6" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="H838" s="6" t="s">
-        <v>5274</v>
+        <v>5276</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
-        <v>5275</v>
+        <v>5277</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>5276</v>
+        <v>5278</v>
       </c>
       <c r="D839" s="5" t="s">
-        <v>5277</v>
+        <v>5279</v>
       </c>
       <c r="E839" s="5" t="s">
-        <v>5278</v>
+        <v>5280</v>
       </c>
       <c r="F839" s="5" t="s">
+        <v>5281</v>
+      </c>
+      <c r="G839" s="5" t="s">
+        <v>5281</v>
+      </c>
+      <c r="H839" s="5" t="s">
         <v>5279</v>
-      </c>
-      <c r="G839" s="5" t="s">
-        <v>5280</v>
-      </c>
-      <c r="H839" s="5" t="s">
-        <v>5277</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
-        <v>5281</v>
+        <v>5282</v>
       </c>
       <c r="C840" s="6" t="s">
-        <v>5282</v>
+        <v>5283</v>
       </c>
       <c r="D840" s="6" t="s">
-        <v>5283</v>
+        <v>5284</v>
       </c>
       <c r="E840" s="6" t="s">
-        <v>5284</v>
+        <v>5285</v>
       </c>
       <c r="F840" s="6" t="s">
-        <v>5285</v>
+        <v>5286</v>
       </c>
       <c r="G840" s="6" t="s">
-        <v>5286</v>
+        <v>5287</v>
       </c>
       <c r="H840" s="6" t="s">
-        <v>5287</v>
+        <v>5288</v>
       </c>
     </row>
     <row r="841">
       <c r="B841" s="5" t="s">
-        <v>5288</v>
+        <v>5289</v>
       </c>
       <c r="C841" s="5" t="s">
-        <v>5289</v>
+        <v>5290</v>
       </c>
       <c r="D841" s="5" t="s">
-        <v>5290</v>
+        <v>5291</v>
       </c>
       <c r="E841" s="5" t="s">
+        <v>5292</v>
+      </c>
+      <c r="F841" s="5" t="s">
+        <v>5293</v>
+      </c>
+      <c r="G841" s="5" t="s">
+        <v>5294</v>
+      </c>
+      <c r="H841" s="5" t="s">
         <v>5291</v>
-      </c>
-      <c r="F841" s="5" t="s">
-        <v>5292</v>
-      </c>
-      <c r="G841" s="5" t="s">
-        <v>5292</v>
-      </c>
-      <c r="H841" s="5" t="s">
-        <v>5293</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
-        <v>5294</v>
+        <v>5295</v>
       </c>
       <c r="C842" s="6" t="s">
-        <v>5295</v>
+        <v>5296</v>
       </c>
       <c r="D842" s="6" t="s">
-        <v>5296</v>
+        <v>5297</v>
       </c>
       <c r="E842" s="6" t="s">
-        <v>5297</v>
+        <v>5298</v>
       </c>
       <c r="F842" s="6" t="s">
-        <v>5298</v>
+        <v>5299</v>
       </c>
       <c r="G842" s="6" t="s">
-        <v>5298</v>
+        <v>5300</v>
       </c>
       <c r="H842" s="6" t="s">
-        <v>5299</v>
+        <v>5301</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
-        <v>5300</v>
+        <v>5302</v>
       </c>
       <c r="C843" s="5" t="s">
-        <v>5301</v>
+        <v>5303</v>
       </c>
       <c r="D843" s="5" t="s">
-        <v>5302</v>
+        <v>5304</v>
       </c>
       <c r="E843" s="5" t="s">
-        <v>5303</v>
+        <v>5305</v>
       </c>
       <c r="F843" s="5" t="s">
-        <v>5304</v>
+        <v>5306</v>
       </c>
       <c r="G843" s="5" t="s">
-        <v>5305</v>
+        <v>5306</v>
       </c>
       <c r="H843" s="5" t="s">
-        <v>5306</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="844">
       <c r="B844" s="6" t="s">
-        <v>5307</v>
+        <v>5308</v>
       </c>
       <c r="C844" s="6" t="s">
-        <v>5308</v>
+        <v>5309</v>
       </c>
       <c r="D844" s="6" t="s">
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="E844" s="6" t="s">
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>5311</v>
+        <v>5312</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5311</v>
+        <v>5312</v>
       </c>
       <c r="H844" s="6" t="s">
-        <v>5312</v>
+        <v>5313</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5313</v>
+        <v>5314</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>5314</v>
+        <v>5315</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5315</v>
+        <v>5316</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>5316</v>
+        <v>5317</v>
       </c>
       <c r="F845" s="5" t="s">
-        <v>5317</v>
+        <v>5318</v>
       </c>
       <c r="G845" s="5" t="s">
-        <v>5318</v>
+        <v>5319</v>
       </c>
       <c r="H845" s="5" t="s">
-        <v>5319</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
-        <v>5320</v>
+        <v>5321</v>
       </c>
       <c r="C846" s="6" t="s">
-        <v>5321</v>
+        <v>5322</v>
       </c>
       <c r="D846" s="6" t="s">
-        <v>5322</v>
+        <v>5323</v>
       </c>
       <c r="E846" s="6" t="s">
-        <v>5323</v>
+        <v>5324</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>5324</v>
+        <v>5325</v>
       </c>
       <c r="G846" s="6" t="s">
-        <v>5324</v>
+        <v>5325</v>
       </c>
       <c r="H846" s="6" t="s">
-        <v>5325</v>
+        <v>5326</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
-        <v>5326</v>
+        <v>5327</v>
       </c>
       <c r="C847" s="5" t="s">
-        <v>5327</v>
+        <v>5328</v>
       </c>
       <c r="D847" s="5" t="s">
-        <v>5328</v>
+        <v>5329</v>
       </c>
       <c r="E847" s="5" t="s">
-        <v>5329</v>
+        <v>5330</v>
       </c>
       <c r="F847" s="5" t="s">
-        <v>5330</v>
+        <v>5331</v>
       </c>
       <c r="G847" s="5" t="s">
-        <v>5330</v>
+        <v>5332</v>
       </c>
       <c r="H847" s="5" t="s">
-        <v>5331</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
-        <v>5332</v>
+        <v>5334</v>
       </c>
       <c r="C848" s="6" t="s">
-        <v>5333</v>
+        <v>5335</v>
       </c>
       <c r="D848" s="6" t="s">
-        <v>5333</v>
+        <v>5336</v>
       </c>
       <c r="E848" s="6" t="s">
-        <v>5333</v>
+        <v>5337</v>
       </c>
       <c r="F848" s="6" t="s">
-        <v>5333</v>
+        <v>5338</v>
       </c>
       <c r="G848" s="6" t="s">
-        <v>5333</v>
+        <v>5338</v>
       </c>
       <c r="H848" s="6" t="s">
-        <v>5333</v>
+        <v>5339</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
-        <v>5334</v>
+        <v>5340</v>
       </c>
       <c r="C849" s="5" t="s">
-        <v>5335</v>
+        <v>5341</v>
       </c>
       <c r="D849" s="5" t="s">
-        <v>5336</v>
+        <v>5342</v>
       </c>
       <c r="E849" s="5" t="s">
-        <v>5337</v>
+        <v>5343</v>
       </c>
       <c r="F849" s="5" t="s">
-        <v>5338</v>
+        <v>5344</v>
       </c>
       <c r="G849" s="5" t="s">
-        <v>5338</v>
+        <v>5344</v>
       </c>
       <c r="H849" s="5" t="s">
-        <v>5336</v>
+        <v>5345</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
-        <v>5339</v>
+        <v>5346</v>
       </c>
       <c r="C850" s="6" t="s">
-        <v>5340</v>
+        <v>5347</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>5341</v>
+        <v>5347</v>
       </c>
       <c r="E850" s="6" t="s">
-        <v>5342</v>
+        <v>5347</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>5343</v>
+        <v>5347</v>
       </c>
       <c r="G850" s="6" t="s">
-        <v>5344</v>
+        <v>5347</v>
       </c>
       <c r="H850" s="6" t="s">
-        <v>5341</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
-        <v>5345</v>
+        <v>5348</v>
       </c>
       <c r="C851" s="5" t="s">
-        <v>5346</v>
+        <v>5349</v>
       </c>
       <c r="D851" s="5" t="s">
-        <v>5347</v>
+        <v>5350</v>
       </c>
       <c r="E851" s="5" t="s">
-        <v>5348</v>
+        <v>5351</v>
       </c>
       <c r="F851" s="5" t="s">
-        <v>5348</v>
+        <v>5352</v>
       </c>
       <c r="G851" s="5" t="s">
-        <v>5348</v>
+        <v>5352</v>
       </c>
       <c r="H851" s="5" t="s">
-        <v>5347</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
-        <v>5349</v>
+        <v>5353</v>
       </c>
       <c r="C852" s="6" t="s">
-        <v>5350</v>
+        <v>5354</v>
       </c>
       <c r="D852" s="6" t="s">
-        <v>5351</v>
+        <v>5355</v>
       </c>
       <c r="E852" s="6" t="s">
-        <v>5352</v>
+        <v>5356</v>
       </c>
       <c r="F852" s="6" t="s">
-        <v>5352</v>
+        <v>5357</v>
       </c>
       <c r="G852" s="6" t="s">
-        <v>5352</v>
+        <v>5358</v>
       </c>
       <c r="H852" s="6" t="s">
-        <v>5351</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
-        <v>5353</v>
+        <v>5359</v>
       </c>
       <c r="C853" s="5" t="s">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="D853" s="5" t="s">
-        <v>5355</v>
+        <v>5361</v>
       </c>
       <c r="E853" s="5" t="s">
-        <v>5356</v>
+        <v>5362</v>
       </c>
       <c r="F853" s="5" t="s">
-        <v>5357</v>
+        <v>5362</v>
       </c>
       <c r="G853" s="5" t="s">
-        <v>5358</v>
+        <v>5362</v>
       </c>
       <c r="H853" s="5" t="s">
-        <v>5359</v>
+        <v>5361</v>
       </c>
     </row>
     <row r="854">
       <c r="B854" s="6" t="s">
-        <v>5360</v>
+        <v>5363</v>
       </c>
       <c r="C854" s="6" t="s">
-        <v>5361</v>
+        <v>5364</v>
       </c>
       <c r="D854" s="6" t="s">
-        <v>5362</v>
+        <v>5365</v>
       </c>
       <c r="E854" s="6" t="s">
-        <v>5363</v>
+        <v>5366</v>
       </c>
       <c r="F854" s="6" t="s">
-        <v>5364</v>
+        <v>5366</v>
       </c>
       <c r="G854" s="6" t="s">
+        <v>5366</v>
+      </c>
+      <c r="H854" s="6" t="s">
         <v>5365</v>
-      </c>
-      <c r="H854" s="6" t="s">
-        <v>5362</v>
       </c>
     </row>
     <row r="855">
       <c r="B855" s="5" t="s">
-        <v>5366</v>
+        <v>5367</v>
       </c>
       <c r="C855" s="5" t="s">
-        <v>5367</v>
+        <v>5368</v>
       </c>
       <c r="D855" s="5" t="s">
-        <v>5368</v>
+        <v>5369</v>
       </c>
       <c r="E855" s="5" t="s">
-        <v>5369</v>
+        <v>5370</v>
       </c>
       <c r="F855" s="5" t="s">
-        <v>5370</v>
+        <v>5371</v>
       </c>
       <c r="G855" s="5" t="s">
-        <v>5371</v>
+        <v>5372</v>
       </c>
       <c r="H855" s="5" t="s">
-        <v>5372</v>
+        <v>5373</v>
       </c>
     </row>
     <row r="856">
       <c r="B856" s="6" t="s">
-        <v>5373</v>
+        <v>5374</v>
       </c>
       <c r="C856" s="6" t="s">
-        <v>5374</v>
+        <v>5375</v>
       </c>
       <c r="D856" s="6" t="s">
-        <v>5375</v>
+        <v>5376</v>
       </c>
       <c r="E856" s="6" t="s">
+        <v>5377</v>
+      </c>
+      <c r="F856" s="6" t="s">
+        <v>5378</v>
+      </c>
+      <c r="G856" s="6" t="s">
+        <v>5379</v>
+      </c>
+      <c r="H856" s="6" t="s">
         <v>5376</v>
-      </c>
-      <c r="F856" s="6" t="s">
-        <v>5377</v>
-      </c>
-      <c r="G856" s="6" t="s">
-        <v>5378</v>
-      </c>
-      <c r="H856" s="6" t="s">
-        <v>5379</v>
       </c>
     </row>
     <row r="857">
@@ -36290,57 +36332,103 @@
         <v>5392</v>
       </c>
       <c r="H858" s="6" t="s">
-        <v>5362</v>
+        <v>5393</v>
       </c>
     </row>
     <row r="859">
       <c r="B859" s="5" t="s">
-        <v>5393</v>
+        <v>5394</v>
       </c>
       <c r="C859" s="5" t="s">
-        <v>5394</v>
+        <v>5395</v>
       </c>
       <c r="D859" s="5" t="s">
-        <v>5395</v>
+        <v>5396</v>
       </c>
       <c r="E859" s="5" t="s">
-        <v>5396</v>
+        <v>5397</v>
       </c>
       <c r="F859" s="5" t="s">
-        <v>5397</v>
+        <v>5398</v>
       </c>
       <c r="G859" s="5" t="s">
-        <v>5398</v>
+        <v>5399</v>
       </c>
       <c r="H859" s="5" t="s">
-        <v>5399</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="860">
       <c r="B860" s="6" t="s">
-        <v>5400</v>
+        <v>5401</v>
       </c>
       <c r="C860" s="6" t="s">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="D860" s="6" t="s">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="E860" s="6" t="s">
-        <v>5403</v>
+        <v>5404</v>
       </c>
       <c r="F860" s="6" t="s">
-        <v>5404</v>
+        <v>5405</v>
       </c>
       <c r="G860" s="6" t="s">
-        <v>5404</v>
+        <v>5406</v>
       </c>
       <c r="H860" s="6" t="s">
-        <v>5405</v>
+        <v>5376</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="B861" s="5" t="s">
+        <v>5407</v>
+      </c>
+      <c r="C861" s="5" t="s">
+        <v>5408</v>
+      </c>
+      <c r="D861" s="5" t="s">
+        <v>5409</v>
+      </c>
+      <c r="E861" s="5" t="s">
+        <v>5410</v>
+      </c>
+      <c r="F861" s="5" t="s">
+        <v>5411</v>
+      </c>
+      <c r="G861" s="5" t="s">
+        <v>5412</v>
+      </c>
+      <c r="H861" s="5" t="s">
+        <v>5413</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="B862" s="6" t="s">
+        <v>5414</v>
+      </c>
+      <c r="C862" s="6" t="s">
+        <v>5415</v>
+      </c>
+      <c r="D862" s="6" t="s">
+        <v>5416</v>
+      </c>
+      <c r="E862" s="6" t="s">
+        <v>5417</v>
+      </c>
+      <c r="F862" s="6" t="s">
+        <v>5418</v>
+      </c>
+      <c r="G862" s="6" t="s">
+        <v>5418</v>
+      </c>
+      <c r="H862" s="6" t="s">
+        <v>5419</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H860"/>
+  <autoFilter ref="B2:H862"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36359,10 +36447,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5406</v>
+        <v>5420</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5407</v>
+        <v>5421</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36373,16 +36461,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5408</v>
+        <v>5422</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5409</v>
+        <v>5423</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5410</v>
+        <v>5424</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5411</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="3">
@@ -36390,16 +36478,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5412</v>
+        <v>5426</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5413</v>
+        <v>5427</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5414</v>
+        <v>5428</v>
       </c>
     </row>
     <row r="4">
@@ -36410,24 +36498,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5415</v>
+        <v>5429</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5416</v>
+        <v>5430</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5417</v>
+        <v>5431</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5418</v>
+        <v>5432</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5419</v>
+        <v>5433</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36435,13 +36523,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5420</v>
+        <v>5434</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5421</v>
+        <v>5435</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36449,13 +36537,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5422</v>
+        <v>5436</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5423</v>
+        <v>5437</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36463,13 +36551,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5424</v>
+        <v>5438</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5425</v>
+        <v>5439</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36477,13 +36565,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5426</v>
+        <v>5440</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5427</v>
+        <v>5441</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36491,13 +36579,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5428</v>
+        <v>5442</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5429</v>
+        <v>5443</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36505,13 +36593,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5430</v>
+        <v>5444</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5431</v>
+        <v>5445</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36519,13 +36607,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5432</v>
+        <v>5446</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5433</v>
+        <v>5447</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36533,13 +36621,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5434</v>
+        <v>5448</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5435</v>
+        <v>5449</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36547,13 +36635,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5436</v>
+        <v>5450</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5437</v>
+        <v>5451</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36567,7 +36655,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5438</v>
+        <v>5452</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36575,13 +36663,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5439</v>
+        <v>5453</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5440</v>
+        <v>5454</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36589,13 +36677,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5441</v>
+        <v>5455</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5442</v>
+        <v>5456</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36603,13 +36691,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5443</v>
+        <v>5457</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5444</v>
+        <v>5458</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36617,13 +36705,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5445</v>
+        <v>5459</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5446</v>
+        <v>5460</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36631,13 +36719,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5447</v>
+        <v>5461</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5448</v>
+        <v>5462</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36645,13 +36733,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5449</v>
+        <v>5463</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5450</v>
+        <v>5464</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36659,13 +36747,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5451</v>
+        <v>5465</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5452</v>
+        <v>5466</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36673,13 +36761,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5453</v>
+        <v>5467</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5454</v>
+        <v>5468</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36687,13 +36775,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5455</v>
+        <v>5469</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5456</v>
+        <v>5470</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$862]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$863]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6097" uniqueCount="5471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6104" uniqueCount="5478">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -15056,6 +15056,27 @@
   </si>
   <si>
     <t xml:space="preserve">Mischen, Shop, Packs und Auslöser gehen alle daraus hervor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.seed.locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판이 도는 동안에는 바꿀 수 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It cannot change while a run is going</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゲーム中は変えられません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">游戏进行中无法更改</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遊戲進行中無法更改</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicht änderbar während eines Durchgangs</t>
   </si>
   <si>
     <t xml:space="preserve">ui.button.random</t>
@@ -16629,7 +16650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H862"/>
+  <dimension ref="A1:H863"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -34983,91 +35004,91 @@
         <v>5027</v>
       </c>
       <c r="C800" s="6" t="s">
-        <v>3021</v>
+        <v>5028</v>
       </c>
       <c r="D800" s="6" t="s">
-        <v>5028</v>
+        <v>5029</v>
       </c>
       <c r="E800" s="6" t="s">
-        <v>3023</v>
+        <v>5030</v>
       </c>
       <c r="F800" s="6" t="s">
-        <v>5029</v>
+        <v>5031</v>
       </c>
       <c r="G800" s="6" t="s">
-        <v>5030</v>
+        <v>5032</v>
       </c>
       <c r="H800" s="6" t="s">
-        <v>5031</v>
+        <v>5033</v>
       </c>
     </row>
     <row r="801">
       <c r="B801" s="5" t="s">
-        <v>5032</v>
+        <v>5034</v>
       </c>
       <c r="C801" s="5" t="s">
-        <v>3014</v>
+        <v>3021</v>
       </c>
       <c r="D801" s="5" t="s">
-        <v>5033</v>
+        <v>5035</v>
       </c>
       <c r="E801" s="5" t="s">
-        <v>3016</v>
+        <v>3023</v>
       </c>
       <c r="F801" s="5" t="s">
-        <v>5034</v>
+        <v>5036</v>
       </c>
       <c r="G801" s="5" t="s">
-        <v>5035</v>
+        <v>5037</v>
       </c>
       <c r="H801" s="5" t="s">
-        <v>5036</v>
+        <v>5038</v>
       </c>
     </row>
     <row r="802">
       <c r="B802" s="6" t="s">
-        <v>5037</v>
+        <v>5039</v>
       </c>
       <c r="C802" s="6" t="s">
-        <v>5038</v>
+        <v>3014</v>
       </c>
       <c r="D802" s="6" t="s">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="E802" s="6" t="s">
-        <v>5040</v>
+        <v>3016</v>
       </c>
       <c r="F802" s="6" t="s">
         <v>5041</v>
       </c>
       <c r="G802" s="6" t="s">
-        <v>5040</v>
+        <v>5042</v>
       </c>
       <c r="H802" s="6" t="s">
-        <v>4443</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="803">
       <c r="B803" s="5" t="s">
-        <v>5042</v>
+        <v>5044</v>
       </c>
       <c r="C803" s="5" t="s">
-        <v>5043</v>
+        <v>5045</v>
       </c>
       <c r="D803" s="5" t="s">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E803" s="5" t="s">
-        <v>5045</v>
+        <v>5047</v>
       </c>
       <c r="F803" s="5" t="s">
-        <v>5046</v>
+        <v>5048</v>
       </c>
       <c r="G803" s="5" t="s">
         <v>5047</v>
       </c>
       <c r="H803" s="5" t="s">
-        <v>5048</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="804">
@@ -35087,27 +35108,27 @@
         <v>5053</v>
       </c>
       <c r="G804" s="6" t="s">
-        <v>5053</v>
+        <v>5054</v>
       </c>
       <c r="H804" s="6" t="s">
-        <v>5054</v>
+        <v>5055</v>
       </c>
     </row>
     <row r="805">
       <c r="B805" s="5" t="s">
-        <v>5055</v>
+        <v>5056</v>
       </c>
       <c r="C805" s="5" t="s">
-        <v>5056</v>
+        <v>5057</v>
       </c>
       <c r="D805" s="5" t="s">
-        <v>5057</v>
+        <v>5058</v>
       </c>
       <c r="E805" s="5" t="s">
-        <v>5058</v>
+        <v>5059</v>
       </c>
       <c r="F805" s="5" t="s">
-        <v>5059</v>
+        <v>5060</v>
       </c>
       <c r="G805" s="5" t="s">
         <v>5060</v>
@@ -35222,30 +35243,30 @@
         <v>5093</v>
       </c>
       <c r="F810" s="6" t="s">
-        <v>5093</v>
+        <v>5094</v>
       </c>
       <c r="G810" s="6" t="s">
-        <v>5093</v>
+        <v>5095</v>
       </c>
       <c r="H810" s="6" t="s">
-        <v>5094</v>
+        <v>5096</v>
       </c>
     </row>
     <row r="811">
       <c r="B811" s="5" t="s">
-        <v>5095</v>
+        <v>5097</v>
       </c>
       <c r="C811" s="5" t="s">
-        <v>5096</v>
+        <v>5098</v>
       </c>
       <c r="D811" s="5" t="s">
-        <v>5097</v>
+        <v>5099</v>
       </c>
       <c r="E811" s="5" t="s">
-        <v>5098</v>
+        <v>5100</v>
       </c>
       <c r="F811" s="5" t="s">
-        <v>5099</v>
+        <v>5100</v>
       </c>
       <c r="G811" s="5" t="s">
         <v>5100</v>
@@ -35317,73 +35338,73 @@
         <v>5120</v>
       </c>
       <c r="G814" s="6" t="s">
-        <v>5120</v>
+        <v>5121</v>
       </c>
       <c r="H814" s="6" t="s">
-        <v>5121</v>
+        <v>5122</v>
       </c>
     </row>
     <row r="815">
       <c r="B815" s="5" t="s">
-        <v>5122</v>
+        <v>5123</v>
       </c>
       <c r="C815" s="5" t="s">
-        <v>5123</v>
+        <v>5124</v>
       </c>
       <c r="D815" s="5" t="s">
-        <v>5124</v>
+        <v>5125</v>
       </c>
       <c r="E815" s="5" t="s">
-        <v>5125</v>
+        <v>5126</v>
       </c>
       <c r="F815" s="5" t="s">
-        <v>5126</v>
+        <v>5127</v>
       </c>
       <c r="G815" s="5" t="s">
-        <v>5126</v>
+        <v>5127</v>
       </c>
       <c r="H815" s="5" t="s">
-        <v>5127</v>
+        <v>5128</v>
       </c>
     </row>
     <row r="816">
       <c r="B816" s="6" t="s">
-        <v>5128</v>
+        <v>5129</v>
       </c>
       <c r="C816" s="6" t="s">
-        <v>5129</v>
+        <v>5130</v>
       </c>
       <c r="D816" s="6" t="s">
-        <v>5130</v>
+        <v>5131</v>
       </c>
       <c r="E816" s="6" t="s">
-        <v>5131</v>
+        <v>5132</v>
       </c>
       <c r="F816" s="6" t="s">
-        <v>5132</v>
+        <v>5133</v>
       </c>
       <c r="G816" s="6" t="s">
-        <v>5132</v>
+        <v>5133</v>
       </c>
       <c r="H816" s="6" t="s">
-        <v>5133</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="817">
       <c r="B817" s="5" t="s">
-        <v>5134</v>
+        <v>5135</v>
       </c>
       <c r="C817" s="5" t="s">
-        <v>5135</v>
+        <v>5136</v>
       </c>
       <c r="D817" s="5" t="s">
-        <v>5136</v>
+        <v>5137</v>
       </c>
       <c r="E817" s="5" t="s">
-        <v>5137</v>
+        <v>5138</v>
       </c>
       <c r="F817" s="5" t="s">
-        <v>5138</v>
+        <v>5139</v>
       </c>
       <c r="G817" s="5" t="s">
         <v>5139</v>
@@ -35501,56 +35522,56 @@
         <v>5173</v>
       </c>
       <c r="G822" s="6" t="s">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="H822" s="6" t="s">
-        <v>5174</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="823">
       <c r="B823" s="5" t="s">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="C823" s="5" t="s">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D823" s="5" t="s">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="E823" s="5" t="s">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="F823" s="5" t="s">
-        <v>5178</v>
+        <v>5180</v>
       </c>
       <c r="G823" s="5" t="s">
-        <v>5178</v>
+        <v>5180</v>
       </c>
       <c r="H823" s="5" t="s">
-        <v>5177</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="824">
       <c r="B824" s="6" t="s">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="C824" s="6" t="s">
-        <v>5180</v>
+        <v>5183</v>
       </c>
       <c r="D824" s="6" t="s">
-        <v>5181</v>
+        <v>5184</v>
       </c>
       <c r="E824" s="6" t="s">
-        <v>5182</v>
+        <v>5185</v>
       </c>
       <c r="F824" s="6" t="s">
-        <v>5183</v>
+        <v>5185</v>
       </c>
       <c r="G824" s="6" t="s">
+        <v>5185</v>
+      </c>
+      <c r="H824" s="6" t="s">
         <v>5184</v>
-      </c>
-      <c r="H824" s="6" t="s">
-        <v>5185</v>
       </c>
     </row>
     <row r="825">
@@ -35607,42 +35628,42 @@
         <v>5201</v>
       </c>
       <c r="D827" s="5" t="s">
-        <v>5177</v>
+        <v>5202</v>
       </c>
       <c r="E827" s="5" t="s">
-        <v>5202</v>
+        <v>5203</v>
       </c>
       <c r="F827" s="5" t="s">
-        <v>5203</v>
+        <v>5204</v>
       </c>
       <c r="G827" s="5" t="s">
-        <v>5203</v>
+        <v>5205</v>
       </c>
       <c r="H827" s="5" t="s">
-        <v>5177</v>
+        <v>5206</v>
       </c>
     </row>
     <row r="828">
       <c r="B828" s="6" t="s">
-        <v>5204</v>
+        <v>5207</v>
       </c>
       <c r="C828" s="6" t="s">
-        <v>5205</v>
+        <v>5208</v>
       </c>
       <c r="D828" s="6" t="s">
-        <v>5206</v>
+        <v>5184</v>
       </c>
       <c r="E828" s="6" t="s">
-        <v>5207</v>
+        <v>5209</v>
       </c>
       <c r="F828" s="6" t="s">
-        <v>5208</v>
+        <v>5210</v>
       </c>
       <c r="G828" s="6" t="s">
-        <v>5209</v>
+        <v>5210</v>
       </c>
       <c r="H828" s="6" t="s">
-        <v>5210</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="829">
@@ -35665,30 +35686,30 @@
         <v>5216</v>
       </c>
       <c r="H829" s="5" t="s">
-        <v>5213</v>
+        <v>5217</v>
       </c>
     </row>
     <row r="830">
       <c r="B830" s="6" t="s">
-        <v>5217</v>
+        <v>5218</v>
       </c>
       <c r="C830" s="6" t="s">
-        <v>5218</v>
+        <v>5219</v>
       </c>
       <c r="D830" s="6" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="E830" s="6" t="s">
+        <v>5221</v>
+      </c>
+      <c r="F830" s="6" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G830" s="6" t="s">
+        <v>5223</v>
+      </c>
+      <c r="H830" s="6" t="s">
         <v>5220</v>
-      </c>
-      <c r="F830" s="6" t="s">
-        <v>5221</v>
-      </c>
-      <c r="G830" s="6" t="s">
-        <v>5222</v>
-      </c>
-      <c r="H830" s="6" t="s">
-        <v>5223</v>
       </c>
     </row>
     <row r="831">
@@ -35777,27 +35798,27 @@
         <v>5249</v>
       </c>
       <c r="G834" s="6" t="s">
-        <v>5249</v>
+        <v>5250</v>
       </c>
       <c r="H834" s="6" t="s">
-        <v>5250</v>
+        <v>5251</v>
       </c>
     </row>
     <row r="835">
       <c r="B835" s="5" t="s">
-        <v>5251</v>
+        <v>5252</v>
       </c>
       <c r="C835" s="5" t="s">
-        <v>5252</v>
+        <v>5253</v>
       </c>
       <c r="D835" s="5" t="s">
-        <v>5253</v>
+        <v>5254</v>
       </c>
       <c r="E835" s="5" t="s">
-        <v>5254</v>
+        <v>5255</v>
       </c>
       <c r="F835" s="5" t="s">
-        <v>5255</v>
+        <v>5256</v>
       </c>
       <c r="G835" s="5" t="s">
         <v>5256</v>
@@ -35823,27 +35844,27 @@
         <v>5262</v>
       </c>
       <c r="G836" s="6" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="H836" s="6" t="s">
-        <v>5263</v>
+        <v>5264</v>
       </c>
     </row>
     <row r="837">
       <c r="B837" s="5" t="s">
-        <v>5264</v>
+        <v>5265</v>
       </c>
       <c r="C837" s="5" t="s">
-        <v>5265</v>
+        <v>5266</v>
       </c>
       <c r="D837" s="5" t="s">
-        <v>5266</v>
+        <v>5267</v>
       </c>
       <c r="E837" s="5" t="s">
-        <v>5267</v>
+        <v>5268</v>
       </c>
       <c r="F837" s="5" t="s">
-        <v>5268</v>
+        <v>5269</v>
       </c>
       <c r="G837" s="5" t="s">
         <v>5269</v>
@@ -35869,56 +35890,56 @@
         <v>5275</v>
       </c>
       <c r="G838" s="6" t="s">
-        <v>5274</v>
+        <v>5276</v>
       </c>
       <c r="H838" s="6" t="s">
-        <v>5276</v>
+        <v>5277</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
-        <v>5277</v>
+        <v>5278</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>5278</v>
+        <v>5279</v>
       </c>
       <c r="D839" s="5" t="s">
-        <v>5279</v>
+        <v>5280</v>
       </c>
       <c r="E839" s="5" t="s">
-        <v>5280</v>
+        <v>5281</v>
       </c>
       <c r="F839" s="5" t="s">
-        <v>5281</v>
+        <v>5282</v>
       </c>
       <c r="G839" s="5" t="s">
         <v>5281</v>
       </c>
       <c r="H839" s="5" t="s">
-        <v>5279</v>
+        <v>5283</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
-        <v>5282</v>
+        <v>5284</v>
       </c>
       <c r="C840" s="6" t="s">
-        <v>5283</v>
+        <v>5285</v>
       </c>
       <c r="D840" s="6" t="s">
-        <v>5284</v>
+        <v>5286</v>
       </c>
       <c r="E840" s="6" t="s">
-        <v>5285</v>
+        <v>5287</v>
       </c>
       <c r="F840" s="6" t="s">
+        <v>5288</v>
+      </c>
+      <c r="G840" s="6" t="s">
+        <v>5288</v>
+      </c>
+      <c r="H840" s="6" t="s">
         <v>5286</v>
-      </c>
-      <c r="G840" s="6" t="s">
-        <v>5287</v>
-      </c>
-      <c r="H840" s="6" t="s">
-        <v>5288</v>
       </c>
     </row>
     <row r="841">
@@ -35941,30 +35962,30 @@
         <v>5294</v>
       </c>
       <c r="H841" s="5" t="s">
-        <v>5291</v>
+        <v>5295</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
-        <v>5295</v>
+        <v>5296</v>
       </c>
       <c r="C842" s="6" t="s">
-        <v>5296</v>
+        <v>5297</v>
       </c>
       <c r="D842" s="6" t="s">
-        <v>5297</v>
+        <v>5298</v>
       </c>
       <c r="E842" s="6" t="s">
+        <v>5299</v>
+      </c>
+      <c r="F842" s="6" t="s">
+        <v>5300</v>
+      </c>
+      <c r="G842" s="6" t="s">
+        <v>5301</v>
+      </c>
+      <c r="H842" s="6" t="s">
         <v>5298</v>
-      </c>
-      <c r="F842" s="6" t="s">
-        <v>5299</v>
-      </c>
-      <c r="G842" s="6" t="s">
-        <v>5300</v>
-      </c>
-      <c r="H842" s="6" t="s">
-        <v>5301</v>
       </c>
     </row>
     <row r="843">
@@ -35984,50 +36005,50 @@
         <v>5306</v>
       </c>
       <c r="G843" s="5" t="s">
-        <v>5306</v>
+        <v>5307</v>
       </c>
       <c r="H843" s="5" t="s">
-        <v>5307</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="844">
       <c r="B844" s="6" t="s">
-        <v>5308</v>
+        <v>5309</v>
       </c>
       <c r="C844" s="6" t="s">
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="D844" s="6" t="s">
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="E844" s="6" t="s">
-        <v>5311</v>
+        <v>5312</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>5312</v>
+        <v>5313</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5312</v>
+        <v>5313</v>
       </c>
       <c r="H844" s="6" t="s">
-        <v>5313</v>
+        <v>5314</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5314</v>
+        <v>5315</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>5315</v>
+        <v>5316</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5316</v>
+        <v>5317</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>5317</v>
+        <v>5318</v>
       </c>
       <c r="F845" s="5" t="s">
-        <v>5318</v>
+        <v>5319</v>
       </c>
       <c r="G845" s="5" t="s">
         <v>5319</v>
@@ -36053,27 +36074,27 @@
         <v>5325</v>
       </c>
       <c r="G846" s="6" t="s">
-        <v>5325</v>
+        <v>5326</v>
       </c>
       <c r="H846" s="6" t="s">
-        <v>5326</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
-        <v>5327</v>
+        <v>5328</v>
       </c>
       <c r="C847" s="5" t="s">
-        <v>5328</v>
+        <v>5329</v>
       </c>
       <c r="D847" s="5" t="s">
-        <v>5329</v>
+        <v>5330</v>
       </c>
       <c r="E847" s="5" t="s">
-        <v>5330</v>
+        <v>5331</v>
       </c>
       <c r="F847" s="5" t="s">
-        <v>5331</v>
+        <v>5332</v>
       </c>
       <c r="G847" s="5" t="s">
         <v>5332</v>
@@ -36099,171 +36120,171 @@
         <v>5338</v>
       </c>
       <c r="G848" s="6" t="s">
-        <v>5338</v>
+        <v>5339</v>
       </c>
       <c r="H848" s="6" t="s">
-        <v>5339</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
-        <v>5340</v>
+        <v>5341</v>
       </c>
       <c r="C849" s="5" t="s">
-        <v>5341</v>
+        <v>5342</v>
       </c>
       <c r="D849" s="5" t="s">
-        <v>5342</v>
+        <v>5343</v>
       </c>
       <c r="E849" s="5" t="s">
-        <v>5343</v>
+        <v>5344</v>
       </c>
       <c r="F849" s="5" t="s">
-        <v>5344</v>
+        <v>5345</v>
       </c>
       <c r="G849" s="5" t="s">
-        <v>5344</v>
+        <v>5345</v>
       </c>
       <c r="H849" s="5" t="s">
-        <v>5345</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
-        <v>5346</v>
+        <v>5347</v>
       </c>
       <c r="C850" s="6" t="s">
-        <v>5347</v>
+        <v>5348</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>5347</v>
+        <v>5349</v>
       </c>
       <c r="E850" s="6" t="s">
-        <v>5347</v>
+        <v>5350</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>5347</v>
+        <v>5351</v>
       </c>
       <c r="G850" s="6" t="s">
-        <v>5347</v>
+        <v>5351</v>
       </c>
       <c r="H850" s="6" t="s">
-        <v>5347</v>
+        <v>5352</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
-        <v>5348</v>
+        <v>5353</v>
       </c>
       <c r="C851" s="5" t="s">
-        <v>5349</v>
+        <v>5354</v>
       </c>
       <c r="D851" s="5" t="s">
-        <v>5350</v>
+        <v>5354</v>
       </c>
       <c r="E851" s="5" t="s">
-        <v>5351</v>
+        <v>5354</v>
       </c>
       <c r="F851" s="5" t="s">
-        <v>5352</v>
+        <v>5354</v>
       </c>
       <c r="G851" s="5" t="s">
-        <v>5352</v>
+        <v>5354</v>
       </c>
       <c r="H851" s="5" t="s">
-        <v>5350</v>
+        <v>5354</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
-        <v>5353</v>
+        <v>5355</v>
       </c>
       <c r="C852" s="6" t="s">
-        <v>5354</v>
+        <v>5356</v>
       </c>
       <c r="D852" s="6" t="s">
-        <v>5355</v>
+        <v>5357</v>
       </c>
       <c r="E852" s="6" t="s">
-        <v>5356</v>
+        <v>5358</v>
       </c>
       <c r="F852" s="6" t="s">
+        <v>5359</v>
+      </c>
+      <c r="G852" s="6" t="s">
+        <v>5359</v>
+      </c>
+      <c r="H852" s="6" t="s">
         <v>5357</v>
-      </c>
-      <c r="G852" s="6" t="s">
-        <v>5358</v>
-      </c>
-      <c r="H852" s="6" t="s">
-        <v>5355</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
-        <v>5359</v>
+        <v>5360</v>
       </c>
       <c r="C853" s="5" t="s">
-        <v>5360</v>
+        <v>5361</v>
       </c>
       <c r="D853" s="5" t="s">
-        <v>5361</v>
+        <v>5362</v>
       </c>
       <c r="E853" s="5" t="s">
+        <v>5363</v>
+      </c>
+      <c r="F853" s="5" t="s">
+        <v>5364</v>
+      </c>
+      <c r="G853" s="5" t="s">
+        <v>5365</v>
+      </c>
+      <c r="H853" s="5" t="s">
         <v>5362</v>
-      </c>
-      <c r="F853" s="5" t="s">
-        <v>5362</v>
-      </c>
-      <c r="G853" s="5" t="s">
-        <v>5362</v>
-      </c>
-      <c r="H853" s="5" t="s">
-        <v>5361</v>
       </c>
     </row>
     <row r="854">
       <c r="B854" s="6" t="s">
-        <v>5363</v>
+        <v>5366</v>
       </c>
       <c r="C854" s="6" t="s">
-        <v>5364</v>
+        <v>5367</v>
       </c>
       <c r="D854" s="6" t="s">
-        <v>5365</v>
+        <v>5368</v>
       </c>
       <c r="E854" s="6" t="s">
-        <v>5366</v>
+        <v>5369</v>
       </c>
       <c r="F854" s="6" t="s">
-        <v>5366</v>
+        <v>5369</v>
       </c>
       <c r="G854" s="6" t="s">
-        <v>5366</v>
+        <v>5369</v>
       </c>
       <c r="H854" s="6" t="s">
-        <v>5365</v>
+        <v>5368</v>
       </c>
     </row>
     <row r="855">
       <c r="B855" s="5" t="s">
-        <v>5367</v>
+        <v>5370</v>
       </c>
       <c r="C855" s="5" t="s">
-        <v>5368</v>
+        <v>5371</v>
       </c>
       <c r="D855" s="5" t="s">
-        <v>5369</v>
+        <v>5372</v>
       </c>
       <c r="E855" s="5" t="s">
-        <v>5370</v>
+        <v>5373</v>
       </c>
       <c r="F855" s="5" t="s">
-        <v>5371</v>
+        <v>5373</v>
       </c>
       <c r="G855" s="5" t="s">
+        <v>5373</v>
+      </c>
+      <c r="H855" s="5" t="s">
         <v>5372</v>
-      </c>
-      <c r="H855" s="5" t="s">
-        <v>5373</v>
       </c>
     </row>
     <row r="856">
@@ -36286,30 +36307,30 @@
         <v>5379</v>
       </c>
       <c r="H856" s="6" t="s">
-        <v>5376</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="857">
       <c r="B857" s="5" t="s">
-        <v>5380</v>
+        <v>5381</v>
       </c>
       <c r="C857" s="5" t="s">
-        <v>5381</v>
+        <v>5382</v>
       </c>
       <c r="D857" s="5" t="s">
-        <v>5382</v>
+        <v>5383</v>
       </c>
       <c r="E857" s="5" t="s">
+        <v>5384</v>
+      </c>
+      <c r="F857" s="5" t="s">
+        <v>5385</v>
+      </c>
+      <c r="G857" s="5" t="s">
+        <v>5386</v>
+      </c>
+      <c r="H857" s="5" t="s">
         <v>5383</v>
-      </c>
-      <c r="F857" s="5" t="s">
-        <v>5384</v>
-      </c>
-      <c r="G857" s="5" t="s">
-        <v>5385</v>
-      </c>
-      <c r="H857" s="5" t="s">
-        <v>5386</v>
       </c>
     </row>
     <row r="858">
@@ -36378,30 +36399,30 @@
         <v>5406</v>
       </c>
       <c r="H860" s="6" t="s">
-        <v>5376</v>
+        <v>5407</v>
       </c>
     </row>
     <row r="861">
       <c r="B861" s="5" t="s">
-        <v>5407</v>
+        <v>5408</v>
       </c>
       <c r="C861" s="5" t="s">
-        <v>5408</v>
+        <v>5409</v>
       </c>
       <c r="D861" s="5" t="s">
-        <v>5409</v>
+        <v>5410</v>
       </c>
       <c r="E861" s="5" t="s">
-        <v>5410</v>
+        <v>5411</v>
       </c>
       <c r="F861" s="5" t="s">
-        <v>5411</v>
+        <v>5412</v>
       </c>
       <c r="G861" s="5" t="s">
-        <v>5412</v>
+        <v>5413</v>
       </c>
       <c r="H861" s="5" t="s">
-        <v>5413</v>
+        <v>5383</v>
       </c>
     </row>
     <row r="862">
@@ -36421,14 +36442,37 @@
         <v>5418</v>
       </c>
       <c r="G862" s="6" t="s">
-        <v>5418</v>
+        <v>5419</v>
       </c>
       <c r="H862" s="6" t="s">
-        <v>5419</v>
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="B863" s="5" t="s">
+        <v>5421</v>
+      </c>
+      <c r="C863" s="5" t="s">
+        <v>5422</v>
+      </c>
+      <c r="D863" s="5" t="s">
+        <v>5423</v>
+      </c>
+      <c r="E863" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="F863" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="G863" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="H863" s="5" t="s">
+        <v>5426</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H862"/>
+  <autoFilter ref="B2:H863"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36447,10 +36491,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5420</v>
+        <v>5427</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5421</v>
+        <v>5428</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36461,16 +36505,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5422</v>
+        <v>5429</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5423</v>
+        <v>5430</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5424</v>
+        <v>5431</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5425</v>
+        <v>5432</v>
       </c>
     </row>
     <row r="3">
@@ -36478,16 +36522,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5426</v>
+        <v>5433</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5427</v>
+        <v>5434</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5428</v>
+        <v>5435</v>
       </c>
     </row>
     <row r="4">
@@ -36498,24 +36542,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5429</v>
+        <v>5436</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5430</v>
+        <v>5437</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5431</v>
+        <v>5438</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5432</v>
+        <v>5439</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5433</v>
+        <v>5440</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36523,13 +36567,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5434</v>
+        <v>5441</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5435</v>
+        <v>5442</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36537,13 +36581,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5436</v>
+        <v>5443</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5437</v>
+        <v>5444</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36551,13 +36595,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5438</v>
+        <v>5445</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5439</v>
+        <v>5446</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36565,13 +36609,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5440</v>
+        <v>5447</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5441</v>
+        <v>5448</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36579,13 +36623,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5443</v>
+        <v>5450</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36593,13 +36637,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5444</v>
+        <v>5451</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5445</v>
+        <v>5452</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36607,13 +36651,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5446</v>
+        <v>5453</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5447</v>
+        <v>5454</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36621,13 +36665,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5448</v>
+        <v>5455</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5449</v>
+        <v>5456</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36635,13 +36679,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5450</v>
+        <v>5457</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5451</v>
+        <v>5458</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36655,7 +36699,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5452</v>
+        <v>5459</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36663,13 +36707,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5453</v>
+        <v>5460</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5454</v>
+        <v>5461</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36677,13 +36721,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5455</v>
+        <v>5462</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5456</v>
+        <v>5463</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36691,13 +36735,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5457</v>
+        <v>5464</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5458</v>
+        <v>5465</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36705,13 +36749,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5459</v>
+        <v>5466</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5460</v>
+        <v>5467</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36719,13 +36763,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5461</v>
+        <v>5468</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5462</v>
+        <v>5469</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36733,13 +36777,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5463</v>
+        <v>5470</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5464</v>
+        <v>5471</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36747,13 +36791,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5465</v>
+        <v>5472</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5466</v>
+        <v>5473</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36761,13 +36805,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5467</v>
+        <v>5474</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5468</v>
+        <v>5475</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36775,13 +36819,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5469</v>
+        <v>5476</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5470</v>
+        <v>5477</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$863]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$864]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6104" uniqueCount="5478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6111" uniqueCount="5485">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -12938,6 +12938,27 @@
   </si>
   <si>
     <t xml:space="preserve">Neuer Lauf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.to_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">타이틀로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title Screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイトルへ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返回标题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返回標題</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zum Titel</t>
   </si>
   <si>
     <t xml:space="preserve">ui.button.play</t>
@@ -16650,7 +16671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H863"/>
+  <dimension ref="A1:H864"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -32086,36 +32107,36 @@
         <v>4308</v>
       </c>
       <c r="D673" s="5" t="s">
-        <v>4281</v>
+        <v>4309</v>
       </c>
       <c r="E673" s="5" t="s">
-        <v>4309</v>
+        <v>4310</v>
       </c>
       <c r="F673" s="5" t="s">
-        <v>4310</v>
+        <v>4311</v>
       </c>
       <c r="G673" s="5" t="s">
-        <v>4310</v>
+        <v>4312</v>
       </c>
       <c r="H673" s="5" t="s">
-        <v>4311</v>
+        <v>4313</v>
       </c>
     </row>
     <row r="674">
       <c r="B674" s="6" t="s">
-        <v>4312</v>
+        <v>4314</v>
       </c>
       <c r="C674" s="6" t="s">
-        <v>4313</v>
+        <v>4315</v>
       </c>
       <c r="D674" s="6" t="s">
-        <v>4314</v>
+        <v>4281</v>
       </c>
       <c r="E674" s="6" t="s">
-        <v>4315</v>
+        <v>4316</v>
       </c>
       <c r="F674" s="6" t="s">
-        <v>4316</v>
+        <v>4317</v>
       </c>
       <c r="G674" s="6" t="s">
         <v>4317</v>
@@ -32187,102 +32208,102 @@
         <v>4337</v>
       </c>
       <c r="G677" s="5" t="s">
-        <v>4337</v>
+        <v>4338</v>
       </c>
       <c r="H677" s="5" t="s">
-        <v>4338</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="678">
       <c r="B678" s="6" t="s">
-        <v>4339</v>
+        <v>4340</v>
       </c>
       <c r="C678" s="6" t="s">
-        <v>4340</v>
+        <v>4341</v>
       </c>
       <c r="D678" s="6" t="s">
-        <v>4341</v>
+        <v>4342</v>
       </c>
       <c r="E678" s="6" t="s">
-        <v>4342</v>
+        <v>4343</v>
       </c>
       <c r="F678" s="6" t="s">
-        <v>3744</v>
+        <v>4344</v>
       </c>
       <c r="G678" s="6" t="s">
-        <v>3744</v>
+        <v>4344</v>
       </c>
       <c r="H678" s="6" t="s">
-        <v>4343</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="679">
       <c r="B679" s="5" t="s">
-        <v>4344</v>
+        <v>4346</v>
       </c>
       <c r="C679" s="5" t="s">
-        <v>4345</v>
+        <v>4347</v>
       </c>
       <c r="D679" s="5" t="s">
-        <v>4346</v>
+        <v>4348</v>
       </c>
       <c r="E679" s="5" t="s">
-        <v>4347</v>
+        <v>4349</v>
       </c>
       <c r="F679" s="5" t="s">
-        <v>4348</v>
+        <v>3744</v>
       </c>
       <c r="G679" s="5" t="s">
-        <v>4348</v>
+        <v>3744</v>
       </c>
       <c r="H679" s="5" t="s">
-        <v>4349</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="680">
       <c r="B680" s="6" t="s">
-        <v>4350</v>
+        <v>4351</v>
       </c>
       <c r="C680" s="6" t="s">
-        <v>4351</v>
+        <v>4352</v>
       </c>
       <c r="D680" s="6" t="s">
-        <v>4352</v>
+        <v>4353</v>
       </c>
       <c r="E680" s="6" t="s">
-        <v>4353</v>
+        <v>4354</v>
       </c>
       <c r="F680" s="6" t="s">
-        <v>4354</v>
+        <v>4355</v>
       </c>
       <c r="G680" s="6" t="s">
         <v>4355</v>
       </c>
       <c r="H680" s="6" t="s">
-        <v>4352</v>
+        <v>4356</v>
       </c>
     </row>
     <row r="681">
       <c r="B681" s="5" t="s">
-        <v>4356</v>
+        <v>4357</v>
       </c>
       <c r="C681" s="5" t="s">
-        <v>4357</v>
+        <v>4358</v>
       </c>
       <c r="D681" s="5" t="s">
-        <v>4358</v>
+        <v>4359</v>
       </c>
       <c r="E681" s="5" t="s">
+        <v>4360</v>
+      </c>
+      <c r="F681" s="5" t="s">
+        <v>4361</v>
+      </c>
+      <c r="G681" s="5" t="s">
+        <v>4362</v>
+      </c>
+      <c r="H681" s="5" t="s">
         <v>4359</v>
-      </c>
-      <c r="F681" s="5" t="s">
-        <v>4360</v>
-      </c>
-      <c r="G681" s="5" t="s">
-        <v>4361</v>
-      </c>
-      <c r="H681" s="5" t="s">
-        <v>4362</v>
       </c>
     </row>
     <row r="682">
@@ -32325,76 +32346,76 @@
         <v>4374</v>
       </c>
       <c r="G683" s="5" t="s">
-        <v>4374</v>
+        <v>4375</v>
       </c>
       <c r="H683" s="5" t="s">
-        <v>4375</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="684">
       <c r="B684" s="6" t="s">
-        <v>4376</v>
+        <v>4377</v>
       </c>
       <c r="C684" s="6" t="s">
-        <v>4377</v>
+        <v>4378</v>
       </c>
       <c r="D684" s="6" t="s">
-        <v>4378</v>
+        <v>4379</v>
       </c>
       <c r="E684" s="6" t="s">
-        <v>4379</v>
+        <v>4380</v>
       </c>
       <c r="F684" s="6" t="s">
-        <v>4380</v>
+        <v>4381</v>
       </c>
       <c r="G684" s="6" t="s">
-        <v>4380</v>
+        <v>4381</v>
       </c>
       <c r="H684" s="6" t="s">
-        <v>4381</v>
+        <v>4382</v>
       </c>
     </row>
     <row r="685">
       <c r="B685" s="5" t="s">
-        <v>4382</v>
+        <v>4383</v>
       </c>
       <c r="C685" s="5" t="s">
-        <v>4383</v>
+        <v>4384</v>
       </c>
       <c r="D685" s="5" t="s">
-        <v>4384</v>
+        <v>4385</v>
       </c>
       <c r="E685" s="5" t="s">
-        <v>2250</v>
+        <v>4386</v>
       </c>
       <c r="F685" s="5" t="s">
-        <v>2251</v>
+        <v>4387</v>
       </c>
       <c r="G685" s="5" t="s">
-        <v>2252</v>
+        <v>4387</v>
       </c>
       <c r="H685" s="5" t="s">
-        <v>4385</v>
+        <v>4388</v>
       </c>
     </row>
     <row r="686">
       <c r="B686" s="6" t="s">
-        <v>4386</v>
+        <v>4389</v>
       </c>
       <c r="C686" s="6" t="s">
-        <v>4387</v>
+        <v>4390</v>
       </c>
       <c r="D686" s="6" t="s">
-        <v>4388</v>
+        <v>4391</v>
       </c>
       <c r="E686" s="6" t="s">
-        <v>4389</v>
+        <v>2250</v>
       </c>
       <c r="F686" s="6" t="s">
-        <v>4390</v>
+        <v>2251</v>
       </c>
       <c r="G686" s="6" t="s">
-        <v>4391</v>
+        <v>2252</v>
       </c>
       <c r="H686" s="6" t="s">
         <v>4392</v>
@@ -32440,217 +32461,217 @@
         <v>4404</v>
       </c>
       <c r="G688" s="6" t="s">
-        <v>4404</v>
+        <v>4405</v>
       </c>
       <c r="H688" s="6" t="s">
-        <v>4405</v>
+        <v>4406</v>
       </c>
     </row>
     <row r="689">
       <c r="B689" s="5" t="s">
-        <v>4406</v>
+        <v>4407</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>3495</v>
+        <v>4408</v>
       </c>
       <c r="D689" s="5" t="s">
-        <v>3500</v>
+        <v>4409</v>
       </c>
       <c r="E689" s="5" t="s">
-        <v>3497</v>
+        <v>4410</v>
       </c>
       <c r="F689" s="5" t="s">
-        <v>3498</v>
+        <v>4411</v>
       </c>
       <c r="G689" s="5" t="s">
-        <v>3499</v>
+        <v>4411</v>
       </c>
       <c r="H689" s="5" t="s">
-        <v>3500</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="690">
       <c r="B690" s="6" t="s">
-        <v>4407</v>
+        <v>4413</v>
       </c>
       <c r="C690" s="6" t="s">
-        <v>2045</v>
+        <v>3495</v>
       </c>
       <c r="D690" s="6" t="s">
-        <v>2046</v>
+        <v>3500</v>
       </c>
       <c r="E690" s="6" t="s">
-        <v>2048</v>
+        <v>3497</v>
       </c>
       <c r="F690" s="6" t="s">
-        <v>2048</v>
+        <v>3498</v>
       </c>
       <c r="G690" s="6" t="s">
-        <v>2048</v>
+        <v>3499</v>
       </c>
       <c r="H690" s="6" t="s">
-        <v>2046</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="691">
       <c r="B691" s="5" t="s">
-        <v>4408</v>
+        <v>4414</v>
       </c>
       <c r="C691" s="5" t="s">
-        <v>4409</v>
+        <v>2045</v>
       </c>
       <c r="D691" s="5" t="s">
-        <v>4410</v>
+        <v>2046</v>
       </c>
       <c r="E691" s="5" t="s">
-        <v>4411</v>
+        <v>2048</v>
       </c>
       <c r="F691" s="5" t="s">
-        <v>4412</v>
+        <v>2048</v>
       </c>
       <c r="G691" s="5" t="s">
-        <v>4413</v>
+        <v>2048</v>
       </c>
       <c r="H691" s="5" t="s">
-        <v>4410</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="692">
       <c r="B692" s="6" t="s">
-        <v>4414</v>
+        <v>4415</v>
       </c>
       <c r="C692" s="6" t="s">
-        <v>4415</v>
+        <v>4416</v>
       </c>
       <c r="D692" s="6" t="s">
-        <v>4416</v>
+        <v>4417</v>
       </c>
       <c r="E692" s="6" t="s">
+        <v>4418</v>
+      </c>
+      <c r="F692" s="6" t="s">
+        <v>4419</v>
+      </c>
+      <c r="G692" s="6" t="s">
+        <v>4420</v>
+      </c>
+      <c r="H692" s="6" t="s">
         <v>4417</v>
-      </c>
-      <c r="F692" s="6" t="s">
-        <v>4417</v>
-      </c>
-      <c r="G692" s="6" t="s">
-        <v>4417</v>
-      </c>
-      <c r="H692" s="6" t="s">
-        <v>4416</v>
       </c>
     </row>
     <row r="693">
       <c r="B693" s="5" t="s">
-        <v>4418</v>
+        <v>4421</v>
       </c>
       <c r="C693" s="5" t="s">
-        <v>4419</v>
+        <v>4422</v>
       </c>
       <c r="D693" s="5" t="s">
-        <v>4341</v>
+        <v>4423</v>
       </c>
       <c r="E693" s="5" t="s">
-        <v>4420</v>
+        <v>4424</v>
       </c>
       <c r="F693" s="5" t="s">
-        <v>4310</v>
+        <v>4424</v>
       </c>
       <c r="G693" s="5" t="s">
-        <v>4310</v>
+        <v>4424</v>
       </c>
       <c r="H693" s="5" t="s">
-        <v>4421</v>
+        <v>4423</v>
       </c>
     </row>
     <row r="694">
       <c r="B694" s="6" t="s">
-        <v>4422</v>
+        <v>4425</v>
       </c>
       <c r="C694" s="6" t="s">
-        <v>4423</v>
+        <v>4426</v>
       </c>
       <c r="D694" s="6" t="s">
-        <v>4424</v>
+        <v>4348</v>
       </c>
       <c r="E694" s="6" t="s">
-        <v>4425</v>
+        <v>4427</v>
       </c>
       <c r="F694" s="6" t="s">
-        <v>4316</v>
+        <v>4317</v>
       </c>
       <c r="G694" s="6" t="s">
         <v>4317</v>
       </c>
       <c r="H694" s="6" t="s">
-        <v>4426</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="695">
       <c r="B695" s="5" t="s">
-        <v>4427</v>
+        <v>4429</v>
       </c>
       <c r="C695" s="5" t="s">
-        <v>3510</v>
+        <v>4430</v>
       </c>
       <c r="D695" s="5" t="s">
-        <v>4428</v>
+        <v>4431</v>
       </c>
       <c r="E695" s="5" t="s">
-        <v>3512</v>
+        <v>4432</v>
       </c>
       <c r="F695" s="5" t="s">
-        <v>3513</v>
+        <v>4323</v>
       </c>
       <c r="G695" s="5" t="s">
-        <v>3514</v>
+        <v>4324</v>
       </c>
       <c r="H695" s="5" t="s">
-        <v>3515</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="696">
       <c r="B696" s="6" t="s">
-        <v>4429</v>
+        <v>4434</v>
       </c>
       <c r="C696" s="6" t="s">
-        <v>4081</v>
+        <v>3510</v>
       </c>
       <c r="D696" s="6" t="s">
-        <v>4082</v>
+        <v>4435</v>
       </c>
       <c r="E696" s="6" t="s">
-        <v>4083</v>
+        <v>3512</v>
       </c>
       <c r="F696" s="6" t="s">
-        <v>4084</v>
+        <v>3513</v>
       </c>
       <c r="G696" s="6" t="s">
-        <v>4084</v>
+        <v>3514</v>
       </c>
       <c r="H696" s="6" t="s">
-        <v>4082</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="697">
       <c r="B697" s="5" t="s">
-        <v>4430</v>
+        <v>4436</v>
       </c>
       <c r="C697" s="5" t="s">
-        <v>4431</v>
+        <v>4081</v>
       </c>
       <c r="D697" s="5" t="s">
-        <v>4432</v>
+        <v>4082</v>
       </c>
       <c r="E697" s="5" t="s">
-        <v>4433</v>
+        <v>4083</v>
       </c>
       <c r="F697" s="5" t="s">
-        <v>4434</v>
+        <v>4084</v>
       </c>
       <c r="G697" s="5" t="s">
-        <v>4435</v>
+        <v>4084</v>
       </c>
       <c r="H697" s="5" t="s">
-        <v>4436</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="698">
@@ -32690,33 +32711,33 @@
         <v>4447</v>
       </c>
       <c r="F699" s="5" t="s">
-        <v>2042</v>
+        <v>4448</v>
       </c>
       <c r="G699" s="5" t="s">
-        <v>2043</v>
+        <v>4449</v>
       </c>
       <c r="H699" s="5" t="s">
-        <v>4448</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="700">
       <c r="B700" s="6" t="s">
-        <v>4449</v>
+        <v>4451</v>
       </c>
       <c r="C700" s="6" t="s">
-        <v>4450</v>
+        <v>4452</v>
       </c>
       <c r="D700" s="6" t="s">
-        <v>4451</v>
+        <v>4453</v>
       </c>
       <c r="E700" s="6" t="s">
-        <v>4452</v>
+        <v>4454</v>
       </c>
       <c r="F700" s="6" t="s">
-        <v>4453</v>
+        <v>2042</v>
       </c>
       <c r="G700" s="6" t="s">
-        <v>4454</v>
+        <v>2043</v>
       </c>
       <c r="H700" s="6" t="s">
         <v>4455</v>
@@ -32785,30 +32806,30 @@
         <v>4474</v>
       </c>
       <c r="G703" s="5" t="s">
-        <v>4473</v>
+        <v>4475</v>
       </c>
       <c r="H703" s="5" t="s">
-        <v>4475</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="704">
       <c r="B704" s="6" t="s">
-        <v>4476</v>
+        <v>4477</v>
       </c>
       <c r="C704" s="6" t="s">
-        <v>4477</v>
+        <v>4478</v>
       </c>
       <c r="D704" s="6" t="s">
-        <v>4478</v>
+        <v>4479</v>
       </c>
       <c r="E704" s="6" t="s">
-        <v>4479</v>
+        <v>4480</v>
       </c>
       <c r="F704" s="6" t="s">
+        <v>4481</v>
+      </c>
+      <c r="G704" s="6" t="s">
         <v>4480</v>
-      </c>
-      <c r="G704" s="6" t="s">
-        <v>4481</v>
       </c>
       <c r="H704" s="6" t="s">
         <v>4482</v>
@@ -32874,243 +32895,243 @@
         <v>4500</v>
       </c>
       <c r="F707" s="5" t="s">
-        <v>4500</v>
+        <v>4501</v>
       </c>
       <c r="G707" s="5" t="s">
-        <v>4500</v>
+        <v>4502</v>
       </c>
       <c r="H707" s="5" t="s">
-        <v>4501</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="708">
       <c r="B708" s="6" t="s">
-        <v>4502</v>
+        <v>4504</v>
       </c>
       <c r="C708" s="6" t="s">
-        <v>4503</v>
+        <v>4505</v>
       </c>
       <c r="D708" s="6" t="s">
-        <v>4504</v>
+        <v>4506</v>
       </c>
       <c r="E708" s="6" t="s">
-        <v>4505</v>
+        <v>4507</v>
       </c>
       <c r="F708" s="6" t="s">
-        <v>4506</v>
+        <v>4507</v>
       </c>
       <c r="G708" s="6" t="s">
-        <v>4506</v>
+        <v>4507</v>
       </c>
       <c r="H708" s="6" t="s">
-        <v>4507</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="709">
       <c r="B709" s="5" t="s">
-        <v>4508</v>
+        <v>4509</v>
       </c>
       <c r="C709" s="5" t="s">
-        <v>4509</v>
+        <v>4510</v>
       </c>
       <c r="D709" s="5" t="s">
-        <v>4510</v>
+        <v>4511</v>
       </c>
       <c r="E709" s="5" t="s">
-        <v>4511</v>
+        <v>4512</v>
       </c>
       <c r="F709" s="5" t="s">
-        <v>4512</v>
+        <v>4513</v>
       </c>
       <c r="G709" s="5" t="s">
-        <v>4512</v>
+        <v>4513</v>
       </c>
       <c r="H709" s="5" t="s">
-        <v>4513</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="710">
       <c r="B710" s="6" t="s">
-        <v>4514</v>
+        <v>4515</v>
       </c>
       <c r="C710" s="6" t="s">
-        <v>4515</v>
+        <v>4516</v>
       </c>
       <c r="D710" s="6" t="s">
-        <v>4516</v>
+        <v>4517</v>
       </c>
       <c r="E710" s="6" t="s">
-        <v>4517</v>
+        <v>4518</v>
       </c>
       <c r="F710" s="6" t="s">
-        <v>4516</v>
+        <v>4519</v>
       </c>
       <c r="G710" s="6" t="s">
-        <v>4516</v>
+        <v>4519</v>
       </c>
       <c r="H710" s="6" t="s">
-        <v>4516</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="711">
       <c r="B711" s="5" t="s">
-        <v>4518</v>
+        <v>4521</v>
       </c>
       <c r="C711" s="5" t="s">
-        <v>3610</v>
+        <v>4522</v>
       </c>
       <c r="D711" s="5" t="s">
-        <v>2981</v>
+        <v>4523</v>
       </c>
       <c r="E711" s="5" t="s">
-        <v>3612</v>
+        <v>4524</v>
       </c>
       <c r="F711" s="5" t="s">
-        <v>3613</v>
+        <v>4523</v>
       </c>
       <c r="G711" s="5" t="s">
-        <v>3613</v>
+        <v>4523</v>
       </c>
       <c r="H711" s="5" t="s">
-        <v>2981</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="712">
       <c r="B712" s="6" t="s">
-        <v>4519</v>
+        <v>4525</v>
       </c>
       <c r="C712" s="6" t="s">
-        <v>4520</v>
+        <v>3610</v>
       </c>
       <c r="D712" s="6" t="s">
-        <v>4521</v>
+        <v>2981</v>
       </c>
       <c r="E712" s="6" t="s">
-        <v>4522</v>
+        <v>3612</v>
       </c>
       <c r="F712" s="6" t="s">
-        <v>4522</v>
+        <v>3613</v>
       </c>
       <c r="G712" s="6" t="s">
-        <v>4522</v>
+        <v>3613</v>
       </c>
       <c r="H712" s="6" t="s">
-        <v>4523</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="713">
       <c r="B713" s="5" t="s">
-        <v>4524</v>
+        <v>4526</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>3657</v>
+        <v>4527</v>
       </c>
       <c r="D713" s="5" t="s">
-        <v>4525</v>
+        <v>4528</v>
       </c>
       <c r="E713" s="5" t="s">
-        <v>3659</v>
+        <v>4529</v>
       </c>
       <c r="F713" s="5" t="s">
-        <v>3660</v>
+        <v>4529</v>
       </c>
       <c r="G713" s="5" t="s">
-        <v>3661</v>
+        <v>4529</v>
       </c>
       <c r="H713" s="5" t="s">
-        <v>4526</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="714">
       <c r="B714" s="6" t="s">
-        <v>4527</v>
+        <v>4531</v>
       </c>
       <c r="C714" s="6" t="s">
-        <v>3651</v>
+        <v>3657</v>
       </c>
       <c r="D714" s="6" t="s">
-        <v>4528</v>
+        <v>4532</v>
       </c>
       <c r="E714" s="6" t="s">
-        <v>3653</v>
+        <v>3659</v>
       </c>
       <c r="F714" s="6" t="s">
-        <v>3654</v>
+        <v>3660</v>
       </c>
       <c r="G714" s="6" t="s">
-        <v>3654</v>
+        <v>3661</v>
       </c>
       <c r="H714" s="6" t="s">
-        <v>4529</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="715">
       <c r="B715" s="5" t="s">
-        <v>4530</v>
+        <v>4534</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>4531</v>
+        <v>3651</v>
       </c>
       <c r="D715" s="5" t="s">
-        <v>4532</v>
+        <v>4535</v>
       </c>
       <c r="E715" s="5" t="s">
-        <v>4533</v>
+        <v>3653</v>
       </c>
       <c r="F715" s="5" t="s">
-        <v>4534</v>
+        <v>3654</v>
       </c>
       <c r="G715" s="5" t="s">
-        <v>4535</v>
+        <v>3654</v>
       </c>
       <c r="H715" s="5" t="s">
-        <v>4532</v>
+        <v>4536</v>
       </c>
     </row>
     <row r="716">
       <c r="B716" s="6" t="s">
-        <v>4536</v>
+        <v>4537</v>
       </c>
       <c r="C716" s="6" t="s">
-        <v>4537</v>
+        <v>4538</v>
       </c>
       <c r="D716" s="6" t="s">
-        <v>4538</v>
+        <v>4539</v>
       </c>
       <c r="E716" s="6" t="s">
+        <v>4540</v>
+      </c>
+      <c r="F716" s="6" t="s">
+        <v>4541</v>
+      </c>
+      <c r="G716" s="6" t="s">
+        <v>4542</v>
+      </c>
+      <c r="H716" s="6" t="s">
         <v>4539</v>
-      </c>
-      <c r="F716" s="6" t="s">
-        <v>4540</v>
-      </c>
-      <c r="G716" s="6" t="s">
-        <v>4540</v>
-      </c>
-      <c r="H716" s="6" t="s">
-        <v>4538</v>
       </c>
     </row>
     <row r="717">
       <c r="B717" s="5" t="s">
-        <v>4541</v>
+        <v>4543</v>
       </c>
       <c r="C717" s="5" t="s">
-        <v>4542</v>
+        <v>4544</v>
       </c>
       <c r="D717" s="5" t="s">
-        <v>4543</v>
+        <v>4545</v>
       </c>
       <c r="E717" s="5" t="s">
-        <v>4544</v>
+        <v>4546</v>
       </c>
       <c r="F717" s="5" t="s">
+        <v>4547</v>
+      </c>
+      <c r="G717" s="5" t="s">
+        <v>4547</v>
+      </c>
+      <c r="H717" s="5" t="s">
         <v>4545</v>
-      </c>
-      <c r="G717" s="5" t="s">
-        <v>4546</v>
-      </c>
-      <c r="H717" s="5" t="s">
-        <v>4547</v>
       </c>
     </row>
     <row r="718">
@@ -33118,505 +33139,505 @@
         <v>4548</v>
       </c>
       <c r="C718" s="6" t="s">
-        <v>3749</v>
+        <v>4549</v>
       </c>
       <c r="D718" s="6" t="s">
-        <v>4549</v>
+        <v>4550</v>
       </c>
       <c r="E718" s="6" t="s">
-        <v>3751</v>
+        <v>4551</v>
       </c>
       <c r="F718" s="6" t="s">
-        <v>3752</v>
+        <v>4552</v>
       </c>
       <c r="G718" s="6" t="s">
-        <v>3752</v>
+        <v>4553</v>
       </c>
       <c r="H718" s="6" t="s">
-        <v>3753</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="719">
       <c r="B719" s="5" t="s">
-        <v>4550</v>
+        <v>4555</v>
       </c>
       <c r="C719" s="5" t="s">
-        <v>4551</v>
+        <v>3749</v>
       </c>
       <c r="D719" s="5" t="s">
-        <v>4352</v>
+        <v>4556</v>
       </c>
       <c r="E719" s="5" t="s">
-        <v>4552</v>
+        <v>3751</v>
       </c>
       <c r="F719" s="5" t="s">
-        <v>4553</v>
+        <v>3752</v>
       </c>
       <c r="G719" s="5" t="s">
-        <v>4554</v>
+        <v>3752</v>
       </c>
       <c r="H719" s="5" t="s">
-        <v>4352</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="720">
       <c r="B720" s="6" t="s">
-        <v>4555</v>
+        <v>4557</v>
       </c>
       <c r="C720" s="6" t="s">
-        <v>4556</v>
+        <v>4558</v>
       </c>
       <c r="D720" s="6" t="s">
-        <v>4557</v>
+        <v>4359</v>
       </c>
       <c r="E720" s="6" t="s">
-        <v>4558</v>
+        <v>4559</v>
       </c>
       <c r="F720" s="6" t="s">
-        <v>4559</v>
+        <v>4560</v>
       </c>
       <c r="G720" s="6" t="s">
-        <v>4559</v>
+        <v>4561</v>
       </c>
       <c r="H720" s="6" t="s">
-        <v>4557</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="721">
       <c r="B721" s="5" t="s">
-        <v>4560</v>
+        <v>4562</v>
       </c>
       <c r="C721" s="5" t="s">
-        <v>4561</v>
+        <v>4563</v>
       </c>
       <c r="D721" s="5" t="s">
-        <v>4562</v>
+        <v>4564</v>
       </c>
       <c r="E721" s="5" t="s">
-        <v>4563</v>
+        <v>4565</v>
       </c>
       <c r="F721" s="5" t="s">
+        <v>4566</v>
+      </c>
+      <c r="G721" s="5" t="s">
+        <v>4566</v>
+      </c>
+      <c r="H721" s="5" t="s">
         <v>4564</v>
-      </c>
-      <c r="G721" s="5" t="s">
-        <v>4564</v>
-      </c>
-      <c r="H721" s="5" t="s">
-        <v>4565</v>
       </c>
     </row>
     <row r="722">
       <c r="B722" s="6" t="s">
-        <v>4566</v>
+        <v>4567</v>
       </c>
       <c r="C722" s="6" t="s">
-        <v>3741</v>
+        <v>4568</v>
       </c>
       <c r="D722" s="6" t="s">
-        <v>4557</v>
+        <v>4569</v>
       </c>
       <c r="E722" s="6" t="s">
-        <v>3743</v>
+        <v>4570</v>
       </c>
       <c r="F722" s="6" t="s">
-        <v>3744</v>
+        <v>4571</v>
       </c>
       <c r="G722" s="6" t="s">
-        <v>3744</v>
+        <v>4571</v>
       </c>
       <c r="H722" s="6" t="s">
-        <v>3745</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="723">
       <c r="B723" s="5" t="s">
-        <v>4567</v>
+        <v>4573</v>
       </c>
       <c r="C723" s="5" t="s">
-        <v>3623</v>
+        <v>3741</v>
       </c>
       <c r="D723" s="5" t="s">
-        <v>4568</v>
+        <v>4564</v>
       </c>
       <c r="E723" s="5" t="s">
-        <v>3625</v>
+        <v>3743</v>
       </c>
       <c r="F723" s="5" t="s">
-        <v>3626</v>
+        <v>3744</v>
       </c>
       <c r="G723" s="5" t="s">
-        <v>3627</v>
+        <v>3744</v>
       </c>
       <c r="H723" s="5" t="s">
-        <v>4569</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="724">
       <c r="B724" s="6" t="s">
-        <v>4570</v>
+        <v>4574</v>
       </c>
       <c r="C724" s="6" t="s">
-        <v>4571</v>
+        <v>3623</v>
       </c>
       <c r="D724" s="6" t="s">
-        <v>4572</v>
+        <v>4575</v>
       </c>
       <c r="E724" s="6" t="s">
-        <v>4573</v>
+        <v>3625</v>
       </c>
       <c r="F724" s="6" t="s">
-        <v>4574</v>
+        <v>3626</v>
       </c>
       <c r="G724" s="6" t="s">
-        <v>4574</v>
+        <v>3627</v>
       </c>
       <c r="H724" s="6" t="s">
-        <v>4575</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="725">
       <c r="B725" s="5" t="s">
-        <v>4576</v>
+        <v>4577</v>
       </c>
       <c r="C725" s="5" t="s">
-        <v>4577</v>
+        <v>4578</v>
       </c>
       <c r="D725" s="5" t="s">
-        <v>4578</v>
+        <v>4579</v>
       </c>
       <c r="E725" s="5" t="s">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="F725" s="5" t="s">
-        <v>4579</v>
+        <v>4581</v>
       </c>
       <c r="G725" s="5" t="s">
-        <v>4579</v>
+        <v>4581</v>
       </c>
       <c r="H725" s="5" t="s">
-        <v>4580</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="726">
       <c r="B726" s="6" t="s">
-        <v>4581</v>
+        <v>4583</v>
       </c>
       <c r="C726" s="6" t="s">
-        <v>4582</v>
+        <v>4584</v>
       </c>
       <c r="D726" s="6" t="s">
-        <v>4583</v>
+        <v>4585</v>
       </c>
       <c r="E726" s="6" t="s">
-        <v>4584</v>
+        <v>4586</v>
       </c>
       <c r="F726" s="6" t="s">
-        <v>4585</v>
+        <v>4586</v>
       </c>
       <c r="G726" s="6" t="s">
-        <v>4585</v>
+        <v>4586</v>
       </c>
       <c r="H726" s="6" t="s">
-        <v>4586</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="727">
       <c r="B727" s="5" t="s">
-        <v>4587</v>
+        <v>4588</v>
       </c>
       <c r="C727" s="5" t="s">
-        <v>3808</v>
+        <v>4589</v>
       </c>
       <c r="D727" s="5" t="s">
-        <v>4588</v>
+        <v>4590</v>
       </c>
       <c r="E727" s="5" t="s">
-        <v>3810</v>
+        <v>4591</v>
       </c>
       <c r="F727" s="5" t="s">
-        <v>2116</v>
+        <v>4592</v>
       </c>
       <c r="G727" s="5" t="s">
-        <v>2116</v>
+        <v>4592</v>
       </c>
       <c r="H727" s="5" t="s">
-        <v>4589</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="728">
       <c r="B728" s="6" t="s">
-        <v>4590</v>
+        <v>4594</v>
       </c>
       <c r="C728" s="6" t="s">
-        <v>3813</v>
+        <v>3808</v>
       </c>
       <c r="D728" s="6" t="s">
-        <v>4591</v>
+        <v>4595</v>
       </c>
       <c r="E728" s="6" t="s">
-        <v>3815</v>
+        <v>3810</v>
       </c>
       <c r="F728" s="6" t="s">
-        <v>3816</v>
+        <v>2116</v>
       </c>
       <c r="G728" s="6" t="s">
-        <v>3817</v>
+        <v>2116</v>
       </c>
       <c r="H728" s="6" t="s">
-        <v>4592</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="729">
       <c r="B729" s="5" t="s">
-        <v>4593</v>
+        <v>4597</v>
       </c>
       <c r="C729" s="5" t="s">
-        <v>3820</v>
+        <v>3813</v>
       </c>
       <c r="D729" s="5" t="s">
-        <v>4594</v>
+        <v>4598</v>
       </c>
       <c r="E729" s="5" t="s">
-        <v>3822</v>
+        <v>3815</v>
       </c>
       <c r="F729" s="5" t="s">
-        <v>3823</v>
+        <v>3816</v>
       </c>
       <c r="G729" s="5" t="s">
-        <v>3823</v>
+        <v>3817</v>
       </c>
       <c r="H729" s="5" t="s">
-        <v>4595</v>
+        <v>4599</v>
       </c>
     </row>
     <row r="730">
       <c r="B730" s="6" t="s">
-        <v>4596</v>
+        <v>4600</v>
       </c>
       <c r="C730" s="6" t="s">
-        <v>2210</v>
+        <v>3820</v>
       </c>
       <c r="D730" s="6" t="s">
-        <v>2211</v>
+        <v>4601</v>
       </c>
       <c r="E730" s="6" t="s">
-        <v>2212</v>
+        <v>3822</v>
       </c>
       <c r="F730" s="6" t="s">
-        <v>2213</v>
+        <v>3823</v>
       </c>
       <c r="G730" s="6" t="s">
-        <v>2214</v>
+        <v>3823</v>
       </c>
       <c r="H730" s="6" t="s">
-        <v>2215</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="731">
       <c r="B731" s="5" t="s">
-        <v>4597</v>
+        <v>4603</v>
       </c>
       <c r="C731" s="5" t="s">
-        <v>2076</v>
+        <v>2210</v>
       </c>
       <c r="D731" s="5" t="s">
-        <v>2077</v>
+        <v>2211</v>
       </c>
       <c r="E731" s="5" t="s">
-        <v>2078</v>
+        <v>2212</v>
       </c>
       <c r="F731" s="5" t="s">
-        <v>2079</v>
+        <v>2213</v>
       </c>
       <c r="G731" s="5" t="s">
-        <v>2080</v>
+        <v>2214</v>
       </c>
       <c r="H731" s="5" t="s">
-        <v>2077</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="732">
       <c r="B732" s="6" t="s">
-        <v>4598</v>
+        <v>4604</v>
       </c>
       <c r="C732" s="6" t="s">
-        <v>2062</v>
+        <v>2076</v>
       </c>
       <c r="D732" s="6" t="s">
-        <v>2063</v>
+        <v>2077</v>
       </c>
       <c r="E732" s="6" t="s">
-        <v>2064</v>
+        <v>2078</v>
       </c>
       <c r="F732" s="6" t="s">
-        <v>2065</v>
+        <v>2079</v>
       </c>
       <c r="G732" s="6" t="s">
-        <v>2066</v>
+        <v>2080</v>
       </c>
       <c r="H732" s="6" t="s">
-        <v>2067</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="733">
       <c r="B733" s="5" t="s">
-        <v>4599</v>
+        <v>4605</v>
       </c>
       <c r="C733" s="5" t="s">
-        <v>2056</v>
+        <v>2062</v>
       </c>
       <c r="D733" s="5" t="s">
-        <v>2057</v>
+        <v>2063</v>
       </c>
       <c r="E733" s="5" t="s">
-        <v>2058</v>
+        <v>2064</v>
       </c>
       <c r="F733" s="5" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="G733" s="5" t="s">
-        <v>2059</v>
+        <v>2066</v>
       </c>
       <c r="H733" s="5" t="s">
-        <v>2060</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="734">
       <c r="B734" s="6" t="s">
-        <v>4600</v>
+        <v>4606</v>
       </c>
       <c r="C734" s="6" t="s">
-        <v>2069</v>
+        <v>2056</v>
       </c>
       <c r="D734" s="6" t="s">
-        <v>2070</v>
+        <v>2057</v>
       </c>
       <c r="E734" s="6" t="s">
-        <v>2071</v>
+        <v>2058</v>
       </c>
       <c r="F734" s="6" t="s">
-        <v>2072</v>
+        <v>2059</v>
       </c>
       <c r="G734" s="6" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="H734" s="6" t="s">
-        <v>2074</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="735">
       <c r="B735" s="5" t="s">
-        <v>4601</v>
+        <v>4607</v>
       </c>
       <c r="C735" s="5" t="s">
-        <v>2050</v>
+        <v>2069</v>
       </c>
       <c r="D735" s="5" t="s">
-        <v>2051</v>
+        <v>2070</v>
       </c>
       <c r="E735" s="5" t="s">
-        <v>2052</v>
+        <v>2071</v>
       </c>
       <c r="F735" s="5" t="s">
-        <v>2053</v>
+        <v>2072</v>
       </c>
       <c r="G735" s="5" t="s">
-        <v>2054</v>
+        <v>2073</v>
       </c>
       <c r="H735" s="5" t="s">
-        <v>2051</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="736">
       <c r="B736" s="6" t="s">
-        <v>4602</v>
+        <v>4608</v>
       </c>
       <c r="C736" s="6" t="s">
-        <v>2082</v>
+        <v>2050</v>
       </c>
       <c r="D736" s="6" t="s">
-        <v>2083</v>
+        <v>2051</v>
       </c>
       <c r="E736" s="6" t="s">
-        <v>2084</v>
+        <v>2052</v>
       </c>
       <c r="F736" s="6" t="s">
-        <v>2085</v>
+        <v>2053</v>
       </c>
       <c r="G736" s="6" t="s">
-        <v>2086</v>
+        <v>2054</v>
       </c>
       <c r="H736" s="6" t="s">
-        <v>2087</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="737">
       <c r="B737" s="5" t="s">
-        <v>4603</v>
+        <v>4609</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>4604</v>
+        <v>2082</v>
       </c>
       <c r="D737" s="5" t="s">
-        <v>2046</v>
+        <v>2083</v>
       </c>
       <c r="E737" s="5" t="s">
-        <v>2047</v>
+        <v>2084</v>
       </c>
       <c r="F737" s="5" t="s">
-        <v>2048</v>
+        <v>2085</v>
       </c>
       <c r="G737" s="5" t="s">
-        <v>2048</v>
+        <v>2086</v>
       </c>
       <c r="H737" s="5" t="s">
-        <v>2046</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="738">
       <c r="B738" s="6" t="s">
-        <v>4605</v>
+        <v>4610</v>
       </c>
       <c r="C738" s="6" t="s">
-        <v>4606</v>
+        <v>4611</v>
       </c>
       <c r="D738" s="6" t="s">
-        <v>4607</v>
+        <v>2046</v>
       </c>
       <c r="E738" s="6" t="s">
-        <v>4608</v>
+        <v>2047</v>
       </c>
       <c r="F738" s="6" t="s">
-        <v>4609</v>
+        <v>2048</v>
       </c>
       <c r="G738" s="6" t="s">
-        <v>4610</v>
+        <v>2048</v>
       </c>
       <c r="H738" s="6" t="s">
-        <v>4607</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="739">
       <c r="B739" s="5" t="s">
-        <v>4611</v>
+        <v>4612</v>
       </c>
       <c r="C739" s="5" t="s">
-        <v>4612</v>
+        <v>4613</v>
       </c>
       <c r="D739" s="5" t="s">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="E739" s="5" t="s">
+        <v>4615</v>
+      </c>
+      <c r="F739" s="5" t="s">
+        <v>4616</v>
+      </c>
+      <c r="G739" s="5" t="s">
+        <v>4617</v>
+      </c>
+      <c r="H739" s="5" t="s">
         <v>4614</v>
-      </c>
-      <c r="F739" s="5" t="s">
-        <v>4615</v>
-      </c>
-      <c r="G739" s="5" t="s">
-        <v>4616</v>
-      </c>
-      <c r="H739" s="5" t="s">
-        <v>4617</v>
       </c>
     </row>
     <row r="740">
@@ -33682,27 +33703,27 @@
         <v>4636</v>
       </c>
       <c r="G742" s="6" t="s">
-        <v>4636</v>
+        <v>4637</v>
       </c>
       <c r="H742" s="6" t="s">
-        <v>4637</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="743">
       <c r="B743" s="5" t="s">
-        <v>4638</v>
+        <v>4639</v>
       </c>
       <c r="C743" s="5" t="s">
-        <v>4639</v>
+        <v>4640</v>
       </c>
       <c r="D743" s="5" t="s">
-        <v>4640</v>
+        <v>4641</v>
       </c>
       <c r="E743" s="5" t="s">
-        <v>4641</v>
+        <v>4642</v>
       </c>
       <c r="F743" s="5" t="s">
-        <v>4642</v>
+        <v>4643</v>
       </c>
       <c r="G743" s="5" t="s">
         <v>4643</v>
@@ -33748,30 +33769,30 @@
         <v>4655</v>
       </c>
       <c r="F745" s="5" t="s">
-        <v>4655</v>
+        <v>4656</v>
       </c>
       <c r="G745" s="5" t="s">
-        <v>4655</v>
+        <v>4657</v>
       </c>
       <c r="H745" s="5" t="s">
-        <v>4656</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="746">
       <c r="B746" s="6" t="s">
-        <v>4657</v>
+        <v>4659</v>
       </c>
       <c r="C746" s="6" t="s">
-        <v>4658</v>
+        <v>4660</v>
       </c>
       <c r="D746" s="6" t="s">
-        <v>4659</v>
+        <v>4661</v>
       </c>
       <c r="E746" s="6" t="s">
-        <v>4660</v>
+        <v>4662</v>
       </c>
       <c r="F746" s="6" t="s">
-        <v>4661</v>
+        <v>4662</v>
       </c>
       <c r="G746" s="6" t="s">
         <v>4662</v>
@@ -33843,50 +33864,50 @@
         <v>4682</v>
       </c>
       <c r="G749" s="5" t="s">
-        <v>4682</v>
+        <v>4683</v>
       </c>
       <c r="H749" s="5" t="s">
-        <v>4683</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="750">
       <c r="B750" s="6" t="s">
-        <v>4684</v>
+        <v>4685</v>
       </c>
       <c r="C750" s="6" t="s">
-        <v>4685</v>
+        <v>4686</v>
       </c>
       <c r="D750" s="6" t="s">
-        <v>4686</v>
+        <v>4687</v>
       </c>
       <c r="E750" s="6" t="s">
-        <v>4687</v>
+        <v>4688</v>
       </c>
       <c r="F750" s="6" t="s">
-        <v>4688</v>
+        <v>4689</v>
       </c>
       <c r="G750" s="6" t="s">
-        <v>4688</v>
+        <v>4689</v>
       </c>
       <c r="H750" s="6" t="s">
-        <v>4689</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="751">
       <c r="B751" s="5" t="s">
-        <v>4690</v>
+        <v>4691</v>
       </c>
       <c r="C751" s="5" t="s">
-        <v>4691</v>
+        <v>4692</v>
       </c>
       <c r="D751" s="5" t="s">
-        <v>4692</v>
+        <v>4693</v>
       </c>
       <c r="E751" s="5" t="s">
-        <v>4693</v>
+        <v>4694</v>
       </c>
       <c r="F751" s="5" t="s">
-        <v>4694</v>
+        <v>4695</v>
       </c>
       <c r="G751" s="5" t="s">
         <v>4695</v>
@@ -33912,27 +33933,27 @@
         <v>4701</v>
       </c>
       <c r="G752" s="6" t="s">
-        <v>4701</v>
+        <v>4702</v>
       </c>
       <c r="H752" s="6" t="s">
-        <v>4702</v>
+        <v>4703</v>
       </c>
     </row>
     <row r="753">
       <c r="B753" s="5" t="s">
-        <v>4703</v>
+        <v>4704</v>
       </c>
       <c r="C753" s="5" t="s">
-        <v>4704</v>
+        <v>4705</v>
       </c>
       <c r="D753" s="5" t="s">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="E753" s="5" t="s">
-        <v>4706</v>
+        <v>4707</v>
       </c>
       <c r="F753" s="5" t="s">
-        <v>4707</v>
+        <v>4708</v>
       </c>
       <c r="G753" s="5" t="s">
         <v>4708</v>
@@ -34165,27 +34186,27 @@
         <v>4777</v>
       </c>
       <c r="G763" s="5" t="s">
-        <v>4777</v>
+        <v>4778</v>
       </c>
       <c r="H763" s="5" t="s">
-        <v>4778</v>
+        <v>4779</v>
       </c>
     </row>
     <row r="764">
       <c r="B764" s="6" t="s">
-        <v>4779</v>
+        <v>4780</v>
       </c>
       <c r="C764" s="6" t="s">
-        <v>4780</v>
+        <v>4781</v>
       </c>
       <c r="D764" s="6" t="s">
-        <v>4781</v>
+        <v>4782</v>
       </c>
       <c r="E764" s="6" t="s">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="F764" s="6" t="s">
-        <v>4783</v>
+        <v>4784</v>
       </c>
       <c r="G764" s="6" t="s">
         <v>4784</v>
@@ -34556,27 +34577,27 @@
         <v>4895</v>
       </c>
       <c r="G780" s="6" t="s">
-        <v>4895</v>
+        <v>4896</v>
       </c>
       <c r="H780" s="6" t="s">
-        <v>4896</v>
+        <v>4897</v>
       </c>
     </row>
     <row r="781">
       <c r="B781" s="5" t="s">
-        <v>4897</v>
+        <v>4898</v>
       </c>
       <c r="C781" s="5" t="s">
-        <v>4898</v>
+        <v>4899</v>
       </c>
       <c r="D781" s="5" t="s">
-        <v>4899</v>
+        <v>4900</v>
       </c>
       <c r="E781" s="5" t="s">
-        <v>4900</v>
+        <v>4901</v>
       </c>
       <c r="F781" s="5" t="s">
-        <v>4901</v>
+        <v>4902</v>
       </c>
       <c r="G781" s="5" t="s">
         <v>4902</v>
@@ -34625,27 +34646,27 @@
         <v>4915</v>
       </c>
       <c r="G783" s="5" t="s">
-        <v>4915</v>
+        <v>4916</v>
       </c>
       <c r="H783" s="5" t="s">
-        <v>4916</v>
+        <v>4917</v>
       </c>
     </row>
     <row r="784">
       <c r="B784" s="6" t="s">
-        <v>4917</v>
+        <v>4918</v>
       </c>
       <c r="C784" s="6" t="s">
-        <v>4918</v>
+        <v>4919</v>
       </c>
       <c r="D784" s="6" t="s">
-        <v>4919</v>
+        <v>4920</v>
       </c>
       <c r="E784" s="6" t="s">
-        <v>4920</v>
+        <v>4921</v>
       </c>
       <c r="F784" s="6" t="s">
-        <v>4921</v>
+        <v>4922</v>
       </c>
       <c r="G784" s="6" t="s">
         <v>4922</v>
@@ -34717,27 +34738,27 @@
         <v>4942</v>
       </c>
       <c r="G787" s="5" t="s">
-        <v>4942</v>
+        <v>4943</v>
       </c>
       <c r="H787" s="5" t="s">
-        <v>4943</v>
+        <v>4944</v>
       </c>
     </row>
     <row r="788">
       <c r="B788" s="6" t="s">
-        <v>4944</v>
+        <v>4945</v>
       </c>
       <c r="C788" s="6" t="s">
-        <v>4945</v>
+        <v>4946</v>
       </c>
       <c r="D788" s="6" t="s">
-        <v>4946</v>
+        <v>4947</v>
       </c>
       <c r="E788" s="6" t="s">
-        <v>4947</v>
+        <v>4948</v>
       </c>
       <c r="F788" s="6" t="s">
-        <v>4948</v>
+        <v>4949</v>
       </c>
       <c r="G788" s="6" t="s">
         <v>4949</v>
@@ -34904,30 +34925,30 @@
         <v>4998</v>
       </c>
       <c r="H795" s="5" t="s">
-        <v>4995</v>
+        <v>4999</v>
       </c>
     </row>
     <row r="796">
       <c r="B796" s="6" t="s">
-        <v>4999</v>
+        <v>5000</v>
       </c>
       <c r="C796" s="6" t="s">
-        <v>5000</v>
+        <v>5001</v>
       </c>
       <c r="D796" s="6" t="s">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="E796" s="6" t="s">
+        <v>5003</v>
+      </c>
+      <c r="F796" s="6" t="s">
+        <v>5004</v>
+      </c>
+      <c r="G796" s="6" t="s">
+        <v>5005</v>
+      </c>
+      <c r="H796" s="6" t="s">
         <v>5002</v>
-      </c>
-      <c r="F796" s="6" t="s">
-        <v>5003</v>
-      </c>
-      <c r="G796" s="6" t="s">
-        <v>5004</v>
-      </c>
-      <c r="H796" s="6" t="s">
-        <v>5005</v>
       </c>
     </row>
     <row r="797">
@@ -35027,91 +35048,91 @@
         <v>5034</v>
       </c>
       <c r="C801" s="5" t="s">
-        <v>3021</v>
+        <v>5035</v>
       </c>
       <c r="D801" s="5" t="s">
-        <v>5035</v>
+        <v>5036</v>
       </c>
       <c r="E801" s="5" t="s">
-        <v>3023</v>
+        <v>5037</v>
       </c>
       <c r="F801" s="5" t="s">
-        <v>5036</v>
+        <v>5038</v>
       </c>
       <c r="G801" s="5" t="s">
-        <v>5037</v>
+        <v>5039</v>
       </c>
       <c r="H801" s="5" t="s">
-        <v>5038</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="802">
       <c r="B802" s="6" t="s">
-        <v>5039</v>
+        <v>5041</v>
       </c>
       <c r="C802" s="6" t="s">
-        <v>3014</v>
+        <v>3021</v>
       </c>
       <c r="D802" s="6" t="s">
-        <v>5040</v>
+        <v>5042</v>
       </c>
       <c r="E802" s="6" t="s">
-        <v>3016</v>
+        <v>3023</v>
       </c>
       <c r="F802" s="6" t="s">
-        <v>5041</v>
+        <v>5043</v>
       </c>
       <c r="G802" s="6" t="s">
-        <v>5042</v>
+        <v>5044</v>
       </c>
       <c r="H802" s="6" t="s">
-        <v>5043</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="803">
       <c r="B803" s="5" t="s">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="C803" s="5" t="s">
-        <v>5045</v>
+        <v>3014</v>
       </c>
       <c r="D803" s="5" t="s">
-        <v>5046</v>
+        <v>5047</v>
       </c>
       <c r="E803" s="5" t="s">
-        <v>5047</v>
+        <v>3016</v>
       </c>
       <c r="F803" s="5" t="s">
         <v>5048</v>
       </c>
       <c r="G803" s="5" t="s">
-        <v>5047</v>
+        <v>5049</v>
       </c>
       <c r="H803" s="5" t="s">
-        <v>4443</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="804">
       <c r="B804" s="6" t="s">
-        <v>5049</v>
+        <v>5051</v>
       </c>
       <c r="C804" s="6" t="s">
-        <v>5050</v>
+        <v>5052</v>
       </c>
       <c r="D804" s="6" t="s">
-        <v>5051</v>
+        <v>5053</v>
       </c>
       <c r="E804" s="6" t="s">
-        <v>5052</v>
+        <v>5054</v>
       </c>
       <c r="F804" s="6" t="s">
-        <v>5053</v>
+        <v>5055</v>
       </c>
       <c r="G804" s="6" t="s">
         <v>5054</v>
       </c>
       <c r="H804" s="6" t="s">
-        <v>5055</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="805">
@@ -35131,27 +35152,27 @@
         <v>5060</v>
       </c>
       <c r="G805" s="5" t="s">
-        <v>5060</v>
+        <v>5061</v>
       </c>
       <c r="H805" s="5" t="s">
-        <v>5061</v>
+        <v>5062</v>
       </c>
     </row>
     <row r="806">
       <c r="B806" s="6" t="s">
-        <v>5062</v>
+        <v>5063</v>
       </c>
       <c r="C806" s="6" t="s">
-        <v>5063</v>
+        <v>5064</v>
       </c>
       <c r="D806" s="6" t="s">
-        <v>5064</v>
+        <v>5065</v>
       </c>
       <c r="E806" s="6" t="s">
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="F806" s="6" t="s">
-        <v>5066</v>
+        <v>5067</v>
       </c>
       <c r="G806" s="6" t="s">
         <v>5067</v>
@@ -35266,30 +35287,30 @@
         <v>5100</v>
       </c>
       <c r="F811" s="5" t="s">
-        <v>5100</v>
+        <v>5101</v>
       </c>
       <c r="G811" s="5" t="s">
-        <v>5100</v>
+        <v>5102</v>
       </c>
       <c r="H811" s="5" t="s">
-        <v>5101</v>
+        <v>5103</v>
       </c>
     </row>
     <row r="812">
       <c r="B812" s="6" t="s">
-        <v>5102</v>
+        <v>5104</v>
       </c>
       <c r="C812" s="6" t="s">
-        <v>5103</v>
+        <v>5105</v>
       </c>
       <c r="D812" s="6" t="s">
-        <v>5104</v>
+        <v>5106</v>
       </c>
       <c r="E812" s="6" t="s">
-        <v>5105</v>
+        <v>5107</v>
       </c>
       <c r="F812" s="6" t="s">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="G812" s="6" t="s">
         <v>5107</v>
@@ -35361,73 +35382,73 @@
         <v>5127</v>
       </c>
       <c r="G815" s="5" t="s">
-        <v>5127</v>
+        <v>5128</v>
       </c>
       <c r="H815" s="5" t="s">
-        <v>5128</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="816">
       <c r="B816" s="6" t="s">
-        <v>5129</v>
+        <v>5130</v>
       </c>
       <c r="C816" s="6" t="s">
-        <v>5130</v>
+        <v>5131</v>
       </c>
       <c r="D816" s="6" t="s">
-        <v>5131</v>
+        <v>5132</v>
       </c>
       <c r="E816" s="6" t="s">
-        <v>5132</v>
+        <v>5133</v>
       </c>
       <c r="F816" s="6" t="s">
-        <v>5133</v>
+        <v>5134</v>
       </c>
       <c r="G816" s="6" t="s">
-        <v>5133</v>
+        <v>5134</v>
       </c>
       <c r="H816" s="6" t="s">
-        <v>5134</v>
+        <v>5135</v>
       </c>
     </row>
     <row r="817">
       <c r="B817" s="5" t="s">
-        <v>5135</v>
+        <v>5136</v>
       </c>
       <c r="C817" s="5" t="s">
-        <v>5136</v>
+        <v>5137</v>
       </c>
       <c r="D817" s="5" t="s">
-        <v>5137</v>
+        <v>5138</v>
       </c>
       <c r="E817" s="5" t="s">
-        <v>5138</v>
+        <v>5139</v>
       </c>
       <c r="F817" s="5" t="s">
-        <v>5139</v>
+        <v>5140</v>
       </c>
       <c r="G817" s="5" t="s">
-        <v>5139</v>
+        <v>5140</v>
       </c>
       <c r="H817" s="5" t="s">
-        <v>5140</v>
+        <v>5141</v>
       </c>
     </row>
     <row r="818">
       <c r="B818" s="6" t="s">
-        <v>5141</v>
+        <v>5142</v>
       </c>
       <c r="C818" s="6" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="D818" s="6" t="s">
-        <v>5143</v>
+        <v>5144</v>
       </c>
       <c r="E818" s="6" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="F818" s="6" t="s">
-        <v>5145</v>
+        <v>5146</v>
       </c>
       <c r="G818" s="6" t="s">
         <v>5146</v>
@@ -35545,56 +35566,56 @@
         <v>5180</v>
       </c>
       <c r="G823" s="5" t="s">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="H823" s="5" t="s">
-        <v>5181</v>
+        <v>5182</v>
       </c>
     </row>
     <row r="824">
       <c r="B824" s="6" t="s">
-        <v>5182</v>
+        <v>5183</v>
       </c>
       <c r="C824" s="6" t="s">
-        <v>5183</v>
+        <v>5184</v>
       </c>
       <c r="D824" s="6" t="s">
-        <v>5184</v>
+        <v>5185</v>
       </c>
       <c r="E824" s="6" t="s">
-        <v>5185</v>
+        <v>5186</v>
       </c>
       <c r="F824" s="6" t="s">
-        <v>5185</v>
+        <v>5187</v>
       </c>
       <c r="G824" s="6" t="s">
-        <v>5185</v>
+        <v>5187</v>
       </c>
       <c r="H824" s="6" t="s">
-        <v>5184</v>
+        <v>5188</v>
       </c>
     </row>
     <row r="825">
       <c r="B825" s="5" t="s">
-        <v>5186</v>
+        <v>5189</v>
       </c>
       <c r="C825" s="5" t="s">
-        <v>5187</v>
+        <v>5190</v>
       </c>
       <c r="D825" s="5" t="s">
-        <v>5188</v>
+        <v>5191</v>
       </c>
       <c r="E825" s="5" t="s">
-        <v>5189</v>
+        <v>5192</v>
       </c>
       <c r="F825" s="5" t="s">
-        <v>5190</v>
+        <v>5192</v>
       </c>
       <c r="G825" s="5" t="s">
+        <v>5192</v>
+      </c>
+      <c r="H825" s="5" t="s">
         <v>5191</v>
-      </c>
-      <c r="H825" s="5" t="s">
-        <v>5192</v>
       </c>
     </row>
     <row r="826">
@@ -35651,42 +35672,42 @@
         <v>5208</v>
       </c>
       <c r="D828" s="6" t="s">
-        <v>5184</v>
+        <v>5209</v>
       </c>
       <c r="E828" s="6" t="s">
-        <v>5209</v>
+        <v>5210</v>
       </c>
       <c r="F828" s="6" t="s">
-        <v>5210</v>
+        <v>5211</v>
       </c>
       <c r="G828" s="6" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
       <c r="H828" s="6" t="s">
-        <v>5184</v>
+        <v>5213</v>
       </c>
     </row>
     <row r="829">
       <c r="B829" s="5" t="s">
-        <v>5211</v>
+        <v>5214</v>
       </c>
       <c r="C829" s="5" t="s">
-        <v>5212</v>
+        <v>5215</v>
       </c>
       <c r="D829" s="5" t="s">
-        <v>5213</v>
+        <v>5191</v>
       </c>
       <c r="E829" s="5" t="s">
-        <v>5214</v>
+        <v>5216</v>
       </c>
       <c r="F829" s="5" t="s">
-        <v>5215</v>
+        <v>5217</v>
       </c>
       <c r="G829" s="5" t="s">
-        <v>5216</v>
+        <v>5217</v>
       </c>
       <c r="H829" s="5" t="s">
-        <v>5217</v>
+        <v>5191</v>
       </c>
     </row>
     <row r="830">
@@ -35709,30 +35730,30 @@
         <v>5223</v>
       </c>
       <c r="H830" s="6" t="s">
-        <v>5220</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="831">
       <c r="B831" s="5" t="s">
-        <v>5224</v>
+        <v>5225</v>
       </c>
       <c r="C831" s="5" t="s">
-        <v>5225</v>
+        <v>5226</v>
       </c>
       <c r="D831" s="5" t="s">
-        <v>5226</v>
+        <v>5227</v>
       </c>
       <c r="E831" s="5" t="s">
+        <v>5228</v>
+      </c>
+      <c r="F831" s="5" t="s">
+        <v>5229</v>
+      </c>
+      <c r="G831" s="5" t="s">
+        <v>5230</v>
+      </c>
+      <c r="H831" s="5" t="s">
         <v>5227</v>
-      </c>
-      <c r="F831" s="5" t="s">
-        <v>5228</v>
-      </c>
-      <c r="G831" s="5" t="s">
-        <v>5229</v>
-      </c>
-      <c r="H831" s="5" t="s">
-        <v>5230</v>
       </c>
     </row>
     <row r="832">
@@ -35821,27 +35842,27 @@
         <v>5256</v>
       </c>
       <c r="G835" s="5" t="s">
-        <v>5256</v>
+        <v>5257</v>
       </c>
       <c r="H835" s="5" t="s">
-        <v>5257</v>
+        <v>5258</v>
       </c>
     </row>
     <row r="836">
       <c r="B836" s="6" t="s">
-        <v>5258</v>
+        <v>5259</v>
       </c>
       <c r="C836" s="6" t="s">
-        <v>5259</v>
+        <v>5260</v>
       </c>
       <c r="D836" s="6" t="s">
-        <v>5260</v>
+        <v>5261</v>
       </c>
       <c r="E836" s="6" t="s">
-        <v>5261</v>
+        <v>5262</v>
       </c>
       <c r="F836" s="6" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="G836" s="6" t="s">
         <v>5263</v>
@@ -35867,27 +35888,27 @@
         <v>5269</v>
       </c>
       <c r="G837" s="5" t="s">
-        <v>5269</v>
+        <v>5270</v>
       </c>
       <c r="H837" s="5" t="s">
-        <v>5270</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="838">
       <c r="B838" s="6" t="s">
-        <v>5271</v>
+        <v>5272</v>
       </c>
       <c r="C838" s="6" t="s">
-        <v>5272</v>
+        <v>5273</v>
       </c>
       <c r="D838" s="6" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="E838" s="6" t="s">
-        <v>5274</v>
+        <v>5275</v>
       </c>
       <c r="F838" s="6" t="s">
-        <v>5275</v>
+        <v>5276</v>
       </c>
       <c r="G838" s="6" t="s">
         <v>5276</v>
@@ -35913,56 +35934,56 @@
         <v>5282</v>
       </c>
       <c r="G839" s="5" t="s">
-        <v>5281</v>
+        <v>5283</v>
       </c>
       <c r="H839" s="5" t="s">
-        <v>5283</v>
+        <v>5284</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
-        <v>5284</v>
+        <v>5285</v>
       </c>
       <c r="C840" s="6" t="s">
-        <v>5285</v>
+        <v>5286</v>
       </c>
       <c r="D840" s="6" t="s">
-        <v>5286</v>
+        <v>5287</v>
       </c>
       <c r="E840" s="6" t="s">
-        <v>5287</v>
+        <v>5288</v>
       </c>
       <c r="F840" s="6" t="s">
-        <v>5288</v>
+        <v>5289</v>
       </c>
       <c r="G840" s="6" t="s">
         <v>5288</v>
       </c>
       <c r="H840" s="6" t="s">
-        <v>5286</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="841">
       <c r="B841" s="5" t="s">
-        <v>5289</v>
+        <v>5291</v>
       </c>
       <c r="C841" s="5" t="s">
-        <v>5290</v>
+        <v>5292</v>
       </c>
       <c r="D841" s="5" t="s">
-        <v>5291</v>
+        <v>5293</v>
       </c>
       <c r="E841" s="5" t="s">
-        <v>5292</v>
+        <v>5294</v>
       </c>
       <c r="F841" s="5" t="s">
+        <v>5295</v>
+      </c>
+      <c r="G841" s="5" t="s">
+        <v>5295</v>
+      </c>
+      <c r="H841" s="5" t="s">
         <v>5293</v>
-      </c>
-      <c r="G841" s="5" t="s">
-        <v>5294</v>
-      </c>
-      <c r="H841" s="5" t="s">
-        <v>5295</v>
       </c>
     </row>
     <row r="842">
@@ -35985,30 +36006,30 @@
         <v>5301</v>
       </c>
       <c r="H842" s="6" t="s">
-        <v>5298</v>
+        <v>5302</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
-        <v>5302</v>
+        <v>5303</v>
       </c>
       <c r="C843" s="5" t="s">
-        <v>5303</v>
+        <v>5304</v>
       </c>
       <c r="D843" s="5" t="s">
-        <v>5304</v>
+        <v>5305</v>
       </c>
       <c r="E843" s="5" t="s">
+        <v>5306</v>
+      </c>
+      <c r="F843" s="5" t="s">
+        <v>5307</v>
+      </c>
+      <c r="G843" s="5" t="s">
+        <v>5308</v>
+      </c>
+      <c r="H843" s="5" t="s">
         <v>5305</v>
-      </c>
-      <c r="F843" s="5" t="s">
-        <v>5306</v>
-      </c>
-      <c r="G843" s="5" t="s">
-        <v>5307</v>
-      </c>
-      <c r="H843" s="5" t="s">
-        <v>5308</v>
       </c>
     </row>
     <row r="844">
@@ -36028,50 +36049,50 @@
         <v>5313</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5313</v>
+        <v>5314</v>
       </c>
       <c r="H844" s="6" t="s">
-        <v>5314</v>
+        <v>5315</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5315</v>
+        <v>5316</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>5316</v>
+        <v>5317</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5317</v>
+        <v>5318</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>5318</v>
+        <v>5319</v>
       </c>
       <c r="F845" s="5" t="s">
-        <v>5319</v>
+        <v>5320</v>
       </c>
       <c r="G845" s="5" t="s">
-        <v>5319</v>
+        <v>5320</v>
       </c>
       <c r="H845" s="5" t="s">
-        <v>5320</v>
+        <v>5321</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
-        <v>5321</v>
+        <v>5322</v>
       </c>
       <c r="C846" s="6" t="s">
-        <v>5322</v>
+        <v>5323</v>
       </c>
       <c r="D846" s="6" t="s">
-        <v>5323</v>
+        <v>5324</v>
       </c>
       <c r="E846" s="6" t="s">
-        <v>5324</v>
+        <v>5325</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>5325</v>
+        <v>5326</v>
       </c>
       <c r="G846" s="6" t="s">
         <v>5326</v>
@@ -36097,27 +36118,27 @@
         <v>5332</v>
       </c>
       <c r="G847" s="5" t="s">
-        <v>5332</v>
+        <v>5333</v>
       </c>
       <c r="H847" s="5" t="s">
-        <v>5333</v>
+        <v>5334</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
-        <v>5334</v>
+        <v>5335</v>
       </c>
       <c r="C848" s="6" t="s">
-        <v>5335</v>
+        <v>5336</v>
       </c>
       <c r="D848" s="6" t="s">
-        <v>5336</v>
+        <v>5337</v>
       </c>
       <c r="E848" s="6" t="s">
-        <v>5337</v>
+        <v>5338</v>
       </c>
       <c r="F848" s="6" t="s">
-        <v>5338</v>
+        <v>5339</v>
       </c>
       <c r="G848" s="6" t="s">
         <v>5339</v>
@@ -36143,171 +36164,171 @@
         <v>5345</v>
       </c>
       <c r="G849" s="5" t="s">
-        <v>5345</v>
+        <v>5346</v>
       </c>
       <c r="H849" s="5" t="s">
-        <v>5346</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
-        <v>5347</v>
+        <v>5348</v>
       </c>
       <c r="C850" s="6" t="s">
-        <v>5348</v>
+        <v>5349</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>5349</v>
+        <v>5350</v>
       </c>
       <c r="E850" s="6" t="s">
-        <v>5350</v>
+        <v>5351</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>5351</v>
+        <v>5352</v>
       </c>
       <c r="G850" s="6" t="s">
-        <v>5351</v>
+        <v>5352</v>
       </c>
       <c r="H850" s="6" t="s">
-        <v>5352</v>
+        <v>5353</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
-        <v>5353</v>
+        <v>5354</v>
       </c>
       <c r="C851" s="5" t="s">
-        <v>5354</v>
+        <v>5355</v>
       </c>
       <c r="D851" s="5" t="s">
-        <v>5354</v>
+        <v>5356</v>
       </c>
       <c r="E851" s="5" t="s">
-        <v>5354</v>
+        <v>5357</v>
       </c>
       <c r="F851" s="5" t="s">
-        <v>5354</v>
+        <v>5358</v>
       </c>
       <c r="G851" s="5" t="s">
-        <v>5354</v>
+        <v>5358</v>
       </c>
       <c r="H851" s="5" t="s">
-        <v>5354</v>
+        <v>5359</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
-        <v>5355</v>
+        <v>5360</v>
       </c>
       <c r="C852" s="6" t="s">
-        <v>5356</v>
+        <v>5361</v>
       </c>
       <c r="D852" s="6" t="s">
-        <v>5357</v>
+        <v>5361</v>
       </c>
       <c r="E852" s="6" t="s">
-        <v>5358</v>
+        <v>5361</v>
       </c>
       <c r="F852" s="6" t="s">
-        <v>5359</v>
+        <v>5361</v>
       </c>
       <c r="G852" s="6" t="s">
-        <v>5359</v>
+        <v>5361</v>
       </c>
       <c r="H852" s="6" t="s">
-        <v>5357</v>
+        <v>5361</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
-        <v>5360</v>
+        <v>5362</v>
       </c>
       <c r="C853" s="5" t="s">
-        <v>5361</v>
+        <v>5363</v>
       </c>
       <c r="D853" s="5" t="s">
-        <v>5362</v>
+        <v>5364</v>
       </c>
       <c r="E853" s="5" t="s">
-        <v>5363</v>
+        <v>5365</v>
       </c>
       <c r="F853" s="5" t="s">
+        <v>5366</v>
+      </c>
+      <c r="G853" s="5" t="s">
+        <v>5366</v>
+      </c>
+      <c r="H853" s="5" t="s">
         <v>5364</v>
-      </c>
-      <c r="G853" s="5" t="s">
-        <v>5365</v>
-      </c>
-      <c r="H853" s="5" t="s">
-        <v>5362</v>
       </c>
     </row>
     <row r="854">
       <c r="B854" s="6" t="s">
-        <v>5366</v>
+        <v>5367</v>
       </c>
       <c r="C854" s="6" t="s">
-        <v>5367</v>
+        <v>5368</v>
       </c>
       <c r="D854" s="6" t="s">
-        <v>5368</v>
+        <v>5369</v>
       </c>
       <c r="E854" s="6" t="s">
+        <v>5370</v>
+      </c>
+      <c r="F854" s="6" t="s">
+        <v>5371</v>
+      </c>
+      <c r="G854" s="6" t="s">
+        <v>5372</v>
+      </c>
+      <c r="H854" s="6" t="s">
         <v>5369</v>
-      </c>
-      <c r="F854" s="6" t="s">
-        <v>5369</v>
-      </c>
-      <c r="G854" s="6" t="s">
-        <v>5369</v>
-      </c>
-      <c r="H854" s="6" t="s">
-        <v>5368</v>
       </c>
     </row>
     <row r="855">
       <c r="B855" s="5" t="s">
-        <v>5370</v>
+        <v>5373</v>
       </c>
       <c r="C855" s="5" t="s">
-        <v>5371</v>
+        <v>5374</v>
       </c>
       <c r="D855" s="5" t="s">
-        <v>5372</v>
+        <v>5375</v>
       </c>
       <c r="E855" s="5" t="s">
-        <v>5373</v>
+        <v>5376</v>
       </c>
       <c r="F855" s="5" t="s">
-        <v>5373</v>
+        <v>5376</v>
       </c>
       <c r="G855" s="5" t="s">
-        <v>5373</v>
+        <v>5376</v>
       </c>
       <c r="H855" s="5" t="s">
-        <v>5372</v>
+        <v>5375</v>
       </c>
     </row>
     <row r="856">
       <c r="B856" s="6" t="s">
-        <v>5374</v>
+        <v>5377</v>
       </c>
       <c r="C856" s="6" t="s">
-        <v>5375</v>
+        <v>5378</v>
       </c>
       <c r="D856" s="6" t="s">
-        <v>5376</v>
+        <v>5379</v>
       </c>
       <c r="E856" s="6" t="s">
-        <v>5377</v>
+        <v>5380</v>
       </c>
       <c r="F856" s="6" t="s">
-        <v>5378</v>
+        <v>5380</v>
       </c>
       <c r="G856" s="6" t="s">
+        <v>5380</v>
+      </c>
+      <c r="H856" s="6" t="s">
         <v>5379</v>
-      </c>
-      <c r="H856" s="6" t="s">
-        <v>5380</v>
       </c>
     </row>
     <row r="857">
@@ -36330,30 +36351,30 @@
         <v>5386</v>
       </c>
       <c r="H857" s="5" t="s">
-        <v>5383</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="858">
       <c r="B858" s="6" t="s">
-        <v>5387</v>
+        <v>5388</v>
       </c>
       <c r="C858" s="6" t="s">
-        <v>5388</v>
+        <v>5389</v>
       </c>
       <c r="D858" s="6" t="s">
-        <v>5389</v>
+        <v>5390</v>
       </c>
       <c r="E858" s="6" t="s">
+        <v>5391</v>
+      </c>
+      <c r="F858" s="6" t="s">
+        <v>5392</v>
+      </c>
+      <c r="G858" s="6" t="s">
+        <v>5393</v>
+      </c>
+      <c r="H858" s="6" t="s">
         <v>5390</v>
-      </c>
-      <c r="F858" s="6" t="s">
-        <v>5391</v>
-      </c>
-      <c r="G858" s="6" t="s">
-        <v>5392</v>
-      </c>
-      <c r="H858" s="6" t="s">
-        <v>5393</v>
       </c>
     </row>
     <row r="859">
@@ -36422,30 +36443,30 @@
         <v>5413</v>
       </c>
       <c r="H861" s="5" t="s">
-        <v>5383</v>
+        <v>5414</v>
       </c>
     </row>
     <row r="862">
       <c r="B862" s="6" t="s">
-        <v>5414</v>
+        <v>5415</v>
       </c>
       <c r="C862" s="6" t="s">
-        <v>5415</v>
+        <v>5416</v>
       </c>
       <c r="D862" s="6" t="s">
-        <v>5416</v>
+        <v>5417</v>
       </c>
       <c r="E862" s="6" t="s">
-        <v>5417</v>
+        <v>5418</v>
       </c>
       <c r="F862" s="6" t="s">
-        <v>5418</v>
+        <v>5419</v>
       </c>
       <c r="G862" s="6" t="s">
-        <v>5419</v>
+        <v>5420</v>
       </c>
       <c r="H862" s="6" t="s">
-        <v>5420</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="863">
@@ -36465,14 +36486,37 @@
         <v>5425</v>
       </c>
       <c r="G863" s="5" t="s">
-        <v>5425</v>
+        <v>5426</v>
       </c>
       <c r="H863" s="5" t="s">
-        <v>5426</v>
+        <v>5427</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="B864" s="6" t="s">
+        <v>5428</v>
+      </c>
+      <c r="C864" s="6" t="s">
+        <v>5429</v>
+      </c>
+      <c r="D864" s="6" t="s">
+        <v>5430</v>
+      </c>
+      <c r="E864" s="6" t="s">
+        <v>5431</v>
+      </c>
+      <c r="F864" s="6" t="s">
+        <v>5432</v>
+      </c>
+      <c r="G864" s="6" t="s">
+        <v>5432</v>
+      </c>
+      <c r="H864" s="6" t="s">
+        <v>5433</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H863"/>
+  <autoFilter ref="B2:H864"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36491,10 +36535,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5427</v>
+        <v>5434</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5428</v>
+        <v>5435</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36505,16 +36549,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5429</v>
+        <v>5436</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5430</v>
+        <v>5437</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5431</v>
+        <v>5438</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5432</v>
+        <v>5439</v>
       </c>
     </row>
     <row r="3">
@@ -36522,16 +36566,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5433</v>
+        <v>5440</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5434</v>
+        <v>5441</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5435</v>
+        <v>5442</v>
       </c>
     </row>
     <row r="4">
@@ -36542,24 +36586,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5436</v>
+        <v>5443</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5437</v>
+        <v>5444</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5438</v>
+        <v>5445</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5439</v>
+        <v>5446</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5440</v>
+        <v>5447</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36567,13 +36611,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5441</v>
+        <v>5448</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36581,13 +36625,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5443</v>
+        <v>5450</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5444</v>
+        <v>5451</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36595,13 +36639,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5445</v>
+        <v>5452</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5446</v>
+        <v>5453</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36609,13 +36653,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5447</v>
+        <v>5454</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5448</v>
+        <v>5455</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36623,13 +36667,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5449</v>
+        <v>5456</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5450</v>
+        <v>5457</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36637,13 +36681,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5451</v>
+        <v>5458</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5452</v>
+        <v>5459</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36651,13 +36695,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5453</v>
+        <v>5460</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5454</v>
+        <v>5461</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36665,13 +36709,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5455</v>
+        <v>5462</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5456</v>
+        <v>5463</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36679,13 +36723,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5457</v>
+        <v>5464</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5458</v>
+        <v>5465</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36699,7 +36743,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5459</v>
+        <v>5466</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36707,13 +36751,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5460</v>
+        <v>5467</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5461</v>
+        <v>5468</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36721,13 +36765,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5462</v>
+        <v>5469</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5463</v>
+        <v>5470</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36735,13 +36779,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5464</v>
+        <v>5471</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5465</v>
+        <v>5472</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36749,13 +36793,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5466</v>
+        <v>5473</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5467</v>
+        <v>5474</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36763,13 +36807,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5468</v>
+        <v>5475</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5469</v>
+        <v>5476</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36777,13 +36821,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5470</v>
+        <v>5477</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5471</v>
+        <v>5478</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36791,13 +36835,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5472</v>
+        <v>5479</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5473</v>
+        <v>5480</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36805,13 +36849,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5474</v>
+        <v>5481</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5475</v>
+        <v>5482</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36819,13 +36863,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5476</v>
+        <v>5483</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5477</v>
+        <v>5484</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$864]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$868]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6111" uniqueCount="5485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6139" uniqueCount="5512">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -15584,6 +15584,87 @@
   </si>
   <si>
     <t xml:space="preserve">{scale}{body}-Päckchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pack.swap_mark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바꿔서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swap in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入れ替え</t>
+  </si>
+  <si>
+    <t xml:space="preserve">替换</t>
+  </si>
+  <si>
+    <t xml:space="preserve">替換</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tauschen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pack.full_mark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자리 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">空きなし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无空位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無空位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pack.jokers_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커 칸이 찼고 내놓을 조커도 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker slots are full and none can be sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ジョーカー枠が満杯で、売れるものもありません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小丑位已满，也没有可卖出的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小丑位已滿，也沒有可賣出的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker-Plätze sind voll und keiner ist verkäuflich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pack.consumables_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품 칸이 찼습니다. 하나 쓰거나 팔아야 합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumable slots are full. Use or sell one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消費アイテム枠が満杯です。使うか売ってください</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗品位已满，请使用或卖出一个</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗品位已滿，請使用或賣出一個</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbrauchsplätze sind voll. Nutze oder verkaufe einen</t>
   </si>
   <si>
     <t xml:space="preserve">ui.option.speed_value</t>
@@ -16671,7 +16752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H864"/>
+  <dimension ref="A1:H868"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -35609,197 +35690,197 @@
         <v>5192</v>
       </c>
       <c r="F825" s="5" t="s">
-        <v>5192</v>
+        <v>5193</v>
       </c>
       <c r="G825" s="5" t="s">
-        <v>5192</v>
+        <v>5194</v>
       </c>
       <c r="H825" s="5" t="s">
-        <v>5191</v>
+        <v>5195</v>
       </c>
     </row>
     <row r="826">
       <c r="B826" s="6" t="s">
-        <v>5193</v>
+        <v>5196</v>
       </c>
       <c r="C826" s="6" t="s">
-        <v>5194</v>
+        <v>5197</v>
       </c>
       <c r="D826" s="6" t="s">
-        <v>5195</v>
+        <v>5198</v>
       </c>
       <c r="E826" s="6" t="s">
-        <v>5196</v>
+        <v>5199</v>
       </c>
       <c r="F826" s="6" t="s">
-        <v>5197</v>
+        <v>5200</v>
       </c>
       <c r="G826" s="6" t="s">
-        <v>5198</v>
+        <v>5201</v>
       </c>
       <c r="H826" s="6" t="s">
-        <v>5199</v>
+        <v>4964</v>
       </c>
     </row>
     <row r="827">
       <c r="B827" s="5" t="s">
-        <v>5200</v>
+        <v>5202</v>
       </c>
       <c r="C827" s="5" t="s">
-        <v>5201</v>
+        <v>5203</v>
       </c>
       <c r="D827" s="5" t="s">
-        <v>5202</v>
+        <v>5204</v>
       </c>
       <c r="E827" s="5" t="s">
-        <v>5203</v>
+        <v>5205</v>
       </c>
       <c r="F827" s="5" t="s">
-        <v>5204</v>
+        <v>5206</v>
       </c>
       <c r="G827" s="5" t="s">
-        <v>5205</v>
+        <v>5207</v>
       </c>
       <c r="H827" s="5" t="s">
-        <v>5206</v>
+        <v>5208</v>
       </c>
     </row>
     <row r="828">
       <c r="B828" s="6" t="s">
-        <v>5207</v>
+        <v>5209</v>
       </c>
       <c r="C828" s="6" t="s">
-        <v>5208</v>
+        <v>5210</v>
       </c>
       <c r="D828" s="6" t="s">
-        <v>5209</v>
+        <v>5211</v>
       </c>
       <c r="E828" s="6" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
       <c r="F828" s="6" t="s">
-        <v>5211</v>
+        <v>5213</v>
       </c>
       <c r="G828" s="6" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
       <c r="H828" s="6" t="s">
-        <v>5213</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="829">
       <c r="B829" s="5" t="s">
-        <v>5214</v>
+        <v>5216</v>
       </c>
       <c r="C829" s="5" t="s">
-        <v>5215</v>
+        <v>5217</v>
       </c>
       <c r="D829" s="5" t="s">
-        <v>5191</v>
+        <v>5218</v>
       </c>
       <c r="E829" s="5" t="s">
-        <v>5216</v>
+        <v>5219</v>
       </c>
       <c r="F829" s="5" t="s">
-        <v>5217</v>
+        <v>5219</v>
       </c>
       <c r="G829" s="5" t="s">
-        <v>5217</v>
+        <v>5219</v>
       </c>
       <c r="H829" s="5" t="s">
-        <v>5191</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="830">
       <c r="B830" s="6" t="s">
-        <v>5218</v>
+        <v>5220</v>
       </c>
       <c r="C830" s="6" t="s">
-        <v>5219</v>
+        <v>5221</v>
       </c>
       <c r="D830" s="6" t="s">
-        <v>5220</v>
+        <v>5222</v>
       </c>
       <c r="E830" s="6" t="s">
-        <v>5221</v>
+        <v>5223</v>
       </c>
       <c r="F830" s="6" t="s">
-        <v>5222</v>
+        <v>5224</v>
       </c>
       <c r="G830" s="6" t="s">
-        <v>5223</v>
+        <v>5225</v>
       </c>
       <c r="H830" s="6" t="s">
-        <v>5224</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="831">
       <c r="B831" s="5" t="s">
-        <v>5225</v>
+        <v>5227</v>
       </c>
       <c r="C831" s="5" t="s">
-        <v>5226</v>
+        <v>5228</v>
       </c>
       <c r="D831" s="5" t="s">
-        <v>5227</v>
+        <v>5229</v>
       </c>
       <c r="E831" s="5" t="s">
-        <v>5228</v>
+        <v>5230</v>
       </c>
       <c r="F831" s="5" t="s">
-        <v>5229</v>
+        <v>5231</v>
       </c>
       <c r="G831" s="5" t="s">
-        <v>5230</v>
+        <v>5232</v>
       </c>
       <c r="H831" s="5" t="s">
-        <v>5227</v>
+        <v>5233</v>
       </c>
     </row>
     <row r="832">
       <c r="B832" s="6" t="s">
-        <v>5231</v>
+        <v>5234</v>
       </c>
       <c r="C832" s="6" t="s">
-        <v>5232</v>
+        <v>5235</v>
       </c>
       <c r="D832" s="6" t="s">
-        <v>5233</v>
+        <v>5236</v>
       </c>
       <c r="E832" s="6" t="s">
-        <v>5234</v>
+        <v>5237</v>
       </c>
       <c r="F832" s="6" t="s">
-        <v>5235</v>
+        <v>5238</v>
       </c>
       <c r="G832" s="6" t="s">
-        <v>5236</v>
+        <v>5239</v>
       </c>
       <c r="H832" s="6" t="s">
-        <v>5237</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="833">
       <c r="B833" s="5" t="s">
-        <v>5238</v>
+        <v>5241</v>
       </c>
       <c r="C833" s="5" t="s">
-        <v>5239</v>
+        <v>5242</v>
       </c>
       <c r="D833" s="5" t="s">
-        <v>5240</v>
+        <v>5218</v>
       </c>
       <c r="E833" s="5" t="s">
-        <v>5241</v>
+        <v>5243</v>
       </c>
       <c r="F833" s="5" t="s">
-        <v>5242</v>
+        <v>5244</v>
       </c>
       <c r="G833" s="5" t="s">
-        <v>5243</v>
+        <v>5244</v>
       </c>
       <c r="H833" s="5" t="s">
-        <v>5244</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="834">
@@ -35845,24 +35926,24 @@
         <v>5257</v>
       </c>
       <c r="H835" s="5" t="s">
-        <v>5258</v>
+        <v>5254</v>
       </c>
     </row>
     <row r="836">
       <c r="B836" s="6" t="s">
+        <v>5258</v>
+      </c>
+      <c r="C836" s="6" t="s">
         <v>5259</v>
       </c>
-      <c r="C836" s="6" t="s">
+      <c r="D836" s="6" t="s">
         <v>5260</v>
       </c>
-      <c r="D836" s="6" t="s">
+      <c r="E836" s="6" t="s">
         <v>5261</v>
       </c>
-      <c r="E836" s="6" t="s">
+      <c r="F836" s="6" t="s">
         <v>5262</v>
-      </c>
-      <c r="F836" s="6" t="s">
-        <v>5263</v>
       </c>
       <c r="G836" s="6" t="s">
         <v>5263</v>
@@ -35911,516 +35992,516 @@
         <v>5276</v>
       </c>
       <c r="G838" s="6" t="s">
-        <v>5276</v>
+        <v>5277</v>
       </c>
       <c r="H838" s="6" t="s">
-        <v>5277</v>
+        <v>5278</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
-        <v>5278</v>
+        <v>5279</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>5279</v>
+        <v>5280</v>
       </c>
       <c r="D839" s="5" t="s">
-        <v>5280</v>
+        <v>5281</v>
       </c>
       <c r="E839" s="5" t="s">
-        <v>5281</v>
+        <v>5282</v>
       </c>
       <c r="F839" s="5" t="s">
-        <v>5282</v>
+        <v>5283</v>
       </c>
       <c r="G839" s="5" t="s">
-        <v>5283</v>
+        <v>5284</v>
       </c>
       <c r="H839" s="5" t="s">
-        <v>5284</v>
+        <v>5285</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
-        <v>5285</v>
+        <v>5286</v>
       </c>
       <c r="C840" s="6" t="s">
-        <v>5286</v>
+        <v>5287</v>
       </c>
       <c r="D840" s="6" t="s">
-        <v>5287</v>
+        <v>5288</v>
       </c>
       <c r="E840" s="6" t="s">
-        <v>5288</v>
+        <v>5289</v>
       </c>
       <c r="F840" s="6" t="s">
-        <v>5289</v>
+        <v>5290</v>
       </c>
       <c r="G840" s="6" t="s">
-        <v>5288</v>
+        <v>5290</v>
       </c>
       <c r="H840" s="6" t="s">
-        <v>5290</v>
+        <v>5291</v>
       </c>
     </row>
     <row r="841">
       <c r="B841" s="5" t="s">
-        <v>5291</v>
+        <v>5292</v>
       </c>
       <c r="C841" s="5" t="s">
-        <v>5292</v>
+        <v>5293</v>
       </c>
       <c r="D841" s="5" t="s">
-        <v>5293</v>
+        <v>5294</v>
       </c>
       <c r="E841" s="5" t="s">
-        <v>5294</v>
+        <v>5295</v>
       </c>
       <c r="F841" s="5" t="s">
-        <v>5295</v>
+        <v>5296</v>
       </c>
       <c r="G841" s="5" t="s">
-        <v>5295</v>
+        <v>5297</v>
       </c>
       <c r="H841" s="5" t="s">
-        <v>5293</v>
+        <v>5298</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
-        <v>5296</v>
+        <v>5299</v>
       </c>
       <c r="C842" s="6" t="s">
-        <v>5297</v>
+        <v>5300</v>
       </c>
       <c r="D842" s="6" t="s">
-        <v>5298</v>
+        <v>5301</v>
       </c>
       <c r="E842" s="6" t="s">
-        <v>5299</v>
+        <v>5302</v>
       </c>
       <c r="F842" s="6" t="s">
-        <v>5300</v>
+        <v>5303</v>
       </c>
       <c r="G842" s="6" t="s">
-        <v>5301</v>
+        <v>5303</v>
       </c>
       <c r="H842" s="6" t="s">
-        <v>5302</v>
+        <v>5304</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
-        <v>5303</v>
+        <v>5305</v>
       </c>
       <c r="C843" s="5" t="s">
-        <v>5304</v>
+        <v>5306</v>
       </c>
       <c r="D843" s="5" t="s">
-        <v>5305</v>
+        <v>5307</v>
       </c>
       <c r="E843" s="5" t="s">
-        <v>5306</v>
+        <v>5308</v>
       </c>
       <c r="F843" s="5" t="s">
-        <v>5307</v>
+        <v>5309</v>
       </c>
       <c r="G843" s="5" t="s">
-        <v>5308</v>
+        <v>5310</v>
       </c>
       <c r="H843" s="5" t="s">
-        <v>5305</v>
+        <v>5311</v>
       </c>
     </row>
     <row r="844">
       <c r="B844" s="6" t="s">
-        <v>5309</v>
+        <v>5312</v>
       </c>
       <c r="C844" s="6" t="s">
-        <v>5310</v>
+        <v>5313</v>
       </c>
       <c r="D844" s="6" t="s">
-        <v>5311</v>
+        <v>5314</v>
       </c>
       <c r="E844" s="6" t="s">
-        <v>5312</v>
+        <v>5315</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>5313</v>
+        <v>5316</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5314</v>
+        <v>5315</v>
       </c>
       <c r="H844" s="6" t="s">
-        <v>5315</v>
+        <v>5317</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
-        <v>5316</v>
+        <v>5318</v>
       </c>
       <c r="C845" s="5" t="s">
-        <v>5317</v>
+        <v>5319</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>5318</v>
+        <v>5320</v>
       </c>
       <c r="E845" s="5" t="s">
-        <v>5319</v>
+        <v>5321</v>
       </c>
       <c r="F845" s="5" t="s">
+        <v>5322</v>
+      </c>
+      <c r="G845" s="5" t="s">
+        <v>5322</v>
+      </c>
+      <c r="H845" s="5" t="s">
         <v>5320</v>
-      </c>
-      <c r="G845" s="5" t="s">
-        <v>5320</v>
-      </c>
-      <c r="H845" s="5" t="s">
-        <v>5321</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
-        <v>5322</v>
+        <v>5323</v>
       </c>
       <c r="C846" s="6" t="s">
-        <v>5323</v>
+        <v>5324</v>
       </c>
       <c r="D846" s="6" t="s">
-        <v>5324</v>
+        <v>5325</v>
       </c>
       <c r="E846" s="6" t="s">
-        <v>5325</v>
+        <v>5326</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>5326</v>
+        <v>5327</v>
       </c>
       <c r="G846" s="6" t="s">
-        <v>5326</v>
+        <v>5328</v>
       </c>
       <c r="H846" s="6" t="s">
-        <v>5327</v>
+        <v>5329</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
-        <v>5328</v>
+        <v>5330</v>
       </c>
       <c r="C847" s="5" t="s">
-        <v>5329</v>
+        <v>5331</v>
       </c>
       <c r="D847" s="5" t="s">
-        <v>5330</v>
+        <v>5332</v>
       </c>
       <c r="E847" s="5" t="s">
-        <v>5331</v>
+        <v>5333</v>
       </c>
       <c r="F847" s="5" t="s">
+        <v>5334</v>
+      </c>
+      <c r="G847" s="5" t="s">
+        <v>5335</v>
+      </c>
+      <c r="H847" s="5" t="s">
         <v>5332</v>
-      </c>
-      <c r="G847" s="5" t="s">
-        <v>5333</v>
-      </c>
-      <c r="H847" s="5" t="s">
-        <v>5334</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
-        <v>5335</v>
+        <v>5336</v>
       </c>
       <c r="C848" s="6" t="s">
-        <v>5336</v>
+        <v>5337</v>
       </c>
       <c r="D848" s="6" t="s">
-        <v>5337</v>
+        <v>5338</v>
       </c>
       <c r="E848" s="6" t="s">
-        <v>5338</v>
+        <v>5339</v>
       </c>
       <c r="F848" s="6" t="s">
-        <v>5339</v>
+        <v>5340</v>
       </c>
       <c r="G848" s="6" t="s">
-        <v>5339</v>
+        <v>5341</v>
       </c>
       <c r="H848" s="6" t="s">
-        <v>5340</v>
+        <v>5342</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
-        <v>5341</v>
+        <v>5343</v>
       </c>
       <c r="C849" s="5" t="s">
-        <v>5342</v>
+        <v>5344</v>
       </c>
       <c r="D849" s="5" t="s">
-        <v>5343</v>
+        <v>5345</v>
       </c>
       <c r="E849" s="5" t="s">
-        <v>5344</v>
+        <v>5346</v>
       </c>
       <c r="F849" s="5" t="s">
-        <v>5345</v>
+        <v>5347</v>
       </c>
       <c r="G849" s="5" t="s">
-        <v>5346</v>
+        <v>5347</v>
       </c>
       <c r="H849" s="5" t="s">
-        <v>5347</v>
+        <v>5348</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
-        <v>5348</v>
+        <v>5349</v>
       </c>
       <c r="C850" s="6" t="s">
-        <v>5349</v>
+        <v>5350</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>5350</v>
+        <v>5351</v>
       </c>
       <c r="E850" s="6" t="s">
-        <v>5351</v>
+        <v>5352</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>5352</v>
+        <v>5353</v>
       </c>
       <c r="G850" s="6" t="s">
-        <v>5352</v>
+        <v>5353</v>
       </c>
       <c r="H850" s="6" t="s">
-        <v>5353</v>
+        <v>5354</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
-        <v>5354</v>
+        <v>5355</v>
       </c>
       <c r="C851" s="5" t="s">
-        <v>5355</v>
+        <v>5356</v>
       </c>
       <c r="D851" s="5" t="s">
-        <v>5356</v>
+        <v>5357</v>
       </c>
       <c r="E851" s="5" t="s">
-        <v>5357</v>
+        <v>5358</v>
       </c>
       <c r="F851" s="5" t="s">
-        <v>5358</v>
+        <v>5359</v>
       </c>
       <c r="G851" s="5" t="s">
-        <v>5358</v>
+        <v>5360</v>
       </c>
       <c r="H851" s="5" t="s">
-        <v>5359</v>
+        <v>5361</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
-        <v>5360</v>
+        <v>5362</v>
       </c>
       <c r="C852" s="6" t="s">
-        <v>5361</v>
+        <v>5363</v>
       </c>
       <c r="D852" s="6" t="s">
-        <v>5361</v>
+        <v>5364</v>
       </c>
       <c r="E852" s="6" t="s">
-        <v>5361</v>
+        <v>5365</v>
       </c>
       <c r="F852" s="6" t="s">
-        <v>5361</v>
+        <v>5366</v>
       </c>
       <c r="G852" s="6" t="s">
-        <v>5361</v>
+        <v>5366</v>
       </c>
       <c r="H852" s="6" t="s">
-        <v>5361</v>
+        <v>5367</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
-        <v>5362</v>
+        <v>5368</v>
       </c>
       <c r="C853" s="5" t="s">
-        <v>5363</v>
+        <v>5369</v>
       </c>
       <c r="D853" s="5" t="s">
-        <v>5364</v>
+        <v>5370</v>
       </c>
       <c r="E853" s="5" t="s">
-        <v>5365</v>
+        <v>5371</v>
       </c>
       <c r="F853" s="5" t="s">
-        <v>5366</v>
+        <v>5372</v>
       </c>
       <c r="G853" s="5" t="s">
-        <v>5366</v>
+        <v>5373</v>
       </c>
       <c r="H853" s="5" t="s">
-        <v>5364</v>
+        <v>5374</v>
       </c>
     </row>
     <row r="854">
       <c r="B854" s="6" t="s">
-        <v>5367</v>
+        <v>5375</v>
       </c>
       <c r="C854" s="6" t="s">
-        <v>5368</v>
+        <v>5376</v>
       </c>
       <c r="D854" s="6" t="s">
-        <v>5369</v>
+        <v>5377</v>
       </c>
       <c r="E854" s="6" t="s">
-        <v>5370</v>
+        <v>5378</v>
       </c>
       <c r="F854" s="6" t="s">
-        <v>5371</v>
+        <v>5379</v>
       </c>
       <c r="G854" s="6" t="s">
-        <v>5372</v>
+        <v>5379</v>
       </c>
       <c r="H854" s="6" t="s">
-        <v>5369</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="855">
       <c r="B855" s="5" t="s">
-        <v>5373</v>
+        <v>5381</v>
       </c>
       <c r="C855" s="5" t="s">
-        <v>5374</v>
+        <v>5382</v>
       </c>
       <c r="D855" s="5" t="s">
-        <v>5375</v>
+        <v>5383</v>
       </c>
       <c r="E855" s="5" t="s">
-        <v>5376</v>
+        <v>5384</v>
       </c>
       <c r="F855" s="5" t="s">
-        <v>5376</v>
+        <v>5385</v>
       </c>
       <c r="G855" s="5" t="s">
-        <v>5376</v>
+        <v>5385</v>
       </c>
       <c r="H855" s="5" t="s">
-        <v>5375</v>
+        <v>5386</v>
       </c>
     </row>
     <row r="856">
       <c r="B856" s="6" t="s">
-        <v>5377</v>
+        <v>5387</v>
       </c>
       <c r="C856" s="6" t="s">
-        <v>5378</v>
+        <v>5388</v>
       </c>
       <c r="D856" s="6" t="s">
-        <v>5379</v>
+        <v>5388</v>
       </c>
       <c r="E856" s="6" t="s">
-        <v>5380</v>
+        <v>5388</v>
       </c>
       <c r="F856" s="6" t="s">
-        <v>5380</v>
+        <v>5388</v>
       </c>
       <c r="G856" s="6" t="s">
-        <v>5380</v>
+        <v>5388</v>
       </c>
       <c r="H856" s="6" t="s">
-        <v>5379</v>
+        <v>5388</v>
       </c>
     </row>
     <row r="857">
       <c r="B857" s="5" t="s">
-        <v>5381</v>
+        <v>5389</v>
       </c>
       <c r="C857" s="5" t="s">
-        <v>5382</v>
+        <v>5390</v>
       </c>
       <c r="D857" s="5" t="s">
-        <v>5383</v>
+        <v>5391</v>
       </c>
       <c r="E857" s="5" t="s">
-        <v>5384</v>
+        <v>5392</v>
       </c>
       <c r="F857" s="5" t="s">
-        <v>5385</v>
+        <v>5393</v>
       </c>
       <c r="G857" s="5" t="s">
-        <v>5386</v>
+        <v>5393</v>
       </c>
       <c r="H857" s="5" t="s">
-        <v>5387</v>
+        <v>5391</v>
       </c>
     </row>
     <row r="858">
       <c r="B858" s="6" t="s">
-        <v>5388</v>
+        <v>5394</v>
       </c>
       <c r="C858" s="6" t="s">
-        <v>5389</v>
+        <v>5395</v>
       </c>
       <c r="D858" s="6" t="s">
-        <v>5390</v>
+        <v>5396</v>
       </c>
       <c r="E858" s="6" t="s">
-        <v>5391</v>
+        <v>5397</v>
       </c>
       <c r="F858" s="6" t="s">
-        <v>5392</v>
+        <v>5398</v>
       </c>
       <c r="G858" s="6" t="s">
-        <v>5393</v>
+        <v>5399</v>
       </c>
       <c r="H858" s="6" t="s">
-        <v>5390</v>
+        <v>5396</v>
       </c>
     </row>
     <row r="859">
       <c r="B859" s="5" t="s">
-        <v>5394</v>
+        <v>5400</v>
       </c>
       <c r="C859" s="5" t="s">
-        <v>5395</v>
+        <v>5401</v>
       </c>
       <c r="D859" s="5" t="s">
-        <v>5396</v>
+        <v>5402</v>
       </c>
       <c r="E859" s="5" t="s">
-        <v>5397</v>
+        <v>5403</v>
       </c>
       <c r="F859" s="5" t="s">
-        <v>5398</v>
+        <v>5403</v>
       </c>
       <c r="G859" s="5" t="s">
-        <v>5399</v>
+        <v>5403</v>
       </c>
       <c r="H859" s="5" t="s">
-        <v>5400</v>
+        <v>5402</v>
       </c>
     </row>
     <row r="860">
       <c r="B860" s="6" t="s">
-        <v>5401</v>
+        <v>5404</v>
       </c>
       <c r="C860" s="6" t="s">
-        <v>5402</v>
+        <v>5405</v>
       </c>
       <c r="D860" s="6" t="s">
-        <v>5403</v>
+        <v>5406</v>
       </c>
       <c r="E860" s="6" t="s">
-        <v>5404</v>
+        <v>5407</v>
       </c>
       <c r="F860" s="6" t="s">
-        <v>5405</v>
+        <v>5407</v>
       </c>
       <c r="G860" s="6" t="s">
+        <v>5407</v>
+      </c>
+      <c r="H860" s="6" t="s">
         <v>5406</v>
-      </c>
-      <c r="H860" s="6" t="s">
-        <v>5407</v>
       </c>
     </row>
     <row r="861">
@@ -36466,7 +36547,7 @@
         <v>5420</v>
       </c>
       <c r="H862" s="6" t="s">
-        <v>5390</v>
+        <v>5417</v>
       </c>
     </row>
     <row r="863">
@@ -36509,14 +36590,106 @@
         <v>5432</v>
       </c>
       <c r="G864" s="6" t="s">
-        <v>5432</v>
+        <v>5433</v>
       </c>
       <c r="H864" s="6" t="s">
-        <v>5433</v>
+        <v>5434</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="B865" s="5" t="s">
+        <v>5435</v>
+      </c>
+      <c r="C865" s="5" t="s">
+        <v>5436</v>
+      </c>
+      <c r="D865" s="5" t="s">
+        <v>5437</v>
+      </c>
+      <c r="E865" s="5" t="s">
+        <v>5438</v>
+      </c>
+      <c r="F865" s="5" t="s">
+        <v>5439</v>
+      </c>
+      <c r="G865" s="5" t="s">
+        <v>5440</v>
+      </c>
+      <c r="H865" s="5" t="s">
+        <v>5441</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="B866" s="6" t="s">
+        <v>5442</v>
+      </c>
+      <c r="C866" s="6" t="s">
+        <v>5443</v>
+      </c>
+      <c r="D866" s="6" t="s">
+        <v>5444</v>
+      </c>
+      <c r="E866" s="6" t="s">
+        <v>5445</v>
+      </c>
+      <c r="F866" s="6" t="s">
+        <v>5446</v>
+      </c>
+      <c r="G866" s="6" t="s">
+        <v>5447</v>
+      </c>
+      <c r="H866" s="6" t="s">
+        <v>5417</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="B867" s="5" t="s">
+        <v>5448</v>
+      </c>
+      <c r="C867" s="5" t="s">
+        <v>5449</v>
+      </c>
+      <c r="D867" s="5" t="s">
+        <v>5450</v>
+      </c>
+      <c r="E867" s="5" t="s">
+        <v>5451</v>
+      </c>
+      <c r="F867" s="5" t="s">
+        <v>5452</v>
+      </c>
+      <c r="G867" s="5" t="s">
+        <v>5453</v>
+      </c>
+      <c r="H867" s="5" t="s">
+        <v>5454</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="B868" s="6" t="s">
+        <v>5455</v>
+      </c>
+      <c r="C868" s="6" t="s">
+        <v>5456</v>
+      </c>
+      <c r="D868" s="6" t="s">
+        <v>5457</v>
+      </c>
+      <c r="E868" s="6" t="s">
+        <v>5458</v>
+      </c>
+      <c r="F868" s="6" t="s">
+        <v>5459</v>
+      </c>
+      <c r="G868" s="6" t="s">
+        <v>5459</v>
+      </c>
+      <c r="H868" s="6" t="s">
+        <v>5460</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H864"/>
+  <autoFilter ref="B2:H868"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36535,10 +36708,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5434</v>
+        <v>5461</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5435</v>
+        <v>5462</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36549,16 +36722,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5436</v>
+        <v>5463</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5437</v>
+        <v>5464</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5438</v>
+        <v>5465</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5439</v>
+        <v>5466</v>
       </c>
     </row>
     <row r="3">
@@ -36566,16 +36739,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5440</v>
+        <v>5467</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5441</v>
+        <v>5468</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5442</v>
+        <v>5469</v>
       </c>
     </row>
     <row r="4">
@@ -36586,24 +36759,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5443</v>
+        <v>5470</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5444</v>
+        <v>5471</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5445</v>
+        <v>5472</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5446</v>
+        <v>5473</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5447</v>
+        <v>5474</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36611,13 +36784,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5448</v>
+        <v>5475</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5449</v>
+        <v>5476</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36625,13 +36798,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5450</v>
+        <v>5477</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5451</v>
+        <v>5478</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36639,13 +36812,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5452</v>
+        <v>5479</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5453</v>
+        <v>5480</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36653,13 +36826,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5454</v>
+        <v>5481</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5455</v>
+        <v>5482</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36667,13 +36840,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5456</v>
+        <v>5483</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5457</v>
+        <v>5484</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36681,13 +36854,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5458</v>
+        <v>5485</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5459</v>
+        <v>5486</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36695,13 +36868,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5460</v>
+        <v>5487</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5461</v>
+        <v>5488</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36709,13 +36882,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5462</v>
+        <v>5489</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5463</v>
+        <v>5490</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36723,13 +36896,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5464</v>
+        <v>5491</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5465</v>
+        <v>5492</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36743,7 +36916,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5466</v>
+        <v>5493</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36751,13 +36924,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5467</v>
+        <v>5494</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5468</v>
+        <v>5495</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36765,13 +36938,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5469</v>
+        <v>5496</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5470</v>
+        <v>5497</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36779,13 +36952,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5471</v>
+        <v>5498</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5472</v>
+        <v>5499</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36793,13 +36966,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5473</v>
+        <v>5500</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5474</v>
+        <v>5501</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36807,13 +36980,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5475</v>
+        <v>5502</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5476</v>
+        <v>5503</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36821,13 +36994,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5477</v>
+        <v>5504</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5478</v>
+        <v>5505</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -36835,13 +37008,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5479</v>
+        <v>5506</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5480</v>
+        <v>5507</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -36849,13 +37022,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5481</v>
+        <v>5508</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5482</v>
+        <v>5509</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -36863,13 +37036,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5483</v>
+        <v>5510</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5484</v>
+        <v>5511</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$868]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$871]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6139" uniqueCount="5512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6160" uniqueCount="5532">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -13546,6 +13546,45 @@
     <t xml:space="preserve">Zinsen</t>
   </si>
   <si>
+    <t xml:space="preserve">ui.money.sell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売却</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出售所得</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkauf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.money.spent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구입</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">购买</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購買</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kauf</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.blind.small</t>
   </si>
   <si>
@@ -15953,6 +15992,27 @@
   </si>
   <si>
     <t xml:space="preserve">Mach Platz für 「{name}」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.swap.paid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">내놓은 것의 값은 그대로 들어옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You receive the full sell value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手放したものの値段はそのまま入ります</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出售所得会全额入账</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出售所得會全額入帳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Du erhältst den vollen Verkaufswert</t>
   </si>
   <si>
     <t xml:space="preserve">ui.card.enhancement</t>
@@ -16752,7 +16812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H868"/>
+  <dimension ref="A1:H871"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -33048,700 +33108,700 @@
         <v>4519</v>
       </c>
       <c r="G710" s="6" t="s">
-        <v>4519</v>
+        <v>4520</v>
       </c>
       <c r="H710" s="6" t="s">
-        <v>4520</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="711">
       <c r="B711" s="5" t="s">
-        <v>4521</v>
+        <v>4522</v>
       </c>
       <c r="C711" s="5" t="s">
-        <v>4522</v>
+        <v>4523</v>
       </c>
       <c r="D711" s="5" t="s">
-        <v>4523</v>
+        <v>4524</v>
       </c>
       <c r="E711" s="5" t="s">
-        <v>4524</v>
+        <v>4525</v>
       </c>
       <c r="F711" s="5" t="s">
-        <v>4523</v>
+        <v>4526</v>
       </c>
       <c r="G711" s="5" t="s">
-        <v>4523</v>
+        <v>4526</v>
       </c>
       <c r="H711" s="5" t="s">
-        <v>4523</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="712">
       <c r="B712" s="6" t="s">
-        <v>4525</v>
+        <v>4528</v>
       </c>
       <c r="C712" s="6" t="s">
-        <v>3610</v>
+        <v>4529</v>
       </c>
       <c r="D712" s="6" t="s">
-        <v>2981</v>
+        <v>4530</v>
       </c>
       <c r="E712" s="6" t="s">
-        <v>3612</v>
+        <v>4531</v>
       </c>
       <c r="F712" s="6" t="s">
-        <v>3613</v>
+        <v>4532</v>
       </c>
       <c r="G712" s="6" t="s">
-        <v>3613</v>
+        <v>4532</v>
       </c>
       <c r="H712" s="6" t="s">
-        <v>2981</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="713">
       <c r="B713" s="5" t="s">
-        <v>4526</v>
+        <v>4534</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>4527</v>
+        <v>4535</v>
       </c>
       <c r="D713" s="5" t="s">
-        <v>4528</v>
+        <v>4536</v>
       </c>
       <c r="E713" s="5" t="s">
-        <v>4529</v>
+        <v>4537</v>
       </c>
       <c r="F713" s="5" t="s">
-        <v>4529</v>
+        <v>4536</v>
       </c>
       <c r="G713" s="5" t="s">
-        <v>4529</v>
+        <v>4536</v>
       </c>
       <c r="H713" s="5" t="s">
-        <v>4530</v>
+        <v>4536</v>
       </c>
     </row>
     <row r="714">
       <c r="B714" s="6" t="s">
-        <v>4531</v>
+        <v>4538</v>
       </c>
       <c r="C714" s="6" t="s">
-        <v>3657</v>
+        <v>3610</v>
       </c>
       <c r="D714" s="6" t="s">
-        <v>4532</v>
+        <v>2981</v>
       </c>
       <c r="E714" s="6" t="s">
-        <v>3659</v>
+        <v>3612</v>
       </c>
       <c r="F714" s="6" t="s">
-        <v>3660</v>
+        <v>3613</v>
       </c>
       <c r="G714" s="6" t="s">
-        <v>3661</v>
+        <v>3613</v>
       </c>
       <c r="H714" s="6" t="s">
-        <v>4533</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="715">
       <c r="B715" s="5" t="s">
-        <v>4534</v>
+        <v>4539</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>3651</v>
+        <v>4540</v>
       </c>
       <c r="D715" s="5" t="s">
-        <v>4535</v>
+        <v>4541</v>
       </c>
       <c r="E715" s="5" t="s">
-        <v>3653</v>
+        <v>4542</v>
       </c>
       <c r="F715" s="5" t="s">
-        <v>3654</v>
+        <v>4542</v>
       </c>
       <c r="G715" s="5" t="s">
-        <v>3654</v>
+        <v>4542</v>
       </c>
       <c r="H715" s="5" t="s">
-        <v>4536</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="716">
       <c r="B716" s="6" t="s">
-        <v>4537</v>
+        <v>4544</v>
       </c>
       <c r="C716" s="6" t="s">
-        <v>4538</v>
+        <v>3657</v>
       </c>
       <c r="D716" s="6" t="s">
-        <v>4539</v>
+        <v>4545</v>
       </c>
       <c r="E716" s="6" t="s">
-        <v>4540</v>
+        <v>3659</v>
       </c>
       <c r="F716" s="6" t="s">
-        <v>4541</v>
+        <v>3660</v>
       </c>
       <c r="G716" s="6" t="s">
-        <v>4542</v>
+        <v>3661</v>
       </c>
       <c r="H716" s="6" t="s">
-        <v>4539</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="717">
       <c r="B717" s="5" t="s">
-        <v>4543</v>
+        <v>4547</v>
       </c>
       <c r="C717" s="5" t="s">
-        <v>4544</v>
+        <v>3651</v>
       </c>
       <c r="D717" s="5" t="s">
-        <v>4545</v>
+        <v>4548</v>
       </c>
       <c r="E717" s="5" t="s">
-        <v>4546</v>
+        <v>3653</v>
       </c>
       <c r="F717" s="5" t="s">
-        <v>4547</v>
+        <v>3654</v>
       </c>
       <c r="G717" s="5" t="s">
-        <v>4547</v>
+        <v>3654</v>
       </c>
       <c r="H717" s="5" t="s">
-        <v>4545</v>
+        <v>4549</v>
       </c>
     </row>
     <row r="718">
       <c r="B718" s="6" t="s">
-        <v>4548</v>
+        <v>4550</v>
       </c>
       <c r="C718" s="6" t="s">
-        <v>4549</v>
+        <v>4551</v>
       </c>
       <c r="D718" s="6" t="s">
-        <v>4550</v>
+        <v>4552</v>
       </c>
       <c r="E718" s="6" t="s">
-        <v>4551</v>
+        <v>4553</v>
       </c>
       <c r="F718" s="6" t="s">
+        <v>4554</v>
+      </c>
+      <c r="G718" s="6" t="s">
+        <v>4555</v>
+      </c>
+      <c r="H718" s="6" t="s">
         <v>4552</v>
-      </c>
-      <c r="G718" s="6" t="s">
-        <v>4553</v>
-      </c>
-      <c r="H718" s="6" t="s">
-        <v>4554</v>
       </c>
     </row>
     <row r="719">
       <c r="B719" s="5" t="s">
-        <v>4555</v>
+        <v>4556</v>
       </c>
       <c r="C719" s="5" t="s">
-        <v>3749</v>
+        <v>4557</v>
       </c>
       <c r="D719" s="5" t="s">
-        <v>4556</v>
+        <v>4558</v>
       </c>
       <c r="E719" s="5" t="s">
-        <v>3751</v>
+        <v>4559</v>
       </c>
       <c r="F719" s="5" t="s">
-        <v>3752</v>
+        <v>4560</v>
       </c>
       <c r="G719" s="5" t="s">
-        <v>3752</v>
+        <v>4560</v>
       </c>
       <c r="H719" s="5" t="s">
-        <v>3753</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="720">
       <c r="B720" s="6" t="s">
-        <v>4557</v>
+        <v>4561</v>
       </c>
       <c r="C720" s="6" t="s">
-        <v>4558</v>
+        <v>4562</v>
       </c>
       <c r="D720" s="6" t="s">
-        <v>4359</v>
+        <v>4563</v>
       </c>
       <c r="E720" s="6" t="s">
-        <v>4559</v>
+        <v>4564</v>
       </c>
       <c r="F720" s="6" t="s">
-        <v>4560</v>
+        <v>4565</v>
       </c>
       <c r="G720" s="6" t="s">
-        <v>4561</v>
+        <v>4566</v>
       </c>
       <c r="H720" s="6" t="s">
-        <v>4359</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="721">
       <c r="B721" s="5" t="s">
-        <v>4562</v>
+        <v>4568</v>
       </c>
       <c r="C721" s="5" t="s">
-        <v>4563</v>
+        <v>3749</v>
       </c>
       <c r="D721" s="5" t="s">
-        <v>4564</v>
+        <v>4569</v>
       </c>
       <c r="E721" s="5" t="s">
-        <v>4565</v>
+        <v>3751</v>
       </c>
       <c r="F721" s="5" t="s">
-        <v>4566</v>
+        <v>3752</v>
       </c>
       <c r="G721" s="5" t="s">
-        <v>4566</v>
+        <v>3752</v>
       </c>
       <c r="H721" s="5" t="s">
-        <v>4564</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="722">
       <c r="B722" s="6" t="s">
-        <v>4567</v>
+        <v>4570</v>
       </c>
       <c r="C722" s="6" t="s">
-        <v>4568</v>
+        <v>4571</v>
       </c>
       <c r="D722" s="6" t="s">
-        <v>4569</v>
+        <v>4359</v>
       </c>
       <c r="E722" s="6" t="s">
-        <v>4570</v>
+        <v>4572</v>
       </c>
       <c r="F722" s="6" t="s">
-        <v>4571</v>
+        <v>4573</v>
       </c>
       <c r="G722" s="6" t="s">
-        <v>4571</v>
+        <v>4574</v>
       </c>
       <c r="H722" s="6" t="s">
-        <v>4572</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="723">
       <c r="B723" s="5" t="s">
-        <v>4573</v>
+        <v>4575</v>
       </c>
       <c r="C723" s="5" t="s">
-        <v>3741</v>
+        <v>4576</v>
       </c>
       <c r="D723" s="5" t="s">
-        <v>4564</v>
+        <v>4577</v>
       </c>
       <c r="E723" s="5" t="s">
-        <v>3743</v>
+        <v>4578</v>
       </c>
       <c r="F723" s="5" t="s">
-        <v>3744</v>
+        <v>4579</v>
       </c>
       <c r="G723" s="5" t="s">
-        <v>3744</v>
+        <v>4579</v>
       </c>
       <c r="H723" s="5" t="s">
-        <v>3745</v>
+        <v>4577</v>
       </c>
     </row>
     <row r="724">
       <c r="B724" s="6" t="s">
-        <v>4574</v>
+        <v>4580</v>
       </c>
       <c r="C724" s="6" t="s">
-        <v>3623</v>
+        <v>4581</v>
       </c>
       <c r="D724" s="6" t="s">
-        <v>4575</v>
+        <v>4582</v>
       </c>
       <c r="E724" s="6" t="s">
-        <v>3625</v>
+        <v>4583</v>
       </c>
       <c r="F724" s="6" t="s">
-        <v>3626</v>
+        <v>4584</v>
       </c>
       <c r="G724" s="6" t="s">
-        <v>3627</v>
+        <v>4584</v>
       </c>
       <c r="H724" s="6" t="s">
-        <v>4576</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="725">
       <c r="B725" s="5" t="s">
+        <v>4586</v>
+      </c>
+      <c r="C725" s="5" t="s">
+        <v>3741</v>
+      </c>
+      <c r="D725" s="5" t="s">
         <v>4577</v>
       </c>
-      <c r="C725" s="5" t="s">
-        <v>4578</v>
-      </c>
-      <c r="D725" s="5" t="s">
-        <v>4579</v>
-      </c>
       <c r="E725" s="5" t="s">
-        <v>4580</v>
+        <v>3743</v>
       </c>
       <c r="F725" s="5" t="s">
-        <v>4581</v>
+        <v>3744</v>
       </c>
       <c r="G725" s="5" t="s">
-        <v>4581</v>
+        <v>3744</v>
       </c>
       <c r="H725" s="5" t="s">
-        <v>4582</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="726">
       <c r="B726" s="6" t="s">
-        <v>4583</v>
+        <v>4587</v>
       </c>
       <c r="C726" s="6" t="s">
-        <v>4584</v>
+        <v>3623</v>
       </c>
       <c r="D726" s="6" t="s">
-        <v>4585</v>
+        <v>4588</v>
       </c>
       <c r="E726" s="6" t="s">
-        <v>4586</v>
+        <v>3625</v>
       </c>
       <c r="F726" s="6" t="s">
-        <v>4586</v>
+        <v>3626</v>
       </c>
       <c r="G726" s="6" t="s">
-        <v>4586</v>
+        <v>3627</v>
       </c>
       <c r="H726" s="6" t="s">
-        <v>4587</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="727">
       <c r="B727" s="5" t="s">
-        <v>4588</v>
+        <v>4590</v>
       </c>
       <c r="C727" s="5" t="s">
-        <v>4589</v>
+        <v>4591</v>
       </c>
       <c r="D727" s="5" t="s">
-        <v>4590</v>
+        <v>4592</v>
       </c>
       <c r="E727" s="5" t="s">
-        <v>4591</v>
+        <v>4593</v>
       </c>
       <c r="F727" s="5" t="s">
-        <v>4592</v>
+        <v>4594</v>
       </c>
       <c r="G727" s="5" t="s">
-        <v>4592</v>
+        <v>4594</v>
       </c>
       <c r="H727" s="5" t="s">
-        <v>4593</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="728">
       <c r="B728" s="6" t="s">
-        <v>4594</v>
+        <v>4596</v>
       </c>
       <c r="C728" s="6" t="s">
-        <v>3808</v>
+        <v>4597</v>
       </c>
       <c r="D728" s="6" t="s">
-        <v>4595</v>
+        <v>4598</v>
       </c>
       <c r="E728" s="6" t="s">
-        <v>3810</v>
+        <v>4599</v>
       </c>
       <c r="F728" s="6" t="s">
-        <v>2116</v>
+        <v>4599</v>
       </c>
       <c r="G728" s="6" t="s">
-        <v>2116</v>
+        <v>4599</v>
       </c>
       <c r="H728" s="6" t="s">
-        <v>4596</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="729">
       <c r="B729" s="5" t="s">
-        <v>4597</v>
+        <v>4601</v>
       </c>
       <c r="C729" s="5" t="s">
-        <v>3813</v>
+        <v>4602</v>
       </c>
       <c r="D729" s="5" t="s">
-        <v>4598</v>
+        <v>4603</v>
       </c>
       <c r="E729" s="5" t="s">
-        <v>3815</v>
+        <v>4604</v>
       </c>
       <c r="F729" s="5" t="s">
-        <v>3816</v>
+        <v>4605</v>
       </c>
       <c r="G729" s="5" t="s">
-        <v>3817</v>
+        <v>4605</v>
       </c>
       <c r="H729" s="5" t="s">
-        <v>4599</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="730">
       <c r="B730" s="6" t="s">
-        <v>4600</v>
+        <v>4607</v>
       </c>
       <c r="C730" s="6" t="s">
-        <v>3820</v>
+        <v>3808</v>
       </c>
       <c r="D730" s="6" t="s">
-        <v>4601</v>
+        <v>4608</v>
       </c>
       <c r="E730" s="6" t="s">
-        <v>3822</v>
+        <v>3810</v>
       </c>
       <c r="F730" s="6" t="s">
-        <v>3823</v>
+        <v>2116</v>
       </c>
       <c r="G730" s="6" t="s">
-        <v>3823</v>
+        <v>2116</v>
       </c>
       <c r="H730" s="6" t="s">
-        <v>4602</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="731">
       <c r="B731" s="5" t="s">
-        <v>4603</v>
+        <v>4610</v>
       </c>
       <c r="C731" s="5" t="s">
-        <v>2210</v>
+        <v>3813</v>
       </c>
       <c r="D731" s="5" t="s">
-        <v>2211</v>
+        <v>4611</v>
       </c>
       <c r="E731" s="5" t="s">
-        <v>2212</v>
+        <v>3815</v>
       </c>
       <c r="F731" s="5" t="s">
-        <v>2213</v>
+        <v>3816</v>
       </c>
       <c r="G731" s="5" t="s">
-        <v>2214</v>
+        <v>3817</v>
       </c>
       <c r="H731" s="5" t="s">
-        <v>2215</v>
+        <v>4612</v>
       </c>
     </row>
     <row r="732">
       <c r="B732" s="6" t="s">
-        <v>4604</v>
+        <v>4613</v>
       </c>
       <c r="C732" s="6" t="s">
-        <v>2076</v>
+        <v>3820</v>
       </c>
       <c r="D732" s="6" t="s">
-        <v>2077</v>
+        <v>4614</v>
       </c>
       <c r="E732" s="6" t="s">
-        <v>2078</v>
+        <v>3822</v>
       </c>
       <c r="F732" s="6" t="s">
-        <v>2079</v>
+        <v>3823</v>
       </c>
       <c r="G732" s="6" t="s">
-        <v>2080</v>
+        <v>3823</v>
       </c>
       <c r="H732" s="6" t="s">
-        <v>2077</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="733">
       <c r="B733" s="5" t="s">
-        <v>4605</v>
+        <v>4616</v>
       </c>
       <c r="C733" s="5" t="s">
-        <v>2062</v>
+        <v>2210</v>
       </c>
       <c r="D733" s="5" t="s">
-        <v>2063</v>
+        <v>2211</v>
       </c>
       <c r="E733" s="5" t="s">
-        <v>2064</v>
+        <v>2212</v>
       </c>
       <c r="F733" s="5" t="s">
-        <v>2065</v>
+        <v>2213</v>
       </c>
       <c r="G733" s="5" t="s">
-        <v>2066</v>
+        <v>2214</v>
       </c>
       <c r="H733" s="5" t="s">
-        <v>2067</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="734">
       <c r="B734" s="6" t="s">
-        <v>4606</v>
+        <v>4617</v>
       </c>
       <c r="C734" s="6" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="D734" s="6" t="s">
-        <v>2057</v>
+        <v>2077</v>
       </c>
       <c r="E734" s="6" t="s">
-        <v>2058</v>
+        <v>2078</v>
       </c>
       <c r="F734" s="6" t="s">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="G734" s="6" t="s">
-        <v>2059</v>
+        <v>2080</v>
       </c>
       <c r="H734" s="6" t="s">
-        <v>2060</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="735">
       <c r="B735" s="5" t="s">
-        <v>4607</v>
+        <v>4618</v>
       </c>
       <c r="C735" s="5" t="s">
-        <v>2069</v>
+        <v>2062</v>
       </c>
       <c r="D735" s="5" t="s">
-        <v>2070</v>
+        <v>2063</v>
       </c>
       <c r="E735" s="5" t="s">
-        <v>2071</v>
+        <v>2064</v>
       </c>
       <c r="F735" s="5" t="s">
-        <v>2072</v>
+        <v>2065</v>
       </c>
       <c r="G735" s="5" t="s">
-        <v>2073</v>
+        <v>2066</v>
       </c>
       <c r="H735" s="5" t="s">
-        <v>2074</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="736">
       <c r="B736" s="6" t="s">
-        <v>4608</v>
+        <v>4619</v>
       </c>
       <c r="C736" s="6" t="s">
-        <v>2050</v>
+        <v>2056</v>
       </c>
       <c r="D736" s="6" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
       <c r="E736" s="6" t="s">
-        <v>2052</v>
+        <v>2058</v>
       </c>
       <c r="F736" s="6" t="s">
-        <v>2053</v>
+        <v>2059</v>
       </c>
       <c r="G736" s="6" t="s">
-        <v>2054</v>
+        <v>2059</v>
       </c>
       <c r="H736" s="6" t="s">
-        <v>2051</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="737">
       <c r="B737" s="5" t="s">
-        <v>4609</v>
+        <v>4620</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>2082</v>
+        <v>2069</v>
       </c>
       <c r="D737" s="5" t="s">
-        <v>2083</v>
+        <v>2070</v>
       </c>
       <c r="E737" s="5" t="s">
-        <v>2084</v>
+        <v>2071</v>
       </c>
       <c r="F737" s="5" t="s">
-        <v>2085</v>
+        <v>2072</v>
       </c>
       <c r="G737" s="5" t="s">
-        <v>2086</v>
+        <v>2073</v>
       </c>
       <c r="H737" s="5" t="s">
-        <v>2087</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="738">
       <c r="B738" s="6" t="s">
-        <v>4610</v>
+        <v>4621</v>
       </c>
       <c r="C738" s="6" t="s">
-        <v>4611</v>
+        <v>2050</v>
       </c>
       <c r="D738" s="6" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="E738" s="6" t="s">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="F738" s="6" t="s">
-        <v>2048</v>
+        <v>2053</v>
       </c>
       <c r="G738" s="6" t="s">
-        <v>2048</v>
+        <v>2054</v>
       </c>
       <c r="H738" s="6" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="739">
       <c r="B739" s="5" t="s">
-        <v>4612</v>
+        <v>4622</v>
       </c>
       <c r="C739" s="5" t="s">
-        <v>4613</v>
+        <v>2082</v>
       </c>
       <c r="D739" s="5" t="s">
-        <v>4614</v>
+        <v>2083</v>
       </c>
       <c r="E739" s="5" t="s">
-        <v>4615</v>
+        <v>2084</v>
       </c>
       <c r="F739" s="5" t="s">
-        <v>4616</v>
+        <v>2085</v>
       </c>
       <c r="G739" s="5" t="s">
-        <v>4617</v>
+        <v>2086</v>
       </c>
       <c r="H739" s="5" t="s">
-        <v>4614</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="740">
       <c r="B740" s="6" t="s">
-        <v>4618</v>
+        <v>4623</v>
       </c>
       <c r="C740" s="6" t="s">
-        <v>4619</v>
+        <v>4624</v>
       </c>
       <c r="D740" s="6" t="s">
-        <v>4620</v>
+        <v>2046</v>
       </c>
       <c r="E740" s="6" t="s">
-        <v>4621</v>
+        <v>2047</v>
       </c>
       <c r="F740" s="6" t="s">
-        <v>4622</v>
+        <v>2048</v>
       </c>
       <c r="G740" s="6" t="s">
-        <v>4623</v>
+        <v>2048</v>
       </c>
       <c r="H740" s="6" t="s">
-        <v>4624</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="741">
@@ -33764,47 +33824,47 @@
         <v>4630</v>
       </c>
       <c r="H741" s="5" t="s">
-        <v>4631</v>
+        <v>4627</v>
       </c>
     </row>
     <row r="742">
       <c r="B742" s="6" t="s">
+        <v>4631</v>
+      </c>
+      <c r="C742" s="6" t="s">
         <v>4632</v>
       </c>
-      <c r="C742" s="6" t="s">
+      <c r="D742" s="6" t="s">
         <v>4633</v>
       </c>
-      <c r="D742" s="6" t="s">
+      <c r="E742" s="6" t="s">
         <v>4634</v>
       </c>
-      <c r="E742" s="6" t="s">
+      <c r="F742" s="6" t="s">
         <v>4635</v>
       </c>
-      <c r="F742" s="6" t="s">
+      <c r="G742" s="6" t="s">
         <v>4636</v>
       </c>
-      <c r="G742" s="6" t="s">
+      <c r="H742" s="6" t="s">
         <v>4637</v>
-      </c>
-      <c r="H742" s="6" t="s">
-        <v>4638</v>
       </c>
     </row>
     <row r="743">
       <c r="B743" s="5" t="s">
+        <v>4638</v>
+      </c>
+      <c r="C743" s="5" t="s">
         <v>4639</v>
       </c>
-      <c r="C743" s="5" t="s">
+      <c r="D743" s="5" t="s">
         <v>4640</v>
       </c>
-      <c r="D743" s="5" t="s">
+      <c r="E743" s="5" t="s">
         <v>4641</v>
       </c>
-      <c r="E743" s="5" t="s">
+      <c r="F743" s="5" t="s">
         <v>4642</v>
-      </c>
-      <c r="F743" s="5" t="s">
-        <v>4643</v>
       </c>
       <c r="G743" s="5" t="s">
         <v>4643</v>
@@ -33853,119 +33913,119 @@
         <v>4656</v>
       </c>
       <c r="G745" s="5" t="s">
+        <v>4656</v>
+      </c>
+      <c r="H745" s="5" t="s">
         <v>4657</v>
-      </c>
-      <c r="H745" s="5" t="s">
-        <v>4658</v>
       </c>
     </row>
     <row r="746">
       <c r="B746" s="6" t="s">
+        <v>4658</v>
+      </c>
+      <c r="C746" s="6" t="s">
         <v>4659</v>
       </c>
-      <c r="C746" s="6" t="s">
+      <c r="D746" s="6" t="s">
         <v>4660</v>
       </c>
-      <c r="D746" s="6" t="s">
+      <c r="E746" s="6" t="s">
         <v>4661</v>
-      </c>
-      <c r="E746" s="6" t="s">
-        <v>4662</v>
       </c>
       <c r="F746" s="6" t="s">
         <v>4662</v>
       </c>
       <c r="G746" s="6" t="s">
-        <v>4662</v>
+        <v>4663</v>
       </c>
       <c r="H746" s="6" t="s">
-        <v>4663</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="747">
       <c r="B747" s="5" t="s">
-        <v>4664</v>
+        <v>4665</v>
       </c>
       <c r="C747" s="5" t="s">
-        <v>4665</v>
+        <v>4666</v>
       </c>
       <c r="D747" s="5" t="s">
-        <v>4666</v>
+        <v>4667</v>
       </c>
       <c r="E747" s="5" t="s">
-        <v>4667</v>
+        <v>4668</v>
       </c>
       <c r="F747" s="5" t="s">
-        <v>4668</v>
+        <v>4669</v>
       </c>
       <c r="G747" s="5" t="s">
-        <v>4669</v>
+        <v>4670</v>
       </c>
       <c r="H747" s="5" t="s">
-        <v>4670</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="748">
       <c r="B748" s="6" t="s">
-        <v>4671</v>
+        <v>4672</v>
       </c>
       <c r="C748" s="6" t="s">
-        <v>4672</v>
+        <v>4673</v>
       </c>
       <c r="D748" s="6" t="s">
-        <v>4673</v>
+        <v>4674</v>
       </c>
       <c r="E748" s="6" t="s">
-        <v>4674</v>
+        <v>4675</v>
       </c>
       <c r="F748" s="6" t="s">
         <v>4675</v>
       </c>
       <c r="G748" s="6" t="s">
+        <v>4675</v>
+      </c>
+      <c r="H748" s="6" t="s">
         <v>4676</v>
-      </c>
-      <c r="H748" s="6" t="s">
-        <v>4677</v>
       </c>
     </row>
     <row r="749">
       <c r="B749" s="5" t="s">
+        <v>4677</v>
+      </c>
+      <c r="C749" s="5" t="s">
         <v>4678</v>
       </c>
-      <c r="C749" s="5" t="s">
+      <c r="D749" s="5" t="s">
         <v>4679</v>
       </c>
-      <c r="D749" s="5" t="s">
+      <c r="E749" s="5" t="s">
         <v>4680</v>
       </c>
-      <c r="E749" s="5" t="s">
+      <c r="F749" s="5" t="s">
         <v>4681</v>
       </c>
-      <c r="F749" s="5" t="s">
+      <c r="G749" s="5" t="s">
         <v>4682</v>
       </c>
-      <c r="G749" s="5" t="s">
+      <c r="H749" s="5" t="s">
         <v>4683</v>
-      </c>
-      <c r="H749" s="5" t="s">
-        <v>4684</v>
       </c>
     </row>
     <row r="750">
       <c r="B750" s="6" t="s">
+        <v>4684</v>
+      </c>
+      <c r="C750" s="6" t="s">
         <v>4685</v>
       </c>
-      <c r="C750" s="6" t="s">
+      <c r="D750" s="6" t="s">
         <v>4686</v>
       </c>
-      <c r="D750" s="6" t="s">
+      <c r="E750" s="6" t="s">
         <v>4687</v>
       </c>
-      <c r="E750" s="6" t="s">
+      <c r="F750" s="6" t="s">
         <v>4688</v>
-      </c>
-      <c r="F750" s="6" t="s">
-        <v>4689</v>
       </c>
       <c r="G750" s="6" t="s">
         <v>4689</v>
@@ -33991,27 +34051,27 @@
         <v>4695</v>
       </c>
       <c r="G751" s="5" t="s">
-        <v>4695</v>
+        <v>4696</v>
       </c>
       <c r="H751" s="5" t="s">
-        <v>4696</v>
+        <v>4697</v>
       </c>
     </row>
     <row r="752">
       <c r="B752" s="6" t="s">
-        <v>4697</v>
+        <v>4698</v>
       </c>
       <c r="C752" s="6" t="s">
-        <v>4698</v>
+        <v>4699</v>
       </c>
       <c r="D752" s="6" t="s">
-        <v>4699</v>
+        <v>4700</v>
       </c>
       <c r="E752" s="6" t="s">
-        <v>4700</v>
+        <v>4701</v>
       </c>
       <c r="F752" s="6" t="s">
-        <v>4701</v>
+        <v>4702</v>
       </c>
       <c r="G752" s="6" t="s">
         <v>4702</v>
@@ -34083,211 +34143,211 @@
         <v>4721</v>
       </c>
       <c r="G755" s="5" t="s">
+        <v>4721</v>
+      </c>
+      <c r="H755" s="5" t="s">
         <v>4722</v>
-      </c>
-      <c r="H755" s="5" t="s">
-        <v>4723</v>
       </c>
     </row>
     <row r="756">
       <c r="B756" s="6" t="s">
+        <v>4723</v>
+      </c>
+      <c r="C756" s="6" t="s">
         <v>4724</v>
       </c>
-      <c r="C756" s="6" t="s">
+      <c r="D756" s="6" t="s">
         <v>4725</v>
       </c>
-      <c r="D756" s="6" t="s">
+      <c r="E756" s="6" t="s">
         <v>4726</v>
       </c>
-      <c r="E756" s="6" t="s">
+      <c r="F756" s="6" t="s">
         <v>4727</v>
       </c>
-      <c r="F756" s="6" t="s">
+      <c r="G756" s="6" t="s">
         <v>4728</v>
       </c>
-      <c r="G756" s="6" t="s">
+      <c r="H756" s="6" t="s">
         <v>4729</v>
-      </c>
-      <c r="H756" s="6" t="s">
-        <v>4730</v>
       </c>
     </row>
     <row r="757">
       <c r="B757" s="5" t="s">
+        <v>4730</v>
+      </c>
+      <c r="C757" s="5" t="s">
         <v>4731</v>
       </c>
-      <c r="C757" s="5" t="s">
+      <c r="D757" s="5" t="s">
         <v>4732</v>
       </c>
-      <c r="D757" s="5" t="s">
+      <c r="E757" s="5" t="s">
         <v>4733</v>
       </c>
-      <c r="E757" s="5" t="s">
+      <c r="F757" s="5" t="s">
         <v>4734</v>
       </c>
-      <c r="F757" s="5" t="s">
+      <c r="G757" s="5" t="s">
         <v>4735</v>
       </c>
-      <c r="G757" s="5" t="s">
+      <c r="H757" s="5" t="s">
         <v>4736</v>
-      </c>
-      <c r="H757" s="5" t="s">
-        <v>4737</v>
       </c>
     </row>
     <row r="758">
       <c r="B758" s="6" t="s">
+        <v>4737</v>
+      </c>
+      <c r="C758" s="6" t="s">
         <v>4738</v>
       </c>
-      <c r="C758" s="6" t="s">
+      <c r="D758" s="6" t="s">
         <v>4739</v>
       </c>
-      <c r="D758" s="6" t="s">
+      <c r="E758" s="6" t="s">
         <v>4740</v>
       </c>
-      <c r="E758" s="6" t="s">
+      <c r="F758" s="6" t="s">
         <v>4741</v>
       </c>
-      <c r="F758" s="6" t="s">
+      <c r="G758" s="6" t="s">
         <v>4742</v>
       </c>
-      <c r="G758" s="6" t="s">
+      <c r="H758" s="6" t="s">
         <v>4743</v>
-      </c>
-      <c r="H758" s="6" t="s">
-        <v>4744</v>
       </c>
     </row>
     <row r="759">
       <c r="B759" s="5" t="s">
+        <v>4744</v>
+      </c>
+      <c r="C759" s="5" t="s">
         <v>4745</v>
       </c>
-      <c r="C759" s="5" t="s">
+      <c r="D759" s="5" t="s">
         <v>4746</v>
       </c>
-      <c r="D759" s="5" t="s">
+      <c r="E759" s="5" t="s">
         <v>4747</v>
       </c>
-      <c r="E759" s="5" t="s">
+      <c r="F759" s="5" t="s">
         <v>4748</v>
       </c>
-      <c r="F759" s="5" t="s">
+      <c r="G759" s="5" t="s">
         <v>4749</v>
       </c>
-      <c r="G759" s="5" t="s">
+      <c r="H759" s="5" t="s">
         <v>4750</v>
-      </c>
-      <c r="H759" s="5" t="s">
-        <v>4751</v>
       </c>
     </row>
     <row r="760">
       <c r="B760" s="6" t="s">
+        <v>4751</v>
+      </c>
+      <c r="C760" s="6" t="s">
         <v>4752</v>
       </c>
-      <c r="C760" s="6" t="s">
+      <c r="D760" s="6" t="s">
         <v>4753</v>
       </c>
-      <c r="D760" s="6" t="s">
+      <c r="E760" s="6" t="s">
         <v>4754</v>
       </c>
-      <c r="E760" s="6" t="s">
+      <c r="F760" s="6" t="s">
         <v>4755</v>
       </c>
-      <c r="F760" s="6" t="s">
+      <c r="G760" s="6" t="s">
         <v>4756</v>
       </c>
-      <c r="G760" s="6" t="s">
+      <c r="H760" s="6" t="s">
         <v>4757</v>
-      </c>
-      <c r="H760" s="6" t="s">
-        <v>4758</v>
       </c>
     </row>
     <row r="761">
       <c r="B761" s="5" t="s">
+        <v>4758</v>
+      </c>
+      <c r="C761" s="5" t="s">
         <v>4759</v>
       </c>
-      <c r="C761" s="5" t="s">
+      <c r="D761" s="5" t="s">
         <v>4760</v>
       </c>
-      <c r="D761" s="5" t="s">
+      <c r="E761" s="5" t="s">
         <v>4761</v>
       </c>
-      <c r="E761" s="5" t="s">
+      <c r="F761" s="5" t="s">
         <v>4762</v>
       </c>
-      <c r="F761" s="5" t="s">
+      <c r="G761" s="5" t="s">
         <v>4763</v>
       </c>
-      <c r="G761" s="5" t="s">
+      <c r="H761" s="5" t="s">
         <v>4764</v>
-      </c>
-      <c r="H761" s="5" t="s">
-        <v>4765</v>
       </c>
     </row>
     <row r="762">
       <c r="B762" s="6" t="s">
+        <v>4765</v>
+      </c>
+      <c r="C762" s="6" t="s">
         <v>4766</v>
       </c>
-      <c r="C762" s="6" t="s">
+      <c r="D762" s="6" t="s">
         <v>4767</v>
       </c>
-      <c r="D762" s="6" t="s">
+      <c r="E762" s="6" t="s">
         <v>4768</v>
       </c>
-      <c r="E762" s="6" t="s">
+      <c r="F762" s="6" t="s">
         <v>4769</v>
       </c>
-      <c r="F762" s="6" t="s">
+      <c r="G762" s="6" t="s">
         <v>4770</v>
       </c>
-      <c r="G762" s="6" t="s">
+      <c r="H762" s="6" t="s">
         <v>4771</v>
-      </c>
-      <c r="H762" s="6" t="s">
-        <v>4772</v>
       </c>
     </row>
     <row r="763">
       <c r="B763" s="5" t="s">
+        <v>4772</v>
+      </c>
+      <c r="C763" s="5" t="s">
         <v>4773</v>
       </c>
-      <c r="C763" s="5" t="s">
+      <c r="D763" s="5" t="s">
         <v>4774</v>
       </c>
-      <c r="D763" s="5" t="s">
+      <c r="E763" s="5" t="s">
         <v>4775</v>
       </c>
-      <c r="E763" s="5" t="s">
+      <c r="F763" s="5" t="s">
         <v>4776</v>
       </c>
-      <c r="F763" s="5" t="s">
+      <c r="G763" s="5" t="s">
         <v>4777</v>
       </c>
-      <c r="G763" s="5" t="s">
+      <c r="H763" s="5" t="s">
         <v>4778</v>
-      </c>
-      <c r="H763" s="5" t="s">
-        <v>4779</v>
       </c>
     </row>
     <row r="764">
       <c r="B764" s="6" t="s">
+        <v>4779</v>
+      </c>
+      <c r="C764" s="6" t="s">
         <v>4780</v>
       </c>
-      <c r="C764" s="6" t="s">
+      <c r="D764" s="6" t="s">
         <v>4781</v>
       </c>
-      <c r="D764" s="6" t="s">
+      <c r="E764" s="6" t="s">
         <v>4782</v>
       </c>
-      <c r="E764" s="6" t="s">
+      <c r="F764" s="6" t="s">
         <v>4783</v>
-      </c>
-      <c r="F764" s="6" t="s">
-        <v>4784</v>
       </c>
       <c r="G764" s="6" t="s">
         <v>4784</v>
@@ -34336,349 +34396,349 @@
         <v>4797</v>
       </c>
       <c r="G766" s="6" t="s">
+        <v>4797</v>
+      </c>
+      <c r="H766" s="6" t="s">
         <v>4798</v>
-      </c>
-      <c r="H766" s="6" t="s">
-        <v>4799</v>
       </c>
     </row>
     <row r="767">
       <c r="B767" s="5" t="s">
+        <v>4799</v>
+      </c>
+      <c r="C767" s="5" t="s">
         <v>4800</v>
       </c>
-      <c r="C767" s="5" t="s">
+      <c r="D767" s="5" t="s">
         <v>4801</v>
       </c>
-      <c r="D767" s="5" t="s">
+      <c r="E767" s="5" t="s">
         <v>4802</v>
       </c>
-      <c r="E767" s="5" t="s">
+      <c r="F767" s="5" t="s">
         <v>4803</v>
       </c>
-      <c r="F767" s="5" t="s">
+      <c r="G767" s="5" t="s">
         <v>4804</v>
       </c>
-      <c r="G767" s="5" t="s">
+      <c r="H767" s="5" t="s">
         <v>4805</v>
-      </c>
-      <c r="H767" s="5" t="s">
-        <v>4806</v>
       </c>
     </row>
     <row r="768">
       <c r="B768" s="6" t="s">
+        <v>4806</v>
+      </c>
+      <c r="C768" s="6" t="s">
         <v>4807</v>
       </c>
-      <c r="C768" s="6" t="s">
+      <c r="D768" s="6" t="s">
         <v>4808</v>
       </c>
-      <c r="D768" s="6" t="s">
+      <c r="E768" s="6" t="s">
         <v>4809</v>
       </c>
-      <c r="E768" s="6" t="s">
+      <c r="F768" s="6" t="s">
         <v>4810</v>
       </c>
-      <c r="F768" s="6" t="s">
+      <c r="G768" s="6" t="s">
         <v>4811</v>
       </c>
-      <c r="G768" s="6" t="s">
+      <c r="H768" s="6" t="s">
         <v>4812</v>
-      </c>
-      <c r="H768" s="6" t="s">
-        <v>4813</v>
       </c>
     </row>
     <row r="769">
       <c r="B769" s="5" t="s">
+        <v>4813</v>
+      </c>
+      <c r="C769" s="5" t="s">
         <v>4814</v>
       </c>
-      <c r="C769" s="5" t="s">
+      <c r="D769" s="5" t="s">
         <v>4815</v>
       </c>
-      <c r="D769" s="5" t="s">
+      <c r="E769" s="5" t="s">
         <v>4816</v>
       </c>
-      <c r="E769" s="5" t="s">
+      <c r="F769" s="5" t="s">
         <v>4817</v>
       </c>
-      <c r="F769" s="5" t="s">
+      <c r="G769" s="5" t="s">
         <v>4818</v>
       </c>
-      <c r="G769" s="5" t="s">
+      <c r="H769" s="5" t="s">
         <v>4819</v>
-      </c>
-      <c r="H769" s="5" t="s">
-        <v>4820</v>
       </c>
     </row>
     <row r="770">
       <c r="B770" s="6" t="s">
+        <v>4820</v>
+      </c>
+      <c r="C770" s="6" t="s">
         <v>4821</v>
       </c>
-      <c r="C770" s="6" t="s">
+      <c r="D770" s="6" t="s">
         <v>4822</v>
       </c>
-      <c r="D770" s="6" t="s">
+      <c r="E770" s="6" t="s">
         <v>4823</v>
       </c>
-      <c r="E770" s="6" t="s">
+      <c r="F770" s="6" t="s">
         <v>4824</v>
       </c>
-      <c r="F770" s="6" t="s">
+      <c r="G770" s="6" t="s">
         <v>4825</v>
       </c>
-      <c r="G770" s="6" t="s">
+      <c r="H770" s="6" t="s">
         <v>4826</v>
-      </c>
-      <c r="H770" s="6" t="s">
-        <v>4827</v>
       </c>
     </row>
     <row r="771">
       <c r="B771" s="5" t="s">
+        <v>4827</v>
+      </c>
+      <c r="C771" s="5" t="s">
         <v>4828</v>
       </c>
-      <c r="C771" s="5" t="s">
+      <c r="D771" s="5" t="s">
         <v>4829</v>
       </c>
-      <c r="D771" s="5" t="s">
+      <c r="E771" s="5" t="s">
         <v>4830</v>
       </c>
-      <c r="E771" s="5" t="s">
+      <c r="F771" s="5" t="s">
         <v>4831</v>
       </c>
-      <c r="F771" s="5" t="s">
+      <c r="G771" s="5" t="s">
         <v>4832</v>
       </c>
-      <c r="G771" s="5" t="s">
+      <c r="H771" s="5" t="s">
         <v>4833</v>
-      </c>
-      <c r="H771" s="5" t="s">
-        <v>4834</v>
       </c>
     </row>
     <row r="772">
       <c r="B772" s="6" t="s">
+        <v>4834</v>
+      </c>
+      <c r="C772" s="6" t="s">
         <v>4835</v>
       </c>
-      <c r="C772" s="6" t="s">
+      <c r="D772" s="6" t="s">
         <v>4836</v>
       </c>
-      <c r="D772" s="6" t="s">
+      <c r="E772" s="6" t="s">
         <v>4837</v>
       </c>
-      <c r="E772" s="6" t="s">
+      <c r="F772" s="6" t="s">
         <v>4838</v>
       </c>
-      <c r="F772" s="6" t="s">
+      <c r="G772" s="6" t="s">
         <v>4839</v>
       </c>
-      <c r="G772" s="6" t="s">
+      <c r="H772" s="6" t="s">
         <v>4840</v>
-      </c>
-      <c r="H772" s="6" t="s">
-        <v>4841</v>
       </c>
     </row>
     <row r="773">
       <c r="B773" s="5" t="s">
+        <v>4841</v>
+      </c>
+      <c r="C773" s="5" t="s">
         <v>4842</v>
       </c>
-      <c r="C773" s="5" t="s">
+      <c r="D773" s="5" t="s">
         <v>4843</v>
       </c>
-      <c r="D773" s="5" t="s">
+      <c r="E773" s="5" t="s">
         <v>4844</v>
       </c>
-      <c r="E773" s="5" t="s">
+      <c r="F773" s="5" t="s">
         <v>4845</v>
       </c>
-      <c r="F773" s="5" t="s">
+      <c r="G773" s="5" t="s">
         <v>4846</v>
       </c>
-      <c r="G773" s="5" t="s">
+      <c r="H773" s="5" t="s">
         <v>4847</v>
-      </c>
-      <c r="H773" s="5" t="s">
-        <v>4848</v>
       </c>
     </row>
     <row r="774">
       <c r="B774" s="6" t="s">
+        <v>4848</v>
+      </c>
+      <c r="C774" s="6" t="s">
         <v>4849</v>
       </c>
-      <c r="C774" s="6" t="s">
+      <c r="D774" s="6" t="s">
         <v>4850</v>
       </c>
-      <c r="D774" s="6" t="s">
+      <c r="E774" s="6" t="s">
         <v>4851</v>
       </c>
-      <c r="E774" s="6" t="s">
+      <c r="F774" s="6" t="s">
         <v>4852</v>
       </c>
-      <c r="F774" s="6" t="s">
+      <c r="G774" s="6" t="s">
         <v>4853</v>
       </c>
-      <c r="G774" s="6" t="s">
+      <c r="H774" s="6" t="s">
         <v>4854</v>
-      </c>
-      <c r="H774" s="6" t="s">
-        <v>4855</v>
       </c>
     </row>
     <row r="775">
       <c r="B775" s="5" t="s">
+        <v>4855</v>
+      </c>
+      <c r="C775" s="5" t="s">
         <v>4856</v>
       </c>
-      <c r="C775" s="5" t="s">
+      <c r="D775" s="5" t="s">
         <v>4857</v>
       </c>
-      <c r="D775" s="5" t="s">
+      <c r="E775" s="5" t="s">
         <v>4858</v>
       </c>
-      <c r="E775" s="5" t="s">
+      <c r="F775" s="5" t="s">
         <v>4859</v>
       </c>
-      <c r="F775" s="5" t="s">
+      <c r="G775" s="5" t="s">
         <v>4860</v>
       </c>
-      <c r="G775" s="5" t="s">
+      <c r="H775" s="5" t="s">
         <v>4861</v>
-      </c>
-      <c r="H775" s="5" t="s">
-        <v>4862</v>
       </c>
     </row>
     <row r="776">
       <c r="B776" s="6" t="s">
+        <v>4862</v>
+      </c>
+      <c r="C776" s="6" t="s">
         <v>4863</v>
       </c>
-      <c r="C776" s="6" t="s">
+      <c r="D776" s="6" t="s">
         <v>4864</v>
       </c>
-      <c r="D776" s="6" t="s">
+      <c r="E776" s="6" t="s">
         <v>4865</v>
       </c>
-      <c r="E776" s="6" t="s">
+      <c r="F776" s="6" t="s">
         <v>4866</v>
       </c>
-      <c r="F776" s="6" t="s">
+      <c r="G776" s="6" t="s">
         <v>4867</v>
       </c>
-      <c r="G776" s="6" t="s">
+      <c r="H776" s="6" t="s">
         <v>4868</v>
-      </c>
-      <c r="H776" s="6" t="s">
-        <v>4869</v>
       </c>
     </row>
     <row r="777">
       <c r="B777" s="5" t="s">
+        <v>4869</v>
+      </c>
+      <c r="C777" s="5" t="s">
         <v>4870</v>
       </c>
-      <c r="C777" s="5" t="s">
+      <c r="D777" s="5" t="s">
         <v>4871</v>
       </c>
-      <c r="D777" s="5" t="s">
+      <c r="E777" s="5" t="s">
         <v>4872</v>
       </c>
-      <c r="E777" s="5" t="s">
+      <c r="F777" s="5" t="s">
         <v>4873</v>
       </c>
-      <c r="F777" s="5" t="s">
+      <c r="G777" s="5" t="s">
         <v>4874</v>
       </c>
-      <c r="G777" s="5" t="s">
+      <c r="H777" s="5" t="s">
         <v>4875</v>
-      </c>
-      <c r="H777" s="5" t="s">
-        <v>4876</v>
       </c>
     </row>
     <row r="778">
       <c r="B778" s="6" t="s">
+        <v>4876</v>
+      </c>
+      <c r="C778" s="6" t="s">
         <v>4877</v>
       </c>
-      <c r="C778" s="6" t="s">
+      <c r="D778" s="6" t="s">
         <v>4878</v>
       </c>
-      <c r="D778" s="6" t="s">
+      <c r="E778" s="6" t="s">
         <v>4879</v>
       </c>
-      <c r="E778" s="6" t="s">
+      <c r="F778" s="6" t="s">
         <v>4880</v>
       </c>
-      <c r="F778" s="6" t="s">
+      <c r="G778" s="6" t="s">
         <v>4881</v>
       </c>
-      <c r="G778" s="6" t="s">
+      <c r="H778" s="6" t="s">
         <v>4882</v>
-      </c>
-      <c r="H778" s="6" t="s">
-        <v>4883</v>
       </c>
     </row>
     <row r="779">
       <c r="B779" s="5" t="s">
+        <v>4883</v>
+      </c>
+      <c r="C779" s="5" t="s">
         <v>4884</v>
       </c>
-      <c r="C779" s="5" t="s">
+      <c r="D779" s="5" t="s">
         <v>4885</v>
       </c>
-      <c r="D779" s="5" t="s">
+      <c r="E779" s="5" t="s">
         <v>4886</v>
       </c>
-      <c r="E779" s="5" t="s">
+      <c r="F779" s="5" t="s">
         <v>4887</v>
       </c>
-      <c r="F779" s="5" t="s">
+      <c r="G779" s="5" t="s">
         <v>4888</v>
       </c>
-      <c r="G779" s="5" t="s">
+      <c r="H779" s="5" t="s">
         <v>4889</v>
-      </c>
-      <c r="H779" s="5" t="s">
-        <v>4890</v>
       </c>
     </row>
     <row r="780">
       <c r="B780" s="6" t="s">
+        <v>4890</v>
+      </c>
+      <c r="C780" s="6" t="s">
         <v>4891</v>
       </c>
-      <c r="C780" s="6" t="s">
+      <c r="D780" s="6" t="s">
         <v>4892</v>
       </c>
-      <c r="D780" s="6" t="s">
+      <c r="E780" s="6" t="s">
         <v>4893</v>
       </c>
-      <c r="E780" s="6" t="s">
+      <c r="F780" s="6" t="s">
         <v>4894</v>
       </c>
-      <c r="F780" s="6" t="s">
+      <c r="G780" s="6" t="s">
         <v>4895</v>
       </c>
-      <c r="G780" s="6" t="s">
+      <c r="H780" s="6" t="s">
         <v>4896</v>
-      </c>
-      <c r="H780" s="6" t="s">
-        <v>4897</v>
       </c>
     </row>
     <row r="781">
       <c r="B781" s="5" t="s">
+        <v>4897</v>
+      </c>
+      <c r="C781" s="5" t="s">
         <v>4898</v>
       </c>
-      <c r="C781" s="5" t="s">
+      <c r="D781" s="5" t="s">
         <v>4899</v>
       </c>
-      <c r="D781" s="5" t="s">
+      <c r="E781" s="5" t="s">
         <v>4900</v>
       </c>
-      <c r="E781" s="5" t="s">
+      <c r="F781" s="5" t="s">
         <v>4901</v>
-      </c>
-      <c r="F781" s="5" t="s">
-        <v>4902</v>
       </c>
       <c r="G781" s="5" t="s">
         <v>4902</v>
@@ -34727,27 +34787,27 @@
         <v>4915</v>
       </c>
       <c r="G783" s="5" t="s">
+        <v>4915</v>
+      </c>
+      <c r="H783" s="5" t="s">
         <v>4916</v>
-      </c>
-      <c r="H783" s="5" t="s">
-        <v>4917</v>
       </c>
     </row>
     <row r="784">
       <c r="B784" s="6" t="s">
+        <v>4917</v>
+      </c>
+      <c r="C784" s="6" t="s">
         <v>4918</v>
       </c>
-      <c r="C784" s="6" t="s">
+      <c r="D784" s="6" t="s">
         <v>4919</v>
       </c>
-      <c r="D784" s="6" t="s">
+      <c r="E784" s="6" t="s">
         <v>4920</v>
       </c>
-      <c r="E784" s="6" t="s">
+      <c r="F784" s="6" t="s">
         <v>4921</v>
-      </c>
-      <c r="F784" s="6" t="s">
-        <v>4922</v>
       </c>
       <c r="G784" s="6" t="s">
         <v>4922</v>
@@ -34796,50 +34856,50 @@
         <v>4935</v>
       </c>
       <c r="G786" s="6" t="s">
+        <v>4935</v>
+      </c>
+      <c r="H786" s="6" t="s">
         <v>4936</v>
-      </c>
-      <c r="H786" s="6" t="s">
-        <v>4937</v>
       </c>
     </row>
     <row r="787">
       <c r="B787" s="5" t="s">
+        <v>4937</v>
+      </c>
+      <c r="C787" s="5" t="s">
         <v>4938</v>
       </c>
-      <c r="C787" s="5" t="s">
+      <c r="D787" s="5" t="s">
         <v>4939</v>
       </c>
-      <c r="D787" s="5" t="s">
+      <c r="E787" s="5" t="s">
         <v>4940</v>
       </c>
-      <c r="E787" s="5" t="s">
+      <c r="F787" s="5" t="s">
         <v>4941</v>
       </c>
-      <c r="F787" s="5" t="s">
+      <c r="G787" s="5" t="s">
         <v>4942</v>
       </c>
-      <c r="G787" s="5" t="s">
+      <c r="H787" s="5" t="s">
         <v>4943</v>
-      </c>
-      <c r="H787" s="5" t="s">
-        <v>4944</v>
       </c>
     </row>
     <row r="788">
       <c r="B788" s="6" t="s">
+        <v>4944</v>
+      </c>
+      <c r="C788" s="6" t="s">
         <v>4945</v>
       </c>
-      <c r="C788" s="6" t="s">
+      <c r="D788" s="6" t="s">
         <v>4946</v>
       </c>
-      <c r="D788" s="6" t="s">
+      <c r="E788" s="6" t="s">
         <v>4947</v>
       </c>
-      <c r="E788" s="6" t="s">
+      <c r="F788" s="6" t="s">
         <v>4948</v>
-      </c>
-      <c r="F788" s="6" t="s">
-        <v>4949</v>
       </c>
       <c r="G788" s="6" t="s">
         <v>4949</v>
@@ -34888,148 +34948,148 @@
         <v>4962</v>
       </c>
       <c r="G790" s="6" t="s">
+        <v>4962</v>
+      </c>
+      <c r="H790" s="6" t="s">
         <v>4963</v>
-      </c>
-      <c r="H790" s="6" t="s">
-        <v>4964</v>
       </c>
     </row>
     <row r="791">
       <c r="B791" s="5" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C791" s="5" t="s">
         <v>4965</v>
       </c>
-      <c r="C791" s="5" t="s">
+      <c r="D791" s="5" t="s">
         <v>4966</v>
       </c>
-      <c r="D791" s="5" t="s">
+      <c r="E791" s="5" t="s">
         <v>4967</v>
       </c>
-      <c r="E791" s="5" t="s">
+      <c r="F791" s="5" t="s">
         <v>4968</v>
       </c>
-      <c r="F791" s="5" t="s">
+      <c r="G791" s="5" t="s">
         <v>4969</v>
       </c>
-      <c r="G791" s="5" t="s">
+      <c r="H791" s="5" t="s">
         <v>4970</v>
-      </c>
-      <c r="H791" s="5" t="s">
-        <v>4971</v>
       </c>
     </row>
     <row r="792">
       <c r="B792" s="6" t="s">
+        <v>4971</v>
+      </c>
+      <c r="C792" s="6" t="s">
         <v>4972</v>
       </c>
-      <c r="C792" s="6" t="s">
+      <c r="D792" s="6" t="s">
         <v>4973</v>
       </c>
-      <c r="D792" s="6" t="s">
+      <c r="E792" s="6" t="s">
         <v>4974</v>
       </c>
-      <c r="E792" s="6" t="s">
+      <c r="F792" s="6" t="s">
         <v>4975</v>
       </c>
-      <c r="F792" s="6" t="s">
+      <c r="G792" s="6" t="s">
         <v>4976</v>
       </c>
-      <c r="G792" s="6" t="s">
+      <c r="H792" s="6" t="s">
         <v>4977</v>
-      </c>
-      <c r="H792" s="6" t="s">
-        <v>4978</v>
       </c>
     </row>
     <row r="793">
       <c r="B793" s="5" t="s">
+        <v>4978</v>
+      </c>
+      <c r="C793" s="5" t="s">
         <v>4979</v>
       </c>
-      <c r="C793" s="5" t="s">
+      <c r="D793" s="5" t="s">
         <v>4980</v>
       </c>
-      <c r="D793" s="5" t="s">
+      <c r="E793" s="5" t="s">
         <v>4981</v>
       </c>
-      <c r="E793" s="5" t="s">
+      <c r="F793" s="5" t="s">
         <v>4982</v>
       </c>
-      <c r="F793" s="5" t="s">
+      <c r="G793" s="5" t="s">
         <v>4983</v>
       </c>
-      <c r="G793" s="5" t="s">
+      <c r="H793" s="5" t="s">
         <v>4984</v>
-      </c>
-      <c r="H793" s="5" t="s">
-        <v>4985</v>
       </c>
     </row>
     <row r="794">
       <c r="B794" s="6" t="s">
+        <v>4985</v>
+      </c>
+      <c r="C794" s="6" t="s">
         <v>4986</v>
       </c>
-      <c r="C794" s="6" t="s">
+      <c r="D794" s="6" t="s">
         <v>4987</v>
       </c>
-      <c r="D794" s="6" t="s">
+      <c r="E794" s="6" t="s">
         <v>4988</v>
       </c>
-      <c r="E794" s="6" t="s">
+      <c r="F794" s="6" t="s">
         <v>4989</v>
       </c>
-      <c r="F794" s="6" t="s">
+      <c r="G794" s="6" t="s">
         <v>4990</v>
       </c>
-      <c r="G794" s="6" t="s">
+      <c r="H794" s="6" t="s">
         <v>4991</v>
-      </c>
-      <c r="H794" s="6" t="s">
-        <v>4992</v>
       </c>
     </row>
     <row r="795">
       <c r="B795" s="5" t="s">
+        <v>4992</v>
+      </c>
+      <c r="C795" s="5" t="s">
         <v>4993</v>
       </c>
-      <c r="C795" s="5" t="s">
+      <c r="D795" s="5" t="s">
         <v>4994</v>
       </c>
-      <c r="D795" s="5" t="s">
+      <c r="E795" s="5" t="s">
         <v>4995</v>
       </c>
-      <c r="E795" s="5" t="s">
+      <c r="F795" s="5" t="s">
         <v>4996</v>
       </c>
-      <c r="F795" s="5" t="s">
+      <c r="G795" s="5" t="s">
         <v>4997</v>
       </c>
-      <c r="G795" s="5" t="s">
+      <c r="H795" s="5" t="s">
         <v>4998</v>
-      </c>
-      <c r="H795" s="5" t="s">
-        <v>4999</v>
       </c>
     </row>
     <row r="796">
       <c r="B796" s="6" t="s">
+        <v>4999</v>
+      </c>
+      <c r="C796" s="6" t="s">
         <v>5000</v>
       </c>
-      <c r="C796" s="6" t="s">
+      <c r="D796" s="6" t="s">
         <v>5001</v>
       </c>
-      <c r="D796" s="6" t="s">
+      <c r="E796" s="6" t="s">
         <v>5002</v>
       </c>
-      <c r="E796" s="6" t="s">
+      <c r="F796" s="6" t="s">
         <v>5003</v>
       </c>
-      <c r="F796" s="6" t="s">
+      <c r="G796" s="6" t="s">
         <v>5004</v>
       </c>
-      <c r="G796" s="6" t="s">
+      <c r="H796" s="6" t="s">
         <v>5005</v>
-      </c>
-      <c r="H796" s="6" t="s">
-        <v>5002</v>
       </c>
     </row>
     <row r="797">
@@ -35075,191 +35135,191 @@
         <v>5018</v>
       </c>
       <c r="H798" s="6" t="s">
-        <v>5019</v>
+        <v>5015</v>
       </c>
     </row>
     <row r="799">
       <c r="B799" s="5" t="s">
+        <v>5019</v>
+      </c>
+      <c r="C799" s="5" t="s">
         <v>5020</v>
       </c>
-      <c r="C799" s="5" t="s">
+      <c r="D799" s="5" t="s">
         <v>5021</v>
       </c>
-      <c r="D799" s="5" t="s">
+      <c r="E799" s="5" t="s">
         <v>5022</v>
       </c>
-      <c r="E799" s="5" t="s">
+      <c r="F799" s="5" t="s">
         <v>5023</v>
       </c>
-      <c r="F799" s="5" t="s">
+      <c r="G799" s="5" t="s">
         <v>5024</v>
       </c>
-      <c r="G799" s="5" t="s">
+      <c r="H799" s="5" t="s">
         <v>5025</v>
-      </c>
-      <c r="H799" s="5" t="s">
-        <v>5026</v>
       </c>
     </row>
     <row r="800">
       <c r="B800" s="6" t="s">
+        <v>5026</v>
+      </c>
+      <c r="C800" s="6" t="s">
         <v>5027</v>
       </c>
-      <c r="C800" s="6" t="s">
+      <c r="D800" s="6" t="s">
         <v>5028</v>
       </c>
-      <c r="D800" s="6" t="s">
+      <c r="E800" s="6" t="s">
         <v>5029</v>
       </c>
-      <c r="E800" s="6" t="s">
+      <c r="F800" s="6" t="s">
         <v>5030</v>
       </c>
-      <c r="F800" s="6" t="s">
+      <c r="G800" s="6" t="s">
         <v>5031</v>
       </c>
-      <c r="G800" s="6" t="s">
+      <c r="H800" s="6" t="s">
         <v>5032</v>
-      </c>
-      <c r="H800" s="6" t="s">
-        <v>5033</v>
       </c>
     </row>
     <row r="801">
       <c r="B801" s="5" t="s">
+        <v>5033</v>
+      </c>
+      <c r="C801" s="5" t="s">
         <v>5034</v>
       </c>
-      <c r="C801" s="5" t="s">
+      <c r="D801" s="5" t="s">
         <v>5035</v>
       </c>
-      <c r="D801" s="5" t="s">
+      <c r="E801" s="5" t="s">
         <v>5036</v>
       </c>
-      <c r="E801" s="5" t="s">
+      <c r="F801" s="5" t="s">
         <v>5037</v>
       </c>
-      <c r="F801" s="5" t="s">
+      <c r="G801" s="5" t="s">
         <v>5038</v>
       </c>
-      <c r="G801" s="5" t="s">
+      <c r="H801" s="5" t="s">
         <v>5039</v>
-      </c>
-      <c r="H801" s="5" t="s">
-        <v>5040</v>
       </c>
     </row>
     <row r="802">
       <c r="B802" s="6" t="s">
+        <v>5040</v>
+      </c>
+      <c r="C802" s="6" t="s">
         <v>5041</v>
-      </c>
-      <c r="C802" s="6" t="s">
-        <v>3021</v>
       </c>
       <c r="D802" s="6" t="s">
         <v>5042</v>
       </c>
       <c r="E802" s="6" t="s">
-        <v>3023</v>
+        <v>5043</v>
       </c>
       <c r="F802" s="6" t="s">
-        <v>5043</v>
+        <v>5044</v>
       </c>
       <c r="G802" s="6" t="s">
-        <v>5044</v>
+        <v>5045</v>
       </c>
       <c r="H802" s="6" t="s">
-        <v>5045</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="803">
       <c r="B803" s="5" t="s">
-        <v>5046</v>
+        <v>5047</v>
       </c>
       <c r="C803" s="5" t="s">
-        <v>3014</v>
+        <v>5048</v>
       </c>
       <c r="D803" s="5" t="s">
-        <v>5047</v>
+        <v>5049</v>
       </c>
       <c r="E803" s="5" t="s">
-        <v>3016</v>
+        <v>5050</v>
       </c>
       <c r="F803" s="5" t="s">
-        <v>5048</v>
+        <v>5051</v>
       </c>
       <c r="G803" s="5" t="s">
-        <v>5049</v>
+        <v>5052</v>
       </c>
       <c r="H803" s="5" t="s">
-        <v>5050</v>
+        <v>5053</v>
       </c>
     </row>
     <row r="804">
       <c r="B804" s="6" t="s">
-        <v>5051</v>
+        <v>5054</v>
       </c>
       <c r="C804" s="6" t="s">
-        <v>5052</v>
+        <v>3021</v>
       </c>
       <c r="D804" s="6" t="s">
-        <v>5053</v>
+        <v>5055</v>
       </c>
       <c r="E804" s="6" t="s">
-        <v>5054</v>
+        <v>3023</v>
       </c>
       <c r="F804" s="6" t="s">
-        <v>5055</v>
+        <v>5056</v>
       </c>
       <c r="G804" s="6" t="s">
-        <v>5054</v>
+        <v>5057</v>
       </c>
       <c r="H804" s="6" t="s">
-        <v>4450</v>
+        <v>5058</v>
       </c>
     </row>
     <row r="805">
       <c r="B805" s="5" t="s">
-        <v>5056</v>
+        <v>5059</v>
       </c>
       <c r="C805" s="5" t="s">
-        <v>5057</v>
+        <v>3014</v>
       </c>
       <c r="D805" s="5" t="s">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="E805" s="5" t="s">
-        <v>5059</v>
+        <v>3016</v>
       </c>
       <c r="F805" s="5" t="s">
-        <v>5060</v>
+        <v>5061</v>
       </c>
       <c r="G805" s="5" t="s">
-        <v>5061</v>
+        <v>5062</v>
       </c>
       <c r="H805" s="5" t="s">
-        <v>5062</v>
+        <v>5063</v>
       </c>
     </row>
     <row r="806">
       <c r="B806" s="6" t="s">
-        <v>5063</v>
+        <v>5064</v>
       </c>
       <c r="C806" s="6" t="s">
-        <v>5064</v>
+        <v>5065</v>
       </c>
       <c r="D806" s="6" t="s">
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="E806" s="6" t="s">
-        <v>5066</v>
+        <v>5067</v>
       </c>
       <c r="F806" s="6" t="s">
-        <v>5067</v>
+        <v>5068</v>
       </c>
       <c r="G806" s="6" t="s">
         <v>5067</v>
       </c>
       <c r="H806" s="6" t="s">
-        <v>5068</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="807">
@@ -35302,188 +35362,188 @@
         <v>5080</v>
       </c>
       <c r="G808" s="6" t="s">
+        <v>5080</v>
+      </c>
+      <c r="H808" s="6" t="s">
         <v>5081</v>
-      </c>
-      <c r="H808" s="6" t="s">
-        <v>5082</v>
       </c>
     </row>
     <row r="809">
       <c r="B809" s="5" t="s">
+        <v>5082</v>
+      </c>
+      <c r="C809" s="5" t="s">
         <v>5083</v>
       </c>
-      <c r="C809" s="5" t="s">
+      <c r="D809" s="5" t="s">
         <v>5084</v>
       </c>
-      <c r="D809" s="5" t="s">
+      <c r="E809" s="5" t="s">
         <v>5085</v>
       </c>
-      <c r="E809" s="5" t="s">
+      <c r="F809" s="5" t="s">
         <v>5086</v>
       </c>
-      <c r="F809" s="5" t="s">
+      <c r="G809" s="5" t="s">
         <v>5087</v>
       </c>
-      <c r="G809" s="5" t="s">
+      <c r="H809" s="5" t="s">
         <v>5088</v>
-      </c>
-      <c r="H809" s="5" t="s">
-        <v>5089</v>
       </c>
     </row>
     <row r="810">
       <c r="B810" s="6" t="s">
+        <v>5089</v>
+      </c>
+      <c r="C810" s="6" t="s">
         <v>5090</v>
       </c>
-      <c r="C810" s="6" t="s">
+      <c r="D810" s="6" t="s">
         <v>5091</v>
       </c>
-      <c r="D810" s="6" t="s">
+      <c r="E810" s="6" t="s">
         <v>5092</v>
       </c>
-      <c r="E810" s="6" t="s">
+      <c r="F810" s="6" t="s">
         <v>5093</v>
       </c>
-      <c r="F810" s="6" t="s">
+      <c r="G810" s="6" t="s">
         <v>5094</v>
       </c>
-      <c r="G810" s="6" t="s">
+      <c r="H810" s="6" t="s">
         <v>5095</v>
-      </c>
-      <c r="H810" s="6" t="s">
-        <v>5096</v>
       </c>
     </row>
     <row r="811">
       <c r="B811" s="5" t="s">
+        <v>5096</v>
+      </c>
+      <c r="C811" s="5" t="s">
         <v>5097</v>
       </c>
-      <c r="C811" s="5" t="s">
+      <c r="D811" s="5" t="s">
         <v>5098</v>
       </c>
-      <c r="D811" s="5" t="s">
+      <c r="E811" s="5" t="s">
         <v>5099</v>
       </c>
-      <c r="E811" s="5" t="s">
+      <c r="F811" s="5" t="s">
         <v>5100</v>
       </c>
-      <c r="F811" s="5" t="s">
+      <c r="G811" s="5" t="s">
         <v>5101</v>
       </c>
-      <c r="G811" s="5" t="s">
+      <c r="H811" s="5" t="s">
         <v>5102</v>
-      </c>
-      <c r="H811" s="5" t="s">
-        <v>5103</v>
       </c>
     </row>
     <row r="812">
       <c r="B812" s="6" t="s">
+        <v>5103</v>
+      </c>
+      <c r="C812" s="6" t="s">
         <v>5104</v>
       </c>
-      <c r="C812" s="6" t="s">
+      <c r="D812" s="6" t="s">
         <v>5105</v>
       </c>
-      <c r="D812" s="6" t="s">
+      <c r="E812" s="6" t="s">
         <v>5106</v>
-      </c>
-      <c r="E812" s="6" t="s">
-        <v>5107</v>
       </c>
       <c r="F812" s="6" t="s">
         <v>5107</v>
       </c>
       <c r="G812" s="6" t="s">
-        <v>5107</v>
+        <v>5108</v>
       </c>
       <c r="H812" s="6" t="s">
-        <v>5108</v>
+        <v>5109</v>
       </c>
     </row>
     <row r="813">
       <c r="B813" s="5" t="s">
-        <v>5109</v>
+        <v>5110</v>
       </c>
       <c r="C813" s="5" t="s">
-        <v>5110</v>
+        <v>5111</v>
       </c>
       <c r="D813" s="5" t="s">
-        <v>5111</v>
+        <v>5112</v>
       </c>
       <c r="E813" s="5" t="s">
-        <v>5112</v>
+        <v>5113</v>
       </c>
       <c r="F813" s="5" t="s">
-        <v>5113</v>
+        <v>5114</v>
       </c>
       <c r="G813" s="5" t="s">
-        <v>5114</v>
+        <v>5115</v>
       </c>
       <c r="H813" s="5" t="s">
-        <v>5115</v>
+        <v>5116</v>
       </c>
     </row>
     <row r="814">
       <c r="B814" s="6" t="s">
-        <v>5116</v>
+        <v>5117</v>
       </c>
       <c r="C814" s="6" t="s">
-        <v>5117</v>
+        <v>5118</v>
       </c>
       <c r="D814" s="6" t="s">
-        <v>5118</v>
+        <v>5119</v>
       </c>
       <c r="E814" s="6" t="s">
-        <v>5119</v>
+        <v>5120</v>
       </c>
       <c r="F814" s="6" t="s">
         <v>5120</v>
       </c>
       <c r="G814" s="6" t="s">
+        <v>5120</v>
+      </c>
+      <c r="H814" s="6" t="s">
         <v>5121</v>
-      </c>
-      <c r="H814" s="6" t="s">
-        <v>5122</v>
       </c>
     </row>
     <row r="815">
       <c r="B815" s="5" t="s">
+        <v>5122</v>
+      </c>
+      <c r="C815" s="5" t="s">
         <v>5123</v>
       </c>
-      <c r="C815" s="5" t="s">
+      <c r="D815" s="5" t="s">
         <v>5124</v>
       </c>
-      <c r="D815" s="5" t="s">
+      <c r="E815" s="5" t="s">
         <v>5125</v>
       </c>
-      <c r="E815" s="5" t="s">
+      <c r="F815" s="5" t="s">
         <v>5126</v>
       </c>
-      <c r="F815" s="5" t="s">
+      <c r="G815" s="5" t="s">
         <v>5127</v>
       </c>
-      <c r="G815" s="5" t="s">
+      <c r="H815" s="5" t="s">
         <v>5128</v>
-      </c>
-      <c r="H815" s="5" t="s">
-        <v>5129</v>
       </c>
     </row>
     <row r="816">
       <c r="B816" s="6" t="s">
+        <v>5129</v>
+      </c>
+      <c r="C816" s="6" t="s">
         <v>5130</v>
       </c>
-      <c r="C816" s="6" t="s">
+      <c r="D816" s="6" t="s">
         <v>5131</v>
       </c>
-      <c r="D816" s="6" t="s">
+      <c r="E816" s="6" t="s">
         <v>5132</v>
       </c>
-      <c r="E816" s="6" t="s">
+      <c r="F816" s="6" t="s">
         <v>5133</v>
-      </c>
-      <c r="F816" s="6" t="s">
-        <v>5134</v>
       </c>
       <c r="G816" s="6" t="s">
         <v>5134</v>
@@ -35509,50 +35569,50 @@
         <v>5140</v>
       </c>
       <c r="G817" s="5" t="s">
-        <v>5140</v>
+        <v>5141</v>
       </c>
       <c r="H817" s="5" t="s">
-        <v>5141</v>
+        <v>5142</v>
       </c>
     </row>
     <row r="818">
       <c r="B818" s="6" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="C818" s="6" t="s">
-        <v>5143</v>
+        <v>5144</v>
       </c>
       <c r="D818" s="6" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="E818" s="6" t="s">
-        <v>5145</v>
+        <v>5146</v>
       </c>
       <c r="F818" s="6" t="s">
-        <v>5146</v>
+        <v>5147</v>
       </c>
       <c r="G818" s="6" t="s">
-        <v>5146</v>
+        <v>5147</v>
       </c>
       <c r="H818" s="6" t="s">
-        <v>5147</v>
+        <v>5148</v>
       </c>
     </row>
     <row r="819">
       <c r="B819" s="5" t="s">
-        <v>5148</v>
+        <v>5149</v>
       </c>
       <c r="C819" s="5" t="s">
-        <v>5149</v>
+        <v>5150</v>
       </c>
       <c r="D819" s="5" t="s">
-        <v>5150</v>
+        <v>5151</v>
       </c>
       <c r="E819" s="5" t="s">
-        <v>5151</v>
+        <v>5152</v>
       </c>
       <c r="F819" s="5" t="s">
-        <v>5152</v>
+        <v>5153</v>
       </c>
       <c r="G819" s="5" t="s">
         <v>5153</v>
@@ -35578,96 +35638,96 @@
         <v>5159</v>
       </c>
       <c r="G820" s="6" t="s">
+        <v>5159</v>
+      </c>
+      <c r="H820" s="6" t="s">
         <v>5160</v>
-      </c>
-      <c r="H820" s="6" t="s">
-        <v>5161</v>
       </c>
     </row>
     <row r="821">
       <c r="B821" s="5" t="s">
+        <v>5161</v>
+      </c>
+      <c r="C821" s="5" t="s">
         <v>5162</v>
       </c>
-      <c r="C821" s="5" t="s">
+      <c r="D821" s="5" t="s">
         <v>5163</v>
       </c>
-      <c r="D821" s="5" t="s">
+      <c r="E821" s="5" t="s">
         <v>5164</v>
       </c>
-      <c r="E821" s="5" t="s">
+      <c r="F821" s="5" t="s">
         <v>5165</v>
       </c>
-      <c r="F821" s="5" t="s">
+      <c r="G821" s="5" t="s">
         <v>5166</v>
       </c>
-      <c r="G821" s="5" t="s">
+      <c r="H821" s="5" t="s">
         <v>5167</v>
-      </c>
-      <c r="H821" s="5" t="s">
-        <v>5168</v>
       </c>
     </row>
     <row r="822">
       <c r="B822" s="6" t="s">
+        <v>5168</v>
+      </c>
+      <c r="C822" s="6" t="s">
         <v>5169</v>
       </c>
-      <c r="C822" s="6" t="s">
+      <c r="D822" s="6" t="s">
         <v>5170</v>
       </c>
-      <c r="D822" s="6" t="s">
+      <c r="E822" s="6" t="s">
         <v>5171</v>
       </c>
-      <c r="E822" s="6" t="s">
+      <c r="F822" s="6" t="s">
         <v>5172</v>
       </c>
-      <c r="F822" s="6" t="s">
+      <c r="G822" s="6" t="s">
         <v>5173</v>
       </c>
-      <c r="G822" s="6" t="s">
+      <c r="H822" s="6" t="s">
         <v>5174</v>
-      </c>
-      <c r="H822" s="6" t="s">
-        <v>5175</v>
       </c>
     </row>
     <row r="823">
       <c r="B823" s="5" t="s">
+        <v>5175</v>
+      </c>
+      <c r="C823" s="5" t="s">
         <v>5176</v>
       </c>
-      <c r="C823" s="5" t="s">
+      <c r="D823" s="5" t="s">
         <v>5177</v>
       </c>
-      <c r="D823" s="5" t="s">
+      <c r="E823" s="5" t="s">
         <v>5178</v>
       </c>
-      <c r="E823" s="5" t="s">
+      <c r="F823" s="5" t="s">
         <v>5179</v>
       </c>
-      <c r="F823" s="5" t="s">
+      <c r="G823" s="5" t="s">
         <v>5180</v>
       </c>
-      <c r="G823" s="5" t="s">
+      <c r="H823" s="5" t="s">
         <v>5181</v>
-      </c>
-      <c r="H823" s="5" t="s">
-        <v>5182</v>
       </c>
     </row>
     <row r="824">
       <c r="B824" s="6" t="s">
+        <v>5182</v>
+      </c>
+      <c r="C824" s="6" t="s">
         <v>5183</v>
       </c>
-      <c r="C824" s="6" t="s">
+      <c r="D824" s="6" t="s">
         <v>5184</v>
       </c>
-      <c r="D824" s="6" t="s">
+      <c r="E824" s="6" t="s">
         <v>5185</v>
       </c>
-      <c r="E824" s="6" t="s">
+      <c r="F824" s="6" t="s">
         <v>5186</v>
-      </c>
-      <c r="F824" s="6" t="s">
-        <v>5187</v>
       </c>
       <c r="G824" s="6" t="s">
         <v>5187</v>
@@ -35716,10 +35776,10 @@
         <v>5200</v>
       </c>
       <c r="G826" s="6" t="s">
+        <v>5200</v>
+      </c>
+      <c r="H826" s="6" t="s">
         <v>5201</v>
-      </c>
-      <c r="H826" s="6" t="s">
-        <v>4964</v>
       </c>
     </row>
     <row r="827">
@@ -35765,110 +35825,110 @@
         <v>5214</v>
       </c>
       <c r="H828" s="6" t="s">
-        <v>5215</v>
+        <v>4977</v>
       </c>
     </row>
     <row r="829">
       <c r="B829" s="5" t="s">
+        <v>5215</v>
+      </c>
+      <c r="C829" s="5" t="s">
         <v>5216</v>
       </c>
-      <c r="C829" s="5" t="s">
+      <c r="D829" s="5" t="s">
         <v>5217</v>
       </c>
-      <c r="D829" s="5" t="s">
+      <c r="E829" s="5" t="s">
         <v>5218</v>
-      </c>
-      <c r="E829" s="5" t="s">
-        <v>5219</v>
       </c>
       <c r="F829" s="5" t="s">
         <v>5219</v>
       </c>
       <c r="G829" s="5" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="H829" s="5" t="s">
-        <v>5218</v>
+        <v>5221</v>
       </c>
     </row>
     <row r="830">
       <c r="B830" s="6" t="s">
-        <v>5220</v>
+        <v>5222</v>
       </c>
       <c r="C830" s="6" t="s">
-        <v>5221</v>
+        <v>5223</v>
       </c>
       <c r="D830" s="6" t="s">
-        <v>5222</v>
+        <v>5224</v>
       </c>
       <c r="E830" s="6" t="s">
-        <v>5223</v>
+        <v>5225</v>
       </c>
       <c r="F830" s="6" t="s">
-        <v>5224</v>
+        <v>5226</v>
       </c>
       <c r="G830" s="6" t="s">
-        <v>5225</v>
+        <v>5227</v>
       </c>
       <c r="H830" s="6" t="s">
-        <v>5226</v>
+        <v>5228</v>
       </c>
     </row>
     <row r="831">
       <c r="B831" s="5" t="s">
-        <v>5227</v>
+        <v>5229</v>
       </c>
       <c r="C831" s="5" t="s">
-        <v>5228</v>
+        <v>5230</v>
       </c>
       <c r="D831" s="5" t="s">
-        <v>5229</v>
+        <v>5231</v>
       </c>
       <c r="E831" s="5" t="s">
-        <v>5230</v>
+        <v>5232</v>
       </c>
       <c r="F831" s="5" t="s">
-        <v>5231</v>
+        <v>5232</v>
       </c>
       <c r="G831" s="5" t="s">
         <v>5232</v>
       </c>
       <c r="H831" s="5" t="s">
-        <v>5233</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="832">
       <c r="B832" s="6" t="s">
+        <v>5233</v>
+      </c>
+      <c r="C832" s="6" t="s">
         <v>5234</v>
       </c>
-      <c r="C832" s="6" t="s">
+      <c r="D832" s="6" t="s">
         <v>5235</v>
       </c>
-      <c r="D832" s="6" t="s">
+      <c r="E832" s="6" t="s">
         <v>5236</v>
       </c>
-      <c r="E832" s="6" t="s">
+      <c r="F832" s="6" t="s">
         <v>5237</v>
       </c>
-      <c r="F832" s="6" t="s">
+      <c r="G832" s="6" t="s">
         <v>5238</v>
       </c>
-      <c r="G832" s="6" t="s">
+      <c r="H832" s="6" t="s">
         <v>5239</v>
-      </c>
-      <c r="H832" s="6" t="s">
-        <v>5240</v>
       </c>
     </row>
     <row r="833">
       <c r="B833" s="5" t="s">
+        <v>5240</v>
+      </c>
+      <c r="C833" s="5" t="s">
         <v>5241</v>
       </c>
-      <c r="C833" s="5" t="s">
+      <c r="D833" s="5" t="s">
         <v>5242</v>
-      </c>
-      <c r="D833" s="5" t="s">
-        <v>5218</v>
       </c>
       <c r="E833" s="5" t="s">
         <v>5243</v>
@@ -35877,56 +35937,56 @@
         <v>5244</v>
       </c>
       <c r="G833" s="5" t="s">
-        <v>5244</v>
+        <v>5245</v>
       </c>
       <c r="H833" s="5" t="s">
-        <v>5218</v>
+        <v>5246</v>
       </c>
     </row>
     <row r="834">
       <c r="B834" s="6" t="s">
-        <v>5245</v>
+        <v>5247</v>
       </c>
       <c r="C834" s="6" t="s">
-        <v>5246</v>
+        <v>5248</v>
       </c>
       <c r="D834" s="6" t="s">
-        <v>5247</v>
+        <v>5249</v>
       </c>
       <c r="E834" s="6" t="s">
-        <v>5248</v>
+        <v>5250</v>
       </c>
       <c r="F834" s="6" t="s">
-        <v>5249</v>
+        <v>5251</v>
       </c>
       <c r="G834" s="6" t="s">
-        <v>5250</v>
+        <v>5252</v>
       </c>
       <c r="H834" s="6" t="s">
-        <v>5251</v>
+        <v>5253</v>
       </c>
     </row>
     <row r="835">
       <c r="B835" s="5" t="s">
-        <v>5252</v>
+        <v>5254</v>
       </c>
       <c r="C835" s="5" t="s">
-        <v>5253</v>
+        <v>5255</v>
       </c>
       <c r="D835" s="5" t="s">
-        <v>5254</v>
+        <v>5231</v>
       </c>
       <c r="E835" s="5" t="s">
-        <v>5255</v>
+        <v>5256</v>
       </c>
       <c r="F835" s="5" t="s">
-        <v>5256</v>
+        <v>5257</v>
       </c>
       <c r="G835" s="5" t="s">
         <v>5257</v>
       </c>
       <c r="H835" s="5" t="s">
-        <v>5254</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="836">
@@ -35972,70 +36032,70 @@
         <v>5270</v>
       </c>
       <c r="H837" s="5" t="s">
-        <v>5271</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="838">
       <c r="B838" s="6" t="s">
+        <v>5271</v>
+      </c>
+      <c r="C838" s="6" t="s">
         <v>5272</v>
       </c>
-      <c r="C838" s="6" t="s">
+      <c r="D838" s="6" t="s">
         <v>5273</v>
       </c>
-      <c r="D838" s="6" t="s">
+      <c r="E838" s="6" t="s">
         <v>5274</v>
       </c>
-      <c r="E838" s="6" t="s">
+      <c r="F838" s="6" t="s">
         <v>5275</v>
       </c>
-      <c r="F838" s="6" t="s">
+      <c r="G838" s="6" t="s">
         <v>5276</v>
       </c>
-      <c r="G838" s="6" t="s">
+      <c r="H838" s="6" t="s">
         <v>5277</v>
-      </c>
-      <c r="H838" s="6" t="s">
-        <v>5278</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
+        <v>5278</v>
+      </c>
+      <c r="C839" s="5" t="s">
         <v>5279</v>
       </c>
-      <c r="C839" s="5" t="s">
+      <c r="D839" s="5" t="s">
         <v>5280</v>
       </c>
-      <c r="D839" s="5" t="s">
+      <c r="E839" s="5" t="s">
         <v>5281</v>
       </c>
-      <c r="E839" s="5" t="s">
+      <c r="F839" s="5" t="s">
         <v>5282</v>
       </c>
-      <c r="F839" s="5" t="s">
+      <c r="G839" s="5" t="s">
         <v>5283</v>
       </c>
-      <c r="G839" s="5" t="s">
+      <c r="H839" s="5" t="s">
         <v>5284</v>
-      </c>
-      <c r="H839" s="5" t="s">
-        <v>5285</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
+        <v>5285</v>
+      </c>
+      <c r="C840" s="6" t="s">
         <v>5286</v>
       </c>
-      <c r="C840" s="6" t="s">
+      <c r="D840" s="6" t="s">
         <v>5287</v>
       </c>
-      <c r="D840" s="6" t="s">
+      <c r="E840" s="6" t="s">
         <v>5288</v>
       </c>
-      <c r="E840" s="6" t="s">
+      <c r="F840" s="6" t="s">
         <v>5289</v>
-      </c>
-      <c r="F840" s="6" t="s">
-        <v>5290</v>
       </c>
       <c r="G840" s="6" t="s">
         <v>5290</v>
@@ -36130,7 +36190,7 @@
         <v>5316</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>5315</v>
+        <v>5316</v>
       </c>
       <c r="H844" s="6" t="s">
         <v>5317</v>
@@ -36153,79 +36213,79 @@
         <v>5322</v>
       </c>
       <c r="G845" s="5" t="s">
-        <v>5322</v>
+        <v>5323</v>
       </c>
       <c r="H845" s="5" t="s">
-        <v>5320</v>
+        <v>5324</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
-        <v>5323</v>
+        <v>5325</v>
       </c>
       <c r="C846" s="6" t="s">
-        <v>5324</v>
+        <v>5326</v>
       </c>
       <c r="D846" s="6" t="s">
-        <v>5325</v>
+        <v>5327</v>
       </c>
       <c r="E846" s="6" t="s">
-        <v>5326</v>
+        <v>5328</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>5327</v>
+        <v>5329</v>
       </c>
       <c r="G846" s="6" t="s">
-        <v>5328</v>
+        <v>5330</v>
       </c>
       <c r="H846" s="6" t="s">
-        <v>5329</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
-        <v>5330</v>
+        <v>5332</v>
       </c>
       <c r="C847" s="5" t="s">
-        <v>5331</v>
+        <v>5333</v>
       </c>
       <c r="D847" s="5" t="s">
-        <v>5332</v>
+        <v>5334</v>
       </c>
       <c r="E847" s="5" t="s">
-        <v>5333</v>
+        <v>5335</v>
       </c>
       <c r="F847" s="5" t="s">
-        <v>5334</v>
+        <v>5336</v>
       </c>
       <c r="G847" s="5" t="s">
         <v>5335</v>
       </c>
       <c r="H847" s="5" t="s">
-        <v>5332</v>
+        <v>5337</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
-        <v>5336</v>
+        <v>5338</v>
       </c>
       <c r="C848" s="6" t="s">
-        <v>5337</v>
+        <v>5339</v>
       </c>
       <c r="D848" s="6" t="s">
-        <v>5338</v>
+        <v>5340</v>
       </c>
       <c r="E848" s="6" t="s">
-        <v>5339</v>
+        <v>5341</v>
       </c>
       <c r="F848" s="6" t="s">
+        <v>5342</v>
+      </c>
+      <c r="G848" s="6" t="s">
+        <v>5342</v>
+      </c>
+      <c r="H848" s="6" t="s">
         <v>5340</v>
-      </c>
-      <c r="G848" s="6" t="s">
-        <v>5341</v>
-      </c>
-      <c r="H848" s="6" t="s">
-        <v>5342</v>
       </c>
     </row>
     <row r="849">
@@ -36245,96 +36305,96 @@
         <v>5347</v>
       </c>
       <c r="G849" s="5" t="s">
-        <v>5347</v>
+        <v>5348</v>
       </c>
       <c r="H849" s="5" t="s">
-        <v>5348</v>
+        <v>5349</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
-        <v>5349</v>
+        <v>5350</v>
       </c>
       <c r="C850" s="6" t="s">
-        <v>5350</v>
+        <v>5351</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>5351</v>
+        <v>5352</v>
       </c>
       <c r="E850" s="6" t="s">
+        <v>5353</v>
+      </c>
+      <c r="F850" s="6" t="s">
+        <v>5354</v>
+      </c>
+      <c r="G850" s="6" t="s">
+        <v>5355</v>
+      </c>
+      <c r="H850" s="6" t="s">
         <v>5352</v>
-      </c>
-      <c r="F850" s="6" t="s">
-        <v>5353</v>
-      </c>
-      <c r="G850" s="6" t="s">
-        <v>5353</v>
-      </c>
-      <c r="H850" s="6" t="s">
-        <v>5354</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
-        <v>5355</v>
+        <v>5356</v>
       </c>
       <c r="C851" s="5" t="s">
-        <v>5356</v>
+        <v>5357</v>
       </c>
       <c r="D851" s="5" t="s">
-        <v>5357</v>
+        <v>5358</v>
       </c>
       <c r="E851" s="5" t="s">
-        <v>5358</v>
+        <v>5359</v>
       </c>
       <c r="F851" s="5" t="s">
-        <v>5359</v>
+        <v>5360</v>
       </c>
       <c r="G851" s="5" t="s">
-        <v>5360</v>
+        <v>5361</v>
       </c>
       <c r="H851" s="5" t="s">
-        <v>5361</v>
+        <v>5362</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
-        <v>5362</v>
+        <v>5363</v>
       </c>
       <c r="C852" s="6" t="s">
-        <v>5363</v>
+        <v>5364</v>
       </c>
       <c r="D852" s="6" t="s">
-        <v>5364</v>
+        <v>5365</v>
       </c>
       <c r="E852" s="6" t="s">
-        <v>5365</v>
+        <v>5366</v>
       </c>
       <c r="F852" s="6" t="s">
-        <v>5366</v>
+        <v>5367</v>
       </c>
       <c r="G852" s="6" t="s">
-        <v>5366</v>
+        <v>5367</v>
       </c>
       <c r="H852" s="6" t="s">
-        <v>5367</v>
+        <v>5368</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
-        <v>5368</v>
+        <v>5369</v>
       </c>
       <c r="C853" s="5" t="s">
-        <v>5369</v>
+        <v>5370</v>
       </c>
       <c r="D853" s="5" t="s">
-        <v>5370</v>
+        <v>5371</v>
       </c>
       <c r="E853" s="5" t="s">
-        <v>5371</v>
+        <v>5372</v>
       </c>
       <c r="F853" s="5" t="s">
-        <v>5372</v>
+        <v>5373</v>
       </c>
       <c r="G853" s="5" t="s">
         <v>5373</v>
@@ -36360,217 +36420,217 @@
         <v>5379</v>
       </c>
       <c r="G854" s="6" t="s">
-        <v>5379</v>
+        <v>5380</v>
       </c>
       <c r="H854" s="6" t="s">
-        <v>5380</v>
+        <v>5381</v>
       </c>
     </row>
     <row r="855">
       <c r="B855" s="5" t="s">
-        <v>5381</v>
+        <v>5382</v>
       </c>
       <c r="C855" s="5" t="s">
-        <v>5382</v>
+        <v>5383</v>
       </c>
       <c r="D855" s="5" t="s">
-        <v>5383</v>
+        <v>5384</v>
       </c>
       <c r="E855" s="5" t="s">
-        <v>5384</v>
+        <v>5385</v>
       </c>
       <c r="F855" s="5" t="s">
-        <v>5385</v>
+        <v>5386</v>
       </c>
       <c r="G855" s="5" t="s">
-        <v>5385</v>
+        <v>5386</v>
       </c>
       <c r="H855" s="5" t="s">
-        <v>5386</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="856">
       <c r="B856" s="6" t="s">
-        <v>5387</v>
+        <v>5388</v>
       </c>
       <c r="C856" s="6" t="s">
-        <v>5388</v>
+        <v>5389</v>
       </c>
       <c r="D856" s="6" t="s">
-        <v>5388</v>
+        <v>5390</v>
       </c>
       <c r="E856" s="6" t="s">
-        <v>5388</v>
+        <v>5391</v>
       </c>
       <c r="F856" s="6" t="s">
-        <v>5388</v>
+        <v>5392</v>
       </c>
       <c r="G856" s="6" t="s">
-        <v>5388</v>
+        <v>5393</v>
       </c>
       <c r="H856" s="6" t="s">
-        <v>5388</v>
+        <v>5394</v>
       </c>
     </row>
     <row r="857">
       <c r="B857" s="5" t="s">
-        <v>5389</v>
+        <v>5395</v>
       </c>
       <c r="C857" s="5" t="s">
-        <v>5390</v>
+        <v>5396</v>
       </c>
       <c r="D857" s="5" t="s">
-        <v>5391</v>
+        <v>5397</v>
       </c>
       <c r="E857" s="5" t="s">
-        <v>5392</v>
+        <v>5398</v>
       </c>
       <c r="F857" s="5" t="s">
-        <v>5393</v>
+        <v>5399</v>
       </c>
       <c r="G857" s="5" t="s">
-        <v>5393</v>
+        <v>5399</v>
       </c>
       <c r="H857" s="5" t="s">
-        <v>5391</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="858">
       <c r="B858" s="6" t="s">
-        <v>5394</v>
+        <v>5401</v>
       </c>
       <c r="C858" s="6" t="s">
-        <v>5395</v>
+        <v>5402</v>
       </c>
       <c r="D858" s="6" t="s">
-        <v>5396</v>
+        <v>5403</v>
       </c>
       <c r="E858" s="6" t="s">
-        <v>5397</v>
+        <v>5404</v>
       </c>
       <c r="F858" s="6" t="s">
-        <v>5398</v>
+        <v>5405</v>
       </c>
       <c r="G858" s="6" t="s">
-        <v>5399</v>
+        <v>5405</v>
       </c>
       <c r="H858" s="6" t="s">
-        <v>5396</v>
+        <v>5406</v>
       </c>
     </row>
     <row r="859">
       <c r="B859" s="5" t="s">
-        <v>5400</v>
+        <v>5407</v>
       </c>
       <c r="C859" s="5" t="s">
-        <v>5401</v>
+        <v>5408</v>
       </c>
       <c r="D859" s="5" t="s">
-        <v>5402</v>
+        <v>5408</v>
       </c>
       <c r="E859" s="5" t="s">
-        <v>5403</v>
+        <v>5408</v>
       </c>
       <c r="F859" s="5" t="s">
-        <v>5403</v>
+        <v>5408</v>
       </c>
       <c r="G859" s="5" t="s">
-        <v>5403</v>
+        <v>5408</v>
       </c>
       <c r="H859" s="5" t="s">
-        <v>5402</v>
+        <v>5408</v>
       </c>
     </row>
     <row r="860">
       <c r="B860" s="6" t="s">
-        <v>5404</v>
+        <v>5409</v>
       </c>
       <c r="C860" s="6" t="s">
-        <v>5405</v>
+        <v>5410</v>
       </c>
       <c r="D860" s="6" t="s">
-        <v>5406</v>
+        <v>5411</v>
       </c>
       <c r="E860" s="6" t="s">
-        <v>5407</v>
+        <v>5412</v>
       </c>
       <c r="F860" s="6" t="s">
-        <v>5407</v>
+        <v>5413</v>
       </c>
       <c r="G860" s="6" t="s">
-        <v>5407</v>
+        <v>5413</v>
       </c>
       <c r="H860" s="6" t="s">
-        <v>5406</v>
+        <v>5411</v>
       </c>
     </row>
     <row r="861">
       <c r="B861" s="5" t="s">
-        <v>5408</v>
+        <v>5414</v>
       </c>
       <c r="C861" s="5" t="s">
-        <v>5409</v>
+        <v>5415</v>
       </c>
       <c r="D861" s="5" t="s">
-        <v>5410</v>
+        <v>5416</v>
       </c>
       <c r="E861" s="5" t="s">
-        <v>5411</v>
+        <v>5417</v>
       </c>
       <c r="F861" s="5" t="s">
-        <v>5412</v>
+        <v>5418</v>
       </c>
       <c r="G861" s="5" t="s">
-        <v>5413</v>
+        <v>5419</v>
       </c>
       <c r="H861" s="5" t="s">
-        <v>5414</v>
+        <v>5416</v>
       </c>
     </row>
     <row r="862">
       <c r="B862" s="6" t="s">
-        <v>5415</v>
+        <v>5420</v>
       </c>
       <c r="C862" s="6" t="s">
-        <v>5416</v>
+        <v>5421</v>
       </c>
       <c r="D862" s="6" t="s">
-        <v>5417</v>
+        <v>5422</v>
       </c>
       <c r="E862" s="6" t="s">
-        <v>5418</v>
+        <v>5423</v>
       </c>
       <c r="F862" s="6" t="s">
-        <v>5419</v>
+        <v>5423</v>
       </c>
       <c r="G862" s="6" t="s">
-        <v>5420</v>
+        <v>5423</v>
       </c>
       <c r="H862" s="6" t="s">
-        <v>5417</v>
+        <v>5422</v>
       </c>
     </row>
     <row r="863">
       <c r="B863" s="5" t="s">
-        <v>5421</v>
+        <v>5424</v>
       </c>
       <c r="C863" s="5" t="s">
-        <v>5422</v>
+        <v>5425</v>
       </c>
       <c r="D863" s="5" t="s">
-        <v>5423</v>
+        <v>5426</v>
       </c>
       <c r="E863" s="5" t="s">
-        <v>5424</v>
+        <v>5427</v>
       </c>
       <c r="F863" s="5" t="s">
-        <v>5425</v>
+        <v>5427</v>
       </c>
       <c r="G863" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="H863" s="5" t="s">
         <v>5426</v>
-      </c>
-      <c r="H863" s="5" t="s">
-        <v>5427</v>
       </c>
     </row>
     <row r="864">
@@ -36616,30 +36676,30 @@
         <v>5440</v>
       </c>
       <c r="H865" s="5" t="s">
-        <v>5441</v>
+        <v>5437</v>
       </c>
     </row>
     <row r="866">
       <c r="B866" s="6" t="s">
+        <v>5441</v>
+      </c>
+      <c r="C866" s="6" t="s">
         <v>5442</v>
       </c>
-      <c r="C866" s="6" t="s">
+      <c r="D866" s="6" t="s">
         <v>5443</v>
       </c>
-      <c r="D866" s="6" t="s">
+      <c r="E866" s="6" t="s">
         <v>5444</v>
       </c>
-      <c r="E866" s="6" t="s">
+      <c r="F866" s="6" t="s">
         <v>5445</v>
       </c>
-      <c r="F866" s="6" t="s">
+      <c r="G866" s="6" t="s">
         <v>5446</v>
       </c>
-      <c r="G866" s="6" t="s">
+      <c r="H866" s="6" t="s">
         <v>5447</v>
-      </c>
-      <c r="H866" s="6" t="s">
-        <v>5417</v>
       </c>
     </row>
     <row r="867">
@@ -36682,14 +36742,83 @@
         <v>5459</v>
       </c>
       <c r="G868" s="6" t="s">
-        <v>5459</v>
+        <v>5460</v>
       </c>
       <c r="H868" s="6" t="s">
-        <v>5460</v>
+        <v>5461</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="B869" s="5" t="s">
+        <v>5462</v>
+      </c>
+      <c r="C869" s="5" t="s">
+        <v>5463</v>
+      </c>
+      <c r="D869" s="5" t="s">
+        <v>5464</v>
+      </c>
+      <c r="E869" s="5" t="s">
+        <v>5465</v>
+      </c>
+      <c r="F869" s="5" t="s">
+        <v>5466</v>
+      </c>
+      <c r="G869" s="5" t="s">
+        <v>5467</v>
+      </c>
+      <c r="H869" s="5" t="s">
+        <v>5437</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="B870" s="6" t="s">
+        <v>5468</v>
+      </c>
+      <c r="C870" s="6" t="s">
+        <v>5469</v>
+      </c>
+      <c r="D870" s="6" t="s">
+        <v>5470</v>
+      </c>
+      <c r="E870" s="6" t="s">
+        <v>5471</v>
+      </c>
+      <c r="F870" s="6" t="s">
+        <v>5472</v>
+      </c>
+      <c r="G870" s="6" t="s">
+        <v>5473</v>
+      </c>
+      <c r="H870" s="6" t="s">
+        <v>5474</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="B871" s="5" t="s">
+        <v>5475</v>
+      </c>
+      <c r="C871" s="5" t="s">
+        <v>5476</v>
+      </c>
+      <c r="D871" s="5" t="s">
+        <v>5477</v>
+      </c>
+      <c r="E871" s="5" t="s">
+        <v>5478</v>
+      </c>
+      <c r="F871" s="5" t="s">
+        <v>5479</v>
+      </c>
+      <c r="G871" s="5" t="s">
+        <v>5479</v>
+      </c>
+      <c r="H871" s="5" t="s">
+        <v>5480</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H868"/>
+  <autoFilter ref="B2:H871"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36708,10 +36837,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5461</v>
+        <v>5481</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5462</v>
+        <v>5482</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36722,16 +36851,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5463</v>
+        <v>5483</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5464</v>
+        <v>5484</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5465</v>
+        <v>5485</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5466</v>
+        <v>5486</v>
       </c>
     </row>
     <row r="3">
@@ -36739,16 +36868,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5467</v>
+        <v>5487</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5468</v>
+        <v>5488</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5469</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="4">
@@ -36759,24 +36888,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5470</v>
+        <v>5490</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5471</v>
+        <v>5491</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5472</v>
+        <v>5492</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5473</v>
+        <v>5493</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5474</v>
+        <v>5494</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36784,13 +36913,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5475</v>
+        <v>5495</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5476</v>
+        <v>5496</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36798,13 +36927,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5477</v>
+        <v>5497</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5478</v>
+        <v>5498</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36812,13 +36941,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5479</v>
+        <v>5499</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5480</v>
+        <v>5500</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36826,13 +36955,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5481</v>
+        <v>5501</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5482</v>
+        <v>5502</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36840,13 +36969,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5483</v>
+        <v>5503</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5484</v>
+        <v>5504</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36854,13 +36983,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5485</v>
+        <v>5505</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5486</v>
+        <v>5506</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36868,13 +36997,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5487</v>
+        <v>5507</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5488</v>
+        <v>5508</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -36882,13 +37011,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5489</v>
+        <v>5509</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5490</v>
+        <v>5510</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -36896,13 +37025,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5491</v>
+        <v>5511</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5492</v>
+        <v>5512</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -36916,7 +37045,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5493</v>
+        <v>5513</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -36924,13 +37053,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5494</v>
+        <v>5514</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5495</v>
+        <v>5515</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -36938,13 +37067,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5496</v>
+        <v>5516</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5497</v>
+        <v>5517</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -36952,13 +37081,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5498</v>
+        <v>5518</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5499</v>
+        <v>5519</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -36966,13 +37095,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5500</v>
+        <v>5520</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5501</v>
+        <v>5521</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -36980,13 +37109,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5502</v>
+        <v>5522</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5503</v>
+        <v>5523</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -36994,13 +37123,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5504</v>
+        <v>5524</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5505</v>
+        <v>5525</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -37008,13 +37137,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5506</v>
+        <v>5526</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5507</v>
+        <v>5527</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -37022,13 +37151,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5508</v>
+        <v>5528</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5509</v>
+        <v>5529</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -37036,13 +37165,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5510</v>
+        <v>5530</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5511</v>
+        <v>5531</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$871]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$872]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6160" uniqueCount="5532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6167" uniqueCount="5539">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -16460,6 +16460,27 @@
   </si>
   <si>
     <t xml:space="preserve">Kassieren  ${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.payout.counting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정산 중</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counting up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">精算中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正在结算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正在結算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wird abgerechnet</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -16812,7 +16833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H871"/>
+  <dimension ref="A1:H872"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -36817,8 +36838,31 @@
         <v>5480</v>
       </c>
     </row>
+    <row r="872">
+      <c r="B872" s="6" t="s">
+        <v>5481</v>
+      </c>
+      <c r="C872" s="6" t="s">
+        <v>5482</v>
+      </c>
+      <c r="D872" s="6" t="s">
+        <v>5483</v>
+      </c>
+      <c r="E872" s="6" t="s">
+        <v>5484</v>
+      </c>
+      <c r="F872" s="6" t="s">
+        <v>5485</v>
+      </c>
+      <c r="G872" s="6" t="s">
+        <v>5486</v>
+      </c>
+      <c r="H872" s="6" t="s">
+        <v>5487</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H871"/>
+  <autoFilter ref="B2:H872"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36837,10 +36881,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5481</v>
+        <v>5488</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5482</v>
+        <v>5489</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36851,16 +36895,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5483</v>
+        <v>5490</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5484</v>
+        <v>5491</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5485</v>
+        <v>5492</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5486</v>
+        <v>5493</v>
       </c>
     </row>
     <row r="3">
@@ -36868,16 +36912,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5487</v>
+        <v>5494</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5488</v>
+        <v>5495</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5489</v>
+        <v>5496</v>
       </c>
     </row>
     <row r="4">
@@ -36888,24 +36932,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5490</v>
+        <v>5497</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5491</v>
+        <v>5498</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5492</v>
+        <v>5499</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5493</v>
+        <v>5500</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5494</v>
+        <v>5501</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36913,13 +36957,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5495</v>
+        <v>5502</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5496</v>
+        <v>5503</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36927,13 +36971,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5497</v>
+        <v>5504</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5498</v>
+        <v>5505</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36941,13 +36985,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5499</v>
+        <v>5506</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5500</v>
+        <v>5507</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36955,13 +36999,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5501</v>
+        <v>5508</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5502</v>
+        <v>5509</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -36969,13 +37013,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5503</v>
+        <v>5510</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5504</v>
+        <v>5511</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -36983,13 +37027,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5505</v>
+        <v>5512</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5506</v>
+        <v>5513</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -36997,13 +37041,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5507</v>
+        <v>5514</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5508</v>
+        <v>5515</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -37011,13 +37055,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5509</v>
+        <v>5516</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5510</v>
+        <v>5517</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -37025,13 +37069,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5511</v>
+        <v>5518</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5512</v>
+        <v>5519</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -37045,7 +37089,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5513</v>
+        <v>5520</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -37053,13 +37097,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5514</v>
+        <v>5521</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5515</v>
+        <v>5522</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -37067,13 +37111,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5516</v>
+        <v>5523</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5517</v>
+        <v>5524</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -37081,13 +37125,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5518</v>
+        <v>5525</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5519</v>
+        <v>5526</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -37095,13 +37139,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5520</v>
+        <v>5527</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5521</v>
+        <v>5528</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -37109,13 +37153,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5522</v>
+        <v>5529</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5523</v>
+        <v>5530</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -37123,13 +37167,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5524</v>
+        <v>5531</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5525</v>
+        <v>5532</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -37137,13 +37181,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5526</v>
+        <v>5533</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5527</v>
+        <v>5534</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -37151,13 +37195,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5528</v>
+        <v>5535</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5529</v>
+        <v>5536</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -37165,13 +37209,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5530</v>
+        <v>5537</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5531</v>
+        <v>5538</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$872]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$880]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6167" uniqueCount="5539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6223" uniqueCount="5589">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -13186,6 +13186,165 @@
     <t xml:space="preserve">Benutzen</t>
   </si>
   <si>
+    <t xml:space="preserve">ui.button.buy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">買う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">购买</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購買</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaufen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.take</t>
+  </si>
+  <si>
+    <t xml:space="preserve">집는다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拿取</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nehmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.swap_take</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바꿔 집는다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swap for It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入れ替える</t>
+  </si>
+  <si>
+    <t xml:space="preserve">换取</t>
+  </si>
+  <si>
+    <t xml:space="preserve">換取</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tauschen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.run_info.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">런 정보</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run Info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラン情報</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局信息</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局資訊</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rundeninfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.tab.blinds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">블라인드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blinds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ブラインド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盲注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.tab.stakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스테이크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステーク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">难度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">難度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einsätze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.run_info.current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지금</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当前</t>
+  </si>
+  <si>
+    <t xml:space="preserve">當前</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aktuell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.stake.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안테 표 {column}열 · 스몰 보상 ${reward} · 버리기 {discards}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ante col. {column} · Small reward ${reward} · Discards {discards}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アンティ表 {column}列 · スモール報酬 ${reward} · 捨て札 {discards}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">底注表第 {column} 列 · 小盲奖励 ${reward} · 弃牌 {discards}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">底注表第 {column} 列 · 小盲獎勵 ${reward} · 棄牌 {discards}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ante-Spalte {column} · Small-Belohnung ${reward} · Ablegen {discards}</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.button.skip</t>
   </si>
   <si>
@@ -13576,12 +13735,6 @@
     <t xml:space="preserve">購入</t>
   </si>
   <si>
-    <t xml:space="preserve">购买</t>
-  </si>
-  <si>
-    <t xml:space="preserve">購買</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kauf</t>
   </si>
   <si>
@@ -15641,9 +15794,6 @@
   </si>
   <si>
     <t xml:space="preserve">替換</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tauschen</t>
   </si>
   <si>
     <t xml:space="preserve">ui.pack.full_mark</t>
@@ -16833,7 +16983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H872"/>
+  <dimension ref="A1:H880"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -32571,453 +32721,453 @@
         <v>4391</v>
       </c>
       <c r="E686" s="6" t="s">
-        <v>2250</v>
+        <v>4392</v>
       </c>
       <c r="F686" s="6" t="s">
-        <v>2251</v>
+        <v>4393</v>
       </c>
       <c r="G686" s="6" t="s">
-        <v>2252</v>
+        <v>4394</v>
       </c>
       <c r="H686" s="6" t="s">
-        <v>4392</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="687">
       <c r="B687" s="5" t="s">
-        <v>4393</v>
+        <v>4396</v>
       </c>
       <c r="C687" s="5" t="s">
-        <v>4394</v>
+        <v>4397</v>
       </c>
       <c r="D687" s="5" t="s">
-        <v>4395</v>
+        <v>4398</v>
       </c>
       <c r="E687" s="5" t="s">
-        <v>4396</v>
+        <v>4399</v>
       </c>
       <c r="F687" s="5" t="s">
-        <v>4397</v>
+        <v>4400</v>
       </c>
       <c r="G687" s="5" t="s">
-        <v>4398</v>
+        <v>4400</v>
       </c>
       <c r="H687" s="5" t="s">
-        <v>4399</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="688">
       <c r="B688" s="6" t="s">
-        <v>4400</v>
+        <v>4402</v>
       </c>
       <c r="C688" s="6" t="s">
-        <v>4401</v>
+        <v>4403</v>
       </c>
       <c r="D688" s="6" t="s">
-        <v>4402</v>
+        <v>4404</v>
       </c>
       <c r="E688" s="6" t="s">
-        <v>4403</v>
+        <v>4405</v>
       </c>
       <c r="F688" s="6" t="s">
-        <v>4404</v>
+        <v>4406</v>
       </c>
       <c r="G688" s="6" t="s">
-        <v>4405</v>
+        <v>4407</v>
       </c>
       <c r="H688" s="6" t="s">
-        <v>4406</v>
+        <v>4408</v>
       </c>
     </row>
     <row r="689">
       <c r="B689" s="5" t="s">
-        <v>4407</v>
+        <v>4409</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>4408</v>
+        <v>4410</v>
       </c>
       <c r="D689" s="5" t="s">
-        <v>4409</v>
+        <v>4411</v>
       </c>
       <c r="E689" s="5" t="s">
-        <v>4410</v>
+        <v>4412</v>
       </c>
       <c r="F689" s="5" t="s">
-        <v>4411</v>
+        <v>4413</v>
       </c>
       <c r="G689" s="5" t="s">
-        <v>4411</v>
+        <v>4414</v>
       </c>
       <c r="H689" s="5" t="s">
-        <v>4412</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="690">
       <c r="B690" s="6" t="s">
-        <v>4413</v>
+        <v>4416</v>
       </c>
       <c r="C690" s="6" t="s">
-        <v>3495</v>
+        <v>4417</v>
       </c>
       <c r="D690" s="6" t="s">
-        <v>3500</v>
+        <v>4418</v>
       </c>
       <c r="E690" s="6" t="s">
-        <v>3497</v>
+        <v>4419</v>
       </c>
       <c r="F690" s="6" t="s">
-        <v>3498</v>
+        <v>4420</v>
       </c>
       <c r="G690" s="6" t="s">
-        <v>3499</v>
+        <v>4420</v>
       </c>
       <c r="H690" s="6" t="s">
-        <v>3500</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="691">
       <c r="B691" s="5" t="s">
-        <v>4414</v>
+        <v>4421</v>
       </c>
       <c r="C691" s="5" t="s">
-        <v>2045</v>
+        <v>4422</v>
       </c>
       <c r="D691" s="5" t="s">
-        <v>2046</v>
+        <v>4423</v>
       </c>
       <c r="E691" s="5" t="s">
-        <v>2048</v>
+        <v>4424</v>
       </c>
       <c r="F691" s="5" t="s">
-        <v>2048</v>
+        <v>4425</v>
       </c>
       <c r="G691" s="5" t="s">
-        <v>2048</v>
+        <v>4426</v>
       </c>
       <c r="H691" s="5" t="s">
-        <v>2046</v>
+        <v>4427</v>
       </c>
     </row>
     <row r="692">
       <c r="B692" s="6" t="s">
-        <v>4415</v>
+        <v>4428</v>
       </c>
       <c r="C692" s="6" t="s">
-        <v>4416</v>
+        <v>4429</v>
       </c>
       <c r="D692" s="6" t="s">
-        <v>4417</v>
+        <v>4430</v>
       </c>
       <c r="E692" s="6" t="s">
-        <v>4418</v>
+        <v>4431</v>
       </c>
       <c r="F692" s="6" t="s">
-        <v>4419</v>
+        <v>4432</v>
       </c>
       <c r="G692" s="6" t="s">
-        <v>4420</v>
+        <v>4433</v>
       </c>
       <c r="H692" s="6" t="s">
-        <v>4417</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="693">
       <c r="B693" s="5" t="s">
-        <v>4421</v>
+        <v>4435</v>
       </c>
       <c r="C693" s="5" t="s">
-        <v>4422</v>
+        <v>4436</v>
       </c>
       <c r="D693" s="5" t="s">
-        <v>4423</v>
+        <v>4437</v>
       </c>
       <c r="E693" s="5" t="s">
-        <v>4424</v>
+        <v>4438</v>
       </c>
       <c r="F693" s="5" t="s">
-        <v>4424</v>
+        <v>4439</v>
       </c>
       <c r="G693" s="5" t="s">
-        <v>4424</v>
+        <v>4440</v>
       </c>
       <c r="H693" s="5" t="s">
-        <v>4423</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="694">
       <c r="B694" s="6" t="s">
-        <v>4425</v>
+        <v>4442</v>
       </c>
       <c r="C694" s="6" t="s">
-        <v>4426</v>
+        <v>4443</v>
       </c>
       <c r="D694" s="6" t="s">
-        <v>4348</v>
+        <v>4444</v>
       </c>
       <c r="E694" s="6" t="s">
-        <v>4427</v>
+        <v>2250</v>
       </c>
       <c r="F694" s="6" t="s">
-        <v>4317</v>
+        <v>2251</v>
       </c>
       <c r="G694" s="6" t="s">
-        <v>4317</v>
+        <v>2252</v>
       </c>
       <c r="H694" s="6" t="s">
-        <v>4428</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="695">
       <c r="B695" s="5" t="s">
-        <v>4429</v>
+        <v>4446</v>
       </c>
       <c r="C695" s="5" t="s">
-        <v>4430</v>
+        <v>4447</v>
       </c>
       <c r="D695" s="5" t="s">
-        <v>4431</v>
+        <v>4448</v>
       </c>
       <c r="E695" s="5" t="s">
-        <v>4432</v>
+        <v>4449</v>
       </c>
       <c r="F695" s="5" t="s">
-        <v>4323</v>
+        <v>4450</v>
       </c>
       <c r="G695" s="5" t="s">
-        <v>4324</v>
+        <v>4451</v>
       </c>
       <c r="H695" s="5" t="s">
-        <v>4433</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="696">
       <c r="B696" s="6" t="s">
-        <v>4434</v>
+        <v>4453</v>
       </c>
       <c r="C696" s="6" t="s">
-        <v>3510</v>
+        <v>4454</v>
       </c>
       <c r="D696" s="6" t="s">
-        <v>4435</v>
+        <v>4455</v>
       </c>
       <c r="E696" s="6" t="s">
-        <v>3512</v>
+        <v>4456</v>
       </c>
       <c r="F696" s="6" t="s">
-        <v>3513</v>
+        <v>4457</v>
       </c>
       <c r="G696" s="6" t="s">
-        <v>3514</v>
+        <v>4458</v>
       </c>
       <c r="H696" s="6" t="s">
-        <v>3515</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="697">
       <c r="B697" s="5" t="s">
-        <v>4436</v>
+        <v>4460</v>
       </c>
       <c r="C697" s="5" t="s">
-        <v>4081</v>
+        <v>4461</v>
       </c>
       <c r="D697" s="5" t="s">
-        <v>4082</v>
+        <v>4462</v>
       </c>
       <c r="E697" s="5" t="s">
-        <v>4083</v>
+        <v>4463</v>
       </c>
       <c r="F697" s="5" t="s">
-        <v>4084</v>
+        <v>4464</v>
       </c>
       <c r="G697" s="5" t="s">
-        <v>4084</v>
+        <v>4464</v>
       </c>
       <c r="H697" s="5" t="s">
-        <v>4082</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="698">
       <c r="B698" s="6" t="s">
-        <v>4437</v>
+        <v>4466</v>
       </c>
       <c r="C698" s="6" t="s">
-        <v>4438</v>
+        <v>3495</v>
       </c>
       <c r="D698" s="6" t="s">
-        <v>4439</v>
+        <v>3500</v>
       </c>
       <c r="E698" s="6" t="s">
-        <v>4440</v>
+        <v>3497</v>
       </c>
       <c r="F698" s="6" t="s">
-        <v>4441</v>
+        <v>3498</v>
       </c>
       <c r="G698" s="6" t="s">
-        <v>4442</v>
+        <v>3499</v>
       </c>
       <c r="H698" s="6" t="s">
-        <v>4443</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="699">
       <c r="B699" s="5" t="s">
-        <v>4444</v>
+        <v>4467</v>
       </c>
       <c r="C699" s="5" t="s">
-        <v>4445</v>
+        <v>2045</v>
       </c>
       <c r="D699" s="5" t="s">
-        <v>4446</v>
+        <v>2046</v>
       </c>
       <c r="E699" s="5" t="s">
-        <v>4447</v>
+        <v>2048</v>
       </c>
       <c r="F699" s="5" t="s">
-        <v>4448</v>
+        <v>2048</v>
       </c>
       <c r="G699" s="5" t="s">
-        <v>4449</v>
+        <v>2048</v>
       </c>
       <c r="H699" s="5" t="s">
-        <v>4450</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="700">
       <c r="B700" s="6" t="s">
-        <v>4451</v>
+        <v>4468</v>
       </c>
       <c r="C700" s="6" t="s">
-        <v>4452</v>
+        <v>4469</v>
       </c>
       <c r="D700" s="6" t="s">
-        <v>4453</v>
+        <v>4470</v>
       </c>
       <c r="E700" s="6" t="s">
-        <v>4454</v>
+        <v>4471</v>
       </c>
       <c r="F700" s="6" t="s">
-        <v>2042</v>
+        <v>4472</v>
       </c>
       <c r="G700" s="6" t="s">
-        <v>2043</v>
+        <v>4473</v>
       </c>
       <c r="H700" s="6" t="s">
-        <v>4455</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="701">
       <c r="B701" s="5" t="s">
-        <v>4456</v>
+        <v>4474</v>
       </c>
       <c r="C701" s="5" t="s">
-        <v>4457</v>
+        <v>4475</v>
       </c>
       <c r="D701" s="5" t="s">
-        <v>4458</v>
+        <v>4476</v>
       </c>
       <c r="E701" s="5" t="s">
-        <v>4459</v>
+        <v>4477</v>
       </c>
       <c r="F701" s="5" t="s">
-        <v>4460</v>
+        <v>4477</v>
       </c>
       <c r="G701" s="5" t="s">
-        <v>4461</v>
+        <v>4477</v>
       </c>
       <c r="H701" s="5" t="s">
-        <v>4462</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="702">
       <c r="B702" s="6" t="s">
-        <v>4463</v>
+        <v>4478</v>
       </c>
       <c r="C702" s="6" t="s">
-        <v>4464</v>
+        <v>4479</v>
       </c>
       <c r="D702" s="6" t="s">
-        <v>4465</v>
+        <v>4348</v>
       </c>
       <c r="E702" s="6" t="s">
-        <v>4466</v>
+        <v>4480</v>
       </c>
       <c r="F702" s="6" t="s">
-        <v>4467</v>
+        <v>4317</v>
       </c>
       <c r="G702" s="6" t="s">
-        <v>4468</v>
+        <v>4317</v>
       </c>
       <c r="H702" s="6" t="s">
-        <v>4469</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="703">
       <c r="B703" s="5" t="s">
-        <v>4470</v>
+        <v>4482</v>
       </c>
       <c r="C703" s="5" t="s">
-        <v>4471</v>
+        <v>4483</v>
       </c>
       <c r="D703" s="5" t="s">
-        <v>4472</v>
+        <v>4484</v>
       </c>
       <c r="E703" s="5" t="s">
-        <v>4473</v>
+        <v>4485</v>
       </c>
       <c r="F703" s="5" t="s">
-        <v>4474</v>
+        <v>4323</v>
       </c>
       <c r="G703" s="5" t="s">
-        <v>4475</v>
+        <v>4324</v>
       </c>
       <c r="H703" s="5" t="s">
-        <v>4476</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="704">
       <c r="B704" s="6" t="s">
-        <v>4477</v>
+        <v>4487</v>
       </c>
       <c r="C704" s="6" t="s">
-        <v>4478</v>
+        <v>3510</v>
       </c>
       <c r="D704" s="6" t="s">
-        <v>4479</v>
+        <v>4488</v>
       </c>
       <c r="E704" s="6" t="s">
-        <v>4480</v>
+        <v>3512</v>
       </c>
       <c r="F704" s="6" t="s">
-        <v>4481</v>
+        <v>3513</v>
       </c>
       <c r="G704" s="6" t="s">
-        <v>4480</v>
+        <v>3514</v>
       </c>
       <c r="H704" s="6" t="s">
-        <v>4482</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="705">
       <c r="B705" s="5" t="s">
-        <v>4483</v>
+        <v>4489</v>
       </c>
       <c r="C705" s="5" t="s">
-        <v>4484</v>
+        <v>4081</v>
       </c>
       <c r="D705" s="5" t="s">
-        <v>4485</v>
+        <v>4082</v>
       </c>
       <c r="E705" s="5" t="s">
-        <v>4486</v>
+        <v>4083</v>
       </c>
       <c r="F705" s="5" t="s">
-        <v>4487</v>
+        <v>4084</v>
       </c>
       <c r="G705" s="5" t="s">
-        <v>4488</v>
+        <v>4084</v>
       </c>
       <c r="H705" s="5" t="s">
-        <v>4489</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="706">
@@ -33080,10 +33230,10 @@
         <v>4507</v>
       </c>
       <c r="F708" s="6" t="s">
-        <v>4507</v>
+        <v>2042</v>
       </c>
       <c r="G708" s="6" t="s">
-        <v>4507</v>
+        <v>2043</v>
       </c>
       <c r="H708" s="6" t="s">
         <v>4508</v>
@@ -33106,1062 +33256,1062 @@
         <v>4513</v>
       </c>
       <c r="G709" s="5" t="s">
-        <v>4513</v>
+        <v>4514</v>
       </c>
       <c r="H709" s="5" t="s">
-        <v>4514</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="710">
       <c r="B710" s="6" t="s">
-        <v>4515</v>
+        <v>4516</v>
       </c>
       <c r="C710" s="6" t="s">
-        <v>4516</v>
+        <v>4517</v>
       </c>
       <c r="D710" s="6" t="s">
-        <v>4517</v>
+        <v>4518</v>
       </c>
       <c r="E710" s="6" t="s">
-        <v>4518</v>
+        <v>4519</v>
       </c>
       <c r="F710" s="6" t="s">
-        <v>4519</v>
+        <v>4520</v>
       </c>
       <c r="G710" s="6" t="s">
-        <v>4520</v>
+        <v>4521</v>
       </c>
       <c r="H710" s="6" t="s">
-        <v>4521</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="711">
       <c r="B711" s="5" t="s">
-        <v>4522</v>
+        <v>4523</v>
       </c>
       <c r="C711" s="5" t="s">
-        <v>4523</v>
+        <v>4524</v>
       </c>
       <c r="D711" s="5" t="s">
-        <v>4524</v>
+        <v>4525</v>
       </c>
       <c r="E711" s="5" t="s">
-        <v>4525</v>
+        <v>4526</v>
       </c>
       <c r="F711" s="5" t="s">
-        <v>4526</v>
+        <v>4527</v>
       </c>
       <c r="G711" s="5" t="s">
-        <v>4526</v>
+        <v>4528</v>
       </c>
       <c r="H711" s="5" t="s">
-        <v>4527</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="712">
       <c r="B712" s="6" t="s">
-        <v>4528</v>
+        <v>4530</v>
       </c>
       <c r="C712" s="6" t="s">
-        <v>4529</v>
+        <v>4531</v>
       </c>
       <c r="D712" s="6" t="s">
-        <v>4530</v>
+        <v>4532</v>
       </c>
       <c r="E712" s="6" t="s">
-        <v>4531</v>
+        <v>4533</v>
       </c>
       <c r="F712" s="6" t="s">
-        <v>4532</v>
+        <v>4534</v>
       </c>
       <c r="G712" s="6" t="s">
-        <v>4532</v>
+        <v>4533</v>
       </c>
       <c r="H712" s="6" t="s">
-        <v>4533</v>
+        <v>4535</v>
       </c>
     </row>
     <row r="713">
       <c r="B713" s="5" t="s">
-        <v>4534</v>
+        <v>4536</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>4535</v>
+        <v>4537</v>
       </c>
       <c r="D713" s="5" t="s">
-        <v>4536</v>
+        <v>4538</v>
       </c>
       <c r="E713" s="5" t="s">
-        <v>4537</v>
+        <v>4539</v>
       </c>
       <c r="F713" s="5" t="s">
-        <v>4536</v>
+        <v>4540</v>
       </c>
       <c r="G713" s="5" t="s">
-        <v>4536</v>
+        <v>4541</v>
       </c>
       <c r="H713" s="5" t="s">
-        <v>4536</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="714">
       <c r="B714" s="6" t="s">
-        <v>4538</v>
+        <v>4543</v>
       </c>
       <c r="C714" s="6" t="s">
-        <v>3610</v>
+        <v>4544</v>
       </c>
       <c r="D714" s="6" t="s">
-        <v>2981</v>
+        <v>4545</v>
       </c>
       <c r="E714" s="6" t="s">
-        <v>3612</v>
+        <v>4546</v>
       </c>
       <c r="F714" s="6" t="s">
-        <v>3613</v>
+        <v>4547</v>
       </c>
       <c r="G714" s="6" t="s">
-        <v>3613</v>
+        <v>4548</v>
       </c>
       <c r="H714" s="6" t="s">
-        <v>2981</v>
+        <v>4549</v>
       </c>
     </row>
     <row r="715">
       <c r="B715" s="5" t="s">
-        <v>4539</v>
+        <v>4550</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>4540</v>
+        <v>4551</v>
       </c>
       <c r="D715" s="5" t="s">
-        <v>4541</v>
+        <v>4552</v>
       </c>
       <c r="E715" s="5" t="s">
-        <v>4542</v>
+        <v>4553</v>
       </c>
       <c r="F715" s="5" t="s">
-        <v>4542</v>
+        <v>4554</v>
       </c>
       <c r="G715" s="5" t="s">
-        <v>4542</v>
+        <v>4555</v>
       </c>
       <c r="H715" s="5" t="s">
-        <v>4543</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="716">
       <c r="B716" s="6" t="s">
-        <v>4544</v>
+        <v>4557</v>
       </c>
       <c r="C716" s="6" t="s">
-        <v>3657</v>
+        <v>4558</v>
       </c>
       <c r="D716" s="6" t="s">
-        <v>4545</v>
+        <v>4559</v>
       </c>
       <c r="E716" s="6" t="s">
-        <v>3659</v>
+        <v>4560</v>
       </c>
       <c r="F716" s="6" t="s">
-        <v>3660</v>
+        <v>4560</v>
       </c>
       <c r="G716" s="6" t="s">
-        <v>3661</v>
+        <v>4560</v>
       </c>
       <c r="H716" s="6" t="s">
-        <v>4546</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="717">
       <c r="B717" s="5" t="s">
-        <v>4547</v>
+        <v>4562</v>
       </c>
       <c r="C717" s="5" t="s">
-        <v>3651</v>
+        <v>4563</v>
       </c>
       <c r="D717" s="5" t="s">
-        <v>4548</v>
+        <v>4564</v>
       </c>
       <c r="E717" s="5" t="s">
-        <v>3653</v>
+        <v>4565</v>
       </c>
       <c r="F717" s="5" t="s">
-        <v>3654</v>
+        <v>4566</v>
       </c>
       <c r="G717" s="5" t="s">
-        <v>3654</v>
+        <v>4566</v>
       </c>
       <c r="H717" s="5" t="s">
-        <v>4549</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="718">
       <c r="B718" s="6" t="s">
-        <v>4550</v>
+        <v>4568</v>
       </c>
       <c r="C718" s="6" t="s">
-        <v>4551</v>
+        <v>4569</v>
       </c>
       <c r="D718" s="6" t="s">
-        <v>4552</v>
+        <v>4570</v>
       </c>
       <c r="E718" s="6" t="s">
-        <v>4553</v>
+        <v>4571</v>
       </c>
       <c r="F718" s="6" t="s">
-        <v>4554</v>
+        <v>4393</v>
       </c>
       <c r="G718" s="6" t="s">
-        <v>4555</v>
+        <v>4394</v>
       </c>
       <c r="H718" s="6" t="s">
-        <v>4552</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="719">
       <c r="B719" s="5" t="s">
-        <v>4556</v>
+        <v>4573</v>
       </c>
       <c r="C719" s="5" t="s">
-        <v>4557</v>
+        <v>4574</v>
       </c>
       <c r="D719" s="5" t="s">
-        <v>4558</v>
+        <v>4575</v>
       </c>
       <c r="E719" s="5" t="s">
-        <v>4559</v>
+        <v>4576</v>
       </c>
       <c r="F719" s="5" t="s">
-        <v>4560</v>
+        <v>4577</v>
       </c>
       <c r="G719" s="5" t="s">
-        <v>4560</v>
+        <v>4577</v>
       </c>
       <c r="H719" s="5" t="s">
-        <v>4558</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="720">
       <c r="B720" s="6" t="s">
-        <v>4561</v>
+        <v>4579</v>
       </c>
       <c r="C720" s="6" t="s">
-        <v>4562</v>
+        <v>4580</v>
       </c>
       <c r="D720" s="6" t="s">
-        <v>4563</v>
+        <v>4581</v>
       </c>
       <c r="E720" s="6" t="s">
-        <v>4564</v>
+        <v>4582</v>
       </c>
       <c r="F720" s="6" t="s">
-        <v>4565</v>
+        <v>4583</v>
       </c>
       <c r="G720" s="6" t="s">
-        <v>4566</v>
+        <v>4583</v>
       </c>
       <c r="H720" s="6" t="s">
-        <v>4567</v>
+        <v>4584</v>
       </c>
     </row>
     <row r="721">
       <c r="B721" s="5" t="s">
-        <v>4568</v>
+        <v>4585</v>
       </c>
       <c r="C721" s="5" t="s">
-        <v>3749</v>
+        <v>4586</v>
       </c>
       <c r="D721" s="5" t="s">
-        <v>4569</v>
+        <v>4587</v>
       </c>
       <c r="E721" s="5" t="s">
-        <v>3751</v>
+        <v>4588</v>
       </c>
       <c r="F721" s="5" t="s">
-        <v>3752</v>
+        <v>4587</v>
       </c>
       <c r="G721" s="5" t="s">
-        <v>3752</v>
+        <v>4587</v>
       </c>
       <c r="H721" s="5" t="s">
-        <v>3753</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="722">
       <c r="B722" s="6" t="s">
-        <v>4570</v>
+        <v>4589</v>
       </c>
       <c r="C722" s="6" t="s">
-        <v>4571</v>
+        <v>3610</v>
       </c>
       <c r="D722" s="6" t="s">
-        <v>4359</v>
+        <v>2981</v>
       </c>
       <c r="E722" s="6" t="s">
-        <v>4572</v>
+        <v>3612</v>
       </c>
       <c r="F722" s="6" t="s">
-        <v>4573</v>
+        <v>3613</v>
       </c>
       <c r="G722" s="6" t="s">
-        <v>4574</v>
+        <v>3613</v>
       </c>
       <c r="H722" s="6" t="s">
-        <v>4359</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="723">
       <c r="B723" s="5" t="s">
-        <v>4575</v>
+        <v>4590</v>
       </c>
       <c r="C723" s="5" t="s">
-        <v>4576</v>
+        <v>4591</v>
       </c>
       <c r="D723" s="5" t="s">
-        <v>4577</v>
+        <v>4592</v>
       </c>
       <c r="E723" s="5" t="s">
-        <v>4578</v>
+        <v>4593</v>
       </c>
       <c r="F723" s="5" t="s">
-        <v>4579</v>
+        <v>4593</v>
       </c>
       <c r="G723" s="5" t="s">
-        <v>4579</v>
+        <v>4593</v>
       </c>
       <c r="H723" s="5" t="s">
-        <v>4577</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="724">
       <c r="B724" s="6" t="s">
-        <v>4580</v>
+        <v>4595</v>
       </c>
       <c r="C724" s="6" t="s">
-        <v>4581</v>
+        <v>3657</v>
       </c>
       <c r="D724" s="6" t="s">
-        <v>4582</v>
+        <v>4596</v>
       </c>
       <c r="E724" s="6" t="s">
-        <v>4583</v>
+        <v>3659</v>
       </c>
       <c r="F724" s="6" t="s">
-        <v>4584</v>
+        <v>3660</v>
       </c>
       <c r="G724" s="6" t="s">
-        <v>4584</v>
+        <v>3661</v>
       </c>
       <c r="H724" s="6" t="s">
-        <v>4585</v>
+        <v>4597</v>
       </c>
     </row>
     <row r="725">
       <c r="B725" s="5" t="s">
-        <v>4586</v>
+        <v>4598</v>
       </c>
       <c r="C725" s="5" t="s">
-        <v>3741</v>
+        <v>3651</v>
       </c>
       <c r="D725" s="5" t="s">
-        <v>4577</v>
+        <v>4599</v>
       </c>
       <c r="E725" s="5" t="s">
-        <v>3743</v>
+        <v>3653</v>
       </c>
       <c r="F725" s="5" t="s">
-        <v>3744</v>
+        <v>3654</v>
       </c>
       <c r="G725" s="5" t="s">
-        <v>3744</v>
+        <v>3654</v>
       </c>
       <c r="H725" s="5" t="s">
-        <v>3745</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="726">
       <c r="B726" s="6" t="s">
-        <v>4587</v>
+        <v>4601</v>
       </c>
       <c r="C726" s="6" t="s">
-        <v>3623</v>
+        <v>4602</v>
       </c>
       <c r="D726" s="6" t="s">
-        <v>4588</v>
+        <v>4603</v>
       </c>
       <c r="E726" s="6" t="s">
-        <v>3625</v>
+        <v>4604</v>
       </c>
       <c r="F726" s="6" t="s">
-        <v>3626</v>
+        <v>4605</v>
       </c>
       <c r="G726" s="6" t="s">
-        <v>3627</v>
+        <v>4606</v>
       </c>
       <c r="H726" s="6" t="s">
-        <v>4589</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="727">
       <c r="B727" s="5" t="s">
-        <v>4590</v>
+        <v>4607</v>
       </c>
       <c r="C727" s="5" t="s">
-        <v>4591</v>
+        <v>4608</v>
       </c>
       <c r="D727" s="5" t="s">
-        <v>4592</v>
+        <v>4609</v>
       </c>
       <c r="E727" s="5" t="s">
-        <v>4593</v>
+        <v>4610</v>
       </c>
       <c r="F727" s="5" t="s">
-        <v>4594</v>
+        <v>4611</v>
       </c>
       <c r="G727" s="5" t="s">
-        <v>4594</v>
+        <v>4611</v>
       </c>
       <c r="H727" s="5" t="s">
-        <v>4595</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="728">
       <c r="B728" s="6" t="s">
-        <v>4596</v>
+        <v>4612</v>
       </c>
       <c r="C728" s="6" t="s">
-        <v>4597</v>
+        <v>4613</v>
       </c>
       <c r="D728" s="6" t="s">
-        <v>4598</v>
+        <v>4614</v>
       </c>
       <c r="E728" s="6" t="s">
-        <v>4599</v>
+        <v>4615</v>
       </c>
       <c r="F728" s="6" t="s">
-        <v>4599</v>
+        <v>4616</v>
       </c>
       <c r="G728" s="6" t="s">
-        <v>4599</v>
+        <v>4617</v>
       </c>
       <c r="H728" s="6" t="s">
-        <v>4600</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="729">
       <c r="B729" s="5" t="s">
-        <v>4601</v>
+        <v>4619</v>
       </c>
       <c r="C729" s="5" t="s">
-        <v>4602</v>
+        <v>3749</v>
       </c>
       <c r="D729" s="5" t="s">
-        <v>4603</v>
+        <v>4620</v>
       </c>
       <c r="E729" s="5" t="s">
-        <v>4604</v>
+        <v>3751</v>
       </c>
       <c r="F729" s="5" t="s">
-        <v>4605</v>
+        <v>3752</v>
       </c>
       <c r="G729" s="5" t="s">
-        <v>4605</v>
+        <v>3752</v>
       </c>
       <c r="H729" s="5" t="s">
-        <v>4606</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="730">
       <c r="B730" s="6" t="s">
-        <v>4607</v>
+        <v>4621</v>
       </c>
       <c r="C730" s="6" t="s">
-        <v>3808</v>
+        <v>4622</v>
       </c>
       <c r="D730" s="6" t="s">
-        <v>4608</v>
+        <v>4359</v>
       </c>
       <c r="E730" s="6" t="s">
-        <v>3810</v>
+        <v>4623</v>
       </c>
       <c r="F730" s="6" t="s">
-        <v>2116</v>
+        <v>4624</v>
       </c>
       <c r="G730" s="6" t="s">
-        <v>2116</v>
+        <v>4625</v>
       </c>
       <c r="H730" s="6" t="s">
-        <v>4609</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="731">
       <c r="B731" s="5" t="s">
-        <v>4610</v>
+        <v>4626</v>
       </c>
       <c r="C731" s="5" t="s">
-        <v>3813</v>
+        <v>4627</v>
       </c>
       <c r="D731" s="5" t="s">
-        <v>4611</v>
+        <v>4628</v>
       </c>
       <c r="E731" s="5" t="s">
-        <v>3815</v>
+        <v>4629</v>
       </c>
       <c r="F731" s="5" t="s">
-        <v>3816</v>
+        <v>4630</v>
       </c>
       <c r="G731" s="5" t="s">
-        <v>3817</v>
+        <v>4630</v>
       </c>
       <c r="H731" s="5" t="s">
-        <v>4612</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="732">
       <c r="B732" s="6" t="s">
-        <v>4613</v>
+        <v>4631</v>
       </c>
       <c r="C732" s="6" t="s">
-        <v>3820</v>
+        <v>4632</v>
       </c>
       <c r="D732" s="6" t="s">
-        <v>4614</v>
+        <v>4633</v>
       </c>
       <c r="E732" s="6" t="s">
-        <v>3822</v>
+        <v>4634</v>
       </c>
       <c r="F732" s="6" t="s">
-        <v>3823</v>
+        <v>4635</v>
       </c>
       <c r="G732" s="6" t="s">
-        <v>3823</v>
+        <v>4635</v>
       </c>
       <c r="H732" s="6" t="s">
-        <v>4615</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="733">
       <c r="B733" s="5" t="s">
-        <v>4616</v>
+        <v>4637</v>
       </c>
       <c r="C733" s="5" t="s">
-        <v>2210</v>
+        <v>3741</v>
       </c>
       <c r="D733" s="5" t="s">
-        <v>2211</v>
+        <v>4628</v>
       </c>
       <c r="E733" s="5" t="s">
-        <v>2212</v>
+        <v>3743</v>
       </c>
       <c r="F733" s="5" t="s">
-        <v>2213</v>
+        <v>3744</v>
       </c>
       <c r="G733" s="5" t="s">
-        <v>2214</v>
+        <v>3744</v>
       </c>
       <c r="H733" s="5" t="s">
-        <v>2215</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="734">
       <c r="B734" s="6" t="s">
-        <v>4617</v>
+        <v>4638</v>
       </c>
       <c r="C734" s="6" t="s">
-        <v>2076</v>
+        <v>3623</v>
       </c>
       <c r="D734" s="6" t="s">
-        <v>2077</v>
+        <v>4639</v>
       </c>
       <c r="E734" s="6" t="s">
-        <v>2078</v>
+        <v>3625</v>
       </c>
       <c r="F734" s="6" t="s">
-        <v>2079</v>
+        <v>3626</v>
       </c>
       <c r="G734" s="6" t="s">
-        <v>2080</v>
+        <v>3627</v>
       </c>
       <c r="H734" s="6" t="s">
-        <v>2077</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="735">
       <c r="B735" s="5" t="s">
-        <v>4618</v>
+        <v>4641</v>
       </c>
       <c r="C735" s="5" t="s">
-        <v>2062</v>
+        <v>4642</v>
       </c>
       <c r="D735" s="5" t="s">
-        <v>2063</v>
+        <v>4643</v>
       </c>
       <c r="E735" s="5" t="s">
-        <v>2064</v>
+        <v>4644</v>
       </c>
       <c r="F735" s="5" t="s">
-        <v>2065</v>
+        <v>4645</v>
       </c>
       <c r="G735" s="5" t="s">
-        <v>2066</v>
+        <v>4645</v>
       </c>
       <c r="H735" s="5" t="s">
-        <v>2067</v>
+        <v>4646</v>
       </c>
     </row>
     <row r="736">
       <c r="B736" s="6" t="s">
-        <v>4619</v>
+        <v>4647</v>
       </c>
       <c r="C736" s="6" t="s">
-        <v>2056</v>
+        <v>4648</v>
       </c>
       <c r="D736" s="6" t="s">
-        <v>2057</v>
+        <v>4649</v>
       </c>
       <c r="E736" s="6" t="s">
-        <v>2058</v>
+        <v>4650</v>
       </c>
       <c r="F736" s="6" t="s">
-        <v>2059</v>
+        <v>4650</v>
       </c>
       <c r="G736" s="6" t="s">
-        <v>2059</v>
+        <v>4650</v>
       </c>
       <c r="H736" s="6" t="s">
-        <v>2060</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="737">
       <c r="B737" s="5" t="s">
-        <v>4620</v>
+        <v>4652</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>2069</v>
+        <v>4653</v>
       </c>
       <c r="D737" s="5" t="s">
-        <v>2070</v>
+        <v>4654</v>
       </c>
       <c r="E737" s="5" t="s">
-        <v>2071</v>
+        <v>4655</v>
       </c>
       <c r="F737" s="5" t="s">
-        <v>2072</v>
+        <v>4656</v>
       </c>
       <c r="G737" s="5" t="s">
-        <v>2073</v>
+        <v>4656</v>
       </c>
       <c r="H737" s="5" t="s">
-        <v>2074</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="738">
       <c r="B738" s="6" t="s">
-        <v>4621</v>
+        <v>4658</v>
       </c>
       <c r="C738" s="6" t="s">
-        <v>2050</v>
+        <v>3808</v>
       </c>
       <c r="D738" s="6" t="s">
-        <v>2051</v>
+        <v>4659</v>
       </c>
       <c r="E738" s="6" t="s">
-        <v>2052</v>
+        <v>3810</v>
       </c>
       <c r="F738" s="6" t="s">
-        <v>2053</v>
+        <v>2116</v>
       </c>
       <c r="G738" s="6" t="s">
-        <v>2054</v>
+        <v>2116</v>
       </c>
       <c r="H738" s="6" t="s">
-        <v>2051</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="739">
       <c r="B739" s="5" t="s">
-        <v>4622</v>
+        <v>4661</v>
       </c>
       <c r="C739" s="5" t="s">
-        <v>2082</v>
+        <v>3813</v>
       </c>
       <c r="D739" s="5" t="s">
-        <v>2083</v>
+        <v>4662</v>
       </c>
       <c r="E739" s="5" t="s">
-        <v>2084</v>
+        <v>3815</v>
       </c>
       <c r="F739" s="5" t="s">
-        <v>2085</v>
+        <v>3816</v>
       </c>
       <c r="G739" s="5" t="s">
-        <v>2086</v>
+        <v>3817</v>
       </c>
       <c r="H739" s="5" t="s">
-        <v>2087</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="740">
       <c r="B740" s="6" t="s">
-        <v>4623</v>
+        <v>4664</v>
       </c>
       <c r="C740" s="6" t="s">
-        <v>4624</v>
+        <v>3820</v>
       </c>
       <c r="D740" s="6" t="s">
-        <v>2046</v>
+        <v>4665</v>
       </c>
       <c r="E740" s="6" t="s">
-        <v>2047</v>
+        <v>3822</v>
       </c>
       <c r="F740" s="6" t="s">
-        <v>2048</v>
+        <v>3823</v>
       </c>
       <c r="G740" s="6" t="s">
-        <v>2048</v>
+        <v>3823</v>
       </c>
       <c r="H740" s="6" t="s">
-        <v>2046</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="741">
       <c r="B741" s="5" t="s">
-        <v>4625</v>
+        <v>4667</v>
       </c>
       <c r="C741" s="5" t="s">
-        <v>4626</v>
+        <v>2210</v>
       </c>
       <c r="D741" s="5" t="s">
-        <v>4627</v>
+        <v>2211</v>
       </c>
       <c r="E741" s="5" t="s">
-        <v>4628</v>
+        <v>2212</v>
       </c>
       <c r="F741" s="5" t="s">
-        <v>4629</v>
+        <v>2213</v>
       </c>
       <c r="G741" s="5" t="s">
-        <v>4630</v>
+        <v>2214</v>
       </c>
       <c r="H741" s="5" t="s">
-        <v>4627</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="742">
       <c r="B742" s="6" t="s">
-        <v>4631</v>
+        <v>4668</v>
       </c>
       <c r="C742" s="6" t="s">
-        <v>4632</v>
+        <v>2076</v>
       </c>
       <c r="D742" s="6" t="s">
-        <v>4633</v>
+        <v>2077</v>
       </c>
       <c r="E742" s="6" t="s">
-        <v>4634</v>
+        <v>2078</v>
       </c>
       <c r="F742" s="6" t="s">
-        <v>4635</v>
+        <v>2079</v>
       </c>
       <c r="G742" s="6" t="s">
-        <v>4636</v>
+        <v>2080</v>
       </c>
       <c r="H742" s="6" t="s">
-        <v>4637</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="743">
       <c r="B743" s="5" t="s">
-        <v>4638</v>
+        <v>4669</v>
       </c>
       <c r="C743" s="5" t="s">
-        <v>4639</v>
+        <v>2062</v>
       </c>
       <c r="D743" s="5" t="s">
-        <v>4640</v>
+        <v>2063</v>
       </c>
       <c r="E743" s="5" t="s">
-        <v>4641</v>
+        <v>2064</v>
       </c>
       <c r="F743" s="5" t="s">
-        <v>4642</v>
+        <v>2065</v>
       </c>
       <c r="G743" s="5" t="s">
-        <v>4643</v>
+        <v>2066</v>
       </c>
       <c r="H743" s="5" t="s">
-        <v>4644</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="744">
       <c r="B744" s="6" t="s">
-        <v>4645</v>
+        <v>4670</v>
       </c>
       <c r="C744" s="6" t="s">
-        <v>4646</v>
+        <v>2056</v>
       </c>
       <c r="D744" s="6" t="s">
-        <v>4647</v>
+        <v>2057</v>
       </c>
       <c r="E744" s="6" t="s">
-        <v>4648</v>
+        <v>2058</v>
       </c>
       <c r="F744" s="6" t="s">
-        <v>4649</v>
+        <v>2059</v>
       </c>
       <c r="G744" s="6" t="s">
-        <v>4650</v>
+        <v>2059</v>
       </c>
       <c r="H744" s="6" t="s">
-        <v>4651</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="745">
       <c r="B745" s="5" t="s">
-        <v>4652</v>
+        <v>4671</v>
       </c>
       <c r="C745" s="5" t="s">
-        <v>4653</v>
+        <v>2069</v>
       </c>
       <c r="D745" s="5" t="s">
-        <v>4654</v>
+        <v>2070</v>
       </c>
       <c r="E745" s="5" t="s">
-        <v>4655</v>
+        <v>2071</v>
       </c>
       <c r="F745" s="5" t="s">
-        <v>4656</v>
+        <v>2072</v>
       </c>
       <c r="G745" s="5" t="s">
-        <v>4656</v>
+        <v>2073</v>
       </c>
       <c r="H745" s="5" t="s">
-        <v>4657</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="746">
       <c r="B746" s="6" t="s">
-        <v>4658</v>
+        <v>4672</v>
       </c>
       <c r="C746" s="6" t="s">
-        <v>4659</v>
+        <v>2050</v>
       </c>
       <c r="D746" s="6" t="s">
-        <v>4660</v>
+        <v>2051</v>
       </c>
       <c r="E746" s="6" t="s">
-        <v>4661</v>
+        <v>2052</v>
       </c>
       <c r="F746" s="6" t="s">
-        <v>4662</v>
+        <v>2053</v>
       </c>
       <c r="G746" s="6" t="s">
-        <v>4663</v>
+        <v>2054</v>
       </c>
       <c r="H746" s="6" t="s">
-        <v>4664</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="747">
       <c r="B747" s="5" t="s">
-        <v>4665</v>
+        <v>4673</v>
       </c>
       <c r="C747" s="5" t="s">
-        <v>4666</v>
+        <v>2082</v>
       </c>
       <c r="D747" s="5" t="s">
-        <v>4667</v>
+        <v>2083</v>
       </c>
       <c r="E747" s="5" t="s">
-        <v>4668</v>
+        <v>2084</v>
       </c>
       <c r="F747" s="5" t="s">
-        <v>4669</v>
+        <v>2085</v>
       </c>
       <c r="G747" s="5" t="s">
-        <v>4670</v>
+        <v>2086</v>
       </c>
       <c r="H747" s="5" t="s">
-        <v>4671</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="748">
       <c r="B748" s="6" t="s">
-        <v>4672</v>
+        <v>4674</v>
       </c>
       <c r="C748" s="6" t="s">
-        <v>4673</v>
+        <v>4675</v>
       </c>
       <c r="D748" s="6" t="s">
-        <v>4674</v>
+        <v>2046</v>
       </c>
       <c r="E748" s="6" t="s">
-        <v>4675</v>
+        <v>2047</v>
       </c>
       <c r="F748" s="6" t="s">
-        <v>4675</v>
+        <v>2048</v>
       </c>
       <c r="G748" s="6" t="s">
-        <v>4675</v>
+        <v>2048</v>
       </c>
       <c r="H748" s="6" t="s">
-        <v>4676</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="749">
       <c r="B749" s="5" t="s">
+        <v>4676</v>
+      </c>
+      <c r="C749" s="5" t="s">
         <v>4677</v>
       </c>
-      <c r="C749" s="5" t="s">
+      <c r="D749" s="5" t="s">
         <v>4678</v>
       </c>
-      <c r="D749" s="5" t="s">
+      <c r="E749" s="5" t="s">
         <v>4679</v>
       </c>
-      <c r="E749" s="5" t="s">
+      <c r="F749" s="5" t="s">
         <v>4680</v>
       </c>
-      <c r="F749" s="5" t="s">
+      <c r="G749" s="5" t="s">
         <v>4681</v>
       </c>
-      <c r="G749" s="5" t="s">
-        <v>4682</v>
-      </c>
       <c r="H749" s="5" t="s">
-        <v>4683</v>
+        <v>4678</v>
       </c>
     </row>
     <row r="750">
       <c r="B750" s="6" t="s">
+        <v>4682</v>
+      </c>
+      <c r="C750" s="6" t="s">
+        <v>4683</v>
+      </c>
+      <c r="D750" s="6" t="s">
         <v>4684</v>
       </c>
-      <c r="C750" s="6" t="s">
+      <c r="E750" s="6" t="s">
         <v>4685</v>
       </c>
-      <c r="D750" s="6" t="s">
+      <c r="F750" s="6" t="s">
         <v>4686</v>
       </c>
-      <c r="E750" s="6" t="s">
+      <c r="G750" s="6" t="s">
         <v>4687</v>
       </c>
-      <c r="F750" s="6" t="s">
+      <c r="H750" s="6" t="s">
         <v>4688</v>
-      </c>
-      <c r="G750" s="6" t="s">
-        <v>4689</v>
-      </c>
-      <c r="H750" s="6" t="s">
-        <v>4690</v>
       </c>
     </row>
     <row r="751">
       <c r="B751" s="5" t="s">
+        <v>4689</v>
+      </c>
+      <c r="C751" s="5" t="s">
+        <v>4690</v>
+      </c>
+      <c r="D751" s="5" t="s">
         <v>4691</v>
       </c>
-      <c r="C751" s="5" t="s">
+      <c r="E751" s="5" t="s">
         <v>4692</v>
       </c>
-      <c r="D751" s="5" t="s">
+      <c r="F751" s="5" t="s">
         <v>4693</v>
       </c>
-      <c r="E751" s="5" t="s">
+      <c r="G751" s="5" t="s">
         <v>4694</v>
       </c>
-      <c r="F751" s="5" t="s">
+      <c r="H751" s="5" t="s">
         <v>4695</v>
-      </c>
-      <c r="G751" s="5" t="s">
-        <v>4696</v>
-      </c>
-      <c r="H751" s="5" t="s">
-        <v>4697</v>
       </c>
     </row>
     <row r="752">
       <c r="B752" s="6" t="s">
+        <v>4696</v>
+      </c>
+      <c r="C752" s="6" t="s">
+        <v>4697</v>
+      </c>
+      <c r="D752" s="6" t="s">
         <v>4698</v>
       </c>
-      <c r="C752" s="6" t="s">
+      <c r="E752" s="6" t="s">
         <v>4699</v>
       </c>
-      <c r="D752" s="6" t="s">
+      <c r="F752" s="6" t="s">
         <v>4700</v>
       </c>
-      <c r="E752" s="6" t="s">
+      <c r="G752" s="6" t="s">
         <v>4701</v>
       </c>
-      <c r="F752" s="6" t="s">
+      <c r="H752" s="6" t="s">
         <v>4702</v>
-      </c>
-      <c r="G752" s="6" t="s">
-        <v>4702</v>
-      </c>
-      <c r="H752" s="6" t="s">
-        <v>4703</v>
       </c>
     </row>
     <row r="753">
       <c r="B753" s="5" t="s">
+        <v>4703</v>
+      </c>
+      <c r="C753" s="5" t="s">
         <v>4704</v>
       </c>
-      <c r="C753" s="5" t="s">
+      <c r="D753" s="5" t="s">
         <v>4705</v>
       </c>
-      <c r="D753" s="5" t="s">
+      <c r="E753" s="5" t="s">
         <v>4706</v>
       </c>
-      <c r="E753" s="5" t="s">
+      <c r="F753" s="5" t="s">
         <v>4707</v>
       </c>
-      <c r="F753" s="5" t="s">
+      <c r="G753" s="5" t="s">
+        <v>4707</v>
+      </c>
+      <c r="H753" s="5" t="s">
         <v>4708</v>
-      </c>
-      <c r="G753" s="5" t="s">
-        <v>4708</v>
-      </c>
-      <c r="H753" s="5" t="s">
-        <v>4709</v>
       </c>
     </row>
     <row r="754">
       <c r="B754" s="6" t="s">
+        <v>4709</v>
+      </c>
+      <c r="C754" s="6" t="s">
         <v>4710</v>
       </c>
-      <c r="C754" s="6" t="s">
+      <c r="D754" s="6" t="s">
         <v>4711</v>
       </c>
-      <c r="D754" s="6" t="s">
+      <c r="E754" s="6" t="s">
         <v>4712</v>
       </c>
-      <c r="E754" s="6" t="s">
+      <c r="F754" s="6" t="s">
         <v>4713</v>
       </c>
-      <c r="F754" s="6" t="s">
+      <c r="G754" s="6" t="s">
         <v>4714</v>
       </c>
-      <c r="G754" s="6" t="s">
+      <c r="H754" s="6" t="s">
         <v>4715</v>
-      </c>
-      <c r="H754" s="6" t="s">
-        <v>4716</v>
       </c>
     </row>
     <row r="755">
       <c r="B755" s="5" t="s">
+        <v>4716</v>
+      </c>
+      <c r="C755" s="5" t="s">
         <v>4717</v>
       </c>
-      <c r="C755" s="5" t="s">
+      <c r="D755" s="5" t="s">
         <v>4718</v>
       </c>
-      <c r="D755" s="5" t="s">
+      <c r="E755" s="5" t="s">
         <v>4719</v>
       </c>
-      <c r="E755" s="5" t="s">
+      <c r="F755" s="5" t="s">
         <v>4720</v>
-      </c>
-      <c r="F755" s="5" t="s">
-        <v>4721</v>
       </c>
       <c r="G755" s="5" t="s">
         <v>4721</v>
@@ -34184,1131 +34334,1131 @@
         <v>4726</v>
       </c>
       <c r="F756" s="6" t="s">
+        <v>4726</v>
+      </c>
+      <c r="G756" s="6" t="s">
+        <v>4726</v>
+      </c>
+      <c r="H756" s="6" t="s">
         <v>4727</v>
-      </c>
-      <c r="G756" s="6" t="s">
-        <v>4728</v>
-      </c>
-      <c r="H756" s="6" t="s">
-        <v>4729</v>
       </c>
     </row>
     <row r="757">
       <c r="B757" s="5" t="s">
+        <v>4728</v>
+      </c>
+      <c r="C757" s="5" t="s">
+        <v>4729</v>
+      </c>
+      <c r="D757" s="5" t="s">
         <v>4730</v>
       </c>
-      <c r="C757" s="5" t="s">
+      <c r="E757" s="5" t="s">
         <v>4731</v>
       </c>
-      <c r="D757" s="5" t="s">
+      <c r="F757" s="5" t="s">
         <v>4732</v>
       </c>
-      <c r="E757" s="5" t="s">
+      <c r="G757" s="5" t="s">
         <v>4733</v>
       </c>
-      <c r="F757" s="5" t="s">
+      <c r="H757" s="5" t="s">
         <v>4734</v>
-      </c>
-      <c r="G757" s="5" t="s">
-        <v>4735</v>
-      </c>
-      <c r="H757" s="5" t="s">
-        <v>4736</v>
       </c>
     </row>
     <row r="758">
       <c r="B758" s="6" t="s">
+        <v>4735</v>
+      </c>
+      <c r="C758" s="6" t="s">
+        <v>4736</v>
+      </c>
+      <c r="D758" s="6" t="s">
         <v>4737</v>
       </c>
-      <c r="C758" s="6" t="s">
+      <c r="E758" s="6" t="s">
         <v>4738</v>
       </c>
-      <c r="D758" s="6" t="s">
+      <c r="F758" s="6" t="s">
         <v>4739</v>
       </c>
-      <c r="E758" s="6" t="s">
+      <c r="G758" s="6" t="s">
         <v>4740</v>
       </c>
-      <c r="F758" s="6" t="s">
+      <c r="H758" s="6" t="s">
         <v>4741</v>
-      </c>
-      <c r="G758" s="6" t="s">
-        <v>4742</v>
-      </c>
-      <c r="H758" s="6" t="s">
-        <v>4743</v>
       </c>
     </row>
     <row r="759">
       <c r="B759" s="5" t="s">
+        <v>4742</v>
+      </c>
+      <c r="C759" s="5" t="s">
+        <v>4743</v>
+      </c>
+      <c r="D759" s="5" t="s">
         <v>4744</v>
       </c>
-      <c r="C759" s="5" t="s">
+      <c r="E759" s="5" t="s">
         <v>4745</v>
       </c>
-      <c r="D759" s="5" t="s">
+      <c r="F759" s="5" t="s">
         <v>4746</v>
       </c>
-      <c r="E759" s="5" t="s">
+      <c r="G759" s="5" t="s">
         <v>4747</v>
       </c>
-      <c r="F759" s="5" t="s">
+      <c r="H759" s="5" t="s">
         <v>4748</v>
-      </c>
-      <c r="G759" s="5" t="s">
-        <v>4749</v>
-      </c>
-      <c r="H759" s="5" t="s">
-        <v>4750</v>
       </c>
     </row>
     <row r="760">
       <c r="B760" s="6" t="s">
+        <v>4749</v>
+      </c>
+      <c r="C760" s="6" t="s">
+        <v>4750</v>
+      </c>
+      <c r="D760" s="6" t="s">
         <v>4751</v>
       </c>
-      <c r="C760" s="6" t="s">
+      <c r="E760" s="6" t="s">
         <v>4752</v>
       </c>
-      <c r="D760" s="6" t="s">
+      <c r="F760" s="6" t="s">
         <v>4753</v>
       </c>
-      <c r="E760" s="6" t="s">
+      <c r="G760" s="6" t="s">
+        <v>4753</v>
+      </c>
+      <c r="H760" s="6" t="s">
         <v>4754</v>
-      </c>
-      <c r="F760" s="6" t="s">
-        <v>4755</v>
-      </c>
-      <c r="G760" s="6" t="s">
-        <v>4756</v>
-      </c>
-      <c r="H760" s="6" t="s">
-        <v>4757</v>
       </c>
     </row>
     <row r="761">
       <c r="B761" s="5" t="s">
+        <v>4755</v>
+      </c>
+      <c r="C761" s="5" t="s">
+        <v>4756</v>
+      </c>
+      <c r="D761" s="5" t="s">
+        <v>4757</v>
+      </c>
+      <c r="E761" s="5" t="s">
         <v>4758</v>
       </c>
-      <c r="C761" s="5" t="s">
+      <c r="F761" s="5" t="s">
         <v>4759</v>
       </c>
-      <c r="D761" s="5" t="s">
+      <c r="G761" s="5" t="s">
+        <v>4759</v>
+      </c>
+      <c r="H761" s="5" t="s">
         <v>4760</v>
-      </c>
-      <c r="E761" s="5" t="s">
-        <v>4761</v>
-      </c>
-      <c r="F761" s="5" t="s">
-        <v>4762</v>
-      </c>
-      <c r="G761" s="5" t="s">
-        <v>4763</v>
-      </c>
-      <c r="H761" s="5" t="s">
-        <v>4764</v>
       </c>
     </row>
     <row r="762">
       <c r="B762" s="6" t="s">
+        <v>4761</v>
+      </c>
+      <c r="C762" s="6" t="s">
+        <v>4762</v>
+      </c>
+      <c r="D762" s="6" t="s">
+        <v>4763</v>
+      </c>
+      <c r="E762" s="6" t="s">
+        <v>4764</v>
+      </c>
+      <c r="F762" s="6" t="s">
         <v>4765</v>
       </c>
-      <c r="C762" s="6" t="s">
+      <c r="G762" s="6" t="s">
         <v>4766</v>
       </c>
-      <c r="D762" s="6" t="s">
+      <c r="H762" s="6" t="s">
         <v>4767</v>
-      </c>
-      <c r="E762" s="6" t="s">
-        <v>4768</v>
-      </c>
-      <c r="F762" s="6" t="s">
-        <v>4769</v>
-      </c>
-      <c r="G762" s="6" t="s">
-        <v>4770</v>
-      </c>
-      <c r="H762" s="6" t="s">
-        <v>4771</v>
       </c>
     </row>
     <row r="763">
       <c r="B763" s="5" t="s">
+        <v>4768</v>
+      </c>
+      <c r="C763" s="5" t="s">
+        <v>4769</v>
+      </c>
+      <c r="D763" s="5" t="s">
+        <v>4770</v>
+      </c>
+      <c r="E763" s="5" t="s">
+        <v>4771</v>
+      </c>
+      <c r="F763" s="5" t="s">
         <v>4772</v>
       </c>
-      <c r="C763" s="5" t="s">
+      <c r="G763" s="5" t="s">
+        <v>4772</v>
+      </c>
+      <c r="H763" s="5" t="s">
         <v>4773</v>
-      </c>
-      <c r="D763" s="5" t="s">
-        <v>4774</v>
-      </c>
-      <c r="E763" s="5" t="s">
-        <v>4775</v>
-      </c>
-      <c r="F763" s="5" t="s">
-        <v>4776</v>
-      </c>
-      <c r="G763" s="5" t="s">
-        <v>4777</v>
-      </c>
-      <c r="H763" s="5" t="s">
-        <v>4778</v>
       </c>
     </row>
     <row r="764">
       <c r="B764" s="6" t="s">
+        <v>4774</v>
+      </c>
+      <c r="C764" s="6" t="s">
+        <v>4775</v>
+      </c>
+      <c r="D764" s="6" t="s">
+        <v>4776</v>
+      </c>
+      <c r="E764" s="6" t="s">
+        <v>4777</v>
+      </c>
+      <c r="F764" s="6" t="s">
+        <v>4778</v>
+      </c>
+      <c r="G764" s="6" t="s">
         <v>4779</v>
       </c>
-      <c r="C764" s="6" t="s">
+      <c r="H764" s="6" t="s">
         <v>4780</v>
-      </c>
-      <c r="D764" s="6" t="s">
-        <v>4781</v>
-      </c>
-      <c r="E764" s="6" t="s">
-        <v>4782</v>
-      </c>
-      <c r="F764" s="6" t="s">
-        <v>4783</v>
-      </c>
-      <c r="G764" s="6" t="s">
-        <v>4784</v>
-      </c>
-      <c r="H764" s="6" t="s">
-        <v>4785</v>
       </c>
     </row>
     <row r="765">
       <c r="B765" s="5" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C765" s="5" t="s">
+        <v>4782</v>
+      </c>
+      <c r="D765" s="5" t="s">
+        <v>4783</v>
+      </c>
+      <c r="E765" s="5" t="s">
+        <v>4784</v>
+      </c>
+      <c r="F765" s="5" t="s">
+        <v>4785</v>
+      </c>
+      <c r="G765" s="5" t="s">
         <v>4786</v>
       </c>
-      <c r="C765" s="5" t="s">
+      <c r="H765" s="5" t="s">
         <v>4787</v>
-      </c>
-      <c r="D765" s="5" t="s">
-        <v>4788</v>
-      </c>
-      <c r="E765" s="5" t="s">
-        <v>4789</v>
-      </c>
-      <c r="F765" s="5" t="s">
-        <v>4790</v>
-      </c>
-      <c r="G765" s="5" t="s">
-        <v>4791</v>
-      </c>
-      <c r="H765" s="5" t="s">
-        <v>4792</v>
       </c>
     </row>
     <row r="766">
       <c r="B766" s="6" t="s">
+        <v>4788</v>
+      </c>
+      <c r="C766" s="6" t="s">
+        <v>4789</v>
+      </c>
+      <c r="D766" s="6" t="s">
+        <v>4790</v>
+      </c>
+      <c r="E766" s="6" t="s">
+        <v>4791</v>
+      </c>
+      <c r="F766" s="6" t="s">
+        <v>4792</v>
+      </c>
+      <c r="G766" s="6" t="s">
         <v>4793</v>
       </c>
-      <c r="C766" s="6" t="s">
+      <c r="H766" s="6" t="s">
         <v>4794</v>
-      </c>
-      <c r="D766" s="6" t="s">
-        <v>4795</v>
-      </c>
-      <c r="E766" s="6" t="s">
-        <v>4796</v>
-      </c>
-      <c r="F766" s="6" t="s">
-        <v>4797</v>
-      </c>
-      <c r="G766" s="6" t="s">
-        <v>4797</v>
-      </c>
-      <c r="H766" s="6" t="s">
-        <v>4798</v>
       </c>
     </row>
     <row r="767">
       <c r="B767" s="5" t="s">
+        <v>4795</v>
+      </c>
+      <c r="C767" s="5" t="s">
+        <v>4796</v>
+      </c>
+      <c r="D767" s="5" t="s">
+        <v>4797</v>
+      </c>
+      <c r="E767" s="5" t="s">
+        <v>4798</v>
+      </c>
+      <c r="F767" s="5" t="s">
         <v>4799</v>
       </c>
-      <c r="C767" s="5" t="s">
+      <c r="G767" s="5" t="s">
         <v>4800</v>
       </c>
-      <c r="D767" s="5" t="s">
+      <c r="H767" s="5" t="s">
         <v>4801</v>
-      </c>
-      <c r="E767" s="5" t="s">
-        <v>4802</v>
-      </c>
-      <c r="F767" s="5" t="s">
-        <v>4803</v>
-      </c>
-      <c r="G767" s="5" t="s">
-        <v>4804</v>
-      </c>
-      <c r="H767" s="5" t="s">
-        <v>4805</v>
       </c>
     </row>
     <row r="768">
       <c r="B768" s="6" t="s">
+        <v>4802</v>
+      </c>
+      <c r="C768" s="6" t="s">
+        <v>4803</v>
+      </c>
+      <c r="D768" s="6" t="s">
+        <v>4804</v>
+      </c>
+      <c r="E768" s="6" t="s">
+        <v>4805</v>
+      </c>
+      <c r="F768" s="6" t="s">
         <v>4806</v>
       </c>
-      <c r="C768" s="6" t="s">
+      <c r="G768" s="6" t="s">
         <v>4807</v>
       </c>
-      <c r="D768" s="6" t="s">
+      <c r="H768" s="6" t="s">
         <v>4808</v>
-      </c>
-      <c r="E768" s="6" t="s">
-        <v>4809</v>
-      </c>
-      <c r="F768" s="6" t="s">
-        <v>4810</v>
-      </c>
-      <c r="G768" s="6" t="s">
-        <v>4811</v>
-      </c>
-      <c r="H768" s="6" t="s">
-        <v>4812</v>
       </c>
     </row>
     <row r="769">
       <c r="B769" s="5" t="s">
+        <v>4809</v>
+      </c>
+      <c r="C769" s="5" t="s">
+        <v>4810</v>
+      </c>
+      <c r="D769" s="5" t="s">
+        <v>4811</v>
+      </c>
+      <c r="E769" s="5" t="s">
+        <v>4812</v>
+      </c>
+      <c r="F769" s="5" t="s">
         <v>4813</v>
       </c>
-      <c r="C769" s="5" t="s">
+      <c r="G769" s="5" t="s">
         <v>4814</v>
       </c>
-      <c r="D769" s="5" t="s">
+      <c r="H769" s="5" t="s">
         <v>4815</v>
-      </c>
-      <c r="E769" s="5" t="s">
-        <v>4816</v>
-      </c>
-      <c r="F769" s="5" t="s">
-        <v>4817</v>
-      </c>
-      <c r="G769" s="5" t="s">
-        <v>4818</v>
-      </c>
-      <c r="H769" s="5" t="s">
-        <v>4819</v>
       </c>
     </row>
     <row r="770">
       <c r="B770" s="6" t="s">
+        <v>4816</v>
+      </c>
+      <c r="C770" s="6" t="s">
+        <v>4817</v>
+      </c>
+      <c r="D770" s="6" t="s">
+        <v>4818</v>
+      </c>
+      <c r="E770" s="6" t="s">
+        <v>4819</v>
+      </c>
+      <c r="F770" s="6" t="s">
         <v>4820</v>
       </c>
-      <c r="C770" s="6" t="s">
+      <c r="G770" s="6" t="s">
         <v>4821</v>
       </c>
-      <c r="D770" s="6" t="s">
+      <c r="H770" s="6" t="s">
         <v>4822</v>
-      </c>
-      <c r="E770" s="6" t="s">
-        <v>4823</v>
-      </c>
-      <c r="F770" s="6" t="s">
-        <v>4824</v>
-      </c>
-      <c r="G770" s="6" t="s">
-        <v>4825</v>
-      </c>
-      <c r="H770" s="6" t="s">
-        <v>4826</v>
       </c>
     </row>
     <row r="771">
       <c r="B771" s="5" t="s">
+        <v>4823</v>
+      </c>
+      <c r="C771" s="5" t="s">
+        <v>4824</v>
+      </c>
+      <c r="D771" s="5" t="s">
+        <v>4825</v>
+      </c>
+      <c r="E771" s="5" t="s">
+        <v>4826</v>
+      </c>
+      <c r="F771" s="5" t="s">
         <v>4827</v>
       </c>
-      <c r="C771" s="5" t="s">
+      <c r="G771" s="5" t="s">
         <v>4828</v>
       </c>
-      <c r="D771" s="5" t="s">
+      <c r="H771" s="5" t="s">
         <v>4829</v>
-      </c>
-      <c r="E771" s="5" t="s">
-        <v>4830</v>
-      </c>
-      <c r="F771" s="5" t="s">
-        <v>4831</v>
-      </c>
-      <c r="G771" s="5" t="s">
-        <v>4832</v>
-      </c>
-      <c r="H771" s="5" t="s">
-        <v>4833</v>
       </c>
     </row>
     <row r="772">
       <c r="B772" s="6" t="s">
+        <v>4830</v>
+      </c>
+      <c r="C772" s="6" t="s">
+        <v>4831</v>
+      </c>
+      <c r="D772" s="6" t="s">
+        <v>4832</v>
+      </c>
+      <c r="E772" s="6" t="s">
+        <v>4833</v>
+      </c>
+      <c r="F772" s="6" t="s">
         <v>4834</v>
       </c>
-      <c r="C772" s="6" t="s">
+      <c r="G772" s="6" t="s">
         <v>4835</v>
       </c>
-      <c r="D772" s="6" t="s">
+      <c r="H772" s="6" t="s">
         <v>4836</v>
-      </c>
-      <c r="E772" s="6" t="s">
-        <v>4837</v>
-      </c>
-      <c r="F772" s="6" t="s">
-        <v>4838</v>
-      </c>
-      <c r="G772" s="6" t="s">
-        <v>4839</v>
-      </c>
-      <c r="H772" s="6" t="s">
-        <v>4840</v>
       </c>
     </row>
     <row r="773">
       <c r="B773" s="5" t="s">
+        <v>4837</v>
+      </c>
+      <c r="C773" s="5" t="s">
+        <v>4838</v>
+      </c>
+      <c r="D773" s="5" t="s">
+        <v>4839</v>
+      </c>
+      <c r="E773" s="5" t="s">
+        <v>4840</v>
+      </c>
+      <c r="F773" s="5" t="s">
         <v>4841</v>
       </c>
-      <c r="C773" s="5" t="s">
+      <c r="G773" s="5" t="s">
         <v>4842</v>
       </c>
-      <c r="D773" s="5" t="s">
+      <c r="H773" s="5" t="s">
         <v>4843</v>
-      </c>
-      <c r="E773" s="5" t="s">
-        <v>4844</v>
-      </c>
-      <c r="F773" s="5" t="s">
-        <v>4845</v>
-      </c>
-      <c r="G773" s="5" t="s">
-        <v>4846</v>
-      </c>
-      <c r="H773" s="5" t="s">
-        <v>4847</v>
       </c>
     </row>
     <row r="774">
       <c r="B774" s="6" t="s">
+        <v>4844</v>
+      </c>
+      <c r="C774" s="6" t="s">
+        <v>4845</v>
+      </c>
+      <c r="D774" s="6" t="s">
+        <v>4846</v>
+      </c>
+      <c r="E774" s="6" t="s">
+        <v>4847</v>
+      </c>
+      <c r="F774" s="6" t="s">
         <v>4848</v>
       </c>
-      <c r="C774" s="6" t="s">
+      <c r="G774" s="6" t="s">
+        <v>4848</v>
+      </c>
+      <c r="H774" s="6" t="s">
         <v>4849</v>
-      </c>
-      <c r="D774" s="6" t="s">
-        <v>4850</v>
-      </c>
-      <c r="E774" s="6" t="s">
-        <v>4851</v>
-      </c>
-      <c r="F774" s="6" t="s">
-        <v>4852</v>
-      </c>
-      <c r="G774" s="6" t="s">
-        <v>4853</v>
-      </c>
-      <c r="H774" s="6" t="s">
-        <v>4854</v>
       </c>
     </row>
     <row r="775">
       <c r="B775" s="5" t="s">
+        <v>4850</v>
+      </c>
+      <c r="C775" s="5" t="s">
+        <v>4851</v>
+      </c>
+      <c r="D775" s="5" t="s">
+        <v>4852</v>
+      </c>
+      <c r="E775" s="5" t="s">
+        <v>4853</v>
+      </c>
+      <c r="F775" s="5" t="s">
+        <v>4854</v>
+      </c>
+      <c r="G775" s="5" t="s">
         <v>4855</v>
       </c>
-      <c r="C775" s="5" t="s">
+      <c r="H775" s="5" t="s">
         <v>4856</v>
-      </c>
-      <c r="D775" s="5" t="s">
-        <v>4857</v>
-      </c>
-      <c r="E775" s="5" t="s">
-        <v>4858</v>
-      </c>
-      <c r="F775" s="5" t="s">
-        <v>4859</v>
-      </c>
-      <c r="G775" s="5" t="s">
-        <v>4860</v>
-      </c>
-      <c r="H775" s="5" t="s">
-        <v>4861</v>
       </c>
     </row>
     <row r="776">
       <c r="B776" s="6" t="s">
+        <v>4857</v>
+      </c>
+      <c r="C776" s="6" t="s">
+        <v>4858</v>
+      </c>
+      <c r="D776" s="6" t="s">
+        <v>4859</v>
+      </c>
+      <c r="E776" s="6" t="s">
+        <v>4860</v>
+      </c>
+      <c r="F776" s="6" t="s">
+        <v>4861</v>
+      </c>
+      <c r="G776" s="6" t="s">
         <v>4862</v>
       </c>
-      <c r="C776" s="6" t="s">
+      <c r="H776" s="6" t="s">
         <v>4863</v>
-      </c>
-      <c r="D776" s="6" t="s">
-        <v>4864</v>
-      </c>
-      <c r="E776" s="6" t="s">
-        <v>4865</v>
-      </c>
-      <c r="F776" s="6" t="s">
-        <v>4866</v>
-      </c>
-      <c r="G776" s="6" t="s">
-        <v>4867</v>
-      </c>
-      <c r="H776" s="6" t="s">
-        <v>4868</v>
       </c>
     </row>
     <row r="777">
       <c r="B777" s="5" t="s">
+        <v>4864</v>
+      </c>
+      <c r="C777" s="5" t="s">
+        <v>4865</v>
+      </c>
+      <c r="D777" s="5" t="s">
+        <v>4866</v>
+      </c>
+      <c r="E777" s="5" t="s">
+        <v>4867</v>
+      </c>
+      <c r="F777" s="5" t="s">
+        <v>4868</v>
+      </c>
+      <c r="G777" s="5" t="s">
         <v>4869</v>
       </c>
-      <c r="C777" s="5" t="s">
+      <c r="H777" s="5" t="s">
         <v>4870</v>
-      </c>
-      <c r="D777" s="5" t="s">
-        <v>4871</v>
-      </c>
-      <c r="E777" s="5" t="s">
-        <v>4872</v>
-      </c>
-      <c r="F777" s="5" t="s">
-        <v>4873</v>
-      </c>
-      <c r="G777" s="5" t="s">
-        <v>4874</v>
-      </c>
-      <c r="H777" s="5" t="s">
-        <v>4875</v>
       </c>
     </row>
     <row r="778">
       <c r="B778" s="6" t="s">
+        <v>4871</v>
+      </c>
+      <c r="C778" s="6" t="s">
+        <v>4872</v>
+      </c>
+      <c r="D778" s="6" t="s">
+        <v>4873</v>
+      </c>
+      <c r="E778" s="6" t="s">
+        <v>4874</v>
+      </c>
+      <c r="F778" s="6" t="s">
+        <v>4875</v>
+      </c>
+      <c r="G778" s="6" t="s">
         <v>4876</v>
       </c>
-      <c r="C778" s="6" t="s">
+      <c r="H778" s="6" t="s">
         <v>4877</v>
-      </c>
-      <c r="D778" s="6" t="s">
-        <v>4878</v>
-      </c>
-      <c r="E778" s="6" t="s">
-        <v>4879</v>
-      </c>
-      <c r="F778" s="6" t="s">
-        <v>4880</v>
-      </c>
-      <c r="G778" s="6" t="s">
-        <v>4881</v>
-      </c>
-      <c r="H778" s="6" t="s">
-        <v>4882</v>
       </c>
     </row>
     <row r="779">
       <c r="B779" s="5" t="s">
+        <v>4878</v>
+      </c>
+      <c r="C779" s="5" t="s">
+        <v>4879</v>
+      </c>
+      <c r="D779" s="5" t="s">
+        <v>4880</v>
+      </c>
+      <c r="E779" s="5" t="s">
+        <v>4881</v>
+      </c>
+      <c r="F779" s="5" t="s">
+        <v>4882</v>
+      </c>
+      <c r="G779" s="5" t="s">
         <v>4883</v>
       </c>
-      <c r="C779" s="5" t="s">
+      <c r="H779" s="5" t="s">
         <v>4884</v>
-      </c>
-      <c r="D779" s="5" t="s">
-        <v>4885</v>
-      </c>
-      <c r="E779" s="5" t="s">
-        <v>4886</v>
-      </c>
-      <c r="F779" s="5" t="s">
-        <v>4887</v>
-      </c>
-      <c r="G779" s="5" t="s">
-        <v>4888</v>
-      </c>
-      <c r="H779" s="5" t="s">
-        <v>4889</v>
       </c>
     </row>
     <row r="780">
       <c r="B780" s="6" t="s">
+        <v>4885</v>
+      </c>
+      <c r="C780" s="6" t="s">
+        <v>4886</v>
+      </c>
+      <c r="D780" s="6" t="s">
+        <v>4887</v>
+      </c>
+      <c r="E780" s="6" t="s">
+        <v>4888</v>
+      </c>
+      <c r="F780" s="6" t="s">
+        <v>4889</v>
+      </c>
+      <c r="G780" s="6" t="s">
         <v>4890</v>
       </c>
-      <c r="C780" s="6" t="s">
+      <c r="H780" s="6" t="s">
         <v>4891</v>
-      </c>
-      <c r="D780" s="6" t="s">
-        <v>4892</v>
-      </c>
-      <c r="E780" s="6" t="s">
-        <v>4893</v>
-      </c>
-      <c r="F780" s="6" t="s">
-        <v>4894</v>
-      </c>
-      <c r="G780" s="6" t="s">
-        <v>4895</v>
-      </c>
-      <c r="H780" s="6" t="s">
-        <v>4896</v>
       </c>
     </row>
     <row r="781">
       <c r="B781" s="5" t="s">
+        <v>4892</v>
+      </c>
+      <c r="C781" s="5" t="s">
+        <v>4893</v>
+      </c>
+      <c r="D781" s="5" t="s">
+        <v>4894</v>
+      </c>
+      <c r="E781" s="5" t="s">
+        <v>4895</v>
+      </c>
+      <c r="F781" s="5" t="s">
+        <v>4896</v>
+      </c>
+      <c r="G781" s="5" t="s">
         <v>4897</v>
       </c>
-      <c r="C781" s="5" t="s">
+      <c r="H781" s="5" t="s">
         <v>4898</v>
-      </c>
-      <c r="D781" s="5" t="s">
-        <v>4899</v>
-      </c>
-      <c r="E781" s="5" t="s">
-        <v>4900</v>
-      </c>
-      <c r="F781" s="5" t="s">
-        <v>4901</v>
-      </c>
-      <c r="G781" s="5" t="s">
-        <v>4902</v>
-      </c>
-      <c r="H781" s="5" t="s">
-        <v>4903</v>
       </c>
     </row>
     <row r="782">
       <c r="B782" s="6" t="s">
+        <v>4899</v>
+      </c>
+      <c r="C782" s="6" t="s">
+        <v>4900</v>
+      </c>
+      <c r="D782" s="6" t="s">
+        <v>4901</v>
+      </c>
+      <c r="E782" s="6" t="s">
+        <v>4902</v>
+      </c>
+      <c r="F782" s="6" t="s">
+        <v>4903</v>
+      </c>
+      <c r="G782" s="6" t="s">
         <v>4904</v>
       </c>
-      <c r="C782" s="6" t="s">
+      <c r="H782" s="6" t="s">
         <v>4905</v>
-      </c>
-      <c r="D782" s="6" t="s">
-        <v>4906</v>
-      </c>
-      <c r="E782" s="6" t="s">
-        <v>4907</v>
-      </c>
-      <c r="F782" s="6" t="s">
-        <v>4908</v>
-      </c>
-      <c r="G782" s="6" t="s">
-        <v>4909</v>
-      </c>
-      <c r="H782" s="6" t="s">
-        <v>4910</v>
       </c>
     </row>
     <row r="783">
       <c r="B783" s="5" t="s">
+        <v>4906</v>
+      </c>
+      <c r="C783" s="5" t="s">
+        <v>4907</v>
+      </c>
+      <c r="D783" s="5" t="s">
+        <v>4908</v>
+      </c>
+      <c r="E783" s="5" t="s">
+        <v>4909</v>
+      </c>
+      <c r="F783" s="5" t="s">
+        <v>4910</v>
+      </c>
+      <c r="G783" s="5" t="s">
         <v>4911</v>
       </c>
-      <c r="C783" s="5" t="s">
+      <c r="H783" s="5" t="s">
         <v>4912</v>
-      </c>
-      <c r="D783" s="5" t="s">
-        <v>4913</v>
-      </c>
-      <c r="E783" s="5" t="s">
-        <v>4914</v>
-      </c>
-      <c r="F783" s="5" t="s">
-        <v>4915</v>
-      </c>
-      <c r="G783" s="5" t="s">
-        <v>4915</v>
-      </c>
-      <c r="H783" s="5" t="s">
-        <v>4916</v>
       </c>
     </row>
     <row r="784">
       <c r="B784" s="6" t="s">
+        <v>4913</v>
+      </c>
+      <c r="C784" s="6" t="s">
+        <v>4914</v>
+      </c>
+      <c r="D784" s="6" t="s">
+        <v>4915</v>
+      </c>
+      <c r="E784" s="6" t="s">
+        <v>4916</v>
+      </c>
+      <c r="F784" s="6" t="s">
         <v>4917</v>
       </c>
-      <c r="C784" s="6" t="s">
+      <c r="G784" s="6" t="s">
         <v>4918</v>
       </c>
-      <c r="D784" s="6" t="s">
+      <c r="H784" s="6" t="s">
         <v>4919</v>
-      </c>
-      <c r="E784" s="6" t="s">
-        <v>4920</v>
-      </c>
-      <c r="F784" s="6" t="s">
-        <v>4921</v>
-      </c>
-      <c r="G784" s="6" t="s">
-        <v>4922</v>
-      </c>
-      <c r="H784" s="6" t="s">
-        <v>4923</v>
       </c>
     </row>
     <row r="785">
       <c r="B785" s="5" t="s">
+        <v>4920</v>
+      </c>
+      <c r="C785" s="5" t="s">
+        <v>4921</v>
+      </c>
+      <c r="D785" s="5" t="s">
+        <v>4922</v>
+      </c>
+      <c r="E785" s="5" t="s">
+        <v>4923</v>
+      </c>
+      <c r="F785" s="5" t="s">
         <v>4924</v>
       </c>
-      <c r="C785" s="5" t="s">
+      <c r="G785" s="5" t="s">
         <v>4925</v>
       </c>
-      <c r="D785" s="5" t="s">
+      <c r="H785" s="5" t="s">
         <v>4926</v>
-      </c>
-      <c r="E785" s="5" t="s">
-        <v>4927</v>
-      </c>
-      <c r="F785" s="5" t="s">
-        <v>4928</v>
-      </c>
-      <c r="G785" s="5" t="s">
-        <v>4929</v>
-      </c>
-      <c r="H785" s="5" t="s">
-        <v>4930</v>
       </c>
     </row>
     <row r="786">
       <c r="B786" s="6" t="s">
+        <v>4927</v>
+      </c>
+      <c r="C786" s="6" t="s">
+        <v>4928</v>
+      </c>
+      <c r="D786" s="6" t="s">
+        <v>4929</v>
+      </c>
+      <c r="E786" s="6" t="s">
+        <v>4930</v>
+      </c>
+      <c r="F786" s="6" t="s">
         <v>4931</v>
       </c>
-      <c r="C786" s="6" t="s">
+      <c r="G786" s="6" t="s">
         <v>4932</v>
       </c>
-      <c r="D786" s="6" t="s">
+      <c r="H786" s="6" t="s">
         <v>4933</v>
-      </c>
-      <c r="E786" s="6" t="s">
-        <v>4934</v>
-      </c>
-      <c r="F786" s="6" t="s">
-        <v>4935</v>
-      </c>
-      <c r="G786" s="6" t="s">
-        <v>4935</v>
-      </c>
-      <c r="H786" s="6" t="s">
-        <v>4936</v>
       </c>
     </row>
     <row r="787">
       <c r="B787" s="5" t="s">
+        <v>4934</v>
+      </c>
+      <c r="C787" s="5" t="s">
+        <v>4935</v>
+      </c>
+      <c r="D787" s="5" t="s">
+        <v>4936</v>
+      </c>
+      <c r="E787" s="5" t="s">
         <v>4937</v>
       </c>
-      <c r="C787" s="5" t="s">
+      <c r="F787" s="5" t="s">
         <v>4938</v>
       </c>
-      <c r="D787" s="5" t="s">
+      <c r="G787" s="5" t="s">
         <v>4939</v>
       </c>
-      <c r="E787" s="5" t="s">
+      <c r="H787" s="5" t="s">
         <v>4940</v>
-      </c>
-      <c r="F787" s="5" t="s">
-        <v>4941</v>
-      </c>
-      <c r="G787" s="5" t="s">
-        <v>4942</v>
-      </c>
-      <c r="H787" s="5" t="s">
-        <v>4943</v>
       </c>
     </row>
     <row r="788">
       <c r="B788" s="6" t="s">
+        <v>4941</v>
+      </c>
+      <c r="C788" s="6" t="s">
+        <v>4942</v>
+      </c>
+      <c r="D788" s="6" t="s">
+        <v>4943</v>
+      </c>
+      <c r="E788" s="6" t="s">
         <v>4944</v>
       </c>
-      <c r="C788" s="6" t="s">
+      <c r="F788" s="6" t="s">
         <v>4945</v>
       </c>
-      <c r="D788" s="6" t="s">
+      <c r="G788" s="6" t="s">
         <v>4946</v>
       </c>
-      <c r="E788" s="6" t="s">
+      <c r="H788" s="6" t="s">
         <v>4947</v>
-      </c>
-      <c r="F788" s="6" t="s">
-        <v>4948</v>
-      </c>
-      <c r="G788" s="6" t="s">
-        <v>4949</v>
-      </c>
-      <c r="H788" s="6" t="s">
-        <v>4950</v>
       </c>
     </row>
     <row r="789">
       <c r="B789" s="5" t="s">
+        <v>4948</v>
+      </c>
+      <c r="C789" s="5" t="s">
+        <v>4949</v>
+      </c>
+      <c r="D789" s="5" t="s">
+        <v>4950</v>
+      </c>
+      <c r="E789" s="5" t="s">
         <v>4951</v>
       </c>
-      <c r="C789" s="5" t="s">
+      <c r="F789" s="5" t="s">
         <v>4952</v>
       </c>
-      <c r="D789" s="5" t="s">
+      <c r="G789" s="5" t="s">
         <v>4953</v>
       </c>
-      <c r="E789" s="5" t="s">
+      <c r="H789" s="5" t="s">
         <v>4954</v>
-      </c>
-      <c r="F789" s="5" t="s">
-        <v>4955</v>
-      </c>
-      <c r="G789" s="5" t="s">
-        <v>4956</v>
-      </c>
-      <c r="H789" s="5" t="s">
-        <v>4957</v>
       </c>
     </row>
     <row r="790">
       <c r="B790" s="6" t="s">
+        <v>4955</v>
+      </c>
+      <c r="C790" s="6" t="s">
+        <v>4956</v>
+      </c>
+      <c r="D790" s="6" t="s">
+        <v>4957</v>
+      </c>
+      <c r="E790" s="6" t="s">
         <v>4958</v>
       </c>
-      <c r="C790" s="6" t="s">
+      <c r="F790" s="6" t="s">
         <v>4959</v>
       </c>
-      <c r="D790" s="6" t="s">
+      <c r="G790" s="6" t="s">
         <v>4960</v>
       </c>
-      <c r="E790" s="6" t="s">
+      <c r="H790" s="6" t="s">
         <v>4961</v>
-      </c>
-      <c r="F790" s="6" t="s">
-        <v>4962</v>
-      </c>
-      <c r="G790" s="6" t="s">
-        <v>4962</v>
-      </c>
-      <c r="H790" s="6" t="s">
-        <v>4963</v>
       </c>
     </row>
     <row r="791">
       <c r="B791" s="5" t="s">
+        <v>4962</v>
+      </c>
+      <c r="C791" s="5" t="s">
+        <v>4963</v>
+      </c>
+      <c r="D791" s="5" t="s">
         <v>4964</v>
       </c>
-      <c r="C791" s="5" t="s">
+      <c r="E791" s="5" t="s">
         <v>4965</v>
       </c>
-      <c r="D791" s="5" t="s">
+      <c r="F791" s="5" t="s">
         <v>4966</v>
       </c>
-      <c r="E791" s="5" t="s">
+      <c r="G791" s="5" t="s">
+        <v>4966</v>
+      </c>
+      <c r="H791" s="5" t="s">
         <v>4967</v>
-      </c>
-      <c r="F791" s="5" t="s">
-        <v>4968</v>
-      </c>
-      <c r="G791" s="5" t="s">
-        <v>4969</v>
-      </c>
-      <c r="H791" s="5" t="s">
-        <v>4970</v>
       </c>
     </row>
     <row r="792">
       <c r="B792" s="6" t="s">
+        <v>4968</v>
+      </c>
+      <c r="C792" s="6" t="s">
+        <v>4969</v>
+      </c>
+      <c r="D792" s="6" t="s">
+        <v>4970</v>
+      </c>
+      <c r="E792" s="6" t="s">
         <v>4971</v>
       </c>
-      <c r="C792" s="6" t="s">
+      <c r="F792" s="6" t="s">
         <v>4972</v>
       </c>
-      <c r="D792" s="6" t="s">
+      <c r="G792" s="6" t="s">
         <v>4973</v>
       </c>
-      <c r="E792" s="6" t="s">
+      <c r="H792" s="6" t="s">
         <v>4974</v>
-      </c>
-      <c r="F792" s="6" t="s">
-        <v>4975</v>
-      </c>
-      <c r="G792" s="6" t="s">
-        <v>4976</v>
-      </c>
-      <c r="H792" s="6" t="s">
-        <v>4977</v>
       </c>
     </row>
     <row r="793">
       <c r="B793" s="5" t="s">
+        <v>4975</v>
+      </c>
+      <c r="C793" s="5" t="s">
+        <v>4976</v>
+      </c>
+      <c r="D793" s="5" t="s">
+        <v>4977</v>
+      </c>
+      <c r="E793" s="5" t="s">
         <v>4978</v>
       </c>
-      <c r="C793" s="5" t="s">
+      <c r="F793" s="5" t="s">
         <v>4979</v>
       </c>
-      <c r="D793" s="5" t="s">
+      <c r="G793" s="5" t="s">
         <v>4980</v>
       </c>
-      <c r="E793" s="5" t="s">
+      <c r="H793" s="5" t="s">
         <v>4981</v>
-      </c>
-      <c r="F793" s="5" t="s">
-        <v>4982</v>
-      </c>
-      <c r="G793" s="5" t="s">
-        <v>4983</v>
-      </c>
-      <c r="H793" s="5" t="s">
-        <v>4984</v>
       </c>
     </row>
     <row r="794">
       <c r="B794" s="6" t="s">
+        <v>4982</v>
+      </c>
+      <c r="C794" s="6" t="s">
+        <v>4983</v>
+      </c>
+      <c r="D794" s="6" t="s">
+        <v>4984</v>
+      </c>
+      <c r="E794" s="6" t="s">
         <v>4985</v>
       </c>
-      <c r="C794" s="6" t="s">
+      <c r="F794" s="6" t="s">
         <v>4986</v>
       </c>
-      <c r="D794" s="6" t="s">
+      <c r="G794" s="6" t="s">
+        <v>4986</v>
+      </c>
+      <c r="H794" s="6" t="s">
         <v>4987</v>
-      </c>
-      <c r="E794" s="6" t="s">
-        <v>4988</v>
-      </c>
-      <c r="F794" s="6" t="s">
-        <v>4989</v>
-      </c>
-      <c r="G794" s="6" t="s">
-        <v>4990</v>
-      </c>
-      <c r="H794" s="6" t="s">
-        <v>4991</v>
       </c>
     </row>
     <row r="795">
       <c r="B795" s="5" t="s">
+        <v>4988</v>
+      </c>
+      <c r="C795" s="5" t="s">
+        <v>4989</v>
+      </c>
+      <c r="D795" s="5" t="s">
+        <v>4990</v>
+      </c>
+      <c r="E795" s="5" t="s">
+        <v>4991</v>
+      </c>
+      <c r="F795" s="5" t="s">
         <v>4992</v>
       </c>
-      <c r="C795" s="5" t="s">
+      <c r="G795" s="5" t="s">
         <v>4993</v>
       </c>
-      <c r="D795" s="5" t="s">
+      <c r="H795" s="5" t="s">
         <v>4994</v>
-      </c>
-      <c r="E795" s="5" t="s">
-        <v>4995</v>
-      </c>
-      <c r="F795" s="5" t="s">
-        <v>4996</v>
-      </c>
-      <c r="G795" s="5" t="s">
-        <v>4997</v>
-      </c>
-      <c r="H795" s="5" t="s">
-        <v>4998</v>
       </c>
     </row>
     <row r="796">
       <c r="B796" s="6" t="s">
+        <v>4995</v>
+      </c>
+      <c r="C796" s="6" t="s">
+        <v>4996</v>
+      </c>
+      <c r="D796" s="6" t="s">
+        <v>4997</v>
+      </c>
+      <c r="E796" s="6" t="s">
+        <v>4998</v>
+      </c>
+      <c r="F796" s="6" t="s">
         <v>4999</v>
       </c>
-      <c r="C796" s="6" t="s">
+      <c r="G796" s="6" t="s">
         <v>5000</v>
       </c>
-      <c r="D796" s="6" t="s">
+      <c r="H796" s="6" t="s">
         <v>5001</v>
-      </c>
-      <c r="E796" s="6" t="s">
-        <v>5002</v>
-      </c>
-      <c r="F796" s="6" t="s">
-        <v>5003</v>
-      </c>
-      <c r="G796" s="6" t="s">
-        <v>5004</v>
-      </c>
-      <c r="H796" s="6" t="s">
-        <v>5005</v>
       </c>
     </row>
     <row r="797">
       <c r="B797" s="5" t="s">
+        <v>5002</v>
+      </c>
+      <c r="C797" s="5" t="s">
+        <v>5003</v>
+      </c>
+      <c r="D797" s="5" t="s">
+        <v>5004</v>
+      </c>
+      <c r="E797" s="5" t="s">
+        <v>5005</v>
+      </c>
+      <c r="F797" s="5" t="s">
         <v>5006</v>
       </c>
-      <c r="C797" s="5" t="s">
+      <c r="G797" s="5" t="s">
         <v>5007</v>
       </c>
-      <c r="D797" s="5" t="s">
+      <c r="H797" s="5" t="s">
         <v>5008</v>
-      </c>
-      <c r="E797" s="5" t="s">
-        <v>5009</v>
-      </c>
-      <c r="F797" s="5" t="s">
-        <v>5010</v>
-      </c>
-      <c r="G797" s="5" t="s">
-        <v>5011</v>
-      </c>
-      <c r="H797" s="5" t="s">
-        <v>5012</v>
       </c>
     </row>
     <row r="798">
       <c r="B798" s="6" t="s">
+        <v>5009</v>
+      </c>
+      <c r="C798" s="6" t="s">
+        <v>5010</v>
+      </c>
+      <c r="D798" s="6" t="s">
+        <v>5011</v>
+      </c>
+      <c r="E798" s="6" t="s">
+        <v>5012</v>
+      </c>
+      <c r="F798" s="6" t="s">
         <v>5013</v>
       </c>
-      <c r="C798" s="6" t="s">
+      <c r="G798" s="6" t="s">
+        <v>5013</v>
+      </c>
+      <c r="H798" s="6" t="s">
         <v>5014</v>
-      </c>
-      <c r="D798" s="6" t="s">
-        <v>5015</v>
-      </c>
-      <c r="E798" s="6" t="s">
-        <v>5016</v>
-      </c>
-      <c r="F798" s="6" t="s">
-        <v>5017</v>
-      </c>
-      <c r="G798" s="6" t="s">
-        <v>5018</v>
-      </c>
-      <c r="H798" s="6" t="s">
-        <v>5015</v>
       </c>
     </row>
     <row r="799">
       <c r="B799" s="5" t="s">
+        <v>5015</v>
+      </c>
+      <c r="C799" s="5" t="s">
+        <v>5016</v>
+      </c>
+      <c r="D799" s="5" t="s">
+        <v>5017</v>
+      </c>
+      <c r="E799" s="5" t="s">
+        <v>5018</v>
+      </c>
+      <c r="F799" s="5" t="s">
         <v>5019</v>
       </c>
-      <c r="C799" s="5" t="s">
+      <c r="G799" s="5" t="s">
         <v>5020</v>
       </c>
-      <c r="D799" s="5" t="s">
+      <c r="H799" s="5" t="s">
         <v>5021</v>
-      </c>
-      <c r="E799" s="5" t="s">
-        <v>5022</v>
-      </c>
-      <c r="F799" s="5" t="s">
-        <v>5023</v>
-      </c>
-      <c r="G799" s="5" t="s">
-        <v>5024</v>
-      </c>
-      <c r="H799" s="5" t="s">
-        <v>5025</v>
       </c>
     </row>
     <row r="800">
       <c r="B800" s="6" t="s">
+        <v>5022</v>
+      </c>
+      <c r="C800" s="6" t="s">
+        <v>5023</v>
+      </c>
+      <c r="D800" s="6" t="s">
+        <v>5024</v>
+      </c>
+      <c r="E800" s="6" t="s">
+        <v>5025</v>
+      </c>
+      <c r="F800" s="6" t="s">
         <v>5026</v>
       </c>
-      <c r="C800" s="6" t="s">
+      <c r="G800" s="6" t="s">
         <v>5027</v>
       </c>
-      <c r="D800" s="6" t="s">
+      <c r="H800" s="6" t="s">
         <v>5028</v>
-      </c>
-      <c r="E800" s="6" t="s">
-        <v>5029</v>
-      </c>
-      <c r="F800" s="6" t="s">
-        <v>5030</v>
-      </c>
-      <c r="G800" s="6" t="s">
-        <v>5031</v>
-      </c>
-      <c r="H800" s="6" t="s">
-        <v>5032</v>
       </c>
     </row>
     <row r="801">
       <c r="B801" s="5" t="s">
+        <v>5029</v>
+      </c>
+      <c r="C801" s="5" t="s">
+        <v>5030</v>
+      </c>
+      <c r="D801" s="5" t="s">
+        <v>5031</v>
+      </c>
+      <c r="E801" s="5" t="s">
+        <v>5032</v>
+      </c>
+      <c r="F801" s="5" t="s">
         <v>5033</v>
       </c>
-      <c r="C801" s="5" t="s">
+      <c r="G801" s="5" t="s">
         <v>5034</v>
       </c>
-      <c r="D801" s="5" t="s">
+      <c r="H801" s="5" t="s">
         <v>5035</v>
-      </c>
-      <c r="E801" s="5" t="s">
-        <v>5036</v>
-      </c>
-      <c r="F801" s="5" t="s">
-        <v>5037</v>
-      </c>
-      <c r="G801" s="5" t="s">
-        <v>5038</v>
-      </c>
-      <c r="H801" s="5" t="s">
-        <v>5039</v>
       </c>
     </row>
     <row r="802">
       <c r="B802" s="6" t="s">
+        <v>5036</v>
+      </c>
+      <c r="C802" s="6" t="s">
+        <v>5037</v>
+      </c>
+      <c r="D802" s="6" t="s">
+        <v>5038</v>
+      </c>
+      <c r="E802" s="6" t="s">
+        <v>5039</v>
+      </c>
+      <c r="F802" s="6" t="s">
         <v>5040</v>
       </c>
-      <c r="C802" s="6" t="s">
+      <c r="G802" s="6" t="s">
         <v>5041</v>
       </c>
-      <c r="D802" s="6" t="s">
+      <c r="H802" s="6" t="s">
         <v>5042</v>
-      </c>
-      <c r="E802" s="6" t="s">
-        <v>5043</v>
-      </c>
-      <c r="F802" s="6" t="s">
-        <v>5044</v>
-      </c>
-      <c r="G802" s="6" t="s">
-        <v>5045</v>
-      </c>
-      <c r="H802" s="6" t="s">
-        <v>5046</v>
       </c>
     </row>
     <row r="803">
       <c r="B803" s="5" t="s">
+        <v>5043</v>
+      </c>
+      <c r="C803" s="5" t="s">
+        <v>5044</v>
+      </c>
+      <c r="D803" s="5" t="s">
+        <v>5045</v>
+      </c>
+      <c r="E803" s="5" t="s">
+        <v>5046</v>
+      </c>
+      <c r="F803" s="5" t="s">
         <v>5047</v>
       </c>
-      <c r="C803" s="5" t="s">
+      <c r="G803" s="5" t="s">
         <v>5048</v>
       </c>
-      <c r="D803" s="5" t="s">
+      <c r="H803" s="5" t="s">
         <v>5049</v>
-      </c>
-      <c r="E803" s="5" t="s">
-        <v>5050</v>
-      </c>
-      <c r="F803" s="5" t="s">
-        <v>5051</v>
-      </c>
-      <c r="G803" s="5" t="s">
-        <v>5052</v>
-      </c>
-      <c r="H803" s="5" t="s">
-        <v>5053</v>
       </c>
     </row>
     <row r="804">
       <c r="B804" s="6" t="s">
+        <v>5050</v>
+      </c>
+      <c r="C804" s="6" t="s">
+        <v>5051</v>
+      </c>
+      <c r="D804" s="6" t="s">
+        <v>5052</v>
+      </c>
+      <c r="E804" s="6" t="s">
+        <v>5053</v>
+      </c>
+      <c r="F804" s="6" t="s">
         <v>5054</v>
       </c>
-      <c r="C804" s="6" t="s">
-        <v>3021</v>
-      </c>
-      <c r="D804" s="6" t="s">
+      <c r="G804" s="6" t="s">
         <v>5055</v>
       </c>
-      <c r="E804" s="6" t="s">
-        <v>3023</v>
-      </c>
-      <c r="F804" s="6" t="s">
+      <c r="H804" s="6" t="s">
         <v>5056</v>
-      </c>
-      <c r="G804" s="6" t="s">
-        <v>5057</v>
-      </c>
-      <c r="H804" s="6" t="s">
-        <v>5058</v>
       </c>
     </row>
     <row r="805">
       <c r="B805" s="5" t="s">
+        <v>5057</v>
+      </c>
+      <c r="C805" s="5" t="s">
+        <v>5058</v>
+      </c>
+      <c r="D805" s="5" t="s">
         <v>5059</v>
       </c>
-      <c r="C805" s="5" t="s">
-        <v>3014</v>
-      </c>
-      <c r="D805" s="5" t="s">
+      <c r="E805" s="5" t="s">
         <v>5060</v>
-      </c>
-      <c r="E805" s="5" t="s">
-        <v>3016</v>
       </c>
       <c r="F805" s="5" t="s">
         <v>5061</v>
@@ -35337,139 +35487,139 @@
         <v>5068</v>
       </c>
       <c r="G806" s="6" t="s">
-        <v>5067</v>
+        <v>5069</v>
       </c>
       <c r="H806" s="6" t="s">
-        <v>4450</v>
+        <v>5066</v>
       </c>
     </row>
     <row r="807">
       <c r="B807" s="5" t="s">
-        <v>5069</v>
+        <v>5070</v>
       </c>
       <c r="C807" s="5" t="s">
-        <v>5070</v>
+        <v>5071</v>
       </c>
       <c r="D807" s="5" t="s">
-        <v>5071</v>
+        <v>5072</v>
       </c>
       <c r="E807" s="5" t="s">
-        <v>5072</v>
+        <v>5073</v>
       </c>
       <c r="F807" s="5" t="s">
-        <v>5073</v>
+        <v>5074</v>
       </c>
       <c r="G807" s="5" t="s">
-        <v>5074</v>
+        <v>5075</v>
       </c>
       <c r="H807" s="5" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
     </row>
     <row r="808">
       <c r="B808" s="6" t="s">
-        <v>5076</v>
+        <v>5077</v>
       </c>
       <c r="C808" s="6" t="s">
-        <v>5077</v>
+        <v>5078</v>
       </c>
       <c r="D808" s="6" t="s">
-        <v>5078</v>
+        <v>5079</v>
       </c>
       <c r="E808" s="6" t="s">
-        <v>5079</v>
+        <v>5080</v>
       </c>
       <c r="F808" s="6" t="s">
-        <v>5080</v>
+        <v>5081</v>
       </c>
       <c r="G808" s="6" t="s">
-        <v>5080</v>
+        <v>5082</v>
       </c>
       <c r="H808" s="6" t="s">
-        <v>5081</v>
+        <v>5083</v>
       </c>
     </row>
     <row r="809">
       <c r="B809" s="5" t="s">
-        <v>5082</v>
+        <v>5084</v>
       </c>
       <c r="C809" s="5" t="s">
-        <v>5083</v>
+        <v>5085</v>
       </c>
       <c r="D809" s="5" t="s">
-        <v>5084</v>
+        <v>5086</v>
       </c>
       <c r="E809" s="5" t="s">
-        <v>5085</v>
+        <v>5087</v>
       </c>
       <c r="F809" s="5" t="s">
-        <v>5086</v>
+        <v>5088</v>
       </c>
       <c r="G809" s="5" t="s">
-        <v>5087</v>
+        <v>5089</v>
       </c>
       <c r="H809" s="5" t="s">
-        <v>5088</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="810">
       <c r="B810" s="6" t="s">
-        <v>5089</v>
+        <v>5091</v>
       </c>
       <c r="C810" s="6" t="s">
-        <v>5090</v>
+        <v>5092</v>
       </c>
       <c r="D810" s="6" t="s">
-        <v>5091</v>
+        <v>5093</v>
       </c>
       <c r="E810" s="6" t="s">
-        <v>5092</v>
+        <v>5094</v>
       </c>
       <c r="F810" s="6" t="s">
-        <v>5093</v>
+        <v>5095</v>
       </c>
       <c r="G810" s="6" t="s">
-        <v>5094</v>
+        <v>5096</v>
       </c>
       <c r="H810" s="6" t="s">
-        <v>5095</v>
+        <v>5097</v>
       </c>
     </row>
     <row r="811">
       <c r="B811" s="5" t="s">
-        <v>5096</v>
+        <v>5098</v>
       </c>
       <c r="C811" s="5" t="s">
-        <v>5097</v>
+        <v>5099</v>
       </c>
       <c r="D811" s="5" t="s">
-        <v>5098</v>
+        <v>5100</v>
       </c>
       <c r="E811" s="5" t="s">
-        <v>5099</v>
+        <v>5101</v>
       </c>
       <c r="F811" s="5" t="s">
-        <v>5100</v>
+        <v>5102</v>
       </c>
       <c r="G811" s="5" t="s">
-        <v>5101</v>
+        <v>5103</v>
       </c>
       <c r="H811" s="5" t="s">
-        <v>5102</v>
+        <v>5104</v>
       </c>
     </row>
     <row r="812">
       <c r="B812" s="6" t="s">
-        <v>5103</v>
+        <v>5105</v>
       </c>
       <c r="C812" s="6" t="s">
-        <v>5104</v>
+        <v>3021</v>
       </c>
       <c r="D812" s="6" t="s">
-        <v>5105</v>
+        <v>5106</v>
       </c>
       <c r="E812" s="6" t="s">
-        <v>5106</v>
+        <v>3023</v>
       </c>
       <c r="F812" s="6" t="s">
         <v>5107</v>
@@ -35486,177 +35636,177 @@
         <v>5110</v>
       </c>
       <c r="C813" s="5" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D813" s="5" t="s">
         <v>5111</v>
       </c>
-      <c r="D813" s="5" t="s">
+      <c r="E813" s="5" t="s">
+        <v>3016</v>
+      </c>
+      <c r="F813" s="5" t="s">
         <v>5112</v>
       </c>
-      <c r="E813" s="5" t="s">
+      <c r="G813" s="5" t="s">
         <v>5113</v>
       </c>
-      <c r="F813" s="5" t="s">
+      <c r="H813" s="5" t="s">
         <v>5114</v>
-      </c>
-      <c r="G813" s="5" t="s">
-        <v>5115</v>
-      </c>
-      <c r="H813" s="5" t="s">
-        <v>5116</v>
       </c>
     </row>
     <row r="814">
       <c r="B814" s="6" t="s">
+        <v>5115</v>
+      </c>
+      <c r="C814" s="6" t="s">
+        <v>5116</v>
+      </c>
+      <c r="D814" s="6" t="s">
         <v>5117</v>
       </c>
-      <c r="C814" s="6" t="s">
+      <c r="E814" s="6" t="s">
         <v>5118</v>
       </c>
-      <c r="D814" s="6" t="s">
+      <c r="F814" s="6" t="s">
         <v>5119</v>
       </c>
-      <c r="E814" s="6" t="s">
-        <v>5120</v>
-      </c>
-      <c r="F814" s="6" t="s">
-        <v>5120</v>
-      </c>
       <c r="G814" s="6" t="s">
-        <v>5120</v>
+        <v>5118</v>
       </c>
       <c r="H814" s="6" t="s">
-        <v>5121</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="815">
       <c r="B815" s="5" t="s">
+        <v>5120</v>
+      </c>
+      <c r="C815" s="5" t="s">
+        <v>5121</v>
+      </c>
+      <c r="D815" s="5" t="s">
         <v>5122</v>
       </c>
-      <c r="C815" s="5" t="s">
+      <c r="E815" s="5" t="s">
         <v>5123</v>
       </c>
-      <c r="D815" s="5" t="s">
+      <c r="F815" s="5" t="s">
         <v>5124</v>
       </c>
-      <c r="E815" s="5" t="s">
+      <c r="G815" s="5" t="s">
         <v>5125</v>
       </c>
-      <c r="F815" s="5" t="s">
+      <c r="H815" s="5" t="s">
         <v>5126</v>
-      </c>
-      <c r="G815" s="5" t="s">
-        <v>5127</v>
-      </c>
-      <c r="H815" s="5" t="s">
-        <v>5128</v>
       </c>
     </row>
     <row r="816">
       <c r="B816" s="6" t="s">
+        <v>5127</v>
+      </c>
+      <c r="C816" s="6" t="s">
+        <v>5128</v>
+      </c>
+      <c r="D816" s="6" t="s">
         <v>5129</v>
       </c>
-      <c r="C816" s="6" t="s">
+      <c r="E816" s="6" t="s">
         <v>5130</v>
       </c>
-      <c r="D816" s="6" t="s">
+      <c r="F816" s="6" t="s">
         <v>5131</v>
       </c>
-      <c r="E816" s="6" t="s">
+      <c r="G816" s="6" t="s">
+        <v>5131</v>
+      </c>
+      <c r="H816" s="6" t="s">
         <v>5132</v>
-      </c>
-      <c r="F816" s="6" t="s">
-        <v>5133</v>
-      </c>
-      <c r="G816" s="6" t="s">
-        <v>5134</v>
-      </c>
-      <c r="H816" s="6" t="s">
-        <v>5135</v>
       </c>
     </row>
     <row r="817">
       <c r="B817" s="5" t="s">
+        <v>5133</v>
+      </c>
+      <c r="C817" s="5" t="s">
+        <v>5134</v>
+      </c>
+      <c r="D817" s="5" t="s">
+        <v>5135</v>
+      </c>
+      <c r="E817" s="5" t="s">
         <v>5136</v>
       </c>
-      <c r="C817" s="5" t="s">
+      <c r="F817" s="5" t="s">
         <v>5137</v>
       </c>
-      <c r="D817" s="5" t="s">
+      <c r="G817" s="5" t="s">
         <v>5138</v>
       </c>
-      <c r="E817" s="5" t="s">
+      <c r="H817" s="5" t="s">
         <v>5139</v>
-      </c>
-      <c r="F817" s="5" t="s">
-        <v>5140</v>
-      </c>
-      <c r="G817" s="5" t="s">
-        <v>5141</v>
-      </c>
-      <c r="H817" s="5" t="s">
-        <v>5142</v>
       </c>
     </row>
     <row r="818">
       <c r="B818" s="6" t="s">
+        <v>5140</v>
+      </c>
+      <c r="C818" s="6" t="s">
+        <v>5141</v>
+      </c>
+      <c r="D818" s="6" t="s">
+        <v>5142</v>
+      </c>
+      <c r="E818" s="6" t="s">
         <v>5143</v>
       </c>
-      <c r="C818" s="6" t="s">
+      <c r="F818" s="6" t="s">
         <v>5144</v>
       </c>
-      <c r="D818" s="6" t="s">
+      <c r="G818" s="6" t="s">
         <v>5145</v>
       </c>
-      <c r="E818" s="6" t="s">
+      <c r="H818" s="6" t="s">
         <v>5146</v>
-      </c>
-      <c r="F818" s="6" t="s">
-        <v>5147</v>
-      </c>
-      <c r="G818" s="6" t="s">
-        <v>5147</v>
-      </c>
-      <c r="H818" s="6" t="s">
-        <v>5148</v>
       </c>
     </row>
     <row r="819">
       <c r="B819" s="5" t="s">
+        <v>5147</v>
+      </c>
+      <c r="C819" s="5" t="s">
+        <v>5148</v>
+      </c>
+      <c r="D819" s="5" t="s">
         <v>5149</v>
       </c>
-      <c r="C819" s="5" t="s">
+      <c r="E819" s="5" t="s">
         <v>5150</v>
       </c>
-      <c r="D819" s="5" t="s">
+      <c r="F819" s="5" t="s">
         <v>5151</v>
       </c>
-      <c r="E819" s="5" t="s">
+      <c r="G819" s="5" t="s">
         <v>5152</v>
       </c>
-      <c r="F819" s="5" t="s">
+      <c r="H819" s="5" t="s">
         <v>5153</v>
-      </c>
-      <c r="G819" s="5" t="s">
-        <v>5153</v>
-      </c>
-      <c r="H819" s="5" t="s">
-        <v>5154</v>
       </c>
     </row>
     <row r="820">
       <c r="B820" s="6" t="s">
+        <v>5154</v>
+      </c>
+      <c r="C820" s="6" t="s">
         <v>5155</v>
       </c>
-      <c r="C820" s="6" t="s">
+      <c r="D820" s="6" t="s">
         <v>5156</v>
       </c>
-      <c r="D820" s="6" t="s">
+      <c r="E820" s="6" t="s">
         <v>5157</v>
       </c>
-      <c r="E820" s="6" t="s">
+      <c r="F820" s="6" t="s">
         <v>5158</v>
-      </c>
-      <c r="F820" s="6" t="s">
-        <v>5159</v>
       </c>
       <c r="G820" s="6" t="s">
         <v>5159</v>
@@ -35702,220 +35852,220 @@
         <v>5171</v>
       </c>
       <c r="F822" s="6" t="s">
+        <v>5171</v>
+      </c>
+      <c r="G822" s="6" t="s">
+        <v>5171</v>
+      </c>
+      <c r="H822" s="6" t="s">
         <v>5172</v>
-      </c>
-      <c r="G822" s="6" t="s">
-        <v>5173</v>
-      </c>
-      <c r="H822" s="6" t="s">
-        <v>5174</v>
       </c>
     </row>
     <row r="823">
       <c r="B823" s="5" t="s">
+        <v>5173</v>
+      </c>
+      <c r="C823" s="5" t="s">
+        <v>5174</v>
+      </c>
+      <c r="D823" s="5" t="s">
         <v>5175</v>
       </c>
-      <c r="C823" s="5" t="s">
+      <c r="E823" s="5" t="s">
         <v>5176</v>
       </c>
-      <c r="D823" s="5" t="s">
+      <c r="F823" s="5" t="s">
         <v>5177</v>
       </c>
-      <c r="E823" s="5" t="s">
+      <c r="G823" s="5" t="s">
         <v>5178</v>
       </c>
-      <c r="F823" s="5" t="s">
+      <c r="H823" s="5" t="s">
         <v>5179</v>
-      </c>
-      <c r="G823" s="5" t="s">
-        <v>5180</v>
-      </c>
-      <c r="H823" s="5" t="s">
-        <v>5181</v>
       </c>
     </row>
     <row r="824">
       <c r="B824" s="6" t="s">
+        <v>5180</v>
+      </c>
+      <c r="C824" s="6" t="s">
+        <v>5181</v>
+      </c>
+      <c r="D824" s="6" t="s">
         <v>5182</v>
       </c>
-      <c r="C824" s="6" t="s">
+      <c r="E824" s="6" t="s">
         <v>5183</v>
       </c>
-      <c r="D824" s="6" t="s">
+      <c r="F824" s="6" t="s">
         <v>5184</v>
       </c>
-      <c r="E824" s="6" t="s">
+      <c r="G824" s="6" t="s">
         <v>5185</v>
       </c>
-      <c r="F824" s="6" t="s">
+      <c r="H824" s="6" t="s">
         <v>5186</v>
-      </c>
-      <c r="G824" s="6" t="s">
-        <v>5187</v>
-      </c>
-      <c r="H824" s="6" t="s">
-        <v>5188</v>
       </c>
     </row>
     <row r="825">
       <c r="B825" s="5" t="s">
+        <v>5187</v>
+      </c>
+      <c r="C825" s="5" t="s">
+        <v>5188</v>
+      </c>
+      <c r="D825" s="5" t="s">
         <v>5189</v>
       </c>
-      <c r="C825" s="5" t="s">
+      <c r="E825" s="5" t="s">
         <v>5190</v>
       </c>
-      <c r="D825" s="5" t="s">
+      <c r="F825" s="5" t="s">
         <v>5191</v>
       </c>
-      <c r="E825" s="5" t="s">
+      <c r="G825" s="5" t="s">
         <v>5192</v>
       </c>
-      <c r="F825" s="5" t="s">
+      <c r="H825" s="5" t="s">
         <v>5193</v>
-      </c>
-      <c r="G825" s="5" t="s">
-        <v>5194</v>
-      </c>
-      <c r="H825" s="5" t="s">
-        <v>5195</v>
       </c>
     </row>
     <row r="826">
       <c r="B826" s="6" t="s">
+        <v>5194</v>
+      </c>
+      <c r="C826" s="6" t="s">
+        <v>5195</v>
+      </c>
+      <c r="D826" s="6" t="s">
         <v>5196</v>
       </c>
-      <c r="C826" s="6" t="s">
+      <c r="E826" s="6" t="s">
         <v>5197</v>
       </c>
-      <c r="D826" s="6" t="s">
+      <c r="F826" s="6" t="s">
         <v>5198</v>
       </c>
-      <c r="E826" s="6" t="s">
+      <c r="G826" s="6" t="s">
+        <v>5198</v>
+      </c>
+      <c r="H826" s="6" t="s">
         <v>5199</v>
-      </c>
-      <c r="F826" s="6" t="s">
-        <v>5200</v>
-      </c>
-      <c r="G826" s="6" t="s">
-        <v>5200</v>
-      </c>
-      <c r="H826" s="6" t="s">
-        <v>5201</v>
       </c>
     </row>
     <row r="827">
       <c r="B827" s="5" t="s">
+        <v>5200</v>
+      </c>
+      <c r="C827" s="5" t="s">
+        <v>5201</v>
+      </c>
+      <c r="D827" s="5" t="s">
         <v>5202</v>
       </c>
-      <c r="C827" s="5" t="s">
+      <c r="E827" s="5" t="s">
         <v>5203</v>
       </c>
-      <c r="D827" s="5" t="s">
+      <c r="F827" s="5" t="s">
         <v>5204</v>
       </c>
-      <c r="E827" s="5" t="s">
+      <c r="G827" s="5" t="s">
+        <v>5204</v>
+      </c>
+      <c r="H827" s="5" t="s">
         <v>5205</v>
-      </c>
-      <c r="F827" s="5" t="s">
-        <v>5206</v>
-      </c>
-      <c r="G827" s="5" t="s">
-        <v>5207</v>
-      </c>
-      <c r="H827" s="5" t="s">
-        <v>5208</v>
       </c>
     </row>
     <row r="828">
       <c r="B828" s="6" t="s">
+        <v>5206</v>
+      </c>
+      <c r="C828" s="6" t="s">
+        <v>5207</v>
+      </c>
+      <c r="D828" s="6" t="s">
+        <v>5208</v>
+      </c>
+      <c r="E828" s="6" t="s">
         <v>5209</v>
       </c>
-      <c r="C828" s="6" t="s">
+      <c r="F828" s="6" t="s">
         <v>5210</v>
       </c>
-      <c r="D828" s="6" t="s">
+      <c r="G828" s="6" t="s">
+        <v>5210</v>
+      </c>
+      <c r="H828" s="6" t="s">
         <v>5211</v>
-      </c>
-      <c r="E828" s="6" t="s">
-        <v>5212</v>
-      </c>
-      <c r="F828" s="6" t="s">
-        <v>5213</v>
-      </c>
-      <c r="G828" s="6" t="s">
-        <v>5214</v>
-      </c>
-      <c r="H828" s="6" t="s">
-        <v>4977</v>
       </c>
     </row>
     <row r="829">
       <c r="B829" s="5" t="s">
+        <v>5212</v>
+      </c>
+      <c r="C829" s="5" t="s">
+        <v>5213</v>
+      </c>
+      <c r="D829" s="5" t="s">
+        <v>5214</v>
+      </c>
+      <c r="E829" s="5" t="s">
         <v>5215</v>
       </c>
-      <c r="C829" s="5" t="s">
+      <c r="F829" s="5" t="s">
         <v>5216</v>
       </c>
-      <c r="D829" s="5" t="s">
+      <c r="G829" s="5" t="s">
         <v>5217</v>
       </c>
-      <c r="E829" s="5" t="s">
+      <c r="H829" s="5" t="s">
         <v>5218</v>
-      </c>
-      <c r="F829" s="5" t="s">
-        <v>5219</v>
-      </c>
-      <c r="G829" s="5" t="s">
-        <v>5220</v>
-      </c>
-      <c r="H829" s="5" t="s">
-        <v>5221</v>
       </c>
     </row>
     <row r="830">
       <c r="B830" s="6" t="s">
+        <v>5219</v>
+      </c>
+      <c r="C830" s="6" t="s">
+        <v>5220</v>
+      </c>
+      <c r="D830" s="6" t="s">
+        <v>5221</v>
+      </c>
+      <c r="E830" s="6" t="s">
         <v>5222</v>
       </c>
-      <c r="C830" s="6" t="s">
+      <c r="F830" s="6" t="s">
         <v>5223</v>
       </c>
-      <c r="D830" s="6" t="s">
+      <c r="G830" s="6" t="s">
         <v>5224</v>
       </c>
-      <c r="E830" s="6" t="s">
+      <c r="H830" s="6" t="s">
         <v>5225</v>
-      </c>
-      <c r="F830" s="6" t="s">
-        <v>5226</v>
-      </c>
-      <c r="G830" s="6" t="s">
-        <v>5227</v>
-      </c>
-      <c r="H830" s="6" t="s">
-        <v>5228</v>
       </c>
     </row>
     <row r="831">
       <c r="B831" s="5" t="s">
+        <v>5226</v>
+      </c>
+      <c r="C831" s="5" t="s">
+        <v>5227</v>
+      </c>
+      <c r="D831" s="5" t="s">
+        <v>5228</v>
+      </c>
+      <c r="E831" s="5" t="s">
         <v>5229</v>
       </c>
-      <c r="C831" s="5" t="s">
+      <c r="F831" s="5" t="s">
         <v>5230</v>
       </c>
-      <c r="D831" s="5" t="s">
+      <c r="G831" s="5" t="s">
         <v>5231</v>
       </c>
-      <c r="E831" s="5" t="s">
+      <c r="H831" s="5" t="s">
         <v>5232</v>
-      </c>
-      <c r="F831" s="5" t="s">
-        <v>5232</v>
-      </c>
-      <c r="G831" s="5" t="s">
-        <v>5232</v>
-      </c>
-      <c r="H831" s="5" t="s">
-        <v>5231</v>
       </c>
     </row>
     <row r="832">
@@ -35981,21 +36131,21 @@
         <v>5251</v>
       </c>
       <c r="G834" s="6" t="s">
+        <v>5251</v>
+      </c>
+      <c r="H834" s="6" t="s">
         <v>5252</v>
-      </c>
-      <c r="H834" s="6" t="s">
-        <v>5253</v>
       </c>
     </row>
     <row r="835">
       <c r="B835" s="5" t="s">
+        <v>5253</v>
+      </c>
+      <c r="C835" s="5" t="s">
         <v>5254</v>
       </c>
-      <c r="C835" s="5" t="s">
+      <c r="D835" s="5" t="s">
         <v>5255</v>
-      </c>
-      <c r="D835" s="5" t="s">
-        <v>5231</v>
       </c>
       <c r="E835" s="5" t="s">
         <v>5256</v>
@@ -36004,33 +36154,33 @@
         <v>5257</v>
       </c>
       <c r="G835" s="5" t="s">
-        <v>5257</v>
+        <v>5258</v>
       </c>
       <c r="H835" s="5" t="s">
-        <v>5231</v>
+        <v>4408</v>
       </c>
     </row>
     <row r="836">
       <c r="B836" s="6" t="s">
-        <v>5258</v>
+        <v>5259</v>
       </c>
       <c r="C836" s="6" t="s">
-        <v>5259</v>
+        <v>5260</v>
       </c>
       <c r="D836" s="6" t="s">
-        <v>5260</v>
+        <v>5261</v>
       </c>
       <c r="E836" s="6" t="s">
-        <v>5261</v>
+        <v>5262</v>
       </c>
       <c r="F836" s="6" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="G836" s="6" t="s">
-        <v>5263</v>
+        <v>5264</v>
       </c>
       <c r="H836" s="6" t="s">
-        <v>5264</v>
+        <v>5028</v>
       </c>
     </row>
     <row r="837">
@@ -36053,369 +36203,369 @@
         <v>5270</v>
       </c>
       <c r="H837" s="5" t="s">
-        <v>5267</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="838">
       <c r="B838" s="6" t="s">
-        <v>5271</v>
+        <v>5272</v>
       </c>
       <c r="C838" s="6" t="s">
-        <v>5272</v>
+        <v>5273</v>
       </c>
       <c r="D838" s="6" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="E838" s="6" t="s">
-        <v>5274</v>
+        <v>5275</v>
       </c>
       <c r="F838" s="6" t="s">
-        <v>5275</v>
+        <v>5276</v>
       </c>
       <c r="G838" s="6" t="s">
-        <v>5276</v>
+        <v>5277</v>
       </c>
       <c r="H838" s="6" t="s">
-        <v>5277</v>
+        <v>5278</v>
       </c>
     </row>
     <row r="839">
       <c r="B839" s="5" t="s">
-        <v>5278</v>
+        <v>5279</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>5279</v>
+        <v>5280</v>
       </c>
       <c r="D839" s="5" t="s">
-        <v>5280</v>
+        <v>5281</v>
       </c>
       <c r="E839" s="5" t="s">
-        <v>5281</v>
+        <v>5282</v>
       </c>
       <c r="F839" s="5" t="s">
         <v>5282</v>
       </c>
       <c r="G839" s="5" t="s">
-        <v>5283</v>
+        <v>5282</v>
       </c>
       <c r="H839" s="5" t="s">
-        <v>5284</v>
+        <v>5281</v>
       </c>
     </row>
     <row r="840">
       <c r="B840" s="6" t="s">
+        <v>5283</v>
+      </c>
+      <c r="C840" s="6" t="s">
+        <v>5284</v>
+      </c>
+      <c r="D840" s="6" t="s">
         <v>5285</v>
       </c>
-      <c r="C840" s="6" t="s">
+      <c r="E840" s="6" t="s">
         <v>5286</v>
       </c>
-      <c r="D840" s="6" t="s">
+      <c r="F840" s="6" t="s">
         <v>5287</v>
       </c>
-      <c r="E840" s="6" t="s">
+      <c r="G840" s="6" t="s">
         <v>5288</v>
       </c>
-      <c r="F840" s="6" t="s">
+      <c r="H840" s="6" t="s">
         <v>5289</v>
-      </c>
-      <c r="G840" s="6" t="s">
-        <v>5290</v>
-      </c>
-      <c r="H840" s="6" t="s">
-        <v>5291</v>
       </c>
     </row>
     <row r="841">
       <c r="B841" s="5" t="s">
+        <v>5290</v>
+      </c>
+      <c r="C841" s="5" t="s">
+        <v>5291</v>
+      </c>
+      <c r="D841" s="5" t="s">
         <v>5292</v>
       </c>
-      <c r="C841" s="5" t="s">
+      <c r="E841" s="5" t="s">
         <v>5293</v>
       </c>
-      <c r="D841" s="5" t="s">
+      <c r="F841" s="5" t="s">
         <v>5294</v>
       </c>
-      <c r="E841" s="5" t="s">
+      <c r="G841" s="5" t="s">
         <v>5295</v>
       </c>
-      <c r="F841" s="5" t="s">
+      <c r="H841" s="5" t="s">
         <v>5296</v>
-      </c>
-      <c r="G841" s="5" t="s">
-        <v>5297</v>
-      </c>
-      <c r="H841" s="5" t="s">
-        <v>5298</v>
       </c>
     </row>
     <row r="842">
       <c r="B842" s="6" t="s">
+        <v>5297</v>
+      </c>
+      <c r="C842" s="6" t="s">
+        <v>5298</v>
+      </c>
+      <c r="D842" s="6" t="s">
         <v>5299</v>
       </c>
-      <c r="C842" s="6" t="s">
+      <c r="E842" s="6" t="s">
         <v>5300</v>
       </c>
-      <c r="D842" s="6" t="s">
+      <c r="F842" s="6" t="s">
         <v>5301</v>
       </c>
-      <c r="E842" s="6" t="s">
+      <c r="G842" s="6" t="s">
         <v>5302</v>
       </c>
-      <c r="F842" s="6" t="s">
+      <c r="H842" s="6" t="s">
         <v>5303</v>
-      </c>
-      <c r="G842" s="6" t="s">
-        <v>5303</v>
-      </c>
-      <c r="H842" s="6" t="s">
-        <v>5304</v>
       </c>
     </row>
     <row r="843">
       <c r="B843" s="5" t="s">
+        <v>5304</v>
+      </c>
+      <c r="C843" s="5" t="s">
         <v>5305</v>
       </c>
-      <c r="C843" s="5" t="s">
+      <c r="D843" s="5" t="s">
+        <v>5281</v>
+      </c>
+      <c r="E843" s="5" t="s">
         <v>5306</v>
       </c>
-      <c r="D843" s="5" t="s">
+      <c r="F843" s="5" t="s">
         <v>5307</v>
       </c>
-      <c r="E843" s="5" t="s">
-        <v>5308</v>
-      </c>
-      <c r="F843" s="5" t="s">
-        <v>5309</v>
-      </c>
       <c r="G843" s="5" t="s">
-        <v>5310</v>
+        <v>5307</v>
       </c>
       <c r="H843" s="5" t="s">
-        <v>5311</v>
+        <v>5281</v>
       </c>
     </row>
     <row r="844">
       <c r="B844" s="6" t="s">
+        <v>5308</v>
+      </c>
+      <c r="C844" s="6" t="s">
+        <v>5309</v>
+      </c>
+      <c r="D844" s="6" t="s">
+        <v>5310</v>
+      </c>
+      <c r="E844" s="6" t="s">
+        <v>5311</v>
+      </c>
+      <c r="F844" s="6" t="s">
         <v>5312</v>
       </c>
-      <c r="C844" s="6" t="s">
+      <c r="G844" s="6" t="s">
         <v>5313</v>
       </c>
-      <c r="D844" s="6" t="s">
+      <c r="H844" s="6" t="s">
         <v>5314</v>
-      </c>
-      <c r="E844" s="6" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F844" s="6" t="s">
-        <v>5316</v>
-      </c>
-      <c r="G844" s="6" t="s">
-        <v>5316</v>
-      </c>
-      <c r="H844" s="6" t="s">
-        <v>5317</v>
       </c>
     </row>
     <row r="845">
       <c r="B845" s="5" t="s">
+        <v>5315</v>
+      </c>
+      <c r="C845" s="5" t="s">
+        <v>5316</v>
+      </c>
+      <c r="D845" s="5" t="s">
+        <v>5317</v>
+      </c>
+      <c r="E845" s="5" t="s">
         <v>5318</v>
       </c>
-      <c r="C845" s="5" t="s">
+      <c r="F845" s="5" t="s">
         <v>5319</v>
       </c>
-      <c r="D845" s="5" t="s">
+      <c r="G845" s="5" t="s">
         <v>5320</v>
       </c>
-      <c r="E845" s="5" t="s">
-        <v>5321</v>
-      </c>
-      <c r="F845" s="5" t="s">
-        <v>5322</v>
-      </c>
-      <c r="G845" s="5" t="s">
-        <v>5323</v>
-      </c>
       <c r="H845" s="5" t="s">
-        <v>5324</v>
+        <v>5317</v>
       </c>
     </row>
     <row r="846">
       <c r="B846" s="6" t="s">
+        <v>5321</v>
+      </c>
+      <c r="C846" s="6" t="s">
+        <v>5322</v>
+      </c>
+      <c r="D846" s="6" t="s">
+        <v>5323</v>
+      </c>
+      <c r="E846" s="6" t="s">
+        <v>5324</v>
+      </c>
+      <c r="F846" s="6" t="s">
         <v>5325</v>
       </c>
-      <c r="C846" s="6" t="s">
+      <c r="G846" s="6" t="s">
         <v>5326</v>
       </c>
-      <c r="D846" s="6" t="s">
+      <c r="H846" s="6" t="s">
         <v>5327</v>
-      </c>
-      <c r="E846" s="6" t="s">
-        <v>5328</v>
-      </c>
-      <c r="F846" s="6" t="s">
-        <v>5329</v>
-      </c>
-      <c r="G846" s="6" t="s">
-        <v>5330</v>
-      </c>
-      <c r="H846" s="6" t="s">
-        <v>5331</v>
       </c>
     </row>
     <row r="847">
       <c r="B847" s="5" t="s">
+        <v>5328</v>
+      </c>
+      <c r="C847" s="5" t="s">
+        <v>5329</v>
+      </c>
+      <c r="D847" s="5" t="s">
+        <v>5330</v>
+      </c>
+      <c r="E847" s="5" t="s">
+        <v>5331</v>
+      </c>
+      <c r="F847" s="5" t="s">
         <v>5332</v>
       </c>
-      <c r="C847" s="5" t="s">
+      <c r="G847" s="5" t="s">
         <v>5333</v>
       </c>
-      <c r="D847" s="5" t="s">
+      <c r="H847" s="5" t="s">
         <v>5334</v>
-      </c>
-      <c r="E847" s="5" t="s">
-        <v>5335</v>
-      </c>
-      <c r="F847" s="5" t="s">
-        <v>5336</v>
-      </c>
-      <c r="G847" s="5" t="s">
-        <v>5335</v>
-      </c>
-      <c r="H847" s="5" t="s">
-        <v>5337</v>
       </c>
     </row>
     <row r="848">
       <c r="B848" s="6" t="s">
+        <v>5335</v>
+      </c>
+      <c r="C848" s="6" t="s">
+        <v>5336</v>
+      </c>
+      <c r="D848" s="6" t="s">
+        <v>5337</v>
+      </c>
+      <c r="E848" s="6" t="s">
         <v>5338</v>
       </c>
-      <c r="C848" s="6" t="s">
+      <c r="F848" s="6" t="s">
         <v>5339</v>
       </c>
-      <c r="D848" s="6" t="s">
+      <c r="G848" s="6" t="s">
         <v>5340</v>
       </c>
-      <c r="E848" s="6" t="s">
+      <c r="H848" s="6" t="s">
         <v>5341</v>
-      </c>
-      <c r="F848" s="6" t="s">
-        <v>5342</v>
-      </c>
-      <c r="G848" s="6" t="s">
-        <v>5342</v>
-      </c>
-      <c r="H848" s="6" t="s">
-        <v>5340</v>
       </c>
     </row>
     <row r="849">
       <c r="B849" s="5" t="s">
+        <v>5342</v>
+      </c>
+      <c r="C849" s="5" t="s">
         <v>5343</v>
       </c>
-      <c r="C849" s="5" t="s">
+      <c r="D849" s="5" t="s">
         <v>5344</v>
       </c>
-      <c r="D849" s="5" t="s">
+      <c r="E849" s="5" t="s">
         <v>5345</v>
       </c>
-      <c r="E849" s="5" t="s">
+      <c r="F849" s="5" t="s">
         <v>5346</v>
       </c>
-      <c r="F849" s="5" t="s">
+      <c r="G849" s="5" t="s">
         <v>5347</v>
       </c>
-      <c r="G849" s="5" t="s">
+      <c r="H849" s="5" t="s">
         <v>5348</v>
-      </c>
-      <c r="H849" s="5" t="s">
-        <v>5349</v>
       </c>
     </row>
     <row r="850">
       <c r="B850" s="6" t="s">
+        <v>5349</v>
+      </c>
+      <c r="C850" s="6" t="s">
         <v>5350</v>
       </c>
-      <c r="C850" s="6" t="s">
+      <c r="D850" s="6" t="s">
         <v>5351</v>
       </c>
-      <c r="D850" s="6" t="s">
+      <c r="E850" s="6" t="s">
         <v>5352</v>
       </c>
-      <c r="E850" s="6" t="s">
+      <c r="F850" s="6" t="s">
         <v>5353</v>
       </c>
-      <c r="F850" s="6" t="s">
+      <c r="G850" s="6" t="s">
+        <v>5353</v>
+      </c>
+      <c r="H850" s="6" t="s">
         <v>5354</v>
-      </c>
-      <c r="G850" s="6" t="s">
-        <v>5355</v>
-      </c>
-      <c r="H850" s="6" t="s">
-        <v>5352</v>
       </c>
     </row>
     <row r="851">
       <c r="B851" s="5" t="s">
+        <v>5355</v>
+      </c>
+      <c r="C851" s="5" t="s">
         <v>5356</v>
       </c>
-      <c r="C851" s="5" t="s">
+      <c r="D851" s="5" t="s">
         <v>5357</v>
       </c>
-      <c r="D851" s="5" t="s">
+      <c r="E851" s="5" t="s">
         <v>5358</v>
       </c>
-      <c r="E851" s="5" t="s">
+      <c r="F851" s="5" t="s">
         <v>5359</v>
       </c>
-      <c r="F851" s="5" t="s">
+      <c r="G851" s="5" t="s">
         <v>5360</v>
       </c>
-      <c r="G851" s="5" t="s">
+      <c r="H851" s="5" t="s">
         <v>5361</v>
-      </c>
-      <c r="H851" s="5" t="s">
-        <v>5362</v>
       </c>
     </row>
     <row r="852">
       <c r="B852" s="6" t="s">
+        <v>5362</v>
+      </c>
+      <c r="C852" s="6" t="s">
         <v>5363</v>
       </c>
-      <c r="C852" s="6" t="s">
+      <c r="D852" s="6" t="s">
         <v>5364</v>
       </c>
-      <c r="D852" s="6" t="s">
+      <c r="E852" s="6" t="s">
         <v>5365</v>
       </c>
-      <c r="E852" s="6" t="s">
+      <c r="F852" s="6" t="s">
         <v>5366</v>
       </c>
-      <c r="F852" s="6" t="s">
+      <c r="G852" s="6" t="s">
+        <v>5366</v>
+      </c>
+      <c r="H852" s="6" t="s">
         <v>5367</v>
-      </c>
-      <c r="G852" s="6" t="s">
-        <v>5367</v>
-      </c>
-      <c r="H852" s="6" t="s">
-        <v>5368</v>
       </c>
     </row>
     <row r="853">
       <c r="B853" s="5" t="s">
+        <v>5368</v>
+      </c>
+      <c r="C853" s="5" t="s">
         <v>5369</v>
       </c>
-      <c r="C853" s="5" t="s">
+      <c r="D853" s="5" t="s">
         <v>5370</v>
       </c>
-      <c r="D853" s="5" t="s">
+      <c r="E853" s="5" t="s">
         <v>5371</v>
       </c>
-      <c r="E853" s="5" t="s">
+      <c r="F853" s="5" t="s">
         <v>5372</v>
-      </c>
-      <c r="F853" s="5" t="s">
-        <v>5373</v>
       </c>
       <c r="G853" s="5" t="s">
         <v>5373</v>
@@ -36464,7 +36614,7 @@
         <v>5386</v>
       </c>
       <c r="G855" s="5" t="s">
-        <v>5386</v>
+        <v>5385</v>
       </c>
       <c r="H855" s="5" t="s">
         <v>5387</v>
@@ -36487,283 +36637,283 @@
         <v>5392</v>
       </c>
       <c r="G856" s="6" t="s">
-        <v>5393</v>
+        <v>5392</v>
       </c>
       <c r="H856" s="6" t="s">
-        <v>5394</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="857">
       <c r="B857" s="5" t="s">
+        <v>5393</v>
+      </c>
+      <c r="C857" s="5" t="s">
+        <v>5394</v>
+      </c>
+      <c r="D857" s="5" t="s">
         <v>5395</v>
       </c>
-      <c r="C857" s="5" t="s">
+      <c r="E857" s="5" t="s">
         <v>5396</v>
       </c>
-      <c r="D857" s="5" t="s">
+      <c r="F857" s="5" t="s">
         <v>5397</v>
       </c>
-      <c r="E857" s="5" t="s">
+      <c r="G857" s="5" t="s">
         <v>5398</v>
       </c>
-      <c r="F857" s="5" t="s">
+      <c r="H857" s="5" t="s">
         <v>5399</v>
-      </c>
-      <c r="G857" s="5" t="s">
-        <v>5399</v>
-      </c>
-      <c r="H857" s="5" t="s">
-        <v>5400</v>
       </c>
     </row>
     <row r="858">
       <c r="B858" s="6" t="s">
+        <v>5400</v>
+      </c>
+      <c r="C858" s="6" t="s">
         <v>5401</v>
       </c>
-      <c r="C858" s="6" t="s">
+      <c r="D858" s="6" t="s">
         <v>5402</v>
       </c>
-      <c r="D858" s="6" t="s">
+      <c r="E858" s="6" t="s">
         <v>5403</v>
       </c>
-      <c r="E858" s="6" t="s">
+      <c r="F858" s="6" t="s">
         <v>5404</v>
-      </c>
-      <c r="F858" s="6" t="s">
-        <v>5405</v>
       </c>
       <c r="G858" s="6" t="s">
         <v>5405</v>
       </c>
       <c r="H858" s="6" t="s">
-        <v>5406</v>
+        <v>5402</v>
       </c>
     </row>
     <row r="859">
       <c r="B859" s="5" t="s">
+        <v>5406</v>
+      </c>
+      <c r="C859" s="5" t="s">
         <v>5407</v>
-      </c>
-      <c r="C859" s="5" t="s">
-        <v>5408</v>
       </c>
       <c r="D859" s="5" t="s">
         <v>5408</v>
       </c>
       <c r="E859" s="5" t="s">
-        <v>5408</v>
+        <v>5409</v>
       </c>
       <c r="F859" s="5" t="s">
-        <v>5408</v>
+        <v>5410</v>
       </c>
       <c r="G859" s="5" t="s">
-        <v>5408</v>
+        <v>5411</v>
       </c>
       <c r="H859" s="5" t="s">
-        <v>5408</v>
+        <v>5412</v>
       </c>
     </row>
     <row r="860">
       <c r="B860" s="6" t="s">
-        <v>5409</v>
+        <v>5413</v>
       </c>
       <c r="C860" s="6" t="s">
-        <v>5410</v>
+        <v>5414</v>
       </c>
       <c r="D860" s="6" t="s">
-        <v>5411</v>
+        <v>5415</v>
       </c>
       <c r="E860" s="6" t="s">
-        <v>5412</v>
+        <v>5416</v>
       </c>
       <c r="F860" s="6" t="s">
-        <v>5413</v>
+        <v>5417</v>
       </c>
       <c r="G860" s="6" t="s">
-        <v>5413</v>
+        <v>5417</v>
       </c>
       <c r="H860" s="6" t="s">
-        <v>5411</v>
+        <v>5418</v>
       </c>
     </row>
     <row r="861">
       <c r="B861" s="5" t="s">
-        <v>5414</v>
+        <v>5419</v>
       </c>
       <c r="C861" s="5" t="s">
-        <v>5415</v>
+        <v>5420</v>
       </c>
       <c r="D861" s="5" t="s">
-        <v>5416</v>
+        <v>5421</v>
       </c>
       <c r="E861" s="5" t="s">
-        <v>5417</v>
+        <v>5422</v>
       </c>
       <c r="F861" s="5" t="s">
-        <v>5418</v>
+        <v>5423</v>
       </c>
       <c r="G861" s="5" t="s">
-        <v>5419</v>
+        <v>5423</v>
       </c>
       <c r="H861" s="5" t="s">
-        <v>5416</v>
+        <v>5424</v>
       </c>
     </row>
     <row r="862">
       <c r="B862" s="6" t="s">
-        <v>5420</v>
+        <v>5425</v>
       </c>
       <c r="C862" s="6" t="s">
-        <v>5421</v>
+        <v>5426</v>
       </c>
       <c r="D862" s="6" t="s">
-        <v>5422</v>
+        <v>5427</v>
       </c>
       <c r="E862" s="6" t="s">
-        <v>5423</v>
+        <v>5428</v>
       </c>
       <c r="F862" s="6" t="s">
-        <v>5423</v>
+        <v>5429</v>
       </c>
       <c r="G862" s="6" t="s">
-        <v>5423</v>
+        <v>5430</v>
       </c>
       <c r="H862" s="6" t="s">
-        <v>5422</v>
+        <v>5431</v>
       </c>
     </row>
     <row r="863">
       <c r="B863" s="5" t="s">
-        <v>5424</v>
+        <v>5432</v>
       </c>
       <c r="C863" s="5" t="s">
-        <v>5425</v>
+        <v>5433</v>
       </c>
       <c r="D863" s="5" t="s">
-        <v>5426</v>
+        <v>5434</v>
       </c>
       <c r="E863" s="5" t="s">
-        <v>5427</v>
+        <v>5435</v>
       </c>
       <c r="F863" s="5" t="s">
-        <v>5427</v>
+        <v>5436</v>
       </c>
       <c r="G863" s="5" t="s">
-        <v>5427</v>
+        <v>5436</v>
       </c>
       <c r="H863" s="5" t="s">
-        <v>5426</v>
+        <v>5437</v>
       </c>
     </row>
     <row r="864">
       <c r="B864" s="6" t="s">
-        <v>5428</v>
+        <v>5438</v>
       </c>
       <c r="C864" s="6" t="s">
-        <v>5429</v>
+        <v>5439</v>
       </c>
       <c r="D864" s="6" t="s">
-        <v>5430</v>
+        <v>5440</v>
       </c>
       <c r="E864" s="6" t="s">
-        <v>5431</v>
+        <v>5441</v>
       </c>
       <c r="F864" s="6" t="s">
-        <v>5432</v>
+        <v>5442</v>
       </c>
       <c r="G864" s="6" t="s">
-        <v>5433</v>
+        <v>5443</v>
       </c>
       <c r="H864" s="6" t="s">
-        <v>5434</v>
+        <v>5444</v>
       </c>
     </row>
     <row r="865">
       <c r="B865" s="5" t="s">
-        <v>5435</v>
+        <v>5445</v>
       </c>
       <c r="C865" s="5" t="s">
-        <v>5436</v>
+        <v>5446</v>
       </c>
       <c r="D865" s="5" t="s">
-        <v>5437</v>
+        <v>5447</v>
       </c>
       <c r="E865" s="5" t="s">
-        <v>5438</v>
+        <v>5448</v>
       </c>
       <c r="F865" s="5" t="s">
-        <v>5439</v>
+        <v>5449</v>
       </c>
       <c r="G865" s="5" t="s">
-        <v>5440</v>
+        <v>5449</v>
       </c>
       <c r="H865" s="5" t="s">
-        <v>5437</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="866">
       <c r="B866" s="6" t="s">
-        <v>5441</v>
+        <v>5451</v>
       </c>
       <c r="C866" s="6" t="s">
-        <v>5442</v>
+        <v>5452</v>
       </c>
       <c r="D866" s="6" t="s">
-        <v>5443</v>
+        <v>5453</v>
       </c>
       <c r="E866" s="6" t="s">
-        <v>5444</v>
+        <v>5454</v>
       </c>
       <c r="F866" s="6" t="s">
-        <v>5445</v>
+        <v>5455</v>
       </c>
       <c r="G866" s="6" t="s">
-        <v>5446</v>
+        <v>5455</v>
       </c>
       <c r="H866" s="6" t="s">
-        <v>5447</v>
+        <v>5456</v>
       </c>
     </row>
     <row r="867">
       <c r="B867" s="5" t="s">
-        <v>5448</v>
+        <v>5457</v>
       </c>
       <c r="C867" s="5" t="s">
-        <v>5449</v>
+        <v>5458</v>
       </c>
       <c r="D867" s="5" t="s">
-        <v>5450</v>
+        <v>5458</v>
       </c>
       <c r="E867" s="5" t="s">
-        <v>5451</v>
+        <v>5458</v>
       </c>
       <c r="F867" s="5" t="s">
-        <v>5452</v>
+        <v>5458</v>
       </c>
       <c r="G867" s="5" t="s">
-        <v>5453</v>
+        <v>5458</v>
       </c>
       <c r="H867" s="5" t="s">
-        <v>5454</v>
+        <v>5458</v>
       </c>
     </row>
     <row r="868">
       <c r="B868" s="6" t="s">
-        <v>5455</v>
+        <v>5459</v>
       </c>
       <c r="C868" s="6" t="s">
-        <v>5456</v>
+        <v>5460</v>
       </c>
       <c r="D868" s="6" t="s">
-        <v>5457</v>
+        <v>5461</v>
       </c>
       <c r="E868" s="6" t="s">
-        <v>5458</v>
+        <v>5462</v>
       </c>
       <c r="F868" s="6" t="s">
-        <v>5459</v>
+        <v>5463</v>
       </c>
       <c r="G868" s="6" t="s">
-        <v>5460</v>
+        <v>5463</v>
       </c>
       <c r="H868" s="6" t="s">
         <v>5461</v>
@@ -36771,98 +36921,282 @@
     </row>
     <row r="869">
       <c r="B869" s="5" t="s">
-        <v>5462</v>
+        <v>5464</v>
       </c>
       <c r="C869" s="5" t="s">
-        <v>5463</v>
+        <v>5465</v>
       </c>
       <c r="D869" s="5" t="s">
-        <v>5464</v>
+        <v>5466</v>
       </c>
       <c r="E869" s="5" t="s">
-        <v>5465</v>
+        <v>5467</v>
       </c>
       <c r="F869" s="5" t="s">
+        <v>5468</v>
+      </c>
+      <c r="G869" s="5" t="s">
+        <v>5469</v>
+      </c>
+      <c r="H869" s="5" t="s">
         <v>5466</v>
-      </c>
-      <c r="G869" s="5" t="s">
-        <v>5467</v>
-      </c>
-      <c r="H869" s="5" t="s">
-        <v>5437</v>
       </c>
     </row>
     <row r="870">
       <c r="B870" s="6" t="s">
-        <v>5468</v>
+        <v>5470</v>
       </c>
       <c r="C870" s="6" t="s">
-        <v>5469</v>
+        <v>5471</v>
       </c>
       <c r="D870" s="6" t="s">
-        <v>5470</v>
+        <v>5472</v>
       </c>
       <c r="E870" s="6" t="s">
-        <v>5471</v>
+        <v>5473</v>
       </c>
       <c r="F870" s="6" t="s">
-        <v>5472</v>
+        <v>5473</v>
       </c>
       <c r="G870" s="6" t="s">
         <v>5473</v>
       </c>
       <c r="H870" s="6" t="s">
-        <v>5474</v>
+        <v>5472</v>
       </c>
     </row>
     <row r="871">
       <c r="B871" s="5" t="s">
+        <v>5474</v>
+      </c>
+      <c r="C871" s="5" t="s">
         <v>5475</v>
       </c>
-      <c r="C871" s="5" t="s">
+      <c r="D871" s="5" t="s">
         <v>5476</v>
       </c>
-      <c r="D871" s="5" t="s">
+      <c r="E871" s="5" t="s">
         <v>5477</v>
       </c>
-      <c r="E871" s="5" t="s">
-        <v>5478</v>
-      </c>
       <c r="F871" s="5" t="s">
-        <v>5479</v>
+        <v>5477</v>
       </c>
       <c r="G871" s="5" t="s">
-        <v>5479</v>
+        <v>5477</v>
       </c>
       <c r="H871" s="5" t="s">
-        <v>5480</v>
+        <v>5476</v>
       </c>
     </row>
     <row r="872">
       <c r="B872" s="6" t="s">
+        <v>5478</v>
+      </c>
+      <c r="C872" s="6" t="s">
+        <v>5479</v>
+      </c>
+      <c r="D872" s="6" t="s">
+        <v>5480</v>
+      </c>
+      <c r="E872" s="6" t="s">
         <v>5481</v>
       </c>
-      <c r="C872" s="6" t="s">
+      <c r="F872" s="6" t="s">
         <v>5482</v>
       </c>
-      <c r="D872" s="6" t="s">
+      <c r="G872" s="6" t="s">
         <v>5483</v>
       </c>
-      <c r="E872" s="6" t="s">
+      <c r="H872" s="6" t="s">
         <v>5484</v>
       </c>
-      <c r="F872" s="6" t="s">
+    </row>
+    <row r="873">
+      <c r="B873" s="5" t="s">
         <v>5485</v>
       </c>
-      <c r="G872" s="6" t="s">
+      <c r="C873" s="5" t="s">
         <v>5486</v>
       </c>
-      <c r="H872" s="6" t="s">
+      <c r="D873" s="5" t="s">
         <v>5487</v>
       </c>
+      <c r="E873" s="5" t="s">
+        <v>5488</v>
+      </c>
+      <c r="F873" s="5" t="s">
+        <v>5489</v>
+      </c>
+      <c r="G873" s="5" t="s">
+        <v>5490</v>
+      </c>
+      <c r="H873" s="5" t="s">
+        <v>5487</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="B874" s="6" t="s">
+        <v>5491</v>
+      </c>
+      <c r="C874" s="6" t="s">
+        <v>5492</v>
+      </c>
+      <c r="D874" s="6" t="s">
+        <v>5493</v>
+      </c>
+      <c r="E874" s="6" t="s">
+        <v>5494</v>
+      </c>
+      <c r="F874" s="6" t="s">
+        <v>5495</v>
+      </c>
+      <c r="G874" s="6" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H874" s="6" t="s">
+        <v>5497</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="B875" s="5" t="s">
+        <v>5498</v>
+      </c>
+      <c r="C875" s="5" t="s">
+        <v>5499</v>
+      </c>
+      <c r="D875" s="5" t="s">
+        <v>5500</v>
+      </c>
+      <c r="E875" s="5" t="s">
+        <v>5501</v>
+      </c>
+      <c r="F875" s="5" t="s">
+        <v>5502</v>
+      </c>
+      <c r="G875" s="5" t="s">
+        <v>5503</v>
+      </c>
+      <c r="H875" s="5" t="s">
+        <v>5504</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="B876" s="6" t="s">
+        <v>5505</v>
+      </c>
+      <c r="C876" s="6" t="s">
+        <v>5506</v>
+      </c>
+      <c r="D876" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="E876" s="6" t="s">
+        <v>5508</v>
+      </c>
+      <c r="F876" s="6" t="s">
+        <v>5509</v>
+      </c>
+      <c r="G876" s="6" t="s">
+        <v>5510</v>
+      </c>
+      <c r="H876" s="6" t="s">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="B877" s="5" t="s">
+        <v>5512</v>
+      </c>
+      <c r="C877" s="5" t="s">
+        <v>5513</v>
+      </c>
+      <c r="D877" s="5" t="s">
+        <v>5514</v>
+      </c>
+      <c r="E877" s="5" t="s">
+        <v>5515</v>
+      </c>
+      <c r="F877" s="5" t="s">
+        <v>5516</v>
+      </c>
+      <c r="G877" s="5" t="s">
+        <v>5517</v>
+      </c>
+      <c r="H877" s="5" t="s">
+        <v>5487</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="B878" s="6" t="s">
+        <v>5518</v>
+      </c>
+      <c r="C878" s="6" t="s">
+        <v>5519</v>
+      </c>
+      <c r="D878" s="6" t="s">
+        <v>5520</v>
+      </c>
+      <c r="E878" s="6" t="s">
+        <v>5521</v>
+      </c>
+      <c r="F878" s="6" t="s">
+        <v>5522</v>
+      </c>
+      <c r="G878" s="6" t="s">
+        <v>5523</v>
+      </c>
+      <c r="H878" s="6" t="s">
+        <v>5524</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="B879" s="5" t="s">
+        <v>5525</v>
+      </c>
+      <c r="C879" s="5" t="s">
+        <v>5526</v>
+      </c>
+      <c r="D879" s="5" t="s">
+        <v>5527</v>
+      </c>
+      <c r="E879" s="5" t="s">
+        <v>5528</v>
+      </c>
+      <c r="F879" s="5" t="s">
+        <v>5529</v>
+      </c>
+      <c r="G879" s="5" t="s">
+        <v>5529</v>
+      </c>
+      <c r="H879" s="5" t="s">
+        <v>5530</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="B880" s="6" t="s">
+        <v>5531</v>
+      </c>
+      <c r="C880" s="6" t="s">
+        <v>5532</v>
+      </c>
+      <c r="D880" s="6" t="s">
+        <v>5533</v>
+      </c>
+      <c r="E880" s="6" t="s">
+        <v>5534</v>
+      </c>
+      <c r="F880" s="6" t="s">
+        <v>5535</v>
+      </c>
+      <c r="G880" s="6" t="s">
+        <v>5536</v>
+      </c>
+      <c r="H880" s="6" t="s">
+        <v>5537</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H872"/>
+  <autoFilter ref="B2:H880"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36881,10 +37215,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5488</v>
+        <v>5538</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5489</v>
+        <v>5539</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -36895,16 +37229,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5490</v>
+        <v>5540</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5491</v>
+        <v>5541</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5492</v>
+        <v>5542</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5493</v>
+        <v>5543</v>
       </c>
     </row>
     <row r="3">
@@ -36912,16 +37246,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5494</v>
+        <v>5544</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5495</v>
+        <v>5545</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>5496</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="4">
@@ -36932,24 +37266,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5497</v>
+        <v>5547</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5498</v>
+        <v>5548</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>5499</v>
+        <v>5549</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>5500</v>
+        <v>5550</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2145</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5501</v>
+        <v>5551</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -36957,13 +37291,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>5502</v>
+        <v>5552</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2152</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5503</v>
+        <v>5553</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -36971,13 +37305,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>5504</v>
+        <v>5554</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2158</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5505</v>
+        <v>5555</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -36985,13 +37319,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>5506</v>
+        <v>5556</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>5507</v>
+        <v>5557</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -36999,13 +37333,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>5508</v>
+        <v>5558</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2171</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5509</v>
+        <v>5559</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -37013,13 +37347,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>5510</v>
+        <v>5560</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>5511</v>
+        <v>5561</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -37027,13 +37361,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>5512</v>
+        <v>5562</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>2184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5513</v>
+        <v>5563</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -37041,13 +37375,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>5514</v>
+        <v>5564</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>5515</v>
+        <v>5565</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -37055,13 +37389,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>5516</v>
+        <v>5566</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>2197</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5517</v>
+        <v>5567</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -37069,13 +37403,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>5518</v>
+        <v>5568</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2203</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5519</v>
+        <v>5569</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -37089,7 +37423,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5520</v>
+        <v>5570</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -37097,13 +37431,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>5521</v>
+        <v>5571</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2217</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5522</v>
+        <v>5572</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -37111,13 +37445,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>5523</v>
+        <v>5573</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>2224</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5524</v>
+        <v>5574</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -37125,13 +37459,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>5525</v>
+        <v>5575</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>5526</v>
+        <v>5576</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -37139,13 +37473,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>5527</v>
+        <v>5577</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>2237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5528</v>
+        <v>5578</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -37153,13 +37487,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>5529</v>
+        <v>5579</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2243</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>5530</v>
+        <v>5580</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -37167,13 +37501,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>5531</v>
+        <v>5581</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>2248</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5532</v>
+        <v>5582</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -37181,13 +37515,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>5533</v>
+        <v>5583</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>5534</v>
+        <v>5584</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -37195,13 +37529,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>5535</v>
+        <v>5585</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5536</v>
+        <v>5586</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -37209,13 +37543,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>5537</v>
+        <v>5587</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2263</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>5538</v>
+        <v>5588</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1230]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1239]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7273" uniqueCount="6639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7336" uniqueCount="6692">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -19781,6 +19781,165 @@
   </si>
   <si>
     <t xml:space="preserve">Wird abgerechnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.jokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小丑牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커 풀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker Pool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ジョーカープール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小丑牌池</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker-Pool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 150종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base 150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基本 150 種</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基础 150 种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基礎 150 種</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis 150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">확장 500종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拡張 500 種</t>
+  </si>
+  <si>
+    <t xml:space="preserve">扩展 500 种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">擴展 500 種</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alle 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{count}종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{count} jokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{count} 種</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{count} 种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{count} Joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{at} / {of} 쪽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{at} / {of}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.hint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드를 누르면 효과가 적힙니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap a card to read its effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カードを押すと効果が出ます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击卡牌查看效果。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">點擊卡牌查看效果。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tippe eine Karte an, um ihre Wirkung zu lesen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.baseNote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원작을 그대로 옮긴 150종입니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 150 jokers ported one to one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原作をそのまま移した 150 種です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原封不动移植的 150 种。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原封不動移植的 150 種。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die 150 eins zu eins übertragenen Joker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.allNote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자작 350종이 함께 나옵니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds 350 original jokers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自作 350 種が加わります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加入自制 350 种。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加入自製 350 種。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zusätzlich 350 eigene Joker.</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -20133,7 +20292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1230"/>
+  <dimension ref="A1:H1239"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -44195,8 +44354,215 @@
         <v>6587</v>
       </c>
     </row>
+    <row r="1231">
+      <c r="B1231" s="5" t="s">
+        <v>6588</v>
+      </c>
+      <c r="C1231" s="5" t="s">
+        <v>4660</v>
+      </c>
+      <c r="D1231" s="5" t="s">
+        <v>6589</v>
+      </c>
+      <c r="E1231" s="5" t="s">
+        <v>4662</v>
+      </c>
+      <c r="F1231" s="5" t="s">
+        <v>6590</v>
+      </c>
+      <c r="G1231" s="5" t="s">
+        <v>6590</v>
+      </c>
+      <c r="H1231" s="5" t="s">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="B1232" s="6" t="s">
+        <v>6591</v>
+      </c>
+      <c r="C1232" s="6" t="s">
+        <v>6592</v>
+      </c>
+      <c r="D1232" s="6" t="s">
+        <v>6593</v>
+      </c>
+      <c r="E1232" s="6" t="s">
+        <v>6594</v>
+      </c>
+      <c r="F1232" s="6" t="s">
+        <v>6595</v>
+      </c>
+      <c r="G1232" s="6" t="s">
+        <v>6595</v>
+      </c>
+      <c r="H1232" s="6" t="s">
+        <v>6596</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="B1233" s="5" t="s">
+        <v>6597</v>
+      </c>
+      <c r="C1233" s="5" t="s">
+        <v>6598</v>
+      </c>
+      <c r="D1233" s="5" t="s">
+        <v>6599</v>
+      </c>
+      <c r="E1233" s="5" t="s">
+        <v>6600</v>
+      </c>
+      <c r="F1233" s="5" t="s">
+        <v>6601</v>
+      </c>
+      <c r="G1233" s="5" t="s">
+        <v>6602</v>
+      </c>
+      <c r="H1233" s="5" t="s">
+        <v>6603</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="B1234" s="6" t="s">
+        <v>6604</v>
+      </c>
+      <c r="C1234" s="6" t="s">
+        <v>6605</v>
+      </c>
+      <c r="D1234" s="6" t="s">
+        <v>6606</v>
+      </c>
+      <c r="E1234" s="6" t="s">
+        <v>6607</v>
+      </c>
+      <c r="F1234" s="6" t="s">
+        <v>6608</v>
+      </c>
+      <c r="G1234" s="6" t="s">
+        <v>6609</v>
+      </c>
+      <c r="H1234" s="6" t="s">
+        <v>6610</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="B1235" s="5" t="s">
+        <v>6611</v>
+      </c>
+      <c r="C1235" s="5" t="s">
+        <v>6612</v>
+      </c>
+      <c r="D1235" s="5" t="s">
+        <v>6613</v>
+      </c>
+      <c r="E1235" s="5" t="s">
+        <v>6614</v>
+      </c>
+      <c r="F1235" s="5" t="s">
+        <v>6615</v>
+      </c>
+      <c r="G1235" s="5" t="s">
+        <v>6614</v>
+      </c>
+      <c r="H1235" s="5" t="s">
+        <v>6616</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="B1236" s="6" t="s">
+        <v>6617</v>
+      </c>
+      <c r="C1236" s="6" t="s">
+        <v>6618</v>
+      </c>
+      <c r="D1236" s="6" t="s">
+        <v>6619</v>
+      </c>
+      <c r="E1236" s="6" t="s">
+        <v>6619</v>
+      </c>
+      <c r="F1236" s="6" t="s">
+        <v>6619</v>
+      </c>
+      <c r="G1236" s="6" t="s">
+        <v>6619</v>
+      </c>
+      <c r="H1236" s="6" t="s">
+        <v>6619</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="B1237" s="5" t="s">
+        <v>6620</v>
+      </c>
+      <c r="C1237" s="5" t="s">
+        <v>6621</v>
+      </c>
+      <c r="D1237" s="5" t="s">
+        <v>6622</v>
+      </c>
+      <c r="E1237" s="5" t="s">
+        <v>6623</v>
+      </c>
+      <c r="F1237" s="5" t="s">
+        <v>6624</v>
+      </c>
+      <c r="G1237" s="5" t="s">
+        <v>6625</v>
+      </c>
+      <c r="H1237" s="5" t="s">
+        <v>6626</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="B1238" s="6" t="s">
+        <v>6627</v>
+      </c>
+      <c r="C1238" s="6" t="s">
+        <v>6628</v>
+      </c>
+      <c r="D1238" s="6" t="s">
+        <v>6629</v>
+      </c>
+      <c r="E1238" s="6" t="s">
+        <v>6630</v>
+      </c>
+      <c r="F1238" s="6" t="s">
+        <v>6631</v>
+      </c>
+      <c r="G1238" s="6" t="s">
+        <v>6632</v>
+      </c>
+      <c r="H1238" s="6" t="s">
+        <v>6633</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="B1239" s="5" t="s">
+        <v>6634</v>
+      </c>
+      <c r="C1239" s="5" t="s">
+        <v>6635</v>
+      </c>
+      <c r="D1239" s="5" t="s">
+        <v>6636</v>
+      </c>
+      <c r="E1239" s="5" t="s">
+        <v>6637</v>
+      </c>
+      <c r="F1239" s="5" t="s">
+        <v>6638</v>
+      </c>
+      <c r="G1239" s="5" t="s">
+        <v>6639</v>
+      </c>
+      <c r="H1239" s="5" t="s">
+        <v>6640</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H1230"/>
+  <autoFilter ref="B2:H1239"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -44215,10 +44581,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>6588</v>
+        <v>6641</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6589</v>
+        <v>6642</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -44229,16 +44595,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6590</v>
+        <v>6643</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>6591</v>
+        <v>6644</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6592</v>
+        <v>6645</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6593</v>
+        <v>6646</v>
       </c>
     </row>
     <row r="3">
@@ -44246,16 +44612,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6594</v>
+        <v>6647</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>6595</v>
+        <v>6648</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>6596</v>
+        <v>6649</v>
       </c>
     </row>
     <row r="4">
@@ -44266,24 +44632,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>6597</v>
+        <v>6650</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>6598</v>
+        <v>6651</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>6599</v>
+        <v>6652</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>6600</v>
+        <v>6653</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>3195</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>6601</v>
+        <v>6654</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -44291,13 +44657,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>6602</v>
+        <v>6655</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>3202</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>6603</v>
+        <v>6656</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -44305,13 +44671,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>6604</v>
+        <v>6657</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>3208</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>6605</v>
+        <v>6658</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -44319,13 +44685,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>6606</v>
+        <v>6659</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>3214</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>6607</v>
+        <v>6660</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -44333,13 +44699,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>6608</v>
+        <v>6661</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>3221</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>6609</v>
+        <v>6662</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -44347,13 +44713,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>6610</v>
+        <v>6663</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>3228</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>6611</v>
+        <v>6664</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -44361,13 +44727,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>6612</v>
+        <v>6665</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3234</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>6613</v>
+        <v>6666</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -44375,13 +44741,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>6614</v>
+        <v>6667</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>3240</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>6615</v>
+        <v>6668</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -44389,13 +44755,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>6616</v>
+        <v>6669</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>3247</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>6617</v>
+        <v>6670</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -44403,13 +44769,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>6618</v>
+        <v>6671</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>3253</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>6619</v>
+        <v>6672</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -44423,7 +44789,7 @@
         <v>3260</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>6620</v>
+        <v>6673</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -44431,13 +44797,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>6621</v>
+        <v>6674</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>3267</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>6622</v>
+        <v>6675</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -44445,13 +44811,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>6623</v>
+        <v>6676</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>3274</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>6624</v>
+        <v>6677</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -44459,13 +44825,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>6625</v>
+        <v>6678</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>3280</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>6626</v>
+        <v>6679</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -44473,13 +44839,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>6627</v>
+        <v>6680</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>3287</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>6628</v>
+        <v>6681</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -44487,13 +44853,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>6629</v>
+        <v>6682</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>3293</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>6630</v>
+        <v>6683</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -44501,13 +44867,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>6631</v>
+        <v>6684</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>3298</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>6632</v>
+        <v>6685</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -44515,13 +44881,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>6633</v>
+        <v>6686</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>3305</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>6634</v>
+        <v>6687</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -44529,13 +44895,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>6635</v>
+        <v>6688</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>3126</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>6636</v>
+        <v>6689</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -44543,13 +44909,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>6637</v>
+        <v>6690</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>3313</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>6638</v>
+        <v>6691</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1239]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1242]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8736" uniqueCount="7959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8757" uniqueCount="7976">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -23653,24 +23653,6 @@
     <t xml:space="preserve">Alle 500</t>
   </si>
   <si>
-    <t xml:space="preserve">ui.pool.count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{count}종</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{count} jokers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{count} 種</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{count} 种</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{count} Joker</t>
-  </si>
-  <si>
     <t xml:space="preserve">ui.pool.page</t>
   </si>
   <si>
@@ -23741,6 +23723,75 @@
   </si>
   <si>
     <t xml:space="preserve">Zusätzlich 350 eigene Joker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.sortOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">順</t>
+  </si>
+  <si>
+    <t xml:space="preserve">顺序</t>
+  </si>
+  <si>
+    <t xml:space="preserve">順序</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.sortRarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">희귀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.sortName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名前</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名稱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.pool.sortCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">価格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">价格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">價格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preis</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -24093,7 +24144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1239"/>
+  <dimension ref="A1:H1242"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -52458,112 +52509,181 @@
         <v>7880</v>
       </c>
       <c r="E1235" s="5" t="s">
-        <v>7881</v>
+        <v>7880</v>
       </c>
       <c r="F1235" s="5" t="s">
-        <v>7882</v>
+        <v>7880</v>
       </c>
       <c r="G1235" s="5" t="s">
-        <v>7881</v>
+        <v>7880</v>
       </c>
       <c r="H1235" s="5" t="s">
-        <v>7883</v>
+        <v>7880</v>
       </c>
     </row>
     <row r="1236">
       <c r="B1236" s="6" t="s">
+        <v>7881</v>
+      </c>
+      <c r="C1236" s="6" t="s">
+        <v>7882</v>
+      </c>
+      <c r="D1236" s="6" t="s">
+        <v>7883</v>
+      </c>
+      <c r="E1236" s="6" t="s">
         <v>7884</v>
       </c>
-      <c r="C1236" s="6" t="s">
+      <c r="F1236" s="6" t="s">
         <v>7885</v>
-      </c>
-      <c r="D1236" s="6" t="s">
-        <v>7886</v>
-      </c>
-      <c r="E1236" s="6" t="s">
-        <v>7886</v>
-      </c>
-      <c r="F1236" s="6" t="s">
-        <v>7886</v>
       </c>
       <c r="G1236" s="6" t="s">
         <v>7886</v>
       </c>
       <c r="H1236" s="6" t="s">
-        <v>7886</v>
+        <v>7887</v>
       </c>
     </row>
     <row r="1237">
       <c r="B1237" s="5" t="s">
-        <v>7887</v>
+        <v>7888</v>
       </c>
       <c r="C1237" s="5" t="s">
-        <v>7888</v>
+        <v>7889</v>
       </c>
       <c r="D1237" s="5" t="s">
-        <v>7889</v>
+        <v>7890</v>
       </c>
       <c r="E1237" s="5" t="s">
-        <v>7890</v>
+        <v>7891</v>
       </c>
       <c r="F1237" s="5" t="s">
-        <v>7891</v>
+        <v>7892</v>
       </c>
       <c r="G1237" s="5" t="s">
-        <v>7892</v>
+        <v>7893</v>
       </c>
       <c r="H1237" s="5" t="s">
-        <v>7893</v>
+        <v>7894</v>
       </c>
     </row>
     <row r="1238">
       <c r="B1238" s="6" t="s">
-        <v>7894</v>
+        <v>7895</v>
       </c>
       <c r="C1238" s="6" t="s">
-        <v>7895</v>
+        <v>7896</v>
       </c>
       <c r="D1238" s="6" t="s">
-        <v>7896</v>
+        <v>7897</v>
       </c>
       <c r="E1238" s="6" t="s">
-        <v>7897</v>
+        <v>7898</v>
       </c>
       <c r="F1238" s="6" t="s">
-        <v>7898</v>
+        <v>7899</v>
       </c>
       <c r="G1238" s="6" t="s">
-        <v>7899</v>
+        <v>7900</v>
       </c>
       <c r="H1238" s="6" t="s">
-        <v>7900</v>
+        <v>7901</v>
       </c>
     </row>
     <row r="1239">
       <c r="B1239" s="5" t="s">
-        <v>7901</v>
+        <v>7902</v>
       </c>
       <c r="C1239" s="5" t="s">
-        <v>7902</v>
+        <v>7903</v>
       </c>
       <c r="D1239" s="5" t="s">
-        <v>7903</v>
+        <v>7904</v>
       </c>
       <c r="E1239" s="5" t="s">
-        <v>7904</v>
+        <v>7905</v>
       </c>
       <c r="F1239" s="5" t="s">
-        <v>7905</v>
+        <v>7906</v>
       </c>
       <c r="G1239" s="5" t="s">
-        <v>7906</v>
+        <v>7907</v>
       </c>
       <c r="H1239" s="5" t="s">
-        <v>7907</v>
+        <v>7908</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="B1240" s="6" t="s">
+        <v>7909</v>
+      </c>
+      <c r="C1240" s="6" t="s">
+        <v>7910</v>
+      </c>
+      <c r="D1240" s="6" t="s">
+        <v>7911</v>
+      </c>
+      <c r="E1240" s="6" t="s">
+        <v>6139</v>
+      </c>
+      <c r="F1240" s="6" t="s">
+        <v>6140</v>
+      </c>
+      <c r="G1240" s="6" t="s">
+        <v>6140</v>
+      </c>
+      <c r="H1240" s="6" t="s">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="B1241" s="5" t="s">
+        <v>7912</v>
+      </c>
+      <c r="C1241" s="5" t="s">
+        <v>7913</v>
+      </c>
+      <c r="D1241" s="5" t="s">
+        <v>7914</v>
+      </c>
+      <c r="E1241" s="5" t="s">
+        <v>7915</v>
+      </c>
+      <c r="F1241" s="5" t="s">
+        <v>7916</v>
+      </c>
+      <c r="G1241" s="5" t="s">
+        <v>7917</v>
+      </c>
+      <c r="H1241" s="5" t="s">
+        <v>7914</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="B1242" s="6" t="s">
+        <v>7918</v>
+      </c>
+      <c r="C1242" s="6" t="s">
+        <v>7919</v>
+      </c>
+      <c r="D1242" s="6" t="s">
+        <v>7920</v>
+      </c>
+      <c r="E1242" s="6" t="s">
+        <v>7921</v>
+      </c>
+      <c r="F1242" s="6" t="s">
+        <v>7922</v>
+      </c>
+      <c r="G1242" s="6" t="s">
+        <v>7923</v>
+      </c>
+      <c r="H1242" s="6" t="s">
+        <v>7924</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H1239"/>
+  <autoFilter ref="B2:H1242"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -52582,10 +52702,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>7908</v>
+        <v>7925</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7909</v>
+        <v>7926</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -52596,16 +52716,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7910</v>
+        <v>7927</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7911</v>
+        <v>7928</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7912</v>
+        <v>7929</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>7913</v>
+        <v>7930</v>
       </c>
     </row>
     <row r="3">
@@ -52613,16 +52733,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7914</v>
+        <v>7931</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7915</v>
+        <v>7932</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>7916</v>
+        <v>7933</v>
       </c>
     </row>
     <row r="4">
@@ -52633,24 +52753,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7917</v>
+        <v>7934</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>7918</v>
+        <v>7935</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>7919</v>
+        <v>7936</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>7920</v>
+        <v>7937</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4463</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>7921</v>
+        <v>7938</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -52658,13 +52778,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>7922</v>
+        <v>7939</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4470</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7923</v>
+        <v>7940</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -52672,13 +52792,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>7924</v>
+        <v>7941</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4476</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>7925</v>
+        <v>7942</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -52686,13 +52806,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>7926</v>
+        <v>7943</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4482</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>7927</v>
+        <v>7944</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -52700,13 +52820,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>7928</v>
+        <v>7945</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4489</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>7929</v>
+        <v>7946</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -52714,13 +52834,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>7930</v>
+        <v>7947</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4496</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>7931</v>
+        <v>7948</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -52728,13 +52848,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>7932</v>
+        <v>7949</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4502</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>7933</v>
+        <v>7950</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -52742,13 +52862,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>7934</v>
+        <v>7951</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4508</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>7935</v>
+        <v>7952</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -52756,13 +52876,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>7936</v>
+        <v>7953</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4515</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>7937</v>
+        <v>7954</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -52770,13 +52890,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>7938</v>
+        <v>7955</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4521</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>7939</v>
+        <v>7956</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -52790,7 +52910,7 @@
         <v>4527</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>7940</v>
+        <v>7957</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -52798,13 +52918,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>7941</v>
+        <v>7958</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4534</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>7942</v>
+        <v>7959</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -52812,13 +52932,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>7943</v>
+        <v>7960</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4541</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>7944</v>
+        <v>7961</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -52826,13 +52946,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>7945</v>
+        <v>7962</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4547</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>7946</v>
+        <v>7963</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -52840,13 +52960,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>7947</v>
+        <v>7964</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4554</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>7948</v>
+        <v>7965</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -52854,13 +52974,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>7949</v>
+        <v>7966</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4560</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>7950</v>
+        <v>7967</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -52868,13 +52988,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>7951</v>
+        <v>7968</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4565</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>7952</v>
+        <v>7969</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -52882,13 +53002,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>7953</v>
+        <v>7970</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4572</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>7954</v>
+        <v>7971</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -52896,13 +53016,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>7955</v>
+        <v>7972</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4394</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>7956</v>
+        <v>7973</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -52910,13 +53030,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>7957</v>
+        <v>7974</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4580</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>7958</v>
+        <v>7975</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8757" uniqueCount="7976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8757" uniqueCount="7975">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -23665,22 +23665,19 @@
     <t xml:space="preserve">ui.pool.hint</t>
   </si>
   <si>
-    <t xml:space="preserve">카드를 누르면 효과가 적힙니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tap a card to read its effect.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カードを押すと効果が出ます。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">点击卡牌查看效果。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">點擊卡牌查看效果。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tippe eine Karte an, um ihre Wirkung zu lesen.</t>
+    <t xml:space="preserve">카드를 가리키면 효과가 뜹니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point at a card to see its effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カードを指すと効果が出ます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">指向卡牌查看效果。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeige auf eine Karte, um ihre Wirkung zu sehen.</t>
   </si>
   <si>
     <t xml:space="preserve">ui.pool.baseNote</t>
@@ -52538,90 +52535,90 @@
         <v>7885</v>
       </c>
       <c r="G1236" s="6" t="s">
+        <v>7885</v>
+      </c>
+      <c r="H1236" s="6" t="s">
         <v>7886</v>
-      </c>
-      <c r="H1236" s="6" t="s">
-        <v>7887</v>
       </c>
     </row>
     <row r="1237">
       <c r="B1237" s="5" t="s">
+        <v>7887</v>
+      </c>
+      <c r="C1237" s="5" t="s">
         <v>7888</v>
       </c>
-      <c r="C1237" s="5" t="s">
+      <c r="D1237" s="5" t="s">
         <v>7889</v>
       </c>
-      <c r="D1237" s="5" t="s">
+      <c r="E1237" s="5" t="s">
         <v>7890</v>
       </c>
-      <c r="E1237" s="5" t="s">
+      <c r="F1237" s="5" t="s">
         <v>7891</v>
       </c>
-      <c r="F1237" s="5" t="s">
+      <c r="G1237" s="5" t="s">
         <v>7892</v>
       </c>
-      <c r="G1237" s="5" t="s">
+      <c r="H1237" s="5" t="s">
         <v>7893</v>
-      </c>
-      <c r="H1237" s="5" t="s">
-        <v>7894</v>
       </c>
     </row>
     <row r="1238">
       <c r="B1238" s="6" t="s">
+        <v>7894</v>
+      </c>
+      <c r="C1238" s="6" t="s">
         <v>7895</v>
       </c>
-      <c r="C1238" s="6" t="s">
+      <c r="D1238" s="6" t="s">
         <v>7896</v>
       </c>
-      <c r="D1238" s="6" t="s">
+      <c r="E1238" s="6" t="s">
         <v>7897</v>
       </c>
-      <c r="E1238" s="6" t="s">
+      <c r="F1238" s="6" t="s">
         <v>7898</v>
       </c>
-      <c r="F1238" s="6" t="s">
+      <c r="G1238" s="6" t="s">
         <v>7899</v>
       </c>
-      <c r="G1238" s="6" t="s">
+      <c r="H1238" s="6" t="s">
         <v>7900</v>
-      </c>
-      <c r="H1238" s="6" t="s">
-        <v>7901</v>
       </c>
     </row>
     <row r="1239">
       <c r="B1239" s="5" t="s">
+        <v>7901</v>
+      </c>
+      <c r="C1239" s="5" t="s">
         <v>7902</v>
       </c>
-      <c r="C1239" s="5" t="s">
+      <c r="D1239" s="5" t="s">
         <v>7903</v>
       </c>
-      <c r="D1239" s="5" t="s">
+      <c r="E1239" s="5" t="s">
         <v>7904</v>
       </c>
-      <c r="E1239" s="5" t="s">
+      <c r="F1239" s="5" t="s">
         <v>7905</v>
       </c>
-      <c r="F1239" s="5" t="s">
+      <c r="G1239" s="5" t="s">
         <v>7906</v>
       </c>
-      <c r="G1239" s="5" t="s">
+      <c r="H1239" s="5" t="s">
         <v>7907</v>
-      </c>
-      <c r="H1239" s="5" t="s">
-        <v>7908</v>
       </c>
     </row>
     <row r="1240">
       <c r="B1240" s="6" t="s">
+        <v>7908</v>
+      </c>
+      <c r="C1240" s="6" t="s">
         <v>7909</v>
       </c>
-      <c r="C1240" s="6" t="s">
+      <c r="D1240" s="6" t="s">
         <v>7910</v>
-      </c>
-      <c r="D1240" s="6" t="s">
-        <v>7911</v>
       </c>
       <c r="E1240" s="6" t="s">
         <v>6139</v>
@@ -52638,48 +52635,48 @@
     </row>
     <row r="1241">
       <c r="B1241" s="5" t="s">
+        <v>7911</v>
+      </c>
+      <c r="C1241" s="5" t="s">
         <v>7912</v>
       </c>
-      <c r="C1241" s="5" t="s">
+      <c r="D1241" s="5" t="s">
         <v>7913</v>
       </c>
-      <c r="D1241" s="5" t="s">
+      <c r="E1241" s="5" t="s">
         <v>7914</v>
       </c>
-      <c r="E1241" s="5" t="s">
+      <c r="F1241" s="5" t="s">
         <v>7915</v>
       </c>
-      <c r="F1241" s="5" t="s">
+      <c r="G1241" s="5" t="s">
         <v>7916</v>
       </c>
-      <c r="G1241" s="5" t="s">
-        <v>7917</v>
-      </c>
       <c r="H1241" s="5" t="s">
-        <v>7914</v>
+        <v>7913</v>
       </c>
     </row>
     <row r="1242">
       <c r="B1242" s="6" t="s">
+        <v>7917</v>
+      </c>
+      <c r="C1242" s="6" t="s">
         <v>7918</v>
       </c>
-      <c r="C1242" s="6" t="s">
+      <c r="D1242" s="6" t="s">
         <v>7919</v>
       </c>
-      <c r="D1242" s="6" t="s">
+      <c r="E1242" s="6" t="s">
         <v>7920</v>
       </c>
-      <c r="E1242" s="6" t="s">
+      <c r="F1242" s="6" t="s">
         <v>7921</v>
       </c>
-      <c r="F1242" s="6" t="s">
+      <c r="G1242" s="6" t="s">
         <v>7922</v>
       </c>
-      <c r="G1242" s="6" t="s">
+      <c r="H1242" s="6" t="s">
         <v>7923</v>
-      </c>
-      <c r="H1242" s="6" t="s">
-        <v>7924</v>
       </c>
     </row>
   </sheetData>
@@ -52702,10 +52699,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>7924</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7925</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>7926</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -52716,16 +52713,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>7926</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>7927</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>7928</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>7929</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>7930</v>
       </c>
     </row>
     <row r="3">
@@ -52733,16 +52730,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>7930</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7931</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7932</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>7933</v>
+        <v>7932</v>
       </c>
     </row>
     <row r="4">
@@ -52753,24 +52750,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>7933</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>7934</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>7935</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>7936</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>7937</v>
+        <v>7936</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4463</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>7938</v>
+        <v>7937</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -52778,13 +52775,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>7939</v>
+        <v>7938</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4470</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7940</v>
+        <v>7939</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -52792,13 +52789,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>7941</v>
+        <v>7940</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4476</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>7942</v>
+        <v>7941</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -52806,13 +52803,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>7943</v>
+        <v>7942</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4482</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>7944</v>
+        <v>7943</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -52820,13 +52817,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>7945</v>
+        <v>7944</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4489</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>7946</v>
+        <v>7945</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -52834,13 +52831,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>7947</v>
+        <v>7946</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4496</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>7948</v>
+        <v>7947</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -52848,13 +52845,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>7949</v>
+        <v>7948</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4502</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>7950</v>
+        <v>7949</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -52862,13 +52859,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>7951</v>
+        <v>7950</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4508</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>7952</v>
+        <v>7951</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -52876,13 +52873,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>7953</v>
+        <v>7952</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4515</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>7954</v>
+        <v>7953</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -52890,13 +52887,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>7955</v>
+        <v>7954</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4521</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>7956</v>
+        <v>7955</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -52910,7 +52907,7 @@
         <v>4527</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>7957</v>
+        <v>7956</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -52918,13 +52915,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>7958</v>
+        <v>7957</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4534</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>7959</v>
+        <v>7958</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -52932,13 +52929,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>7960</v>
+        <v>7959</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4541</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -52946,13 +52943,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4547</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>7963</v>
+        <v>7962</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -52960,13 +52957,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>7964</v>
+        <v>7963</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4554</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>7965</v>
+        <v>7964</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -52974,13 +52971,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>7966</v>
+        <v>7965</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4560</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>7967</v>
+        <v>7966</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -52988,13 +52985,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>7968</v>
+        <v>7967</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4565</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>7969</v>
+        <v>7968</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -53002,13 +52999,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>7970</v>
+        <v>7969</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4572</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>7971</v>
+        <v>7970</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -53016,13 +53013,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>7972</v>
+        <v>7971</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4394</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>7973</v>
+        <v>7972</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -53030,13 +53027,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>7974</v>
+        <v>7973</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4580</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>7975</v>
+        <v>7974</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1242]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1262]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8757" uniqueCount="7975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8897" uniqueCount="8098">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -23789,6 +23789,375 @@
   </si>
   <si>
     <t xml:space="preserve">Preis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.dry_season.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마른 철</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry Season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">枯れ季</t>
+  </si>
+  <si>
+    <t xml:space="preserve">旱季</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dürre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.face_town.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림 마을</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Court Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">絵札の町</t>
+  </si>
+  <si>
+    <t xml:space="preserve">花牌小镇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">花牌小鎮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilderstadt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.coin_ceiling.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">동전 천장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin Ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">硬貨の天井</t>
+  </si>
+  <si>
+    <t xml:space="preserve">硬币天花板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">硬幣天花板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Münzdecke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.shear_edge.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가위날</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shear Edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋏の刃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">剪刃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scherenschneide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.blind_draw.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엎어진 패</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blind Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">伏せ札</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暗抽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blindzug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.low_field.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낮은 들</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">低い野</t>
+  </si>
+  <si>
+    <t xml:space="preserve">低野</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiefes Feld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.heavy_purse.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무거운 지갑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Purse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">重い財布</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沉重钱袋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沉重錢袋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwere Geldbörse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.evergreen.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evergreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">常緑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">常绿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">常綠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immergrün</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.stone_court.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돌이 된 얼굴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone Court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">石の顔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">石面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steinhof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.red_wax.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">붉은 밀랍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Wax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤い蝋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">红蜡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紅蠟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotes Wachs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.sealed_fate.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">굳는 편성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sealed Fate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">固まる編成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besiegeltes Los</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.rising_price.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오르는 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rising Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上がる値</t>
+  </si>
+  <si>
+    <t xml:space="preserve">涨价</t>
+  </si>
+  <si>
+    <t xml:space="preserve">漲價</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steigender Preis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.vine_night.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덩굴의 밤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vine Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蔓の夜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藤夜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebennacht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.glass_field.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유리밭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">硝子畑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">玻璃田</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glasfeld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.stone_row.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돌의 줄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.sky_road.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하늘길</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sky Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">空の道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天路</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Himmelsweg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.five_leaves.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다섯 잎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five Leaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">五葉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">五叶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fünf Blätter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.single_thread.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한 올</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Thread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一筋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一线</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一線</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einzelner Faden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.barren_road.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메마른 길</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barren Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">枯れ道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">荒路</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karger Weg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge.bare_field.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">맨 밭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">裸の畑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">裸田</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacktes Feld</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -24141,7 +24510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1242"/>
+  <dimension ref="A1:H1262"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -52679,8 +53048,468 @@
         <v>7923</v>
       </c>
     </row>
+    <row r="1243">
+      <c r="B1243" s="5" t="s">
+        <v>7924</v>
+      </c>
+      <c r="C1243" s="5" t="s">
+        <v>7925</v>
+      </c>
+      <c r="D1243" s="5" t="s">
+        <v>7926</v>
+      </c>
+      <c r="E1243" s="5" t="s">
+        <v>7927</v>
+      </c>
+      <c r="F1243" s="5" t="s">
+        <v>7928</v>
+      </c>
+      <c r="G1243" s="5" t="s">
+        <v>7928</v>
+      </c>
+      <c r="H1243" s="5" t="s">
+        <v>7929</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="B1244" s="6" t="s">
+        <v>7930</v>
+      </c>
+      <c r="C1244" s="6" t="s">
+        <v>7931</v>
+      </c>
+      <c r="D1244" s="6" t="s">
+        <v>7932</v>
+      </c>
+      <c r="E1244" s="6" t="s">
+        <v>7933</v>
+      </c>
+      <c r="F1244" s="6" t="s">
+        <v>7934</v>
+      </c>
+      <c r="G1244" s="6" t="s">
+        <v>7935</v>
+      </c>
+      <c r="H1244" s="6" t="s">
+        <v>7936</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="B1245" s="5" t="s">
+        <v>7937</v>
+      </c>
+      <c r="C1245" s="5" t="s">
+        <v>7938</v>
+      </c>
+      <c r="D1245" s="5" t="s">
+        <v>7939</v>
+      </c>
+      <c r="E1245" s="5" t="s">
+        <v>7940</v>
+      </c>
+      <c r="F1245" s="5" t="s">
+        <v>7941</v>
+      </c>
+      <c r="G1245" s="5" t="s">
+        <v>7942</v>
+      </c>
+      <c r="H1245" s="5" t="s">
+        <v>7943</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="B1246" s="6" t="s">
+        <v>7944</v>
+      </c>
+      <c r="C1246" s="6" t="s">
+        <v>7945</v>
+      </c>
+      <c r="D1246" s="6" t="s">
+        <v>7946</v>
+      </c>
+      <c r="E1246" s="6" t="s">
+        <v>7947</v>
+      </c>
+      <c r="F1246" s="6" t="s">
+        <v>7948</v>
+      </c>
+      <c r="G1246" s="6" t="s">
+        <v>7948</v>
+      </c>
+      <c r="H1246" s="6" t="s">
+        <v>7949</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="B1247" s="5" t="s">
+        <v>7950</v>
+      </c>
+      <c r="C1247" s="5" t="s">
+        <v>7951</v>
+      </c>
+      <c r="D1247" s="5" t="s">
+        <v>7952</v>
+      </c>
+      <c r="E1247" s="5" t="s">
+        <v>7953</v>
+      </c>
+      <c r="F1247" s="5" t="s">
+        <v>7954</v>
+      </c>
+      <c r="G1247" s="5" t="s">
+        <v>7954</v>
+      </c>
+      <c r="H1247" s="5" t="s">
+        <v>7955</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="B1248" s="6" t="s">
+        <v>7956</v>
+      </c>
+      <c r="C1248" s="6" t="s">
+        <v>7957</v>
+      </c>
+      <c r="D1248" s="6" t="s">
+        <v>7958</v>
+      </c>
+      <c r="E1248" s="6" t="s">
+        <v>7959</v>
+      </c>
+      <c r="F1248" s="6" t="s">
+        <v>7960</v>
+      </c>
+      <c r="G1248" s="6" t="s">
+        <v>7960</v>
+      </c>
+      <c r="H1248" s="6" t="s">
+        <v>7961</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="B1249" s="5" t="s">
+        <v>7962</v>
+      </c>
+      <c r="C1249" s="5" t="s">
+        <v>7963</v>
+      </c>
+      <c r="D1249" s="5" t="s">
+        <v>7964</v>
+      </c>
+      <c r="E1249" s="5" t="s">
+        <v>7965</v>
+      </c>
+      <c r="F1249" s="5" t="s">
+        <v>7966</v>
+      </c>
+      <c r="G1249" s="5" t="s">
+        <v>7967</v>
+      </c>
+      <c r="H1249" s="5" t="s">
+        <v>7968</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="B1250" s="6" t="s">
+        <v>7969</v>
+      </c>
+      <c r="C1250" s="6" t="s">
+        <v>7970</v>
+      </c>
+      <c r="D1250" s="6" t="s">
+        <v>7971</v>
+      </c>
+      <c r="E1250" s="6" t="s">
+        <v>7972</v>
+      </c>
+      <c r="F1250" s="6" t="s">
+        <v>7973</v>
+      </c>
+      <c r="G1250" s="6" t="s">
+        <v>7974</v>
+      </c>
+      <c r="H1250" s="6" t="s">
+        <v>7975</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="B1251" s="5" t="s">
+        <v>7976</v>
+      </c>
+      <c r="C1251" s="5" t="s">
+        <v>7977</v>
+      </c>
+      <c r="D1251" s="5" t="s">
+        <v>7978</v>
+      </c>
+      <c r="E1251" s="5" t="s">
+        <v>7979</v>
+      </c>
+      <c r="F1251" s="5" t="s">
+        <v>7980</v>
+      </c>
+      <c r="G1251" s="5" t="s">
+        <v>7980</v>
+      </c>
+      <c r="H1251" s="5" t="s">
+        <v>7981</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="B1252" s="6" t="s">
+        <v>7982</v>
+      </c>
+      <c r="C1252" s="6" t="s">
+        <v>7983</v>
+      </c>
+      <c r="D1252" s="6" t="s">
+        <v>7984</v>
+      </c>
+      <c r="E1252" s="6" t="s">
+        <v>7985</v>
+      </c>
+      <c r="F1252" s="6" t="s">
+        <v>7986</v>
+      </c>
+      <c r="G1252" s="6" t="s">
+        <v>7987</v>
+      </c>
+      <c r="H1252" s="6" t="s">
+        <v>7988</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="B1253" s="5" t="s">
+        <v>7989</v>
+      </c>
+      <c r="C1253" s="5" t="s">
+        <v>7990</v>
+      </c>
+      <c r="D1253" s="5" t="s">
+        <v>7991</v>
+      </c>
+      <c r="E1253" s="5" t="s">
+        <v>7992</v>
+      </c>
+      <c r="F1253" s="5" t="s">
+        <v>7993</v>
+      </c>
+      <c r="G1253" s="5" t="s">
+        <v>7993</v>
+      </c>
+      <c r="H1253" s="5" t="s">
+        <v>7994</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="B1254" s="6" t="s">
+        <v>7995</v>
+      </c>
+      <c r="C1254" s="6" t="s">
+        <v>7996</v>
+      </c>
+      <c r="D1254" s="6" t="s">
+        <v>7997</v>
+      </c>
+      <c r="E1254" s="6" t="s">
+        <v>7998</v>
+      </c>
+      <c r="F1254" s="6" t="s">
+        <v>7999</v>
+      </c>
+      <c r="G1254" s="6" t="s">
+        <v>8000</v>
+      </c>
+      <c r="H1254" s="6" t="s">
+        <v>8001</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="B1255" s="5" t="s">
+        <v>8002</v>
+      </c>
+      <c r="C1255" s="5" t="s">
+        <v>8003</v>
+      </c>
+      <c r="D1255" s="5" t="s">
+        <v>8004</v>
+      </c>
+      <c r="E1255" s="5" t="s">
+        <v>8005</v>
+      </c>
+      <c r="F1255" s="5" t="s">
+        <v>8006</v>
+      </c>
+      <c r="G1255" s="5" t="s">
+        <v>8006</v>
+      </c>
+      <c r="H1255" s="5" t="s">
+        <v>8007</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="B1256" s="6" t="s">
+        <v>8008</v>
+      </c>
+      <c r="C1256" s="6" t="s">
+        <v>8009</v>
+      </c>
+      <c r="D1256" s="6" t="s">
+        <v>8010</v>
+      </c>
+      <c r="E1256" s="6" t="s">
+        <v>8011</v>
+      </c>
+      <c r="F1256" s="6" t="s">
+        <v>8012</v>
+      </c>
+      <c r="G1256" s="6" t="s">
+        <v>8012</v>
+      </c>
+      <c r="H1256" s="6" t="s">
+        <v>8013</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="B1257" s="5" t="s">
+        <v>8014</v>
+      </c>
+      <c r="C1257" s="5" t="s">
+        <v>8015</v>
+      </c>
+      <c r="D1257" s="5" t="s">
+        <v>2758</v>
+      </c>
+      <c r="E1257" s="5" t="s">
+        <v>2759</v>
+      </c>
+      <c r="F1257" s="5" t="s">
+        <v>2760</v>
+      </c>
+      <c r="G1257" s="5" t="s">
+        <v>2760</v>
+      </c>
+      <c r="H1257" s="5" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="B1258" s="6" t="s">
+        <v>8016</v>
+      </c>
+      <c r="C1258" s="6" t="s">
+        <v>8017</v>
+      </c>
+      <c r="D1258" s="6" t="s">
+        <v>8018</v>
+      </c>
+      <c r="E1258" s="6" t="s">
+        <v>8019</v>
+      </c>
+      <c r="F1258" s="6" t="s">
+        <v>8020</v>
+      </c>
+      <c r="G1258" s="6" t="s">
+        <v>8020</v>
+      </c>
+      <c r="H1258" s="6" t="s">
+        <v>8021</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="B1259" s="5" t="s">
+        <v>8022</v>
+      </c>
+      <c r="C1259" s="5" t="s">
+        <v>8023</v>
+      </c>
+      <c r="D1259" s="5" t="s">
+        <v>8024</v>
+      </c>
+      <c r="E1259" s="5" t="s">
+        <v>8025</v>
+      </c>
+      <c r="F1259" s="5" t="s">
+        <v>8026</v>
+      </c>
+      <c r="G1259" s="5" t="s">
+        <v>8025</v>
+      </c>
+      <c r="H1259" s="5" t="s">
+        <v>8027</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="B1260" s="6" t="s">
+        <v>8028</v>
+      </c>
+      <c r="C1260" s="6" t="s">
+        <v>8029</v>
+      </c>
+      <c r="D1260" s="6" t="s">
+        <v>8030</v>
+      </c>
+      <c r="E1260" s="6" t="s">
+        <v>8031</v>
+      </c>
+      <c r="F1260" s="6" t="s">
+        <v>8032</v>
+      </c>
+      <c r="G1260" s="6" t="s">
+        <v>8033</v>
+      </c>
+      <c r="H1260" s="6" t="s">
+        <v>8034</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="B1261" s="5" t="s">
+        <v>8035</v>
+      </c>
+      <c r="C1261" s="5" t="s">
+        <v>8036</v>
+      </c>
+      <c r="D1261" s="5" t="s">
+        <v>8037</v>
+      </c>
+      <c r="E1261" s="5" t="s">
+        <v>8038</v>
+      </c>
+      <c r="F1261" s="5" t="s">
+        <v>8039</v>
+      </c>
+      <c r="G1261" s="5" t="s">
+        <v>8039</v>
+      </c>
+      <c r="H1261" s="5" t="s">
+        <v>8040</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="B1262" s="6" t="s">
+        <v>8041</v>
+      </c>
+      <c r="C1262" s="6" t="s">
+        <v>8042</v>
+      </c>
+      <c r="D1262" s="6" t="s">
+        <v>8043</v>
+      </c>
+      <c r="E1262" s="6" t="s">
+        <v>8044</v>
+      </c>
+      <c r="F1262" s="6" t="s">
+        <v>8045</v>
+      </c>
+      <c r="G1262" s="6" t="s">
+        <v>8045</v>
+      </c>
+      <c r="H1262" s="6" t="s">
+        <v>8046</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H1242"/>
+  <autoFilter ref="B2:H1262"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -52699,10 +53528,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>7924</v>
+        <v>8047</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7925</v>
+        <v>8048</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -52713,16 +53542,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7926</v>
+        <v>8049</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7927</v>
+        <v>8050</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7928</v>
+        <v>8051</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>7929</v>
+        <v>8052</v>
       </c>
     </row>
     <row r="3">
@@ -52730,16 +53559,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7930</v>
+        <v>8053</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7931</v>
+        <v>8054</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>7932</v>
+        <v>8055</v>
       </c>
     </row>
     <row r="4">
@@ -52750,24 +53579,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7933</v>
+        <v>8056</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>7934</v>
+        <v>8057</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>7935</v>
+        <v>8058</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>7936</v>
+        <v>8059</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4463</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>7937</v>
+        <v>8060</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -52775,13 +53604,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>7938</v>
+        <v>8061</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4470</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7939</v>
+        <v>8062</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -52789,13 +53618,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>7940</v>
+        <v>8063</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4476</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>7941</v>
+        <v>8064</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -52803,13 +53632,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>7942</v>
+        <v>8065</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4482</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>7943</v>
+        <v>8066</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -52817,13 +53646,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>7944</v>
+        <v>8067</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4489</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>7945</v>
+        <v>8068</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -52831,13 +53660,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>7946</v>
+        <v>8069</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4496</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>7947</v>
+        <v>8070</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -52845,13 +53674,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>7948</v>
+        <v>8071</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4502</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>7949</v>
+        <v>8072</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -52859,13 +53688,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>7950</v>
+        <v>8073</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4508</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>7951</v>
+        <v>8074</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -52873,13 +53702,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>7952</v>
+        <v>8075</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4515</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>7953</v>
+        <v>8076</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -52887,13 +53716,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>7954</v>
+        <v>8077</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4521</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>7955</v>
+        <v>8078</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -52907,7 +53736,7 @@
         <v>4527</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>7956</v>
+        <v>8079</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -52915,13 +53744,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>7957</v>
+        <v>8080</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4534</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>7958</v>
+        <v>8081</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -52929,13 +53758,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>7959</v>
+        <v>8082</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4541</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>7960</v>
+        <v>8083</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -52943,13 +53772,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>7961</v>
+        <v>8084</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4547</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>7962</v>
+        <v>8085</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -52957,13 +53786,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>7963</v>
+        <v>8086</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4554</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>7964</v>
+        <v>8087</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -52971,13 +53800,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>7965</v>
+        <v>8088</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4560</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>7966</v>
+        <v>8089</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -52985,13 +53814,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>7967</v>
+        <v>8090</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4565</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>7968</v>
+        <v>8091</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -52999,13 +53828,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>7969</v>
+        <v>8092</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4572</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>7970</v>
+        <v>8093</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -53013,13 +53842,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>7971</v>
+        <v>8094</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4394</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>7972</v>
+        <v>8095</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -53027,13 +53856,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>7973</v>
+        <v>8096</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4580</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>7974</v>
+        <v>8097</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1262]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1307]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8897" uniqueCount="8098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9212" uniqueCount="8360">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -15850,22 +15850,22 @@
     <t xml:space="preserve">phrase.op.OpGrant</t>
   </si>
   <si>
-    <t xml:space="preserve">{create}를 {count}개 가지고 시작합니다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start with {count} {create}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{create}を {count} 個持って始めます</t>
-  </si>
-  <si>
-    <t xml:space="preserve">开局带有 {count} 个{create}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">開局帶有 {count} 個{create}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beginnt mit {count} {create}</t>
+    <t xml:space="preserve">{create} 「{name}」 {count}개를 가지고 시작합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start with {count}× {create} "{name}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{create}「{name}」を{count}個持って始めます</t>
+  </si>
+  <si>
+    <t xml:space="preserve">携带{count}个{create}「{name}」开局</t>
+  </si>
+  <si>
+    <t xml:space="preserve">攜帶{count}個{create}「{name}」開局</t>
+  </si>
+  <si>
+    <t xml:space="preserve">startet mit {count}× {create} „{name}“</t>
   </si>
   <si>
     <t xml:space="preserve">phrase.op.OpNothing</t>
@@ -16945,22 +16945,22 @@
     <t xml:space="preserve">phrase.rule.StartingMoney</t>
   </si>
   <si>
-    <t xml:space="preserve">${value}을 더 가지고 시작합니다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start with ${value} more</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${value} 多く持って始めます</t>
-  </si>
-  <si>
-    <t xml:space="preserve">开局多带 ${value}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">開局多帶 ${value}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beginnt mit ${value} mehr</t>
+    <t xml:space="preserve">시작 금액 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">starting money ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開始金額 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">起始金额 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">起始金額 ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Startgeld ${value}</t>
   </si>
   <si>
     <t xml:space="preserve">phrase.rule.NoInterest</t>
@@ -24158,6 +24158,792 @@
   </si>
   <si>
     <t xml:space="preserve">Nacktes Feld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">챌린지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">チャレンジ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">挑战</t>
+  </si>
+  <si>
+    <t xml:space="preserve">挑戰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herausforderungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 챌린지로 시작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">これで始める</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以此开始</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以此開始</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herausforderung starten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">규칙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RULES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ルール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規則</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGELN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.bans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">禁止</t>
+  </si>
+  <si>
+    <t xml:space="preserve">禁用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GESPERRT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.noRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작 조건만 다릅니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only the starting setup differs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開始条件だけが違います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仅起始条件不同。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">僅起始條件不同。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nur der Startaufbau unterscheidet sich.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">앞의 챌린지를 깨면 열립니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beat the previous challenge to unlock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前のチャレンジを倒すと開きます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击败前一个挑战后开启。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">擊敗前一個挑戰後開啟。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besiege die vorherige Herausforderung.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">열려 있습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開いています</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freigeschaltet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.beaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">깼습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クリア済み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已通过</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已通過</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geschlagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banLine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{what} {n}종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{what} ×{n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{what} {n}種</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{what} {n}种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banJoker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banVoucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vouchers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">兑换券</t>
+  </si>
+  <si>
+    <t xml:space="preserve">兌換券</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gutscheine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banTarot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banPlanet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planeten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banSpectral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spectrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banTag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banPack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부스터 팩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">补充包</t>
+  </si>
+  <si>
+    <t xml:space="preserve">補充包</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.banBoss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss盲注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.basePool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">챌린지는 기본 조커 150종으로 돕니다. 확장을 켜 두어도 그렇습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenges always run on the base 150 jokers, even with the expansion on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">チャレンジは基本ジョーカー150種で回ります。拡張を入れていても同じです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">挑战始终使用基础150种小丑牌，即使开启扩展。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">挑戰始終使用基礎150種小丑牌，即使開啟擴充。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herausforderungen nutzen stets die 150 Basis-Joker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.challenges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.challenge.lockedAll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">런을 한 번 이기면 챌린지가 열립니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win a run to unlock challenges.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ランに一度勝つとチャレンジが開きます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赢下一局后开启挑战。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">贏下一局後開啟挑戰。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gewinne einen Run, um Herausforderungen freizuschalten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.NoSmallBlindReward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스몰 블라인드의 보상이 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small blinds give no reward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スモールブラインドの報酬がありません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小盲注无奖励</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小盲注無獎勵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kleine Blinds geben kein Geld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.NoBigBlindReward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빅 블라인드의 보상이 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">big blinds give no reward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ビッグブラインドの報酬がありません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大盲注无奖励</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大盲注無獎勵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">große Blinds geben kein Geld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.NoBossBlindReward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스 블라인드의 보상이 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boss blinds give no reward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボスブラインドの報酬がありません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss盲注无奖励</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss盲注無獎勵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss-Blinds geben kein Geld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.ChipsCappedByMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">칩이 보유액을 넘지 못합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chips cannot exceed your money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">チップは所持金を超えません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">筹码不能超过持有金额</t>
+  </si>
+  <si>
+    <t xml:space="preserve">籌碼不能超過持有金額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chips können das Geld nicht übersteigen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.FaceDownDrawRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value}장에 1장이 뒤집혀 뽑힙니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 in {value} cards are drawn face down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value}枚に1枚が伏せて引かれます</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每{value}张有1张背面朝上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每{value}張有1張背面朝上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 von {value} Karten kommt verdeckt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.HandSizePerMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보유 ${value} 마다 패 크기 -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 hand size per ${value} held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所持金${value} ごとに手札 -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每持有${value} 手牌 -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 Handkarte je ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.AllJokersEternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 조커가 `Eternal` 입니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all jokers are Eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">すべてのジョーカーが `Eternal` です</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所有小丑牌为 `Eternal`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所有小丑牌為 `Eternal`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alle Joker sind Eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.DebuffPlayedAfterScoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낸 카드가 득점 뒤에 무력화됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">played cards are debuffed after scoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出したカードは得点後に無効化されます</t>
+  </si>
+  <si>
+    <t xml:space="preserve">打出的牌计分后被废除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">打出的牌計分後被廢除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gespielte Karten werden nach dem Punkten entwertet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.PriceRisePerPurchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">살 때마다 값이 ${value} 오릅니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prices rise ${value} per purchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購入ごとに値が${value} 上がります</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每次购买价格上涨${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每次購買價格上漲${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preise steigen um ${value} je Kauf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.NoJokersInShop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점에 조커가 나오지 않습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jokers no longer appear in the shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ショップにジョーカーが出ません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商店不再出现小丑牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商店不再出現小丑牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker erscheinen nicht im Shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.DiscardCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버릴 때마다 ${value} 를 냅니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discards each cost ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">捨てるたびに${value} かかります</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每次弃牌花费${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每次棄牌花費${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jedes Abwerfen kostet ${value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phrase.rule.PinnedJokerSlot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value}번째 조커를 옮길 수 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joker {value} cannot be moved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{value}番目のジョーカーは動かせません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第{value}个小丑牌无法移动</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第{value}個小丑牌無法移動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker {value} lässt sich nicht bewegen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.no_small_blind_reward.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스몰 블라인드의 격파 보상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small blind reward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スモールブラインドの報酬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小盲注奖励</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小盲注獎勵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belohnung kleiner Blind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.no_big_blind_reward.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빅 블라인드의 격파 보상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">big blind reward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ビッグブラインドの報酬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大盲注奖励</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大盲注獎勵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belohnung großer Blind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.no_boss_blind_reward.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스 블라인드의 격파 보상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boss blind reward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボスブラインドの報酬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss盲注奖励</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss盲注獎勵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belohnung Boss-Blind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.chips_capped_by_money.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">칩의 상한이 보유액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chips capped by money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">チップの上限は所持金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">筹码上限为持有金额</t>
+  </si>
+  <si>
+    <t xml:space="preserve">籌碼上限為持有金額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chips durch Geld begrenzt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.face_down_draw_rate.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뒤집혀 뽑히는 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">face-down draw rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">伏せて引く割合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">背面抽牌比例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdeckt-Zieh-Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.hand_size_per_money.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보유액에 따른 패 크기 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand size lost per money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所持金による手札減少</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按金额减少手牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按金額減少手牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handgröße je Geld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.all_jokers_eternal.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 조커가 `Eternal`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all jokers Eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全ジョーカーが `Eternal`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alle Joker Eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.debuff_played_after_scoring.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">득점 뒤 낸 카드 무력화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">played cards debuffed after scoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">得点後に出した札を無効化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">计分后废除打出的牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">計分後廢除打出的牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gespielte Karten entwertet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.price_rise_per_purchase.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구매마다 오르는 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price rise per purchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購入ごとの値上がり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每次购买涨价</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每次購買漲價</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preisanstieg je Kauf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.no_jokers_in_shop.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상점의 조커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jokers in shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ショップのジョーカー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商店的小丑牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker im Shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.discard_cost.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버리기의 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discard cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">捨てる費用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">弃牌费用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">棄牌費用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abwurfkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule.pinned_joker_slot.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">옮길 수 없는 조커 자리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pinned joker slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">固定されたジョーカー枠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">固定小丑牌位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixierter Joker-Platz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.toTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back to Title</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -24510,7 +25296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1262"/>
+  <dimension ref="A1:H1307"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -53508,8 +54294,1043 @@
         <v>8046</v>
       </c>
     </row>
+    <row r="1263">
+      <c r="B1263" s="5" t="s">
+        <v>8047</v>
+      </c>
+      <c r="C1263" s="5" t="s">
+        <v>8048</v>
+      </c>
+      <c r="D1263" s="5" t="s">
+        <v>8049</v>
+      </c>
+      <c r="E1263" s="5" t="s">
+        <v>8050</v>
+      </c>
+      <c r="F1263" s="5" t="s">
+        <v>8051</v>
+      </c>
+      <c r="G1263" s="5" t="s">
+        <v>8052</v>
+      </c>
+      <c r="H1263" s="5" t="s">
+        <v>8053</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="B1264" s="6" t="s">
+        <v>8054</v>
+      </c>
+      <c r="C1264" s="6" t="s">
+        <v>8055</v>
+      </c>
+      <c r="D1264" s="6" t="s">
+        <v>8056</v>
+      </c>
+      <c r="E1264" s="6" t="s">
+        <v>8057</v>
+      </c>
+      <c r="F1264" s="6" t="s">
+        <v>8058</v>
+      </c>
+      <c r="G1264" s="6" t="s">
+        <v>8059</v>
+      </c>
+      <c r="H1264" s="6" t="s">
+        <v>8060</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="B1265" s="5" t="s">
+        <v>8061</v>
+      </c>
+      <c r="C1265" s="5" t="s">
+        <v>8062</v>
+      </c>
+      <c r="D1265" s="5" t="s">
+        <v>8063</v>
+      </c>
+      <c r="E1265" s="5" t="s">
+        <v>8064</v>
+      </c>
+      <c r="F1265" s="5" t="s">
+        <v>8065</v>
+      </c>
+      <c r="G1265" s="5" t="s">
+        <v>8066</v>
+      </c>
+      <c r="H1265" s="5" t="s">
+        <v>8067</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="B1266" s="6" t="s">
+        <v>8068</v>
+      </c>
+      <c r="C1266" s="6" t="s">
+        <v>8069</v>
+      </c>
+      <c r="D1266" s="6" t="s">
+        <v>8070</v>
+      </c>
+      <c r="E1266" s="6" t="s">
+        <v>8071</v>
+      </c>
+      <c r="F1266" s="6" t="s">
+        <v>8072</v>
+      </c>
+      <c r="G1266" s="6" t="s">
+        <v>8072</v>
+      </c>
+      <c r="H1266" s="6" t="s">
+        <v>8073</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="B1267" s="5" t="s">
+        <v>8074</v>
+      </c>
+      <c r="C1267" s="5" t="s">
+        <v>8075</v>
+      </c>
+      <c r="D1267" s="5" t="s">
+        <v>8076</v>
+      </c>
+      <c r="E1267" s="5" t="s">
+        <v>8077</v>
+      </c>
+      <c r="F1267" s="5" t="s">
+        <v>8078</v>
+      </c>
+      <c r="G1267" s="5" t="s">
+        <v>8079</v>
+      </c>
+      <c r="H1267" s="5" t="s">
+        <v>8080</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="B1268" s="6" t="s">
+        <v>8081</v>
+      </c>
+      <c r="C1268" s="6" t="s">
+        <v>8082</v>
+      </c>
+      <c r="D1268" s="6" t="s">
+        <v>8083</v>
+      </c>
+      <c r="E1268" s="6" t="s">
+        <v>8084</v>
+      </c>
+      <c r="F1268" s="6" t="s">
+        <v>8085</v>
+      </c>
+      <c r="G1268" s="6" t="s">
+        <v>8086</v>
+      </c>
+      <c r="H1268" s="6" t="s">
+        <v>8087</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="B1269" s="5" t="s">
+        <v>8088</v>
+      </c>
+      <c r="C1269" s="5" t="s">
+        <v>8089</v>
+      </c>
+      <c r="D1269" s="5" t="s">
+        <v>8090</v>
+      </c>
+      <c r="E1269" s="5" t="s">
+        <v>8091</v>
+      </c>
+      <c r="F1269" s="5" t="s">
+        <v>7289</v>
+      </c>
+      <c r="G1269" s="5" t="s">
+        <v>7290</v>
+      </c>
+      <c r="H1269" s="5" t="s">
+        <v>8092</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="B1270" s="6" t="s">
+        <v>8093</v>
+      </c>
+      <c r="C1270" s="6" t="s">
+        <v>8094</v>
+      </c>
+      <c r="D1270" s="6" t="s">
+        <v>8095</v>
+      </c>
+      <c r="E1270" s="6" t="s">
+        <v>8096</v>
+      </c>
+      <c r="F1270" s="6" t="s">
+        <v>8097</v>
+      </c>
+      <c r="G1270" s="6" t="s">
+        <v>8098</v>
+      </c>
+      <c r="H1270" s="6" t="s">
+        <v>8099</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="B1271" s="5" t="s">
+        <v>8100</v>
+      </c>
+      <c r="C1271" s="5" t="s">
+        <v>8101</v>
+      </c>
+      <c r="D1271" s="5" t="s">
+        <v>8102</v>
+      </c>
+      <c r="E1271" s="5" t="s">
+        <v>8103</v>
+      </c>
+      <c r="F1271" s="5" t="s">
+        <v>8104</v>
+      </c>
+      <c r="G1271" s="5" t="s">
+        <v>8103</v>
+      </c>
+      <c r="H1271" s="5" t="s">
+        <v>8102</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="B1272" s="6" t="s">
+        <v>8105</v>
+      </c>
+      <c r="C1272" s="6" t="s">
+        <v>5927</v>
+      </c>
+      <c r="D1272" s="6" t="s">
+        <v>7856</v>
+      </c>
+      <c r="E1272" s="6" t="s">
+        <v>5929</v>
+      </c>
+      <c r="F1272" s="6" t="s">
+        <v>7857</v>
+      </c>
+      <c r="G1272" s="6" t="s">
+        <v>7857</v>
+      </c>
+      <c r="H1272" s="6" t="s">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="B1273" s="5" t="s">
+        <v>8106</v>
+      </c>
+      <c r="C1273" s="5" t="s">
+        <v>5974</v>
+      </c>
+      <c r="D1273" s="5" t="s">
+        <v>8107</v>
+      </c>
+      <c r="E1273" s="5" t="s">
+        <v>5976</v>
+      </c>
+      <c r="F1273" s="5" t="s">
+        <v>8108</v>
+      </c>
+      <c r="G1273" s="5" t="s">
+        <v>8109</v>
+      </c>
+      <c r="H1273" s="5" t="s">
+        <v>8110</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="B1274" s="6" t="s">
+        <v>8111</v>
+      </c>
+      <c r="C1274" s="6" t="s">
+        <v>6919</v>
+      </c>
+      <c r="D1274" s="6" t="s">
+        <v>8112</v>
+      </c>
+      <c r="E1274" s="6" t="s">
+        <v>6921</v>
+      </c>
+      <c r="F1274" s="6" t="s">
+        <v>5910</v>
+      </c>
+      <c r="G1274" s="6" t="s">
+        <v>5911</v>
+      </c>
+      <c r="H1274" s="6" t="s">
+        <v>6920</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="B1275" s="5" t="s">
+        <v>8113</v>
+      </c>
+      <c r="C1275" s="5" t="s">
+        <v>6925</v>
+      </c>
+      <c r="D1275" s="5" t="s">
+        <v>8114</v>
+      </c>
+      <c r="E1275" s="5" t="s">
+        <v>6927</v>
+      </c>
+      <c r="F1275" s="5" t="s">
+        <v>5917</v>
+      </c>
+      <c r="G1275" s="5" t="s">
+        <v>5917</v>
+      </c>
+      <c r="H1275" s="5" t="s">
+        <v>8115</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="B1276" s="6" t="s">
+        <v>8116</v>
+      </c>
+      <c r="C1276" s="6" t="s">
+        <v>6930</v>
+      </c>
+      <c r="D1276" s="6" t="s">
+        <v>8117</v>
+      </c>
+      <c r="E1276" s="6" t="s">
+        <v>6932</v>
+      </c>
+      <c r="F1276" s="6" t="s">
+        <v>5923</v>
+      </c>
+      <c r="G1276" s="6" t="s">
+        <v>5924</v>
+      </c>
+      <c r="H1276" s="6" t="s">
+        <v>6935</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="B1277" s="5" t="s">
+        <v>8118</v>
+      </c>
+      <c r="C1277" s="5" t="s">
+        <v>5940</v>
+      </c>
+      <c r="D1277" s="5" t="s">
+        <v>8119</v>
+      </c>
+      <c r="E1277" s="5" t="s">
+        <v>5942</v>
+      </c>
+      <c r="F1277" s="5" t="s">
+        <v>5943</v>
+      </c>
+      <c r="G1277" s="5" t="s">
+        <v>5944</v>
+      </c>
+      <c r="H1277" s="5" t="s">
+        <v>8120</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="B1278" s="6" t="s">
+        <v>8121</v>
+      </c>
+      <c r="C1278" s="6" t="s">
+        <v>8122</v>
+      </c>
+      <c r="D1278" s="6" t="s">
+        <v>8123</v>
+      </c>
+      <c r="E1278" s="6" t="s">
+        <v>5970</v>
+      </c>
+      <c r="F1278" s="6" t="s">
+        <v>8124</v>
+      </c>
+      <c r="G1278" s="6" t="s">
+        <v>8125</v>
+      </c>
+      <c r="H1278" s="6" t="s">
+        <v>6917</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="B1279" s="5" t="s">
+        <v>8126</v>
+      </c>
+      <c r="C1279" s="5" t="s">
+        <v>6903</v>
+      </c>
+      <c r="D1279" s="5" t="s">
+        <v>8127</v>
+      </c>
+      <c r="E1279" s="5" t="s">
+        <v>6905</v>
+      </c>
+      <c r="F1279" s="5" t="s">
+        <v>8128</v>
+      </c>
+      <c r="G1279" s="5" t="s">
+        <v>8128</v>
+      </c>
+      <c r="H1279" s="5" t="s">
+        <v>8129</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="B1280" s="6" t="s">
+        <v>8130</v>
+      </c>
+      <c r="C1280" s="6" t="s">
+        <v>8131</v>
+      </c>
+      <c r="D1280" s="6" t="s">
+        <v>8132</v>
+      </c>
+      <c r="E1280" s="6" t="s">
+        <v>8133</v>
+      </c>
+      <c r="F1280" s="6" t="s">
+        <v>8134</v>
+      </c>
+      <c r="G1280" s="6" t="s">
+        <v>8135</v>
+      </c>
+      <c r="H1280" s="6" t="s">
+        <v>8136</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="B1281" s="5" t="s">
+        <v>8137</v>
+      </c>
+      <c r="C1281" s="5" t="s">
+        <v>8048</v>
+      </c>
+      <c r="D1281" s="5" t="s">
+        <v>8049</v>
+      </c>
+      <c r="E1281" s="5" t="s">
+        <v>8050</v>
+      </c>
+      <c r="F1281" s="5" t="s">
+        <v>8051</v>
+      </c>
+      <c r="G1281" s="5" t="s">
+        <v>8052</v>
+      </c>
+      <c r="H1281" s="5" t="s">
+        <v>8053</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="B1282" s="6" t="s">
+        <v>8138</v>
+      </c>
+      <c r="C1282" s="6" t="s">
+        <v>8139</v>
+      </c>
+      <c r="D1282" s="6" t="s">
+        <v>8140</v>
+      </c>
+      <c r="E1282" s="6" t="s">
+        <v>8141</v>
+      </c>
+      <c r="F1282" s="6" t="s">
+        <v>8142</v>
+      </c>
+      <c r="G1282" s="6" t="s">
+        <v>8143</v>
+      </c>
+      <c r="H1282" s="6" t="s">
+        <v>8144</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="B1283" s="5" t="s">
+        <v>8145</v>
+      </c>
+      <c r="C1283" s="5" t="s">
+        <v>8146</v>
+      </c>
+      <c r="D1283" s="5" t="s">
+        <v>8147</v>
+      </c>
+      <c r="E1283" s="5" t="s">
+        <v>8148</v>
+      </c>
+      <c r="F1283" s="5" t="s">
+        <v>8149</v>
+      </c>
+      <c r="G1283" s="5" t="s">
+        <v>8150</v>
+      </c>
+      <c r="H1283" s="5" t="s">
+        <v>8151</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="B1284" s="6" t="s">
+        <v>8152</v>
+      </c>
+      <c r="C1284" s="6" t="s">
+        <v>8153</v>
+      </c>
+      <c r="D1284" s="6" t="s">
+        <v>8154</v>
+      </c>
+      <c r="E1284" s="6" t="s">
+        <v>8155</v>
+      </c>
+      <c r="F1284" s="6" t="s">
+        <v>8156</v>
+      </c>
+      <c r="G1284" s="6" t="s">
+        <v>8157</v>
+      </c>
+      <c r="H1284" s="6" t="s">
+        <v>8158</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="B1285" s="5" t="s">
+        <v>8159</v>
+      </c>
+      <c r="C1285" s="5" t="s">
+        <v>8160</v>
+      </c>
+      <c r="D1285" s="5" t="s">
+        <v>8161</v>
+      </c>
+      <c r="E1285" s="5" t="s">
+        <v>8162</v>
+      </c>
+      <c r="F1285" s="5" t="s">
+        <v>8163</v>
+      </c>
+      <c r="G1285" s="5" t="s">
+        <v>8164</v>
+      </c>
+      <c r="H1285" s="5" t="s">
+        <v>8165</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="B1286" s="6" t="s">
+        <v>8166</v>
+      </c>
+      <c r="C1286" s="6" t="s">
+        <v>8167</v>
+      </c>
+      <c r="D1286" s="6" t="s">
+        <v>8168</v>
+      </c>
+      <c r="E1286" s="6" t="s">
+        <v>8169</v>
+      </c>
+      <c r="F1286" s="6" t="s">
+        <v>8170</v>
+      </c>
+      <c r="G1286" s="6" t="s">
+        <v>8171</v>
+      </c>
+      <c r="H1286" s="6" t="s">
+        <v>8172</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="B1287" s="5" t="s">
+        <v>8173</v>
+      </c>
+      <c r="C1287" s="5" t="s">
+        <v>8174</v>
+      </c>
+      <c r="D1287" s="5" t="s">
+        <v>8175</v>
+      </c>
+      <c r="E1287" s="5" t="s">
+        <v>8176</v>
+      </c>
+      <c r="F1287" s="5" t="s">
+        <v>8177</v>
+      </c>
+      <c r="G1287" s="5" t="s">
+        <v>8178</v>
+      </c>
+      <c r="H1287" s="5" t="s">
+        <v>8179</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="B1288" s="6" t="s">
+        <v>8180</v>
+      </c>
+      <c r="C1288" s="6" t="s">
+        <v>8181</v>
+      </c>
+      <c r="D1288" s="6" t="s">
+        <v>8182</v>
+      </c>
+      <c r="E1288" s="6" t="s">
+        <v>8183</v>
+      </c>
+      <c r="F1288" s="6" t="s">
+        <v>8184</v>
+      </c>
+      <c r="G1288" s="6" t="s">
+        <v>8184</v>
+      </c>
+      <c r="H1288" s="6" t="s">
+        <v>8185</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="B1289" s="5" t="s">
+        <v>8186</v>
+      </c>
+      <c r="C1289" s="5" t="s">
+        <v>8187</v>
+      </c>
+      <c r="D1289" s="5" t="s">
+        <v>8188</v>
+      </c>
+      <c r="E1289" s="5" t="s">
+        <v>8189</v>
+      </c>
+      <c r="F1289" s="5" t="s">
+        <v>8190</v>
+      </c>
+      <c r="G1289" s="5" t="s">
+        <v>8191</v>
+      </c>
+      <c r="H1289" s="5" t="s">
+        <v>8192</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="B1290" s="6" t="s">
+        <v>8193</v>
+      </c>
+      <c r="C1290" s="6" t="s">
+        <v>8194</v>
+      </c>
+      <c r="D1290" s="6" t="s">
+        <v>8195</v>
+      </c>
+      <c r="E1290" s="6" t="s">
+        <v>8196</v>
+      </c>
+      <c r="F1290" s="6" t="s">
+        <v>8197</v>
+      </c>
+      <c r="G1290" s="6" t="s">
+        <v>8198</v>
+      </c>
+      <c r="H1290" s="6" t="s">
+        <v>8199</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="B1291" s="5" t="s">
+        <v>8200</v>
+      </c>
+      <c r="C1291" s="5" t="s">
+        <v>8201</v>
+      </c>
+      <c r="D1291" s="5" t="s">
+        <v>8202</v>
+      </c>
+      <c r="E1291" s="5" t="s">
+        <v>8203</v>
+      </c>
+      <c r="F1291" s="5" t="s">
+        <v>8204</v>
+      </c>
+      <c r="G1291" s="5" t="s">
+        <v>8205</v>
+      </c>
+      <c r="H1291" s="5" t="s">
+        <v>8206</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="B1292" s="6" t="s">
+        <v>8207</v>
+      </c>
+      <c r="C1292" s="6" t="s">
+        <v>8208</v>
+      </c>
+      <c r="D1292" s="6" t="s">
+        <v>8209</v>
+      </c>
+      <c r="E1292" s="6" t="s">
+        <v>8210</v>
+      </c>
+      <c r="F1292" s="6" t="s">
+        <v>8211</v>
+      </c>
+      <c r="G1292" s="6" t="s">
+        <v>8212</v>
+      </c>
+      <c r="H1292" s="6" t="s">
+        <v>8213</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="B1293" s="5" t="s">
+        <v>8214</v>
+      </c>
+      <c r="C1293" s="5" t="s">
+        <v>8215</v>
+      </c>
+      <c r="D1293" s="5" t="s">
+        <v>8216</v>
+      </c>
+      <c r="E1293" s="5" t="s">
+        <v>8217</v>
+      </c>
+      <c r="F1293" s="5" t="s">
+        <v>8218</v>
+      </c>
+      <c r="G1293" s="5" t="s">
+        <v>8219</v>
+      </c>
+      <c r="H1293" s="5" t="s">
+        <v>8220</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="B1294" s="6" t="s">
+        <v>8221</v>
+      </c>
+      <c r="C1294" s="6" t="s">
+        <v>8222</v>
+      </c>
+      <c r="D1294" s="6" t="s">
+        <v>8223</v>
+      </c>
+      <c r="E1294" s="6" t="s">
+        <v>8224</v>
+      </c>
+      <c r="F1294" s="6" t="s">
+        <v>8225</v>
+      </c>
+      <c r="G1294" s="6" t="s">
+        <v>8226</v>
+      </c>
+      <c r="H1294" s="6" t="s">
+        <v>8227</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="B1295" s="5" t="s">
+        <v>8228</v>
+      </c>
+      <c r="C1295" s="5" t="s">
+        <v>8229</v>
+      </c>
+      <c r="D1295" s="5" t="s">
+        <v>8230</v>
+      </c>
+      <c r="E1295" s="5" t="s">
+        <v>8231</v>
+      </c>
+      <c r="F1295" s="5" t="s">
+        <v>8232</v>
+      </c>
+      <c r="G1295" s="5" t="s">
+        <v>8233</v>
+      </c>
+      <c r="H1295" s="5" t="s">
+        <v>8234</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="B1296" s="6" t="s">
+        <v>8235</v>
+      </c>
+      <c r="C1296" s="6" t="s">
+        <v>8236</v>
+      </c>
+      <c r="D1296" s="6" t="s">
+        <v>8237</v>
+      </c>
+      <c r="E1296" s="6" t="s">
+        <v>8238</v>
+      </c>
+      <c r="F1296" s="6" t="s">
+        <v>8239</v>
+      </c>
+      <c r="G1296" s="6" t="s">
+        <v>8240</v>
+      </c>
+      <c r="H1296" s="6" t="s">
+        <v>8241</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="B1297" s="5" t="s">
+        <v>8242</v>
+      </c>
+      <c r="C1297" s="5" t="s">
+        <v>8243</v>
+      </c>
+      <c r="D1297" s="5" t="s">
+        <v>8244</v>
+      </c>
+      <c r="E1297" s="5" t="s">
+        <v>8245</v>
+      </c>
+      <c r="F1297" s="5" t="s">
+        <v>8246</v>
+      </c>
+      <c r="G1297" s="5" t="s">
+        <v>8247</v>
+      </c>
+      <c r="H1297" s="5" t="s">
+        <v>8248</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="B1298" s="6" t="s">
+        <v>8249</v>
+      </c>
+      <c r="C1298" s="6" t="s">
+        <v>8250</v>
+      </c>
+      <c r="D1298" s="6" t="s">
+        <v>8251</v>
+      </c>
+      <c r="E1298" s="6" t="s">
+        <v>8252</v>
+      </c>
+      <c r="F1298" s="6" t="s">
+        <v>8253</v>
+      </c>
+      <c r="G1298" s="6" t="s">
+        <v>8254</v>
+      </c>
+      <c r="H1298" s="6" t="s">
+        <v>8255</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="B1299" s="5" t="s">
+        <v>8256</v>
+      </c>
+      <c r="C1299" s="5" t="s">
+        <v>8257</v>
+      </c>
+      <c r="D1299" s="5" t="s">
+        <v>8258</v>
+      </c>
+      <c r="E1299" s="5" t="s">
+        <v>8259</v>
+      </c>
+      <c r="F1299" s="5" t="s">
+        <v>8260</v>
+      </c>
+      <c r="G1299" s="5" t="s">
+        <v>8260</v>
+      </c>
+      <c r="H1299" s="5" t="s">
+        <v>8261</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="B1300" s="6" t="s">
+        <v>8262</v>
+      </c>
+      <c r="C1300" s="6" t="s">
+        <v>8263</v>
+      </c>
+      <c r="D1300" s="6" t="s">
+        <v>8264</v>
+      </c>
+      <c r="E1300" s="6" t="s">
+        <v>8265</v>
+      </c>
+      <c r="F1300" s="6" t="s">
+        <v>8266</v>
+      </c>
+      <c r="G1300" s="6" t="s">
+        <v>8267</v>
+      </c>
+      <c r="H1300" s="6" t="s">
+        <v>8268</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="B1301" s="5" t="s">
+        <v>8269</v>
+      </c>
+      <c r="C1301" s="5" t="s">
+        <v>8270</v>
+      </c>
+      <c r="D1301" s="5" t="s">
+        <v>8271</v>
+      </c>
+      <c r="E1301" s="5" t="s">
+        <v>8272</v>
+      </c>
+      <c r="F1301" s="5" t="s">
+        <v>8190</v>
+      </c>
+      <c r="G1301" s="5" t="s">
+        <v>8191</v>
+      </c>
+      <c r="H1301" s="5" t="s">
+        <v>8273</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="B1302" s="6" t="s">
+        <v>8274</v>
+      </c>
+      <c r="C1302" s="6" t="s">
+        <v>8275</v>
+      </c>
+      <c r="D1302" s="6" t="s">
+        <v>8276</v>
+      </c>
+      <c r="E1302" s="6" t="s">
+        <v>8277</v>
+      </c>
+      <c r="F1302" s="6" t="s">
+        <v>8278</v>
+      </c>
+      <c r="G1302" s="6" t="s">
+        <v>8279</v>
+      </c>
+      <c r="H1302" s="6" t="s">
+        <v>8280</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="B1303" s="5" t="s">
+        <v>8281</v>
+      </c>
+      <c r="C1303" s="5" t="s">
+        <v>8282</v>
+      </c>
+      <c r="D1303" s="5" t="s">
+        <v>8283</v>
+      </c>
+      <c r="E1303" s="5" t="s">
+        <v>8284</v>
+      </c>
+      <c r="F1303" s="5" t="s">
+        <v>8285</v>
+      </c>
+      <c r="G1303" s="5" t="s">
+        <v>8286</v>
+      </c>
+      <c r="H1303" s="5" t="s">
+        <v>8287</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="B1304" s="6" t="s">
+        <v>8288</v>
+      </c>
+      <c r="C1304" s="6" t="s">
+        <v>8289</v>
+      </c>
+      <c r="D1304" s="6" t="s">
+        <v>8290</v>
+      </c>
+      <c r="E1304" s="6" t="s">
+        <v>8291</v>
+      </c>
+      <c r="F1304" s="6" t="s">
+        <v>8292</v>
+      </c>
+      <c r="G1304" s="6" t="s">
+        <v>8292</v>
+      </c>
+      <c r="H1304" s="6" t="s">
+        <v>8293</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="B1305" s="5" t="s">
+        <v>8294</v>
+      </c>
+      <c r="C1305" s="5" t="s">
+        <v>8295</v>
+      </c>
+      <c r="D1305" s="5" t="s">
+        <v>8296</v>
+      </c>
+      <c r="E1305" s="5" t="s">
+        <v>8297</v>
+      </c>
+      <c r="F1305" s="5" t="s">
+        <v>8298</v>
+      </c>
+      <c r="G1305" s="5" t="s">
+        <v>8299</v>
+      </c>
+      <c r="H1305" s="5" t="s">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="B1306" s="6" t="s">
+        <v>8301</v>
+      </c>
+      <c r="C1306" s="6" t="s">
+        <v>8302</v>
+      </c>
+      <c r="D1306" s="6" t="s">
+        <v>8303</v>
+      </c>
+      <c r="E1306" s="6" t="s">
+        <v>8304</v>
+      </c>
+      <c r="F1306" s="6" t="s">
+        <v>8305</v>
+      </c>
+      <c r="G1306" s="6" t="s">
+        <v>8305</v>
+      </c>
+      <c r="H1306" s="6" t="s">
+        <v>8306</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="B1307" s="5" t="s">
+        <v>8307</v>
+      </c>
+      <c r="C1307" s="5" t="s">
+        <v>6625</v>
+      </c>
+      <c r="D1307" s="5" t="s">
+        <v>8308</v>
+      </c>
+      <c r="E1307" s="5" t="s">
+        <v>6627</v>
+      </c>
+      <c r="F1307" s="5" t="s">
+        <v>6628</v>
+      </c>
+      <c r="G1307" s="5" t="s">
+        <v>6629</v>
+      </c>
+      <c r="H1307" s="5" t="s">
+        <v>6630</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H1262"/>
+  <autoFilter ref="B2:H1307"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -53528,10 +55349,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>8047</v>
+        <v>8309</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8048</v>
+        <v>8310</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -53542,16 +55363,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8049</v>
+        <v>8311</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8050</v>
+        <v>8312</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8051</v>
+        <v>8313</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8052</v>
+        <v>8314</v>
       </c>
     </row>
     <row r="3">
@@ -53559,16 +55380,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8053</v>
+        <v>8315</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8054</v>
+        <v>8316</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8055</v>
+        <v>8317</v>
       </c>
     </row>
     <row r="4">
@@ -53579,24 +55400,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8056</v>
+        <v>8318</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8057</v>
+        <v>8319</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8058</v>
+        <v>8320</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>8059</v>
+        <v>8321</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4463</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8060</v>
+        <v>8322</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -53604,13 +55425,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>8061</v>
+        <v>8323</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4470</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>8062</v>
+        <v>8324</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -53618,13 +55439,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>8063</v>
+        <v>8325</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4476</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8064</v>
+        <v>8326</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -53632,13 +55453,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>8065</v>
+        <v>8327</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4482</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>8066</v>
+        <v>8328</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -53646,13 +55467,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>8067</v>
+        <v>8329</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4489</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8068</v>
+        <v>8330</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -53660,13 +55481,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>8069</v>
+        <v>8331</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4496</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>8070</v>
+        <v>8332</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -53674,13 +55495,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>8071</v>
+        <v>8333</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4502</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>8072</v>
+        <v>8334</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -53688,13 +55509,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>8073</v>
+        <v>8335</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4508</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>8074</v>
+        <v>8336</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -53702,13 +55523,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>8075</v>
+        <v>8337</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4515</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8076</v>
+        <v>8338</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -53716,13 +55537,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>8077</v>
+        <v>8339</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4521</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>8078</v>
+        <v>8340</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -53736,7 +55557,7 @@
         <v>4527</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8079</v>
+        <v>8341</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -53744,13 +55565,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>8080</v>
+        <v>8342</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4534</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>8081</v>
+        <v>8343</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -53758,13 +55579,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>8082</v>
+        <v>8344</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4541</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>8083</v>
+        <v>8345</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -53772,13 +55593,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>8084</v>
+        <v>8346</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4547</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>8085</v>
+        <v>8347</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -53786,13 +55607,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>8086</v>
+        <v>8348</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4554</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>8087</v>
+        <v>8349</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -53800,13 +55621,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>8088</v>
+        <v>8350</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4560</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>8089</v>
+        <v>8351</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -53814,13 +55635,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>8090</v>
+        <v>8352</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4565</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>8091</v>
+        <v>8353</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -53828,13 +55649,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>8092</v>
+        <v>8354</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4572</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>8093</v>
+        <v>8355</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -53842,13 +55663,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>8094</v>
+        <v>8356</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4394</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>8095</v>
+        <v>8357</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -53856,13 +55677,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>8096</v>
+        <v>8358</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4580</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>8097</v>
+        <v>8359</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1307]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1373]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9212" uniqueCount="8360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9408" uniqueCount="8541">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -24944,6 +24944,549 @@
   </si>
   <si>
     <t xml:space="preserve">Back to Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.leaderboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리더보드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaderboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그아웃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.toMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">내 자리로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.confirmName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 이름으로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use this name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.deleteAccount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계정 삭제</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">신고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.login.why</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리더보드는 계정이 있어야 합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The leaderboard needs an account.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.login.keep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">들고 있는 것: 표시 이름과 제공자의 식별자. 이메일은 받지 않습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We keep a display name and the provider id. We do not take your email.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.login.none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지금은 로그인할 수 있는 곳이 없습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No sign-in provider is available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.handle.ask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순위표에 적힐 이름을 정합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose the name shown on the board.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.handle.rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영문 · 숫자 · 밑줄 3~16자. 30일에 한 번 바꿀 수 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letters, digits, underscore. 3-16 characters. Changeable once every 30 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.tab.Main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.tab.Stake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.tab.Deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.tab.Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.metric.Ascent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">등정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.metric.BestHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한 손 최고 점수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.metric.FewestHands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최소 핸드 완주</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fewest hands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.metric.MoneyAtWin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">완주 소지금</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money at win</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.metric.Wins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">완주 횟수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.metric.Skips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">건너뛴 블라인드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blinds skipped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.metric.ChallengesBeaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">깬 챌린지 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenges beaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.period.season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 시즌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.period.all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체 기간</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.pool.all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">확장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expanded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.col.rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.col.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.col.tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">등급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.col.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아직 아무도 오르지 않았습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nobody here yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.noRecord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아직 기록이 없습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No record yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">내 자리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.loading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">불러오는 중</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n}명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{at} / {all}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.hands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 핸드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} hands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.beaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.card.signedOut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.card.noTier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">등급 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unranked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.profile.lastSeason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지난 시즌 {tier}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last season {tier}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.profile.devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인된 기계 {n}대</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} signed-in devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.profile.deleteWarn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계정과 모든 기록이 지워집니다. 되돌리지 않습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The account and every record are removed. This cannot be undone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.ranked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.ranked.on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 런은 끝나면 순위에 오릅니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This run will be ranked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.ranked.off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 런은 순위에 오르지 않습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This run will not be ranked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.ranked.cannot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지금은 랭크 런을 시작할 수 없습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannot start a ranked run now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.end.judging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순위를 세는 중</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.end.same</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} #{rank} · 그대로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} #{rank} · unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.end.up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} #{rank} ↑{by}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.end.first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순위표에 올랐습니다 — {name} #{rank}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are on the board — {name} #{rank}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.end.rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 런은 순위에 오르지 않았습니다 — {why}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This run was not ranked — {why}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.end.later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나중에 다시 보냅니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We will send it again later.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.end.tierUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">등급이 {tier} 가 되었습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You reached {tier}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">되지 않았습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That did not work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.offline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서버에 닿지 못했습니다. 게임은 그대로 하실 수 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could not reach the server. The game keeps working.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.unauthorized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다시 로그인해야 합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please sign in again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.bad_seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 시드로 시작한 랭크 런이 아닙니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This run did not start from that ranked seed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.bad_fingerprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">게임이 낡았습니다. 새로 고치면 다시 올릴 수 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This build is out of date. Reload and try again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.too_many</t>
+  </si>
+  <si>
+    <t xml:space="preserve">너무 잦습니다. 잠시 뒤에 다시 하십시오.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Too many requests. Try again shortly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.taken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이미 쓰이는 이름입니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That name is taken.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.cooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아직 이름을 바꿀 수 없습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You cannot change the name yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영문 · 숫자 · 밑줄 3~16자입니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use 3-16 letters, digits or underscores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.fail.unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서버가 이 요청을 받지 않았습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The server refused the request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.cleared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cleared</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -25104,7 +25647,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -25141,6 +25684,12 @@
     <font>
       <sz val="10"/>
       <color rgb="1F2328"/>
+      <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="C0392B"/>
       <name val="Malgun Gothic"/>
     </font>
   </fonts>
@@ -25270,7 +25819,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -25290,13 +25839,16 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1307"/>
+  <dimension ref="A1:H1373"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -55329,8 +55881,728 @@
         <v>6630</v>
       </c>
     </row>
+    <row r="1308">
+      <c r="B1308" s="6" t="s">
+        <v>8309</v>
+      </c>
+      <c r="C1308" s="6" t="s">
+        <v>8310</v>
+      </c>
+      <c r="D1308" s="6" t="s">
+        <v>8311</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="B1309" s="5" t="s">
+        <v>8312</v>
+      </c>
+      <c r="C1309" s="5" t="s">
+        <v>8313</v>
+      </c>
+      <c r="D1309" s="5" t="s">
+        <v>8314</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="B1310" s="6" t="s">
+        <v>8315</v>
+      </c>
+      <c r="C1310" s="6" t="s">
+        <v>8316</v>
+      </c>
+      <c r="D1310" s="6" t="s">
+        <v>8317</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="B1311" s="5" t="s">
+        <v>8318</v>
+      </c>
+      <c r="C1311" s="5" t="s">
+        <v>8319</v>
+      </c>
+      <c r="D1311" s="5" t="s">
+        <v>8320</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="B1312" s="6" t="s">
+        <v>8321</v>
+      </c>
+      <c r="C1312" s="6" t="s">
+        <v>8322</v>
+      </c>
+      <c r="D1312" s="6" t="s">
+        <v>8323</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="B1313" s="5" t="s">
+        <v>8324</v>
+      </c>
+      <c r="C1313" s="5" t="s">
+        <v>8325</v>
+      </c>
+      <c r="D1313" s="5" t="s">
+        <v>8326</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="B1314" s="6" t="s">
+        <v>8327</v>
+      </c>
+      <c r="C1314" s="6" t="s">
+        <v>8328</v>
+      </c>
+      <c r="D1314" s="6" t="s">
+        <v>8329</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="B1315" s="5" t="s">
+        <v>8330</v>
+      </c>
+      <c r="C1315" s="5" t="s">
+        <v>8310</v>
+      </c>
+      <c r="D1315" s="5" t="s">
+        <v>8311</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="B1316" s="6" t="s">
+        <v>8331</v>
+      </c>
+      <c r="C1316" s="6" t="s">
+        <v>8332</v>
+      </c>
+      <c r="D1316" s="6" t="s">
+        <v>8333</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="B1317" s="5" t="s">
+        <v>8334</v>
+      </c>
+      <c r="C1317" s="5" t="s">
+        <v>8335</v>
+      </c>
+      <c r="D1317" s="5" t="s">
+        <v>8336</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="B1318" s="6" t="s">
+        <v>8337</v>
+      </c>
+      <c r="C1318" s="6" t="s">
+        <v>8338</v>
+      </c>
+      <c r="D1318" s="6" t="s">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="B1319" s="5" t="s">
+        <v>8340</v>
+      </c>
+      <c r="C1319" s="5" t="s">
+        <v>8341</v>
+      </c>
+      <c r="D1319" s="5" t="s">
+        <v>8342</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="B1320" s="6" t="s">
+        <v>8343</v>
+      </c>
+      <c r="C1320" s="6" t="s">
+        <v>8344</v>
+      </c>
+      <c r="D1320" s="6" t="s">
+        <v>8345</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="B1321" s="5" t="s">
+        <v>8346</v>
+      </c>
+      <c r="C1321" s="5" t="s">
+        <v>8347</v>
+      </c>
+      <c r="D1321" s="5" t="s">
+        <v>8348</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="B1322" s="6" t="s">
+        <v>8349</v>
+      </c>
+      <c r="C1322" s="6" t="s">
+        <v>6739</v>
+      </c>
+      <c r="D1322" s="6" t="s">
+        <v>8350</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="B1323" s="5" t="s">
+        <v>8351</v>
+      </c>
+      <c r="C1323" s="5" t="s">
+        <v>6939</v>
+      </c>
+      <c r="D1323" s="5" t="s">
+        <v>6676</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="B1324" s="6" t="s">
+        <v>8352</v>
+      </c>
+      <c r="C1324" s="6" t="s">
+        <v>8048</v>
+      </c>
+      <c r="D1324" s="6" t="s">
+        <v>8353</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="B1325" s="5" t="s">
+        <v>8354</v>
+      </c>
+      <c r="C1325" s="5" t="s">
+        <v>8355</v>
+      </c>
+      <c r="D1325" s="5" t="s">
+        <v>8356</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="B1326" s="6" t="s">
+        <v>8357</v>
+      </c>
+      <c r="C1326" s="6" t="s">
+        <v>8358</v>
+      </c>
+      <c r="D1326" s="6" t="s">
+        <v>8359</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="B1327" s="5" t="s">
+        <v>8360</v>
+      </c>
+      <c r="C1327" s="5" t="s">
+        <v>8361</v>
+      </c>
+      <c r="D1327" s="5" t="s">
+        <v>8362</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="B1328" s="6" t="s">
+        <v>8363</v>
+      </c>
+      <c r="C1328" s="6" t="s">
+        <v>8364</v>
+      </c>
+      <c r="D1328" s="6" t="s">
+        <v>8365</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="B1329" s="5" t="s">
+        <v>8366</v>
+      </c>
+      <c r="C1329" s="5" t="s">
+        <v>8367</v>
+      </c>
+      <c r="D1329" s="5" t="s">
+        <v>8368</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="B1330" s="6" t="s">
+        <v>8369</v>
+      </c>
+      <c r="C1330" s="6" t="s">
+        <v>8370</v>
+      </c>
+      <c r="D1330" s="6" t="s">
+        <v>8371</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="B1331" s="5" t="s">
+        <v>8372</v>
+      </c>
+      <c r="C1331" s="5" t="s">
+        <v>8373</v>
+      </c>
+      <c r="D1331" s="5" t="s">
+        <v>8374</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="B1332" s="6" t="s">
+        <v>8375</v>
+      </c>
+      <c r="C1332" s="6" t="s">
+        <v>8376</v>
+      </c>
+      <c r="D1332" s="6" t="s">
+        <v>8377</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="B1333" s="5" t="s">
+        <v>8378</v>
+      </c>
+      <c r="C1333" s="5" t="s">
+        <v>8379</v>
+      </c>
+      <c r="D1333" s="5" t="s">
+        <v>8380</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="B1334" s="6" t="s">
+        <v>8381</v>
+      </c>
+      <c r="C1334" s="6" t="s">
+        <v>8382</v>
+      </c>
+      <c r="D1334" s="6" t="s">
+        <v>8383</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="B1335" s="5" t="s">
+        <v>8384</v>
+      </c>
+      <c r="C1335" s="7" t="s">
+        <v>8385</v>
+      </c>
+      <c r="D1335" s="7" t="s">
+        <v>8385</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="B1336" s="6" t="s">
+        <v>8386</v>
+      </c>
+      <c r="C1336" s="6" t="s">
+        <v>7912</v>
+      </c>
+      <c r="D1336" s="6" t="s">
+        <v>7913</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="B1337" s="5" t="s">
+        <v>8387</v>
+      </c>
+      <c r="C1337" s="5" t="s">
+        <v>8388</v>
+      </c>
+      <c r="D1337" s="5" t="s">
+        <v>8389</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="B1338" s="6" t="s">
+        <v>8390</v>
+      </c>
+      <c r="C1338" s="6" t="s">
+        <v>8391</v>
+      </c>
+      <c r="D1338" s="6" t="s">
+        <v>8392</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="B1339" s="5" t="s">
+        <v>8393</v>
+      </c>
+      <c r="C1339" s="5" t="s">
+        <v>8394</v>
+      </c>
+      <c r="D1339" s="5" t="s">
+        <v>8395</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="B1340" s="6" t="s">
+        <v>8396</v>
+      </c>
+      <c r="C1340" s="6" t="s">
+        <v>8397</v>
+      </c>
+      <c r="D1340" s="6" t="s">
+        <v>8398</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="B1341" s="5" t="s">
+        <v>8399</v>
+      </c>
+      <c r="C1341" s="5" t="s">
+        <v>8400</v>
+      </c>
+      <c r="D1341" s="5" t="s">
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="B1342" s="6" t="s">
+        <v>8402</v>
+      </c>
+      <c r="C1342" s="6" t="s">
+        <v>8403</v>
+      </c>
+      <c r="D1342" s="6" t="s">
+        <v>8404</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="B1343" s="5" t="s">
+        <v>8405</v>
+      </c>
+      <c r="C1343" s="5" t="s">
+        <v>8406</v>
+      </c>
+      <c r="D1343" s="5" t="s">
+        <v>8407</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="B1344" s="6" t="s">
+        <v>8408</v>
+      </c>
+      <c r="C1344" s="6" t="s">
+        <v>8409</v>
+      </c>
+      <c r="D1344" s="6" t="s">
+        <v>8409</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="B1345" s="5" t="s">
+        <v>8410</v>
+      </c>
+      <c r="C1345" s="5" t="s">
+        <v>8411</v>
+      </c>
+      <c r="D1345" s="5" t="s">
+        <v>8412</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="B1346" s="6" t="s">
+        <v>8413</v>
+      </c>
+      <c r="C1346" s="6" t="s">
+        <v>8409</v>
+      </c>
+      <c r="D1346" s="6" t="s">
+        <v>8409</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="B1347" s="5" t="s">
+        <v>8414</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="B1348" s="6" t="s">
+        <v>8415</v>
+      </c>
+      <c r="C1348" s="6" t="s">
+        <v>8416</v>
+      </c>
+      <c r="D1348" s="6" t="s">
+        <v>8417</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="B1349" s="5" t="s">
+        <v>8418</v>
+      </c>
+      <c r="C1349" s="5" t="s">
+        <v>8419</v>
+      </c>
+      <c r="D1349" s="5" t="s">
+        <v>8420</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="B1350" s="6" t="s">
+        <v>8421</v>
+      </c>
+      <c r="C1350" s="6" t="s">
+        <v>8422</v>
+      </c>
+      <c r="D1350" s="6" t="s">
+        <v>8423</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="B1351" s="5" t="s">
+        <v>8424</v>
+      </c>
+      <c r="C1351" s="5" t="s">
+        <v>8425</v>
+      </c>
+      <c r="D1351" s="5" t="s">
+        <v>8426</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="B1352" s="6" t="s">
+        <v>8427</v>
+      </c>
+      <c r="C1352" s="6" t="s">
+        <v>6006</v>
+      </c>
+      <c r="D1352" s="6" t="s">
+        <v>8428</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="B1353" s="5" t="s">
+        <v>8429</v>
+      </c>
+      <c r="C1353" s="5" t="s">
+        <v>8430</v>
+      </c>
+      <c r="D1353" s="5" t="s">
+        <v>8431</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="B1354" s="6" t="s">
+        <v>8432</v>
+      </c>
+      <c r="C1354" s="6" t="s">
+        <v>8433</v>
+      </c>
+      <c r="D1354" s="6" t="s">
+        <v>8434</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="B1355" s="5" t="s">
+        <v>8435</v>
+      </c>
+      <c r="C1355" s="5" t="s">
+        <v>8436</v>
+      </c>
+      <c r="D1355" s="5" t="s">
+        <v>8437</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="B1356" s="6" t="s">
+        <v>8438</v>
+      </c>
+      <c r="C1356" s="6" t="s">
+        <v>8439</v>
+      </c>
+      <c r="D1356" s="6" t="s">
+        <v>8440</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="B1357" s="5" t="s">
+        <v>8441</v>
+      </c>
+      <c r="C1357" s="5" t="s">
+        <v>8442</v>
+      </c>
+      <c r="D1357" s="5" t="s">
+        <v>8443</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="B1358" s="6" t="s">
+        <v>8444</v>
+      </c>
+      <c r="C1358" s="6" t="s">
+        <v>8445</v>
+      </c>
+      <c r="D1358" s="6" t="s">
+        <v>8445</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="B1359" s="5" t="s">
+        <v>8446</v>
+      </c>
+      <c r="C1359" s="5" t="s">
+        <v>8447</v>
+      </c>
+      <c r="D1359" s="5" t="s">
+        <v>8448</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="B1360" s="6" t="s">
+        <v>8449</v>
+      </c>
+      <c r="C1360" s="6" t="s">
+        <v>8450</v>
+      </c>
+      <c r="D1360" s="6" t="s">
+        <v>8451</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="B1361" s="5" t="s">
+        <v>8452</v>
+      </c>
+      <c r="C1361" s="5" t="s">
+        <v>8453</v>
+      </c>
+      <c r="D1361" s="5" t="s">
+        <v>8454</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="B1362" s="6" t="s">
+        <v>8455</v>
+      </c>
+      <c r="C1362" s="6" t="s">
+        <v>8456</v>
+      </c>
+      <c r="D1362" s="6" t="s">
+        <v>8457</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="B1363" s="5" t="s">
+        <v>8458</v>
+      </c>
+      <c r="C1363" s="5" t="s">
+        <v>8459</v>
+      </c>
+      <c r="D1363" s="5" t="s">
+        <v>8460</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="B1364" s="6" t="s">
+        <v>8461</v>
+      </c>
+      <c r="C1364" s="6" t="s">
+        <v>8462</v>
+      </c>
+      <c r="D1364" s="6" t="s">
+        <v>8463</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="B1365" s="5" t="s">
+        <v>8464</v>
+      </c>
+      <c r="C1365" s="5" t="s">
+        <v>8465</v>
+      </c>
+      <c r="D1365" s="5" t="s">
+        <v>8466</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="B1366" s="6" t="s">
+        <v>8467</v>
+      </c>
+      <c r="C1366" s="6" t="s">
+        <v>8468</v>
+      </c>
+      <c r="D1366" s="6" t="s">
+        <v>8469</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="B1367" s="5" t="s">
+        <v>8470</v>
+      </c>
+      <c r="C1367" s="5" t="s">
+        <v>8471</v>
+      </c>
+      <c r="D1367" s="5" t="s">
+        <v>8472</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="B1368" s="6" t="s">
+        <v>8473</v>
+      </c>
+      <c r="C1368" s="6" t="s">
+        <v>8474</v>
+      </c>
+      <c r="D1368" s="6" t="s">
+        <v>8475</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="B1369" s="5" t="s">
+        <v>8476</v>
+      </c>
+      <c r="C1369" s="5" t="s">
+        <v>8477</v>
+      </c>
+      <c r="D1369" s="5" t="s">
+        <v>8478</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="B1370" s="6" t="s">
+        <v>8479</v>
+      </c>
+      <c r="C1370" s="6" t="s">
+        <v>8480</v>
+      </c>
+      <c r="D1370" s="6" t="s">
+        <v>8481</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="B1371" s="5" t="s">
+        <v>8482</v>
+      </c>
+      <c r="C1371" s="5" t="s">
+        <v>8483</v>
+      </c>
+      <c r="D1371" s="5" t="s">
+        <v>8484</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="B1372" s="6" t="s">
+        <v>8485</v>
+      </c>
+      <c r="C1372" s="6" t="s">
+        <v>8486</v>
+      </c>
+      <c r="D1372" s="6" t="s">
+        <v>8487</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="B1373" s="5" t="s">
+        <v>8488</v>
+      </c>
+      <c r="C1373" s="5" t="s">
+        <v>4476</v>
+      </c>
+      <c r="D1373" s="5" t="s">
+        <v>8489</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H1307"/>
+  <autoFilter ref="B2:H1373"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -55349,10 +56621,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>8309</v>
+        <v>8490</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8310</v>
+        <v>8491</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -55363,16 +56635,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8311</v>
+        <v>8492</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8312</v>
+        <v>8493</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8313</v>
+        <v>8494</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8314</v>
+        <v>8495</v>
       </c>
     </row>
     <row r="3">
@@ -55380,16 +56652,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8315</v>
+        <v>8496</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8316</v>
+        <v>8497</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8317</v>
+        <v>8498</v>
       </c>
     </row>
     <row r="4">
@@ -55400,24 +56672,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8318</v>
+        <v>8499</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8319</v>
+        <v>8500</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8320</v>
+        <v>8501</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>8321</v>
+        <v>8502</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4463</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8322</v>
+        <v>8503</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -55425,13 +56697,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>8323</v>
+        <v>8504</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4470</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>8324</v>
+        <v>8505</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -55439,13 +56711,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>8325</v>
+        <v>8506</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4476</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8326</v>
+        <v>8507</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -55453,13 +56725,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>8327</v>
+        <v>8508</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4482</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>8328</v>
+        <v>8509</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -55467,13 +56739,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>8329</v>
+        <v>8510</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4489</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8330</v>
+        <v>8511</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -55481,13 +56753,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>8331</v>
+        <v>8512</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4496</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>8332</v>
+        <v>8513</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -55495,13 +56767,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>8333</v>
+        <v>8514</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4502</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>8334</v>
+        <v>8515</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -55509,13 +56781,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>8335</v>
+        <v>8516</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4508</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>8336</v>
+        <v>8517</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -55523,13 +56795,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>8337</v>
+        <v>8518</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4515</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8338</v>
+        <v>8519</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -55537,13 +56809,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>8339</v>
+        <v>8520</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4521</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>8340</v>
+        <v>8521</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -55557,7 +56829,7 @@
         <v>4527</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8341</v>
+        <v>8522</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -55565,13 +56837,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>8342</v>
+        <v>8523</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4534</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>8343</v>
+        <v>8524</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -55579,13 +56851,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>8344</v>
+        <v>8525</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4541</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>8345</v>
+        <v>8526</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -55593,13 +56865,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>8346</v>
+        <v>8527</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4547</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>8347</v>
+        <v>8528</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -55607,13 +56879,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>8348</v>
+        <v>8529</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4554</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>8349</v>
+        <v>8530</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -55621,13 +56893,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>8350</v>
+        <v>8531</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4560</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>8351</v>
+        <v>8532</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -55635,13 +56907,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>8352</v>
+        <v>8533</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4565</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>8353</v>
+        <v>8534</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -55649,13 +56921,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>8354</v>
+        <v>8535</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4572</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>8355</v>
+        <v>8536</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -55663,13 +56935,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>8356</v>
+        <v>8537</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4394</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>8357</v>
+        <v>8538</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -55677,13 +56949,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>8358</v>
+        <v>8539</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4580</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>8359</v>
+        <v>8540</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1373]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1378]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9408" uniqueCount="8541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9443" uniqueCount="8566">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -24200,6 +24200,81 @@
   </si>
   <si>
     <t xml:space="preserve">Herausforderung starten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.setup.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱과 스테이크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deck &amp; Stake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デッキとステーク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">牌组与赌注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">牌組與賭注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deck &amp; Einsatz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.setup.decks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DECK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.setup.stakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赌注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">賭注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EINSATZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.setup.effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작 조건</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STARTING RULES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開始条件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">起始条件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">起始條件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STARTREGELN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.setup.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 덱으로 시작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runde starten</t>
   </si>
   <si>
     <t xml:space="preserve">ui.challenge.rules</t>
@@ -25839,7 +25914,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -25848,7 +25923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1373"/>
+  <dimension ref="A1:H1378"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -54920,160 +54995,160 @@
         <v>8068</v>
       </c>
       <c r="C1266" s="6" t="s">
+        <v>6939</v>
+      </c>
+      <c r="D1266" s="6" t="s">
         <v>8069</v>
       </c>
-      <c r="D1266" s="6" t="s">
-        <v>8070</v>
-      </c>
       <c r="E1266" s="6" t="s">
-        <v>8071</v>
+        <v>6940</v>
       </c>
       <c r="F1266" s="6" t="s">
-        <v>8072</v>
+        <v>6941</v>
       </c>
       <c r="G1266" s="6" t="s">
-        <v>8072</v>
+        <v>6942</v>
       </c>
       <c r="H1266" s="6" t="s">
-        <v>8073</v>
+        <v>8069</v>
       </c>
     </row>
     <row r="1267">
       <c r="B1267" s="5" t="s">
+        <v>8070</v>
+      </c>
+      <c r="C1267" s="5" t="s">
+        <v>6739</v>
+      </c>
+      <c r="D1267" s="5" t="s">
+        <v>8071</v>
+      </c>
+      <c r="E1267" s="5" t="s">
+        <v>6741</v>
+      </c>
+      <c r="F1267" s="5" t="s">
+        <v>8072</v>
+      </c>
+      <c r="G1267" s="5" t="s">
+        <v>8073</v>
+      </c>
+      <c r="H1267" s="5" t="s">
         <v>8074</v>
-      </c>
-      <c r="C1267" s="5" t="s">
-        <v>8075</v>
-      </c>
-      <c r="D1267" s="5" t="s">
-        <v>8076</v>
-      </c>
-      <c r="E1267" s="5" t="s">
-        <v>8077</v>
-      </c>
-      <c r="F1267" s="5" t="s">
-        <v>8078</v>
-      </c>
-      <c r="G1267" s="5" t="s">
-        <v>8079</v>
-      </c>
-      <c r="H1267" s="5" t="s">
-        <v>8080</v>
       </c>
     </row>
     <row r="1268">
       <c r="B1268" s="6" t="s">
+        <v>8075</v>
+      </c>
+      <c r="C1268" s="6" t="s">
+        <v>8076</v>
+      </c>
+      <c r="D1268" s="6" t="s">
+        <v>8077</v>
+      </c>
+      <c r="E1268" s="6" t="s">
+        <v>8078</v>
+      </c>
+      <c r="F1268" s="6" t="s">
+        <v>8079</v>
+      </c>
+      <c r="G1268" s="6" t="s">
+        <v>8080</v>
+      </c>
+      <c r="H1268" s="6" t="s">
         <v>8081</v>
-      </c>
-      <c r="C1268" s="6" t="s">
-        <v>8082</v>
-      </c>
-      <c r="D1268" s="6" t="s">
-        <v>8083</v>
-      </c>
-      <c r="E1268" s="6" t="s">
-        <v>8084</v>
-      </c>
-      <c r="F1268" s="6" t="s">
-        <v>8085</v>
-      </c>
-      <c r="G1268" s="6" t="s">
-        <v>8086</v>
-      </c>
-      <c r="H1268" s="6" t="s">
-        <v>8087</v>
       </c>
     </row>
     <row r="1269">
       <c r="B1269" s="5" t="s">
-        <v>8088</v>
+        <v>8082</v>
       </c>
       <c r="C1269" s="5" t="s">
-        <v>8089</v>
+        <v>8083</v>
       </c>
       <c r="D1269" s="5" t="s">
-        <v>8090</v>
+        <v>8084</v>
       </c>
       <c r="E1269" s="5" t="s">
-        <v>8091</v>
+        <v>8057</v>
       </c>
       <c r="F1269" s="5" t="s">
-        <v>7289</v>
+        <v>8058</v>
       </c>
       <c r="G1269" s="5" t="s">
-        <v>7290</v>
+        <v>8059</v>
       </c>
       <c r="H1269" s="5" t="s">
-        <v>8092</v>
+        <v>8085</v>
       </c>
     </row>
     <row r="1270">
       <c r="B1270" s="6" t="s">
-        <v>8093</v>
+        <v>8086</v>
       </c>
       <c r="C1270" s="6" t="s">
-        <v>8094</v>
+        <v>8087</v>
       </c>
       <c r="D1270" s="6" t="s">
-        <v>8095</v>
+        <v>8088</v>
       </c>
       <c r="E1270" s="6" t="s">
-        <v>8096</v>
+        <v>8089</v>
       </c>
       <c r="F1270" s="6" t="s">
-        <v>8097</v>
+        <v>8090</v>
       </c>
       <c r="G1270" s="6" t="s">
-        <v>8098</v>
+        <v>8091</v>
       </c>
       <c r="H1270" s="6" t="s">
-        <v>8099</v>
+        <v>8092</v>
       </c>
     </row>
     <row r="1271">
       <c r="B1271" s="5" t="s">
-        <v>8100</v>
+        <v>8093</v>
       </c>
       <c r="C1271" s="5" t="s">
-        <v>8101</v>
+        <v>8094</v>
       </c>
       <c r="D1271" s="5" t="s">
-        <v>8102</v>
+        <v>8095</v>
       </c>
       <c r="E1271" s="5" t="s">
-        <v>8103</v>
+        <v>8096</v>
       </c>
       <c r="F1271" s="5" t="s">
-        <v>8104</v>
+        <v>8097</v>
       </c>
       <c r="G1271" s="5" t="s">
-        <v>8103</v>
+        <v>8097</v>
       </c>
       <c r="H1271" s="5" t="s">
-        <v>8102</v>
+        <v>8098</v>
       </c>
     </row>
     <row r="1272">
       <c r="B1272" s="6" t="s">
+        <v>8099</v>
+      </c>
+      <c r="C1272" s="6" t="s">
+        <v>8100</v>
+      </c>
+      <c r="D1272" s="6" t="s">
+        <v>8101</v>
+      </c>
+      <c r="E1272" s="6" t="s">
+        <v>8102</v>
+      </c>
+      <c r="F1272" s="6" t="s">
+        <v>8103</v>
+      </c>
+      <c r="G1272" s="6" t="s">
+        <v>8104</v>
+      </c>
+      <c r="H1272" s="6" t="s">
         <v>8105</v>
-      </c>
-      <c r="C1272" s="6" t="s">
-        <v>5927</v>
-      </c>
-      <c r="D1272" s="6" t="s">
-        <v>7856</v>
-      </c>
-      <c r="E1272" s="6" t="s">
-        <v>5929</v>
-      </c>
-      <c r="F1272" s="6" t="s">
-        <v>7857</v>
-      </c>
-      <c r="G1272" s="6" t="s">
-        <v>7857</v>
-      </c>
-      <c r="H1272" s="6" t="s">
-        <v>5298</v>
       </c>
     </row>
     <row r="1273">
@@ -55081,243 +55156,243 @@
         <v>8106</v>
       </c>
       <c r="C1273" s="5" t="s">
-        <v>5974</v>
+        <v>8107</v>
       </c>
       <c r="D1273" s="5" t="s">
-        <v>8107</v>
+        <v>8108</v>
       </c>
       <c r="E1273" s="5" t="s">
-        <v>5976</v>
+        <v>8109</v>
       </c>
       <c r="F1273" s="5" t="s">
-        <v>8108</v>
+        <v>8110</v>
       </c>
       <c r="G1273" s="5" t="s">
-        <v>8109</v>
+        <v>8111</v>
       </c>
       <c r="H1273" s="5" t="s">
-        <v>8110</v>
+        <v>8112</v>
       </c>
     </row>
     <row r="1274">
       <c r="B1274" s="6" t="s">
-        <v>8111</v>
+        <v>8113</v>
       </c>
       <c r="C1274" s="6" t="s">
-        <v>6919</v>
+        <v>8114</v>
       </c>
       <c r="D1274" s="6" t="s">
-        <v>8112</v>
+        <v>8115</v>
       </c>
       <c r="E1274" s="6" t="s">
-        <v>6921</v>
+        <v>8116</v>
       </c>
       <c r="F1274" s="6" t="s">
-        <v>5910</v>
+        <v>7289</v>
       </c>
       <c r="G1274" s="6" t="s">
-        <v>5911</v>
+        <v>7290</v>
       </c>
       <c r="H1274" s="6" t="s">
-        <v>6920</v>
+        <v>8117</v>
       </c>
     </row>
     <row r="1275">
       <c r="B1275" s="5" t="s">
-        <v>8113</v>
+        <v>8118</v>
       </c>
       <c r="C1275" s="5" t="s">
-        <v>6925</v>
+        <v>8119</v>
       </c>
       <c r="D1275" s="5" t="s">
-        <v>8114</v>
+        <v>8120</v>
       </c>
       <c r="E1275" s="5" t="s">
-        <v>6927</v>
+        <v>8121</v>
       </c>
       <c r="F1275" s="5" t="s">
-        <v>5917</v>
+        <v>8122</v>
       </c>
       <c r="G1275" s="5" t="s">
-        <v>5917</v>
+        <v>8123</v>
       </c>
       <c r="H1275" s="5" t="s">
-        <v>8115</v>
+        <v>8124</v>
       </c>
     </row>
     <row r="1276">
       <c r="B1276" s="6" t="s">
-        <v>8116</v>
+        <v>8125</v>
       </c>
       <c r="C1276" s="6" t="s">
-        <v>6930</v>
+        <v>8126</v>
       </c>
       <c r="D1276" s="6" t="s">
-        <v>8117</v>
+        <v>8127</v>
       </c>
       <c r="E1276" s="6" t="s">
-        <v>6932</v>
+        <v>8128</v>
       </c>
       <c r="F1276" s="6" t="s">
-        <v>5923</v>
+        <v>8129</v>
       </c>
       <c r="G1276" s="6" t="s">
-        <v>5924</v>
+        <v>8128</v>
       </c>
       <c r="H1276" s="6" t="s">
-        <v>6935</v>
+        <v>8127</v>
       </c>
     </row>
     <row r="1277">
       <c r="B1277" s="5" t="s">
-        <v>8118</v>
+        <v>8130</v>
       </c>
       <c r="C1277" s="5" t="s">
-        <v>5940</v>
+        <v>5927</v>
       </c>
       <c r="D1277" s="5" t="s">
-        <v>8119</v>
+        <v>7856</v>
       </c>
       <c r="E1277" s="5" t="s">
-        <v>5942</v>
+        <v>5929</v>
       </c>
       <c r="F1277" s="5" t="s">
-        <v>5943</v>
+        <v>7857</v>
       </c>
       <c r="G1277" s="5" t="s">
-        <v>5944</v>
+        <v>7857</v>
       </c>
       <c r="H1277" s="5" t="s">
-        <v>8120</v>
+        <v>5298</v>
       </c>
     </row>
     <row r="1278">
       <c r="B1278" s="6" t="s">
-        <v>8121</v>
+        <v>8131</v>
       </c>
       <c r="C1278" s="6" t="s">
-        <v>8122</v>
+        <v>5974</v>
       </c>
       <c r="D1278" s="6" t="s">
-        <v>8123</v>
+        <v>8132</v>
       </c>
       <c r="E1278" s="6" t="s">
-        <v>5970</v>
+        <v>5976</v>
       </c>
       <c r="F1278" s="6" t="s">
-        <v>8124</v>
+        <v>8133</v>
       </c>
       <c r="G1278" s="6" t="s">
-        <v>8125</v>
+        <v>8134</v>
       </c>
       <c r="H1278" s="6" t="s">
-        <v>6917</v>
+        <v>8135</v>
       </c>
     </row>
     <row r="1279">
       <c r="B1279" s="5" t="s">
-        <v>8126</v>
+        <v>8136</v>
       </c>
       <c r="C1279" s="5" t="s">
-        <v>6903</v>
+        <v>6919</v>
       </c>
       <c r="D1279" s="5" t="s">
-        <v>8127</v>
+        <v>8137</v>
       </c>
       <c r="E1279" s="5" t="s">
-        <v>6905</v>
+        <v>6921</v>
       </c>
       <c r="F1279" s="5" t="s">
-        <v>8128</v>
+        <v>5910</v>
       </c>
       <c r="G1279" s="5" t="s">
-        <v>8128</v>
+        <v>5911</v>
       </c>
       <c r="H1279" s="5" t="s">
-        <v>8129</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="1280">
       <c r="B1280" s="6" t="s">
-        <v>8130</v>
+        <v>8138</v>
       </c>
       <c r="C1280" s="6" t="s">
-        <v>8131</v>
+        <v>6925</v>
       </c>
       <c r="D1280" s="6" t="s">
-        <v>8132</v>
+        <v>8139</v>
       </c>
       <c r="E1280" s="6" t="s">
-        <v>8133</v>
+        <v>6927</v>
       </c>
       <c r="F1280" s="6" t="s">
-        <v>8134</v>
+        <v>5917</v>
       </c>
       <c r="G1280" s="6" t="s">
-        <v>8135</v>
+        <v>5917</v>
       </c>
       <c r="H1280" s="6" t="s">
-        <v>8136</v>
+        <v>8140</v>
       </c>
     </row>
     <row r="1281">
       <c r="B1281" s="5" t="s">
-        <v>8137</v>
+        <v>8141</v>
       </c>
       <c r="C1281" s="5" t="s">
-        <v>8048</v>
+        <v>6930</v>
       </c>
       <c r="D1281" s="5" t="s">
-        <v>8049</v>
+        <v>8142</v>
       </c>
       <c r="E1281" s="5" t="s">
-        <v>8050</v>
+        <v>6932</v>
       </c>
       <c r="F1281" s="5" t="s">
-        <v>8051</v>
+        <v>5923</v>
       </c>
       <c r="G1281" s="5" t="s">
-        <v>8052</v>
+        <v>5924</v>
       </c>
       <c r="H1281" s="5" t="s">
-        <v>8053</v>
+        <v>6935</v>
       </c>
     </row>
     <row r="1282">
       <c r="B1282" s="6" t="s">
-        <v>8138</v>
+        <v>8143</v>
       </c>
       <c r="C1282" s="6" t="s">
-        <v>8139</v>
+        <v>5940</v>
       </c>
       <c r="D1282" s="6" t="s">
-        <v>8140</v>
+        <v>8144</v>
       </c>
       <c r="E1282" s="6" t="s">
-        <v>8141</v>
+        <v>5942</v>
       </c>
       <c r="F1282" s="6" t="s">
-        <v>8142</v>
+        <v>5943</v>
       </c>
       <c r="G1282" s="6" t="s">
-        <v>8143</v>
+        <v>5944</v>
       </c>
       <c r="H1282" s="6" t="s">
-        <v>8144</v>
+        <v>8145</v>
       </c>
     </row>
     <row r="1283">
       <c r="B1283" s="5" t="s">
-        <v>8145</v>
+        <v>8146</v>
       </c>
       <c r="C1283" s="5" t="s">
-        <v>8146</v>
+        <v>8147</v>
       </c>
       <c r="D1283" s="5" t="s">
-        <v>8147</v>
+        <v>8148</v>
       </c>
       <c r="E1283" s="5" t="s">
-        <v>8148</v>
+        <v>5970</v>
       </c>
       <c r="F1283" s="5" t="s">
         <v>8149</v>
@@ -55326,1283 +55401,1398 @@
         <v>8150</v>
       </c>
       <c r="H1283" s="5" t="s">
-        <v>8151</v>
+        <v>6917</v>
       </c>
     </row>
     <row r="1284">
       <c r="B1284" s="6" t="s">
+        <v>8151</v>
+      </c>
+      <c r="C1284" s="6" t="s">
+        <v>6903</v>
+      </c>
+      <c r="D1284" s="6" t="s">
         <v>8152</v>
       </c>
-      <c r="C1284" s="6" t="s">
+      <c r="E1284" s="6" t="s">
+        <v>6905</v>
+      </c>
+      <c r="F1284" s="6" t="s">
         <v>8153</v>
       </c>
-      <c r="D1284" s="6" t="s">
+      <c r="G1284" s="6" t="s">
+        <v>8153</v>
+      </c>
+      <c r="H1284" s="6" t="s">
         <v>8154</v>
-      </c>
-      <c r="E1284" s="6" t="s">
-        <v>8155</v>
-      </c>
-      <c r="F1284" s="6" t="s">
-        <v>8156</v>
-      </c>
-      <c r="G1284" s="6" t="s">
-        <v>8157</v>
-      </c>
-      <c r="H1284" s="6" t="s">
-        <v>8158</v>
       </c>
     </row>
     <row r="1285">
       <c r="B1285" s="5" t="s">
+        <v>8155</v>
+      </c>
+      <c r="C1285" s="5" t="s">
+        <v>8156</v>
+      </c>
+      <c r="D1285" s="5" t="s">
+        <v>8157</v>
+      </c>
+      <c r="E1285" s="5" t="s">
+        <v>8158</v>
+      </c>
+      <c r="F1285" s="5" t="s">
         <v>8159</v>
       </c>
-      <c r="C1285" s="5" t="s">
+      <c r="G1285" s="5" t="s">
         <v>8160</v>
       </c>
-      <c r="D1285" s="5" t="s">
+      <c r="H1285" s="5" t="s">
         <v>8161</v>
-      </c>
-      <c r="E1285" s="5" t="s">
-        <v>8162</v>
-      </c>
-      <c r="F1285" s="5" t="s">
-        <v>8163</v>
-      </c>
-      <c r="G1285" s="5" t="s">
-        <v>8164</v>
-      </c>
-      <c r="H1285" s="5" t="s">
-        <v>8165</v>
       </c>
     </row>
     <row r="1286">
       <c r="B1286" s="6" t="s">
-        <v>8166</v>
+        <v>8162</v>
       </c>
       <c r="C1286" s="6" t="s">
-        <v>8167</v>
+        <v>8048</v>
       </c>
       <c r="D1286" s="6" t="s">
-        <v>8168</v>
+        <v>8049</v>
       </c>
       <c r="E1286" s="6" t="s">
-        <v>8169</v>
+        <v>8050</v>
       </c>
       <c r="F1286" s="6" t="s">
-        <v>8170</v>
+        <v>8051</v>
       </c>
       <c r="G1286" s="6" t="s">
-        <v>8171</v>
+        <v>8052</v>
       </c>
       <c r="H1286" s="6" t="s">
-        <v>8172</v>
+        <v>8053</v>
       </c>
     </row>
     <row r="1287">
       <c r="B1287" s="5" t="s">
-        <v>8173</v>
+        <v>8163</v>
       </c>
       <c r="C1287" s="5" t="s">
-        <v>8174</v>
+        <v>8164</v>
       </c>
       <c r="D1287" s="5" t="s">
-        <v>8175</v>
+        <v>8165</v>
       </c>
       <c r="E1287" s="5" t="s">
-        <v>8176</v>
+        <v>8166</v>
       </c>
       <c r="F1287" s="5" t="s">
-        <v>8177</v>
+        <v>8167</v>
       </c>
       <c r="G1287" s="5" t="s">
-        <v>8178</v>
+        <v>8168</v>
       </c>
       <c r="H1287" s="5" t="s">
-        <v>8179</v>
+        <v>8169</v>
       </c>
     </row>
     <row r="1288">
       <c r="B1288" s="6" t="s">
-        <v>8180</v>
+        <v>8170</v>
       </c>
       <c r="C1288" s="6" t="s">
-        <v>8181</v>
+        <v>8171</v>
       </c>
       <c r="D1288" s="6" t="s">
-        <v>8182</v>
+        <v>8172</v>
       </c>
       <c r="E1288" s="6" t="s">
-        <v>8183</v>
+        <v>8173</v>
       </c>
       <c r="F1288" s="6" t="s">
-        <v>8184</v>
+        <v>8174</v>
       </c>
       <c r="G1288" s="6" t="s">
-        <v>8184</v>
+        <v>8175</v>
       </c>
       <c r="H1288" s="6" t="s">
-        <v>8185</v>
+        <v>8176</v>
       </c>
     </row>
     <row r="1289">
       <c r="B1289" s="5" t="s">
-        <v>8186</v>
+        <v>8177</v>
       </c>
       <c r="C1289" s="5" t="s">
-        <v>8187</v>
+        <v>8178</v>
       </c>
       <c r="D1289" s="5" t="s">
-        <v>8188</v>
+        <v>8179</v>
       </c>
       <c r="E1289" s="5" t="s">
-        <v>8189</v>
+        <v>8180</v>
       </c>
       <c r="F1289" s="5" t="s">
-        <v>8190</v>
+        <v>8181</v>
       </c>
       <c r="G1289" s="5" t="s">
-        <v>8191</v>
+        <v>8182</v>
       </c>
       <c r="H1289" s="5" t="s">
-        <v>8192</v>
+        <v>8183</v>
       </c>
     </row>
     <row r="1290">
       <c r="B1290" s="6" t="s">
-        <v>8193</v>
+        <v>8184</v>
       </c>
       <c r="C1290" s="6" t="s">
-        <v>8194</v>
+        <v>8185</v>
       </c>
       <c r="D1290" s="6" t="s">
-        <v>8195</v>
+        <v>8186</v>
       </c>
       <c r="E1290" s="6" t="s">
-        <v>8196</v>
+        <v>8187</v>
       </c>
       <c r="F1290" s="6" t="s">
-        <v>8197</v>
+        <v>8188</v>
       </c>
       <c r="G1290" s="6" t="s">
-        <v>8198</v>
+        <v>8189</v>
       </c>
       <c r="H1290" s="6" t="s">
-        <v>8199</v>
+        <v>8190</v>
       </c>
     </row>
     <row r="1291">
       <c r="B1291" s="5" t="s">
-        <v>8200</v>
+        <v>8191</v>
       </c>
       <c r="C1291" s="5" t="s">
-        <v>8201</v>
+        <v>8192</v>
       </c>
       <c r="D1291" s="5" t="s">
-        <v>8202</v>
+        <v>8193</v>
       </c>
       <c r="E1291" s="5" t="s">
-        <v>8203</v>
+        <v>8194</v>
       </c>
       <c r="F1291" s="5" t="s">
-        <v>8204</v>
+        <v>8195</v>
       </c>
       <c r="G1291" s="5" t="s">
-        <v>8205</v>
+        <v>8196</v>
       </c>
       <c r="H1291" s="5" t="s">
-        <v>8206</v>
+        <v>8197</v>
       </c>
     </row>
     <row r="1292">
       <c r="B1292" s="6" t="s">
-        <v>8207</v>
+        <v>8198</v>
       </c>
       <c r="C1292" s="6" t="s">
-        <v>8208</v>
+        <v>8199</v>
       </c>
       <c r="D1292" s="6" t="s">
-        <v>8209</v>
+        <v>8200</v>
       </c>
       <c r="E1292" s="6" t="s">
-        <v>8210</v>
+        <v>8201</v>
       </c>
       <c r="F1292" s="6" t="s">
-        <v>8211</v>
+        <v>8202</v>
       </c>
       <c r="G1292" s="6" t="s">
-        <v>8212</v>
+        <v>8203</v>
       </c>
       <c r="H1292" s="6" t="s">
-        <v>8213</v>
+        <v>8204</v>
       </c>
     </row>
     <row r="1293">
       <c r="B1293" s="5" t="s">
-        <v>8214</v>
+        <v>8205</v>
       </c>
       <c r="C1293" s="5" t="s">
-        <v>8215</v>
+        <v>8206</v>
       </c>
       <c r="D1293" s="5" t="s">
-        <v>8216</v>
+        <v>8207</v>
       </c>
       <c r="E1293" s="5" t="s">
-        <v>8217</v>
+        <v>8208</v>
       </c>
       <c r="F1293" s="5" t="s">
-        <v>8218</v>
+        <v>8209</v>
       </c>
       <c r="G1293" s="5" t="s">
-        <v>8219</v>
+        <v>8209</v>
       </c>
       <c r="H1293" s="5" t="s">
-        <v>8220</v>
+        <v>8210</v>
       </c>
     </row>
     <row r="1294">
       <c r="B1294" s="6" t="s">
-        <v>8221</v>
+        <v>8211</v>
       </c>
       <c r="C1294" s="6" t="s">
-        <v>8222</v>
+        <v>8212</v>
       </c>
       <c r="D1294" s="6" t="s">
-        <v>8223</v>
+        <v>8213</v>
       </c>
       <c r="E1294" s="6" t="s">
-        <v>8224</v>
+        <v>8214</v>
       </c>
       <c r="F1294" s="6" t="s">
-        <v>8225</v>
+        <v>8215</v>
       </c>
       <c r="G1294" s="6" t="s">
-        <v>8226</v>
+        <v>8216</v>
       </c>
       <c r="H1294" s="6" t="s">
-        <v>8227</v>
+        <v>8217</v>
       </c>
     </row>
     <row r="1295">
       <c r="B1295" s="5" t="s">
-        <v>8228</v>
+        <v>8218</v>
       </c>
       <c r="C1295" s="5" t="s">
-        <v>8229</v>
+        <v>8219</v>
       </c>
       <c r="D1295" s="5" t="s">
-        <v>8230</v>
+        <v>8220</v>
       </c>
       <c r="E1295" s="5" t="s">
-        <v>8231</v>
+        <v>8221</v>
       </c>
       <c r="F1295" s="5" t="s">
-        <v>8232</v>
+        <v>8222</v>
       </c>
       <c r="G1295" s="5" t="s">
-        <v>8233</v>
+        <v>8223</v>
       </c>
       <c r="H1295" s="5" t="s">
-        <v>8234</v>
+        <v>8224</v>
       </c>
     </row>
     <row r="1296">
       <c r="B1296" s="6" t="s">
-        <v>8235</v>
+        <v>8225</v>
       </c>
       <c r="C1296" s="6" t="s">
-        <v>8236</v>
+        <v>8226</v>
       </c>
       <c r="D1296" s="6" t="s">
-        <v>8237</v>
+        <v>8227</v>
       </c>
       <c r="E1296" s="6" t="s">
-        <v>8238</v>
+        <v>8228</v>
       </c>
       <c r="F1296" s="6" t="s">
-        <v>8239</v>
+        <v>8229</v>
       </c>
       <c r="G1296" s="6" t="s">
-        <v>8240</v>
+        <v>8230</v>
       </c>
       <c r="H1296" s="6" t="s">
-        <v>8241</v>
+        <v>8231</v>
       </c>
     </row>
     <row r="1297">
       <c r="B1297" s="5" t="s">
-        <v>8242</v>
+        <v>8232</v>
       </c>
       <c r="C1297" s="5" t="s">
-        <v>8243</v>
+        <v>8233</v>
       </c>
       <c r="D1297" s="5" t="s">
-        <v>8244</v>
+        <v>8234</v>
       </c>
       <c r="E1297" s="5" t="s">
-        <v>8245</v>
+        <v>8235</v>
       </c>
       <c r="F1297" s="5" t="s">
-        <v>8246</v>
+        <v>8236</v>
       </c>
       <c r="G1297" s="5" t="s">
-        <v>8247</v>
+        <v>8237</v>
       </c>
       <c r="H1297" s="5" t="s">
-        <v>8248</v>
+        <v>8238</v>
       </c>
     </row>
     <row r="1298">
       <c r="B1298" s="6" t="s">
-        <v>8249</v>
+        <v>8239</v>
       </c>
       <c r="C1298" s="6" t="s">
-        <v>8250</v>
+        <v>8240</v>
       </c>
       <c r="D1298" s="6" t="s">
-        <v>8251</v>
+        <v>8241</v>
       </c>
       <c r="E1298" s="6" t="s">
-        <v>8252</v>
+        <v>8242</v>
       </c>
       <c r="F1298" s="6" t="s">
-        <v>8253</v>
+        <v>8243</v>
       </c>
       <c r="G1298" s="6" t="s">
-        <v>8254</v>
+        <v>8244</v>
       </c>
       <c r="H1298" s="6" t="s">
-        <v>8255</v>
+        <v>8245</v>
       </c>
     </row>
     <row r="1299">
       <c r="B1299" s="5" t="s">
-        <v>8256</v>
+        <v>8246</v>
       </c>
       <c r="C1299" s="5" t="s">
-        <v>8257</v>
+        <v>8247</v>
       </c>
       <c r="D1299" s="5" t="s">
-        <v>8258</v>
+        <v>8248</v>
       </c>
       <c r="E1299" s="5" t="s">
-        <v>8259</v>
+        <v>8249</v>
       </c>
       <c r="F1299" s="5" t="s">
-        <v>8260</v>
+        <v>8250</v>
       </c>
       <c r="G1299" s="5" t="s">
-        <v>8260</v>
+        <v>8251</v>
       </c>
       <c r="H1299" s="5" t="s">
-        <v>8261</v>
+        <v>8252</v>
       </c>
     </row>
     <row r="1300">
       <c r="B1300" s="6" t="s">
-        <v>8262</v>
+        <v>8253</v>
       </c>
       <c r="C1300" s="6" t="s">
-        <v>8263</v>
+        <v>8254</v>
       </c>
       <c r="D1300" s="6" t="s">
-        <v>8264</v>
+        <v>8255</v>
       </c>
       <c r="E1300" s="6" t="s">
-        <v>8265</v>
+        <v>8256</v>
       </c>
       <c r="F1300" s="6" t="s">
-        <v>8266</v>
+        <v>8257</v>
       </c>
       <c r="G1300" s="6" t="s">
-        <v>8267</v>
+        <v>8258</v>
       </c>
       <c r="H1300" s="6" t="s">
-        <v>8268</v>
+        <v>8259</v>
       </c>
     </row>
     <row r="1301">
       <c r="B1301" s="5" t="s">
-        <v>8269</v>
+        <v>8260</v>
       </c>
       <c r="C1301" s="5" t="s">
-        <v>8270</v>
+        <v>8261</v>
       </c>
       <c r="D1301" s="5" t="s">
-        <v>8271</v>
+        <v>8262</v>
       </c>
       <c r="E1301" s="5" t="s">
-        <v>8272</v>
+        <v>8263</v>
       </c>
       <c r="F1301" s="5" t="s">
-        <v>8190</v>
+        <v>8264</v>
       </c>
       <c r="G1301" s="5" t="s">
-        <v>8191</v>
+        <v>8265</v>
       </c>
       <c r="H1301" s="5" t="s">
-        <v>8273</v>
+        <v>8266</v>
       </c>
     </row>
     <row r="1302">
       <c r="B1302" s="6" t="s">
-        <v>8274</v>
+        <v>8267</v>
       </c>
       <c r="C1302" s="6" t="s">
-        <v>8275</v>
+        <v>8268</v>
       </c>
       <c r="D1302" s="6" t="s">
-        <v>8276</v>
+        <v>8269</v>
       </c>
       <c r="E1302" s="6" t="s">
-        <v>8277</v>
+        <v>8270</v>
       </c>
       <c r="F1302" s="6" t="s">
-        <v>8278</v>
+        <v>8271</v>
       </c>
       <c r="G1302" s="6" t="s">
-        <v>8279</v>
+        <v>8272</v>
       </c>
       <c r="H1302" s="6" t="s">
-        <v>8280</v>
+        <v>8273</v>
       </c>
     </row>
     <row r="1303">
       <c r="B1303" s="5" t="s">
-        <v>8281</v>
+        <v>8274</v>
       </c>
       <c r="C1303" s="5" t="s">
-        <v>8282</v>
+        <v>8275</v>
       </c>
       <c r="D1303" s="5" t="s">
-        <v>8283</v>
+        <v>8276</v>
       </c>
       <c r="E1303" s="5" t="s">
-        <v>8284</v>
+        <v>8277</v>
       </c>
       <c r="F1303" s="5" t="s">
-        <v>8285</v>
+        <v>8278</v>
       </c>
       <c r="G1303" s="5" t="s">
-        <v>8286</v>
+        <v>8279</v>
       </c>
       <c r="H1303" s="5" t="s">
-        <v>8287</v>
+        <v>8280</v>
       </c>
     </row>
     <row r="1304">
       <c r="B1304" s="6" t="s">
-        <v>8288</v>
+        <v>8281</v>
       </c>
       <c r="C1304" s="6" t="s">
-        <v>8289</v>
+        <v>8282</v>
       </c>
       <c r="D1304" s="6" t="s">
-        <v>8290</v>
+        <v>8283</v>
       </c>
       <c r="E1304" s="6" t="s">
-        <v>8291</v>
+        <v>8284</v>
       </c>
       <c r="F1304" s="6" t="s">
-        <v>8292</v>
+        <v>8285</v>
       </c>
       <c r="G1304" s="6" t="s">
-        <v>8292</v>
+        <v>8285</v>
       </c>
       <c r="H1304" s="6" t="s">
-        <v>8293</v>
+        <v>8286</v>
       </c>
     </row>
     <row r="1305">
       <c r="B1305" s="5" t="s">
-        <v>8294</v>
+        <v>8287</v>
       </c>
       <c r="C1305" s="5" t="s">
-        <v>8295</v>
+        <v>8288</v>
       </c>
       <c r="D1305" s="5" t="s">
-        <v>8296</v>
+        <v>8289</v>
       </c>
       <c r="E1305" s="5" t="s">
-        <v>8297</v>
+        <v>8290</v>
       </c>
       <c r="F1305" s="5" t="s">
-        <v>8298</v>
+        <v>8291</v>
       </c>
       <c r="G1305" s="5" t="s">
-        <v>8299</v>
+        <v>8292</v>
       </c>
       <c r="H1305" s="5" t="s">
-        <v>8300</v>
+        <v>8293</v>
       </c>
     </row>
     <row r="1306">
       <c r="B1306" s="6" t="s">
-        <v>8301</v>
+        <v>8294</v>
       </c>
       <c r="C1306" s="6" t="s">
-        <v>8302</v>
+        <v>8295</v>
       </c>
       <c r="D1306" s="6" t="s">
-        <v>8303</v>
+        <v>8296</v>
       </c>
       <c r="E1306" s="6" t="s">
-        <v>8304</v>
+        <v>8297</v>
       </c>
       <c r="F1306" s="6" t="s">
-        <v>8305</v>
+        <v>8215</v>
       </c>
       <c r="G1306" s="6" t="s">
-        <v>8305</v>
+        <v>8216</v>
       </c>
       <c r="H1306" s="6" t="s">
-        <v>8306</v>
+        <v>8298</v>
       </c>
     </row>
     <row r="1307">
       <c r="B1307" s="5" t="s">
-        <v>8307</v>
+        <v>8299</v>
       </c>
       <c r="C1307" s="5" t="s">
-        <v>6625</v>
+        <v>8300</v>
       </c>
       <c r="D1307" s="5" t="s">
-        <v>8308</v>
+        <v>8301</v>
       </c>
       <c r="E1307" s="5" t="s">
-        <v>6627</v>
+        <v>8302</v>
       </c>
       <c r="F1307" s="5" t="s">
-        <v>6628</v>
+        <v>8303</v>
       </c>
       <c r="G1307" s="5" t="s">
-        <v>6629</v>
+        <v>8304</v>
       </c>
       <c r="H1307" s="5" t="s">
-        <v>6630</v>
+        <v>8305</v>
       </c>
     </row>
     <row r="1308">
       <c r="B1308" s="6" t="s">
+        <v>8306</v>
+      </c>
+      <c r="C1308" s="6" t="s">
+        <v>8307</v>
+      </c>
+      <c r="D1308" s="6" t="s">
+        <v>8308</v>
+      </c>
+      <c r="E1308" s="6" t="s">
         <v>8309</v>
       </c>
-      <c r="C1308" s="6" t="s">
+      <c r="F1308" s="6" t="s">
         <v>8310</v>
       </c>
-      <c r="D1308" s="6" t="s">
+      <c r="G1308" s="6" t="s">
         <v>8311</v>
+      </c>
+      <c r="H1308" s="6" t="s">
+        <v>8312</v>
       </c>
     </row>
     <row r="1309">
       <c r="B1309" s="5" t="s">
-        <v>8312</v>
+        <v>8313</v>
       </c>
       <c r="C1309" s="5" t="s">
-        <v>8313</v>
+        <v>8314</v>
       </c>
       <c r="D1309" s="5" t="s">
-        <v>8314</v>
+        <v>8315</v>
+      </c>
+      <c r="E1309" s="5" t="s">
+        <v>8316</v>
+      </c>
+      <c r="F1309" s="5" t="s">
+        <v>8317</v>
+      </c>
+      <c r="G1309" s="5" t="s">
+        <v>8317</v>
+      </c>
+      <c r="H1309" s="5" t="s">
+        <v>8318</v>
       </c>
     </row>
     <row r="1310">
       <c r="B1310" s="6" t="s">
-        <v>8315</v>
+        <v>8319</v>
       </c>
       <c r="C1310" s="6" t="s">
-        <v>8316</v>
+        <v>8320</v>
       </c>
       <c r="D1310" s="6" t="s">
-        <v>8317</v>
+        <v>8321</v>
+      </c>
+      <c r="E1310" s="6" t="s">
+        <v>8322</v>
+      </c>
+      <c r="F1310" s="6" t="s">
+        <v>8323</v>
+      </c>
+      <c r="G1310" s="6" t="s">
+        <v>8324</v>
+      </c>
+      <c r="H1310" s="6" t="s">
+        <v>8325</v>
       </c>
     </row>
     <row r="1311">
       <c r="B1311" s="5" t="s">
-        <v>8318</v>
+        <v>8326</v>
       </c>
       <c r="C1311" s="5" t="s">
-        <v>8319</v>
+        <v>8327</v>
       </c>
       <c r="D1311" s="5" t="s">
-        <v>8320</v>
+        <v>8328</v>
+      </c>
+      <c r="E1311" s="5" t="s">
+        <v>8329</v>
+      </c>
+      <c r="F1311" s="5" t="s">
+        <v>8330</v>
+      </c>
+      <c r="G1311" s="5" t="s">
+        <v>8330</v>
+      </c>
+      <c r="H1311" s="5" t="s">
+        <v>8331</v>
       </c>
     </row>
     <row r="1312">
       <c r="B1312" s="6" t="s">
-        <v>8321</v>
+        <v>8332</v>
       </c>
       <c r="C1312" s="6" t="s">
-        <v>8322</v>
+        <v>6625</v>
       </c>
       <c r="D1312" s="6" t="s">
-        <v>8323</v>
+        <v>8333</v>
+      </c>
+      <c r="E1312" s="6" t="s">
+        <v>6627</v>
+      </c>
+      <c r="F1312" s="6" t="s">
+        <v>6628</v>
+      </c>
+      <c r="G1312" s="6" t="s">
+        <v>6629</v>
+      </c>
+      <c r="H1312" s="6" t="s">
+        <v>6630</v>
       </c>
     </row>
     <row r="1313">
       <c r="B1313" s="5" t="s">
-        <v>8324</v>
+        <v>8334</v>
       </c>
       <c r="C1313" s="5" t="s">
-        <v>8325</v>
+        <v>8335</v>
       </c>
       <c r="D1313" s="5" t="s">
-        <v>8326</v>
+        <v>8336</v>
       </c>
     </row>
     <row r="1314">
       <c r="B1314" s="6" t="s">
-        <v>8327</v>
+        <v>8337</v>
       </c>
       <c r="C1314" s="6" t="s">
-        <v>8328</v>
+        <v>8338</v>
       </c>
       <c r="D1314" s="6" t="s">
-        <v>8329</v>
+        <v>8339</v>
       </c>
     </row>
     <row r="1315">
       <c r="B1315" s="5" t="s">
-        <v>8330</v>
+        <v>8340</v>
       </c>
       <c r="C1315" s="5" t="s">
-        <v>8310</v>
+        <v>8341</v>
       </c>
       <c r="D1315" s="5" t="s">
-        <v>8311</v>
+        <v>8342</v>
       </c>
     </row>
     <row r="1316">
       <c r="B1316" s="6" t="s">
-        <v>8331</v>
+        <v>8343</v>
       </c>
       <c r="C1316" s="6" t="s">
-        <v>8332</v>
+        <v>8344</v>
       </c>
       <c r="D1316" s="6" t="s">
-        <v>8333</v>
+        <v>8345</v>
       </c>
     </row>
     <row r="1317">
       <c r="B1317" s="5" t="s">
-        <v>8334</v>
+        <v>8346</v>
       </c>
       <c r="C1317" s="5" t="s">
-        <v>8335</v>
+        <v>8347</v>
       </c>
       <c r="D1317" s="5" t="s">
-        <v>8336</v>
+        <v>8348</v>
       </c>
     </row>
     <row r="1318">
       <c r="B1318" s="6" t="s">
-        <v>8337</v>
+        <v>8349</v>
       </c>
       <c r="C1318" s="6" t="s">
-        <v>8338</v>
+        <v>8350</v>
       </c>
       <c r="D1318" s="6" t="s">
-        <v>8339</v>
+        <v>8351</v>
       </c>
     </row>
     <row r="1319">
       <c r="B1319" s="5" t="s">
-        <v>8340</v>
+        <v>8352</v>
       </c>
       <c r="C1319" s="5" t="s">
-        <v>8341</v>
+        <v>8353</v>
       </c>
       <c r="D1319" s="5" t="s">
-        <v>8342</v>
+        <v>8354</v>
       </c>
     </row>
     <row r="1320">
       <c r="B1320" s="6" t="s">
-        <v>8343</v>
+        <v>8355</v>
       </c>
       <c r="C1320" s="6" t="s">
-        <v>8344</v>
+        <v>8335</v>
       </c>
       <c r="D1320" s="6" t="s">
-        <v>8345</v>
+        <v>8336</v>
       </c>
     </row>
     <row r="1321">
       <c r="B1321" s="5" t="s">
-        <v>8346</v>
+        <v>8356</v>
       </c>
       <c r="C1321" s="5" t="s">
-        <v>8347</v>
+        <v>8357</v>
       </c>
       <c r="D1321" s="5" t="s">
-        <v>8348</v>
+        <v>8358</v>
       </c>
     </row>
     <row r="1322">
       <c r="B1322" s="6" t="s">
-        <v>8349</v>
+        <v>8359</v>
       </c>
       <c r="C1322" s="6" t="s">
-        <v>6739</v>
+        <v>8360</v>
       </c>
       <c r="D1322" s="6" t="s">
-        <v>8350</v>
+        <v>8361</v>
       </c>
     </row>
     <row r="1323">
       <c r="B1323" s="5" t="s">
-        <v>8351</v>
+        <v>8362</v>
       </c>
       <c r="C1323" s="5" t="s">
-        <v>6939</v>
+        <v>8363</v>
       </c>
       <c r="D1323" s="5" t="s">
-        <v>6676</v>
+        <v>8364</v>
       </c>
     </row>
     <row r="1324">
       <c r="B1324" s="6" t="s">
-        <v>8352</v>
+        <v>8365</v>
       </c>
       <c r="C1324" s="6" t="s">
-        <v>8048</v>
+        <v>8366</v>
       </c>
       <c r="D1324" s="6" t="s">
-        <v>8353</v>
+        <v>8367</v>
       </c>
     </row>
     <row r="1325">
       <c r="B1325" s="5" t="s">
-        <v>8354</v>
+        <v>8368</v>
       </c>
       <c r="C1325" s="5" t="s">
-        <v>8355</v>
+        <v>8369</v>
       </c>
       <c r="D1325" s="5" t="s">
-        <v>8356</v>
+        <v>8370</v>
       </c>
     </row>
     <row r="1326">
       <c r="B1326" s="6" t="s">
-        <v>8357</v>
+        <v>8371</v>
       </c>
       <c r="C1326" s="6" t="s">
-        <v>8358</v>
+        <v>8372</v>
       </c>
       <c r="D1326" s="6" t="s">
-        <v>8359</v>
+        <v>8373</v>
       </c>
     </row>
     <row r="1327">
       <c r="B1327" s="5" t="s">
-        <v>8360</v>
+        <v>8374</v>
       </c>
       <c r="C1327" s="5" t="s">
-        <v>8361</v>
+        <v>6739</v>
       </c>
       <c r="D1327" s="5" t="s">
-        <v>8362</v>
+        <v>8375</v>
       </c>
     </row>
     <row r="1328">
       <c r="B1328" s="6" t="s">
-        <v>8363</v>
+        <v>8376</v>
       </c>
       <c r="C1328" s="6" t="s">
-        <v>8364</v>
+        <v>6939</v>
       </c>
       <c r="D1328" s="6" t="s">
-        <v>8365</v>
+        <v>6676</v>
       </c>
     </row>
     <row r="1329">
       <c r="B1329" s="5" t="s">
-        <v>8366</v>
+        <v>8377</v>
       </c>
       <c r="C1329" s="5" t="s">
-        <v>8367</v>
+        <v>8048</v>
       </c>
       <c r="D1329" s="5" t="s">
-        <v>8368</v>
+        <v>8378</v>
       </c>
     </row>
     <row r="1330">
       <c r="B1330" s="6" t="s">
-        <v>8369</v>
+        <v>8379</v>
       </c>
       <c r="C1330" s="6" t="s">
-        <v>8370</v>
+        <v>8380</v>
       </c>
       <c r="D1330" s="6" t="s">
-        <v>8371</v>
+        <v>8381</v>
       </c>
     </row>
     <row r="1331">
       <c r="B1331" s="5" t="s">
-        <v>8372</v>
+        <v>8382</v>
       </c>
       <c r="C1331" s="5" t="s">
-        <v>8373</v>
+        <v>8383</v>
       </c>
       <c r="D1331" s="5" t="s">
-        <v>8374</v>
+        <v>8384</v>
       </c>
     </row>
     <row r="1332">
       <c r="B1332" s="6" t="s">
-        <v>8375</v>
+        <v>8385</v>
       </c>
       <c r="C1332" s="6" t="s">
-        <v>8376</v>
+        <v>8386</v>
       </c>
       <c r="D1332" s="6" t="s">
-        <v>8377</v>
+        <v>8387</v>
       </c>
     </row>
     <row r="1333">
       <c r="B1333" s="5" t="s">
-        <v>8378</v>
+        <v>8388</v>
       </c>
       <c r="C1333" s="5" t="s">
-        <v>8379</v>
+        <v>8389</v>
       </c>
       <c r="D1333" s="5" t="s">
-        <v>8380</v>
+        <v>8390</v>
       </c>
     </row>
     <row r="1334">
       <c r="B1334" s="6" t="s">
-        <v>8381</v>
+        <v>8391</v>
       </c>
       <c r="C1334" s="6" t="s">
-        <v>8382</v>
+        <v>8392</v>
       </c>
       <c r="D1334" s="6" t="s">
-        <v>8383</v>
+        <v>8393</v>
       </c>
     </row>
     <row r="1335">
       <c r="B1335" s="5" t="s">
-        <v>8384</v>
-      </c>
-      <c r="C1335" s="7" t="s">
-        <v>8385</v>
-      </c>
-      <c r="D1335" s="7" t="s">
-        <v>8385</v>
+        <v>8394</v>
+      </c>
+      <c r="C1335" s="5" t="s">
+        <v>8395</v>
+      </c>
+      <c r="D1335" s="5" t="s">
+        <v>8396</v>
       </c>
     </row>
     <row r="1336">
       <c r="B1336" s="6" t="s">
-        <v>8386</v>
+        <v>8397</v>
       </c>
       <c r="C1336" s="6" t="s">
-        <v>7912</v>
+        <v>8398</v>
       </c>
       <c r="D1336" s="6" t="s">
-        <v>7913</v>
+        <v>8399</v>
       </c>
     </row>
     <row r="1337">
       <c r="B1337" s="5" t="s">
-        <v>8387</v>
+        <v>8400</v>
       </c>
       <c r="C1337" s="5" t="s">
-        <v>8388</v>
+        <v>8401</v>
       </c>
       <c r="D1337" s="5" t="s">
-        <v>8389</v>
+        <v>8402</v>
       </c>
     </row>
     <row r="1338">
       <c r="B1338" s="6" t="s">
-        <v>8390</v>
+        <v>8403</v>
       </c>
       <c r="C1338" s="6" t="s">
-        <v>8391</v>
+        <v>8404</v>
       </c>
       <c r="D1338" s="6" t="s">
-        <v>8392</v>
+        <v>8405</v>
       </c>
     </row>
     <row r="1339">
       <c r="B1339" s="5" t="s">
-        <v>8393</v>
+        <v>8406</v>
       </c>
       <c r="C1339" s="5" t="s">
-        <v>8394</v>
+        <v>8407</v>
       </c>
       <c r="D1339" s="5" t="s">
-        <v>8395</v>
+        <v>8408</v>
       </c>
     </row>
     <row r="1340">
       <c r="B1340" s="6" t="s">
-        <v>8396</v>
-      </c>
-      <c r="C1340" s="6" t="s">
-        <v>8397</v>
-      </c>
-      <c r="D1340" s="6" t="s">
-        <v>8398</v>
+        <v>8409</v>
+      </c>
+      <c r="C1340" s="7" t="s">
+        <v>8410</v>
+      </c>
+      <c r="D1340" s="7" t="s">
+        <v>8410</v>
       </c>
     </row>
     <row r="1341">
       <c r="B1341" s="5" t="s">
-        <v>8399</v>
+        <v>8411</v>
       </c>
       <c r="C1341" s="5" t="s">
-        <v>8400</v>
+        <v>7912</v>
       </c>
       <c r="D1341" s="5" t="s">
-        <v>8401</v>
+        <v>7913</v>
       </c>
     </row>
     <row r="1342">
       <c r="B1342" s="6" t="s">
-        <v>8402</v>
+        <v>8412</v>
       </c>
       <c r="C1342" s="6" t="s">
-        <v>8403</v>
+        <v>8413</v>
       </c>
       <c r="D1342" s="6" t="s">
-        <v>8404</v>
+        <v>8414</v>
       </c>
     </row>
     <row r="1343">
       <c r="B1343" s="5" t="s">
-        <v>8405</v>
+        <v>8415</v>
       </c>
       <c r="C1343" s="5" t="s">
-        <v>8406</v>
+        <v>8416</v>
       </c>
       <c r="D1343" s="5" t="s">
-        <v>8407</v>
+        <v>8417</v>
       </c>
     </row>
     <row r="1344">
       <c r="B1344" s="6" t="s">
-        <v>8408</v>
+        <v>8418</v>
       </c>
       <c r="C1344" s="6" t="s">
-        <v>8409</v>
+        <v>8419</v>
       </c>
       <c r="D1344" s="6" t="s">
-        <v>8409</v>
+        <v>8420</v>
       </c>
     </row>
     <row r="1345">
       <c r="B1345" s="5" t="s">
-        <v>8410</v>
+        <v>8421</v>
       </c>
       <c r="C1345" s="5" t="s">
-        <v>8411</v>
+        <v>8422</v>
       </c>
       <c r="D1345" s="5" t="s">
-        <v>8412</v>
+        <v>8423</v>
       </c>
     </row>
     <row r="1346">
       <c r="B1346" s="6" t="s">
-        <v>8413</v>
+        <v>8424</v>
       </c>
       <c r="C1346" s="6" t="s">
-        <v>8409</v>
+        <v>8425</v>
       </c>
       <c r="D1346" s="6" t="s">
-        <v>8409</v>
+        <v>8426</v>
       </c>
     </row>
     <row r="1347">
       <c r="B1347" s="5" t="s">
-        <v>8414</v>
+        <v>8427</v>
+      </c>
+      <c r="C1347" s="5" t="s">
+        <v>8428</v>
+      </c>
+      <c r="D1347" s="5" t="s">
+        <v>8429</v>
       </c>
     </row>
     <row r="1348">
       <c r="B1348" s="6" t="s">
-        <v>8415</v>
+        <v>8430</v>
       </c>
       <c r="C1348" s="6" t="s">
-        <v>8416</v>
+        <v>8431</v>
       </c>
       <c r="D1348" s="6" t="s">
-        <v>8417</v>
+        <v>8432</v>
       </c>
     </row>
     <row r="1349">
       <c r="B1349" s="5" t="s">
-        <v>8418</v>
+        <v>8433</v>
       </c>
       <c r="C1349" s="5" t="s">
-        <v>8419</v>
+        <v>8434</v>
       </c>
       <c r="D1349" s="5" t="s">
-        <v>8420</v>
+        <v>8434</v>
       </c>
     </row>
     <row r="1350">
       <c r="B1350" s="6" t="s">
-        <v>8421</v>
+        <v>8435</v>
       </c>
       <c r="C1350" s="6" t="s">
-        <v>8422</v>
+        <v>8436</v>
       </c>
       <c r="D1350" s="6" t="s">
-        <v>8423</v>
+        <v>8437</v>
       </c>
     </row>
     <row r="1351">
       <c r="B1351" s="5" t="s">
-        <v>8424</v>
+        <v>8438</v>
       </c>
       <c r="C1351" s="5" t="s">
-        <v>8425</v>
+        <v>8434</v>
       </c>
       <c r="D1351" s="5" t="s">
-        <v>8426</v>
+        <v>8434</v>
       </c>
     </row>
     <row r="1352">
       <c r="B1352" s="6" t="s">
-        <v>8427</v>
-      </c>
-      <c r="C1352" s="6" t="s">
-        <v>6006</v>
-      </c>
-      <c r="D1352" s="6" t="s">
-        <v>8428</v>
+        <v>8439</v>
       </c>
     </row>
     <row r="1353">
       <c r="B1353" s="5" t="s">
-        <v>8429</v>
+        <v>8440</v>
       </c>
       <c r="C1353" s="5" t="s">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="D1353" s="5" t="s">
-        <v>8431</v>
+        <v>8442</v>
       </c>
     </row>
     <row r="1354">
       <c r="B1354" s="6" t="s">
-        <v>8432</v>
+        <v>8443</v>
       </c>
       <c r="C1354" s="6" t="s">
-        <v>8433</v>
+        <v>8444</v>
       </c>
       <c r="D1354" s="6" t="s">
-        <v>8434</v>
+        <v>8445</v>
       </c>
     </row>
     <row r="1355">
       <c r="B1355" s="5" t="s">
-        <v>8435</v>
+        <v>8446</v>
       </c>
       <c r="C1355" s="5" t="s">
-        <v>8436</v>
+        <v>8447</v>
       </c>
       <c r="D1355" s="5" t="s">
-        <v>8437</v>
+        <v>8448</v>
       </c>
     </row>
     <row r="1356">
       <c r="B1356" s="6" t="s">
-        <v>8438</v>
+        <v>8449</v>
       </c>
       <c r="C1356" s="6" t="s">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D1356" s="6" t="s">
-        <v>8440</v>
+        <v>8451</v>
       </c>
     </row>
     <row r="1357">
       <c r="B1357" s="5" t="s">
-        <v>8441</v>
+        <v>8452</v>
       </c>
       <c r="C1357" s="5" t="s">
-        <v>8442</v>
+        <v>6006</v>
       </c>
       <c r="D1357" s="5" t="s">
-        <v>8443</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="1358">
       <c r="B1358" s="6" t="s">
-        <v>8444</v>
+        <v>8454</v>
       </c>
       <c r="C1358" s="6" t="s">
-        <v>8445</v>
+        <v>8455</v>
       </c>
       <c r="D1358" s="6" t="s">
-        <v>8445</v>
+        <v>8456</v>
       </c>
     </row>
     <row r="1359">
       <c r="B1359" s="5" t="s">
-        <v>8446</v>
+        <v>8457</v>
       </c>
       <c r="C1359" s="5" t="s">
-        <v>8447</v>
+        <v>8458</v>
       </c>
       <c r="D1359" s="5" t="s">
-        <v>8448</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="1360">
       <c r="B1360" s="6" t="s">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="C1360" s="6" t="s">
-        <v>8450</v>
+        <v>8461</v>
       </c>
       <c r="D1360" s="6" t="s">
-        <v>8451</v>
+        <v>8462</v>
       </c>
     </row>
     <row r="1361">
       <c r="B1361" s="5" t="s">
-        <v>8452</v>
+        <v>8463</v>
       </c>
       <c r="C1361" s="5" t="s">
-        <v>8453</v>
+        <v>8464</v>
       </c>
       <c r="D1361" s="5" t="s">
-        <v>8454</v>
+        <v>8465</v>
       </c>
     </row>
     <row r="1362">
       <c r="B1362" s="6" t="s">
-        <v>8455</v>
+        <v>8466</v>
       </c>
       <c r="C1362" s="6" t="s">
-        <v>8456</v>
+        <v>8467</v>
       </c>
       <c r="D1362" s="6" t="s">
-        <v>8457</v>
+        <v>8468</v>
       </c>
     </row>
     <row r="1363">
       <c r="B1363" s="5" t="s">
-        <v>8458</v>
+        <v>8469</v>
       </c>
       <c r="C1363" s="5" t="s">
-        <v>8459</v>
+        <v>8470</v>
       </c>
       <c r="D1363" s="5" t="s">
-        <v>8460</v>
+        <v>8470</v>
       </c>
     </row>
     <row r="1364">
       <c r="B1364" s="6" t="s">
-        <v>8461</v>
+        <v>8471</v>
       </c>
       <c r="C1364" s="6" t="s">
-        <v>8462</v>
+        <v>8472</v>
       </c>
       <c r="D1364" s="6" t="s">
-        <v>8463</v>
+        <v>8473</v>
       </c>
     </row>
     <row r="1365">
       <c r="B1365" s="5" t="s">
-        <v>8464</v>
+        <v>8474</v>
       </c>
       <c r="C1365" s="5" t="s">
-        <v>8465</v>
+        <v>8475</v>
       </c>
       <c r="D1365" s="5" t="s">
-        <v>8466</v>
+        <v>8476</v>
       </c>
     </row>
     <row r="1366">
       <c r="B1366" s="6" t="s">
-        <v>8467</v>
+        <v>8477</v>
       </c>
       <c r="C1366" s="6" t="s">
-        <v>8468</v>
+        <v>8478</v>
       </c>
       <c r="D1366" s="6" t="s">
-        <v>8469</v>
+        <v>8479</v>
       </c>
     </row>
     <row r="1367">
       <c r="B1367" s="5" t="s">
-        <v>8470</v>
+        <v>8480</v>
       </c>
       <c r="C1367" s="5" t="s">
-        <v>8471</v>
+        <v>8481</v>
       </c>
       <c r="D1367" s="5" t="s">
-        <v>8472</v>
+        <v>8482</v>
       </c>
     </row>
     <row r="1368">
       <c r="B1368" s="6" t="s">
-        <v>8473</v>
+        <v>8483</v>
       </c>
       <c r="C1368" s="6" t="s">
-        <v>8474</v>
+        <v>8484</v>
       </c>
       <c r="D1368" s="6" t="s">
-        <v>8475</v>
+        <v>8485</v>
       </c>
     </row>
     <row r="1369">
       <c r="B1369" s="5" t="s">
-        <v>8476</v>
+        <v>8486</v>
       </c>
       <c r="C1369" s="5" t="s">
-        <v>8477</v>
+        <v>8487</v>
       </c>
       <c r="D1369" s="5" t="s">
-        <v>8478</v>
+        <v>8488</v>
       </c>
     </row>
     <row r="1370">
       <c r="B1370" s="6" t="s">
-        <v>8479</v>
+        <v>8489</v>
       </c>
       <c r="C1370" s="6" t="s">
-        <v>8480</v>
+        <v>8490</v>
       </c>
       <c r="D1370" s="6" t="s">
-        <v>8481</v>
+        <v>8491</v>
       </c>
     </row>
     <row r="1371">
       <c r="B1371" s="5" t="s">
-        <v>8482</v>
+        <v>8492</v>
       </c>
       <c r="C1371" s="5" t="s">
-        <v>8483</v>
+        <v>8493</v>
       </c>
       <c r="D1371" s="5" t="s">
-        <v>8484</v>
+        <v>8494</v>
       </c>
     </row>
     <row r="1372">
       <c r="B1372" s="6" t="s">
-        <v>8485</v>
+        <v>8495</v>
       </c>
       <c r="C1372" s="6" t="s">
-        <v>8486</v>
+        <v>8496</v>
       </c>
       <c r="D1372" s="6" t="s">
-        <v>8487</v>
+        <v>8497</v>
       </c>
     </row>
     <row r="1373">
       <c r="B1373" s="5" t="s">
-        <v>8488</v>
+        <v>8498</v>
       </c>
       <c r="C1373" s="5" t="s">
+        <v>8499</v>
+      </c>
+      <c r="D1373" s="5" t="s">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="B1374" s="6" t="s">
+        <v>8501</v>
+      </c>
+      <c r="C1374" s="6" t="s">
+        <v>8502</v>
+      </c>
+      <c r="D1374" s="6" t="s">
+        <v>8503</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="B1375" s="5" t="s">
+        <v>8504</v>
+      </c>
+      <c r="C1375" s="5" t="s">
+        <v>8505</v>
+      </c>
+      <c r="D1375" s="5" t="s">
+        <v>8506</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="B1376" s="6" t="s">
+        <v>8507</v>
+      </c>
+      <c r="C1376" s="6" t="s">
+        <v>8508</v>
+      </c>
+      <c r="D1376" s="6" t="s">
+        <v>8509</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="B1377" s="5" t="s">
+        <v>8510</v>
+      </c>
+      <c r="C1377" s="5" t="s">
+        <v>8511</v>
+      </c>
+      <c r="D1377" s="5" t="s">
+        <v>8512</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="B1378" s="6" t="s">
+        <v>8513</v>
+      </c>
+      <c r="C1378" s="6" t="s">
         <v>4476</v>
       </c>
-      <c r="D1373" s="5" t="s">
-        <v>8489</v>
+      <c r="D1378" s="6" t="s">
+        <v>8514</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H1373"/>
+  <autoFilter ref="B2:H1378"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -56621,10 +56811,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>8490</v>
+        <v>8515</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8491</v>
+        <v>8516</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -56635,16 +56825,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8492</v>
+        <v>8517</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8493</v>
+        <v>8518</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8494</v>
+        <v>8519</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8495</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="3">
@@ -56652,16 +56842,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8496</v>
+        <v>8521</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8497</v>
+        <v>8522</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8498</v>
+        <v>8523</v>
       </c>
     </row>
     <row r="4">
@@ -56672,24 +56862,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8499</v>
+        <v>8524</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8500</v>
+        <v>8525</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8501</v>
+        <v>8526</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>8502</v>
+        <v>8527</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4463</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8503</v>
+        <v>8528</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -56697,13 +56887,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>8504</v>
+        <v>8529</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4470</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>8505</v>
+        <v>8530</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -56711,13 +56901,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>8506</v>
+        <v>8531</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4476</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8507</v>
+        <v>8532</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -56725,13 +56915,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>8508</v>
+        <v>8533</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4482</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>8509</v>
+        <v>8534</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -56739,13 +56929,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>8510</v>
+        <v>8535</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4489</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8511</v>
+        <v>8536</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -56753,13 +56943,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>8512</v>
+        <v>8537</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4496</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>8513</v>
+        <v>8538</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -56767,13 +56957,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>8514</v>
+        <v>8539</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4502</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>8515</v>
+        <v>8540</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -56781,13 +56971,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>8516</v>
+        <v>8541</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4508</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>8517</v>
+        <v>8542</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -56795,13 +56985,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>8518</v>
+        <v>8543</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4515</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8519</v>
+        <v>8544</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -56809,13 +56999,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>8520</v>
+        <v>8545</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4521</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>8521</v>
+        <v>8546</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -56829,7 +57019,7 @@
         <v>4527</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8522</v>
+        <v>8547</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -56837,13 +57027,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>8523</v>
+        <v>8548</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4534</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>8524</v>
+        <v>8549</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -56851,13 +57041,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>8525</v>
+        <v>8550</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4541</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>8526</v>
+        <v>8551</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -56865,13 +57055,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>8527</v>
+        <v>8552</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4547</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>8528</v>
+        <v>8553</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -56879,13 +57069,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>8529</v>
+        <v>8554</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4554</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>8530</v>
+        <v>8555</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -56893,13 +57083,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>8531</v>
+        <v>8556</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4560</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>8532</v>
+        <v>8557</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -56907,13 +57097,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>8533</v>
+        <v>8558</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4565</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>8534</v>
+        <v>8559</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -56921,13 +57111,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>8535</v>
+        <v>8560</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4572</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>8536</v>
+        <v>8561</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -56935,13 +57125,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>8537</v>
+        <v>8562</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4394</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>8538</v>
+        <v>8563</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -56949,13 +57139,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>8539</v>
+        <v>8564</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4580</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>8540</v>
+        <v>8565</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9443" uniqueCount="8566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9703" uniqueCount="8777">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -25030,6 +25030,15 @@
     <t xml:space="preserve">Leaderboard</t>
   </si>
   <si>
+    <t xml:space="preserve">ランキング</t>
+  </si>
+  <si>
+    <t xml:space="preserve">排行榜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rangliste</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.button.login</t>
   </si>
   <si>
@@ -25039,6 +25048,18 @@
     <t xml:space="preserve">Sign in</t>
   </si>
   <si>
+    <t xml:space="preserve">ログイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anmelden</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.button.logout</t>
   </si>
   <si>
@@ -25048,6 +25069,18 @@
     <t xml:space="preserve">Sign out</t>
   </si>
   <si>
+    <t xml:space="preserve">ログアウト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">退出登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abmelden</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.button.toMe</t>
   </si>
   <si>
@@ -25057,6 +25090,15 @@
     <t xml:space="preserve">Find me</t>
   </si>
   <si>
+    <t xml:space="preserve">自分の順位へ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定位到我</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zu mir springen</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.button.confirmName</t>
   </si>
   <si>
@@ -25066,6 +25108,18 @@
     <t xml:space="preserve">Use this name</t>
   </si>
   <si>
+    <t xml:space="preserve">この名前にする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使用此名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使用此名稱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diesen Namen nutzen</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.button.deleteAccount</t>
   </si>
   <si>
@@ -25075,6 +25129,18 @@
     <t xml:space="preserve">Delete account</t>
   </si>
   <si>
+    <t xml:space="preserve">アカウント削除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">删除账号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">刪除帳號</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konto löschen</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.button.report</t>
   </si>
   <si>
@@ -25084,6 +25150,18 @@
     <t xml:space="preserve">Report</t>
   </si>
   <si>
+    <t xml:space="preserve">報告</t>
+  </si>
+  <si>
+    <t xml:space="preserve">举报</t>
+  </si>
+  <si>
+    <t xml:space="preserve">舉報</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melden</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.title</t>
   </si>
   <si>
@@ -25096,6 +25174,18 @@
     <t xml:space="preserve">The leaderboard needs an account.</t>
   </si>
   <si>
+    <t xml:space="preserve">ランキングにはアカウントが必要です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">排行榜需要账号。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">排行榜需要帳號。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Für die Rangliste wird ein Konto benötigt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.login.keep</t>
   </si>
   <si>
@@ -25105,6 +25195,18 @@
     <t xml:space="preserve">We keep a display name and the provider id. We do not take your email.</t>
   </si>
   <si>
+    <t xml:space="preserve">保持するもの: 表示名と提供元の識別子。メールアドレスは受け取りません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们保存显示名称与提供方标识。不收取邮箱地址。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我們保存顯示名稱與提供方識別碼。不收取電子郵件地址。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gespeichert werden Anzeigename und Anbieter-ID. Die E-Mail-Adresse wird nicht erfasst.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.login.none</t>
   </si>
   <si>
@@ -25114,6 +25216,18 @@
     <t xml:space="preserve">No sign-in provider is available.</t>
   </si>
   <si>
+    <t xml:space="preserve">今はログインできる先がありません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目前没有可用的登录方式。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目前沒有可用的登入方式。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derzeit ist kein Anbieter verfügbar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.handle.ask</t>
   </si>
   <si>
@@ -25123,6 +25237,18 @@
     <t xml:space="preserve">Choose the name shown on the board.</t>
   </si>
   <si>
+    <t xml:space="preserve">ランキングに表示される名前を決めます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">设置排行榜上显示的名称。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定排行榜上顯示的名稱。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wähle den Namen, der in der Rangliste erscheint.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.handle.rule</t>
   </si>
   <si>
@@ -25132,6 +25258,18 @@
     <t xml:space="preserve">Letters, digits, underscore. 3-16 characters. Changeable once every 30 days.</t>
   </si>
   <si>
+    <t xml:space="preserve">英字・数字・アンダースコアで3〜16文字。30日に一度変更できます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">字母、数字、下划线，3~16 个字符。每 30 天可更改一次。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">字母、數字、底線，3~16 個字元。每 30 天可更改一次。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buchstaben, Zahlen, Unterstrich. 3-16 Zeichen. Alle 30 Tage änderbar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.tab.Main</t>
   </si>
   <si>
@@ -25141,12 +25279,27 @@
     <t xml:space="preserve">Overall</t>
   </si>
   <si>
+    <t xml:space="preserve">全体</t>
+  </si>
+  <si>
+    <t xml:space="preserve">总榜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">總榜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamt</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.tab.Stake</t>
   </si>
   <si>
     <t xml:space="preserve">Stake</t>
   </si>
   <si>
+    <t xml:space="preserve">Einsatz</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.tab.Deck</t>
   </si>
   <si>
@@ -25156,6 +25309,9 @@
     <t xml:space="preserve">Challenge</t>
   </si>
   <si>
+    <t xml:space="preserve">Herausforderung</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.metric.Ascent</t>
   </si>
   <si>
@@ -25165,6 +25321,15 @@
     <t xml:space="preserve">Ascent</t>
   </si>
   <si>
+    <t xml:space="preserve">登頂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登顶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufstieg</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.metric.BestHand</t>
   </si>
   <si>
@@ -25174,6 +25339,18 @@
     <t xml:space="preserve">Best hand</t>
   </si>
   <si>
+    <t xml:space="preserve">一手の最高得点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">单手最高得分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">單手最高得分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beste Hand</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.metric.FewestHands</t>
   </si>
   <si>
@@ -25183,6 +25360,18 @@
     <t xml:space="preserve">Fewest hands</t>
   </si>
   <si>
+    <t xml:space="preserve">最少ハンドで完走</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最少出牌通关</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最少出牌通關</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenigste Hände</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.metric.MoneyAtWin</t>
   </si>
   <si>
@@ -25192,6 +25381,18 @@
     <t xml:space="preserve">Money at win</t>
   </si>
   <si>
+    <t xml:space="preserve">完走時の所持金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通关时金钱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通關時金錢</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geld bei Sieg</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.metric.Wins</t>
   </si>
   <si>
@@ -25201,6 +25402,18 @@
     <t xml:space="preserve">Wins</t>
   </si>
   <si>
+    <t xml:space="preserve">完走回数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通关次数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通關次數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siege</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.metric.Skips</t>
   </si>
   <si>
@@ -25210,6 +25423,15 @@
     <t xml:space="preserve">Blinds skipped</t>
   </si>
   <si>
+    <t xml:space="preserve">跳过的盲注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">跳過的盲注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übersprungene Blinds</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.metric.ChallengesBeaten</t>
   </si>
   <si>
@@ -25219,6 +25441,18 @@
     <t xml:space="preserve">Challenges beaten</t>
   </si>
   <si>
+    <t xml:space="preserve">クリアしたチャレンジ数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">完成的挑战数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">完成的挑戰數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bestandene Herausforderungen</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.period.season</t>
   </si>
   <si>
@@ -25228,6 +25462,18 @@
     <t xml:space="preserve">This season</t>
   </si>
   <si>
+    <t xml:space="preserve">今シーズン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本赛季</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本賽季</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Saison</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.period.all</t>
   </si>
   <si>
@@ -25237,6 +25483,18 @@
     <t xml:space="preserve">All time</t>
   </si>
   <si>
+    <t xml:space="preserve">全期間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全部时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全部時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamtzeit</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.pool.all</t>
   </si>
   <si>
@@ -25246,6 +25504,18 @@
     <t xml:space="preserve">Expanded</t>
   </si>
   <si>
+    <t xml:space="preserve">拡張</t>
+  </si>
+  <si>
+    <t xml:space="preserve">扩展</t>
+  </si>
+  <si>
+    <t xml:space="preserve">擴展</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erweitert</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.col.rank</t>
   </si>
   <si>
@@ -25264,6 +25534,15 @@
     <t xml:space="preserve">Tier</t>
   </si>
   <si>
+    <t xml:space="preserve">ティア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">段位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stufe</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.col.value</t>
   </si>
   <si>
@@ -25273,6 +25552,15 @@
     <t xml:space="preserve">Value</t>
   </si>
   <si>
+    <t xml:space="preserve">値</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">數值</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.empty</t>
   </si>
   <si>
@@ -25282,6 +25570,18 @@
     <t xml:space="preserve">Nobody here yet.</t>
   </si>
   <si>
+    <t xml:space="preserve">まだ誰も載っていません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还没有人上榜。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">還沒有人上榜。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noch niemand hier.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.noRecord</t>
   </si>
   <si>
@@ -25291,6 +25591,18 @@
     <t xml:space="preserve">No record yet.</t>
   </si>
   <si>
+    <t xml:space="preserve">まだ記録がありません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还没有记录。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">還沒有記錄。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noch kein Eintrag.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.mine</t>
   </si>
   <si>
@@ -25300,6 +25612,15 @@
     <t xml:space="preserve">You</t>
   </si>
   <si>
+    <t xml:space="preserve">自分の順位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的排名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Du</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.loading</t>
   </si>
   <si>
@@ -25309,6 +25630,18 @@
     <t xml:space="preserve">Loading</t>
   </si>
   <si>
+    <t xml:space="preserve">読み込み中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加载中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">載入中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wird geladen</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.total</t>
   </si>
   <si>
@@ -25318,6 +25651,15 @@
     <t xml:space="preserve">{n} players</t>
   </si>
   <si>
+    <t xml:space="preserve">{n}人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} Spieler</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.page</t>
   </si>
   <si>
@@ -25333,6 +25675,15 @@
     <t xml:space="preserve">{n} hands</t>
   </si>
   <si>
+    <t xml:space="preserve">{n} ハンド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} 次出牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} Hände</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.beaten</t>
   </si>
   <si>
@@ -25348,6 +25699,18 @@
     <t xml:space="preserve">Unranked</t>
   </si>
   <si>
+    <t xml:space="preserve">ティアなし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无段位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無段位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohne Stufe</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.profile.lastSeason</t>
   </si>
   <si>
@@ -25357,6 +25720,18 @@
     <t xml:space="preserve">Last season {tier}</t>
   </si>
   <si>
+    <t xml:space="preserve">前シーズン {tier}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上赛季 {tier}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上賽季 {tier}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letzte Saison {tier}</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.profile.devices</t>
   </si>
   <si>
@@ -25366,6 +25741,18 @@
     <t xml:space="preserve">{n} signed-in devices</t>
   </si>
   <si>
+    <t xml:space="preserve">ログイン中の端末 {n}台</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已登录设备 {n} 台</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已登入裝置 {n} 台</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{n} angemeldete Geräte</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.profile.deleteWarn</t>
   </si>
   <si>
@@ -25375,12 +25762,30 @@
     <t xml:space="preserve">The account and every record are removed. This cannot be undone.</t>
   </si>
   <si>
+    <t xml:space="preserve">アカウントとすべての記録が消えます。取り消せません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">账号与所有记录都会被删除。无法撤销。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">帳號與所有記錄都會被刪除。無法復原。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konto und alle Einträge werden entfernt. Das lässt sich nicht rückgängig machen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.ranked</t>
   </si>
   <si>
     <t xml:space="preserve">Ranked</t>
   </si>
   <si>
+    <t xml:space="preserve">排位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gewertet</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.ranked.on</t>
   </si>
   <si>
@@ -25390,6 +25795,18 @@
     <t xml:space="preserve">This run will be ranked.</t>
   </si>
   <si>
+    <t xml:space="preserve">このランは終わると順位に載ります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局结束后会计入排名。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局結束後會計入排名。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieser Lauf wird gewertet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.ranked.off</t>
   </si>
   <si>
@@ -25399,6 +25816,18 @@
     <t xml:space="preserve">This run will not be ranked.</t>
   </si>
   <si>
+    <t xml:space="preserve">このランは順位に載りません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局不会计入排名。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局不會計入排名。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieser Lauf wird nicht gewertet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.ranked.cannot</t>
   </si>
   <si>
@@ -25408,6 +25837,18 @@
     <t xml:space="preserve">Cannot start a ranked run now.</t>
   </si>
   <si>
+    <t xml:space="preserve">今はランクランを始められません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目前无法开始排位对局。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目前無法開始排位對局。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein gewerteter Lauf ist jetzt nicht möglich.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.end.judging</t>
   </si>
   <si>
@@ -25417,6 +25858,18 @@
     <t xml:space="preserve">Ranking</t>
   </si>
   <si>
+    <t xml:space="preserve">順位を数えています</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正在统计排名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正在統計排名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wertung läuft</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.end.same</t>
   </si>
   <si>
@@ -25426,6 +25879,18 @@
     <t xml:space="preserve">{name} #{rank} · unchanged</t>
   </si>
   <si>
+    <t xml:space="preserve">{name} #{rank} · 変化なし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} #{rank} · 不变</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} #{rank} · 不變</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} #{rank} · unverändert</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.end.up</t>
   </si>
   <si>
@@ -25441,6 +25906,15 @@
     <t xml:space="preserve">You are on the board — {name} #{rank}</t>
   </si>
   <si>
+    <t xml:space="preserve">ランキングに載りました — {name} #{rank}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已上榜 — {name} #{rank}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Du stehst in der Rangliste — {name} #{rank}</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.end.rejected</t>
   </si>
   <si>
@@ -25450,6 +25924,18 @@
     <t xml:space="preserve">This run was not ranked — {why}</t>
   </si>
   <si>
+    <t xml:space="preserve">このランは順位に載りませんでした — {why}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局未计入排名 — {why}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局未計入排名 — {why}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieser Lauf wurde nicht gewertet — {why}</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.end.later</t>
   </si>
   <si>
@@ -25459,6 +25945,18 @@
     <t xml:space="preserve">We will send it again later.</t>
   </si>
   <si>
+    <t xml:space="preserve">あとでもう一度送ります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">稍后会再次提交。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">稍後會再次提交。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir senden es später erneut.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.end.tierUp</t>
   </si>
   <si>
@@ -25468,6 +25966,15 @@
     <t xml:space="preserve">You reached {tier}</t>
   </si>
   <si>
+    <t xml:space="preserve">ティアが {tier} になりました</t>
+  </si>
+  <si>
+    <t xml:space="preserve">段位提升到 {tier}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Du hast {tier} erreicht</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.title</t>
   </si>
   <si>
@@ -25477,6 +25984,15 @@
     <t xml:space="preserve">That did not work</t>
   </si>
   <si>
+    <t xml:space="preserve">できませんでした</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未能完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das hat nicht funktioniert</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.offline</t>
   </si>
   <si>
@@ -25486,6 +26002,18 @@
     <t xml:space="preserve">Could not reach the server. The game keeps working.</t>
   </si>
   <si>
+    <t xml:space="preserve">サーバーに届きませんでした。ゲームはそのまま遊べます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无法连接服务器。游戏仍可继续。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無法連線伺服器。遊戲仍可繼續。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Server war nicht erreichbar. Das Spiel läuft weiter.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.unauthorized</t>
   </si>
   <si>
@@ -25495,6 +26023,18 @@
     <t xml:space="preserve">Please sign in again.</t>
   </si>
   <si>
+    <t xml:space="preserve">もう一度ログインしてください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请重新登录。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">請重新登入。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitte melde dich erneut an.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.bad_seed</t>
   </si>
   <si>
@@ -25504,6 +26044,18 @@
     <t xml:space="preserve">This run did not start from that ranked seed.</t>
   </si>
   <si>
+    <t xml:space="preserve">そのシードで始めたランクランではありません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局并非以该排位种子开始。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本局並非以該排位種子開始。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieser Lauf begann nicht mit diesem gewerteten Seed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.bad_fingerprint</t>
   </si>
   <si>
@@ -25513,6 +26065,18 @@
     <t xml:space="preserve">This build is out of date. Reload and try again.</t>
   </si>
   <si>
+    <t xml:space="preserve">ゲームが古いです。読み込み直すと再送できます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">游戏版本过旧。刷新后可重试。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遊戲版本過舊。重新載入後可再試。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Version ist veraltet. Neu laden und erneut versuchen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.too_many</t>
   </si>
   <si>
@@ -25522,6 +26086,18 @@
     <t xml:space="preserve">Too many requests. Try again shortly.</t>
   </si>
   <si>
+    <t xml:space="preserve">要求が多すぎます。しばらくしてからもう一度。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请求过于频繁。请稍后再试。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">請求過於頻繁。請稍後再試。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zu viele Anfragen. Versuche es in Kürze erneut.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.taken</t>
   </si>
   <si>
@@ -25531,6 +26107,18 @@
     <t xml:space="preserve">That name is taken.</t>
   </si>
   <si>
+    <t xml:space="preserve">すでに使われている名前です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">该名称已被使用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">該名稱已被使用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieser Name ist belegt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.cooldown</t>
   </si>
   <si>
@@ -25540,6 +26128,18 @@
     <t xml:space="preserve">You cannot change the name yet.</t>
   </si>
   <si>
+    <t xml:space="preserve">まだ名前を変えられません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暂时无法更改名称。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暫時無法更改名稱。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Name kann noch nicht geändert werden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.shape</t>
   </si>
   <si>
@@ -25549,6 +26149,18 @@
     <t xml:space="preserve">Use 3-16 letters, digits or underscores.</t>
   </si>
   <si>
+    <t xml:space="preserve">英字・数字・アンダースコアで3〜16文字です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">需为字母、数字或下划线，3~16 个字符。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">需為字母、數字或底線，3~16 個字元。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-16 Buchstaben, Zahlen oder Unterstriche.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.fail.unknown</t>
   </si>
   <si>
@@ -25558,10 +26170,31 @@
     <t xml:space="preserve">The server refused the request.</t>
   </si>
   <si>
+    <t xml:space="preserve">サーバーがこの要求を受け付けませんでした。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务器拒绝了该请求。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">伺服器拒絕了該請求。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Server hat die Anfrage abgelehnt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.lb.cleared</t>
   </si>
   <si>
     <t xml:space="preserve">cleared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通关</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通關</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geschafft</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -56081,76 +56714,160 @@
       <c r="D1313" s="5" t="s">
         <v>8336</v>
       </c>
+      <c r="E1313" s="5" t="s">
+        <v>8337</v>
+      </c>
+      <c r="F1313" s="5" t="s">
+        <v>8338</v>
+      </c>
+      <c r="G1313" s="5" t="s">
+        <v>8338</v>
+      </c>
+      <c r="H1313" s="5" t="s">
+        <v>8339</v>
+      </c>
     </row>
     <row r="1314">
       <c r="B1314" s="6" t="s">
-        <v>8337</v>
+        <v>8340</v>
       </c>
       <c r="C1314" s="6" t="s">
-        <v>8338</v>
+        <v>8341</v>
       </c>
       <c r="D1314" s="6" t="s">
-        <v>8339</v>
+        <v>8342</v>
+      </c>
+      <c r="E1314" s="6" t="s">
+        <v>8343</v>
+      </c>
+      <c r="F1314" s="6" t="s">
+        <v>8344</v>
+      </c>
+      <c r="G1314" s="6" t="s">
+        <v>8345</v>
+      </c>
+      <c r="H1314" s="6" t="s">
+        <v>8346</v>
       </c>
     </row>
     <row r="1315">
       <c r="B1315" s="5" t="s">
-        <v>8340</v>
+        <v>8347</v>
       </c>
       <c r="C1315" s="5" t="s">
-        <v>8341</v>
+        <v>8348</v>
       </c>
       <c r="D1315" s="5" t="s">
-        <v>8342</v>
+        <v>8349</v>
+      </c>
+      <c r="E1315" s="5" t="s">
+        <v>8350</v>
+      </c>
+      <c r="F1315" s="5" t="s">
+        <v>8351</v>
+      </c>
+      <c r="G1315" s="5" t="s">
+        <v>8352</v>
+      </c>
+      <c r="H1315" s="5" t="s">
+        <v>8353</v>
       </c>
     </row>
     <row r="1316">
       <c r="B1316" s="6" t="s">
-        <v>8343</v>
+        <v>8354</v>
       </c>
       <c r="C1316" s="6" t="s">
-        <v>8344</v>
+        <v>8355</v>
       </c>
       <c r="D1316" s="6" t="s">
-        <v>8345</v>
+        <v>8356</v>
+      </c>
+      <c r="E1316" s="6" t="s">
+        <v>8357</v>
+      </c>
+      <c r="F1316" s="6" t="s">
+        <v>8358</v>
+      </c>
+      <c r="G1316" s="6" t="s">
+        <v>8358</v>
+      </c>
+      <c r="H1316" s="6" t="s">
+        <v>8359</v>
       </c>
     </row>
     <row r="1317">
       <c r="B1317" s="5" t="s">
-        <v>8346</v>
+        <v>8360</v>
       </c>
       <c r="C1317" s="5" t="s">
-        <v>8347</v>
+        <v>8361</v>
       </c>
       <c r="D1317" s="5" t="s">
-        <v>8348</v>
+        <v>8362</v>
+      </c>
+      <c r="E1317" s="5" t="s">
+        <v>8363</v>
+      </c>
+      <c r="F1317" s="5" t="s">
+        <v>8364</v>
+      </c>
+      <c r="G1317" s="5" t="s">
+        <v>8365</v>
+      </c>
+      <c r="H1317" s="5" t="s">
+        <v>8366</v>
       </c>
     </row>
     <row r="1318">
       <c r="B1318" s="6" t="s">
-        <v>8349</v>
+        <v>8367</v>
       </c>
       <c r="C1318" s="6" t="s">
-        <v>8350</v>
+        <v>8368</v>
       </c>
       <c r="D1318" s="6" t="s">
-        <v>8351</v>
+        <v>8369</v>
+      </c>
+      <c r="E1318" s="6" t="s">
+        <v>8370</v>
+      </c>
+      <c r="F1318" s="6" t="s">
+        <v>8371</v>
+      </c>
+      <c r="G1318" s="6" t="s">
+        <v>8372</v>
+      </c>
+      <c r="H1318" s="6" t="s">
+        <v>8373</v>
       </c>
     </row>
     <row r="1319">
       <c r="B1319" s="5" t="s">
-        <v>8352</v>
+        <v>8374</v>
       </c>
       <c r="C1319" s="5" t="s">
-        <v>8353</v>
+        <v>8375</v>
       </c>
       <c r="D1319" s="5" t="s">
-        <v>8354</v>
+        <v>8376</v>
+      </c>
+      <c r="E1319" s="5" t="s">
+        <v>8377</v>
+      </c>
+      <c r="F1319" s="5" t="s">
+        <v>8378</v>
+      </c>
+      <c r="G1319" s="5" t="s">
+        <v>8379</v>
+      </c>
+      <c r="H1319" s="5" t="s">
+        <v>8380</v>
       </c>
     </row>
     <row r="1320">
       <c r="B1320" s="6" t="s">
-        <v>8355</v>
+        <v>8381</v>
       </c>
       <c r="C1320" s="6" t="s">
         <v>8335</v>
@@ -56158,87 +56875,183 @@
       <c r="D1320" s="6" t="s">
         <v>8336</v>
       </c>
+      <c r="E1320" s="6" t="s">
+        <v>8337</v>
+      </c>
+      <c r="F1320" s="6" t="s">
+        <v>8338</v>
+      </c>
+      <c r="G1320" s="6" t="s">
+        <v>8338</v>
+      </c>
+      <c r="H1320" s="6" t="s">
+        <v>8339</v>
+      </c>
     </row>
     <row r="1321">
       <c r="B1321" s="5" t="s">
-        <v>8356</v>
+        <v>8382</v>
       </c>
       <c r="C1321" s="5" t="s">
-        <v>8357</v>
+        <v>8383</v>
       </c>
       <c r="D1321" s="5" t="s">
-        <v>8358</v>
+        <v>8384</v>
+      </c>
+      <c r="E1321" s="5" t="s">
+        <v>8385</v>
+      </c>
+      <c r="F1321" s="5" t="s">
+        <v>8386</v>
+      </c>
+      <c r="G1321" s="5" t="s">
+        <v>8387</v>
+      </c>
+      <c r="H1321" s="5" t="s">
+        <v>8388</v>
       </c>
     </row>
     <row r="1322">
       <c r="B1322" s="6" t="s">
-        <v>8359</v>
+        <v>8389</v>
       </c>
       <c r="C1322" s="6" t="s">
-        <v>8360</v>
+        <v>8390</v>
       </c>
       <c r="D1322" s="6" t="s">
-        <v>8361</v>
+        <v>8391</v>
+      </c>
+      <c r="E1322" s="6" t="s">
+        <v>8392</v>
+      </c>
+      <c r="F1322" s="6" t="s">
+        <v>8393</v>
+      </c>
+      <c r="G1322" s="6" t="s">
+        <v>8394</v>
+      </c>
+      <c r="H1322" s="6" t="s">
+        <v>8395</v>
       </c>
     </row>
     <row r="1323">
       <c r="B1323" s="5" t="s">
-        <v>8362</v>
+        <v>8396</v>
       </c>
       <c r="C1323" s="5" t="s">
-        <v>8363</v>
+        <v>8397</v>
       </c>
       <c r="D1323" s="5" t="s">
-        <v>8364</v>
+        <v>8398</v>
+      </c>
+      <c r="E1323" s="5" t="s">
+        <v>8399</v>
+      </c>
+      <c r="F1323" s="5" t="s">
+        <v>8400</v>
+      </c>
+      <c r="G1323" s="5" t="s">
+        <v>8401</v>
+      </c>
+      <c r="H1323" s="5" t="s">
+        <v>8402</v>
       </c>
     </row>
     <row r="1324">
       <c r="B1324" s="6" t="s">
-        <v>8365</v>
+        <v>8403</v>
       </c>
       <c r="C1324" s="6" t="s">
-        <v>8366</v>
+        <v>8404</v>
       </c>
       <c r="D1324" s="6" t="s">
-        <v>8367</v>
+        <v>8405</v>
+      </c>
+      <c r="E1324" s="6" t="s">
+        <v>8406</v>
+      </c>
+      <c r="F1324" s="6" t="s">
+        <v>8407</v>
+      </c>
+      <c r="G1324" s="6" t="s">
+        <v>8408</v>
+      </c>
+      <c r="H1324" s="6" t="s">
+        <v>8409</v>
       </c>
     </row>
     <row r="1325">
       <c r="B1325" s="5" t="s">
-        <v>8368</v>
+        <v>8410</v>
       </c>
       <c r="C1325" s="5" t="s">
-        <v>8369</v>
+        <v>8411</v>
       </c>
       <c r="D1325" s="5" t="s">
-        <v>8370</v>
+        <v>8412</v>
+      </c>
+      <c r="E1325" s="5" t="s">
+        <v>8413</v>
+      </c>
+      <c r="F1325" s="5" t="s">
+        <v>8414</v>
+      </c>
+      <c r="G1325" s="5" t="s">
+        <v>8415</v>
+      </c>
+      <c r="H1325" s="5" t="s">
+        <v>8416</v>
       </c>
     </row>
     <row r="1326">
       <c r="B1326" s="6" t="s">
-        <v>8371</v>
+        <v>8417</v>
       </c>
       <c r="C1326" s="6" t="s">
-        <v>8372</v>
+        <v>8418</v>
       </c>
       <c r="D1326" s="6" t="s">
-        <v>8373</v>
+        <v>8419</v>
+      </c>
+      <c r="E1326" s="6" t="s">
+        <v>8420</v>
+      </c>
+      <c r="F1326" s="6" t="s">
+        <v>8421</v>
+      </c>
+      <c r="G1326" s="6" t="s">
+        <v>8422</v>
+      </c>
+      <c r="H1326" s="6" t="s">
+        <v>8423</v>
       </c>
     </row>
     <row r="1327">
       <c r="B1327" s="5" t="s">
-        <v>8374</v>
+        <v>8424</v>
       </c>
       <c r="C1327" s="5" t="s">
         <v>6739</v>
       </c>
       <c r="D1327" s="5" t="s">
-        <v>8375</v>
+        <v>8425</v>
+      </c>
+      <c r="E1327" s="5" t="s">
+        <v>6741</v>
+      </c>
+      <c r="F1327" s="5" t="s">
+        <v>8072</v>
+      </c>
+      <c r="G1327" s="5" t="s">
+        <v>8073</v>
+      </c>
+      <c r="H1327" s="5" t="s">
+        <v>8426</v>
       </c>
     </row>
     <row r="1328">
       <c r="B1328" s="6" t="s">
-        <v>8376</v>
+        <v>8427</v>
       </c>
       <c r="C1328" s="6" t="s">
         <v>6939</v>
@@ -56246,142 +57059,298 @@
       <c r="D1328" s="6" t="s">
         <v>6676</v>
       </c>
+      <c r="E1328" s="6" t="s">
+        <v>6940</v>
+      </c>
+      <c r="F1328" s="6" t="s">
+        <v>6941</v>
+      </c>
+      <c r="G1328" s="6" t="s">
+        <v>6942</v>
+      </c>
+      <c r="H1328" s="6" t="s">
+        <v>6676</v>
+      </c>
     </row>
     <row r="1329">
       <c r="B1329" s="5" t="s">
-        <v>8377</v>
+        <v>8428</v>
       </c>
       <c r="C1329" s="5" t="s">
         <v>8048</v>
       </c>
       <c r="D1329" s="5" t="s">
-        <v>8378</v>
+        <v>8429</v>
+      </c>
+      <c r="E1329" s="5" t="s">
+        <v>8050</v>
+      </c>
+      <c r="F1329" s="5" t="s">
+        <v>8051</v>
+      </c>
+      <c r="G1329" s="5" t="s">
+        <v>8052</v>
+      </c>
+      <c r="H1329" s="5" t="s">
+        <v>8430</v>
       </c>
     </row>
     <row r="1330">
       <c r="B1330" s="6" t="s">
-        <v>8379</v>
+        <v>8431</v>
       </c>
       <c r="C1330" s="6" t="s">
-        <v>8380</v>
+        <v>8432</v>
       </c>
       <c r="D1330" s="6" t="s">
-        <v>8381</v>
+        <v>8433</v>
+      </c>
+      <c r="E1330" s="6" t="s">
+        <v>8434</v>
+      </c>
+      <c r="F1330" s="6" t="s">
+        <v>8435</v>
+      </c>
+      <c r="G1330" s="6" t="s">
+        <v>8434</v>
+      </c>
+      <c r="H1330" s="6" t="s">
+        <v>8436</v>
       </c>
     </row>
     <row r="1331">
       <c r="B1331" s="5" t="s">
-        <v>8382</v>
+        <v>8437</v>
       </c>
       <c r="C1331" s="5" t="s">
-        <v>8383</v>
+        <v>8438</v>
       </c>
       <c r="D1331" s="5" t="s">
-        <v>8384</v>
+        <v>8439</v>
+      </c>
+      <c r="E1331" s="5" t="s">
+        <v>8440</v>
+      </c>
+      <c r="F1331" s="5" t="s">
+        <v>8441</v>
+      </c>
+      <c r="G1331" s="5" t="s">
+        <v>8442</v>
+      </c>
+      <c r="H1331" s="5" t="s">
+        <v>8443</v>
       </c>
     </row>
     <row r="1332">
       <c r="B1332" s="6" t="s">
-        <v>8385</v>
+        <v>8444</v>
       </c>
       <c r="C1332" s="6" t="s">
-        <v>8386</v>
+        <v>8445</v>
       </c>
       <c r="D1332" s="6" t="s">
-        <v>8387</v>
+        <v>8446</v>
+      </c>
+      <c r="E1332" s="6" t="s">
+        <v>8447</v>
+      </c>
+      <c r="F1332" s="6" t="s">
+        <v>8448</v>
+      </c>
+      <c r="G1332" s="6" t="s">
+        <v>8449</v>
+      </c>
+      <c r="H1332" s="6" t="s">
+        <v>8450</v>
       </c>
     </row>
     <row r="1333">
       <c r="B1333" s="5" t="s">
-        <v>8388</v>
+        <v>8451</v>
       </c>
       <c r="C1333" s="5" t="s">
-        <v>8389</v>
+        <v>8452</v>
       </c>
       <c r="D1333" s="5" t="s">
-        <v>8390</v>
+        <v>8453</v>
+      </c>
+      <c r="E1333" s="5" t="s">
+        <v>8454</v>
+      </c>
+      <c r="F1333" s="5" t="s">
+        <v>8455</v>
+      </c>
+      <c r="G1333" s="5" t="s">
+        <v>8456</v>
+      </c>
+      <c r="H1333" s="5" t="s">
+        <v>8457</v>
       </c>
     </row>
     <row r="1334">
       <c r="B1334" s="6" t="s">
-        <v>8391</v>
+        <v>8458</v>
       </c>
       <c r="C1334" s="6" t="s">
-        <v>8392</v>
+        <v>8459</v>
       </c>
       <c r="D1334" s="6" t="s">
-        <v>8393</v>
+        <v>8460</v>
+      </c>
+      <c r="E1334" s="6" t="s">
+        <v>8461</v>
+      </c>
+      <c r="F1334" s="6" t="s">
+        <v>8462</v>
+      </c>
+      <c r="G1334" s="6" t="s">
+        <v>8463</v>
+      </c>
+      <c r="H1334" s="6" t="s">
+        <v>8464</v>
       </c>
     </row>
     <row r="1335">
       <c r="B1335" s="5" t="s">
-        <v>8394</v>
+        <v>8465</v>
       </c>
       <c r="C1335" s="5" t="s">
-        <v>8395</v>
+        <v>8466</v>
       </c>
       <c r="D1335" s="5" t="s">
-        <v>8396</v>
+        <v>8467</v>
+      </c>
+      <c r="E1335" s="5" t="s">
+        <v>5347</v>
+      </c>
+      <c r="F1335" s="5" t="s">
+        <v>8468</v>
+      </c>
+      <c r="G1335" s="5" t="s">
+        <v>8469</v>
+      </c>
+      <c r="H1335" s="5" t="s">
+        <v>8470</v>
       </c>
     </row>
     <row r="1336">
       <c r="B1336" s="6" t="s">
-        <v>8397</v>
+        <v>8471</v>
       </c>
       <c r="C1336" s="6" t="s">
-        <v>8398</v>
+        <v>8472</v>
       </c>
       <c r="D1336" s="6" t="s">
-        <v>8399</v>
+        <v>8473</v>
+      </c>
+      <c r="E1336" s="6" t="s">
+        <v>8474</v>
+      </c>
+      <c r="F1336" s="6" t="s">
+        <v>8475</v>
+      </c>
+      <c r="G1336" s="6" t="s">
+        <v>8476</v>
+      </c>
+      <c r="H1336" s="6" t="s">
+        <v>8477</v>
       </c>
     </row>
     <row r="1337">
       <c r="B1337" s="5" t="s">
-        <v>8400</v>
+        <v>8478</v>
       </c>
       <c r="C1337" s="5" t="s">
-        <v>8401</v>
+        <v>8479</v>
       </c>
       <c r="D1337" s="5" t="s">
-        <v>8402</v>
+        <v>8480</v>
+      </c>
+      <c r="E1337" s="5" t="s">
+        <v>8481</v>
+      </c>
+      <c r="F1337" s="5" t="s">
+        <v>8482</v>
+      </c>
+      <c r="G1337" s="5" t="s">
+        <v>8483</v>
+      </c>
+      <c r="H1337" s="5" t="s">
+        <v>8484</v>
       </c>
     </row>
     <row r="1338">
       <c r="B1338" s="6" t="s">
-        <v>8403</v>
+        <v>8485</v>
       </c>
       <c r="C1338" s="6" t="s">
-        <v>8404</v>
+        <v>8486</v>
       </c>
       <c r="D1338" s="6" t="s">
-        <v>8405</v>
+        <v>8487</v>
+      </c>
+      <c r="E1338" s="6" t="s">
+        <v>8488</v>
+      </c>
+      <c r="F1338" s="6" t="s">
+        <v>8489</v>
+      </c>
+      <c r="G1338" s="6" t="s">
+        <v>8490</v>
+      </c>
+      <c r="H1338" s="6" t="s">
+        <v>8491</v>
       </c>
     </row>
     <row r="1339">
       <c r="B1339" s="5" t="s">
-        <v>8406</v>
+        <v>8492</v>
       </c>
       <c r="C1339" s="5" t="s">
-        <v>8407</v>
+        <v>8493</v>
       </c>
       <c r="D1339" s="5" t="s">
-        <v>8408</v>
+        <v>8494</v>
+      </c>
+      <c r="E1339" s="5" t="s">
+        <v>8495</v>
+      </c>
+      <c r="F1339" s="5" t="s">
+        <v>8496</v>
+      </c>
+      <c r="G1339" s="5" t="s">
+        <v>8497</v>
+      </c>
+      <c r="H1339" s="5" t="s">
+        <v>8498</v>
       </c>
     </row>
     <row r="1340">
       <c r="B1340" s="6" t="s">
-        <v>8409</v>
+        <v>8499</v>
       </c>
       <c r="C1340" s="7" t="s">
-        <v>8410</v>
+        <v>8500</v>
       </c>
       <c r="D1340" s="7" t="s">
-        <v>8410</v>
+        <v>8500</v>
+      </c>
+      <c r="E1340" s="7" t="s">
+        <v>8500</v>
+      </c>
+      <c r="F1340" s="7" t="s">
+        <v>8500</v>
+      </c>
+      <c r="G1340" s="7" t="s">
+        <v>8500</v>
+      </c>
+      <c r="H1340" s="7" t="s">
+        <v>8500</v>
       </c>
     </row>
     <row r="1341">
       <c r="B1341" s="5" t="s">
-        <v>8411</v>
+        <v>8501</v>
       </c>
       <c r="C1341" s="5" t="s">
         <v>7912</v>
@@ -56389,406 +57358,850 @@
       <c r="D1341" s="5" t="s">
         <v>7913</v>
       </c>
+      <c r="E1341" s="5" t="s">
+        <v>7914</v>
+      </c>
+      <c r="F1341" s="5" t="s">
+        <v>7915</v>
+      </c>
+      <c r="G1341" s="5" t="s">
+        <v>7916</v>
+      </c>
+      <c r="H1341" s="5" t="s">
+        <v>7913</v>
+      </c>
     </row>
     <row r="1342">
       <c r="B1342" s="6" t="s">
-        <v>8412</v>
+        <v>8502</v>
       </c>
       <c r="C1342" s="6" t="s">
-        <v>8413</v>
+        <v>8503</v>
       </c>
       <c r="D1342" s="6" t="s">
-        <v>8414</v>
+        <v>8504</v>
+      </c>
+      <c r="E1342" s="6" t="s">
+        <v>8505</v>
+      </c>
+      <c r="F1342" s="6" t="s">
+        <v>8506</v>
+      </c>
+      <c r="G1342" s="6" t="s">
+        <v>8506</v>
+      </c>
+      <c r="H1342" s="6" t="s">
+        <v>8507</v>
       </c>
     </row>
     <row r="1343">
       <c r="B1343" s="5" t="s">
-        <v>8415</v>
+        <v>8508</v>
       </c>
       <c r="C1343" s="5" t="s">
-        <v>8416</v>
+        <v>8509</v>
       </c>
       <c r="D1343" s="5" t="s">
-        <v>8417</v>
+        <v>8510</v>
+      </c>
+      <c r="E1343" s="5" t="s">
+        <v>8511</v>
+      </c>
+      <c r="F1343" s="5" t="s">
+        <v>8512</v>
+      </c>
+      <c r="G1343" s="5" t="s">
+        <v>8513</v>
+      </c>
+      <c r="H1343" s="5" t="s">
+        <v>6011</v>
       </c>
     </row>
     <row r="1344">
       <c r="B1344" s="6" t="s">
-        <v>8418</v>
+        <v>8514</v>
       </c>
       <c r="C1344" s="6" t="s">
-        <v>8419</v>
+        <v>8515</v>
       </c>
       <c r="D1344" s="6" t="s">
-        <v>8420</v>
+        <v>8516</v>
+      </c>
+      <c r="E1344" s="6" t="s">
+        <v>8517</v>
+      </c>
+      <c r="F1344" s="6" t="s">
+        <v>8518</v>
+      </c>
+      <c r="G1344" s="6" t="s">
+        <v>8519</v>
+      </c>
+      <c r="H1344" s="6" t="s">
+        <v>8520</v>
       </c>
     </row>
     <row r="1345">
       <c r="B1345" s="5" t="s">
-        <v>8421</v>
+        <v>8521</v>
       </c>
       <c r="C1345" s="5" t="s">
-        <v>8422</v>
+        <v>8522</v>
       </c>
       <c r="D1345" s="5" t="s">
-        <v>8423</v>
+        <v>8523</v>
+      </c>
+      <c r="E1345" s="5" t="s">
+        <v>8524</v>
+      </c>
+      <c r="F1345" s="5" t="s">
+        <v>8525</v>
+      </c>
+      <c r="G1345" s="5" t="s">
+        <v>8526</v>
+      </c>
+      <c r="H1345" s="5" t="s">
+        <v>8527</v>
       </c>
     </row>
     <row r="1346">
       <c r="B1346" s="6" t="s">
-        <v>8424</v>
+        <v>8528</v>
       </c>
       <c r="C1346" s="6" t="s">
-        <v>8425</v>
+        <v>8529</v>
       </c>
       <c r="D1346" s="6" t="s">
-        <v>8426</v>
+        <v>8530</v>
+      </c>
+      <c r="E1346" s="6" t="s">
+        <v>8531</v>
+      </c>
+      <c r="F1346" s="6" t="s">
+        <v>8532</v>
+      </c>
+      <c r="G1346" s="6" t="s">
+        <v>8532</v>
+      </c>
+      <c r="H1346" s="6" t="s">
+        <v>8533</v>
       </c>
     </row>
     <row r="1347">
       <c r="B1347" s="5" t="s">
-        <v>8427</v>
+        <v>8534</v>
       </c>
       <c r="C1347" s="5" t="s">
-        <v>8428</v>
+        <v>8535</v>
       </c>
       <c r="D1347" s="5" t="s">
-        <v>8429</v>
+        <v>8536</v>
+      </c>
+      <c r="E1347" s="5" t="s">
+        <v>8537</v>
+      </c>
+      <c r="F1347" s="5" t="s">
+        <v>8538</v>
+      </c>
+      <c r="G1347" s="5" t="s">
+        <v>8539</v>
+      </c>
+      <c r="H1347" s="5" t="s">
+        <v>8540</v>
       </c>
     </row>
     <row r="1348">
       <c r="B1348" s="6" t="s">
-        <v>8430</v>
+        <v>8541</v>
       </c>
       <c r="C1348" s="6" t="s">
-        <v>8431</v>
+        <v>8542</v>
       </c>
       <c r="D1348" s="6" t="s">
-        <v>8432</v>
+        <v>8543</v>
+      </c>
+      <c r="E1348" s="6" t="s">
+        <v>8544</v>
+      </c>
+      <c r="F1348" s="6" t="s">
+        <v>8545</v>
+      </c>
+      <c r="G1348" s="6" t="s">
+        <v>8545</v>
+      </c>
+      <c r="H1348" s="6" t="s">
+        <v>8546</v>
       </c>
     </row>
     <row r="1349">
       <c r="B1349" s="5" t="s">
-        <v>8433</v>
+        <v>8547</v>
       </c>
       <c r="C1349" s="5" t="s">
-        <v>8434</v>
+        <v>8548</v>
       </c>
       <c r="D1349" s="5" t="s">
-        <v>8434</v>
+        <v>8548</v>
+      </c>
+      <c r="E1349" s="5" t="s">
+        <v>8548</v>
+      </c>
+      <c r="F1349" s="5" t="s">
+        <v>8548</v>
+      </c>
+      <c r="G1349" s="5" t="s">
+        <v>8548</v>
+      </c>
+      <c r="H1349" s="5" t="s">
+        <v>8548</v>
       </c>
     </row>
     <row r="1350">
       <c r="B1350" s="6" t="s">
-        <v>8435</v>
+        <v>8549</v>
       </c>
       <c r="C1350" s="6" t="s">
-        <v>8436</v>
+        <v>8550</v>
       </c>
       <c r="D1350" s="6" t="s">
-        <v>8437</v>
+        <v>8551</v>
+      </c>
+      <c r="E1350" s="6" t="s">
+        <v>8552</v>
+      </c>
+      <c r="F1350" s="6" t="s">
+        <v>8553</v>
+      </c>
+      <c r="G1350" s="6" t="s">
+        <v>8553</v>
+      </c>
+      <c r="H1350" s="6" t="s">
+        <v>8554</v>
       </c>
     </row>
     <row r="1351">
       <c r="B1351" s="5" t="s">
-        <v>8438</v>
+        <v>8555</v>
       </c>
       <c r="C1351" s="5" t="s">
-        <v>8434</v>
+        <v>8548</v>
       </c>
       <c r="D1351" s="5" t="s">
-        <v>8434</v>
+        <v>8548</v>
+      </c>
+      <c r="E1351" s="5" t="s">
+        <v>8548</v>
+      </c>
+      <c r="F1351" s="5" t="s">
+        <v>8548</v>
+      </c>
+      <c r="G1351" s="5" t="s">
+        <v>8548</v>
+      </c>
+      <c r="H1351" s="5" t="s">
+        <v>8548</v>
       </c>
     </row>
     <row r="1352">
       <c r="B1352" s="6" t="s">
-        <v>8439</v>
+        <v>8556</v>
       </c>
     </row>
     <row r="1353">
       <c r="B1353" s="5" t="s">
-        <v>8440</v>
+        <v>8557</v>
       </c>
       <c r="C1353" s="5" t="s">
-        <v>8441</v>
+        <v>8558</v>
       </c>
       <c r="D1353" s="5" t="s">
-        <v>8442</v>
+        <v>8559</v>
+      </c>
+      <c r="E1353" s="5" t="s">
+        <v>8560</v>
+      </c>
+      <c r="F1353" s="5" t="s">
+        <v>8561</v>
+      </c>
+      <c r="G1353" s="5" t="s">
+        <v>8562</v>
+      </c>
+      <c r="H1353" s="5" t="s">
+        <v>8563</v>
       </c>
     </row>
     <row r="1354">
       <c r="B1354" s="6" t="s">
-        <v>8443</v>
+        <v>8564</v>
       </c>
       <c r="C1354" s="6" t="s">
-        <v>8444</v>
+        <v>8565</v>
       </c>
       <c r="D1354" s="6" t="s">
-        <v>8445</v>
+        <v>8566</v>
+      </c>
+      <c r="E1354" s="6" t="s">
+        <v>8567</v>
+      </c>
+      <c r="F1354" s="6" t="s">
+        <v>8568</v>
+      </c>
+      <c r="G1354" s="6" t="s">
+        <v>8569</v>
+      </c>
+      <c r="H1354" s="6" t="s">
+        <v>8570</v>
       </c>
     </row>
     <row r="1355">
       <c r="B1355" s="5" t="s">
-        <v>8446</v>
+        <v>8571</v>
       </c>
       <c r="C1355" s="5" t="s">
-        <v>8447</v>
+        <v>8572</v>
       </c>
       <c r="D1355" s="5" t="s">
-        <v>8448</v>
+        <v>8573</v>
+      </c>
+      <c r="E1355" s="5" t="s">
+        <v>8574</v>
+      </c>
+      <c r="F1355" s="5" t="s">
+        <v>8575</v>
+      </c>
+      <c r="G1355" s="5" t="s">
+        <v>8576</v>
+      </c>
+      <c r="H1355" s="5" t="s">
+        <v>8577</v>
       </c>
     </row>
     <row r="1356">
       <c r="B1356" s="6" t="s">
-        <v>8449</v>
+        <v>8578</v>
       </c>
       <c r="C1356" s="6" t="s">
-        <v>8450</v>
+        <v>8579</v>
       </c>
       <c r="D1356" s="6" t="s">
-        <v>8451</v>
+        <v>8580</v>
+      </c>
+      <c r="E1356" s="6" t="s">
+        <v>8581</v>
+      </c>
+      <c r="F1356" s="6" t="s">
+        <v>8582</v>
+      </c>
+      <c r="G1356" s="6" t="s">
+        <v>8583</v>
+      </c>
+      <c r="H1356" s="6" t="s">
+        <v>8584</v>
       </c>
     </row>
     <row r="1357">
       <c r="B1357" s="5" t="s">
-        <v>8452</v>
+        <v>8585</v>
       </c>
       <c r="C1357" s="5" t="s">
         <v>6006</v>
       </c>
       <c r="D1357" s="5" t="s">
-        <v>8453</v>
+        <v>8586</v>
+      </c>
+      <c r="E1357" s="5" t="s">
+        <v>6008</v>
+      </c>
+      <c r="F1357" s="5" t="s">
+        <v>8587</v>
+      </c>
+      <c r="G1357" s="5" t="s">
+        <v>8587</v>
+      </c>
+      <c r="H1357" s="5" t="s">
+        <v>8588</v>
       </c>
     </row>
     <row r="1358">
       <c r="B1358" s="6" t="s">
-        <v>8454</v>
+        <v>8589</v>
       </c>
       <c r="C1358" s="6" t="s">
-        <v>8455</v>
+        <v>8590</v>
       </c>
       <c r="D1358" s="6" t="s">
-        <v>8456</v>
+        <v>8591</v>
+      </c>
+      <c r="E1358" s="6" t="s">
+        <v>8592</v>
+      </c>
+      <c r="F1358" s="6" t="s">
+        <v>8593</v>
+      </c>
+      <c r="G1358" s="6" t="s">
+        <v>8594</v>
+      </c>
+      <c r="H1358" s="6" t="s">
+        <v>8595</v>
       </c>
     </row>
     <row r="1359">
       <c r="B1359" s="5" t="s">
-        <v>8457</v>
+        <v>8596</v>
       </c>
       <c r="C1359" s="5" t="s">
-        <v>8458</v>
+        <v>8597</v>
       </c>
       <c r="D1359" s="5" t="s">
-        <v>8459</v>
+        <v>8598</v>
+      </c>
+      <c r="E1359" s="5" t="s">
+        <v>8599</v>
+      </c>
+      <c r="F1359" s="5" t="s">
+        <v>8600</v>
+      </c>
+      <c r="G1359" s="5" t="s">
+        <v>8601</v>
+      </c>
+      <c r="H1359" s="5" t="s">
+        <v>8602</v>
       </c>
     </row>
     <row r="1360">
       <c r="B1360" s="6" t="s">
-        <v>8460</v>
+        <v>8603</v>
       </c>
       <c r="C1360" s="6" t="s">
-        <v>8461</v>
+        <v>8604</v>
       </c>
       <c r="D1360" s="6" t="s">
-        <v>8462</v>
+        <v>8605</v>
+      </c>
+      <c r="E1360" s="6" t="s">
+        <v>8606</v>
+      </c>
+      <c r="F1360" s="6" t="s">
+        <v>8607</v>
+      </c>
+      <c r="G1360" s="6" t="s">
+        <v>8608</v>
+      </c>
+      <c r="H1360" s="6" t="s">
+        <v>8609</v>
       </c>
     </row>
     <row r="1361">
       <c r="B1361" s="5" t="s">
-        <v>8463</v>
+        <v>8610</v>
       </c>
       <c r="C1361" s="5" t="s">
-        <v>8464</v>
+        <v>8611</v>
       </c>
       <c r="D1361" s="5" t="s">
-        <v>8465</v>
+        <v>8612</v>
+      </c>
+      <c r="E1361" s="5" t="s">
+        <v>8613</v>
+      </c>
+      <c r="F1361" s="5" t="s">
+        <v>8614</v>
+      </c>
+      <c r="G1361" s="5" t="s">
+        <v>8615</v>
+      </c>
+      <c r="H1361" s="5" t="s">
+        <v>8616</v>
       </c>
     </row>
     <row r="1362">
       <c r="B1362" s="6" t="s">
-        <v>8466</v>
+        <v>8617</v>
       </c>
       <c r="C1362" s="6" t="s">
-        <v>8467</v>
+        <v>8618</v>
       </c>
       <c r="D1362" s="6" t="s">
-        <v>8468</v>
+        <v>8619</v>
+      </c>
+      <c r="E1362" s="6" t="s">
+        <v>8620</v>
+      </c>
+      <c r="F1362" s="6" t="s">
+        <v>8621</v>
+      </c>
+      <c r="G1362" s="6" t="s">
+        <v>8622</v>
+      </c>
+      <c r="H1362" s="6" t="s">
+        <v>8623</v>
       </c>
     </row>
     <row r="1363">
       <c r="B1363" s="5" t="s">
-        <v>8469</v>
+        <v>8624</v>
       </c>
       <c r="C1363" s="5" t="s">
-        <v>8470</v>
+        <v>8625</v>
       </c>
       <c r="D1363" s="5" t="s">
-        <v>8470</v>
+        <v>8625</v>
+      </c>
+      <c r="E1363" s="5" t="s">
+        <v>8625</v>
+      </c>
+      <c r="F1363" s="5" t="s">
+        <v>8625</v>
+      </c>
+      <c r="G1363" s="5" t="s">
+        <v>8625</v>
+      </c>
+      <c r="H1363" s="5" t="s">
+        <v>8625</v>
       </c>
     </row>
     <row r="1364">
       <c r="B1364" s="6" t="s">
-        <v>8471</v>
+        <v>8626</v>
       </c>
       <c r="C1364" s="6" t="s">
-        <v>8472</v>
+        <v>8627</v>
       </c>
       <c r="D1364" s="6" t="s">
-        <v>8473</v>
+        <v>8628</v>
+      </c>
+      <c r="E1364" s="6" t="s">
+        <v>8629</v>
+      </c>
+      <c r="F1364" s="6" t="s">
+        <v>8630</v>
+      </c>
+      <c r="G1364" s="6" t="s">
+        <v>8630</v>
+      </c>
+      <c r="H1364" s="6" t="s">
+        <v>8631</v>
       </c>
     </row>
     <row r="1365">
       <c r="B1365" s="5" t="s">
-        <v>8474</v>
+        <v>8632</v>
       </c>
       <c r="C1365" s="5" t="s">
-        <v>8475</v>
+        <v>8633</v>
       </c>
       <c r="D1365" s="5" t="s">
-        <v>8476</v>
+        <v>8634</v>
+      </c>
+      <c r="E1365" s="5" t="s">
+        <v>8635</v>
+      </c>
+      <c r="F1365" s="5" t="s">
+        <v>8636</v>
+      </c>
+      <c r="G1365" s="5" t="s">
+        <v>8637</v>
+      </c>
+      <c r="H1365" s="5" t="s">
+        <v>8638</v>
       </c>
     </row>
     <row r="1366">
       <c r="B1366" s="6" t="s">
-        <v>8477</v>
+        <v>8639</v>
       </c>
       <c r="C1366" s="6" t="s">
-        <v>8478</v>
+        <v>8640</v>
       </c>
       <c r="D1366" s="6" t="s">
-        <v>8479</v>
+        <v>8641</v>
+      </c>
+      <c r="E1366" s="6" t="s">
+        <v>8642</v>
+      </c>
+      <c r="F1366" s="6" t="s">
+        <v>8643</v>
+      </c>
+      <c r="G1366" s="6" t="s">
+        <v>8644</v>
+      </c>
+      <c r="H1366" s="6" t="s">
+        <v>8645</v>
       </c>
     </row>
     <row r="1367">
       <c r="B1367" s="5" t="s">
-        <v>8480</v>
+        <v>8646</v>
       </c>
       <c r="C1367" s="5" t="s">
-        <v>8481</v>
+        <v>8647</v>
       </c>
       <c r="D1367" s="5" t="s">
-        <v>8482</v>
+        <v>8648</v>
+      </c>
+      <c r="E1367" s="5" t="s">
+        <v>8649</v>
+      </c>
+      <c r="F1367" s="5" t="s">
+        <v>8650</v>
+      </c>
+      <c r="G1367" s="5" t="s">
+        <v>8650</v>
+      </c>
+      <c r="H1367" s="5" t="s">
+        <v>8651</v>
       </c>
     </row>
     <row r="1368">
       <c r="B1368" s="6" t="s">
-        <v>8483</v>
+        <v>8652</v>
       </c>
       <c r="C1368" s="6" t="s">
-        <v>8484</v>
+        <v>8653</v>
       </c>
       <c r="D1368" s="6" t="s">
-        <v>8485</v>
+        <v>8654</v>
+      </c>
+      <c r="E1368" s="6" t="s">
+        <v>8655</v>
+      </c>
+      <c r="F1368" s="6" t="s">
+        <v>8656</v>
+      </c>
+      <c r="G1368" s="6" t="s">
+        <v>8656</v>
+      </c>
+      <c r="H1368" s="6" t="s">
+        <v>8657</v>
       </c>
     </row>
     <row r="1369">
       <c r="B1369" s="5" t="s">
-        <v>8486</v>
+        <v>8658</v>
       </c>
       <c r="C1369" s="5" t="s">
-        <v>8487</v>
+        <v>8659</v>
       </c>
       <c r="D1369" s="5" t="s">
-        <v>8488</v>
+        <v>8660</v>
+      </c>
+      <c r="E1369" s="5" t="s">
+        <v>8661</v>
+      </c>
+      <c r="F1369" s="5" t="s">
+        <v>8662</v>
+      </c>
+      <c r="G1369" s="5" t="s">
+        <v>8663</v>
+      </c>
+      <c r="H1369" s="5" t="s">
+        <v>8664</v>
       </c>
     </row>
     <row r="1370">
       <c r="B1370" s="6" t="s">
-        <v>8489</v>
+        <v>8665</v>
       </c>
       <c r="C1370" s="6" t="s">
-        <v>8490</v>
+        <v>8666</v>
       </c>
       <c r="D1370" s="6" t="s">
-        <v>8491</v>
+        <v>8667</v>
+      </c>
+      <c r="E1370" s="6" t="s">
+        <v>8668</v>
+      </c>
+      <c r="F1370" s="6" t="s">
+        <v>8669</v>
+      </c>
+      <c r="G1370" s="6" t="s">
+        <v>8670</v>
+      </c>
+      <c r="H1370" s="6" t="s">
+        <v>8671</v>
       </c>
     </row>
     <row r="1371">
       <c r="B1371" s="5" t="s">
-        <v>8492</v>
+        <v>8672</v>
       </c>
       <c r="C1371" s="5" t="s">
-        <v>8493</v>
+        <v>8673</v>
       </c>
       <c r="D1371" s="5" t="s">
-        <v>8494</v>
+        <v>8674</v>
+      </c>
+      <c r="E1371" s="5" t="s">
+        <v>8675</v>
+      </c>
+      <c r="F1371" s="5" t="s">
+        <v>8676</v>
+      </c>
+      <c r="G1371" s="5" t="s">
+        <v>8677</v>
+      </c>
+      <c r="H1371" s="5" t="s">
+        <v>8678</v>
       </c>
     </row>
     <row r="1372">
       <c r="B1372" s="6" t="s">
-        <v>8495</v>
+        <v>8679</v>
       </c>
       <c r="C1372" s="6" t="s">
-        <v>8496</v>
+        <v>8680</v>
       </c>
       <c r="D1372" s="6" t="s">
-        <v>8497</v>
+        <v>8681</v>
+      </c>
+      <c r="E1372" s="6" t="s">
+        <v>8682</v>
+      </c>
+      <c r="F1372" s="6" t="s">
+        <v>8683</v>
+      </c>
+      <c r="G1372" s="6" t="s">
+        <v>8684</v>
+      </c>
+      <c r="H1372" s="6" t="s">
+        <v>8685</v>
       </c>
     </row>
     <row r="1373">
       <c r="B1373" s="5" t="s">
-        <v>8498</v>
+        <v>8686</v>
       </c>
       <c r="C1373" s="5" t="s">
-        <v>8499</v>
+        <v>8687</v>
       </c>
       <c r="D1373" s="5" t="s">
-        <v>8500</v>
+        <v>8688</v>
+      </c>
+      <c r="E1373" s="5" t="s">
+        <v>8689</v>
+      </c>
+      <c r="F1373" s="5" t="s">
+        <v>8690</v>
+      </c>
+      <c r="G1373" s="5" t="s">
+        <v>8691</v>
+      </c>
+      <c r="H1373" s="5" t="s">
+        <v>8692</v>
       </c>
     </row>
     <row r="1374">
       <c r="B1374" s="6" t="s">
-        <v>8501</v>
+        <v>8693</v>
       </c>
       <c r="C1374" s="6" t="s">
-        <v>8502</v>
+        <v>8694</v>
       </c>
       <c r="D1374" s="6" t="s">
-        <v>8503</v>
+        <v>8695</v>
+      </c>
+      <c r="E1374" s="6" t="s">
+        <v>8696</v>
+      </c>
+      <c r="F1374" s="6" t="s">
+        <v>8697</v>
+      </c>
+      <c r="G1374" s="6" t="s">
+        <v>8698</v>
+      </c>
+      <c r="H1374" s="6" t="s">
+        <v>8699</v>
       </c>
     </row>
     <row r="1375">
       <c r="B1375" s="5" t="s">
-        <v>8504</v>
+        <v>8700</v>
       </c>
       <c r="C1375" s="5" t="s">
-        <v>8505</v>
+        <v>8701</v>
       </c>
       <c r="D1375" s="5" t="s">
-        <v>8506</v>
+        <v>8702</v>
+      </c>
+      <c r="E1375" s="5" t="s">
+        <v>8703</v>
+      </c>
+      <c r="F1375" s="5" t="s">
+        <v>8704</v>
+      </c>
+      <c r="G1375" s="5" t="s">
+        <v>8705</v>
+      </c>
+      <c r="H1375" s="5" t="s">
+        <v>8706</v>
       </c>
     </row>
     <row r="1376">
       <c r="B1376" s="6" t="s">
-        <v>8507</v>
+        <v>8707</v>
       </c>
       <c r="C1376" s="6" t="s">
-        <v>8508</v>
+        <v>8708</v>
       </c>
       <c r="D1376" s="6" t="s">
-        <v>8509</v>
+        <v>8709</v>
+      </c>
+      <c r="E1376" s="6" t="s">
+        <v>8710</v>
+      </c>
+      <c r="F1376" s="6" t="s">
+        <v>8711</v>
+      </c>
+      <c r="G1376" s="6" t="s">
+        <v>8712</v>
+      </c>
+      <c r="H1376" s="6" t="s">
+        <v>8713</v>
       </c>
     </row>
     <row r="1377">
       <c r="B1377" s="5" t="s">
-        <v>8510</v>
+        <v>8714</v>
       </c>
       <c r="C1377" s="5" t="s">
-        <v>8511</v>
+        <v>8715</v>
       </c>
       <c r="D1377" s="5" t="s">
-        <v>8512</v>
+        <v>8716</v>
+      </c>
+      <c r="E1377" s="5" t="s">
+        <v>8717</v>
+      </c>
+      <c r="F1377" s="5" t="s">
+        <v>8718</v>
+      </c>
+      <c r="G1377" s="5" t="s">
+        <v>8719</v>
+      </c>
+      <c r="H1377" s="5" t="s">
+        <v>8720</v>
       </c>
     </row>
     <row r="1378">
       <c r="B1378" s="6" t="s">
-        <v>8513</v>
+        <v>8721</v>
       </c>
       <c r="C1378" s="6" t="s">
         <v>4476</v>
       </c>
       <c r="D1378" s="6" t="s">
-        <v>8514</v>
+        <v>8722</v>
+      </c>
+      <c r="E1378" s="6" t="s">
+        <v>4478</v>
+      </c>
+      <c r="F1378" s="6" t="s">
+        <v>8723</v>
+      </c>
+      <c r="G1378" s="6" t="s">
+        <v>8724</v>
+      </c>
+      <c r="H1378" s="6" t="s">
+        <v>8725</v>
       </c>
     </row>
   </sheetData>
@@ -56811,10 +58224,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>8515</v>
+        <v>8726</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8516</v>
+        <v>8727</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -56825,16 +58238,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8517</v>
+        <v>8728</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8518</v>
+        <v>8729</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8519</v>
+        <v>8730</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8520</v>
+        <v>8731</v>
       </c>
     </row>
     <row r="3">
@@ -56842,16 +58255,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8521</v>
+        <v>8732</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8522</v>
+        <v>8733</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8523</v>
+        <v>8734</v>
       </c>
     </row>
     <row r="4">
@@ -56862,24 +58275,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8524</v>
+        <v>8735</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8525</v>
+        <v>8736</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8526</v>
+        <v>8737</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>8527</v>
+        <v>8738</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4463</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8528</v>
+        <v>8739</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -56887,13 +58300,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>8529</v>
+        <v>8740</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4470</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>8530</v>
+        <v>8741</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -56901,13 +58314,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>8531</v>
+        <v>8742</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4476</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8532</v>
+        <v>8743</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -56915,13 +58328,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>8533</v>
+        <v>8744</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4482</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>8534</v>
+        <v>8745</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -56929,13 +58342,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>8535</v>
+        <v>8746</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4489</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8536</v>
+        <v>8747</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -56943,13 +58356,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>8537</v>
+        <v>8748</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4496</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>8538</v>
+        <v>8749</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -56957,13 +58370,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>8539</v>
+        <v>8750</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4502</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>8540</v>
+        <v>8751</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -56971,13 +58384,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>8541</v>
+        <v>8752</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4508</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>8542</v>
+        <v>8753</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -56985,13 +58398,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>8543</v>
+        <v>8754</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4515</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8544</v>
+        <v>8755</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -56999,13 +58412,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>8545</v>
+        <v>8756</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4521</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>8546</v>
+        <v>8757</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -57019,7 +58432,7 @@
         <v>4527</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8547</v>
+        <v>8758</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -57027,13 +58440,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>8548</v>
+        <v>8759</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4534</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>8549</v>
+        <v>8760</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -57041,13 +58454,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>8550</v>
+        <v>8761</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4541</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>8551</v>
+        <v>8762</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -57055,13 +58468,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>8552</v>
+        <v>8763</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4547</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>8553</v>
+        <v>8764</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -57069,13 +58482,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>8554</v>
+        <v>8765</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4554</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>8555</v>
+        <v>8766</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -57083,13 +58496,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>8556</v>
+        <v>8767</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4560</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>8557</v>
+        <v>8768</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -57097,13 +58510,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>8558</v>
+        <v>8769</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4565</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>8559</v>
+        <v>8770</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -57111,13 +58524,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>8560</v>
+        <v>8771</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4572</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>8561</v>
+        <v>8772</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -57125,13 +58538,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>8562</v>
+        <v>8773</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4394</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>8563</v>
+        <v>8774</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -57139,13 +58552,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>8564</v>
+        <v>8775</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4580</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>8565</v>
+        <v>8776</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1405]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1427]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9892" uniqueCount="8926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9958" uniqueCount="8990">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -26642,6 +26642,198 @@
   </si>
   <si>
     <t xml:space="preserve">geschafft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.single</t>
+  </si>
+  <si>
+    <t xml:space="preserve">싱글플레이로 시작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play without an account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.singleNote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">언제든지 나중에 계정을 연결할 수 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can link an account later at any time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.chip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.guest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">싱글플레이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계정 연결</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.needLink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순위표에 오르려면 계정을 연결해야 합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link an account to appear on the leaderboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뒤로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.why</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계정이 있으면 순위표에 오르고, 기록이 이 기계에만 남지 않습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An account puts you on the leaderboard and keeps your records off this device alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.devLogin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">개발용 로그인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev sign-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.continueWith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} 로 계속하기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continue with {name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.or</t>
+  </si>
+  <si>
+    <t xml:space="preserve">또는</t>
+  </si>
+  <si>
+    <t xml:space="preserve">or</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.guestStart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계정 없이 시작하기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start without an account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계속하면 이용약관과 개인정보처리방침에 동의하는 것으로 봅니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By continuing you agree to the Terms of Service and Privacy Policy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.signedInAs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} 으로 하고 있습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signed in as {name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.rankedStart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">랭크 시작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start ranked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.lb.rankedOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아니오</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.signOutAsk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그아웃할까요?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign out?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.signOutBody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 기계에서만 로그아웃합니다. 다시 로그인하면 기록이 그대로 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signs out on this device only. Your records stay when you sign back in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.signingIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인 중</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signing in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.account.signingOut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그아웃 중</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signing out</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -27003,7 +27195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1405"/>
+  <dimension ref="A1:H1427"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -59272,8 +59464,250 @@
         <v>8874</v>
       </c>
     </row>
+    <row r="1406">
+      <c r="B1406" s="6" t="s">
+        <v>8875</v>
+      </c>
+      <c r="C1406" s="6" t="s">
+        <v>8876</v>
+      </c>
+      <c r="D1406" s="6" t="s">
+        <v>8877</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="B1407" s="5" t="s">
+        <v>8878</v>
+      </c>
+      <c r="C1407" s="5" t="s">
+        <v>8879</v>
+      </c>
+      <c r="D1407" s="5" t="s">
+        <v>8880</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="B1408" s="6" t="s">
+        <v>8881</v>
+      </c>
+      <c r="C1408" s="6" t="s">
+        <v>8882</v>
+      </c>
+      <c r="D1408" s="6" t="s">
+        <v>8883</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="B1409" s="5" t="s">
+        <v>8884</v>
+      </c>
+      <c r="C1409" s="5" t="s">
+        <v>8885</v>
+      </c>
+      <c r="D1409" s="5" t="s">
+        <v>8886</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="B1410" s="6" t="s">
+        <v>8887</v>
+      </c>
+      <c r="C1410" s="6" t="s">
+        <v>8888</v>
+      </c>
+      <c r="D1410" s="6" t="s">
+        <v>8889</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="B1411" s="5" t="s">
+        <v>8890</v>
+      </c>
+      <c r="C1411" s="5" t="s">
+        <v>8891</v>
+      </c>
+      <c r="D1411" s="5" t="s">
+        <v>8892</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="B1412" s="6" t="s">
+        <v>8893</v>
+      </c>
+      <c r="C1412" s="6" t="s">
+        <v>8894</v>
+      </c>
+      <c r="D1412" s="6" t="s">
+        <v>8895</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="B1413" s="5" t="s">
+        <v>8896</v>
+      </c>
+      <c r="C1413" s="5" t="s">
+        <v>8897</v>
+      </c>
+      <c r="D1413" s="5" t="s">
+        <v>8898</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="B1414" s="6" t="s">
+        <v>8899</v>
+      </c>
+      <c r="C1414" s="6" t="s">
+        <v>8900</v>
+      </c>
+      <c r="D1414" s="6" t="s">
+        <v>8901</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="B1415" s="5" t="s">
+        <v>8902</v>
+      </c>
+      <c r="C1415" s="5" t="s">
+        <v>8903</v>
+      </c>
+      <c r="D1415" s="5" t="s">
+        <v>8904</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="B1416" s="6" t="s">
+        <v>8905</v>
+      </c>
+      <c r="C1416" s="6" t="s">
+        <v>8906</v>
+      </c>
+      <c r="D1416" s="6" t="s">
+        <v>8907</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="B1417" s="5" t="s">
+        <v>8908</v>
+      </c>
+      <c r="C1417" s="5" t="s">
+        <v>8909</v>
+      </c>
+      <c r="D1417" s="5" t="s">
+        <v>8910</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="B1418" s="6" t="s">
+        <v>8911</v>
+      </c>
+      <c r="C1418" s="6" t="s">
+        <v>8912</v>
+      </c>
+      <c r="D1418" s="6" t="s">
+        <v>8913</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="B1419" s="5" t="s">
+        <v>8914</v>
+      </c>
+      <c r="C1419" s="5" t="s">
+        <v>8915</v>
+      </c>
+      <c r="D1419" s="5" t="s">
+        <v>8916</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="B1420" s="6" t="s">
+        <v>8917</v>
+      </c>
+      <c r="C1420" s="6" t="s">
+        <v>8918</v>
+      </c>
+      <c r="D1420" s="6" t="s">
+        <v>8919</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="B1421" s="5" t="s">
+        <v>8920</v>
+      </c>
+      <c r="C1421" s="5" t="s">
+        <v>6112</v>
+      </c>
+      <c r="D1421" s="5" t="s">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="B1422" s="6" t="s">
+        <v>8921</v>
+      </c>
+      <c r="C1422" s="6" t="s">
+        <v>8922</v>
+      </c>
+      <c r="D1422" s="6" t="s">
+        <v>8923</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="B1423" s="5" t="s">
+        <v>8924</v>
+      </c>
+      <c r="C1423" s="5" t="s">
+        <v>8925</v>
+      </c>
+      <c r="D1423" s="5" t="s">
+        <v>8926</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="B1424" s="6" t="s">
+        <v>8927</v>
+      </c>
+      <c r="C1424" s="6" t="s">
+        <v>8928</v>
+      </c>
+      <c r="D1424" s="6" t="s">
+        <v>8929</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="B1425" s="5" t="s">
+        <v>8930</v>
+      </c>
+      <c r="C1425" s="5" t="s">
+        <v>8931</v>
+      </c>
+      <c r="D1425" s="5" t="s">
+        <v>8932</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="B1426" s="6" t="s">
+        <v>8933</v>
+      </c>
+      <c r="C1426" s="6" t="s">
+        <v>8934</v>
+      </c>
+      <c r="D1426" s="6" t="s">
+        <v>8935</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="B1427" s="5" t="s">
+        <v>8936</v>
+      </c>
+      <c r="C1427" s="5" t="s">
+        <v>8937</v>
+      </c>
+      <c r="D1427" s="5" t="s">
+        <v>8938</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H1405"/>
+  <autoFilter ref="B2:H1427"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -59292,10 +59726,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>8875</v>
+        <v>8939</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8876</v>
+        <v>8940</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -59306,16 +59740,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8877</v>
+        <v>8941</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8878</v>
+        <v>8942</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8879</v>
+        <v>8943</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8880</v>
+        <v>8944</v>
       </c>
     </row>
     <row r="3">
@@ -59323,16 +59757,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8881</v>
+        <v>8945</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8882</v>
+        <v>8946</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8883</v>
+        <v>8947</v>
       </c>
     </row>
     <row r="4">
@@ -59343,24 +59777,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8884</v>
+        <v>8948</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8885</v>
+        <v>8949</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8886</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>8887</v>
+        <v>8951</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4569</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8888</v>
+        <v>8952</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -59368,13 +59802,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>8889</v>
+        <v>8953</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4576</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>8890</v>
+        <v>8954</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -59382,13 +59816,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>8891</v>
+        <v>8955</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4582</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8892</v>
+        <v>8956</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -59396,13 +59830,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>8893</v>
+        <v>8957</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4588</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>8894</v>
+        <v>8958</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -59410,13 +59844,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>8895</v>
+        <v>8959</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4595</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8896</v>
+        <v>8960</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -59424,13 +59858,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>8897</v>
+        <v>8961</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4602</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>8898</v>
+        <v>8962</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -59438,13 +59872,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>8899</v>
+        <v>8963</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4608</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>8900</v>
+        <v>8964</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -59452,13 +59886,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>8901</v>
+        <v>8965</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4614</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>8902</v>
+        <v>8966</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -59466,13 +59900,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>8903</v>
+        <v>8967</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4621</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8904</v>
+        <v>8968</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -59480,13 +59914,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>8905</v>
+        <v>8969</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4627</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>8906</v>
+        <v>8970</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -59500,7 +59934,7 @@
         <v>4633</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8907</v>
+        <v>8971</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -59508,13 +59942,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>8908</v>
+        <v>8972</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4640</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>8909</v>
+        <v>8973</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -59522,13 +59956,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>8910</v>
+        <v>8974</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4647</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>8911</v>
+        <v>8975</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -59536,13 +59970,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>8912</v>
+        <v>8976</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4653</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>8913</v>
+        <v>8977</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -59550,13 +59984,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>8914</v>
+        <v>8978</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4660</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>8915</v>
+        <v>8979</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -59564,13 +59998,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>8916</v>
+        <v>8980</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4666</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>8917</v>
+        <v>8981</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -59578,13 +60012,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>8918</v>
+        <v>8982</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4671</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>8919</v>
+        <v>8983</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -59592,13 +60026,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>8920</v>
+        <v>8984</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4678</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>8921</v>
+        <v>8985</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -59606,13 +60040,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>8922</v>
+        <v>8986</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4500</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>8923</v>
+        <v>8987</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -59620,13 +60054,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>8924</v>
+        <v>8988</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4686</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>8925</v>
+        <v>8989</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1427]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1428]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9958" uniqueCount="8990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9965" uniqueCount="8996">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -21134,6 +21134,24 @@
   </si>
   <si>
     <t xml:space="preserve">Kauf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.money.rental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">임대료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">レンタル料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">租金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miete</t>
   </si>
   <si>
     <t xml:space="preserve">ui.blind.small</t>
@@ -27186,7 +27204,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -27195,7 +27213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1427"/>
+  <dimension ref="A1:H1428"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -52412,128 +52430,128 @@
         <v>7054</v>
       </c>
       <c r="F1098" s="6" t="s">
-        <v>7053</v>
+        <v>7055</v>
       </c>
       <c r="G1098" s="6" t="s">
-        <v>7053</v>
+        <v>7055</v>
       </c>
       <c r="H1098" s="6" t="s">
-        <v>7053</v>
+        <v>7056</v>
       </c>
     </row>
     <row r="1099">
       <c r="B1099" s="5" t="s">
-        <v>7055</v>
+        <v>7057</v>
       </c>
       <c r="C1099" s="5" t="s">
-        <v>6033</v>
+        <v>7058</v>
       </c>
       <c r="D1099" s="5" t="s">
-        <v>5404</v>
+        <v>7059</v>
       </c>
       <c r="E1099" s="5" t="s">
-        <v>6035</v>
+        <v>7060</v>
       </c>
       <c r="F1099" s="5" t="s">
-        <v>6036</v>
+        <v>7059</v>
       </c>
       <c r="G1099" s="5" t="s">
-        <v>6036</v>
+        <v>7059</v>
       </c>
       <c r="H1099" s="5" t="s">
-        <v>5404</v>
+        <v>7059</v>
       </c>
     </row>
     <row r="1100">
       <c r="B1100" s="6" t="s">
-        <v>7056</v>
+        <v>7061</v>
       </c>
       <c r="C1100" s="6" t="s">
-        <v>7057</v>
+        <v>6033</v>
       </c>
       <c r="D1100" s="6" t="s">
-        <v>7058</v>
+        <v>5404</v>
       </c>
       <c r="E1100" s="6" t="s">
-        <v>7059</v>
+        <v>6035</v>
       </c>
       <c r="F1100" s="6" t="s">
-        <v>7059</v>
+        <v>6036</v>
       </c>
       <c r="G1100" s="6" t="s">
-        <v>7059</v>
+        <v>6036</v>
       </c>
       <c r="H1100" s="6" t="s">
-        <v>7060</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1101">
       <c r="B1101" s="5" t="s">
-        <v>7061</v>
+        <v>7062</v>
       </c>
       <c r="C1101" s="5" t="s">
-        <v>6080</v>
+        <v>7063</v>
       </c>
       <c r="D1101" s="5" t="s">
-        <v>7062</v>
+        <v>7064</v>
       </c>
       <c r="E1101" s="5" t="s">
-        <v>6082</v>
+        <v>7065</v>
       </c>
       <c r="F1101" s="5" t="s">
-        <v>6083</v>
+        <v>7065</v>
       </c>
       <c r="G1101" s="5" t="s">
-        <v>6084</v>
+        <v>7065</v>
       </c>
       <c r="H1101" s="5" t="s">
-        <v>7063</v>
+        <v>7066</v>
       </c>
     </row>
     <row r="1102">
       <c r="B1102" s="6" t="s">
-        <v>7064</v>
+        <v>7067</v>
       </c>
       <c r="C1102" s="6" t="s">
-        <v>6074</v>
+        <v>6080</v>
       </c>
       <c r="D1102" s="6" t="s">
-        <v>7065</v>
+        <v>7068</v>
       </c>
       <c r="E1102" s="6" t="s">
-        <v>6076</v>
+        <v>6082</v>
       </c>
       <c r="F1102" s="6" t="s">
-        <v>6077</v>
+        <v>6083</v>
       </c>
       <c r="G1102" s="6" t="s">
-        <v>6077</v>
+        <v>6084</v>
       </c>
       <c r="H1102" s="6" t="s">
-        <v>7066</v>
+        <v>7069</v>
       </c>
     </row>
     <row r="1103">
       <c r="B1103" s="5" t="s">
-        <v>7067</v>
+        <v>7070</v>
       </c>
       <c r="C1103" s="5" t="s">
-        <v>7068</v>
+        <v>6074</v>
       </c>
       <c r="D1103" s="5" t="s">
-        <v>7069</v>
+        <v>7071</v>
       </c>
       <c r="E1103" s="5" t="s">
-        <v>7070</v>
+        <v>6076</v>
       </c>
       <c r="F1103" s="5" t="s">
-        <v>7071</v>
+        <v>6077</v>
       </c>
       <c r="G1103" s="5" t="s">
+        <v>6077</v>
+      </c>
+      <c r="H1103" s="5" t="s">
         <v>7072</v>
-      </c>
-      <c r="H1103" s="5" t="s">
-        <v>7069</v>
       </c>
     </row>
     <row r="1104">
@@ -52553,7 +52571,7 @@
         <v>7077</v>
       </c>
       <c r="G1104" s="6" t="s">
-        <v>7077</v>
+        <v>7078</v>
       </c>
       <c r="H1104" s="6" t="s">
         <v>7075</v>
@@ -52561,82 +52579,82 @@
     </row>
     <row r="1105">
       <c r="B1105" s="5" t="s">
-        <v>7078</v>
+        <v>7079</v>
       </c>
       <c r="C1105" s="5" t="s">
-        <v>7079</v>
+        <v>7080</v>
       </c>
       <c r="D1105" s="5" t="s">
-        <v>7080</v>
+        <v>7081</v>
       </c>
       <c r="E1105" s="5" t="s">
-        <v>7081</v>
+        <v>7082</v>
       </c>
       <c r="F1105" s="5" t="s">
-        <v>7082</v>
+        <v>7083</v>
       </c>
       <c r="G1105" s="5" t="s">
         <v>7083</v>
       </c>
       <c r="H1105" s="5" t="s">
-        <v>7084</v>
+        <v>7081</v>
       </c>
     </row>
     <row r="1106">
       <c r="B1106" s="6" t="s">
+        <v>7084</v>
+      </c>
+      <c r="C1106" s="6" t="s">
         <v>7085</v>
-      </c>
-      <c r="C1106" s="6" t="s">
-        <v>6172</v>
       </c>
       <c r="D1106" s="6" t="s">
         <v>7086</v>
       </c>
       <c r="E1106" s="6" t="s">
-        <v>6174</v>
+        <v>7087</v>
       </c>
       <c r="F1106" s="6" t="s">
-        <v>6175</v>
+        <v>7088</v>
       </c>
       <c r="G1106" s="6" t="s">
-        <v>6175</v>
+        <v>7089</v>
       </c>
       <c r="H1106" s="6" t="s">
-        <v>6176</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="1107">
       <c r="B1107" s="5" t="s">
-        <v>7087</v>
+        <v>7091</v>
       </c>
       <c r="C1107" s="5" t="s">
-        <v>7088</v>
+        <v>6172</v>
       </c>
       <c r="D1107" s="5" t="s">
-        <v>6825</v>
+        <v>7092</v>
       </c>
       <c r="E1107" s="5" t="s">
-        <v>7089</v>
+        <v>6174</v>
       </c>
       <c r="F1107" s="5" t="s">
-        <v>7090</v>
+        <v>6175</v>
       </c>
       <c r="G1107" s="5" t="s">
-        <v>7091</v>
+        <v>6175</v>
       </c>
       <c r="H1107" s="5" t="s">
-        <v>6825</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="1108">
       <c r="B1108" s="6" t="s">
-        <v>7092</v>
+        <v>7093</v>
       </c>
       <c r="C1108" s="6" t="s">
-        <v>7093</v>
+        <v>7094</v>
       </c>
       <c r="D1108" s="6" t="s">
-        <v>7094</v>
+        <v>6825</v>
       </c>
       <c r="E1108" s="6" t="s">
         <v>7095</v>
@@ -52645,33 +52663,33 @@
         <v>7096</v>
       </c>
       <c r="G1108" s="6" t="s">
-        <v>7096</v>
+        <v>7097</v>
       </c>
       <c r="H1108" s="6" t="s">
-        <v>7094</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="1109">
       <c r="B1109" s="5" t="s">
-        <v>7097</v>
+        <v>7098</v>
       </c>
       <c r="C1109" s="5" t="s">
-        <v>7098</v>
+        <v>7099</v>
       </c>
       <c r="D1109" s="5" t="s">
-        <v>7099</v>
+        <v>7100</v>
       </c>
       <c r="E1109" s="5" t="s">
+        <v>7101</v>
+      </c>
+      <c r="F1109" s="5" t="s">
+        <v>7102</v>
+      </c>
+      <c r="G1109" s="5" t="s">
+        <v>7102</v>
+      </c>
+      <c r="H1109" s="5" t="s">
         <v>7100</v>
-      </c>
-      <c r="F1109" s="5" t="s">
-        <v>7101</v>
-      </c>
-      <c r="G1109" s="5" t="s">
-        <v>7101</v>
-      </c>
-      <c r="H1109" s="5" t="s">
-        <v>7102</v>
       </c>
     </row>
     <row r="1110">
@@ -52679,65 +52697,65 @@
         <v>7103</v>
       </c>
       <c r="C1110" s="6" t="s">
-        <v>6164</v>
+        <v>7104</v>
       </c>
       <c r="D1110" s="6" t="s">
-        <v>7094</v>
+        <v>7105</v>
       </c>
       <c r="E1110" s="6" t="s">
-        <v>6166</v>
+        <v>7106</v>
       </c>
       <c r="F1110" s="6" t="s">
-        <v>6167</v>
+        <v>7107</v>
       </c>
       <c r="G1110" s="6" t="s">
-        <v>6167</v>
+        <v>7107</v>
       </c>
       <c r="H1110" s="6" t="s">
-        <v>6168</v>
+        <v>7108</v>
       </c>
     </row>
     <row r="1111">
       <c r="B1111" s="5" t="s">
-        <v>7104</v>
+        <v>7109</v>
       </c>
       <c r="C1111" s="5" t="s">
-        <v>6046</v>
+        <v>6164</v>
       </c>
       <c r="D1111" s="5" t="s">
-        <v>7105</v>
+        <v>7100</v>
       </c>
       <c r="E1111" s="5" t="s">
-        <v>6048</v>
+        <v>6166</v>
       </c>
       <c r="F1111" s="5" t="s">
-        <v>6049</v>
+        <v>6167</v>
       </c>
       <c r="G1111" s="5" t="s">
-        <v>6050</v>
+        <v>6167</v>
       </c>
       <c r="H1111" s="5" t="s">
-        <v>7106</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="1112">
       <c r="B1112" s="6" t="s">
-        <v>7107</v>
+        <v>7110</v>
       </c>
       <c r="C1112" s="6" t="s">
-        <v>7108</v>
+        <v>6046</v>
       </c>
       <c r="D1112" s="6" t="s">
-        <v>7109</v>
+        <v>7111</v>
       </c>
       <c r="E1112" s="6" t="s">
-        <v>7110</v>
+        <v>6048</v>
       </c>
       <c r="F1112" s="6" t="s">
-        <v>7111</v>
+        <v>6049</v>
       </c>
       <c r="G1112" s="6" t="s">
-        <v>7111</v>
+        <v>6050</v>
       </c>
       <c r="H1112" s="6" t="s">
         <v>7112</v>
@@ -52757,27 +52775,27 @@
         <v>7116</v>
       </c>
       <c r="F1113" s="5" t="s">
-        <v>7116</v>
+        <v>7117</v>
       </c>
       <c r="G1113" s="5" t="s">
-        <v>7116</v>
+        <v>7117</v>
       </c>
       <c r="H1113" s="5" t="s">
-        <v>7117</v>
+        <v>7118</v>
       </c>
     </row>
     <row r="1114">
       <c r="B1114" s="6" t="s">
-        <v>7118</v>
+        <v>7119</v>
       </c>
       <c r="C1114" s="6" t="s">
-        <v>7119</v>
+        <v>7120</v>
       </c>
       <c r="D1114" s="6" t="s">
-        <v>7120</v>
+        <v>7121</v>
       </c>
       <c r="E1114" s="6" t="s">
-        <v>7121</v>
+        <v>7122</v>
       </c>
       <c r="F1114" s="6" t="s">
         <v>7122</v>
@@ -52794,275 +52812,275 @@
         <v>7124</v>
       </c>
       <c r="C1115" s="5" t="s">
-        <v>6231</v>
+        <v>7125</v>
       </c>
       <c r="D1115" s="5" t="s">
-        <v>7125</v>
+        <v>7126</v>
       </c>
       <c r="E1115" s="5" t="s">
-        <v>6233</v>
+        <v>7127</v>
       </c>
       <c r="F1115" s="5" t="s">
-        <v>4540</v>
+        <v>7128</v>
       </c>
       <c r="G1115" s="5" t="s">
-        <v>4540</v>
+        <v>7128</v>
       </c>
       <c r="H1115" s="5" t="s">
-        <v>7126</v>
+        <v>7129</v>
       </c>
     </row>
     <row r="1116">
       <c r="B1116" s="6" t="s">
-        <v>7127</v>
+        <v>7130</v>
       </c>
       <c r="C1116" s="6" t="s">
-        <v>6236</v>
+        <v>6231</v>
       </c>
       <c r="D1116" s="6" t="s">
-        <v>7128</v>
+        <v>7131</v>
       </c>
       <c r="E1116" s="6" t="s">
-        <v>6238</v>
+        <v>6233</v>
       </c>
       <c r="F1116" s="6" t="s">
-        <v>6239</v>
+        <v>4540</v>
       </c>
       <c r="G1116" s="6" t="s">
-        <v>6240</v>
+        <v>4540</v>
       </c>
       <c r="H1116" s="6" t="s">
-        <v>7129</v>
+        <v>7132</v>
       </c>
     </row>
     <row r="1117">
       <c r="B1117" s="5" t="s">
-        <v>7130</v>
+        <v>7133</v>
       </c>
       <c r="C1117" s="5" t="s">
-        <v>6243</v>
+        <v>6236</v>
       </c>
       <c r="D1117" s="5" t="s">
-        <v>7131</v>
+        <v>7134</v>
       </c>
       <c r="E1117" s="5" t="s">
-        <v>6245</v>
+        <v>6238</v>
       </c>
       <c r="F1117" s="5" t="s">
-        <v>6246</v>
+        <v>6239</v>
       </c>
       <c r="G1117" s="5" t="s">
-        <v>6246</v>
+        <v>6240</v>
       </c>
       <c r="H1117" s="5" t="s">
-        <v>7132</v>
+        <v>7135</v>
       </c>
     </row>
     <row r="1118">
       <c r="B1118" s="6" t="s">
-        <v>7133</v>
+        <v>7136</v>
       </c>
       <c r="C1118" s="6" t="s">
-        <v>4633</v>
+        <v>6243</v>
       </c>
       <c r="D1118" s="6" t="s">
-        <v>4634</v>
+        <v>7137</v>
       </c>
       <c r="E1118" s="6" t="s">
-        <v>4635</v>
+        <v>6245</v>
       </c>
       <c r="F1118" s="6" t="s">
-        <v>4636</v>
+        <v>6246</v>
       </c>
       <c r="G1118" s="6" t="s">
-        <v>4637</v>
+        <v>6246</v>
       </c>
       <c r="H1118" s="6" t="s">
-        <v>4638</v>
+        <v>7138</v>
       </c>
     </row>
     <row r="1119">
       <c r="B1119" s="5" t="s">
-        <v>7134</v>
+        <v>7139</v>
       </c>
       <c r="C1119" s="5" t="s">
-        <v>4500</v>
+        <v>4633</v>
       </c>
       <c r="D1119" s="5" t="s">
-        <v>4501</v>
+        <v>4634</v>
       </c>
       <c r="E1119" s="5" t="s">
-        <v>4502</v>
+        <v>4635</v>
       </c>
       <c r="F1119" s="5" t="s">
-        <v>4503</v>
+        <v>4636</v>
       </c>
       <c r="G1119" s="5" t="s">
-        <v>4504</v>
+        <v>4637</v>
       </c>
       <c r="H1119" s="5" t="s">
-        <v>4501</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="1120">
       <c r="B1120" s="6" t="s">
-        <v>7135</v>
+        <v>7140</v>
       </c>
       <c r="C1120" s="6" t="s">
-        <v>4486</v>
+        <v>4500</v>
       </c>
       <c r="D1120" s="6" t="s">
-        <v>4487</v>
+        <v>4501</v>
       </c>
       <c r="E1120" s="6" t="s">
-        <v>4488</v>
+        <v>4502</v>
       </c>
       <c r="F1120" s="6" t="s">
-        <v>4489</v>
+        <v>4503</v>
       </c>
       <c r="G1120" s="6" t="s">
-        <v>4490</v>
+        <v>4504</v>
       </c>
       <c r="H1120" s="6" t="s">
-        <v>4491</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="1121">
       <c r="B1121" s="5" t="s">
-        <v>7136</v>
+        <v>7141</v>
       </c>
       <c r="C1121" s="5" t="s">
-        <v>4480</v>
+        <v>4486</v>
       </c>
       <c r="D1121" s="5" t="s">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E1121" s="5" t="s">
-        <v>4482</v>
+        <v>4488</v>
       </c>
       <c r="F1121" s="5" t="s">
-        <v>4483</v>
+        <v>4489</v>
       </c>
       <c r="G1121" s="5" t="s">
-        <v>4483</v>
+        <v>4490</v>
       </c>
       <c r="H1121" s="5" t="s">
-        <v>4484</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="1122">
       <c r="B1122" s="6" t="s">
-        <v>7137</v>
+        <v>7142</v>
       </c>
       <c r="C1122" s="6" t="s">
-        <v>4493</v>
+        <v>4480</v>
       </c>
       <c r="D1122" s="6" t="s">
-        <v>4494</v>
+        <v>4481</v>
       </c>
       <c r="E1122" s="6" t="s">
-        <v>4495</v>
+        <v>4482</v>
       </c>
       <c r="F1122" s="6" t="s">
-        <v>4496</v>
+        <v>4483</v>
       </c>
       <c r="G1122" s="6" t="s">
-        <v>4497</v>
+        <v>4483</v>
       </c>
       <c r="H1122" s="6" t="s">
-        <v>4498</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="1123">
       <c r="B1123" s="5" t="s">
-        <v>7138</v>
+        <v>7143</v>
       </c>
       <c r="C1123" s="5" t="s">
-        <v>4474</v>
+        <v>4493</v>
       </c>
       <c r="D1123" s="5" t="s">
-        <v>4475</v>
+        <v>4494</v>
       </c>
       <c r="E1123" s="5" t="s">
-        <v>4476</v>
+        <v>4495</v>
       </c>
       <c r="F1123" s="5" t="s">
-        <v>4477</v>
+        <v>4496</v>
       </c>
       <c r="G1123" s="5" t="s">
-        <v>4478</v>
+        <v>4497</v>
       </c>
       <c r="H1123" s="5" t="s">
-        <v>4475</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="1124">
       <c r="B1124" s="6" t="s">
-        <v>7139</v>
+        <v>7144</v>
       </c>
       <c r="C1124" s="6" t="s">
-        <v>4506</v>
+        <v>4474</v>
       </c>
       <c r="D1124" s="6" t="s">
-        <v>4507</v>
+        <v>4475</v>
       </c>
       <c r="E1124" s="6" t="s">
-        <v>4508</v>
+        <v>4476</v>
       </c>
       <c r="F1124" s="6" t="s">
-        <v>4509</v>
+        <v>4477</v>
       </c>
       <c r="G1124" s="6" t="s">
-        <v>4510</v>
+        <v>4478</v>
       </c>
       <c r="H1124" s="6" t="s">
-        <v>4511</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="1125">
       <c r="B1125" s="5" t="s">
-        <v>7140</v>
+        <v>7145</v>
       </c>
       <c r="C1125" s="5" t="s">
-        <v>7141</v>
+        <v>4506</v>
       </c>
       <c r="D1125" s="5" t="s">
-        <v>4470</v>
+        <v>4507</v>
       </c>
       <c r="E1125" s="5" t="s">
-        <v>4471</v>
+        <v>4508</v>
       </c>
       <c r="F1125" s="5" t="s">
-        <v>4472</v>
+        <v>4509</v>
       </c>
       <c r="G1125" s="5" t="s">
-        <v>4472</v>
+        <v>4510</v>
       </c>
       <c r="H1125" s="5" t="s">
-        <v>4470</v>
+        <v>4511</v>
       </c>
     </row>
     <row r="1126">
       <c r="B1126" s="6" t="s">
-        <v>7142</v>
+        <v>7146</v>
       </c>
       <c r="C1126" s="6" t="s">
-        <v>7143</v>
+        <v>7147</v>
       </c>
       <c r="D1126" s="6" t="s">
-        <v>7144</v>
+        <v>4470</v>
       </c>
       <c r="E1126" s="6" t="s">
-        <v>7145</v>
+        <v>4471</v>
       </c>
       <c r="F1126" s="6" t="s">
-        <v>7146</v>
+        <v>4472</v>
       </c>
       <c r="G1126" s="6" t="s">
-        <v>7147</v>
+        <v>4472</v>
       </c>
       <c r="H1126" s="6" t="s">
-        <v>7144</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="1127">
@@ -53085,70 +53103,70 @@
         <v>7153</v>
       </c>
       <c r="H1127" s="5" t="s">
-        <v>7154</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="1128">
       <c r="B1128" s="6" t="s">
+        <v>7154</v>
+      </c>
+      <c r="C1128" s="6" t="s">
         <v>7155</v>
       </c>
-      <c r="C1128" s="6" t="s">
+      <c r="D1128" s="6" t="s">
         <v>7156</v>
       </c>
-      <c r="D1128" s="6" t="s">
+      <c r="E1128" s="6" t="s">
         <v>7157</v>
       </c>
-      <c r="E1128" s="6" t="s">
+      <c r="F1128" s="6" t="s">
         <v>7158</v>
       </c>
-      <c r="F1128" s="6" t="s">
+      <c r="G1128" s="6" t="s">
         <v>7159</v>
       </c>
-      <c r="G1128" s="6" t="s">
+      <c r="H1128" s="6" t="s">
         <v>7160</v>
-      </c>
-      <c r="H1128" s="6" t="s">
-        <v>7161</v>
       </c>
     </row>
     <row r="1129">
       <c r="B1129" s="5" t="s">
+        <v>7161</v>
+      </c>
+      <c r="C1129" s="5" t="s">
         <v>7162</v>
       </c>
-      <c r="C1129" s="5" t="s">
+      <c r="D1129" s="5" t="s">
         <v>7163</v>
       </c>
-      <c r="D1129" s="5" t="s">
+      <c r="E1129" s="5" t="s">
         <v>7164</v>
       </c>
-      <c r="E1129" s="5" t="s">
+      <c r="F1129" s="5" t="s">
         <v>7165</v>
       </c>
-      <c r="F1129" s="5" t="s">
+      <c r="G1129" s="5" t="s">
         <v>7166</v>
       </c>
-      <c r="G1129" s="5" t="s">
+      <c r="H1129" s="5" t="s">
         <v>7167</v>
-      </c>
-      <c r="H1129" s="5" t="s">
-        <v>7168</v>
       </c>
     </row>
     <row r="1130">
       <c r="B1130" s="6" t="s">
+        <v>7168</v>
+      </c>
+      <c r="C1130" s="6" t="s">
         <v>7169</v>
       </c>
-      <c r="C1130" s="6" t="s">
+      <c r="D1130" s="6" t="s">
         <v>7170</v>
       </c>
-      <c r="D1130" s="6" t="s">
+      <c r="E1130" s="6" t="s">
         <v>7171</v>
       </c>
-      <c r="E1130" s="6" t="s">
+      <c r="F1130" s="6" t="s">
         <v>7172</v>
-      </c>
-      <c r="F1130" s="6" t="s">
-        <v>7173</v>
       </c>
       <c r="G1130" s="6" t="s">
         <v>7173</v>
@@ -53174,142 +53192,142 @@
         <v>7179</v>
       </c>
       <c r="G1131" s="5" t="s">
+        <v>7179</v>
+      </c>
+      <c r="H1131" s="5" t="s">
         <v>7180</v>
-      </c>
-      <c r="H1131" s="5" t="s">
-        <v>7181</v>
       </c>
     </row>
     <row r="1132">
       <c r="B1132" s="6" t="s">
+        <v>7181</v>
+      </c>
+      <c r="C1132" s="6" t="s">
         <v>7182</v>
       </c>
-      <c r="C1132" s="6" t="s">
+      <c r="D1132" s="6" t="s">
         <v>7183</v>
       </c>
-      <c r="D1132" s="6" t="s">
+      <c r="E1132" s="6" t="s">
         <v>7184</v>
       </c>
-      <c r="E1132" s="6" t="s">
+      <c r="F1132" s="6" t="s">
         <v>7185</v>
       </c>
-      <c r="F1132" s="6" t="s">
+      <c r="G1132" s="6" t="s">
         <v>7186</v>
       </c>
-      <c r="G1132" s="6" t="s">
+      <c r="H1132" s="6" t="s">
         <v>7187</v>
-      </c>
-      <c r="H1132" s="6" t="s">
-        <v>7188</v>
       </c>
     </row>
     <row r="1133">
       <c r="B1133" s="5" t="s">
+        <v>7188</v>
+      </c>
+      <c r="C1133" s="5" t="s">
         <v>7189</v>
       </c>
-      <c r="C1133" s="5" t="s">
+      <c r="D1133" s="5" t="s">
         <v>7190</v>
       </c>
-      <c r="D1133" s="5" t="s">
+      <c r="E1133" s="5" t="s">
         <v>7191</v>
-      </c>
-      <c r="E1133" s="5" t="s">
-        <v>7192</v>
       </c>
       <c r="F1133" s="5" t="s">
         <v>7192</v>
       </c>
       <c r="G1133" s="5" t="s">
-        <v>7192</v>
+        <v>7193</v>
       </c>
       <c r="H1133" s="5" t="s">
-        <v>7193</v>
+        <v>7194</v>
       </c>
     </row>
     <row r="1134">
       <c r="B1134" s="6" t="s">
-        <v>7194</v>
+        <v>7195</v>
       </c>
       <c r="C1134" s="6" t="s">
-        <v>7195</v>
+        <v>7196</v>
       </c>
       <c r="D1134" s="6" t="s">
-        <v>7196</v>
+        <v>7197</v>
       </c>
       <c r="E1134" s="6" t="s">
-        <v>7197</v>
+        <v>7198</v>
       </c>
       <c r="F1134" s="6" t="s">
         <v>7198</v>
       </c>
       <c r="G1134" s="6" t="s">
+        <v>7198</v>
+      </c>
+      <c r="H1134" s="6" t="s">
         <v>7199</v>
-      </c>
-      <c r="H1134" s="6" t="s">
-        <v>7200</v>
       </c>
     </row>
     <row r="1135">
       <c r="B1135" s="5" t="s">
+        <v>7200</v>
+      </c>
+      <c r="C1135" s="5" t="s">
         <v>7201</v>
       </c>
-      <c r="C1135" s="5" t="s">
+      <c r="D1135" s="5" t="s">
         <v>7202</v>
       </c>
-      <c r="D1135" s="5" t="s">
+      <c r="E1135" s="5" t="s">
         <v>7203</v>
       </c>
-      <c r="E1135" s="5" t="s">
+      <c r="F1135" s="5" t="s">
         <v>7204</v>
       </c>
-      <c r="F1135" s="5" t="s">
+      <c r="G1135" s="5" t="s">
         <v>7205</v>
       </c>
-      <c r="G1135" s="5" t="s">
+      <c r="H1135" s="5" t="s">
         <v>7206</v>
-      </c>
-      <c r="H1135" s="5" t="s">
-        <v>7207</v>
       </c>
     </row>
     <row r="1136">
       <c r="B1136" s="6" t="s">
+        <v>7207</v>
+      </c>
+      <c r="C1136" s="6" t="s">
         <v>7208</v>
       </c>
-      <c r="C1136" s="6" t="s">
+      <c r="D1136" s="6" t="s">
         <v>7209</v>
       </c>
-      <c r="D1136" s="6" t="s">
+      <c r="E1136" s="6" t="s">
         <v>7210</v>
       </c>
-      <c r="E1136" s="6" t="s">
+      <c r="F1136" s="6" t="s">
         <v>7211</v>
       </c>
-      <c r="F1136" s="6" t="s">
+      <c r="G1136" s="6" t="s">
         <v>7212</v>
       </c>
-      <c r="G1136" s="6" t="s">
+      <c r="H1136" s="6" t="s">
         <v>7213</v>
-      </c>
-      <c r="H1136" s="6" t="s">
-        <v>7214</v>
       </c>
     </row>
     <row r="1137">
       <c r="B1137" s="5" t="s">
+        <v>7214</v>
+      </c>
+      <c r="C1137" s="5" t="s">
         <v>7215</v>
       </c>
-      <c r="C1137" s="5" t="s">
+      <c r="D1137" s="5" t="s">
         <v>7216</v>
       </c>
-      <c r="D1137" s="5" t="s">
+      <c r="E1137" s="5" t="s">
         <v>7217</v>
       </c>
-      <c r="E1137" s="5" t="s">
+      <c r="F1137" s="5" t="s">
         <v>7218</v>
-      </c>
-      <c r="F1137" s="5" t="s">
-        <v>7219</v>
       </c>
       <c r="G1137" s="5" t="s">
         <v>7219</v>
@@ -53358,27 +53376,27 @@
         <v>7231</v>
       </c>
       <c r="G1139" s="5" t="s">
+        <v>7231</v>
+      </c>
+      <c r="H1139" s="5" t="s">
         <v>7232</v>
-      </c>
-      <c r="H1139" s="5" t="s">
-        <v>7233</v>
       </c>
     </row>
     <row r="1140">
       <c r="B1140" s="6" t="s">
+        <v>7233</v>
+      </c>
+      <c r="C1140" s="6" t="s">
         <v>7234</v>
       </c>
-      <c r="C1140" s="6" t="s">
+      <c r="D1140" s="6" t="s">
         <v>7235</v>
       </c>
-      <c r="D1140" s="6" t="s">
+      <c r="E1140" s="6" t="s">
         <v>7236</v>
       </c>
-      <c r="E1140" s="6" t="s">
+      <c r="F1140" s="6" t="s">
         <v>7237</v>
-      </c>
-      <c r="F1140" s="6" t="s">
-        <v>7238</v>
       </c>
       <c r="G1140" s="6" t="s">
         <v>7238</v>
@@ -53404,234 +53422,234 @@
         <v>7244</v>
       </c>
       <c r="G1141" s="5" t="s">
+        <v>7244</v>
+      </c>
+      <c r="H1141" s="5" t="s">
         <v>7245</v>
-      </c>
-      <c r="H1141" s="5" t="s">
-        <v>7246</v>
       </c>
     </row>
     <row r="1142">
       <c r="B1142" s="6" t="s">
+        <v>7246</v>
+      </c>
+      <c r="C1142" s="6" t="s">
         <v>7247</v>
       </c>
-      <c r="C1142" s="6" t="s">
+      <c r="D1142" s="6" t="s">
         <v>7248</v>
       </c>
-      <c r="D1142" s="6" t="s">
+      <c r="E1142" s="6" t="s">
         <v>7249</v>
       </c>
-      <c r="E1142" s="6" t="s">
+      <c r="F1142" s="6" t="s">
         <v>7250</v>
       </c>
-      <c r="F1142" s="6" t="s">
+      <c r="G1142" s="6" t="s">
         <v>7251</v>
       </c>
-      <c r="G1142" s="6" t="s">
+      <c r="H1142" s="6" t="s">
         <v>7252</v>
-      </c>
-      <c r="H1142" s="6" t="s">
-        <v>7253</v>
       </c>
     </row>
     <row r="1143">
       <c r="B1143" s="5" t="s">
+        <v>7253</v>
+      </c>
+      <c r="C1143" s="5" t="s">
         <v>7254</v>
       </c>
-      <c r="C1143" s="5" t="s">
+      <c r="D1143" s="5" t="s">
         <v>7255</v>
       </c>
-      <c r="D1143" s="5" t="s">
+      <c r="E1143" s="5" t="s">
         <v>7256</v>
       </c>
-      <c r="E1143" s="5" t="s">
+      <c r="F1143" s="5" t="s">
         <v>7257</v>
       </c>
-      <c r="F1143" s="5" t="s">
+      <c r="G1143" s="5" t="s">
         <v>7258</v>
       </c>
-      <c r="G1143" s="5" t="s">
+      <c r="H1143" s="5" t="s">
         <v>7259</v>
-      </c>
-      <c r="H1143" s="5" t="s">
-        <v>7260</v>
       </c>
     </row>
     <row r="1144">
       <c r="B1144" s="6" t="s">
+        <v>7260</v>
+      </c>
+      <c r="C1144" s="6" t="s">
         <v>7261</v>
       </c>
-      <c r="C1144" s="6" t="s">
+      <c r="D1144" s="6" t="s">
         <v>7262</v>
       </c>
-      <c r="D1144" s="6" t="s">
+      <c r="E1144" s="6" t="s">
         <v>7263</v>
       </c>
-      <c r="E1144" s="6" t="s">
+      <c r="F1144" s="6" t="s">
         <v>7264</v>
       </c>
-      <c r="F1144" s="6" t="s">
+      <c r="G1144" s="6" t="s">
         <v>7265</v>
       </c>
-      <c r="G1144" s="6" t="s">
+      <c r="H1144" s="6" t="s">
         <v>7266</v>
-      </c>
-      <c r="H1144" s="6" t="s">
-        <v>7267</v>
       </c>
     </row>
     <row r="1145">
       <c r="B1145" s="5" t="s">
+        <v>7267</v>
+      </c>
+      <c r="C1145" s="5" t="s">
         <v>7268</v>
       </c>
-      <c r="C1145" s="5" t="s">
+      <c r="D1145" s="5" t="s">
         <v>7269</v>
       </c>
-      <c r="D1145" s="5" t="s">
+      <c r="E1145" s="5" t="s">
         <v>7270</v>
       </c>
-      <c r="E1145" s="5" t="s">
+      <c r="F1145" s="5" t="s">
         <v>7271</v>
       </c>
-      <c r="F1145" s="5" t="s">
+      <c r="G1145" s="5" t="s">
         <v>7272</v>
       </c>
-      <c r="G1145" s="5" t="s">
+      <c r="H1145" s="5" t="s">
         <v>7273</v>
-      </c>
-      <c r="H1145" s="5" t="s">
-        <v>7274</v>
       </c>
     </row>
     <row r="1146">
       <c r="B1146" s="6" t="s">
+        <v>7274</v>
+      </c>
+      <c r="C1146" s="6" t="s">
         <v>7275</v>
       </c>
-      <c r="C1146" s="6" t="s">
+      <c r="D1146" s="6" t="s">
         <v>7276</v>
       </c>
-      <c r="D1146" s="6" t="s">
+      <c r="E1146" s="6" t="s">
         <v>7277</v>
       </c>
-      <c r="E1146" s="6" t="s">
+      <c r="F1146" s="6" t="s">
         <v>7278</v>
       </c>
-      <c r="F1146" s="6" t="s">
+      <c r="G1146" s="6" t="s">
         <v>7279</v>
       </c>
-      <c r="G1146" s="6" t="s">
+      <c r="H1146" s="6" t="s">
         <v>7280</v>
-      </c>
-      <c r="H1146" s="6" t="s">
-        <v>7281</v>
       </c>
     </row>
     <row r="1147">
       <c r="B1147" s="5" t="s">
+        <v>7281</v>
+      </c>
+      <c r="C1147" s="5" t="s">
         <v>7282</v>
       </c>
-      <c r="C1147" s="5" t="s">
+      <c r="D1147" s="5" t="s">
         <v>7283</v>
       </c>
-      <c r="D1147" s="5" t="s">
+      <c r="E1147" s="5" t="s">
         <v>7284</v>
       </c>
-      <c r="E1147" s="5" t="s">
+      <c r="F1147" s="5" t="s">
         <v>7285</v>
       </c>
-      <c r="F1147" s="5" t="s">
+      <c r="G1147" s="5" t="s">
         <v>7286</v>
       </c>
-      <c r="G1147" s="5" t="s">
+      <c r="H1147" s="5" t="s">
         <v>7287</v>
-      </c>
-      <c r="H1147" s="5" t="s">
-        <v>7288</v>
       </c>
     </row>
     <row r="1148">
       <c r="B1148" s="6" t="s">
+        <v>7288</v>
+      </c>
+      <c r="C1148" s="6" t="s">
         <v>7289</v>
       </c>
-      <c r="C1148" s="6" t="s">
+      <c r="D1148" s="6" t="s">
         <v>7290</v>
       </c>
-      <c r="D1148" s="6" t="s">
+      <c r="E1148" s="6" t="s">
         <v>7291</v>
       </c>
-      <c r="E1148" s="6" t="s">
+      <c r="F1148" s="6" t="s">
         <v>7292</v>
       </c>
-      <c r="F1148" s="6" t="s">
+      <c r="G1148" s="6" t="s">
         <v>7293</v>
       </c>
-      <c r="G1148" s="6" t="s">
+      <c r="H1148" s="6" t="s">
         <v>7294</v>
-      </c>
-      <c r="H1148" s="6" t="s">
-        <v>7295</v>
       </c>
     </row>
     <row r="1149">
       <c r="B1149" s="5" t="s">
+        <v>7295</v>
+      </c>
+      <c r="C1149" s="5" t="s">
         <v>7296</v>
       </c>
-      <c r="C1149" s="5" t="s">
+      <c r="D1149" s="5" t="s">
         <v>7297</v>
       </c>
-      <c r="D1149" s="5" t="s">
+      <c r="E1149" s="5" t="s">
         <v>7298</v>
       </c>
-      <c r="E1149" s="5" t="s">
+      <c r="F1149" s="5" t="s">
         <v>7299</v>
       </c>
-      <c r="F1149" s="5" t="s">
+      <c r="G1149" s="5" t="s">
         <v>7300</v>
       </c>
-      <c r="G1149" s="5" t="s">
+      <c r="H1149" s="5" t="s">
         <v>7301</v>
-      </c>
-      <c r="H1149" s="5" t="s">
-        <v>7302</v>
       </c>
     </row>
     <row r="1150">
       <c r="B1150" s="6" t="s">
+        <v>7302</v>
+      </c>
+      <c r="C1150" s="6" t="s">
         <v>7303</v>
       </c>
-      <c r="C1150" s="6" t="s">
+      <c r="D1150" s="6" t="s">
         <v>7304</v>
       </c>
-      <c r="D1150" s="6" t="s">
+      <c r="E1150" s="6" t="s">
         <v>7305</v>
       </c>
-      <c r="E1150" s="6" t="s">
+      <c r="F1150" s="6" t="s">
         <v>7306</v>
       </c>
-      <c r="F1150" s="6" t="s">
+      <c r="G1150" s="6" t="s">
         <v>7307</v>
       </c>
-      <c r="G1150" s="6" t="s">
+      <c r="H1150" s="6" t="s">
         <v>7308</v>
-      </c>
-      <c r="H1150" s="6" t="s">
-        <v>7309</v>
       </c>
     </row>
     <row r="1151">
       <c r="B1151" s="5" t="s">
+        <v>7309</v>
+      </c>
+      <c r="C1151" s="5" t="s">
         <v>7310</v>
       </c>
-      <c r="C1151" s="5" t="s">
+      <c r="D1151" s="5" t="s">
         <v>7311</v>
       </c>
-      <c r="D1151" s="5" t="s">
+      <c r="E1151" s="5" t="s">
         <v>7312</v>
       </c>
-      <c r="E1151" s="5" t="s">
+      <c r="F1151" s="5" t="s">
         <v>7313</v>
-      </c>
-      <c r="F1151" s="5" t="s">
-        <v>7314</v>
       </c>
       <c r="G1151" s="5" t="s">
         <v>7314</v>
@@ -53657,372 +53675,372 @@
         <v>7320</v>
       </c>
       <c r="G1152" s="6" t="s">
+        <v>7320</v>
+      </c>
+      <c r="H1152" s="6" t="s">
         <v>7321</v>
-      </c>
-      <c r="H1152" s="6" t="s">
-        <v>7322</v>
       </c>
     </row>
     <row r="1153">
       <c r="B1153" s="5" t="s">
+        <v>7322</v>
+      </c>
+      <c r="C1153" s="5" t="s">
         <v>7323</v>
       </c>
-      <c r="C1153" s="5" t="s">
+      <c r="D1153" s="5" t="s">
         <v>7324</v>
       </c>
-      <c r="D1153" s="5" t="s">
+      <c r="E1153" s="5" t="s">
         <v>7325</v>
       </c>
-      <c r="E1153" s="5" t="s">
+      <c r="F1153" s="5" t="s">
         <v>7326</v>
       </c>
-      <c r="F1153" s="5" t="s">
+      <c r="G1153" s="5" t="s">
         <v>7327</v>
       </c>
-      <c r="G1153" s="5" t="s">
+      <c r="H1153" s="5" t="s">
         <v>7328</v>
-      </c>
-      <c r="H1153" s="5" t="s">
-        <v>7329</v>
       </c>
     </row>
     <row r="1154">
       <c r="B1154" s="6" t="s">
+        <v>7329</v>
+      </c>
+      <c r="C1154" s="6" t="s">
         <v>7330</v>
       </c>
-      <c r="C1154" s="6" t="s">
+      <c r="D1154" s="6" t="s">
         <v>7331</v>
       </c>
-      <c r="D1154" s="6" t="s">
+      <c r="E1154" s="6" t="s">
         <v>7332</v>
       </c>
-      <c r="E1154" s="6" t="s">
+      <c r="F1154" s="6" t="s">
         <v>7333</v>
       </c>
-      <c r="F1154" s="6" t="s">
+      <c r="G1154" s="6" t="s">
         <v>7334</v>
       </c>
-      <c r="G1154" s="6" t="s">
+      <c r="H1154" s="6" t="s">
         <v>7335</v>
-      </c>
-      <c r="H1154" s="6" t="s">
-        <v>7336</v>
       </c>
     </row>
     <row r="1155">
       <c r="B1155" s="5" t="s">
+        <v>7336</v>
+      </c>
+      <c r="C1155" s="5" t="s">
         <v>7337</v>
       </c>
-      <c r="C1155" s="5" t="s">
+      <c r="D1155" s="5" t="s">
         <v>7338</v>
       </c>
-      <c r="D1155" s="5" t="s">
+      <c r="E1155" s="5" t="s">
         <v>7339</v>
       </c>
-      <c r="E1155" s="5" t="s">
+      <c r="F1155" s="5" t="s">
         <v>7340</v>
       </c>
-      <c r="F1155" s="5" t="s">
+      <c r="G1155" s="5" t="s">
         <v>7341</v>
       </c>
-      <c r="G1155" s="5" t="s">
+      <c r="H1155" s="5" t="s">
         <v>7342</v>
-      </c>
-      <c r="H1155" s="5" t="s">
-        <v>7343</v>
       </c>
     </row>
     <row r="1156">
       <c r="B1156" s="6" t="s">
+        <v>7343</v>
+      </c>
+      <c r="C1156" s="6" t="s">
         <v>7344</v>
       </c>
-      <c r="C1156" s="6" t="s">
+      <c r="D1156" s="6" t="s">
         <v>7345</v>
       </c>
-      <c r="D1156" s="6" t="s">
+      <c r="E1156" s="6" t="s">
         <v>7346</v>
       </c>
-      <c r="E1156" s="6" t="s">
+      <c r="F1156" s="6" t="s">
         <v>7347</v>
       </c>
-      <c r="F1156" s="6" t="s">
+      <c r="G1156" s="6" t="s">
         <v>7348</v>
       </c>
-      <c r="G1156" s="6" t="s">
+      <c r="H1156" s="6" t="s">
         <v>7349</v>
-      </c>
-      <c r="H1156" s="6" t="s">
-        <v>7350</v>
       </c>
     </row>
     <row r="1157">
       <c r="B1157" s="5" t="s">
+        <v>7350</v>
+      </c>
+      <c r="C1157" s="5" t="s">
         <v>7351</v>
       </c>
-      <c r="C1157" s="5" t="s">
+      <c r="D1157" s="5" t="s">
         <v>7352</v>
       </c>
-      <c r="D1157" s="5" t="s">
+      <c r="E1157" s="5" t="s">
         <v>7353</v>
       </c>
-      <c r="E1157" s="5" t="s">
+      <c r="F1157" s="5" t="s">
         <v>7354</v>
       </c>
-      <c r="F1157" s="5" t="s">
+      <c r="G1157" s="5" t="s">
         <v>7355</v>
       </c>
-      <c r="G1157" s="5" t="s">
+      <c r="H1157" s="5" t="s">
         <v>7356</v>
-      </c>
-      <c r="H1157" s="5" t="s">
-        <v>7357</v>
       </c>
     </row>
     <row r="1158">
       <c r="B1158" s="6" t="s">
+        <v>7357</v>
+      </c>
+      <c r="C1158" s="6" t="s">
         <v>7358</v>
       </c>
-      <c r="C1158" s="6" t="s">
+      <c r="D1158" s="6" t="s">
         <v>7359</v>
       </c>
-      <c r="D1158" s="6" t="s">
+      <c r="E1158" s="6" t="s">
         <v>7360</v>
       </c>
-      <c r="E1158" s="6" t="s">
+      <c r="F1158" s="6" t="s">
         <v>7361</v>
       </c>
-      <c r="F1158" s="6" t="s">
+      <c r="G1158" s="6" t="s">
         <v>7362</v>
       </c>
-      <c r="G1158" s="6" t="s">
+      <c r="H1158" s="6" t="s">
         <v>7363</v>
-      </c>
-      <c r="H1158" s="6" t="s">
-        <v>7364</v>
       </c>
     </row>
     <row r="1159">
       <c r="B1159" s="5" t="s">
+        <v>7364</v>
+      </c>
+      <c r="C1159" s="5" t="s">
         <v>7365</v>
       </c>
-      <c r="C1159" s="5" t="s">
+      <c r="D1159" s="5" t="s">
         <v>7366</v>
       </c>
-      <c r="D1159" s="5" t="s">
+      <c r="E1159" s="5" t="s">
         <v>7367</v>
       </c>
-      <c r="E1159" s="5" t="s">
+      <c r="F1159" s="5" t="s">
         <v>7368</v>
       </c>
-      <c r="F1159" s="5" t="s">
+      <c r="G1159" s="5" t="s">
         <v>7369</v>
       </c>
-      <c r="G1159" s="5" t="s">
+      <c r="H1159" s="5" t="s">
         <v>7370</v>
-      </c>
-      <c r="H1159" s="5" t="s">
-        <v>7371</v>
       </c>
     </row>
     <row r="1160">
       <c r="B1160" s="6" t="s">
+        <v>7371</v>
+      </c>
+      <c r="C1160" s="6" t="s">
         <v>7372</v>
       </c>
-      <c r="C1160" s="6" t="s">
+      <c r="D1160" s="6" t="s">
         <v>7373</v>
       </c>
-      <c r="D1160" s="6" t="s">
+      <c r="E1160" s="6" t="s">
         <v>7374</v>
       </c>
-      <c r="E1160" s="6" t="s">
+      <c r="F1160" s="6" t="s">
         <v>7375</v>
       </c>
-      <c r="F1160" s="6" t="s">
+      <c r="G1160" s="6" t="s">
         <v>7376</v>
       </c>
-      <c r="G1160" s="6" t="s">
+      <c r="H1160" s="6" t="s">
         <v>7377</v>
-      </c>
-      <c r="H1160" s="6" t="s">
-        <v>7378</v>
       </c>
     </row>
     <row r="1161">
       <c r="B1161" s="5" t="s">
+        <v>7378</v>
+      </c>
+      <c r="C1161" s="5" t="s">
         <v>7379</v>
       </c>
-      <c r="C1161" s="5" t="s">
+      <c r="D1161" s="5" t="s">
         <v>7380</v>
       </c>
-      <c r="D1161" s="5" t="s">
+      <c r="E1161" s="5" t="s">
         <v>7381</v>
       </c>
-      <c r="E1161" s="5" t="s">
+      <c r="F1161" s="5" t="s">
         <v>7382</v>
       </c>
-      <c r="F1161" s="5" t="s">
+      <c r="G1161" s="5" t="s">
         <v>7383</v>
       </c>
-      <c r="G1161" s="5" t="s">
+      <c r="H1161" s="5" t="s">
         <v>7384</v>
-      </c>
-      <c r="H1161" s="5" t="s">
-        <v>7385</v>
       </c>
     </row>
     <row r="1162">
       <c r="B1162" s="6" t="s">
+        <v>7385</v>
+      </c>
+      <c r="C1162" s="6" t="s">
         <v>7386</v>
       </c>
-      <c r="C1162" s="6" t="s">
+      <c r="D1162" s="6" t="s">
         <v>7387</v>
       </c>
-      <c r="D1162" s="6" t="s">
+      <c r="E1162" s="6" t="s">
         <v>7388</v>
       </c>
-      <c r="E1162" s="6" t="s">
+      <c r="F1162" s="6" t="s">
         <v>7389</v>
       </c>
-      <c r="F1162" s="6" t="s">
+      <c r="G1162" s="6" t="s">
         <v>7390</v>
       </c>
-      <c r="G1162" s="6" t="s">
+      <c r="H1162" s="6" t="s">
         <v>7391</v>
-      </c>
-      <c r="H1162" s="6" t="s">
-        <v>7392</v>
       </c>
     </row>
     <row r="1163">
       <c r="B1163" s="5" t="s">
+        <v>7392</v>
+      </c>
+      <c r="C1163" s="5" t="s">
         <v>7393</v>
       </c>
-      <c r="C1163" s="5" t="s">
+      <c r="D1163" s="5" t="s">
         <v>7394</v>
       </c>
-      <c r="D1163" s="5" t="s">
+      <c r="E1163" s="5" t="s">
         <v>7395</v>
       </c>
-      <c r="E1163" s="5" t="s">
+      <c r="F1163" s="5" t="s">
         <v>7396</v>
       </c>
-      <c r="F1163" s="5" t="s">
+      <c r="G1163" s="5" t="s">
         <v>7397</v>
       </c>
-      <c r="G1163" s="5" t="s">
+      <c r="H1163" s="5" t="s">
         <v>7398</v>
-      </c>
-      <c r="H1163" s="5" t="s">
-        <v>7399</v>
       </c>
     </row>
     <row r="1164">
       <c r="B1164" s="6" t="s">
+        <v>7399</v>
+      </c>
+      <c r="C1164" s="6" t="s">
         <v>7400</v>
       </c>
-      <c r="C1164" s="6" t="s">
+      <c r="D1164" s="6" t="s">
         <v>7401</v>
       </c>
-      <c r="D1164" s="6" t="s">
+      <c r="E1164" s="6" t="s">
         <v>7402</v>
       </c>
-      <c r="E1164" s="6" t="s">
+      <c r="F1164" s="6" t="s">
         <v>7403</v>
       </c>
-      <c r="F1164" s="6" t="s">
+      <c r="G1164" s="6" t="s">
         <v>7404</v>
       </c>
-      <c r="G1164" s="6" t="s">
+      <c r="H1164" s="6" t="s">
         <v>7405</v>
-      </c>
-      <c r="H1164" s="6" t="s">
-        <v>7406</v>
       </c>
     </row>
     <row r="1165">
       <c r="B1165" s="5" t="s">
+        <v>7406</v>
+      </c>
+      <c r="C1165" s="5" t="s">
         <v>7407</v>
       </c>
-      <c r="C1165" s="5" t="s">
+      <c r="D1165" s="5" t="s">
         <v>7408</v>
       </c>
-      <c r="D1165" s="5" t="s">
+      <c r="E1165" s="5" t="s">
         <v>7409</v>
       </c>
-      <c r="E1165" s="5" t="s">
+      <c r="F1165" s="5" t="s">
         <v>7410</v>
       </c>
-      <c r="F1165" s="5" t="s">
+      <c r="G1165" s="5" t="s">
         <v>7411</v>
       </c>
-      <c r="G1165" s="5" t="s">
+      <c r="H1165" s="5" t="s">
         <v>7412</v>
-      </c>
-      <c r="H1165" s="5" t="s">
-        <v>7413</v>
       </c>
     </row>
     <row r="1166">
       <c r="B1166" s="6" t="s">
+        <v>7413</v>
+      </c>
+      <c r="C1166" s="6" t="s">
         <v>7414</v>
       </c>
-      <c r="C1166" s="6" t="s">
+      <c r="D1166" s="6" t="s">
         <v>7415</v>
       </c>
-      <c r="D1166" s="6" t="s">
+      <c r="E1166" s="6" t="s">
         <v>7416</v>
       </c>
-      <c r="E1166" s="6" t="s">
+      <c r="F1166" s="6" t="s">
         <v>7417</v>
       </c>
-      <c r="F1166" s="6" t="s">
+      <c r="G1166" s="6" t="s">
         <v>7418</v>
       </c>
-      <c r="G1166" s="6" t="s">
+      <c r="H1166" s="6" t="s">
         <v>7419</v>
-      </c>
-      <c r="H1166" s="6" t="s">
-        <v>7420</v>
       </c>
     </row>
     <row r="1167">
       <c r="B1167" s="5" t="s">
+        <v>7420</v>
+      </c>
+      <c r="C1167" s="5" t="s">
         <v>7421</v>
       </c>
-      <c r="C1167" s="5" t="s">
+      <c r="D1167" s="5" t="s">
         <v>7422</v>
       </c>
-      <c r="D1167" s="5" t="s">
+      <c r="E1167" s="5" t="s">
         <v>7423</v>
       </c>
-      <c r="E1167" s="5" t="s">
+      <c r="F1167" s="5" t="s">
         <v>7424</v>
       </c>
-      <c r="F1167" s="5" t="s">
+      <c r="G1167" s="5" t="s">
         <v>7425</v>
       </c>
-      <c r="G1167" s="5" t="s">
+      <c r="H1167" s="5" t="s">
         <v>7426</v>
-      </c>
-      <c r="H1167" s="5" t="s">
-        <v>7427</v>
       </c>
     </row>
     <row r="1168">
       <c r="B1168" s="6" t="s">
+        <v>7427</v>
+      </c>
+      <c r="C1168" s="6" t="s">
         <v>7428</v>
       </c>
-      <c r="C1168" s="6" t="s">
+      <c r="D1168" s="6" t="s">
         <v>7429</v>
       </c>
-      <c r="D1168" s="6" t="s">
+      <c r="E1168" s="6" t="s">
         <v>7430</v>
       </c>
-      <c r="E1168" s="6" t="s">
+      <c r="F1168" s="6" t="s">
         <v>7431</v>
-      </c>
-      <c r="F1168" s="6" t="s">
-        <v>7432</v>
       </c>
       <c r="G1168" s="6" t="s">
         <v>7432</v>
@@ -54048,50 +54066,50 @@
         <v>7438</v>
       </c>
       <c r="G1169" s="5" t="s">
+        <v>7438</v>
+      </c>
+      <c r="H1169" s="5" t="s">
         <v>7439</v>
-      </c>
-      <c r="H1169" s="5" t="s">
-        <v>7440</v>
       </c>
     </row>
     <row r="1170">
       <c r="B1170" s="6" t="s">
+        <v>7440</v>
+      </c>
+      <c r="C1170" s="6" t="s">
         <v>7441</v>
       </c>
-      <c r="C1170" s="6" t="s">
+      <c r="D1170" s="6" t="s">
         <v>7442</v>
       </c>
-      <c r="D1170" s="6" t="s">
+      <c r="E1170" s="6" t="s">
         <v>7443</v>
       </c>
-      <c r="E1170" s="6" t="s">
+      <c r="F1170" s="6" t="s">
         <v>7444</v>
       </c>
-      <c r="F1170" s="6" t="s">
+      <c r="G1170" s="6" t="s">
         <v>7445</v>
       </c>
-      <c r="G1170" s="6" t="s">
+      <c r="H1170" s="6" t="s">
         <v>7446</v>
-      </c>
-      <c r="H1170" s="6" t="s">
-        <v>7447</v>
       </c>
     </row>
     <row r="1171">
       <c r="B1171" s="5" t="s">
+        <v>7447</v>
+      </c>
+      <c r="C1171" s="5" t="s">
         <v>7448</v>
       </c>
-      <c r="C1171" s="5" t="s">
+      <c r="D1171" s="5" t="s">
         <v>7449</v>
       </c>
-      <c r="D1171" s="5" t="s">
+      <c r="E1171" s="5" t="s">
         <v>7450</v>
       </c>
-      <c r="E1171" s="5" t="s">
+      <c r="F1171" s="5" t="s">
         <v>7451</v>
-      </c>
-      <c r="F1171" s="5" t="s">
-        <v>7452</v>
       </c>
       <c r="G1171" s="5" t="s">
         <v>7452</v>
@@ -54117,73 +54135,73 @@
         <v>7458</v>
       </c>
       <c r="G1172" s="6" t="s">
+        <v>7458</v>
+      </c>
+      <c r="H1172" s="6" t="s">
         <v>7459</v>
-      </c>
-      <c r="H1172" s="6" t="s">
-        <v>7460</v>
       </c>
     </row>
     <row r="1173">
       <c r="B1173" s="5" t="s">
+        <v>7460</v>
+      </c>
+      <c r="C1173" s="5" t="s">
         <v>7461</v>
       </c>
-      <c r="C1173" s="5" t="s">
+      <c r="D1173" s="5" t="s">
         <v>7462</v>
       </c>
-      <c r="D1173" s="5" t="s">
+      <c r="E1173" s="5" t="s">
         <v>7463</v>
       </c>
-      <c r="E1173" s="5" t="s">
+      <c r="F1173" s="5" t="s">
         <v>7464</v>
       </c>
-      <c r="F1173" s="5" t="s">
+      <c r="G1173" s="5" t="s">
         <v>7465</v>
       </c>
-      <c r="G1173" s="5" t="s">
+      <c r="H1173" s="5" t="s">
         <v>7466</v>
-      </c>
-      <c r="H1173" s="5" t="s">
-        <v>7467</v>
       </c>
     </row>
     <row r="1174">
       <c r="B1174" s="6" t="s">
+        <v>7467</v>
+      </c>
+      <c r="C1174" s="6" t="s">
         <v>7468</v>
       </c>
-      <c r="C1174" s="6" t="s">
+      <c r="D1174" s="6" t="s">
         <v>7469</v>
       </c>
-      <c r="D1174" s="6" t="s">
+      <c r="E1174" s="6" t="s">
         <v>7470</v>
       </c>
-      <c r="E1174" s="6" t="s">
+      <c r="F1174" s="6" t="s">
         <v>7471</v>
       </c>
-      <c r="F1174" s="6" t="s">
+      <c r="G1174" s="6" t="s">
         <v>7472</v>
       </c>
-      <c r="G1174" s="6" t="s">
+      <c r="H1174" s="6" t="s">
         <v>7473</v>
-      </c>
-      <c r="H1174" s="6" t="s">
-        <v>7474</v>
       </c>
     </row>
     <row r="1175">
       <c r="B1175" s="5" t="s">
+        <v>7474</v>
+      </c>
+      <c r="C1175" s="5" t="s">
         <v>7475</v>
       </c>
-      <c r="C1175" s="5" t="s">
+      <c r="D1175" s="5" t="s">
         <v>7476</v>
       </c>
-      <c r="D1175" s="5" t="s">
+      <c r="E1175" s="5" t="s">
         <v>7477</v>
       </c>
-      <c r="E1175" s="5" t="s">
+      <c r="F1175" s="5" t="s">
         <v>7478</v>
-      </c>
-      <c r="F1175" s="5" t="s">
-        <v>7479</v>
       </c>
       <c r="G1175" s="5" t="s">
         <v>7479</v>
@@ -54209,171 +54227,171 @@
         <v>7485</v>
       </c>
       <c r="G1176" s="6" t="s">
+        <v>7485</v>
+      </c>
+      <c r="H1176" s="6" t="s">
         <v>7486</v>
-      </c>
-      <c r="H1176" s="6" t="s">
-        <v>7487</v>
       </c>
     </row>
     <row r="1177">
       <c r="B1177" s="5" t="s">
+        <v>7487</v>
+      </c>
+      <c r="C1177" s="5" t="s">
         <v>7488</v>
       </c>
-      <c r="C1177" s="5" t="s">
+      <c r="D1177" s="5" t="s">
         <v>7489</v>
       </c>
-      <c r="D1177" s="5" t="s">
+      <c r="E1177" s="5" t="s">
         <v>7490</v>
       </c>
-      <c r="E1177" s="5" t="s">
+      <c r="F1177" s="5" t="s">
         <v>7491</v>
       </c>
-      <c r="F1177" s="5" t="s">
+      <c r="G1177" s="5" t="s">
         <v>7492</v>
       </c>
-      <c r="G1177" s="5" t="s">
+      <c r="H1177" s="5" t="s">
         <v>7493</v>
-      </c>
-      <c r="H1177" s="5" t="s">
-        <v>7494</v>
       </c>
     </row>
     <row r="1178">
       <c r="B1178" s="6" t="s">
+        <v>7494</v>
+      </c>
+      <c r="C1178" s="6" t="s">
         <v>7495</v>
       </c>
-      <c r="C1178" s="6" t="s">
+      <c r="D1178" s="6" t="s">
         <v>7496</v>
       </c>
-      <c r="D1178" s="6" t="s">
+      <c r="E1178" s="6" t="s">
         <v>7497</v>
       </c>
-      <c r="E1178" s="6" t="s">
+      <c r="F1178" s="6" t="s">
         <v>7498</v>
       </c>
-      <c r="F1178" s="6" t="s">
+      <c r="G1178" s="6" t="s">
         <v>7499</v>
       </c>
-      <c r="G1178" s="6" t="s">
+      <c r="H1178" s="6" t="s">
         <v>7500</v>
-      </c>
-      <c r="H1178" s="6" t="s">
-        <v>7501</v>
       </c>
     </row>
     <row r="1179">
       <c r="B1179" s="5" t="s">
+        <v>7501</v>
+      </c>
+      <c r="C1179" s="5" t="s">
         <v>7502</v>
       </c>
-      <c r="C1179" s="5" t="s">
+      <c r="D1179" s="5" t="s">
         <v>7503</v>
       </c>
-      <c r="D1179" s="5" t="s">
+      <c r="E1179" s="5" t="s">
         <v>7504</v>
       </c>
-      <c r="E1179" s="5" t="s">
+      <c r="F1179" s="5" t="s">
         <v>7505</v>
       </c>
-      <c r="F1179" s="5" t="s">
+      <c r="G1179" s="5" t="s">
         <v>7506</v>
       </c>
-      <c r="G1179" s="5" t="s">
+      <c r="H1179" s="5" t="s">
         <v>7507</v>
-      </c>
-      <c r="H1179" s="5" t="s">
-        <v>7508</v>
       </c>
     </row>
     <row r="1180">
       <c r="B1180" s="6" t="s">
+        <v>7508</v>
+      </c>
+      <c r="C1180" s="6" t="s">
         <v>7509</v>
       </c>
-      <c r="C1180" s="6" t="s">
+      <c r="D1180" s="6" t="s">
         <v>7510</v>
       </c>
-      <c r="D1180" s="6" t="s">
+      <c r="E1180" s="6" t="s">
         <v>7511</v>
       </c>
-      <c r="E1180" s="6" t="s">
+      <c r="F1180" s="6" t="s">
         <v>7512</v>
       </c>
-      <c r="F1180" s="6" t="s">
+      <c r="G1180" s="6" t="s">
         <v>7513</v>
       </c>
-      <c r="G1180" s="6" t="s">
+      <c r="H1180" s="6" t="s">
         <v>7514</v>
-      </c>
-      <c r="H1180" s="6" t="s">
-        <v>7515</v>
       </c>
     </row>
     <row r="1181">
       <c r="B1181" s="5" t="s">
+        <v>7515</v>
+      </c>
+      <c r="C1181" s="5" t="s">
         <v>7516</v>
       </c>
-      <c r="C1181" s="5" t="s">
+      <c r="D1181" s="5" t="s">
         <v>7517</v>
       </c>
-      <c r="D1181" s="5" t="s">
+      <c r="E1181" s="5" t="s">
         <v>7518</v>
       </c>
-      <c r="E1181" s="5" t="s">
+      <c r="F1181" s="5" t="s">
         <v>7519</v>
       </c>
-      <c r="F1181" s="5" t="s">
+      <c r="G1181" s="5" t="s">
         <v>7520</v>
       </c>
-      <c r="G1181" s="5" t="s">
+      <c r="H1181" s="5" t="s">
         <v>7521</v>
-      </c>
-      <c r="H1181" s="5" t="s">
-        <v>7522</v>
       </c>
     </row>
     <row r="1182">
       <c r="B1182" s="6" t="s">
+        <v>7522</v>
+      </c>
+      <c r="C1182" s="6" t="s">
         <v>7523</v>
       </c>
-      <c r="C1182" s="6" t="s">
+      <c r="D1182" s="6" t="s">
         <v>7524</v>
       </c>
-      <c r="D1182" s="6" t="s">
+      <c r="E1182" s="6" t="s">
         <v>7525</v>
       </c>
-      <c r="E1182" s="6" t="s">
+      <c r="F1182" s="6" t="s">
         <v>7526</v>
       </c>
-      <c r="F1182" s="6" t="s">
+      <c r="G1182" s="6" t="s">
         <v>7527</v>
       </c>
-      <c r="G1182" s="6" t="s">
+      <c r="H1182" s="6" t="s">
         <v>7528</v>
-      </c>
-      <c r="H1182" s="6" t="s">
-        <v>7529</v>
       </c>
     </row>
     <row r="1183">
       <c r="B1183" s="5" t="s">
+        <v>7529</v>
+      </c>
+      <c r="C1183" s="5" t="s">
         <v>7530</v>
       </c>
-      <c r="C1183" s="5" t="s">
+      <c r="D1183" s="5" t="s">
         <v>7531</v>
       </c>
-      <c r="D1183" s="5" t="s">
+      <c r="E1183" s="5" t="s">
         <v>7532</v>
       </c>
-      <c r="E1183" s="5" t="s">
+      <c r="F1183" s="5" t="s">
         <v>7533</v>
       </c>
-      <c r="F1183" s="5" t="s">
+      <c r="G1183" s="5" t="s">
         <v>7534</v>
       </c>
-      <c r="G1183" s="5" t="s">
+      <c r="H1183" s="5" t="s">
         <v>7535</v>
-      </c>
-      <c r="H1183" s="5" t="s">
-        <v>7532</v>
       </c>
     </row>
     <row r="1184">
@@ -54396,208 +54414,208 @@
         <v>7541</v>
       </c>
       <c r="H1184" s="6" t="s">
-        <v>7542</v>
+        <v>7538</v>
       </c>
     </row>
     <row r="1185">
       <c r="B1185" s="5" t="s">
+        <v>7542</v>
+      </c>
+      <c r="C1185" s="5" t="s">
         <v>7543</v>
       </c>
-      <c r="C1185" s="5" t="s">
+      <c r="D1185" s="5" t="s">
         <v>7544</v>
       </c>
-      <c r="D1185" s="5" t="s">
+      <c r="E1185" s="5" t="s">
         <v>7545</v>
       </c>
-      <c r="E1185" s="5" t="s">
+      <c r="F1185" s="5" t="s">
         <v>7546</v>
       </c>
-      <c r="F1185" s="5" t="s">
+      <c r="G1185" s="5" t="s">
         <v>7547</v>
       </c>
-      <c r="G1185" s="5" t="s">
+      <c r="H1185" s="5" t="s">
         <v>7548</v>
-      </c>
-      <c r="H1185" s="5" t="s">
-        <v>7549</v>
       </c>
     </row>
     <row r="1186">
       <c r="B1186" s="6" t="s">
+        <v>7549</v>
+      </c>
+      <c r="C1186" s="6" t="s">
         <v>7550</v>
       </c>
-      <c r="C1186" s="6" t="s">
+      <c r="D1186" s="6" t="s">
         <v>7551</v>
       </c>
-      <c r="D1186" s="6" t="s">
+      <c r="E1186" s="6" t="s">
         <v>7552</v>
       </c>
-      <c r="E1186" s="6" t="s">
+      <c r="F1186" s="6" t="s">
         <v>7553</v>
       </c>
-      <c r="F1186" s="6" t="s">
+      <c r="G1186" s="6" t="s">
         <v>7554</v>
       </c>
-      <c r="G1186" s="6" t="s">
+      <c r="H1186" s="6" t="s">
         <v>7555</v>
-      </c>
-      <c r="H1186" s="6" t="s">
-        <v>7556</v>
       </c>
     </row>
     <row r="1187">
       <c r="B1187" s="5" t="s">
+        <v>7556</v>
+      </c>
+      <c r="C1187" s="5" t="s">
         <v>7557</v>
       </c>
-      <c r="C1187" s="5" t="s">
+      <c r="D1187" s="5" t="s">
         <v>7558</v>
       </c>
-      <c r="D1187" s="5" t="s">
+      <c r="E1187" s="5" t="s">
         <v>7559</v>
       </c>
-      <c r="E1187" s="5" t="s">
+      <c r="F1187" s="5" t="s">
         <v>7560</v>
       </c>
-      <c r="F1187" s="5" t="s">
+      <c r="G1187" s="5" t="s">
         <v>7561</v>
       </c>
-      <c r="G1187" s="5" t="s">
+      <c r="H1187" s="5" t="s">
         <v>7562</v>
-      </c>
-      <c r="H1187" s="5" t="s">
-        <v>7563</v>
       </c>
     </row>
     <row r="1188">
       <c r="B1188" s="6" t="s">
+        <v>7563</v>
+      </c>
+      <c r="C1188" s="6" t="s">
         <v>7564</v>
       </c>
-      <c r="C1188" s="6" t="s">
+      <c r="D1188" s="6" t="s">
         <v>7565</v>
       </c>
-      <c r="D1188" s="6" t="s">
+      <c r="E1188" s="6" t="s">
         <v>7566</v>
       </c>
-      <c r="E1188" s="6" t="s">
+      <c r="F1188" s="6" t="s">
         <v>7567</v>
       </c>
-      <c r="F1188" s="6" t="s">
+      <c r="G1188" s="6" t="s">
         <v>7568</v>
       </c>
-      <c r="G1188" s="6" t="s">
+      <c r="H1188" s="6" t="s">
         <v>7569</v>
-      </c>
-      <c r="H1188" s="6" t="s">
-        <v>7570</v>
       </c>
     </row>
     <row r="1189">
       <c r="B1189" s="5" t="s">
+        <v>7570</v>
+      </c>
+      <c r="C1189" s="5" t="s">
         <v>7571</v>
-      </c>
-      <c r="C1189" s="5" t="s">
-        <v>5444</v>
       </c>
       <c r="D1189" s="5" t="s">
         <v>7572</v>
       </c>
       <c r="E1189" s="5" t="s">
-        <v>5446</v>
+        <v>7573</v>
       </c>
       <c r="F1189" s="5" t="s">
-        <v>7573</v>
+        <v>7574</v>
       </c>
       <c r="G1189" s="5" t="s">
-        <v>7574</v>
+        <v>7575</v>
       </c>
       <c r="H1189" s="5" t="s">
-        <v>7575</v>
+        <v>7576</v>
       </c>
     </row>
     <row r="1190">
       <c r="B1190" s="6" t="s">
-        <v>7576</v>
+        <v>7577</v>
       </c>
       <c r="C1190" s="6" t="s">
-        <v>5437</v>
+        <v>5444</v>
       </c>
       <c r="D1190" s="6" t="s">
-        <v>7577</v>
+        <v>7578</v>
       </c>
       <c r="E1190" s="6" t="s">
-        <v>5439</v>
+        <v>5446</v>
       </c>
       <c r="F1190" s="6" t="s">
-        <v>7578</v>
+        <v>7579</v>
       </c>
       <c r="G1190" s="6" t="s">
-        <v>7579</v>
+        <v>7580</v>
       </c>
       <c r="H1190" s="6" t="s">
-        <v>7580</v>
+        <v>7581</v>
       </c>
     </row>
     <row r="1191">
       <c r="B1191" s="5" t="s">
-        <v>7581</v>
+        <v>7582</v>
       </c>
       <c r="C1191" s="5" t="s">
-        <v>7582</v>
+        <v>5437</v>
       </c>
       <c r="D1191" s="5" t="s">
         <v>7583</v>
       </c>
       <c r="E1191" s="5" t="s">
+        <v>5439</v>
+      </c>
+      <c r="F1191" s="5" t="s">
         <v>7584</v>
       </c>
-      <c r="F1191" s="5" t="s">
+      <c r="G1191" s="5" t="s">
         <v>7585</v>
       </c>
-      <c r="G1191" s="5" t="s">
-        <v>7584</v>
-      </c>
       <c r="H1191" s="5" t="s">
-        <v>6969</v>
+        <v>7586</v>
       </c>
     </row>
     <row r="1192">
       <c r="B1192" s="6" t="s">
-        <v>7586</v>
+        <v>7587</v>
       </c>
       <c r="C1192" s="6" t="s">
-        <v>7587</v>
+        <v>7588</v>
       </c>
       <c r="D1192" s="6" t="s">
-        <v>7588</v>
+        <v>7589</v>
       </c>
       <c r="E1192" s="6" t="s">
-        <v>7589</v>
+        <v>7590</v>
       </c>
       <c r="F1192" s="6" t="s">
+        <v>7591</v>
+      </c>
+      <c r="G1192" s="6" t="s">
         <v>7590</v>
       </c>
-      <c r="G1192" s="6" t="s">
-        <v>7591</v>
-      </c>
       <c r="H1192" s="6" t="s">
-        <v>7592</v>
+        <v>6969</v>
       </c>
     </row>
     <row r="1193">
       <c r="B1193" s="5" t="s">
+        <v>7592</v>
+      </c>
+      <c r="C1193" s="5" t="s">
         <v>7593</v>
       </c>
-      <c r="C1193" s="5" t="s">
+      <c r="D1193" s="5" t="s">
         <v>7594</v>
       </c>
-      <c r="D1193" s="5" t="s">
+      <c r="E1193" s="5" t="s">
         <v>7595</v>
       </c>
-      <c r="E1193" s="5" t="s">
+      <c r="F1193" s="5" t="s">
         <v>7596</v>
-      </c>
-      <c r="F1193" s="5" t="s">
-        <v>7597</v>
       </c>
       <c r="G1193" s="5" t="s">
         <v>7597</v>
@@ -54623,211 +54641,211 @@
         <v>7603</v>
       </c>
       <c r="G1194" s="6" t="s">
+        <v>7603</v>
+      </c>
+      <c r="H1194" s="6" t="s">
         <v>7604</v>
-      </c>
-      <c r="H1194" s="6" t="s">
-        <v>7605</v>
       </c>
     </row>
     <row r="1195">
       <c r="B1195" s="5" t="s">
+        <v>7605</v>
+      </c>
+      <c r="C1195" s="5" t="s">
         <v>7606</v>
       </c>
-      <c r="C1195" s="5" t="s">
+      <c r="D1195" s="5" t="s">
         <v>7607</v>
       </c>
-      <c r="D1195" s="5" t="s">
+      <c r="E1195" s="5" t="s">
         <v>7608</v>
       </c>
-      <c r="E1195" s="5" t="s">
+      <c r="F1195" s="5" t="s">
         <v>7609</v>
       </c>
-      <c r="F1195" s="5" t="s">
+      <c r="G1195" s="5" t="s">
         <v>7610</v>
       </c>
-      <c r="G1195" s="5" t="s">
+      <c r="H1195" s="5" t="s">
         <v>7611</v>
-      </c>
-      <c r="H1195" s="5" t="s">
-        <v>7612</v>
       </c>
     </row>
     <row r="1196">
       <c r="B1196" s="6" t="s">
+        <v>7612</v>
+      </c>
+      <c r="C1196" s="6" t="s">
         <v>7613</v>
       </c>
-      <c r="C1196" s="6" t="s">
+      <c r="D1196" s="6" t="s">
         <v>7614</v>
       </c>
-      <c r="D1196" s="6" t="s">
+      <c r="E1196" s="6" t="s">
         <v>7615</v>
       </c>
-      <c r="E1196" s="6" t="s">
+      <c r="F1196" s="6" t="s">
         <v>7616</v>
       </c>
-      <c r="F1196" s="6" t="s">
+      <c r="G1196" s="6" t="s">
         <v>7617</v>
       </c>
-      <c r="G1196" s="6" t="s">
+      <c r="H1196" s="6" t="s">
         <v>7618</v>
-      </c>
-      <c r="H1196" s="6" t="s">
-        <v>7619</v>
       </c>
     </row>
     <row r="1197">
       <c r="B1197" s="5" t="s">
+        <v>7619</v>
+      </c>
+      <c r="C1197" s="5" t="s">
         <v>7620</v>
       </c>
-      <c r="C1197" s="5" t="s">
+      <c r="D1197" s="5" t="s">
         <v>7621</v>
       </c>
-      <c r="D1197" s="5" t="s">
+      <c r="E1197" s="5" t="s">
         <v>7622</v>
       </c>
-      <c r="E1197" s="5" t="s">
+      <c r="F1197" s="5" t="s">
         <v>7623</v>
       </c>
-      <c r="F1197" s="5" t="s">
+      <c r="G1197" s="5" t="s">
         <v>7624</v>
       </c>
-      <c r="G1197" s="5" t="s">
+      <c r="H1197" s="5" t="s">
         <v>7625</v>
-      </c>
-      <c r="H1197" s="5" t="s">
-        <v>7626</v>
       </c>
     </row>
     <row r="1198">
       <c r="B1198" s="6" t="s">
+        <v>7626</v>
+      </c>
+      <c r="C1198" s="6" t="s">
         <v>7627</v>
       </c>
-      <c r="C1198" s="6" t="s">
+      <c r="D1198" s="6" t="s">
         <v>7628</v>
       </c>
-      <c r="D1198" s="6" t="s">
+      <c r="E1198" s="6" t="s">
         <v>7629</v>
       </c>
-      <c r="E1198" s="6" t="s">
+      <c r="F1198" s="6" t="s">
         <v>7630</v>
       </c>
-      <c r="F1198" s="6" t="s">
+      <c r="G1198" s="6" t="s">
         <v>7631</v>
       </c>
-      <c r="G1198" s="6" t="s">
+      <c r="H1198" s="6" t="s">
         <v>7632</v>
-      </c>
-      <c r="H1198" s="6" t="s">
-        <v>7633</v>
       </c>
     </row>
     <row r="1199">
       <c r="B1199" s="5" t="s">
+        <v>7633</v>
+      </c>
+      <c r="C1199" s="5" t="s">
         <v>7634</v>
       </c>
-      <c r="C1199" s="5" t="s">
+      <c r="D1199" s="5" t="s">
         <v>7635</v>
       </c>
-      <c r="D1199" s="5" t="s">
+      <c r="E1199" s="5" t="s">
         <v>7636</v>
-      </c>
-      <c r="E1199" s="5" t="s">
-        <v>7637</v>
       </c>
       <c r="F1199" s="5" t="s">
         <v>7637</v>
       </c>
       <c r="G1199" s="5" t="s">
-        <v>7637</v>
+        <v>7638</v>
       </c>
       <c r="H1199" s="5" t="s">
-        <v>7638</v>
+        <v>7639</v>
       </c>
     </row>
     <row r="1200">
       <c r="B1200" s="6" t="s">
-        <v>7639</v>
+        <v>7640</v>
       </c>
       <c r="C1200" s="6" t="s">
-        <v>7640</v>
+        <v>7641</v>
       </c>
       <c r="D1200" s="6" t="s">
-        <v>7641</v>
+        <v>7642</v>
       </c>
       <c r="E1200" s="6" t="s">
-        <v>7642</v>
+        <v>7643</v>
       </c>
       <c r="F1200" s="6" t="s">
         <v>7643</v>
       </c>
       <c r="G1200" s="6" t="s">
+        <v>7643</v>
+      </c>
+      <c r="H1200" s="6" t="s">
         <v>7644</v>
-      </c>
-      <c r="H1200" s="6" t="s">
-        <v>7645</v>
       </c>
     </row>
     <row r="1201">
       <c r="B1201" s="5" t="s">
+        <v>7645</v>
+      </c>
+      <c r="C1201" s="5" t="s">
         <v>7646</v>
       </c>
-      <c r="C1201" s="5" t="s">
+      <c r="D1201" s="5" t="s">
         <v>7647</v>
       </c>
-      <c r="D1201" s="5" t="s">
+      <c r="E1201" s="5" t="s">
         <v>7648</v>
       </c>
-      <c r="E1201" s="5" t="s">
+      <c r="F1201" s="5" t="s">
         <v>7649</v>
       </c>
-      <c r="F1201" s="5" t="s">
+      <c r="G1201" s="5" t="s">
         <v>7650</v>
       </c>
-      <c r="G1201" s="5" t="s">
+      <c r="H1201" s="5" t="s">
         <v>7651</v>
-      </c>
-      <c r="H1201" s="5" t="s">
-        <v>7652</v>
       </c>
     </row>
     <row r="1202">
       <c r="B1202" s="6" t="s">
+        <v>7652</v>
+      </c>
+      <c r="C1202" s="6" t="s">
         <v>7653</v>
       </c>
-      <c r="C1202" s="6" t="s">
+      <c r="D1202" s="6" t="s">
         <v>7654</v>
       </c>
-      <c r="D1202" s="6" t="s">
+      <c r="E1202" s="6" t="s">
         <v>7655</v>
       </c>
-      <c r="E1202" s="6" t="s">
+      <c r="F1202" s="6" t="s">
         <v>7656</v>
       </c>
-      <c r="F1202" s="6" t="s">
+      <c r="G1202" s="6" t="s">
         <v>7657</v>
       </c>
-      <c r="G1202" s="6" t="s">
+      <c r="H1202" s="6" t="s">
         <v>7658</v>
-      </c>
-      <c r="H1202" s="6" t="s">
-        <v>7659</v>
       </c>
     </row>
     <row r="1203">
       <c r="B1203" s="5" t="s">
+        <v>7659</v>
+      </c>
+      <c r="C1203" s="5" t="s">
         <v>7660</v>
       </c>
-      <c r="C1203" s="5" t="s">
+      <c r="D1203" s="5" t="s">
         <v>7661</v>
       </c>
-      <c r="D1203" s="5" t="s">
+      <c r="E1203" s="5" t="s">
         <v>7662</v>
       </c>
-      <c r="E1203" s="5" t="s">
+      <c r="F1203" s="5" t="s">
         <v>7663</v>
-      </c>
-      <c r="F1203" s="5" t="s">
-        <v>7664</v>
       </c>
       <c r="G1203" s="5" t="s">
         <v>7664</v>
@@ -54899,119 +54917,119 @@
         <v>7682</v>
       </c>
       <c r="G1206" s="6" t="s">
+        <v>7682</v>
+      </c>
+      <c r="H1206" s="6" t="s">
         <v>7683</v>
-      </c>
-      <c r="H1206" s="6" t="s">
-        <v>7684</v>
       </c>
     </row>
     <row r="1207">
       <c r="B1207" s="5" t="s">
+        <v>7684</v>
+      </c>
+      <c r="C1207" s="5" t="s">
         <v>7685</v>
       </c>
-      <c r="C1207" s="5" t="s">
+      <c r="D1207" s="5" t="s">
         <v>7686</v>
       </c>
-      <c r="D1207" s="5" t="s">
+      <c r="E1207" s="5" t="s">
         <v>7687</v>
       </c>
-      <c r="E1207" s="5" t="s">
+      <c r="F1207" s="5" t="s">
         <v>7688</v>
       </c>
-      <c r="F1207" s="5" t="s">
+      <c r="G1207" s="5" t="s">
         <v>7689</v>
       </c>
-      <c r="G1207" s="5" t="s">
+      <c r="H1207" s="5" t="s">
         <v>7690</v>
-      </c>
-      <c r="H1207" s="5" t="s">
-        <v>7691</v>
       </c>
     </row>
     <row r="1208">
       <c r="B1208" s="6" t="s">
+        <v>7691</v>
+      </c>
+      <c r="C1208" s="6" t="s">
         <v>7692</v>
       </c>
-      <c r="C1208" s="6" t="s">
+      <c r="D1208" s="6" t="s">
         <v>7693</v>
       </c>
-      <c r="D1208" s="6" t="s">
+      <c r="E1208" s="6" t="s">
         <v>7694</v>
       </c>
-      <c r="E1208" s="6" t="s">
+      <c r="F1208" s="6" t="s">
         <v>7695</v>
       </c>
-      <c r="F1208" s="6" t="s">
+      <c r="G1208" s="6" t="s">
         <v>7696</v>
       </c>
-      <c r="G1208" s="6" t="s">
+      <c r="H1208" s="6" t="s">
         <v>7697</v>
-      </c>
-      <c r="H1208" s="6" t="s">
-        <v>7698</v>
       </c>
     </row>
     <row r="1209">
       <c r="B1209" s="5" t="s">
+        <v>7698</v>
+      </c>
+      <c r="C1209" s="5" t="s">
         <v>7699</v>
       </c>
-      <c r="C1209" s="5" t="s">
+      <c r="D1209" s="5" t="s">
         <v>7700</v>
       </c>
-      <c r="D1209" s="5" t="s">
+      <c r="E1209" s="5" t="s">
         <v>7701</v>
       </c>
-      <c r="E1209" s="5" t="s">
+      <c r="F1209" s="5" t="s">
         <v>7702</v>
       </c>
-      <c r="F1209" s="5" t="s">
+      <c r="G1209" s="5" t="s">
         <v>7703</v>
       </c>
-      <c r="G1209" s="5" t="s">
+      <c r="H1209" s="5" t="s">
         <v>7704</v>
-      </c>
-      <c r="H1209" s="5" t="s">
-        <v>7705</v>
       </c>
     </row>
     <row r="1210">
       <c r="B1210" s="6" t="s">
+        <v>7705</v>
+      </c>
+      <c r="C1210" s="6" t="s">
         <v>7706</v>
       </c>
-      <c r="C1210" s="6" t="s">
+      <c r="D1210" s="6" t="s">
         <v>7707</v>
       </c>
-      <c r="D1210" s="6" t="s">
+      <c r="E1210" s="6" t="s">
         <v>7708</v>
       </c>
-      <c r="E1210" s="6" t="s">
+      <c r="F1210" s="6" t="s">
         <v>7709</v>
       </c>
-      <c r="F1210" s="6" t="s">
+      <c r="G1210" s="6" t="s">
         <v>7710</v>
       </c>
-      <c r="G1210" s="6" t="s">
+      <c r="H1210" s="6" t="s">
         <v>7711</v>
-      </c>
-      <c r="H1210" s="6" t="s">
-        <v>7712</v>
       </c>
     </row>
     <row r="1211">
       <c r="B1211" s="5" t="s">
+        <v>7712</v>
+      </c>
+      <c r="C1211" s="5" t="s">
         <v>7713</v>
       </c>
-      <c r="C1211" s="5" t="s">
+      <c r="D1211" s="5" t="s">
         <v>7714</v>
       </c>
-      <c r="D1211" s="5" t="s">
+      <c r="E1211" s="5" t="s">
         <v>7715</v>
       </c>
-      <c r="E1211" s="5" t="s">
+      <c r="F1211" s="5" t="s">
         <v>7716</v>
-      </c>
-      <c r="F1211" s="5" t="s">
-        <v>7717</v>
       </c>
       <c r="G1211" s="5" t="s">
         <v>7717</v>
@@ -55037,10 +55055,10 @@
         <v>7723</v>
       </c>
       <c r="G1212" s="6" t="s">
+        <v>7723</v>
+      </c>
+      <c r="H1212" s="6" t="s">
         <v>7724</v>
-      </c>
-      <c r="H1212" s="6" t="s">
-        <v>6874</v>
       </c>
     </row>
     <row r="1213">
@@ -55063,7 +55081,7 @@
         <v>7730</v>
       </c>
       <c r="H1213" s="5" t="s">
-        <v>7494</v>
+        <v>6874</v>
       </c>
     </row>
     <row r="1214">
@@ -55086,133 +55104,133 @@
         <v>7736</v>
       </c>
       <c r="H1214" s="6" t="s">
-        <v>7737</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="1215">
       <c r="B1215" s="5" t="s">
+        <v>7737</v>
+      </c>
+      <c r="C1215" s="5" t="s">
         <v>7738</v>
       </c>
-      <c r="C1215" s="5" t="s">
+      <c r="D1215" s="5" t="s">
         <v>7739</v>
       </c>
-      <c r="D1215" s="5" t="s">
+      <c r="E1215" s="5" t="s">
         <v>7740</v>
       </c>
-      <c r="E1215" s="5" t="s">
+      <c r="F1215" s="5" t="s">
         <v>7741</v>
       </c>
-      <c r="F1215" s="5" t="s">
+      <c r="G1215" s="5" t="s">
         <v>7742</v>
       </c>
-      <c r="G1215" s="5" t="s">
+      <c r="H1215" s="5" t="s">
         <v>7743</v>
-      </c>
-      <c r="H1215" s="5" t="s">
-        <v>7744</v>
       </c>
     </row>
     <row r="1216">
       <c r="B1216" s="6" t="s">
+        <v>7744</v>
+      </c>
+      <c r="C1216" s="6" t="s">
         <v>7745</v>
       </c>
-      <c r="C1216" s="6" t="s">
+      <c r="D1216" s="6" t="s">
         <v>7746</v>
       </c>
-      <c r="D1216" s="6" t="s">
+      <c r="E1216" s="6" t="s">
         <v>7747</v>
-      </c>
-      <c r="E1216" s="6" t="s">
-        <v>7748</v>
       </c>
       <c r="F1216" s="6" t="s">
         <v>7748</v>
       </c>
       <c r="G1216" s="6" t="s">
-        <v>7748</v>
+        <v>7749</v>
       </c>
       <c r="H1216" s="6" t="s">
-        <v>7747</v>
+        <v>7750</v>
       </c>
     </row>
     <row r="1217">
       <c r="B1217" s="5" t="s">
-        <v>7749</v>
+        <v>7751</v>
       </c>
       <c r="C1217" s="5" t="s">
-        <v>7750</v>
+        <v>7752</v>
       </c>
       <c r="D1217" s="5" t="s">
-        <v>7751</v>
+        <v>7753</v>
       </c>
       <c r="E1217" s="5" t="s">
-        <v>7752</v>
+        <v>7754</v>
       </c>
       <c r="F1217" s="5" t="s">
-        <v>7753</v>
+        <v>7754</v>
       </c>
       <c r="G1217" s="5" t="s">
         <v>7754</v>
       </c>
       <c r="H1217" s="5" t="s">
-        <v>7755</v>
+        <v>7753</v>
       </c>
     </row>
     <row r="1218">
       <c r="B1218" s="6" t="s">
+        <v>7755</v>
+      </c>
+      <c r="C1218" s="6" t="s">
         <v>7756</v>
       </c>
-      <c r="C1218" s="6" t="s">
+      <c r="D1218" s="6" t="s">
         <v>7757</v>
       </c>
-      <c r="D1218" s="6" t="s">
+      <c r="E1218" s="6" t="s">
         <v>7758</v>
       </c>
-      <c r="E1218" s="6" t="s">
+      <c r="F1218" s="6" t="s">
         <v>7759</v>
       </c>
-      <c r="F1218" s="6" t="s">
+      <c r="G1218" s="6" t="s">
         <v>7760</v>
       </c>
-      <c r="G1218" s="6" t="s">
+      <c r="H1218" s="6" t="s">
         <v>7761</v>
-      </c>
-      <c r="H1218" s="6" t="s">
-        <v>7762</v>
       </c>
     </row>
     <row r="1219">
       <c r="B1219" s="5" t="s">
+        <v>7762</v>
+      </c>
+      <c r="C1219" s="5" t="s">
         <v>7763</v>
       </c>
-      <c r="C1219" s="5" t="s">
+      <c r="D1219" s="5" t="s">
         <v>7764</v>
       </c>
-      <c r="D1219" s="5" t="s">
+      <c r="E1219" s="5" t="s">
         <v>7765</v>
       </c>
-      <c r="E1219" s="5" t="s">
+      <c r="F1219" s="5" t="s">
         <v>7766</v>
       </c>
-      <c r="F1219" s="5" t="s">
+      <c r="G1219" s="5" t="s">
         <v>7767</v>
       </c>
-      <c r="G1219" s="5" t="s">
+      <c r="H1219" s="5" t="s">
         <v>7768</v>
-      </c>
-      <c r="H1219" s="5" t="s">
-        <v>7769</v>
       </c>
     </row>
     <row r="1220">
       <c r="B1220" s="6" t="s">
+        <v>7769</v>
+      </c>
+      <c r="C1220" s="6" t="s">
         <v>7770</v>
       </c>
-      <c r="C1220" s="6" t="s">
+      <c r="D1220" s="6" t="s">
         <v>7771</v>
-      </c>
-      <c r="D1220" s="6" t="s">
-        <v>7747</v>
       </c>
       <c r="E1220" s="6" t="s">
         <v>7772</v>
@@ -55221,56 +55239,56 @@
         <v>7773</v>
       </c>
       <c r="G1220" s="6" t="s">
-        <v>7773</v>
+        <v>7774</v>
       </c>
       <c r="H1220" s="6" t="s">
-        <v>7747</v>
+        <v>7775</v>
       </c>
     </row>
     <row r="1221">
       <c r="B1221" s="5" t="s">
-        <v>7774</v>
+        <v>7776</v>
       </c>
       <c r="C1221" s="5" t="s">
-        <v>7775</v>
+        <v>7777</v>
       </c>
       <c r="D1221" s="5" t="s">
-        <v>7776</v>
+        <v>7753</v>
       </c>
       <c r="E1221" s="5" t="s">
-        <v>7777</v>
+        <v>7778</v>
       </c>
       <c r="F1221" s="5" t="s">
-        <v>7778</v>
+        <v>7779</v>
       </c>
       <c r="G1221" s="5" t="s">
         <v>7779</v>
       </c>
       <c r="H1221" s="5" t="s">
-        <v>7780</v>
+        <v>7753</v>
       </c>
     </row>
     <row r="1222">
       <c r="B1222" s="6" t="s">
+        <v>7780</v>
+      </c>
+      <c r="C1222" s="6" t="s">
         <v>7781</v>
       </c>
-      <c r="C1222" s="6" t="s">
+      <c r="D1222" s="6" t="s">
         <v>7782</v>
       </c>
-      <c r="D1222" s="6" t="s">
+      <c r="E1222" s="6" t="s">
         <v>7783</v>
       </c>
-      <c r="E1222" s="6" t="s">
+      <c r="F1222" s="6" t="s">
         <v>7784</v>
       </c>
-      <c r="F1222" s="6" t="s">
+      <c r="G1222" s="6" t="s">
         <v>7785</v>
       </c>
-      <c r="G1222" s="6" t="s">
+      <c r="H1222" s="6" t="s">
         <v>7786</v>
-      </c>
-      <c r="H1222" s="6" t="s">
-        <v>7783</v>
       </c>
     </row>
     <row r="1223">
@@ -55293,93 +55311,93 @@
         <v>7792</v>
       </c>
       <c r="H1223" s="5" t="s">
-        <v>7793</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="1224">
       <c r="B1224" s="6" t="s">
+        <v>7793</v>
+      </c>
+      <c r="C1224" s="6" t="s">
         <v>7794</v>
       </c>
-      <c r="C1224" s="6" t="s">
+      <c r="D1224" s="6" t="s">
         <v>7795</v>
       </c>
-      <c r="D1224" s="6" t="s">
+      <c r="E1224" s="6" t="s">
         <v>7796</v>
       </c>
-      <c r="E1224" s="6" t="s">
+      <c r="F1224" s="6" t="s">
         <v>7797</v>
       </c>
-      <c r="F1224" s="6" t="s">
+      <c r="G1224" s="6" t="s">
         <v>7798</v>
       </c>
-      <c r="G1224" s="6" t="s">
+      <c r="H1224" s="6" t="s">
         <v>7799</v>
-      </c>
-      <c r="H1224" s="6" t="s">
-        <v>7800</v>
       </c>
     </row>
     <row r="1225">
       <c r="B1225" s="5" t="s">
+        <v>7800</v>
+      </c>
+      <c r="C1225" s="5" t="s">
         <v>7801</v>
       </c>
-      <c r="C1225" s="5" t="s">
+      <c r="D1225" s="5" t="s">
         <v>7802</v>
       </c>
-      <c r="D1225" s="5" t="s">
+      <c r="E1225" s="5" t="s">
         <v>7803</v>
       </c>
-      <c r="E1225" s="5" t="s">
+      <c r="F1225" s="5" t="s">
         <v>7804</v>
       </c>
-      <c r="F1225" s="5" t="s">
+      <c r="G1225" s="5" t="s">
         <v>7805</v>
       </c>
-      <c r="G1225" s="5" t="s">
+      <c r="H1225" s="5" t="s">
         <v>7806</v>
-      </c>
-      <c r="H1225" s="5" t="s">
-        <v>7807</v>
       </c>
     </row>
     <row r="1226">
       <c r="B1226" s="6" t="s">
+        <v>7807</v>
+      </c>
+      <c r="C1226" s="6" t="s">
         <v>7808</v>
       </c>
-      <c r="C1226" s="6" t="s">
+      <c r="D1226" s="6" t="s">
         <v>7809</v>
       </c>
-      <c r="D1226" s="6" t="s">
+      <c r="E1226" s="6" t="s">
         <v>7810</v>
       </c>
-      <c r="E1226" s="6" t="s">
+      <c r="F1226" s="6" t="s">
         <v>7811</v>
       </c>
-      <c r="F1226" s="6" t="s">
+      <c r="G1226" s="6" t="s">
         <v>7812</v>
       </c>
-      <c r="G1226" s="6" t="s">
+      <c r="H1226" s="6" t="s">
         <v>7813</v>
-      </c>
-      <c r="H1226" s="6" t="s">
-        <v>7814</v>
       </c>
     </row>
     <row r="1227">
       <c r="B1227" s="5" t="s">
+        <v>7814</v>
+      </c>
+      <c r="C1227" s="5" t="s">
         <v>7815</v>
       </c>
-      <c r="C1227" s="5" t="s">
+      <c r="D1227" s="5" t="s">
         <v>7816</v>
       </c>
-      <c r="D1227" s="5" t="s">
+      <c r="E1227" s="5" t="s">
         <v>7817</v>
       </c>
-      <c r="E1227" s="5" t="s">
+      <c r="F1227" s="5" t="s">
         <v>7818</v>
-      </c>
-      <c r="F1227" s="5" t="s">
-        <v>7819</v>
       </c>
       <c r="G1227" s="5" t="s">
         <v>7819</v>
@@ -55405,27 +55423,27 @@
         <v>7825</v>
       </c>
       <c r="G1228" s="6" t="s">
+        <v>7825</v>
+      </c>
+      <c r="H1228" s="6" t="s">
         <v>7826</v>
-      </c>
-      <c r="H1228" s="6" t="s">
-        <v>7827</v>
       </c>
     </row>
     <row r="1229">
       <c r="B1229" s="5" t="s">
+        <v>7827</v>
+      </c>
+      <c r="C1229" s="5" t="s">
         <v>7828</v>
       </c>
-      <c r="C1229" s="5" t="s">
+      <c r="D1229" s="5" t="s">
         <v>7829</v>
       </c>
-      <c r="D1229" s="5" t="s">
+      <c r="E1229" s="5" t="s">
         <v>7830</v>
       </c>
-      <c r="E1229" s="5" t="s">
+      <c r="F1229" s="5" t="s">
         <v>7831</v>
-      </c>
-      <c r="F1229" s="5" t="s">
-        <v>7832</v>
       </c>
       <c r="G1229" s="5" t="s">
         <v>7832</v>
@@ -55451,53 +55469,53 @@
         <v>7838</v>
       </c>
       <c r="G1230" s="6" t="s">
+        <v>7838</v>
+      </c>
+      <c r="H1230" s="6" t="s">
         <v>7839</v>
-      </c>
-      <c r="H1230" s="6" t="s">
-        <v>7840</v>
       </c>
     </row>
     <row r="1231">
       <c r="B1231" s="5" t="s">
+        <v>7840</v>
+      </c>
+      <c r="C1231" s="5" t="s">
         <v>7841</v>
       </c>
-      <c r="C1231" s="5" t="s">
+      <c r="D1231" s="5" t="s">
         <v>7842</v>
       </c>
-      <c r="D1231" s="5" t="s">
+      <c r="E1231" s="5" t="s">
         <v>7843</v>
       </c>
-      <c r="E1231" s="5" t="s">
+      <c r="F1231" s="5" t="s">
         <v>7844</v>
       </c>
-      <c r="F1231" s="5" t="s">
+      <c r="G1231" s="5" t="s">
         <v>7845</v>
       </c>
-      <c r="G1231" s="5" t="s">
+      <c r="H1231" s="5" t="s">
         <v>7846</v>
-      </c>
-      <c r="H1231" s="5" t="s">
-        <v>7847</v>
       </c>
     </row>
     <row r="1232">
       <c r="B1232" s="6" t="s">
+        <v>7847</v>
+      </c>
+      <c r="C1232" s="6" t="s">
         <v>7848</v>
       </c>
-      <c r="C1232" s="6" t="s">
+      <c r="D1232" s="6" t="s">
         <v>7849</v>
       </c>
-      <c r="D1232" s="6" t="s">
+      <c r="E1232" s="6" t="s">
         <v>7850</v>
       </c>
-      <c r="E1232" s="6" t="s">
+      <c r="F1232" s="6" t="s">
         <v>7851</v>
       </c>
-      <c r="F1232" s="6" t="s">
+      <c r="G1232" s="6" t="s">
         <v>7852</v>
-      </c>
-      <c r="G1232" s="6" t="s">
-        <v>7851</v>
       </c>
       <c r="H1232" s="6" t="s">
         <v>7853</v>
@@ -55520,56 +55538,56 @@
         <v>7858</v>
       </c>
       <c r="G1233" s="5" t="s">
-        <v>7858</v>
+        <v>7857</v>
       </c>
       <c r="H1233" s="5" t="s">
-        <v>7856</v>
+        <v>7859</v>
       </c>
     </row>
     <row r="1234">
       <c r="B1234" s="6" t="s">
-        <v>7859</v>
+        <v>7860</v>
       </c>
       <c r="C1234" s="6" t="s">
-        <v>7860</v>
+        <v>7861</v>
       </c>
       <c r="D1234" s="6" t="s">
-        <v>7861</v>
+        <v>7862</v>
       </c>
       <c r="E1234" s="6" t="s">
-        <v>7862</v>
+        <v>7863</v>
       </c>
       <c r="F1234" s="6" t="s">
-        <v>7863</v>
+        <v>7864</v>
       </c>
       <c r="G1234" s="6" t="s">
         <v>7864</v>
       </c>
       <c r="H1234" s="6" t="s">
-        <v>7865</v>
+        <v>7862</v>
       </c>
     </row>
     <row r="1235">
       <c r="B1235" s="5" t="s">
+        <v>7865</v>
+      </c>
+      <c r="C1235" s="5" t="s">
         <v>7866</v>
       </c>
-      <c r="C1235" s="5" t="s">
+      <c r="D1235" s="5" t="s">
         <v>7867</v>
       </c>
-      <c r="D1235" s="5" t="s">
+      <c r="E1235" s="5" t="s">
         <v>7868</v>
       </c>
-      <c r="E1235" s="5" t="s">
+      <c r="F1235" s="5" t="s">
         <v>7869</v>
       </c>
-      <c r="F1235" s="5" t="s">
+      <c r="G1235" s="5" t="s">
         <v>7870</v>
       </c>
-      <c r="G1235" s="5" t="s">
+      <c r="H1235" s="5" t="s">
         <v>7871</v>
-      </c>
-      <c r="H1235" s="5" t="s">
-        <v>7868</v>
       </c>
     </row>
     <row r="1236">
@@ -55592,24 +55610,24 @@
         <v>7877</v>
       </c>
       <c r="H1236" s="6" t="s">
-        <v>7878</v>
+        <v>7874</v>
       </c>
     </row>
     <row r="1237">
       <c r="B1237" s="5" t="s">
+        <v>7878</v>
+      </c>
+      <c r="C1237" s="5" t="s">
         <v>7879</v>
       </c>
-      <c r="C1237" s="5" t="s">
+      <c r="D1237" s="5" t="s">
         <v>7880</v>
       </c>
-      <c r="D1237" s="5" t="s">
+      <c r="E1237" s="5" t="s">
         <v>7881</v>
       </c>
-      <c r="E1237" s="5" t="s">
+      <c r="F1237" s="5" t="s">
         <v>7882</v>
-      </c>
-      <c r="F1237" s="5" t="s">
-        <v>7883</v>
       </c>
       <c r="G1237" s="5" t="s">
         <v>7883</v>
@@ -55658,27 +55676,27 @@
         <v>7895</v>
       </c>
       <c r="G1239" s="5" t="s">
+        <v>7895</v>
+      </c>
+      <c r="H1239" s="5" t="s">
         <v>7896</v>
-      </c>
-      <c r="H1239" s="5" t="s">
-        <v>7897</v>
       </c>
     </row>
     <row r="1240">
       <c r="B1240" s="6" t="s">
+        <v>7897</v>
+      </c>
+      <c r="C1240" s="6" t="s">
         <v>7898</v>
       </c>
-      <c r="C1240" s="6" t="s">
+      <c r="D1240" s="6" t="s">
         <v>7899</v>
       </c>
-      <c r="D1240" s="6" t="s">
+      <c r="E1240" s="6" t="s">
         <v>7900</v>
       </c>
-      <c r="E1240" s="6" t="s">
+      <c r="F1240" s="6" t="s">
         <v>7901</v>
-      </c>
-      <c r="F1240" s="6" t="s">
-        <v>7902</v>
       </c>
       <c r="G1240" s="6" t="s">
         <v>7902</v>
@@ -55704,27 +55722,27 @@
         <v>7908</v>
       </c>
       <c r="G1241" s="5" t="s">
+        <v>7908</v>
+      </c>
+      <c r="H1241" s="5" t="s">
         <v>7909</v>
-      </c>
-      <c r="H1241" s="5" t="s">
-        <v>7910</v>
       </c>
     </row>
     <row r="1242">
       <c r="B1242" s="6" t="s">
+        <v>7910</v>
+      </c>
+      <c r="C1242" s="6" t="s">
         <v>7911</v>
       </c>
-      <c r="C1242" s="6" t="s">
+      <c r="D1242" s="6" t="s">
         <v>7912</v>
       </c>
-      <c r="D1242" s="6" t="s">
+      <c r="E1242" s="6" t="s">
         <v>7913</v>
       </c>
-      <c r="E1242" s="6" t="s">
+      <c r="F1242" s="6" t="s">
         <v>7914</v>
-      </c>
-      <c r="F1242" s="6" t="s">
-        <v>7915</v>
       </c>
       <c r="G1242" s="6" t="s">
         <v>7915</v>
@@ -55764,65 +55782,65 @@
         <v>7924</v>
       </c>
       <c r="D1244" s="6" t="s">
-        <v>7924</v>
+        <v>7925</v>
       </c>
       <c r="E1244" s="6" t="s">
-        <v>7924</v>
+        <v>7926</v>
       </c>
       <c r="F1244" s="6" t="s">
-        <v>7924</v>
+        <v>7927</v>
       </c>
       <c r="G1244" s="6" t="s">
-        <v>7924</v>
+        <v>7927</v>
       </c>
       <c r="H1244" s="6" t="s">
-        <v>7924</v>
+        <v>7928</v>
       </c>
     </row>
     <row r="1245">
       <c r="B1245" s="5" t="s">
-        <v>7925</v>
+        <v>7929</v>
       </c>
       <c r="C1245" s="5" t="s">
-        <v>7926</v>
+        <v>7930</v>
       </c>
       <c r="D1245" s="5" t="s">
-        <v>7927</v>
+        <v>7930</v>
       </c>
       <c r="E1245" s="5" t="s">
-        <v>7928</v>
+        <v>7930</v>
       </c>
       <c r="F1245" s="5" t="s">
-        <v>7929</v>
+        <v>7930</v>
       </c>
       <c r="G1245" s="5" t="s">
-        <v>7929</v>
+        <v>7930</v>
       </c>
       <c r="H1245" s="5" t="s">
-        <v>7927</v>
+        <v>7930</v>
       </c>
     </row>
     <row r="1246">
       <c r="B1246" s="6" t="s">
-        <v>7930</v>
+        <v>7931</v>
       </c>
       <c r="C1246" s="6" t="s">
-        <v>7931</v>
+        <v>7932</v>
       </c>
       <c r="D1246" s="6" t="s">
-        <v>7932</v>
+        <v>7933</v>
       </c>
       <c r="E1246" s="6" t="s">
-        <v>7933</v>
+        <v>7934</v>
       </c>
       <c r="F1246" s="6" t="s">
-        <v>7934</v>
+        <v>7935</v>
       </c>
       <c r="G1246" s="6" t="s">
         <v>7935</v>
       </c>
       <c r="H1246" s="6" t="s">
-        <v>7932</v>
+        <v>7933</v>
       </c>
     </row>
     <row r="1247">
@@ -55839,10 +55857,10 @@
         <v>7939</v>
       </c>
       <c r="F1247" s="5" t="s">
-        <v>7939</v>
+        <v>7940</v>
       </c>
       <c r="G1247" s="5" t="s">
-        <v>7939</v>
+        <v>7941</v>
       </c>
       <c r="H1247" s="5" t="s">
         <v>7938</v>
@@ -55850,71 +55868,71 @@
     </row>
     <row r="1248">
       <c r="B1248" s="6" t="s">
-        <v>7940</v>
+        <v>7942</v>
       </c>
       <c r="C1248" s="6" t="s">
-        <v>7941</v>
+        <v>7943</v>
       </c>
       <c r="D1248" s="6" t="s">
-        <v>7942</v>
+        <v>7944</v>
       </c>
       <c r="E1248" s="6" t="s">
-        <v>7943</v>
+        <v>7945</v>
       </c>
       <c r="F1248" s="6" t="s">
-        <v>7943</v>
+        <v>7945</v>
       </c>
       <c r="G1248" s="6" t="s">
-        <v>7943</v>
+        <v>7945</v>
       </c>
       <c r="H1248" s="6" t="s">
-        <v>7942</v>
+        <v>7944</v>
       </c>
     </row>
     <row r="1249">
       <c r="B1249" s="5" t="s">
-        <v>7944</v>
+        <v>7946</v>
       </c>
       <c r="C1249" s="5" t="s">
-        <v>7945</v>
+        <v>7947</v>
       </c>
       <c r="D1249" s="5" t="s">
-        <v>7946</v>
+        <v>7948</v>
       </c>
       <c r="E1249" s="5" t="s">
-        <v>7947</v>
+        <v>7949</v>
       </c>
       <c r="F1249" s="5" t="s">
-        <v>7948</v>
+        <v>7949</v>
       </c>
       <c r="G1249" s="5" t="s">
         <v>7949</v>
       </c>
       <c r="H1249" s="5" t="s">
-        <v>7950</v>
+        <v>7948</v>
       </c>
     </row>
     <row r="1250">
       <c r="B1250" s="6" t="s">
+        <v>7950</v>
+      </c>
+      <c r="C1250" s="6" t="s">
         <v>7951</v>
       </c>
-      <c r="C1250" s="6" t="s">
+      <c r="D1250" s="6" t="s">
         <v>7952</v>
       </c>
-      <c r="D1250" s="6" t="s">
+      <c r="E1250" s="6" t="s">
         <v>7953</v>
       </c>
-      <c r="E1250" s="6" t="s">
+      <c r="F1250" s="6" t="s">
         <v>7954</v>
       </c>
-      <c r="F1250" s="6" t="s">
+      <c r="G1250" s="6" t="s">
         <v>7955</v>
       </c>
-      <c r="G1250" s="6" t="s">
+      <c r="H1250" s="6" t="s">
         <v>7956</v>
-      </c>
-      <c r="H1250" s="6" t="s">
-        <v>7953</v>
       </c>
     </row>
     <row r="1251">
@@ -55937,76 +55955,76 @@
         <v>7962</v>
       </c>
       <c r="H1251" s="5" t="s">
-        <v>7963</v>
+        <v>7959</v>
       </c>
     </row>
     <row r="1252">
       <c r="B1252" s="6" t="s">
+        <v>7963</v>
+      </c>
+      <c r="C1252" s="6" t="s">
         <v>7964</v>
       </c>
-      <c r="C1252" s="6" t="s">
+      <c r="D1252" s="6" t="s">
         <v>7965</v>
       </c>
-      <c r="D1252" s="6" t="s">
+      <c r="E1252" s="6" t="s">
         <v>7966</v>
       </c>
-      <c r="E1252" s="6" t="s">
+      <c r="F1252" s="6" t="s">
         <v>7967</v>
       </c>
-      <c r="F1252" s="6" t="s">
+      <c r="G1252" s="6" t="s">
         <v>7968</v>
       </c>
-      <c r="G1252" s="6" t="s">
+      <c r="H1252" s="6" t="s">
         <v>7969</v>
-      </c>
-      <c r="H1252" s="6" t="s">
-        <v>7970</v>
       </c>
     </row>
     <row r="1253">
       <c r="B1253" s="5" t="s">
+        <v>7970</v>
+      </c>
+      <c r="C1253" s="5" t="s">
         <v>7971</v>
       </c>
-      <c r="C1253" s="5" t="s">
+      <c r="D1253" s="5" t="s">
         <v>7972</v>
       </c>
-      <c r="D1253" s="5" t="s">
+      <c r="E1253" s="5" t="s">
         <v>7973</v>
       </c>
-      <c r="E1253" s="5" t="s">
+      <c r="F1253" s="5" t="s">
         <v>7974</v>
       </c>
-      <c r="F1253" s="5" t="s">
+      <c r="G1253" s="5" t="s">
         <v>7975</v>
       </c>
-      <c r="G1253" s="5" t="s">
+      <c r="H1253" s="5" t="s">
         <v>7976</v>
-      </c>
-      <c r="H1253" s="5" t="s">
-        <v>7977</v>
       </c>
     </row>
     <row r="1254">
       <c r="B1254" s="6" t="s">
+        <v>7977</v>
+      </c>
+      <c r="C1254" s="6" t="s">
         <v>7978</v>
       </c>
-      <c r="C1254" s="6" t="s">
+      <c r="D1254" s="6" t="s">
         <v>7979</v>
       </c>
-      <c r="D1254" s="6" t="s">
+      <c r="E1254" s="6" t="s">
         <v>7980</v>
       </c>
-      <c r="E1254" s="6" t="s">
+      <c r="F1254" s="6" t="s">
         <v>7981</v>
       </c>
-      <c r="F1254" s="6" t="s">
+      <c r="G1254" s="6" t="s">
         <v>7982</v>
       </c>
-      <c r="G1254" s="6" t="s">
+      <c r="H1254" s="6" t="s">
         <v>7983</v>
-      </c>
-      <c r="H1254" s="6" t="s">
-        <v>7953</v>
       </c>
     </row>
     <row r="1255">
@@ -56029,24 +56047,24 @@
         <v>7989</v>
       </c>
       <c r="H1255" s="5" t="s">
-        <v>7990</v>
+        <v>7959</v>
       </c>
     </row>
     <row r="1256">
       <c r="B1256" s="6" t="s">
+        <v>7990</v>
+      </c>
+      <c r="C1256" s="6" t="s">
         <v>7991</v>
       </c>
-      <c r="C1256" s="6" t="s">
+      <c r="D1256" s="6" t="s">
         <v>7992</v>
       </c>
-      <c r="D1256" s="6" t="s">
+      <c r="E1256" s="6" t="s">
         <v>7993</v>
       </c>
-      <c r="E1256" s="6" t="s">
+      <c r="F1256" s="6" t="s">
         <v>7994</v>
-      </c>
-      <c r="F1256" s="6" t="s">
-        <v>7995</v>
       </c>
       <c r="G1256" s="6" t="s">
         <v>7995</v>
@@ -56072,56 +56090,56 @@
         <v>8001</v>
       </c>
       <c r="G1257" s="5" t="s">
+        <v>8001</v>
+      </c>
+      <c r="H1257" s="5" t="s">
         <v>8002</v>
-      </c>
-      <c r="H1257" s="5" t="s">
-        <v>8003</v>
       </c>
     </row>
     <row r="1258">
       <c r="B1258" s="6" t="s">
+        <v>8003</v>
+      </c>
+      <c r="C1258" s="6" t="s">
         <v>8004</v>
-      </c>
-      <c r="C1258" s="6" t="s">
-        <v>6033</v>
       </c>
       <c r="D1258" s="6" t="s">
         <v>8005</v>
       </c>
       <c r="E1258" s="6" t="s">
-        <v>6035</v>
+        <v>8006</v>
       </c>
       <c r="F1258" s="6" t="s">
-        <v>8006</v>
+        <v>8007</v>
       </c>
       <c r="G1258" s="6" t="s">
-        <v>8006</v>
+        <v>8008</v>
       </c>
       <c r="H1258" s="6" t="s">
-        <v>5404</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="1259">
       <c r="B1259" s="5" t="s">
-        <v>8007</v>
+        <v>8010</v>
       </c>
       <c r="C1259" s="5" t="s">
-        <v>8008</v>
+        <v>6033</v>
       </c>
       <c r="D1259" s="5" t="s">
-        <v>8009</v>
+        <v>8011</v>
       </c>
       <c r="E1259" s="5" t="s">
-        <v>8010</v>
+        <v>6035</v>
       </c>
       <c r="F1259" s="5" t="s">
-        <v>8011</v>
+        <v>8012</v>
       </c>
       <c r="G1259" s="5" t="s">
-        <v>8011</v>
+        <v>8012</v>
       </c>
       <c r="H1259" s="5" t="s">
-        <v>8012</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1260">
@@ -56141,76 +56159,76 @@
         <v>8017</v>
       </c>
       <c r="G1260" s="6" t="s">
+        <v>8017</v>
+      </c>
+      <c r="H1260" s="6" t="s">
         <v>8018</v>
-      </c>
-      <c r="H1260" s="6" t="s">
-        <v>8019</v>
       </c>
     </row>
     <row r="1261">
       <c r="B1261" s="5" t="s">
+        <v>8019</v>
+      </c>
+      <c r="C1261" s="5" t="s">
         <v>8020</v>
       </c>
-      <c r="C1261" s="5" t="s">
+      <c r="D1261" s="5" t="s">
         <v>8021</v>
       </c>
-      <c r="D1261" s="5" t="s">
+      <c r="E1261" s="5" t="s">
         <v>8022</v>
       </c>
-      <c r="E1261" s="5" t="s">
+      <c r="F1261" s="5" t="s">
         <v>8023</v>
       </c>
-      <c r="F1261" s="5" t="s">
+      <c r="G1261" s="5" t="s">
         <v>8024</v>
       </c>
-      <c r="G1261" s="5" t="s">
+      <c r="H1261" s="5" t="s">
         <v>8025</v>
-      </c>
-      <c r="H1261" s="5" t="s">
-        <v>8026</v>
       </c>
     </row>
     <row r="1262">
       <c r="B1262" s="6" t="s">
+        <v>8026</v>
+      </c>
+      <c r="C1262" s="6" t="s">
         <v>8027</v>
       </c>
-      <c r="C1262" s="6" t="s">
+      <c r="D1262" s="6" t="s">
         <v>8028</v>
-      </c>
-      <c r="D1262" s="6" t="s">
-        <v>8029</v>
       </c>
       <c r="E1262" s="6" t="s">
         <v>8029</v>
       </c>
       <c r="F1262" s="6" t="s">
-        <v>8029</v>
+        <v>8030</v>
       </c>
       <c r="G1262" s="6" t="s">
-        <v>8029</v>
+        <v>8031</v>
       </c>
       <c r="H1262" s="6" t="s">
-        <v>8029</v>
+        <v>8032</v>
       </c>
     </row>
     <row r="1263">
       <c r="B1263" s="5" t="s">
-        <v>8030</v>
+        <v>8033</v>
       </c>
       <c r="C1263" s="5" t="s">
-        <v>8031</v>
+        <v>8034</v>
       </c>
       <c r="D1263" s="5" t="s">
-        <v>8032</v>
+        <v>8035</v>
       </c>
       <c r="E1263" s="5" t="s">
-        <v>8033</v>
+        <v>8035</v>
       </c>
       <c r="F1263" s="5" t="s">
-        <v>8034</v>
+        <v>8035</v>
       </c>
       <c r="G1263" s="5" t="s">
-        <v>8034</v>
+        <v>8035</v>
       </c>
       <c r="H1263" s="5" t="s">
         <v>8035</v>
@@ -56233,102 +56251,102 @@
         <v>8040</v>
       </c>
       <c r="G1264" s="6" t="s">
+        <v>8040</v>
+      </c>
+      <c r="H1264" s="6" t="s">
         <v>8041</v>
-      </c>
-      <c r="H1264" s="6" t="s">
-        <v>8042</v>
       </c>
     </row>
     <row r="1265">
       <c r="B1265" s="5" t="s">
+        <v>8042</v>
+      </c>
+      <c r="C1265" s="5" t="s">
         <v>8043</v>
       </c>
-      <c r="C1265" s="5" t="s">
+      <c r="D1265" s="5" t="s">
         <v>8044</v>
       </c>
-      <c r="D1265" s="5" t="s">
+      <c r="E1265" s="5" t="s">
         <v>8045</v>
       </c>
-      <c r="E1265" s="5" t="s">
+      <c r="F1265" s="5" t="s">
         <v>8046</v>
       </c>
-      <c r="F1265" s="5" t="s">
+      <c r="G1265" s="5" t="s">
         <v>8047</v>
       </c>
-      <c r="G1265" s="5" t="s">
+      <c r="H1265" s="5" t="s">
         <v>8048</v>
-      </c>
-      <c r="H1265" s="5" t="s">
-        <v>8049</v>
       </c>
     </row>
     <row r="1266">
       <c r="B1266" s="6" t="s">
+        <v>8049</v>
+      </c>
+      <c r="C1266" s="6" t="s">
         <v>8050</v>
       </c>
-      <c r="C1266" s="6" t="s">
+      <c r="D1266" s="6" t="s">
         <v>8051</v>
       </c>
-      <c r="D1266" s="6" t="s">
+      <c r="E1266" s="6" t="s">
         <v>8052</v>
       </c>
-      <c r="E1266" s="6" t="s">
+      <c r="F1266" s="6" t="s">
         <v>8053</v>
       </c>
-      <c r="F1266" s="6" t="s">
+      <c r="G1266" s="6" t="s">
         <v>8054</v>
       </c>
-      <c r="G1266" s="6" t="s">
+      <c r="H1266" s="6" t="s">
         <v>8055</v>
-      </c>
-      <c r="H1266" s="6" t="s">
-        <v>8056</v>
       </c>
     </row>
     <row r="1267">
       <c r="B1267" s="5" t="s">
+        <v>8056</v>
+      </c>
+      <c r="C1267" s="5" t="s">
         <v>8057</v>
       </c>
-      <c r="C1267" s="5" t="s">
+      <c r="D1267" s="5" t="s">
         <v>8058</v>
       </c>
-      <c r="D1267" s="5" t="s">
+      <c r="E1267" s="5" t="s">
         <v>8059</v>
       </c>
-      <c r="E1267" s="5" t="s">
-        <v>6245</v>
-      </c>
       <c r="F1267" s="5" t="s">
-        <v>6246</v>
+        <v>8060</v>
       </c>
       <c r="G1267" s="5" t="s">
-        <v>6246</v>
+        <v>8061</v>
       </c>
       <c r="H1267" s="5" t="s">
-        <v>7132</v>
+        <v>8062</v>
       </c>
     </row>
     <row r="1268">
       <c r="B1268" s="6" t="s">
-        <v>8060</v>
+        <v>8063</v>
       </c>
       <c r="C1268" s="6" t="s">
-        <v>8061</v>
+        <v>8064</v>
       </c>
       <c r="D1268" s="6" t="s">
-        <v>8062</v>
+        <v>8065</v>
       </c>
       <c r="E1268" s="6" t="s">
-        <v>8063</v>
+        <v>6245</v>
       </c>
       <c r="F1268" s="6" t="s">
-        <v>8064</v>
+        <v>6246</v>
       </c>
       <c r="G1268" s="6" t="s">
-        <v>8065</v>
+        <v>6246</v>
       </c>
       <c r="H1268" s="6" t="s">
-        <v>8062</v>
+        <v>7138</v>
       </c>
     </row>
     <row r="1269">
@@ -56351,24 +56369,24 @@
         <v>8071</v>
       </c>
       <c r="H1269" s="5" t="s">
-        <v>8072</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="1270">
       <c r="B1270" s="6" t="s">
+        <v>8072</v>
+      </c>
+      <c r="C1270" s="6" t="s">
         <v>8073</v>
       </c>
-      <c r="C1270" s="6" t="s">
+      <c r="D1270" s="6" t="s">
         <v>8074</v>
       </c>
-      <c r="D1270" s="6" t="s">
+      <c r="E1270" s="6" t="s">
         <v>8075</v>
       </c>
-      <c r="E1270" s="6" t="s">
+      <c r="F1270" s="6" t="s">
         <v>8076</v>
-      </c>
-      <c r="F1270" s="6" t="s">
-        <v>8077</v>
       </c>
       <c r="G1270" s="6" t="s">
         <v>8077</v>
@@ -56394,50 +56412,50 @@
         <v>8083</v>
       </c>
       <c r="G1271" s="5" t="s">
+        <v>8083</v>
+      </c>
+      <c r="H1271" s="5" t="s">
         <v>8084</v>
-      </c>
-      <c r="H1271" s="5" t="s">
-        <v>8085</v>
       </c>
     </row>
     <row r="1272">
       <c r="B1272" s="6" t="s">
+        <v>8085</v>
+      </c>
+      <c r="C1272" s="6" t="s">
         <v>8086</v>
       </c>
-      <c r="C1272" s="6" t="s">
+      <c r="D1272" s="6" t="s">
         <v>8087</v>
       </c>
-      <c r="D1272" s="6" t="s">
+      <c r="E1272" s="6" t="s">
         <v>8088</v>
       </c>
-      <c r="E1272" s="6" t="s">
+      <c r="F1272" s="6" t="s">
         <v>8089</v>
       </c>
-      <c r="F1272" s="6" t="s">
+      <c r="G1272" s="6" t="s">
         <v>8090</v>
       </c>
-      <c r="G1272" s="6" t="s">
+      <c r="H1272" s="6" t="s">
         <v>8091</v>
-      </c>
-      <c r="H1272" s="6" t="s">
-        <v>8092</v>
       </c>
     </row>
     <row r="1273">
       <c r="B1273" s="5" t="s">
+        <v>8092</v>
+      </c>
+      <c r="C1273" s="5" t="s">
         <v>8093</v>
       </c>
-      <c r="C1273" s="5" t="s">
+      <c r="D1273" s="5" t="s">
         <v>8094</v>
       </c>
-      <c r="D1273" s="5" t="s">
+      <c r="E1273" s="5" t="s">
         <v>8095</v>
       </c>
-      <c r="E1273" s="5" t="s">
+      <c r="F1273" s="5" t="s">
         <v>8096</v>
-      </c>
-      <c r="F1273" s="5" t="s">
-        <v>8097</v>
       </c>
       <c r="G1273" s="5" t="s">
         <v>8097</v>
@@ -56509,50 +56527,50 @@
         <v>8115</v>
       </c>
       <c r="G1276" s="6" t="s">
+        <v>8115</v>
+      </c>
+      <c r="H1276" s="6" t="s">
         <v>8116</v>
-      </c>
-      <c r="H1276" s="6" t="s">
-        <v>8117</v>
       </c>
     </row>
     <row r="1277">
       <c r="B1277" s="5" t="s">
+        <v>8117</v>
+      </c>
+      <c r="C1277" s="5" t="s">
         <v>8118</v>
       </c>
-      <c r="C1277" s="5" t="s">
+      <c r="D1277" s="5" t="s">
         <v>8119</v>
       </c>
-      <c r="D1277" s="5" t="s">
+      <c r="E1277" s="5" t="s">
         <v>8120</v>
       </c>
-      <c r="E1277" s="5" t="s">
+      <c r="F1277" s="5" t="s">
         <v>8121</v>
       </c>
-      <c r="F1277" s="5" t="s">
+      <c r="G1277" s="5" t="s">
         <v>8122</v>
       </c>
-      <c r="G1277" s="5" t="s">
+      <c r="H1277" s="5" t="s">
         <v>8123</v>
-      </c>
-      <c r="H1277" s="5" t="s">
-        <v>8124</v>
       </c>
     </row>
     <row r="1278">
       <c r="B1278" s="6" t="s">
+        <v>8124</v>
+      </c>
+      <c r="C1278" s="6" t="s">
         <v>8125</v>
       </c>
-      <c r="C1278" s="6" t="s">
+      <c r="D1278" s="6" t="s">
         <v>8126</v>
       </c>
-      <c r="D1278" s="6" t="s">
+      <c r="E1278" s="6" t="s">
         <v>8127</v>
       </c>
-      <c r="E1278" s="6" t="s">
+      <c r="F1278" s="6" t="s">
         <v>8128</v>
-      </c>
-      <c r="F1278" s="6" t="s">
-        <v>8129</v>
       </c>
       <c r="G1278" s="6" t="s">
         <v>8129</v>
@@ -56578,27 +56596,27 @@
         <v>8135</v>
       </c>
       <c r="G1279" s="5" t="s">
+        <v>8135</v>
+      </c>
+      <c r="H1279" s="5" t="s">
         <v>8136</v>
-      </c>
-      <c r="H1279" s="5" t="s">
-        <v>8137</v>
       </c>
     </row>
     <row r="1280">
       <c r="B1280" s="6" t="s">
+        <v>8137</v>
+      </c>
+      <c r="C1280" s="6" t="s">
         <v>8138</v>
       </c>
-      <c r="C1280" s="6" t="s">
+      <c r="D1280" s="6" t="s">
         <v>8139</v>
       </c>
-      <c r="D1280" s="6" t="s">
+      <c r="E1280" s="6" t="s">
         <v>8140</v>
       </c>
-      <c r="E1280" s="6" t="s">
+      <c r="F1280" s="6" t="s">
         <v>8141</v>
-      </c>
-      <c r="F1280" s="6" t="s">
-        <v>8142</v>
       </c>
       <c r="G1280" s="6" t="s">
         <v>8142</v>
@@ -56624,27 +56642,27 @@
         <v>8148</v>
       </c>
       <c r="G1281" s="5" t="s">
+        <v>8148</v>
+      </c>
+      <c r="H1281" s="5" t="s">
         <v>8149</v>
-      </c>
-      <c r="H1281" s="5" t="s">
-        <v>8150</v>
       </c>
     </row>
     <row r="1282">
       <c r="B1282" s="6" t="s">
+        <v>8150</v>
+      </c>
+      <c r="C1282" s="6" t="s">
         <v>8151</v>
       </c>
-      <c r="C1282" s="6" t="s">
+      <c r="D1282" s="6" t="s">
         <v>8152</v>
       </c>
-      <c r="D1282" s="6" t="s">
+      <c r="E1282" s="6" t="s">
         <v>8153</v>
       </c>
-      <c r="E1282" s="6" t="s">
+      <c r="F1282" s="6" t="s">
         <v>8154</v>
-      </c>
-      <c r="F1282" s="6" t="s">
-        <v>8155</v>
       </c>
       <c r="G1282" s="6" t="s">
         <v>8155</v>
@@ -56684,42 +56702,42 @@
         <v>8164</v>
       </c>
       <c r="D1284" s="6" t="s">
-        <v>2758</v>
+        <v>8165</v>
       </c>
       <c r="E1284" s="6" t="s">
-        <v>2759</v>
+        <v>8166</v>
       </c>
       <c r="F1284" s="6" t="s">
-        <v>2760</v>
+        <v>8167</v>
       </c>
       <c r="G1284" s="6" t="s">
-        <v>2760</v>
+        <v>8167</v>
       </c>
       <c r="H1284" s="6" t="s">
-        <v>2761</v>
+        <v>8168</v>
       </c>
     </row>
     <row r="1285">
       <c r="B1285" s="5" t="s">
-        <v>8165</v>
+        <v>8169</v>
       </c>
       <c r="C1285" s="5" t="s">
-        <v>8166</v>
+        <v>8170</v>
       </c>
       <c r="D1285" s="5" t="s">
-        <v>8167</v>
+        <v>2758</v>
       </c>
       <c r="E1285" s="5" t="s">
-        <v>8168</v>
+        <v>2759</v>
       </c>
       <c r="F1285" s="5" t="s">
-        <v>8169</v>
+        <v>2760</v>
       </c>
       <c r="G1285" s="5" t="s">
-        <v>8169</v>
+        <v>2760</v>
       </c>
       <c r="H1285" s="5" t="s">
-        <v>8170</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="1286">
@@ -56739,7 +56757,7 @@
         <v>8175</v>
       </c>
       <c r="G1286" s="6" t="s">
-        <v>8174</v>
+        <v>8175</v>
       </c>
       <c r="H1286" s="6" t="s">
         <v>8176</v>
@@ -56762,27 +56780,27 @@
         <v>8181</v>
       </c>
       <c r="G1287" s="5" t="s">
+        <v>8180</v>
+      </c>
+      <c r="H1287" s="5" t="s">
         <v>8182</v>
-      </c>
-      <c r="H1287" s="5" t="s">
-        <v>8183</v>
       </c>
     </row>
     <row r="1288">
       <c r="B1288" s="6" t="s">
+        <v>8183</v>
+      </c>
+      <c r="C1288" s="6" t="s">
         <v>8184</v>
       </c>
-      <c r="C1288" s="6" t="s">
+      <c r="D1288" s="6" t="s">
         <v>8185</v>
       </c>
-      <c r="D1288" s="6" t="s">
+      <c r="E1288" s="6" t="s">
         <v>8186</v>
       </c>
-      <c r="E1288" s="6" t="s">
+      <c r="F1288" s="6" t="s">
         <v>8187</v>
-      </c>
-      <c r="F1288" s="6" t="s">
-        <v>8188</v>
       </c>
       <c r="G1288" s="6" t="s">
         <v>8188</v>
@@ -56831,188 +56849,188 @@
         <v>8200</v>
       </c>
       <c r="G1290" s="6" t="s">
+        <v>8200</v>
+      </c>
+      <c r="H1290" s="6" t="s">
         <v>8201</v>
-      </c>
-      <c r="H1290" s="6" t="s">
-        <v>8202</v>
       </c>
     </row>
     <row r="1291">
       <c r="B1291" s="5" t="s">
+        <v>8202</v>
+      </c>
+      <c r="C1291" s="5" t="s">
         <v>8203</v>
       </c>
-      <c r="C1291" s="5" t="s">
+      <c r="D1291" s="5" t="s">
         <v>8204</v>
       </c>
-      <c r="D1291" s="5" t="s">
+      <c r="E1291" s="5" t="s">
         <v>8205</v>
       </c>
-      <c r="E1291" s="5" t="s">
+      <c r="F1291" s="5" t="s">
         <v>8206</v>
       </c>
-      <c r="F1291" s="5" t="s">
+      <c r="G1291" s="5" t="s">
         <v>8207</v>
       </c>
-      <c r="G1291" s="5" t="s">
+      <c r="H1291" s="5" t="s">
         <v>8208</v>
-      </c>
-      <c r="H1291" s="5" t="s">
-        <v>8209</v>
       </c>
     </row>
     <row r="1292">
       <c r="B1292" s="6" t="s">
+        <v>8209</v>
+      </c>
+      <c r="C1292" s="6" t="s">
         <v>8210</v>
       </c>
-      <c r="C1292" s="6" t="s">
+      <c r="D1292" s="6" t="s">
         <v>8211</v>
       </c>
-      <c r="D1292" s="6" t="s">
+      <c r="E1292" s="6" t="s">
         <v>8212</v>
       </c>
-      <c r="E1292" s="6" t="s">
+      <c r="F1292" s="6" t="s">
         <v>8213</v>
       </c>
-      <c r="F1292" s="6" t="s">
+      <c r="G1292" s="6" t="s">
         <v>8214</v>
       </c>
-      <c r="G1292" s="6" t="s">
+      <c r="H1292" s="6" t="s">
         <v>8215</v>
-      </c>
-      <c r="H1292" s="6" t="s">
-        <v>8216</v>
       </c>
     </row>
     <row r="1293">
       <c r="B1293" s="5" t="s">
+        <v>8216</v>
+      </c>
+      <c r="C1293" s="5" t="s">
         <v>8217</v>
-      </c>
-      <c r="C1293" s="5" t="s">
-        <v>7088</v>
       </c>
       <c r="D1293" s="5" t="s">
         <v>8218</v>
       </c>
       <c r="E1293" s="5" t="s">
-        <v>7089</v>
+        <v>8219</v>
       </c>
       <c r="F1293" s="5" t="s">
-        <v>7090</v>
+        <v>8220</v>
       </c>
       <c r="G1293" s="5" t="s">
-        <v>7091</v>
+        <v>8221</v>
       </c>
       <c r="H1293" s="5" t="s">
-        <v>8218</v>
+        <v>8222</v>
       </c>
     </row>
     <row r="1294">
       <c r="B1294" s="6" t="s">
-        <v>8219</v>
+        <v>8223</v>
       </c>
       <c r="C1294" s="6" t="s">
-        <v>6888</v>
+        <v>7094</v>
       </c>
       <c r="D1294" s="6" t="s">
-        <v>8220</v>
+        <v>8224</v>
       </c>
       <c r="E1294" s="6" t="s">
-        <v>6890</v>
+        <v>7095</v>
       </c>
       <c r="F1294" s="6" t="s">
-        <v>8221</v>
+        <v>7096</v>
       </c>
       <c r="G1294" s="6" t="s">
-        <v>8222</v>
+        <v>7097</v>
       </c>
       <c r="H1294" s="6" t="s">
-        <v>8223</v>
+        <v>8224</v>
       </c>
     </row>
     <row r="1295">
       <c r="B1295" s="5" t="s">
-        <v>8224</v>
+        <v>8225</v>
       </c>
       <c r="C1295" s="5" t="s">
-        <v>8225</v>
+        <v>6888</v>
       </c>
       <c r="D1295" s="5" t="s">
         <v>8226</v>
       </c>
       <c r="E1295" s="5" t="s">
+        <v>6890</v>
+      </c>
+      <c r="F1295" s="5" t="s">
         <v>8227</v>
       </c>
-      <c r="F1295" s="5" t="s">
+      <c r="G1295" s="5" t="s">
         <v>8228</v>
       </c>
-      <c r="G1295" s="5" t="s">
+      <c r="H1295" s="5" t="s">
         <v>8229</v>
-      </c>
-      <c r="H1295" s="5" t="s">
-        <v>8230</v>
       </c>
     </row>
     <row r="1296">
       <c r="B1296" s="6" t="s">
+        <v>8230</v>
+      </c>
+      <c r="C1296" s="6" t="s">
         <v>8231</v>
       </c>
-      <c r="C1296" s="6" t="s">
+      <c r="D1296" s="6" t="s">
         <v>8232</v>
       </c>
-      <c r="D1296" s="6" t="s">
+      <c r="E1296" s="6" t="s">
         <v>8233</v>
       </c>
-      <c r="E1296" s="6" t="s">
-        <v>8206</v>
-      </c>
       <c r="F1296" s="6" t="s">
-        <v>8207</v>
+        <v>8234</v>
       </c>
       <c r="G1296" s="6" t="s">
-        <v>8208</v>
+        <v>8235</v>
       </c>
       <c r="H1296" s="6" t="s">
-        <v>8234</v>
+        <v>8236</v>
       </c>
     </row>
     <row r="1297">
       <c r="B1297" s="5" t="s">
-        <v>8235</v>
+        <v>8237</v>
       </c>
       <c r="C1297" s="5" t="s">
-        <v>8236</v>
+        <v>8238</v>
       </c>
       <c r="D1297" s="5" t="s">
-        <v>8237</v>
+        <v>8239</v>
       </c>
       <c r="E1297" s="5" t="s">
-        <v>8238</v>
+        <v>8212</v>
       </c>
       <c r="F1297" s="5" t="s">
-        <v>8239</v>
+        <v>8213</v>
       </c>
       <c r="G1297" s="5" t="s">
+        <v>8214</v>
+      </c>
+      <c r="H1297" s="5" t="s">
         <v>8240</v>
-      </c>
-      <c r="H1297" s="5" t="s">
-        <v>8241</v>
       </c>
     </row>
     <row r="1298">
       <c r="B1298" s="6" t="s">
+        <v>8241</v>
+      </c>
+      <c r="C1298" s="6" t="s">
         <v>8242</v>
       </c>
-      <c r="C1298" s="6" t="s">
+      <c r="D1298" s="6" t="s">
         <v>8243</v>
       </c>
-      <c r="D1298" s="6" t="s">
+      <c r="E1298" s="6" t="s">
         <v>8244</v>
       </c>
-      <c r="E1298" s="6" t="s">
+      <c r="F1298" s="6" t="s">
         <v>8245</v>
-      </c>
-      <c r="F1298" s="6" t="s">
-        <v>8246</v>
       </c>
       <c r="G1298" s="6" t="s">
         <v>8246</v>
@@ -57038,487 +57056,487 @@
         <v>8252</v>
       </c>
       <c r="G1299" s="5" t="s">
+        <v>8252</v>
+      </c>
+      <c r="H1299" s="5" t="s">
         <v>8253</v>
-      </c>
-      <c r="H1299" s="5" t="s">
-        <v>8254</v>
       </c>
     </row>
     <row r="1300">
       <c r="B1300" s="6" t="s">
+        <v>8254</v>
+      </c>
+      <c r="C1300" s="6" t="s">
         <v>8255</v>
       </c>
-      <c r="C1300" s="6" t="s">
+      <c r="D1300" s="6" t="s">
         <v>8256</v>
       </c>
-      <c r="D1300" s="6" t="s">
+      <c r="E1300" s="6" t="s">
         <v>8257</v>
       </c>
-      <c r="E1300" s="6" t="s">
+      <c r="F1300" s="6" t="s">
         <v>8258</v>
       </c>
-      <c r="F1300" s="6" t="s">
+      <c r="G1300" s="6" t="s">
         <v>8259</v>
       </c>
-      <c r="G1300" s="6" t="s">
+      <c r="H1300" s="6" t="s">
         <v>8260</v>
-      </c>
-      <c r="H1300" s="6" t="s">
-        <v>8261</v>
       </c>
     </row>
     <row r="1301">
       <c r="B1301" s="5" t="s">
+        <v>8261</v>
+      </c>
+      <c r="C1301" s="5" t="s">
         <v>8262</v>
       </c>
-      <c r="C1301" s="5" t="s">
+      <c r="D1301" s="5" t="s">
         <v>8263</v>
       </c>
-      <c r="D1301" s="5" t="s">
+      <c r="E1301" s="5" t="s">
         <v>8264</v>
       </c>
-      <c r="E1301" s="5" t="s">
+      <c r="F1301" s="5" t="s">
         <v>8265</v>
       </c>
-      <c r="F1301" s="5" t="s">
-        <v>7438</v>
-      </c>
       <c r="G1301" s="5" t="s">
-        <v>7439</v>
+        <v>8266</v>
       </c>
       <c r="H1301" s="5" t="s">
-        <v>8266</v>
+        <v>8267</v>
       </c>
     </row>
     <row r="1302">
       <c r="B1302" s="6" t="s">
-        <v>8267</v>
+        <v>8268</v>
       </c>
       <c r="C1302" s="6" t="s">
-        <v>8268</v>
+        <v>8269</v>
       </c>
       <c r="D1302" s="6" t="s">
-        <v>8269</v>
+        <v>8270</v>
       </c>
       <c r="E1302" s="6" t="s">
-        <v>8270</v>
+        <v>8271</v>
       </c>
       <c r="F1302" s="6" t="s">
-        <v>8271</v>
+        <v>7444</v>
       </c>
       <c r="G1302" s="6" t="s">
+        <v>7445</v>
+      </c>
+      <c r="H1302" s="6" t="s">
         <v>8272</v>
-      </c>
-      <c r="H1302" s="6" t="s">
-        <v>8273</v>
       </c>
     </row>
     <row r="1303">
       <c r="B1303" s="5" t="s">
+        <v>8273</v>
+      </c>
+      <c r="C1303" s="5" t="s">
         <v>8274</v>
       </c>
-      <c r="C1303" s="5" t="s">
+      <c r="D1303" s="5" t="s">
         <v>8275</v>
       </c>
-      <c r="D1303" s="5" t="s">
+      <c r="E1303" s="5" t="s">
         <v>8276</v>
       </c>
-      <c r="E1303" s="5" t="s">
+      <c r="F1303" s="5" t="s">
         <v>8277</v>
       </c>
-      <c r="F1303" s="5" t="s">
+      <c r="G1303" s="5" t="s">
         <v>8278</v>
       </c>
-      <c r="G1303" s="5" t="s">
-        <v>8277</v>
-      </c>
       <c r="H1303" s="5" t="s">
-        <v>8276</v>
+        <v>8279</v>
       </c>
     </row>
     <row r="1304">
       <c r="B1304" s="6" t="s">
-        <v>8279</v>
+        <v>8280</v>
       </c>
       <c r="C1304" s="6" t="s">
-        <v>6033</v>
+        <v>8281</v>
       </c>
       <c r="D1304" s="6" t="s">
-        <v>8005</v>
+        <v>8282</v>
       </c>
       <c r="E1304" s="6" t="s">
-        <v>6035</v>
+        <v>8283</v>
       </c>
       <c r="F1304" s="6" t="s">
-        <v>8006</v>
+        <v>8284</v>
       </c>
       <c r="G1304" s="6" t="s">
-        <v>8006</v>
+        <v>8283</v>
       </c>
       <c r="H1304" s="6" t="s">
-        <v>5404</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="1305">
       <c r="B1305" s="5" t="s">
-        <v>8280</v>
+        <v>8285</v>
       </c>
       <c r="C1305" s="5" t="s">
-        <v>6080</v>
+        <v>6033</v>
       </c>
       <c r="D1305" s="5" t="s">
-        <v>8281</v>
+        <v>8011</v>
       </c>
       <c r="E1305" s="5" t="s">
-        <v>6082</v>
+        <v>6035</v>
       </c>
       <c r="F1305" s="5" t="s">
-        <v>8282</v>
+        <v>8012</v>
       </c>
       <c r="G1305" s="5" t="s">
-        <v>8283</v>
+        <v>8012</v>
       </c>
       <c r="H1305" s="5" t="s">
-        <v>8284</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1306">
       <c r="B1306" s="6" t="s">
-        <v>8285</v>
+        <v>8286</v>
       </c>
       <c r="C1306" s="6" t="s">
-        <v>7068</v>
+        <v>6080</v>
       </c>
       <c r="D1306" s="6" t="s">
-        <v>8286</v>
+        <v>8287</v>
       </c>
       <c r="E1306" s="6" t="s">
-        <v>7070</v>
+        <v>6082</v>
       </c>
       <c r="F1306" s="6" t="s">
-        <v>6016</v>
+        <v>8288</v>
       </c>
       <c r="G1306" s="6" t="s">
-        <v>6017</v>
+        <v>8289</v>
       </c>
       <c r="H1306" s="6" t="s">
-        <v>7069</v>
+        <v>8290</v>
       </c>
     </row>
     <row r="1307">
       <c r="B1307" s="5" t="s">
-        <v>8287</v>
+        <v>8291</v>
       </c>
       <c r="C1307" s="5" t="s">
         <v>7074</v>
       </c>
       <c r="D1307" s="5" t="s">
-        <v>8288</v>
+        <v>8292</v>
       </c>
       <c r="E1307" s="5" t="s">
         <v>7076</v>
       </c>
       <c r="F1307" s="5" t="s">
-        <v>6023</v>
+        <v>6016</v>
       </c>
       <c r="G1307" s="5" t="s">
-        <v>6023</v>
+        <v>6017</v>
       </c>
       <c r="H1307" s="5" t="s">
-        <v>8289</v>
+        <v>7075</v>
       </c>
     </row>
     <row r="1308">
       <c r="B1308" s="6" t="s">
-        <v>8290</v>
+        <v>8293</v>
       </c>
       <c r="C1308" s="6" t="s">
-        <v>7079</v>
+        <v>7080</v>
       </c>
       <c r="D1308" s="6" t="s">
-        <v>8291</v>
+        <v>8294</v>
       </c>
       <c r="E1308" s="6" t="s">
-        <v>7081</v>
+        <v>7082</v>
       </c>
       <c r="F1308" s="6" t="s">
-        <v>6029</v>
+        <v>6023</v>
       </c>
       <c r="G1308" s="6" t="s">
-        <v>6030</v>
+        <v>6023</v>
       </c>
       <c r="H1308" s="6" t="s">
-        <v>7084</v>
+        <v>8295</v>
       </c>
     </row>
     <row r="1309">
       <c r="B1309" s="5" t="s">
-        <v>8292</v>
+        <v>8296</v>
       </c>
       <c r="C1309" s="5" t="s">
-        <v>6046</v>
+        <v>7085</v>
       </c>
       <c r="D1309" s="5" t="s">
-        <v>8293</v>
+        <v>8297</v>
       </c>
       <c r="E1309" s="5" t="s">
-        <v>6048</v>
+        <v>7087</v>
       </c>
       <c r="F1309" s="5" t="s">
-        <v>6049</v>
+        <v>6029</v>
       </c>
       <c r="G1309" s="5" t="s">
-        <v>6050</v>
+        <v>6030</v>
       </c>
       <c r="H1309" s="5" t="s">
-        <v>8294</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="1310">
       <c r="B1310" s="6" t="s">
-        <v>8295</v>
+        <v>8298</v>
       </c>
       <c r="C1310" s="6" t="s">
-        <v>8296</v>
+        <v>6046</v>
       </c>
       <c r="D1310" s="6" t="s">
-        <v>8297</v>
+        <v>8299</v>
       </c>
       <c r="E1310" s="6" t="s">
-        <v>6076</v>
+        <v>6048</v>
       </c>
       <c r="F1310" s="6" t="s">
-        <v>8298</v>
+        <v>6049</v>
       </c>
       <c r="G1310" s="6" t="s">
-        <v>8299</v>
+        <v>6050</v>
       </c>
       <c r="H1310" s="6" t="s">
-        <v>7066</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="1311">
       <c r="B1311" s="5" t="s">
-        <v>8300</v>
+        <v>8301</v>
       </c>
       <c r="C1311" s="5" t="s">
-        <v>7052</v>
+        <v>8302</v>
       </c>
       <c r="D1311" s="5" t="s">
-        <v>8301</v>
+        <v>8303</v>
       </c>
       <c r="E1311" s="5" t="s">
-        <v>7054</v>
+        <v>6076</v>
       </c>
       <c r="F1311" s="5" t="s">
-        <v>8302</v>
+        <v>8304</v>
       </c>
       <c r="G1311" s="5" t="s">
-        <v>8302</v>
+        <v>8305</v>
       </c>
       <c r="H1311" s="5" t="s">
-        <v>8303</v>
+        <v>7072</v>
       </c>
     </row>
     <row r="1312">
       <c r="B1312" s="6" t="s">
-        <v>8304</v>
+        <v>8306</v>
       </c>
       <c r="C1312" s="6" t="s">
-        <v>8305</v>
+        <v>7058</v>
       </c>
       <c r="D1312" s="6" t="s">
-        <v>8306</v>
+        <v>8307</v>
       </c>
       <c r="E1312" s="6" t="s">
-        <v>8307</v>
+        <v>7060</v>
       </c>
       <c r="F1312" s="6" t="s">
         <v>8308</v>
       </c>
       <c r="G1312" s="6" t="s">
+        <v>8308</v>
+      </c>
+      <c r="H1312" s="6" t="s">
         <v>8309</v>
-      </c>
-      <c r="H1312" s="6" t="s">
-        <v>8310</v>
       </c>
     </row>
     <row r="1313">
       <c r="B1313" s="5" t="s">
+        <v>8310</v>
+      </c>
+      <c r="C1313" s="5" t="s">
         <v>8311</v>
       </c>
-      <c r="C1313" s="5" t="s">
-        <v>8197</v>
-      </c>
       <c r="D1313" s="5" t="s">
-        <v>8198</v>
+        <v>8312</v>
       </c>
       <c r="E1313" s="5" t="s">
-        <v>8199</v>
+        <v>8313</v>
       </c>
       <c r="F1313" s="5" t="s">
-        <v>8200</v>
+        <v>8314</v>
       </c>
       <c r="G1313" s="5" t="s">
-        <v>8201</v>
+        <v>8315</v>
       </c>
       <c r="H1313" s="5" t="s">
-        <v>8202</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="1314">
       <c r="B1314" s="6" t="s">
-        <v>8312</v>
+        <v>8317</v>
       </c>
       <c r="C1314" s="6" t="s">
-        <v>8313</v>
+        <v>8203</v>
       </c>
       <c r="D1314" s="6" t="s">
-        <v>8314</v>
+        <v>8204</v>
       </c>
       <c r="E1314" s="6" t="s">
-        <v>8315</v>
+        <v>8205</v>
       </c>
       <c r="F1314" s="6" t="s">
-        <v>8316</v>
+        <v>8206</v>
       </c>
       <c r="G1314" s="6" t="s">
-        <v>8317</v>
+        <v>8207</v>
       </c>
       <c r="H1314" s="6" t="s">
-        <v>8318</v>
+        <v>8208</v>
       </c>
     </row>
     <row r="1315">
       <c r="B1315" s="5" t="s">
+        <v>8318</v>
+      </c>
+      <c r="C1315" s="5" t="s">
         <v>8319</v>
       </c>
-      <c r="C1315" s="5" t="s">
+      <c r="D1315" s="5" t="s">
         <v>8320</v>
       </c>
-      <c r="D1315" s="5" t="s">
+      <c r="E1315" s="5" t="s">
         <v>8321</v>
       </c>
-      <c r="E1315" s="5" t="s">
+      <c r="F1315" s="5" t="s">
         <v>8322</v>
       </c>
-      <c r="F1315" s="5" t="s">
+      <c r="G1315" s="5" t="s">
         <v>8323</v>
       </c>
-      <c r="G1315" s="5" t="s">
+      <c r="H1315" s="5" t="s">
         <v>8324</v>
-      </c>
-      <c r="H1315" s="5" t="s">
-        <v>8325</v>
       </c>
     </row>
     <row r="1316">
       <c r="B1316" s="6" t="s">
+        <v>8325</v>
+      </c>
+      <c r="C1316" s="6" t="s">
         <v>8326</v>
       </c>
-      <c r="C1316" s="6" t="s">
+      <c r="D1316" s="6" t="s">
         <v>8327</v>
       </c>
-      <c r="D1316" s="6" t="s">
+      <c r="E1316" s="6" t="s">
         <v>8328</v>
       </c>
-      <c r="E1316" s="6" t="s">
+      <c r="F1316" s="6" t="s">
         <v>8329</v>
       </c>
-      <c r="F1316" s="6" t="s">
+      <c r="G1316" s="6" t="s">
         <v>8330</v>
       </c>
-      <c r="G1316" s="6" t="s">
+      <c r="H1316" s="6" t="s">
         <v>8331</v>
-      </c>
-      <c r="H1316" s="6" t="s">
-        <v>8332</v>
       </c>
     </row>
     <row r="1317">
       <c r="B1317" s="5" t="s">
+        <v>8332</v>
+      </c>
+      <c r="C1317" s="5" t="s">
         <v>8333</v>
       </c>
-      <c r="C1317" s="5" t="s">
+      <c r="D1317" s="5" t="s">
         <v>8334</v>
       </c>
-      <c r="D1317" s="5" t="s">
+      <c r="E1317" s="5" t="s">
         <v>8335</v>
       </c>
-      <c r="E1317" s="5" t="s">
+      <c r="F1317" s="5" t="s">
         <v>8336</v>
       </c>
-      <c r="F1317" s="5" t="s">
+      <c r="G1317" s="5" t="s">
         <v>8337</v>
       </c>
-      <c r="G1317" s="5" t="s">
+      <c r="H1317" s="5" t="s">
         <v>8338</v>
-      </c>
-      <c r="H1317" s="5" t="s">
-        <v>8339</v>
       </c>
     </row>
     <row r="1318">
       <c r="B1318" s="6" t="s">
+        <v>8339</v>
+      </c>
+      <c r="C1318" s="6" t="s">
         <v>8340</v>
       </c>
-      <c r="C1318" s="6" t="s">
+      <c r="D1318" s="6" t="s">
         <v>8341</v>
       </c>
-      <c r="D1318" s="6" t="s">
+      <c r="E1318" s="6" t="s">
         <v>8342</v>
       </c>
-      <c r="E1318" s="6" t="s">
+      <c r="F1318" s="6" t="s">
         <v>8343</v>
       </c>
-      <c r="F1318" s="6" t="s">
+      <c r="G1318" s="6" t="s">
         <v>8344</v>
       </c>
-      <c r="G1318" s="6" t="s">
+      <c r="H1318" s="6" t="s">
         <v>8345</v>
-      </c>
-      <c r="H1318" s="6" t="s">
-        <v>8346</v>
       </c>
     </row>
     <row r="1319">
       <c r="B1319" s="5" t="s">
+        <v>8346</v>
+      </c>
+      <c r="C1319" s="5" t="s">
         <v>8347</v>
       </c>
-      <c r="C1319" s="5" t="s">
+      <c r="D1319" s="5" t="s">
         <v>8348</v>
       </c>
-      <c r="D1319" s="5" t="s">
+      <c r="E1319" s="5" t="s">
         <v>8349</v>
       </c>
-      <c r="E1319" s="5" t="s">
+      <c r="F1319" s="5" t="s">
         <v>8350</v>
       </c>
-      <c r="F1319" s="5" t="s">
+      <c r="G1319" s="5" t="s">
         <v>8351</v>
       </c>
-      <c r="G1319" s="5" t="s">
+      <c r="H1319" s="5" t="s">
         <v>8352</v>
-      </c>
-      <c r="H1319" s="5" t="s">
-        <v>8353</v>
       </c>
     </row>
     <row r="1320">
       <c r="B1320" s="6" t="s">
+        <v>8353</v>
+      </c>
+      <c r="C1320" s="6" t="s">
         <v>8354</v>
       </c>
-      <c r="C1320" s="6" t="s">
+      <c r="D1320" s="6" t="s">
         <v>8355</v>
       </c>
-      <c r="D1320" s="6" t="s">
+      <c r="E1320" s="6" t="s">
         <v>8356</v>
       </c>
-      <c r="E1320" s="6" t="s">
+      <c r="F1320" s="6" t="s">
         <v>8357</v>
-      </c>
-      <c r="F1320" s="6" t="s">
-        <v>8358</v>
       </c>
       <c r="G1320" s="6" t="s">
         <v>8358</v>
@@ -57544,234 +57562,234 @@
         <v>8364</v>
       </c>
       <c r="G1321" s="5" t="s">
+        <v>8364</v>
+      </c>
+      <c r="H1321" s="5" t="s">
         <v>8365</v>
-      </c>
-      <c r="H1321" s="5" t="s">
-        <v>8366</v>
       </c>
     </row>
     <row r="1322">
       <c r="B1322" s="6" t="s">
+        <v>8366</v>
+      </c>
+      <c r="C1322" s="6" t="s">
         <v>8367</v>
       </c>
-      <c r="C1322" s="6" t="s">
+      <c r="D1322" s="6" t="s">
         <v>8368</v>
       </c>
-      <c r="D1322" s="6" t="s">
+      <c r="E1322" s="6" t="s">
         <v>8369</v>
       </c>
-      <c r="E1322" s="6" t="s">
+      <c r="F1322" s="6" t="s">
         <v>8370</v>
       </c>
-      <c r="F1322" s="6" t="s">
+      <c r="G1322" s="6" t="s">
         <v>8371</v>
       </c>
-      <c r="G1322" s="6" t="s">
+      <c r="H1322" s="6" t="s">
         <v>8372</v>
-      </c>
-      <c r="H1322" s="6" t="s">
-        <v>8373</v>
       </c>
     </row>
     <row r="1323">
       <c r="B1323" s="5" t="s">
+        <v>8373</v>
+      </c>
+      <c r="C1323" s="5" t="s">
         <v>8374</v>
       </c>
-      <c r="C1323" s="5" t="s">
+      <c r="D1323" s="5" t="s">
         <v>8375</v>
       </c>
-      <c r="D1323" s="5" t="s">
+      <c r="E1323" s="5" t="s">
         <v>8376</v>
       </c>
-      <c r="E1323" s="5" t="s">
+      <c r="F1323" s="5" t="s">
         <v>8377</v>
       </c>
-      <c r="F1323" s="5" t="s">
+      <c r="G1323" s="5" t="s">
         <v>8378</v>
       </c>
-      <c r="G1323" s="5" t="s">
+      <c r="H1323" s="5" t="s">
         <v>8379</v>
-      </c>
-      <c r="H1323" s="5" t="s">
-        <v>8380</v>
       </c>
     </row>
     <row r="1324">
       <c r="B1324" s="6" t="s">
+        <v>8380</v>
+      </c>
+      <c r="C1324" s="6" t="s">
         <v>8381</v>
       </c>
-      <c r="C1324" s="6" t="s">
+      <c r="D1324" s="6" t="s">
         <v>8382</v>
       </c>
-      <c r="D1324" s="6" t="s">
+      <c r="E1324" s="6" t="s">
         <v>8383</v>
       </c>
-      <c r="E1324" s="6" t="s">
+      <c r="F1324" s="6" t="s">
         <v>8384</v>
       </c>
-      <c r="F1324" s="6" t="s">
+      <c r="G1324" s="6" t="s">
         <v>8385</v>
       </c>
-      <c r="G1324" s="6" t="s">
+      <c r="H1324" s="6" t="s">
         <v>8386</v>
-      </c>
-      <c r="H1324" s="6" t="s">
-        <v>8387</v>
       </c>
     </row>
     <row r="1325">
       <c r="B1325" s="5" t="s">
+        <v>8387</v>
+      </c>
+      <c r="C1325" s="5" t="s">
         <v>8388</v>
       </c>
-      <c r="C1325" s="5" t="s">
+      <c r="D1325" s="5" t="s">
         <v>8389</v>
       </c>
-      <c r="D1325" s="5" t="s">
+      <c r="E1325" s="5" t="s">
         <v>8390</v>
       </c>
-      <c r="E1325" s="5" t="s">
+      <c r="F1325" s="5" t="s">
         <v>8391</v>
       </c>
-      <c r="F1325" s="5" t="s">
+      <c r="G1325" s="5" t="s">
         <v>8392</v>
       </c>
-      <c r="G1325" s="5" t="s">
+      <c r="H1325" s="5" t="s">
         <v>8393</v>
-      </c>
-      <c r="H1325" s="5" t="s">
-        <v>8394</v>
       </c>
     </row>
     <row r="1326">
       <c r="B1326" s="6" t="s">
+        <v>8394</v>
+      </c>
+      <c r="C1326" s="6" t="s">
         <v>8395</v>
       </c>
-      <c r="C1326" s="6" t="s">
+      <c r="D1326" s="6" t="s">
         <v>8396</v>
       </c>
-      <c r="D1326" s="6" t="s">
+      <c r="E1326" s="6" t="s">
         <v>8397</v>
       </c>
-      <c r="E1326" s="6" t="s">
+      <c r="F1326" s="6" t="s">
         <v>8398</v>
       </c>
-      <c r="F1326" s="6" t="s">
+      <c r="G1326" s="6" t="s">
         <v>8399</v>
       </c>
-      <c r="G1326" s="6" t="s">
+      <c r="H1326" s="6" t="s">
         <v>8400</v>
-      </c>
-      <c r="H1326" s="6" t="s">
-        <v>8401</v>
       </c>
     </row>
     <row r="1327">
       <c r="B1327" s="5" t="s">
+        <v>8401</v>
+      </c>
+      <c r="C1327" s="5" t="s">
         <v>8402</v>
       </c>
-      <c r="C1327" s="5" t="s">
+      <c r="D1327" s="5" t="s">
         <v>8403</v>
       </c>
-      <c r="D1327" s="5" t="s">
+      <c r="E1327" s="5" t="s">
         <v>8404</v>
       </c>
-      <c r="E1327" s="5" t="s">
+      <c r="F1327" s="5" t="s">
         <v>8405</v>
       </c>
-      <c r="F1327" s="5" t="s">
+      <c r="G1327" s="5" t="s">
         <v>8406</v>
       </c>
-      <c r="G1327" s="5" t="s">
+      <c r="H1327" s="5" t="s">
         <v>8407</v>
-      </c>
-      <c r="H1327" s="5" t="s">
-        <v>8408</v>
       </c>
     </row>
     <row r="1328">
       <c r="B1328" s="6" t="s">
+        <v>8408</v>
+      </c>
+      <c r="C1328" s="6" t="s">
         <v>8409</v>
       </c>
-      <c r="C1328" s="6" t="s">
+      <c r="D1328" s="6" t="s">
         <v>8410</v>
       </c>
-      <c r="D1328" s="6" t="s">
+      <c r="E1328" s="6" t="s">
         <v>8411</v>
       </c>
-      <c r="E1328" s="6" t="s">
+      <c r="F1328" s="6" t="s">
         <v>8412</v>
       </c>
-      <c r="F1328" s="6" t="s">
+      <c r="G1328" s="6" t="s">
         <v>8413</v>
       </c>
-      <c r="G1328" s="6" t="s">
+      <c r="H1328" s="6" t="s">
         <v>8414</v>
-      </c>
-      <c r="H1328" s="6" t="s">
-        <v>8415</v>
       </c>
     </row>
     <row r="1329">
       <c r="B1329" s="5" t="s">
+        <v>8415</v>
+      </c>
+      <c r="C1329" s="5" t="s">
         <v>8416</v>
       </c>
-      <c r="C1329" s="5" t="s">
+      <c r="D1329" s="5" t="s">
         <v>8417</v>
       </c>
-      <c r="D1329" s="5" t="s">
+      <c r="E1329" s="5" t="s">
         <v>8418</v>
       </c>
-      <c r="E1329" s="5" t="s">
+      <c r="F1329" s="5" t="s">
         <v>8419</v>
       </c>
-      <c r="F1329" s="5" t="s">
+      <c r="G1329" s="5" t="s">
         <v>8420</v>
       </c>
-      <c r="G1329" s="5" t="s">
+      <c r="H1329" s="5" t="s">
         <v>8421</v>
-      </c>
-      <c r="H1329" s="5" t="s">
-        <v>8422</v>
       </c>
     </row>
     <row r="1330">
       <c r="B1330" s="6" t="s">
+        <v>8422</v>
+      </c>
+      <c r="C1330" s="6" t="s">
         <v>8423</v>
       </c>
-      <c r="C1330" s="6" t="s">
+      <c r="D1330" s="6" t="s">
         <v>8424</v>
       </c>
-      <c r="D1330" s="6" t="s">
+      <c r="E1330" s="6" t="s">
         <v>8425</v>
       </c>
-      <c r="E1330" s="6" t="s">
+      <c r="F1330" s="6" t="s">
         <v>8426</v>
       </c>
-      <c r="F1330" s="6" t="s">
+      <c r="G1330" s="6" t="s">
         <v>8427</v>
       </c>
-      <c r="G1330" s="6" t="s">
+      <c r="H1330" s="6" t="s">
         <v>8428</v>
-      </c>
-      <c r="H1330" s="6" t="s">
-        <v>8429</v>
       </c>
     </row>
     <row r="1331">
       <c r="B1331" s="5" t="s">
+        <v>8429</v>
+      </c>
+      <c r="C1331" s="5" t="s">
         <v>8430</v>
       </c>
-      <c r="C1331" s="5" t="s">
+      <c r="D1331" s="5" t="s">
         <v>8431</v>
       </c>
-      <c r="D1331" s="5" t="s">
+      <c r="E1331" s="5" t="s">
         <v>8432</v>
       </c>
-      <c r="E1331" s="5" t="s">
+      <c r="F1331" s="5" t="s">
         <v>8433</v>
-      </c>
-      <c r="F1331" s="5" t="s">
-        <v>8434</v>
       </c>
       <c r="G1331" s="5" t="s">
         <v>8434</v>
@@ -57797,96 +57815,96 @@
         <v>8440</v>
       </c>
       <c r="G1332" s="6" t="s">
+        <v>8440</v>
+      </c>
+      <c r="H1332" s="6" t="s">
         <v>8441</v>
-      </c>
-      <c r="H1332" s="6" t="s">
-        <v>8442</v>
       </c>
     </row>
     <row r="1333">
       <c r="B1333" s="5" t="s">
+        <v>8442</v>
+      </c>
+      <c r="C1333" s="5" t="s">
         <v>8443</v>
       </c>
-      <c r="C1333" s="5" t="s">
+      <c r="D1333" s="5" t="s">
         <v>8444</v>
       </c>
-      <c r="D1333" s="5" t="s">
+      <c r="E1333" s="5" t="s">
         <v>8445</v>
       </c>
-      <c r="E1333" s="5" t="s">
+      <c r="F1333" s="5" t="s">
         <v>8446</v>
       </c>
-      <c r="F1333" s="5" t="s">
-        <v>8364</v>
-      </c>
       <c r="G1333" s="5" t="s">
-        <v>8365</v>
+        <v>8447</v>
       </c>
       <c r="H1333" s="5" t="s">
-        <v>8447</v>
+        <v>8448</v>
       </c>
     </row>
     <row r="1334">
       <c r="B1334" s="6" t="s">
-        <v>8448</v>
+        <v>8449</v>
       </c>
       <c r="C1334" s="6" t="s">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D1334" s="6" t="s">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="E1334" s="6" t="s">
-        <v>8451</v>
+        <v>8452</v>
       </c>
       <c r="F1334" s="6" t="s">
-        <v>8452</v>
+        <v>8370</v>
       </c>
       <c r="G1334" s="6" t="s">
+        <v>8371</v>
+      </c>
+      <c r="H1334" s="6" t="s">
         <v>8453</v>
-      </c>
-      <c r="H1334" s="6" t="s">
-        <v>8454</v>
       </c>
     </row>
     <row r="1335">
       <c r="B1335" s="5" t="s">
+        <v>8454</v>
+      </c>
+      <c r="C1335" s="5" t="s">
         <v>8455</v>
       </c>
-      <c r="C1335" s="5" t="s">
+      <c r="D1335" s="5" t="s">
         <v>8456</v>
       </c>
-      <c r="D1335" s="5" t="s">
+      <c r="E1335" s="5" t="s">
         <v>8457</v>
       </c>
-      <c r="E1335" s="5" t="s">
+      <c r="F1335" s="5" t="s">
         <v>8458</v>
       </c>
-      <c r="F1335" s="5" t="s">
+      <c r="G1335" s="5" t="s">
         <v>8459</v>
       </c>
-      <c r="G1335" s="5" t="s">
+      <c r="H1335" s="5" t="s">
         <v>8460</v>
-      </c>
-      <c r="H1335" s="5" t="s">
-        <v>8461</v>
       </c>
     </row>
     <row r="1336">
       <c r="B1336" s="6" t="s">
+        <v>8461</v>
+      </c>
+      <c r="C1336" s="6" t="s">
         <v>8462</v>
       </c>
-      <c r="C1336" s="6" t="s">
+      <c r="D1336" s="6" t="s">
         <v>8463</v>
       </c>
-      <c r="D1336" s="6" t="s">
+      <c r="E1336" s="6" t="s">
         <v>8464</v>
       </c>
-      <c r="E1336" s="6" t="s">
+      <c r="F1336" s="6" t="s">
         <v>8465</v>
-      </c>
-      <c r="F1336" s="6" t="s">
-        <v>8466</v>
       </c>
       <c r="G1336" s="6" t="s">
         <v>8466</v>
@@ -57912,27 +57930,27 @@
         <v>8472</v>
       </c>
       <c r="G1337" s="5" t="s">
+        <v>8472</v>
+      </c>
+      <c r="H1337" s="5" t="s">
         <v>8473</v>
-      </c>
-      <c r="H1337" s="5" t="s">
-        <v>8474</v>
       </c>
     </row>
     <row r="1338">
       <c r="B1338" s="6" t="s">
+        <v>8474</v>
+      </c>
+      <c r="C1338" s="6" t="s">
         <v>8475</v>
       </c>
-      <c r="C1338" s="6" t="s">
+      <c r="D1338" s="6" t="s">
         <v>8476</v>
       </c>
-      <c r="D1338" s="6" t="s">
+      <c r="E1338" s="6" t="s">
         <v>8477</v>
       </c>
-      <c r="E1338" s="6" t="s">
+      <c r="F1338" s="6" t="s">
         <v>8478</v>
-      </c>
-      <c r="F1338" s="6" t="s">
-        <v>8479</v>
       </c>
       <c r="G1338" s="6" t="s">
         <v>8479</v>
@@ -57946,45 +57964,45 @@
         <v>8481</v>
       </c>
       <c r="C1339" s="5" t="s">
-        <v>6774</v>
+        <v>8482</v>
       </c>
       <c r="D1339" s="5" t="s">
-        <v>8482</v>
+        <v>8483</v>
       </c>
       <c r="E1339" s="5" t="s">
-        <v>6776</v>
+        <v>8484</v>
       </c>
       <c r="F1339" s="5" t="s">
-        <v>6777</v>
+        <v>8485</v>
       </c>
       <c r="G1339" s="5" t="s">
-        <v>6778</v>
+        <v>8485</v>
       </c>
       <c r="H1339" s="5" t="s">
-        <v>6779</v>
+        <v>8486</v>
       </c>
     </row>
     <row r="1340">
       <c r="B1340" s="6" t="s">
-        <v>8483</v>
+        <v>8487</v>
       </c>
       <c r="C1340" s="6" t="s">
-        <v>8484</v>
+        <v>6774</v>
       </c>
       <c r="D1340" s="6" t="s">
-        <v>8485</v>
+        <v>8488</v>
       </c>
       <c r="E1340" s="6" t="s">
-        <v>8486</v>
+        <v>6776</v>
       </c>
       <c r="F1340" s="6" t="s">
-        <v>8487</v>
+        <v>6777</v>
       </c>
       <c r="G1340" s="6" t="s">
-        <v>8487</v>
+        <v>6778</v>
       </c>
       <c r="H1340" s="6" t="s">
-        <v>8488</v>
+        <v>6779</v>
       </c>
     </row>
     <row r="1341">
@@ -58004,50 +58022,50 @@
         <v>8493</v>
       </c>
       <c r="G1341" s="5" t="s">
+        <v>8493</v>
+      </c>
+      <c r="H1341" s="5" t="s">
         <v>8494</v>
-      </c>
-      <c r="H1341" s="5" t="s">
-        <v>8495</v>
       </c>
     </row>
     <row r="1342">
       <c r="B1342" s="6" t="s">
+        <v>8495</v>
+      </c>
+      <c r="C1342" s="6" t="s">
         <v>8496</v>
       </c>
-      <c r="C1342" s="6" t="s">
+      <c r="D1342" s="6" t="s">
         <v>8497</v>
       </c>
-      <c r="D1342" s="6" t="s">
+      <c r="E1342" s="6" t="s">
         <v>8498</v>
       </c>
-      <c r="E1342" s="6" t="s">
+      <c r="F1342" s="6" t="s">
         <v>8499</v>
       </c>
-      <c r="F1342" s="6" t="s">
+      <c r="G1342" s="6" t="s">
         <v>8500</v>
       </c>
-      <c r="G1342" s="6" t="s">
+      <c r="H1342" s="6" t="s">
         <v>8501</v>
-      </c>
-      <c r="H1342" s="6" t="s">
-        <v>8502</v>
       </c>
     </row>
     <row r="1343">
       <c r="B1343" s="5" t="s">
+        <v>8502</v>
+      </c>
+      <c r="C1343" s="5" t="s">
         <v>8503</v>
       </c>
-      <c r="C1343" s="5" t="s">
+      <c r="D1343" s="5" t="s">
         <v>8504</v>
       </c>
-      <c r="D1343" s="5" t="s">
+      <c r="E1343" s="5" t="s">
         <v>8505</v>
       </c>
-      <c r="E1343" s="5" t="s">
+      <c r="F1343" s="5" t="s">
         <v>8506</v>
-      </c>
-      <c r="F1343" s="5" t="s">
-        <v>8507</v>
       </c>
       <c r="G1343" s="5" t="s">
         <v>8507</v>
@@ -58073,306 +58091,306 @@
         <v>8513</v>
       </c>
       <c r="G1344" s="6" t="s">
+        <v>8513</v>
+      </c>
+      <c r="H1344" s="6" t="s">
         <v>8514</v>
-      </c>
-      <c r="H1344" s="6" t="s">
-        <v>8515</v>
       </c>
     </row>
     <row r="1345">
       <c r="B1345" s="5" t="s">
+        <v>8515</v>
+      </c>
+      <c r="C1345" s="5" t="s">
         <v>8516</v>
       </c>
-      <c r="C1345" s="5" t="s">
+      <c r="D1345" s="5" t="s">
         <v>8517</v>
       </c>
-      <c r="D1345" s="5" t="s">
+      <c r="E1345" s="5" t="s">
         <v>8518</v>
       </c>
-      <c r="E1345" s="5" t="s">
+      <c r="F1345" s="5" t="s">
         <v>8519</v>
       </c>
-      <c r="F1345" s="5" t="s">
+      <c r="G1345" s="5" t="s">
         <v>8520</v>
       </c>
-      <c r="G1345" s="5" t="s">
+      <c r="H1345" s="5" t="s">
         <v>8521</v>
-      </c>
-      <c r="H1345" s="5" t="s">
-        <v>8522</v>
       </c>
     </row>
     <row r="1346">
       <c r="B1346" s="6" t="s">
+        <v>8522</v>
+      </c>
+      <c r="C1346" s="6" t="s">
         <v>8523</v>
       </c>
-      <c r="C1346" s="6" t="s">
+      <c r="D1346" s="6" t="s">
         <v>8524</v>
       </c>
-      <c r="D1346" s="6" t="s">
+      <c r="E1346" s="6" t="s">
         <v>8525</v>
       </c>
-      <c r="E1346" s="6" t="s">
+      <c r="F1346" s="6" t="s">
         <v>8526</v>
       </c>
-      <c r="F1346" s="6" t="s">
+      <c r="G1346" s="6" t="s">
         <v>8527</v>
       </c>
-      <c r="G1346" s="6" t="s">
+      <c r="H1346" s="6" t="s">
         <v>8528</v>
-      </c>
-      <c r="H1346" s="6" t="s">
-        <v>8529</v>
       </c>
     </row>
     <row r="1347">
       <c r="B1347" s="5" t="s">
+        <v>8529</v>
+      </c>
+      <c r="C1347" s="5" t="s">
         <v>8530</v>
       </c>
-      <c r="C1347" s="5" t="s">
-        <v>8484</v>
-      </c>
       <c r="D1347" s="5" t="s">
-        <v>8485</v>
+        <v>8531</v>
       </c>
       <c r="E1347" s="5" t="s">
-        <v>8486</v>
+        <v>8532</v>
       </c>
       <c r="F1347" s="5" t="s">
-        <v>8487</v>
+        <v>8533</v>
       </c>
       <c r="G1347" s="5" t="s">
-        <v>8487</v>
+        <v>8534</v>
       </c>
       <c r="H1347" s="5" t="s">
-        <v>8488</v>
+        <v>8535</v>
       </c>
     </row>
     <row r="1348">
       <c r="B1348" s="6" t="s">
-        <v>8531</v>
+        <v>8536</v>
       </c>
       <c r="C1348" s="6" t="s">
-        <v>8532</v>
+        <v>8490</v>
       </c>
       <c r="D1348" s="6" t="s">
-        <v>8533</v>
+        <v>8491</v>
       </c>
       <c r="E1348" s="6" t="s">
-        <v>8534</v>
+        <v>8492</v>
       </c>
       <c r="F1348" s="6" t="s">
-        <v>8535</v>
+        <v>8493</v>
       </c>
       <c r="G1348" s="6" t="s">
-        <v>8536</v>
+        <v>8493</v>
       </c>
       <c r="H1348" s="6" t="s">
-        <v>8537</v>
+        <v>8494</v>
       </c>
     </row>
     <row r="1349">
       <c r="B1349" s="5" t="s">
+        <v>8537</v>
+      </c>
+      <c r="C1349" s="5" t="s">
         <v>8538</v>
       </c>
-      <c r="C1349" s="5" t="s">
+      <c r="D1349" s="5" t="s">
         <v>8539</v>
       </c>
-      <c r="D1349" s="5" t="s">
+      <c r="E1349" s="5" t="s">
         <v>8540</v>
       </c>
-      <c r="E1349" s="5" t="s">
+      <c r="F1349" s="5" t="s">
         <v>8541</v>
       </c>
-      <c r="F1349" s="5" t="s">
+      <c r="G1349" s="5" t="s">
         <v>8542</v>
       </c>
-      <c r="G1349" s="5" t="s">
+      <c r="H1349" s="5" t="s">
         <v>8543</v>
-      </c>
-      <c r="H1349" s="5" t="s">
-        <v>8544</v>
       </c>
     </row>
     <row r="1350">
       <c r="B1350" s="6" t="s">
+        <v>8544</v>
+      </c>
+      <c r="C1350" s="6" t="s">
         <v>8545</v>
       </c>
-      <c r="C1350" s="6" t="s">
+      <c r="D1350" s="6" t="s">
         <v>8546</v>
       </c>
-      <c r="D1350" s="6" t="s">
+      <c r="E1350" s="6" t="s">
         <v>8547</v>
       </c>
-      <c r="E1350" s="6" t="s">
+      <c r="F1350" s="6" t="s">
         <v>8548</v>
       </c>
-      <c r="F1350" s="6" t="s">
+      <c r="G1350" s="6" t="s">
         <v>8549</v>
       </c>
-      <c r="G1350" s="6" t="s">
+      <c r="H1350" s="6" t="s">
         <v>8550</v>
-      </c>
-      <c r="H1350" s="6" t="s">
-        <v>8551</v>
       </c>
     </row>
     <row r="1351">
       <c r="B1351" s="5" t="s">
+        <v>8551</v>
+      </c>
+      <c r="C1351" s="5" t="s">
         <v>8552</v>
       </c>
-      <c r="C1351" s="5" t="s">
+      <c r="D1351" s="5" t="s">
         <v>8553</v>
       </c>
-      <c r="D1351" s="5" t="s">
+      <c r="E1351" s="5" t="s">
         <v>8554</v>
       </c>
-      <c r="E1351" s="5" t="s">
+      <c r="F1351" s="5" t="s">
         <v>8555</v>
       </c>
-      <c r="F1351" s="5" t="s">
+      <c r="G1351" s="5" t="s">
         <v>8556</v>
       </c>
-      <c r="G1351" s="5" t="s">
+      <c r="H1351" s="5" t="s">
         <v>8557</v>
-      </c>
-      <c r="H1351" s="5" t="s">
-        <v>8558</v>
       </c>
     </row>
     <row r="1352">
       <c r="B1352" s="6" t="s">
+        <v>8558</v>
+      </c>
+      <c r="C1352" s="6" t="s">
         <v>8559</v>
       </c>
-      <c r="C1352" s="6" t="s">
+      <c r="D1352" s="6" t="s">
         <v>8560</v>
       </c>
-      <c r="D1352" s="6" t="s">
+      <c r="E1352" s="6" t="s">
         <v>8561</v>
       </c>
-      <c r="E1352" s="6" t="s">
+      <c r="F1352" s="6" t="s">
         <v>8562</v>
       </c>
-      <c r="F1352" s="6" t="s">
+      <c r="G1352" s="6" t="s">
         <v>8563</v>
       </c>
-      <c r="G1352" s="6" t="s">
+      <c r="H1352" s="6" t="s">
         <v>8564</v>
-      </c>
-      <c r="H1352" s="6" t="s">
-        <v>8565</v>
       </c>
     </row>
     <row r="1353">
       <c r="B1353" s="5" t="s">
+        <v>8565</v>
+      </c>
+      <c r="C1353" s="5" t="s">
         <v>8566</v>
       </c>
-      <c r="C1353" s="5" t="s">
+      <c r="D1353" s="5" t="s">
         <v>8567</v>
       </c>
-      <c r="D1353" s="5" t="s">
+      <c r="E1353" s="5" t="s">
         <v>8568</v>
       </c>
-      <c r="E1353" s="5" t="s">
+      <c r="F1353" s="5" t="s">
         <v>8569</v>
       </c>
-      <c r="F1353" s="5" t="s">
+      <c r="G1353" s="5" t="s">
         <v>8570</v>
       </c>
-      <c r="G1353" s="5" t="s">
+      <c r="H1353" s="5" t="s">
         <v>8571</v>
-      </c>
-      <c r="H1353" s="5" t="s">
-        <v>8572</v>
       </c>
     </row>
     <row r="1354">
       <c r="B1354" s="6" t="s">
+        <v>8572</v>
+      </c>
+      <c r="C1354" s="6" t="s">
         <v>8573</v>
-      </c>
-      <c r="C1354" s="6" t="s">
-        <v>6888</v>
       </c>
       <c r="D1354" s="6" t="s">
         <v>8574</v>
       </c>
       <c r="E1354" s="6" t="s">
-        <v>6890</v>
+        <v>8575</v>
       </c>
       <c r="F1354" s="6" t="s">
-        <v>8221</v>
+        <v>8576</v>
       </c>
       <c r="G1354" s="6" t="s">
-        <v>8222</v>
+        <v>8577</v>
       </c>
       <c r="H1354" s="6" t="s">
-        <v>8575</v>
+        <v>8578</v>
       </c>
     </row>
     <row r="1355">
       <c r="B1355" s="5" t="s">
-        <v>8576</v>
+        <v>8579</v>
       </c>
       <c r="C1355" s="5" t="s">
-        <v>7088</v>
+        <v>6888</v>
       </c>
       <c r="D1355" s="5" t="s">
-        <v>6825</v>
+        <v>8580</v>
       </c>
       <c r="E1355" s="5" t="s">
-        <v>7089</v>
+        <v>6890</v>
       </c>
       <c r="F1355" s="5" t="s">
-        <v>7090</v>
+        <v>8227</v>
       </c>
       <c r="G1355" s="5" t="s">
-        <v>7091</v>
+        <v>8228</v>
       </c>
       <c r="H1355" s="5" t="s">
-        <v>6825</v>
+        <v>8581</v>
       </c>
     </row>
     <row r="1356">
       <c r="B1356" s="6" t="s">
-        <v>8577</v>
+        <v>8582</v>
       </c>
       <c r="C1356" s="6" t="s">
-        <v>8197</v>
+        <v>7094</v>
       </c>
       <c r="D1356" s="6" t="s">
-        <v>8578</v>
+        <v>6825</v>
       </c>
       <c r="E1356" s="6" t="s">
-        <v>8199</v>
+        <v>7095</v>
       </c>
       <c r="F1356" s="6" t="s">
-        <v>8200</v>
+        <v>7096</v>
       </c>
       <c r="G1356" s="6" t="s">
-        <v>8201</v>
+        <v>7097</v>
       </c>
       <c r="H1356" s="6" t="s">
-        <v>8579</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="1357">
       <c r="B1357" s="5" t="s">
-        <v>8580</v>
+        <v>8583</v>
       </c>
       <c r="C1357" s="5" t="s">
-        <v>8581</v>
+        <v>8203</v>
       </c>
       <c r="D1357" s="5" t="s">
-        <v>8582</v>
+        <v>8584</v>
       </c>
       <c r="E1357" s="5" t="s">
-        <v>8583</v>
+        <v>8205</v>
       </c>
       <c r="F1357" s="5" t="s">
-        <v>8584</v>
+        <v>8206</v>
       </c>
       <c r="G1357" s="5" t="s">
-        <v>8583</v>
+        <v>8207</v>
       </c>
       <c r="H1357" s="5" t="s">
         <v>8585</v>
@@ -58395,93 +58413,93 @@
         <v>8590</v>
       </c>
       <c r="G1358" s="6" t="s">
+        <v>8589</v>
+      </c>
+      <c r="H1358" s="6" t="s">
         <v>8591</v>
-      </c>
-      <c r="H1358" s="6" t="s">
-        <v>8592</v>
       </c>
     </row>
     <row r="1359">
       <c r="B1359" s="5" t="s">
+        <v>8592</v>
+      </c>
+      <c r="C1359" s="5" t="s">
         <v>8593</v>
       </c>
-      <c r="C1359" s="5" t="s">
+      <c r="D1359" s="5" t="s">
         <v>8594</v>
       </c>
-      <c r="D1359" s="5" t="s">
+      <c r="E1359" s="5" t="s">
         <v>8595</v>
       </c>
-      <c r="E1359" s="5" t="s">
+      <c r="F1359" s="5" t="s">
         <v>8596</v>
       </c>
-      <c r="F1359" s="5" t="s">
+      <c r="G1359" s="5" t="s">
         <v>8597</v>
       </c>
-      <c r="G1359" s="5" t="s">
+      <c r="H1359" s="5" t="s">
         <v>8598</v>
-      </c>
-      <c r="H1359" s="5" t="s">
-        <v>8599</v>
       </c>
     </row>
     <row r="1360">
       <c r="B1360" s="6" t="s">
+        <v>8599</v>
+      </c>
+      <c r="C1360" s="6" t="s">
         <v>8600</v>
       </c>
-      <c r="C1360" s="6" t="s">
+      <c r="D1360" s="6" t="s">
         <v>8601</v>
       </c>
-      <c r="D1360" s="6" t="s">
+      <c r="E1360" s="6" t="s">
         <v>8602</v>
       </c>
-      <c r="E1360" s="6" t="s">
+      <c r="F1360" s="6" t="s">
         <v>8603</v>
       </c>
-      <c r="F1360" s="6" t="s">
+      <c r="G1360" s="6" t="s">
         <v>8604</v>
       </c>
-      <c r="G1360" s="6" t="s">
+      <c r="H1360" s="6" t="s">
         <v>8605</v>
-      </c>
-      <c r="H1360" s="6" t="s">
-        <v>8606</v>
       </c>
     </row>
     <row r="1361">
       <c r="B1361" s="5" t="s">
+        <v>8606</v>
+      </c>
+      <c r="C1361" s="5" t="s">
         <v>8607</v>
       </c>
-      <c r="C1361" s="5" t="s">
+      <c r="D1361" s="5" t="s">
         <v>8608</v>
       </c>
-      <c r="D1361" s="5" t="s">
+      <c r="E1361" s="5" t="s">
         <v>8609</v>
       </c>
-      <c r="E1361" s="5" t="s">
+      <c r="F1361" s="5" t="s">
         <v>8610</v>
       </c>
-      <c r="F1361" s="5" t="s">
+      <c r="G1361" s="5" t="s">
         <v>8611</v>
       </c>
-      <c r="G1361" s="5" t="s">
+      <c r="H1361" s="5" t="s">
         <v>8612</v>
-      </c>
-      <c r="H1361" s="5" t="s">
-        <v>8613</v>
       </c>
     </row>
     <row r="1362">
       <c r="B1362" s="6" t="s">
+        <v>8613</v>
+      </c>
+      <c r="C1362" s="6" t="s">
         <v>8614</v>
       </c>
-      <c r="C1362" s="6" t="s">
+      <c r="D1362" s="6" t="s">
         <v>8615</v>
       </c>
-      <c r="D1362" s="6" t="s">
+      <c r="E1362" s="6" t="s">
         <v>8616</v>
-      </c>
-      <c r="E1362" s="6" t="s">
-        <v>5453</v>
       </c>
       <c r="F1362" s="6" t="s">
         <v>8617</v>
@@ -58504,154 +58522,154 @@
         <v>8622</v>
       </c>
       <c r="E1363" s="5" t="s">
+        <v>5453</v>
+      </c>
+      <c r="F1363" s="5" t="s">
         <v>8623</v>
       </c>
-      <c r="F1363" s="5" t="s">
+      <c r="G1363" s="5" t="s">
         <v>8624</v>
       </c>
-      <c r="G1363" s="5" t="s">
+      <c r="H1363" s="5" t="s">
         <v>8625</v>
-      </c>
-      <c r="H1363" s="5" t="s">
-        <v>8626</v>
       </c>
     </row>
     <row r="1364">
       <c r="B1364" s="6" t="s">
+        <v>8626</v>
+      </c>
+      <c r="C1364" s="6" t="s">
         <v>8627</v>
       </c>
-      <c r="C1364" s="6" t="s">
+      <c r="D1364" s="6" t="s">
         <v>8628</v>
       </c>
-      <c r="D1364" s="6" t="s">
+      <c r="E1364" s="6" t="s">
         <v>8629</v>
       </c>
-      <c r="E1364" s="6" t="s">
+      <c r="F1364" s="6" t="s">
         <v>8630</v>
       </c>
-      <c r="F1364" s="6" t="s">
+      <c r="G1364" s="6" t="s">
         <v>8631</v>
       </c>
-      <c r="G1364" s="6" t="s">
+      <c r="H1364" s="6" t="s">
         <v>8632</v>
-      </c>
-      <c r="H1364" s="6" t="s">
-        <v>8633</v>
       </c>
     </row>
     <row r="1365">
       <c r="B1365" s="5" t="s">
+        <v>8633</v>
+      </c>
+      <c r="C1365" s="5" t="s">
         <v>8634</v>
       </c>
-      <c r="C1365" s="5" t="s">
+      <c r="D1365" s="5" t="s">
         <v>8635</v>
       </c>
-      <c r="D1365" s="5" t="s">
+      <c r="E1365" s="5" t="s">
         <v>8636</v>
       </c>
-      <c r="E1365" s="5" t="s">
+      <c r="F1365" s="5" t="s">
         <v>8637</v>
       </c>
-      <c r="F1365" s="5" t="s">
+      <c r="G1365" s="5" t="s">
         <v>8638</v>
       </c>
-      <c r="G1365" s="5" t="s">
+      <c r="H1365" s="5" t="s">
         <v>8639</v>
-      </c>
-      <c r="H1365" s="5" t="s">
-        <v>8640</v>
       </c>
     </row>
     <row r="1366">
       <c r="B1366" s="6" t="s">
+        <v>8640</v>
+      </c>
+      <c r="C1366" s="6" t="s">
         <v>8641</v>
       </c>
-      <c r="C1366" s="6" t="s">
+      <c r="D1366" s="6" t="s">
         <v>8642</v>
       </c>
-      <c r="D1366" s="6" t="s">
+      <c r="E1366" s="6" t="s">
         <v>8643</v>
       </c>
-      <c r="E1366" s="6" t="s">
+      <c r="F1366" s="6" t="s">
         <v>8644</v>
       </c>
-      <c r="F1366" s="6" t="s">
+      <c r="G1366" s="6" t="s">
         <v>8645</v>
       </c>
-      <c r="G1366" s="6" t="s">
+      <c r="H1366" s="6" t="s">
         <v>8646</v>
-      </c>
-      <c r="H1366" s="6" t="s">
-        <v>8647</v>
       </c>
     </row>
     <row r="1367">
       <c r="B1367" s="5" t="s">
+        <v>8647</v>
+      </c>
+      <c r="C1367" s="5" t="s">
         <v>8648</v>
       </c>
-      <c r="C1367" s="7" t="s">
+      <c r="D1367" s="5" t="s">
         <v>8649</v>
       </c>
-      <c r="D1367" s="7" t="s">
-        <v>8649</v>
-      </c>
-      <c r="E1367" s="7" t="s">
-        <v>8649</v>
-      </c>
-      <c r="F1367" s="7" t="s">
-        <v>8649</v>
-      </c>
-      <c r="G1367" s="7" t="s">
-        <v>8649</v>
-      </c>
-      <c r="H1367" s="7" t="s">
-        <v>8649</v>
+      <c r="E1367" s="5" t="s">
+        <v>8650</v>
+      </c>
+      <c r="F1367" s="5" t="s">
+        <v>8651</v>
+      </c>
+      <c r="G1367" s="5" t="s">
+        <v>8652</v>
+      </c>
+      <c r="H1367" s="5" t="s">
+        <v>8653</v>
       </c>
     </row>
     <row r="1368">
       <c r="B1368" s="6" t="s">
-        <v>8650</v>
-      </c>
-      <c r="C1368" s="6" t="s">
-        <v>8061</v>
-      </c>
-      <c r="D1368" s="6" t="s">
-        <v>8062</v>
-      </c>
-      <c r="E1368" s="6" t="s">
-        <v>8063</v>
-      </c>
-      <c r="F1368" s="6" t="s">
-        <v>8064</v>
-      </c>
-      <c r="G1368" s="6" t="s">
-        <v>8065</v>
-      </c>
-      <c r="H1368" s="6" t="s">
-        <v>8062</v>
+        <v>8654</v>
+      </c>
+      <c r="C1368" s="7" t="s">
+        <v>8655</v>
+      </c>
+      <c r="D1368" s="7" t="s">
+        <v>8655</v>
+      </c>
+      <c r="E1368" s="7" t="s">
+        <v>8655</v>
+      </c>
+      <c r="F1368" s="7" t="s">
+        <v>8655</v>
+      </c>
+      <c r="G1368" s="7" t="s">
+        <v>8655</v>
+      </c>
+      <c r="H1368" s="7" t="s">
+        <v>8655</v>
       </c>
     </row>
     <row r="1369">
       <c r="B1369" s="5" t="s">
-        <v>8651</v>
+        <v>8656</v>
       </c>
       <c r="C1369" s="5" t="s">
-        <v>8652</v>
+        <v>8067</v>
       </c>
       <c r="D1369" s="5" t="s">
-        <v>8653</v>
+        <v>8068</v>
       </c>
       <c r="E1369" s="5" t="s">
-        <v>8654</v>
+        <v>8069</v>
       </c>
       <c r="F1369" s="5" t="s">
-        <v>8655</v>
+        <v>8070</v>
       </c>
       <c r="G1369" s="5" t="s">
-        <v>8655</v>
+        <v>8071</v>
       </c>
       <c r="H1369" s="5" t="s">
-        <v>8656</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="1370">
@@ -58671,10 +58689,10 @@
         <v>8661</v>
       </c>
       <c r="G1370" s="6" t="s">
+        <v>8661</v>
+      </c>
+      <c r="H1370" s="6" t="s">
         <v>8662</v>
-      </c>
-      <c r="H1370" s="6" t="s">
-        <v>6117</v>
       </c>
     </row>
     <row r="1371">
@@ -58697,47 +58715,47 @@
         <v>8668</v>
       </c>
       <c r="H1371" s="5" t="s">
-        <v>8669</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="1372">
       <c r="B1372" s="6" t="s">
+        <v>8669</v>
+      </c>
+      <c r="C1372" s="6" t="s">
         <v>8670</v>
       </c>
-      <c r="C1372" s="6" t="s">
+      <c r="D1372" s="6" t="s">
         <v>8671</v>
       </c>
-      <c r="D1372" s="6" t="s">
+      <c r="E1372" s="6" t="s">
         <v>8672</v>
       </c>
-      <c r="E1372" s="6" t="s">
+      <c r="F1372" s="6" t="s">
         <v>8673</v>
       </c>
-      <c r="F1372" s="6" t="s">
+      <c r="G1372" s="6" t="s">
         <v>8674</v>
       </c>
-      <c r="G1372" s="6" t="s">
+      <c r="H1372" s="6" t="s">
         <v>8675</v>
-      </c>
-      <c r="H1372" s="6" t="s">
-        <v>8676</v>
       </c>
     </row>
     <row r="1373">
       <c r="B1373" s="5" t="s">
+        <v>8676</v>
+      </c>
+      <c r="C1373" s="5" t="s">
         <v>8677</v>
       </c>
-      <c r="C1373" s="5" t="s">
+      <c r="D1373" s="5" t="s">
         <v>8678</v>
       </c>
-      <c r="D1373" s="5" t="s">
+      <c r="E1373" s="5" t="s">
         <v>8679</v>
       </c>
-      <c r="E1373" s="5" t="s">
+      <c r="F1373" s="5" t="s">
         <v>8680</v>
-      </c>
-      <c r="F1373" s="5" t="s">
-        <v>8681</v>
       </c>
       <c r="G1373" s="5" t="s">
         <v>8681</v>
@@ -58763,27 +58781,27 @@
         <v>8687</v>
       </c>
       <c r="G1374" s="6" t="s">
+        <v>8687</v>
+      </c>
+      <c r="H1374" s="6" t="s">
         <v>8688</v>
-      </c>
-      <c r="H1374" s="6" t="s">
-        <v>8689</v>
       </c>
     </row>
     <row r="1375">
       <c r="B1375" s="5" t="s">
+        <v>8689</v>
+      </c>
+      <c r="C1375" s="5" t="s">
         <v>8690</v>
       </c>
-      <c r="C1375" s="5" t="s">
+      <c r="D1375" s="5" t="s">
         <v>8691</v>
       </c>
-      <c r="D1375" s="5" t="s">
+      <c r="E1375" s="5" t="s">
         <v>8692</v>
       </c>
-      <c r="E1375" s="5" t="s">
+      <c r="F1375" s="5" t="s">
         <v>8693</v>
-      </c>
-      <c r="F1375" s="5" t="s">
-        <v>8694</v>
       </c>
       <c r="G1375" s="5" t="s">
         <v>8694</v>
@@ -58800,39 +58818,39 @@
         <v>8697</v>
       </c>
       <c r="D1376" s="6" t="s">
-        <v>8697</v>
+        <v>8698</v>
       </c>
       <c r="E1376" s="6" t="s">
-        <v>8697</v>
+        <v>8699</v>
       </c>
       <c r="F1376" s="6" t="s">
-        <v>8697</v>
+        <v>8700</v>
       </c>
       <c r="G1376" s="6" t="s">
-        <v>8697</v>
+        <v>8700</v>
       </c>
       <c r="H1376" s="6" t="s">
-        <v>8697</v>
+        <v>8701</v>
       </c>
     </row>
     <row r="1377">
       <c r="B1377" s="5" t="s">
-        <v>8698</v>
+        <v>8702</v>
       </c>
       <c r="C1377" s="5" t="s">
-        <v>8699</v>
+        <v>8703</v>
       </c>
       <c r="D1377" s="5" t="s">
-        <v>8700</v>
+        <v>8703</v>
       </c>
       <c r="E1377" s="5" t="s">
-        <v>8701</v>
+        <v>8703</v>
       </c>
       <c r="F1377" s="5" t="s">
-        <v>8702</v>
+        <v>8703</v>
       </c>
       <c r="G1377" s="5" t="s">
-        <v>8702</v>
+        <v>8703</v>
       </c>
       <c r="H1377" s="5" t="s">
         <v>8703</v>
@@ -58843,300 +58861,300 @@
         <v>8704</v>
       </c>
       <c r="C1378" s="6" t="s">
-        <v>8697</v>
+        <v>8705</v>
       </c>
       <c r="D1378" s="6" t="s">
-        <v>8697</v>
+        <v>8706</v>
       </c>
       <c r="E1378" s="6" t="s">
-        <v>8697</v>
+        <v>8707</v>
       </c>
       <c r="F1378" s="6" t="s">
-        <v>8697</v>
+        <v>8708</v>
       </c>
       <c r="G1378" s="6" t="s">
-        <v>8697</v>
+        <v>8708</v>
       </c>
       <c r="H1378" s="6" t="s">
-        <v>8697</v>
+        <v>8709</v>
       </c>
     </row>
     <row r="1379">
       <c r="B1379" s="5" t="s">
-        <v>8705</v>
+        <v>8710</v>
+      </c>
+      <c r="C1379" s="5" t="s">
+        <v>8703</v>
+      </c>
+      <c r="D1379" s="5" t="s">
+        <v>8703</v>
+      </c>
+      <c r="E1379" s="5" t="s">
+        <v>8703</v>
+      </c>
+      <c r="F1379" s="5" t="s">
+        <v>8703</v>
+      </c>
+      <c r="G1379" s="5" t="s">
+        <v>8703</v>
+      </c>
+      <c r="H1379" s="5" t="s">
+        <v>8703</v>
       </c>
     </row>
     <row r="1380">
       <c r="B1380" s="6" t="s">
-        <v>8706</v>
-      </c>
-      <c r="C1380" s="6" t="s">
-        <v>8707</v>
-      </c>
-      <c r="D1380" s="6" t="s">
-        <v>8708</v>
-      </c>
-      <c r="E1380" s="6" t="s">
-        <v>8709</v>
-      </c>
-      <c r="F1380" s="6" t="s">
-        <v>8710</v>
-      </c>
-      <c r="G1380" s="6" t="s">
         <v>8711</v>
-      </c>
-      <c r="H1380" s="6" t="s">
-        <v>8712</v>
       </c>
     </row>
     <row r="1381">
       <c r="B1381" s="5" t="s">
+        <v>8712</v>
+      </c>
+      <c r="C1381" s="5" t="s">
         <v>8713</v>
       </c>
-      <c r="C1381" s="5" t="s">
+      <c r="D1381" s="5" t="s">
         <v>8714</v>
       </c>
-      <c r="D1381" s="5" t="s">
+      <c r="E1381" s="5" t="s">
         <v>8715</v>
       </c>
-      <c r="E1381" s="5" t="s">
+      <c r="F1381" s="5" t="s">
         <v>8716</v>
       </c>
-      <c r="F1381" s="5" t="s">
+      <c r="G1381" s="5" t="s">
         <v>8717</v>
       </c>
-      <c r="G1381" s="5" t="s">
+      <c r="H1381" s="5" t="s">
         <v>8718</v>
-      </c>
-      <c r="H1381" s="5" t="s">
-        <v>8719</v>
       </c>
     </row>
     <row r="1382">
       <c r="B1382" s="6" t="s">
+        <v>8719</v>
+      </c>
+      <c r="C1382" s="6" t="s">
         <v>8720</v>
       </c>
-      <c r="C1382" s="6" t="s">
+      <c r="D1382" s="6" t="s">
         <v>8721</v>
       </c>
-      <c r="D1382" s="6" t="s">
+      <c r="E1382" s="6" t="s">
         <v>8722</v>
       </c>
-      <c r="E1382" s="6" t="s">
+      <c r="F1382" s="6" t="s">
         <v>8723</v>
       </c>
-      <c r="F1382" s="6" t="s">
+      <c r="G1382" s="6" t="s">
         <v>8724</v>
       </c>
-      <c r="G1382" s="6" t="s">
+      <c r="H1382" s="6" t="s">
         <v>8725</v>
-      </c>
-      <c r="H1382" s="6" t="s">
-        <v>8726</v>
       </c>
     </row>
     <row r="1383">
       <c r="B1383" s="5" t="s">
+        <v>8726</v>
+      </c>
+      <c r="C1383" s="5" t="s">
         <v>8727</v>
       </c>
-      <c r="C1383" s="5" t="s">
+      <c r="D1383" s="5" t="s">
         <v>8728</v>
       </c>
-      <c r="D1383" s="5" t="s">
+      <c r="E1383" s="5" t="s">
         <v>8729</v>
       </c>
-      <c r="E1383" s="5" t="s">
+      <c r="F1383" s="5" t="s">
         <v>8730</v>
       </c>
-      <c r="F1383" s="5" t="s">
+      <c r="G1383" s="5" t="s">
         <v>8731</v>
       </c>
-      <c r="G1383" s="5" t="s">
+      <c r="H1383" s="5" t="s">
         <v>8732</v>
-      </c>
-      <c r="H1383" s="5" t="s">
-        <v>8733</v>
       </c>
     </row>
     <row r="1384">
       <c r="B1384" s="6" t="s">
+        <v>8733</v>
+      </c>
+      <c r="C1384" s="6" t="s">
         <v>8734</v>
-      </c>
-      <c r="C1384" s="6" t="s">
-        <v>6112</v>
       </c>
       <c r="D1384" s="6" t="s">
         <v>8735</v>
       </c>
       <c r="E1384" s="6" t="s">
-        <v>6114</v>
+        <v>8736</v>
       </c>
       <c r="F1384" s="6" t="s">
-        <v>8736</v>
+        <v>8737</v>
       </c>
       <c r="G1384" s="6" t="s">
-        <v>8736</v>
+        <v>8738</v>
       </c>
       <c r="H1384" s="6" t="s">
-        <v>8737</v>
+        <v>8739</v>
       </c>
     </row>
     <row r="1385">
       <c r="B1385" s="5" t="s">
-        <v>8738</v>
+        <v>8740</v>
       </c>
       <c r="C1385" s="5" t="s">
-        <v>8739</v>
+        <v>6112</v>
       </c>
       <c r="D1385" s="5" t="s">
-        <v>8740</v>
+        <v>8741</v>
       </c>
       <c r="E1385" s="5" t="s">
-        <v>8741</v>
+        <v>6114</v>
       </c>
       <c r="F1385" s="5" t="s">
         <v>8742</v>
       </c>
       <c r="G1385" s="5" t="s">
+        <v>8742</v>
+      </c>
+      <c r="H1385" s="5" t="s">
         <v>8743</v>
-      </c>
-      <c r="H1385" s="5" t="s">
-        <v>8744</v>
       </c>
     </row>
     <row r="1386">
       <c r="B1386" s="6" t="s">
+        <v>8744</v>
+      </c>
+      <c r="C1386" s="6" t="s">
         <v>8745</v>
       </c>
-      <c r="C1386" s="6" t="s">
+      <c r="D1386" s="6" t="s">
         <v>8746</v>
       </c>
-      <c r="D1386" s="6" t="s">
+      <c r="E1386" s="6" t="s">
         <v>8747</v>
       </c>
-      <c r="E1386" s="6" t="s">
+      <c r="F1386" s="6" t="s">
         <v>8748</v>
       </c>
-      <c r="F1386" s="6" t="s">
+      <c r="G1386" s="6" t="s">
         <v>8749</v>
       </c>
-      <c r="G1386" s="6" t="s">
+      <c r="H1386" s="6" t="s">
         <v>8750</v>
-      </c>
-      <c r="H1386" s="6" t="s">
-        <v>8751</v>
       </c>
     </row>
     <row r="1387">
       <c r="B1387" s="5" t="s">
+        <v>8751</v>
+      </c>
+      <c r="C1387" s="5" t="s">
         <v>8752</v>
       </c>
-      <c r="C1387" s="5" t="s">
+      <c r="D1387" s="5" t="s">
         <v>8753</v>
       </c>
-      <c r="D1387" s="5" t="s">
+      <c r="E1387" s="5" t="s">
         <v>8754</v>
       </c>
-      <c r="E1387" s="5" t="s">
+      <c r="F1387" s="5" t="s">
         <v>8755</v>
       </c>
-      <c r="F1387" s="5" t="s">
+      <c r="G1387" s="5" t="s">
         <v>8756</v>
       </c>
-      <c r="G1387" s="5" t="s">
+      <c r="H1387" s="5" t="s">
         <v>8757</v>
-      </c>
-      <c r="H1387" s="5" t="s">
-        <v>8758</v>
       </c>
     </row>
     <row r="1388">
       <c r="B1388" s="6" t="s">
+        <v>8758</v>
+      </c>
+      <c r="C1388" s="6" t="s">
         <v>8759</v>
       </c>
-      <c r="C1388" s="6" t="s">
+      <c r="D1388" s="6" t="s">
         <v>8760</v>
       </c>
-      <c r="D1388" s="6" t="s">
+      <c r="E1388" s="6" t="s">
         <v>8761</v>
       </c>
-      <c r="E1388" s="6" t="s">
+      <c r="F1388" s="6" t="s">
         <v>8762</v>
       </c>
-      <c r="F1388" s="6" t="s">
+      <c r="G1388" s="6" t="s">
         <v>8763</v>
       </c>
-      <c r="G1388" s="6" t="s">
+      <c r="H1388" s="6" t="s">
         <v>8764</v>
-      </c>
-      <c r="H1388" s="6" t="s">
-        <v>8765</v>
       </c>
     </row>
     <row r="1389">
       <c r="B1389" s="5" t="s">
+        <v>8765</v>
+      </c>
+      <c r="C1389" s="5" t="s">
         <v>8766</v>
       </c>
-      <c r="C1389" s="5" t="s">
+      <c r="D1389" s="5" t="s">
         <v>8767</v>
       </c>
-      <c r="D1389" s="5" t="s">
+      <c r="E1389" s="5" t="s">
         <v>8768</v>
       </c>
-      <c r="E1389" s="5" t="s">
+      <c r="F1389" s="5" t="s">
         <v>8769</v>
       </c>
-      <c r="F1389" s="5" t="s">
+      <c r="G1389" s="5" t="s">
         <v>8770</v>
       </c>
-      <c r="G1389" s="5" t="s">
+      <c r="H1389" s="5" t="s">
         <v>8771</v>
-      </c>
-      <c r="H1389" s="5" t="s">
-        <v>8772</v>
       </c>
     </row>
     <row r="1390">
       <c r="B1390" s="6" t="s">
+        <v>8772</v>
+      </c>
+      <c r="C1390" s="6" t="s">
         <v>8773</v>
-      </c>
-      <c r="C1390" s="6" t="s">
-        <v>8774</v>
       </c>
       <c r="D1390" s="6" t="s">
         <v>8774</v>
       </c>
       <c r="E1390" s="6" t="s">
-        <v>8774</v>
+        <v>8775</v>
       </c>
       <c r="F1390" s="6" t="s">
-        <v>8774</v>
+        <v>8776</v>
       </c>
       <c r="G1390" s="6" t="s">
-        <v>8774</v>
+        <v>8777</v>
       </c>
       <c r="H1390" s="6" t="s">
-        <v>8774</v>
+        <v>8778</v>
       </c>
     </row>
     <row r="1391">
       <c r="B1391" s="5" t="s">
-        <v>8775</v>
+        <v>8779</v>
       </c>
       <c r="C1391" s="5" t="s">
-        <v>8776</v>
+        <v>8780</v>
       </c>
       <c r="D1391" s="5" t="s">
-        <v>8777</v>
+        <v>8780</v>
       </c>
       <c r="E1391" s="5" t="s">
-        <v>8778</v>
+        <v>8780</v>
       </c>
       <c r="F1391" s="5" t="s">
-        <v>8779</v>
+        <v>8780</v>
       </c>
       <c r="G1391" s="5" t="s">
-        <v>8779</v>
+        <v>8780</v>
       </c>
       <c r="H1391" s="5" t="s">
         <v>8780</v>
@@ -59159,50 +59177,50 @@
         <v>8785</v>
       </c>
       <c r="G1392" s="6" t="s">
+        <v>8785</v>
+      </c>
+      <c r="H1392" s="6" t="s">
         <v>8786</v>
-      </c>
-      <c r="H1392" s="6" t="s">
-        <v>8787</v>
       </c>
     </row>
     <row r="1393">
       <c r="B1393" s="5" t="s">
+        <v>8787</v>
+      </c>
+      <c r="C1393" s="5" t="s">
         <v>8788</v>
       </c>
-      <c r="C1393" s="5" t="s">
+      <c r="D1393" s="5" t="s">
         <v>8789</v>
       </c>
-      <c r="D1393" s="5" t="s">
+      <c r="E1393" s="5" t="s">
         <v>8790</v>
       </c>
-      <c r="E1393" s="5" t="s">
+      <c r="F1393" s="5" t="s">
         <v>8791</v>
       </c>
-      <c r="F1393" s="5" t="s">
+      <c r="G1393" s="5" t="s">
         <v>8792</v>
       </c>
-      <c r="G1393" s="5" t="s">
+      <c r="H1393" s="5" t="s">
         <v>8793</v>
-      </c>
-      <c r="H1393" s="5" t="s">
-        <v>8794</v>
       </c>
     </row>
     <row r="1394">
       <c r="B1394" s="6" t="s">
+        <v>8794</v>
+      </c>
+      <c r="C1394" s="6" t="s">
         <v>8795</v>
       </c>
-      <c r="C1394" s="6" t="s">
+      <c r="D1394" s="6" t="s">
         <v>8796</v>
       </c>
-      <c r="D1394" s="6" t="s">
+      <c r="E1394" s="6" t="s">
         <v>8797</v>
       </c>
-      <c r="E1394" s="6" t="s">
+      <c r="F1394" s="6" t="s">
         <v>8798</v>
-      </c>
-      <c r="F1394" s="6" t="s">
-        <v>8799</v>
       </c>
       <c r="G1394" s="6" t="s">
         <v>8799</v>
@@ -59251,463 +59269,486 @@
         <v>8811</v>
       </c>
       <c r="G1396" s="6" t="s">
+        <v>8811</v>
+      </c>
+      <c r="H1396" s="6" t="s">
         <v>8812</v>
-      </c>
-      <c r="H1396" s="6" t="s">
-        <v>8813</v>
       </c>
     </row>
     <row r="1397">
       <c r="B1397" s="5" t="s">
+        <v>8813</v>
+      </c>
+      <c r="C1397" s="5" t="s">
         <v>8814</v>
       </c>
-      <c r="C1397" s="5" t="s">
+      <c r="D1397" s="5" t="s">
         <v>8815</v>
       </c>
-      <c r="D1397" s="5" t="s">
+      <c r="E1397" s="5" t="s">
         <v>8816</v>
       </c>
-      <c r="E1397" s="5" t="s">
+      <c r="F1397" s="5" t="s">
         <v>8817</v>
       </c>
-      <c r="F1397" s="5" t="s">
+      <c r="G1397" s="5" t="s">
         <v>8818</v>
       </c>
-      <c r="G1397" s="5" t="s">
+      <c r="H1397" s="5" t="s">
         <v>8819</v>
-      </c>
-      <c r="H1397" s="5" t="s">
-        <v>8820</v>
       </c>
     </row>
     <row r="1398">
       <c r="B1398" s="6" t="s">
+        <v>8820</v>
+      </c>
+      <c r="C1398" s="6" t="s">
         <v>8821</v>
       </c>
-      <c r="C1398" s="6" t="s">
+      <c r="D1398" s="6" t="s">
         <v>8822</v>
       </c>
-      <c r="D1398" s="6" t="s">
+      <c r="E1398" s="6" t="s">
         <v>8823</v>
       </c>
-      <c r="E1398" s="6" t="s">
+      <c r="F1398" s="6" t="s">
         <v>8824</v>
       </c>
-      <c r="F1398" s="6" t="s">
+      <c r="G1398" s="6" t="s">
         <v>8825</v>
       </c>
-      <c r="G1398" s="6" t="s">
+      <c r="H1398" s="6" t="s">
         <v>8826</v>
-      </c>
-      <c r="H1398" s="6" t="s">
-        <v>8827</v>
       </c>
     </row>
     <row r="1399">
       <c r="B1399" s="5" t="s">
+        <v>8827</v>
+      </c>
+      <c r="C1399" s="5" t="s">
         <v>8828</v>
       </c>
-      <c r="C1399" s="5" t="s">
+      <c r="D1399" s="5" t="s">
         <v>8829</v>
       </c>
-      <c r="D1399" s="5" t="s">
+      <c r="E1399" s="5" t="s">
         <v>8830</v>
       </c>
-      <c r="E1399" s="5" t="s">
+      <c r="F1399" s="5" t="s">
         <v>8831</v>
       </c>
-      <c r="F1399" s="5" t="s">
+      <c r="G1399" s="5" t="s">
         <v>8832</v>
       </c>
-      <c r="G1399" s="5" t="s">
+      <c r="H1399" s="5" t="s">
         <v>8833</v>
-      </c>
-      <c r="H1399" s="5" t="s">
-        <v>8834</v>
       </c>
     </row>
     <row r="1400">
       <c r="B1400" s="6" t="s">
+        <v>8834</v>
+      </c>
+      <c r="C1400" s="6" t="s">
         <v>8835</v>
       </c>
-      <c r="C1400" s="6" t="s">
+      <c r="D1400" s="6" t="s">
         <v>8836</v>
       </c>
-      <c r="D1400" s="6" t="s">
+      <c r="E1400" s="6" t="s">
         <v>8837</v>
       </c>
-      <c r="E1400" s="6" t="s">
+      <c r="F1400" s="6" t="s">
         <v>8838</v>
       </c>
-      <c r="F1400" s="6" t="s">
+      <c r="G1400" s="6" t="s">
         <v>8839</v>
       </c>
-      <c r="G1400" s="6" t="s">
+      <c r="H1400" s="6" t="s">
         <v>8840</v>
-      </c>
-      <c r="H1400" s="6" t="s">
-        <v>8841</v>
       </c>
     </row>
     <row r="1401">
       <c r="B1401" s="5" t="s">
+        <v>8841</v>
+      </c>
+      <c r="C1401" s="5" t="s">
         <v>8842</v>
       </c>
-      <c r="C1401" s="5" t="s">
+      <c r="D1401" s="5" t="s">
         <v>8843</v>
       </c>
-      <c r="D1401" s="5" t="s">
+      <c r="E1401" s="5" t="s">
         <v>8844</v>
       </c>
-      <c r="E1401" s="5" t="s">
+      <c r="F1401" s="5" t="s">
         <v>8845</v>
       </c>
-      <c r="F1401" s="5" t="s">
+      <c r="G1401" s="5" t="s">
         <v>8846</v>
       </c>
-      <c r="G1401" s="5" t="s">
+      <c r="H1401" s="5" t="s">
         <v>8847</v>
-      </c>
-      <c r="H1401" s="5" t="s">
-        <v>8848</v>
       </c>
     </row>
     <row r="1402">
       <c r="B1402" s="6" t="s">
+        <v>8848</v>
+      </c>
+      <c r="C1402" s="6" t="s">
         <v>8849</v>
       </c>
-      <c r="C1402" s="6" t="s">
+      <c r="D1402" s="6" t="s">
         <v>8850</v>
       </c>
-      <c r="D1402" s="6" t="s">
+      <c r="E1402" s="6" t="s">
         <v>8851</v>
       </c>
-      <c r="E1402" s="6" t="s">
+      <c r="F1402" s="6" t="s">
         <v>8852</v>
       </c>
-      <c r="F1402" s="6" t="s">
+      <c r="G1402" s="6" t="s">
         <v>8853</v>
       </c>
-      <c r="G1402" s="6" t="s">
+      <c r="H1402" s="6" t="s">
         <v>8854</v>
-      </c>
-      <c r="H1402" s="6" t="s">
-        <v>8855</v>
       </c>
     </row>
     <row r="1403">
       <c r="B1403" s="5" t="s">
+        <v>8855</v>
+      </c>
+      <c r="C1403" s="5" t="s">
         <v>8856</v>
       </c>
-      <c r="C1403" s="5" t="s">
+      <c r="D1403" s="5" t="s">
         <v>8857</v>
       </c>
-      <c r="D1403" s="5" t="s">
+      <c r="E1403" s="5" t="s">
         <v>8858</v>
       </c>
-      <c r="E1403" s="5" t="s">
+      <c r="F1403" s="5" t="s">
         <v>8859</v>
       </c>
-      <c r="F1403" s="5" t="s">
+      <c r="G1403" s="5" t="s">
         <v>8860</v>
       </c>
-      <c r="G1403" s="5" t="s">
+      <c r="H1403" s="5" t="s">
         <v>8861</v>
-      </c>
-      <c r="H1403" s="5" t="s">
-        <v>8862</v>
       </c>
     </row>
     <row r="1404">
       <c r="B1404" s="6" t="s">
+        <v>8862</v>
+      </c>
+      <c r="C1404" s="6" t="s">
         <v>8863</v>
       </c>
-      <c r="C1404" s="6" t="s">
+      <c r="D1404" s="6" t="s">
         <v>8864</v>
       </c>
-      <c r="D1404" s="6" t="s">
+      <c r="E1404" s="6" t="s">
         <v>8865</v>
       </c>
-      <c r="E1404" s="6" t="s">
+      <c r="F1404" s="6" t="s">
         <v>8866</v>
       </c>
-      <c r="F1404" s="6" t="s">
+      <c r="G1404" s="6" t="s">
         <v>8867</v>
       </c>
-      <c r="G1404" s="6" t="s">
+      <c r="H1404" s="6" t="s">
         <v>8868</v>
-      </c>
-      <c r="H1404" s="6" t="s">
-        <v>8869</v>
       </c>
     </row>
     <row r="1405">
       <c r="B1405" s="5" t="s">
+        <v>8869</v>
+      </c>
+      <c r="C1405" s="5" t="s">
         <v>8870</v>
-      </c>
-      <c r="C1405" s="5" t="s">
-        <v>4582</v>
       </c>
       <c r="D1405" s="5" t="s">
         <v>8871</v>
       </c>
       <c r="E1405" s="5" t="s">
-        <v>4584</v>
+        <v>8872</v>
       </c>
       <c r="F1405" s="5" t="s">
-        <v>8872</v>
+        <v>8873</v>
       </c>
       <c r="G1405" s="5" t="s">
-        <v>8873</v>
+        <v>8874</v>
       </c>
       <c r="H1405" s="5" t="s">
-        <v>8874</v>
+        <v>8875</v>
       </c>
     </row>
     <row r="1406">
       <c r="B1406" s="6" t="s">
-        <v>8875</v>
+        <v>8876</v>
       </c>
       <c r="C1406" s="6" t="s">
-        <v>8876</v>
+        <v>4582</v>
       </c>
       <c r="D1406" s="6" t="s">
         <v>8877</v>
       </c>
+      <c r="E1406" s="6" t="s">
+        <v>4584</v>
+      </c>
+      <c r="F1406" s="6" t="s">
+        <v>8878</v>
+      </c>
+      <c r="G1406" s="6" t="s">
+        <v>8879</v>
+      </c>
+      <c r="H1406" s="6" t="s">
+        <v>8880</v>
+      </c>
     </row>
     <row r="1407">
       <c r="B1407" s="5" t="s">
-        <v>8878</v>
+        <v>8881</v>
       </c>
       <c r="C1407" s="5" t="s">
-        <v>8879</v>
+        <v>8882</v>
       </c>
       <c r="D1407" s="5" t="s">
-        <v>8880</v>
+        <v>8883</v>
       </c>
     </row>
     <row r="1408">
       <c r="B1408" s="6" t="s">
-        <v>8881</v>
+        <v>8884</v>
       </c>
       <c r="C1408" s="6" t="s">
-        <v>8882</v>
+        <v>8885</v>
       </c>
       <c r="D1408" s="6" t="s">
-        <v>8883</v>
+        <v>8886</v>
       </c>
     </row>
     <row r="1409">
       <c r="B1409" s="5" t="s">
-        <v>8884</v>
+        <v>8887</v>
       </c>
       <c r="C1409" s="5" t="s">
-        <v>8885</v>
+        <v>8888</v>
       </c>
       <c r="D1409" s="5" t="s">
-        <v>8886</v>
+        <v>8889</v>
       </c>
     </row>
     <row r="1410">
       <c r="B1410" s="6" t="s">
-        <v>8887</v>
+        <v>8890</v>
       </c>
       <c r="C1410" s="6" t="s">
-        <v>8888</v>
+        <v>8891</v>
       </c>
       <c r="D1410" s="6" t="s">
-        <v>8889</v>
+        <v>8892</v>
       </c>
     </row>
     <row r="1411">
       <c r="B1411" s="5" t="s">
-        <v>8890</v>
+        <v>8893</v>
       </c>
       <c r="C1411" s="5" t="s">
-        <v>8891</v>
+        <v>8894</v>
       </c>
       <c r="D1411" s="5" t="s">
-        <v>8892</v>
+        <v>8895</v>
       </c>
     </row>
     <row r="1412">
       <c r="B1412" s="6" t="s">
-        <v>8893</v>
+        <v>8896</v>
       </c>
       <c r="C1412" s="6" t="s">
-        <v>8894</v>
+        <v>8897</v>
       </c>
       <c r="D1412" s="6" t="s">
-        <v>8895</v>
+        <v>8898</v>
       </c>
     </row>
     <row r="1413">
       <c r="B1413" s="5" t="s">
-        <v>8896</v>
+        <v>8899</v>
       </c>
       <c r="C1413" s="5" t="s">
-        <v>8897</v>
+        <v>8900</v>
       </c>
       <c r="D1413" s="5" t="s">
-        <v>8898</v>
+        <v>8901</v>
       </c>
     </row>
     <row r="1414">
       <c r="B1414" s="6" t="s">
-        <v>8899</v>
+        <v>8902</v>
       </c>
       <c r="C1414" s="6" t="s">
-        <v>8900</v>
+        <v>8903</v>
       </c>
       <c r="D1414" s="6" t="s">
-        <v>8901</v>
+        <v>8904</v>
       </c>
     </row>
     <row r="1415">
       <c r="B1415" s="5" t="s">
-        <v>8902</v>
+        <v>8905</v>
       </c>
       <c r="C1415" s="5" t="s">
-        <v>8903</v>
+        <v>8906</v>
       </c>
       <c r="D1415" s="5" t="s">
-        <v>8904</v>
+        <v>8907</v>
       </c>
     </row>
     <row r="1416">
       <c r="B1416" s="6" t="s">
-        <v>8905</v>
+        <v>8908</v>
       </c>
       <c r="C1416" s="6" t="s">
-        <v>8906</v>
+        <v>8909</v>
       </c>
       <c r="D1416" s="6" t="s">
-        <v>8907</v>
+        <v>8910</v>
       </c>
     </row>
     <row r="1417">
       <c r="B1417" s="5" t="s">
-        <v>8908</v>
+        <v>8911</v>
       </c>
       <c r="C1417" s="5" t="s">
-        <v>8909</v>
+        <v>8912</v>
       </c>
       <c r="D1417" s="5" t="s">
-        <v>8910</v>
+        <v>8913</v>
       </c>
     </row>
     <row r="1418">
       <c r="B1418" s="6" t="s">
-        <v>8911</v>
+        <v>8914</v>
       </c>
       <c r="C1418" s="6" t="s">
-        <v>8912</v>
+        <v>8915</v>
       </c>
       <c r="D1418" s="6" t="s">
-        <v>8913</v>
+        <v>8916</v>
       </c>
     </row>
     <row r="1419">
       <c r="B1419" s="5" t="s">
-        <v>8914</v>
+        <v>8917</v>
       </c>
       <c r="C1419" s="5" t="s">
-        <v>8915</v>
+        <v>8918</v>
       </c>
       <c r="D1419" s="5" t="s">
-        <v>8916</v>
+        <v>8919</v>
       </c>
     </row>
     <row r="1420">
       <c r="B1420" s="6" t="s">
-        <v>8917</v>
+        <v>8920</v>
       </c>
       <c r="C1420" s="6" t="s">
-        <v>8918</v>
+        <v>8921</v>
       </c>
       <c r="D1420" s="6" t="s">
-        <v>8919</v>
+        <v>8922</v>
       </c>
     </row>
     <row r="1421">
       <c r="B1421" s="5" t="s">
-        <v>8920</v>
+        <v>8923</v>
       </c>
       <c r="C1421" s="5" t="s">
-        <v>6112</v>
+        <v>8924</v>
       </c>
       <c r="D1421" s="5" t="s">
-        <v>8735</v>
+        <v>8925</v>
       </c>
     </row>
     <row r="1422">
       <c r="B1422" s="6" t="s">
-        <v>8921</v>
+        <v>8926</v>
       </c>
       <c r="C1422" s="6" t="s">
-        <v>8922</v>
+        <v>6112</v>
       </c>
       <c r="D1422" s="6" t="s">
-        <v>8923</v>
+        <v>8741</v>
       </c>
     </row>
     <row r="1423">
       <c r="B1423" s="5" t="s">
-        <v>8924</v>
+        <v>8927</v>
       </c>
       <c r="C1423" s="5" t="s">
-        <v>8925</v>
+        <v>8928</v>
       </c>
       <c r="D1423" s="5" t="s">
-        <v>8926</v>
+        <v>8929</v>
       </c>
     </row>
     <row r="1424">
       <c r="B1424" s="6" t="s">
-        <v>8927</v>
+        <v>8930</v>
       </c>
       <c r="C1424" s="6" t="s">
-        <v>8928</v>
+        <v>8931</v>
       </c>
       <c r="D1424" s="6" t="s">
-        <v>8929</v>
+        <v>8932</v>
       </c>
     </row>
     <row r="1425">
       <c r="B1425" s="5" t="s">
-        <v>8930</v>
+        <v>8933</v>
       </c>
       <c r="C1425" s="5" t="s">
-        <v>8931</v>
+        <v>8934</v>
       </c>
       <c r="D1425" s="5" t="s">
-        <v>8932</v>
+        <v>8935</v>
       </c>
     </row>
     <row r="1426">
       <c r="B1426" s="6" t="s">
-        <v>8933</v>
+        <v>8936</v>
       </c>
       <c r="C1426" s="6" t="s">
-        <v>8934</v>
+        <v>8937</v>
       </c>
       <c r="D1426" s="6" t="s">
-        <v>8935</v>
+        <v>8938</v>
       </c>
     </row>
     <row r="1427">
       <c r="B1427" s="5" t="s">
-        <v>8936</v>
+        <v>8939</v>
       </c>
       <c r="C1427" s="5" t="s">
-        <v>8937</v>
+        <v>8940</v>
       </c>
       <c r="D1427" s="5" t="s">
-        <v>8938</v>
+        <v>8941</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="B1428" s="6" t="s">
+        <v>8942</v>
+      </c>
+      <c r="C1428" s="6" t="s">
+        <v>8943</v>
+      </c>
+      <c r="D1428" s="6" t="s">
+        <v>8944</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H1427"/>
+  <autoFilter ref="B2:H1428"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -59726,10 +59767,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>8939</v>
+        <v>8945</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8940</v>
+        <v>8946</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -59740,16 +59781,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8941</v>
+        <v>8947</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8942</v>
+        <v>8948</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8943</v>
+        <v>8949</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8944</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="3">
@@ -59757,16 +59798,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8945</v>
+        <v>8951</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8946</v>
+        <v>8952</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8947</v>
+        <v>8953</v>
       </c>
     </row>
     <row r="4">
@@ -59777,24 +59818,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8948</v>
+        <v>8954</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8949</v>
+        <v>8955</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8950</v>
+        <v>8956</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>8951</v>
+        <v>8957</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4569</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8952</v>
+        <v>8958</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -59802,13 +59843,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>8953</v>
+        <v>8959</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4576</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>8954</v>
+        <v>8960</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -59816,13 +59857,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>8955</v>
+        <v>8961</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4582</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8956</v>
+        <v>8962</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -59830,13 +59871,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>8957</v>
+        <v>8963</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4588</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>8958</v>
+        <v>8964</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -59844,13 +59885,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>8959</v>
+        <v>8965</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4595</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8960</v>
+        <v>8966</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -59858,13 +59899,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>8961</v>
+        <v>8967</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4602</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>8962</v>
+        <v>8968</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -59872,13 +59913,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>8963</v>
+        <v>8969</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4608</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>8964</v>
+        <v>8970</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -59886,13 +59927,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>8965</v>
+        <v>8971</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4614</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>8966</v>
+        <v>8972</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -59900,13 +59941,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>8967</v>
+        <v>8973</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4621</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8968</v>
+        <v>8974</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -59914,13 +59955,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>8969</v>
+        <v>8975</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4627</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>8970</v>
+        <v>8976</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -59934,7 +59975,7 @@
         <v>4633</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8971</v>
+        <v>8977</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -59942,13 +59983,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>8972</v>
+        <v>8978</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4640</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>8973</v>
+        <v>8979</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -59956,13 +59997,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>8974</v>
+        <v>8980</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4647</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>8975</v>
+        <v>8981</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -59970,13 +60011,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>8976</v>
+        <v>8982</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4653</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>8977</v>
+        <v>8983</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -59984,13 +60025,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>8978</v>
+        <v>8984</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4660</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>8979</v>
+        <v>8985</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -59998,13 +60039,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>8980</v>
+        <v>8986</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4666</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>8981</v>
+        <v>8987</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -60012,13 +60053,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>8982</v>
+        <v>8988</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4671</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>8983</v>
+        <v>8989</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -60026,13 +60067,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>8984</v>
+        <v>8990</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4678</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>8985</v>
+        <v>8991</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -60040,13 +60081,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>8986</v>
+        <v>8992</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4500</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>8987</v>
+        <v>8993</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -60054,13 +60095,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>8988</v>
+        <v>8994</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4686</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>8989</v>
+        <v>8995</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1431]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1433]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9986" uniqueCount="9015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10000" uniqueCount="9028">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -24104,6 +24104,45 @@
   </si>
   <si>
     <t xml:space="preserve">Wird abgerechnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.payout.nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">받을 것이 없습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing to cash out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受け取るものがありません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没有可收下的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沒有可收下的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nichts zu kassieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.payout.next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">次へ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下一步</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weiter</t>
   </si>
   <si>
     <t xml:space="preserve">ui.button.jokers</t>
@@ -27270,7 +27309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1431"/>
+  <dimension ref="A1:H1433"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -56250,68 +56289,68 @@
         <v>8029</v>
       </c>
       <c r="C1262" s="6" t="s">
-        <v>6033</v>
+        <v>8030</v>
       </c>
       <c r="D1262" s="6" t="s">
-        <v>8030</v>
+        <v>8031</v>
       </c>
       <c r="E1262" s="6" t="s">
-        <v>6035</v>
+        <v>8032</v>
       </c>
       <c r="F1262" s="6" t="s">
-        <v>8031</v>
+        <v>8033</v>
       </c>
       <c r="G1262" s="6" t="s">
-        <v>8031</v>
+        <v>8034</v>
       </c>
       <c r="H1262" s="6" t="s">
-        <v>5404</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="1263">
       <c r="B1263" s="5" t="s">
-        <v>8032</v>
+        <v>8036</v>
       </c>
       <c r="C1263" s="5" t="s">
-        <v>8033</v>
+        <v>8037</v>
       </c>
       <c r="D1263" s="5" t="s">
-        <v>8034</v>
+        <v>8038</v>
       </c>
       <c r="E1263" s="5" t="s">
-        <v>8035</v>
+        <v>8039</v>
       </c>
       <c r="F1263" s="5" t="s">
-        <v>8036</v>
+        <v>8040</v>
       </c>
       <c r="G1263" s="5" t="s">
-        <v>8036</v>
+        <v>8040</v>
       </c>
       <c r="H1263" s="5" t="s">
-        <v>8037</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="1264">
       <c r="B1264" s="6" t="s">
-        <v>8038</v>
+        <v>8042</v>
       </c>
       <c r="C1264" s="6" t="s">
-        <v>8039</v>
+        <v>6033</v>
       </c>
       <c r="D1264" s="6" t="s">
-        <v>8040</v>
+        <v>8043</v>
       </c>
       <c r="E1264" s="6" t="s">
-        <v>8041</v>
+        <v>6035</v>
       </c>
       <c r="F1264" s="6" t="s">
-        <v>8042</v>
+        <v>8044</v>
       </c>
       <c r="G1264" s="6" t="s">
-        <v>8043</v>
+        <v>8044</v>
       </c>
       <c r="H1264" s="6" t="s">
-        <v>8044</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1265">
@@ -56331,76 +56370,76 @@
         <v>8049</v>
       </c>
       <c r="G1265" s="5" t="s">
+        <v>8049</v>
+      </c>
+      <c r="H1265" s="5" t="s">
         <v>8050</v>
-      </c>
-      <c r="H1265" s="5" t="s">
-        <v>8051</v>
       </c>
     </row>
     <row r="1266">
       <c r="B1266" s="6" t="s">
+        <v>8051</v>
+      </c>
+      <c r="C1266" s="6" t="s">
         <v>8052</v>
       </c>
-      <c r="C1266" s="6" t="s">
+      <c r="D1266" s="6" t="s">
         <v>8053</v>
-      </c>
-      <c r="D1266" s="6" t="s">
-        <v>8054</v>
       </c>
       <c r="E1266" s="6" t="s">
         <v>8054</v>
       </c>
       <c r="F1266" s="6" t="s">
-        <v>8054</v>
+        <v>8055</v>
       </c>
       <c r="G1266" s="6" t="s">
-        <v>8054</v>
+        <v>8056</v>
       </c>
       <c r="H1266" s="6" t="s">
-        <v>8054</v>
+        <v>8057</v>
       </c>
     </row>
     <row r="1267">
       <c r="B1267" s="5" t="s">
-        <v>8055</v>
+        <v>8058</v>
       </c>
       <c r="C1267" s="5" t="s">
-        <v>8056</v>
+        <v>8059</v>
       </c>
       <c r="D1267" s="5" t="s">
-        <v>8057</v>
+        <v>8060</v>
       </c>
       <c r="E1267" s="5" t="s">
-        <v>8058</v>
+        <v>8061</v>
       </c>
       <c r="F1267" s="5" t="s">
-        <v>8059</v>
+        <v>8062</v>
       </c>
       <c r="G1267" s="5" t="s">
-        <v>8059</v>
+        <v>8063</v>
       </c>
       <c r="H1267" s="5" t="s">
-        <v>8060</v>
+        <v>8064</v>
       </c>
     </row>
     <row r="1268">
       <c r="B1268" s="6" t="s">
-        <v>8061</v>
+        <v>8065</v>
       </c>
       <c r="C1268" s="6" t="s">
-        <v>8062</v>
+        <v>8066</v>
       </c>
       <c r="D1268" s="6" t="s">
-        <v>8063</v>
+        <v>8067</v>
       </c>
       <c r="E1268" s="6" t="s">
-        <v>8064</v>
+        <v>8067</v>
       </c>
       <c r="F1268" s="6" t="s">
-        <v>8065</v>
+        <v>8067</v>
       </c>
       <c r="G1268" s="6" t="s">
-        <v>8066</v>
+        <v>8067</v>
       </c>
       <c r="H1268" s="6" t="s">
         <v>8067</v>
@@ -56423,102 +56462,102 @@
         <v>8072</v>
       </c>
       <c r="G1269" s="5" t="s">
+        <v>8072</v>
+      </c>
+      <c r="H1269" s="5" t="s">
         <v>8073</v>
-      </c>
-      <c r="H1269" s="5" t="s">
-        <v>8074</v>
       </c>
     </row>
     <row r="1270">
       <c r="B1270" s="6" t="s">
+        <v>8074</v>
+      </c>
+      <c r="C1270" s="6" t="s">
         <v>8075</v>
       </c>
-      <c r="C1270" s="6" t="s">
+      <c r="D1270" s="6" t="s">
         <v>8076</v>
       </c>
-      <c r="D1270" s="6" t="s">
+      <c r="E1270" s="6" t="s">
         <v>8077</v>
       </c>
-      <c r="E1270" s="6" t="s">
+      <c r="F1270" s="6" t="s">
         <v>8078</v>
       </c>
-      <c r="F1270" s="6" t="s">
+      <c r="G1270" s="6" t="s">
         <v>8079</v>
       </c>
-      <c r="G1270" s="6" t="s">
+      <c r="H1270" s="6" t="s">
         <v>8080</v>
-      </c>
-      <c r="H1270" s="6" t="s">
-        <v>8081</v>
       </c>
     </row>
     <row r="1271">
       <c r="B1271" s="5" t="s">
+        <v>8081</v>
+      </c>
+      <c r="C1271" s="5" t="s">
         <v>8082</v>
       </c>
-      <c r="C1271" s="5" t="s">
+      <c r="D1271" s="5" t="s">
         <v>8083</v>
       </c>
-      <c r="D1271" s="5" t="s">
+      <c r="E1271" s="5" t="s">
         <v>8084</v>
       </c>
-      <c r="E1271" s="5" t="s">
-        <v>6245</v>
-      </c>
       <c r="F1271" s="5" t="s">
-        <v>6246</v>
+        <v>8085</v>
       </c>
       <c r="G1271" s="5" t="s">
-        <v>6246</v>
+        <v>8086</v>
       </c>
       <c r="H1271" s="5" t="s">
-        <v>7145</v>
+        <v>8087</v>
       </c>
     </row>
     <row r="1272">
       <c r="B1272" s="6" t="s">
-        <v>8085</v>
+        <v>8088</v>
       </c>
       <c r="C1272" s="6" t="s">
-        <v>8086</v>
+        <v>8089</v>
       </c>
       <c r="D1272" s="6" t="s">
-        <v>8087</v>
+        <v>8090</v>
       </c>
       <c r="E1272" s="6" t="s">
-        <v>8088</v>
+        <v>8091</v>
       </c>
       <c r="F1272" s="6" t="s">
-        <v>8089</v>
+        <v>8092</v>
       </c>
       <c r="G1272" s="6" t="s">
-        <v>8090</v>
+        <v>8093</v>
       </c>
       <c r="H1272" s="6" t="s">
-        <v>8087</v>
+        <v>8094</v>
       </c>
     </row>
     <row r="1273">
       <c r="B1273" s="5" t="s">
-        <v>8091</v>
+        <v>8095</v>
       </c>
       <c r="C1273" s="5" t="s">
-        <v>8092</v>
+        <v>8096</v>
       </c>
       <c r="D1273" s="5" t="s">
-        <v>8093</v>
+        <v>8097</v>
       </c>
       <c r="E1273" s="5" t="s">
-        <v>8094</v>
+        <v>6245</v>
       </c>
       <c r="F1273" s="5" t="s">
-        <v>8095</v>
+        <v>6246</v>
       </c>
       <c r="G1273" s="5" t="s">
-        <v>8096</v>
+        <v>6246</v>
       </c>
       <c r="H1273" s="5" t="s">
-        <v>8097</v>
+        <v>7145</v>
       </c>
     </row>
     <row r="1274">
@@ -56538,10 +56577,10 @@
         <v>8102</v>
       </c>
       <c r="G1274" s="6" t="s">
-        <v>8102</v>
+        <v>8103</v>
       </c>
       <c r="H1274" s="6" t="s">
-        <v>8103</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="1275">
@@ -56584,27 +56623,27 @@
         <v>8115</v>
       </c>
       <c r="G1276" s="6" t="s">
+        <v>8115</v>
+      </c>
+      <c r="H1276" s="6" t="s">
         <v>8116</v>
-      </c>
-      <c r="H1276" s="6" t="s">
-        <v>8117</v>
       </c>
     </row>
     <row r="1277">
       <c r="B1277" s="5" t="s">
+        <v>8117</v>
+      </c>
+      <c r="C1277" s="5" t="s">
         <v>8118</v>
       </c>
-      <c r="C1277" s="5" t="s">
+      <c r="D1277" s="5" t="s">
         <v>8119</v>
       </c>
-      <c r="D1277" s="5" t="s">
+      <c r="E1277" s="5" t="s">
         <v>8120</v>
       </c>
-      <c r="E1277" s="5" t="s">
+      <c r="F1277" s="5" t="s">
         <v>8121</v>
-      </c>
-      <c r="F1277" s="5" t="s">
-        <v>8122</v>
       </c>
       <c r="G1277" s="5" t="s">
         <v>8122</v>
@@ -56630,50 +56669,50 @@
         <v>8128</v>
       </c>
       <c r="G1278" s="6" t="s">
-        <v>8128</v>
+        <v>8129</v>
       </c>
       <c r="H1278" s="6" t="s">
-        <v>8129</v>
+        <v>8130</v>
       </c>
     </row>
     <row r="1279">
       <c r="B1279" s="5" t="s">
-        <v>8130</v>
+        <v>8131</v>
       </c>
       <c r="C1279" s="5" t="s">
-        <v>8131</v>
+        <v>8132</v>
       </c>
       <c r="D1279" s="5" t="s">
-        <v>8132</v>
+        <v>8133</v>
       </c>
       <c r="E1279" s="5" t="s">
-        <v>8133</v>
+        <v>8134</v>
       </c>
       <c r="F1279" s="5" t="s">
-        <v>8134</v>
+        <v>8135</v>
       </c>
       <c r="G1279" s="5" t="s">
-        <v>8134</v>
+        <v>8135</v>
       </c>
       <c r="H1279" s="5" t="s">
-        <v>8135</v>
+        <v>8136</v>
       </c>
     </row>
     <row r="1280">
       <c r="B1280" s="6" t="s">
-        <v>8136</v>
+        <v>8137</v>
       </c>
       <c r="C1280" s="6" t="s">
-        <v>8137</v>
+        <v>8138</v>
       </c>
       <c r="D1280" s="6" t="s">
-        <v>8138</v>
+        <v>8139</v>
       </c>
       <c r="E1280" s="6" t="s">
-        <v>8139</v>
+        <v>8140</v>
       </c>
       <c r="F1280" s="6" t="s">
-        <v>8140</v>
+        <v>8141</v>
       </c>
       <c r="G1280" s="6" t="s">
         <v>8141</v>
@@ -56699,27 +56738,27 @@
         <v>8147</v>
       </c>
       <c r="G1281" s="5" t="s">
+        <v>8147</v>
+      </c>
+      <c r="H1281" s="5" t="s">
         <v>8148</v>
-      </c>
-      <c r="H1281" s="5" t="s">
-        <v>8149</v>
       </c>
     </row>
     <row r="1282">
       <c r="B1282" s="6" t="s">
+        <v>8149</v>
+      </c>
+      <c r="C1282" s="6" t="s">
         <v>8150</v>
       </c>
-      <c r="C1282" s="6" t="s">
+      <c r="D1282" s="6" t="s">
         <v>8151</v>
       </c>
-      <c r="D1282" s="6" t="s">
+      <c r="E1282" s="6" t="s">
         <v>8152</v>
       </c>
-      <c r="E1282" s="6" t="s">
+      <c r="F1282" s="6" t="s">
         <v>8153</v>
-      </c>
-      <c r="F1282" s="6" t="s">
-        <v>8154</v>
       </c>
       <c r="G1282" s="6" t="s">
         <v>8154</v>
@@ -56837,96 +56876,96 @@
         <v>8186</v>
       </c>
       <c r="G1287" s="5" t="s">
-        <v>8186</v>
+        <v>8187</v>
       </c>
       <c r="H1287" s="5" t="s">
-        <v>8187</v>
+        <v>8188</v>
       </c>
     </row>
     <row r="1288">
       <c r="B1288" s="6" t="s">
-        <v>8188</v>
+        <v>8189</v>
       </c>
       <c r="C1288" s="6" t="s">
-        <v>8189</v>
+        <v>8190</v>
       </c>
       <c r="D1288" s="6" t="s">
-        <v>2758</v>
+        <v>8191</v>
       </c>
       <c r="E1288" s="6" t="s">
-        <v>2759</v>
+        <v>8192</v>
       </c>
       <c r="F1288" s="6" t="s">
-        <v>2760</v>
+        <v>8193</v>
       </c>
       <c r="G1288" s="6" t="s">
-        <v>2760</v>
+        <v>8193</v>
       </c>
       <c r="H1288" s="6" t="s">
-        <v>2761</v>
+        <v>8194</v>
       </c>
     </row>
     <row r="1289">
       <c r="B1289" s="5" t="s">
-        <v>8190</v>
+        <v>8195</v>
       </c>
       <c r="C1289" s="5" t="s">
-        <v>8191</v>
+        <v>8196</v>
       </c>
       <c r="D1289" s="5" t="s">
-        <v>8192</v>
+        <v>8197</v>
       </c>
       <c r="E1289" s="5" t="s">
-        <v>8193</v>
+        <v>8198</v>
       </c>
       <c r="F1289" s="5" t="s">
-        <v>8194</v>
+        <v>8199</v>
       </c>
       <c r="G1289" s="5" t="s">
-        <v>8194</v>
+        <v>8199</v>
       </c>
       <c r="H1289" s="5" t="s">
-        <v>8195</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="1290">
       <c r="B1290" s="6" t="s">
-        <v>8196</v>
+        <v>8201</v>
       </c>
       <c r="C1290" s="6" t="s">
-        <v>8197</v>
+        <v>8202</v>
       </c>
       <c r="D1290" s="6" t="s">
-        <v>8198</v>
+        <v>2758</v>
       </c>
       <c r="E1290" s="6" t="s">
-        <v>8199</v>
+        <v>2759</v>
       </c>
       <c r="F1290" s="6" t="s">
-        <v>8200</v>
+        <v>2760</v>
       </c>
       <c r="G1290" s="6" t="s">
-        <v>8199</v>
+        <v>2760</v>
       </c>
       <c r="H1290" s="6" t="s">
-        <v>8201</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="1291">
       <c r="B1291" s="5" t="s">
-        <v>8202</v>
+        <v>8203</v>
       </c>
       <c r="C1291" s="5" t="s">
-        <v>8203</v>
+        <v>8204</v>
       </c>
       <c r="D1291" s="5" t="s">
-        <v>8204</v>
+        <v>8205</v>
       </c>
       <c r="E1291" s="5" t="s">
-        <v>8205</v>
+        <v>8206</v>
       </c>
       <c r="F1291" s="5" t="s">
-        <v>8206</v>
+        <v>8207</v>
       </c>
       <c r="G1291" s="5" t="s">
         <v>8207</v>
@@ -56952,7 +56991,7 @@
         <v>8213</v>
       </c>
       <c r="G1292" s="6" t="s">
-        <v>8213</v>
+        <v>8212</v>
       </c>
       <c r="H1292" s="6" t="s">
         <v>8214</v>
@@ -56975,27 +57014,27 @@
         <v>8219</v>
       </c>
       <c r="G1293" s="5" t="s">
-        <v>8219</v>
+        <v>8220</v>
       </c>
       <c r="H1293" s="5" t="s">
-        <v>8220</v>
+        <v>8221</v>
       </c>
     </row>
     <row r="1294">
       <c r="B1294" s="6" t="s">
-        <v>8221</v>
+        <v>8222</v>
       </c>
       <c r="C1294" s="6" t="s">
-        <v>8222</v>
+        <v>8223</v>
       </c>
       <c r="D1294" s="6" t="s">
-        <v>8223</v>
+        <v>8224</v>
       </c>
       <c r="E1294" s="6" t="s">
-        <v>8224</v>
+        <v>8225</v>
       </c>
       <c r="F1294" s="6" t="s">
-        <v>8225</v>
+        <v>8226</v>
       </c>
       <c r="G1294" s="6" t="s">
         <v>8226</v>
@@ -57021,168 +57060,168 @@
         <v>8232</v>
       </c>
       <c r="G1295" s="5" t="s">
+        <v>8232</v>
+      </c>
+      <c r="H1295" s="5" t="s">
         <v>8233</v>
-      </c>
-      <c r="H1295" s="5" t="s">
-        <v>8234</v>
       </c>
     </row>
     <row r="1296">
       <c r="B1296" s="6" t="s">
+        <v>8234</v>
+      </c>
+      <c r="C1296" s="6" t="s">
         <v>8235</v>
       </c>
-      <c r="C1296" s="6" t="s">
+      <c r="D1296" s="6" t="s">
         <v>8236</v>
       </c>
-      <c r="D1296" s="6" t="s">
+      <c r="E1296" s="6" t="s">
         <v>8237</v>
       </c>
-      <c r="E1296" s="6" t="s">
+      <c r="F1296" s="6" t="s">
         <v>8238</v>
       </c>
-      <c r="F1296" s="6" t="s">
+      <c r="G1296" s="6" t="s">
         <v>8239</v>
       </c>
-      <c r="G1296" s="6" t="s">
+      <c r="H1296" s="6" t="s">
         <v>8240</v>
-      </c>
-      <c r="H1296" s="6" t="s">
-        <v>8241</v>
       </c>
     </row>
     <row r="1297">
       <c r="B1297" s="5" t="s">
+        <v>8241</v>
+      </c>
+      <c r="C1297" s="5" t="s">
         <v>8242</v>
-      </c>
-      <c r="C1297" s="5" t="s">
-        <v>7101</v>
       </c>
       <c r="D1297" s="5" t="s">
         <v>8243</v>
       </c>
       <c r="E1297" s="5" t="s">
-        <v>7102</v>
+        <v>8244</v>
       </c>
       <c r="F1297" s="5" t="s">
-        <v>7103</v>
+        <v>8245</v>
       </c>
       <c r="G1297" s="5" t="s">
-        <v>7104</v>
+        <v>8246</v>
       </c>
       <c r="H1297" s="5" t="s">
-        <v>8243</v>
+        <v>8247</v>
       </c>
     </row>
     <row r="1298">
       <c r="B1298" s="6" t="s">
-        <v>8244</v>
+        <v>8248</v>
       </c>
       <c r="C1298" s="6" t="s">
-        <v>6895</v>
+        <v>8249</v>
       </c>
       <c r="D1298" s="6" t="s">
-        <v>8245</v>
+        <v>8250</v>
       </c>
       <c r="E1298" s="6" t="s">
-        <v>6897</v>
+        <v>8251</v>
       </c>
       <c r="F1298" s="6" t="s">
-        <v>8246</v>
+        <v>8252</v>
       </c>
       <c r="G1298" s="6" t="s">
-        <v>8247</v>
+        <v>8253</v>
       </c>
       <c r="H1298" s="6" t="s">
-        <v>8248</v>
+        <v>8254</v>
       </c>
     </row>
     <row r="1299">
       <c r="B1299" s="5" t="s">
-        <v>8249</v>
+        <v>8255</v>
       </c>
       <c r="C1299" s="5" t="s">
-        <v>8250</v>
+        <v>7101</v>
       </c>
       <c r="D1299" s="5" t="s">
-        <v>8251</v>
+        <v>8256</v>
       </c>
       <c r="E1299" s="5" t="s">
-        <v>8252</v>
+        <v>7102</v>
       </c>
       <c r="F1299" s="5" t="s">
-        <v>8253</v>
+        <v>7103</v>
       </c>
       <c r="G1299" s="5" t="s">
-        <v>8254</v>
+        <v>7104</v>
       </c>
       <c r="H1299" s="5" t="s">
-        <v>8255</v>
+        <v>8256</v>
       </c>
     </row>
     <row r="1300">
       <c r="B1300" s="6" t="s">
-        <v>8256</v>
+        <v>8257</v>
       </c>
       <c r="C1300" s="6" t="s">
-        <v>8257</v>
+        <v>6895</v>
       </c>
       <c r="D1300" s="6" t="s">
         <v>8258</v>
       </c>
       <c r="E1300" s="6" t="s">
-        <v>8231</v>
+        <v>6897</v>
       </c>
       <c r="F1300" s="6" t="s">
-        <v>8232</v>
+        <v>8259</v>
       </c>
       <c r="G1300" s="6" t="s">
-        <v>8233</v>
+        <v>8260</v>
       </c>
       <c r="H1300" s="6" t="s">
-        <v>8259</v>
+        <v>8261</v>
       </c>
     </row>
     <row r="1301">
       <c r="B1301" s="5" t="s">
-        <v>8260</v>
+        <v>8262</v>
       </c>
       <c r="C1301" s="5" t="s">
-        <v>8261</v>
+        <v>8263</v>
       </c>
       <c r="D1301" s="5" t="s">
-        <v>8262</v>
+        <v>8264</v>
       </c>
       <c r="E1301" s="5" t="s">
-        <v>8263</v>
+        <v>8265</v>
       </c>
       <c r="F1301" s="5" t="s">
-        <v>8264</v>
+        <v>8266</v>
       </c>
       <c r="G1301" s="5" t="s">
-        <v>8265</v>
+        <v>8267</v>
       </c>
       <c r="H1301" s="5" t="s">
-        <v>8266</v>
+        <v>8268</v>
       </c>
     </row>
     <row r="1302">
       <c r="B1302" s="6" t="s">
-        <v>8267</v>
+        <v>8269</v>
       </c>
       <c r="C1302" s="6" t="s">
-        <v>8268</v>
+        <v>8270</v>
       </c>
       <c r="D1302" s="6" t="s">
-        <v>8269</v>
+        <v>8271</v>
       </c>
       <c r="E1302" s="6" t="s">
-        <v>8270</v>
+        <v>8244</v>
       </c>
       <c r="F1302" s="6" t="s">
-        <v>8271</v>
+        <v>8245</v>
       </c>
       <c r="G1302" s="6" t="s">
-        <v>8271</v>
+        <v>8246</v>
       </c>
       <c r="H1302" s="6" t="s">
         <v>8272</v>
@@ -57228,464 +57267,464 @@
         <v>8284</v>
       </c>
       <c r="G1304" s="6" t="s">
+        <v>8284</v>
+      </c>
+      <c r="H1304" s="6" t="s">
         <v>8285</v>
-      </c>
-      <c r="H1304" s="6" t="s">
-        <v>8286</v>
       </c>
     </row>
     <row r="1305">
       <c r="B1305" s="5" t="s">
+        <v>8286</v>
+      </c>
+      <c r="C1305" s="5" t="s">
         <v>8287</v>
       </c>
-      <c r="C1305" s="5" t="s">
+      <c r="D1305" s="5" t="s">
         <v>8288</v>
       </c>
-      <c r="D1305" s="5" t="s">
+      <c r="E1305" s="5" t="s">
         <v>8289</v>
       </c>
-      <c r="E1305" s="5" t="s">
+      <c r="F1305" s="5" t="s">
         <v>8290</v>
       </c>
-      <c r="F1305" s="5" t="s">
-        <v>7463</v>
-      </c>
       <c r="G1305" s="5" t="s">
-        <v>7464</v>
+        <v>8291</v>
       </c>
       <c r="H1305" s="5" t="s">
-        <v>8291</v>
+        <v>8292</v>
       </c>
     </row>
     <row r="1306">
       <c r="B1306" s="6" t="s">
-        <v>8292</v>
+        <v>8293</v>
       </c>
       <c r="C1306" s="6" t="s">
-        <v>8293</v>
+        <v>8294</v>
       </c>
       <c r="D1306" s="6" t="s">
-        <v>8294</v>
+        <v>8295</v>
       </c>
       <c r="E1306" s="6" t="s">
-        <v>8295</v>
+        <v>8296</v>
       </c>
       <c r="F1306" s="6" t="s">
-        <v>8296</v>
+        <v>8297</v>
       </c>
       <c r="G1306" s="6" t="s">
-        <v>8297</v>
+        <v>8298</v>
       </c>
       <c r="H1306" s="6" t="s">
-        <v>8298</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="1307">
       <c r="B1307" s="5" t="s">
-        <v>8299</v>
+        <v>8300</v>
       </c>
       <c r="C1307" s="5" t="s">
-        <v>8300</v>
+        <v>8301</v>
       </c>
       <c r="D1307" s="5" t="s">
-        <v>8301</v>
+        <v>8302</v>
       </c>
       <c r="E1307" s="5" t="s">
-        <v>8302</v>
+        <v>8303</v>
       </c>
       <c r="F1307" s="5" t="s">
-        <v>8303</v>
+        <v>7463</v>
       </c>
       <c r="G1307" s="5" t="s">
-        <v>8302</v>
+        <v>7464</v>
       </c>
       <c r="H1307" s="5" t="s">
-        <v>8301</v>
+        <v>8304</v>
       </c>
     </row>
     <row r="1308">
       <c r="B1308" s="6" t="s">
-        <v>8304</v>
+        <v>8305</v>
       </c>
       <c r="C1308" s="6" t="s">
-        <v>6033</v>
+        <v>8306</v>
       </c>
       <c r="D1308" s="6" t="s">
-        <v>8030</v>
+        <v>8307</v>
       </c>
       <c r="E1308" s="6" t="s">
-        <v>6035</v>
+        <v>8308</v>
       </c>
       <c r="F1308" s="6" t="s">
-        <v>8031</v>
+        <v>8309</v>
       </c>
       <c r="G1308" s="6" t="s">
-        <v>8031</v>
+        <v>8310</v>
       </c>
       <c r="H1308" s="6" t="s">
-        <v>5404</v>
+        <v>8311</v>
       </c>
     </row>
     <row r="1309">
       <c r="B1309" s="5" t="s">
-        <v>8305</v>
+        <v>8312</v>
       </c>
       <c r="C1309" s="5" t="s">
-        <v>6080</v>
+        <v>8313</v>
       </c>
       <c r="D1309" s="5" t="s">
-        <v>8306</v>
+        <v>8314</v>
       </c>
       <c r="E1309" s="5" t="s">
-        <v>6082</v>
+        <v>8315</v>
       </c>
       <c r="F1309" s="5" t="s">
-        <v>8307</v>
+        <v>8316</v>
       </c>
       <c r="G1309" s="5" t="s">
-        <v>8308</v>
+        <v>8315</v>
       </c>
       <c r="H1309" s="5" t="s">
-        <v>8309</v>
+        <v>8314</v>
       </c>
     </row>
     <row r="1310">
       <c r="B1310" s="6" t="s">
-        <v>8310</v>
+        <v>8317</v>
       </c>
       <c r="C1310" s="6" t="s">
-        <v>7081</v>
+        <v>6033</v>
       </c>
       <c r="D1310" s="6" t="s">
-        <v>8311</v>
+        <v>8043</v>
       </c>
       <c r="E1310" s="6" t="s">
-        <v>7083</v>
+        <v>6035</v>
       </c>
       <c r="F1310" s="6" t="s">
-        <v>6016</v>
+        <v>8044</v>
       </c>
       <c r="G1310" s="6" t="s">
-        <v>6017</v>
+        <v>8044</v>
       </c>
       <c r="H1310" s="6" t="s">
-        <v>7082</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1311">
       <c r="B1311" s="5" t="s">
-        <v>8312</v>
+        <v>8318</v>
       </c>
       <c r="C1311" s="5" t="s">
-        <v>7087</v>
+        <v>6080</v>
       </c>
       <c r="D1311" s="5" t="s">
-        <v>8313</v>
+        <v>8319</v>
       </c>
       <c r="E1311" s="5" t="s">
-        <v>7089</v>
+        <v>6082</v>
       </c>
       <c r="F1311" s="5" t="s">
-        <v>6023</v>
+        <v>8320</v>
       </c>
       <c r="G1311" s="5" t="s">
-        <v>6023</v>
+        <v>8321</v>
       </c>
       <c r="H1311" s="5" t="s">
-        <v>8314</v>
+        <v>8322</v>
       </c>
     </row>
     <row r="1312">
       <c r="B1312" s="6" t="s">
-        <v>8315</v>
+        <v>8323</v>
       </c>
       <c r="C1312" s="6" t="s">
-        <v>7092</v>
+        <v>7081</v>
       </c>
       <c r="D1312" s="6" t="s">
-        <v>8316</v>
+        <v>8324</v>
       </c>
       <c r="E1312" s="6" t="s">
-        <v>7094</v>
+        <v>7083</v>
       </c>
       <c r="F1312" s="6" t="s">
-        <v>6029</v>
+        <v>6016</v>
       </c>
       <c r="G1312" s="6" t="s">
-        <v>6030</v>
+        <v>6017</v>
       </c>
       <c r="H1312" s="6" t="s">
-        <v>7097</v>
+        <v>7082</v>
       </c>
     </row>
     <row r="1313">
       <c r="B1313" s="5" t="s">
-        <v>8317</v>
+        <v>8325</v>
       </c>
       <c r="C1313" s="5" t="s">
-        <v>6046</v>
+        <v>7087</v>
       </c>
       <c r="D1313" s="5" t="s">
-        <v>8318</v>
+        <v>8326</v>
       </c>
       <c r="E1313" s="5" t="s">
-        <v>6048</v>
+        <v>7089</v>
       </c>
       <c r="F1313" s="5" t="s">
-        <v>6049</v>
+        <v>6023</v>
       </c>
       <c r="G1313" s="5" t="s">
-        <v>6050</v>
+        <v>6023</v>
       </c>
       <c r="H1313" s="5" t="s">
-        <v>8319</v>
+        <v>8327</v>
       </c>
     </row>
     <row r="1314">
       <c r="B1314" s="6" t="s">
-        <v>8320</v>
+        <v>8328</v>
       </c>
       <c r="C1314" s="6" t="s">
-        <v>8321</v>
+        <v>7092</v>
       </c>
       <c r="D1314" s="6" t="s">
-        <v>8322</v>
+        <v>8329</v>
       </c>
       <c r="E1314" s="6" t="s">
-        <v>6076</v>
+        <v>7094</v>
       </c>
       <c r="F1314" s="6" t="s">
-        <v>8323</v>
+        <v>6029</v>
       </c>
       <c r="G1314" s="6" t="s">
-        <v>8324</v>
+        <v>6030</v>
       </c>
       <c r="H1314" s="6" t="s">
-        <v>7079</v>
+        <v>7097</v>
       </c>
     </row>
     <row r="1315">
       <c r="B1315" s="5" t="s">
-        <v>8325</v>
+        <v>8330</v>
       </c>
       <c r="C1315" s="5" t="s">
-        <v>7065</v>
+        <v>6046</v>
       </c>
       <c r="D1315" s="5" t="s">
-        <v>8326</v>
+        <v>8331</v>
       </c>
       <c r="E1315" s="5" t="s">
-        <v>7067</v>
+        <v>6048</v>
       </c>
       <c r="F1315" s="5" t="s">
-        <v>8327</v>
+        <v>6049</v>
       </c>
       <c r="G1315" s="5" t="s">
-        <v>8327</v>
+        <v>6050</v>
       </c>
       <c r="H1315" s="5" t="s">
-        <v>8328</v>
+        <v>8332</v>
       </c>
     </row>
     <row r="1316">
       <c r="B1316" s="6" t="s">
-        <v>8329</v>
+        <v>8333</v>
       </c>
       <c r="C1316" s="6" t="s">
-        <v>8330</v>
+        <v>8334</v>
       </c>
       <c r="D1316" s="6" t="s">
-        <v>8331</v>
+        <v>8335</v>
       </c>
       <c r="E1316" s="6" t="s">
-        <v>8332</v>
+        <v>6076</v>
       </c>
       <c r="F1316" s="6" t="s">
-        <v>8333</v>
+        <v>8336</v>
       </c>
       <c r="G1316" s="6" t="s">
-        <v>8334</v>
+        <v>8337</v>
       </c>
       <c r="H1316" s="6" t="s">
-        <v>8335</v>
+        <v>7079</v>
       </c>
     </row>
     <row r="1317">
       <c r="B1317" s="5" t="s">
-        <v>8336</v>
+        <v>8338</v>
       </c>
       <c r="C1317" s="5" t="s">
-        <v>8222</v>
+        <v>7065</v>
       </c>
       <c r="D1317" s="5" t="s">
-        <v>8223</v>
+        <v>8339</v>
       </c>
       <c r="E1317" s="5" t="s">
-        <v>8224</v>
+        <v>7067</v>
       </c>
       <c r="F1317" s="5" t="s">
-        <v>8225</v>
+        <v>8340</v>
       </c>
       <c r="G1317" s="5" t="s">
-        <v>8226</v>
+        <v>8340</v>
       </c>
       <c r="H1317" s="5" t="s">
-        <v>8227</v>
+        <v>8341</v>
       </c>
     </row>
     <row r="1318">
       <c r="B1318" s="6" t="s">
-        <v>8337</v>
+        <v>8342</v>
       </c>
       <c r="C1318" s="6" t="s">
-        <v>8338</v>
+        <v>8343</v>
       </c>
       <c r="D1318" s="6" t="s">
-        <v>8339</v>
+        <v>8344</v>
       </c>
       <c r="E1318" s="6" t="s">
-        <v>8340</v>
+        <v>8345</v>
       </c>
       <c r="F1318" s="6" t="s">
-        <v>8341</v>
+        <v>8346</v>
       </c>
       <c r="G1318" s="6" t="s">
-        <v>8342</v>
+        <v>8347</v>
       </c>
       <c r="H1318" s="6" t="s">
-        <v>8343</v>
+        <v>8348</v>
       </c>
     </row>
     <row r="1319">
       <c r="B1319" s="5" t="s">
-        <v>8344</v>
+        <v>8349</v>
       </c>
       <c r="C1319" s="5" t="s">
-        <v>8345</v>
+        <v>8235</v>
       </c>
       <c r="D1319" s="5" t="s">
-        <v>8346</v>
+        <v>8236</v>
       </c>
       <c r="E1319" s="5" t="s">
-        <v>8347</v>
+        <v>8237</v>
       </c>
       <c r="F1319" s="5" t="s">
-        <v>8348</v>
+        <v>8238</v>
       </c>
       <c r="G1319" s="5" t="s">
-        <v>8349</v>
+        <v>8239</v>
       </c>
       <c r="H1319" s="5" t="s">
-        <v>8350</v>
+        <v>8240</v>
       </c>
     </row>
     <row r="1320">
       <c r="B1320" s="6" t="s">
+        <v>8350</v>
+      </c>
+      <c r="C1320" s="6" t="s">
         <v>8351</v>
       </c>
-      <c r="C1320" s="6" t="s">
+      <c r="D1320" s="6" t="s">
         <v>8352</v>
       </c>
-      <c r="D1320" s="6" t="s">
+      <c r="E1320" s="6" t="s">
         <v>8353</v>
       </c>
-      <c r="E1320" s="6" t="s">
+      <c r="F1320" s="6" t="s">
         <v>8354</v>
       </c>
-      <c r="F1320" s="6" t="s">
+      <c r="G1320" s="6" t="s">
         <v>8355</v>
       </c>
-      <c r="G1320" s="6" t="s">
+      <c r="H1320" s="6" t="s">
         <v>8356</v>
-      </c>
-      <c r="H1320" s="6" t="s">
-        <v>8357</v>
       </c>
     </row>
     <row r="1321">
       <c r="B1321" s="5" t="s">
+        <v>8357</v>
+      </c>
+      <c r="C1321" s="5" t="s">
         <v>8358</v>
       </c>
-      <c r="C1321" s="5" t="s">
+      <c r="D1321" s="5" t="s">
         <v>8359</v>
       </c>
-      <c r="D1321" s="5" t="s">
+      <c r="E1321" s="5" t="s">
         <v>8360</v>
       </c>
-      <c r="E1321" s="5" t="s">
+      <c r="F1321" s="5" t="s">
         <v>8361</v>
       </c>
-      <c r="F1321" s="5" t="s">
+      <c r="G1321" s="5" t="s">
         <v>8362</v>
       </c>
-      <c r="G1321" s="5" t="s">
+      <c r="H1321" s="5" t="s">
         <v>8363</v>
-      </c>
-      <c r="H1321" s="5" t="s">
-        <v>8364</v>
       </c>
     </row>
     <row r="1322">
       <c r="B1322" s="6" t="s">
+        <v>8364</v>
+      </c>
+      <c r="C1322" s="6" t="s">
         <v>8365</v>
       </c>
-      <c r="C1322" s="6" t="s">
+      <c r="D1322" s="6" t="s">
         <v>8366</v>
       </c>
-      <c r="D1322" s="6" t="s">
+      <c r="E1322" s="6" t="s">
         <v>8367</v>
       </c>
-      <c r="E1322" s="6" t="s">
+      <c r="F1322" s="6" t="s">
         <v>8368</v>
       </c>
-      <c r="F1322" s="6" t="s">
+      <c r="G1322" s="6" t="s">
         <v>8369</v>
       </c>
-      <c r="G1322" s="6" t="s">
+      <c r="H1322" s="6" t="s">
         <v>8370</v>
-      </c>
-      <c r="H1322" s="6" t="s">
-        <v>8371</v>
       </c>
     </row>
     <row r="1323">
       <c r="B1323" s="5" t="s">
+        <v>8371</v>
+      </c>
+      <c r="C1323" s="5" t="s">
         <v>8372</v>
       </c>
-      <c r="C1323" s="5" t="s">
+      <c r="D1323" s="5" t="s">
         <v>8373</v>
       </c>
-      <c r="D1323" s="5" t="s">
+      <c r="E1323" s="5" t="s">
         <v>8374</v>
       </c>
-      <c r="E1323" s="5" t="s">
+      <c r="F1323" s="5" t="s">
         <v>8375</v>
       </c>
-      <c r="F1323" s="5" t="s">
+      <c r="G1323" s="5" t="s">
         <v>8376</v>
       </c>
-      <c r="G1323" s="5" t="s">
+      <c r="H1323" s="5" t="s">
         <v>8377</v>
-      </c>
-      <c r="H1323" s="5" t="s">
-        <v>8378</v>
       </c>
     </row>
     <row r="1324">
       <c r="B1324" s="6" t="s">
+        <v>8378</v>
+      </c>
+      <c r="C1324" s="6" t="s">
         <v>8379</v>
       </c>
-      <c r="C1324" s="6" t="s">
+      <c r="D1324" s="6" t="s">
         <v>8380</v>
       </c>
-      <c r="D1324" s="6" t="s">
+      <c r="E1324" s="6" t="s">
         <v>8381</v>
       </c>
-      <c r="E1324" s="6" t="s">
+      <c r="F1324" s="6" t="s">
         <v>8382</v>
-      </c>
-      <c r="F1324" s="6" t="s">
-        <v>8383</v>
       </c>
       <c r="G1324" s="6" t="s">
         <v>8383</v>
@@ -57734,211 +57773,211 @@
         <v>8396</v>
       </c>
       <c r="G1326" s="6" t="s">
+        <v>8396</v>
+      </c>
+      <c r="H1326" s="6" t="s">
         <v>8397</v>
-      </c>
-      <c r="H1326" s="6" t="s">
-        <v>8398</v>
       </c>
     </row>
     <row r="1327">
       <c r="B1327" s="5" t="s">
+        <v>8398</v>
+      </c>
+      <c r="C1327" s="5" t="s">
         <v>8399</v>
       </c>
-      <c r="C1327" s="5" t="s">
+      <c r="D1327" s="5" t="s">
         <v>8400</v>
       </c>
-      <c r="D1327" s="5" t="s">
+      <c r="E1327" s="5" t="s">
         <v>8401</v>
       </c>
-      <c r="E1327" s="5" t="s">
+      <c r="F1327" s="5" t="s">
         <v>8402</v>
       </c>
-      <c r="F1327" s="5" t="s">
+      <c r="G1327" s="5" t="s">
         <v>8403</v>
       </c>
-      <c r="G1327" s="5" t="s">
+      <c r="H1327" s="5" t="s">
         <v>8404</v>
-      </c>
-      <c r="H1327" s="5" t="s">
-        <v>8405</v>
       </c>
     </row>
     <row r="1328">
       <c r="B1328" s="6" t="s">
+        <v>8405</v>
+      </c>
+      <c r="C1328" s="6" t="s">
         <v>8406</v>
       </c>
-      <c r="C1328" s="6" t="s">
+      <c r="D1328" s="6" t="s">
         <v>8407</v>
       </c>
-      <c r="D1328" s="6" t="s">
+      <c r="E1328" s="6" t="s">
         <v>8408</v>
       </c>
-      <c r="E1328" s="6" t="s">
+      <c r="F1328" s="6" t="s">
         <v>8409</v>
       </c>
-      <c r="F1328" s="6" t="s">
+      <c r="G1328" s="6" t="s">
         <v>8410</v>
       </c>
-      <c r="G1328" s="6" t="s">
+      <c r="H1328" s="6" t="s">
         <v>8411</v>
-      </c>
-      <c r="H1328" s="6" t="s">
-        <v>8412</v>
       </c>
     </row>
     <row r="1329">
       <c r="B1329" s="5" t="s">
+        <v>8412</v>
+      </c>
+      <c r="C1329" s="5" t="s">
         <v>8413</v>
       </c>
-      <c r="C1329" s="5" t="s">
+      <c r="D1329" s="5" t="s">
         <v>8414</v>
       </c>
-      <c r="D1329" s="5" t="s">
+      <c r="E1329" s="5" t="s">
         <v>8415</v>
       </c>
-      <c r="E1329" s="5" t="s">
+      <c r="F1329" s="5" t="s">
         <v>8416</v>
       </c>
-      <c r="F1329" s="5" t="s">
+      <c r="G1329" s="5" t="s">
         <v>8417</v>
       </c>
-      <c r="G1329" s="5" t="s">
+      <c r="H1329" s="5" t="s">
         <v>8418</v>
-      </c>
-      <c r="H1329" s="5" t="s">
-        <v>8419</v>
       </c>
     </row>
     <row r="1330">
       <c r="B1330" s="6" t="s">
+        <v>8419</v>
+      </c>
+      <c r="C1330" s="6" t="s">
         <v>8420</v>
       </c>
-      <c r="C1330" s="6" t="s">
+      <c r="D1330" s="6" t="s">
         <v>8421</v>
       </c>
-      <c r="D1330" s="6" t="s">
+      <c r="E1330" s="6" t="s">
         <v>8422</v>
       </c>
-      <c r="E1330" s="6" t="s">
+      <c r="F1330" s="6" t="s">
         <v>8423</v>
       </c>
-      <c r="F1330" s="6" t="s">
+      <c r="G1330" s="6" t="s">
         <v>8424</v>
       </c>
-      <c r="G1330" s="6" t="s">
+      <c r="H1330" s="6" t="s">
         <v>8425</v>
-      </c>
-      <c r="H1330" s="6" t="s">
-        <v>8426</v>
       </c>
     </row>
     <row r="1331">
       <c r="B1331" s="5" t="s">
+        <v>8426</v>
+      </c>
+      <c r="C1331" s="5" t="s">
         <v>8427</v>
       </c>
-      <c r="C1331" s="5" t="s">
+      <c r="D1331" s="5" t="s">
         <v>8428</v>
       </c>
-      <c r="D1331" s="5" t="s">
+      <c r="E1331" s="5" t="s">
         <v>8429</v>
       </c>
-      <c r="E1331" s="5" t="s">
+      <c r="F1331" s="5" t="s">
         <v>8430</v>
       </c>
-      <c r="F1331" s="5" t="s">
+      <c r="G1331" s="5" t="s">
         <v>8431</v>
       </c>
-      <c r="G1331" s="5" t="s">
+      <c r="H1331" s="5" t="s">
         <v>8432</v>
-      </c>
-      <c r="H1331" s="5" t="s">
-        <v>8433</v>
       </c>
     </row>
     <row r="1332">
       <c r="B1332" s="6" t="s">
+        <v>8433</v>
+      </c>
+      <c r="C1332" s="6" t="s">
         <v>8434</v>
       </c>
-      <c r="C1332" s="6" t="s">
+      <c r="D1332" s="6" t="s">
         <v>8435</v>
       </c>
-      <c r="D1332" s="6" t="s">
+      <c r="E1332" s="6" t="s">
         <v>8436</v>
       </c>
-      <c r="E1332" s="6" t="s">
+      <c r="F1332" s="6" t="s">
         <v>8437</v>
       </c>
-      <c r="F1332" s="6" t="s">
+      <c r="G1332" s="6" t="s">
         <v>8438</v>
       </c>
-      <c r="G1332" s="6" t="s">
+      <c r="H1332" s="6" t="s">
         <v>8439</v>
-      </c>
-      <c r="H1332" s="6" t="s">
-        <v>8440</v>
       </c>
     </row>
     <row r="1333">
       <c r="B1333" s="5" t="s">
+        <v>8440</v>
+      </c>
+      <c r="C1333" s="5" t="s">
         <v>8441</v>
       </c>
-      <c r="C1333" s="5" t="s">
+      <c r="D1333" s="5" t="s">
         <v>8442</v>
       </c>
-      <c r="D1333" s="5" t="s">
+      <c r="E1333" s="5" t="s">
         <v>8443</v>
       </c>
-      <c r="E1333" s="5" t="s">
+      <c r="F1333" s="5" t="s">
         <v>8444</v>
       </c>
-      <c r="F1333" s="5" t="s">
+      <c r="G1333" s="5" t="s">
         <v>8445</v>
       </c>
-      <c r="G1333" s="5" t="s">
+      <c r="H1333" s="5" t="s">
         <v>8446</v>
-      </c>
-      <c r="H1333" s="5" t="s">
-        <v>8447</v>
       </c>
     </row>
     <row r="1334">
       <c r="B1334" s="6" t="s">
+        <v>8447</v>
+      </c>
+      <c r="C1334" s="6" t="s">
         <v>8448</v>
       </c>
-      <c r="C1334" s="6" t="s">
+      <c r="D1334" s="6" t="s">
         <v>8449</v>
       </c>
-      <c r="D1334" s="6" t="s">
+      <c r="E1334" s="6" t="s">
         <v>8450</v>
       </c>
-      <c r="E1334" s="6" t="s">
+      <c r="F1334" s="6" t="s">
         <v>8451</v>
       </c>
-      <c r="F1334" s="6" t="s">
+      <c r="G1334" s="6" t="s">
         <v>8452</v>
       </c>
-      <c r="G1334" s="6" t="s">
+      <c r="H1334" s="6" t="s">
         <v>8453</v>
-      </c>
-      <c r="H1334" s="6" t="s">
-        <v>8454</v>
       </c>
     </row>
     <row r="1335">
       <c r="B1335" s="5" t="s">
+        <v>8454</v>
+      </c>
+      <c r="C1335" s="5" t="s">
         <v>8455</v>
       </c>
-      <c r="C1335" s="5" t="s">
+      <c r="D1335" s="5" t="s">
         <v>8456</v>
       </c>
-      <c r="D1335" s="5" t="s">
+      <c r="E1335" s="5" t="s">
         <v>8457</v>
       </c>
-      <c r="E1335" s="5" t="s">
+      <c r="F1335" s="5" t="s">
         <v>8458</v>
-      </c>
-      <c r="F1335" s="5" t="s">
-        <v>8459</v>
       </c>
       <c r="G1335" s="5" t="s">
         <v>8459</v>
@@ -57984,76 +58023,76 @@
         <v>8471</v>
       </c>
       <c r="F1337" s="5" t="s">
-        <v>8389</v>
+        <v>8472</v>
       </c>
       <c r="G1337" s="5" t="s">
-        <v>8390</v>
+        <v>8472</v>
       </c>
       <c r="H1337" s="5" t="s">
-        <v>8472</v>
+        <v>8473</v>
       </c>
     </row>
     <row r="1338">
       <c r="B1338" s="6" t="s">
-        <v>8473</v>
+        <v>8474</v>
       </c>
       <c r="C1338" s="6" t="s">
-        <v>8474</v>
+        <v>8475</v>
       </c>
       <c r="D1338" s="6" t="s">
-        <v>8475</v>
+        <v>8476</v>
       </c>
       <c r="E1338" s="6" t="s">
-        <v>8476</v>
+        <v>8477</v>
       </c>
       <c r="F1338" s="6" t="s">
-        <v>8477</v>
+        <v>8478</v>
       </c>
       <c r="G1338" s="6" t="s">
-        <v>8478</v>
+        <v>8479</v>
       </c>
       <c r="H1338" s="6" t="s">
-        <v>8479</v>
+        <v>8480</v>
       </c>
     </row>
     <row r="1339">
       <c r="B1339" s="5" t="s">
-        <v>8480</v>
+        <v>8481</v>
       </c>
       <c r="C1339" s="5" t="s">
-        <v>8481</v>
+        <v>8482</v>
       </c>
       <c r="D1339" s="5" t="s">
-        <v>8482</v>
+        <v>8483</v>
       </c>
       <c r="E1339" s="5" t="s">
-        <v>8483</v>
+        <v>8484</v>
       </c>
       <c r="F1339" s="5" t="s">
-        <v>8484</v>
+        <v>8402</v>
       </c>
       <c r="G1339" s="5" t="s">
+        <v>8403</v>
+      </c>
+      <c r="H1339" s="5" t="s">
         <v>8485</v>
-      </c>
-      <c r="H1339" s="5" t="s">
-        <v>8486</v>
       </c>
     </row>
     <row r="1340">
       <c r="B1340" s="6" t="s">
+        <v>8486</v>
+      </c>
+      <c r="C1340" s="6" t="s">
         <v>8487</v>
       </c>
-      <c r="C1340" s="6" t="s">
+      <c r="D1340" s="6" t="s">
         <v>8488</v>
       </c>
-      <c r="D1340" s="6" t="s">
+      <c r="E1340" s="6" t="s">
         <v>8489</v>
       </c>
-      <c r="E1340" s="6" t="s">
+      <c r="F1340" s="6" t="s">
         <v>8490</v>
-      </c>
-      <c r="F1340" s="6" t="s">
-        <v>8491</v>
       </c>
       <c r="G1340" s="6" t="s">
         <v>8491</v>
@@ -58113,68 +58152,68 @@
         <v>8506</v>
       </c>
       <c r="C1343" s="5" t="s">
-        <v>6781</v>
+        <v>8507</v>
       </c>
       <c r="D1343" s="5" t="s">
-        <v>8507</v>
+        <v>8508</v>
       </c>
       <c r="E1343" s="5" t="s">
-        <v>6783</v>
+        <v>8509</v>
       </c>
       <c r="F1343" s="5" t="s">
-        <v>6784</v>
+        <v>8510</v>
       </c>
       <c r="G1343" s="5" t="s">
-        <v>6785</v>
+        <v>8511</v>
       </c>
       <c r="H1343" s="5" t="s">
-        <v>6786</v>
+        <v>8512</v>
       </c>
     </row>
     <row r="1344">
       <c r="B1344" s="6" t="s">
-        <v>8508</v>
+        <v>8513</v>
       </c>
       <c r="C1344" s="6" t="s">
-        <v>8509</v>
+        <v>8514</v>
       </c>
       <c r="D1344" s="6" t="s">
-        <v>8510</v>
+        <v>8515</v>
       </c>
       <c r="E1344" s="6" t="s">
-        <v>8511</v>
+        <v>8516</v>
       </c>
       <c r="F1344" s="6" t="s">
-        <v>8512</v>
+        <v>8517</v>
       </c>
       <c r="G1344" s="6" t="s">
-        <v>8512</v>
+        <v>8517</v>
       </c>
       <c r="H1344" s="6" t="s">
-        <v>8513</v>
+        <v>8518</v>
       </c>
     </row>
     <row r="1345">
       <c r="B1345" s="5" t="s">
-        <v>8514</v>
+        <v>8519</v>
       </c>
       <c r="C1345" s="5" t="s">
-        <v>8515</v>
+        <v>6781</v>
       </c>
       <c r="D1345" s="5" t="s">
-        <v>8516</v>
+        <v>8520</v>
       </c>
       <c r="E1345" s="5" t="s">
-        <v>8517</v>
+        <v>6783</v>
       </c>
       <c r="F1345" s="5" t="s">
-        <v>8518</v>
+        <v>6784</v>
       </c>
       <c r="G1345" s="5" t="s">
-        <v>8519</v>
+        <v>6785</v>
       </c>
       <c r="H1345" s="5" t="s">
-        <v>8520</v>
+        <v>6786</v>
       </c>
     </row>
     <row r="1346">
@@ -58194,27 +58233,27 @@
         <v>8525</v>
       </c>
       <c r="G1346" s="6" t="s">
+        <v>8525</v>
+      </c>
+      <c r="H1346" s="6" t="s">
         <v>8526</v>
-      </c>
-      <c r="H1346" s="6" t="s">
-        <v>8527</v>
       </c>
     </row>
     <row r="1347">
       <c r="B1347" s="5" t="s">
+        <v>8527</v>
+      </c>
+      <c r="C1347" s="5" t="s">
         <v>8528</v>
       </c>
-      <c r="C1347" s="5" t="s">
+      <c r="D1347" s="5" t="s">
         <v>8529</v>
       </c>
-      <c r="D1347" s="5" t="s">
+      <c r="E1347" s="5" t="s">
         <v>8530</v>
       </c>
-      <c r="E1347" s="5" t="s">
+      <c r="F1347" s="5" t="s">
         <v>8531</v>
-      </c>
-      <c r="F1347" s="5" t="s">
-        <v>8532</v>
       </c>
       <c r="G1347" s="5" t="s">
         <v>8532</v>
@@ -58263,306 +58302,306 @@
         <v>8545</v>
       </c>
       <c r="G1349" s="5" t="s">
+        <v>8545</v>
+      </c>
+      <c r="H1349" s="5" t="s">
         <v>8546</v>
-      </c>
-      <c r="H1349" s="5" t="s">
-        <v>8547</v>
       </c>
     </row>
     <row r="1350">
       <c r="B1350" s="6" t="s">
+        <v>8547</v>
+      </c>
+      <c r="C1350" s="6" t="s">
         <v>8548</v>
       </c>
-      <c r="C1350" s="6" t="s">
+      <c r="D1350" s="6" t="s">
         <v>8549</v>
       </c>
-      <c r="D1350" s="6" t="s">
+      <c r="E1350" s="6" t="s">
         <v>8550</v>
       </c>
-      <c r="E1350" s="6" t="s">
+      <c r="F1350" s="6" t="s">
         <v>8551</v>
       </c>
-      <c r="F1350" s="6" t="s">
+      <c r="G1350" s="6" t="s">
         <v>8552</v>
       </c>
-      <c r="G1350" s="6" t="s">
+      <c r="H1350" s="6" t="s">
         <v>8553</v>
-      </c>
-      <c r="H1350" s="6" t="s">
-        <v>8554</v>
       </c>
     </row>
     <row r="1351">
       <c r="B1351" s="5" t="s">
+        <v>8554</v>
+      </c>
+      <c r="C1351" s="5" t="s">
         <v>8555</v>
       </c>
-      <c r="C1351" s="5" t="s">
-        <v>8509</v>
-      </c>
       <c r="D1351" s="5" t="s">
-        <v>8510</v>
+        <v>8556</v>
       </c>
       <c r="E1351" s="5" t="s">
-        <v>8511</v>
+        <v>8557</v>
       </c>
       <c r="F1351" s="5" t="s">
-        <v>8512</v>
+        <v>8558</v>
       </c>
       <c r="G1351" s="5" t="s">
-        <v>8512</v>
+        <v>8559</v>
       </c>
       <c r="H1351" s="5" t="s">
-        <v>8513</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="1352">
       <c r="B1352" s="6" t="s">
-        <v>8556</v>
+        <v>8561</v>
       </c>
       <c r="C1352" s="6" t="s">
-        <v>8557</v>
+        <v>8562</v>
       </c>
       <c r="D1352" s="6" t="s">
-        <v>8558</v>
+        <v>8563</v>
       </c>
       <c r="E1352" s="6" t="s">
-        <v>8559</v>
+        <v>8564</v>
       </c>
       <c r="F1352" s="6" t="s">
-        <v>8560</v>
+        <v>8565</v>
       </c>
       <c r="G1352" s="6" t="s">
-        <v>8561</v>
+        <v>8566</v>
       </c>
       <c r="H1352" s="6" t="s">
-        <v>8562</v>
+        <v>8567</v>
       </c>
     </row>
     <row r="1353">
       <c r="B1353" s="5" t="s">
-        <v>8563</v>
+        <v>8568</v>
       </c>
       <c r="C1353" s="5" t="s">
-        <v>8564</v>
+        <v>8522</v>
       </c>
       <c r="D1353" s="5" t="s">
-        <v>8565</v>
+        <v>8523</v>
       </c>
       <c r="E1353" s="5" t="s">
-        <v>8566</v>
+        <v>8524</v>
       </c>
       <c r="F1353" s="5" t="s">
-        <v>8567</v>
+        <v>8525</v>
       </c>
       <c r="G1353" s="5" t="s">
-        <v>8568</v>
+        <v>8525</v>
       </c>
       <c r="H1353" s="5" t="s">
-        <v>8569</v>
+        <v>8526</v>
       </c>
     </row>
     <row r="1354">
       <c r="B1354" s="6" t="s">
+        <v>8569</v>
+      </c>
+      <c r="C1354" s="6" t="s">
         <v>8570</v>
       </c>
-      <c r="C1354" s="6" t="s">
+      <c r="D1354" s="6" t="s">
         <v>8571</v>
       </c>
-      <c r="D1354" s="6" t="s">
+      <c r="E1354" s="6" t="s">
         <v>8572</v>
       </c>
-      <c r="E1354" s="6" t="s">
+      <c r="F1354" s="6" t="s">
         <v>8573</v>
       </c>
-      <c r="F1354" s="6" t="s">
+      <c r="G1354" s="6" t="s">
         <v>8574</v>
       </c>
-      <c r="G1354" s="6" t="s">
+      <c r="H1354" s="6" t="s">
         <v>8575</v>
-      </c>
-      <c r="H1354" s="6" t="s">
-        <v>8576</v>
       </c>
     </row>
     <row r="1355">
       <c r="B1355" s="5" t="s">
+        <v>8576</v>
+      </c>
+      <c r="C1355" s="5" t="s">
         <v>8577</v>
       </c>
-      <c r="C1355" s="5" t="s">
+      <c r="D1355" s="5" t="s">
         <v>8578</v>
       </c>
-      <c r="D1355" s="5" t="s">
+      <c r="E1355" s="5" t="s">
         <v>8579</v>
       </c>
-      <c r="E1355" s="5" t="s">
+      <c r="F1355" s="5" t="s">
         <v>8580</v>
       </c>
-      <c r="F1355" s="5" t="s">
+      <c r="G1355" s="5" t="s">
         <v>8581</v>
       </c>
-      <c r="G1355" s="5" t="s">
+      <c r="H1355" s="5" t="s">
         <v>8582</v>
-      </c>
-      <c r="H1355" s="5" t="s">
-        <v>8583</v>
       </c>
     </row>
     <row r="1356">
       <c r="B1356" s="6" t="s">
+        <v>8583</v>
+      </c>
+      <c r="C1356" s="6" t="s">
         <v>8584</v>
       </c>
-      <c r="C1356" s="6" t="s">
+      <c r="D1356" s="6" t="s">
         <v>8585</v>
       </c>
-      <c r="D1356" s="6" t="s">
+      <c r="E1356" s="6" t="s">
         <v>8586</v>
       </c>
-      <c r="E1356" s="6" t="s">
+      <c r="F1356" s="6" t="s">
         <v>8587</v>
       </c>
-      <c r="F1356" s="6" t="s">
+      <c r="G1356" s="6" t="s">
         <v>8588</v>
       </c>
-      <c r="G1356" s="6" t="s">
+      <c r="H1356" s="6" t="s">
         <v>8589</v>
-      </c>
-      <c r="H1356" s="6" t="s">
-        <v>8590</v>
       </c>
     </row>
     <row r="1357">
       <c r="B1357" s="5" t="s">
+        <v>8590</v>
+      </c>
+      <c r="C1357" s="5" t="s">
         <v>8591</v>
       </c>
-      <c r="C1357" s="5" t="s">
+      <c r="D1357" s="5" t="s">
         <v>8592</v>
       </c>
-      <c r="D1357" s="5" t="s">
+      <c r="E1357" s="5" t="s">
         <v>8593</v>
       </c>
-      <c r="E1357" s="5" t="s">
+      <c r="F1357" s="5" t="s">
         <v>8594</v>
       </c>
-      <c r="F1357" s="5" t="s">
+      <c r="G1357" s="5" t="s">
         <v>8595</v>
       </c>
-      <c r="G1357" s="5" t="s">
+      <c r="H1357" s="5" t="s">
         <v>8596</v>
-      </c>
-      <c r="H1357" s="5" t="s">
-        <v>8597</v>
       </c>
     </row>
     <row r="1358">
       <c r="B1358" s="6" t="s">
+        <v>8597</v>
+      </c>
+      <c r="C1358" s="6" t="s">
         <v>8598</v>
-      </c>
-      <c r="C1358" s="6" t="s">
-        <v>6895</v>
       </c>
       <c r="D1358" s="6" t="s">
         <v>8599</v>
       </c>
       <c r="E1358" s="6" t="s">
-        <v>6897</v>
+        <v>8600</v>
       </c>
       <c r="F1358" s="6" t="s">
-        <v>8246</v>
+        <v>8601</v>
       </c>
       <c r="G1358" s="6" t="s">
-        <v>8247</v>
+        <v>8602</v>
       </c>
       <c r="H1358" s="6" t="s">
-        <v>8600</v>
+        <v>8603</v>
       </c>
     </row>
     <row r="1359">
       <c r="B1359" s="5" t="s">
-        <v>8601</v>
+        <v>8604</v>
       </c>
       <c r="C1359" s="5" t="s">
-        <v>7101</v>
+        <v>8605</v>
       </c>
       <c r="D1359" s="5" t="s">
-        <v>6832</v>
+        <v>8606</v>
       </c>
       <c r="E1359" s="5" t="s">
-        <v>7102</v>
+        <v>8607</v>
       </c>
       <c r="F1359" s="5" t="s">
-        <v>7103</v>
+        <v>8608</v>
       </c>
       <c r="G1359" s="5" t="s">
-        <v>7104</v>
+        <v>8609</v>
       </c>
       <c r="H1359" s="5" t="s">
-        <v>6832</v>
+        <v>8610</v>
       </c>
     </row>
     <row r="1360">
       <c r="B1360" s="6" t="s">
-        <v>8602</v>
+        <v>8611</v>
       </c>
       <c r="C1360" s="6" t="s">
-        <v>8222</v>
+        <v>6895</v>
       </c>
       <c r="D1360" s="6" t="s">
-        <v>8603</v>
+        <v>8612</v>
       </c>
       <c r="E1360" s="6" t="s">
-        <v>8224</v>
+        <v>6897</v>
       </c>
       <c r="F1360" s="6" t="s">
-        <v>8225</v>
+        <v>8259</v>
       </c>
       <c r="G1360" s="6" t="s">
-        <v>8226</v>
+        <v>8260</v>
       </c>
       <c r="H1360" s="6" t="s">
-        <v>8604</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="1361">
       <c r="B1361" s="5" t="s">
-        <v>8605</v>
+        <v>8614</v>
       </c>
       <c r="C1361" s="5" t="s">
-        <v>8606</v>
+        <v>7101</v>
       </c>
       <c r="D1361" s="5" t="s">
-        <v>8607</v>
+        <v>6832</v>
       </c>
       <c r="E1361" s="5" t="s">
-        <v>8608</v>
+        <v>7102</v>
       </c>
       <c r="F1361" s="5" t="s">
-        <v>8609</v>
+        <v>7103</v>
       </c>
       <c r="G1361" s="5" t="s">
-        <v>8608</v>
+        <v>7104</v>
       </c>
       <c r="H1361" s="5" t="s">
-        <v>8610</v>
+        <v>6832</v>
       </c>
     </row>
     <row r="1362">
       <c r="B1362" s="6" t="s">
-        <v>8611</v>
+        <v>8615</v>
       </c>
       <c r="C1362" s="6" t="s">
-        <v>8612</v>
+        <v>8235</v>
       </c>
       <c r="D1362" s="6" t="s">
-        <v>8613</v>
+        <v>8616</v>
       </c>
       <c r="E1362" s="6" t="s">
-        <v>8614</v>
+        <v>8237</v>
       </c>
       <c r="F1362" s="6" t="s">
-        <v>8615</v>
+        <v>8238</v>
       </c>
       <c r="G1362" s="6" t="s">
-        <v>8616</v>
+        <v>8239</v>
       </c>
       <c r="H1362" s="6" t="s">
         <v>8617</v>
@@ -58585,70 +58624,70 @@
         <v>8622</v>
       </c>
       <c r="G1363" s="5" t="s">
+        <v>8621</v>
+      </c>
+      <c r="H1363" s="5" t="s">
         <v>8623</v>
-      </c>
-      <c r="H1363" s="5" t="s">
-        <v>8624</v>
       </c>
     </row>
     <row r="1364">
       <c r="B1364" s="6" t="s">
+        <v>8624</v>
+      </c>
+      <c r="C1364" s="6" t="s">
         <v>8625</v>
       </c>
-      <c r="C1364" s="6" t="s">
+      <c r="D1364" s="6" t="s">
         <v>8626</v>
       </c>
-      <c r="D1364" s="6" t="s">
+      <c r="E1364" s="6" t="s">
         <v>8627</v>
       </c>
-      <c r="E1364" s="6" t="s">
+      <c r="F1364" s="6" t="s">
         <v>8628</v>
       </c>
-      <c r="F1364" s="6" t="s">
+      <c r="G1364" s="6" t="s">
         <v>8629</v>
       </c>
-      <c r="G1364" s="6" t="s">
+      <c r="H1364" s="6" t="s">
         <v>8630</v>
-      </c>
-      <c r="H1364" s="6" t="s">
-        <v>8631</v>
       </c>
     </row>
     <row r="1365">
       <c r="B1365" s="5" t="s">
+        <v>8631</v>
+      </c>
+      <c r="C1365" s="5" t="s">
         <v>8632</v>
       </c>
-      <c r="C1365" s="5" t="s">
+      <c r="D1365" s="5" t="s">
         <v>8633</v>
       </c>
-      <c r="D1365" s="5" t="s">
+      <c r="E1365" s="5" t="s">
         <v>8634</v>
       </c>
-      <c r="E1365" s="5" t="s">
+      <c r="F1365" s="5" t="s">
         <v>8635</v>
       </c>
-      <c r="F1365" s="5" t="s">
+      <c r="G1365" s="5" t="s">
         <v>8636</v>
       </c>
-      <c r="G1365" s="5" t="s">
+      <c r="H1365" s="5" t="s">
         <v>8637</v>
-      </c>
-      <c r="H1365" s="5" t="s">
-        <v>8638</v>
       </c>
     </row>
     <row r="1366">
       <c r="B1366" s="6" t="s">
+        <v>8638</v>
+      </c>
+      <c r="C1366" s="6" t="s">
         <v>8639</v>
       </c>
-      <c r="C1366" s="6" t="s">
+      <c r="D1366" s="6" t="s">
         <v>8640</v>
       </c>
-      <c r="D1366" s="6" t="s">
+      <c r="E1366" s="6" t="s">
         <v>8641</v>
-      </c>
-      <c r="E1366" s="6" t="s">
-        <v>5453</v>
       </c>
       <c r="F1366" s="6" t="s">
         <v>8642</v>
@@ -58694,171 +58733,171 @@
         <v>8654</v>
       </c>
       <c r="E1368" s="6" t="s">
+        <v>5453</v>
+      </c>
+      <c r="F1368" s="6" t="s">
         <v>8655</v>
       </c>
-      <c r="F1368" s="6" t="s">
+      <c r="G1368" s="6" t="s">
         <v>8656</v>
       </c>
-      <c r="G1368" s="6" t="s">
+      <c r="H1368" s="6" t="s">
         <v>8657</v>
-      </c>
-      <c r="H1368" s="6" t="s">
-        <v>8658</v>
       </c>
     </row>
     <row r="1369">
       <c r="B1369" s="5" t="s">
+        <v>8658</v>
+      </c>
+      <c r="C1369" s="5" t="s">
         <v>8659</v>
       </c>
-      <c r="C1369" s="5" t="s">
+      <c r="D1369" s="5" t="s">
         <v>8660</v>
       </c>
-      <c r="D1369" s="5" t="s">
+      <c r="E1369" s="5" t="s">
         <v>8661</v>
       </c>
-      <c r="E1369" s="5" t="s">
+      <c r="F1369" s="5" t="s">
         <v>8662</v>
       </c>
-      <c r="F1369" s="5" t="s">
+      <c r="G1369" s="5" t="s">
         <v>8663</v>
       </c>
-      <c r="G1369" s="5" t="s">
+      <c r="H1369" s="5" t="s">
         <v>8664</v>
-      </c>
-      <c r="H1369" s="5" t="s">
-        <v>8665</v>
       </c>
     </row>
     <row r="1370">
       <c r="B1370" s="6" t="s">
+        <v>8665</v>
+      </c>
+      <c r="C1370" s="6" t="s">
         <v>8666</v>
       </c>
-      <c r="C1370" s="6" t="s">
+      <c r="D1370" s="6" t="s">
         <v>8667</v>
       </c>
-      <c r="D1370" s="6" t="s">
+      <c r="E1370" s="6" t="s">
         <v>8668</v>
       </c>
-      <c r="E1370" s="6" t="s">
+      <c r="F1370" s="6" t="s">
         <v>8669</v>
       </c>
-      <c r="F1370" s="6" t="s">
+      <c r="G1370" s="6" t="s">
         <v>8670</v>
       </c>
-      <c r="G1370" s="6" t="s">
+      <c r="H1370" s="6" t="s">
         <v>8671</v>
-      </c>
-      <c r="H1370" s="6" t="s">
-        <v>8672</v>
       </c>
     </row>
     <row r="1371">
       <c r="B1371" s="5" t="s">
+        <v>8672</v>
+      </c>
+      <c r="C1371" s="5" t="s">
         <v>8673</v>
       </c>
-      <c r="C1371" s="7" t="s">
+      <c r="D1371" s="5" t="s">
         <v>8674</v>
       </c>
-      <c r="D1371" s="7" t="s">
-        <v>8674</v>
-      </c>
-      <c r="E1371" s="7" t="s">
-        <v>8674</v>
-      </c>
-      <c r="F1371" s="7" t="s">
-        <v>8674</v>
-      </c>
-      <c r="G1371" s="7" t="s">
-        <v>8674</v>
-      </c>
-      <c r="H1371" s="7" t="s">
-        <v>8674</v>
+      <c r="E1371" s="5" t="s">
+        <v>8675</v>
+      </c>
+      <c r="F1371" s="5" t="s">
+        <v>8676</v>
+      </c>
+      <c r="G1371" s="5" t="s">
+        <v>8677</v>
+      </c>
+      <c r="H1371" s="5" t="s">
+        <v>8678</v>
       </c>
     </row>
     <row r="1372">
       <c r="B1372" s="6" t="s">
-        <v>8675</v>
+        <v>8679</v>
       </c>
       <c r="C1372" s="6" t="s">
-        <v>8086</v>
+        <v>8680</v>
       </c>
       <c r="D1372" s="6" t="s">
-        <v>8087</v>
+        <v>8681</v>
       </c>
       <c r="E1372" s="6" t="s">
-        <v>8088</v>
+        <v>8682</v>
       </c>
       <c r="F1372" s="6" t="s">
-        <v>8089</v>
+        <v>8683</v>
       </c>
       <c r="G1372" s="6" t="s">
-        <v>8090</v>
+        <v>8684</v>
       </c>
       <c r="H1372" s="6" t="s">
-        <v>8087</v>
+        <v>8685</v>
       </c>
     </row>
     <row r="1373">
       <c r="B1373" s="5" t="s">
-        <v>8676</v>
-      </c>
-      <c r="C1373" s="5" t="s">
-        <v>8677</v>
-      </c>
-      <c r="D1373" s="5" t="s">
-        <v>8678</v>
-      </c>
-      <c r="E1373" s="5" t="s">
-        <v>8679</v>
-      </c>
-      <c r="F1373" s="5" t="s">
-        <v>8680</v>
-      </c>
-      <c r="G1373" s="5" t="s">
-        <v>8680</v>
-      </c>
-      <c r="H1373" s="5" t="s">
-        <v>8681</v>
+        <v>8686</v>
+      </c>
+      <c r="C1373" s="7" t="s">
+        <v>8687</v>
+      </c>
+      <c r="D1373" s="7" t="s">
+        <v>8687</v>
+      </c>
+      <c r="E1373" s="7" t="s">
+        <v>8687</v>
+      </c>
+      <c r="F1373" s="7" t="s">
+        <v>8687</v>
+      </c>
+      <c r="G1373" s="7" t="s">
+        <v>8687</v>
+      </c>
+      <c r="H1373" s="7" t="s">
+        <v>8687</v>
       </c>
     </row>
     <row r="1374">
       <c r="B1374" s="6" t="s">
-        <v>8682</v>
+        <v>8688</v>
       </c>
       <c r="C1374" s="6" t="s">
-        <v>8683</v>
+        <v>8099</v>
       </c>
       <c r="D1374" s="6" t="s">
-        <v>8684</v>
+        <v>8100</v>
       </c>
       <c r="E1374" s="6" t="s">
-        <v>8685</v>
+        <v>8101</v>
       </c>
       <c r="F1374" s="6" t="s">
-        <v>8686</v>
+        <v>8102</v>
       </c>
       <c r="G1374" s="6" t="s">
-        <v>8687</v>
+        <v>8103</v>
       </c>
       <c r="H1374" s="6" t="s">
-        <v>6117</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="1375">
       <c r="B1375" s="5" t="s">
-        <v>8688</v>
+        <v>8689</v>
       </c>
       <c r="C1375" s="5" t="s">
-        <v>8689</v>
+        <v>8690</v>
       </c>
       <c r="D1375" s="5" t="s">
-        <v>8690</v>
+        <v>8691</v>
       </c>
       <c r="E1375" s="5" t="s">
-        <v>8691</v>
+        <v>8692</v>
       </c>
       <c r="F1375" s="5" t="s">
-        <v>8692</v>
+        <v>8693</v>
       </c>
       <c r="G1375" s="5" t="s">
         <v>8693</v>
@@ -58887,24 +58926,24 @@
         <v>8700</v>
       </c>
       <c r="H1376" s="6" t="s">
-        <v>8701</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="1377">
       <c r="B1377" s="5" t="s">
+        <v>8701</v>
+      </c>
+      <c r="C1377" s="5" t="s">
         <v>8702</v>
       </c>
-      <c r="C1377" s="5" t="s">
+      <c r="D1377" s="5" t="s">
         <v>8703</v>
       </c>
-      <c r="D1377" s="5" t="s">
+      <c r="E1377" s="5" t="s">
         <v>8704</v>
       </c>
-      <c r="E1377" s="5" t="s">
+      <c r="F1377" s="5" t="s">
         <v>8705</v>
-      </c>
-      <c r="F1377" s="5" t="s">
-        <v>8706</v>
       </c>
       <c r="G1377" s="5" t="s">
         <v>8706</v>
@@ -58967,366 +59006,366 @@
         <v>8722</v>
       </c>
       <c r="D1380" s="6" t="s">
-        <v>8722</v>
+        <v>8723</v>
       </c>
       <c r="E1380" s="6" t="s">
-        <v>8722</v>
+        <v>8724</v>
       </c>
       <c r="F1380" s="6" t="s">
-        <v>8722</v>
+        <v>8725</v>
       </c>
       <c r="G1380" s="6" t="s">
-        <v>8722</v>
+        <v>8726</v>
       </c>
       <c r="H1380" s="6" t="s">
-        <v>8722</v>
+        <v>8727</v>
       </c>
     </row>
     <row r="1381">
       <c r="B1381" s="5" t="s">
-        <v>8723</v>
+        <v>8728</v>
       </c>
       <c r="C1381" s="5" t="s">
-        <v>8724</v>
+        <v>8729</v>
       </c>
       <c r="D1381" s="5" t="s">
-        <v>8725</v>
+        <v>8730</v>
       </c>
       <c r="E1381" s="5" t="s">
-        <v>8726</v>
+        <v>8731</v>
       </c>
       <c r="F1381" s="5" t="s">
-        <v>8727</v>
+        <v>8732</v>
       </c>
       <c r="G1381" s="5" t="s">
-        <v>8727</v>
+        <v>8732</v>
       </c>
       <c r="H1381" s="5" t="s">
-        <v>8728</v>
+        <v>8733</v>
       </c>
     </row>
     <row r="1382">
       <c r="B1382" s="6" t="s">
-        <v>8729</v>
+        <v>8734</v>
       </c>
       <c r="C1382" s="6" t="s">
-        <v>8722</v>
+        <v>8735</v>
       </c>
       <c r="D1382" s="6" t="s">
-        <v>8722</v>
+        <v>8735</v>
       </c>
       <c r="E1382" s="6" t="s">
-        <v>8722</v>
+        <v>8735</v>
       </c>
       <c r="F1382" s="6" t="s">
-        <v>8722</v>
+        <v>8735</v>
       </c>
       <c r="G1382" s="6" t="s">
-        <v>8722</v>
+        <v>8735</v>
       </c>
       <c r="H1382" s="6" t="s">
-        <v>8722</v>
+        <v>8735</v>
       </c>
     </row>
     <row r="1383">
       <c r="B1383" s="5" t="s">
-        <v>8730</v>
+        <v>8736</v>
+      </c>
+      <c r="C1383" s="5" t="s">
+        <v>8737</v>
+      </c>
+      <c r="D1383" s="5" t="s">
+        <v>8738</v>
+      </c>
+      <c r="E1383" s="5" t="s">
+        <v>8739</v>
+      </c>
+      <c r="F1383" s="5" t="s">
+        <v>8740</v>
+      </c>
+      <c r="G1383" s="5" t="s">
+        <v>8740</v>
+      </c>
+      <c r="H1383" s="5" t="s">
+        <v>8741</v>
       </c>
     </row>
     <row r="1384">
       <c r="B1384" s="6" t="s">
-        <v>8731</v>
+        <v>8742</v>
       </c>
       <c r="C1384" s="6" t="s">
-        <v>8732</v>
+        <v>8735</v>
       </c>
       <c r="D1384" s="6" t="s">
-        <v>8733</v>
+        <v>8735</v>
       </c>
       <c r="E1384" s="6" t="s">
-        <v>8734</v>
+        <v>8735</v>
       </c>
       <c r="F1384" s="6" t="s">
         <v>8735</v>
       </c>
       <c r="G1384" s="6" t="s">
-        <v>8736</v>
+        <v>8735</v>
       </c>
       <c r="H1384" s="6" t="s">
-        <v>8737</v>
+        <v>8735</v>
       </c>
     </row>
     <row r="1385">
       <c r="B1385" s="5" t="s">
-        <v>8738</v>
-      </c>
-      <c r="C1385" s="5" t="s">
-        <v>8739</v>
-      </c>
-      <c r="D1385" s="5" t="s">
-        <v>8740</v>
-      </c>
-      <c r="E1385" s="5" t="s">
-        <v>8741</v>
-      </c>
-      <c r="F1385" s="5" t="s">
-        <v>8742</v>
-      </c>
-      <c r="G1385" s="5" t="s">
         <v>8743</v>
-      </c>
-      <c r="H1385" s="5" t="s">
-        <v>8744</v>
       </c>
     </row>
     <row r="1386">
       <c r="B1386" s="6" t="s">
+        <v>8744</v>
+      </c>
+      <c r="C1386" s="6" t="s">
         <v>8745</v>
       </c>
-      <c r="C1386" s="6" t="s">
+      <c r="D1386" s="6" t="s">
         <v>8746</v>
       </c>
-      <c r="D1386" s="6" t="s">
+      <c r="E1386" s="6" t="s">
         <v>8747</v>
       </c>
-      <c r="E1386" s="6" t="s">
+      <c r="F1386" s="6" t="s">
         <v>8748</v>
       </c>
-      <c r="F1386" s="6" t="s">
+      <c r="G1386" s="6" t="s">
         <v>8749</v>
       </c>
-      <c r="G1386" s="6" t="s">
+      <c r="H1386" s="6" t="s">
         <v>8750</v>
-      </c>
-      <c r="H1386" s="6" t="s">
-        <v>8751</v>
       </c>
     </row>
     <row r="1387">
       <c r="B1387" s="5" t="s">
+        <v>8751</v>
+      </c>
+      <c r="C1387" s="5" t="s">
         <v>8752</v>
       </c>
-      <c r="C1387" s="5" t="s">
+      <c r="D1387" s="5" t="s">
         <v>8753</v>
       </c>
-      <c r="D1387" s="5" t="s">
+      <c r="E1387" s="5" t="s">
         <v>8754</v>
       </c>
-      <c r="E1387" s="5" t="s">
+      <c r="F1387" s="5" t="s">
         <v>8755</v>
       </c>
-      <c r="F1387" s="5" t="s">
+      <c r="G1387" s="5" t="s">
         <v>8756</v>
       </c>
-      <c r="G1387" s="5" t="s">
+      <c r="H1387" s="5" t="s">
         <v>8757</v>
-      </c>
-      <c r="H1387" s="5" t="s">
-        <v>8758</v>
       </c>
     </row>
     <row r="1388">
       <c r="B1388" s="6" t="s">
+        <v>8758</v>
+      </c>
+      <c r="C1388" s="6" t="s">
         <v>8759</v>
-      </c>
-      <c r="C1388" s="6" t="s">
-        <v>6112</v>
       </c>
       <c r="D1388" s="6" t="s">
         <v>8760</v>
       </c>
       <c r="E1388" s="6" t="s">
-        <v>6114</v>
+        <v>8761</v>
       </c>
       <c r="F1388" s="6" t="s">
-        <v>8761</v>
+        <v>8762</v>
       </c>
       <c r="G1388" s="6" t="s">
-        <v>8761</v>
+        <v>8763</v>
       </c>
       <c r="H1388" s="6" t="s">
-        <v>8762</v>
+        <v>8764</v>
       </c>
     </row>
     <row r="1389">
       <c r="B1389" s="5" t="s">
-        <v>8763</v>
+        <v>8765</v>
       </c>
       <c r="C1389" s="5" t="s">
-        <v>8764</v>
+        <v>8766</v>
       </c>
       <c r="D1389" s="5" t="s">
-        <v>8765</v>
+        <v>8767</v>
       </c>
       <c r="E1389" s="5" t="s">
-        <v>8766</v>
+        <v>8768</v>
       </c>
       <c r="F1389" s="5" t="s">
-        <v>8767</v>
+        <v>8769</v>
       </c>
       <c r="G1389" s="5" t="s">
-        <v>8768</v>
+        <v>8770</v>
       </c>
       <c r="H1389" s="5" t="s">
-        <v>8769</v>
+        <v>8771</v>
       </c>
     </row>
     <row r="1390">
       <c r="B1390" s="6" t="s">
-        <v>8770</v>
+        <v>8772</v>
       </c>
       <c r="C1390" s="6" t="s">
-        <v>8771</v>
+        <v>6112</v>
       </c>
       <c r="D1390" s="6" t="s">
-        <v>8772</v>
+        <v>8773</v>
       </c>
       <c r="E1390" s="6" t="s">
-        <v>8773</v>
+        <v>6114</v>
       </c>
       <c r="F1390" s="6" t="s">
         <v>8774</v>
       </c>
       <c r="G1390" s="6" t="s">
+        <v>8774</v>
+      </c>
+      <c r="H1390" s="6" t="s">
         <v>8775</v>
-      </c>
-      <c r="H1390" s="6" t="s">
-        <v>8776</v>
       </c>
     </row>
     <row r="1391">
       <c r="B1391" s="5" t="s">
+        <v>8776</v>
+      </c>
+      <c r="C1391" s="5" t="s">
         <v>8777</v>
       </c>
-      <c r="C1391" s="5" t="s">
+      <c r="D1391" s="5" t="s">
         <v>8778</v>
       </c>
-      <c r="D1391" s="5" t="s">
+      <c r="E1391" s="5" t="s">
         <v>8779</v>
       </c>
-      <c r="E1391" s="5" t="s">
+      <c r="F1391" s="5" t="s">
         <v>8780</v>
       </c>
-      <c r="F1391" s="5" t="s">
+      <c r="G1391" s="5" t="s">
         <v>8781</v>
       </c>
-      <c r="G1391" s="5" t="s">
+      <c r="H1391" s="5" t="s">
         <v>8782</v>
-      </c>
-      <c r="H1391" s="5" t="s">
-        <v>8783</v>
       </c>
     </row>
     <row r="1392">
       <c r="B1392" s="6" t="s">
+        <v>8783</v>
+      </c>
+      <c r="C1392" s="6" t="s">
         <v>8784</v>
       </c>
-      <c r="C1392" s="6" t="s">
+      <c r="D1392" s="6" t="s">
         <v>8785</v>
       </c>
-      <c r="D1392" s="6" t="s">
+      <c r="E1392" s="6" t="s">
         <v>8786</v>
       </c>
-      <c r="E1392" s="6" t="s">
+      <c r="F1392" s="6" t="s">
         <v>8787</v>
       </c>
-      <c r="F1392" s="6" t="s">
+      <c r="G1392" s="6" t="s">
         <v>8788</v>
       </c>
-      <c r="G1392" s="6" t="s">
+      <c r="H1392" s="6" t="s">
         <v>8789</v>
-      </c>
-      <c r="H1392" s="6" t="s">
-        <v>8790</v>
       </c>
     </row>
     <row r="1393">
       <c r="B1393" s="5" t="s">
+        <v>8790</v>
+      </c>
+      <c r="C1393" s="5" t="s">
         <v>8791</v>
       </c>
-      <c r="C1393" s="5" t="s">
+      <c r="D1393" s="5" t="s">
         <v>8792</v>
       </c>
-      <c r="D1393" s="5" t="s">
+      <c r="E1393" s="5" t="s">
         <v>8793</v>
       </c>
-      <c r="E1393" s="5" t="s">
+      <c r="F1393" s="5" t="s">
         <v>8794</v>
       </c>
-      <c r="F1393" s="5" t="s">
+      <c r="G1393" s="5" t="s">
         <v>8795</v>
       </c>
-      <c r="G1393" s="5" t="s">
+      <c r="H1393" s="5" t="s">
         <v>8796</v>
-      </c>
-      <c r="H1393" s="5" t="s">
-        <v>8797</v>
       </c>
     </row>
     <row r="1394">
       <c r="B1394" s="6" t="s">
+        <v>8797</v>
+      </c>
+      <c r="C1394" s="6" t="s">
         <v>8798</v>
-      </c>
-      <c r="C1394" s="6" t="s">
-        <v>8799</v>
       </c>
       <c r="D1394" s="6" t="s">
         <v>8799</v>
       </c>
       <c r="E1394" s="6" t="s">
-        <v>8799</v>
+        <v>8800</v>
       </c>
       <c r="F1394" s="6" t="s">
-        <v>8799</v>
+        <v>8801</v>
       </c>
       <c r="G1394" s="6" t="s">
-        <v>8799</v>
+        <v>8802</v>
       </c>
       <c r="H1394" s="6" t="s">
-        <v>8799</v>
+        <v>8803</v>
       </c>
     </row>
     <row r="1395">
       <c r="B1395" s="5" t="s">
-        <v>8800</v>
+        <v>8804</v>
       </c>
       <c r="C1395" s="5" t="s">
-        <v>8801</v>
+        <v>8805</v>
       </c>
       <c r="D1395" s="5" t="s">
-        <v>8802</v>
+        <v>8806</v>
       </c>
       <c r="E1395" s="5" t="s">
-        <v>8803</v>
+        <v>8807</v>
       </c>
       <c r="F1395" s="5" t="s">
-        <v>8804</v>
+        <v>8808</v>
       </c>
       <c r="G1395" s="5" t="s">
-        <v>8804</v>
+        <v>8809</v>
       </c>
       <c r="H1395" s="5" t="s">
-        <v>8805</v>
+        <v>8810</v>
       </c>
     </row>
     <row r="1396">
       <c r="B1396" s="6" t="s">
-        <v>8806</v>
+        <v>8811</v>
       </c>
       <c r="C1396" s="6" t="s">
-        <v>8807</v>
+        <v>8812</v>
       </c>
       <c r="D1396" s="6" t="s">
-        <v>8808</v>
+        <v>8812</v>
       </c>
       <c r="E1396" s="6" t="s">
-        <v>8809</v>
+        <v>8812</v>
       </c>
       <c r="F1396" s="6" t="s">
-        <v>8810</v>
+        <v>8812</v>
       </c>
       <c r="G1396" s="6" t="s">
-        <v>8811</v>
+        <v>8812</v>
       </c>
       <c r="H1396" s="6" t="s">
         <v>8812</v>
@@ -59349,27 +59388,27 @@
         <v>8817</v>
       </c>
       <c r="G1397" s="5" t="s">
+        <v>8817</v>
+      </c>
+      <c r="H1397" s="5" t="s">
         <v>8818</v>
-      </c>
-      <c r="H1397" s="5" t="s">
-        <v>8819</v>
       </c>
     </row>
     <row r="1398">
       <c r="B1398" s="6" t="s">
+        <v>8819</v>
+      </c>
+      <c r="C1398" s="6" t="s">
         <v>8820</v>
       </c>
-      <c r="C1398" s="6" t="s">
+      <c r="D1398" s="6" t="s">
         <v>8821</v>
       </c>
-      <c r="D1398" s="6" t="s">
+      <c r="E1398" s="6" t="s">
         <v>8822</v>
       </c>
-      <c r="E1398" s="6" t="s">
+      <c r="F1398" s="6" t="s">
         <v>8823</v>
-      </c>
-      <c r="F1398" s="6" t="s">
-        <v>8824</v>
       </c>
       <c r="G1398" s="6" t="s">
         <v>8824</v>
@@ -59395,27 +59434,27 @@
         <v>8830</v>
       </c>
       <c r="G1399" s="5" t="s">
-        <v>8830</v>
+        <v>8831</v>
       </c>
       <c r="H1399" s="5" t="s">
-        <v>8831</v>
+        <v>8832</v>
       </c>
     </row>
     <row r="1400">
       <c r="B1400" s="6" t="s">
-        <v>8832</v>
+        <v>8833</v>
       </c>
       <c r="C1400" s="6" t="s">
-        <v>8833</v>
+        <v>8834</v>
       </c>
       <c r="D1400" s="6" t="s">
-        <v>8834</v>
+        <v>8835</v>
       </c>
       <c r="E1400" s="6" t="s">
-        <v>8835</v>
+        <v>8836</v>
       </c>
       <c r="F1400" s="6" t="s">
-        <v>8836</v>
+        <v>8837</v>
       </c>
       <c r="G1400" s="6" t="s">
         <v>8837</v>
@@ -59441,440 +59480,486 @@
         <v>8843</v>
       </c>
       <c r="G1401" s="5" t="s">
+        <v>8843</v>
+      </c>
+      <c r="H1401" s="5" t="s">
         <v>8844</v>
-      </c>
-      <c r="H1401" s="5" t="s">
-        <v>8845</v>
       </c>
     </row>
     <row r="1402">
       <c r="B1402" s="6" t="s">
+        <v>8845</v>
+      </c>
+      <c r="C1402" s="6" t="s">
         <v>8846</v>
       </c>
-      <c r="C1402" s="6" t="s">
+      <c r="D1402" s="6" t="s">
         <v>8847</v>
       </c>
-      <c r="D1402" s="6" t="s">
+      <c r="E1402" s="6" t="s">
         <v>8848</v>
       </c>
-      <c r="E1402" s="6" t="s">
+      <c r="F1402" s="6" t="s">
         <v>8849</v>
       </c>
-      <c r="F1402" s="6" t="s">
+      <c r="G1402" s="6" t="s">
         <v>8850</v>
       </c>
-      <c r="G1402" s="6" t="s">
+      <c r="H1402" s="6" t="s">
         <v>8851</v>
-      </c>
-      <c r="H1402" s="6" t="s">
-        <v>8852</v>
       </c>
     </row>
     <row r="1403">
       <c r="B1403" s="5" t="s">
+        <v>8852</v>
+      </c>
+      <c r="C1403" s="5" t="s">
         <v>8853</v>
       </c>
-      <c r="C1403" s="5" t="s">
+      <c r="D1403" s="5" t="s">
         <v>8854</v>
       </c>
-      <c r="D1403" s="5" t="s">
+      <c r="E1403" s="5" t="s">
         <v>8855</v>
       </c>
-      <c r="E1403" s="5" t="s">
+      <c r="F1403" s="5" t="s">
         <v>8856</v>
       </c>
-      <c r="F1403" s="5" t="s">
+      <c r="G1403" s="5" t="s">
         <v>8857</v>
       </c>
-      <c r="G1403" s="5" t="s">
+      <c r="H1403" s="5" t="s">
         <v>8858</v>
-      </c>
-      <c r="H1403" s="5" t="s">
-        <v>8859</v>
       </c>
     </row>
     <row r="1404">
       <c r="B1404" s="6" t="s">
+        <v>8859</v>
+      </c>
+      <c r="C1404" s="6" t="s">
         <v>8860</v>
       </c>
-      <c r="C1404" s="6" t="s">
+      <c r="D1404" s="6" t="s">
         <v>8861</v>
       </c>
-      <c r="D1404" s="6" t="s">
+      <c r="E1404" s="6" t="s">
         <v>8862</v>
       </c>
-      <c r="E1404" s="6" t="s">
+      <c r="F1404" s="6" t="s">
         <v>8863</v>
       </c>
-      <c r="F1404" s="6" t="s">
+      <c r="G1404" s="6" t="s">
         <v>8864</v>
       </c>
-      <c r="G1404" s="6" t="s">
+      <c r="H1404" s="6" t="s">
         <v>8865</v>
-      </c>
-      <c r="H1404" s="6" t="s">
-        <v>8866</v>
       </c>
     </row>
     <row r="1405">
       <c r="B1405" s="5" t="s">
+        <v>8866</v>
+      </c>
+      <c r="C1405" s="5" t="s">
         <v>8867</v>
       </c>
-      <c r="C1405" s="5" t="s">
+      <c r="D1405" s="5" t="s">
         <v>8868</v>
       </c>
-      <c r="D1405" s="5" t="s">
+      <c r="E1405" s="5" t="s">
         <v>8869</v>
       </c>
-      <c r="E1405" s="5" t="s">
+      <c r="F1405" s="5" t="s">
         <v>8870</v>
       </c>
-      <c r="F1405" s="5" t="s">
+      <c r="G1405" s="5" t="s">
         <v>8871</v>
       </c>
-      <c r="G1405" s="5" t="s">
+      <c r="H1405" s="5" t="s">
         <v>8872</v>
-      </c>
-      <c r="H1405" s="5" t="s">
-        <v>8873</v>
       </c>
     </row>
     <row r="1406">
       <c r="B1406" s="6" t="s">
+        <v>8873</v>
+      </c>
+      <c r="C1406" s="6" t="s">
         <v>8874</v>
       </c>
-      <c r="C1406" s="6" t="s">
+      <c r="D1406" s="6" t="s">
         <v>8875</v>
       </c>
-      <c r="D1406" s="6" t="s">
+      <c r="E1406" s="6" t="s">
         <v>8876</v>
       </c>
-      <c r="E1406" s="6" t="s">
+      <c r="F1406" s="6" t="s">
         <v>8877</v>
       </c>
-      <c r="F1406" s="6" t="s">
+      <c r="G1406" s="6" t="s">
         <v>8878</v>
       </c>
-      <c r="G1406" s="6" t="s">
+      <c r="H1406" s="6" t="s">
         <v>8879</v>
-      </c>
-      <c r="H1406" s="6" t="s">
-        <v>8880</v>
       </c>
     </row>
     <row r="1407">
       <c r="B1407" s="5" t="s">
+        <v>8880</v>
+      </c>
+      <c r="C1407" s="5" t="s">
         <v>8881</v>
       </c>
-      <c r="C1407" s="5" t="s">
+      <c r="D1407" s="5" t="s">
         <v>8882</v>
       </c>
-      <c r="D1407" s="5" t="s">
+      <c r="E1407" s="5" t="s">
         <v>8883</v>
       </c>
-      <c r="E1407" s="5" t="s">
+      <c r="F1407" s="5" t="s">
         <v>8884</v>
       </c>
-      <c r="F1407" s="5" t="s">
+      <c r="G1407" s="5" t="s">
         <v>8885</v>
       </c>
-      <c r="G1407" s="5" t="s">
+      <c r="H1407" s="5" t="s">
         <v>8886</v>
-      </c>
-      <c r="H1407" s="5" t="s">
-        <v>8887</v>
       </c>
     </row>
     <row r="1408">
       <c r="B1408" s="6" t="s">
+        <v>8887</v>
+      </c>
+      <c r="C1408" s="6" t="s">
         <v>8888</v>
       </c>
-      <c r="C1408" s="6" t="s">
+      <c r="D1408" s="6" t="s">
         <v>8889</v>
       </c>
-      <c r="D1408" s="6" t="s">
+      <c r="E1408" s="6" t="s">
         <v>8890</v>
       </c>
-      <c r="E1408" s="6" t="s">
+      <c r="F1408" s="6" t="s">
         <v>8891</v>
       </c>
-      <c r="F1408" s="6" t="s">
+      <c r="G1408" s="6" t="s">
         <v>8892</v>
       </c>
-      <c r="G1408" s="6" t="s">
+      <c r="H1408" s="6" t="s">
         <v>8893</v>
-      </c>
-      <c r="H1408" s="6" t="s">
-        <v>8894</v>
       </c>
     </row>
     <row r="1409">
       <c r="B1409" s="5" t="s">
+        <v>8894</v>
+      </c>
+      <c r="C1409" s="5" t="s">
         <v>8895</v>
-      </c>
-      <c r="C1409" s="5" t="s">
-        <v>4582</v>
       </c>
       <c r="D1409" s="5" t="s">
         <v>8896</v>
       </c>
       <c r="E1409" s="5" t="s">
-        <v>4584</v>
+        <v>8897</v>
       </c>
       <c r="F1409" s="5" t="s">
-        <v>8897</v>
+        <v>8898</v>
       </c>
       <c r="G1409" s="5" t="s">
-        <v>8898</v>
+        <v>8899</v>
       </c>
       <c r="H1409" s="5" t="s">
-        <v>8899</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="1410">
       <c r="B1410" s="6" t="s">
-        <v>8900</v>
+        <v>8901</v>
       </c>
       <c r="C1410" s="6" t="s">
-        <v>8901</v>
+        <v>8902</v>
       </c>
       <c r="D1410" s="6" t="s">
-        <v>8902</v>
+        <v>8903</v>
+      </c>
+      <c r="E1410" s="6" t="s">
+        <v>8904</v>
+      </c>
+      <c r="F1410" s="6" t="s">
+        <v>8905</v>
+      </c>
+      <c r="G1410" s="6" t="s">
+        <v>8906</v>
+      </c>
+      <c r="H1410" s="6" t="s">
+        <v>8907</v>
       </c>
     </row>
     <row r="1411">
       <c r="B1411" s="5" t="s">
-        <v>8903</v>
+        <v>8908</v>
       </c>
       <c r="C1411" s="5" t="s">
-        <v>8904</v>
+        <v>4582</v>
       </c>
       <c r="D1411" s="5" t="s">
-        <v>8905</v>
+        <v>8909</v>
+      </c>
+      <c r="E1411" s="5" t="s">
+        <v>4584</v>
+      </c>
+      <c r="F1411" s="5" t="s">
+        <v>8910</v>
+      </c>
+      <c r="G1411" s="5" t="s">
+        <v>8911</v>
+      </c>
+      <c r="H1411" s="5" t="s">
+        <v>8912</v>
       </c>
     </row>
     <row r="1412">
       <c r="B1412" s="6" t="s">
-        <v>8906</v>
+        <v>8913</v>
       </c>
       <c r="C1412" s="6" t="s">
-        <v>8907</v>
+        <v>8914</v>
       </c>
       <c r="D1412" s="6" t="s">
-        <v>8908</v>
+        <v>8915</v>
       </c>
     </row>
     <row r="1413">
       <c r="B1413" s="5" t="s">
-        <v>8909</v>
+        <v>8916</v>
       </c>
       <c r="C1413" s="5" t="s">
-        <v>8910</v>
+        <v>8917</v>
       </c>
       <c r="D1413" s="5" t="s">
-        <v>8911</v>
+        <v>8918</v>
       </c>
     </row>
     <row r="1414">
       <c r="B1414" s="6" t="s">
-        <v>8912</v>
+        <v>8919</v>
       </c>
       <c r="C1414" s="6" t="s">
-        <v>8913</v>
+        <v>8920</v>
       </c>
       <c r="D1414" s="6" t="s">
-        <v>8914</v>
+        <v>8921</v>
       </c>
     </row>
     <row r="1415">
       <c r="B1415" s="5" t="s">
-        <v>8915</v>
+        <v>8922</v>
       </c>
       <c r="C1415" s="5" t="s">
-        <v>8916</v>
+        <v>8923</v>
       </c>
       <c r="D1415" s="5" t="s">
-        <v>8917</v>
+        <v>8924</v>
       </c>
     </row>
     <row r="1416">
       <c r="B1416" s="6" t="s">
-        <v>8918</v>
+        <v>8925</v>
       </c>
       <c r="C1416" s="6" t="s">
-        <v>8919</v>
+        <v>8926</v>
       </c>
       <c r="D1416" s="6" t="s">
-        <v>8920</v>
+        <v>8927</v>
       </c>
     </row>
     <row r="1417">
       <c r="B1417" s="5" t="s">
-        <v>8921</v>
+        <v>8928</v>
       </c>
       <c r="C1417" s="5" t="s">
-        <v>8922</v>
+        <v>8929</v>
       </c>
       <c r="D1417" s="5" t="s">
-        <v>8923</v>
+        <v>8930</v>
       </c>
     </row>
     <row r="1418">
       <c r="B1418" s="6" t="s">
-        <v>8924</v>
+        <v>8931</v>
       </c>
       <c r="C1418" s="6" t="s">
-        <v>8925</v>
+        <v>8932</v>
       </c>
       <c r="D1418" s="6" t="s">
-        <v>8926</v>
+        <v>8933</v>
       </c>
     </row>
     <row r="1419">
       <c r="B1419" s="5" t="s">
-        <v>8927</v>
+        <v>8934</v>
       </c>
       <c r="C1419" s="5" t="s">
-        <v>8928</v>
+        <v>8935</v>
       </c>
       <c r="D1419" s="5" t="s">
-        <v>8929</v>
+        <v>8936</v>
       </c>
     </row>
     <row r="1420">
       <c r="B1420" s="6" t="s">
-        <v>8930</v>
+        <v>8937</v>
       </c>
       <c r="C1420" s="6" t="s">
-        <v>8931</v>
+        <v>8938</v>
       </c>
       <c r="D1420" s="6" t="s">
-        <v>8932</v>
+        <v>8939</v>
       </c>
     </row>
     <row r="1421">
       <c r="B1421" s="5" t="s">
-        <v>8933</v>
+        <v>8940</v>
       </c>
       <c r="C1421" s="5" t="s">
-        <v>8934</v>
+        <v>8941</v>
       </c>
       <c r="D1421" s="5" t="s">
-        <v>8935</v>
+        <v>8942</v>
       </c>
     </row>
     <row r="1422">
       <c r="B1422" s="6" t="s">
-        <v>8936</v>
+        <v>8943</v>
       </c>
       <c r="C1422" s="6" t="s">
-        <v>8937</v>
+        <v>8944</v>
       </c>
       <c r="D1422" s="6" t="s">
-        <v>8938</v>
+        <v>8945</v>
       </c>
     </row>
     <row r="1423">
       <c r="B1423" s="5" t="s">
-        <v>8939</v>
+        <v>8946</v>
       </c>
       <c r="C1423" s="5" t="s">
-        <v>8940</v>
+        <v>8947</v>
       </c>
       <c r="D1423" s="5" t="s">
-        <v>8941</v>
+        <v>8948</v>
       </c>
     </row>
     <row r="1424">
       <c r="B1424" s="6" t="s">
-        <v>8942</v>
+        <v>8949</v>
       </c>
       <c r="C1424" s="6" t="s">
-        <v>8943</v>
+        <v>8950</v>
       </c>
       <c r="D1424" s="6" t="s">
-        <v>8944</v>
+        <v>8951</v>
       </c>
     </row>
     <row r="1425">
       <c r="B1425" s="5" t="s">
-        <v>8945</v>
+        <v>8952</v>
       </c>
       <c r="C1425" s="5" t="s">
-        <v>6112</v>
+        <v>8953</v>
       </c>
       <c r="D1425" s="5" t="s">
-        <v>8760</v>
+        <v>8954</v>
       </c>
     </row>
     <row r="1426">
       <c r="B1426" s="6" t="s">
-        <v>8946</v>
+        <v>8955</v>
       </c>
       <c r="C1426" s="6" t="s">
-        <v>8947</v>
+        <v>8956</v>
       </c>
       <c r="D1426" s="6" t="s">
-        <v>8948</v>
+        <v>8957</v>
       </c>
     </row>
     <row r="1427">
       <c r="B1427" s="5" t="s">
-        <v>8949</v>
+        <v>8958</v>
       </c>
       <c r="C1427" s="5" t="s">
-        <v>8950</v>
+        <v>6112</v>
       </c>
       <c r="D1427" s="5" t="s">
-        <v>8951</v>
+        <v>8773</v>
       </c>
     </row>
     <row r="1428">
       <c r="B1428" s="6" t="s">
-        <v>8952</v>
+        <v>8959</v>
       </c>
       <c r="C1428" s="6" t="s">
-        <v>8953</v>
+        <v>8960</v>
       </c>
       <c r="D1428" s="6" t="s">
-        <v>8954</v>
+        <v>8961</v>
       </c>
     </row>
     <row r="1429">
       <c r="B1429" s="5" t="s">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="C1429" s="5" t="s">
-        <v>8956</v>
+        <v>8963</v>
       </c>
       <c r="D1429" s="5" t="s">
-        <v>8957</v>
+        <v>8964</v>
       </c>
     </row>
     <row r="1430">
       <c r="B1430" s="6" t="s">
-        <v>8958</v>
+        <v>8965</v>
       </c>
       <c r="C1430" s="6" t="s">
-        <v>8959</v>
+        <v>8966</v>
       </c>
       <c r="D1430" s="6" t="s">
-        <v>8960</v>
+        <v>8967</v>
       </c>
     </row>
     <row r="1431">
       <c r="B1431" s="5" t="s">
-        <v>8961</v>
+        <v>8968</v>
       </c>
       <c r="C1431" s="5" t="s">
-        <v>8962</v>
+        <v>8969</v>
       </c>
       <c r="D1431" s="5" t="s">
-        <v>8963</v>
+        <v>8970</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="B1432" s="6" t="s">
+        <v>8971</v>
+      </c>
+      <c r="C1432" s="6" t="s">
+        <v>8972</v>
+      </c>
+      <c r="D1432" s="6" t="s">
+        <v>8973</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="B1433" s="5" t="s">
+        <v>8974</v>
+      </c>
+      <c r="C1433" s="5" t="s">
+        <v>8975</v>
+      </c>
+      <c r="D1433" s="5" t="s">
+        <v>8976</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H1431"/>
+  <autoFilter ref="B2:H1433"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -59893,10 +59978,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>8964</v>
+        <v>8977</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8965</v>
+        <v>8978</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -59907,16 +59992,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8966</v>
+        <v>8979</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8967</v>
+        <v>8980</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8968</v>
+        <v>8981</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8969</v>
+        <v>8982</v>
       </c>
     </row>
     <row r="3">
@@ -59924,16 +60009,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8970</v>
+        <v>8983</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8971</v>
+        <v>8984</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8972</v>
+        <v>8985</v>
       </c>
     </row>
     <row r="4">
@@ -59944,24 +60029,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8973</v>
+        <v>8986</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8974</v>
+        <v>8987</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8975</v>
+        <v>8988</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>8976</v>
+        <v>8989</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4569</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8977</v>
+        <v>8990</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -59969,13 +60054,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>8978</v>
+        <v>8991</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4576</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>8979</v>
+        <v>8992</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -59983,13 +60068,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>8980</v>
+        <v>8993</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4582</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8981</v>
+        <v>8994</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -59997,13 +60082,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>8982</v>
+        <v>8995</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4588</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>8983</v>
+        <v>8996</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -60011,13 +60096,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>8984</v>
+        <v>8997</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4595</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8985</v>
+        <v>8998</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -60025,13 +60110,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>8986</v>
+        <v>8999</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4602</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>8987</v>
+        <v>9000</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -60039,13 +60124,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>8988</v>
+        <v>9001</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4608</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>8989</v>
+        <v>9002</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -60053,13 +60138,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>8990</v>
+        <v>9003</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4614</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>8991</v>
+        <v>9004</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -60067,13 +60152,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>8992</v>
+        <v>9005</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4621</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8993</v>
+        <v>9006</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -60081,13 +60166,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>8994</v>
+        <v>9007</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4627</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>8995</v>
+        <v>9008</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -60101,7 +60186,7 @@
         <v>4633</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8996</v>
+        <v>9009</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -60109,13 +60194,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>8997</v>
+        <v>9010</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4640</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>8998</v>
+        <v>9011</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -60123,13 +60208,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>8999</v>
+        <v>9012</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4647</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>9000</v>
+        <v>9013</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -60137,13 +60222,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>9001</v>
+        <v>9014</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4653</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>9002</v>
+        <v>9015</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -60151,13 +60236,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>9003</v>
+        <v>9016</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4660</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>9004</v>
+        <v>9017</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -60165,13 +60250,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>9005</v>
+        <v>9018</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4666</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>9006</v>
+        <v>9019</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -60179,13 +60264,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>9007</v>
+        <v>9020</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4671</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>9008</v>
+        <v>9021</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -60193,13 +60278,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>9009</v>
+        <v>9022</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4678</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>9010</v>
+        <v>9023</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -60207,13 +60292,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>9011</v>
+        <v>9024</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4500</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>9012</v>
+        <v>9025</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -60221,13 +60306,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>9013</v>
+        <v>9026</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4686</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>9014</v>
+        <v>9027</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1442"/>
+  <dimension ref="A1:H1448"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col width="41.015625" customWidth="1" min="1" max="1"/>
@@ -53410,6 +53410,228 @@
       <c r="H1442" t="inlineStr">
         <is>
           <t>Leer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>ui.option.uiTheme</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>판의 색</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Panel colour</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>パネルの色</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>面板颜色</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>面板顏色</t>
+        </is>
+      </c>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>Tafelfarbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>ui.option.note.uiTheme</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>판과 테와 선의 색입니다. 값과 단추의 색은 바뀌지 않습니다</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>The colour of panels, borders and lines. Value and button colours do not change.</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>パネル・枠・線の色です。値とボタンの色は変わりません。</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>面板、边框和线条的颜色。数值和按钮的颜色不变。</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>面板、邊框和線條的顏色。數值和按鈕的顏色不變。</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>Die Farbe von Tafeln, Rändern und Linien. Wert- und Knopffarben bleiben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>ui.theme.slate</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>남흑</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Slate</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>紺黒</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>蓝黑</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>藍黑</t>
+        </is>
+      </c>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>Schiefer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>ui.theme.ink</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>먹</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Ink</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>墨</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>墨黑</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>墨黑</t>
+        </is>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>Tusche</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>ui.theme.navy</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>청</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>藍</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>藏蓝</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>藏藍</t>
+        </is>
+      </c>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>ui.theme.bright</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>밝게</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Bright</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>明るめ</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>明亮</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>明亮</t>
+        </is>
+      </c>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>Hell</t>
         </is>
       </c>
     </row>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -53421,32 +53421,32 @@
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>판의 색</t>
+          <t>테마</t>
         </is>
       </c>
       <c r="D1443" t="inlineStr">
         <is>
-          <t>Panel colour</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>パネルの色</t>
+          <t>テーマ</t>
         </is>
       </c>
       <c r="F1443" t="inlineStr">
         <is>
-          <t>面板颜色</t>
+          <t>主题</t>
         </is>
       </c>
       <c r="G1443" t="inlineStr">
         <is>
-          <t>面板顏色</t>
+          <t>主題</t>
         </is>
       </c>
       <c r="H1443" t="inlineStr">
         <is>
-          <t>Tafelfarbe</t>
+          <t>Thema</t>
         </is>
       </c>
     </row>
@@ -53495,32 +53495,32 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>남흑</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
         <is>
-          <t>Slate</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>紺黒</t>
+          <t>標準</t>
         </is>
       </c>
       <c r="F1445" t="inlineStr">
         <is>
-          <t>蓝黑</t>
+          <t>默认</t>
         </is>
       </c>
       <c r="G1445" t="inlineStr">
         <is>
-          <t>藍黑</t>
+          <t>預設</t>
         </is>
       </c>
       <c r="H1445" t="inlineStr">
         <is>
-          <t>Schiefer</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -53532,32 +53532,32 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>먹</t>
+          <t>검정</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
         <is>
-          <t>Ink</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>墨</t>
+          <t>ブラック</t>
         </is>
       </c>
       <c r="F1446" t="inlineStr">
         <is>
-          <t>墨黑</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="G1446" t="inlineStr">
         <is>
-          <t>墨黑</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="H1446" t="inlineStr">
         <is>
-          <t>Tusche</t>
+          <t>Schwarz</t>
         </is>
       </c>
     </row>
@@ -53569,7 +53569,7 @@
       </c>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>청</t>
+          <t>남색</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr">
@@ -53579,7 +53579,7 @@
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>藍</t>
+          <t>ネイビー</t>
         </is>
       </c>
       <c r="F1447" t="inlineStr">
@@ -53606,32 +53606,32 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>밝게</t>
+          <t>밝은 회색</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
         <is>
-          <t>Bright</t>
+          <t>Light grey</t>
         </is>
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>明るめ</t>
+          <t>ライトグレー</t>
         </is>
       </c>
       <c r="F1448" t="inlineStr">
         <is>
-          <t>明亮</t>
+          <t>浅灰</t>
         </is>
       </c>
       <c r="G1448" t="inlineStr">
         <is>
-          <t>明亮</t>
+          <t>淺灰</t>
         </is>
       </c>
       <c r="H1448" t="inlineStr">
         <is>
-          <t>Hell</t>
+          <t>Hellgrau</t>
         </is>
       </c>
     </row>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -50968,32 +50968,32 @@
       </c>
       <c r="C1364" s="6" t="inlineStr">
         <is>
-          <t>런을 한 번 이기면 챌린지가 열립니다.</t>
+          <t>보스 블라인드를 한 번 격파하면 챌린지가 열립니다.</t>
         </is>
       </c>
       <c r="D1364" s="6" t="inlineStr">
         <is>
-          <t>Win a run to unlock challenges.</t>
+          <t>Beat a boss blind to unlock challenges.</t>
         </is>
       </c>
       <c r="E1364" s="6" t="inlineStr">
         <is>
-          <t>ランに一度勝つとチャレンジが開きます。</t>
+          <t>ボスブラインドを一度倒すとチャレンジが開きます。</t>
         </is>
       </c>
       <c r="F1364" s="6" t="inlineStr">
         <is>
-          <t>赢下一局后开启挑战。</t>
+          <t>击败一次 Boss 盲注后开启挑战。</t>
         </is>
       </c>
       <c r="G1364" s="6" t="inlineStr">
         <is>
-          <t>贏下一局後開啟挑戰。</t>
+          <t>擊敗一次 Boss 盲注後開啟挑戰。</t>
         </is>
       </c>
       <c r="H1364" s="6" t="inlineStr">
         <is>
-          <t>Gewinne einen Run, um Herausforderungen freizuschalten.</t>
+          <t>Besiege einen Boss-Blind, um Herausforderungen freizuschalten.</t>
         </is>
       </c>
     </row>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1524]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1538]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10657" uniqueCount="9601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10755" uniqueCount="9653">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -28667,6 +28667,162 @@
   </si>
   <si>
     <t xml:space="preserve">Dein Fortschritt wird gespeichert. Du kannst beim nächsten Start fortsetzen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">콜렉션</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コレクション</t>
+  </si>
+  <si>
+    <t xml:space="preserve">收藏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sammlung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.collection.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.collection.found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">발견 {at} / {of}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{at} / {of} found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">発見 {at} / {of}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已发现 {at} / {of}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已發現 {at} / {of}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{at} / {of} entdeckt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.collection.hint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">만나 본 것이 앞면입니다. 가리키면 설명이 뜹니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What you have met shows its face. Point at one to see it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出会ったものが表になります。指すと説明が出ます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遇到过的会翻到正面。指向即可查看说明。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遇過的會翻到正面。指向即可查看說明。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was du getroffen hast, zeigt sein Gesicht. Zeige darauf für Details.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.collection.unseen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아직 만나지 못했습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not met yet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">まだ出会っていません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">尚未遇到</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noch nicht getroffen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.kind.joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.kind.enhancement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enhancement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.kind.seal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蜡封</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蠟封</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.kind.edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.kind.blind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.kind.boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.kind.stake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.quit.browser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">탭은 스스로 닫히지 않습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This tab cannot close itself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タブは自分で閉じられません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">标签页无法自行关闭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">分頁無法自行關閉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieser Tab kann sich nicht selbst schließen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.quit.browserBody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">브라우저에서 탭을 닫아 주십시오.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close the tab in your browser.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ブラウザでタブを閉じてください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请在浏览器中关闭标签页。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">請在瀏覽器中關閉分頁。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schließe den Tab in deinem Browser.</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -29028,7 +29184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1524"/>
+  <dimension ref="A1:H1538"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -63830,8 +63986,330 @@
         <v>9549</v>
       </c>
     </row>
+    <row r="1525">
+      <c r="B1525" s="5" t="s">
+        <v>9550</v>
+      </c>
+      <c r="C1525" s="5" t="s">
+        <v>9551</v>
+      </c>
+      <c r="D1525" s="5" t="s">
+        <v>9552</v>
+      </c>
+      <c r="E1525" s="5" t="s">
+        <v>9553</v>
+      </c>
+      <c r="F1525" s="5" t="s">
+        <v>9554</v>
+      </c>
+      <c r="G1525" s="5" t="s">
+        <v>9554</v>
+      </c>
+      <c r="H1525" s="5" t="s">
+        <v>9555</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="B1526" s="6" t="s">
+        <v>9556</v>
+      </c>
+      <c r="C1526" s="6" t="s">
+        <v>9551</v>
+      </c>
+      <c r="D1526" s="6" t="s">
+        <v>9552</v>
+      </c>
+      <c r="E1526" s="6" t="s">
+        <v>9553</v>
+      </c>
+      <c r="F1526" s="6" t="s">
+        <v>9554</v>
+      </c>
+      <c r="G1526" s="6" t="s">
+        <v>9554</v>
+      </c>
+      <c r="H1526" s="6" t="s">
+        <v>9555</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="B1527" s="5" t="s">
+        <v>9557</v>
+      </c>
+      <c r="C1527" s="5" t="s">
+        <v>9558</v>
+      </c>
+      <c r="D1527" s="5" t="s">
+        <v>9559</v>
+      </c>
+      <c r="E1527" s="5" t="s">
+        <v>9560</v>
+      </c>
+      <c r="F1527" s="5" t="s">
+        <v>9561</v>
+      </c>
+      <c r="G1527" s="5" t="s">
+        <v>9562</v>
+      </c>
+      <c r="H1527" s="5" t="s">
+        <v>9563</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="B1528" s="6" t="s">
+        <v>9564</v>
+      </c>
+      <c r="C1528" s="6" t="s">
+        <v>9565</v>
+      </c>
+      <c r="D1528" s="6" t="s">
+        <v>9566</v>
+      </c>
+      <c r="E1528" s="6" t="s">
+        <v>9567</v>
+      </c>
+      <c r="F1528" s="6" t="s">
+        <v>9568</v>
+      </c>
+      <c r="G1528" s="6" t="s">
+        <v>9569</v>
+      </c>
+      <c r="H1528" s="6" t="s">
+        <v>9570</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="B1529" s="5" t="s">
+        <v>9571</v>
+      </c>
+      <c r="C1529" s="5" t="s">
+        <v>9572</v>
+      </c>
+      <c r="D1529" s="5" t="s">
+        <v>9573</v>
+      </c>
+      <c r="E1529" s="5" t="s">
+        <v>9574</v>
+      </c>
+      <c r="F1529" s="5" t="s">
+        <v>9575</v>
+      </c>
+      <c r="G1529" s="5" t="s">
+        <v>9575</v>
+      </c>
+      <c r="H1529" s="5" t="s">
+        <v>9576</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="B1530" s="6" t="s">
+        <v>9577</v>
+      </c>
+      <c r="C1530" s="6" t="s">
+        <v>6033</v>
+      </c>
+      <c r="D1530" s="6" t="s">
+        <v>5404</v>
+      </c>
+      <c r="E1530" s="6" t="s">
+        <v>6035</v>
+      </c>
+      <c r="F1530" s="6" t="s">
+        <v>8321</v>
+      </c>
+      <c r="G1530" s="6" t="s">
+        <v>8321</v>
+      </c>
+      <c r="H1530" s="6" t="s">
+        <v>5404</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="B1531" s="5" t="s">
+        <v>9578</v>
+      </c>
+      <c r="C1531" s="5" t="s">
+        <v>6087</v>
+      </c>
+      <c r="D1531" s="5" t="s">
+        <v>9579</v>
+      </c>
+      <c r="E1531" s="5" t="s">
+        <v>6089</v>
+      </c>
+      <c r="F1531" s="5" t="s">
+        <v>6090</v>
+      </c>
+      <c r="G1531" s="5" t="s">
+        <v>6089</v>
+      </c>
+      <c r="H1531" s="5" t="s">
+        <v>6091</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="B1532" s="6" t="s">
+        <v>9580</v>
+      </c>
+      <c r="C1532" s="6" t="s">
+        <v>6093</v>
+      </c>
+      <c r="D1532" s="6" t="s">
+        <v>9581</v>
+      </c>
+      <c r="E1532" s="6" t="s">
+        <v>6095</v>
+      </c>
+      <c r="F1532" s="6" t="s">
+        <v>9582</v>
+      </c>
+      <c r="G1532" s="6" t="s">
+        <v>9583</v>
+      </c>
+      <c r="H1532" s="6" t="s">
+        <v>6098</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="B1533" s="5" t="s">
+        <v>9584</v>
+      </c>
+      <c r="C1533" s="5" t="s">
+        <v>6100</v>
+      </c>
+      <c r="D1533" s="5" t="s">
+        <v>6104</v>
+      </c>
+      <c r="E1533" s="5" t="s">
+        <v>6102</v>
+      </c>
+      <c r="F1533" s="5" t="s">
+        <v>6103</v>
+      </c>
+      <c r="G1533" s="5" t="s">
+        <v>6103</v>
+      </c>
+      <c r="H1533" s="5" t="s">
+        <v>6104</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="B1534" s="6" t="s">
+        <v>9585</v>
+      </c>
+      <c r="C1534" s="6" t="s">
+        <v>6890</v>
+      </c>
+      <c r="D1534" s="6" t="s">
+        <v>6944</v>
+      </c>
+      <c r="E1534" s="6" t="s">
+        <v>6892</v>
+      </c>
+      <c r="F1534" s="6" t="s">
+        <v>6893</v>
+      </c>
+      <c r="G1534" s="6" t="s">
+        <v>6893</v>
+      </c>
+      <c r="H1534" s="6" t="s">
+        <v>6944</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="B1535" s="5" t="s">
+        <v>9586</v>
+      </c>
+      <c r="C1535" s="5" t="s">
+        <v>7349</v>
+      </c>
+      <c r="D1535" s="5" t="s">
+        <v>7350</v>
+      </c>
+      <c r="E1535" s="5" t="s">
+        <v>7351</v>
+      </c>
+      <c r="F1535" s="5" t="s">
+        <v>7350</v>
+      </c>
+      <c r="G1535" s="5" t="s">
+        <v>7350</v>
+      </c>
+      <c r="H1535" s="5" t="s">
+        <v>7350</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="B1536" s="6" t="s">
+        <v>9587</v>
+      </c>
+      <c r="C1536" s="6" t="s">
+        <v>6895</v>
+      </c>
+      <c r="D1536" s="6" t="s">
+        <v>8889</v>
+      </c>
+      <c r="E1536" s="6" t="s">
+        <v>6897</v>
+      </c>
+      <c r="F1536" s="6" t="s">
+        <v>6533</v>
+      </c>
+      <c r="G1536" s="6" t="s">
+        <v>6533</v>
+      </c>
+      <c r="H1536" s="6" t="s">
+        <v>8890</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="B1537" s="5" t="s">
+        <v>9588</v>
+      </c>
+      <c r="C1537" s="5" t="s">
+        <v>9589</v>
+      </c>
+      <c r="D1537" s="5" t="s">
+        <v>9590</v>
+      </c>
+      <c r="E1537" s="5" t="s">
+        <v>9591</v>
+      </c>
+      <c r="F1537" s="5" t="s">
+        <v>9592</v>
+      </c>
+      <c r="G1537" s="5" t="s">
+        <v>9593</v>
+      </c>
+      <c r="H1537" s="5" t="s">
+        <v>9594</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="B1538" s="6" t="s">
+        <v>9595</v>
+      </c>
+      <c r="C1538" s="6" t="s">
+        <v>9596</v>
+      </c>
+      <c r="D1538" s="6" t="s">
+        <v>9597</v>
+      </c>
+      <c r="E1538" s="6" t="s">
+        <v>9598</v>
+      </c>
+      <c r="F1538" s="6" t="s">
+        <v>9599</v>
+      </c>
+      <c r="G1538" s="6" t="s">
+        <v>9600</v>
+      </c>
+      <c r="H1538" s="6" t="s">
+        <v>9601</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H1524"/>
+  <autoFilter ref="B2:H1538"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -63850,10 +64328,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9550</v>
+        <v>9602</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9551</v>
+        <v>9603</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -63864,16 +64342,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9552</v>
+        <v>9604</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9553</v>
+        <v>9605</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9554</v>
+        <v>9606</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9555</v>
+        <v>9607</v>
       </c>
     </row>
     <row r="3">
@@ -63881,16 +64359,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9556</v>
+        <v>9608</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9557</v>
+        <v>9609</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>9558</v>
+        <v>9610</v>
       </c>
     </row>
     <row r="4">
@@ -63901,24 +64379,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9559</v>
+        <v>9611</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9560</v>
+        <v>9612</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>9561</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>9562</v>
+        <v>9614</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4569</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>9563</v>
+        <v>9615</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -63926,13 +64404,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>9564</v>
+        <v>9616</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4576</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>9565</v>
+        <v>9617</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -63940,13 +64418,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>9566</v>
+        <v>9618</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4582</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>9567</v>
+        <v>9619</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -63954,13 +64432,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>9568</v>
+        <v>9620</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4588</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9569</v>
+        <v>9621</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -63968,13 +64446,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>9570</v>
+        <v>9622</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4595</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>9571</v>
+        <v>9623</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -63982,13 +64460,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>9572</v>
+        <v>9624</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4602</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>9573</v>
+        <v>9625</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -63996,13 +64474,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>9574</v>
+        <v>9626</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4608</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>9575</v>
+        <v>9627</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -64010,13 +64488,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>9576</v>
+        <v>9628</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4614</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>9577</v>
+        <v>9629</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -64024,13 +64502,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>9578</v>
+        <v>9630</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4621</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>9579</v>
+        <v>9631</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -64038,13 +64516,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>9580</v>
+        <v>9632</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4627</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>9581</v>
+        <v>9633</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -64058,7 +64536,7 @@
         <v>4633</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>9582</v>
+        <v>9634</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -64066,13 +64544,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>9583</v>
+        <v>9635</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4640</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>9584</v>
+        <v>9636</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -64080,13 +64558,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>9585</v>
+        <v>9637</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4647</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>9586</v>
+        <v>9638</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -64094,13 +64572,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>9587</v>
+        <v>9639</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4653</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>9588</v>
+        <v>9640</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -64108,13 +64586,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>9589</v>
+        <v>9641</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4660</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>9590</v>
+        <v>9642</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -64122,13 +64600,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>9591</v>
+        <v>9643</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4666</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>9592</v>
+        <v>9644</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -64136,13 +64614,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>9593</v>
+        <v>9645</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4671</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>9594</v>
+        <v>9646</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -64150,13 +64628,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>9595</v>
+        <v>9647</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4678</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>9596</v>
+        <v>9648</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -64164,13 +64642,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>9597</v>
+        <v>9649</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4500</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>9598</v>
+        <v>9650</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -64178,13 +64656,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>9599</v>
+        <v>9651</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4686</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>9600</v>
+        <v>9652</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1538]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1540]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10755" uniqueCount="9653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10769" uniqueCount="9667">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -22573,6 +22573,27 @@
     <t xml:space="preserve">Farbsaum</t>
   </si>
   <si>
+    <t xml:space="preserve">ui.option.transition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면 전환</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scene Transitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面切り替え</t>
+  </si>
+  <si>
+    <t xml:space="preserve">场景切换</t>
+  </si>
+  <si>
+    <t xml:space="preserve">場景切換</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szenenübergänge</t>
+  </si>
+  <si>
     <t xml:space="preserve">ui.option.speed</t>
   </si>
   <si>
@@ -22916,6 +22937,27 @@
   </si>
   <si>
     <t xml:space="preserve">Farben trennen sich bei einem großen Treffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.option.note.transition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">씬이 갈릴 때 화면이 지워졌다 돌아옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The screen wipes out and back when scenes change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シーンが変わるとき画面が消えて戻ります</t>
+  </si>
+  <si>
+    <t xml:space="preserve">切换场景时画面会消失后返回</t>
+  </si>
+  <si>
+    <t xml:space="preserve">切換場景時畫面會消失後返回</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beim Szenenwechsel blendet der Bildschirm aus und wieder ein</t>
   </si>
   <si>
     <t xml:space="preserve">ui.option.note.haptics</t>
@@ -29184,7 +29226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1538"/>
+  <dimension ref="A1:H1540"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -56428,56 +56470,56 @@
         <v>7529</v>
       </c>
       <c r="G1186" s="6" t="s">
-        <v>7529</v>
+        <v>7530</v>
       </c>
       <c r="H1186" s="6" t="s">
-        <v>7530</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="1187">
       <c r="B1187" s="5" t="s">
-        <v>7531</v>
+        <v>7532</v>
       </c>
       <c r="C1187" s="5" t="s">
-        <v>7532</v>
+        <v>7533</v>
       </c>
       <c r="D1187" s="5" t="s">
-        <v>7533</v>
+        <v>7534</v>
       </c>
       <c r="E1187" s="5" t="s">
-        <v>7534</v>
+        <v>7535</v>
       </c>
       <c r="F1187" s="5" t="s">
-        <v>7535</v>
+        <v>7536</v>
       </c>
       <c r="G1187" s="5" t="s">
-        <v>7534</v>
+        <v>7536</v>
       </c>
       <c r="H1187" s="5" t="s">
-        <v>7533</v>
+        <v>7537</v>
       </c>
     </row>
     <row r="1188">
       <c r="B1188" s="6" t="s">
-        <v>7536</v>
+        <v>7538</v>
       </c>
       <c r="C1188" s="6" t="s">
-        <v>7537</v>
+        <v>7539</v>
       </c>
       <c r="D1188" s="6" t="s">
-        <v>7538</v>
+        <v>7540</v>
       </c>
       <c r="E1188" s="6" t="s">
-        <v>7539</v>
+        <v>7541</v>
       </c>
       <c r="F1188" s="6" t="s">
-        <v>7540</v>
+        <v>7542</v>
       </c>
       <c r="G1188" s="6" t="s">
         <v>7541</v>
       </c>
       <c r="H1188" s="6" t="s">
-        <v>7542</v>
+        <v>7540</v>
       </c>
     </row>
     <row r="1189">
@@ -56704,27 +56746,27 @@
         <v>7610</v>
       </c>
       <c r="G1198" s="6" t="s">
-        <v>7610</v>
+        <v>7611</v>
       </c>
       <c r="H1198" s="6" t="s">
-        <v>7611</v>
+        <v>7612</v>
       </c>
     </row>
     <row r="1199">
       <c r="B1199" s="5" t="s">
-        <v>7612</v>
+        <v>7613</v>
       </c>
       <c r="C1199" s="5" t="s">
-        <v>7613</v>
+        <v>7614</v>
       </c>
       <c r="D1199" s="5" t="s">
-        <v>7614</v>
+        <v>7615</v>
       </c>
       <c r="E1199" s="5" t="s">
-        <v>7615</v>
+        <v>7616</v>
       </c>
       <c r="F1199" s="5" t="s">
-        <v>7616</v>
+        <v>7617</v>
       </c>
       <c r="G1199" s="5" t="s">
         <v>7617</v>
@@ -57118,50 +57160,50 @@
         <v>7735</v>
       </c>
       <c r="G1216" s="6" t="s">
-        <v>7735</v>
+        <v>7736</v>
       </c>
       <c r="H1216" s="6" t="s">
-        <v>7736</v>
+        <v>7737</v>
       </c>
     </row>
     <row r="1217">
       <c r="B1217" s="5" t="s">
-        <v>7737</v>
+        <v>7738</v>
       </c>
       <c r="C1217" s="5" t="s">
-        <v>7738</v>
+        <v>7739</v>
       </c>
       <c r="D1217" s="5" t="s">
-        <v>7739</v>
+        <v>7740</v>
       </c>
       <c r="E1217" s="5" t="s">
-        <v>7740</v>
+        <v>7741</v>
       </c>
       <c r="F1217" s="5" t="s">
-        <v>7741</v>
+        <v>7742</v>
       </c>
       <c r="G1217" s="5" t="s">
-        <v>7742</v>
+        <v>7743</v>
       </c>
       <c r="H1217" s="5" t="s">
-        <v>7743</v>
+        <v>7744</v>
       </c>
     </row>
     <row r="1218">
       <c r="B1218" s="6" t="s">
-        <v>7744</v>
+        <v>7745</v>
       </c>
       <c r="C1218" s="6" t="s">
-        <v>7745</v>
+        <v>7746</v>
       </c>
       <c r="D1218" s="6" t="s">
-        <v>7746</v>
+        <v>7747</v>
       </c>
       <c r="E1218" s="6" t="s">
-        <v>7747</v>
+        <v>7748</v>
       </c>
       <c r="F1218" s="6" t="s">
-        <v>7748</v>
+        <v>7749</v>
       </c>
       <c r="G1218" s="6" t="s">
         <v>7749</v>
@@ -57187,50 +57229,50 @@
         <v>7755</v>
       </c>
       <c r="G1219" s="5" t="s">
-        <v>7755</v>
+        <v>7756</v>
       </c>
       <c r="H1219" s="5" t="s">
-        <v>7756</v>
+        <v>7757</v>
       </c>
     </row>
     <row r="1220">
       <c r="B1220" s="6" t="s">
-        <v>7757</v>
+        <v>7758</v>
       </c>
       <c r="C1220" s="6" t="s">
-        <v>7758</v>
+        <v>7759</v>
       </c>
       <c r="D1220" s="6" t="s">
-        <v>7759</v>
+        <v>7760</v>
       </c>
       <c r="E1220" s="6" t="s">
-        <v>7760</v>
+        <v>7761</v>
       </c>
       <c r="F1220" s="6" t="s">
-        <v>7761</v>
+        <v>7762</v>
       </c>
       <c r="G1220" s="6" t="s">
-        <v>7762</v>
+        <v>7763</v>
       </c>
       <c r="H1220" s="6" t="s">
-        <v>7763</v>
+        <v>7764</v>
       </c>
     </row>
     <row r="1221">
       <c r="B1221" s="5" t="s">
-        <v>7764</v>
+        <v>7765</v>
       </c>
       <c r="C1221" s="5" t="s">
-        <v>7765</v>
+        <v>7766</v>
       </c>
       <c r="D1221" s="5" t="s">
-        <v>7766</v>
+        <v>7767</v>
       </c>
       <c r="E1221" s="5" t="s">
-        <v>7767</v>
+        <v>7768</v>
       </c>
       <c r="F1221" s="5" t="s">
-        <v>7768</v>
+        <v>7769</v>
       </c>
       <c r="G1221" s="5" t="s">
         <v>7769</v>
@@ -57279,50 +57321,50 @@
         <v>7782</v>
       </c>
       <c r="G1223" s="5" t="s">
-        <v>7782</v>
+        <v>7783</v>
       </c>
       <c r="H1223" s="5" t="s">
-        <v>7783</v>
+        <v>7784</v>
       </c>
     </row>
     <row r="1224">
       <c r="B1224" s="6" t="s">
-        <v>7784</v>
+        <v>7785</v>
       </c>
       <c r="C1224" s="6" t="s">
-        <v>7785</v>
+        <v>7786</v>
       </c>
       <c r="D1224" s="6" t="s">
-        <v>7786</v>
+        <v>7787</v>
       </c>
       <c r="E1224" s="6" t="s">
-        <v>7787</v>
+        <v>7788</v>
       </c>
       <c r="F1224" s="6" t="s">
-        <v>7788</v>
+        <v>7789</v>
       </c>
       <c r="G1224" s="6" t="s">
-        <v>7789</v>
+        <v>7790</v>
       </c>
       <c r="H1224" s="6" t="s">
-        <v>7790</v>
+        <v>7791</v>
       </c>
     </row>
     <row r="1225">
       <c r="B1225" s="5" t="s">
-        <v>7791</v>
+        <v>7792</v>
       </c>
       <c r="C1225" s="5" t="s">
-        <v>7792</v>
+        <v>7793</v>
       </c>
       <c r="D1225" s="5" t="s">
-        <v>7793</v>
+        <v>7794</v>
       </c>
       <c r="E1225" s="5" t="s">
-        <v>7794</v>
+        <v>7795</v>
       </c>
       <c r="F1225" s="5" t="s">
-        <v>7795</v>
+        <v>7796</v>
       </c>
       <c r="G1225" s="5" t="s">
         <v>7796</v>
@@ -57466,53 +57508,53 @@
         <v>7838</v>
       </c>
       <c r="H1231" s="5" t="s">
-        <v>7835</v>
+        <v>7839</v>
       </c>
     </row>
     <row r="1232">
       <c r="B1232" s="6" t="s">
-        <v>7839</v>
+        <v>7840</v>
       </c>
       <c r="C1232" s="6" t="s">
-        <v>7840</v>
+        <v>7841</v>
       </c>
       <c r="D1232" s="6" t="s">
-        <v>7841</v>
+        <v>7842</v>
       </c>
       <c r="E1232" s="6" t="s">
-        <v>7842</v>
+        <v>7843</v>
       </c>
       <c r="F1232" s="6" t="s">
-        <v>7843</v>
+        <v>7844</v>
       </c>
       <c r="G1232" s="6" t="s">
-        <v>7844</v>
+        <v>7845</v>
       </c>
       <c r="H1232" s="6" t="s">
-        <v>7845</v>
+        <v>7846</v>
       </c>
     </row>
     <row r="1233">
       <c r="B1233" s="5" t="s">
-        <v>7846</v>
+        <v>7847</v>
       </c>
       <c r="C1233" s="5" t="s">
-        <v>7847</v>
+        <v>7848</v>
       </c>
       <c r="D1233" s="5" t="s">
-        <v>7848</v>
+        <v>7849</v>
       </c>
       <c r="E1233" s="5" t="s">
+        <v>7850</v>
+      </c>
+      <c r="F1233" s="5" t="s">
+        <v>7851</v>
+      </c>
+      <c r="G1233" s="5" t="s">
+        <v>7852</v>
+      </c>
+      <c r="H1233" s="5" t="s">
         <v>7849</v>
-      </c>
-      <c r="F1233" s="5" t="s">
-        <v>7850</v>
-      </c>
-      <c r="G1233" s="5" t="s">
-        <v>7851</v>
-      </c>
-      <c r="H1233" s="5" t="s">
-        <v>7852</v>
       </c>
     </row>
     <row r="1234">
@@ -57589,154 +57631,154 @@
         <v>7874</v>
       </c>
       <c r="C1237" s="5" t="s">
-        <v>5444</v>
+        <v>7875</v>
       </c>
       <c r="D1237" s="5" t="s">
-        <v>7875</v>
+        <v>7876</v>
       </c>
       <c r="E1237" s="5" t="s">
-        <v>5446</v>
+        <v>7877</v>
       </c>
       <c r="F1237" s="5" t="s">
-        <v>7876</v>
+        <v>7878</v>
       </c>
       <c r="G1237" s="5" t="s">
-        <v>7877</v>
+        <v>7879</v>
       </c>
       <c r="H1237" s="5" t="s">
-        <v>7878</v>
+        <v>7880</v>
       </c>
     </row>
     <row r="1238">
       <c r="B1238" s="6" t="s">
-        <v>7879</v>
+        <v>7881</v>
       </c>
       <c r="C1238" s="6" t="s">
-        <v>5437</v>
+        <v>7882</v>
       </c>
       <c r="D1238" s="6" t="s">
-        <v>7880</v>
+        <v>7883</v>
       </c>
       <c r="E1238" s="6" t="s">
-        <v>5439</v>
+        <v>7884</v>
       </c>
       <c r="F1238" s="6" t="s">
-        <v>7881</v>
+        <v>7885</v>
       </c>
       <c r="G1238" s="6" t="s">
-        <v>7882</v>
+        <v>7886</v>
       </c>
       <c r="H1238" s="6" t="s">
-        <v>7883</v>
+        <v>7887</v>
       </c>
     </row>
     <row r="1239">
       <c r="B1239" s="5" t="s">
-        <v>7884</v>
+        <v>7888</v>
       </c>
       <c r="C1239" s="5" t="s">
-        <v>7885</v>
+        <v>5444</v>
       </c>
       <c r="D1239" s="5" t="s">
-        <v>7886</v>
+        <v>7889</v>
       </c>
       <c r="E1239" s="5" t="s">
-        <v>7887</v>
+        <v>5446</v>
       </c>
       <c r="F1239" s="5" t="s">
-        <v>7888</v>
+        <v>7890</v>
       </c>
       <c r="G1239" s="5" t="s">
-        <v>7887</v>
+        <v>7891</v>
       </c>
       <c r="H1239" s="5" t="s">
-        <v>7260</v>
+        <v>7892</v>
       </c>
     </row>
     <row r="1240">
       <c r="B1240" s="6" t="s">
-        <v>7889</v>
+        <v>7893</v>
       </c>
       <c r="C1240" s="6" t="s">
-        <v>7890</v>
+        <v>5437</v>
       </c>
       <c r="D1240" s="6" t="s">
-        <v>7891</v>
+        <v>7894</v>
       </c>
       <c r="E1240" s="6" t="s">
-        <v>7892</v>
+        <v>5439</v>
       </c>
       <c r="F1240" s="6" t="s">
-        <v>7893</v>
+        <v>7895</v>
       </c>
       <c r="G1240" s="6" t="s">
-        <v>7894</v>
+        <v>7896</v>
       </c>
       <c r="H1240" s="6" t="s">
-        <v>7895</v>
+        <v>7897</v>
       </c>
     </row>
     <row r="1241">
       <c r="B1241" s="5" t="s">
-        <v>7896</v>
+        <v>7898</v>
       </c>
       <c r="C1241" s="5" t="s">
-        <v>7897</v>
+        <v>7899</v>
       </c>
       <c r="D1241" s="5" t="s">
-        <v>7898</v>
+        <v>7900</v>
       </c>
       <c r="E1241" s="5" t="s">
-        <v>7899</v>
+        <v>7901</v>
       </c>
       <c r="F1241" s="5" t="s">
-        <v>7900</v>
+        <v>7902</v>
       </c>
       <c r="G1241" s="5" t="s">
-        <v>7900</v>
+        <v>7901</v>
       </c>
       <c r="H1241" s="5" t="s">
-        <v>7901</v>
+        <v>7260</v>
       </c>
     </row>
     <row r="1242">
       <c r="B1242" s="6" t="s">
-        <v>7902</v>
+        <v>7903</v>
       </c>
       <c r="C1242" s="6" t="s">
-        <v>7903</v>
+        <v>7904</v>
       </c>
       <c r="D1242" s="6" t="s">
-        <v>7904</v>
+        <v>7905</v>
       </c>
       <c r="E1242" s="6" t="s">
-        <v>7905</v>
+        <v>7906</v>
       </c>
       <c r="F1242" s="6" t="s">
-        <v>7906</v>
+        <v>7907</v>
       </c>
       <c r="G1242" s="6" t="s">
-        <v>7907</v>
+        <v>7908</v>
       </c>
       <c r="H1242" s="6" t="s">
-        <v>7908</v>
+        <v>7909</v>
       </c>
     </row>
     <row r="1243">
       <c r="B1243" s="5" t="s">
-        <v>7909</v>
+        <v>7910</v>
       </c>
       <c r="C1243" s="5" t="s">
-        <v>7910</v>
+        <v>7911</v>
       </c>
       <c r="D1243" s="5" t="s">
-        <v>7911</v>
+        <v>7912</v>
       </c>
       <c r="E1243" s="5" t="s">
-        <v>7912</v>
+        <v>7913</v>
       </c>
       <c r="F1243" s="5" t="s">
-        <v>7913</v>
+        <v>7914</v>
       </c>
       <c r="G1243" s="5" t="s">
         <v>7914</v>
@@ -57828,53 +57870,53 @@
         <v>7940</v>
       </c>
       <c r="F1247" s="5" t="s">
-        <v>7940</v>
+        <v>7941</v>
       </c>
       <c r="G1247" s="5" t="s">
-        <v>7940</v>
+        <v>7942</v>
       </c>
       <c r="H1247" s="5" t="s">
-        <v>7941</v>
+        <v>7943</v>
       </c>
     </row>
     <row r="1248">
       <c r="B1248" s="6" t="s">
-        <v>7942</v>
+        <v>7944</v>
       </c>
       <c r="C1248" s="6" t="s">
-        <v>7943</v>
+        <v>7945</v>
       </c>
       <c r="D1248" s="6" t="s">
-        <v>7944</v>
+        <v>7946</v>
       </c>
       <c r="E1248" s="6" t="s">
-        <v>7945</v>
+        <v>7947</v>
       </c>
       <c r="F1248" s="6" t="s">
-        <v>7946</v>
+        <v>7948</v>
       </c>
       <c r="G1248" s="6" t="s">
-        <v>7947</v>
+        <v>7949</v>
       </c>
       <c r="H1248" s="6" t="s">
-        <v>7948</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="1249">
       <c r="B1249" s="5" t="s">
-        <v>7949</v>
+        <v>7951</v>
       </c>
       <c r="C1249" s="5" t="s">
-        <v>7950</v>
+        <v>7952</v>
       </c>
       <c r="D1249" s="5" t="s">
-        <v>7951</v>
+        <v>7953</v>
       </c>
       <c r="E1249" s="5" t="s">
-        <v>7952</v>
+        <v>7954</v>
       </c>
       <c r="F1249" s="5" t="s">
-        <v>7953</v>
+        <v>7954</v>
       </c>
       <c r="G1249" s="5" t="s">
         <v>7954</v>
@@ -57923,96 +57965,96 @@
         <v>7967</v>
       </c>
       <c r="G1251" s="5" t="s">
-        <v>7967</v>
+        <v>7968</v>
       </c>
       <c r="H1251" s="5" t="s">
-        <v>7968</v>
+        <v>7969</v>
       </c>
     </row>
     <row r="1252">
       <c r="B1252" s="6" t="s">
-        <v>7969</v>
+        <v>7970</v>
       </c>
       <c r="C1252" s="6" t="s">
-        <v>7970</v>
+        <v>7971</v>
       </c>
       <c r="D1252" s="6" t="s">
-        <v>7971</v>
+        <v>7972</v>
       </c>
       <c r="E1252" s="6" t="s">
-        <v>7972</v>
+        <v>7973</v>
       </c>
       <c r="F1252" s="6" t="s">
-        <v>7973</v>
+        <v>7974</v>
       </c>
       <c r="G1252" s="6" t="s">
-        <v>7973</v>
+        <v>7975</v>
       </c>
       <c r="H1252" s="6" t="s">
-        <v>7974</v>
+        <v>7976</v>
       </c>
     </row>
     <row r="1253">
       <c r="B1253" s="5" t="s">
-        <v>7975</v>
+        <v>7977</v>
       </c>
       <c r="C1253" s="5" t="s">
-        <v>7976</v>
+        <v>7978</v>
       </c>
       <c r="D1253" s="5" t="s">
-        <v>7977</v>
+        <v>7979</v>
       </c>
       <c r="E1253" s="5" t="s">
-        <v>7978</v>
+        <v>7980</v>
       </c>
       <c r="F1253" s="5" t="s">
-        <v>7979</v>
+        <v>7981</v>
       </c>
       <c r="G1253" s="5" t="s">
-        <v>7979</v>
+        <v>7981</v>
       </c>
       <c r="H1253" s="5" t="s">
-        <v>7980</v>
+        <v>7982</v>
       </c>
     </row>
     <row r="1254">
       <c r="B1254" s="6" t="s">
-        <v>7981</v>
+        <v>7983</v>
       </c>
       <c r="C1254" s="6" t="s">
-        <v>7982</v>
+        <v>7984</v>
       </c>
       <c r="D1254" s="6" t="s">
-        <v>7983</v>
+        <v>7985</v>
       </c>
       <c r="E1254" s="6" t="s">
-        <v>7984</v>
+        <v>7986</v>
       </c>
       <c r="F1254" s="6" t="s">
-        <v>7985</v>
+        <v>7987</v>
       </c>
       <c r="G1254" s="6" t="s">
-        <v>7986</v>
+        <v>7987</v>
       </c>
       <c r="H1254" s="6" t="s">
-        <v>7987</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="1255">
       <c r="B1255" s="5" t="s">
-        <v>7988</v>
+        <v>7989</v>
       </c>
       <c r="C1255" s="5" t="s">
-        <v>7989</v>
+        <v>7990</v>
       </c>
       <c r="D1255" s="5" t="s">
-        <v>7990</v>
+        <v>7991</v>
       </c>
       <c r="E1255" s="5" t="s">
-        <v>7991</v>
+        <v>7992</v>
       </c>
       <c r="F1255" s="5" t="s">
-        <v>7992</v>
+        <v>7993</v>
       </c>
       <c r="G1255" s="5" t="s">
         <v>7993</v>
@@ -58107,102 +58149,102 @@
         <v>8020</v>
       </c>
       <c r="G1259" s="5" t="s">
-        <v>8020</v>
+        <v>8021</v>
       </c>
       <c r="H1259" s="5" t="s">
-        <v>8021</v>
+        <v>8022</v>
       </c>
     </row>
     <row r="1260">
       <c r="B1260" s="6" t="s">
-        <v>8022</v>
+        <v>8023</v>
       </c>
       <c r="C1260" s="6" t="s">
-        <v>8023</v>
+        <v>8024</v>
       </c>
       <c r="D1260" s="6" t="s">
-        <v>8024</v>
+        <v>8025</v>
       </c>
       <c r="E1260" s="6" t="s">
-        <v>8025</v>
+        <v>8026</v>
       </c>
       <c r="F1260" s="6" t="s">
-        <v>8026</v>
+        <v>8027</v>
       </c>
       <c r="G1260" s="6" t="s">
-        <v>8027</v>
+        <v>8028</v>
       </c>
       <c r="H1260" s="6" t="s">
-        <v>6881</v>
+        <v>8029</v>
       </c>
     </row>
     <row r="1261">
       <c r="B1261" s="5" t="s">
-        <v>8028</v>
+        <v>8030</v>
       </c>
       <c r="C1261" s="5" t="s">
-        <v>8029</v>
+        <v>8031</v>
       </c>
       <c r="D1261" s="5" t="s">
-        <v>8030</v>
+        <v>8032</v>
       </c>
       <c r="E1261" s="5" t="s">
-        <v>8031</v>
+        <v>8033</v>
       </c>
       <c r="F1261" s="5" t="s">
-        <v>8032</v>
+        <v>8034</v>
       </c>
       <c r="G1261" s="5" t="s">
-        <v>8033</v>
+        <v>8034</v>
       </c>
       <c r="H1261" s="5" t="s">
-        <v>7797</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="1262">
       <c r="B1262" s="6" t="s">
-        <v>8034</v>
+        <v>8036</v>
       </c>
       <c r="C1262" s="6" t="s">
-        <v>8035</v>
+        <v>8037</v>
       </c>
       <c r="D1262" s="6" t="s">
-        <v>8036</v>
+        <v>8038</v>
       </c>
       <c r="E1262" s="6" t="s">
-        <v>8037</v>
+        <v>8039</v>
       </c>
       <c r="F1262" s="6" t="s">
-        <v>8038</v>
+        <v>8040</v>
       </c>
       <c r="G1262" s="6" t="s">
-        <v>8039</v>
+        <v>8041</v>
       </c>
       <c r="H1262" s="6" t="s">
-        <v>8040</v>
+        <v>6881</v>
       </c>
     </row>
     <row r="1263">
       <c r="B1263" s="5" t="s">
-        <v>8041</v>
+        <v>8042</v>
       </c>
       <c r="C1263" s="5" t="s">
-        <v>8042</v>
+        <v>8043</v>
       </c>
       <c r="D1263" s="5" t="s">
-        <v>8043</v>
+        <v>8044</v>
       </c>
       <c r="E1263" s="5" t="s">
-        <v>8044</v>
+        <v>8045</v>
       </c>
       <c r="F1263" s="5" t="s">
-        <v>8045</v>
+        <v>8046</v>
       </c>
       <c r="G1263" s="5" t="s">
-        <v>8046</v>
+        <v>8047</v>
       </c>
       <c r="H1263" s="5" t="s">
-        <v>8047</v>
+        <v>7811</v>
       </c>
     </row>
     <row r="1264">
@@ -58219,59 +58261,59 @@
         <v>8051</v>
       </c>
       <c r="F1264" s="6" t="s">
-        <v>8051</v>
+        <v>8052</v>
       </c>
       <c r="G1264" s="6" t="s">
-        <v>8051</v>
+        <v>8053</v>
       </c>
       <c r="H1264" s="6" t="s">
-        <v>8050</v>
+        <v>8054</v>
       </c>
     </row>
     <row r="1265">
       <c r="B1265" s="5" t="s">
-        <v>8052</v>
+        <v>8055</v>
       </c>
       <c r="C1265" s="5" t="s">
-        <v>8053</v>
+        <v>8056</v>
       </c>
       <c r="D1265" s="5" t="s">
-        <v>8054</v>
+        <v>8057</v>
       </c>
       <c r="E1265" s="5" t="s">
-        <v>8055</v>
+        <v>8058</v>
       </c>
       <c r="F1265" s="5" t="s">
-        <v>8056</v>
+        <v>8059</v>
       </c>
       <c r="G1265" s="5" t="s">
-        <v>8057</v>
+        <v>8060</v>
       </c>
       <c r="H1265" s="5" t="s">
-        <v>8058</v>
+        <v>8061</v>
       </c>
     </row>
     <row r="1266">
       <c r="B1266" s="6" t="s">
-        <v>8059</v>
+        <v>8062</v>
       </c>
       <c r="C1266" s="6" t="s">
-        <v>8060</v>
+        <v>8063</v>
       </c>
       <c r="D1266" s="6" t="s">
-        <v>8061</v>
+        <v>8064</v>
       </c>
       <c r="E1266" s="6" t="s">
-        <v>8062</v>
+        <v>8065</v>
       </c>
       <c r="F1266" s="6" t="s">
-        <v>8063</v>
+        <v>8065</v>
       </c>
       <c r="G1266" s="6" t="s">
+        <v>8065</v>
+      </c>
+      <c r="H1266" s="6" t="s">
         <v>8064</v>
-      </c>
-      <c r="H1266" s="6" t="s">
-        <v>8065</v>
       </c>
     </row>
     <row r="1267">
@@ -58305,111 +58347,111 @@
         <v>8074</v>
       </c>
       <c r="D1268" s="6" t="s">
-        <v>8050</v>
+        <v>8075</v>
       </c>
       <c r="E1268" s="6" t="s">
-        <v>8075</v>
+        <v>8076</v>
       </c>
       <c r="F1268" s="6" t="s">
-        <v>8076</v>
+        <v>8077</v>
       </c>
       <c r="G1268" s="6" t="s">
-        <v>8076</v>
+        <v>8078</v>
       </c>
       <c r="H1268" s="6" t="s">
-        <v>8050</v>
+        <v>8079</v>
       </c>
     </row>
     <row r="1269">
       <c r="B1269" s="5" t="s">
-        <v>8077</v>
+        <v>8080</v>
       </c>
       <c r="C1269" s="5" t="s">
-        <v>8078</v>
+        <v>8081</v>
       </c>
       <c r="D1269" s="5" t="s">
-        <v>8079</v>
+        <v>8082</v>
       </c>
       <c r="E1269" s="5" t="s">
-        <v>8080</v>
+        <v>8083</v>
       </c>
       <c r="F1269" s="5" t="s">
-        <v>8081</v>
+        <v>8084</v>
       </c>
       <c r="G1269" s="5" t="s">
-        <v>8082</v>
+        <v>8085</v>
       </c>
       <c r="H1269" s="5" t="s">
-        <v>8083</v>
+        <v>8086</v>
       </c>
     </row>
     <row r="1270">
       <c r="B1270" s="6" t="s">
-        <v>8084</v>
+        <v>8087</v>
       </c>
       <c r="C1270" s="6" t="s">
-        <v>8085</v>
+        <v>8088</v>
       </c>
       <c r="D1270" s="6" t="s">
-        <v>8086</v>
+        <v>8064</v>
       </c>
       <c r="E1270" s="6" t="s">
-        <v>8087</v>
+        <v>8089</v>
       </c>
       <c r="F1270" s="6" t="s">
-        <v>8088</v>
+        <v>8090</v>
       </c>
       <c r="G1270" s="6" t="s">
-        <v>8089</v>
+        <v>8090</v>
       </c>
       <c r="H1270" s="6" t="s">
-        <v>8086</v>
+        <v>8064</v>
       </c>
     </row>
     <row r="1271">
       <c r="B1271" s="5" t="s">
-        <v>8090</v>
+        <v>8091</v>
       </c>
       <c r="C1271" s="5" t="s">
-        <v>8091</v>
+        <v>8092</v>
       </c>
       <c r="D1271" s="5" t="s">
-        <v>8092</v>
+        <v>8093</v>
       </c>
       <c r="E1271" s="5" t="s">
-        <v>8093</v>
+        <v>8094</v>
       </c>
       <c r="F1271" s="5" t="s">
-        <v>8094</v>
+        <v>8095</v>
       </c>
       <c r="G1271" s="5" t="s">
-        <v>8095</v>
+        <v>8096</v>
       </c>
       <c r="H1271" s="5" t="s">
-        <v>8096</v>
+        <v>8097</v>
       </c>
     </row>
     <row r="1272">
       <c r="B1272" s="6" t="s">
-        <v>8097</v>
+        <v>8098</v>
       </c>
       <c r="C1272" s="6" t="s">
-        <v>8098</v>
+        <v>8099</v>
       </c>
       <c r="D1272" s="6" t="s">
-        <v>8099</v>
+        <v>8100</v>
       </c>
       <c r="E1272" s="6" t="s">
+        <v>8101</v>
+      </c>
+      <c r="F1272" s="6" t="s">
+        <v>8102</v>
+      </c>
+      <c r="G1272" s="6" t="s">
+        <v>8103</v>
+      </c>
+      <c r="H1272" s="6" t="s">
         <v>8100</v>
-      </c>
-      <c r="F1272" s="6" t="s">
-        <v>8101</v>
-      </c>
-      <c r="G1272" s="6" t="s">
-        <v>8102</v>
-      </c>
-      <c r="H1272" s="6" t="s">
-        <v>8103</v>
       </c>
     </row>
     <row r="1273">
@@ -58475,96 +58517,96 @@
         <v>8122</v>
       </c>
       <c r="G1275" s="5" t="s">
-        <v>8122</v>
+        <v>8123</v>
       </c>
       <c r="H1275" s="5" t="s">
-        <v>8123</v>
+        <v>8124</v>
       </c>
     </row>
     <row r="1276">
       <c r="B1276" s="6" t="s">
-        <v>8124</v>
+        <v>8125</v>
       </c>
       <c r="C1276" s="6" t="s">
-        <v>8125</v>
+        <v>8126</v>
       </c>
       <c r="D1276" s="6" t="s">
-        <v>8126</v>
+        <v>8127</v>
       </c>
       <c r="E1276" s="6" t="s">
-        <v>8127</v>
+        <v>8128</v>
       </c>
       <c r="F1276" s="6" t="s">
-        <v>8128</v>
+        <v>8129</v>
       </c>
       <c r="G1276" s="6" t="s">
-        <v>8129</v>
+        <v>8130</v>
       </c>
       <c r="H1276" s="6" t="s">
-        <v>8130</v>
+        <v>8131</v>
       </c>
     </row>
     <row r="1277">
       <c r="B1277" s="5" t="s">
-        <v>8131</v>
+        <v>8132</v>
       </c>
       <c r="C1277" s="5" t="s">
-        <v>8132</v>
+        <v>8133</v>
       </c>
       <c r="D1277" s="5" t="s">
-        <v>8133</v>
+        <v>8134</v>
       </c>
       <c r="E1277" s="5" t="s">
-        <v>8134</v>
+        <v>8135</v>
       </c>
       <c r="F1277" s="5" t="s">
-        <v>8135</v>
+        <v>8136</v>
       </c>
       <c r="G1277" s="5" t="s">
-        <v>8135</v>
+        <v>8136</v>
       </c>
       <c r="H1277" s="5" t="s">
-        <v>8136</v>
+        <v>8137</v>
       </c>
     </row>
     <row r="1278">
       <c r="B1278" s="6" t="s">
-        <v>8137</v>
+        <v>8138</v>
       </c>
       <c r="C1278" s="6" t="s">
-        <v>8138</v>
+        <v>8139</v>
       </c>
       <c r="D1278" s="6" t="s">
-        <v>8139</v>
+        <v>8140</v>
       </c>
       <c r="E1278" s="6" t="s">
-        <v>8140</v>
+        <v>8141</v>
       </c>
       <c r="F1278" s="6" t="s">
-        <v>8141</v>
+        <v>8142</v>
       </c>
       <c r="G1278" s="6" t="s">
-        <v>8142</v>
+        <v>8143</v>
       </c>
       <c r="H1278" s="6" t="s">
-        <v>8143</v>
+        <v>8144</v>
       </c>
     </row>
     <row r="1279">
       <c r="B1279" s="5" t="s">
-        <v>8144</v>
+        <v>8145</v>
       </c>
       <c r="C1279" s="5" t="s">
-        <v>8145</v>
+        <v>8146</v>
       </c>
       <c r="D1279" s="5" t="s">
-        <v>8146</v>
+        <v>8147</v>
       </c>
       <c r="E1279" s="5" t="s">
-        <v>8147</v>
+        <v>8148</v>
       </c>
       <c r="F1279" s="5" t="s">
-        <v>8148</v>
+        <v>8149</v>
       </c>
       <c r="G1279" s="5" t="s">
         <v>8149</v>
@@ -58590,470 +58632,470 @@
         <v>8155</v>
       </c>
       <c r="G1280" s="6" t="s">
-        <v>8154</v>
+        <v>8156</v>
       </c>
       <c r="H1280" s="6" t="s">
-        <v>8156</v>
+        <v>8157</v>
       </c>
     </row>
     <row r="1281">
       <c r="B1281" s="5" t="s">
-        <v>8157</v>
+        <v>8158</v>
       </c>
       <c r="C1281" s="5" t="s">
-        <v>8158</v>
+        <v>8159</v>
       </c>
       <c r="D1281" s="5" t="s">
-        <v>8159</v>
+        <v>8160</v>
       </c>
       <c r="E1281" s="5" t="s">
-        <v>8160</v>
+        <v>8161</v>
       </c>
       <c r="F1281" s="5" t="s">
-        <v>8161</v>
+        <v>8162</v>
       </c>
       <c r="G1281" s="5" t="s">
-        <v>8161</v>
+        <v>8163</v>
       </c>
       <c r="H1281" s="5" t="s">
-        <v>8159</v>
+        <v>8164</v>
       </c>
     </row>
     <row r="1282">
       <c r="B1282" s="6" t="s">
-        <v>8162</v>
+        <v>8165</v>
       </c>
       <c r="C1282" s="6" t="s">
-        <v>8163</v>
+        <v>8166</v>
       </c>
       <c r="D1282" s="6" t="s">
-        <v>8164</v>
+        <v>8167</v>
       </c>
       <c r="E1282" s="6" t="s">
-        <v>8165</v>
+        <v>8168</v>
       </c>
       <c r="F1282" s="6" t="s">
-        <v>8166</v>
+        <v>8169</v>
       </c>
       <c r="G1282" s="6" t="s">
-        <v>8167</v>
+        <v>8168</v>
       </c>
       <c r="H1282" s="6" t="s">
-        <v>8168</v>
+        <v>8170</v>
       </c>
     </row>
     <row r="1283">
       <c r="B1283" s="5" t="s">
-        <v>8169</v>
+        <v>8171</v>
       </c>
       <c r="C1283" s="5" t="s">
-        <v>8170</v>
+        <v>8172</v>
       </c>
       <c r="D1283" s="5" t="s">
-        <v>8171</v>
+        <v>8173</v>
       </c>
       <c r="E1283" s="5" t="s">
-        <v>8172</v>
+        <v>8174</v>
       </c>
       <c r="F1283" s="5" t="s">
+        <v>8175</v>
+      </c>
+      <c r="G1283" s="5" t="s">
+        <v>8175</v>
+      </c>
+      <c r="H1283" s="5" t="s">
         <v>8173</v>
-      </c>
-      <c r="G1283" s="5" t="s">
-        <v>8174</v>
-      </c>
-      <c r="H1283" s="5" t="s">
-        <v>8171</v>
       </c>
     </row>
     <row r="1284">
       <c r="B1284" s="6" t="s">
-        <v>8175</v>
+        <v>8176</v>
       </c>
       <c r="C1284" s="6" t="s">
-        <v>8176</v>
+        <v>8177</v>
       </c>
       <c r="D1284" s="6" t="s">
-        <v>8177</v>
+        <v>8178</v>
       </c>
       <c r="E1284" s="6" t="s">
-        <v>8178</v>
+        <v>8179</v>
       </c>
       <c r="F1284" s="6" t="s">
-        <v>8179</v>
+        <v>8180</v>
       </c>
       <c r="G1284" s="6" t="s">
-        <v>8180</v>
+        <v>8181</v>
       </c>
       <c r="H1284" s="6" t="s">
-        <v>8181</v>
+        <v>8182</v>
       </c>
     </row>
     <row r="1285">
       <c r="B1285" s="5" t="s">
-        <v>8182</v>
+        <v>8183</v>
       </c>
       <c r="C1285" s="5" t="s">
-        <v>8183</v>
+        <v>8184</v>
       </c>
       <c r="D1285" s="5" t="s">
-        <v>8184</v>
+        <v>8185</v>
       </c>
       <c r="E1285" s="5" t="s">
+        <v>8186</v>
+      </c>
+      <c r="F1285" s="5" t="s">
+        <v>8187</v>
+      </c>
+      <c r="G1285" s="5" t="s">
+        <v>8188</v>
+      </c>
+      <c r="H1285" s="5" t="s">
         <v>8185</v>
-      </c>
-      <c r="F1285" s="5" t="s">
-        <v>8186</v>
-      </c>
-      <c r="G1285" s="5" t="s">
-        <v>8186</v>
-      </c>
-      <c r="H1285" s="5" t="s">
-        <v>8187</v>
       </c>
     </row>
     <row r="1286">
       <c r="B1286" s="6" t="s">
-        <v>8188</v>
+        <v>8189</v>
       </c>
       <c r="C1286" s="6" t="s">
-        <v>8189</v>
+        <v>8190</v>
       </c>
       <c r="D1286" s="6" t="s">
-        <v>8190</v>
+        <v>8191</v>
       </c>
       <c r="E1286" s="6" t="s">
-        <v>8191</v>
+        <v>8192</v>
       </c>
       <c r="F1286" s="6" t="s">
-        <v>8192</v>
+        <v>8193</v>
       </c>
       <c r="G1286" s="6" t="s">
-        <v>8192</v>
+        <v>8194</v>
       </c>
       <c r="H1286" s="6" t="s">
-        <v>8193</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="1287">
       <c r="B1287" s="5" t="s">
-        <v>8194</v>
+        <v>8196</v>
       </c>
       <c r="C1287" s="5" t="s">
-        <v>8195</v>
+        <v>8197</v>
       </c>
       <c r="D1287" s="5" t="s">
-        <v>8196</v>
+        <v>8198</v>
       </c>
       <c r="E1287" s="5" t="s">
-        <v>8197</v>
+        <v>8199</v>
       </c>
       <c r="F1287" s="5" t="s">
-        <v>8198</v>
+        <v>8200</v>
       </c>
       <c r="G1287" s="5" t="s">
-        <v>8199</v>
+        <v>8200</v>
       </c>
       <c r="H1287" s="5" t="s">
-        <v>8200</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="1288">
       <c r="B1288" s="6" t="s">
-        <v>8201</v>
+        <v>8202</v>
       </c>
       <c r="C1288" s="6" t="s">
-        <v>8202</v>
+        <v>8203</v>
       </c>
       <c r="D1288" s="6" t="s">
-        <v>8203</v>
+        <v>8204</v>
       </c>
       <c r="E1288" s="6" t="s">
-        <v>8204</v>
+        <v>8205</v>
       </c>
       <c r="F1288" s="6" t="s">
-        <v>8205</v>
+        <v>8206</v>
       </c>
       <c r="G1288" s="6" t="s">
-        <v>8205</v>
+        <v>8206</v>
       </c>
       <c r="H1288" s="6" t="s">
-        <v>8206</v>
+        <v>8207</v>
       </c>
     </row>
     <row r="1289">
       <c r="B1289" s="5" t="s">
-        <v>8207</v>
+        <v>8208</v>
       </c>
       <c r="C1289" s="5" t="s">
-        <v>8208</v>
+        <v>8209</v>
       </c>
       <c r="D1289" s="5" t="s">
-        <v>8209</v>
+        <v>8210</v>
       </c>
       <c r="E1289" s="5" t="s">
-        <v>8210</v>
+        <v>8211</v>
       </c>
       <c r="F1289" s="5" t="s">
-        <v>8211</v>
+        <v>8212</v>
       </c>
       <c r="G1289" s="5" t="s">
-        <v>8212</v>
+        <v>8213</v>
       </c>
       <c r="H1289" s="5" t="s">
-        <v>8213</v>
+        <v>8214</v>
       </c>
     </row>
     <row r="1290">
       <c r="B1290" s="6" t="s">
-        <v>8214</v>
+        <v>8215</v>
       </c>
       <c r="C1290" s="6" t="s">
-        <v>8215</v>
+        <v>8216</v>
       </c>
       <c r="D1290" s="6" t="s">
-        <v>8216</v>
+        <v>8217</v>
       </c>
       <c r="E1290" s="6" t="s">
-        <v>8217</v>
+        <v>8218</v>
       </c>
       <c r="F1290" s="6" t="s">
-        <v>8218</v>
+        <v>8219</v>
       </c>
       <c r="G1290" s="6" t="s">
-        <v>8218</v>
+        <v>8219</v>
       </c>
       <c r="H1290" s="6" t="s">
-        <v>8219</v>
+        <v>8220</v>
       </c>
     </row>
     <row r="1291">
       <c r="B1291" s="5" t="s">
-        <v>8220</v>
+        <v>8221</v>
       </c>
       <c r="C1291" s="5" t="s">
-        <v>8221</v>
+        <v>8222</v>
       </c>
       <c r="D1291" s="5" t="s">
-        <v>8222</v>
+        <v>8223</v>
       </c>
       <c r="E1291" s="5" t="s">
-        <v>8223</v>
+        <v>8224</v>
       </c>
       <c r="F1291" s="5" t="s">
-        <v>8224</v>
+        <v>8225</v>
       </c>
       <c r="G1291" s="5" t="s">
-        <v>8224</v>
+        <v>8226</v>
       </c>
       <c r="H1291" s="5" t="s">
-        <v>8225</v>
+        <v>8227</v>
       </c>
     </row>
     <row r="1292">
       <c r="B1292" s="6" t="s">
-        <v>8226</v>
+        <v>8228</v>
       </c>
       <c r="C1292" s="6" t="s">
-        <v>8227</v>
+        <v>8229</v>
       </c>
       <c r="D1292" s="6" t="s">
-        <v>8227</v>
+        <v>8230</v>
       </c>
       <c r="E1292" s="6" t="s">
-        <v>8227</v>
+        <v>8231</v>
       </c>
       <c r="F1292" s="6" t="s">
-        <v>8227</v>
+        <v>8232</v>
       </c>
       <c r="G1292" s="6" t="s">
-        <v>8227</v>
+        <v>8232</v>
       </c>
       <c r="H1292" s="6" t="s">
-        <v>8227</v>
+        <v>8233</v>
       </c>
     </row>
     <row r="1293">
       <c r="B1293" s="5" t="s">
-        <v>8228</v>
+        <v>8234</v>
       </c>
       <c r="C1293" s="5" t="s">
-        <v>8229</v>
+        <v>8235</v>
       </c>
       <c r="D1293" s="5" t="s">
-        <v>8230</v>
+        <v>8236</v>
       </c>
       <c r="E1293" s="5" t="s">
-        <v>8231</v>
+        <v>8237</v>
       </c>
       <c r="F1293" s="5" t="s">
-        <v>8232</v>
+        <v>8238</v>
       </c>
       <c r="G1293" s="5" t="s">
-        <v>8232</v>
+        <v>8238</v>
       </c>
       <c r="H1293" s="5" t="s">
-        <v>8230</v>
+        <v>8239</v>
       </c>
     </row>
     <row r="1294">
       <c r="B1294" s="6" t="s">
-        <v>8233</v>
+        <v>8240</v>
       </c>
       <c r="C1294" s="6" t="s">
-        <v>8234</v>
+        <v>8241</v>
       </c>
       <c r="D1294" s="6" t="s">
-        <v>8235</v>
+        <v>8241</v>
       </c>
       <c r="E1294" s="6" t="s">
-        <v>8236</v>
+        <v>8241</v>
       </c>
       <c r="F1294" s="6" t="s">
-        <v>8237</v>
+        <v>8241</v>
       </c>
       <c r="G1294" s="6" t="s">
-        <v>8238</v>
+        <v>8241</v>
       </c>
       <c r="H1294" s="6" t="s">
-        <v>8235</v>
+        <v>8241</v>
       </c>
     </row>
     <row r="1295">
       <c r="B1295" s="5" t="s">
-        <v>8239</v>
+        <v>8242</v>
       </c>
       <c r="C1295" s="5" t="s">
-        <v>8240</v>
+        <v>8243</v>
       </c>
       <c r="D1295" s="5" t="s">
-        <v>8241</v>
+        <v>8244</v>
       </c>
       <c r="E1295" s="5" t="s">
-        <v>8242</v>
+        <v>8245</v>
       </c>
       <c r="F1295" s="5" t="s">
-        <v>8242</v>
+        <v>8246</v>
       </c>
       <c r="G1295" s="5" t="s">
-        <v>8242</v>
+        <v>8246</v>
       </c>
       <c r="H1295" s="5" t="s">
-        <v>8241</v>
+        <v>8244</v>
       </c>
     </row>
     <row r="1296">
       <c r="B1296" s="6" t="s">
-        <v>8243</v>
+        <v>8247</v>
       </c>
       <c r="C1296" s="6" t="s">
-        <v>8244</v>
+        <v>8248</v>
       </c>
       <c r="D1296" s="6" t="s">
-        <v>8245</v>
+        <v>8249</v>
       </c>
       <c r="E1296" s="6" t="s">
-        <v>8246</v>
+        <v>8250</v>
       </c>
       <c r="F1296" s="6" t="s">
-        <v>8246</v>
+        <v>8251</v>
       </c>
       <c r="G1296" s="6" t="s">
-        <v>8246</v>
+        <v>8252</v>
       </c>
       <c r="H1296" s="6" t="s">
-        <v>8245</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="1297">
       <c r="B1297" s="5" t="s">
-        <v>8247</v>
+        <v>8253</v>
       </c>
       <c r="C1297" s="5" t="s">
-        <v>8248</v>
+        <v>8254</v>
       </c>
       <c r="D1297" s="5" t="s">
-        <v>8249</v>
+        <v>8255</v>
       </c>
       <c r="E1297" s="5" t="s">
-        <v>8250</v>
+        <v>8256</v>
       </c>
       <c r="F1297" s="5" t="s">
-        <v>8251</v>
+        <v>8256</v>
       </c>
       <c r="G1297" s="5" t="s">
-        <v>8252</v>
+        <v>8256</v>
       </c>
       <c r="H1297" s="5" t="s">
-        <v>8253</v>
+        <v>8255</v>
       </c>
     </row>
     <row r="1298">
       <c r="B1298" s="6" t="s">
-        <v>8254</v>
+        <v>8257</v>
       </c>
       <c r="C1298" s="6" t="s">
-        <v>8255</v>
+        <v>8258</v>
       </c>
       <c r="D1298" s="6" t="s">
-        <v>8256</v>
+        <v>8259</v>
       </c>
       <c r="E1298" s="6" t="s">
-        <v>8257</v>
+        <v>8260</v>
       </c>
       <c r="F1298" s="6" t="s">
-        <v>8258</v>
+        <v>8260</v>
       </c>
       <c r="G1298" s="6" t="s">
+        <v>8260</v>
+      </c>
+      <c r="H1298" s="6" t="s">
         <v>8259</v>
-      </c>
-      <c r="H1298" s="6" t="s">
-        <v>8256</v>
       </c>
     </row>
     <row r="1299">
       <c r="B1299" s="5" t="s">
-        <v>8260</v>
+        <v>8261</v>
       </c>
       <c r="C1299" s="5" t="s">
-        <v>8261</v>
+        <v>8262</v>
       </c>
       <c r="D1299" s="5" t="s">
-        <v>8262</v>
+        <v>8263</v>
       </c>
       <c r="E1299" s="5" t="s">
-        <v>8263</v>
+        <v>8264</v>
       </c>
       <c r="F1299" s="5" t="s">
-        <v>8264</v>
+        <v>8265</v>
       </c>
       <c r="G1299" s="5" t="s">
-        <v>8265</v>
+        <v>8266</v>
       </c>
       <c r="H1299" s="5" t="s">
-        <v>8266</v>
+        <v>8267</v>
       </c>
     </row>
     <row r="1300">
       <c r="B1300" s="6" t="s">
-        <v>8267</v>
+        <v>8268</v>
       </c>
       <c r="C1300" s="6" t="s">
-        <v>8268</v>
+        <v>8269</v>
       </c>
       <c r="D1300" s="6" t="s">
-        <v>8269</v>
+        <v>8270</v>
       </c>
       <c r="E1300" s="6" t="s">
+        <v>8271</v>
+      </c>
+      <c r="F1300" s="6" t="s">
+        <v>8272</v>
+      </c>
+      <c r="G1300" s="6" t="s">
+        <v>8273</v>
+      </c>
+      <c r="H1300" s="6" t="s">
         <v>8270</v>
-      </c>
-      <c r="F1300" s="6" t="s">
-        <v>8271</v>
-      </c>
-      <c r="G1300" s="6" t="s">
-        <v>8272</v>
-      </c>
-      <c r="H1300" s="6" t="s">
-        <v>8273</v>
       </c>
     </row>
     <row r="1301">
@@ -59099,93 +59141,93 @@
         <v>8286</v>
       </c>
       <c r="H1302" s="6" t="s">
-        <v>8256</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="1303">
       <c r="B1303" s="5" t="s">
-        <v>8287</v>
+        <v>8288</v>
       </c>
       <c r="C1303" s="5" t="s">
-        <v>8288</v>
+        <v>8289</v>
       </c>
       <c r="D1303" s="5" t="s">
-        <v>8289</v>
+        <v>8290</v>
       </c>
       <c r="E1303" s="5" t="s">
-        <v>8290</v>
+        <v>8291</v>
       </c>
       <c r="F1303" s="5" t="s">
-        <v>8291</v>
+        <v>8292</v>
       </c>
       <c r="G1303" s="5" t="s">
-        <v>8292</v>
+        <v>8293</v>
       </c>
       <c r="H1303" s="5" t="s">
-        <v>8293</v>
+        <v>8294</v>
       </c>
     </row>
     <row r="1304">
       <c r="B1304" s="6" t="s">
-        <v>8294</v>
+        <v>8295</v>
       </c>
       <c r="C1304" s="6" t="s">
-        <v>8295</v>
+        <v>8296</v>
       </c>
       <c r="D1304" s="6" t="s">
-        <v>8296</v>
+        <v>8297</v>
       </c>
       <c r="E1304" s="6" t="s">
-        <v>8297</v>
+        <v>8298</v>
       </c>
       <c r="F1304" s="6" t="s">
-        <v>8298</v>
+        <v>8299</v>
       </c>
       <c r="G1304" s="6" t="s">
-        <v>8298</v>
+        <v>8300</v>
       </c>
       <c r="H1304" s="6" t="s">
-        <v>8299</v>
+        <v>8270</v>
       </c>
     </row>
     <row r="1305">
       <c r="B1305" s="5" t="s">
-        <v>8300</v>
+        <v>8301</v>
       </c>
       <c r="C1305" s="5" t="s">
-        <v>8301</v>
+        <v>8302</v>
       </c>
       <c r="D1305" s="5" t="s">
-        <v>8302</v>
+        <v>8303</v>
       </c>
       <c r="E1305" s="5" t="s">
-        <v>8303</v>
+        <v>8304</v>
       </c>
       <c r="F1305" s="5" t="s">
-        <v>8304</v>
+        <v>8305</v>
       </c>
       <c r="G1305" s="5" t="s">
-        <v>8305</v>
+        <v>8306</v>
       </c>
       <c r="H1305" s="5" t="s">
-        <v>8306</v>
+        <v>8307</v>
       </c>
     </row>
     <row r="1306">
       <c r="B1306" s="6" t="s">
-        <v>8307</v>
+        <v>8308</v>
       </c>
       <c r="C1306" s="6" t="s">
-        <v>8308</v>
+        <v>8309</v>
       </c>
       <c r="D1306" s="6" t="s">
-        <v>8309</v>
+        <v>8310</v>
       </c>
       <c r="E1306" s="6" t="s">
-        <v>8310</v>
+        <v>8311</v>
       </c>
       <c r="F1306" s="6" t="s">
-        <v>8311</v>
+        <v>8312</v>
       </c>
       <c r="G1306" s="6" t="s">
         <v>8312</v>
@@ -59211,96 +59253,96 @@
         <v>8318</v>
       </c>
       <c r="G1307" s="5" t="s">
-        <v>8318</v>
+        <v>8319</v>
       </c>
       <c r="H1307" s="5" t="s">
-        <v>8319</v>
+        <v>8320</v>
       </c>
     </row>
     <row r="1308">
       <c r="B1308" s="6" t="s">
-        <v>8320</v>
+        <v>8321</v>
       </c>
       <c r="C1308" s="6" t="s">
-        <v>6033</v>
+        <v>8322</v>
       </c>
       <c r="D1308" s="6" t="s">
-        <v>6936</v>
+        <v>8323</v>
       </c>
       <c r="E1308" s="6" t="s">
-        <v>6035</v>
+        <v>8324</v>
       </c>
       <c r="F1308" s="6" t="s">
-        <v>8321</v>
+        <v>8325</v>
       </c>
       <c r="G1308" s="6" t="s">
-        <v>8321</v>
+        <v>8326</v>
       </c>
       <c r="H1308" s="6" t="s">
-        <v>5404</v>
+        <v>8327</v>
       </c>
     </row>
     <row r="1309">
       <c r="B1309" s="5" t="s">
-        <v>8322</v>
+        <v>8328</v>
       </c>
       <c r="C1309" s="5" t="s">
-        <v>8323</v>
+        <v>8329</v>
       </c>
       <c r="D1309" s="5" t="s">
-        <v>8324</v>
+        <v>8330</v>
       </c>
       <c r="E1309" s="5" t="s">
-        <v>8325</v>
+        <v>8331</v>
       </c>
       <c r="F1309" s="5" t="s">
-        <v>8326</v>
+        <v>8332</v>
       </c>
       <c r="G1309" s="5" t="s">
-        <v>8326</v>
+        <v>8332</v>
       </c>
       <c r="H1309" s="5" t="s">
-        <v>8327</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="1310">
       <c r="B1310" s="6" t="s">
-        <v>8328</v>
+        <v>8334</v>
       </c>
       <c r="C1310" s="6" t="s">
-        <v>8329</v>
+        <v>6033</v>
       </c>
       <c r="D1310" s="6" t="s">
-        <v>8330</v>
+        <v>6936</v>
       </c>
       <c r="E1310" s="6" t="s">
-        <v>8331</v>
+        <v>6035</v>
       </c>
       <c r="F1310" s="6" t="s">
-        <v>8332</v>
+        <v>8335</v>
       </c>
       <c r="G1310" s="6" t="s">
-        <v>8333</v>
+        <v>8335</v>
       </c>
       <c r="H1310" s="6" t="s">
-        <v>8334</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1311">
       <c r="B1311" s="5" t="s">
-        <v>8335</v>
+        <v>8336</v>
       </c>
       <c r="C1311" s="5" t="s">
-        <v>8336</v>
+        <v>8337</v>
       </c>
       <c r="D1311" s="5" t="s">
-        <v>8337</v>
+        <v>8338</v>
       </c>
       <c r="E1311" s="5" t="s">
-        <v>8338</v>
+        <v>8339</v>
       </c>
       <c r="F1311" s="5" t="s">
-        <v>8339</v>
+        <v>8340</v>
       </c>
       <c r="G1311" s="5" t="s">
         <v>8340</v>
@@ -59320,79 +59362,79 @@
         <v>8344</v>
       </c>
       <c r="E1312" s="6" t="s">
-        <v>8344</v>
+        <v>8345</v>
       </c>
       <c r="F1312" s="6" t="s">
-        <v>8344</v>
+        <v>8346</v>
       </c>
       <c r="G1312" s="6" t="s">
-        <v>8344</v>
+        <v>8347</v>
       </c>
       <c r="H1312" s="6" t="s">
-        <v>8344</v>
+        <v>8348</v>
       </c>
     </row>
     <row r="1313">
       <c r="B1313" s="5" t="s">
-        <v>8345</v>
+        <v>8349</v>
       </c>
       <c r="C1313" s="5" t="s">
-        <v>8346</v>
+        <v>8350</v>
       </c>
       <c r="D1313" s="5" t="s">
-        <v>8347</v>
+        <v>8351</v>
       </c>
       <c r="E1313" s="5" t="s">
-        <v>8348</v>
+        <v>8352</v>
       </c>
       <c r="F1313" s="5" t="s">
-        <v>8349</v>
+        <v>8353</v>
       </c>
       <c r="G1313" s="5" t="s">
-        <v>8349</v>
+        <v>8354</v>
       </c>
       <c r="H1313" s="5" t="s">
-        <v>8350</v>
+        <v>8355</v>
       </c>
     </row>
     <row r="1314">
       <c r="B1314" s="6" t="s">
-        <v>8351</v>
+        <v>8356</v>
       </c>
       <c r="C1314" s="6" t="s">
-        <v>8352</v>
+        <v>8357</v>
       </c>
       <c r="D1314" s="6" t="s">
-        <v>8353</v>
+        <v>8358</v>
       </c>
       <c r="E1314" s="6" t="s">
-        <v>8354</v>
+        <v>8358</v>
       </c>
       <c r="F1314" s="6" t="s">
-        <v>8355</v>
+        <v>8358</v>
       </c>
       <c r="G1314" s="6" t="s">
-        <v>8356</v>
+        <v>8358</v>
       </c>
       <c r="H1314" s="6" t="s">
-        <v>8357</v>
+        <v>8358</v>
       </c>
     </row>
     <row r="1315">
       <c r="B1315" s="5" t="s">
-        <v>8358</v>
+        <v>8359</v>
       </c>
       <c r="C1315" s="5" t="s">
-        <v>8359</v>
+        <v>8360</v>
       </c>
       <c r="D1315" s="5" t="s">
-        <v>8360</v>
+        <v>8361</v>
       </c>
       <c r="E1315" s="5" t="s">
-        <v>8361</v>
+        <v>8362</v>
       </c>
       <c r="F1315" s="5" t="s">
-        <v>8362</v>
+        <v>8363</v>
       </c>
       <c r="G1315" s="5" t="s">
         <v>8363</v>
@@ -59435,125 +59477,125 @@
         <v>8374</v>
       </c>
       <c r="E1317" s="5" t="s">
-        <v>6245</v>
+        <v>8375</v>
       </c>
       <c r="F1317" s="5" t="s">
-        <v>6246</v>
+        <v>8376</v>
       </c>
       <c r="G1317" s="5" t="s">
-        <v>6246</v>
+        <v>8377</v>
       </c>
       <c r="H1317" s="5" t="s">
-        <v>7423</v>
+        <v>8378</v>
       </c>
     </row>
     <row r="1318">
       <c r="B1318" s="6" t="s">
-        <v>8375</v>
+        <v>8379</v>
       </c>
       <c r="C1318" s="6" t="s">
-        <v>8376</v>
+        <v>8380</v>
       </c>
       <c r="D1318" s="6" t="s">
-        <v>8377</v>
+        <v>8381</v>
       </c>
       <c r="E1318" s="6" t="s">
-        <v>8378</v>
+        <v>8382</v>
       </c>
       <c r="F1318" s="6" t="s">
-        <v>8379</v>
+        <v>8383</v>
       </c>
       <c r="G1318" s="6" t="s">
-        <v>8380</v>
+        <v>8384</v>
       </c>
       <c r="H1318" s="6" t="s">
-        <v>8377</v>
+        <v>8385</v>
       </c>
     </row>
     <row r="1319">
       <c r="B1319" s="5" t="s">
-        <v>8381</v>
+        <v>8386</v>
       </c>
       <c r="C1319" s="5" t="s">
-        <v>8382</v>
+        <v>8387</v>
       </c>
       <c r="D1319" s="5" t="s">
-        <v>8383</v>
+        <v>8388</v>
       </c>
       <c r="E1319" s="5" t="s">
-        <v>8384</v>
+        <v>6245</v>
       </c>
       <c r="F1319" s="5" t="s">
-        <v>8385</v>
+        <v>6246</v>
       </c>
       <c r="G1319" s="5" t="s">
-        <v>8386</v>
+        <v>6246</v>
       </c>
       <c r="H1319" s="5" t="s">
-        <v>8387</v>
+        <v>7423</v>
       </c>
     </row>
     <row r="1320">
       <c r="B1320" s="6" t="s">
-        <v>8388</v>
+        <v>8389</v>
       </c>
       <c r="C1320" s="6" t="s">
-        <v>8389</v>
+        <v>8390</v>
       </c>
       <c r="D1320" s="6" t="s">
-        <v>8390</v>
+        <v>8391</v>
       </c>
       <c r="E1320" s="6" t="s">
+        <v>8392</v>
+      </c>
+      <c r="F1320" s="6" t="s">
+        <v>8393</v>
+      </c>
+      <c r="G1320" s="6" t="s">
+        <v>8394</v>
+      </c>
+      <c r="H1320" s="6" t="s">
         <v>8391</v>
-      </c>
-      <c r="F1320" s="6" t="s">
-        <v>8392</v>
-      </c>
-      <c r="G1320" s="6" t="s">
-        <v>8392</v>
-      </c>
-      <c r="H1320" s="6" t="s">
-        <v>8393</v>
       </c>
     </row>
     <row r="1321">
       <c r="B1321" s="5" t="s">
-        <v>8394</v>
+        <v>8395</v>
       </c>
       <c r="C1321" s="5" t="s">
-        <v>8395</v>
+        <v>8396</v>
       </c>
       <c r="D1321" s="5" t="s">
-        <v>8396</v>
+        <v>8397</v>
       </c>
       <c r="E1321" s="5" t="s">
-        <v>8397</v>
+        <v>8398</v>
       </c>
       <c r="F1321" s="5" t="s">
-        <v>8398</v>
+        <v>8399</v>
       </c>
       <c r="G1321" s="5" t="s">
-        <v>8399</v>
+        <v>8400</v>
       </c>
       <c r="H1321" s="5" t="s">
-        <v>8400</v>
+        <v>8401</v>
       </c>
     </row>
     <row r="1322">
       <c r="B1322" s="6" t="s">
-        <v>8401</v>
+        <v>8402</v>
       </c>
       <c r="C1322" s="6" t="s">
-        <v>8402</v>
+        <v>8403</v>
       </c>
       <c r="D1322" s="6" t="s">
-        <v>8403</v>
+        <v>8404</v>
       </c>
       <c r="E1322" s="6" t="s">
-        <v>8404</v>
+        <v>8405</v>
       </c>
       <c r="F1322" s="6" t="s">
-        <v>8405</v>
+        <v>8406</v>
       </c>
       <c r="G1322" s="6" t="s">
         <v>8406</v>
@@ -59579,96 +59621,96 @@
         <v>8412</v>
       </c>
       <c r="G1323" s="5" t="s">
-        <v>8412</v>
+        <v>8413</v>
       </c>
       <c r="H1323" s="5" t="s">
-        <v>8413</v>
+        <v>8414</v>
       </c>
     </row>
     <row r="1324">
       <c r="B1324" s="6" t="s">
-        <v>8414</v>
+        <v>8415</v>
       </c>
       <c r="C1324" s="6" t="s">
-        <v>8415</v>
+        <v>8416</v>
       </c>
       <c r="D1324" s="6" t="s">
-        <v>8416</v>
+        <v>8417</v>
       </c>
       <c r="E1324" s="6" t="s">
-        <v>8417</v>
+        <v>8418</v>
       </c>
       <c r="F1324" s="6" t="s">
-        <v>8418</v>
+        <v>8419</v>
       </c>
       <c r="G1324" s="6" t="s">
-        <v>8418</v>
+        <v>8420</v>
       </c>
       <c r="H1324" s="6" t="s">
-        <v>8419</v>
+        <v>8421</v>
       </c>
     </row>
     <row r="1325">
       <c r="B1325" s="5" t="s">
-        <v>8420</v>
+        <v>8422</v>
       </c>
       <c r="C1325" s="5" t="s">
-        <v>8421</v>
+        <v>8423</v>
       </c>
       <c r="D1325" s="5" t="s">
-        <v>8422</v>
+        <v>8424</v>
       </c>
       <c r="E1325" s="5" t="s">
-        <v>8423</v>
+        <v>8425</v>
       </c>
       <c r="F1325" s="5" t="s">
-        <v>8424</v>
+        <v>8426</v>
       </c>
       <c r="G1325" s="5" t="s">
-        <v>8424</v>
+        <v>8426</v>
       </c>
       <c r="H1325" s="5" t="s">
-        <v>8425</v>
+        <v>8427</v>
       </c>
     </row>
     <row r="1326">
       <c r="B1326" s="6" t="s">
-        <v>8426</v>
+        <v>8428</v>
       </c>
       <c r="C1326" s="6" t="s">
-        <v>8427</v>
+        <v>8429</v>
       </c>
       <c r="D1326" s="6" t="s">
-        <v>8428</v>
+        <v>8430</v>
       </c>
       <c r="E1326" s="6" t="s">
-        <v>8429</v>
+        <v>8431</v>
       </c>
       <c r="F1326" s="6" t="s">
-        <v>8430</v>
+        <v>8432</v>
       </c>
       <c r="G1326" s="6" t="s">
-        <v>8431</v>
+        <v>8432</v>
       </c>
       <c r="H1326" s="6" t="s">
-        <v>8432</v>
+        <v>8433</v>
       </c>
     </row>
     <row r="1327">
       <c r="B1327" s="5" t="s">
-        <v>8433</v>
+        <v>8434</v>
       </c>
       <c r="C1327" s="5" t="s">
-        <v>8434</v>
+        <v>8435</v>
       </c>
       <c r="D1327" s="5" t="s">
-        <v>8435</v>
+        <v>8436</v>
       </c>
       <c r="E1327" s="5" t="s">
-        <v>8436</v>
+        <v>8437</v>
       </c>
       <c r="F1327" s="5" t="s">
-        <v>8437</v>
+        <v>8438</v>
       </c>
       <c r="G1327" s="5" t="s">
         <v>8438</v>
@@ -59694,303 +59736,303 @@
         <v>8444</v>
       </c>
       <c r="G1328" s="6" t="s">
-        <v>8444</v>
+        <v>8445</v>
       </c>
       <c r="H1328" s="6" t="s">
-        <v>8445</v>
+        <v>8446</v>
       </c>
     </row>
     <row r="1329">
       <c r="B1329" s="5" t="s">
-        <v>8446</v>
+        <v>8447</v>
       </c>
       <c r="C1329" s="5" t="s">
-        <v>8447</v>
+        <v>8448</v>
       </c>
       <c r="D1329" s="5" t="s">
-        <v>8448</v>
+        <v>8449</v>
       </c>
       <c r="E1329" s="5" t="s">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="F1329" s="5" t="s">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="G1329" s="5" t="s">
-        <v>8451</v>
+        <v>8452</v>
       </c>
       <c r="H1329" s="5" t="s">
-        <v>8452</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="1330">
       <c r="B1330" s="6" t="s">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="C1330" s="6" t="s">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D1330" s="6" t="s">
-        <v>8455</v>
+        <v>8456</v>
       </c>
       <c r="E1330" s="6" t="s">
-        <v>8456</v>
+        <v>8457</v>
       </c>
       <c r="F1330" s="6" t="s">
-        <v>8457</v>
+        <v>8458</v>
       </c>
       <c r="G1330" s="6" t="s">
-        <v>8457</v>
+        <v>8458</v>
       </c>
       <c r="H1330" s="6" t="s">
-        <v>8458</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="1331">
       <c r="B1331" s="5" t="s">
-        <v>8459</v>
+        <v>8460</v>
       </c>
       <c r="C1331" s="5" t="s">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D1331" s="5" t="s">
-        <v>8461</v>
+        <v>8462</v>
       </c>
       <c r="E1331" s="5" t="s">
-        <v>8462</v>
+        <v>8463</v>
       </c>
       <c r="F1331" s="5" t="s">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="G1331" s="5" t="s">
-        <v>8464</v>
+        <v>8465</v>
       </c>
       <c r="H1331" s="5" t="s">
-        <v>8465</v>
+        <v>8466</v>
       </c>
     </row>
     <row r="1332">
       <c r="B1332" s="6" t="s">
-        <v>8466</v>
+        <v>8467</v>
       </c>
       <c r="C1332" s="6" t="s">
-        <v>8467</v>
+        <v>8468</v>
       </c>
       <c r="D1332" s="6" t="s">
-        <v>8468</v>
+        <v>8469</v>
       </c>
       <c r="E1332" s="6" t="s">
-        <v>8469</v>
+        <v>8470</v>
       </c>
       <c r="F1332" s="6" t="s">
-        <v>8470</v>
+        <v>8471</v>
       </c>
       <c r="G1332" s="6" t="s">
-        <v>8470</v>
+        <v>8471</v>
       </c>
       <c r="H1332" s="6" t="s">
-        <v>8471</v>
+        <v>8472</v>
       </c>
     </row>
     <row r="1333">
       <c r="B1333" s="5" t="s">
-        <v>8472</v>
+        <v>8473</v>
       </c>
       <c r="C1333" s="5" t="s">
-        <v>8473</v>
+        <v>8474</v>
       </c>
       <c r="D1333" s="5" t="s">
-        <v>8474</v>
+        <v>8475</v>
       </c>
       <c r="E1333" s="5" t="s">
-        <v>8475</v>
+        <v>8476</v>
       </c>
       <c r="F1333" s="5" t="s">
-        <v>8476</v>
+        <v>8477</v>
       </c>
       <c r="G1333" s="5" t="s">
-        <v>8476</v>
+        <v>8478</v>
       </c>
       <c r="H1333" s="5" t="s">
-        <v>8477</v>
+        <v>8479</v>
       </c>
     </row>
     <row r="1334">
       <c r="B1334" s="6" t="s">
-        <v>8478</v>
+        <v>8480</v>
       </c>
       <c r="C1334" s="6" t="s">
-        <v>8479</v>
+        <v>8481</v>
       </c>
       <c r="D1334" s="6" t="s">
-        <v>2758</v>
+        <v>8482</v>
       </c>
       <c r="E1334" s="6" t="s">
-        <v>2759</v>
+        <v>8483</v>
       </c>
       <c r="F1334" s="6" t="s">
-        <v>2760</v>
+        <v>8484</v>
       </c>
       <c r="G1334" s="6" t="s">
-        <v>2760</v>
+        <v>8484</v>
       </c>
       <c r="H1334" s="6" t="s">
-        <v>2761</v>
+        <v>8485</v>
       </c>
     </row>
     <row r="1335">
       <c r="B1335" s="5" t="s">
-        <v>8480</v>
+        <v>8486</v>
       </c>
       <c r="C1335" s="5" t="s">
-        <v>8481</v>
+        <v>8487</v>
       </c>
       <c r="D1335" s="5" t="s">
-        <v>8482</v>
+        <v>8488</v>
       </c>
       <c r="E1335" s="5" t="s">
-        <v>8483</v>
+        <v>8489</v>
       </c>
       <c r="F1335" s="5" t="s">
-        <v>8484</v>
+        <v>8490</v>
       </c>
       <c r="G1335" s="5" t="s">
-        <v>8484</v>
+        <v>8490</v>
       </c>
       <c r="H1335" s="5" t="s">
-        <v>8485</v>
+        <v>8491</v>
       </c>
     </row>
     <row r="1336">
       <c r="B1336" s="6" t="s">
-        <v>8486</v>
+        <v>8492</v>
       </c>
       <c r="C1336" s="6" t="s">
-        <v>8487</v>
+        <v>8493</v>
       </c>
       <c r="D1336" s="6" t="s">
-        <v>8488</v>
+        <v>2758</v>
       </c>
       <c r="E1336" s="6" t="s">
-        <v>8489</v>
+        <v>2759</v>
       </c>
       <c r="F1336" s="6" t="s">
-        <v>8490</v>
+        <v>2760</v>
       </c>
       <c r="G1336" s="6" t="s">
-        <v>8489</v>
+        <v>2760</v>
       </c>
       <c r="H1336" s="6" t="s">
-        <v>8491</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="1337">
       <c r="B1337" s="5" t="s">
-        <v>8492</v>
+        <v>8494</v>
       </c>
       <c r="C1337" s="5" t="s">
-        <v>8493</v>
+        <v>8495</v>
       </c>
       <c r="D1337" s="5" t="s">
-        <v>8494</v>
+        <v>8496</v>
       </c>
       <c r="E1337" s="5" t="s">
-        <v>8495</v>
+        <v>8497</v>
       </c>
       <c r="F1337" s="5" t="s">
-        <v>8496</v>
+        <v>8498</v>
       </c>
       <c r="G1337" s="5" t="s">
-        <v>8497</v>
+        <v>8498</v>
       </c>
       <c r="H1337" s="5" t="s">
-        <v>8498</v>
+        <v>8499</v>
       </c>
     </row>
     <row r="1338">
       <c r="B1338" s="6" t="s">
-        <v>8499</v>
+        <v>8500</v>
       </c>
       <c r="C1338" s="6" t="s">
-        <v>8500</v>
+        <v>8501</v>
       </c>
       <c r="D1338" s="6" t="s">
-        <v>8501</v>
+        <v>8502</v>
       </c>
       <c r="E1338" s="6" t="s">
-        <v>8502</v>
+        <v>8503</v>
       </c>
       <c r="F1338" s="6" t="s">
-        <v>8503</v>
+        <v>8504</v>
       </c>
       <c r="G1338" s="6" t="s">
         <v>8503</v>
       </c>
       <c r="H1338" s="6" t="s">
-        <v>8504</v>
+        <v>8505</v>
       </c>
     </row>
     <row r="1339">
       <c r="B1339" s="5" t="s">
-        <v>8505</v>
+        <v>8506</v>
       </c>
       <c r="C1339" s="5" t="s">
-        <v>8506</v>
+        <v>8507</v>
       </c>
       <c r="D1339" s="5" t="s">
-        <v>8507</v>
+        <v>8508</v>
       </c>
       <c r="E1339" s="5" t="s">
-        <v>8508</v>
+        <v>8509</v>
       </c>
       <c r="F1339" s="5" t="s">
-        <v>8509</v>
+        <v>8510</v>
       </c>
       <c r="G1339" s="5" t="s">
-        <v>8509</v>
+        <v>8511</v>
       </c>
       <c r="H1339" s="5" t="s">
-        <v>8510</v>
+        <v>8512</v>
       </c>
     </row>
     <row r="1340">
       <c r="B1340" s="6" t="s">
-        <v>8511</v>
+        <v>8513</v>
       </c>
       <c r="C1340" s="6" t="s">
-        <v>8512</v>
+        <v>8514</v>
       </c>
       <c r="D1340" s="6" t="s">
-        <v>8513</v>
+        <v>8515</v>
       </c>
       <c r="E1340" s="6" t="s">
-        <v>8514</v>
+        <v>8516</v>
       </c>
       <c r="F1340" s="6" t="s">
-        <v>8515</v>
+        <v>8517</v>
       </c>
       <c r="G1340" s="6" t="s">
-        <v>8516</v>
+        <v>8517</v>
       </c>
       <c r="H1340" s="6" t="s">
-        <v>8517</v>
+        <v>8518</v>
       </c>
     </row>
     <row r="1341">
       <c r="B1341" s="5" t="s">
-        <v>8518</v>
+        <v>8519</v>
       </c>
       <c r="C1341" s="5" t="s">
-        <v>8519</v>
+        <v>8520</v>
       </c>
       <c r="D1341" s="5" t="s">
-        <v>8520</v>
+        <v>8521</v>
       </c>
       <c r="E1341" s="5" t="s">
-        <v>8521</v>
+        <v>8522</v>
       </c>
       <c r="F1341" s="5" t="s">
-        <v>8522</v>
+        <v>8523</v>
       </c>
       <c r="G1341" s="5" t="s">
         <v>8523</v>
@@ -60027,177 +60069,177 @@
         <v>8532</v>
       </c>
       <c r="C1343" s="5" t="s">
-        <v>6931</v>
+        <v>8533</v>
       </c>
       <c r="D1343" s="5" t="s">
-        <v>8533</v>
+        <v>8534</v>
       </c>
       <c r="E1343" s="5" t="s">
-        <v>6932</v>
+        <v>8535</v>
       </c>
       <c r="F1343" s="5" t="s">
-        <v>6933</v>
+        <v>8536</v>
       </c>
       <c r="G1343" s="5" t="s">
-        <v>6934</v>
+        <v>8537</v>
       </c>
       <c r="H1343" s="5" t="s">
-        <v>8533</v>
+        <v>8538</v>
       </c>
     </row>
     <row r="1344">
       <c r="B1344" s="6" t="s">
-        <v>8534</v>
+        <v>8539</v>
       </c>
       <c r="C1344" s="6" t="s">
-        <v>6895</v>
+        <v>8540</v>
       </c>
       <c r="D1344" s="6" t="s">
-        <v>8535</v>
+        <v>8541</v>
       </c>
       <c r="E1344" s="6" t="s">
-        <v>6897</v>
+        <v>8542</v>
       </c>
       <c r="F1344" s="6" t="s">
-        <v>8536</v>
+        <v>8543</v>
       </c>
       <c r="G1344" s="6" t="s">
-        <v>8537</v>
+        <v>8544</v>
       </c>
       <c r="H1344" s="6" t="s">
-        <v>8538</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="1345">
       <c r="B1345" s="5" t="s">
-        <v>8539</v>
+        <v>8546</v>
       </c>
       <c r="C1345" s="5" t="s">
-        <v>8540</v>
+        <v>6931</v>
       </c>
       <c r="D1345" s="5" t="s">
-        <v>8541</v>
+        <v>8547</v>
       </c>
       <c r="E1345" s="5" t="s">
-        <v>8542</v>
+        <v>6932</v>
       </c>
       <c r="F1345" s="5" t="s">
-        <v>8543</v>
+        <v>6933</v>
       </c>
       <c r="G1345" s="5" t="s">
-        <v>8544</v>
+        <v>6934</v>
       </c>
       <c r="H1345" s="5" t="s">
-        <v>8545</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="1346">
       <c r="B1346" s="6" t="s">
-        <v>8546</v>
+        <v>8548</v>
       </c>
       <c r="C1346" s="6" t="s">
-        <v>8547</v>
+        <v>6895</v>
       </c>
       <c r="D1346" s="6" t="s">
-        <v>8548</v>
+        <v>8549</v>
       </c>
       <c r="E1346" s="6" t="s">
-        <v>8521</v>
+        <v>6897</v>
       </c>
       <c r="F1346" s="6" t="s">
-        <v>8522</v>
+        <v>8550</v>
       </c>
       <c r="G1346" s="6" t="s">
-        <v>8523</v>
+        <v>8551</v>
       </c>
       <c r="H1346" s="6" t="s">
-        <v>8549</v>
+        <v>8552</v>
       </c>
     </row>
     <row r="1347">
       <c r="B1347" s="5" t="s">
-        <v>8550</v>
+        <v>8553</v>
       </c>
       <c r="C1347" s="5" t="s">
-        <v>8551</v>
+        <v>8554</v>
       </c>
       <c r="D1347" s="5" t="s">
-        <v>8552</v>
+        <v>8555</v>
       </c>
       <c r="E1347" s="5" t="s">
-        <v>8553</v>
+        <v>8556</v>
       </c>
       <c r="F1347" s="5" t="s">
-        <v>8554</v>
+        <v>8557</v>
       </c>
       <c r="G1347" s="5" t="s">
-        <v>8555</v>
+        <v>8558</v>
       </c>
       <c r="H1347" s="5" t="s">
-        <v>8556</v>
+        <v>8559</v>
       </c>
     </row>
     <row r="1348">
       <c r="B1348" s="6" t="s">
-        <v>8557</v>
+        <v>8560</v>
       </c>
       <c r="C1348" s="6" t="s">
-        <v>8558</v>
+        <v>8561</v>
       </c>
       <c r="D1348" s="6" t="s">
-        <v>8559</v>
+        <v>8562</v>
       </c>
       <c r="E1348" s="6" t="s">
-        <v>8560</v>
+        <v>8535</v>
       </c>
       <c r="F1348" s="6" t="s">
-        <v>8561</v>
+        <v>8536</v>
       </c>
       <c r="G1348" s="6" t="s">
-        <v>8561</v>
+        <v>8537</v>
       </c>
       <c r="H1348" s="6" t="s">
-        <v>8562</v>
+        <v>8563</v>
       </c>
     </row>
     <row r="1349">
       <c r="B1349" s="5" t="s">
-        <v>8563</v>
+        <v>8564</v>
       </c>
       <c r="C1349" s="5" t="s">
-        <v>8564</v>
+        <v>8565</v>
       </c>
       <c r="D1349" s="5" t="s">
-        <v>8565</v>
+        <v>8566</v>
       </c>
       <c r="E1349" s="5" t="s">
-        <v>8566</v>
+        <v>8567</v>
       </c>
       <c r="F1349" s="5" t="s">
-        <v>8567</v>
+        <v>8568</v>
       </c>
       <c r="G1349" s="5" t="s">
-        <v>8568</v>
+        <v>8569</v>
       </c>
       <c r="H1349" s="5" t="s">
-        <v>8569</v>
+        <v>8570</v>
       </c>
     </row>
     <row r="1350">
       <c r="B1350" s="6" t="s">
-        <v>8570</v>
+        <v>8571</v>
       </c>
       <c r="C1350" s="6" t="s">
-        <v>8571</v>
+        <v>8572</v>
       </c>
       <c r="D1350" s="6" t="s">
-        <v>8572</v>
+        <v>8573</v>
       </c>
       <c r="E1350" s="6" t="s">
-        <v>8573</v>
+        <v>8574</v>
       </c>
       <c r="F1350" s="6" t="s">
-        <v>8574</v>
+        <v>8575</v>
       </c>
       <c r="G1350" s="6" t="s">
         <v>8575</v>
@@ -60220,335 +60262,335 @@
         <v>8580</v>
       </c>
       <c r="F1351" s="5" t="s">
-        <v>7741</v>
+        <v>8581</v>
       </c>
       <c r="G1351" s="5" t="s">
-        <v>7742</v>
+        <v>8582</v>
       </c>
       <c r="H1351" s="5" t="s">
-        <v>8581</v>
+        <v>8583</v>
       </c>
     </row>
     <row r="1352">
       <c r="B1352" s="6" t="s">
-        <v>8582</v>
+        <v>8584</v>
       </c>
       <c r="C1352" s="6" t="s">
-        <v>8583</v>
+        <v>8585</v>
       </c>
       <c r="D1352" s="6" t="s">
-        <v>8584</v>
+        <v>8586</v>
       </c>
       <c r="E1352" s="6" t="s">
-        <v>8585</v>
+        <v>8587</v>
       </c>
       <c r="F1352" s="6" t="s">
-        <v>8586</v>
+        <v>8588</v>
       </c>
       <c r="G1352" s="6" t="s">
-        <v>8587</v>
+        <v>8589</v>
       </c>
       <c r="H1352" s="6" t="s">
-        <v>8588</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="1353">
       <c r="B1353" s="5" t="s">
-        <v>8589</v>
+        <v>8591</v>
       </c>
       <c r="C1353" s="5" t="s">
-        <v>8590</v>
+        <v>8592</v>
       </c>
       <c r="D1353" s="5" t="s">
-        <v>8591</v>
+        <v>8593</v>
       </c>
       <c r="E1353" s="5" t="s">
-        <v>8592</v>
+        <v>8594</v>
       </c>
       <c r="F1353" s="5" t="s">
-        <v>8593</v>
+        <v>7755</v>
       </c>
       <c r="G1353" s="5" t="s">
-        <v>8592</v>
+        <v>7756</v>
       </c>
       <c r="H1353" s="5" t="s">
-        <v>8591</v>
+        <v>8595</v>
       </c>
     </row>
     <row r="1354">
       <c r="B1354" s="6" t="s">
-        <v>8594</v>
+        <v>8596</v>
       </c>
       <c r="C1354" s="6" t="s">
-        <v>6033</v>
+        <v>8597</v>
       </c>
       <c r="D1354" s="6" t="s">
-        <v>6936</v>
+        <v>8598</v>
       </c>
       <c r="E1354" s="6" t="s">
-        <v>6035</v>
+        <v>8599</v>
       </c>
       <c r="F1354" s="6" t="s">
-        <v>8321</v>
+        <v>8600</v>
       </c>
       <c r="G1354" s="6" t="s">
-        <v>8321</v>
+        <v>8601</v>
       </c>
       <c r="H1354" s="6" t="s">
-        <v>5404</v>
+        <v>8602</v>
       </c>
     </row>
     <row r="1355">
       <c r="B1355" s="5" t="s">
-        <v>8595</v>
+        <v>8603</v>
       </c>
       <c r="C1355" s="5" t="s">
-        <v>6080</v>
+        <v>8604</v>
       </c>
       <c r="D1355" s="5" t="s">
-        <v>8596</v>
+        <v>8605</v>
       </c>
       <c r="E1355" s="5" t="s">
-        <v>6082</v>
+        <v>8606</v>
       </c>
       <c r="F1355" s="5" t="s">
-        <v>8597</v>
+        <v>8607</v>
       </c>
       <c r="G1355" s="5" t="s">
-        <v>8598</v>
+        <v>8606</v>
       </c>
       <c r="H1355" s="5" t="s">
-        <v>8599</v>
+        <v>8605</v>
       </c>
     </row>
     <row r="1356">
       <c r="B1356" s="6" t="s">
-        <v>8600</v>
+        <v>8608</v>
       </c>
       <c r="C1356" s="6" t="s">
-        <v>7363</v>
+        <v>6033</v>
       </c>
       <c r="D1356" s="6" t="s">
-        <v>8601</v>
+        <v>6936</v>
       </c>
       <c r="E1356" s="6" t="s">
-        <v>7365</v>
+        <v>6035</v>
       </c>
       <c r="F1356" s="6" t="s">
-        <v>6016</v>
+        <v>8335</v>
       </c>
       <c r="G1356" s="6" t="s">
-        <v>6017</v>
+        <v>8335</v>
       </c>
       <c r="H1356" s="6" t="s">
-        <v>7364</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1357">
       <c r="B1357" s="5" t="s">
-        <v>8602</v>
+        <v>8609</v>
       </c>
       <c r="C1357" s="5" t="s">
-        <v>7369</v>
+        <v>6080</v>
       </c>
       <c r="D1357" s="5" t="s">
-        <v>8603</v>
+        <v>8610</v>
       </c>
       <c r="E1357" s="5" t="s">
-        <v>7371</v>
+        <v>6082</v>
       </c>
       <c r="F1357" s="5" t="s">
-        <v>6023</v>
+        <v>8611</v>
       </c>
       <c r="G1357" s="5" t="s">
-        <v>6023</v>
+        <v>8612</v>
       </c>
       <c r="H1357" s="5" t="s">
-        <v>8604</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="1358">
       <c r="B1358" s="6" t="s">
-        <v>8605</v>
+        <v>8614</v>
       </c>
       <c r="C1358" s="6" t="s">
-        <v>7374</v>
+        <v>7363</v>
       </c>
       <c r="D1358" s="6" t="s">
-        <v>8606</v>
+        <v>8615</v>
       </c>
       <c r="E1358" s="6" t="s">
-        <v>7376</v>
+        <v>7365</v>
       </c>
       <c r="F1358" s="6" t="s">
-        <v>6029</v>
+        <v>6016</v>
       </c>
       <c r="G1358" s="6" t="s">
-        <v>6030</v>
+        <v>6017</v>
       </c>
       <c r="H1358" s="6" t="s">
-        <v>7379</v>
+        <v>7364</v>
       </c>
     </row>
     <row r="1359">
       <c r="B1359" s="5" t="s">
-        <v>8607</v>
+        <v>8616</v>
       </c>
       <c r="C1359" s="5" t="s">
-        <v>6046</v>
+        <v>7369</v>
       </c>
       <c r="D1359" s="5" t="s">
-        <v>8608</v>
+        <v>8617</v>
       </c>
       <c r="E1359" s="5" t="s">
-        <v>6048</v>
+        <v>7371</v>
       </c>
       <c r="F1359" s="5" t="s">
-        <v>6049</v>
+        <v>6023</v>
       </c>
       <c r="G1359" s="5" t="s">
-        <v>6050</v>
+        <v>6023</v>
       </c>
       <c r="H1359" s="5" t="s">
-        <v>8609</v>
+        <v>8618</v>
       </c>
     </row>
     <row r="1360">
       <c r="B1360" s="6" t="s">
-        <v>8610</v>
+        <v>8619</v>
       </c>
       <c r="C1360" s="6" t="s">
-        <v>8611</v>
+        <v>7374</v>
       </c>
       <c r="D1360" s="6" t="s">
-        <v>8612</v>
+        <v>8620</v>
       </c>
       <c r="E1360" s="6" t="s">
-        <v>6076</v>
+        <v>7376</v>
       </c>
       <c r="F1360" s="6" t="s">
-        <v>8613</v>
+        <v>6029</v>
       </c>
       <c r="G1360" s="6" t="s">
-        <v>8614</v>
+        <v>6030</v>
       </c>
       <c r="H1360" s="6" t="s">
-        <v>7361</v>
+        <v>7379</v>
       </c>
     </row>
     <row r="1361">
       <c r="B1361" s="5" t="s">
-        <v>8615</v>
+        <v>8621</v>
       </c>
       <c r="C1361" s="5" t="s">
-        <v>7349</v>
+        <v>6046</v>
       </c>
       <c r="D1361" s="5" t="s">
-        <v>8616</v>
+        <v>8622</v>
       </c>
       <c r="E1361" s="5" t="s">
-        <v>7351</v>
+        <v>6048</v>
       </c>
       <c r="F1361" s="5" t="s">
-        <v>8617</v>
+        <v>6049</v>
       </c>
       <c r="G1361" s="5" t="s">
-        <v>8617</v>
+        <v>6050</v>
       </c>
       <c r="H1361" s="5" t="s">
-        <v>8618</v>
+        <v>8623</v>
       </c>
     </row>
     <row r="1362">
       <c r="B1362" s="6" t="s">
-        <v>8619</v>
+        <v>8624</v>
       </c>
       <c r="C1362" s="6" t="s">
-        <v>8620</v>
+        <v>8625</v>
       </c>
       <c r="D1362" s="6" t="s">
-        <v>8621</v>
+        <v>8626</v>
       </c>
       <c r="E1362" s="6" t="s">
-        <v>8622</v>
+        <v>6076</v>
       </c>
       <c r="F1362" s="6" t="s">
-        <v>8623</v>
+        <v>8627</v>
       </c>
       <c r="G1362" s="6" t="s">
-        <v>8624</v>
+        <v>8628</v>
       </c>
       <c r="H1362" s="6" t="s">
-        <v>8625</v>
+        <v>7361</v>
       </c>
     </row>
     <row r="1363">
       <c r="B1363" s="5" t="s">
-        <v>8626</v>
+        <v>8629</v>
       </c>
       <c r="C1363" s="5" t="s">
-        <v>8512</v>
+        <v>7349</v>
       </c>
       <c r="D1363" s="5" t="s">
-        <v>8513</v>
+        <v>8630</v>
       </c>
       <c r="E1363" s="5" t="s">
-        <v>8514</v>
+        <v>7351</v>
       </c>
       <c r="F1363" s="5" t="s">
-        <v>8515</v>
+        <v>8631</v>
       </c>
       <c r="G1363" s="5" t="s">
-        <v>8516</v>
+        <v>8631</v>
       </c>
       <c r="H1363" s="5" t="s">
-        <v>8517</v>
+        <v>8632</v>
       </c>
     </row>
     <row r="1364">
       <c r="B1364" s="6" t="s">
-        <v>8627</v>
+        <v>8633</v>
       </c>
       <c r="C1364" s="6" t="s">
-        <v>8628</v>
+        <v>8634</v>
       </c>
       <c r="D1364" s="6" t="s">
-        <v>8629</v>
+        <v>8635</v>
       </c>
       <c r="E1364" s="6" t="s">
-        <v>8630</v>
+        <v>8636</v>
       </c>
       <c r="F1364" s="6" t="s">
-        <v>8631</v>
+        <v>8637</v>
       </c>
       <c r="G1364" s="6" t="s">
-        <v>8632</v>
+        <v>8638</v>
       </c>
       <c r="H1364" s="6" t="s">
-        <v>8633</v>
+        <v>8639</v>
       </c>
     </row>
     <row r="1365">
       <c r="B1365" s="5" t="s">
-        <v>8634</v>
+        <v>8640</v>
       </c>
       <c r="C1365" s="5" t="s">
-        <v>8635</v>
+        <v>8526</v>
       </c>
       <c r="D1365" s="5" t="s">
-        <v>8636</v>
+        <v>8527</v>
       </c>
       <c r="E1365" s="5" t="s">
-        <v>8637</v>
+        <v>8528</v>
       </c>
       <c r="F1365" s="5" t="s">
-        <v>8638</v>
+        <v>8529</v>
       </c>
       <c r="G1365" s="5" t="s">
-        <v>8639</v>
+        <v>8530</v>
       </c>
       <c r="H1365" s="5" t="s">
-        <v>8640</v>
+        <v>8531</v>
       </c>
     </row>
     <row r="1366">
@@ -60660,50 +60702,50 @@
         <v>8673</v>
       </c>
       <c r="G1370" s="6" t="s">
-        <v>8673</v>
+        <v>8674</v>
       </c>
       <c r="H1370" s="6" t="s">
-        <v>8674</v>
+        <v>8675</v>
       </c>
     </row>
     <row r="1371">
       <c r="B1371" s="5" t="s">
-        <v>8675</v>
+        <v>8676</v>
       </c>
       <c r="C1371" s="5" t="s">
-        <v>8676</v>
+        <v>8677</v>
       </c>
       <c r="D1371" s="5" t="s">
-        <v>8677</v>
+        <v>8678</v>
       </c>
       <c r="E1371" s="5" t="s">
-        <v>8678</v>
+        <v>8679</v>
       </c>
       <c r="F1371" s="5" t="s">
-        <v>8679</v>
+        <v>8680</v>
       </c>
       <c r="G1371" s="5" t="s">
-        <v>8680</v>
+        <v>8681</v>
       </c>
       <c r="H1371" s="5" t="s">
-        <v>8681</v>
+        <v>8682</v>
       </c>
     </row>
     <row r="1372">
       <c r="B1372" s="6" t="s">
-        <v>8682</v>
+        <v>8683</v>
       </c>
       <c r="C1372" s="6" t="s">
-        <v>8683</v>
+        <v>8684</v>
       </c>
       <c r="D1372" s="6" t="s">
-        <v>8684</v>
+        <v>8685</v>
       </c>
       <c r="E1372" s="6" t="s">
-        <v>8685</v>
+        <v>8686</v>
       </c>
       <c r="F1372" s="6" t="s">
-        <v>8686</v>
+        <v>8687</v>
       </c>
       <c r="G1372" s="6" t="s">
         <v>8687</v>
@@ -60913,99 +60955,99 @@
         <v>8749</v>
       </c>
       <c r="G1381" s="5" t="s">
-        <v>8749</v>
+        <v>8750</v>
       </c>
       <c r="H1381" s="5" t="s">
-        <v>8750</v>
+        <v>8751</v>
       </c>
     </row>
     <row r="1382">
       <c r="B1382" s="6" t="s">
-        <v>8751</v>
+        <v>8752</v>
       </c>
       <c r="C1382" s="6" t="s">
-        <v>8752</v>
+        <v>8753</v>
       </c>
       <c r="D1382" s="6" t="s">
-        <v>8753</v>
+        <v>8754</v>
       </c>
       <c r="E1382" s="6" t="s">
-        <v>8754</v>
+        <v>8755</v>
       </c>
       <c r="F1382" s="6" t="s">
-        <v>8755</v>
+        <v>8756</v>
       </c>
       <c r="G1382" s="6" t="s">
-        <v>8756</v>
+        <v>8757</v>
       </c>
       <c r="H1382" s="6" t="s">
-        <v>8757</v>
+        <v>8758</v>
       </c>
     </row>
     <row r="1383">
       <c r="B1383" s="5" t="s">
-        <v>8758</v>
+        <v>8759</v>
       </c>
       <c r="C1383" s="5" t="s">
-        <v>8759</v>
+        <v>8760</v>
       </c>
       <c r="D1383" s="5" t="s">
-        <v>8760</v>
+        <v>8761</v>
       </c>
       <c r="E1383" s="5" t="s">
-        <v>8761</v>
+        <v>8762</v>
       </c>
       <c r="F1383" s="5" t="s">
-        <v>8679</v>
+        <v>8763</v>
       </c>
       <c r="G1383" s="5" t="s">
-        <v>8680</v>
+        <v>8763</v>
       </c>
       <c r="H1383" s="5" t="s">
-        <v>8762</v>
+        <v>8764</v>
       </c>
     </row>
     <row r="1384">
       <c r="B1384" s="6" t="s">
-        <v>8763</v>
+        <v>8765</v>
       </c>
       <c r="C1384" s="6" t="s">
-        <v>8764</v>
+        <v>8766</v>
       </c>
       <c r="D1384" s="6" t="s">
-        <v>8765</v>
+        <v>8767</v>
       </c>
       <c r="E1384" s="6" t="s">
-        <v>8766</v>
+        <v>8768</v>
       </c>
       <c r="F1384" s="6" t="s">
-        <v>8767</v>
+        <v>8769</v>
       </c>
       <c r="G1384" s="6" t="s">
-        <v>8768</v>
+        <v>8770</v>
       </c>
       <c r="H1384" s="6" t="s">
-        <v>8769</v>
+        <v>8771</v>
       </c>
     </row>
     <row r="1385">
       <c r="B1385" s="5" t="s">
-        <v>8770</v>
+        <v>8772</v>
       </c>
       <c r="C1385" s="5" t="s">
-        <v>8771</v>
+        <v>8773</v>
       </c>
       <c r="D1385" s="5" t="s">
-        <v>8772</v>
+        <v>8774</v>
       </c>
       <c r="E1385" s="5" t="s">
-        <v>8773</v>
+        <v>8775</v>
       </c>
       <c r="F1385" s="5" t="s">
-        <v>8774</v>
+        <v>8693</v>
       </c>
       <c r="G1385" s="5" t="s">
-        <v>8775</v>
+        <v>8694</v>
       </c>
       <c r="H1385" s="5" t="s">
         <v>8776</v>
@@ -61028,142 +61070,142 @@
         <v>8781</v>
       </c>
       <c r="G1386" s="6" t="s">
-        <v>8781</v>
+        <v>8782</v>
       </c>
       <c r="H1386" s="6" t="s">
-        <v>8782</v>
+        <v>8783</v>
       </c>
     </row>
     <row r="1387">
       <c r="B1387" s="5" t="s">
-        <v>8783</v>
+        <v>8784</v>
       </c>
       <c r="C1387" s="5" t="s">
-        <v>8784</v>
+        <v>8785</v>
       </c>
       <c r="D1387" s="5" t="s">
-        <v>8785</v>
+        <v>8786</v>
       </c>
       <c r="E1387" s="5" t="s">
-        <v>8786</v>
+        <v>8787</v>
       </c>
       <c r="F1387" s="5" t="s">
-        <v>8787</v>
+        <v>8788</v>
       </c>
       <c r="G1387" s="5" t="s">
-        <v>8788</v>
+        <v>8789</v>
       </c>
       <c r="H1387" s="5" t="s">
-        <v>8789</v>
+        <v>8790</v>
       </c>
     </row>
     <row r="1388">
       <c r="B1388" s="6" t="s">
-        <v>8790</v>
+        <v>8791</v>
       </c>
       <c r="C1388" s="6" t="s">
-        <v>8791</v>
+        <v>8792</v>
       </c>
       <c r="D1388" s="6" t="s">
-        <v>8792</v>
+        <v>8793</v>
       </c>
       <c r="E1388" s="6" t="s">
-        <v>8793</v>
+        <v>8794</v>
       </c>
       <c r="F1388" s="6" t="s">
-        <v>8794</v>
+        <v>8795</v>
       </c>
       <c r="G1388" s="6" t="s">
-        <v>8794</v>
+        <v>8795</v>
       </c>
       <c r="H1388" s="6" t="s">
-        <v>8795</v>
+        <v>8796</v>
       </c>
     </row>
     <row r="1389">
       <c r="B1389" s="5" t="s">
-        <v>8796</v>
+        <v>8797</v>
       </c>
       <c r="C1389" s="5" t="s">
-        <v>6781</v>
+        <v>8798</v>
       </c>
       <c r="D1389" s="5" t="s">
-        <v>8797</v>
+        <v>8799</v>
       </c>
       <c r="E1389" s="5" t="s">
-        <v>6783</v>
+        <v>8800</v>
       </c>
       <c r="F1389" s="5" t="s">
-        <v>6784</v>
+        <v>8801</v>
       </c>
       <c r="G1389" s="5" t="s">
-        <v>6785</v>
+        <v>8802</v>
       </c>
       <c r="H1389" s="5" t="s">
-        <v>6786</v>
+        <v>8803</v>
       </c>
     </row>
     <row r="1390">
       <c r="B1390" s="6" t="s">
-        <v>8798</v>
+        <v>8804</v>
       </c>
       <c r="C1390" s="6" t="s">
-        <v>8799</v>
+        <v>8805</v>
       </c>
       <c r="D1390" s="6" t="s">
-        <v>8800</v>
+        <v>8806</v>
       </c>
       <c r="E1390" s="6" t="s">
-        <v>8801</v>
+        <v>8807</v>
       </c>
       <c r="F1390" s="6" t="s">
-        <v>8802</v>
+        <v>8808</v>
       </c>
       <c r="G1390" s="6" t="s">
-        <v>8802</v>
+        <v>8808</v>
       </c>
       <c r="H1390" s="6" t="s">
-        <v>8803</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="1391">
       <c r="B1391" s="5" t="s">
-        <v>8804</v>
+        <v>8810</v>
       </c>
       <c r="C1391" s="5" t="s">
-        <v>8805</v>
+        <v>6781</v>
       </c>
       <c r="D1391" s="5" t="s">
-        <v>8806</v>
+        <v>8811</v>
       </c>
       <c r="E1391" s="5" t="s">
-        <v>8807</v>
+        <v>6783</v>
       </c>
       <c r="F1391" s="5" t="s">
-        <v>8808</v>
+        <v>6784</v>
       </c>
       <c r="G1391" s="5" t="s">
-        <v>8809</v>
+        <v>6785</v>
       </c>
       <c r="H1391" s="5" t="s">
-        <v>8810</v>
+        <v>6786</v>
       </c>
     </row>
     <row r="1392">
       <c r="B1392" s="6" t="s">
-        <v>8811</v>
+        <v>8812</v>
       </c>
       <c r="C1392" s="6" t="s">
-        <v>8812</v>
+        <v>8813</v>
       </c>
       <c r="D1392" s="6" t="s">
-        <v>8813</v>
+        <v>8814</v>
       </c>
       <c r="E1392" s="6" t="s">
-        <v>8814</v>
+        <v>8815</v>
       </c>
       <c r="F1392" s="6" t="s">
-        <v>8815</v>
+        <v>8816</v>
       </c>
       <c r="G1392" s="6" t="s">
         <v>8816</v>
@@ -61189,50 +61231,50 @@
         <v>8822</v>
       </c>
       <c r="G1393" s="5" t="s">
-        <v>8822</v>
+        <v>8823</v>
       </c>
       <c r="H1393" s="5" t="s">
-        <v>8823</v>
+        <v>8824</v>
       </c>
     </row>
     <row r="1394">
       <c r="B1394" s="6" t="s">
-        <v>8824</v>
+        <v>8825</v>
       </c>
       <c r="C1394" s="6" t="s">
-        <v>8825</v>
+        <v>8826</v>
       </c>
       <c r="D1394" s="6" t="s">
-        <v>8826</v>
+        <v>8827</v>
       </c>
       <c r="E1394" s="6" t="s">
-        <v>8827</v>
+        <v>8828</v>
       </c>
       <c r="F1394" s="6" t="s">
-        <v>8828</v>
+        <v>8829</v>
       </c>
       <c r="G1394" s="6" t="s">
-        <v>8829</v>
+        <v>8830</v>
       </c>
       <c r="H1394" s="6" t="s">
-        <v>8830</v>
+        <v>8831</v>
       </c>
     </row>
     <row r="1395">
       <c r="B1395" s="5" t="s">
-        <v>8831</v>
+        <v>8832</v>
       </c>
       <c r="C1395" s="5" t="s">
-        <v>8832</v>
+        <v>8833</v>
       </c>
       <c r="D1395" s="5" t="s">
-        <v>8833</v>
+        <v>8834</v>
       </c>
       <c r="E1395" s="5" t="s">
-        <v>8834</v>
+        <v>8835</v>
       </c>
       <c r="F1395" s="5" t="s">
-        <v>8835</v>
+        <v>8836</v>
       </c>
       <c r="G1395" s="5" t="s">
         <v>8836</v>
@@ -61269,68 +61311,68 @@
         <v>8845</v>
       </c>
       <c r="C1397" s="5" t="s">
-        <v>8799</v>
+        <v>8846</v>
       </c>
       <c r="D1397" s="5" t="s">
-        <v>8800</v>
+        <v>8847</v>
       </c>
       <c r="E1397" s="5" t="s">
-        <v>8801</v>
+        <v>8848</v>
       </c>
       <c r="F1397" s="5" t="s">
-        <v>8802</v>
+        <v>8849</v>
       </c>
       <c r="G1397" s="5" t="s">
-        <v>8802</v>
+        <v>8850</v>
       </c>
       <c r="H1397" s="5" t="s">
-        <v>8803</v>
+        <v>8851</v>
       </c>
     </row>
     <row r="1398">
       <c r="B1398" s="6" t="s">
-        <v>8846</v>
+        <v>8852</v>
       </c>
       <c r="C1398" s="6" t="s">
-        <v>8847</v>
+        <v>8853</v>
       </c>
       <c r="D1398" s="6" t="s">
-        <v>8848</v>
+        <v>8854</v>
       </c>
       <c r="E1398" s="6" t="s">
-        <v>8849</v>
+        <v>8855</v>
       </c>
       <c r="F1398" s="6" t="s">
-        <v>8850</v>
+        <v>8856</v>
       </c>
       <c r="G1398" s="6" t="s">
-        <v>8851</v>
+        <v>8857</v>
       </c>
       <c r="H1398" s="6" t="s">
-        <v>8852</v>
+        <v>8858</v>
       </c>
     </row>
     <row r="1399">
       <c r="B1399" s="5" t="s">
-        <v>8853</v>
+        <v>8859</v>
       </c>
       <c r="C1399" s="5" t="s">
-        <v>8854</v>
+        <v>8813</v>
       </c>
       <c r="D1399" s="5" t="s">
-        <v>8855</v>
+        <v>8814</v>
       </c>
       <c r="E1399" s="5" t="s">
-        <v>8856</v>
+        <v>8815</v>
       </c>
       <c r="F1399" s="5" t="s">
-        <v>8857</v>
+        <v>8816</v>
       </c>
       <c r="G1399" s="5" t="s">
-        <v>8858</v>
+        <v>8816</v>
       </c>
       <c r="H1399" s="5" t="s">
-        <v>8859</v>
+        <v>8817</v>
       </c>
     </row>
     <row r="1400">
@@ -61430,134 +61472,134 @@
         <v>8888</v>
       </c>
       <c r="C1404" s="6" t="s">
-        <v>6895</v>
+        <v>8889</v>
       </c>
       <c r="D1404" s="6" t="s">
-        <v>8889</v>
+        <v>8890</v>
       </c>
       <c r="E1404" s="6" t="s">
-        <v>6897</v>
+        <v>8891</v>
       </c>
       <c r="F1404" s="6" t="s">
-        <v>8536</v>
+        <v>8892</v>
       </c>
       <c r="G1404" s="6" t="s">
-        <v>8537</v>
+        <v>8893</v>
       </c>
       <c r="H1404" s="6" t="s">
-        <v>8890</v>
+        <v>8894</v>
       </c>
     </row>
     <row r="1405">
       <c r="B1405" s="5" t="s">
-        <v>8891</v>
+        <v>8895</v>
       </c>
       <c r="C1405" s="5" t="s">
-        <v>6931</v>
+        <v>8896</v>
       </c>
       <c r="D1405" s="5" t="s">
-        <v>6832</v>
+        <v>8897</v>
       </c>
       <c r="E1405" s="5" t="s">
-        <v>6932</v>
+        <v>8898</v>
       </c>
       <c r="F1405" s="5" t="s">
-        <v>6933</v>
+        <v>8899</v>
       </c>
       <c r="G1405" s="5" t="s">
-        <v>6934</v>
+        <v>8900</v>
       </c>
       <c r="H1405" s="5" t="s">
-        <v>6832</v>
+        <v>8901</v>
       </c>
     </row>
     <row r="1406">
       <c r="B1406" s="6" t="s">
-        <v>8892</v>
+        <v>8902</v>
       </c>
       <c r="C1406" s="6" t="s">
-        <v>8512</v>
+        <v>6895</v>
       </c>
       <c r="D1406" s="6" t="s">
-        <v>8893</v>
+        <v>8903</v>
       </c>
       <c r="E1406" s="6" t="s">
-        <v>8514</v>
+        <v>6897</v>
       </c>
       <c r="F1406" s="6" t="s">
-        <v>8515</v>
+        <v>8550</v>
       </c>
       <c r="G1406" s="6" t="s">
-        <v>8516</v>
+        <v>8551</v>
       </c>
       <c r="H1406" s="6" t="s">
-        <v>8894</v>
+        <v>8904</v>
       </c>
     </row>
     <row r="1407">
       <c r="B1407" s="5" t="s">
-        <v>8895</v>
+        <v>8905</v>
       </c>
       <c r="C1407" s="5" t="s">
-        <v>8896</v>
+        <v>6931</v>
       </c>
       <c r="D1407" s="5" t="s">
-        <v>8897</v>
+        <v>6832</v>
       </c>
       <c r="E1407" s="5" t="s">
-        <v>8898</v>
+        <v>6932</v>
       </c>
       <c r="F1407" s="5" t="s">
-        <v>8899</v>
+        <v>6933</v>
       </c>
       <c r="G1407" s="5" t="s">
-        <v>8898</v>
+        <v>6934</v>
       </c>
       <c r="H1407" s="5" t="s">
-        <v>8900</v>
+        <v>6832</v>
       </c>
     </row>
     <row r="1408">
       <c r="B1408" s="6" t="s">
-        <v>8901</v>
+        <v>8906</v>
       </c>
       <c r="C1408" s="6" t="s">
-        <v>8902</v>
+        <v>8526</v>
       </c>
       <c r="D1408" s="6" t="s">
-        <v>8903</v>
+        <v>8907</v>
       </c>
       <c r="E1408" s="6" t="s">
-        <v>8904</v>
+        <v>8528</v>
       </c>
       <c r="F1408" s="6" t="s">
-        <v>8905</v>
+        <v>8529</v>
       </c>
       <c r="G1408" s="6" t="s">
-        <v>8906</v>
+        <v>8530</v>
       </c>
       <c r="H1408" s="6" t="s">
-        <v>8907</v>
+        <v>8908</v>
       </c>
     </row>
     <row r="1409">
       <c r="B1409" s="5" t="s">
-        <v>8908</v>
+        <v>8909</v>
       </c>
       <c r="C1409" s="5" t="s">
-        <v>8909</v>
+        <v>8910</v>
       </c>
       <c r="D1409" s="5" t="s">
-        <v>8910</v>
+        <v>8911</v>
       </c>
       <c r="E1409" s="5" t="s">
-        <v>8911</v>
+        <v>8912</v>
       </c>
       <c r="F1409" s="5" t="s">
+        <v>8913</v>
+      </c>
+      <c r="G1409" s="5" t="s">
         <v>8912</v>
-      </c>
-      <c r="G1409" s="5" t="s">
-        <v>8913</v>
       </c>
       <c r="H1409" s="5" t="s">
         <v>8914</v>
@@ -61620,53 +61662,53 @@
         <v>8931</v>
       </c>
       <c r="E1412" s="6" t="s">
-        <v>5453</v>
+        <v>8932</v>
       </c>
       <c r="F1412" s="6" t="s">
-        <v>8932</v>
+        <v>8933</v>
       </c>
       <c r="G1412" s="6" t="s">
-        <v>8933</v>
+        <v>8934</v>
       </c>
       <c r="H1412" s="6" t="s">
-        <v>8934</v>
+        <v>8935</v>
       </c>
     </row>
     <row r="1413">
       <c r="B1413" s="5" t="s">
-        <v>8935</v>
+        <v>8936</v>
       </c>
       <c r="C1413" s="5" t="s">
-        <v>8936</v>
+        <v>8937</v>
       </c>
       <c r="D1413" s="5" t="s">
-        <v>8937</v>
+        <v>8938</v>
       </c>
       <c r="E1413" s="5" t="s">
-        <v>8938</v>
+        <v>8939</v>
       </c>
       <c r="F1413" s="5" t="s">
-        <v>8939</v>
+        <v>8940</v>
       </c>
       <c r="G1413" s="5" t="s">
-        <v>8940</v>
+        <v>8941</v>
       </c>
       <c r="H1413" s="5" t="s">
-        <v>8941</v>
+        <v>8942</v>
       </c>
     </row>
     <row r="1414">
       <c r="B1414" s="6" t="s">
-        <v>8942</v>
+        <v>8943</v>
       </c>
       <c r="C1414" s="6" t="s">
-        <v>8943</v>
+        <v>8944</v>
       </c>
       <c r="D1414" s="6" t="s">
-        <v>8944</v>
+        <v>8945</v>
       </c>
       <c r="E1414" s="6" t="s">
-        <v>8945</v>
+        <v>5453</v>
       </c>
       <c r="F1414" s="6" t="s">
         <v>8946</v>
@@ -61728,138 +61770,138 @@
       <c r="B1417" s="5" t="s">
         <v>8963</v>
       </c>
-      <c r="C1417" s="7" t="s">
+      <c r="C1417" s="5" t="s">
         <v>8964</v>
       </c>
-      <c r="D1417" s="7" t="s">
-        <v>8964</v>
-      </c>
-      <c r="E1417" s="7" t="s">
-        <v>8964</v>
-      </c>
-      <c r="F1417" s="7" t="s">
-        <v>8964</v>
-      </c>
-      <c r="G1417" s="7" t="s">
-        <v>8964</v>
-      </c>
-      <c r="H1417" s="7" t="s">
-        <v>8964</v>
+      <c r="D1417" s="5" t="s">
+        <v>8965</v>
+      </c>
+      <c r="E1417" s="5" t="s">
+        <v>8966</v>
+      </c>
+      <c r="F1417" s="5" t="s">
+        <v>8967</v>
+      </c>
+      <c r="G1417" s="5" t="s">
+        <v>8968</v>
+      </c>
+      <c r="H1417" s="5" t="s">
+        <v>8969</v>
       </c>
     </row>
     <row r="1418">
       <c r="B1418" s="6" t="s">
-        <v>8965</v>
+        <v>8970</v>
       </c>
       <c r="C1418" s="6" t="s">
-        <v>8376</v>
+        <v>8971</v>
       </c>
       <c r="D1418" s="6" t="s">
-        <v>8377</v>
+        <v>8972</v>
       </c>
       <c r="E1418" s="6" t="s">
-        <v>8378</v>
+        <v>8973</v>
       </c>
       <c r="F1418" s="6" t="s">
-        <v>8379</v>
+        <v>8974</v>
       </c>
       <c r="G1418" s="6" t="s">
-        <v>8380</v>
+        <v>8975</v>
       </c>
       <c r="H1418" s="6" t="s">
-        <v>8377</v>
+        <v>8976</v>
       </c>
     </row>
     <row r="1419">
       <c r="B1419" s="5" t="s">
-        <v>8966</v>
-      </c>
-      <c r="C1419" s="5" t="s">
-        <v>8967</v>
-      </c>
-      <c r="D1419" s="5" t="s">
-        <v>8968</v>
-      </c>
-      <c r="E1419" s="5" t="s">
-        <v>8969</v>
-      </c>
-      <c r="F1419" s="5" t="s">
-        <v>8970</v>
-      </c>
-      <c r="G1419" s="5" t="s">
-        <v>8970</v>
-      </c>
-      <c r="H1419" s="5" t="s">
-        <v>8971</v>
+        <v>8977</v>
+      </c>
+      <c r="C1419" s="7" t="s">
+        <v>8978</v>
+      </c>
+      <c r="D1419" s="7" t="s">
+        <v>8978</v>
+      </c>
+      <c r="E1419" s="7" t="s">
+        <v>8978</v>
+      </c>
+      <c r="F1419" s="7" t="s">
+        <v>8978</v>
+      </c>
+      <c r="G1419" s="7" t="s">
+        <v>8978</v>
+      </c>
+      <c r="H1419" s="7" t="s">
+        <v>8978</v>
       </c>
     </row>
     <row r="1420">
       <c r="B1420" s="6" t="s">
-        <v>8972</v>
+        <v>8979</v>
       </c>
       <c r="C1420" s="6" t="s">
-        <v>8973</v>
+        <v>8390</v>
       </c>
       <c r="D1420" s="6" t="s">
-        <v>8974</v>
+        <v>8391</v>
       </c>
       <c r="E1420" s="6" t="s">
-        <v>8975</v>
+        <v>8392</v>
       </c>
       <c r="F1420" s="6" t="s">
-        <v>8976</v>
+        <v>8393</v>
       </c>
       <c r="G1420" s="6" t="s">
-        <v>8977</v>
+        <v>8394</v>
       </c>
       <c r="H1420" s="6" t="s">
-        <v>6117</v>
+        <v>8391</v>
       </c>
     </row>
     <row r="1421">
       <c r="B1421" s="5" t="s">
-        <v>8978</v>
+        <v>8980</v>
       </c>
       <c r="C1421" s="5" t="s">
-        <v>8979</v>
+        <v>8981</v>
       </c>
       <c r="D1421" s="5" t="s">
-        <v>8980</v>
+        <v>8982</v>
       </c>
       <c r="E1421" s="5" t="s">
-        <v>8981</v>
+        <v>8983</v>
       </c>
       <c r="F1421" s="5" t="s">
-        <v>8982</v>
+        <v>8984</v>
       </c>
       <c r="G1421" s="5" t="s">
-        <v>8983</v>
+        <v>8984</v>
       </c>
       <c r="H1421" s="5" t="s">
-        <v>8984</v>
+        <v>8985</v>
       </c>
     </row>
     <row r="1422">
       <c r="B1422" s="6" t="s">
-        <v>8985</v>
+        <v>8986</v>
       </c>
       <c r="C1422" s="6" t="s">
-        <v>8986</v>
+        <v>8987</v>
       </c>
       <c r="D1422" s="6" t="s">
-        <v>8987</v>
+        <v>8988</v>
       </c>
       <c r="E1422" s="6" t="s">
-        <v>8988</v>
+        <v>8989</v>
       </c>
       <c r="F1422" s="6" t="s">
-        <v>8989</v>
+        <v>8990</v>
       </c>
       <c r="G1422" s="6" t="s">
-        <v>8990</v>
+        <v>8991</v>
       </c>
       <c r="H1422" s="6" t="s">
-        <v>8991</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="1423">
@@ -61879,175 +61921,175 @@
         <v>8996</v>
       </c>
       <c r="G1423" s="5" t="s">
-        <v>8996</v>
+        <v>8997</v>
       </c>
       <c r="H1423" s="5" t="s">
-        <v>8997</v>
+        <v>8998</v>
       </c>
     </row>
     <row r="1424">
       <c r="B1424" s="6" t="s">
-        <v>8998</v>
+        <v>8999</v>
       </c>
       <c r="C1424" s="6" t="s">
-        <v>8999</v>
+        <v>9000</v>
       </c>
       <c r="D1424" s="6" t="s">
-        <v>9000</v>
+        <v>9001</v>
       </c>
       <c r="E1424" s="6" t="s">
-        <v>9001</v>
+        <v>9002</v>
       </c>
       <c r="F1424" s="6" t="s">
-        <v>9002</v>
+        <v>9003</v>
       </c>
       <c r="G1424" s="6" t="s">
-        <v>9003</v>
+        <v>9004</v>
       </c>
       <c r="H1424" s="6" t="s">
-        <v>9004</v>
+        <v>9005</v>
       </c>
     </row>
     <row r="1425">
       <c r="B1425" s="5" t="s">
-        <v>9005</v>
+        <v>9006</v>
       </c>
       <c r="C1425" s="5" t="s">
-        <v>9006</v>
+        <v>9007</v>
       </c>
       <c r="D1425" s="5" t="s">
-        <v>9007</v>
+        <v>9008</v>
       </c>
       <c r="E1425" s="5" t="s">
-        <v>9008</v>
+        <v>9009</v>
       </c>
       <c r="F1425" s="5" t="s">
-        <v>9009</v>
+        <v>9010</v>
       </c>
       <c r="G1425" s="5" t="s">
-        <v>9009</v>
+        <v>9010</v>
       </c>
       <c r="H1425" s="5" t="s">
-        <v>9010</v>
+        <v>9011</v>
       </c>
     </row>
     <row r="1426">
       <c r="B1426" s="6" t="s">
-        <v>9011</v>
+        <v>9012</v>
       </c>
       <c r="C1426" s="6" t="s">
-        <v>9012</v>
+        <v>9013</v>
       </c>
       <c r="D1426" s="6" t="s">
-        <v>9012</v>
+        <v>9014</v>
       </c>
       <c r="E1426" s="6" t="s">
-        <v>9012</v>
+        <v>9015</v>
       </c>
       <c r="F1426" s="6" t="s">
-        <v>9012</v>
+        <v>9016</v>
       </c>
       <c r="G1426" s="6" t="s">
-        <v>9012</v>
+        <v>9017</v>
       </c>
       <c r="H1426" s="6" t="s">
-        <v>9012</v>
+        <v>9018</v>
       </c>
     </row>
     <row r="1427">
       <c r="B1427" s="5" t="s">
-        <v>9013</v>
+        <v>9019</v>
       </c>
       <c r="C1427" s="5" t="s">
-        <v>9014</v>
+        <v>9020</v>
       </c>
       <c r="D1427" s="5" t="s">
-        <v>9015</v>
+        <v>9021</v>
       </c>
       <c r="E1427" s="5" t="s">
-        <v>9016</v>
+        <v>9022</v>
       </c>
       <c r="F1427" s="5" t="s">
-        <v>9017</v>
+        <v>9023</v>
       </c>
       <c r="G1427" s="5" t="s">
-        <v>9017</v>
+        <v>9023</v>
       </c>
       <c r="H1427" s="5" t="s">
-        <v>9018</v>
+        <v>9024</v>
       </c>
     </row>
     <row r="1428">
       <c r="B1428" s="6" t="s">
-        <v>9019</v>
+        <v>9025</v>
       </c>
       <c r="C1428" s="6" t="s">
-        <v>9012</v>
+        <v>9026</v>
       </c>
       <c r="D1428" s="6" t="s">
-        <v>9012</v>
+        <v>9026</v>
       </c>
       <c r="E1428" s="6" t="s">
-        <v>9012</v>
+        <v>9026</v>
       </c>
       <c r="F1428" s="6" t="s">
-        <v>9012</v>
+        <v>9026</v>
       </c>
       <c r="G1428" s="6" t="s">
-        <v>9012</v>
+        <v>9026</v>
       </c>
       <c r="H1428" s="6" t="s">
-        <v>9012</v>
+        <v>9026</v>
       </c>
     </row>
     <row r="1429">
       <c r="B1429" s="5" t="s">
-        <v>9020</v>
+        <v>9027</v>
+      </c>
+      <c r="C1429" s="5" t="s">
+        <v>9028</v>
+      </c>
+      <c r="D1429" s="5" t="s">
+        <v>9029</v>
+      </c>
+      <c r="E1429" s="5" t="s">
+        <v>9030</v>
+      </c>
+      <c r="F1429" s="5" t="s">
+        <v>9031</v>
+      </c>
+      <c r="G1429" s="5" t="s">
+        <v>9031</v>
+      </c>
+      <c r="H1429" s="5" t="s">
+        <v>9032</v>
       </c>
     </row>
     <row r="1430">
       <c r="B1430" s="6" t="s">
-        <v>9021</v>
+        <v>9033</v>
       </c>
       <c r="C1430" s="6" t="s">
-        <v>9022</v>
+        <v>9026</v>
       </c>
       <c r="D1430" s="6" t="s">
-        <v>9023</v>
+        <v>9026</v>
       </c>
       <c r="E1430" s="6" t="s">
-        <v>9024</v>
+        <v>9026</v>
       </c>
       <c r="F1430" s="6" t="s">
-        <v>9025</v>
+        <v>9026</v>
       </c>
       <c r="G1430" s="6" t="s">
         <v>9026</v>
       </c>
       <c r="H1430" s="6" t="s">
-        <v>9027</v>
+        <v>9026</v>
       </c>
     </row>
     <row r="1431">
       <c r="B1431" s="5" t="s">
-        <v>9028</v>
-      </c>
-      <c r="C1431" s="5" t="s">
-        <v>9029</v>
-      </c>
-      <c r="D1431" s="5" t="s">
-        <v>9030</v>
-      </c>
-      <c r="E1431" s="5" t="s">
-        <v>9031</v>
-      </c>
-      <c r="F1431" s="5" t="s">
-        <v>9032</v>
-      </c>
-      <c r="G1431" s="5" t="s">
-        <v>9033</v>
-      </c>
-      <c r="H1431" s="5" t="s">
         <v>9034</v>
       </c>
     </row>
@@ -62102,62 +62144,62 @@
         <v>9049</v>
       </c>
       <c r="C1434" s="6" t="s">
-        <v>6112</v>
+        <v>9050</v>
       </c>
       <c r="D1434" s="6" t="s">
-        <v>9050</v>
+        <v>9051</v>
       </c>
       <c r="E1434" s="6" t="s">
-        <v>6114</v>
+        <v>9052</v>
       </c>
       <c r="F1434" s="6" t="s">
-        <v>9051</v>
+        <v>9053</v>
       </c>
       <c r="G1434" s="6" t="s">
-        <v>9051</v>
+        <v>9054</v>
       </c>
       <c r="H1434" s="6" t="s">
-        <v>9052</v>
+        <v>9055</v>
       </c>
     </row>
     <row r="1435">
       <c r="B1435" s="5" t="s">
-        <v>9053</v>
+        <v>9056</v>
       </c>
       <c r="C1435" s="5" t="s">
-        <v>9054</v>
+        <v>9057</v>
       </c>
       <c r="D1435" s="5" t="s">
-        <v>9055</v>
+        <v>9058</v>
       </c>
       <c r="E1435" s="5" t="s">
-        <v>9056</v>
+        <v>9059</v>
       </c>
       <c r="F1435" s="5" t="s">
-        <v>9057</v>
+        <v>9060</v>
       </c>
       <c r="G1435" s="5" t="s">
-        <v>9058</v>
+        <v>9061</v>
       </c>
       <c r="H1435" s="5" t="s">
-        <v>9059</v>
+        <v>9062</v>
       </c>
     </row>
     <row r="1436">
       <c r="B1436" s="6" t="s">
-        <v>9060</v>
+        <v>9063</v>
       </c>
       <c r="C1436" s="6" t="s">
-        <v>9061</v>
+        <v>6112</v>
       </c>
       <c r="D1436" s="6" t="s">
-        <v>9062</v>
+        <v>9064</v>
       </c>
       <c r="E1436" s="6" t="s">
-        <v>9063</v>
+        <v>6114</v>
       </c>
       <c r="F1436" s="6" t="s">
-        <v>9064</v>
+        <v>9065</v>
       </c>
       <c r="G1436" s="6" t="s">
         <v>9065</v>
@@ -62243,82 +62285,82 @@
         <v>9089</v>
       </c>
       <c r="D1440" s="6" t="s">
-        <v>9089</v>
+        <v>9090</v>
       </c>
       <c r="E1440" s="6" t="s">
-        <v>9089</v>
+        <v>9091</v>
       </c>
       <c r="F1440" s="6" t="s">
-        <v>9089</v>
+        <v>9092</v>
       </c>
       <c r="G1440" s="6" t="s">
-        <v>9089</v>
+        <v>9093</v>
       </c>
       <c r="H1440" s="6" t="s">
-        <v>9089</v>
+        <v>9094</v>
       </c>
     </row>
     <row r="1441">
       <c r="B1441" s="5" t="s">
-        <v>9090</v>
+        <v>9095</v>
       </c>
       <c r="C1441" s="5" t="s">
-        <v>9091</v>
+        <v>9096</v>
       </c>
       <c r="D1441" s="5" t="s">
-        <v>9092</v>
+        <v>9097</v>
       </c>
       <c r="E1441" s="5" t="s">
-        <v>9093</v>
+        <v>9098</v>
       </c>
       <c r="F1441" s="5" t="s">
-        <v>9094</v>
+        <v>9099</v>
       </c>
       <c r="G1441" s="5" t="s">
-        <v>9094</v>
+        <v>9100</v>
       </c>
       <c r="H1441" s="5" t="s">
-        <v>9095</v>
+        <v>9101</v>
       </c>
     </row>
     <row r="1442">
       <c r="B1442" s="6" t="s">
-        <v>9096</v>
+        <v>9102</v>
       </c>
       <c r="C1442" s="6" t="s">
-        <v>9097</v>
+        <v>9103</v>
       </c>
       <c r="D1442" s="6" t="s">
-        <v>9098</v>
+        <v>9103</v>
       </c>
       <c r="E1442" s="6" t="s">
-        <v>9099</v>
+        <v>9103</v>
       </c>
       <c r="F1442" s="6" t="s">
-        <v>9100</v>
+        <v>9103</v>
       </c>
       <c r="G1442" s="6" t="s">
-        <v>9101</v>
+        <v>9103</v>
       </c>
       <c r="H1442" s="6" t="s">
-        <v>9102</v>
+        <v>9103</v>
       </c>
     </row>
     <row r="1443">
       <c r="B1443" s="5" t="s">
-        <v>9103</v>
+        <v>9104</v>
       </c>
       <c r="C1443" s="5" t="s">
-        <v>9104</v>
+        <v>9105</v>
       </c>
       <c r="D1443" s="5" t="s">
-        <v>9105</v>
+        <v>9106</v>
       </c>
       <c r="E1443" s="5" t="s">
-        <v>9106</v>
+        <v>9107</v>
       </c>
       <c r="F1443" s="5" t="s">
-        <v>9107</v>
+        <v>9108</v>
       </c>
       <c r="G1443" s="5" t="s">
         <v>9108</v>
@@ -62344,73 +62386,73 @@
         <v>9114</v>
       </c>
       <c r="G1444" s="6" t="s">
-        <v>9114</v>
+        <v>9115</v>
       </c>
       <c r="H1444" s="6" t="s">
-        <v>9115</v>
+        <v>9116</v>
       </c>
     </row>
     <row r="1445">
       <c r="B1445" s="5" t="s">
-        <v>9116</v>
+        <v>9117</v>
       </c>
       <c r="C1445" s="5" t="s">
-        <v>9117</v>
+        <v>9118</v>
       </c>
       <c r="D1445" s="5" t="s">
-        <v>9118</v>
+        <v>9119</v>
       </c>
       <c r="E1445" s="5" t="s">
-        <v>9119</v>
+        <v>9120</v>
       </c>
       <c r="F1445" s="5" t="s">
-        <v>9120</v>
+        <v>9121</v>
       </c>
       <c r="G1445" s="5" t="s">
-        <v>9120</v>
+        <v>9122</v>
       </c>
       <c r="H1445" s="5" t="s">
-        <v>9121</v>
+        <v>9123</v>
       </c>
     </row>
     <row r="1446">
       <c r="B1446" s="6" t="s">
-        <v>9122</v>
+        <v>9124</v>
       </c>
       <c r="C1446" s="6" t="s">
-        <v>9123</v>
+        <v>9125</v>
       </c>
       <c r="D1446" s="6" t="s">
-        <v>9124</v>
+        <v>9126</v>
       </c>
       <c r="E1446" s="6" t="s">
-        <v>9125</v>
+        <v>9127</v>
       </c>
       <c r="F1446" s="6" t="s">
-        <v>9126</v>
+        <v>9128</v>
       </c>
       <c r="G1446" s="6" t="s">
-        <v>9127</v>
+        <v>9128</v>
       </c>
       <c r="H1446" s="6" t="s">
-        <v>9128</v>
+        <v>9129</v>
       </c>
     </row>
     <row r="1447">
       <c r="B1447" s="5" t="s">
-        <v>9129</v>
+        <v>9130</v>
       </c>
       <c r="C1447" s="5" t="s">
-        <v>9130</v>
+        <v>9131</v>
       </c>
       <c r="D1447" s="5" t="s">
-        <v>9131</v>
+        <v>9132</v>
       </c>
       <c r="E1447" s="5" t="s">
-        <v>9132</v>
+        <v>9133</v>
       </c>
       <c r="F1447" s="5" t="s">
-        <v>9133</v>
+        <v>9134</v>
       </c>
       <c r="G1447" s="5" t="s">
         <v>9134</v>
@@ -62585,439 +62627,439 @@
         <v>9185</v>
       </c>
       <c r="C1455" s="5" t="s">
-        <v>4582</v>
+        <v>9186</v>
       </c>
       <c r="D1455" s="5" t="s">
-        <v>9186</v>
+        <v>9187</v>
       </c>
       <c r="E1455" s="5" t="s">
-        <v>4584</v>
+        <v>9188</v>
       </c>
       <c r="F1455" s="5" t="s">
-        <v>9187</v>
+        <v>9189</v>
       </c>
       <c r="G1455" s="5" t="s">
-        <v>9188</v>
+        <v>9190</v>
       </c>
       <c r="H1455" s="5" t="s">
-        <v>9189</v>
+        <v>9191</v>
       </c>
     </row>
     <row r="1456">
       <c r="B1456" s="6" t="s">
-        <v>9190</v>
+        <v>9192</v>
       </c>
       <c r="C1456" s="6" t="s">
-        <v>9191</v>
+        <v>9193</v>
       </c>
       <c r="D1456" s="6" t="s">
-        <v>9192</v>
+        <v>9194</v>
       </c>
       <c r="E1456" s="6" t="s">
-        <v>9193</v>
+        <v>9195</v>
       </c>
       <c r="F1456" s="6" t="s">
-        <v>9194</v>
+        <v>9196</v>
       </c>
       <c r="G1456" s="6" t="s">
-        <v>9195</v>
+        <v>9197</v>
       </c>
       <c r="H1456" s="6" t="s">
-        <v>9196</v>
+        <v>9198</v>
       </c>
     </row>
     <row r="1457">
       <c r="B1457" s="5" t="s">
-        <v>9197</v>
+        <v>9199</v>
       </c>
       <c r="C1457" s="5" t="s">
-        <v>9198</v>
+        <v>4582</v>
       </c>
       <c r="D1457" s="5" t="s">
-        <v>9199</v>
+        <v>9200</v>
+      </c>
+      <c r="E1457" s="5" t="s">
+        <v>4584</v>
+      </c>
+      <c r="F1457" s="5" t="s">
+        <v>9201</v>
+      </c>
+      <c r="G1457" s="5" t="s">
+        <v>9202</v>
+      </c>
+      <c r="H1457" s="5" t="s">
+        <v>9203</v>
       </c>
     </row>
     <row r="1458">
       <c r="B1458" s="6" t="s">
-        <v>9200</v>
+        <v>9204</v>
       </c>
       <c r="C1458" s="6" t="s">
-        <v>9201</v>
+        <v>9205</v>
       </c>
       <c r="D1458" s="6" t="s">
-        <v>9202</v>
+        <v>9206</v>
+      </c>
+      <c r="E1458" s="6" t="s">
+        <v>9207</v>
+      </c>
+      <c r="F1458" s="6" t="s">
+        <v>9208</v>
+      </c>
+      <c r="G1458" s="6" t="s">
+        <v>9209</v>
+      </c>
+      <c r="H1458" s="6" t="s">
+        <v>9210</v>
       </c>
     </row>
     <row r="1459">
       <c r="B1459" s="5" t="s">
-        <v>9203</v>
+        <v>9211</v>
       </c>
       <c r="C1459" s="5" t="s">
-        <v>9204</v>
+        <v>9212</v>
       </c>
       <c r="D1459" s="5" t="s">
-        <v>9205</v>
+        <v>9213</v>
       </c>
     </row>
     <row r="1460">
       <c r="B1460" s="6" t="s">
-        <v>9206</v>
+        <v>9214</v>
       </c>
       <c r="C1460" s="6" t="s">
-        <v>9207</v>
+        <v>9215</v>
       </c>
       <c r="D1460" s="6" t="s">
-        <v>9208</v>
+        <v>9216</v>
       </c>
     </row>
     <row r="1461">
       <c r="B1461" s="5" t="s">
-        <v>9209</v>
+        <v>9217</v>
       </c>
       <c r="C1461" s="5" t="s">
-        <v>9210</v>
+        <v>9218</v>
       </c>
       <c r="D1461" s="5" t="s">
-        <v>9211</v>
+        <v>9219</v>
       </c>
     </row>
     <row r="1462">
       <c r="B1462" s="6" t="s">
-        <v>9212</v>
+        <v>9220</v>
       </c>
       <c r="C1462" s="6" t="s">
-        <v>9213</v>
+        <v>9221</v>
       </c>
       <c r="D1462" s="6" t="s">
-        <v>9214</v>
+        <v>9222</v>
       </c>
     </row>
     <row r="1463">
       <c r="B1463" s="5" t="s">
-        <v>9215</v>
+        <v>9223</v>
       </c>
       <c r="C1463" s="5" t="s">
-        <v>9216</v>
+        <v>9224</v>
       </c>
       <c r="D1463" s="5" t="s">
-        <v>9217</v>
+        <v>9225</v>
       </c>
     </row>
     <row r="1464">
       <c r="B1464" s="6" t="s">
-        <v>9218</v>
+        <v>9226</v>
       </c>
       <c r="C1464" s="6" t="s">
-        <v>9219</v>
+        <v>9227</v>
       </c>
       <c r="D1464" s="6" t="s">
-        <v>9220</v>
-      </c>
-      <c r="E1464" s="6" t="s">
-        <v>9221</v>
-      </c>
-      <c r="F1464" s="6" t="s">
-        <v>9222</v>
-      </c>
-      <c r="G1464" s="6" t="s">
-        <v>9223</v>
-      </c>
-      <c r="H1464" s="6" t="s">
-        <v>9224</v>
+        <v>9228</v>
       </c>
     </row>
     <row r="1465">
       <c r="B1465" s="5" t="s">
-        <v>9225</v>
+        <v>9229</v>
       </c>
       <c r="C1465" s="5" t="s">
-        <v>9226</v>
+        <v>9230</v>
       </c>
       <c r="D1465" s="5" t="s">
-        <v>9227</v>
+        <v>9231</v>
       </c>
     </row>
     <row r="1466">
       <c r="B1466" s="6" t="s">
-        <v>9228</v>
+        <v>9232</v>
       </c>
       <c r="C1466" s="6" t="s">
-        <v>9229</v>
+        <v>9233</v>
       </c>
       <c r="D1466" s="6" t="s">
-        <v>9230</v>
+        <v>9234</v>
+      </c>
+      <c r="E1466" s="6" t="s">
+        <v>9235</v>
+      </c>
+      <c r="F1466" s="6" t="s">
+        <v>9236</v>
+      </c>
+      <c r="G1466" s="6" t="s">
+        <v>9237</v>
+      </c>
+      <c r="H1466" s="6" t="s">
+        <v>9238</v>
       </c>
     </row>
     <row r="1467">
       <c r="B1467" s="5" t="s">
-        <v>9231</v>
+        <v>9239</v>
       </c>
       <c r="C1467" s="5" t="s">
-        <v>9232</v>
+        <v>9240</v>
       </c>
       <c r="D1467" s="5" t="s">
-        <v>9233</v>
+        <v>9241</v>
       </c>
     </row>
     <row r="1468">
       <c r="B1468" s="6" t="s">
-        <v>9234</v>
+        <v>9242</v>
       </c>
       <c r="C1468" s="6" t="s">
-        <v>6112</v>
+        <v>9243</v>
       </c>
       <c r="D1468" s="6" t="s">
-        <v>9050</v>
+        <v>9244</v>
       </c>
     </row>
     <row r="1469">
       <c r="B1469" s="5" t="s">
-        <v>9235</v>
+        <v>9245</v>
       </c>
       <c r="C1469" s="5" t="s">
-        <v>9236</v>
+        <v>9246</v>
       </c>
       <c r="D1469" s="5" t="s">
-        <v>9237</v>
+        <v>9247</v>
       </c>
     </row>
     <row r="1470">
       <c r="B1470" s="6" t="s">
-        <v>9238</v>
+        <v>9248</v>
       </c>
       <c r="C1470" s="6" t="s">
-        <v>9239</v>
+        <v>6112</v>
       </c>
       <c r="D1470" s="6" t="s">
-        <v>9240</v>
+        <v>9064</v>
       </c>
     </row>
     <row r="1471">
       <c r="B1471" s="5" t="s">
-        <v>9241</v>
+        <v>9249</v>
       </c>
       <c r="C1471" s="5" t="s">
-        <v>9242</v>
+        <v>9250</v>
       </c>
       <c r="D1471" s="5" t="s">
-        <v>9243</v>
+        <v>9251</v>
       </c>
     </row>
     <row r="1472">
       <c r="B1472" s="6" t="s">
-        <v>9244</v>
+        <v>9252</v>
       </c>
       <c r="C1472" s="6" t="s">
-        <v>9245</v>
+        <v>9253</v>
       </c>
       <c r="D1472" s="6" t="s">
-        <v>9246</v>
+        <v>9254</v>
       </c>
     </row>
     <row r="1473">
       <c r="B1473" s="5" t="s">
-        <v>9247</v>
+        <v>9255</v>
       </c>
       <c r="C1473" s="5" t="s">
-        <v>9248</v>
+        <v>9256</v>
       </c>
       <c r="D1473" s="5" t="s">
-        <v>9249</v>
+        <v>9257</v>
       </c>
     </row>
     <row r="1474">
       <c r="B1474" s="6" t="s">
-        <v>9250</v>
+        <v>9258</v>
       </c>
       <c r="C1474" s="6" t="s">
-        <v>9251</v>
+        <v>9259</v>
       </c>
       <c r="D1474" s="6" t="s">
-        <v>9252</v>
+        <v>9260</v>
       </c>
     </row>
     <row r="1475">
       <c r="B1475" s="5" t="s">
-        <v>9253</v>
+        <v>9261</v>
       </c>
       <c r="C1475" s="5" t="s">
-        <v>9254</v>
+        <v>9262</v>
       </c>
       <c r="D1475" s="5" t="s">
-        <v>9255</v>
-      </c>
-      <c r="E1475" s="5" t="s">
-        <v>9256</v>
-      </c>
-      <c r="F1475" s="5" t="s">
-        <v>9257</v>
-      </c>
-      <c r="G1475" s="5" t="s">
-        <v>9257</v>
-      </c>
-      <c r="H1475" s="5" t="s">
-        <v>9258</v>
+        <v>9263</v>
       </c>
     </row>
     <row r="1476">
       <c r="B1476" s="6" t="s">
-        <v>9259</v>
+        <v>9264</v>
       </c>
       <c r="C1476" s="6" t="s">
-        <v>9260</v>
+        <v>9265</v>
       </c>
       <c r="D1476" s="6" t="s">
-        <v>9261</v>
-      </c>
-      <c r="E1476" s="6" t="s">
-        <v>9262</v>
-      </c>
-      <c r="F1476" s="6" t="s">
-        <v>9263</v>
-      </c>
-      <c r="G1476" s="6" t="s">
-        <v>9262</v>
-      </c>
-      <c r="H1476" s="6" t="s">
-        <v>9264</v>
+        <v>9266</v>
       </c>
     </row>
     <row r="1477">
       <c r="B1477" s="5" t="s">
-        <v>9265</v>
+        <v>9267</v>
       </c>
       <c r="C1477" s="5" t="s">
-        <v>9266</v>
+        <v>9268</v>
       </c>
       <c r="D1477" s="5" t="s">
-        <v>9267</v>
+        <v>9269</v>
       </c>
       <c r="E1477" s="5" t="s">
-        <v>7899</v>
+        <v>9270</v>
       </c>
       <c r="F1477" s="5" t="s">
-        <v>7900</v>
+        <v>9271</v>
       </c>
       <c r="G1477" s="5" t="s">
-        <v>7900</v>
+        <v>9271</v>
       </c>
       <c r="H1477" s="5" t="s">
-        <v>7901</v>
+        <v>9272</v>
       </c>
     </row>
     <row r="1478">
       <c r="B1478" s="6" t="s">
-        <v>9268</v>
+        <v>9273</v>
       </c>
       <c r="C1478" s="6" t="s">
-        <v>9269</v>
+        <v>9274</v>
       </c>
       <c r="D1478" s="6" t="s">
-        <v>9270</v>
+        <v>9275</v>
       </c>
       <c r="E1478" s="6" t="s">
-        <v>9271</v>
+        <v>9276</v>
       </c>
       <c r="F1478" s="6" t="s">
-        <v>9272</v>
+        <v>9277</v>
       </c>
       <c r="G1478" s="6" t="s">
-        <v>9272</v>
+        <v>9276</v>
       </c>
       <c r="H1478" s="6" t="s">
-        <v>9273</v>
+        <v>9278</v>
       </c>
     </row>
     <row r="1479">
       <c r="B1479" s="5" t="s">
-        <v>9274</v>
+        <v>9279</v>
       </c>
       <c r="C1479" s="5" t="s">
-        <v>9275</v>
+        <v>9280</v>
       </c>
       <c r="D1479" s="5" t="s">
-        <v>8903</v>
+        <v>9281</v>
       </c>
       <c r="E1479" s="5" t="s">
-        <v>9276</v>
+        <v>7913</v>
       </c>
       <c r="F1479" s="5" t="s">
-        <v>9277</v>
+        <v>7914</v>
       </c>
       <c r="G1479" s="5" t="s">
-        <v>9277</v>
+        <v>7914</v>
       </c>
       <c r="H1479" s="5" t="s">
-        <v>8907</v>
+        <v>7915</v>
       </c>
     </row>
     <row r="1480">
       <c r="B1480" s="6" t="s">
-        <v>9278</v>
+        <v>9282</v>
       </c>
       <c r="C1480" s="6" t="s">
-        <v>9279</v>
+        <v>9283</v>
       </c>
       <c r="D1480" s="6" t="s">
-        <v>7245</v>
+        <v>9284</v>
       </c>
       <c r="E1480" s="6" t="s">
-        <v>5935</v>
+        <v>9285</v>
       </c>
       <c r="F1480" s="6" t="s">
-        <v>9280</v>
+        <v>9286</v>
       </c>
       <c r="G1480" s="6" t="s">
-        <v>9280</v>
+        <v>9286</v>
       </c>
       <c r="H1480" s="6" t="s">
-        <v>5938</v>
+        <v>9287</v>
       </c>
     </row>
     <row r="1481">
       <c r="B1481" s="5" t="s">
-        <v>9281</v>
+        <v>9288</v>
       </c>
       <c r="C1481" s="5" t="s">
-        <v>9282</v>
+        <v>9289</v>
       </c>
       <c r="D1481" s="5" t="s">
-        <v>9283</v>
+        <v>8917</v>
       </c>
       <c r="E1481" s="5" t="s">
-        <v>9284</v>
+        <v>9290</v>
       </c>
       <c r="F1481" s="5" t="s">
-        <v>9285</v>
+        <v>9291</v>
       </c>
       <c r="G1481" s="5" t="s">
-        <v>9286</v>
+        <v>9291</v>
       </c>
       <c r="H1481" s="5" t="s">
-        <v>9287</v>
+        <v>8921</v>
       </c>
     </row>
     <row r="1482">
       <c r="B1482" s="6" t="s">
-        <v>9288</v>
+        <v>9292</v>
       </c>
       <c r="C1482" s="6" t="s">
-        <v>9289</v>
+        <v>9293</v>
       </c>
       <c r="D1482" s="6" t="s">
-        <v>9290</v>
+        <v>7245</v>
       </c>
       <c r="E1482" s="6" t="s">
-        <v>9291</v>
+        <v>5935</v>
       </c>
       <c r="F1482" s="6" t="s">
-        <v>9292</v>
+        <v>9294</v>
       </c>
       <c r="G1482" s="6" t="s">
-        <v>9293</v>
+        <v>9294</v>
       </c>
       <c r="H1482" s="6" t="s">
-        <v>9294</v>
+        <v>5938</v>
       </c>
     </row>
     <row r="1483">
@@ -63037,50 +63079,50 @@
         <v>9299</v>
       </c>
       <c r="G1483" s="5" t="s">
-        <v>9299</v>
+        <v>9300</v>
       </c>
       <c r="H1483" s="5" t="s">
-        <v>9300</v>
+        <v>9301</v>
       </c>
     </row>
     <row r="1484">
       <c r="B1484" s="6" t="s">
-        <v>9301</v>
+        <v>9302</v>
       </c>
       <c r="C1484" s="6" t="s">
-        <v>9302</v>
+        <v>9303</v>
       </c>
       <c r="D1484" s="6" t="s">
-        <v>9303</v>
+        <v>9304</v>
       </c>
       <c r="E1484" s="6" t="s">
-        <v>9304</v>
+        <v>9305</v>
       </c>
       <c r="F1484" s="6" t="s">
-        <v>9305</v>
+        <v>9306</v>
       </c>
       <c r="G1484" s="6" t="s">
-        <v>9306</v>
+        <v>9307</v>
       </c>
       <c r="H1484" s="6" t="s">
-        <v>9307</v>
+        <v>9308</v>
       </c>
     </row>
     <row r="1485">
       <c r="B1485" s="5" t="s">
-        <v>9308</v>
+        <v>9309</v>
       </c>
       <c r="C1485" s="5" t="s">
-        <v>9309</v>
+        <v>9310</v>
       </c>
       <c r="D1485" s="5" t="s">
-        <v>9310</v>
+        <v>9311</v>
       </c>
       <c r="E1485" s="5" t="s">
-        <v>9311</v>
+        <v>9312</v>
       </c>
       <c r="F1485" s="5" t="s">
-        <v>9312</v>
+        <v>9313</v>
       </c>
       <c r="G1485" s="5" t="s">
         <v>9313</v>
@@ -63140,85 +63182,85 @@
         <v>9329</v>
       </c>
       <c r="C1488" s="6" t="s">
-        <v>4537</v>
+        <v>9330</v>
       </c>
       <c r="D1488" s="6" t="s">
-        <v>9330</v>
+        <v>9331</v>
       </c>
       <c r="E1488" s="6" t="s">
-        <v>7438</v>
+        <v>9332</v>
       </c>
       <c r="F1488" s="6" t="s">
-        <v>9331</v>
+        <v>9333</v>
       </c>
       <c r="G1488" s="6" t="s">
-        <v>9332</v>
+        <v>9334</v>
       </c>
       <c r="H1488" s="6" t="s">
-        <v>7435</v>
+        <v>9335</v>
       </c>
     </row>
     <row r="1489">
       <c r="B1489" s="5" t="s">
-        <v>9333</v>
+        <v>9336</v>
       </c>
       <c r="C1489" s="5" t="s">
-        <v>9334</v>
+        <v>9337</v>
       </c>
       <c r="D1489" s="5" t="s">
-        <v>9335</v>
+        <v>9338</v>
       </c>
       <c r="E1489" s="5" t="s">
-        <v>9336</v>
+        <v>9339</v>
       </c>
       <c r="F1489" s="5" t="s">
-        <v>9337</v>
+        <v>9340</v>
       </c>
       <c r="G1489" s="5" t="s">
-        <v>9337</v>
+        <v>9341</v>
       </c>
       <c r="H1489" s="5" t="s">
-        <v>9338</v>
+        <v>9342</v>
       </c>
     </row>
     <row r="1490">
       <c r="B1490" s="6" t="s">
-        <v>9339</v>
+        <v>9343</v>
       </c>
       <c r="C1490" s="6" t="s">
-        <v>9340</v>
+        <v>4537</v>
       </c>
       <c r="D1490" s="6" t="s">
-        <v>9341</v>
+        <v>9344</v>
       </c>
       <c r="E1490" s="6" t="s">
-        <v>9342</v>
+        <v>7438</v>
       </c>
       <c r="F1490" s="6" t="s">
-        <v>9343</v>
+        <v>9345</v>
       </c>
       <c r="G1490" s="6" t="s">
-        <v>9344</v>
+        <v>9346</v>
       </c>
       <c r="H1490" s="6" t="s">
-        <v>9345</v>
+        <v>7435</v>
       </c>
     </row>
     <row r="1491">
       <c r="B1491" s="5" t="s">
-        <v>9346</v>
+        <v>9347</v>
       </c>
       <c r="C1491" s="5" t="s">
-        <v>9347</v>
+        <v>9348</v>
       </c>
       <c r="D1491" s="5" t="s">
-        <v>9348</v>
+        <v>9349</v>
       </c>
       <c r="E1491" s="5" t="s">
-        <v>9349</v>
+        <v>9350</v>
       </c>
       <c r="F1491" s="5" t="s">
-        <v>9350</v>
+        <v>9351</v>
       </c>
       <c r="G1491" s="5" t="s">
         <v>9351</v>
@@ -63290,171 +63332,171 @@
         <v>9371</v>
       </c>
       <c r="G1494" s="6" t="s">
-        <v>9371</v>
+        <v>9372</v>
       </c>
       <c r="H1494" s="6" t="s">
-        <v>9372</v>
+        <v>9373</v>
       </c>
     </row>
     <row r="1495">
       <c r="B1495" s="5" t="s">
-        <v>9373</v>
+        <v>9374</v>
       </c>
       <c r="C1495" s="5" t="s">
-        <v>9374</v>
+        <v>9375</v>
       </c>
       <c r="D1495" s="5" t="s">
-        <v>9375</v>
+        <v>9376</v>
       </c>
       <c r="E1495" s="5" t="s">
-        <v>9376</v>
+        <v>9377</v>
       </c>
       <c r="F1495" s="5" t="s">
-        <v>9377</v>
+        <v>9378</v>
       </c>
       <c r="G1495" s="5" t="s">
-        <v>9377</v>
+        <v>9379</v>
       </c>
       <c r="H1495" s="5" t="s">
-        <v>4535</v>
+        <v>9380</v>
       </c>
     </row>
     <row r="1496">
       <c r="B1496" s="6" t="s">
-        <v>9378</v>
+        <v>9381</v>
       </c>
       <c r="C1496" s="6" t="s">
-        <v>9379</v>
+        <v>9382</v>
       </c>
       <c r="D1496" s="6" t="s">
-        <v>9380</v>
+        <v>9383</v>
       </c>
       <c r="E1496" s="6" t="s">
-        <v>9381</v>
+        <v>9384</v>
       </c>
       <c r="F1496" s="6" t="s">
-        <v>9382</v>
+        <v>9385</v>
       </c>
       <c r="G1496" s="6" t="s">
-        <v>9383</v>
+        <v>9385</v>
       </c>
       <c r="H1496" s="6" t="s">
-        <v>8549</v>
+        <v>9386</v>
       </c>
     </row>
     <row r="1497">
       <c r="B1497" s="5" t="s">
-        <v>9384</v>
+        <v>9387</v>
       </c>
       <c r="C1497" s="5" t="s">
-        <v>9385</v>
+        <v>9388</v>
       </c>
       <c r="D1497" s="5" t="s">
-        <v>6775</v>
+        <v>9389</v>
       </c>
       <c r="E1497" s="5" t="s">
-        <v>6776</v>
+        <v>9390</v>
       </c>
       <c r="F1497" s="5" t="s">
-        <v>9386</v>
+        <v>9391</v>
       </c>
       <c r="G1497" s="5" t="s">
-        <v>9386</v>
+        <v>9391</v>
       </c>
       <c r="H1497" s="5" t="s">
-        <v>9387</v>
+        <v>4535</v>
       </c>
     </row>
     <row r="1498">
       <c r="B1498" s="6" t="s">
-        <v>9388</v>
+        <v>9392</v>
       </c>
       <c r="C1498" s="6" t="s">
-        <v>9389</v>
+        <v>9393</v>
       </c>
       <c r="D1498" s="6" t="s">
-        <v>9390</v>
+        <v>9394</v>
       </c>
       <c r="E1498" s="6" t="s">
-        <v>9391</v>
+        <v>9395</v>
       </c>
       <c r="F1498" s="6" t="s">
-        <v>9392</v>
+        <v>9396</v>
       </c>
       <c r="G1498" s="6" t="s">
-        <v>9393</v>
+        <v>9397</v>
       </c>
       <c r="H1498" s="6" t="s">
-        <v>9394</v>
+        <v>8563</v>
       </c>
     </row>
     <row r="1499">
       <c r="B1499" s="5" t="s">
-        <v>9395</v>
+        <v>9398</v>
       </c>
       <c r="C1499" s="5" t="s">
-        <v>8512</v>
+        <v>9399</v>
       </c>
       <c r="D1499" s="5" t="s">
-        <v>8893</v>
+        <v>6775</v>
       </c>
       <c r="E1499" s="5" t="s">
-        <v>8514</v>
+        <v>6776</v>
       </c>
       <c r="F1499" s="5" t="s">
-        <v>8515</v>
+        <v>9400</v>
       </c>
       <c r="G1499" s="5" t="s">
-        <v>8516</v>
+        <v>9400</v>
       </c>
       <c r="H1499" s="5" t="s">
-        <v>8894</v>
+        <v>9401</v>
       </c>
     </row>
     <row r="1500">
       <c r="B1500" s="6" t="s">
-        <v>9396</v>
+        <v>9402</v>
       </c>
       <c r="C1500" s="6" t="s">
-        <v>9397</v>
+        <v>9403</v>
       </c>
       <c r="D1500" s="6" t="s">
-        <v>9398</v>
+        <v>9404</v>
       </c>
       <c r="E1500" s="6" t="s">
-        <v>9399</v>
+        <v>9405</v>
       </c>
       <c r="F1500" s="6" t="s">
-        <v>9400</v>
+        <v>9406</v>
       </c>
       <c r="G1500" s="6" t="s">
-        <v>9401</v>
+        <v>9407</v>
       </c>
       <c r="H1500" s="6" t="s">
-        <v>9402</v>
+        <v>9408</v>
       </c>
     </row>
     <row r="1501">
       <c r="B1501" s="5" t="s">
-        <v>9403</v>
+        <v>9409</v>
       </c>
       <c r="C1501" s="5" t="s">
-        <v>9404</v>
+        <v>8526</v>
       </c>
       <c r="D1501" s="5" t="s">
-        <v>9405</v>
+        <v>8907</v>
       </c>
       <c r="E1501" s="5" t="s">
-        <v>9406</v>
+        <v>8528</v>
       </c>
       <c r="F1501" s="5" t="s">
-        <v>9407</v>
+        <v>8529</v>
       </c>
       <c r="G1501" s="5" t="s">
-        <v>9408</v>
+        <v>8530</v>
       </c>
       <c r="H1501" s="5" t="s">
-        <v>9409</v>
+        <v>8908</v>
       </c>
     </row>
     <row r="1502">
@@ -63462,125 +63504,125 @@
         <v>9410</v>
       </c>
       <c r="C1502" s="6" t="s">
-        <v>6915</v>
+        <v>9411</v>
       </c>
       <c r="D1502" s="6" t="s">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="E1502" s="6" t="s">
-        <v>6917</v>
+        <v>9413</v>
       </c>
       <c r="F1502" s="6" t="s">
-        <v>6918</v>
+        <v>9414</v>
       </c>
       <c r="G1502" s="6" t="s">
-        <v>6918</v>
+        <v>9415</v>
       </c>
       <c r="H1502" s="6" t="s">
-        <v>9412</v>
+        <v>9416</v>
       </c>
     </row>
     <row r="1503">
       <c r="B1503" s="5" t="s">
-        <v>9413</v>
+        <v>9417</v>
       </c>
       <c r="C1503" s="5" t="s">
-        <v>7399</v>
+        <v>9418</v>
       </c>
       <c r="D1503" s="5" t="s">
-        <v>9414</v>
+        <v>9419</v>
       </c>
       <c r="E1503" s="5" t="s">
-        <v>7401</v>
+        <v>9420</v>
       </c>
       <c r="F1503" s="5" t="s">
-        <v>7402</v>
+        <v>9421</v>
       </c>
       <c r="G1503" s="5" t="s">
-        <v>7402</v>
+        <v>9422</v>
       </c>
       <c r="H1503" s="5" t="s">
-        <v>9415</v>
+        <v>9423</v>
       </c>
     </row>
     <row r="1504">
       <c r="B1504" s="6" t="s">
-        <v>9416</v>
+        <v>9424</v>
       </c>
       <c r="C1504" s="6" t="s">
-        <v>9417</v>
+        <v>6915</v>
       </c>
       <c r="D1504" s="6" t="s">
-        <v>9418</v>
+        <v>9425</v>
       </c>
       <c r="E1504" s="6" t="s">
-        <v>9391</v>
+        <v>6917</v>
       </c>
       <c r="F1504" s="6" t="s">
-        <v>9419</v>
+        <v>6918</v>
       </c>
       <c r="G1504" s="6" t="s">
-        <v>9420</v>
+        <v>6918</v>
       </c>
       <c r="H1504" s="6" t="s">
-        <v>9421</v>
+        <v>9426</v>
       </c>
     </row>
     <row r="1505">
       <c r="B1505" s="5" t="s">
-        <v>9422</v>
+        <v>9427</v>
       </c>
       <c r="C1505" s="5" t="s">
-        <v>7240</v>
+        <v>7399</v>
       </c>
       <c r="D1505" s="5" t="s">
-        <v>6794</v>
+        <v>9428</v>
       </c>
       <c r="E1505" s="5" t="s">
-        <v>9423</v>
+        <v>7401</v>
       </c>
       <c r="F1505" s="5" t="s">
-        <v>9424</v>
+        <v>7402</v>
       </c>
       <c r="G1505" s="5" t="s">
-        <v>9425</v>
+        <v>7402</v>
       </c>
       <c r="H1505" s="5" t="s">
-        <v>9426</v>
+        <v>9429</v>
       </c>
     </row>
     <row r="1506">
       <c r="B1506" s="6" t="s">
-        <v>9427</v>
+        <v>9430</v>
       </c>
       <c r="C1506" s="6" t="s">
-        <v>9428</v>
+        <v>9431</v>
       </c>
       <c r="D1506" s="6" t="s">
-        <v>9429</v>
+        <v>9432</v>
       </c>
       <c r="E1506" s="6" t="s">
-        <v>9430</v>
+        <v>9405</v>
       </c>
       <c r="F1506" s="6" t="s">
-        <v>9431</v>
+        <v>9433</v>
       </c>
       <c r="G1506" s="6" t="s">
-        <v>9432</v>
+        <v>9434</v>
       </c>
       <c r="H1506" s="6" t="s">
-        <v>9433</v>
+        <v>9435</v>
       </c>
     </row>
     <row r="1507">
       <c r="B1507" s="5" t="s">
-        <v>9434</v>
+        <v>9436</v>
       </c>
       <c r="C1507" s="5" t="s">
-        <v>9435</v>
+        <v>7240</v>
       </c>
       <c r="D1507" s="5" t="s">
-        <v>9436</v>
+        <v>6794</v>
       </c>
       <c r="E1507" s="5" t="s">
         <v>9437</v>
@@ -63727,73 +63769,73 @@
         <v>9480</v>
       </c>
       <c r="G1513" s="5" t="s">
-        <v>9480</v>
+        <v>9481</v>
       </c>
       <c r="H1513" s="5" t="s">
-        <v>9481</v>
+        <v>9482</v>
       </c>
     </row>
     <row r="1514">
       <c r="B1514" s="6" t="s">
-        <v>9482</v>
+        <v>9483</v>
       </c>
       <c r="C1514" s="6" t="s">
-        <v>9483</v>
+        <v>9484</v>
       </c>
       <c r="D1514" s="6" t="s">
-        <v>9484</v>
+        <v>9485</v>
       </c>
       <c r="E1514" s="6" t="s">
-        <v>9485</v>
+        <v>9486</v>
       </c>
       <c r="F1514" s="6" t="s">
-        <v>9486</v>
+        <v>9487</v>
       </c>
       <c r="G1514" s="6" t="s">
-        <v>9486</v>
+        <v>9488</v>
       </c>
       <c r="H1514" s="6" t="s">
-        <v>9487</v>
+        <v>9489</v>
       </c>
     </row>
     <row r="1515">
       <c r="B1515" s="5" t="s">
-        <v>9488</v>
+        <v>9490</v>
       </c>
       <c r="C1515" s="5" t="s">
-        <v>9489</v>
+        <v>9491</v>
       </c>
       <c r="D1515" s="5" t="s">
-        <v>9490</v>
+        <v>9492</v>
       </c>
       <c r="E1515" s="5" t="s">
-        <v>9491</v>
+        <v>9493</v>
       </c>
       <c r="F1515" s="5" t="s">
-        <v>9492</v>
+        <v>9494</v>
       </c>
       <c r="G1515" s="5" t="s">
-        <v>9493</v>
+        <v>9494</v>
       </c>
       <c r="H1515" s="5" t="s">
-        <v>9494</v>
+        <v>9495</v>
       </c>
     </row>
     <row r="1516">
       <c r="B1516" s="6" t="s">
-        <v>9495</v>
+        <v>9496</v>
       </c>
       <c r="C1516" s="6" t="s">
-        <v>9496</v>
+        <v>9497</v>
       </c>
       <c r="D1516" s="6" t="s">
-        <v>9497</v>
+        <v>9498</v>
       </c>
       <c r="E1516" s="6" t="s">
-        <v>9498</v>
+        <v>9499</v>
       </c>
       <c r="F1516" s="6" t="s">
-        <v>9499</v>
+        <v>9500</v>
       </c>
       <c r="G1516" s="6" t="s">
         <v>9500</v>
@@ -63879,88 +63921,88 @@
         <v>9524</v>
       </c>
       <c r="D1520" s="6" t="s">
-        <v>8579</v>
+        <v>9525</v>
       </c>
       <c r="E1520" s="6" t="s">
-        <v>9525</v>
+        <v>9526</v>
       </c>
       <c r="F1520" s="6" t="s">
-        <v>7741</v>
+        <v>9527</v>
       </c>
       <c r="G1520" s="6" t="s">
-        <v>7742</v>
+        <v>9528</v>
       </c>
       <c r="H1520" s="6" t="s">
-        <v>9526</v>
+        <v>9529</v>
       </c>
     </row>
     <row r="1521">
       <c r="B1521" s="5" t="s">
-        <v>9527</v>
+        <v>9530</v>
       </c>
       <c r="C1521" s="5" t="s">
-        <v>9528</v>
+        <v>9531</v>
       </c>
       <c r="D1521" s="5" t="s">
-        <v>8584</v>
+        <v>9532</v>
       </c>
       <c r="E1521" s="5" t="s">
-        <v>7276</v>
+        <v>9533</v>
       </c>
       <c r="F1521" s="5" t="s">
-        <v>8586</v>
+        <v>9534</v>
       </c>
       <c r="G1521" s="5" t="s">
-        <v>8587</v>
+        <v>9535</v>
       </c>
       <c r="H1521" s="5" t="s">
-        <v>8588</v>
+        <v>9536</v>
       </c>
     </row>
     <row r="1522">
       <c r="B1522" s="6" t="s">
-        <v>9529</v>
+        <v>9537</v>
       </c>
       <c r="C1522" s="6" t="s">
-        <v>9530</v>
+        <v>9538</v>
       </c>
       <c r="D1522" s="6" t="s">
-        <v>9531</v>
+        <v>8593</v>
       </c>
       <c r="E1522" s="6" t="s">
-        <v>9532</v>
+        <v>9539</v>
       </c>
       <c r="F1522" s="6" t="s">
-        <v>9533</v>
+        <v>7755</v>
       </c>
       <c r="G1522" s="6" t="s">
-        <v>9534</v>
+        <v>7756</v>
       </c>
       <c r="H1522" s="6" t="s">
-        <v>9535</v>
+        <v>9540</v>
       </c>
     </row>
     <row r="1523">
       <c r="B1523" s="5" t="s">
-        <v>9536</v>
+        <v>9541</v>
       </c>
       <c r="C1523" s="5" t="s">
-        <v>9537</v>
+        <v>9542</v>
       </c>
       <c r="D1523" s="5" t="s">
-        <v>9538</v>
+        <v>8598</v>
       </c>
       <c r="E1523" s="5" t="s">
-        <v>9539</v>
+        <v>7276</v>
       </c>
       <c r="F1523" s="5" t="s">
-        <v>9540</v>
+        <v>8600</v>
       </c>
       <c r="G1523" s="5" t="s">
-        <v>9541</v>
+        <v>8601</v>
       </c>
       <c r="H1523" s="5" t="s">
-        <v>9542</v>
+        <v>8602</v>
       </c>
     </row>
     <row r="1524">
@@ -64003,61 +64045,61 @@
         <v>9554</v>
       </c>
       <c r="G1525" s="5" t="s">
-        <v>9554</v>
+        <v>9555</v>
       </c>
       <c r="H1525" s="5" t="s">
-        <v>9555</v>
+        <v>9556</v>
       </c>
     </row>
     <row r="1526">
       <c r="B1526" s="6" t="s">
-        <v>9556</v>
+        <v>9557</v>
       </c>
       <c r="C1526" s="6" t="s">
-        <v>9551</v>
+        <v>9558</v>
       </c>
       <c r="D1526" s="6" t="s">
-        <v>9552</v>
+        <v>9559</v>
       </c>
       <c r="E1526" s="6" t="s">
-        <v>9553</v>
+        <v>9560</v>
       </c>
       <c r="F1526" s="6" t="s">
-        <v>9554</v>
+        <v>9561</v>
       </c>
       <c r="G1526" s="6" t="s">
-        <v>9554</v>
+        <v>9562</v>
       </c>
       <c r="H1526" s="6" t="s">
-        <v>9555</v>
+        <v>9563</v>
       </c>
     </row>
     <row r="1527">
       <c r="B1527" s="5" t="s">
-        <v>9557</v>
+        <v>9564</v>
       </c>
       <c r="C1527" s="5" t="s">
-        <v>9558</v>
+        <v>9565</v>
       </c>
       <c r="D1527" s="5" t="s">
-        <v>9559</v>
+        <v>9566</v>
       </c>
       <c r="E1527" s="5" t="s">
-        <v>9560</v>
+        <v>9567</v>
       </c>
       <c r="F1527" s="5" t="s">
-        <v>9561</v>
+        <v>9568</v>
       </c>
       <c r="G1527" s="5" t="s">
-        <v>9562</v>
+        <v>9568</v>
       </c>
       <c r="H1527" s="5" t="s">
-        <v>9563</v>
+        <v>9569</v>
       </c>
     </row>
     <row r="1528">
       <c r="B1528" s="6" t="s">
-        <v>9564</v>
+        <v>9570</v>
       </c>
       <c r="C1528" s="6" t="s">
         <v>9565</v>
@@ -64072,10 +64114,10 @@
         <v>9568</v>
       </c>
       <c r="G1528" s="6" t="s">
+        <v>9568</v>
+      </c>
+      <c r="H1528" s="6" t="s">
         <v>9569</v>
-      </c>
-      <c r="H1528" s="6" t="s">
-        <v>9570</v>
       </c>
     </row>
     <row r="1529">
@@ -64095,221 +64137,267 @@
         <v>9575</v>
       </c>
       <c r="G1529" s="5" t="s">
-        <v>9575</v>
+        <v>9576</v>
       </c>
       <c r="H1529" s="5" t="s">
-        <v>9576</v>
+        <v>9577</v>
       </c>
     </row>
     <row r="1530">
       <c r="B1530" s="6" t="s">
-        <v>9577</v>
+        <v>9578</v>
       </c>
       <c r="C1530" s="6" t="s">
-        <v>6033</v>
+        <v>9579</v>
       </c>
       <c r="D1530" s="6" t="s">
-        <v>5404</v>
+        <v>9580</v>
       </c>
       <c r="E1530" s="6" t="s">
-        <v>6035</v>
+        <v>9581</v>
       </c>
       <c r="F1530" s="6" t="s">
-        <v>8321</v>
+        <v>9582</v>
       </c>
       <c r="G1530" s="6" t="s">
-        <v>8321</v>
+        <v>9583</v>
       </c>
       <c r="H1530" s="6" t="s">
-        <v>5404</v>
+        <v>9584</v>
       </c>
     </row>
     <row r="1531">
       <c r="B1531" s="5" t="s">
-        <v>9578</v>
+        <v>9585</v>
       </c>
       <c r="C1531" s="5" t="s">
-        <v>6087</v>
+        <v>9586</v>
       </c>
       <c r="D1531" s="5" t="s">
-        <v>9579</v>
+        <v>9587</v>
       </c>
       <c r="E1531" s="5" t="s">
-        <v>6089</v>
+        <v>9588</v>
       </c>
       <c r="F1531" s="5" t="s">
-        <v>6090</v>
+        <v>9589</v>
       </c>
       <c r="G1531" s="5" t="s">
-        <v>6089</v>
+        <v>9589</v>
       </c>
       <c r="H1531" s="5" t="s">
-        <v>6091</v>
+        <v>9590</v>
       </c>
     </row>
     <row r="1532">
       <c r="B1532" s="6" t="s">
-        <v>9580</v>
+        <v>9591</v>
       </c>
       <c r="C1532" s="6" t="s">
-        <v>6093</v>
+        <v>6033</v>
       </c>
       <c r="D1532" s="6" t="s">
-        <v>9581</v>
+        <v>5404</v>
       </c>
       <c r="E1532" s="6" t="s">
-        <v>6095</v>
+        <v>6035</v>
       </c>
       <c r="F1532" s="6" t="s">
-        <v>9582</v>
+        <v>8335</v>
       </c>
       <c r="G1532" s="6" t="s">
-        <v>9583</v>
+        <v>8335</v>
       </c>
       <c r="H1532" s="6" t="s">
-        <v>6098</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1533">
       <c r="B1533" s="5" t="s">
-        <v>9584</v>
+        <v>9592</v>
       </c>
       <c r="C1533" s="5" t="s">
-        <v>6100</v>
+        <v>6087</v>
       </c>
       <c r="D1533" s="5" t="s">
-        <v>6104</v>
+        <v>9593</v>
       </c>
       <c r="E1533" s="5" t="s">
-        <v>6102</v>
+        <v>6089</v>
       </c>
       <c r="F1533" s="5" t="s">
-        <v>6103</v>
+        <v>6090</v>
       </c>
       <c r="G1533" s="5" t="s">
-        <v>6103</v>
+        <v>6089</v>
       </c>
       <c r="H1533" s="5" t="s">
-        <v>6104</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="1534">
       <c r="B1534" s="6" t="s">
-        <v>9585</v>
+        <v>9594</v>
       </c>
       <c r="C1534" s="6" t="s">
-        <v>6890</v>
+        <v>6093</v>
       </c>
       <c r="D1534" s="6" t="s">
-        <v>6944</v>
+        <v>9595</v>
       </c>
       <c r="E1534" s="6" t="s">
-        <v>6892</v>
+        <v>6095</v>
       </c>
       <c r="F1534" s="6" t="s">
-        <v>6893</v>
+        <v>9596</v>
       </c>
       <c r="G1534" s="6" t="s">
-        <v>6893</v>
+        <v>9597</v>
       </c>
       <c r="H1534" s="6" t="s">
-        <v>6944</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="1535">
       <c r="B1535" s="5" t="s">
-        <v>9586</v>
+        <v>9598</v>
       </c>
       <c r="C1535" s="5" t="s">
-        <v>7349</v>
+        <v>6100</v>
       </c>
       <c r="D1535" s="5" t="s">
-        <v>7350</v>
+        <v>6104</v>
       </c>
       <c r="E1535" s="5" t="s">
-        <v>7351</v>
+        <v>6102</v>
       </c>
       <c r="F1535" s="5" t="s">
-        <v>7350</v>
+        <v>6103</v>
       </c>
       <c r="G1535" s="5" t="s">
-        <v>7350</v>
+        <v>6103</v>
       </c>
       <c r="H1535" s="5" t="s">
-        <v>7350</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="1536">
       <c r="B1536" s="6" t="s">
-        <v>9587</v>
+        <v>9599</v>
       </c>
       <c r="C1536" s="6" t="s">
-        <v>6895</v>
+        <v>6890</v>
       </c>
       <c r="D1536" s="6" t="s">
-        <v>8889</v>
+        <v>6944</v>
       </c>
       <c r="E1536" s="6" t="s">
-        <v>6897</v>
+        <v>6892</v>
       </c>
       <c r="F1536" s="6" t="s">
-        <v>6533</v>
+        <v>6893</v>
       </c>
       <c r="G1536" s="6" t="s">
-        <v>6533</v>
+        <v>6893</v>
       </c>
       <c r="H1536" s="6" t="s">
-        <v>8890</v>
+        <v>6944</v>
       </c>
     </row>
     <row r="1537">
       <c r="B1537" s="5" t="s">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="C1537" s="5" t="s">
-        <v>9589</v>
+        <v>7349</v>
       </c>
       <c r="D1537" s="5" t="s">
-        <v>9590</v>
+        <v>7350</v>
       </c>
       <c r="E1537" s="5" t="s">
-        <v>9591</v>
+        <v>7351</v>
       </c>
       <c r="F1537" s="5" t="s">
-        <v>9592</v>
+        <v>7350</v>
       </c>
       <c r="G1537" s="5" t="s">
-        <v>9593</v>
+        <v>7350</v>
       </c>
       <c r="H1537" s="5" t="s">
-        <v>9594</v>
+        <v>7350</v>
       </c>
     </row>
     <row r="1538">
       <c r="B1538" s="6" t="s">
-        <v>9595</v>
+        <v>9601</v>
       </c>
       <c r="C1538" s="6" t="s">
-        <v>9596</v>
+        <v>6895</v>
       </c>
       <c r="D1538" s="6" t="s">
-        <v>9597</v>
+        <v>8903</v>
       </c>
       <c r="E1538" s="6" t="s">
-        <v>9598</v>
+        <v>6897</v>
       </c>
       <c r="F1538" s="6" t="s">
-        <v>9599</v>
+        <v>6533</v>
       </c>
       <c r="G1538" s="6" t="s">
-        <v>9600</v>
+        <v>6533</v>
       </c>
       <c r="H1538" s="6" t="s">
-        <v>9601</v>
+        <v>8904</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="B1539" s="5" t="s">
+        <v>9602</v>
+      </c>
+      <c r="C1539" s="5" t="s">
+        <v>9603</v>
+      </c>
+      <c r="D1539" s="5" t="s">
+        <v>9604</v>
+      </c>
+      <c r="E1539" s="5" t="s">
+        <v>9605</v>
+      </c>
+      <c r="F1539" s="5" t="s">
+        <v>9606</v>
+      </c>
+      <c r="G1539" s="5" t="s">
+        <v>9607</v>
+      </c>
+      <c r="H1539" s="5" t="s">
+        <v>9608</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="B1540" s="6" t="s">
+        <v>9609</v>
+      </c>
+      <c r="C1540" s="6" t="s">
+        <v>9610</v>
+      </c>
+      <c r="D1540" s="6" t="s">
+        <v>9611</v>
+      </c>
+      <c r="E1540" s="6" t="s">
+        <v>9612</v>
+      </c>
+      <c r="F1540" s="6" t="s">
+        <v>9613</v>
+      </c>
+      <c r="G1540" s="6" t="s">
+        <v>9614</v>
+      </c>
+      <c r="H1540" s="6" t="s">
+        <v>9615</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H1538"/>
+  <autoFilter ref="B2:H1540"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -64328,10 +64416,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9602</v>
+        <v>9616</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9603</v>
+        <v>9617</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -64342,16 +64430,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9604</v>
+        <v>9618</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9605</v>
+        <v>9619</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9606</v>
+        <v>9620</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9607</v>
+        <v>9621</v>
       </c>
     </row>
     <row r="3">
@@ -64359,16 +64447,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9608</v>
+        <v>9622</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9609</v>
+        <v>9623</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>9610</v>
+        <v>9624</v>
       </c>
     </row>
     <row r="4">
@@ -64379,24 +64467,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9611</v>
+        <v>9625</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9612</v>
+        <v>9626</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>9613</v>
+        <v>9627</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>9614</v>
+        <v>9628</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4569</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>9615</v>
+        <v>9629</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -64404,13 +64492,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>9616</v>
+        <v>9630</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4576</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>9617</v>
+        <v>9631</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -64418,13 +64506,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>9618</v>
+        <v>9632</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4582</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>9619</v>
+        <v>9633</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -64432,13 +64520,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>9620</v>
+        <v>9634</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4588</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9621</v>
+        <v>9635</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -64446,13 +64534,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>9622</v>
+        <v>9636</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4595</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>9623</v>
+        <v>9637</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -64460,13 +64548,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>9624</v>
+        <v>9638</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4602</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>9625</v>
+        <v>9639</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -64474,13 +64562,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>9626</v>
+        <v>9640</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4608</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>9627</v>
+        <v>9641</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -64488,13 +64576,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>9628</v>
+        <v>9642</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4614</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>9629</v>
+        <v>9643</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -64502,13 +64590,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>9630</v>
+        <v>9644</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4621</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>9631</v>
+        <v>9645</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -64516,13 +64604,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>9632</v>
+        <v>9646</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4627</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>9633</v>
+        <v>9647</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -64536,7 +64624,7 @@
         <v>4633</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>9634</v>
+        <v>9648</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -64544,13 +64632,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>9635</v>
+        <v>9649</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4640</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>9636</v>
+        <v>9650</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -64558,13 +64646,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>9637</v>
+        <v>9651</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4647</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>9638</v>
+        <v>9652</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -64572,13 +64660,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>9639</v>
+        <v>9653</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4653</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>9640</v>
+        <v>9654</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -64586,13 +64674,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>9641</v>
+        <v>9655</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4660</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>9642</v>
+        <v>9656</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -64600,13 +64688,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>9643</v>
+        <v>9657</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4666</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>9644</v>
+        <v>9658</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -64614,13 +64702,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>9645</v>
+        <v>9659</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4671</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>9646</v>
+        <v>9660</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -64628,13 +64716,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>9647</v>
+        <v>9661</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4678</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>9648</v>
+        <v>9662</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -64642,13 +64730,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>9649</v>
+        <v>9663</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4500</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>9650</v>
+        <v>9664</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -64656,13 +64744,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>9651</v>
+        <v>9665</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4686</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>9652</v>
+        <v>9666</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1540]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1548]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10769" uniqueCount="9667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10825" uniqueCount="9722">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -28865,6 +28865,171 @@
   </si>
   <si>
     <t xml:space="preserve">Schließe den Tab in deinem Browser.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.button.give_up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">내놓는다 +${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give up +${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手放す +${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">放弃 +${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">放棄 +${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abgeben +${n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.focus.pick_joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위 줄에서 내놓을 조커를 누르십시오. 누른 것 밑의 단추가 내놓습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap a Joker in the row above; the button under it gives it up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上の列から手放すジョーカーを押してください。下のボタンで手放します</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击上方一排中要放弃的小丑牌，其下方按钮确认放弃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">點擊上方一排中要放棄的小丑牌，其下方按鈕確認放棄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tippe oben einen Joker an; der Knopf darunter gibt ihn ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.focus.pick_item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위 줄에서 내놓을 소모품을 누르십시오. 누른 것 밑의 단추가 내놓습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap a consumable in the row above; the button under it gives it up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上の列から手放す消費アイテムを押してください。下のボタンで手放します</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击上方一排中要放弃的消耗品，其下方按钮确认放弃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">點擊上方一排中要放棄的消耗品，其下方按鈕確認放棄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tippe oben einen Verbrauchsgegenstand an; der Knopf darunter gibt ihn ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.focus.cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그만둔다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never mind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">やめる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">算了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doch nicht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.badge.next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음은 {name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next: {name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">次は {name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下一个：{name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下一個：{name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als Nächstes: {name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.badge.next_target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">요구 점수 {n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target {n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要求スコア {n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要求分数 {n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要求分數 {n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ziel {n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.badge.pack_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마음에 안 들면 건너뜁니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skip it if you would rather not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">気に入らなければスキップします</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不满意可以跳过</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不滿意可以跳過</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Überspringen, wenn nichts passt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.badge.pick_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판 위에서 이 블라인드를 고르거나 건너뜁니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick this blind on the table, or skip it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盤上でこのブラインドを選ぶかスキップします</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在牌桌上选择此盲注或跳过</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在牌桌上選擇此盲注或跳過</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wähle diesen Blind auf dem Tisch oder überspringe ihn</t>
   </si>
   <si>
     <t xml:space="preserve">:table Achievement(key=achievement_id)</t>
@@ -29226,7 +29391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1540"/>
+  <dimension ref="A1:H1548"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -64396,8 +64561,192 @@
         <v>9615</v>
       </c>
     </row>
+    <row r="1541">
+      <c r="B1541" s="5" t="s">
+        <v>9616</v>
+      </c>
+      <c r="C1541" s="5" t="s">
+        <v>9617</v>
+      </c>
+      <c r="D1541" s="5" t="s">
+        <v>9618</v>
+      </c>
+      <c r="E1541" s="5" t="s">
+        <v>9619</v>
+      </c>
+      <c r="F1541" s="5" t="s">
+        <v>9620</v>
+      </c>
+      <c r="G1541" s="5" t="s">
+        <v>9621</v>
+      </c>
+      <c r="H1541" s="5" t="s">
+        <v>9622</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="B1542" s="6" t="s">
+        <v>9623</v>
+      </c>
+      <c r="C1542" s="6" t="s">
+        <v>9624</v>
+      </c>
+      <c r="D1542" s="6" t="s">
+        <v>9625</v>
+      </c>
+      <c r="E1542" s="6" t="s">
+        <v>9626</v>
+      </c>
+      <c r="F1542" s="6" t="s">
+        <v>9627</v>
+      </c>
+      <c r="G1542" s="6" t="s">
+        <v>9628</v>
+      </c>
+      <c r="H1542" s="6" t="s">
+        <v>9629</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="B1543" s="5" t="s">
+        <v>9630</v>
+      </c>
+      <c r="C1543" s="5" t="s">
+        <v>9631</v>
+      </c>
+      <c r="D1543" s="5" t="s">
+        <v>9632</v>
+      </c>
+      <c r="E1543" s="5" t="s">
+        <v>9633</v>
+      </c>
+      <c r="F1543" s="5" t="s">
+        <v>9634</v>
+      </c>
+      <c r="G1543" s="5" t="s">
+        <v>9635</v>
+      </c>
+      <c r="H1543" s="5" t="s">
+        <v>9636</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="B1544" s="6" t="s">
+        <v>9637</v>
+      </c>
+      <c r="C1544" s="6" t="s">
+        <v>9638</v>
+      </c>
+      <c r="D1544" s="6" t="s">
+        <v>9639</v>
+      </c>
+      <c r="E1544" s="6" t="s">
+        <v>9640</v>
+      </c>
+      <c r="F1544" s="6" t="s">
+        <v>9641</v>
+      </c>
+      <c r="G1544" s="6" t="s">
+        <v>9641</v>
+      </c>
+      <c r="H1544" s="6" t="s">
+        <v>9642</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="B1545" s="5" t="s">
+        <v>9643</v>
+      </c>
+      <c r="C1545" s="5" t="s">
+        <v>9644</v>
+      </c>
+      <c r="D1545" s="5" t="s">
+        <v>9645</v>
+      </c>
+      <c r="E1545" s="5" t="s">
+        <v>9646</v>
+      </c>
+      <c r="F1545" s="5" t="s">
+        <v>9647</v>
+      </c>
+      <c r="G1545" s="5" t="s">
+        <v>9648</v>
+      </c>
+      <c r="H1545" s="5" t="s">
+        <v>9649</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="B1546" s="6" t="s">
+        <v>9650</v>
+      </c>
+      <c r="C1546" s="6" t="s">
+        <v>9651</v>
+      </c>
+      <c r="D1546" s="6" t="s">
+        <v>9652</v>
+      </c>
+      <c r="E1546" s="6" t="s">
+        <v>9653</v>
+      </c>
+      <c r="F1546" s="6" t="s">
+        <v>9654</v>
+      </c>
+      <c r="G1546" s="6" t="s">
+        <v>9655</v>
+      </c>
+      <c r="H1546" s="6" t="s">
+        <v>9656</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="B1547" s="5" t="s">
+        <v>9657</v>
+      </c>
+      <c r="C1547" s="5" t="s">
+        <v>9658</v>
+      </c>
+      <c r="D1547" s="5" t="s">
+        <v>9659</v>
+      </c>
+      <c r="E1547" s="5" t="s">
+        <v>9660</v>
+      </c>
+      <c r="F1547" s="5" t="s">
+        <v>9661</v>
+      </c>
+      <c r="G1547" s="5" t="s">
+        <v>9662</v>
+      </c>
+      <c r="H1547" s="5" t="s">
+        <v>9663</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="B1548" s="6" t="s">
+        <v>9664</v>
+      </c>
+      <c r="C1548" s="6" t="s">
+        <v>9665</v>
+      </c>
+      <c r="D1548" s="6" t="s">
+        <v>9666</v>
+      </c>
+      <c r="E1548" s="6" t="s">
+        <v>9667</v>
+      </c>
+      <c r="F1548" s="6" t="s">
+        <v>9668</v>
+      </c>
+      <c r="G1548" s="6" t="s">
+        <v>9669</v>
+      </c>
+      <c r="H1548" s="6" t="s">
+        <v>9670</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H1540"/>
+  <autoFilter ref="B2:H1548"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -64416,10 +64765,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9616</v>
+        <v>9671</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9617</v>
+        <v>9672</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -64430,16 +64779,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9618</v>
+        <v>9673</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9619</v>
+        <v>9674</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9620</v>
+        <v>9675</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9621</v>
+        <v>9676</v>
       </c>
     </row>
     <row r="3">
@@ -64447,16 +64796,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9622</v>
+        <v>9677</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9623</v>
+        <v>9678</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>9624</v>
+        <v>9679</v>
       </c>
     </row>
     <row r="4">
@@ -64467,24 +64816,24 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9625</v>
+        <v>9680</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9626</v>
+        <v>9681</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>9627</v>
+        <v>9682</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>9628</v>
+        <v>9683</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4569</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>9629</v>
+        <v>9684</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -64492,13 +64841,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>9630</v>
+        <v>9685</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4576</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>9631</v>
+        <v>9686</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -64506,13 +64855,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>9632</v>
+        <v>9687</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4582</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>9633</v>
+        <v>9688</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -64520,13 +64869,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>9634</v>
+        <v>9689</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4588</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9635</v>
+        <v>9690</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -64534,13 +64883,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>9636</v>
+        <v>9691</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4595</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>9637</v>
+        <v>9692</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -64548,13 +64897,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>9638</v>
+        <v>9693</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4602</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>9639</v>
+        <v>9694</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -64562,13 +64911,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>9640</v>
+        <v>9695</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4608</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>9641</v>
+        <v>9696</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -64576,13 +64925,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>9642</v>
+        <v>9697</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4614</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>9643</v>
+        <v>9698</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -64590,13 +64939,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>9644</v>
+        <v>9699</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4621</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>9645</v>
+        <v>9700</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -64604,13 +64953,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>9646</v>
+        <v>9701</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4627</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>9647</v>
+        <v>9702</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -64624,7 +64973,7 @@
         <v>4633</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>9648</v>
+        <v>9703</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -64632,13 +64981,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>9649</v>
+        <v>9704</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4640</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>9650</v>
+        <v>9705</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -64646,13 +64995,13 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>9651</v>
+        <v>9706</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4647</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>9652</v>
+        <v>9707</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
@@ -64660,13 +65009,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>9653</v>
+        <v>9708</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4653</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>9654</v>
+        <v>9709</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
@@ -64674,13 +65023,13 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>9655</v>
+        <v>9710</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4660</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>9656</v>
+        <v>9711</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -64688,13 +65037,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>9657</v>
+        <v>9712</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4666</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>9658</v>
+        <v>9713</v>
       </c>
       <c r="E20" s="6">
         <v>16</v>
@@ -64702,13 +65051,13 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>9659</v>
+        <v>9714</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4671</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>9660</v>
+        <v>9715</v>
       </c>
       <c r="E21" s="5">
         <v>17</v>
@@ -64716,13 +65065,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>9661</v>
+        <v>9716</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4678</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>9662</v>
+        <v>9717</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
@@ -64730,13 +65079,13 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>9663</v>
+        <v>9718</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4500</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>9664</v>
+        <v>9719</v>
       </c>
       <c r="E23" s="5">
         <v>19</v>
@@ -64744,13 +65093,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>9665</v>
+        <v>9720</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4686</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>9666</v>
+        <v>9721</v>
       </c>
       <c r="E24" s="6">
         <v>20</v>

--- a/samples/clover/design-data/xlsx/Text.xlsx
+++ b/samples/clover/design-data/xlsx/Text.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Achievement" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1548]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[StringTable!$B$2:$H$1551]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Achievement!$B$2:$E$24]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10825" uniqueCount="9722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10846" uniqueCount="9743">
   <si>
     <t xml:space="preserve">:table StringTable(key=string_id)</t>
   </si>
@@ -22631,6 +22631,69 @@
   </si>
   <si>
     <t xml:space="preserve">Blatt-Hinweise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.option.frames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">프레임 상한</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フレーム上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">帧率上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幀率上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bildratenlimit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.option.frames_free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무제한</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlimited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無制限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无限制</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無限制</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unbegrenzt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui.option.note.frames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">초당 몇 장까지 그릴지입니다. 낮추면 배터리가 덜 듭니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How many frames are drawn each second. Lower uses less battery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">毎秒何枚まで描くかです。下げると電池が長持ちします</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每秒最多绘制多少帧。调低更省电</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每秒最多繪製多少幀。調低更省電</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie viele Bilder pro Sekunde gezeichnet werden. Niedriger schont den Akku</t>
   </si>
   <si>
     <t xml:space="preserve">ui.option.haptics</t>
@@ -29382,7 +29445,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -29391,7 +29454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H1548"/>
+  <dimension ref="A1:H1551"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.015625" customWidth="1"/>
@@ -56681,79 +56744,79 @@
         <v>7542</v>
       </c>
       <c r="G1188" s="6" t="s">
-        <v>7541</v>
+        <v>7543</v>
       </c>
       <c r="H1188" s="6" t="s">
-        <v>7540</v>
+        <v>7544</v>
       </c>
     </row>
     <row r="1189">
       <c r="B1189" s="5" t="s">
-        <v>7543</v>
+        <v>7545</v>
       </c>
       <c r="C1189" s="5" t="s">
-        <v>7544</v>
+        <v>7546</v>
       </c>
       <c r="D1189" s="5" t="s">
-        <v>7545</v>
+        <v>7547</v>
       </c>
       <c r="E1189" s="5" t="s">
-        <v>7546</v>
+        <v>7548</v>
       </c>
       <c r="F1189" s="5" t="s">
-        <v>7547</v>
+        <v>7549</v>
       </c>
       <c r="G1189" s="5" t="s">
-        <v>7548</v>
+        <v>7550</v>
       </c>
       <c r="H1189" s="5" t="s">
-        <v>7549</v>
+        <v>7551</v>
       </c>
     </row>
     <row r="1190">
       <c r="B1190" s="6" t="s">
-        <v>7550</v>
+        <v>7552</v>
       </c>
       <c r="C1190" s="6" t="s">
-        <v>7551</v>
+        <v>7553</v>
       </c>
       <c r="D1190" s="6" t="s">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="E1190" s="6" t="s">
-        <v>7553</v>
+        <v>7555</v>
       </c>
       <c r="F1190" s="6" t="s">
-        <v>7554</v>
+        <v>7556</v>
       </c>
       <c r="G1190" s="6" t="s">
-        <v>7555</v>
+        <v>7557</v>
       </c>
       <c r="H1190" s="6" t="s">
-        <v>7556</v>
+        <v>7558</v>
       </c>
     </row>
     <row r="1191">
       <c r="B1191" s="5" t="s">
-        <v>7557</v>
+        <v>7559</v>
       </c>
       <c r="C1191" s="5" t="s">
-        <v>7558</v>
+        <v>7560</v>
       </c>
       <c r="D1191" s="5" t="s">
-        <v>7559</v>
+        <v>7561</v>
       </c>
       <c r="E1191" s="5" t="s">
-        <v>7560</v>
+        <v>7562</v>
       </c>
       <c r="F1191" s="5" t="s">
-        <v>7561</v>
+        <v>7563</v>
       </c>
       <c r="G1191" s="5" t="s">
         <v>7562</v>
       </c>
       <c r="H1191" s="5" t="s">
-        <v>7563</v>
+        <v>7561</v>
       </c>
     </row>
     <row r="1192">
@@ -56934,73 +56997,73 @@
         <v>7617</v>
       </c>
       <c r="G1199" s="5" t="s">
-        <v>7617</v>
+        <v>7618</v>
       </c>
       <c r="H1199" s="5" t="s">
-        <v>7618</v>
+        <v>7619</v>
       </c>
     </row>
     <row r="1200">
       <c r="B1200" s="6" t="s">
-        <v>7619</v>
+        <v>7620</v>
       </c>
       <c r="C1200" s="6" t="s">
-        <v>7620</v>
+        <v>7621</v>
       </c>
       <c r="D1200" s="6" t="s">
-        <v>7621</v>
+        <v>7622</v>
       </c>
       <c r="E1200" s="6" t="s">
-        <v>7622</v>
+        <v>7623</v>
       </c>
       <c r="F1200" s="6" t="s">
-        <v>7623</v>
+        <v>7624</v>
       </c>
       <c r="G1200" s="6" t="s">
-        <v>7624</v>
+        <v>7625</v>
       </c>
       <c r="H1200" s="6" t="s">
-        <v>7625</v>
+        <v>7626</v>
       </c>
     </row>
     <row r="1201">
       <c r="B1201" s="5" t="s">
-        <v>7626</v>
+        <v>7627</v>
       </c>
       <c r="C1201" s="5" t="s">
-        <v>7627</v>
+        <v>7628</v>
       </c>
       <c r="D1201" s="5" t="s">
-        <v>7628</v>
+        <v>7629</v>
       </c>
       <c r="E1201" s="5" t="s">
-        <v>7629</v>
+        <v>7630</v>
       </c>
       <c r="F1201" s="5" t="s">
-        <v>7630</v>
+        <v>7631</v>
       </c>
       <c r="G1201" s="5" t="s">
-        <v>7631</v>
+        <v>7632</v>
       </c>
       <c r="H1201" s="5" t="s">
-        <v>7632</v>
+        <v>7633</v>
       </c>
     </row>
     <row r="1202">
       <c r="B1202" s="6" t="s">
-        <v>7633</v>
+        <v>7634</v>
       </c>
       <c r="C1202" s="6" t="s">
-        <v>7634</v>
+        <v>7635</v>
       </c>
       <c r="D1202" s="6" t="s">
-        <v>7635</v>
+        <v>7636</v>
       </c>
       <c r="E1202" s="6" t="s">
-        <v>7636</v>
+        <v>7637</v>
       </c>
       <c r="F1202" s="6" t="s">
-        <v>7637</v>
+        <v>7638</v>
       </c>
       <c r="G1202" s="6" t="s">
         <v>7638</v>
@@ -57371,142 +57434,142 @@
         <v>7749</v>
       </c>
       <c r="G1218" s="6" t="s">
-        <v>7749</v>
+        <v>7750</v>
       </c>
       <c r="H1218" s="6" t="s">
-        <v>7750</v>
+        <v>7751</v>
       </c>
     </row>
     <row r="1219">
       <c r="B1219" s="5" t="s">
-        <v>7751</v>
+        <v>7752</v>
       </c>
       <c r="C1219" s="5" t="s">
-        <v>7752</v>
+        <v>7753</v>
       </c>
       <c r="D1219" s="5" t="s">
-        <v>7753</v>
+        <v>7754</v>
       </c>
       <c r="E1219" s="5" t="s">
-        <v>7754</v>
+        <v>7755</v>
       </c>
       <c r="F1219" s="5" t="s">
-        <v>7755</v>
+        <v>7756</v>
       </c>
       <c r="G1219" s="5" t="s">
-        <v>7756</v>
+        <v>7757</v>
       </c>
       <c r="H1219" s="5" t="s">
-        <v>7757</v>
+        <v>7758</v>
       </c>
     </row>
     <row r="1220">
       <c r="B1220" s="6" t="s">
-        <v>7758</v>
+        <v>7759</v>
       </c>
       <c r="C1220" s="6" t="s">
-        <v>7759</v>
+        <v>7760</v>
       </c>
       <c r="D1220" s="6" t="s">
-        <v>7760</v>
+        <v>7761</v>
       </c>
       <c r="E1220" s="6" t="s">
-        <v>7761</v>
+        <v>7762</v>
       </c>
       <c r="F1220" s="6" t="s">
-        <v>7762</v>
+        <v>7763</v>
       </c>
       <c r="G1220" s="6" t="s">
-        <v>7763</v>
+        <v>7764</v>
       </c>
       <c r="H1220" s="6" t="s">
-        <v>7764</v>
+        <v>7765</v>
       </c>
     </row>
     <row r="1221">
       <c r="B1221" s="5" t="s">
-        <v>7765</v>
+        <v>7766</v>
       </c>
       <c r="C1221" s="5" t="s">
-        <v>7766</v>
+        <v>7767</v>
       </c>
       <c r="D1221" s="5" t="s">
-        <v>7767</v>
+        <v>7768</v>
       </c>
       <c r="E1221" s="5" t="s">
-        <v>7768</v>
+        <v>7769</v>
       </c>
       <c r="F1221" s="5" t="s">
-        <v>7769</v>
+        <v>7770</v>
       </c>
       <c r="G1221" s="5" t="s">
-        <v>7769</v>
+        <v>7770</v>
       </c>
       <c r="H1221" s="5" t="s">
-        <v>7770</v>
+        <v>7771</v>
       </c>
     </row>
     <row r="1222">
       <c r="B1222" s="6" t="s">
-        <v>7771</v>
+        <v>7772</v>
       </c>
       <c r="C1222" s="6" t="s">
-        <v>7772</v>
+        <v>7773</v>
       </c>
       <c r="D1222" s="6" t="s">
-        <v>7773</v>
+        <v>7774</v>
       </c>
       <c r="E1222" s="6" t="s">
-        <v>7774</v>
+        <v>7775</v>
       </c>
       <c r="F1222" s="6" t="s">
-        <v>7775</v>
+        <v>7776</v>
       </c>
       <c r="G1222" s="6" t="s">
-        <v>7776</v>
+        <v>7777</v>
       </c>
       <c r="H1222" s="6" t="s">
-        <v>7777</v>
+        <v>7778</v>
       </c>
     </row>
     <row r="1223">
       <c r="B1223" s="5" t="s">
-        <v>7778</v>
+        <v>7779</v>
       </c>
       <c r="C1223" s="5" t="s">
-        <v>7779</v>
+        <v>7780</v>
       </c>
       <c r="D1223" s="5" t="s">
-        <v>7780</v>
+        <v>7781</v>
       </c>
       <c r="E1223" s="5" t="s">
-        <v>7781</v>
+        <v>7782</v>
       </c>
       <c r="F1223" s="5" t="s">
-        <v>7782</v>
+        <v>7783</v>
       </c>
       <c r="G1223" s="5" t="s">
-        <v>7783</v>
+        <v>7784</v>
       </c>
       <c r="H1223" s="5" t="s">
-        <v>7784</v>
+        <v>7785</v>
       </c>
     </row>
     <row r="1224">
       <c r="B1224" s="6" t="s">
-        <v>7785</v>
+        <v>7786</v>
       </c>
       <c r="C1224" s="6" t="s">
-        <v>7786</v>
+        <v>7787</v>
       </c>
       <c r="D1224" s="6" t="s">
-        <v>7787</v>
+        <v>7788</v>
       </c>
       <c r="E1224" s="6" t="s">
-        <v>7788</v>
+        <v>7789</v>
       </c>
       <c r="F1224" s="6" t="s">
-        <v>7789</v>
+        <v>7790</v>
       </c>
       <c r="G1224" s="6" t="s">
         <v>7790</v>
@@ -57532,73 +57595,73 @@
         <v>7796</v>
       </c>
       <c r="G1225" s="5" t="s">
-        <v>7796</v>
+        <v>7797</v>
       </c>
       <c r="H1225" s="5" t="s">
-        <v>7797</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="1226">
       <c r="B1226" s="6" t="s">
-        <v>7798</v>
+        <v>7799</v>
       </c>
       <c r="C1226" s="6" t="s">
-        <v>7799</v>
+        <v>7800</v>
       </c>
       <c r="D1226" s="6" t="s">
-        <v>7800</v>
+        <v>7801</v>
       </c>
       <c r="E1226" s="6" t="s">
-        <v>7801</v>
+        <v>7802</v>
       </c>
       <c r="F1226" s="6" t="s">
-        <v>7802</v>
+        <v>7803</v>
       </c>
       <c r="G1226" s="6" t="s">
-        <v>7803</v>
+        <v>7804</v>
       </c>
       <c r="H1226" s="6" t="s">
-        <v>7804</v>
+        <v>7805</v>
       </c>
     </row>
     <row r="1227">
       <c r="B1227" s="5" t="s">
-        <v>7805</v>
+        <v>7806</v>
       </c>
       <c r="C1227" s="5" t="s">
-        <v>7806</v>
+        <v>7807</v>
       </c>
       <c r="D1227" s="5" t="s">
-        <v>7807</v>
+        <v>7808</v>
       </c>
       <c r="E1227" s="5" t="s">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="F1227" s="5" t="s">
-        <v>7809</v>
+        <v>7810</v>
       </c>
       <c r="G1227" s="5" t="s">
-        <v>7810</v>
+        <v>7811</v>
       </c>
       <c r="H1227" s="5" t="s">
-        <v>7811</v>
+        <v>7812</v>
       </c>
     </row>
     <row r="1228">
       <c r="B1228" s="6" t="s">
-        <v>7812</v>
+        <v>7813</v>
       </c>
       <c r="C1228" s="6" t="s">
-        <v>7813</v>
+        <v>7814</v>
       </c>
       <c r="D1228" s="6" t="s">
-        <v>7814</v>
+        <v>7815</v>
       </c>
       <c r="E1228" s="6" t="s">
-        <v>7815</v>
+        <v>7816</v>
       </c>
       <c r="F1228" s="6" t="s">
-        <v>7816</v>
+        <v>7817</v>
       </c>
       <c r="G1228" s="6" t="s">
         <v>7817</v>
@@ -57719,76 +57782,76 @@
         <v>7852</v>
       </c>
       <c r="H1233" s="5" t="s">
-        <v>7849</v>
+        <v>7853</v>
       </c>
     </row>
     <row r="1234">
       <c r="B1234" s="6" t="s">
-        <v>7853</v>
+        <v>7854</v>
       </c>
       <c r="C1234" s="6" t="s">
-        <v>7854</v>
+        <v>7855</v>
       </c>
       <c r="D1234" s="6" t="s">
-        <v>7855</v>
+        <v>7856</v>
       </c>
       <c r="E1234" s="6" t="s">
-        <v>7856</v>
+        <v>7857</v>
       </c>
       <c r="F1234" s="6" t="s">
-        <v>7857</v>
+        <v>7858</v>
       </c>
       <c r="G1234" s="6" t="s">
-        <v>7858</v>
+        <v>7859</v>
       </c>
       <c r="H1234" s="6" t="s">
-        <v>7859</v>
+        <v>7860</v>
       </c>
     </row>
     <row r="1235">
       <c r="B1235" s="5" t="s">
-        <v>7860</v>
+        <v>7861</v>
       </c>
       <c r="C1235" s="5" t="s">
-        <v>7861</v>
+        <v>7862</v>
       </c>
       <c r="D1235" s="5" t="s">
-        <v>7862</v>
+        <v>7863</v>
       </c>
       <c r="E1235" s="5" t="s">
-        <v>7863</v>
+        <v>7864</v>
       </c>
       <c r="F1235" s="5" t="s">
-        <v>7864</v>
+        <v>7865</v>
       </c>
       <c r="G1235" s="5" t="s">
-        <v>7865</v>
+        <v>7866</v>
       </c>
       <c r="H1235" s="5" t="s">
-        <v>7866</v>
+        <v>7867</v>
       </c>
     </row>
     <row r="1236">
       <c r="B1236" s="6" t="s">
-        <v>7867</v>
+        <v>7868</v>
       </c>
       <c r="C1236" s="6" t="s">
-        <v>7868</v>
+        <v>7869</v>
       </c>
       <c r="D1236" s="6" t="s">
-        <v>7869</v>
+        <v>7870</v>
       </c>
       <c r="E1236" s="6" t="s">
+        <v>7871</v>
+      </c>
+      <c r="F1236" s="6" t="s">
+        <v>7872</v>
+      </c>
+      <c r="G1236" s="6" t="s">
+        <v>7873</v>
+      </c>
+      <c r="H1236" s="6" t="s">
         <v>7870</v>
-      </c>
-      <c r="F1236" s="6" t="s">
-        <v>7871</v>
-      </c>
-      <c r="G1236" s="6" t="s">
-        <v>7872</v>
-      </c>
-      <c r="H1236" s="6" t="s">
-        <v>7873</v>
       </c>
     </row>
     <row r="1237">
@@ -57842,177 +57905,177 @@
         <v>7888</v>
       </c>
       <c r="C1239" s="5" t="s">
-        <v>5444</v>
+        <v>7889</v>
       </c>
       <c r="D1239" s="5" t="s">
-        <v>7889</v>
+        <v>7890</v>
       </c>
       <c r="E1239" s="5" t="s">
-        <v>5446</v>
+        <v>7891</v>
       </c>
       <c r="F1239" s="5" t="s">
-        <v>7890</v>
+        <v>7892</v>
       </c>
       <c r="G1239" s="5" t="s">
-        <v>7891</v>
+        <v>7893</v>
       </c>
       <c r="H1239" s="5" t="s">
-        <v>7892</v>
+        <v>7894</v>
       </c>
     </row>
     <row r="1240">
       <c r="B1240" s="6" t="s">
-        <v>7893</v>
+        <v>7895</v>
       </c>
       <c r="C1240" s="6" t="s">
-        <v>5437</v>
+        <v>7896</v>
       </c>
       <c r="D1240" s="6" t="s">
-        <v>7894</v>
+        <v>7897</v>
       </c>
       <c r="E1240" s="6" t="s">
-        <v>5439</v>
+        <v>7898</v>
       </c>
       <c r="F1240" s="6" t="s">
-        <v>7895</v>
+        <v>7899</v>
       </c>
       <c r="G1240" s="6" t="s">
-        <v>7896</v>
+        <v>7900</v>
       </c>
       <c r="H1240" s="6" t="s">
-        <v>7897</v>
+        <v>7901</v>
       </c>
     </row>
     <row r="1241">
       <c r="B1241" s="5" t="s">
-        <v>7898</v>
+        <v>7902</v>
       </c>
       <c r="C1241" s="5" t="s">
-        <v>7899</v>
+        <v>7903</v>
       </c>
       <c r="D1241" s="5" t="s">
-        <v>7900</v>
+        <v>7904</v>
       </c>
       <c r="E1241" s="5" t="s">
-        <v>7901</v>
+        <v>7905</v>
       </c>
       <c r="F1241" s="5" t="s">
-        <v>7902</v>
+        <v>7906</v>
       </c>
       <c r="G1241" s="5" t="s">
-        <v>7901</v>
+        <v>7907</v>
       </c>
       <c r="H1241" s="5" t="s">
-        <v>7260</v>
+        <v>7908</v>
       </c>
     </row>
     <row r="1242">
       <c r="B1242" s="6" t="s">
-        <v>7903</v>
+        <v>7909</v>
       </c>
       <c r="C1242" s="6" t="s">
-        <v>7904</v>
+        <v>5444</v>
       </c>
       <c r="D1242" s="6" t="s">
-        <v>7905</v>
+        <v>7910</v>
       </c>
       <c r="E1242" s="6" t="s">
-        <v>7906</v>
+        <v>5446</v>
       </c>
       <c r="F1242" s="6" t="s">
-        <v>7907</v>
+        <v>7911</v>
       </c>
       <c r="G1242" s="6" t="s">
-        <v>7908</v>
+        <v>7912</v>
       </c>
       <c r="H1242" s="6" t="s">
-        <v>7909</v>
+        <v>7913</v>
       </c>
     </row>
     <row r="1243">
       <c r="B1243" s="5" t="s">
-        <v>7910</v>
+        <v>7914</v>
       </c>
       <c r="C1243" s="5" t="s">
-        <v>7911</v>
+        <v>5437</v>
       </c>
       <c r="D1243" s="5" t="s">
-        <v>7912</v>
+        <v>7915</v>
       </c>
       <c r="E1243" s="5" t="s">
-        <v>7913</v>
+        <v>5439</v>
       </c>
       <c r="F1243" s="5" t="s">
-        <v>7914</v>
+        <v>7916</v>
       </c>
       <c r="G1243" s="5" t="s">
-        <v>7914</v>
+        <v>7917</v>
       </c>
       <c r="H1243" s="5" t="s">
-        <v>7915</v>
+        <v>7918</v>
       </c>
     </row>
     <row r="1244">
       <c r="B1244" s="6" t="s">
-        <v>7916</v>
+        <v>7919</v>
       </c>
       <c r="C1244" s="6" t="s">
-        <v>7917</v>
+        <v>7920</v>
       </c>
       <c r="D1244" s="6" t="s">
-        <v>7918</v>
+        <v>7921</v>
       </c>
       <c r="E1244" s="6" t="s">
-        <v>7919</v>
+        <v>7922</v>
       </c>
       <c r="F1244" s="6" t="s">
-        <v>7920</v>
+        <v>7923</v>
       </c>
       <c r="G1244" s="6" t="s">
-        <v>7921</v>
+        <v>7922</v>
       </c>
       <c r="H1244" s="6" t="s">
-        <v>7922</v>
+        <v>7260</v>
       </c>
     </row>
     <row r="1245">
       <c r="B1245" s="5" t="s">
-        <v>7923</v>
+        <v>7924</v>
       </c>
       <c r="C1245" s="5" t="s">
-        <v>7924</v>
+        <v>7925</v>
       </c>
       <c r="D1245" s="5" t="s">
-        <v>7925</v>
+        <v>7926</v>
       </c>
       <c r="E1245" s="5" t="s">
-        <v>7926</v>
+        <v>7927</v>
       </c>
       <c r="F1245" s="5" t="s">
-        <v>7927</v>
+        <v>7928</v>
       </c>
       <c r="G1245" s="5" t="s">
-        <v>7928</v>
+        <v>7929</v>
       </c>
       <c r="H1245" s="5" t="s">
-        <v>7929</v>
+        <v>7930</v>
       </c>
     </row>
     <row r="1246">
       <c r="B1246" s="6" t="s">
-        <v>7930</v>
+        <v>7931</v>
       </c>
       <c r="C1246" s="6" t="s">
-        <v>7931</v>
+        <v>7932</v>
       </c>
       <c r="D1246" s="6" t="s">
-        <v>7932</v>
+        <v>7933</v>
       </c>
       <c r="E1246" s="6" t="s">
-        <v>7933</v>
+        <v>7934</v>
       </c>
       <c r="F1246" s="6" t="s">
-        <v>7934</v>
+        <v>7935</v>
       </c>
       <c r="G1246" s="6" t="s">
         <v>7935</v>
@@ -58081,76 +58144,76 @@
         <v>7954</v>
       </c>
       <c r="F1249" s="5" t="s">
-        <v>7954</v>
+        <v>7955</v>
       </c>
       <c r="G1249" s="5" t="s">
-        <v>7954</v>
+        <v>7956</v>
       </c>
       <c r="H1249" s="5" t="s">
-        <v>7955</v>
+        <v>7957</v>
       </c>
     </row>
     <row r="1250">
       <c r="B1250" s="6" t="s">
-        <v>7956</v>
+        <v>7958</v>
       </c>
       <c r="C1250" s="6" t="s">
-        <v>7957</v>
+        <v>7959</v>
       </c>
       <c r="D1250" s="6" t="s">
-        <v>7958</v>
+        <v>7960</v>
       </c>
       <c r="E1250" s="6" t="s">
-        <v>7959</v>
+        <v>7961</v>
       </c>
       <c r="F1250" s="6" t="s">
-        <v>7960</v>
+        <v>7962</v>
       </c>
       <c r="G1250" s="6" t="s">
-        <v>7961</v>
+        <v>7963</v>
       </c>
       <c r="H1250" s="6" t="s">
-        <v>7962</v>
+        <v>7964</v>
       </c>
     </row>
     <row r="1251">
       <c r="B1251" s="5" t="s">
-        <v>7963</v>
+        <v>7965</v>
       </c>
       <c r="C1251" s="5" t="s">
-        <v>7964</v>
+        <v>7966</v>
       </c>
       <c r="D1251" s="5" t="s">
-        <v>7965</v>
+        <v>7967</v>
       </c>
       <c r="E1251" s="5" t="s">
-        <v>7966</v>
+        <v>7968</v>
       </c>
       <c r="F1251" s="5" t="s">
-        <v>7967</v>
+        <v>7969</v>
       </c>
       <c r="G1251" s="5" t="s">
-        <v>7968</v>
+        <v>7970</v>
       </c>
       <c r="H1251" s="5" t="s">
-        <v>7969</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="1252">
       <c r="B1252" s="6" t="s">
-        <v>7970</v>
+        <v>7972</v>
       </c>
       <c r="C1252" s="6" t="s">
-        <v>7971</v>
+        <v>7973</v>
       </c>
       <c r="D1252" s="6" t="s">
-        <v>7972</v>
+        <v>7974</v>
       </c>
       <c r="E1252" s="6" t="s">
-        <v>7973</v>
+        <v>7975</v>
       </c>
       <c r="F1252" s="6" t="s">
-        <v>7974</v>
+        <v>7975</v>
       </c>
       <c r="G1252" s="6" t="s">
         <v>7975</v>
@@ -58176,119 +58239,119 @@
         <v>7981</v>
       </c>
       <c r="G1253" s="5" t="s">
-        <v>7981</v>
+        <v>7982</v>
       </c>
       <c r="H1253" s="5" t="s">
-        <v>7982</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="1254">
       <c r="B1254" s="6" t="s">
-        <v>7983</v>
+        <v>7984</v>
       </c>
       <c r="C1254" s="6" t="s">
-        <v>7984</v>
+        <v>7985</v>
       </c>
       <c r="D1254" s="6" t="s">
-        <v>7985</v>
+        <v>7986</v>
       </c>
       <c r="E1254" s="6" t="s">
-        <v>7986</v>
+        <v>7987</v>
       </c>
       <c r="F1254" s="6" t="s">
-        <v>7987</v>
+        <v>7988</v>
       </c>
       <c r="G1254" s="6" t="s">
-        <v>7987</v>
+        <v>7989</v>
       </c>
       <c r="H1254" s="6" t="s">
-        <v>7988</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="1255">
       <c r="B1255" s="5" t="s">
-        <v>7989</v>
+        <v>7991</v>
       </c>
       <c r="C1255" s="5" t="s">
-        <v>7990</v>
+        <v>7992</v>
       </c>
       <c r="D1255" s="5" t="s">
-        <v>7991</v>
+        <v>7993</v>
       </c>
       <c r="E1255" s="5" t="s">
-        <v>7992</v>
+        <v>7994</v>
       </c>
       <c r="F1255" s="5" t="s">
-        <v>7993</v>
+        <v>7995</v>
       </c>
       <c r="G1255" s="5" t="s">
-        <v>7993</v>
+        <v>7996</v>
       </c>
       <c r="H1255" s="5" t="s">
-        <v>7994</v>
+        <v>7997</v>
       </c>
     </row>
     <row r="1256">
       <c r="B1256" s="6" t="s">
-        <v>7995</v>
+        <v>7998</v>
       </c>
       <c r="C1256" s="6" t="s">
-        <v>7996</v>
+        <v>7999</v>
       </c>
       <c r="D1256" s="6" t="s">
-        <v>7997</v>
+        <v>8000</v>
       </c>
       <c r="E1256" s="6" t="s">
-        <v>7998</v>
+        <v>8001</v>
       </c>
       <c r="F1256" s="6" t="s">
-        <v>7999</v>
+        <v>8002</v>
       </c>
       <c r="G1256" s="6" t="s">
-        <v>8000</v>
+        <v>8002</v>
       </c>
       <c r="H1256" s="6" t="s">
-        <v>8001</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="1257">
       <c r="B1257" s="5" t="s">
-        <v>8002</v>
+        <v>8004</v>
       </c>
       <c r="C1257" s="5" t="s">
-        <v>8003</v>
+        <v>8005</v>
       </c>
       <c r="D1257" s="5" t="s">
-        <v>8004</v>
+        <v>8006</v>
       </c>
       <c r="E1257" s="5" t="s">
-        <v>8005</v>
+        <v>8007</v>
       </c>
       <c r="F1257" s="5" t="s">
-        <v>8006</v>
+        <v>8008</v>
       </c>
       <c r="G1257" s="5" t="s">
-        <v>8007</v>
+        <v>8008</v>
       </c>
       <c r="H1257" s="5" t="s">
-        <v>8008</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="1258">
       <c r="B1258" s="6" t="s">
-        <v>8009</v>
+        <v>8010</v>
       </c>
       <c r="C1258" s="6" t="s">
-        <v>8010</v>
+        <v>8011</v>
       </c>
       <c r="D1258" s="6" t="s">
-        <v>8011</v>
+        <v>8012</v>
       </c>
       <c r="E1258" s="6" t="s">
-        <v>8012</v>
+        <v>8013</v>
       </c>
       <c r="F1258" s="6" t="s">
-        <v>8013</v>
+        <v>8014</v>
       </c>
       <c r="G1258" s="6" t="s">
         <v>8014</v>
@@ -58360,194 +58423,194 @@
         <v>8034</v>
       </c>
       <c r="G1261" s="5" t="s">
-        <v>8034</v>
+        <v>8035</v>
       </c>
       <c r="H1261" s="5" t="s">
-        <v>8035</v>
+        <v>8036</v>
       </c>
     </row>
     <row r="1262">
       <c r="B1262" s="6" t="s">
-        <v>8036</v>
+        <v>8037</v>
       </c>
       <c r="C1262" s="6" t="s">
-        <v>8037</v>
+        <v>8038</v>
       </c>
       <c r="D1262" s="6" t="s">
-        <v>8038</v>
+        <v>8039</v>
       </c>
       <c r="E1262" s="6" t="s">
-        <v>8039</v>
+        <v>8040</v>
       </c>
       <c r="F1262" s="6" t="s">
-        <v>8040</v>
+        <v>8041</v>
       </c>
       <c r="G1262" s="6" t="s">
-        <v>8041</v>
+        <v>8042</v>
       </c>
       <c r="H1262" s="6" t="s">
-        <v>6881</v>
+        <v>8043</v>
       </c>
     </row>
     <row r="1263">
       <c r="B1263" s="5" t="s">
-        <v>8042</v>
+        <v>8044</v>
       </c>
       <c r="C1263" s="5" t="s">
-        <v>8043</v>
+        <v>8045</v>
       </c>
       <c r="D1263" s="5" t="s">
-        <v>8044</v>
+        <v>8046</v>
       </c>
       <c r="E1263" s="5" t="s">
-        <v>8045</v>
+        <v>8047</v>
       </c>
       <c r="F1263" s="5" t="s">
-        <v>8046</v>
+        <v>8048</v>
       </c>
       <c r="G1263" s="5" t="s">
-        <v>8047</v>
+        <v>8049</v>
       </c>
       <c r="H1263" s="5" t="s">
-        <v>7811</v>
+        <v>8050</v>
       </c>
     </row>
     <row r="1264">
       <c r="B1264" s="6" t="s">
-        <v>8048</v>
+        <v>8051</v>
       </c>
       <c r="C1264" s="6" t="s">
-        <v>8049</v>
+        <v>8052</v>
       </c>
       <c r="D1264" s="6" t="s">
-        <v>8050</v>
+        <v>8053</v>
       </c>
       <c r="E1264" s="6" t="s">
-        <v>8051</v>
+        <v>8054</v>
       </c>
       <c r="F1264" s="6" t="s">
-        <v>8052</v>
+        <v>8055</v>
       </c>
       <c r="G1264" s="6" t="s">
-        <v>8053</v>
+        <v>8055</v>
       </c>
       <c r="H1264" s="6" t="s">
-        <v>8054</v>
+        <v>8056</v>
       </c>
     </row>
     <row r="1265">
       <c r="B1265" s="5" t="s">
-        <v>8055</v>
+        <v>8057</v>
       </c>
       <c r="C1265" s="5" t="s">
-        <v>8056</v>
+        <v>8058</v>
       </c>
       <c r="D1265" s="5" t="s">
-        <v>8057</v>
+        <v>8059</v>
       </c>
       <c r="E1265" s="5" t="s">
-        <v>8058</v>
+        <v>8060</v>
       </c>
       <c r="F1265" s="5" t="s">
-        <v>8059</v>
+        <v>8061</v>
       </c>
       <c r="G1265" s="5" t="s">
-        <v>8060</v>
+        <v>8062</v>
       </c>
       <c r="H1265" s="5" t="s">
-        <v>8061</v>
+        <v>6881</v>
       </c>
     </row>
     <row r="1266">
       <c r="B1266" s="6" t="s">
-        <v>8062</v>
+        <v>8063</v>
       </c>
       <c r="C1266" s="6" t="s">
-        <v>8063</v>
+        <v>8064</v>
       </c>
       <c r="D1266" s="6" t="s">
-        <v>8064</v>
+        <v>8065</v>
       </c>
       <c r="E1266" s="6" t="s">
-        <v>8065</v>
+        <v>8066</v>
       </c>
       <c r="F1266" s="6" t="s">
-        <v>8065</v>
+        <v>8067</v>
       </c>
       <c r="G1266" s="6" t="s">
-        <v>8065</v>
+        <v>8068</v>
       </c>
       <c r="H1266" s="6" t="s">
-        <v>8064</v>
+        <v>7832</v>
       </c>
     </row>
     <row r="1267">
       <c r="B1267" s="5" t="s">
-        <v>8066</v>
+        <v>8069</v>
       </c>
       <c r="C1267" s="5" t="s">
-        <v>8067</v>
+        <v>8070</v>
       </c>
       <c r="D1267" s="5" t="s">
-        <v>8068</v>
+        <v>8071</v>
       </c>
       <c r="E1267" s="5" t="s">
-        <v>8069</v>
+        <v>8072</v>
       </c>
       <c r="F1267" s="5" t="s">
-        <v>8070</v>
+        <v>8073</v>
       </c>
       <c r="G1267" s="5" t="s">
-        <v>8071</v>
+        <v>8074</v>
       </c>
       <c r="H1267" s="5" t="s">
-        <v>8072</v>
+        <v>8075</v>
       </c>
     </row>
     <row r="1268">
       <c r="B1268" s="6" t="s">
-        <v>8073</v>
+        <v>8076</v>
       </c>
       <c r="C1268" s="6" t="s">
-        <v>8074</v>
+        <v>8077</v>
       </c>
       <c r="D1268" s="6" t="s">
-        <v>8075</v>
+        <v>8078</v>
       </c>
       <c r="E1268" s="6" t="s">
-        <v>8076</v>
+        <v>8079</v>
       </c>
       <c r="F1268" s="6" t="s">
-        <v>8077</v>
+        <v>8080</v>
       </c>
       <c r="G1268" s="6" t="s">
-        <v>8078</v>
+        <v>8081</v>
       </c>
       <c r="H1268" s="6" t="s">
-        <v>8079</v>
+        <v>8082</v>
       </c>
     </row>
     <row r="1269">
       <c r="B1269" s="5" t="s">
-        <v>8080</v>
+        <v>8083</v>
       </c>
       <c r="C1269" s="5" t="s">
-        <v>8081</v>
+        <v>8084</v>
       </c>
       <c r="D1269" s="5" t="s">
-        <v>8082</v>
+        <v>8085</v>
       </c>
       <c r="E1269" s="5" t="s">
-        <v>8083</v>
+        <v>8086</v>
       </c>
       <c r="F1269" s="5" t="s">
-        <v>8084</v>
+        <v>8086</v>
       </c>
       <c r="G1269" s="5" t="s">
+        <v>8086</v>
+      </c>
+      <c r="H1269" s="5" t="s">
         <v>8085</v>
-      </c>
-      <c r="H1269" s="5" t="s">
-        <v>8086</v>
       </c>
     </row>
     <row r="1270">
@@ -58558,134 +58621,134 @@
         <v>8088</v>
       </c>
       <c r="D1270" s="6" t="s">
-        <v>8064</v>
+        <v>8089</v>
       </c>
       <c r="E1270" s="6" t="s">
-        <v>8089</v>
+        <v>8090</v>
       </c>
       <c r="F1270" s="6" t="s">
-        <v>8090</v>
+        <v>8091</v>
       </c>
       <c r="G1270" s="6" t="s">
-        <v>8090</v>
+        <v>8092</v>
       </c>
       <c r="H1270" s="6" t="s">
-        <v>8064</v>
+        <v>8093</v>
       </c>
     </row>
     <row r="1271">
       <c r="B1271" s="5" t="s">
-        <v>8091</v>
+        <v>8094</v>
       </c>
       <c r="C1271" s="5" t="s">
-        <v>8092</v>
+        <v>8095</v>
       </c>
       <c r="D1271" s="5" t="s">
-        <v>8093</v>
+        <v>8096</v>
       </c>
       <c r="E1271" s="5" t="s">
-        <v>8094</v>
+        <v>8097</v>
       </c>
       <c r="F1271" s="5" t="s">
-        <v>8095</v>
+        <v>8098</v>
       </c>
       <c r="G1271" s="5" t="s">
-        <v>8096</v>
+        <v>8099</v>
       </c>
       <c r="H1271" s="5" t="s">
-        <v>8097</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="1272">
       <c r="B1272" s="6" t="s">
-        <v>8098</v>
+        <v>8101</v>
       </c>
       <c r="C1272" s="6" t="s">
-        <v>8099</v>
+        <v>8102</v>
       </c>
       <c r="D1272" s="6" t="s">
-        <v>8100</v>
+        <v>8103</v>
       </c>
       <c r="E1272" s="6" t="s">
-        <v>8101</v>
+        <v>8104</v>
       </c>
       <c r="F1272" s="6" t="s">
-        <v>8102</v>
+        <v>8105</v>
       </c>
       <c r="G1272" s="6" t="s">
-        <v>8103</v>
+        <v>8106</v>
       </c>
       <c r="H1272" s="6" t="s">
-        <v>8100</v>
+        <v>8107</v>
       </c>
     </row>
     <row r="1273">
       <c r="B1273" s="5" t="s">
-        <v>8104</v>
+        <v>8108</v>
       </c>
       <c r="C1273" s="5" t="s">
-        <v>8105</v>
+        <v>8109</v>
       </c>
       <c r="D1273" s="5" t="s">
-        <v>8106</v>
+        <v>8085</v>
       </c>
       <c r="E1273" s="5" t="s">
-        <v>8107</v>
+        <v>8110</v>
       </c>
       <c r="F1273" s="5" t="s">
-        <v>8108</v>
+        <v>8111</v>
       </c>
       <c r="G1273" s="5" t="s">
-        <v>8109</v>
+        <v>8111</v>
       </c>
       <c r="H1273" s="5" t="s">
-        <v>8110</v>
+        <v>8085</v>
       </c>
     </row>
     <row r="1274">
       <c r="B1274" s="6" t="s">
-        <v>8111</v>
+        <v>8112</v>
       </c>
       <c r="C1274" s="6" t="s">
-        <v>8112</v>
+        <v>8113</v>
       </c>
       <c r="D1274" s="6" t="s">
-        <v>8113</v>
+        <v>8114</v>
       </c>
       <c r="E1274" s="6" t="s">
-        <v>8114</v>
+        <v>8115</v>
       </c>
       <c r="F1274" s="6" t="s">
-        <v>8115</v>
+        <v>8116</v>
       </c>
       <c r="G1274" s="6" t="s">
-        <v>8116</v>
+        <v>8117</v>
       </c>
       <c r="H1274" s="6" t="s">
-        <v>8117</v>
+        <v>8118</v>
       </c>
     </row>
     <row r="1275">
       <c r="B1275" s="5" t="s">
-        <v>8118</v>
+        <v>8119</v>
       </c>
       <c r="C1275" s="5" t="s">
-        <v>8119</v>
+        <v>8120</v>
       </c>
       <c r="D1275" s="5" t="s">
-        <v>8120</v>
+        <v>8121</v>
       </c>
       <c r="E1275" s="5" t="s">
+        <v>8122</v>
+      </c>
+      <c r="F1275" s="5" t="s">
+        <v>8123</v>
+      </c>
+      <c r="G1275" s="5" t="s">
+        <v>8124</v>
+      </c>
+      <c r="H1275" s="5" t="s">
         <v>8121</v>
-      </c>
-      <c r="F1275" s="5" t="s">
-        <v>8122</v>
-      </c>
-      <c r="G1275" s="5" t="s">
-        <v>8123</v>
-      </c>
-      <c r="H1275" s="5" t="s">
-        <v>8124</v>
       </c>
     </row>
     <row r="1276">
@@ -58728,559 +58791,559 @@
         <v>8136</v>
       </c>
       <c r="G1277" s="5" t="s">
-        <v>8136</v>
+        <v>8137</v>
       </c>
       <c r="H1277" s="5" t="s">
-        <v>8137</v>
+        <v>8138</v>
       </c>
     </row>
     <row r="1278">
       <c r="B1278" s="6" t="s">
-        <v>8138</v>
+        <v>8139</v>
       </c>
       <c r="C1278" s="6" t="s">
-        <v>8139</v>
+        <v>8140</v>
       </c>
       <c r="D1278" s="6" t="s">
-        <v>8140</v>
+        <v>8141</v>
       </c>
       <c r="E1278" s="6" t="s">
-        <v>8141</v>
+        <v>8142</v>
       </c>
       <c r="F1278" s="6" t="s">
-        <v>8142</v>
+        <v>8143</v>
       </c>
       <c r="G1278" s="6" t="s">
-        <v>8143</v>
+        <v>8144</v>
       </c>
       <c r="H1278" s="6" t="s">
-        <v>8144</v>
+        <v>8145</v>
       </c>
     </row>
     <row r="1279">
       <c r="B1279" s="5" t="s">
-        <v>8145</v>
+        <v>8146</v>
       </c>
       <c r="C1279" s="5" t="s">
-        <v>8146</v>
+        <v>8147</v>
       </c>
       <c r="D1279" s="5" t="s">
-        <v>8147</v>
+        <v>8148</v>
       </c>
       <c r="E1279" s="5" t="s">
-        <v>8148</v>
+        <v>8149</v>
       </c>
       <c r="F1279" s="5" t="s">
-        <v>8149</v>
+        <v>8150</v>
       </c>
       <c r="G1279" s="5" t="s">
-        <v>8149</v>
+        <v>8151</v>
       </c>
       <c r="H1279" s="5" t="s">
-        <v>8150</v>
+        <v>8152</v>
       </c>
     </row>
     <row r="1280">
       <c r="B1280" s="6" t="s">
-        <v>8151</v>
+        <v>8153</v>
       </c>
       <c r="C1280" s="6" t="s">
-        <v>8152</v>
+        <v>8154</v>
       </c>
       <c r="D1280" s="6" t="s">
-        <v>8153</v>
+        <v>8155</v>
       </c>
       <c r="E1280" s="6" t="s">
-        <v>8154</v>
+        <v>8156</v>
       </c>
       <c r="F1280" s="6" t="s">
-        <v>8155</v>
+        <v>8157</v>
       </c>
       <c r="G1280" s="6" t="s">
-        <v>8156</v>
+        <v>8157</v>
       </c>
       <c r="H1280" s="6" t="s">
-        <v>8157</v>
+        <v>8158</v>
       </c>
     </row>
     <row r="1281">
       <c r="B1281" s="5" t="s">
-        <v>8158</v>
+        <v>8159</v>
       </c>
       <c r="C1281" s="5" t="s">
-        <v>8159</v>
+        <v>8160</v>
       </c>
       <c r="D1281" s="5" t="s">
-        <v>8160</v>
+        <v>8161</v>
       </c>
       <c r="E1281" s="5" t="s">
-        <v>8161</v>
+        <v>8162</v>
       </c>
       <c r="F1281" s="5" t="s">
-        <v>8162</v>
+        <v>8163</v>
       </c>
       <c r="G1281" s="5" t="s">
-        <v>8163</v>
+        <v>8164</v>
       </c>
       <c r="H1281" s="5" t="s">
-        <v>8164</v>
+        <v>8165</v>
       </c>
     </row>
     <row r="1282">
       <c r="B1282" s="6" t="s">
-        <v>8165</v>
+        <v>8166</v>
       </c>
       <c r="C1282" s="6" t="s">
-        <v>8166</v>
+        <v>8167</v>
       </c>
       <c r="D1282" s="6" t="s">
-        <v>8167</v>
+        <v>8168</v>
       </c>
       <c r="E1282" s="6" t="s">
-        <v>8168</v>
+        <v>8169</v>
       </c>
       <c r="F1282" s="6" t="s">
-        <v>8169</v>
+        <v>8170</v>
       </c>
       <c r="G1282" s="6" t="s">
-        <v>8168</v>
+        <v>8170</v>
       </c>
       <c r="H1282" s="6" t="s">
-        <v>8170</v>
+        <v>8171</v>
       </c>
     </row>
     <row r="1283">
       <c r="B1283" s="5" t="s">
-        <v>8171</v>
+        <v>8172</v>
       </c>
       <c r="C1283" s="5" t="s">
-        <v>8172</v>
+        <v>8173</v>
       </c>
       <c r="D1283" s="5" t="s">
-        <v>8173</v>
+        <v>8174</v>
       </c>
       <c r="E1283" s="5" t="s">
-        <v>8174</v>
+        <v>8175</v>
       </c>
       <c r="F1283" s="5" t="s">
-        <v>8175</v>
+        <v>8176</v>
       </c>
       <c r="G1283" s="5" t="s">
-        <v>8175</v>
+        <v>8177</v>
       </c>
       <c r="H1283" s="5" t="s">
-        <v>8173</v>
+        <v>8178</v>
       </c>
     </row>
     <row r="1284">
       <c r="B1284" s="6" t="s">
-        <v>8176</v>
+        <v>8179</v>
       </c>
       <c r="C1284" s="6" t="s">
-        <v>8177</v>
+        <v>8180</v>
       </c>
       <c r="D1284" s="6" t="s">
-        <v>8178</v>
+        <v>8181</v>
       </c>
       <c r="E1284" s="6" t="s">
-        <v>8179</v>
+        <v>8182</v>
       </c>
       <c r="F1284" s="6" t="s">
-        <v>8180</v>
+        <v>8183</v>
       </c>
       <c r="G1284" s="6" t="s">
-        <v>8181</v>
+        <v>8184</v>
       </c>
       <c r="H1284" s="6" t="s">
-        <v>8182</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="1285">
       <c r="B1285" s="5" t="s">
-        <v>8183</v>
+        <v>8186</v>
       </c>
       <c r="C1285" s="5" t="s">
-        <v>8184</v>
+        <v>8187</v>
       </c>
       <c r="D1285" s="5" t="s">
-        <v>8185</v>
+        <v>8188</v>
       </c>
       <c r="E1285" s="5" t="s">
-        <v>8186</v>
+        <v>8189</v>
       </c>
       <c r="F1285" s="5" t="s">
-        <v>8187</v>
+        <v>8190</v>
       </c>
       <c r="G1285" s="5" t="s">
-        <v>8188</v>
+        <v>8189</v>
       </c>
       <c r="H1285" s="5" t="s">
-        <v>8185</v>
+        <v>8191</v>
       </c>
     </row>
     <row r="1286">
       <c r="B1286" s="6" t="s">
-        <v>8189</v>
+        <v>8192</v>
       </c>
       <c r="C1286" s="6" t="s">
-        <v>8190</v>
+        <v>8193</v>
       </c>
       <c r="D1286" s="6" t="s">
-        <v>8191</v>
+        <v>8194</v>
       </c>
       <c r="E1286" s="6" t="s">
-        <v>8192</v>
+        <v>8195</v>
       </c>
       <c r="F1286" s="6" t="s">
-        <v>8193</v>
+        <v>8196</v>
       </c>
       <c r="G1286" s="6" t="s">
+        <v>8196</v>
+      </c>
+      <c r="H1286" s="6" t="s">
         <v>8194</v>
-      </c>
-      <c r="H1286" s="6" t="s">
-        <v>8195</v>
       </c>
     </row>
     <row r="1287">
       <c r="B1287" s="5" t="s">
-        <v>8196</v>
+        <v>8197</v>
       </c>
       <c r="C1287" s="5" t="s">
-        <v>8197</v>
+        <v>8198</v>
       </c>
       <c r="D1287" s="5" t="s">
-        <v>8198</v>
+        <v>8199</v>
       </c>
       <c r="E1287" s="5" t="s">
-        <v>8199</v>
+        <v>8200</v>
       </c>
       <c r="F1287" s="5" t="s">
-        <v>8200</v>
+        <v>8201</v>
       </c>
       <c r="G1287" s="5" t="s">
-        <v>8200</v>
+        <v>8202</v>
       </c>
       <c r="H1287" s="5" t="s">
-        <v>8201</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="1288">
       <c r="B1288" s="6" t="s">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="C1288" s="6" t="s">
-        <v>8203</v>
+        <v>8205</v>
       </c>
       <c r="D1288" s="6" t="s">
-        <v>8204</v>
+        <v>8206</v>
       </c>
       <c r="E1288" s="6" t="s">
-        <v>8205</v>
+        <v>8207</v>
       </c>
       <c r="F1288" s="6" t="s">
+        <v>8208</v>
+      </c>
+      <c r="G1288" s="6" t="s">
+        <v>8209</v>
+      </c>
+      <c r="H1288" s="6" t="s">
         <v>8206</v>
-      </c>
-      <c r="G1288" s="6" t="s">
-        <v>8206</v>
-      </c>
-      <c r="H1288" s="6" t="s">
-        <v>8207</v>
       </c>
     </row>
     <row r="1289">
       <c r="B1289" s="5" t="s">
-        <v>8208</v>
+        <v>8210</v>
       </c>
       <c r="C1289" s="5" t="s">
-        <v>8209</v>
+        <v>8211</v>
       </c>
       <c r="D1289" s="5" t="s">
-        <v>8210</v>
+        <v>8212</v>
       </c>
       <c r="E1289" s="5" t="s">
-        <v>8211</v>
+        <v>8213</v>
       </c>
       <c r="F1289" s="5" t="s">
-        <v>8212</v>
+        <v>8214</v>
       </c>
       <c r="G1289" s="5" t="s">
-        <v>8213</v>
+        <v>8215</v>
       </c>
       <c r="H1289" s="5" t="s">
-        <v>8214</v>
+        <v>8216</v>
       </c>
     </row>
     <row r="1290">
       <c r="B1290" s="6" t="s">
-        <v>8215</v>
+        <v>8217</v>
       </c>
       <c r="C1290" s="6" t="s">
-        <v>8216</v>
+        <v>8218</v>
       </c>
       <c r="D1290" s="6" t="s">
-        <v>8217</v>
+        <v>8219</v>
       </c>
       <c r="E1290" s="6" t="s">
-        <v>8218</v>
+        <v>8220</v>
       </c>
       <c r="F1290" s="6" t="s">
-        <v>8219</v>
+        <v>8221</v>
       </c>
       <c r="G1290" s="6" t="s">
-        <v>8219</v>
+        <v>8221</v>
       </c>
       <c r="H1290" s="6" t="s">
-        <v>8220</v>
+        <v>8222</v>
       </c>
     </row>
     <row r="1291">
       <c r="B1291" s="5" t="s">
-        <v>8221</v>
+        <v>8223</v>
       </c>
       <c r="C1291" s="5" t="s">
-        <v>8222</v>
+        <v>8224</v>
       </c>
       <c r="D1291" s="5" t="s">
-        <v>8223</v>
+        <v>8225</v>
       </c>
       <c r="E1291" s="5" t="s">
-        <v>8224</v>
+        <v>8226</v>
       </c>
       <c r="F1291" s="5" t="s">
-        <v>8225</v>
+        <v>8227</v>
       </c>
       <c r="G1291" s="5" t="s">
-        <v>8226</v>
+        <v>8227</v>
       </c>
       <c r="H1291" s="5" t="s">
-        <v>8227</v>
+        <v>8228</v>
       </c>
     </row>
     <row r="1292">
       <c r="B1292" s="6" t="s">
-        <v>8228</v>
+        <v>8229</v>
       </c>
       <c r="C1292" s="6" t="s">
-        <v>8229</v>
+        <v>8230</v>
       </c>
       <c r="D1292" s="6" t="s">
-        <v>8230</v>
+        <v>8231</v>
       </c>
       <c r="E1292" s="6" t="s">
-        <v>8231</v>
+        <v>8232</v>
       </c>
       <c r="F1292" s="6" t="s">
-        <v>8232</v>
+        <v>8233</v>
       </c>
       <c r="G1292" s="6" t="s">
-        <v>8232</v>
+        <v>8234</v>
       </c>
       <c r="H1292" s="6" t="s">
-        <v>8233</v>
+        <v>8235</v>
       </c>
     </row>
     <row r="1293">
       <c r="B1293" s="5" t="s">
-        <v>8234</v>
+        <v>8236</v>
       </c>
       <c r="C1293" s="5" t="s">
-        <v>8235</v>
+        <v>8237</v>
       </c>
       <c r="D1293" s="5" t="s">
-        <v>8236</v>
+        <v>8238</v>
       </c>
       <c r="E1293" s="5" t="s">
-        <v>8237</v>
+        <v>8239</v>
       </c>
       <c r="F1293" s="5" t="s">
-        <v>8238</v>
+        <v>8240</v>
       </c>
       <c r="G1293" s="5" t="s">
-        <v>8238</v>
+        <v>8240</v>
       </c>
       <c r="H1293" s="5" t="s">
-        <v>8239</v>
+        <v>8241</v>
       </c>
     </row>
     <row r="1294">
       <c r="B1294" s="6" t="s">
-        <v>8240</v>
+        <v>8242</v>
       </c>
       <c r="C1294" s="6" t="s">
-        <v>8241</v>
+        <v>8243</v>
       </c>
       <c r="D1294" s="6" t="s">
-        <v>8241</v>
+        <v>8244</v>
       </c>
       <c r="E1294" s="6" t="s">
-        <v>8241</v>
+        <v>8245</v>
       </c>
       <c r="F1294" s="6" t="s">
-        <v>8241</v>
+        <v>8246</v>
       </c>
       <c r="G1294" s="6" t="s">
-        <v>8241</v>
+        <v>8247</v>
       </c>
       <c r="H1294" s="6" t="s">
-        <v>8241</v>
+        <v>8248</v>
       </c>
     </row>
     <row r="1295">
       <c r="B1295" s="5" t="s">
-        <v>8242</v>
+        <v>8249</v>
       </c>
       <c r="C1295" s="5" t="s">
-        <v>8243</v>
+        <v>8250</v>
       </c>
       <c r="D1295" s="5" t="s">
-        <v>8244</v>
+        <v>8251</v>
       </c>
       <c r="E1295" s="5" t="s">
-        <v>8245</v>
+        <v>8252</v>
       </c>
       <c r="F1295" s="5" t="s">
-        <v>8246</v>
+        <v>8253</v>
       </c>
       <c r="G1295" s="5" t="s">
-        <v>8246</v>
+        <v>8253</v>
       </c>
       <c r="H1295" s="5" t="s">
-        <v>8244</v>
+        <v>8254</v>
       </c>
     </row>
     <row r="1296">
       <c r="B1296" s="6" t="s">
-        <v>8247</v>
+        <v>8255</v>
       </c>
       <c r="C1296" s="6" t="s">
-        <v>8248</v>
+        <v>8256</v>
       </c>
       <c r="D1296" s="6" t="s">
-        <v>8249</v>
+        <v>8257</v>
       </c>
       <c r="E1296" s="6" t="s">
-        <v>8250</v>
+        <v>8258</v>
       </c>
       <c r="F1296" s="6" t="s">
-        <v>8251</v>
+        <v>8259</v>
       </c>
       <c r="G1296" s="6" t="s">
-        <v>8252</v>
+        <v>8259</v>
       </c>
       <c r="H1296" s="6" t="s">
-        <v>8249</v>
+        <v>8260</v>
       </c>
     </row>
     <row r="1297">
       <c r="B1297" s="5" t="s">
-        <v>8253</v>
+        <v>8261</v>
       </c>
       <c r="C1297" s="5" t="s">
-        <v>8254</v>
+        <v>8262</v>
       </c>
       <c r="D1297" s="5" t="s">
-        <v>8255</v>
+        <v>8262</v>
       </c>
       <c r="E1297" s="5" t="s">
-        <v>8256</v>
+        <v>8262</v>
       </c>
       <c r="F1297" s="5" t="s">
-        <v>8256</v>
+        <v>8262</v>
       </c>
       <c r="G1297" s="5" t="s">
-        <v>8256</v>
+        <v>8262</v>
       </c>
       <c r="H1297" s="5" t="s">
-        <v>8255</v>
+        <v>8262</v>
       </c>
     </row>
     <row r="1298">
       <c r="B1298" s="6" t="s">
-        <v>8257</v>
+        <v>8263</v>
       </c>
       <c r="C1298" s="6" t="s">
-        <v>8258</v>
+        <v>8264</v>
       </c>
       <c r="D1298" s="6" t="s">
-        <v>8259</v>
+        <v>8265</v>
       </c>
       <c r="E1298" s="6" t="s">
-        <v>8260</v>
+        <v>8266</v>
       </c>
       <c r="F1298" s="6" t="s">
-        <v>8260</v>
+        <v>8267</v>
       </c>
       <c r="G1298" s="6" t="s">
-        <v>8260</v>
+        <v>8267</v>
       </c>
       <c r="H1298" s="6" t="s">
-        <v>8259</v>
+        <v>8265</v>
       </c>
     </row>
     <row r="1299">
       <c r="B1299" s="5" t="s">
-        <v>8261</v>
+        <v>8268</v>
       </c>
       <c r="C1299" s="5" t="s">
-        <v>8262</v>
+        <v>8269</v>
       </c>
       <c r="D1299" s="5" t="s">
-        <v>8263</v>
+        <v>8270</v>
       </c>
       <c r="E1299" s="5" t="s">
-        <v>8264</v>
+        <v>8271</v>
       </c>
       <c r="F1299" s="5" t="s">
-        <v>8265</v>
+        <v>8272</v>
       </c>
       <c r="G1299" s="5" t="s">
-        <v>8266</v>
+        <v>8273</v>
       </c>
       <c r="H1299" s="5" t="s">
-        <v>8267</v>
+        <v>8270</v>
       </c>
     </row>
     <row r="1300">
       <c r="B1300" s="6" t="s">
-        <v>8268</v>
+        <v>8274</v>
       </c>
       <c r="C1300" s="6" t="s">
-        <v>8269</v>
+        <v>8275</v>
       </c>
       <c r="D1300" s="6" t="s">
-        <v>8270</v>
+        <v>8276</v>
       </c>
       <c r="E1300" s="6" t="s">
-        <v>8271</v>
+        <v>8277</v>
       </c>
       <c r="F1300" s="6" t="s">
-        <v>8272</v>
+        <v>8277</v>
       </c>
       <c r="G1300" s="6" t="s">
-        <v>8273</v>
+        <v>8277</v>
       </c>
       <c r="H1300" s="6" t="s">
-        <v>8270</v>
+        <v>8276</v>
       </c>
     </row>
     <row r="1301">
       <c r="B1301" s="5" t="s">
-        <v>8274</v>
+        <v>8278</v>
       </c>
       <c r="C1301" s="5" t="s">
-        <v>8275</v>
+        <v>8279</v>
       </c>
       <c r="D1301" s="5" t="s">
-        <v>8276</v>
+        <v>8280</v>
       </c>
       <c r="E1301" s="5" t="s">
-        <v>8277</v>
+        <v>8281</v>
       </c>
       <c r="F1301" s="5" t="s">
-        <v>8278</v>
+        <v>8281</v>
       </c>
       <c r="G1301" s="5" t="s">
-        <v>8279</v>
+        <v>8281</v>
       </c>
       <c r="H1301" s="5" t="s">
         <v>8280</v>
@@ -59288,48 +59351,48 @@
     </row>
     <row r="1302">
       <c r="B1302" s="6" t="s">
-        <v>8281</v>
+        <v>8282</v>
       </c>
       <c r="C1302" s="6" t="s">
-        <v>8282</v>
+        <v>8283</v>
       </c>
       <c r="D1302" s="6" t="s">
-        <v>8283</v>
+        <v>8284</v>
       </c>
       <c r="E1302" s="6" t="s">
-        <v>8284</v>
+        <v>8285</v>
       </c>
       <c r="F1302" s="6" t="s">
-        <v>8285</v>
+        <v>8286</v>
       </c>
       <c r="G1302" s="6" t="s">
-        <v>8286</v>
+        <v>8287</v>
       </c>
       <c r="H1302" s="6" t="s">
-        <v>8287</v>
+        <v>8288</v>
       </c>
     </row>
     <row r="1303">
       <c r="B1303" s="5" t="s">
-        <v>8288</v>
+        <v>8289</v>
       </c>
       <c r="C1303" s="5" t="s">
-        <v>8289</v>
+        <v>8290</v>
       </c>
       <c r="D1303" s="5" t="s">
-        <v>8290</v>
+        <v>8291</v>
       </c>
       <c r="E1303" s="5" t="s">
+        <v>8292</v>
+      </c>
+      <c r="F1303" s="5" t="s">
+        <v>8293</v>
+      </c>
+      <c r="G1303" s="5" t="s">
+        <v>8294</v>
+      </c>
+      <c r="H1303" s="5" t="s">
         <v>8291</v>
-      </c>
-      <c r="F1303" s="5" t="s">
-        <v>8292</v>
-      </c>
-      <c r="G1303" s="5" t="s">
-        <v>8293</v>
-      </c>
-      <c r="H1303" s="5" t="s">
-        <v>8294</v>
       </c>
     </row>
     <row r="1304">
@@ -59352,323 +59415,323 @@
         <v>8300</v>
       </c>
       <c r="H1304" s="6" t="s">
-        <v>8270</v>
+        <v>8301</v>
       </c>
     </row>
     <row r="1305">
       <c r="B1305" s="5" t="s">
-        <v>8301</v>
+        <v>8302</v>
       </c>
       <c r="C1305" s="5" t="s">
-        <v>8302</v>
+        <v>8303</v>
       </c>
       <c r="D1305" s="5" t="s">
-        <v>8303</v>
+        <v>8304</v>
       </c>
       <c r="E1305" s="5" t="s">
-        <v>8304</v>
+        <v>8305</v>
       </c>
       <c r="F1305" s="5" t="s">
-        <v>8305</v>
+        <v>8306</v>
       </c>
       <c r="G1305" s="5" t="s">
-        <v>8306</v>
+        <v>8307</v>
       </c>
       <c r="H1305" s="5" t="s">
-        <v>8307</v>
+        <v>8308</v>
       </c>
     </row>
     <row r="1306">
       <c r="B1306" s="6" t="s">
-        <v>8308</v>
+        <v>8309</v>
       </c>
       <c r="C1306" s="6" t="s">
-        <v>8309</v>
+        <v>8310</v>
       </c>
       <c r="D1306" s="6" t="s">
-        <v>8310</v>
+        <v>8311</v>
       </c>
       <c r="E1306" s="6" t="s">
-        <v>8311</v>
+        <v>8312</v>
       </c>
       <c r="F1306" s="6" t="s">
-        <v>8312</v>
+        <v>8313</v>
       </c>
       <c r="G1306" s="6" t="s">
-        <v>8312</v>
+        <v>8314</v>
       </c>
       <c r="H1306" s="6" t="s">
-        <v>8313</v>
+        <v>8315</v>
       </c>
     </row>
     <row r="1307">
       <c r="B1307" s="5" t="s">
-        <v>8314</v>
+        <v>8316</v>
       </c>
       <c r="C1307" s="5" t="s">
-        <v>8315</v>
+        <v>8317</v>
       </c>
       <c r="D1307" s="5" t="s">
-        <v>8316</v>
+        <v>8318</v>
       </c>
       <c r="E1307" s="5" t="s">
-        <v>8317</v>
+        <v>8319</v>
       </c>
       <c r="F1307" s="5" t="s">
-        <v>8318</v>
+        <v>8320</v>
       </c>
       <c r="G1307" s="5" t="s">
-        <v>8319</v>
+        <v>8321</v>
       </c>
       <c r="H1307" s="5" t="s">
-        <v>8320</v>
+        <v>8291</v>
       </c>
     </row>
     <row r="1308">
       <c r="B1308" s="6" t="s">
-        <v>8321</v>
+        <v>8322</v>
       </c>
       <c r="C1308" s="6" t="s">
-        <v>8322</v>
+        <v>8323</v>
       </c>
       <c r="D1308" s="6" t="s">
-        <v>8323</v>
+        <v>8324</v>
       </c>
       <c r="E1308" s="6" t="s">
-        <v>8324</v>
+        <v>8325</v>
       </c>
       <c r="F1308" s="6" t="s">
-        <v>8325</v>
+        <v>8326</v>
       </c>
       <c r="G1308" s="6" t="s">
-        <v>8326</v>
+        <v>8327</v>
       </c>
       <c r="H1308" s="6" t="s">
-        <v>8327</v>
+        <v>8328</v>
       </c>
     </row>
     <row r="1309">
       <c r="B1309" s="5" t="s">
-        <v>8328</v>
+        <v>8329</v>
       </c>
       <c r="C1309" s="5" t="s">
-        <v>8329</v>
+        <v>8330</v>
       </c>
       <c r="D1309" s="5" t="s">
-        <v>8330</v>
+        <v>8331</v>
       </c>
       <c r="E1309" s="5" t="s">
-        <v>8331</v>
+        <v>8332</v>
       </c>
       <c r="F1309" s="5" t="s">
-        <v>8332</v>
+        <v>8333</v>
       </c>
       <c r="G1309" s="5" t="s">
-        <v>8332</v>
+        <v>8333</v>
       </c>
       <c r="H1309" s="5" t="s">
-        <v>8333</v>
+        <v>8334</v>
       </c>
     </row>
     <row r="1310">
       <c r="B1310" s="6" t="s">
-        <v>8334</v>
+        <v>8335</v>
       </c>
       <c r="C1310" s="6" t="s">
-        <v>6033</v>
+        <v>8336</v>
       </c>
       <c r="D1310" s="6" t="s">
-        <v>6936</v>
+        <v>8337</v>
       </c>
       <c r="E1310" s="6" t="s">
-        <v>6035</v>
+        <v>8338</v>
       </c>
       <c r="F1310" s="6" t="s">
-        <v>8335</v>
+        <v>8339</v>
       </c>
       <c r="G1310" s="6" t="s">
-        <v>8335</v>
+        <v>8340</v>
       </c>
       <c r="H1310" s="6" t="s">
-        <v>5404</v>
+        <v>8341</v>
       </c>
     </row>
     <row r="1311">
       <c r="B1311" s="5" t="s">
-        <v>8336</v>
+        <v>8342</v>
       </c>
       <c r="C1311" s="5" t="s">
-        <v>8337</v>
+        <v>8343</v>
       </c>
       <c r="D1311" s="5" t="s">
-        <v>8338</v>
+        <v>8344</v>
       </c>
       <c r="E1311" s="5" t="s">
-        <v>8339</v>
+        <v>8345</v>
       </c>
       <c r="F1311" s="5" t="s">
-        <v>8340</v>
+        <v>8346</v>
       </c>
       <c r="G1311" s="5" t="s">
-        <v>8340</v>
+        <v>8347</v>
       </c>
       <c r="H1311" s="5" t="s">
-        <v>8341</v>
+        <v>8348</v>
       </c>
     </row>
     <row r="1312">
       <c r="B1312" s="6" t="s">
-        <v>8342</v>
+        <v>8349</v>
       </c>
       <c r="C1312" s="6" t="s">
-        <v>8343</v>
+        <v>8350</v>
       </c>
       <c r="D1312" s="6" t="s">
-        <v>8344</v>
+        <v>8351</v>
       </c>
       <c r="E1312" s="6" t="s">
-        <v>8345</v>
+        <v>8352</v>
       </c>
       <c r="F1312" s="6" t="s">
-        <v>8346</v>
+        <v>8353</v>
       </c>
       <c r="G1312" s="6" t="s">
-        <v>8347</v>
+        <v>8353</v>
       </c>
       <c r="H1312" s="6" t="s">
-        <v>8348</v>
+        <v>8354</v>
       </c>
     </row>
     <row r="1313">
       <c r="B1313" s="5" t="s">
-        <v>8349</v>
+        <v>8355</v>
       </c>
       <c r="C1313" s="5" t="s">
-        <v>8350</v>
+        <v>6033</v>
       </c>
       <c r="D1313" s="5" t="s">
-        <v>8351</v>
+        <v>6936</v>
       </c>
       <c r="E1313" s="5" t="s">
-        <v>8352</v>
+        <v>6035</v>
       </c>
       <c r="F1313" s="5" t="s">
-        <v>8353</v>
+        <v>8356</v>
       </c>
       <c r="G1313" s="5" t="s">
-        <v>8354</v>
+        <v>8356</v>
       </c>
       <c r="H1313" s="5" t="s">
-        <v>8355</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1314">
       <c r="B1314" s="6" t="s">
-        <v>8356</v>
+        <v>8357</v>
       </c>
       <c r="C1314" s="6" t="s">
-        <v>8357</v>
+        <v>8358</v>
       </c>
       <c r="D1314" s="6" t="s">
-        <v>8358</v>
+        <v>8359</v>
       </c>
       <c r="E1314" s="6" t="s">
-        <v>8358</v>
+        <v>8360</v>
       </c>
       <c r="F1314" s="6" t="s">
-        <v>8358</v>
+        <v>8361</v>
       </c>
       <c r="G1314" s="6" t="s">
-        <v>8358</v>
+        <v>8361</v>
       </c>
       <c r="H1314" s="6" t="s">
-        <v>8358</v>
+        <v>8362</v>
       </c>
     </row>
     <row r="1315">
       <c r="B1315" s="5" t="s">
-        <v>8359</v>
+        <v>8363</v>
       </c>
       <c r="C1315" s="5" t="s">
-        <v>8360</v>
+        <v>8364</v>
       </c>
       <c r="D1315" s="5" t="s">
-        <v>8361</v>
+        <v>8365</v>
       </c>
       <c r="E1315" s="5" t="s">
-        <v>8362</v>
+        <v>8366</v>
       </c>
       <c r="F1315" s="5" t="s">
-        <v>8363</v>
+        <v>8367</v>
       </c>
       <c r="G1315" s="5" t="s">
-        <v>8363</v>
+        <v>8368</v>
       </c>
       <c r="H1315" s="5" t="s">
-        <v>8364</v>
+        <v>8369</v>
       </c>
     </row>
     <row r="1316">
       <c r="B1316" s="6" t="s">
-        <v>8365</v>
+        <v>8370</v>
       </c>
       <c r="C1316" s="6" t="s">
-        <v>8366</v>
+        <v>8371</v>
       </c>
       <c r="D1316" s="6" t="s">
-        <v>8367</v>
+        <v>8372</v>
       </c>
       <c r="E1316" s="6" t="s">
-        <v>8368</v>
+        <v>8373</v>
       </c>
       <c r="F1316" s="6" t="s">
-        <v>8369</v>
+        <v>8374</v>
       </c>
       <c r="G1316" s="6" t="s">
-        <v>8370</v>
+        <v>8375</v>
       </c>
       <c r="H1316" s="6" t="s">
-        <v>8371</v>
+        <v>8376</v>
       </c>
     </row>
     <row r="1317">
       <c r="B1317" s="5" t="s">
-        <v>8372</v>
+        <v>8377</v>
       </c>
       <c r="C1317" s="5" t="s">
-        <v>8373</v>
+        <v>8378</v>
       </c>
       <c r="D1317" s="5" t="s">
-        <v>8374</v>
+        <v>8379</v>
       </c>
       <c r="E1317" s="5" t="s">
-        <v>8375</v>
+        <v>8379</v>
       </c>
       <c r="F1317" s="5" t="s">
-        <v>8376</v>
+        <v>8379</v>
       </c>
       <c r="G1317" s="5" t="s">
-        <v>8377</v>
+        <v>8379</v>
       </c>
       <c r="H1317" s="5" t="s">
-        <v>8378</v>
+        <v>8379</v>
       </c>
     </row>
     <row r="1318">
       <c r="B1318" s="6" t="s">
-        <v>8379</v>
+        <v>8380</v>
       </c>
       <c r="C1318" s="6" t="s">
-        <v>8380</v>
+        <v>8381</v>
       </c>
       <c r="D1318" s="6" t="s">
-        <v>8381</v>
+        <v>8382</v>
       </c>
       <c r="E1318" s="6" t="s">
-        <v>8382</v>
+        <v>8383</v>
       </c>
       <c r="F1318" s="6" t="s">
-        <v>8383</v>
+        <v>8384</v>
       </c>
       <c r="G1318" s="6" t="s">
         <v>8384</v>
@@ -59688,585 +59751,585 @@
         <v>8388</v>
       </c>
       <c r="E1319" s="5" t="s">
-        <v>6245</v>
+        <v>8389</v>
       </c>
       <c r="F1319" s="5" t="s">
-        <v>6246</v>
+        <v>8390</v>
       </c>
       <c r="G1319" s="5" t="s">
-        <v>6246</v>
+        <v>8391</v>
       </c>
       <c r="H1319" s="5" t="s">
-        <v>7423</v>
+        <v>8392</v>
       </c>
     </row>
     <row r="1320">
       <c r="B1320" s="6" t="s">
-        <v>8389</v>
+        <v>8393</v>
       </c>
       <c r="C1320" s="6" t="s">
-        <v>8390</v>
+        <v>8394</v>
       </c>
       <c r="D1320" s="6" t="s">
-        <v>8391</v>
+        <v>8395</v>
       </c>
       <c r="E1320" s="6" t="s">
-        <v>8392</v>
+        <v>8396</v>
       </c>
       <c r="F1320" s="6" t="s">
-        <v>8393</v>
+        <v>8397</v>
       </c>
       <c r="G1320" s="6" t="s">
-        <v>8394</v>
+        <v>8398</v>
       </c>
       <c r="H1320" s="6" t="s">
-        <v>8391</v>
+        <v>8399</v>
       </c>
     </row>
     <row r="1321">
       <c r="B1321" s="5" t="s">
-        <v>8395</v>
+        <v>8400</v>
       </c>
       <c r="C1321" s="5" t="s">
-        <v>8396</v>
+        <v>8401</v>
       </c>
       <c r="D1321" s="5" t="s">
-        <v>8397</v>
+        <v>8402</v>
       </c>
       <c r="E1321" s="5" t="s">
-        <v>8398</v>
+        <v>8403</v>
       </c>
       <c r="F1321" s="5" t="s">
-        <v>8399</v>
+        <v>8404</v>
       </c>
       <c r="G1321" s="5" t="s">
-        <v>8400</v>
+        <v>8405</v>
       </c>
       <c r="H1321" s="5" t="s">
-        <v>8401</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="1322">
       <c r="B1322" s="6" t="s">
-        <v>8402</v>
+        <v>8407</v>
       </c>
       <c r="C1322" s="6" t="s">
-        <v>8403</v>
+        <v>8408</v>
       </c>
       <c r="D1322" s="6" t="s">
-        <v>8404</v>
+        <v>8409</v>
       </c>
       <c r="E1322" s="6" t="s">
-        <v>8405</v>
+        <v>6245</v>
       </c>
       <c r="F1322" s="6" t="s">
-        <v>8406</v>
+        <v>6246</v>
       </c>
       <c r="G1322" s="6" t="s">
-        <v>8406</v>
+        <v>6246</v>
       </c>
       <c r="H1322" s="6" t="s">
-        <v>8407</v>
+        <v>7423</v>
       </c>
     </row>
     <row r="1323">
       <c r="B1323" s="5" t="s">
-        <v>8408</v>
+        <v>8410</v>
       </c>
       <c r="C1323" s="5" t="s">
-        <v>8409</v>
+        <v>8411</v>
       </c>
       <c r="D1323" s="5" t="s">
-        <v>8410</v>
+        <v>8412</v>
       </c>
       <c r="E1323" s="5" t="s">
-        <v>8411</v>
+        <v>8413</v>
       </c>
       <c r="F1323" s="5" t="s">
+        <v>8414</v>
+      </c>
+      <c r="G1323" s="5" t="s">
+        <v>8415</v>
+      </c>
+      <c r="H1323" s="5" t="s">
         <v>8412</v>
-      </c>
-      <c r="G1323" s="5" t="s">
-        <v>8413</v>
-      </c>
-      <c r="H1323" s="5" t="s">
-        <v>8414</v>
       </c>
     </row>
     <row r="1324">
       <c r="B1324" s="6" t="s">
-        <v>8415</v>
+        <v>8416</v>
       </c>
       <c r="C1324" s="6" t="s">
-        <v>8416</v>
+        <v>8417</v>
       </c>
       <c r="D1324" s="6" t="s">
-        <v>8417</v>
+        <v>8418</v>
       </c>
       <c r="E1324" s="6" t="s">
-        <v>8418</v>
+        <v>8419</v>
       </c>
       <c r="F1324" s="6" t="s">
-        <v>8419</v>
+        <v>8420</v>
       </c>
       <c r="G1324" s="6" t="s">
-        <v>8420</v>
+        <v>8421</v>
       </c>
       <c r="H1324" s="6" t="s">
-        <v>8421</v>
+        <v>8422</v>
       </c>
     </row>
     <row r="1325">
       <c r="B1325" s="5" t="s">
-        <v>8422</v>
+        <v>8423</v>
       </c>
       <c r="C1325" s="5" t="s">
-        <v>8423</v>
+        <v>8424</v>
       </c>
       <c r="D1325" s="5" t="s">
-        <v>8424</v>
+        <v>8425</v>
       </c>
       <c r="E1325" s="5" t="s">
-        <v>8425</v>
+        <v>8426</v>
       </c>
       <c r="F1325" s="5" t="s">
-        <v>8426</v>
+        <v>8427</v>
       </c>
       <c r="G1325" s="5" t="s">
-        <v>8426</v>
+        <v>8427</v>
       </c>
       <c r="H1325" s="5" t="s">
-        <v>8427</v>
+        <v>8428</v>
       </c>
     </row>
     <row r="1326">
       <c r="B1326" s="6" t="s">
-        <v>8428</v>
+        <v>8429</v>
       </c>
       <c r="C1326" s="6" t="s">
-        <v>8429</v>
+        <v>8430</v>
       </c>
       <c r="D1326" s="6" t="s">
-        <v>8430</v>
+        <v>8431</v>
       </c>
       <c r="E1326" s="6" t="s">
-        <v>8431</v>
+        <v>8432</v>
       </c>
       <c r="F1326" s="6" t="s">
-        <v>8432</v>
+        <v>8433</v>
       </c>
       <c r="G1326" s="6" t="s">
-        <v>8432</v>
+        <v>8434</v>
       </c>
       <c r="H1326" s="6" t="s">
-        <v>8433</v>
+        <v>8435</v>
       </c>
     </row>
     <row r="1327">
       <c r="B1327" s="5" t="s">
-        <v>8434</v>
+        <v>8436</v>
       </c>
       <c r="C1327" s="5" t="s">
-        <v>8435</v>
+        <v>8437</v>
       </c>
       <c r="D1327" s="5" t="s">
-        <v>8436</v>
+        <v>8438</v>
       </c>
       <c r="E1327" s="5" t="s">
-        <v>8437</v>
+        <v>8439</v>
       </c>
       <c r="F1327" s="5" t="s">
-        <v>8438</v>
+        <v>8440</v>
       </c>
       <c r="G1327" s="5" t="s">
-        <v>8438</v>
+        <v>8441</v>
       </c>
       <c r="H1327" s="5" t="s">
-        <v>8439</v>
+        <v>8442</v>
       </c>
     </row>
     <row r="1328">
       <c r="B1328" s="6" t="s">
-        <v>8440</v>
+        <v>8443</v>
       </c>
       <c r="C1328" s="6" t="s">
-        <v>8441</v>
+        <v>8444</v>
       </c>
       <c r="D1328" s="6" t="s">
-        <v>8442</v>
+        <v>8445</v>
       </c>
       <c r="E1328" s="6" t="s">
-        <v>8443</v>
+        <v>8446</v>
       </c>
       <c r="F1328" s="6" t="s">
-        <v>8444</v>
+        <v>8447</v>
       </c>
       <c r="G1328" s="6" t="s">
-        <v>8445</v>
+        <v>8447</v>
       </c>
       <c r="H1328" s="6" t="s">
-        <v>8446</v>
+        <v>8448</v>
       </c>
     </row>
     <row r="1329">
       <c r="B1329" s="5" t="s">
-        <v>8447</v>
+        <v>8449</v>
       </c>
       <c r="C1329" s="5" t="s">
-        <v>8448</v>
+        <v>8450</v>
       </c>
       <c r="D1329" s="5" t="s">
-        <v>8449</v>
+        <v>8451</v>
       </c>
       <c r="E1329" s="5" t="s">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="F1329" s="5" t="s">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="G1329" s="5" t="s">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="H1329" s="5" t="s">
-        <v>8453</v>
+        <v>8454</v>
       </c>
     </row>
     <row r="1330">
       <c r="B1330" s="6" t="s">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="C1330" s="6" t="s">
-        <v>8455</v>
+        <v>8456</v>
       </c>
       <c r="D1330" s="6" t="s">
-        <v>8456</v>
+        <v>8457</v>
       </c>
       <c r="E1330" s="6" t="s">
-        <v>8457</v>
+        <v>8458</v>
       </c>
       <c r="F1330" s="6" t="s">
-        <v>8458</v>
+        <v>8459</v>
       </c>
       <c r="G1330" s="6" t="s">
-        <v>8458</v>
+        <v>8459</v>
       </c>
       <c r="H1330" s="6" t="s">
-        <v>8459</v>
+        <v>8460</v>
       </c>
     </row>
     <row r="1331">
       <c r="B1331" s="5" t="s">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="C1331" s="5" t="s">
-        <v>8461</v>
+        <v>8462</v>
       </c>
       <c r="D1331" s="5" t="s">
-        <v>8462</v>
+        <v>8463</v>
       </c>
       <c r="E1331" s="5" t="s">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="F1331" s="5" t="s">
-        <v>8464</v>
+        <v>8465</v>
       </c>
       <c r="G1331" s="5" t="s">
-        <v>8465</v>
+        <v>8466</v>
       </c>
       <c r="H1331" s="5" t="s">
-        <v>8466</v>
+        <v>8467</v>
       </c>
     </row>
     <row r="1332">
       <c r="B1332" s="6" t="s">
-        <v>8467</v>
+        <v>8468</v>
       </c>
       <c r="C1332" s="6" t="s">
-        <v>8468</v>
+        <v>8469</v>
       </c>
       <c r="D1332" s="6" t="s">
-        <v>8469</v>
+        <v>8470</v>
       </c>
       <c r="E1332" s="6" t="s">
-        <v>8470</v>
+        <v>8471</v>
       </c>
       <c r="F1332" s="6" t="s">
-        <v>8471</v>
+        <v>8472</v>
       </c>
       <c r="G1332" s="6" t="s">
-        <v>8471</v>
+        <v>8473</v>
       </c>
       <c r="H1332" s="6" t="s">
-        <v>8472</v>
+        <v>8474</v>
       </c>
     </row>
     <row r="1333">
       <c r="B1333" s="5" t="s">
-        <v>8473</v>
+        <v>8475</v>
       </c>
       <c r="C1333" s="5" t="s">
-        <v>8474</v>
+        <v>8476</v>
       </c>
       <c r="D1333" s="5" t="s">
-        <v>8475</v>
+        <v>8477</v>
       </c>
       <c r="E1333" s="5" t="s">
-        <v>8476</v>
+        <v>8478</v>
       </c>
       <c r="F1333" s="5" t="s">
-        <v>8477</v>
+        <v>8479</v>
       </c>
       <c r="G1333" s="5" t="s">
-        <v>8478</v>
+        <v>8479</v>
       </c>
       <c r="H1333" s="5" t="s">
-        <v>8479</v>
+        <v>8480</v>
       </c>
     </row>
     <row r="1334">
       <c r="B1334" s="6" t="s">
-        <v>8480</v>
+        <v>8481</v>
       </c>
       <c r="C1334" s="6" t="s">
-        <v>8481</v>
+        <v>8482</v>
       </c>
       <c r="D1334" s="6" t="s">
-        <v>8482</v>
+        <v>8483</v>
       </c>
       <c r="E1334" s="6" t="s">
-        <v>8483</v>
+        <v>8484</v>
       </c>
       <c r="F1334" s="6" t="s">
-        <v>8484</v>
+        <v>8485</v>
       </c>
       <c r="G1334" s="6" t="s">
-        <v>8484</v>
+        <v>8486</v>
       </c>
       <c r="H1334" s="6" t="s">
-        <v>8485</v>
+        <v>8487</v>
       </c>
     </row>
     <row r="1335">
       <c r="B1335" s="5" t="s">
-        <v>8486</v>
+        <v>8488</v>
       </c>
       <c r="C1335" s="5" t="s">
-        <v>8487</v>
+        <v>8489</v>
       </c>
       <c r="D1335" s="5" t="s">
-        <v>8488</v>
+        <v>8490</v>
       </c>
       <c r="E1335" s="5" t="s">
-        <v>8489</v>
+        <v>8491</v>
       </c>
       <c r="F1335" s="5" t="s">
-        <v>8490</v>
+        <v>8492</v>
       </c>
       <c r="G1335" s="5" t="s">
-        <v>8490</v>
+        <v>8492</v>
       </c>
       <c r="H1335" s="5" t="s">
-        <v>8491</v>
+        <v>8493</v>
       </c>
     </row>
     <row r="1336">
       <c r="B1336" s="6" t="s">
-        <v>8492</v>
+        <v>8494</v>
       </c>
       <c r="C1336" s="6" t="s">
-        <v>8493</v>
+        <v>8495</v>
       </c>
       <c r="D1336" s="6" t="s">
-        <v>2758</v>
+        <v>8496</v>
       </c>
       <c r="E1336" s="6" t="s">
-        <v>2759</v>
+        <v>8497</v>
       </c>
       <c r="F1336" s="6" t="s">
-        <v>2760</v>
+        <v>8498</v>
       </c>
       <c r="G1336" s="6" t="s">
-        <v>2760</v>
+        <v>8499</v>
       </c>
       <c r="H1336" s="6" t="s">
-        <v>2761</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="1337">
       <c r="B1337" s="5" t="s">
-        <v>8494</v>
+        <v>8501</v>
       </c>
       <c r="C1337" s="5" t="s">
-        <v>8495</v>
+        <v>8502</v>
       </c>
       <c r="D1337" s="5" t="s">
-        <v>8496</v>
+        <v>8503</v>
       </c>
       <c r="E1337" s="5" t="s">
-        <v>8497</v>
+        <v>8504</v>
       </c>
       <c r="F1337" s="5" t="s">
-        <v>8498</v>
+        <v>8505</v>
       </c>
       <c r="G1337" s="5" t="s">
-        <v>8498</v>
+        <v>8505</v>
       </c>
       <c r="H1337" s="5" t="s">
-        <v>8499</v>
+        <v>8506</v>
       </c>
     </row>
     <row r="1338">
       <c r="B1338" s="6" t="s">
-        <v>8500</v>
+        <v>8507</v>
       </c>
       <c r="C1338" s="6" t="s">
-        <v>8501</v>
+        <v>8508</v>
       </c>
       <c r="D1338" s="6" t="s">
-        <v>8502</v>
+        <v>8509</v>
       </c>
       <c r="E1338" s="6" t="s">
-        <v>8503</v>
+        <v>8510</v>
       </c>
       <c r="F1338" s="6" t="s">
-        <v>8504</v>
+        <v>8511</v>
       </c>
       <c r="G1338" s="6" t="s">
-        <v>8503</v>
+        <v>8511</v>
       </c>
       <c r="H1338" s="6" t="s">
-        <v>8505</v>
+        <v>8512</v>
       </c>
     </row>
     <row r="1339">
       <c r="B1339" s="5" t="s">
-        <v>8506</v>
+        <v>8513</v>
       </c>
       <c r="C1339" s="5" t="s">
-        <v>8507</v>
+        <v>8514</v>
       </c>
       <c r="D1339" s="5" t="s">
-        <v>8508</v>
+        <v>2758</v>
       </c>
       <c r="E1339" s="5" t="s">
-        <v>8509</v>
+        <v>2759</v>
       </c>
       <c r="F1339" s="5" t="s">
-        <v>8510</v>
+        <v>2760</v>
       </c>
       <c r="G1339" s="5" t="s">
-        <v>8511</v>
+        <v>2760</v>
       </c>
       <c r="H1339" s="5" t="s">
-        <v>8512</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="1340">
       <c r="B1340" s="6" t="s">
-        <v>8513</v>
+        <v>8515</v>
       </c>
       <c r="C1340" s="6" t="s">
-        <v>8514</v>
+        <v>8516</v>
       </c>
       <c r="D1340" s="6" t="s">
-        <v>8515</v>
+        <v>8517</v>
       </c>
       <c r="E1340" s="6" t="s">
-        <v>8516</v>
+        <v>8518</v>
       </c>
       <c r="F1340" s="6" t="s">
-        <v>8517</v>
+        <v>8519</v>
       </c>
       <c r="G1340" s="6" t="s">
-        <v>8517</v>
+        <v>8519</v>
       </c>
       <c r="H1340" s="6" t="s">
-        <v>8518</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="1341">
       <c r="B1341" s="5" t="s">
-        <v>8519</v>
+        <v>8521</v>
       </c>
       <c r="C1341" s="5" t="s">
-        <v>8520</v>
+        <v>8522</v>
       </c>
       <c r="D1341" s="5" t="s">
-        <v>8521</v>
+        <v>8523</v>
       </c>
       <c r="E1341" s="5" t="s">
-        <v>8522</v>
+        <v>8524</v>
       </c>
       <c r="F1341" s="5" t="s">
-        <v>8523</v>
+        <v>8525</v>
       </c>
       <c r="G1341" s="5" t="s">
-        <v>8523</v>
+        <v>8524</v>
       </c>
       <c r="H1341" s="5" t="s">
-        <v>8524</v>
+        <v>8526</v>
       </c>
     </row>
     <row r="1342">
       <c r="B1342" s="6" t="s">
-        <v>8525</v>
+        <v>8527</v>
       </c>
       <c r="C1342" s="6" t="s">
-        <v>8526</v>
+        <v>8528</v>
       </c>
       <c r="D1342" s="6" t="s">
-        <v>8527</v>
+        <v>8529</v>
       </c>
       <c r="E1342" s="6" t="s">
-        <v>8528</v>
+        <v>8530</v>
       </c>
       <c r="F1342" s="6" t="s">
-        <v>8529</v>
+        <v>8531</v>
       </c>
       <c r="G1342" s="6" t="s">
-        <v>8530</v>
+        <v>8532</v>
       </c>
       <c r="H1342" s="6" t="s">
-        <v>8531</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="1343">
       <c r="B1343" s="5" t="s">
-        <v>8532</v>
+        <v>8534</v>
       </c>
       <c r="C1343" s="5" t="s">
-        <v>8533</v>
+        <v>8535</v>
       </c>
       <c r="D1343" s="5" t="s">
-        <v>8534</v>
+        <v>8536</v>
       </c>
       <c r="E1343" s="5" t="s">
-        <v>8535</v>
+        <v>8537</v>
       </c>
       <c r="F1343" s="5" t="s">
-        <v>8536</v>
+        <v>8538</v>
       </c>
       <c r="G1343" s="5" t="s">
-        <v>8537</v>
+        <v>8538</v>
       </c>
       <c r="H1343" s="5" t="s">
-        <v>8538</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="1344">
       <c r="B1344" s="6" t="s">
-        <v>8539</v>
+        <v>8540</v>
       </c>
       <c r="C1344" s="6" t="s">
-        <v>8540</v>
+        <v>8541</v>
       </c>
       <c r="D1344" s="6" t="s">
-        <v>8541</v>
+        <v>8542</v>
       </c>
       <c r="E1344" s="6" t="s">
-        <v>8542</v>
+        <v>8543</v>
       </c>
       <c r="F1344" s="6" t="s">
-        <v>8543</v>
+        <v>8544</v>
       </c>
       <c r="G1344" s="6" t="s">
         <v>8544</v>
@@ -60280,551 +60343,551 @@
         <v>8546</v>
       </c>
       <c r="C1345" s="5" t="s">
-        <v>6931</v>
+        <v>8547</v>
       </c>
       <c r="D1345" s="5" t="s">
-        <v>8547</v>
+        <v>8548</v>
       </c>
       <c r="E1345" s="5" t="s">
-        <v>6932</v>
+        <v>8549</v>
       </c>
       <c r="F1345" s="5" t="s">
-        <v>6933</v>
+        <v>8550</v>
       </c>
       <c r="G1345" s="5" t="s">
-        <v>6934</v>
+        <v>8551</v>
       </c>
       <c r="H1345" s="5" t="s">
-        <v>8547</v>
+        <v>8552</v>
       </c>
     </row>
     <row r="1346">
       <c r="B1346" s="6" t="s">
-        <v>8548</v>
+        <v>8553</v>
       </c>
       <c r="C1346" s="6" t="s">
-        <v>6895</v>
+        <v>8554</v>
       </c>
       <c r="D1346" s="6" t="s">
-        <v>8549</v>
+        <v>8555</v>
       </c>
       <c r="E1346" s="6" t="s">
-        <v>6897</v>
+        <v>8556</v>
       </c>
       <c r="F1346" s="6" t="s">
-        <v>8550</v>
+        <v>8557</v>
       </c>
       <c r="G1346" s="6" t="s">
-        <v>8551</v>
+        <v>8558</v>
       </c>
       <c r="H1346" s="6" t="s">
-        <v>8552</v>
+        <v>8559</v>
       </c>
     </row>
     <row r="1347">
       <c r="B1347" s="5" t="s">
-        <v>8553</v>
+        <v>8560</v>
       </c>
       <c r="C1347" s="5" t="s">
-        <v>8554</v>
+        <v>8561</v>
       </c>
       <c r="D1347" s="5" t="s">
-        <v>8555</v>
+        <v>8562</v>
       </c>
       <c r="E1347" s="5" t="s">
-        <v>8556</v>
+        <v>8563</v>
       </c>
       <c r="F1347" s="5" t="s">
-        <v>8557</v>
+        <v>8564</v>
       </c>
       <c r="G1347" s="5" t="s">
-        <v>8558</v>
+        <v>8565</v>
       </c>
       <c r="H1347" s="5" t="s">
-        <v>8559</v>
+        <v>8566</v>
       </c>
     </row>
     <row r="1348">
       <c r="B1348" s="6" t="s">
-        <v>8560</v>
+        <v>8567</v>
       </c>
       <c r="C1348" s="6" t="s">
-        <v>8561</v>
+        <v>6931</v>
       </c>
       <c r="D1348" s="6" t="s">
-        <v>8562</v>
+        <v>8568</v>
       </c>
       <c r="E1348" s="6" t="s">
-        <v>8535</v>
+        <v>6932</v>
       </c>
       <c r="F1348" s="6" t="s">
-        <v>8536</v>
+        <v>6933</v>
       </c>
       <c r="G1348" s="6" t="s">
-        <v>8537</v>
+        <v>6934</v>
       </c>
       <c r="H1348" s="6" t="s">
-        <v>8563</v>
+        <v>8568</v>
       </c>
     </row>
     <row r="1349">
       <c r="B1349" s="5" t="s">
-        <v>8564</v>
+        <v>8569</v>
       </c>
       <c r="C1349" s="5" t="s">
-        <v>8565</v>
+        <v>6895</v>
       </c>
       <c r="D1349" s="5" t="s">
-        <v>8566</v>
+        <v>8570</v>
       </c>
       <c r="E1349" s="5" t="s">
-        <v>8567</v>
+        <v>6897</v>
       </c>
       <c r="F1349" s="5" t="s">
-        <v>8568</v>
+        <v>8571</v>
       </c>
       <c r="G1349" s="5" t="s">
-        <v>8569</v>
+        <v>8572</v>
       </c>
       <c r="H1349" s="5" t="s">
-        <v>8570</v>
+        <v>8573</v>
       </c>
     </row>
     <row r="1350">
       <c r="B1350" s="6" t="s">
-        <v>8571</v>
+        <v>8574</v>
       </c>
       <c r="C1350" s="6" t="s">
-        <v>8572</v>
+        <v>8575</v>
       </c>
       <c r="D1350" s="6" t="s">
-        <v>8573</v>
+        <v>8576</v>
       </c>
       <c r="E1350" s="6" t="s">
-        <v>8574</v>
+        <v>8577</v>
       </c>
       <c r="F1350" s="6" t="s">
-        <v>8575</v>
+        <v>8578</v>
       </c>
       <c r="G1350" s="6" t="s">
-        <v>8575</v>
+        <v>8579</v>
       </c>
       <c r="H1350" s="6" t="s">
-        <v>8576</v>
+        <v>8580</v>
       </c>
     </row>
     <row r="1351">
       <c r="B1351" s="5" t="s">
-        <v>8577</v>
+        <v>8581</v>
       </c>
       <c r="C1351" s="5" t="s">
-        <v>8578</v>
+        <v>8582</v>
       </c>
       <c r="D1351" s="5" t="s">
-        <v>8579</v>
+        <v>8583</v>
       </c>
       <c r="E1351" s="5" t="s">
-        <v>8580</v>
+        <v>8556</v>
       </c>
       <c r="F1351" s="5" t="s">
-        <v>8581</v>
+        <v>8557</v>
       </c>
       <c r="G1351" s="5" t="s">
-        <v>8582</v>
+        <v>8558</v>
       </c>
       <c r="H1351" s="5" t="s">
-        <v>8583</v>
+        <v>8584</v>
       </c>
     </row>
     <row r="1352">
       <c r="B1352" s="6" t="s">
-        <v>8584</v>
+        <v>8585</v>
       </c>
       <c r="C1352" s="6" t="s">
-        <v>8585</v>
+        <v>8586</v>
       </c>
       <c r="D1352" s="6" t="s">
-        <v>8586</v>
+        <v>8587</v>
       </c>
       <c r="E1352" s="6" t="s">
-        <v>8587</v>
+        <v>8588</v>
       </c>
       <c r="F1352" s="6" t="s">
-        <v>8588</v>
+        <v>8589</v>
       </c>
       <c r="G1352" s="6" t="s">
-        <v>8589</v>
+        <v>8590</v>
       </c>
       <c r="H1352" s="6" t="s">
-        <v>8590</v>
+        <v>8591</v>
       </c>
     </row>
     <row r="1353">
       <c r="B1353" s="5" t="s">
-        <v>8591</v>
+        <v>8592</v>
       </c>
       <c r="C1353" s="5" t="s">
-        <v>8592</v>
+        <v>8593</v>
       </c>
       <c r="D1353" s="5" t="s">
-        <v>8593</v>
+        <v>8594</v>
       </c>
       <c r="E1353" s="5" t="s">
-        <v>8594</v>
+        <v>8595</v>
       </c>
       <c r="F1353" s="5" t="s">
-        <v>7755</v>
+        <v>8596</v>
       </c>
       <c r="G1353" s="5" t="s">
-        <v>7756</v>
+        <v>8596</v>
       </c>
       <c r="H1353" s="5" t="s">
-        <v>8595</v>
+        <v>8597</v>
       </c>
     </row>
     <row r="1354">
       <c r="B1354" s="6" t="s">
-        <v>8596</v>
+        <v>8598</v>
       </c>
       <c r="C1354" s="6" t="s">
-        <v>8597</v>
+        <v>8599</v>
       </c>
       <c r="D1354" s="6" t="s">
-        <v>8598</v>
+        <v>8600</v>
       </c>
       <c r="E1354" s="6" t="s">
-        <v>8599</v>
+        <v>8601</v>
       </c>
       <c r="F1354" s="6" t="s">
-        <v>8600</v>
+        <v>8602</v>
       </c>
       <c r="G1354" s="6" t="s">
-        <v>8601</v>
+        <v>8603</v>
       </c>
       <c r="H1354" s="6" t="s">
-        <v>8602</v>
+        <v>8604</v>
       </c>
     </row>
     <row r="1355">
       <c r="B1355" s="5" t="s">
-        <v>8603</v>
+        <v>8605</v>
       </c>
       <c r="C1355" s="5" t="s">
-        <v>8604</v>
+        <v>8606</v>
       </c>
       <c r="D1355" s="5" t="s">
-        <v>8605</v>
+        <v>8607</v>
       </c>
       <c r="E1355" s="5" t="s">
-        <v>8606</v>
+        <v>8608</v>
       </c>
       <c r="F1355" s="5" t="s">
-        <v>8607</v>
+        <v>8609</v>
       </c>
       <c r="G1355" s="5" t="s">
-        <v>8606</v>
+        <v>8610</v>
       </c>
       <c r="H1355" s="5" t="s">
-        <v>8605</v>
+        <v>8611</v>
       </c>
     </row>
     <row r="1356">
       <c r="B1356" s="6" t="s">
-        <v>8608</v>
+        <v>8612</v>
       </c>
       <c r="C1356" s="6" t="s">
-        <v>6033</v>
+        <v>8613</v>
       </c>
       <c r="D1356" s="6" t="s">
-        <v>6936</v>
+        <v>8614</v>
       </c>
       <c r="E1356" s="6" t="s">
-        <v>6035</v>
+        <v>8615</v>
       </c>
       <c r="F1356" s="6" t="s">
-        <v>8335</v>
+        <v>7776</v>
       </c>
       <c r="G1356" s="6" t="s">
-        <v>8335</v>
+        <v>7777</v>
       </c>
       <c r="H1356" s="6" t="s">
-        <v>5404</v>
+        <v>8616</v>
       </c>
     </row>
     <row r="1357">
       <c r="B1357" s="5" t="s">
-        <v>8609</v>
+        <v>8617</v>
       </c>
       <c r="C1357" s="5" t="s">
-        <v>6080</v>
+        <v>8618</v>
       </c>
       <c r="D1357" s="5" t="s">
-        <v>8610</v>
+        <v>8619</v>
       </c>
       <c r="E1357" s="5" t="s">
-        <v>6082</v>
+        <v>8620</v>
       </c>
       <c r="F1357" s="5" t="s">
-        <v>8611</v>
+        <v>8621</v>
       </c>
       <c r="G1357" s="5" t="s">
-        <v>8612</v>
+        <v>8622</v>
       </c>
       <c r="H1357" s="5" t="s">
-        <v>8613</v>
+        <v>8623</v>
       </c>
     </row>
     <row r="1358">
       <c r="B1358" s="6" t="s">
-        <v>8614</v>
+        <v>8624</v>
       </c>
       <c r="C1358" s="6" t="s">
-        <v>7363</v>
+        <v>8625</v>
       </c>
       <c r="D1358" s="6" t="s">
-        <v>8615</v>
+        <v>8626</v>
       </c>
       <c r="E1358" s="6" t="s">
-        <v>7365</v>
+        <v>8627</v>
       </c>
       <c r="F1358" s="6" t="s">
-        <v>6016</v>
+        <v>8628</v>
       </c>
       <c r="G1358" s="6" t="s">
-        <v>6017</v>
+        <v>8627</v>
       </c>
       <c r="H1358" s="6" t="s">
-        <v>7364</v>
+        <v>8626</v>
       </c>
     </row>
     <row r="1359">
       <c r="B1359" s="5" t="s">
-        <v>8616</v>
+        <v>8629</v>
       </c>
       <c r="C1359" s="5" t="s">
-        <v>7369</v>
+        <v>6033</v>
       </c>
       <c r="D1359" s="5" t="s">
-        <v>8617</v>
+        <v>6936</v>
       </c>
       <c r="E1359" s="5" t="s">
-        <v>7371</v>
+        <v>6035</v>
       </c>
       <c r="F1359" s="5" t="s">
-        <v>6023</v>
+        <v>8356</v>
       </c>
       <c r="G1359" s="5" t="s">
-        <v>6023</v>
+        <v>8356</v>
       </c>
       <c r="H1359" s="5" t="s">
-        <v>8618</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="1360">
       <c r="B1360" s="6" t="s">
-        <v>8619</v>
+        <v>8630</v>
       </c>
       <c r="C1360" s="6" t="s">
-        <v>7374</v>
+        <v>6080</v>
       </c>
       <c r="D1360" s="6" t="s">
-        <v>8620</v>
+        <v>8631</v>
       </c>
       <c r="E1360" s="6" t="s">
-        <v>7376</v>
+        <v>6082</v>
       </c>
       <c r="F1360" s="6" t="s">
-        <v>6029</v>
+        <v>8632</v>
       </c>
       <c r="G1360" s="6" t="s">
-        <v>6030</v>
+        <v>8633</v>
       </c>
       <c r="H1360" s="6" t="s">
-        <v>7379</v>
+        <v>8634</v>
       </c>
     </row>
     <row r="1361">
       <c r="B1361" s="5" t="s">
-        <v>8621</v>
+        <v>8635</v>
       </c>
       <c r="C1361" s="5" t="s">
-        <v>6046</v>
+        <v>7363</v>
       </c>
       <c r="D1361" s="5" t="s">
-        <v>8622</v>
+        <v>8636</v>
       </c>
       <c r="E1361" s="5" t="s">
-        <v>6048</v>
+        <v>7365</v>
       </c>
       <c r="F1361" s="5" t="s">
-        <v>6049</v>
+        <v>6016</v>
       </c>
       <c r="G1361" s="5" t="s">
-        <v>6050</v>
+        <v>6017</v>
       </c>
       <c r="H1361" s="5" t="s">
-        <v>8623</v>
+        <v>7364</v>
       </c>
     </row>
     <row r="1362">
       <c r="B1362" s="6" t="s">
-        <v>8624</v>
+        <v>8637</v>
       </c>
       <c r="C1362" s="6" t="s">
-        <v>8625</v>
+        <v>7369</v>
       </c>
       <c r="D1362" s="6" t="s">
-        <v>8626</v>
+        <v>8638</v>
       </c>
       <c r="E1362" s="6" t="s">
-        <v>6076</v>
+        <v>7371</v>
       </c>
       <c r="F1362" s="6" t="s">
-        <v>8627</v>
+        <v>6023</v>
       </c>
       <c r="G1362" s="6" t="s">
-        <v>8628</v>
+        <v>6023</v>
       </c>
       <c r="H1362" s="6" t="s">
-        <v>7361</v>
+        <v>8639</v>
       </c>
     </row>
     <row r="1363">
       <c r="B1363" s="5" t="s">
-        <v>8629</v>
+        <v>8640</v>
       </c>
       <c r="C1363" s="5" t="s">
-        <v>7349</v>
+        <v>7374</v>
       </c>
       <c r="D1363" s="5" t="s">
-        <v>8630</v>
+        <v>8641</v>
       </c>
       <c r="E1363" s="5" t="s">
-        <v>7351</v>
+        <v>7376</v>
       </c>
       <c r="F1363" s="5" t="s">
-        <v>8631</v>
+        <v>6029</v>
       </c>
       <c r="G1363" s="5" t="s">
-        <v>8631</v>
+        <v>6030</v>
       </c>
       <c r="H1363" s="5" t="s">
-        <v>8632</v>
+        <v>7379</v>
       </c>
     </row>
     <row r="1364">
       <c r="B1364" s="6" t="s">
-        <v>8633</v>
+        <v>8642</v>
       </c>
       <c r="C1364" s="6" t="s">
-        <v>8634</v>
+        <v>6046</v>
       </c>
       <c r="D1364" s="6" t="s">
-        <v>8635</v>
+        <v>8643</v>
       </c>
       <c r="E1364" s="6" t="s">
-        <v>8636</v>
+        <v>6048</v>
       </c>
       <c r="F1364" s="6" t="s">
-        <v>8637</v>
+        <v>6049</v>
       </c>
       <c r="G1364" s="6" t="s">
-        <v>8638</v>
+        <v>6050</v>
       </c>
       <c r="H1364" s="6" t="s">
-        <v>8639</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="1365">
       <c r="B1365" s="5" t="s">
-        <v>8640</v>
+        <v>8645</v>
       </c>
       <c r="C1365" s="5" t="s">
-        <v>8526</v>
+        <v>8646</v>
       </c>
       <c r="D1365" s="5" t="s">
-        <v>8527</v>
+        <v>8647</v>
       </c>
       <c r="E1365" s="5" t="s">
-        <v>8528</v>
+        <v>6076</v>
       </c>
       <c r="F1365" s="5" t="s">
-        <v>8529</v>
+        <v>8648</v>
       </c>
       <c r="G1365" s="5" t="s">
-        <v>8530</v>
+        <v>8649</v>
       </c>
       <c r="H1365" s="5" t="s">
-        <v>8531</v>
+        <v>7361</v>
       </c>
     </row>
     <row r="1366">
       <c r="B1366" s="6" t="s">
-        <v>8641</v>
+        <v>8650</v>
       </c>
       <c r="C1366" s="6" t="s">
-        <v>8642</v>
+        <v>7349</v>
       </c>
       <c r="D1366" s="6" t="s">
-        <v>8643</v>
+        <v>8651</v>
       </c>
       <c r="E1366" s="6" t="s">
-        <v>8644</v>
+        <v>7351</v>
       </c>
       <c r="F1366" s="6" t="s">
-        <v>8645</v>
+        <v>8652</v>
       </c>
       <c r="G1366" s="6" t="s">
-        <v>8646</v>
+        <v>8652</v>
       </c>
       <c r="H1366" s="6" t="s">
-        <v>8647</v>
+        <v>8653</v>
       </c>
     </row>
     <row r="1367">
       <c r="B1367" s="5" t="s">
-        <v>8648</v>
+        <v>8654</v>
       </c>
       <c r="C1367" s="5" t="s">
-        <v>8649</v>
+        <v>8655</v>
       </c>
       <c r="D1367" s="5" t="s">
-        <v>8650</v>
+        <v>8656</v>
       </c>
       <c r="E1367" s="5" t="s">
-        <v>8651</v>
+        <v>8657</v>
       </c>
       <c r="F1367" s="5" t="s">
-        <v>8652</v>
+        <v>8658</v>
       </c>
       <c r="G1367" s="5" t="s">
-        <v>8653</v>
+        <v>8659</v>
       </c>
       <c r="H1367" s="5" t="s">
-        <v>8654</v>
+        <v>8660</v>
       </c>
     </row>
     <row r="1368">
       <c r="B1368" s="6" t="s">
-        <v>8655</v>
+        <v>8661</v>
       </c>
       <c r="C1368" s="6" t="s">
-        <v>8656</v>
+        <v>8547</v>
       </c>
       <c r="D1368" s="6" t="s">
-        <v>8657</v>
+        <v>8548</v>
       </c>
       <c r="E1368" s="6" t="s">
-        <v>8658</v>
+        <v>8549</v>
       </c>
       <c r="F1368" s="6" t="s">
-        <v>8659</v>
+        <v>8550</v>
       </c>
       <c r="G1368" s="6" t="s">
-        <v>8660</v>
+        <v>8551</v>
       </c>
       <c r="H1368" s="6" t="s">
-        <v>8661</v>
+        <v>8552</v>
       </c>
     </row>
     <row r="1369">
@@ -60913,73 +60976,73 @@
         <v>8687</v>
       </c>
       <c r="G1372" s="6" t="s">
-        <v>8687</v>
+        <v>8688</v>
       </c>
       <c r="H1372" s="6" t="s">
-        <v>8688</v>
+        <v>8689</v>
       </c>
     </row>
     <row r="1373">
       <c r="B1373" s="5" t="s">
-        <v>8689</v>
+        <v>8690</v>
       </c>
       <c r="C1373" s="5" t="s">
-        <v>8690</v>
+        <v>8691</v>
       </c>
       <c r="D1373" s="5" t="s">
-        <v>8691</v>
+        <v>8692</v>
       </c>
       <c r="E1373" s="5" t="s">
-        <v>8692</v>
+        <v>8693</v>
       </c>
       <c r="F1373" s="5" t="s">
-        <v>8693</v>
+        <v>8694</v>
       </c>
       <c r="G1373" s="5" t="s">
-        <v>8694</v>
+        <v>8695</v>
       </c>
       <c r="H1373" s="5" t="s">
-        <v>8695</v>
+        <v>8696</v>
       </c>
     </row>
     <row r="1374">
       <c r="B1374" s="6" t="s">
-        <v>8696</v>
+        <v>8697</v>
       </c>
       <c r="C1374" s="6" t="s">
-        <v>8697</v>
+        <v>8698</v>
       </c>
       <c r="D1374" s="6" t="s">
-        <v>8698</v>
+        <v>8699</v>
       </c>
       <c r="E1374" s="6" t="s">
-        <v>8699</v>
+        <v>8700</v>
       </c>
       <c r="F1374" s="6" t="s">
-        <v>8700</v>
+        <v>8701</v>
       </c>
       <c r="G1374" s="6" t="s">
-        <v>8701</v>
+        <v>8702</v>
       </c>
       <c r="H1374" s="6" t="s">
-        <v>8702</v>
+        <v>8703</v>
       </c>
     </row>
     <row r="1375">
       <c r="B1375" s="5" t="s">
-        <v>8703</v>
+        <v>8704</v>
       </c>
       <c r="C1375" s="5" t="s">
-        <v>8704</v>
+        <v>8705</v>
       </c>
       <c r="D1375" s="5" t="s">
-        <v>8705</v>
+        <v>8706</v>
       </c>
       <c r="E1375" s="5" t="s">
-        <v>8706</v>
+        <v>8707</v>
       </c>
       <c r="F1375" s="5" t="s">
-        <v>8707</v>
+        <v>8708</v>
       </c>
       <c r="G1375" s="5" t="s">
         <v>8708</v>
@@ -61166,349 +61229,349 @@
         <v>8763</v>
       </c>
       <c r="G1383" s="5" t="s">
-        <v>8763</v>
+        <v>8764</v>
       </c>
       <c r="H1383" s="5" t="s">
-        <v>8764</v>
+        <v>8765</v>
       </c>
     </row>
     <row r="1384">
       <c r="B1384" s="6" t="s">
-        <v>8765</v>
+        <v>8766</v>
       </c>
       <c r="C1384" s="6" t="s">
-        <v>8766</v>
+        <v>8767</v>
       </c>
       <c r="D1384" s="6" t="s">
-        <v>8767</v>
+        <v>8768</v>
       </c>
       <c r="E1384" s="6" t="s">
-        <v>8768</v>
+        <v>8769</v>
       </c>
       <c r="F1384" s="6" t="s">
-        <v>8769</v>
+        <v>8770</v>
       </c>
       <c r="G1384" s="6" t="s">
-        <v>8770</v>
+        <v>8771</v>
       </c>
       <c r="H1384" s="6" t="s">
-        <v>8771</v>
+        <v>8772</v>
       </c>
     </row>
     <row r="1385">
       <c r="B1385" s="5" t="s">
-        <v>8772</v>
+        <v>8773</v>
       </c>
       <c r="C1385" s="5" t="s">
-        <v>8773</v>
+        <v>8774</v>
       </c>
       <c r="D1385" s="5" t="s">
-        <v>8774</v>
+        <v>8775</v>
       </c>
       <c r="E1385" s="5" t="s">
-        <v>8775</v>
+        <v>8776</v>
       </c>
       <c r="F1385" s="5" t="s">
-        <v>8693</v>
+        <v>8777</v>
       </c>
       <c r="G1385" s="5" t="s">
-        <v>8694</v>
+        <v>8778</v>
       </c>
       <c r="H1385" s="5" t="s">
-        <v>8776</v>
+        <v>8779</v>
       </c>
     </row>
     <row r="1386">
       <c r="B1386" s="6" t="s">
-        <v>8777</v>
+        <v>8780</v>
       </c>
       <c r="C1386" s="6" t="s">
-        <v>8778</v>
+        <v>8781</v>
       </c>
       <c r="D1386" s="6" t="s">
-        <v>8779</v>
+        <v>8782</v>
       </c>
       <c r="E1386" s="6" t="s">
-        <v>8780</v>
+        <v>8783</v>
       </c>
       <c r="F1386" s="6" t="s">
-        <v>8781</v>
+        <v>8784</v>
       </c>
       <c r="G1386" s="6" t="s">
-        <v>8782</v>
+        <v>8784</v>
       </c>
       <c r="H1386" s="6" t="s">
-        <v>8783</v>
+        <v>8785</v>
       </c>
     </row>
     <row r="1387">
       <c r="B1387" s="5" t="s">
-        <v>8784</v>
+        <v>8786</v>
       </c>
       <c r="C1387" s="5" t="s">
-        <v>8785</v>
+        <v>8787</v>
       </c>
       <c r="D1387" s="5" t="s">
-        <v>8786</v>
+        <v>8788</v>
       </c>
       <c r="E1387" s="5" t="s">
-        <v>8787</v>
+        <v>8789</v>
       </c>
       <c r="F1387" s="5" t="s">
-        <v>8788</v>
+        <v>8790</v>
       </c>
       <c r="G1387" s="5" t="s">
-        <v>8789</v>
+        <v>8791</v>
       </c>
       <c r="H1387" s="5" t="s">
-        <v>8790</v>
+        <v>8792</v>
       </c>
     </row>
     <row r="1388">
       <c r="B1388" s="6" t="s">
-        <v>8791</v>
+        <v>8793</v>
       </c>
       <c r="C1388" s="6" t="s">
-        <v>8792</v>
+        <v>8794</v>
       </c>
       <c r="D1388" s="6" t="s">
-        <v>8793</v>
+        <v>8795</v>
       </c>
       <c r="E1388" s="6" t="s">
-        <v>8794</v>
+        <v>8796</v>
       </c>
       <c r="F1388" s="6" t="s">
-        <v>8795</v>
+        <v>8714</v>
       </c>
       <c r="G1388" s="6" t="s">
-        <v>8795</v>
+        <v>8715</v>
       </c>
       <c r="H1388" s="6" t="s">
-        <v>8796</v>
+        <v>8797</v>
       </c>
     </row>
     <row r="1389">
       <c r="B1389" s="5" t="s">
-        <v>8797</v>
+        <v>8798</v>
       </c>
       <c r="C1389" s="5" t="s">
-        <v>8798</v>
+        <v>8799</v>
       </c>
       <c r="D1389" s="5" t="s">
-        <v>8799</v>
+        <v>8800</v>
       </c>
       <c r="E1389" s="5" t="s">
-        <v>8800</v>
+        <v>8801</v>
       </c>
       <c r="F1389" s="5" t="s">
-        <v>8801</v>
+        <v>8802</v>
       </c>
       <c r="G1389" s="5" t="s">
-        <v>8802</v>
+        <v>8803</v>
       </c>
       <c r="H1389" s="5" t="s">
-        <v>8803</v>
+        <v>8804</v>
       </c>
     </row>
     <row r="1390">
       <c r="B1390" s="6" t="s">
-        <v>8804</v>
+        <v>8805</v>
       </c>
       <c r="C1390" s="6" t="s">
-        <v>8805</v>
+        <v>8806</v>
       </c>
       <c r="D1390" s="6" t="s">
-        <v>8806</v>
+        <v>8807</v>
       </c>
       <c r="E1390" s="6" t="s">
-        <v>8807</v>
+        <v>8808</v>
       </c>
       <c r="F1390" s="6" t="s">
-        <v>8808</v>
+        <v>8809</v>
       </c>
       <c r="G1390" s="6" t="s">
-        <v>8808</v>
+        <v>8810</v>
       </c>
       <c r="H1390" s="6" t="s">
-        <v>8809</v>
+        <v>8811</v>
       </c>
     </row>
     <row r="1391">
       <c r="B1391" s="5" t="s">
-        <v>8810</v>
+        <v>8812</v>
       </c>
       <c r="C1391" s="5" t="s">
-        <v>6781</v>
+        <v>8813</v>
       </c>
       <c r="D1391" s="5" t="s">
-        <v>8811</v>
+        <v>8814</v>
       </c>
       <c r="E1391" s="5" t="s">
-        <v>6783</v>
+        <v>8815</v>
       </c>
       <c r="F1391" s="5" t="s">
-        <v>6784</v>
+        <v>8816</v>
       </c>
       <c r="G1391" s="5" t="s">
-        <v>6785</v>
+        <v>8816</v>
       </c>
       <c r="H1391" s="5" t="s">
-        <v>6786</v>
+        <v>8817</v>
       </c>
     </row>
     <row r="1392">
       <c r="B1392" s="6" t="s">
-        <v>8812</v>
+        <v>8818</v>
       </c>
       <c r="C1392" s="6" t="s">
-        <v>8813</v>
+        <v>8819</v>
       </c>
       <c r="D1392" s="6" t="s">
-        <v>8814</v>
+        <v>8820</v>
       </c>
       <c r="E1392" s="6" t="s">
-        <v>8815</v>
+        <v>8821</v>
       </c>
       <c r="F1392" s="6" t="s">
-        <v>8816</v>
+        <v>8822</v>
       </c>
       <c r="G1392" s="6" t="s">
-        <v>8816</v>
+        <v>8823</v>
       </c>
       <c r="H1392" s="6" t="s">
-        <v>8817</v>
+        <v>8824</v>
       </c>
     </row>
     <row r="1393">
       <c r="B1393" s="5" t="s">
-        <v>8818</v>
+        <v>8825</v>
       </c>
       <c r="C1393" s="5" t="s">
-        <v>8819</v>
+        <v>8826</v>
       </c>
       <c r="D1393" s="5" t="s">
-        <v>8820</v>
+        <v>8827</v>
       </c>
       <c r="E1393" s="5" t="s">
-        <v>8821</v>
+        <v>8828</v>
       </c>
       <c r="F1393" s="5" t="s">
-        <v>8822</v>
+        <v>8829</v>
       </c>
       <c r="G1393" s="5" t="s">
-        <v>8823</v>
+        <v>8829</v>
       </c>
       <c r="H1393" s="5" t="s">
-        <v>8824</v>
+        <v>8830</v>
       </c>
     </row>
     <row r="1394">
       <c r="B1394" s="6" t="s">
-        <v>8825</v>
+        <v>8831</v>
       </c>
       <c r="C1394" s="6" t="s">
-        <v>8826</v>
+        <v>6781</v>
       </c>
       <c r="D1394" s="6" t="s">
-        <v>8827</v>
+        <v>8832</v>
       </c>
       <c r="E1394" s="6" t="s">
-        <v>8828</v>
+        <v>6783</v>
       </c>
       <c r="F1394" s="6" t="s">
-        <v>8829</v>
+        <v>6784</v>
       </c>
       <c r="G1394" s="6" t="s">
-        <v>8830</v>
+        <v>6785</v>
       </c>
       <c r="H1394" s="6" t="s">
-        <v>8831</v>
+        <v>6786</v>
       </c>
     </row>
     <row r="1395">
       <c r="B1395" s="5" t="s">
-        <v>8832</v>
+        <v>8833</v>
       </c>
       <c r="C1395" s="5" t="s">
-        <v>8833</v>
+        <v>8834</v>
       </c>
       <c r="D1395" s="5" t="s">
-        <v>8834</v>
+        <v>8835</v>
       </c>
       <c r="E1395" s="5" t="s">
-        <v>8835</v>
+        <v>8836</v>
       </c>
       <c r="F1395" s="5" t="s">
-        <v>8836</v>
+        <v>8837</v>
       </c>
       <c r="G1395" s="5" t="s">
-        <v>8836</v>
+        <v>8837</v>
       </c>
       <c r="H1395" s="5" t="s">
-        <v>8837</v>
+        <v>8838</v>
       </c>
     </row>
     <row r="1396">
       <c r="B1396" s="6" t="s">
-        <v>8838</v>
+        <v>8839</v>
       </c>
       <c r="C1396" s="6" t="s">
-        <v>8839</v>
+        <v>8840</v>
       </c>
       <c r="D1396" s="6" t="s">
-        <v>8840</v>
+        <v>8841</v>
       </c>
       <c r="E1396" s="6" t="s">
-        <v>8841</v>
+        <v>8842</v>
       </c>
       <c r="F1396" s="6" t="s">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="G1396" s="6" t="s">
-        <v>8843</v>
+        <v>8844</v>
       </c>
       <c r="H1396" s="6" t="s">
-        <v>8844</v>
+        <v>8845</v>
       </c>
     </row>
     <row r="1397">
       <c r="B1397" s="5" t="s">
-        <v>8845</v>
+        <v>8846</v>
       </c>
       <c r="C1397" s="5" t="s">
-        <v>8846</v>
+        <v>8847</v>
       </c>
       <c r="D1397" s="5" t="s">
-        <v>8847</v>
+        <v>8848</v>
       </c>
       <c r="E1397" s="5" t="s">
-        <v>8848</v>
+        <v>8849</v>
       </c>
       <c r="F1397" s="5" t="s">
-        <v>8849</v>
+        <v>8850</v>
       </c>
       <c r="G1397" s="5" t="s">
-        <v>8850</v>
+        <v>8851</v>
       </c>
       <c r="H1397" s="5" t="s">
-        <v>8851</v>
+        <v>8852</v>
       </c>
     </row>
     <row r="1398">
       <c r="B1398" s="6" t="s">
-        <v>8852</v>
+        <v>8853</v>
       </c>
       <c r="C1398" s="6" t="s">
-        <v>8853</v>
+        <v>8854</v>
       </c>
       <c r="D1398" s="6" t="s">
-        <v>8854</v>
+        <v>8855</v>
       </c>
       <c r="E1398" s="6" t="s">
-        <v>8855</v>
+        <v>8856</v>
       </c>
       <c r="F1398" s="6" t="s">
-        <v>8856</v>
+        <v>8857</v>
       </c>
       <c r="G1398" s="6" t="s">
         <v>8857</v>
@@ -61522,91 +61585,91 @@
         <v>8859</v>
       </c>
       <c r="C1399" s="5" t="s">
-        <v>8813</v>
+        <v>8860</v>
       </c>
       <c r="D1399" s="5" t="s">
-        <v>8814</v>
+        <v>8861</v>
       </c>
       <c r="E1399" s="5" t="s">
-        <v>8815</v>
+        <v>8862</v>
       </c>
       <c r="F1399" s="5" t="s">
-        <v>8816</v>
+        <v>8863</v>
       </c>
       <c r="G1399" s="5" t="s">
-        <v>8816</v>
+        <v>8864</v>
       </c>
       <c r="H1399" s="5" t="s">
-        <v>8817</v>
+        <v>8865</v>
       </c>
     </row>
     <row r="1400">
       <c r="B1400" s="6" t="s">
-        <v>8860</v>
+        <v>8866</v>
       </c>
       <c r="C1400" s="6" t="s">
-        <v>8861</v>
+        <v>8867</v>
       </c>
       <c r="D1400" s="6" t="s">
-        <v>8862</v>
+        <v>8868</v>
       </c>
       <c r="E1400" s="6" t="s">
-        <v>8863</v>
+        <v>8869</v>
       </c>
       <c r="F1400" s="6" t="s">
-        <v>8864</v>
+        <v>8870</v>
       </c>
       <c r="G1400" s="6" t="s">
-        <v>8865</v>
+        <v>8871</v>
       </c>
       <c r="H1400" s="6" t="s">
-        <v>8866</v>
+        <v>8872</v>
       </c>
     </row>
     <row r="1401">
       <c r="B1401" s="5" t="s">
-        <v>8867</v>
+        <v>8873</v>
       </c>
       <c r="C1401" s="5" t="s">
-        <v>8868</v>
+        <v>8874</v>
       </c>
       <c r="D1401" s="5" t="s">
-        <v>8869</v>
+        <v>8875</v>
       </c>
       <c r="E1401" s="5" t="s">
-        <v>8870</v>
+        <v>8876</v>
       </c>
       <c r="F1401" s="5" t="s">
-        <v>8871</v>
+        <v>8877</v>
       </c>
       <c r="G1401" s="5" t="s">
-        <v>8872</v>
+        <v>8878</v>
       </c>
       <c r="H1401" s="5" t="s">
-        <v>8873</v>
+        <v>8879</v>
       </c>
     </row>
     <row r="1402">
       <c r="B1402" s="6" t="s">
-        <v>8874</v>
+        <v>8880</v>
       </c>
       <c r="C1402" s="6" t="s">
-        <v>8875</v>
+        <v>8834</v>
       </c>
       <c r="D1402" s="6" t="s">
-        <v>8876</v>
+        <v>8835</v>
       </c>
       <c r="E1402" s="6" t="s">
-        <v>8877</v>
+        <v>8836</v>
       </c>
       <c r="F1402" s="6" t="s">
-        <v>8878</v>
+        <v>8837</v>
       </c>
       <c r="G1402" s="6" t="s">
-        <v>8879</v>
+        <v>8837</v>
       </c>
       <c r="H1402" s="6" t="s">
-        <v>8880</v>
+        <v>8838</v>
       </c>
     </row>
     <row r="1403">
@@ -61683,157 +61746,157 @@
         <v>8902</v>
       </c>
       <c r="C1406" s="6" t="s">
-        <v>6895</v>
+        <v>8903</v>
       </c>
       <c r="D1406" s="6" t="s">
-        <v>8903</v>
+        <v>8904</v>
       </c>
       <c r="E1406" s="6" t="s">
-        <v>6897</v>
+        <v>8905</v>
       </c>
       <c r="F1406" s="6" t="s">
-        <v>8550</v>
+        <v>8906</v>
       </c>
       <c r="G1406" s="6" t="s">
-        <v>8551</v>
+        <v>8907</v>
       </c>
       <c r="H1406" s="6" t="s">
-        <v>8904</v>
+        <v>8908</v>
       </c>
     </row>
     <row r="1407">
       <c r="B1407" s="5" t="s">
-        <v>8905</v>
+        <v>8909</v>
       </c>
       <c r="C1407" s="5" t="s">
-        <v>6931</v>
+        <v>8910</v>
       </c>
       <c r="D1407" s="5" t="s">
-        <v>6832</v>
+        <v>8911</v>
       </c>
       <c r="E1407" s="5" t="s">
-        <v>6932</v>
+        <v>8912</v>
       </c>
       <c r="F1407" s="5" t="s">
-        <v>6933</v>
+        <v>8913</v>
       </c>
       <c r="G1407" s="5" t="s">
-        <v>6934</v>
+        <v>8914</v>
       </c>
       <c r="H1407" s="5" t="s">
-        <v>6832</v>
+        <v>8915</v>
       </c>
     </row>
     <row r="1408">
       <c r="B1408" s="6" t="s">
-        <v>8906</v>
+        <v>8916</v>
       </c>
       <c r="C1408" s="6" t="s">
-        <v>8526</v>
+        <v>8917</v>
       </c>
       <c r="D1408" s="6" t="s">
-        <v>8907</v>
+        <v>8918</v>
       </c>
       <c r="E1408" s="6" t="s">
-        <v>8528</v>
+        <v>8919</v>
       </c>
       <c r="F1408" s="6" t="s">
-        <v>8529</v>
+        <v>8920</v>
       </c>
       <c r="G1408" s="6" t="s">
-        <v>8530</v>
+        <v>8921</v>
       </c>
       <c r="H1408" s="6" t="s">
-        <v>8908</v>
+        <v>8922</v>
       </c>
     </row>
     <row r="1409">
       <c r="B1409" s="5" t="s">
-        <v>8909</v>
+        <v>8923</v>
       </c>
       <c r="C1409" s="5" t="s">
-        <v>8910</v>
+        <v>6895</v>
       </c>
       <c r="D1409" s="5" t="s">
-        <v>8911</v>
+        <v>8924</v>
       </c>
       <c r="E1409" s="5" t="s">
-        <v>8912</v>
+        <v>6897</v>
       </c>
       <c r="F1409" s="5" t="s">
-        <v>8913</v>
+        <v>8571</v>
       </c>
       <c r="G1409" s="5" t="s">
-        <v>8912</v>
+        <v>8572</v>
       </c>
       <c r="H1409" s="5" t="s">
-        <v>8914</v>
+        <v>8925</v>
       </c>
     </row>
     <row r="1410">
       <c r="B1410" s="6" t="s">
-        <v>8915</v>
+        <v>8926</v>
       </c>
       <c r="C1410" s="6" t="s">
-        <v>8916</v>
+        <v>6931</v>
       </c>
       <c r="D1410" s="6" t="s">
-        <v>8917</v>
+        <v>6832</v>
       </c>
       <c r="E1410" s="6" t="s">
-        <v>8918</v>
+        <v>6932</v>
       </c>
       <c r="F1410" s="6" t="s">
-        <v>8919</v>
+        <v>6933</v>
       </c>
       <c r="G1410" s="6" t="s">
-        <v>8920</v>
+        <v>6934</v>
       </c>
       <c r="H1410" s="6" t="s">
-        <v>8921</v>
+        <v>6832</v>
       </c>
     </row>
     <row r="1411">
       <c r="B1411" s="5" t="s">
-        <v>8922</v>
+        <v>8927</v>
       </c>
       <c r="C1411" s="5" t="s">
-        <v>8923</v>
+        <v>8547</v>
       </c>
       <c r="D1411" s="5" t="s">
-        <v>8924</v>
+        <v>8928</v>
       </c>
       <c r="E1411" s="5" t="s">
-        <v>8925</v>
+        <v>8549</v>
       </c>
       <c r="F1411" s="5" t="s">
-        <v>8926</v>
+        <v>8550</v>
       </c>
       <c r="G1411" s="5" t="s">
-        <v>8927</v>
+        <v>8551</v>
       </c>
       <c r="H1411" s="5" t="s">
-        <v>8928</v>
+        <v>8929</v>
       </c>
     </row>
     <row r="1412">
       <c r="B1412" s="6" t="s">
-        <v>8929</v>
+        <v>8930</v>
       </c>
       <c r="C1412" s="6" t="s">
-        <v>8930</v>
+        <v>8931</v>
       </c>
       <c r="D1412" s="6" t="s">
-        <v>8931</v>
+        <v>8932</v>
       </c>
       <c r="E1412" s="6" t="s">
-        <v>8932</v>
+        <v>8933</v>
       </c>
       <c r="F1412" s="6" t="s">
+        <v>8934</v>
+      </c>
+      <c r="G1412" s="6" t="s">
         <v>8933</v>
-      </c>
-      <c r="G1412" s="6" t="s">
-        <v>8934</v>
       </c>
       <c r="H1412" s="6" t="s">
         <v>8935</v>
@@ -61873,76 +61936,76 @@
         <v>8945</v>
       </c>
       <c r="E1414" s="6" t="s">
-        <v>5453</v>
+        <v>8946</v>
       </c>
       <c r="F1414" s="6" t="s">
-        <v>8946</v>
+        <v>8947</v>
       </c>
       <c r="G1414" s="6" t="s">
-        <v>8947</v>
+        <v>8948</v>
       </c>
       <c r="H1414" s="6" t="s">
-        <v>8948</v>
+        <v>8949</v>
       </c>
     </row>
     <row r="1415">
       <c r="B1415" s="5" t="s">
-        <v>8949</v>
+        <v>8950</v>
       </c>
       <c r="C1415" s="5" t="s">
-        <v>8950</v>
+        <v>8951</v>
       </c>
       <c r="D1415" s="5" t="s">
-        <v>8951</v>
+        <v>8952</v>
       </c>
       <c r="E1415" s="5" t="s">
-        <v>8952</v>
+        <v>8953</v>
       </c>
       <c r="F1415" s="5" t="s">
-        <v>8953</v>
+        <v>8954</v>
       </c>
       <c r="G1415" s="5" t="s">
-        <v>8954</v>
+        <v>8955</v>
       </c>
       <c r="H1415" s="5" t="s">
-        <v>8955</v>
+        <v>8956</v>
       </c>
     </row>
     <row r="1416">
       <c r="B1416" s="6" t="s">
-        <v>8956</v>
+        <v>8957</v>
       </c>
       <c r="C1416" s="6" t="s">
-        <v>8957</v>
+        <v>8958</v>
       </c>
       <c r="D1416" s="6" t="s">
-        <v>8958</v>
+        <v>8959</v>
       </c>
       <c r="E1416" s="6" t="s">
-        <v>8959</v>
+        <v>8960</v>
       </c>
       <c r="F1416" s="6" t="s">
-        <v>8960</v>
+        <v>8961</v>
       </c>
       <c r="G1416" s="6" t="s">
-        <v>8961</v>
+        <v>8962</v>
       </c>
       <c r="H1416" s="6" t="s">
-        <v>8962</v>
+        <v>8963</v>
       </c>
     </row>
     <row r="1417">
       <c r="B1417" s="5" t="s">
-        <v>8963</v>
+        <v>8964</v>
       </c>
       <c r="C1417" s="5" t="s">
-        <v>8964</v>
+        <v>8965</v>
       </c>
       <c r="D1417" s="5" t="s">
-        <v>8965</v>
+        <v>8966</v>
       </c>
       <c r="E1417" s="5" t="s">
-        <v>8966</v>
+        <v>5453</v>
       </c>
       <c r="F1417" s="5" t="s">
         <v>8967</v>
@@ -61981,349 +62044,349 @@
       <c r="B1419" s="5" t="s">
         <v>8977</v>
       </c>
-      <c r="C1419" s="7" t="s">
+      <c r="C1419" s="5" t="s">
         <v>8978</v>
       </c>
-      <c r="D1419" s="7" t="s">
-        <v>8978</v>
-      </c>
-      <c r="E1419" s="7" t="s">
-        <v>8978</v>
-      </c>
-      <c r="F1419" s="7" t="s">
-        <v>8978</v>
-      </c>
-      <c r="G1419" s="7" t="s">
-        <v>8978</v>
-      </c>
-      <c r="H1419" s="7" t="s">
-        <v>8978</v>
+      <c r="D1419" s="5" t="s">
+        <v>8979</v>
+      </c>
+      <c r="E1419" s="5" t="s">
+        <v>8980</v>
+      </c>
+      <c r="F1419" s="5" t="s">
+        <v>8981</v>
+      </c>
+      <c r="G1419" s="5" t="s">
+        <v>8982</v>
+      </c>
+      <c r="H1419" s="5" t="s">
+        <v>8983</v>
       </c>
     </row>
     <row r="1420">
       <c r="B1420" s="6" t="s">
-        <v>8979</v>
+        <v>8984</v>
       </c>
       <c r="C1420" s="6" t="s">
-        <v>8390</v>
+        <v>8985</v>
       </c>
       <c r="D1420" s="6" t="s">
-        <v>8391</v>
+        <v>8986</v>
       </c>
       <c r="E1420" s="6" t="s">
-        <v>8392</v>
+        <v>8987</v>
       </c>
       <c r="F1420" s="6" t="s">
-        <v>8393</v>
+        <v>8988</v>
       </c>
       <c r="G1420" s="6" t="s">
-        <v>8394</v>
+        <v>8989</v>
       </c>
       <c r="H1420" s="6" t="s">
-        <v>8391</v>
+        <v>8990</v>
       </c>
     </row>
     <row r="1421">
       <c r="B1421" s="5" t="s">
-        <v>8980</v>
+        <v>8991</v>
       </c>
       <c r="C1421" s="5" t="s">
-        <v>8981</v>
+        <v>8992</v>
       </c>
       <c r="D1421" s="5" t="s">
-        <v>8982</v>
+        <v>8993</v>
       </c>
       <c r="E1421" s="5" t="s">
-        <v>8983</v>
+        <v>8994</v>
       </c>
       <c r="F1421" s="5" t="s">
-        <v>8984</v>
+        <v>8995</v>
       </c>
       <c r="G1421" s="5" t="s">
-        <v>8984</v>
+        <v>8996</v>
       </c>
       <c r="H1421" s="5" t="s">
-        <v>8985</v>
+        <v>8997</v>
       </c>
     </row>
     <row r="1422">
       <c r="B1422" s="6" t="s">
-        <v>8986</v>
-      </c>
-      <c r="C1422" s="6" t="s">
-        <v>8987</v>
-      </c>
-      <c r="D1422" s="6" t="s">
-        <v>8988</v>
-      </c>
-      <c r="E1422" s="6" t="s">
-        <v>8989</v>
-      </c>
-      <c r="F1422" s="6" t="s">
-        <v>8990</v>
-      </c>
-      <c r="G1422" s="6" t="s">
-        <v>8991</v>
-      </c>
-      <c r="H1422" s="6" t="s">
-        <v>6117</v>
+        <v>8998</v>
+      </c>
+      <c r="C1422" s="7" t="s">
+        <v>8999</v>
+      </c>
+      <c r="D1422" s="7" t="s">
+        <v>8999</v>
+      </c>
+      <c r="E1422" s="7" t="s">
+        <v>8999</v>
+      </c>
+      <c r="F1422" s="7" t="s">
+        <v>8999</v>
+      </c>
+      <c r="G1422" s="7" t="s">
+        <v>8999</v>
+      </c>
+      <c r="H1422" s="7" t="s">
+        <v>8999</v>
       </c>
     </row>
     <row r="1423">
       <c r="B1423" s="5" t="s">
-        <v>8992</v>
+        <v>9000</v>
       </c>
       <c r="C1423" s="5" t="s">
-        <v>8993</v>
+        <v>8411</v>
       </c>
       <c r="D1423" s="5" t="s">
-        <v>8994</v>
+        <v>8412</v>
       </c>
       <c r="E1423" s="5" t="s">
-        <v>8995</v>
+        <v>8413</v>
       </c>
       <c r="F1423" s="5" t="s">
-        <v>8996</v>
+        <v>8414</v>
       </c>
       <c r="G1423" s="5" t="s">
-        <v>8997</v>
+        <v>8415</v>
       </c>
       <c r="H1423" s="5" t="s">
-        <v>8998</v>
+        <v>8412</v>
       </c>
     </row>
     <row r="1424">
       <c r="B1424" s="6" t="s">
-        <v>8999</v>
+        <v>9001</v>
       </c>
       <c r="C1424" s="6" t="s">
-        <v>9000</v>
+        <v>9002</v>
       </c>
       <c r="D1424" s="6" t="s">
-        <v>9001</v>
+        <v>9003</v>
       </c>
       <c r="E1424" s="6" t="s">
-        <v>9002</v>
+        <v>9004</v>
       </c>
       <c r="F1424" s="6" t="s">
-        <v>9003</v>
+        <v>9005</v>
       </c>
       <c r="G1424" s="6" t="s">
-        <v>9004</v>
+        <v>9005</v>
       </c>
       <c r="H1424" s="6" t="s">
-        <v>9005</v>
+        <v>9006</v>
       </c>
     </row>
     <row r="1425">
       <c r="B1425" s="5" t="s">
-        <v>9006</v>
+        <v>9007</v>
       </c>
       <c r="C1425" s="5" t="s">
-        <v>9007</v>
+        <v>9008</v>
       </c>
       <c r="D1425" s="5" t="s">
-        <v>9008</v>
+        <v>9009</v>
       </c>
       <c r="E1425" s="5" t="s">
-        <v>9009</v>
+        <v>9010</v>
       </c>
       <c r="F1425" s="5" t="s">
-        <v>9010</v>
+        <v>9011</v>
       </c>
       <c r="G1425" s="5" t="s">
-        <v>9010</v>
+        <v>9012</v>
       </c>
       <c r="H1425" s="5" t="s">
-        <v>9011</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="1426">
       <c r="B1426" s="6" t="s">
-        <v>9012</v>
+        <v>9013</v>
       </c>
       <c r="C1426" s="6" t="s">
-        <v>9013</v>
+        <v>9014</v>
       </c>
       <c r="D1426" s="6" t="s">
-        <v>9014</v>
+        <v>9015</v>
       </c>
       <c r="E1426" s="6" t="s">
-        <v>9015</v>
+        <v>9016</v>
       </c>
       <c r="F1426" s="6" t="s">
-        <v>9016</v>
+        <v>9017</v>
       </c>
       <c r="G1426" s="6" t="s">
-        <v>9017</v>
+        <v>9018</v>
       </c>
       <c r="H1426" s="6" t="s">
-        <v>9018</v>
+        <v>9019</v>
       </c>
     </row>
     <row r="1427">
       <c r="B1427" s="5" t="s">
-        <v>9019</v>
+        <v>9020</v>
       </c>
       <c r="C1427" s="5" t="s">
-        <v>9020</v>
+        <v>9021</v>
       </c>
       <c r="D1427" s="5" t="s">
-        <v>9021</v>
+        <v>9022</v>
       </c>
       <c r="E1427" s="5" t="s">
-        <v>9022</v>
+        <v>9023</v>
       </c>
       <c r="F1427" s="5" t="s">
-        <v>9023</v>
+        <v>9024</v>
       </c>
       <c r="G1427" s="5" t="s">
-        <v>9023</v>
+        <v>9025</v>
       </c>
       <c r="H1427" s="5" t="s">
-        <v>9024</v>
+        <v>9026</v>
       </c>
     </row>
     <row r="1428">
       <c r="B1428" s="6" t="s">
-        <v>9025</v>
+        <v>9027</v>
       </c>
       <c r="C1428" s="6" t="s">
-        <v>9026</v>
+        <v>9028</v>
       </c>
       <c r="D1428" s="6" t="s">
-        <v>9026</v>
+        <v>9029</v>
       </c>
       <c r="E1428" s="6" t="s">
-        <v>9026</v>
+        <v>9030</v>
       </c>
       <c r="F1428" s="6" t="s">
-        <v>9026</v>
+        <v>9031</v>
       </c>
       <c r="G1428" s="6" t="s">
-        <v>9026</v>
+        <v>9031</v>
       </c>
       <c r="H1428" s="6" t="s">
-        <v>9026</v>
+        <v>9032</v>
       </c>
     </row>
     <row r="1429">
       <c r="B1429" s="5" t="s">
-        <v>9027</v>
+        <v>9033</v>
       </c>
       <c r="C1429" s="5" t="s">
-        <v>9028</v>
+        <v>9034</v>
       </c>
       <c r="D1429" s="5" t="s">
-        <v>9029</v>
+        <v>9035</v>
       </c>
       <c r="E1429" s="5" t="s">
-        <v>9030</v>
+        <v>9036</v>
       </c>
       <c r="F1429" s="5" t="s">
-        <v>9031</v>
+        <v>9037</v>
       </c>
       <c r="G1429" s="5" t="s">
-        <v>9031</v>
+        <v>9038</v>
       </c>
       <c r="H1429" s="5" t="s">
-        <v>9032</v>
+        <v>9039</v>
       </c>
     </row>
     <row r="1430">
       <c r="B1430" s="6" t="s">
-        <v>9033</v>
+        <v>9040</v>
       </c>
       <c r="C1430" s="6" t="s">
-        <v>9026</v>
+        <v>9041</v>
       </c>
       <c r="D1430" s="6" t="s">
-        <v>9026</v>
+        <v>9042</v>
       </c>
       <c r="E1430" s="6" t="s">
-        <v>9026</v>
+        <v>9043</v>
       </c>
       <c r="F1430" s="6" t="s">
-        <v>9026</v>
+        <v>9044</v>
       </c>
       <c r="G1430" s="6" t="s">
-        <v>9026</v>
+        <v>9044</v>
       </c>
       <c r="H1430" s="6" t="s">
-        <v>9026</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="1431">
       <c r="B1431" s="5" t="s">
-        <v>9034</v>
+        <v>9046</v>
+      </c>
+      <c r="C1431" s="5" t="s">
+        <v>9047</v>
+      </c>
+      <c r="D1431" s="5" t="s">
+        <v>9047</v>
+      </c>
+      <c r="E1431" s="5" t="s">
+        <v>9047</v>
+      </c>
+      <c r="F1431" s="5" t="s">
+        <v>9047</v>
+      </c>
+      <c r="G1431" s="5" t="s">
+        <v>9047</v>
+      </c>
+      <c r="H1431" s="5" t="s">
+        <v>9047</v>
       </c>
     </row>
     <row r="1432">
       <c r="B1432" s="6" t="s">
-        <v>9035</v>
+        <v>9048</v>
       </c>
       <c r="C1432" s="6" t="s">
-        <v>9036</v>
+        <v>9049</v>
       </c>
       <c r="D1432" s="6" t="s">
-        <v>9037</v>
+        <v>9050</v>
       </c>
       <c r="E1432" s="6" t="s">
-        <v>9038</v>
+        <v>9051</v>
       </c>
       <c r="F1432" s="6" t="s">
-        <v>9039</v>
+        <v>9052</v>
       </c>
       <c r="G1432" s="6" t="s">
-        <v>9040</v>
+        <v>9052</v>
       </c>
       <c r="H1432" s="6" t="s">
-        <v>9041</v>
+        <v>9053</v>
       </c>
     </row>
     <row r="1433">
       <c r="B1433" s="5" t="s">
-        <v>9042</v>
+        <v>9054</v>
       </c>
       <c r="C1433" s="5" t="s">
-        <v>9043</v>
+        <v>9047</v>
       </c>
       <c r="D1433" s="5" t="s">
-        <v>9044</v>
+        <v>9047</v>
       </c>
       <c r="E1433" s="5" t="s">
-        <v>9045</v>
+        <v>9047</v>
       </c>
       <c r="F1433" s="5" t="s">
-        <v>9046</v>
+        <v>9047</v>
       </c>
       <c r="G1433" s="5" t="s">
         <v>9047</v>
       </c>
       <c r="H1433" s="5" t="s">
-        <v>9048</v>
+        <v>9047</v>
       </c>
     </row>
     <row r="1434">
       <c r="B1434" s="6" t="s">
-        <v>9049</v>
-      </c>
-      <c r="C1434" s="6" t="s">
-        <v>9050</v>
-      </c>
-      <c r="D1434" s="6" t="s">
-        <v>9051</v>
-      </c>
-      <c r="E1434" s="6" t="s">
-        <v>9052</v>
-      </c>
-      <c r="F1434" s="6" t="s">
-        <v>9053</v>
-      </c>
-      <c r="G1434" s="6" t="s">
-        <v>9054</v>
-      </c>
-      <c r="H1434" s="6" t="s">
         <v>9055</v>
       </c>
     </row>
@@ -62355,85 +62418,85 @@
         <v>9063</v>
       </c>
       <c r="C1436" s="6" t="s">
-        <v>6112</v>
+        <v>9064</v>
       </c>
       <c r="D1436" s="6" t="s">
-        <v>9064</v>
+        <v>9065</v>
       </c>
       <c r="E1436" s="6" t="s">
-        <v>6114</v>
+        <v>9066</v>
       </c>
       <c r="F1436" s="6" t="s">
-        <v>9065</v>
+        <v>9067</v>
       </c>
       <c r="G1436" s="6" t="s">
-        <v>9065</v>
+        <v>9068</v>
       </c>
       <c r="H1436" s="6" t="s">
-        <v>9066</v>
+        <v>9069</v>
       </c>
     </row>
     <row r="1437">
       <c r="B1437" s="5" t="s">
-        <v>9067</v>
+        <v>9070</v>
       </c>
       <c r="C1437" s="5" t="s">
-        <v>9068</v>
+        <v>9071</v>
       </c>
       <c r="D1437" s="5" t="s">
-        <v>9069</v>
+        <v>9072</v>
       </c>
       <c r="E1437" s="5" t="s">
-        <v>9070</v>
+        <v>9073</v>
       </c>
       <c r="F1437" s="5" t="s">
-        <v>9071</v>
+        <v>9074</v>
       </c>
       <c r="G1437" s="5" t="s">
-        <v>9072</v>
+        <v>9075</v>
       </c>
       <c r="H1437" s="5" t="s">
-        <v>9073</v>
+        <v>9076</v>
       </c>
     </row>
     <row r="1438">
       <c r="B1438" s="6" t="s">
-        <v>9074</v>
+        <v>9077</v>
       </c>
       <c r="C1438" s="6" t="s">
-        <v>9075</v>
+        <v>9078</v>
       </c>
       <c r="D1438" s="6" t="s">
-        <v>9076</v>
+        <v>9079</v>
       </c>
       <c r="E1438" s="6" t="s">
-        <v>9077</v>
+        <v>9080</v>
       </c>
       <c r="F1438" s="6" t="s">
-        <v>9078</v>
+        <v>9081</v>
       </c>
       <c r="G1438" s="6" t="s">
-        <v>9079</v>
+        <v>9082</v>
       </c>
       <c r="H1438" s="6" t="s">
-        <v>9080</v>
+        <v>9083</v>
       </c>
     </row>
     <row r="1439">
       <c r="B1439" s="5" t="s">
-        <v>9081</v>
+        <v>9084</v>
       </c>
       <c r="C1439" s="5" t="s">
-        <v>9082</v>
+        <v>6112</v>
       </c>
       <c r="D1439" s="5" t="s">
-        <v>9083</v>
+        <v>9085</v>
       </c>
       <c r="E1439" s="5" t="s">
-        <v>9084</v>
+        <v>6114</v>
       </c>
       <c r="F1439" s="5" t="s">
-        <v>9085</v>
+        <v>9086</v>
       </c>
       <c r="G1439" s="5" t="s">
         <v>9086</v>
@@ -62496,197 +62559,197 @@
         <v>9103</v>
       </c>
       <c r="D1442" s="6" t="s">
-        <v>9103</v>
+        <v>9104</v>
       </c>
       <c r="E1442" s="6" t="s">
-        <v>9103</v>
+        <v>9105</v>
       </c>
       <c r="F1442" s="6" t="s">
-        <v>9103</v>
+        <v>9106</v>
       </c>
       <c r="G1442" s="6" t="s">
-        <v>9103</v>
+        <v>9107</v>
       </c>
       <c r="H1442" s="6" t="s">
-        <v>9103</v>
+        <v>9108</v>
       </c>
     </row>
     <row r="1443">
       <c r="B1443" s="5" t="s">
-        <v>9104</v>
+        <v>9109</v>
       </c>
       <c r="C1443" s="5" t="s">
-        <v>9105</v>
+        <v>9110</v>
       </c>
       <c r="D1443" s="5" t="s">
-        <v>9106</v>
+        <v>9111</v>
       </c>
       <c r="E1443" s="5" t="s">
-        <v>9107</v>
+        <v>9112</v>
       </c>
       <c r="F1443" s="5" t="s">
-        <v>9108</v>
+        <v>9113</v>
       </c>
       <c r="G1443" s="5" t="s">
-        <v>9108</v>
+        <v>9114</v>
       </c>
       <c r="H1443" s="5" t="s">
-        <v>9109</v>
+        <v>9115</v>
       </c>
     </row>
     <row r="1444">
       <c r="B1444" s="6" t="s">
-        <v>9110</v>
+        <v>9116</v>
       </c>
       <c r="C1444" s="6" t="s">
-        <v>9111</v>
+        <v>9117</v>
       </c>
       <c r="D1444" s="6" t="s">
-        <v>9112</v>
+        <v>9118</v>
       </c>
       <c r="E1444" s="6" t="s">
-        <v>9113</v>
+        <v>9119</v>
       </c>
       <c r="F1444" s="6" t="s">
-        <v>9114</v>
+        <v>9120</v>
       </c>
       <c r="G1444" s="6" t="s">
-        <v>9115</v>
+        <v>9121</v>
       </c>
       <c r="H1444" s="6" t="s">
-        <v>9116</v>
+        <v>9122</v>
       </c>
     </row>
     <row r="1445">
       <c r="B1445" s="5" t="s">
-        <v>9117</v>
+        <v>9123</v>
       </c>
       <c r="C1445" s="5" t="s">
-        <v>9118</v>
+        <v>9124</v>
       </c>
       <c r="D1445" s="5" t="s">
-        <v>9119</v>
+        <v>9124</v>
       </c>
       <c r="E1445" s="5" t="s">
-        <v>9120</v>
+        <v>9124</v>
       </c>
       <c r="F1445" s="5" t="s">
-        <v>9121</v>
+        <v>9124</v>
       </c>
       <c r="G1445" s="5" t="s">
-        <v>9122</v>
+        <v>9124</v>
       </c>
       <c r="H1445" s="5" t="s">
-        <v>9123</v>
+        <v>9124</v>
       </c>
     </row>
     <row r="1446">
       <c r="B1446" s="6" t="s">
-        <v>9124</v>
+        <v>9125</v>
       </c>
       <c r="C1446" s="6" t="s">
-        <v>9125</v>
+        <v>9126</v>
       </c>
       <c r="D1446" s="6" t="s">
-        <v>9126</v>
+        <v>9127</v>
       </c>
       <c r="E1446" s="6" t="s">
-        <v>9127</v>
+        <v>9128</v>
       </c>
       <c r="F1446" s="6" t="s">
-        <v>9128</v>
+        <v>9129</v>
       </c>
       <c r="G1446" s="6" t="s">
-        <v>9128</v>
+        <v>9129</v>
       </c>
       <c r="H1446" s="6" t="s">
-        <v>9129</v>
+        <v>9130</v>
       </c>
     </row>
     <row r="1447">
       <c r="B1447" s="5" t="s">
-        <v>9130</v>
+        <v>9131</v>
       </c>
       <c r="C1447" s="5" t="s">
-        <v>9131</v>
+        <v>9132</v>
       </c>
       <c r="D1447" s="5" t="s">
-        <v>9132</v>
+        <v>9133</v>
       </c>
       <c r="E1447" s="5" t="s">
-        <v>9133</v>
+        <v>9134</v>
       </c>
       <c r="F1447" s="5" t="s">
-        <v>9134</v>
+        <v>9135</v>
       </c>
       <c r="G1447" s="5" t="s">
-        <v>9134</v>
+        <v>9136</v>
       </c>
       <c r="H1447" s="5" t="s">
-        <v>9135</v>
+        <v>9137</v>
       </c>
     </row>
     <row r="1448">
       <c r="B1448" s="6" t="s">
-        <v>9136</v>
+        <v>9138</v>
       </c>
       <c r="C1448" s="6" t="s">
-        <v>9137</v>
+        <v>9139</v>
       </c>
       <c r="D1448" s="6" t="s">
-        <v>9138</v>
+        <v>9140</v>
       </c>
       <c r="E1448" s="6" t="s">
-        <v>9139</v>
+        <v>9141</v>
       </c>
       <c r="F1448" s="6" t="s">
-        <v>9140</v>
+        <v>9142</v>
       </c>
       <c r="G1448" s="6" t="s">
-        <v>9141</v>
+        <v>9143</v>
       </c>
       <c r="H1448" s="6" t="s">
-        <v>9142</v>
+        <v>9144</v>
       </c>
     </row>
     <row r="1449">
       <c r="B1449" s="5" t="s">
-        <v>9143</v>
+        <v>9145</v>
       </c>
       <c r="C1449" s="5" t="s">
-        <v>9144</v>
+        <v>9146</v>
       </c>
       <c r="D1449" s="5" t="s">
-        <v>9145</v>
+        <v>9147</v>
       </c>
       <c r="E1449" s="5" t="s">
-        <v>9146</v>
+        <v>9148</v>
       </c>
       <c r="F1449" s="5" t="s">
-        <v>9147</v>
+        <v>9149</v>
       </c>
       <c r="G1449" s="5" t="s">
-        <v>9148</v>
+        <v>9149</v>
       </c>
       <c r="H1449" s="5" t="s">
-        <v>9149</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="1450">
       <c r="B1450" s="6" t="s">
-        <v>9150</v>
+        <v>9151</v>
       </c>
       <c r="C1450" s="6" t="s">
-        <v>9151</v>
+        <v>9152</v>
       </c>
       <c r="D1450" s="6" t="s">
-        <v>9152</v>
+        <v>9153</v>
       </c>
       <c r="E1450" s="6" t="s">
-        <v>9153</v>
+        <v>9154</v>
       </c>
       <c r="F1450" s="6" t="s">
-        <v>9154</v>
+        <v>9155</v>
       </c>
       <c r="G1450" s="6" t="s">
         <v>9155</v>
@@ -62838,525 +62901,525 @@
         <v>9199</v>
       </c>
       <c r="C1457" s="5" t="s">
-        <v>4582</v>
+        <v>9200</v>
       </c>
       <c r="D1457" s="5" t="s">
-        <v>9200</v>
+        <v>9201</v>
       </c>
       <c r="E1457" s="5" t="s">
-        <v>4584</v>
+        <v>9202</v>
       </c>
       <c r="F1457" s="5" t="s">
-        <v>9201</v>
+        <v>9203</v>
       </c>
       <c r="G1457" s="5" t="s">
-        <v>9202</v>
+        <v>9204</v>
       </c>
       <c r="H1457" s="5" t="s">
-        <v>9203</v>
+        <v>9205</v>
       </c>
     </row>
     <row r="1458">
       <c r="B1458" s="6" t="s">
-        <v>9204</v>
+        <v>9206</v>
       </c>
       <c r="C1458" s="6" t="s">
-        <v>9205</v>
+        <v>9207</v>
       </c>
       <c r="D1458" s="6" t="s">
-        <v>9206</v>
+        <v>9208</v>
       </c>
       <c r="E1458" s="6" t="s">
-        <v>9207</v>
+        <v>9209</v>
       </c>
       <c r="F1458" s="6" t="s">
-        <v>9208</v>
+        <v>9210</v>
       </c>
       <c r="G1458" s="6" t="s">
-        <v>9209</v>
+        <v>9211</v>
       </c>
       <c r="H1458" s="6" t="s">
-        <v>9210</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="1459">
       <c r="B1459" s="5" t="s">
-        <v>9211</v>
+        <v>9213</v>
       </c>
       <c r="C1459" s="5" t="s">
-        <v>9212</v>
+        <v>9214</v>
       </c>
       <c r="D1459" s="5" t="s">
-        <v>9213</v>
+        <v>9215</v>
+      </c>
+      <c r="E1459" s="5" t="s">
+        <v>9216</v>
+      </c>
+      <c r="F1459" s="5" t="s">
+        <v>9217</v>
+      </c>
+      <c r="G1459" s="5" t="s">
+        <v>9218</v>
+      </c>
+      <c r="H1459" s="5" t="s">
+        <v>9219</v>
       </c>
     </row>
     <row r="1460">
       <c r="B1460" s="6" t="s">
-        <v>9214</v>
+        <v>9220</v>
       </c>
       <c r="C1460" s="6" t="s">
-        <v>9215</v>
+        <v>4582</v>
       </c>
       <c r="D1460" s="6" t="s">
-        <v>9216</v>
+        <v>9221</v>
+      </c>
+      <c r="E1460" s="6" t="s">
+        <v>4584</v>
+      </c>
+      <c r="F1460" s="6" t="s">
+        <v>9222</v>
+      </c>
+      <c r="G1460" s="6" t="s">
+        <v>9223</v>
+      </c>
+      <c r="H1460" s="6" t="s">
+        <v>9224</v>
       </c>
     </row>
     <row r="1461">
       <c r="B1461" s="5" t="s">
-        <v>9217</v>
+        <v>9225</v>
       </c>
       <c r="C1461" s="5" t="s">
-        <v>9218</v>
+        <v>9226</v>
       </c>
       <c r="D1461" s="5" t="s">
-        <v>9219</v>
+        <v>9227</v>
+      </c>
+      <c r="E1461" s="5" t="s">
+        <v>9228</v>
+      </c>
+      <c r="F1461" s="5" t="s">
+        <v>9229</v>
+      </c>
+      <c r="G1461" s="5" t="s">
+        <v>9230</v>
+      </c>
+      <c r="H1461" s="5" t="s">
+        <v>9231</v>
       </c>
     </row>
     <row r="1462">
       <c r="B1462" s="6" t="s">
-        <v>9220</v>
+        <v>9232</v>
       </c>
       <c r="C1462" s="6" t="s">
-        <v>9221</v>
+        <v>9233</v>
       </c>
       <c r="D1462" s="6" t="s">
-        <v>9222</v>
+        <v>9234</v>
       </c>
     </row>
     <row r="1463">
       <c r="B1463" s="5" t="s">
-        <v>9223</v>
+        <v>9235</v>
       </c>
       <c r="C1463" s="5" t="s">
-        <v>9224</v>
+        <v>9236</v>
       </c>
       <c r="D1463" s="5" t="s">
-        <v>9225</v>
+        <v>9237</v>
       </c>
     </row>
     <row r="1464">
       <c r="B1464" s="6" t="s">
-        <v>9226</v>
+        <v>9238</v>
       </c>
       <c r="C1464" s="6" t="s">
-        <v>9227</v>
+        <v>9239</v>
       </c>
       <c r="D1464" s="6" t="s">
-        <v>9228</v>
+        <v>9240</v>
       </c>
     </row>
     <row r="1465">
       <c r="B1465" s="5" t="s">
-        <v>9229</v>
+        <v>9241</v>
       </c>
       <c r="C1465" s="5" t="s">
-        <v>9230</v>
+        <v>9242</v>
       </c>
       <c r="D1465" s="5" t="s">
-        <v>9231</v>
+        <v>9243</v>
       </c>
     </row>
     <row r="1466">
       <c r="B1466" s="6" t="s">
-        <v>9232</v>
+        <v>9244</v>
       </c>
       <c r="C1466" s="6" t="s">
-        <v>9233</v>
+        <v>9245</v>
       </c>
       <c r="D1466" s="6" t="s">
-        <v>9234</v>
-      </c>
-      <c r="E1466" s="6" t="s">
-        <v>9235</v>
-      </c>
-      <c r="F1466" s="6" t="s">
-        <v>9236</v>
-      </c>
-      <c r="G1466" s="6" t="s">
-        <v>9237</v>
-      </c>
-      <c r="H1466" s="6" t="s">
-        <v>9238</v>
+        <v>9246</v>
       </c>
     </row>
     <row r="1467">
       <c r="B1467" s="5" t="s">
-        <v>9239</v>
+        <v>9247</v>
       </c>
       <c r="C1467" s="5" t="s">
-        <v>9240</v>
+        <v>9248</v>
       </c>
       <c r="D1467" s="5" t="s">
-        <v>9241</v>
+        <v>9249</v>
       </c>
     </row>
     <row r="1468">
       <c r="B1468" s="6" t="s">
-        <v>9242</v>
+        <v>9250</v>
       </c>
       <c r="C1468" s="6" t="s">
-        <v>9243</v>
+        <v>9251</v>
       </c>
       <c r="D1468" s="6" t="s">
-        <v>9244</v>
+        <v>9252</v>
       </c>
     </row>
     <row r="1469">
       <c r="B1469" s="5" t="s">
-        <v>9245</v>
+        <v>9253</v>
       </c>
       <c r="C1469" s="5" t="s">
-        <v>9246</v>
+        <v>9254</v>
       </c>
       <c r="D1469" s="5" t="s">
-        <v>9247</v>
+        <v>9255</v>
+      </c>
+      <c r="E1469" s="5" t="s">
+        <v>9256</v>
+      </c>
+      <c r="F1469" s="5" t="s">
+        <v>9257</v>
+      </c>
+      <c r="G1469" s="5" t="s">
+        <v>9258</v>
+      </c>
+      <c r="H1469" s="5" t="s">
+        <v>9259</v>
       </c>
     </row>
     <row r="1470">
       <c r="B1470" s="6" t="s">
-        <v>9248</v>
+        <v>9260</v>
       </c>
       <c r="C1470" s="6" t="s">
-        <v>6112</v>
+        <v>9261</v>
       </c>
       <c r="D1470" s="6" t="s">
-        <v>9064</v>
+        <v>9262</v>
       </c>
     </row>
     <row r="1471">
       <c r="B1471" s="5" t="s">
-        <v>9249</v>
+        <v>9263</v>
       </c>
       <c r="C1471" s="5" t="s">
-        <v>9250</v>
+        <v>9264</v>
       </c>
       <c r="D1471" s="5" t="s">
-        <v>9251</v>
+        <v>9265</v>
       </c>
     </row>
     <row r="1472">
       <c r="B1472" s="6" t="s">
-        <v>9252</v>
+        <v>9266</v>
       </c>
       <c r="C1472" s="6" t="s">
-        <v>9253</v>
+        <v>9267</v>
       </c>
       <c r="D1472" s="6" t="s">
-        <v>9254</v>
+        <v>9268</v>
       </c>
     </row>
     <row r="1473">
       <c r="B1473" s="5" t="s">
-        <v>9255</v>
+        <v>9269</v>
       </c>
       <c r="C1473" s="5" t="s">
-        <v>9256</v>
+        <v>6112</v>
       </c>
       <c r="D1473" s="5" t="s">
-        <v>9257</v>
+        <v>9085</v>
       </c>
     </row>
     <row r="1474">
       <c r="B1474" s="6" t="s">
-        <v>9258</v>
+        <v>9270</v>
       </c>
       <c r="C1474" s="6" t="s">
-        <v>9259</v>
+        <v>9271</v>
       </c>
       <c r="D1474" s="6" t="s">
-        <v>9260</v>
+        <v>9272</v>
       </c>
     </row>
     <row r="1475">
       <c r="B1475" s="5" t="s">
-        <v>9261</v>
+        <v>9273</v>
       </c>
       <c r="C1475" s="5" t="s">
-        <v>9262</v>
+        <v>9274</v>
       </c>
       <c r="D1475" s="5" t="s">
-        <v>9263</v>
+        <v>9275</v>
       </c>
     </row>
     <row r="1476">
       <c r="B1476" s="6" t="s">
-        <v>9264</v>
+        <v>9276</v>
       </c>
       <c r="C1476" s="6" t="s">
-        <v>9265</v>
+        <v>9277</v>
       </c>
       <c r="D1476" s="6" t="s">
-        <v>9266</v>
+        <v>9278</v>
       </c>
     </row>
     <row r="1477">
       <c r="B1477" s="5" t="s">
-        <v>9267</v>
+        <v>9279</v>
       </c>
       <c r="C1477" s="5" t="s">
-        <v>9268</v>
+        <v>9280</v>
       </c>
       <c r="D1477" s="5" t="s">
-        <v>9269</v>
-      </c>
-      <c r="E1477" s="5" t="s">
-        <v>9270</v>
-      </c>
-      <c r="F1477" s="5" t="s">
-        <v>9271</v>
-      </c>
-      <c r="G1477" s="5" t="s">
-        <v>9271</v>
-      </c>
-      <c r="H1477" s="5" t="s">
-        <v>9272</v>
+        <v>9281</v>
       </c>
     </row>
     <row r="1478">
       <c r="B1478" s="6" t="s">
-        <v>9273</v>
+        <v>9282</v>
       </c>
       <c r="C1478" s="6" t="s">
-        <v>9274</v>
+        <v>9283</v>
       </c>
       <c r="D1478" s="6" t="s">
-        <v>9275</v>
-      </c>
-      <c r="E1478" s="6" t="s">
-        <v>9276</v>
-      </c>
-      <c r="F1478" s="6" t="s">
-        <v>9277</v>
-      </c>
-      <c r="G1478" s="6" t="s">
-        <v>9276</v>
-      </c>
-      <c r="H1478" s="6" t="s">
-        <v>9278</v>
+        <v>9284</v>
       </c>
     </row>
     <row r="1479">
       <c r="B1479" s="5" t="s">
-        <v>9279</v>
+        <v>9285</v>
       </c>
       <c r="C1479" s="5" t="s">
-        <v>9280</v>
+        <v>9286</v>
       </c>
       <c r="D1479" s="5" t="s">
-        <v>9281</v>
-      </c>
-      <c r="E1479" s="5" t="s">
-        <v>7913</v>
-      </c>
-      <c r="F1479" s="5" t="s">
-        <v>7914</v>
-      </c>
-      <c r="G1479" s="5" t="s">
-        <v>7914</v>
-      </c>
-      <c r="H1479" s="5" t="s">
-        <v>7915</v>
+        <v>9287</v>
       </c>
     </row>
     <row r="1480">
       <c r="B1480" s="6" t="s">
-        <v>9282</v>
+        <v>9288</v>
       </c>
       <c r="C1480" s="6" t="s">
-        <v>9283</v>
+        <v>9289</v>
       </c>
       <c r="D1480" s="6" t="s">
-        <v>9284</v>
+        <v>9290</v>
       </c>
       <c r="E1480" s="6" t="s">
-        <v>9285</v>
+        <v>9291</v>
       </c>
       <c r="F1480" s="6" t="s">
-        <v>9286</v>
+        <v>9292</v>
       </c>
       <c r="G1480" s="6" t="s">
-        <v>9286</v>
+        <v>9292</v>
       </c>
       <c r="H1480" s="6" t="s">
-        <v>9287</v>
+        <v>9293</v>
       </c>
     </row>
     <row r="1481">
       <c r="B1481" s="5" t="s">
-        <v>9288</v>
+        <v>9294</v>
       </c>
       <c r="C1481" s="5" t="s">
-        <v>9289</v>
+        <v>9295</v>
       </c>
       <c r="D1481" s="5" t="s">
-        <v>8917</v>
+        <v>9296</v>
       </c>
       <c r="E1481" s="5" t="s">
-        <v>9290</v>
+        <v>9297</v>
       </c>
       <c r="F1481" s="5" t="s">
-        <v>9291</v>
+        <v>9298</v>
       </c>
       <c r="G1481" s="5" t="s">
-        <v>9291</v>
+        <v>9297</v>
       </c>
       <c r="H1481" s="5" t="s">
-        <v>8921</v>
+        <v>9299</v>
       </c>
     </row>
     <row r="1482">
       <c r="B1482" s="6" t="s">
-        <v>9292</v>
+        <v>9300</v>
       </c>
       <c r="C1482" s="6" t="s">
-        <v>9293</v>
+        <v>9301</v>
       </c>
       <c r="D1482" s="6" t="s">
-        <v>7245</v>
+        <v>9302</v>
       </c>
       <c r="E1482" s="6" t="s">
-        <v>5935</v>
+        <v>7934</v>
       </c>
       <c r="F1482" s="6" t="s">
-        <v>9294</v>
+        <v>7935</v>
       </c>
       <c r="G1482" s="6" t="s">
-        <v>9294</v>
+        <v>7935</v>
       </c>
       <c r="H1482" s="6" t="s">
-        <v>5938</v>
+        <v>7936</v>
       </c>
     </row>
     <row r="1483">
       <c r="B1483" s="5" t="s">
-        <v>9295</v>
+        <v>9303</v>
       </c>
       <c r="C1483" s="5" t="s">
-        <v>9296</v>
+        <v>9304</v>
       </c>
       <c r="D1483" s="5" t="s">
-        <v>9297</v>
+        <v>9305</v>
       </c>
       <c r="E1483" s="5" t="s">
-        <v>9298</v>
+        <v>9306</v>
       </c>
       <c r="F1483" s="5" t="s">
-        <v>9299</v>
+        <v>9307</v>
       </c>
       <c r="G1483" s="5" t="s">
-        <v>9300</v>
+        <v>9307</v>
       </c>
       <c r="H1483" s="5" t="s">
-        <v>9301</v>
+        <v>9308</v>
       </c>
     </row>
     <row r="1484">
       <c r="B1484" s="6" t="s">
-        <v>9302</v>
+        <v>9309</v>
       </c>
       <c r="C1484" s="6" t="s">
-        <v>9303</v>
+        <v>9310</v>
       </c>
       <c r="D1484" s="6" t="s">
-        <v>9304</v>
+        <v>8938</v>
       </c>
       <c r="E1484" s="6" t="s">
-        <v>9305</v>
+        <v>9311</v>
       </c>
       <c r="F1484" s="6" t="s">
-        <v>9306</v>
+        <v>9312</v>
       </c>
       <c r="G1484" s="6" t="s">
-        <v>9307</v>
+        <v>9312</v>
       </c>
       <c r="H1484" s="6" t="s">
-        <v>9308</v>
+        <v>8942</v>
       </c>
     </row>
     <row r="1485">
       <c r="B1485" s="5" t="s">
-        <v>9309</v>
+        <v>9313</v>
       </c>
       <c r="C1485" s="5" t="s">
-        <v>9310</v>
+        <v>9314</v>
       </c>
       <c r="D1485" s="5" t="s">
-        <v>9311</v>
+        <v>7245</v>
       </c>
       <c r="E1485" s="5" t="s">
-        <v>9312</v>
+        <v>5935</v>
       </c>
       <c r="F1485" s="5" t="s">
-        <v>9313</v>
+        <v>9315</v>
       </c>
       <c r="G1485" s="5" t="s">
-        <v>9313</v>
+        <v>9315</v>
       </c>
       <c r="H1485" s="5" t="s">
-        <v>9314</v>
+        <v>5938</v>
       </c>
     </row>
     <row r="1486">
       <c r="B1486" s="6" t="s">
-        <v>9315</v>
+        <v>9316</v>
       </c>
       <c r="C1486" s="6" t="s">
-        <v>9316</v>
+        <v>9317</v>
       </c>
       <c r="D1486" s="6" t="s">
-        <v>9317</v>
+        <v>9318</v>
       </c>
       <c r="E1486" s="6" t="s">
-        <v>9318</v>
+        <v>9319</v>
       </c>
       <c r="F1486" s="6" t="s">
-        <v>9319</v>
+        <v>9320</v>
       </c>
       <c r="G1486" s="6" t="s">
-        <v>9320</v>
+        <v>9321</v>
       </c>
       <c r="H1486" s="6" t="s">
-        <v>9321</v>
+        <v>9322</v>
       </c>
     </row>
     <row r="1487">
       <c r="B1487" s="5" t="s">
-        <v>9322</v>
+        <v>9323</v>
       </c>
       <c r="C1487" s="5" t="s">
-        <v>9323</v>
+        <v>9324</v>
       </c>
       <c r="D1487" s="5" t="s">
-        <v>9324</v>
+        <v>9325</v>
       </c>
       <c r="E1487" s="5" t="s">
-        <v>9325</v>
+        <v>9326</v>
       </c>
       <c r="F1487" s="5" t="s">
-        <v>9326</v>
+        <v>9327</v>
       </c>
       <c r="G1487" s="5" t="s">
-        <v>9327</v>
+        <v>9328</v>
       </c>
       <c r="H1487" s="5" t="s">
-        <v>9328</v>
+        <v>9329</v>
       </c>
     </row>
     <row r="1488">
       <c r="B1488" s="6" t="s">
-        <v>9329</v>
+        <v>9330</v>
       </c>
       <c r="C1488" s="6" t="s">
-        <v>9330</v>
+        <v>9331</v>
       </c>
       <c r="D1488" s="6" t="s">
-        <v>9331</v>
+        <v>9332</v>
       </c>
       <c r="E1488" s="6" t="s">
-        <v>9332</v>
+        <v>9333</v>
       </c>
       <c r="F1488" s="6" t="s">
-        <v>9333</v>
+        <v>9334</v>
       </c>
       <c r="G1488" s="6" t="s">
         <v>9334</v>
@@ -63393,108 +63456,108 @@
         <v>9343</v>
       </c>
       <c r="C1490" s="6" t="s">
-        <v>4537</v>
+        <v>9344</v>
       </c>
       <c r="D1490" s="6" t="s">
-        <v>9344</v>
+        <v>9345</v>
       </c>
       <c r="E1490" s="6" t="s">
-        <v>7438</v>
+        <v>9346</v>
       </c>
       <c r="F1490" s="6" t="s">
-        <v>9345</v>
+        <v>9347</v>
       </c>
       <c r="G1490" s="6" t="s">
-        <v>9346</v>
+  